--- a/Download/Focus_Positivi_ZR.xlsx
+++ b/Download/Focus_Positivi_ZR.xlsx
@@ -4023,7 +4023,7 @@
         <v>46079.0</v>
       </c>
       <c r="D278" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="279">
@@ -7879,7 +7879,7 @@
         <v>11</v>
       </c>
       <c r="B3" t="n">
-        <v>168.0</v>
+        <v>169.0</v>
       </c>
     </row>
     <row r="4">
@@ -7895,7 +7895,7 @@
         <v>13</v>
       </c>
       <c r="B5" t="n">
-        <v>1981.0</v>
+        <v>1983.0</v>
       </c>
     </row>
   </sheetData>
@@ -7993,7 +7993,7 @@
         <v>21</v>
       </c>
       <c r="C8" t="n">
-        <v>338.0</v>
+        <v>339.0</v>
       </c>
     </row>
     <row r="9">
@@ -8059,7 +8059,7 @@
         <v>19</v>
       </c>
       <c r="C14" t="n">
-        <v>314.0</v>
+        <v>315.0</v>
       </c>
     </row>
     <row r="15">
@@ -8081,7 +8081,7 @@
         <v>22</v>
       </c>
       <c r="C16" t="n">
-        <v>327.0</v>
+        <v>328.0</v>
       </c>
     </row>
     <row r="17">

--- a/Download/Focus_Positivi_ZR.xlsx
+++ b/Download/Focus_Positivi_ZR.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="595" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="600" uniqueCount="23">
   <si>
     <t>NOME_REGIONE</t>
   </si>
@@ -1494,30 +1494,30 @@
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B98" t="n">
-        <v>2021.0</v>
+        <v>2026.0</v>
       </c>
       <c r="C98" t="n" s="2">
-        <v>44561.0</v>
+        <v>46086.0</v>
       </c>
       <c r="D98" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B99" t="n">
-        <v>2022.0</v>
+        <v>2026.0</v>
       </c>
       <c r="C99" t="n" s="2">
-        <v>44576.0</v>
+        <v>46093.0</v>
       </c>
       <c r="D99" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="100">
@@ -1525,13 +1525,13 @@
         <v>5</v>
       </c>
       <c r="B100" t="n">
-        <v>2022.0</v>
+        <v>2021.0</v>
       </c>
       <c r="C100" t="n" s="2">
-        <v>44583.0</v>
+        <v>44561.0</v>
       </c>
       <c r="D100" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="101">
@@ -1542,10 +1542,10 @@
         <v>2022.0</v>
       </c>
       <c r="C101" t="n" s="2">
-        <v>44590.0</v>
+        <v>44576.0</v>
       </c>
       <c r="D101" t="n">
-        <v>7.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="102">
@@ -1556,10 +1556,10 @@
         <v>2022.0</v>
       </c>
       <c r="C102" t="n" s="2">
-        <v>44597.0</v>
+        <v>44583.0</v>
       </c>
       <c r="D102" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="103">
@@ -1570,10 +1570,10 @@
         <v>2022.0</v>
       </c>
       <c r="C103" t="n" s="2">
-        <v>44604.0</v>
+        <v>44590.0</v>
       </c>
       <c r="D103" t="n">
-        <v>2.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="104">
@@ -1584,10 +1584,10 @@
         <v>2022.0</v>
       </c>
       <c r="C104" t="n" s="2">
-        <v>44611.0</v>
+        <v>44597.0</v>
       </c>
       <c r="D104" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="105">
@@ -1598,10 +1598,10 @@
         <v>2022.0</v>
       </c>
       <c r="C105" t="n" s="2">
-        <v>44618.0</v>
+        <v>44604.0</v>
       </c>
       <c r="D105" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="106">
@@ -1612,10 +1612,10 @@
         <v>2022.0</v>
       </c>
       <c r="C106" t="n" s="2">
-        <v>44625.0</v>
+        <v>44611.0</v>
       </c>
       <c r="D106" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="107">
@@ -1626,10 +1626,10 @@
         <v>2022.0</v>
       </c>
       <c r="C107" t="n" s="2">
-        <v>44632.0</v>
+        <v>44618.0</v>
       </c>
       <c r="D107" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="108">
@@ -1640,7 +1640,7 @@
         <v>2022.0</v>
       </c>
       <c r="C108" t="n" s="2">
-        <v>44639.0</v>
+        <v>44625.0</v>
       </c>
       <c r="D108" t="n">
         <v>2.0</v>
@@ -1654,10 +1654,10 @@
         <v>2022.0</v>
       </c>
       <c r="C109" t="n" s="2">
-        <v>44646.0</v>
+        <v>44632.0</v>
       </c>
       <c r="D109" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="110">
@@ -1668,7 +1668,7 @@
         <v>2022.0</v>
       </c>
       <c r="C110" t="n" s="2">
-        <v>44653.0</v>
+        <v>44639.0</v>
       </c>
       <c r="D110" t="n">
         <v>2.0</v>
@@ -1682,10 +1682,10 @@
         <v>2022.0</v>
       </c>
       <c r="C111" t="n" s="2">
-        <v>44660.0</v>
+        <v>44646.0</v>
       </c>
       <c r="D111" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="112">
@@ -1696,10 +1696,10 @@
         <v>2022.0</v>
       </c>
       <c r="C112" t="n" s="2">
-        <v>44667.0</v>
+        <v>44653.0</v>
       </c>
       <c r="D112" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="113">
@@ -1710,10 +1710,10 @@
         <v>2022.0</v>
       </c>
       <c r="C113" t="n" s="2">
-        <v>44674.0</v>
+        <v>44660.0</v>
       </c>
       <c r="D113" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="114">
@@ -1724,10 +1724,10 @@
         <v>2022.0</v>
       </c>
       <c r="C114" t="n" s="2">
-        <v>44681.0</v>
+        <v>44667.0</v>
       </c>
       <c r="D114" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="115">
@@ -1738,7 +1738,7 @@
         <v>2022.0</v>
       </c>
       <c r="C115" t="n" s="2">
-        <v>44688.0</v>
+        <v>44674.0</v>
       </c>
       <c r="D115" t="n">
         <v>3.0</v>
@@ -1752,10 +1752,10 @@
         <v>2022.0</v>
       </c>
       <c r="C116" t="n" s="2">
-        <v>44695.0</v>
+        <v>44681.0</v>
       </c>
       <c r="D116" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="117">
@@ -1766,10 +1766,10 @@
         <v>2022.0</v>
       </c>
       <c r="C117" t="n" s="2">
-        <v>44702.0</v>
+        <v>44688.0</v>
       </c>
       <c r="D117" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="118">
@@ -1780,7 +1780,7 @@
         <v>2022.0</v>
       </c>
       <c r="C118" t="n" s="2">
-        <v>44709.0</v>
+        <v>44695.0</v>
       </c>
       <c r="D118" t="n">
         <v>3.0</v>
@@ -1794,10 +1794,10 @@
         <v>2022.0</v>
       </c>
       <c r="C119" t="n" s="2">
-        <v>44716.0</v>
+        <v>44702.0</v>
       </c>
       <c r="D119" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="120">
@@ -1808,10 +1808,10 @@
         <v>2022.0</v>
       </c>
       <c r="C120" t="n" s="2">
-        <v>44723.0</v>
+        <v>44709.0</v>
       </c>
       <c r="D120" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="121">
@@ -1822,7 +1822,7 @@
         <v>2022.0</v>
       </c>
       <c r="C121" t="n" s="2">
-        <v>44730.0</v>
+        <v>44716.0</v>
       </c>
       <c r="D121" t="n">
         <v>1.0</v>
@@ -1836,7 +1836,7 @@
         <v>2022.0</v>
       </c>
       <c r="C122" t="n" s="2">
-        <v>44737.0</v>
+        <v>44723.0</v>
       </c>
       <c r="D122" t="n">
         <v>1.0</v>
@@ -1850,7 +1850,7 @@
         <v>2022.0</v>
       </c>
       <c r="C123" t="n" s="2">
-        <v>44744.0</v>
+        <v>44730.0</v>
       </c>
       <c r="D123" t="n">
         <v>1.0</v>
@@ -1864,7 +1864,7 @@
         <v>2022.0</v>
       </c>
       <c r="C124" t="n" s="2">
-        <v>44751.0</v>
+        <v>44737.0</v>
       </c>
       <c r="D124" t="n">
         <v>1.0</v>
@@ -1878,7 +1878,7 @@
         <v>2022.0</v>
       </c>
       <c r="C125" t="n" s="2">
-        <v>44758.0</v>
+        <v>44744.0</v>
       </c>
       <c r="D125" t="n">
         <v>1.0</v>
@@ -1892,7 +1892,7 @@
         <v>2022.0</v>
       </c>
       <c r="C126" t="n" s="2">
-        <v>44772.0</v>
+        <v>44751.0</v>
       </c>
       <c r="D126" t="n">
         <v>1.0</v>
@@ -1906,7 +1906,7 @@
         <v>2022.0</v>
       </c>
       <c r="C127" t="n" s="2">
-        <v>44793.0</v>
+        <v>44758.0</v>
       </c>
       <c r="D127" t="n">
         <v>1.0</v>
@@ -1920,7 +1920,7 @@
         <v>2022.0</v>
       </c>
       <c r="C128" t="n" s="2">
-        <v>44800.0</v>
+        <v>44772.0</v>
       </c>
       <c r="D128" t="n">
         <v>1.0</v>
@@ -1934,7 +1934,7 @@
         <v>2022.0</v>
       </c>
       <c r="C129" t="n" s="2">
-        <v>44828.0</v>
+        <v>44793.0</v>
       </c>
       <c r="D129" t="n">
         <v>1.0</v>
@@ -1948,7 +1948,7 @@
         <v>2022.0</v>
       </c>
       <c r="C130" t="n" s="2">
-        <v>44849.0</v>
+        <v>44800.0</v>
       </c>
       <c r="D130" t="n">
         <v>1.0</v>
@@ -1962,7 +1962,7 @@
         <v>2022.0</v>
       </c>
       <c r="C131" t="n" s="2">
-        <v>44856.0</v>
+        <v>44828.0</v>
       </c>
       <c r="D131" t="n">
         <v>1.0</v>
@@ -1976,7 +1976,7 @@
         <v>2022.0</v>
       </c>
       <c r="C132" t="n" s="2">
-        <v>44863.0</v>
+        <v>44849.0</v>
       </c>
       <c r="D132" t="n">
         <v>1.0</v>
@@ -1990,10 +1990,10 @@
         <v>2022.0</v>
       </c>
       <c r="C133" t="n" s="2">
-        <v>44884.0</v>
+        <v>44856.0</v>
       </c>
       <c r="D133" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="134">
@@ -2004,7 +2004,7 @@
         <v>2022.0</v>
       </c>
       <c r="C134" t="n" s="2">
-        <v>44891.0</v>
+        <v>44863.0</v>
       </c>
       <c r="D134" t="n">
         <v>1.0</v>
@@ -2018,10 +2018,10 @@
         <v>2022.0</v>
       </c>
       <c r="C135" t="n" s="2">
-        <v>44905.0</v>
+        <v>44884.0</v>
       </c>
       <c r="D135" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="136">
@@ -2032,7 +2032,7 @@
         <v>2022.0</v>
       </c>
       <c r="C136" t="n" s="2">
-        <v>44912.0</v>
+        <v>44891.0</v>
       </c>
       <c r="D136" t="n">
         <v>1.0</v>
@@ -2046,10 +2046,10 @@
         <v>2022.0</v>
       </c>
       <c r="C137" t="n" s="2">
-        <v>44919.0</v>
+        <v>44905.0</v>
       </c>
       <c r="D137" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="138">
@@ -2057,13 +2057,13 @@
         <v>5</v>
       </c>
       <c r="B138" t="n">
-        <v>2023.0</v>
+        <v>2022.0</v>
       </c>
       <c r="C138" t="n" s="2">
-        <v>44934.0</v>
+        <v>44912.0</v>
       </c>
       <c r="D138" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="139">
@@ -2071,13 +2071,13 @@
         <v>5</v>
       </c>
       <c r="B139" t="n">
-        <v>2023.0</v>
+        <v>2022.0</v>
       </c>
       <c r="C139" t="n" s="2">
-        <v>44941.0</v>
+        <v>44919.0</v>
       </c>
       <c r="D139" t="n">
-        <v>8.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="140">
@@ -2088,10 +2088,10 @@
         <v>2023.0</v>
       </c>
       <c r="C140" t="n" s="2">
-        <v>44948.0</v>
+        <v>44934.0</v>
       </c>
       <c r="D140" t="n">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="141">
@@ -2102,10 +2102,10 @@
         <v>2023.0</v>
       </c>
       <c r="C141" t="n" s="2">
-        <v>44955.0</v>
+        <v>44941.0</v>
       </c>
       <c r="D141" t="n">
-        <v>3.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="142">
@@ -2116,10 +2116,10 @@
         <v>2023.0</v>
       </c>
       <c r="C142" t="n" s="2">
-        <v>44962.0</v>
+        <v>44948.0</v>
       </c>
       <c r="D142" t="n">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="143">
@@ -2130,10 +2130,10 @@
         <v>2023.0</v>
       </c>
       <c r="C143" t="n" s="2">
-        <v>44969.0</v>
+        <v>44955.0</v>
       </c>
       <c r="D143" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="144">
@@ -2144,10 +2144,10 @@
         <v>2023.0</v>
       </c>
       <c r="C144" t="n" s="2">
-        <v>44976.0</v>
+        <v>44962.0</v>
       </c>
       <c r="D144" t="n">
-        <v>17.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="145">
@@ -2158,10 +2158,10 @@
         <v>2023.0</v>
       </c>
       <c r="C145" t="n" s="2">
-        <v>44983.0</v>
+        <v>44969.0</v>
       </c>
       <c r="D145" t="n">
-        <v>11.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="146">
@@ -2172,10 +2172,10 @@
         <v>2023.0</v>
       </c>
       <c r="C146" t="n" s="2">
-        <v>44990.0</v>
+        <v>44976.0</v>
       </c>
       <c r="D146" t="n">
-        <v>5.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="147">
@@ -2186,10 +2186,10 @@
         <v>2023.0</v>
       </c>
       <c r="C147" t="n" s="2">
-        <v>44997.0</v>
+        <v>44983.0</v>
       </c>
       <c r="D147" t="n">
-        <v>22.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="148">
@@ -2200,10 +2200,10 @@
         <v>2023.0</v>
       </c>
       <c r="C148" t="n" s="2">
-        <v>45004.0</v>
+        <v>44990.0</v>
       </c>
       <c r="D148" t="n">
-        <v>8.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="149">
@@ -2214,10 +2214,10 @@
         <v>2023.0</v>
       </c>
       <c r="C149" t="n" s="2">
-        <v>45011.0</v>
+        <v>44997.0</v>
       </c>
       <c r="D149" t="n">
-        <v>17.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="150">
@@ -2228,10 +2228,10 @@
         <v>2023.0</v>
       </c>
       <c r="C150" t="n" s="2">
-        <v>45018.0</v>
+        <v>45004.0</v>
       </c>
       <c r="D150" t="n">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="151">
@@ -2242,10 +2242,10 @@
         <v>2023.0</v>
       </c>
       <c r="C151" t="n" s="2">
-        <v>45025.0</v>
+        <v>45011.0</v>
       </c>
       <c r="D151" t="n">
-        <v>13.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="152">
@@ -2256,7 +2256,7 @@
         <v>2023.0</v>
       </c>
       <c r="C152" t="n" s="2">
-        <v>45032.0</v>
+        <v>45018.0</v>
       </c>
       <c r="D152" t="n">
         <v>10.0</v>
@@ -2270,10 +2270,10 @@
         <v>2023.0</v>
       </c>
       <c r="C153" t="n" s="2">
-        <v>45039.0</v>
+        <v>45025.0</v>
       </c>
       <c r="D153" t="n">
-        <v>22.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="154">
@@ -2284,10 +2284,10 @@
         <v>2023.0</v>
       </c>
       <c r="C154" t="n" s="2">
-        <v>45046.0</v>
+        <v>45032.0</v>
       </c>
       <c r="D154" t="n">
-        <v>23.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="155">
@@ -2298,10 +2298,10 @@
         <v>2023.0</v>
       </c>
       <c r="C155" t="n" s="2">
-        <v>45053.0</v>
+        <v>45039.0</v>
       </c>
       <c r="D155" t="n">
-        <v>16.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="156">
@@ -2312,10 +2312,10 @@
         <v>2023.0</v>
       </c>
       <c r="C156" t="n" s="2">
-        <v>45060.0</v>
+        <v>45046.0</v>
       </c>
       <c r="D156" t="n">
-        <v>13.0</v>
+        <v>23.0</v>
       </c>
     </row>
     <row r="157">
@@ -2326,10 +2326,10 @@
         <v>2023.0</v>
       </c>
       <c r="C157" t="n" s="2">
-        <v>45067.0</v>
+        <v>45053.0</v>
       </c>
       <c r="D157" t="n">
-        <v>9.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="158">
@@ -2340,10 +2340,10 @@
         <v>2023.0</v>
       </c>
       <c r="C158" t="n" s="2">
-        <v>45074.0</v>
+        <v>45060.0</v>
       </c>
       <c r="D158" t="n">
-        <v>6.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="159">
@@ -2354,10 +2354,10 @@
         <v>2023.0</v>
       </c>
       <c r="C159" t="n" s="2">
-        <v>45081.0</v>
+        <v>45067.0</v>
       </c>
       <c r="D159" t="n">
-        <v>16.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="160">
@@ -2368,10 +2368,10 @@
         <v>2023.0</v>
       </c>
       <c r="C160" t="n" s="2">
-        <v>45088.0</v>
+        <v>45074.0</v>
       </c>
       <c r="D160" t="n">
-        <v>8.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="161">
@@ -2382,7 +2382,7 @@
         <v>2023.0</v>
       </c>
       <c r="C161" t="n" s="2">
-        <v>45095.0</v>
+        <v>45081.0</v>
       </c>
       <c r="D161" t="n">
         <v>16.0</v>
@@ -2396,10 +2396,10 @@
         <v>2023.0</v>
       </c>
       <c r="C162" t="n" s="2">
-        <v>45102.0</v>
+        <v>45088.0</v>
       </c>
       <c r="D162" t="n">
-        <v>17.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="163">
@@ -2410,10 +2410,10 @@
         <v>2023.0</v>
       </c>
       <c r="C163" t="n" s="2">
-        <v>45109.0</v>
+        <v>45095.0</v>
       </c>
       <c r="D163" t="n">
-        <v>14.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="164">
@@ -2424,10 +2424,10 @@
         <v>2023.0</v>
       </c>
       <c r="C164" t="n" s="2">
-        <v>45116.0</v>
+        <v>45102.0</v>
       </c>
       <c r="D164" t="n">
-        <v>13.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="165">
@@ -2438,10 +2438,10 @@
         <v>2023.0</v>
       </c>
       <c r="C165" t="n" s="2">
-        <v>45123.0</v>
+        <v>45109.0</v>
       </c>
       <c r="D165" t="n">
-        <v>5.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="166">
@@ -2452,10 +2452,10 @@
         <v>2023.0</v>
       </c>
       <c r="C166" t="n" s="2">
-        <v>45130.0</v>
+        <v>45116.0</v>
       </c>
       <c r="D166" t="n">
-        <v>8.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="167">
@@ -2466,10 +2466,10 @@
         <v>2023.0</v>
       </c>
       <c r="C167" t="n" s="2">
-        <v>45137.0</v>
+        <v>45123.0</v>
       </c>
       <c r="D167" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="168">
@@ -2480,10 +2480,10 @@
         <v>2023.0</v>
       </c>
       <c r="C168" t="n" s="2">
-        <v>45144.0</v>
+        <v>45130.0</v>
       </c>
       <c r="D168" t="n">
-        <v>2.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="169">
@@ -2494,10 +2494,10 @@
         <v>2023.0</v>
       </c>
       <c r="C169" t="n" s="2">
-        <v>45151.0</v>
+        <v>45137.0</v>
       </c>
       <c r="D169" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="170">
@@ -2508,10 +2508,10 @@
         <v>2023.0</v>
       </c>
       <c r="C170" t="n" s="2">
-        <v>45158.0</v>
+        <v>45144.0</v>
       </c>
       <c r="D170" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="171">
@@ -2522,10 +2522,10 @@
         <v>2023.0</v>
       </c>
       <c r="C171" t="n" s="2">
-        <v>45165.0</v>
+        <v>45151.0</v>
       </c>
       <c r="D171" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="172">
@@ -2536,10 +2536,10 @@
         <v>2023.0</v>
       </c>
       <c r="C172" t="n" s="2">
-        <v>45172.0</v>
+        <v>45158.0</v>
       </c>
       <c r="D172" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="173">
@@ -2550,10 +2550,10 @@
         <v>2023.0</v>
       </c>
       <c r="C173" t="n" s="2">
-        <v>45179.0</v>
+        <v>45165.0</v>
       </c>
       <c r="D173" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="174">
@@ -2564,10 +2564,10 @@
         <v>2023.0</v>
       </c>
       <c r="C174" t="n" s="2">
-        <v>45186.0</v>
+        <v>45172.0</v>
       </c>
       <c r="D174" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="175">
@@ -2578,10 +2578,10 @@
         <v>2023.0</v>
       </c>
       <c r="C175" t="n" s="2">
-        <v>45193.0</v>
+        <v>45179.0</v>
       </c>
       <c r="D175" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="176">
@@ -2592,10 +2592,10 @@
         <v>2023.0</v>
       </c>
       <c r="C176" t="n" s="2">
-        <v>45200.0</v>
+        <v>45186.0</v>
       </c>
       <c r="D176" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="177">
@@ -2606,7 +2606,7 @@
         <v>2023.0</v>
       </c>
       <c r="C177" t="n" s="2">
-        <v>45207.0</v>
+        <v>45193.0</v>
       </c>
       <c r="D177" t="n">
         <v>1.0</v>
@@ -2620,10 +2620,10 @@
         <v>2023.0</v>
       </c>
       <c r="C178" t="n" s="2">
-        <v>45214.0</v>
+        <v>45200.0</v>
       </c>
       <c r="D178" t="n">
-        <v>8.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="179">
@@ -2634,10 +2634,10 @@
         <v>2023.0</v>
       </c>
       <c r="C179" t="n" s="2">
-        <v>45221.0</v>
+        <v>45207.0</v>
       </c>
       <c r="D179" t="n">
-        <v>8.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="180">
@@ -2648,10 +2648,10 @@
         <v>2023.0</v>
       </c>
       <c r="C180" t="n" s="2">
-        <v>45228.0</v>
+        <v>45214.0</v>
       </c>
       <c r="D180" t="n">
-        <v>17.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="181">
@@ -2662,10 +2662,10 @@
         <v>2023.0</v>
       </c>
       <c r="C181" t="n" s="2">
-        <v>45235.0</v>
+        <v>45221.0</v>
       </c>
       <c r="D181" t="n">
-        <v>9.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="182">
@@ -2676,10 +2676,10 @@
         <v>2023.0</v>
       </c>
       <c r="C182" t="n" s="2">
-        <v>45242.0</v>
+        <v>45228.0</v>
       </c>
       <c r="D182" t="n">
-        <v>9.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="183">
@@ -2690,10 +2690,10 @@
         <v>2023.0</v>
       </c>
       <c r="C183" t="n" s="2">
-        <v>45249.0</v>
+        <v>45235.0</v>
       </c>
       <c r="D183" t="n">
-        <v>14.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="184">
@@ -2704,10 +2704,10 @@
         <v>2023.0</v>
       </c>
       <c r="C184" t="n" s="2">
-        <v>45256.0</v>
+        <v>45242.0</v>
       </c>
       <c r="D184" t="n">
-        <v>17.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="185">
@@ -2718,7 +2718,7 @@
         <v>2023.0</v>
       </c>
       <c r="C185" t="n" s="2">
-        <v>45263.0</v>
+        <v>45249.0</v>
       </c>
       <c r="D185" t="n">
         <v>14.0</v>
@@ -2732,10 +2732,10 @@
         <v>2023.0</v>
       </c>
       <c r="C186" t="n" s="2">
-        <v>45270.0</v>
+        <v>45256.0</v>
       </c>
       <c r="D186" t="n">
-        <v>26.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="187">
@@ -2746,10 +2746,10 @@
         <v>2023.0</v>
       </c>
       <c r="C187" t="n" s="2">
-        <v>45277.0</v>
+        <v>45263.0</v>
       </c>
       <c r="D187" t="n">
-        <v>19.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="188">
@@ -2760,10 +2760,10 @@
         <v>2023.0</v>
       </c>
       <c r="C188" t="n" s="2">
-        <v>45284.0</v>
+        <v>45270.0</v>
       </c>
       <c r="D188" t="n">
-        <v>21.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="189">
@@ -2774,10 +2774,10 @@
         <v>2023.0</v>
       </c>
       <c r="C189" t="n" s="2">
-        <v>45291.0</v>
+        <v>45277.0</v>
       </c>
       <c r="D189" t="n">
-        <v>9.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="190">
@@ -2785,13 +2785,13 @@
         <v>5</v>
       </c>
       <c r="B190" t="n">
-        <v>2024.0</v>
+        <v>2023.0</v>
       </c>
       <c r="C190" t="n" s="2">
-        <v>45299.0</v>
+        <v>45284.0</v>
       </c>
       <c r="D190" t="n">
-        <v>26.0</v>
+        <v>21.0</v>
       </c>
     </row>
     <row r="191">
@@ -2799,13 +2799,13 @@
         <v>5</v>
       </c>
       <c r="B191" t="n">
-        <v>2024.0</v>
+        <v>2023.0</v>
       </c>
       <c r="C191" t="n" s="2">
-        <v>45306.0</v>
+        <v>45291.0</v>
       </c>
       <c r="D191" t="n">
-        <v>14.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="192">
@@ -2816,10 +2816,10 @@
         <v>2024.0</v>
       </c>
       <c r="C192" t="n" s="2">
-        <v>45313.0</v>
+        <v>45299.0</v>
       </c>
       <c r="D192" t="n">
-        <v>15.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="193">
@@ -2830,10 +2830,10 @@
         <v>2024.0</v>
       </c>
       <c r="C193" t="n" s="2">
-        <v>45320.0</v>
+        <v>45306.0</v>
       </c>
       <c r="D193" t="n">
-        <v>18.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="194">
@@ -2844,10 +2844,10 @@
         <v>2024.0</v>
       </c>
       <c r="C194" t="n" s="2">
-        <v>45327.0</v>
+        <v>45313.0</v>
       </c>
       <c r="D194" t="n">
-        <v>17.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="195">
@@ -2858,10 +2858,10 @@
         <v>2024.0</v>
       </c>
       <c r="C195" t="n" s="2">
-        <v>45334.0</v>
+        <v>45320.0</v>
       </c>
       <c r="D195" t="n">
-        <v>13.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="196">
@@ -2872,10 +2872,10 @@
         <v>2024.0</v>
       </c>
       <c r="C196" t="n" s="2">
-        <v>45341.0</v>
+        <v>45327.0</v>
       </c>
       <c r="D196" t="n">
-        <v>11.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="197">
@@ -2886,10 +2886,10 @@
         <v>2024.0</v>
       </c>
       <c r="C197" t="n" s="2">
-        <v>45348.0</v>
+        <v>45334.0</v>
       </c>
       <c r="D197" t="n">
-        <v>8.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="198">
@@ -2900,10 +2900,10 @@
         <v>2024.0</v>
       </c>
       <c r="C198" t="n" s="2">
-        <v>45355.0</v>
+        <v>45341.0</v>
       </c>
       <c r="D198" t="n">
-        <v>1.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="199">
@@ -2914,10 +2914,10 @@
         <v>2024.0</v>
       </c>
       <c r="C199" t="n" s="2">
-        <v>45362.0</v>
+        <v>45348.0</v>
       </c>
       <c r="D199" t="n">
-        <v>4.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="200">
@@ -2928,10 +2928,10 @@
         <v>2024.0</v>
       </c>
       <c r="C200" t="n" s="2">
-        <v>45369.0</v>
+        <v>45355.0</v>
       </c>
       <c r="D200" t="n">
-        <v>8.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="201">
@@ -2942,10 +2942,10 @@
         <v>2024.0</v>
       </c>
       <c r="C201" t="n" s="2">
-        <v>45376.0</v>
+        <v>45362.0</v>
       </c>
       <c r="D201" t="n">
-        <v>9.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="202">
@@ -2956,10 +2956,10 @@
         <v>2024.0</v>
       </c>
       <c r="C202" t="n" s="2">
-        <v>45383.0</v>
+        <v>45369.0</v>
       </c>
       <c r="D202" t="n">
-        <v>5.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="203">
@@ -2970,10 +2970,10 @@
         <v>2024.0</v>
       </c>
       <c r="C203" t="n" s="2">
-        <v>45390.0</v>
+        <v>45376.0</v>
       </c>
       <c r="D203" t="n">
-        <v>6.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="204">
@@ -2984,10 +2984,10 @@
         <v>2024.0</v>
       </c>
       <c r="C204" t="n" s="2">
-        <v>45397.0</v>
+        <v>45383.0</v>
       </c>
       <c r="D204" t="n">
-        <v>13.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="205">
@@ -2998,10 +2998,10 @@
         <v>2024.0</v>
       </c>
       <c r="C205" t="n" s="2">
-        <v>45404.0</v>
+        <v>45390.0</v>
       </c>
       <c r="D205" t="n">
-        <v>24.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="206">
@@ -3012,10 +3012,10 @@
         <v>2024.0</v>
       </c>
       <c r="C206" t="n" s="2">
-        <v>45411.0</v>
+        <v>45397.0</v>
       </c>
       <c r="D206" t="n">
-        <v>17.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="207">
@@ -3026,10 +3026,10 @@
         <v>2024.0</v>
       </c>
       <c r="C207" t="n" s="2">
-        <v>45418.0</v>
+        <v>45404.0</v>
       </c>
       <c r="D207" t="n">
-        <v>3.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="208">
@@ -3040,10 +3040,10 @@
         <v>2024.0</v>
       </c>
       <c r="C208" t="n" s="2">
-        <v>45425.0</v>
+        <v>45411.0</v>
       </c>
       <c r="D208" t="n">
-        <v>16.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="209">
@@ -3054,10 +3054,10 @@
         <v>2024.0</v>
       </c>
       <c r="C209" t="n" s="2">
-        <v>45432.0</v>
+        <v>45418.0</v>
       </c>
       <c r="D209" t="n">
-        <v>19.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="210">
@@ -3068,10 +3068,10 @@
         <v>2024.0</v>
       </c>
       <c r="C210" t="n" s="2">
-        <v>45439.0</v>
+        <v>45425.0</v>
       </c>
       <c r="D210" t="n">
-        <v>30.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="211">
@@ -3082,10 +3082,10 @@
         <v>2024.0</v>
       </c>
       <c r="C211" t="n" s="2">
-        <v>45446.0</v>
+        <v>45432.0</v>
       </c>
       <c r="D211" t="n">
-        <v>28.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="212">
@@ -3096,10 +3096,10 @@
         <v>2024.0</v>
       </c>
       <c r="C212" t="n" s="2">
-        <v>45453.0</v>
+        <v>45439.0</v>
       </c>
       <c r="D212" t="n">
-        <v>19.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="213">
@@ -3110,10 +3110,10 @@
         <v>2024.0</v>
       </c>
       <c r="C213" t="n" s="2">
-        <v>45460.0</v>
+        <v>45446.0</v>
       </c>
       <c r="D213" t="n">
-        <v>26.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="214">
@@ -3124,10 +3124,10 @@
         <v>2024.0</v>
       </c>
       <c r="C214" t="n" s="2">
-        <v>45467.0</v>
+        <v>45453.0</v>
       </c>
       <c r="D214" t="n">
-        <v>8.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="215">
@@ -3138,10 +3138,10 @@
         <v>2024.0</v>
       </c>
       <c r="C215" t="n" s="2">
-        <v>45474.0</v>
+        <v>45460.0</v>
       </c>
       <c r="D215" t="n">
-        <v>12.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="216">
@@ -3152,10 +3152,10 @@
         <v>2024.0</v>
       </c>
       <c r="C216" t="n" s="2">
-        <v>45481.0</v>
+        <v>45467.0</v>
       </c>
       <c r="D216" t="n">
-        <v>12.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="217">
@@ -3166,10 +3166,10 @@
         <v>2024.0</v>
       </c>
       <c r="C217" t="n" s="2">
-        <v>45488.0</v>
+        <v>45474.0</v>
       </c>
       <c r="D217" t="n">
-        <v>4.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="218">
@@ -3180,10 +3180,10 @@
         <v>2024.0</v>
       </c>
       <c r="C218" t="n" s="2">
-        <v>45495.0</v>
+        <v>45481.0</v>
       </c>
       <c r="D218" t="n">
-        <v>6.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="219">
@@ -3194,10 +3194,10 @@
         <v>2024.0</v>
       </c>
       <c r="C219" t="n" s="2">
-        <v>45502.0</v>
+        <v>45488.0</v>
       </c>
       <c r="D219" t="n">
-        <v>7.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="220">
@@ -3208,10 +3208,10 @@
         <v>2024.0</v>
       </c>
       <c r="C220" t="n" s="2">
-        <v>45509.0</v>
+        <v>45495.0</v>
       </c>
       <c r="D220" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="221">
@@ -3222,10 +3222,10 @@
         <v>2024.0</v>
       </c>
       <c r="C221" t="n" s="2">
-        <v>45516.0</v>
+        <v>45502.0</v>
       </c>
       <c r="D221" t="n">
-        <v>4.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="222">
@@ -3236,10 +3236,10 @@
         <v>2024.0</v>
       </c>
       <c r="C222" t="n" s="2">
-        <v>45523.0</v>
+        <v>45509.0</v>
       </c>
       <c r="D222" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="223">
@@ -3250,7 +3250,7 @@
         <v>2024.0</v>
       </c>
       <c r="C223" t="n" s="2">
-        <v>45530.0</v>
+        <v>45516.0</v>
       </c>
       <c r="D223" t="n">
         <v>4.0</v>
@@ -3264,7 +3264,7 @@
         <v>2024.0</v>
       </c>
       <c r="C224" t="n" s="2">
-        <v>45537.0</v>
+        <v>45523.0</v>
       </c>
       <c r="D224" t="n">
         <v>4.0</v>
@@ -3278,10 +3278,10 @@
         <v>2024.0</v>
       </c>
       <c r="C225" t="n" s="2">
-        <v>45544.0</v>
+        <v>45530.0</v>
       </c>
       <c r="D225" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="226">
@@ -3292,10 +3292,10 @@
         <v>2024.0</v>
       </c>
       <c r="C226" t="n" s="2">
-        <v>45551.0</v>
+        <v>45537.0</v>
       </c>
       <c r="D226" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="227">
@@ -3306,7 +3306,7 @@
         <v>2024.0</v>
       </c>
       <c r="C227" t="n" s="2">
-        <v>45558.0</v>
+        <v>45544.0</v>
       </c>
       <c r="D227" t="n">
         <v>1.0</v>
@@ -3320,7 +3320,7 @@
         <v>2024.0</v>
       </c>
       <c r="C228" t="n" s="2">
-        <v>45600.0</v>
+        <v>45551.0</v>
       </c>
       <c r="D228" t="n">
         <v>3.0</v>
@@ -3334,7 +3334,7 @@
         <v>2024.0</v>
       </c>
       <c r="C229" t="n" s="2">
-        <v>45607.0</v>
+        <v>45558.0</v>
       </c>
       <c r="D229" t="n">
         <v>1.0</v>
@@ -3348,10 +3348,10 @@
         <v>2024.0</v>
       </c>
       <c r="C230" t="n" s="2">
-        <v>45628.0</v>
+        <v>45600.0</v>
       </c>
       <c r="D230" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="231">
@@ -3362,10 +3362,10 @@
         <v>2024.0</v>
       </c>
       <c r="C231" t="n" s="2">
-        <v>45635.0</v>
+        <v>45607.0</v>
       </c>
       <c r="D231" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="232">
@@ -3376,10 +3376,10 @@
         <v>2024.0</v>
       </c>
       <c r="C232" t="n" s="2">
-        <v>45642.0</v>
+        <v>45628.0</v>
       </c>
       <c r="D232" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="233">
@@ -3390,10 +3390,10 @@
         <v>2024.0</v>
       </c>
       <c r="C233" t="n" s="2">
-        <v>45649.0</v>
+        <v>45635.0</v>
       </c>
       <c r="D233" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="234">
@@ -3404,10 +3404,10 @@
         <v>2024.0</v>
       </c>
       <c r="C234" t="n" s="2">
-        <v>45656.0</v>
+        <v>45642.0</v>
       </c>
       <c r="D234" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="235">
@@ -3415,13 +3415,13 @@
         <v>5</v>
       </c>
       <c r="B235" t="n">
-        <v>2025.0</v>
+        <v>2024.0</v>
       </c>
       <c r="C235" t="n" s="2">
-        <v>45672.0</v>
+        <v>45649.0</v>
       </c>
       <c r="D235" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="236">
@@ -3429,10 +3429,10 @@
         <v>5</v>
       </c>
       <c r="B236" t="n">
-        <v>2025.0</v>
+        <v>2024.0</v>
       </c>
       <c r="C236" t="n" s="2">
-        <v>45679.0</v>
+        <v>45656.0</v>
       </c>
       <c r="D236" t="n">
         <v>1.0</v>
@@ -3446,10 +3446,10 @@
         <v>2025.0</v>
       </c>
       <c r="C237" t="n" s="2">
-        <v>45686.0</v>
+        <v>45672.0</v>
       </c>
       <c r="D237" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="238">
@@ -3460,10 +3460,10 @@
         <v>2025.0</v>
       </c>
       <c r="C238" t="n" s="2">
-        <v>45721.0</v>
+        <v>45679.0</v>
       </c>
       <c r="D238" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="239">
@@ -3474,7 +3474,7 @@
         <v>2025.0</v>
       </c>
       <c r="C239" t="n" s="2">
-        <v>45728.0</v>
+        <v>45686.0</v>
       </c>
       <c r="D239" t="n">
         <v>1.0</v>
@@ -3488,10 +3488,10 @@
         <v>2025.0</v>
       </c>
       <c r="C240" t="n" s="2">
-        <v>45742.0</v>
+        <v>45721.0</v>
       </c>
       <c r="D240" t="n">
-        <v>9.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="241">
@@ -3502,10 +3502,10 @@
         <v>2025.0</v>
       </c>
       <c r="C241" t="n" s="2">
-        <v>45749.0</v>
+        <v>45728.0</v>
       </c>
       <c r="D241" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="242">
@@ -3516,10 +3516,10 @@
         <v>2025.0</v>
       </c>
       <c r="C242" t="n" s="2">
-        <v>45756.0</v>
+        <v>45742.0</v>
       </c>
       <c r="D242" t="n">
-        <v>2.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="243">
@@ -3530,10 +3530,10 @@
         <v>2025.0</v>
       </c>
       <c r="C243" t="n" s="2">
-        <v>45763.0</v>
+        <v>45749.0</v>
       </c>
       <c r="D243" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="244">
@@ -3544,10 +3544,10 @@
         <v>2025.0</v>
       </c>
       <c r="C244" t="n" s="2">
-        <v>45770.0</v>
+        <v>45756.0</v>
       </c>
       <c r="D244" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="245">
@@ -3558,10 +3558,10 @@
         <v>2025.0</v>
       </c>
       <c r="C245" t="n" s="2">
-        <v>45777.0</v>
+        <v>45763.0</v>
       </c>
       <c r="D245" t="n">
-        <v>7.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="246">
@@ -3572,10 +3572,10 @@
         <v>2025.0</v>
       </c>
       <c r="C246" t="n" s="2">
-        <v>45784.0</v>
+        <v>45770.0</v>
       </c>
       <c r="D246" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="247">
@@ -3586,10 +3586,10 @@
         <v>2025.0</v>
       </c>
       <c r="C247" t="n" s="2">
-        <v>45791.0</v>
+        <v>45777.0</v>
       </c>
       <c r="D247" t="n">
-        <v>5.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="248">
@@ -3600,10 +3600,10 @@
         <v>2025.0</v>
       </c>
       <c r="C248" t="n" s="2">
-        <v>45798.0</v>
+        <v>45784.0</v>
       </c>
       <c r="D248" t="n">
-        <v>8.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="249">
@@ -3614,10 +3614,10 @@
         <v>2025.0</v>
       </c>
       <c r="C249" t="n" s="2">
-        <v>45805.0</v>
+        <v>45791.0</v>
       </c>
       <c r="D249" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="250">
@@ -3628,10 +3628,10 @@
         <v>2025.0</v>
       </c>
       <c r="C250" t="n" s="2">
-        <v>45812.0</v>
+        <v>45798.0</v>
       </c>
       <c r="D250" t="n">
-        <v>3.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="251">
@@ -3642,10 +3642,10 @@
         <v>2025.0</v>
       </c>
       <c r="C251" t="n" s="2">
-        <v>45819.0</v>
+        <v>45805.0</v>
       </c>
       <c r="D251" t="n">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="252">
@@ -3656,10 +3656,10 @@
         <v>2025.0</v>
       </c>
       <c r="C252" t="n" s="2">
-        <v>45826.0</v>
+        <v>45812.0</v>
       </c>
       <c r="D252" t="n">
-        <v>13.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="253">
@@ -3670,10 +3670,10 @@
         <v>2025.0</v>
       </c>
       <c r="C253" t="n" s="2">
-        <v>45833.0</v>
+        <v>45819.0</v>
       </c>
       <c r="D253" t="n">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="254">
@@ -3684,10 +3684,10 @@
         <v>2025.0</v>
       </c>
       <c r="C254" t="n" s="2">
-        <v>45840.0</v>
+        <v>45826.0</v>
       </c>
       <c r="D254" t="n">
-        <v>4.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="255">
@@ -3698,10 +3698,10 @@
         <v>2025.0</v>
       </c>
       <c r="C255" t="n" s="2">
-        <v>45847.0</v>
+        <v>45833.0</v>
       </c>
       <c r="D255" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="256">
@@ -3712,10 +3712,10 @@
         <v>2025.0</v>
       </c>
       <c r="C256" t="n" s="2">
-        <v>45854.0</v>
+        <v>45840.0</v>
       </c>
       <c r="D256" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="257">
@@ -3726,10 +3726,10 @@
         <v>2025.0</v>
       </c>
       <c r="C257" t="n" s="2">
-        <v>45861.0</v>
+        <v>45847.0</v>
       </c>
       <c r="D257" t="n">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="258">
@@ -3740,10 +3740,10 @@
         <v>2025.0</v>
       </c>
       <c r="C258" t="n" s="2">
-        <v>45868.0</v>
+        <v>45854.0</v>
       </c>
       <c r="D258" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="259">
@@ -3754,10 +3754,10 @@
         <v>2025.0</v>
       </c>
       <c r="C259" t="n" s="2">
-        <v>45882.0</v>
+        <v>45861.0</v>
       </c>
       <c r="D259" t="n">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="260">
@@ -3768,10 +3768,10 @@
         <v>2025.0</v>
       </c>
       <c r="C260" t="n" s="2">
-        <v>45889.0</v>
+        <v>45868.0</v>
       </c>
       <c r="D260" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="261">
@@ -3782,10 +3782,10 @@
         <v>2025.0</v>
       </c>
       <c r="C261" t="n" s="2">
-        <v>45896.0</v>
+        <v>45882.0</v>
       </c>
       <c r="D261" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="262">
@@ -3796,10 +3796,10 @@
         <v>2025.0</v>
       </c>
       <c r="C262" t="n" s="2">
-        <v>45903.0</v>
+        <v>45889.0</v>
       </c>
       <c r="D262" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="263">
@@ -3810,10 +3810,10 @@
         <v>2025.0</v>
       </c>
       <c r="C263" t="n" s="2">
-        <v>45910.0</v>
+        <v>45896.0</v>
       </c>
       <c r="D263" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="264">
@@ -3824,10 +3824,10 @@
         <v>2025.0</v>
       </c>
       <c r="C264" t="n" s="2">
-        <v>45973.0</v>
+        <v>45903.0</v>
       </c>
       <c r="D264" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="265">
@@ -3838,10 +3838,10 @@
         <v>2025.0</v>
       </c>
       <c r="C265" t="n" s="2">
-        <v>45987.0</v>
+        <v>45910.0</v>
       </c>
       <c r="D265" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="266">
@@ -3852,7 +3852,7 @@
         <v>2025.0</v>
       </c>
       <c r="C266" t="n" s="2">
-        <v>45994.0</v>
+        <v>45973.0</v>
       </c>
       <c r="D266" t="n">
         <v>1.0</v>
@@ -3866,10 +3866,10 @@
         <v>2025.0</v>
       </c>
       <c r="C267" t="n" s="2">
-        <v>46001.0</v>
+        <v>45987.0</v>
       </c>
       <c r="D267" t="n">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="268">
@@ -3880,10 +3880,10 @@
         <v>2025.0</v>
       </c>
       <c r="C268" t="n" s="2">
-        <v>46008.0</v>
+        <v>45994.0</v>
       </c>
       <c r="D268" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="269">
@@ -3894,10 +3894,10 @@
         <v>2025.0</v>
       </c>
       <c r="C269" t="n" s="2">
-        <v>46022.0</v>
+        <v>46001.0</v>
       </c>
       <c r="D269" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="270">
@@ -3908,7 +3908,7 @@
         <v>2025.0</v>
       </c>
       <c r="C270" t="n" s="2">
-        <v>46029.0</v>
+        <v>46008.0</v>
       </c>
       <c r="D270" t="n">
         <v>5.0</v>
@@ -3919,13 +3919,13 @@
         <v>5</v>
       </c>
       <c r="B271" t="n">
-        <v>2026.0</v>
+        <v>2025.0</v>
       </c>
       <c r="C271" t="n" s="2">
-        <v>46030.0</v>
+        <v>46022.0</v>
       </c>
       <c r="D271" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="272">
@@ -3933,13 +3933,13 @@
         <v>5</v>
       </c>
       <c r="B272" t="n">
-        <v>2026.0</v>
+        <v>2025.0</v>
       </c>
       <c r="C272" t="n" s="2">
-        <v>46037.0</v>
+        <v>46029.0</v>
       </c>
       <c r="D272" t="n">
-        <v>12.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="273">
@@ -3950,10 +3950,10 @@
         <v>2026.0</v>
       </c>
       <c r="C273" t="n" s="2">
-        <v>46044.0</v>
+        <v>46030.0</v>
       </c>
       <c r="D273" t="n">
-        <v>9.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="274">
@@ -3964,10 +3964,10 @@
         <v>2026.0</v>
       </c>
       <c r="C274" t="n" s="2">
-        <v>46051.0</v>
+        <v>46037.0</v>
       </c>
       <c r="D274" t="n">
-        <v>10.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="275">
@@ -3978,10 +3978,10 @@
         <v>2026.0</v>
       </c>
       <c r="C275" t="n" s="2">
-        <v>46058.0</v>
+        <v>46044.0</v>
       </c>
       <c r="D275" t="n">
-        <v>5.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="276">
@@ -3992,10 +3992,10 @@
         <v>2026.0</v>
       </c>
       <c r="C276" t="n" s="2">
-        <v>46065.0</v>
+        <v>46051.0</v>
       </c>
       <c r="D276" t="n">
-        <v>6.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="277">
@@ -4006,7 +4006,7 @@
         <v>2026.0</v>
       </c>
       <c r="C277" t="n" s="2">
-        <v>46072.0</v>
+        <v>46058.0</v>
       </c>
       <c r="D277" t="n">
         <v>5.0</v>
@@ -4020,7 +4020,7 @@
         <v>2026.0</v>
       </c>
       <c r="C278" t="n" s="2">
-        <v>46079.0</v>
+        <v>46065.0</v>
       </c>
       <c r="D278" t="n">
         <v>6.0</v>
@@ -4028,58 +4028,58 @@
     </row>
     <row r="279">
       <c r="A279" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B279" t="n">
-        <v>2023.0</v>
+        <v>2026.0</v>
       </c>
       <c r="C279" t="n" s="2">
-        <v>45095.0</v>
+        <v>46072.0</v>
       </c>
       <c r="D279" t="n">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B280" t="n">
-        <v>2023.0</v>
+        <v>2026.0</v>
       </c>
       <c r="C280" t="n" s="2">
-        <v>45102.0</v>
+        <v>46079.0</v>
       </c>
       <c r="D280" t="n">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B281" t="n">
-        <v>2023.0</v>
+        <v>2026.0</v>
       </c>
       <c r="C281" t="n" s="2">
-        <v>45158.0</v>
+        <v>46086.0</v>
       </c>
       <c r="D281" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B282" t="n">
-        <v>2023.0</v>
+        <v>2026.0</v>
       </c>
       <c r="C282" t="n" s="2">
-        <v>45207.0</v>
+        <v>46093.0</v>
       </c>
       <c r="D282" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="283">
@@ -4090,10 +4090,10 @@
         <v>2023.0</v>
       </c>
       <c r="C283" t="n" s="2">
-        <v>45214.0</v>
+        <v>45095.0</v>
       </c>
       <c r="D283" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="284">
@@ -4104,7 +4104,7 @@
         <v>2023.0</v>
       </c>
       <c r="C284" t="n" s="2">
-        <v>45221.0</v>
+        <v>45102.0</v>
       </c>
       <c r="D284" t="n">
         <v>1.0</v>
@@ -4118,7 +4118,7 @@
         <v>2023.0</v>
       </c>
       <c r="C285" t="n" s="2">
-        <v>45249.0</v>
+        <v>45158.0</v>
       </c>
       <c r="D285" t="n">
         <v>1.0</v>
@@ -4132,7 +4132,7 @@
         <v>2023.0</v>
       </c>
       <c r="C286" t="n" s="2">
-        <v>45256.0</v>
+        <v>45207.0</v>
       </c>
       <c r="D286" t="n">
         <v>3.0</v>
@@ -4146,10 +4146,10 @@
         <v>2023.0</v>
       </c>
       <c r="C287" t="n" s="2">
-        <v>45263.0</v>
+        <v>45214.0</v>
       </c>
       <c r="D287" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="288">
@@ -4160,7 +4160,7 @@
         <v>2023.0</v>
       </c>
       <c r="C288" t="n" s="2">
-        <v>45270.0</v>
+        <v>45221.0</v>
       </c>
       <c r="D288" t="n">
         <v>1.0</v>
@@ -4174,10 +4174,10 @@
         <v>2023.0</v>
       </c>
       <c r="C289" t="n" s="2">
-        <v>45277.0</v>
+        <v>45249.0</v>
       </c>
       <c r="D289" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="290">
@@ -4188,10 +4188,10 @@
         <v>2023.0</v>
       </c>
       <c r="C290" t="n" s="2">
-        <v>45284.0</v>
+        <v>45256.0</v>
       </c>
       <c r="D290" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="291">
@@ -4202,10 +4202,10 @@
         <v>2023.0</v>
       </c>
       <c r="C291" t="n" s="2">
-        <v>45291.0</v>
+        <v>45263.0</v>
       </c>
       <c r="D291" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="292">
@@ -4213,13 +4213,13 @@
         <v>6</v>
       </c>
       <c r="B292" t="n">
-        <v>2024.0</v>
+        <v>2023.0</v>
       </c>
       <c r="C292" t="n" s="2">
-        <v>45306.0</v>
+        <v>45270.0</v>
       </c>
       <c r="D292" t="n">
-        <v>7.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="293">
@@ -4227,13 +4227,13 @@
         <v>6</v>
       </c>
       <c r="B293" t="n">
-        <v>2024.0</v>
+        <v>2023.0</v>
       </c>
       <c r="C293" t="n" s="2">
-        <v>45313.0</v>
+        <v>45277.0</v>
       </c>
       <c r="D293" t="n">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="294">
@@ -4241,13 +4241,13 @@
         <v>6</v>
       </c>
       <c r="B294" t="n">
-        <v>2024.0</v>
+        <v>2023.0</v>
       </c>
       <c r="C294" t="n" s="2">
-        <v>45320.0</v>
+        <v>45284.0</v>
       </c>
       <c r="D294" t="n">
-        <v>19.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="295">
@@ -4255,13 +4255,13 @@
         <v>6</v>
       </c>
       <c r="B295" t="n">
-        <v>2024.0</v>
+        <v>2023.0</v>
       </c>
       <c r="C295" t="n" s="2">
-        <v>45327.0</v>
+        <v>45291.0</v>
       </c>
       <c r="D295" t="n">
-        <v>18.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="296">
@@ -4272,10 +4272,10 @@
         <v>2024.0</v>
       </c>
       <c r="C296" t="n" s="2">
-        <v>45334.0</v>
+        <v>45306.0</v>
       </c>
       <c r="D296" t="n">
-        <v>9.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="297">
@@ -4286,10 +4286,10 @@
         <v>2024.0</v>
       </c>
       <c r="C297" t="n" s="2">
-        <v>45341.0</v>
+        <v>45313.0</v>
       </c>
       <c r="D297" t="n">
-        <v>12.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="298">
@@ -4300,10 +4300,10 @@
         <v>2024.0</v>
       </c>
       <c r="C298" t="n" s="2">
-        <v>45348.0</v>
+        <v>45320.0</v>
       </c>
       <c r="D298" t="n">
-        <v>12.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="299">
@@ -4314,10 +4314,10 @@
         <v>2024.0</v>
       </c>
       <c r="C299" t="n" s="2">
-        <v>45355.0</v>
+        <v>45327.0</v>
       </c>
       <c r="D299" t="n">
-        <v>10.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="300">
@@ -4328,10 +4328,10 @@
         <v>2024.0</v>
       </c>
       <c r="C300" t="n" s="2">
-        <v>45362.0</v>
+        <v>45334.0</v>
       </c>
       <c r="D300" t="n">
-        <v>12.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="301">
@@ -4342,10 +4342,10 @@
         <v>2024.0</v>
       </c>
       <c r="C301" t="n" s="2">
-        <v>45369.0</v>
+        <v>45341.0</v>
       </c>
       <c r="D301" t="n">
-        <v>13.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="302">
@@ -4356,10 +4356,10 @@
         <v>2024.0</v>
       </c>
       <c r="C302" t="n" s="2">
-        <v>45376.0</v>
+        <v>45348.0</v>
       </c>
       <c r="D302" t="n">
-        <v>18.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="303">
@@ -4370,10 +4370,10 @@
         <v>2024.0</v>
       </c>
       <c r="C303" t="n" s="2">
-        <v>45383.0</v>
+        <v>45355.0</v>
       </c>
       <c r="D303" t="n">
-        <v>12.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="304">
@@ -4384,10 +4384,10 @@
         <v>2024.0</v>
       </c>
       <c r="C304" t="n" s="2">
-        <v>45390.0</v>
+        <v>45362.0</v>
       </c>
       <c r="D304" t="n">
-        <v>6.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="305">
@@ -4398,10 +4398,10 @@
         <v>2024.0</v>
       </c>
       <c r="C305" t="n" s="2">
-        <v>45397.0</v>
+        <v>45369.0</v>
       </c>
       <c r="D305" t="n">
-        <v>10.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="306">
@@ -4412,10 +4412,10 @@
         <v>2024.0</v>
       </c>
       <c r="C306" t="n" s="2">
-        <v>45404.0</v>
+        <v>45376.0</v>
       </c>
       <c r="D306" t="n">
-        <v>3.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="307">
@@ -4426,10 +4426,10 @@
         <v>2024.0</v>
       </c>
       <c r="C307" t="n" s="2">
-        <v>45411.0</v>
+        <v>45383.0</v>
       </c>
       <c r="D307" t="n">
-        <v>2.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="308">
@@ -4440,10 +4440,10 @@
         <v>2024.0</v>
       </c>
       <c r="C308" t="n" s="2">
-        <v>45418.0</v>
+        <v>45390.0</v>
       </c>
       <c r="D308" t="n">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="309">
@@ -4454,10 +4454,10 @@
         <v>2024.0</v>
       </c>
       <c r="C309" t="n" s="2">
-        <v>45425.0</v>
+        <v>45397.0</v>
       </c>
       <c r="D309" t="n">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="310">
@@ -4468,10 +4468,10 @@
         <v>2024.0</v>
       </c>
       <c r="C310" t="n" s="2">
-        <v>45432.0</v>
+        <v>45404.0</v>
       </c>
       <c r="D310" t="n">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="311">
@@ -4482,10 +4482,10 @@
         <v>2024.0</v>
       </c>
       <c r="C311" t="n" s="2">
-        <v>45439.0</v>
+        <v>45411.0</v>
       </c>
       <c r="D311" t="n">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="312">
@@ -4496,10 +4496,10 @@
         <v>2024.0</v>
       </c>
       <c r="C312" t="n" s="2">
-        <v>45446.0</v>
+        <v>45418.0</v>
       </c>
       <c r="D312" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="313">
@@ -4510,10 +4510,10 @@
         <v>2024.0</v>
       </c>
       <c r="C313" t="n" s="2">
-        <v>45453.0</v>
+        <v>45425.0</v>
       </c>
       <c r="D313" t="n">
-        <v>4.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="314">
@@ -4524,10 +4524,10 @@
         <v>2024.0</v>
       </c>
       <c r="C314" t="n" s="2">
-        <v>45460.0</v>
+        <v>45432.0</v>
       </c>
       <c r="D314" t="n">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="315">
@@ -4538,10 +4538,10 @@
         <v>2024.0</v>
       </c>
       <c r="C315" t="n" s="2">
-        <v>45467.0</v>
+        <v>45439.0</v>
       </c>
       <c r="D315" t="n">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="316">
@@ -4552,7 +4552,7 @@
         <v>2024.0</v>
       </c>
       <c r="C316" t="n" s="2">
-        <v>45474.0</v>
+        <v>45446.0</v>
       </c>
       <c r="D316" t="n">
         <v>2.0</v>
@@ -4566,10 +4566,10 @@
         <v>2024.0</v>
       </c>
       <c r="C317" t="n" s="2">
-        <v>45481.0</v>
+        <v>45453.0</v>
       </c>
       <c r="D317" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="318">
@@ -4580,10 +4580,10 @@
         <v>2024.0</v>
       </c>
       <c r="C318" t="n" s="2">
-        <v>45488.0</v>
+        <v>45460.0</v>
       </c>
       <c r="D318" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="319">
@@ -4594,10 +4594,10 @@
         <v>2024.0</v>
       </c>
       <c r="C319" t="n" s="2">
-        <v>45495.0</v>
+        <v>45467.0</v>
       </c>
       <c r="D319" t="n">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="320">
@@ -4608,7 +4608,7 @@
         <v>2024.0</v>
       </c>
       <c r="C320" t="n" s="2">
-        <v>45502.0</v>
+        <v>45474.0</v>
       </c>
       <c r="D320" t="n">
         <v>2.0</v>
@@ -4622,7 +4622,7 @@
         <v>2024.0</v>
       </c>
       <c r="C321" t="n" s="2">
-        <v>45509.0</v>
+        <v>45481.0</v>
       </c>
       <c r="D321" t="n">
         <v>1.0</v>
@@ -4636,10 +4636,10 @@
         <v>2024.0</v>
       </c>
       <c r="C322" t="n" s="2">
-        <v>45523.0</v>
+        <v>45488.0</v>
       </c>
       <c r="D322" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="323">
@@ -4650,10 +4650,10 @@
         <v>2024.0</v>
       </c>
       <c r="C323" t="n" s="2">
-        <v>45551.0</v>
+        <v>45495.0</v>
       </c>
       <c r="D323" t="n">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="324">
@@ -4664,10 +4664,10 @@
         <v>2024.0</v>
       </c>
       <c r="C324" t="n" s="2">
-        <v>45558.0</v>
+        <v>45502.0</v>
       </c>
       <c r="D324" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="325">
@@ -4678,10 +4678,10 @@
         <v>2024.0</v>
       </c>
       <c r="C325" t="n" s="2">
-        <v>45572.0</v>
+        <v>45509.0</v>
       </c>
       <c r="D325" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="326">
@@ -4692,7 +4692,7 @@
         <v>2024.0</v>
       </c>
       <c r="C326" t="n" s="2">
-        <v>45593.0</v>
+        <v>45523.0</v>
       </c>
       <c r="D326" t="n">
         <v>1.0</v>
@@ -4706,10 +4706,10 @@
         <v>2024.0</v>
       </c>
       <c r="C327" t="n" s="2">
-        <v>45614.0</v>
+        <v>45551.0</v>
       </c>
       <c r="D327" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="328">
@@ -4720,7 +4720,7 @@
         <v>2024.0</v>
       </c>
       <c r="C328" t="n" s="2">
-        <v>45621.0</v>
+        <v>45558.0</v>
       </c>
       <c r="D328" t="n">
         <v>1.0</v>
@@ -4734,10 +4734,10 @@
         <v>2024.0</v>
       </c>
       <c r="C329" t="n" s="2">
-        <v>45635.0</v>
+        <v>45572.0</v>
       </c>
       <c r="D329" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="330">
@@ -4748,7 +4748,7 @@
         <v>2024.0</v>
       </c>
       <c r="C330" t="n" s="2">
-        <v>45649.0</v>
+        <v>45593.0</v>
       </c>
       <c r="D330" t="n">
         <v>1.0</v>
@@ -4759,13 +4759,13 @@
         <v>6</v>
       </c>
       <c r="B331" t="n">
-        <v>2025.0</v>
+        <v>2024.0</v>
       </c>
       <c r="C331" t="n" s="2">
-        <v>45665.0</v>
+        <v>45614.0</v>
       </c>
       <c r="D331" t="n">
-        <v>9.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="332">
@@ -4773,13 +4773,13 @@
         <v>6</v>
       </c>
       <c r="B332" t="n">
-        <v>2025.0</v>
+        <v>2024.0</v>
       </c>
       <c r="C332" t="n" s="2">
-        <v>45672.0</v>
+        <v>45621.0</v>
       </c>
       <c r="D332" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="333">
@@ -4787,10 +4787,10 @@
         <v>6</v>
       </c>
       <c r="B333" t="n">
-        <v>2025.0</v>
+        <v>2024.0</v>
       </c>
       <c r="C333" t="n" s="2">
-        <v>45679.0</v>
+        <v>45635.0</v>
       </c>
       <c r="D333" t="n">
         <v>1.0</v>
@@ -4801,13 +4801,13 @@
         <v>6</v>
       </c>
       <c r="B334" t="n">
-        <v>2025.0</v>
+        <v>2024.0</v>
       </c>
       <c r="C334" t="n" s="2">
-        <v>45686.0</v>
+        <v>45649.0</v>
       </c>
       <c r="D334" t="n">
-        <v>8.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="335">
@@ -4818,10 +4818,10 @@
         <v>2025.0</v>
       </c>
       <c r="C335" t="n" s="2">
-        <v>45693.0</v>
+        <v>45665.0</v>
       </c>
       <c r="D335" t="n">
-        <v>3.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="336">
@@ -4832,10 +4832,10 @@
         <v>2025.0</v>
       </c>
       <c r="C336" t="n" s="2">
-        <v>45700.0</v>
+        <v>45672.0</v>
       </c>
       <c r="D336" t="n">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="337">
@@ -4846,10 +4846,10 @@
         <v>2025.0</v>
       </c>
       <c r="C337" t="n" s="2">
-        <v>45707.0</v>
+        <v>45679.0</v>
       </c>
       <c r="D337" t="n">
-        <v>8.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="338">
@@ -4860,10 +4860,10 @@
         <v>2025.0</v>
       </c>
       <c r="C338" t="n" s="2">
-        <v>45714.0</v>
+        <v>45686.0</v>
       </c>
       <c r="D338" t="n">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="339">
@@ -4874,10 +4874,10 @@
         <v>2025.0</v>
       </c>
       <c r="C339" t="n" s="2">
-        <v>45721.0</v>
+        <v>45693.0</v>
       </c>
       <c r="D339" t="n">
-        <v>8.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="340">
@@ -4888,10 +4888,10 @@
         <v>2025.0</v>
       </c>
       <c r="C340" t="n" s="2">
-        <v>45728.0</v>
+        <v>45700.0</v>
       </c>
       <c r="D340" t="n">
-        <v>7.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="341">
@@ -4902,10 +4902,10 @@
         <v>2025.0</v>
       </c>
       <c r="C341" t="n" s="2">
-        <v>45735.0</v>
+        <v>45707.0</v>
       </c>
       <c r="D341" t="n">
-        <v>4.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="342">
@@ -4916,10 +4916,10 @@
         <v>2025.0</v>
       </c>
       <c r="C342" t="n" s="2">
-        <v>45742.0</v>
+        <v>45714.0</v>
       </c>
       <c r="D342" t="n">
-        <v>6.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="343">
@@ -4930,10 +4930,10 @@
         <v>2025.0</v>
       </c>
       <c r="C343" t="n" s="2">
-        <v>45749.0</v>
+        <v>45721.0</v>
       </c>
       <c r="D343" t="n">
-        <v>2.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="344">
@@ -4944,10 +4944,10 @@
         <v>2025.0</v>
       </c>
       <c r="C344" t="n" s="2">
-        <v>45756.0</v>
+        <v>45728.0</v>
       </c>
       <c r="D344" t="n">
-        <v>5.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="345">
@@ -4958,7 +4958,7 @@
         <v>2025.0</v>
       </c>
       <c r="C345" t="n" s="2">
-        <v>45763.0</v>
+        <v>45735.0</v>
       </c>
       <c r="D345" t="n">
         <v>4.0</v>
@@ -4972,10 +4972,10 @@
         <v>2025.0</v>
       </c>
       <c r="C346" t="n" s="2">
-        <v>45770.0</v>
+        <v>45742.0</v>
       </c>
       <c r="D346" t="n">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="347">
@@ -4986,10 +4986,10 @@
         <v>2025.0</v>
       </c>
       <c r="C347" t="n" s="2">
-        <v>45777.0</v>
+        <v>45749.0</v>
       </c>
       <c r="D347" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="348">
@@ -5000,10 +5000,10 @@
         <v>2025.0</v>
       </c>
       <c r="C348" t="n" s="2">
-        <v>45784.0</v>
+        <v>45756.0</v>
       </c>
       <c r="D348" t="n">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="349">
@@ -5014,10 +5014,10 @@
         <v>2025.0</v>
       </c>
       <c r="C349" t="n" s="2">
-        <v>45791.0</v>
+        <v>45763.0</v>
       </c>
       <c r="D349" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="350">
@@ -5028,10 +5028,10 @@
         <v>2025.0</v>
       </c>
       <c r="C350" t="n" s="2">
-        <v>45840.0</v>
+        <v>45770.0</v>
       </c>
       <c r="D350" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="351">
@@ -5042,7 +5042,7 @@
         <v>2025.0</v>
       </c>
       <c r="C351" t="n" s="2">
-        <v>46001.0</v>
+        <v>45777.0</v>
       </c>
       <c r="D351" t="n">
         <v>1.0</v>
@@ -5053,10 +5053,10 @@
         <v>6</v>
       </c>
       <c r="B352" t="n">
-        <v>2026.0</v>
+        <v>2025.0</v>
       </c>
       <c r="C352" t="n" s="2">
-        <v>46037.0</v>
+        <v>45784.0</v>
       </c>
       <c r="D352" t="n">
         <v>1.0</v>
@@ -5064,13 +5064,13 @@
     </row>
     <row r="353">
       <c r="A353" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B353" t="n">
-        <v>2021.0</v>
+        <v>2025.0</v>
       </c>
       <c r="C353" t="n" s="2">
-        <v>44561.0</v>
+        <v>45791.0</v>
       </c>
       <c r="D353" t="n">
         <v>1.0</v>
@@ -5078,13 +5078,13 @@
     </row>
     <row r="354">
       <c r="A354" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B354" t="n">
-        <v>2022.0</v>
+        <v>2025.0</v>
       </c>
       <c r="C354" t="n" s="2">
-        <v>44569.0</v>
+        <v>45840.0</v>
       </c>
       <c r="D354" t="n">
         <v>1.0</v>
@@ -5092,30 +5092,30 @@
     </row>
     <row r="355">
       <c r="A355" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B355" t="n">
-        <v>2022.0</v>
+        <v>2025.0</v>
       </c>
       <c r="C355" t="n" s="2">
-        <v>44576.0</v>
+        <v>46001.0</v>
       </c>
       <c r="D355" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B356" t="n">
-        <v>2022.0</v>
+        <v>2026.0</v>
       </c>
       <c r="C356" t="n" s="2">
-        <v>44583.0</v>
+        <v>46037.0</v>
       </c>
       <c r="D356" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="357">
@@ -5123,13 +5123,13 @@
         <v>7</v>
       </c>
       <c r="B357" t="n">
-        <v>2022.0</v>
+        <v>2021.0</v>
       </c>
       <c r="C357" t="n" s="2">
-        <v>44590.0</v>
+        <v>44561.0</v>
       </c>
       <c r="D357" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="358">
@@ -5140,10 +5140,10 @@
         <v>2022.0</v>
       </c>
       <c r="C358" t="n" s="2">
-        <v>44604.0</v>
+        <v>44569.0</v>
       </c>
       <c r="D358" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="359">
@@ -5154,10 +5154,10 @@
         <v>2022.0</v>
       </c>
       <c r="C359" t="n" s="2">
-        <v>44611.0</v>
+        <v>44576.0</v>
       </c>
       <c r="D359" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="360">
@@ -5168,10 +5168,10 @@
         <v>2022.0</v>
       </c>
       <c r="C360" t="n" s="2">
-        <v>44618.0</v>
+        <v>44583.0</v>
       </c>
       <c r="D360" t="n">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="361">
@@ -5182,10 +5182,10 @@
         <v>2022.0</v>
       </c>
       <c r="C361" t="n" s="2">
-        <v>44625.0</v>
+        <v>44590.0</v>
       </c>
       <c r="D361" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="362">
@@ -5196,7 +5196,7 @@
         <v>2022.0</v>
       </c>
       <c r="C362" t="n" s="2">
-        <v>44632.0</v>
+        <v>44604.0</v>
       </c>
       <c r="D362" t="n">
         <v>3.0</v>
@@ -5210,10 +5210,10 @@
         <v>2022.0</v>
       </c>
       <c r="C363" t="n" s="2">
-        <v>44639.0</v>
+        <v>44611.0</v>
       </c>
       <c r="D363" t="n">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="364">
@@ -5224,10 +5224,10 @@
         <v>2022.0</v>
       </c>
       <c r="C364" t="n" s="2">
-        <v>44646.0</v>
+        <v>44618.0</v>
       </c>
       <c r="D364" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="365">
@@ -5238,10 +5238,10 @@
         <v>2022.0</v>
       </c>
       <c r="C365" t="n" s="2">
-        <v>44653.0</v>
+        <v>44625.0</v>
       </c>
       <c r="D365" t="n">
-        <v>9.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="366">
@@ -5252,10 +5252,10 @@
         <v>2022.0</v>
       </c>
       <c r="C366" t="n" s="2">
-        <v>44660.0</v>
+        <v>44632.0</v>
       </c>
       <c r="D366" t="n">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="367">
@@ -5266,10 +5266,10 @@
         <v>2022.0</v>
       </c>
       <c r="C367" t="n" s="2">
-        <v>44667.0</v>
+        <v>44639.0</v>
       </c>
       <c r="D367" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="368">
@@ -5280,10 +5280,10 @@
         <v>2022.0</v>
       </c>
       <c r="C368" t="n" s="2">
-        <v>44674.0</v>
+        <v>44646.0</v>
       </c>
       <c r="D368" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="369">
@@ -5294,10 +5294,10 @@
         <v>2022.0</v>
       </c>
       <c r="C369" t="n" s="2">
-        <v>44681.0</v>
+        <v>44653.0</v>
       </c>
       <c r="D369" t="n">
-        <v>2.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="370">
@@ -5308,7 +5308,7 @@
         <v>2022.0</v>
       </c>
       <c r="C370" t="n" s="2">
-        <v>44688.0</v>
+        <v>44660.0</v>
       </c>
       <c r="D370" t="n">
         <v>6.0</v>
@@ -5322,10 +5322,10 @@
         <v>2022.0</v>
       </c>
       <c r="C371" t="n" s="2">
-        <v>44695.0</v>
+        <v>44667.0</v>
       </c>
       <c r="D371" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="372">
@@ -5336,10 +5336,10 @@
         <v>2022.0</v>
       </c>
       <c r="C372" t="n" s="2">
-        <v>44702.0</v>
+        <v>44674.0</v>
       </c>
       <c r="D372" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="373">
@@ -5350,10 +5350,10 @@
         <v>2022.0</v>
       </c>
       <c r="C373" t="n" s="2">
-        <v>44709.0</v>
+        <v>44681.0</v>
       </c>
       <c r="D373" t="n">
-        <v>8.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="374">
@@ -5364,7 +5364,7 @@
         <v>2022.0</v>
       </c>
       <c r="C374" t="n" s="2">
-        <v>44716.0</v>
+        <v>44688.0</v>
       </c>
       <c r="D374" t="n">
         <v>6.0</v>
@@ -5378,10 +5378,10 @@
         <v>2022.0</v>
       </c>
       <c r="C375" t="n" s="2">
-        <v>44723.0</v>
+        <v>44695.0</v>
       </c>
       <c r="D375" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="376">
@@ -5392,10 +5392,10 @@
         <v>2022.0</v>
       </c>
       <c r="C376" t="n" s="2">
-        <v>44730.0</v>
+        <v>44702.0</v>
       </c>
       <c r="D376" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="377">
@@ -5406,10 +5406,10 @@
         <v>2022.0</v>
       </c>
       <c r="C377" t="n" s="2">
-        <v>44737.0</v>
+        <v>44709.0</v>
       </c>
       <c r="D377" t="n">
-        <v>4.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="378">
@@ -5420,10 +5420,10 @@
         <v>2022.0</v>
       </c>
       <c r="C378" t="n" s="2">
-        <v>44744.0</v>
+        <v>44716.0</v>
       </c>
       <c r="D378" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="379">
@@ -5434,10 +5434,10 @@
         <v>2022.0</v>
       </c>
       <c r="C379" t="n" s="2">
-        <v>44751.0</v>
+        <v>44723.0</v>
       </c>
       <c r="D379" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="380">
@@ -5448,10 +5448,10 @@
         <v>2022.0</v>
       </c>
       <c r="C380" t="n" s="2">
-        <v>44758.0</v>
+        <v>44730.0</v>
       </c>
       <c r="D380" t="n">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="381">
@@ -5462,10 +5462,10 @@
         <v>2022.0</v>
       </c>
       <c r="C381" t="n" s="2">
-        <v>44765.0</v>
+        <v>44737.0</v>
       </c>
       <c r="D381" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="382">
@@ -5476,10 +5476,10 @@
         <v>2022.0</v>
       </c>
       <c r="C382" t="n" s="2">
-        <v>44779.0</v>
+        <v>44744.0</v>
       </c>
       <c r="D382" t="n">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="383">
@@ -5490,10 +5490,10 @@
         <v>2022.0</v>
       </c>
       <c r="C383" t="n" s="2">
-        <v>44786.0</v>
+        <v>44751.0</v>
       </c>
       <c r="D383" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="384">
@@ -5504,10 +5504,10 @@
         <v>2022.0</v>
       </c>
       <c r="C384" t="n" s="2">
-        <v>44863.0</v>
+        <v>44758.0</v>
       </c>
       <c r="D384" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="385">
@@ -5518,7 +5518,7 @@
         <v>2022.0</v>
       </c>
       <c r="C385" t="n" s="2">
-        <v>44870.0</v>
+        <v>44765.0</v>
       </c>
       <c r="D385" t="n">
         <v>1.0</v>
@@ -5532,10 +5532,10 @@
         <v>2022.0</v>
       </c>
       <c r="C386" t="n" s="2">
-        <v>44884.0</v>
+        <v>44779.0</v>
       </c>
       <c r="D386" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="387">
@@ -5546,10 +5546,10 @@
         <v>2022.0</v>
       </c>
       <c r="C387" t="n" s="2">
-        <v>44891.0</v>
+        <v>44786.0</v>
       </c>
       <c r="D387" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="388">
@@ -5560,10 +5560,10 @@
         <v>2022.0</v>
       </c>
       <c r="C388" t="n" s="2">
-        <v>44898.0</v>
+        <v>44863.0</v>
       </c>
       <c r="D388" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="389">
@@ -5574,10 +5574,10 @@
         <v>2022.0</v>
       </c>
       <c r="C389" t="n" s="2">
-        <v>44912.0</v>
+        <v>44870.0</v>
       </c>
       <c r="D389" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="390">
@@ -5588,10 +5588,10 @@
         <v>2022.0</v>
       </c>
       <c r="C390" t="n" s="2">
-        <v>44919.0</v>
+        <v>44884.0</v>
       </c>
       <c r="D390" t="n">
-        <v>7.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="391">
@@ -5602,10 +5602,10 @@
         <v>2022.0</v>
       </c>
       <c r="C391" t="n" s="2">
-        <v>44926.0</v>
+        <v>44891.0</v>
       </c>
       <c r="D391" t="n">
-        <v>12.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="392">
@@ -5613,13 +5613,13 @@
         <v>7</v>
       </c>
       <c r="B392" t="n">
-        <v>2023.0</v>
+        <v>2022.0</v>
       </c>
       <c r="C392" t="n" s="2">
-        <v>44934.0</v>
+        <v>44898.0</v>
       </c>
       <c r="D392" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="393">
@@ -5627,13 +5627,13 @@
         <v>7</v>
       </c>
       <c r="B393" t="n">
-        <v>2023.0</v>
+        <v>2022.0</v>
       </c>
       <c r="C393" t="n" s="2">
-        <v>44941.0</v>
+        <v>44912.0</v>
       </c>
       <c r="D393" t="n">
-        <v>16.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="394">
@@ -5641,13 +5641,13 @@
         <v>7</v>
       </c>
       <c r="B394" t="n">
-        <v>2023.0</v>
+        <v>2022.0</v>
       </c>
       <c r="C394" t="n" s="2">
-        <v>44948.0</v>
+        <v>44919.0</v>
       </c>
       <c r="D394" t="n">
-        <v>5.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="395">
@@ -5655,13 +5655,13 @@
         <v>7</v>
       </c>
       <c r="B395" t="n">
-        <v>2023.0</v>
+        <v>2022.0</v>
       </c>
       <c r="C395" t="n" s="2">
-        <v>44955.0</v>
+        <v>44926.0</v>
       </c>
       <c r="D395" t="n">
-        <v>19.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="396">
@@ -5672,10 +5672,10 @@
         <v>2023.0</v>
       </c>
       <c r="C396" t="n" s="2">
-        <v>44962.0</v>
+        <v>44934.0</v>
       </c>
       <c r="D396" t="n">
-        <v>22.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="397">
@@ -5686,10 +5686,10 @@
         <v>2023.0</v>
       </c>
       <c r="C397" t="n" s="2">
-        <v>44969.0</v>
+        <v>44941.0</v>
       </c>
       <c r="D397" t="n">
-        <v>9.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="398">
@@ -5700,10 +5700,10 @@
         <v>2023.0</v>
       </c>
       <c r="C398" t="n" s="2">
-        <v>44976.0</v>
+        <v>44948.0</v>
       </c>
       <c r="D398" t="n">
-        <v>22.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="399">
@@ -5714,10 +5714,10 @@
         <v>2023.0</v>
       </c>
       <c r="C399" t="n" s="2">
-        <v>44983.0</v>
+        <v>44955.0</v>
       </c>
       <c r="D399" t="n">
-        <v>29.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="400">
@@ -5728,10 +5728,10 @@
         <v>2023.0</v>
       </c>
       <c r="C400" t="n" s="2">
-        <v>44990.0</v>
+        <v>44962.0</v>
       </c>
       <c r="D400" t="n">
-        <v>5.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="401">
@@ -5742,10 +5742,10 @@
         <v>2023.0</v>
       </c>
       <c r="C401" t="n" s="2">
-        <v>44997.0</v>
+        <v>44969.0</v>
       </c>
       <c r="D401" t="n">
-        <v>24.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="402">
@@ -5756,10 +5756,10 @@
         <v>2023.0</v>
       </c>
       <c r="C402" t="n" s="2">
-        <v>45004.0</v>
+        <v>44976.0</v>
       </c>
       <c r="D402" t="n">
-        <v>8.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="403">
@@ -5770,10 +5770,10 @@
         <v>2023.0</v>
       </c>
       <c r="C403" t="n" s="2">
-        <v>45011.0</v>
+        <v>44983.0</v>
       </c>
       <c r="D403" t="n">
-        <v>10.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="404">
@@ -5784,10 +5784,10 @@
         <v>2023.0</v>
       </c>
       <c r="C404" t="n" s="2">
-        <v>45018.0</v>
+        <v>44990.0</v>
       </c>
       <c r="D404" t="n">
-        <v>18.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="405">
@@ -5798,10 +5798,10 @@
         <v>2023.0</v>
       </c>
       <c r="C405" t="n" s="2">
-        <v>45025.0</v>
+        <v>44997.0</v>
       </c>
       <c r="D405" t="n">
-        <v>13.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="406">
@@ -5812,10 +5812,10 @@
         <v>2023.0</v>
       </c>
       <c r="C406" t="n" s="2">
-        <v>45032.0</v>
+        <v>45004.0</v>
       </c>
       <c r="D406" t="n">
-        <v>18.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="407">
@@ -5826,10 +5826,10 @@
         <v>2023.0</v>
       </c>
       <c r="C407" t="n" s="2">
-        <v>45039.0</v>
+        <v>45011.0</v>
       </c>
       <c r="D407" t="n">
-        <v>15.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="408">
@@ -5840,10 +5840,10 @@
         <v>2023.0</v>
       </c>
       <c r="C408" t="n" s="2">
-        <v>45046.0</v>
+        <v>45018.0</v>
       </c>
       <c r="D408" t="n">
-        <v>12.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="409">
@@ -5854,10 +5854,10 @@
         <v>2023.0</v>
       </c>
       <c r="C409" t="n" s="2">
-        <v>45053.0</v>
+        <v>45025.0</v>
       </c>
       <c r="D409" t="n">
-        <v>6.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="410">
@@ -5868,10 +5868,10 @@
         <v>2023.0</v>
       </c>
       <c r="C410" t="n" s="2">
-        <v>45060.0</v>
+        <v>45032.0</v>
       </c>
       <c r="D410" t="n">
-        <v>11.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="411">
@@ -5882,10 +5882,10 @@
         <v>2023.0</v>
       </c>
       <c r="C411" t="n" s="2">
-        <v>45067.0</v>
+        <v>45039.0</v>
       </c>
       <c r="D411" t="n">
-        <v>8.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="412">
@@ -5896,10 +5896,10 @@
         <v>2023.0</v>
       </c>
       <c r="C412" t="n" s="2">
-        <v>45074.0</v>
+        <v>45046.0</v>
       </c>
       <c r="D412" t="n">
-        <v>8.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="413">
@@ -5910,10 +5910,10 @@
         <v>2023.0</v>
       </c>
       <c r="C413" t="n" s="2">
-        <v>45081.0</v>
+        <v>45053.0</v>
       </c>
       <c r="D413" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="414">
@@ -5924,10 +5924,10 @@
         <v>2023.0</v>
       </c>
       <c r="C414" t="n" s="2">
-        <v>45088.0</v>
+        <v>45060.0</v>
       </c>
       <c r="D414" t="n">
-        <v>2.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="415">
@@ -5938,10 +5938,10 @@
         <v>2023.0</v>
       </c>
       <c r="C415" t="n" s="2">
-        <v>45095.0</v>
+        <v>45067.0</v>
       </c>
       <c r="D415" t="n">
-        <v>5.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="416">
@@ -5952,10 +5952,10 @@
         <v>2023.0</v>
       </c>
       <c r="C416" t="n" s="2">
-        <v>45102.0</v>
+        <v>45074.0</v>
       </c>
       <c r="D416" t="n">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="417">
@@ -5966,10 +5966,10 @@
         <v>2023.0</v>
       </c>
       <c r="C417" t="n" s="2">
-        <v>45109.0</v>
+        <v>45081.0</v>
       </c>
       <c r="D417" t="n">
-        <v>9.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="418">
@@ -5980,10 +5980,10 @@
         <v>2023.0</v>
       </c>
       <c r="C418" t="n" s="2">
-        <v>45116.0</v>
+        <v>45088.0</v>
       </c>
       <c r="D418" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="419">
@@ -5994,10 +5994,10 @@
         <v>2023.0</v>
       </c>
       <c r="C419" t="n" s="2">
-        <v>45123.0</v>
+        <v>45095.0</v>
       </c>
       <c r="D419" t="n">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="420">
@@ -6008,10 +6008,10 @@
         <v>2023.0</v>
       </c>
       <c r="C420" t="n" s="2">
-        <v>45130.0</v>
+        <v>45102.0</v>
       </c>
       <c r="D420" t="n">
-        <v>6.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="421">
@@ -6022,10 +6022,10 @@
         <v>2023.0</v>
       </c>
       <c r="C421" t="n" s="2">
-        <v>45137.0</v>
+        <v>45109.0</v>
       </c>
       <c r="D421" t="n">
-        <v>2.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="422">
@@ -6036,10 +6036,10 @@
         <v>2023.0</v>
       </c>
       <c r="C422" t="n" s="2">
-        <v>45144.0</v>
+        <v>45116.0</v>
       </c>
       <c r="D422" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="423">
@@ -6050,10 +6050,10 @@
         <v>2023.0</v>
       </c>
       <c r="C423" t="n" s="2">
-        <v>45151.0</v>
+        <v>45123.0</v>
       </c>
       <c r="D423" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="424">
@@ -6064,10 +6064,10 @@
         <v>2023.0</v>
       </c>
       <c r="C424" t="n" s="2">
-        <v>45165.0</v>
+        <v>45130.0</v>
       </c>
       <c r="D424" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="425">
@@ -6078,7 +6078,7 @@
         <v>2023.0</v>
       </c>
       <c r="C425" t="n" s="2">
-        <v>45172.0</v>
+        <v>45137.0</v>
       </c>
       <c r="D425" t="n">
         <v>2.0</v>
@@ -6092,10 +6092,10 @@
         <v>2023.0</v>
       </c>
       <c r="C426" t="n" s="2">
-        <v>45179.0</v>
+        <v>45144.0</v>
       </c>
       <c r="D426" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="427">
@@ -6106,10 +6106,10 @@
         <v>2023.0</v>
       </c>
       <c r="C427" t="n" s="2">
-        <v>45186.0</v>
+        <v>45151.0</v>
       </c>
       <c r="D427" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="428">
@@ -6120,10 +6120,10 @@
         <v>2023.0</v>
       </c>
       <c r="C428" t="n" s="2">
-        <v>45193.0</v>
+        <v>45165.0</v>
       </c>
       <c r="D428" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="429">
@@ -6134,10 +6134,10 @@
         <v>2023.0</v>
       </c>
       <c r="C429" t="n" s="2">
-        <v>45200.0</v>
+        <v>45172.0</v>
       </c>
       <c r="D429" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="430">
@@ -6148,7 +6148,7 @@
         <v>2023.0</v>
       </c>
       <c r="C430" t="n" s="2">
-        <v>45207.0</v>
+        <v>45179.0</v>
       </c>
       <c r="D430" t="n">
         <v>1.0</v>
@@ -6162,7 +6162,7 @@
         <v>2023.0</v>
       </c>
       <c r="C431" t="n" s="2">
-        <v>45235.0</v>
+        <v>45186.0</v>
       </c>
       <c r="D431" t="n">
         <v>1.0</v>
@@ -6176,10 +6176,10 @@
         <v>2023.0</v>
       </c>
       <c r="C432" t="n" s="2">
-        <v>45242.0</v>
+        <v>45193.0</v>
       </c>
       <c r="D432" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="433">
@@ -6190,10 +6190,10 @@
         <v>2023.0</v>
       </c>
       <c r="C433" t="n" s="2">
-        <v>45249.0</v>
+        <v>45200.0</v>
       </c>
       <c r="D433" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="434">
@@ -6204,10 +6204,10 @@
         <v>2023.0</v>
       </c>
       <c r="C434" t="n" s="2">
-        <v>45256.0</v>
+        <v>45207.0</v>
       </c>
       <c r="D434" t="n">
-        <v>9.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="435">
@@ -6218,10 +6218,10 @@
         <v>2023.0</v>
       </c>
       <c r="C435" t="n" s="2">
-        <v>45263.0</v>
+        <v>45235.0</v>
       </c>
       <c r="D435" t="n">
-        <v>12.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="436">
@@ -6232,10 +6232,10 @@
         <v>2023.0</v>
       </c>
       <c r="C436" t="n" s="2">
-        <v>45270.0</v>
+        <v>45242.0</v>
       </c>
       <c r="D436" t="n">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="437">
@@ -6246,10 +6246,10 @@
         <v>2023.0</v>
       </c>
       <c r="C437" t="n" s="2">
-        <v>45277.0</v>
+        <v>45249.0</v>
       </c>
       <c r="D437" t="n">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="438">
@@ -6260,10 +6260,10 @@
         <v>2023.0</v>
       </c>
       <c r="C438" t="n" s="2">
-        <v>45284.0</v>
+        <v>45256.0</v>
       </c>
       <c r="D438" t="n">
-        <v>7.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="439">
@@ -6274,10 +6274,10 @@
         <v>2023.0</v>
       </c>
       <c r="C439" t="n" s="2">
-        <v>45291.0</v>
+        <v>45263.0</v>
       </c>
       <c r="D439" t="n">
-        <v>13.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="440">
@@ -6285,10 +6285,10 @@
         <v>7</v>
       </c>
       <c r="B440" t="n">
-        <v>2024.0</v>
+        <v>2023.0</v>
       </c>
       <c r="C440" t="n" s="2">
-        <v>45299.0</v>
+        <v>45270.0</v>
       </c>
       <c r="D440" t="n">
         <v>6.0</v>
@@ -6299,13 +6299,13 @@
         <v>7</v>
       </c>
       <c r="B441" t="n">
-        <v>2024.0</v>
+        <v>2023.0</v>
       </c>
       <c r="C441" t="n" s="2">
-        <v>45306.0</v>
+        <v>45277.0</v>
       </c>
       <c r="D441" t="n">
-        <v>11.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="442">
@@ -6313,13 +6313,13 @@
         <v>7</v>
       </c>
       <c r="B442" t="n">
-        <v>2024.0</v>
+        <v>2023.0</v>
       </c>
       <c r="C442" t="n" s="2">
-        <v>45313.0</v>
+        <v>45284.0</v>
       </c>
       <c r="D442" t="n">
-        <v>5.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="443">
@@ -6327,13 +6327,13 @@
         <v>7</v>
       </c>
       <c r="B443" t="n">
-        <v>2024.0</v>
+        <v>2023.0</v>
       </c>
       <c r="C443" t="n" s="2">
-        <v>45320.0</v>
+        <v>45291.0</v>
       </c>
       <c r="D443" t="n">
-        <v>2.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="444">
@@ -6344,10 +6344,10 @@
         <v>2024.0</v>
       </c>
       <c r="C444" t="n" s="2">
-        <v>45327.0</v>
+        <v>45299.0</v>
       </c>
       <c r="D444" t="n">
-        <v>9.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="445">
@@ -6358,10 +6358,10 @@
         <v>2024.0</v>
       </c>
       <c r="C445" t="n" s="2">
-        <v>45334.0</v>
+        <v>45306.0</v>
       </c>
       <c r="D445" t="n">
-        <v>3.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="446">
@@ -6372,10 +6372,10 @@
         <v>2024.0</v>
       </c>
       <c r="C446" t="n" s="2">
-        <v>45341.0</v>
+        <v>45313.0</v>
       </c>
       <c r="D446" t="n">
-        <v>21.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="447">
@@ -6386,10 +6386,10 @@
         <v>2024.0</v>
       </c>
       <c r="C447" t="n" s="2">
-        <v>45348.0</v>
+        <v>45320.0</v>
       </c>
       <c r="D447" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="448">
@@ -6400,7 +6400,7 @@
         <v>2024.0</v>
       </c>
       <c r="C448" t="n" s="2">
-        <v>45355.0</v>
+        <v>45327.0</v>
       </c>
       <c r="D448" t="n">
         <v>9.0</v>
@@ -6414,10 +6414,10 @@
         <v>2024.0</v>
       </c>
       <c r="C449" t="n" s="2">
-        <v>45362.0</v>
+        <v>45334.0</v>
       </c>
       <c r="D449" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="450">
@@ -6428,10 +6428,10 @@
         <v>2024.0</v>
       </c>
       <c r="C450" t="n" s="2">
-        <v>45369.0</v>
+        <v>45341.0</v>
       </c>
       <c r="D450" t="n">
-        <v>14.0</v>
+        <v>21.0</v>
       </c>
     </row>
     <row r="451">
@@ -6442,10 +6442,10 @@
         <v>2024.0</v>
       </c>
       <c r="C451" t="n" s="2">
-        <v>45376.0</v>
+        <v>45348.0</v>
       </c>
       <c r="D451" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="452">
@@ -6456,10 +6456,10 @@
         <v>2024.0</v>
       </c>
       <c r="C452" t="n" s="2">
-        <v>45383.0</v>
+        <v>45355.0</v>
       </c>
       <c r="D452" t="n">
-        <v>2.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="453">
@@ -6470,10 +6470,10 @@
         <v>2024.0</v>
       </c>
       <c r="C453" t="n" s="2">
-        <v>45390.0</v>
+        <v>45362.0</v>
       </c>
       <c r="D453" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="454">
@@ -6484,10 +6484,10 @@
         <v>2024.0</v>
       </c>
       <c r="C454" t="n" s="2">
-        <v>45397.0</v>
+        <v>45369.0</v>
       </c>
       <c r="D454" t="n">
-        <v>1.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="455">
@@ -6498,10 +6498,10 @@
         <v>2024.0</v>
       </c>
       <c r="C455" t="n" s="2">
-        <v>45404.0</v>
+        <v>45376.0</v>
       </c>
       <c r="D455" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="456">
@@ -6512,10 +6512,10 @@
         <v>2024.0</v>
       </c>
       <c r="C456" t="n" s="2">
-        <v>45411.0</v>
+        <v>45383.0</v>
       </c>
       <c r="D456" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="457">
@@ -6526,10 +6526,10 @@
         <v>2024.0</v>
       </c>
       <c r="C457" t="n" s="2">
-        <v>45439.0</v>
+        <v>45390.0</v>
       </c>
       <c r="D457" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="458">
@@ -6540,7 +6540,7 @@
         <v>2024.0</v>
       </c>
       <c r="C458" t="n" s="2">
-        <v>45446.0</v>
+        <v>45397.0</v>
       </c>
       <c r="D458" t="n">
         <v>1.0</v>
@@ -6554,10 +6554,10 @@
         <v>2024.0</v>
       </c>
       <c r="C459" t="n" s="2">
-        <v>45460.0</v>
+        <v>45404.0</v>
       </c>
       <c r="D459" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="460">
@@ -6568,7 +6568,7 @@
         <v>2024.0</v>
       </c>
       <c r="C460" t="n" s="2">
-        <v>45481.0</v>
+        <v>45411.0</v>
       </c>
       <c r="D460" t="n">
         <v>1.0</v>
@@ -6582,10 +6582,10 @@
         <v>2024.0</v>
       </c>
       <c r="C461" t="n" s="2">
-        <v>45516.0</v>
+        <v>45439.0</v>
       </c>
       <c r="D461" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="462">
@@ -6596,7 +6596,7 @@
         <v>2024.0</v>
       </c>
       <c r="C462" t="n" s="2">
-        <v>45551.0</v>
+        <v>45446.0</v>
       </c>
       <c r="D462" t="n">
         <v>1.0</v>
@@ -6610,7 +6610,7 @@
         <v>2024.0</v>
       </c>
       <c r="C463" t="n" s="2">
-        <v>45579.0</v>
+        <v>45460.0</v>
       </c>
       <c r="D463" t="n">
         <v>1.0</v>
@@ -6624,7 +6624,7 @@
         <v>2024.0</v>
       </c>
       <c r="C464" t="n" s="2">
-        <v>45614.0</v>
+        <v>45481.0</v>
       </c>
       <c r="D464" t="n">
         <v>1.0</v>
@@ -6638,10 +6638,10 @@
         <v>2024.0</v>
       </c>
       <c r="C465" t="n" s="2">
-        <v>45635.0</v>
+        <v>45516.0</v>
       </c>
       <c r="D465" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="466">
@@ -6652,10 +6652,10 @@
         <v>2024.0</v>
       </c>
       <c r="C466" t="n" s="2">
-        <v>45642.0</v>
+        <v>45551.0</v>
       </c>
       <c r="D466" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="467">
@@ -6666,10 +6666,10 @@
         <v>2024.0</v>
       </c>
       <c r="C467" t="n" s="2">
-        <v>45649.0</v>
+        <v>45579.0</v>
       </c>
       <c r="D467" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="468">
@@ -6680,10 +6680,10 @@
         <v>2024.0</v>
       </c>
       <c r="C468" t="n" s="2">
-        <v>45656.0</v>
+        <v>45614.0</v>
       </c>
       <c r="D468" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="469">
@@ -6691,13 +6691,13 @@
         <v>7</v>
       </c>
       <c r="B469" t="n">
-        <v>2025.0</v>
+        <v>2024.0</v>
       </c>
       <c r="C469" t="n" s="2">
-        <v>45665.0</v>
+        <v>45635.0</v>
       </c>
       <c r="D469" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="470">
@@ -6705,10 +6705,10 @@
         <v>7</v>
       </c>
       <c r="B470" t="n">
-        <v>2025.0</v>
+        <v>2024.0</v>
       </c>
       <c r="C470" t="n" s="2">
-        <v>45672.0</v>
+        <v>45642.0</v>
       </c>
       <c r="D470" t="n">
         <v>2.0</v>
@@ -6719,13 +6719,13 @@
         <v>7</v>
       </c>
       <c r="B471" t="n">
-        <v>2025.0</v>
+        <v>2024.0</v>
       </c>
       <c r="C471" t="n" s="2">
-        <v>45686.0</v>
+        <v>45649.0</v>
       </c>
       <c r="D471" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="472">
@@ -6733,13 +6733,13 @@
         <v>7</v>
       </c>
       <c r="B472" t="n">
-        <v>2025.0</v>
+        <v>2024.0</v>
       </c>
       <c r="C472" t="n" s="2">
-        <v>45693.0</v>
+        <v>45656.0</v>
       </c>
       <c r="D472" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="473">
@@ -6750,10 +6750,10 @@
         <v>2025.0</v>
       </c>
       <c r="C473" t="n" s="2">
-        <v>45700.0</v>
+        <v>45665.0</v>
       </c>
       <c r="D473" t="n">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="474">
@@ -6764,10 +6764,10 @@
         <v>2025.0</v>
       </c>
       <c r="C474" t="n" s="2">
-        <v>45707.0</v>
+        <v>45672.0</v>
       </c>
       <c r="D474" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="475">
@@ -6778,10 +6778,10 @@
         <v>2025.0</v>
       </c>
       <c r="C475" t="n" s="2">
-        <v>45714.0</v>
+        <v>45686.0</v>
       </c>
       <c r="D475" t="n">
-        <v>8.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="476">
@@ -6792,10 +6792,10 @@
         <v>2025.0</v>
       </c>
       <c r="C476" t="n" s="2">
-        <v>45721.0</v>
+        <v>45693.0</v>
       </c>
       <c r="D476" t="n">
-        <v>11.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="477">
@@ -6806,7 +6806,7 @@
         <v>2025.0</v>
       </c>
       <c r="C477" t="n" s="2">
-        <v>45728.0</v>
+        <v>45700.0</v>
       </c>
       <c r="D477" t="n">
         <v>6.0</v>
@@ -6820,10 +6820,10 @@
         <v>2025.0</v>
       </c>
       <c r="C478" t="n" s="2">
-        <v>45735.0</v>
+        <v>45707.0</v>
       </c>
       <c r="D478" t="n">
-        <v>19.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="479">
@@ -6834,10 +6834,10 @@
         <v>2025.0</v>
       </c>
       <c r="C479" t="n" s="2">
-        <v>45742.0</v>
+        <v>45714.0</v>
       </c>
       <c r="D479" t="n">
-        <v>17.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="480">
@@ -6848,10 +6848,10 @@
         <v>2025.0</v>
       </c>
       <c r="C480" t="n" s="2">
-        <v>45749.0</v>
+        <v>45721.0</v>
       </c>
       <c r="D480" t="n">
-        <v>5.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="481">
@@ -6862,10 +6862,10 @@
         <v>2025.0</v>
       </c>
       <c r="C481" t="n" s="2">
-        <v>45756.0</v>
+        <v>45728.0</v>
       </c>
       <c r="D481" t="n">
-        <v>9.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="482">
@@ -6876,10 +6876,10 @@
         <v>2025.0</v>
       </c>
       <c r="C482" t="n" s="2">
-        <v>45763.0</v>
+        <v>45735.0</v>
       </c>
       <c r="D482" t="n">
-        <v>1.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="483">
@@ -6890,10 +6890,10 @@
         <v>2025.0</v>
       </c>
       <c r="C483" t="n" s="2">
-        <v>45770.0</v>
+        <v>45742.0</v>
       </c>
       <c r="D483" t="n">
-        <v>1.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="484">
@@ -6904,7 +6904,7 @@
         <v>2025.0</v>
       </c>
       <c r="C484" t="n" s="2">
-        <v>45784.0</v>
+        <v>45749.0</v>
       </c>
       <c r="D484" t="n">
         <v>5.0</v>
@@ -6918,10 +6918,10 @@
         <v>2025.0</v>
       </c>
       <c r="C485" t="n" s="2">
-        <v>45791.0</v>
+        <v>45756.0</v>
       </c>
       <c r="D485" t="n">
-        <v>2.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="486">
@@ -6932,7 +6932,7 @@
         <v>2025.0</v>
       </c>
       <c r="C486" t="n" s="2">
-        <v>45805.0</v>
+        <v>45763.0</v>
       </c>
       <c r="D486" t="n">
         <v>1.0</v>
@@ -6946,10 +6946,10 @@
         <v>2025.0</v>
       </c>
       <c r="C487" t="n" s="2">
-        <v>45826.0</v>
+        <v>45770.0</v>
       </c>
       <c r="D487" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="488">
@@ -6960,10 +6960,10 @@
         <v>2025.0</v>
       </c>
       <c r="C488" t="n" s="2">
-        <v>45861.0</v>
+        <v>45784.0</v>
       </c>
       <c r="D488" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="489">
@@ -6974,10 +6974,10 @@
         <v>2025.0</v>
       </c>
       <c r="C489" t="n" s="2">
-        <v>45868.0</v>
+        <v>45791.0</v>
       </c>
       <c r="D489" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="490">
@@ -6988,7 +6988,7 @@
         <v>2025.0</v>
       </c>
       <c r="C490" t="n" s="2">
-        <v>45889.0</v>
+        <v>45805.0</v>
       </c>
       <c r="D490" t="n">
         <v>1.0</v>
@@ -7002,10 +7002,10 @@
         <v>2025.0</v>
       </c>
       <c r="C491" t="n" s="2">
-        <v>45924.0</v>
+        <v>45826.0</v>
       </c>
       <c r="D491" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="492">
@@ -7016,10 +7016,10 @@
         <v>2025.0</v>
       </c>
       <c r="C492" t="n" s="2">
-        <v>45945.0</v>
+        <v>45861.0</v>
       </c>
       <c r="D492" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="493">
@@ -7030,10 +7030,10 @@
         <v>2025.0</v>
       </c>
       <c r="C493" t="n" s="2">
-        <v>45959.0</v>
+        <v>45868.0</v>
       </c>
       <c r="D493" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="494">
@@ -7044,10 +7044,10 @@
         <v>2025.0</v>
       </c>
       <c r="C494" t="n" s="2">
-        <v>46001.0</v>
+        <v>45889.0</v>
       </c>
       <c r="D494" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="495">
@@ -7058,7 +7058,7 @@
         <v>2025.0</v>
       </c>
       <c r="C495" t="n" s="2">
-        <v>46008.0</v>
+        <v>45924.0</v>
       </c>
       <c r="D495" t="n">
         <v>1.0</v>
@@ -7072,7 +7072,7 @@
         <v>2025.0</v>
       </c>
       <c r="C496" t="n" s="2">
-        <v>46022.0</v>
+        <v>45945.0</v>
       </c>
       <c r="D496" t="n">
         <v>1.0</v>
@@ -7083,13 +7083,13 @@
         <v>7</v>
       </c>
       <c r="B497" t="n">
-        <v>2026.0</v>
+        <v>2025.0</v>
       </c>
       <c r="C497" t="n" s="2">
-        <v>46030.0</v>
+        <v>45959.0</v>
       </c>
       <c r="D497" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="498">
@@ -7097,13 +7097,13 @@
         <v>7</v>
       </c>
       <c r="B498" t="n">
-        <v>2026.0</v>
+        <v>2025.0</v>
       </c>
       <c r="C498" t="n" s="2">
-        <v>46051.0</v>
+        <v>46001.0</v>
       </c>
       <c r="D498" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="499">
@@ -7111,10 +7111,10 @@
         <v>7</v>
       </c>
       <c r="B499" t="n">
-        <v>2026.0</v>
+        <v>2025.0</v>
       </c>
       <c r="C499" t="n" s="2">
-        <v>46058.0</v>
+        <v>46008.0</v>
       </c>
       <c r="D499" t="n">
         <v>1.0</v>
@@ -7125,24 +7125,24 @@
         <v>7</v>
       </c>
       <c r="B500" t="n">
-        <v>2026.0</v>
+        <v>2025.0</v>
       </c>
       <c r="C500" t="n" s="2">
-        <v>46065.0</v>
+        <v>46022.0</v>
       </c>
       <c r="D500" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B501" t="n">
-        <v>2024.0</v>
+        <v>2026.0</v>
       </c>
       <c r="C501" t="n" s="2">
-        <v>45495.0</v>
+        <v>46030.0</v>
       </c>
       <c r="D501" t="n">
         <v>1.0</v>
@@ -7150,27 +7150,27 @@
     </row>
     <row r="502">
       <c r="A502" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B502" t="n">
-        <v>2024.0</v>
+        <v>2026.0</v>
       </c>
       <c r="C502" t="n" s="2">
-        <v>45502.0</v>
+        <v>46051.0</v>
       </c>
       <c r="D502" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B503" t="n">
-        <v>2025.0</v>
+        <v>2026.0</v>
       </c>
       <c r="C503" t="n" s="2">
-        <v>45665.0</v>
+        <v>46058.0</v>
       </c>
       <c r="D503" t="n">
         <v>1.0</v>
@@ -7178,16 +7178,16 @@
     </row>
     <row r="504">
       <c r="A504" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B504" t="n">
-        <v>2025.0</v>
+        <v>2026.0</v>
       </c>
       <c r="C504" t="n" s="2">
-        <v>45672.0</v>
+        <v>46065.0</v>
       </c>
       <c r="D504" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="505">
@@ -7195,10 +7195,10 @@
         <v>8</v>
       </c>
       <c r="B505" t="n">
-        <v>2025.0</v>
+        <v>2024.0</v>
       </c>
       <c r="C505" t="n" s="2">
-        <v>45679.0</v>
+        <v>45495.0</v>
       </c>
       <c r="D505" t="n">
         <v>1.0</v>
@@ -7209,13 +7209,13 @@
         <v>8</v>
       </c>
       <c r="B506" t="n">
-        <v>2025.0</v>
+        <v>2024.0</v>
       </c>
       <c r="C506" t="n" s="2">
-        <v>45686.0</v>
+        <v>45502.0</v>
       </c>
       <c r="D506" t="n">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="507">
@@ -7226,7 +7226,7 @@
         <v>2025.0</v>
       </c>
       <c r="C507" t="n" s="2">
-        <v>45693.0</v>
+        <v>45665.0</v>
       </c>
       <c r="D507" t="n">
         <v>1.0</v>
@@ -7240,10 +7240,10 @@
         <v>2025.0</v>
       </c>
       <c r="C508" t="n" s="2">
-        <v>45700.0</v>
+        <v>45672.0</v>
       </c>
       <c r="D508" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="509">
@@ -7254,10 +7254,10 @@
         <v>2025.0</v>
       </c>
       <c r="C509" t="n" s="2">
-        <v>45707.0</v>
+        <v>45679.0</v>
       </c>
       <c r="D509" t="n">
-        <v>7.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="510">
@@ -7268,10 +7268,10 @@
         <v>2025.0</v>
       </c>
       <c r="C510" t="n" s="2">
-        <v>45714.0</v>
+        <v>45686.0</v>
       </c>
       <c r="D510" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="511">
@@ -7282,10 +7282,10 @@
         <v>2025.0</v>
       </c>
       <c r="C511" t="n" s="2">
-        <v>45721.0</v>
+        <v>45693.0</v>
       </c>
       <c r="D511" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="512">
@@ -7296,10 +7296,10 @@
         <v>2025.0</v>
       </c>
       <c r="C512" t="n" s="2">
-        <v>45728.0</v>
+        <v>45700.0</v>
       </c>
       <c r="D512" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="513">
@@ -7310,10 +7310,10 @@
         <v>2025.0</v>
       </c>
       <c r="C513" t="n" s="2">
-        <v>45742.0</v>
+        <v>45707.0</v>
       </c>
       <c r="D513" t="n">
-        <v>1.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="514">
@@ -7324,10 +7324,10 @@
         <v>2025.0</v>
       </c>
       <c r="C514" t="n" s="2">
-        <v>45749.0</v>
+        <v>45714.0</v>
       </c>
       <c r="D514" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="515">
@@ -7338,10 +7338,10 @@
         <v>2025.0</v>
       </c>
       <c r="C515" t="n" s="2">
-        <v>45763.0</v>
+        <v>45721.0</v>
       </c>
       <c r="D515" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="516">
@@ -7352,10 +7352,10 @@
         <v>2025.0</v>
       </c>
       <c r="C516" t="n" s="2">
-        <v>45777.0</v>
+        <v>45728.0</v>
       </c>
       <c r="D516" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="517">
@@ -7366,7 +7366,7 @@
         <v>2025.0</v>
       </c>
       <c r="C517" t="n" s="2">
-        <v>45784.0</v>
+        <v>45742.0</v>
       </c>
       <c r="D517" t="n">
         <v>1.0</v>
@@ -7380,7 +7380,7 @@
         <v>2025.0</v>
       </c>
       <c r="C518" t="n" s="2">
-        <v>45798.0</v>
+        <v>45749.0</v>
       </c>
       <c r="D518" t="n">
         <v>1.0</v>
@@ -7394,7 +7394,7 @@
         <v>2025.0</v>
       </c>
       <c r="C519" t="n" s="2">
-        <v>45805.0</v>
+        <v>45763.0</v>
       </c>
       <c r="D519" t="n">
         <v>1.0</v>
@@ -7408,10 +7408,10 @@
         <v>2025.0</v>
       </c>
       <c r="C520" t="n" s="2">
-        <v>45812.0</v>
+        <v>45777.0</v>
       </c>
       <c r="D520" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="521">
@@ -7422,10 +7422,10 @@
         <v>2025.0</v>
       </c>
       <c r="C521" t="n" s="2">
-        <v>45819.0</v>
+        <v>45784.0</v>
       </c>
       <c r="D521" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="522">
@@ -7436,10 +7436,10 @@
         <v>2025.0</v>
       </c>
       <c r="C522" t="n" s="2">
-        <v>45833.0</v>
+        <v>45798.0</v>
       </c>
       <c r="D522" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="523">
@@ -7450,10 +7450,10 @@
         <v>2025.0</v>
       </c>
       <c r="C523" t="n" s="2">
-        <v>45847.0</v>
+        <v>45805.0</v>
       </c>
       <c r="D523" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="524">
@@ -7464,10 +7464,10 @@
         <v>2025.0</v>
       </c>
       <c r="C524" t="n" s="2">
-        <v>45854.0</v>
+        <v>45812.0</v>
       </c>
       <c r="D524" t="n">
-        <v>8.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="525">
@@ -7478,10 +7478,10 @@
         <v>2025.0</v>
       </c>
       <c r="C525" t="n" s="2">
-        <v>45861.0</v>
+        <v>45819.0</v>
       </c>
       <c r="D525" t="n">
-        <v>12.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="526">
@@ -7492,10 +7492,10 @@
         <v>2025.0</v>
       </c>
       <c r="C526" t="n" s="2">
-        <v>45868.0</v>
+        <v>45833.0</v>
       </c>
       <c r="D526" t="n">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="527">
@@ -7506,10 +7506,10 @@
         <v>2025.0</v>
       </c>
       <c r="C527" t="n" s="2">
-        <v>45875.0</v>
+        <v>45847.0</v>
       </c>
       <c r="D527" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="528">
@@ -7520,10 +7520,10 @@
         <v>2025.0</v>
       </c>
       <c r="C528" t="n" s="2">
-        <v>45896.0</v>
+        <v>45854.0</v>
       </c>
       <c r="D528" t="n">
-        <v>1.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="529">
@@ -7534,10 +7534,10 @@
         <v>2025.0</v>
       </c>
       <c r="C529" t="n" s="2">
-        <v>45903.0</v>
+        <v>45861.0</v>
       </c>
       <c r="D529" t="n">
-        <v>1.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="530">
@@ -7548,10 +7548,10 @@
         <v>2025.0</v>
       </c>
       <c r="C530" t="n" s="2">
-        <v>45931.0</v>
+        <v>45868.0</v>
       </c>
       <c r="D530" t="n">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="531">
@@ -7562,10 +7562,10 @@
         <v>2025.0</v>
       </c>
       <c r="C531" t="n" s="2">
-        <v>45938.0</v>
+        <v>45875.0</v>
       </c>
       <c r="D531" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="532">
@@ -7576,10 +7576,10 @@
         <v>2025.0</v>
       </c>
       <c r="C532" t="n" s="2">
-        <v>45945.0</v>
+        <v>45896.0</v>
       </c>
       <c r="D532" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="533">
@@ -7590,10 +7590,10 @@
         <v>2025.0</v>
       </c>
       <c r="C533" t="n" s="2">
-        <v>45966.0</v>
+        <v>45903.0</v>
       </c>
       <c r="D533" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="534">
@@ -7604,10 +7604,10 @@
         <v>2025.0</v>
       </c>
       <c r="C534" t="n" s="2">
-        <v>45973.0</v>
+        <v>45931.0</v>
       </c>
       <c r="D534" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="535">
@@ -7618,10 +7618,10 @@
         <v>2025.0</v>
       </c>
       <c r="C535" t="n" s="2">
-        <v>45980.0</v>
+        <v>45938.0</v>
       </c>
       <c r="D535" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="536">
@@ -7632,10 +7632,10 @@
         <v>2025.0</v>
       </c>
       <c r="C536" t="n" s="2">
-        <v>45987.0</v>
+        <v>45945.0</v>
       </c>
       <c r="D536" t="n">
-        <v>20.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="537">
@@ -7646,10 +7646,10 @@
         <v>2025.0</v>
       </c>
       <c r="C537" t="n" s="2">
-        <v>45994.0</v>
+        <v>45966.0</v>
       </c>
       <c r="D537" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="538">
@@ -7660,10 +7660,10 @@
         <v>2025.0</v>
       </c>
       <c r="C538" t="n" s="2">
-        <v>46001.0</v>
+        <v>45973.0</v>
       </c>
       <c r="D538" t="n">
-        <v>8.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="539">
@@ -7674,10 +7674,10 @@
         <v>2025.0</v>
       </c>
       <c r="C539" t="n" s="2">
-        <v>46008.0</v>
+        <v>45980.0</v>
       </c>
       <c r="D539" t="n">
-        <v>24.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="540">
@@ -7688,10 +7688,10 @@
         <v>2025.0</v>
       </c>
       <c r="C540" t="n" s="2">
-        <v>46015.0</v>
+        <v>45987.0</v>
       </c>
       <c r="D540" t="n">
-        <v>13.0</v>
+        <v>20.0</v>
       </c>
     </row>
     <row r="541">
@@ -7702,10 +7702,10 @@
         <v>2025.0</v>
       </c>
       <c r="C541" t="n" s="2">
-        <v>46022.0</v>
+        <v>45994.0</v>
       </c>
       <c r="D541" t="n">
-        <v>7.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="542">
@@ -7716,10 +7716,10 @@
         <v>2025.0</v>
       </c>
       <c r="C542" t="n" s="2">
-        <v>46029.0</v>
+        <v>46001.0</v>
       </c>
       <c r="D542" t="n">
-        <v>3.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="543">
@@ -7727,10 +7727,10 @@
         <v>8</v>
       </c>
       <c r="B543" t="n">
-        <v>2026.0</v>
+        <v>2025.0</v>
       </c>
       <c r="C543" t="n" s="2">
-        <v>46030.0</v>
+        <v>46008.0</v>
       </c>
       <c r="D543" t="n">
         <v>24.0</v>
@@ -7741,13 +7741,13 @@
         <v>8</v>
       </c>
       <c r="B544" t="n">
-        <v>2026.0</v>
+        <v>2025.0</v>
       </c>
       <c r="C544" t="n" s="2">
-        <v>46037.0</v>
+        <v>46015.0</v>
       </c>
       <c r="D544" t="n">
-        <v>22.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="545">
@@ -7755,13 +7755,13 @@
         <v>8</v>
       </c>
       <c r="B545" t="n">
-        <v>2026.0</v>
+        <v>2025.0</v>
       </c>
       <c r="C545" t="n" s="2">
-        <v>46044.0</v>
+        <v>46022.0</v>
       </c>
       <c r="D545" t="n">
-        <v>27.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="546">
@@ -7769,13 +7769,13 @@
         <v>8</v>
       </c>
       <c r="B546" t="n">
-        <v>2026.0</v>
+        <v>2025.0</v>
       </c>
       <c r="C546" t="n" s="2">
-        <v>46051.0</v>
+        <v>46029.0</v>
       </c>
       <c r="D546" t="n">
-        <v>18.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="547">
@@ -7786,10 +7786,10 @@
         <v>2026.0</v>
       </c>
       <c r="C547" t="n" s="2">
-        <v>46058.0</v>
+        <v>46030.0</v>
       </c>
       <c r="D547" t="n">
-        <v>25.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="548">
@@ -7800,7 +7800,7 @@
         <v>2026.0</v>
       </c>
       <c r="C548" t="n" s="2">
-        <v>46065.0</v>
+        <v>46037.0</v>
       </c>
       <c r="D548" t="n">
         <v>22.0</v>
@@ -7814,10 +7814,10 @@
         <v>2026.0</v>
       </c>
       <c r="C549" t="n" s="2">
-        <v>46072.0</v>
+        <v>46044.0</v>
       </c>
       <c r="D549" t="n">
-        <v>13.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="550">
@@ -7828,10 +7828,10 @@
         <v>2026.0</v>
       </c>
       <c r="C550" t="n" s="2">
-        <v>46079.0</v>
+        <v>46051.0</v>
       </c>
       <c r="D550" t="n">
-        <v>24.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="551">
@@ -7842,10 +7842,80 @@
         <v>2026.0</v>
       </c>
       <c r="C551" t="n" s="2">
+        <v>46058.0</v>
+      </c>
+      <c r="D551" t="n">
+        <v>25.0</v>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="s">
+        <v>8</v>
+      </c>
+      <c r="B552" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C552" t="n" s="2">
+        <v>46065.0</v>
+      </c>
+      <c r="D552" t="n">
+        <v>22.0</v>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="s">
+        <v>8</v>
+      </c>
+      <c r="B553" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C553" t="n" s="2">
+        <v>46072.0</v>
+      </c>
+      <c r="D553" t="n">
+        <v>13.0</v>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="s">
+        <v>8</v>
+      </c>
+      <c r="B554" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C554" t="n" s="2">
+        <v>46079.0</v>
+      </c>
+      <c r="D554" t="n">
+        <v>24.0</v>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="s">
+        <v>8</v>
+      </c>
+      <c r="B555" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C555" t="n" s="2">
         <v>46086.0</v>
       </c>
-      <c r="D551" t="n">
-        <v>4.0</v>
+      <c r="D555" t="n">
+        <v>26.0</v>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="s">
+        <v>8</v>
+      </c>
+      <c r="B556" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C556" t="n" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="D556" t="n">
+        <v>27.0</v>
       </c>
     </row>
   </sheetData>
@@ -7871,7 +7941,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="n">
-        <v>44.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="3">
@@ -7879,7 +7949,7 @@
         <v>11</v>
       </c>
       <c r="B3" t="n">
-        <v>169.0</v>
+        <v>179.0</v>
       </c>
     </row>
     <row r="4">
@@ -7887,7 +7957,7 @@
         <v>12</v>
       </c>
       <c r="B4" t="n">
-        <v>1104.0</v>
+        <v>1127.0</v>
       </c>
     </row>
     <row r="5">
@@ -7895,7 +7965,7 @@
         <v>13</v>
       </c>
       <c r="B5" t="n">
-        <v>1983.0</v>
+        <v>2007.0</v>
       </c>
     </row>
   </sheetData>
@@ -7949,7 +8019,7 @@
         <v>19</v>
       </c>
       <c r="C4" t="n">
-        <v>126.0</v>
+        <v>128.0</v>
       </c>
     </row>
     <row r="5">
@@ -7960,7 +8030,7 @@
         <v>21</v>
       </c>
       <c r="C5" t="n">
-        <v>394.0</v>
+        <v>402.0</v>
       </c>
     </row>
     <row r="6">
@@ -7971,7 +8041,7 @@
         <v>22</v>
       </c>
       <c r="C6" t="n">
-        <v>284.0</v>
+        <v>285.0</v>
       </c>
     </row>
     <row r="7">
@@ -7982,7 +8052,7 @@
         <v>19</v>
       </c>
       <c r="C7" t="n">
-        <v>148.0</v>
+        <v>151.0</v>
       </c>
     </row>
     <row r="8">
@@ -7993,7 +8063,7 @@
         <v>21</v>
       </c>
       <c r="C8" t="n">
-        <v>339.0</v>
+        <v>341.0</v>
       </c>
     </row>
     <row r="9">
@@ -8004,7 +8074,7 @@
         <v>22</v>
       </c>
       <c r="C9" t="n">
-        <v>320.0</v>
+        <v>322.0</v>
       </c>
     </row>
     <row r="10">
@@ -8026,7 +8096,7 @@
         <v>19</v>
       </c>
       <c r="C11" t="n">
-        <v>30.0</v>
+        <v>34.0</v>
       </c>
     </row>
     <row r="12">
@@ -8037,7 +8107,7 @@
         <v>21</v>
       </c>
       <c r="C12" t="n">
-        <v>52.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="13">
@@ -8059,7 +8129,7 @@
         <v>19</v>
       </c>
       <c r="C14" t="n">
-        <v>315.0</v>
+        <v>338.0</v>
       </c>
     </row>
     <row r="15">
@@ -8070,7 +8140,7 @@
         <v>21</v>
       </c>
       <c r="C15" t="n">
-        <v>349.0</v>
+        <v>353.0</v>
       </c>
     </row>
     <row r="16">
@@ -8081,7 +8151,7 @@
         <v>22</v>
       </c>
       <c r="C16" t="n">
-        <v>328.0</v>
+        <v>337.0</v>
       </c>
     </row>
     <row r="17">
@@ -8092,7 +8162,7 @@
         <v>19</v>
       </c>
       <c r="C17" t="n">
-        <v>98.0</v>
+        <v>100.0</v>
       </c>
     </row>
   </sheetData>

--- a/Download/Focus_Positivi_ZR.xlsx
+++ b/Download/Focus_Positivi_ZR.xlsx
@@ -1517,7 +1517,7 @@
         <v>46093.0</v>
       </c>
       <c r="D99" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="100">
@@ -4079,7 +4079,7 @@
         <v>46093.0</v>
       </c>
       <c r="D282" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="283">
@@ -7941,7 +7941,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="n">
-        <v>48.0</v>
+        <v>45.0</v>
       </c>
     </row>
     <row r="3">
@@ -7949,7 +7949,7 @@
         <v>11</v>
       </c>
       <c r="B3" t="n">
-        <v>179.0</v>
+        <v>180.0</v>
       </c>
     </row>
     <row r="4">
@@ -7957,7 +7957,7 @@
         <v>12</v>
       </c>
       <c r="B4" t="n">
-        <v>1127.0</v>
+        <v>1131.0</v>
       </c>
     </row>
     <row r="5">
@@ -8019,7 +8019,7 @@
         <v>19</v>
       </c>
       <c r="C4" t="n">
-        <v>128.0</v>
+        <v>129.0</v>
       </c>
     </row>
     <row r="5">
@@ -8041,7 +8041,7 @@
         <v>22</v>
       </c>
       <c r="C6" t="n">
-        <v>285.0</v>
+        <v>286.0</v>
       </c>
     </row>
     <row r="7">
@@ -8096,7 +8096,7 @@
         <v>19</v>
       </c>
       <c r="C11" t="n">
-        <v>34.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="12">
@@ -8129,7 +8129,7 @@
         <v>19</v>
       </c>
       <c r="C14" t="n">
-        <v>338.0</v>
+        <v>340.0</v>
       </c>
     </row>
     <row r="15">
@@ -8151,7 +8151,7 @@
         <v>22</v>
       </c>
       <c r="C16" t="n">
-        <v>337.0</v>
+        <v>338.0</v>
       </c>
     </row>
     <row r="17">

--- a/Download/Focus_Positivi_ZR.xlsx
+++ b/Download/Focus_Positivi_ZR.xlsx
@@ -7915,7 +7915,7 @@
         <v>46093.0</v>
       </c>
       <c r="D556" t="n">
-        <v>27.0</v>
+        <v>30.0</v>
       </c>
     </row>
   </sheetData>
@@ -7941,7 +7941,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="n">
-        <v>45.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="3">
@@ -8096,7 +8096,7 @@
         <v>19</v>
       </c>
       <c r="C11" t="n">
-        <v>31.0</v>
+        <v>34.0</v>
       </c>
     </row>
     <row r="12">

--- a/Download/Focus_Positivi_ZR.xlsx
+++ b/Download/Focus_Positivi_ZR.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="600" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="601" uniqueCount="23">
   <si>
     <t>NOME_REGIONE</t>
   </si>
@@ -1522,13 +1522,13 @@
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B100" t="n">
-        <v>2021.0</v>
+        <v>2026.0</v>
       </c>
       <c r="C100" t="n" s="2">
-        <v>44561.0</v>
+        <v>46100.0</v>
       </c>
       <c r="D100" t="n">
         <v>1.0</v>
@@ -1539,13 +1539,13 @@
         <v>5</v>
       </c>
       <c r="B101" t="n">
-        <v>2022.0</v>
+        <v>2021.0</v>
       </c>
       <c r="C101" t="n" s="2">
-        <v>44576.0</v>
+        <v>44561.0</v>
       </c>
       <c r="D101" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="102">
@@ -1556,10 +1556,10 @@
         <v>2022.0</v>
       </c>
       <c r="C102" t="n" s="2">
-        <v>44583.0</v>
+        <v>44576.0</v>
       </c>
       <c r="D102" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="103">
@@ -1570,10 +1570,10 @@
         <v>2022.0</v>
       </c>
       <c r="C103" t="n" s="2">
-        <v>44590.0</v>
+        <v>44583.0</v>
       </c>
       <c r="D103" t="n">
-        <v>7.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="104">
@@ -1584,10 +1584,10 @@
         <v>2022.0</v>
       </c>
       <c r="C104" t="n" s="2">
-        <v>44597.0</v>
+        <v>44590.0</v>
       </c>
       <c r="D104" t="n">
-        <v>3.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="105">
@@ -1598,10 +1598,10 @@
         <v>2022.0</v>
       </c>
       <c r="C105" t="n" s="2">
-        <v>44604.0</v>
+        <v>44597.0</v>
       </c>
       <c r="D105" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="106">
@@ -1612,10 +1612,10 @@
         <v>2022.0</v>
       </c>
       <c r="C106" t="n" s="2">
-        <v>44611.0</v>
+        <v>44604.0</v>
       </c>
       <c r="D106" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="107">
@@ -1626,7 +1626,7 @@
         <v>2022.0</v>
       </c>
       <c r="C107" t="n" s="2">
-        <v>44618.0</v>
+        <v>44611.0</v>
       </c>
       <c r="D107" t="n">
         <v>1.0</v>
@@ -1640,10 +1640,10 @@
         <v>2022.0</v>
       </c>
       <c r="C108" t="n" s="2">
-        <v>44625.0</v>
+        <v>44618.0</v>
       </c>
       <c r="D108" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="109">
@@ -1654,10 +1654,10 @@
         <v>2022.0</v>
       </c>
       <c r="C109" t="n" s="2">
-        <v>44632.0</v>
+        <v>44625.0</v>
       </c>
       <c r="D109" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="110">
@@ -1668,10 +1668,10 @@
         <v>2022.0</v>
       </c>
       <c r="C110" t="n" s="2">
-        <v>44639.0</v>
+        <v>44632.0</v>
       </c>
       <c r="D110" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="111">
@@ -1682,7 +1682,7 @@
         <v>2022.0</v>
       </c>
       <c r="C111" t="n" s="2">
-        <v>44646.0</v>
+        <v>44639.0</v>
       </c>
       <c r="D111" t="n">
         <v>2.0</v>
@@ -1696,7 +1696,7 @@
         <v>2022.0</v>
       </c>
       <c r="C112" t="n" s="2">
-        <v>44653.0</v>
+        <v>44646.0</v>
       </c>
       <c r="D112" t="n">
         <v>2.0</v>
@@ -1710,10 +1710,10 @@
         <v>2022.0</v>
       </c>
       <c r="C113" t="n" s="2">
-        <v>44660.0</v>
+        <v>44653.0</v>
       </c>
       <c r="D113" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="114">
@@ -1724,10 +1724,10 @@
         <v>2022.0</v>
       </c>
       <c r="C114" t="n" s="2">
-        <v>44667.0</v>
+        <v>44660.0</v>
       </c>
       <c r="D114" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="115">
@@ -1738,7 +1738,7 @@
         <v>2022.0</v>
       </c>
       <c r="C115" t="n" s="2">
-        <v>44674.0</v>
+        <v>44667.0</v>
       </c>
       <c r="D115" t="n">
         <v>3.0</v>
@@ -1752,10 +1752,10 @@
         <v>2022.0</v>
       </c>
       <c r="C116" t="n" s="2">
-        <v>44681.0</v>
+        <v>44674.0</v>
       </c>
       <c r="D116" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="117">
@@ -1766,10 +1766,10 @@
         <v>2022.0</v>
       </c>
       <c r="C117" t="n" s="2">
-        <v>44688.0</v>
+        <v>44681.0</v>
       </c>
       <c r="D117" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="118">
@@ -1780,7 +1780,7 @@
         <v>2022.0</v>
       </c>
       <c r="C118" t="n" s="2">
-        <v>44695.0</v>
+        <v>44688.0</v>
       </c>
       <c r="D118" t="n">
         <v>3.0</v>
@@ -1794,10 +1794,10 @@
         <v>2022.0</v>
       </c>
       <c r="C119" t="n" s="2">
-        <v>44702.0</v>
+        <v>44695.0</v>
       </c>
       <c r="D119" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="120">
@@ -1808,10 +1808,10 @@
         <v>2022.0</v>
       </c>
       <c r="C120" t="n" s="2">
-        <v>44709.0</v>
+        <v>44702.0</v>
       </c>
       <c r="D120" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="121">
@@ -1822,10 +1822,10 @@
         <v>2022.0</v>
       </c>
       <c r="C121" t="n" s="2">
-        <v>44716.0</v>
+        <v>44709.0</v>
       </c>
       <c r="D121" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="122">
@@ -1836,7 +1836,7 @@
         <v>2022.0</v>
       </c>
       <c r="C122" t="n" s="2">
-        <v>44723.0</v>
+        <v>44716.0</v>
       </c>
       <c r="D122" t="n">
         <v>1.0</v>
@@ -1850,7 +1850,7 @@
         <v>2022.0</v>
       </c>
       <c r="C123" t="n" s="2">
-        <v>44730.0</v>
+        <v>44723.0</v>
       </c>
       <c r="D123" t="n">
         <v>1.0</v>
@@ -1864,7 +1864,7 @@
         <v>2022.0</v>
       </c>
       <c r="C124" t="n" s="2">
-        <v>44737.0</v>
+        <v>44730.0</v>
       </c>
       <c r="D124" t="n">
         <v>1.0</v>
@@ -1878,7 +1878,7 @@
         <v>2022.0</v>
       </c>
       <c r="C125" t="n" s="2">
-        <v>44744.0</v>
+        <v>44737.0</v>
       </c>
       <c r="D125" t="n">
         <v>1.0</v>
@@ -1892,7 +1892,7 @@
         <v>2022.0</v>
       </c>
       <c r="C126" t="n" s="2">
-        <v>44751.0</v>
+        <v>44744.0</v>
       </c>
       <c r="D126" t="n">
         <v>1.0</v>
@@ -1906,7 +1906,7 @@
         <v>2022.0</v>
       </c>
       <c r="C127" t="n" s="2">
-        <v>44758.0</v>
+        <v>44751.0</v>
       </c>
       <c r="D127" t="n">
         <v>1.0</v>
@@ -1920,7 +1920,7 @@
         <v>2022.0</v>
       </c>
       <c r="C128" t="n" s="2">
-        <v>44772.0</v>
+        <v>44758.0</v>
       </c>
       <c r="D128" t="n">
         <v>1.0</v>
@@ -1934,7 +1934,7 @@
         <v>2022.0</v>
       </c>
       <c r="C129" t="n" s="2">
-        <v>44793.0</v>
+        <v>44772.0</v>
       </c>
       <c r="D129" t="n">
         <v>1.0</v>
@@ -1948,7 +1948,7 @@
         <v>2022.0</v>
       </c>
       <c r="C130" t="n" s="2">
-        <v>44800.0</v>
+        <v>44793.0</v>
       </c>
       <c r="D130" t="n">
         <v>1.0</v>
@@ -1962,7 +1962,7 @@
         <v>2022.0</v>
       </c>
       <c r="C131" t="n" s="2">
-        <v>44828.0</v>
+        <v>44800.0</v>
       </c>
       <c r="D131" t="n">
         <v>1.0</v>
@@ -1976,7 +1976,7 @@
         <v>2022.0</v>
       </c>
       <c r="C132" t="n" s="2">
-        <v>44849.0</v>
+        <v>44828.0</v>
       </c>
       <c r="D132" t="n">
         <v>1.0</v>
@@ -1990,7 +1990,7 @@
         <v>2022.0</v>
       </c>
       <c r="C133" t="n" s="2">
-        <v>44856.0</v>
+        <v>44849.0</v>
       </c>
       <c r="D133" t="n">
         <v>1.0</v>
@@ -2004,7 +2004,7 @@
         <v>2022.0</v>
       </c>
       <c r="C134" t="n" s="2">
-        <v>44863.0</v>
+        <v>44856.0</v>
       </c>
       <c r="D134" t="n">
         <v>1.0</v>
@@ -2018,10 +2018,10 @@
         <v>2022.0</v>
       </c>
       <c r="C135" t="n" s="2">
-        <v>44884.0</v>
+        <v>44863.0</v>
       </c>
       <c r="D135" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="136">
@@ -2032,10 +2032,10 @@
         <v>2022.0</v>
       </c>
       <c r="C136" t="n" s="2">
-        <v>44891.0</v>
+        <v>44884.0</v>
       </c>
       <c r="D136" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="137">
@@ -2046,7 +2046,7 @@
         <v>2022.0</v>
       </c>
       <c r="C137" t="n" s="2">
-        <v>44905.0</v>
+        <v>44891.0</v>
       </c>
       <c r="D137" t="n">
         <v>1.0</v>
@@ -2060,7 +2060,7 @@
         <v>2022.0</v>
       </c>
       <c r="C138" t="n" s="2">
-        <v>44912.0</v>
+        <v>44905.0</v>
       </c>
       <c r="D138" t="n">
         <v>1.0</v>
@@ -2074,10 +2074,10 @@
         <v>2022.0</v>
       </c>
       <c r="C139" t="n" s="2">
-        <v>44919.0</v>
+        <v>44912.0</v>
       </c>
       <c r="D139" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="140">
@@ -2085,13 +2085,13 @@
         <v>5</v>
       </c>
       <c r="B140" t="n">
-        <v>2023.0</v>
+        <v>2022.0</v>
       </c>
       <c r="C140" t="n" s="2">
-        <v>44934.0</v>
+        <v>44919.0</v>
       </c>
       <c r="D140" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="141">
@@ -2102,10 +2102,10 @@
         <v>2023.0</v>
       </c>
       <c r="C141" t="n" s="2">
-        <v>44941.0</v>
+        <v>44934.0</v>
       </c>
       <c r="D141" t="n">
-        <v>8.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="142">
@@ -2116,10 +2116,10 @@
         <v>2023.0</v>
       </c>
       <c r="C142" t="n" s="2">
-        <v>44948.0</v>
+        <v>44941.0</v>
       </c>
       <c r="D142" t="n">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="143">
@@ -2130,10 +2130,10 @@
         <v>2023.0</v>
       </c>
       <c r="C143" t="n" s="2">
-        <v>44955.0</v>
+        <v>44948.0</v>
       </c>
       <c r="D143" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="144">
@@ -2144,10 +2144,10 @@
         <v>2023.0</v>
       </c>
       <c r="C144" t="n" s="2">
-        <v>44962.0</v>
+        <v>44955.0</v>
       </c>
       <c r="D144" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="145">
@@ -2158,7 +2158,7 @@
         <v>2023.0</v>
       </c>
       <c r="C145" t="n" s="2">
-        <v>44969.0</v>
+        <v>44962.0</v>
       </c>
       <c r="D145" t="n">
         <v>4.0</v>
@@ -2172,10 +2172,10 @@
         <v>2023.0</v>
       </c>
       <c r="C146" t="n" s="2">
-        <v>44976.0</v>
+        <v>44969.0</v>
       </c>
       <c r="D146" t="n">
-        <v>17.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="147">
@@ -2186,10 +2186,10 @@
         <v>2023.0</v>
       </c>
       <c r="C147" t="n" s="2">
-        <v>44983.0</v>
+        <v>44976.0</v>
       </c>
       <c r="D147" t="n">
-        <v>11.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="148">
@@ -2200,10 +2200,10 @@
         <v>2023.0</v>
       </c>
       <c r="C148" t="n" s="2">
-        <v>44990.0</v>
+        <v>44983.0</v>
       </c>
       <c r="D148" t="n">
-        <v>5.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="149">
@@ -2214,10 +2214,10 @@
         <v>2023.0</v>
       </c>
       <c r="C149" t="n" s="2">
-        <v>44997.0</v>
+        <v>44990.0</v>
       </c>
       <c r="D149" t="n">
-        <v>22.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="150">
@@ -2228,10 +2228,10 @@
         <v>2023.0</v>
       </c>
       <c r="C150" t="n" s="2">
-        <v>45004.0</v>
+        <v>44997.0</v>
       </c>
       <c r="D150" t="n">
-        <v>8.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="151">
@@ -2242,10 +2242,10 @@
         <v>2023.0</v>
       </c>
       <c r="C151" t="n" s="2">
-        <v>45011.0</v>
+        <v>45004.0</v>
       </c>
       <c r="D151" t="n">
-        <v>17.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="152">
@@ -2256,10 +2256,10 @@
         <v>2023.0</v>
       </c>
       <c r="C152" t="n" s="2">
-        <v>45018.0</v>
+        <v>45011.0</v>
       </c>
       <c r="D152" t="n">
-        <v>10.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="153">
@@ -2270,10 +2270,10 @@
         <v>2023.0</v>
       </c>
       <c r="C153" t="n" s="2">
-        <v>45025.0</v>
+        <v>45018.0</v>
       </c>
       <c r="D153" t="n">
-        <v>13.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="154">
@@ -2284,10 +2284,10 @@
         <v>2023.0</v>
       </c>
       <c r="C154" t="n" s="2">
-        <v>45032.0</v>
+        <v>45025.0</v>
       </c>
       <c r="D154" t="n">
-        <v>10.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="155">
@@ -2298,10 +2298,10 @@
         <v>2023.0</v>
       </c>
       <c r="C155" t="n" s="2">
-        <v>45039.0</v>
+        <v>45032.0</v>
       </c>
       <c r="D155" t="n">
-        <v>22.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="156">
@@ -2312,10 +2312,10 @@
         <v>2023.0</v>
       </c>
       <c r="C156" t="n" s="2">
-        <v>45046.0</v>
+        <v>45039.0</v>
       </c>
       <c r="D156" t="n">
-        <v>23.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="157">
@@ -2326,10 +2326,10 @@
         <v>2023.0</v>
       </c>
       <c r="C157" t="n" s="2">
-        <v>45053.0</v>
+        <v>45046.0</v>
       </c>
       <c r="D157" t="n">
-        <v>16.0</v>
+        <v>23.0</v>
       </c>
     </row>
     <row r="158">
@@ -2340,10 +2340,10 @@
         <v>2023.0</v>
       </c>
       <c r="C158" t="n" s="2">
-        <v>45060.0</v>
+        <v>45053.0</v>
       </c>
       <c r="D158" t="n">
-        <v>13.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="159">
@@ -2354,10 +2354,10 @@
         <v>2023.0</v>
       </c>
       <c r="C159" t="n" s="2">
-        <v>45067.0</v>
+        <v>45060.0</v>
       </c>
       <c r="D159" t="n">
-        <v>9.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="160">
@@ -2368,10 +2368,10 @@
         <v>2023.0</v>
       </c>
       <c r="C160" t="n" s="2">
-        <v>45074.0</v>
+        <v>45067.0</v>
       </c>
       <c r="D160" t="n">
-        <v>6.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="161">
@@ -2382,10 +2382,10 @@
         <v>2023.0</v>
       </c>
       <c r="C161" t="n" s="2">
-        <v>45081.0</v>
+        <v>45074.0</v>
       </c>
       <c r="D161" t="n">
-        <v>16.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="162">
@@ -2396,10 +2396,10 @@
         <v>2023.0</v>
       </c>
       <c r="C162" t="n" s="2">
-        <v>45088.0</v>
+        <v>45081.0</v>
       </c>
       <c r="D162" t="n">
-        <v>8.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="163">
@@ -2410,10 +2410,10 @@
         <v>2023.0</v>
       </c>
       <c r="C163" t="n" s="2">
-        <v>45095.0</v>
+        <v>45088.0</v>
       </c>
       <c r="D163" t="n">
-        <v>16.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="164">
@@ -2424,10 +2424,10 @@
         <v>2023.0</v>
       </c>
       <c r="C164" t="n" s="2">
-        <v>45102.0</v>
+        <v>45095.0</v>
       </c>
       <c r="D164" t="n">
-        <v>17.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="165">
@@ -2438,10 +2438,10 @@
         <v>2023.0</v>
       </c>
       <c r="C165" t="n" s="2">
-        <v>45109.0</v>
+        <v>45102.0</v>
       </c>
       <c r="D165" t="n">
-        <v>14.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="166">
@@ -2452,10 +2452,10 @@
         <v>2023.0</v>
       </c>
       <c r="C166" t="n" s="2">
-        <v>45116.0</v>
+        <v>45109.0</v>
       </c>
       <c r="D166" t="n">
-        <v>13.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="167">
@@ -2466,10 +2466,10 @@
         <v>2023.0</v>
       </c>
       <c r="C167" t="n" s="2">
-        <v>45123.0</v>
+        <v>45116.0</v>
       </c>
       <c r="D167" t="n">
-        <v>5.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="168">
@@ -2480,10 +2480,10 @@
         <v>2023.0</v>
       </c>
       <c r="C168" t="n" s="2">
-        <v>45130.0</v>
+        <v>45123.0</v>
       </c>
       <c r="D168" t="n">
-        <v>8.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="169">
@@ -2494,10 +2494,10 @@
         <v>2023.0</v>
       </c>
       <c r="C169" t="n" s="2">
-        <v>45137.0</v>
+        <v>45130.0</v>
       </c>
       <c r="D169" t="n">
-        <v>4.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="170">
@@ -2508,10 +2508,10 @@
         <v>2023.0</v>
       </c>
       <c r="C170" t="n" s="2">
-        <v>45144.0</v>
+        <v>45137.0</v>
       </c>
       <c r="D170" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="171">
@@ -2522,7 +2522,7 @@
         <v>2023.0</v>
       </c>
       <c r="C171" t="n" s="2">
-        <v>45151.0</v>
+        <v>45144.0</v>
       </c>
       <c r="D171" t="n">
         <v>2.0</v>
@@ -2536,10 +2536,10 @@
         <v>2023.0</v>
       </c>
       <c r="C172" t="n" s="2">
-        <v>45158.0</v>
+        <v>45151.0</v>
       </c>
       <c r="D172" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="173">
@@ -2550,7 +2550,7 @@
         <v>2023.0</v>
       </c>
       <c r="C173" t="n" s="2">
-        <v>45165.0</v>
+        <v>45158.0</v>
       </c>
       <c r="D173" t="n">
         <v>5.0</v>
@@ -2564,10 +2564,10 @@
         <v>2023.0</v>
       </c>
       <c r="C174" t="n" s="2">
-        <v>45172.0</v>
+        <v>45165.0</v>
       </c>
       <c r="D174" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="175">
@@ -2578,10 +2578,10 @@
         <v>2023.0</v>
       </c>
       <c r="C175" t="n" s="2">
-        <v>45179.0</v>
+        <v>45172.0</v>
       </c>
       <c r="D175" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="176">
@@ -2592,10 +2592,10 @@
         <v>2023.0</v>
       </c>
       <c r="C176" t="n" s="2">
-        <v>45186.0</v>
+        <v>45179.0</v>
       </c>
       <c r="D176" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="177">
@@ -2606,7 +2606,7 @@
         <v>2023.0</v>
       </c>
       <c r="C177" t="n" s="2">
-        <v>45193.0</v>
+        <v>45186.0</v>
       </c>
       <c r="D177" t="n">
         <v>1.0</v>
@@ -2620,10 +2620,10 @@
         <v>2023.0</v>
       </c>
       <c r="C178" t="n" s="2">
-        <v>45200.0</v>
+        <v>45193.0</v>
       </c>
       <c r="D178" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="179">
@@ -2634,10 +2634,10 @@
         <v>2023.0</v>
       </c>
       <c r="C179" t="n" s="2">
-        <v>45207.0</v>
+        <v>45200.0</v>
       </c>
       <c r="D179" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="180">
@@ -2648,10 +2648,10 @@
         <v>2023.0</v>
       </c>
       <c r="C180" t="n" s="2">
-        <v>45214.0</v>
+        <v>45207.0</v>
       </c>
       <c r="D180" t="n">
-        <v>8.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="181">
@@ -2662,7 +2662,7 @@
         <v>2023.0</v>
       </c>
       <c r="C181" t="n" s="2">
-        <v>45221.0</v>
+        <v>45214.0</v>
       </c>
       <c r="D181" t="n">
         <v>8.0</v>
@@ -2676,10 +2676,10 @@
         <v>2023.0</v>
       </c>
       <c r="C182" t="n" s="2">
-        <v>45228.0</v>
+        <v>45221.0</v>
       </c>
       <c r="D182" t="n">
-        <v>17.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="183">
@@ -2690,10 +2690,10 @@
         <v>2023.0</v>
       </c>
       <c r="C183" t="n" s="2">
-        <v>45235.0</v>
+        <v>45228.0</v>
       </c>
       <c r="D183" t="n">
-        <v>9.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="184">
@@ -2704,7 +2704,7 @@
         <v>2023.0</v>
       </c>
       <c r="C184" t="n" s="2">
-        <v>45242.0</v>
+        <v>45235.0</v>
       </c>
       <c r="D184" t="n">
         <v>9.0</v>
@@ -2718,10 +2718,10 @@
         <v>2023.0</v>
       </c>
       <c r="C185" t="n" s="2">
-        <v>45249.0</v>
+        <v>45242.0</v>
       </c>
       <c r="D185" t="n">
-        <v>14.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="186">
@@ -2732,10 +2732,10 @@
         <v>2023.0</v>
       </c>
       <c r="C186" t="n" s="2">
-        <v>45256.0</v>
+        <v>45249.0</v>
       </c>
       <c r="D186" t="n">
-        <v>17.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="187">
@@ -2746,10 +2746,10 @@
         <v>2023.0</v>
       </c>
       <c r="C187" t="n" s="2">
-        <v>45263.0</v>
+        <v>45256.0</v>
       </c>
       <c r="D187" t="n">
-        <v>14.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="188">
@@ -2760,10 +2760,10 @@
         <v>2023.0</v>
       </c>
       <c r="C188" t="n" s="2">
-        <v>45270.0</v>
+        <v>45263.0</v>
       </c>
       <c r="D188" t="n">
-        <v>26.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="189">
@@ -2774,10 +2774,10 @@
         <v>2023.0</v>
       </c>
       <c r="C189" t="n" s="2">
-        <v>45277.0</v>
+        <v>45270.0</v>
       </c>
       <c r="D189" t="n">
-        <v>19.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="190">
@@ -2788,10 +2788,10 @@
         <v>2023.0</v>
       </c>
       <c r="C190" t="n" s="2">
-        <v>45284.0</v>
+        <v>45277.0</v>
       </c>
       <c r="D190" t="n">
-        <v>21.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="191">
@@ -2802,10 +2802,10 @@
         <v>2023.0</v>
       </c>
       <c r="C191" t="n" s="2">
-        <v>45291.0</v>
+        <v>45284.0</v>
       </c>
       <c r="D191" t="n">
-        <v>9.0</v>
+        <v>21.0</v>
       </c>
     </row>
     <row r="192">
@@ -2813,13 +2813,13 @@
         <v>5</v>
       </c>
       <c r="B192" t="n">
-        <v>2024.0</v>
+        <v>2023.0</v>
       </c>
       <c r="C192" t="n" s="2">
-        <v>45299.0</v>
+        <v>45291.0</v>
       </c>
       <c r="D192" t="n">
-        <v>26.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="193">
@@ -2830,10 +2830,10 @@
         <v>2024.0</v>
       </c>
       <c r="C193" t="n" s="2">
-        <v>45306.0</v>
+        <v>45299.0</v>
       </c>
       <c r="D193" t="n">
-        <v>14.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="194">
@@ -2844,10 +2844,10 @@
         <v>2024.0</v>
       </c>
       <c r="C194" t="n" s="2">
-        <v>45313.0</v>
+        <v>45306.0</v>
       </c>
       <c r="D194" t="n">
-        <v>15.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="195">
@@ -2858,10 +2858,10 @@
         <v>2024.0</v>
       </c>
       <c r="C195" t="n" s="2">
-        <v>45320.0</v>
+        <v>45313.0</v>
       </c>
       <c r="D195" t="n">
-        <v>18.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="196">
@@ -2872,10 +2872,10 @@
         <v>2024.0</v>
       </c>
       <c r="C196" t="n" s="2">
-        <v>45327.0</v>
+        <v>45320.0</v>
       </c>
       <c r="D196" t="n">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="197">
@@ -2886,10 +2886,10 @@
         <v>2024.0</v>
       </c>
       <c r="C197" t="n" s="2">
-        <v>45334.0</v>
+        <v>45327.0</v>
       </c>
       <c r="D197" t="n">
-        <v>13.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="198">
@@ -2900,10 +2900,10 @@
         <v>2024.0</v>
       </c>
       <c r="C198" t="n" s="2">
-        <v>45341.0</v>
+        <v>45334.0</v>
       </c>
       <c r="D198" t="n">
-        <v>11.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="199">
@@ -2914,10 +2914,10 @@
         <v>2024.0</v>
       </c>
       <c r="C199" t="n" s="2">
-        <v>45348.0</v>
+        <v>45341.0</v>
       </c>
       <c r="D199" t="n">
-        <v>8.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="200">
@@ -2928,10 +2928,10 @@
         <v>2024.0</v>
       </c>
       <c r="C200" t="n" s="2">
-        <v>45355.0</v>
+        <v>45348.0</v>
       </c>
       <c r="D200" t="n">
-        <v>1.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="201">
@@ -2942,10 +2942,10 @@
         <v>2024.0</v>
       </c>
       <c r="C201" t="n" s="2">
-        <v>45362.0</v>
+        <v>45355.0</v>
       </c>
       <c r="D201" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="202">
@@ -2956,10 +2956,10 @@
         <v>2024.0</v>
       </c>
       <c r="C202" t="n" s="2">
-        <v>45369.0</v>
+        <v>45362.0</v>
       </c>
       <c r="D202" t="n">
-        <v>8.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="203">
@@ -2970,10 +2970,10 @@
         <v>2024.0</v>
       </c>
       <c r="C203" t="n" s="2">
-        <v>45376.0</v>
+        <v>45369.0</v>
       </c>
       <c r="D203" t="n">
-        <v>9.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="204">
@@ -2984,10 +2984,10 @@
         <v>2024.0</v>
       </c>
       <c r="C204" t="n" s="2">
-        <v>45383.0</v>
+        <v>45376.0</v>
       </c>
       <c r="D204" t="n">
-        <v>5.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="205">
@@ -2998,10 +2998,10 @@
         <v>2024.0</v>
       </c>
       <c r="C205" t="n" s="2">
-        <v>45390.0</v>
+        <v>45383.0</v>
       </c>
       <c r="D205" t="n">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="206">
@@ -3012,10 +3012,10 @@
         <v>2024.0</v>
       </c>
       <c r="C206" t="n" s="2">
-        <v>45397.0</v>
+        <v>45390.0</v>
       </c>
       <c r="D206" t="n">
-        <v>13.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="207">
@@ -3026,10 +3026,10 @@
         <v>2024.0</v>
       </c>
       <c r="C207" t="n" s="2">
-        <v>45404.0</v>
+        <v>45397.0</v>
       </c>
       <c r="D207" t="n">
-        <v>24.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="208">
@@ -3040,10 +3040,10 @@
         <v>2024.0</v>
       </c>
       <c r="C208" t="n" s="2">
-        <v>45411.0</v>
+        <v>45404.0</v>
       </c>
       <c r="D208" t="n">
-        <v>17.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="209">
@@ -3054,10 +3054,10 @@
         <v>2024.0</v>
       </c>
       <c r="C209" t="n" s="2">
-        <v>45418.0</v>
+        <v>45411.0</v>
       </c>
       <c r="D209" t="n">
-        <v>3.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="210">
@@ -3068,10 +3068,10 @@
         <v>2024.0</v>
       </c>
       <c r="C210" t="n" s="2">
-        <v>45425.0</v>
+        <v>45418.0</v>
       </c>
       <c r="D210" t="n">
-        <v>16.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="211">
@@ -3082,10 +3082,10 @@
         <v>2024.0</v>
       </c>
       <c r="C211" t="n" s="2">
-        <v>45432.0</v>
+        <v>45425.0</v>
       </c>
       <c r="D211" t="n">
-        <v>19.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="212">
@@ -3096,10 +3096,10 @@
         <v>2024.0</v>
       </c>
       <c r="C212" t="n" s="2">
-        <v>45439.0</v>
+        <v>45432.0</v>
       </c>
       <c r="D212" t="n">
-        <v>30.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="213">
@@ -3110,10 +3110,10 @@
         <v>2024.0</v>
       </c>
       <c r="C213" t="n" s="2">
-        <v>45446.0</v>
+        <v>45439.0</v>
       </c>
       <c r="D213" t="n">
-        <v>28.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="214">
@@ -3124,10 +3124,10 @@
         <v>2024.0</v>
       </c>
       <c r="C214" t="n" s="2">
-        <v>45453.0</v>
+        <v>45446.0</v>
       </c>
       <c r="D214" t="n">
-        <v>19.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="215">
@@ -3138,10 +3138,10 @@
         <v>2024.0</v>
       </c>
       <c r="C215" t="n" s="2">
-        <v>45460.0</v>
+        <v>45453.0</v>
       </c>
       <c r="D215" t="n">
-        <v>26.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="216">
@@ -3152,10 +3152,10 @@
         <v>2024.0</v>
       </c>
       <c r="C216" t="n" s="2">
-        <v>45467.0</v>
+        <v>45460.0</v>
       </c>
       <c r="D216" t="n">
-        <v>8.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="217">
@@ -3166,10 +3166,10 @@
         <v>2024.0</v>
       </c>
       <c r="C217" t="n" s="2">
-        <v>45474.0</v>
+        <v>45467.0</v>
       </c>
       <c r="D217" t="n">
-        <v>12.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="218">
@@ -3180,7 +3180,7 @@
         <v>2024.0</v>
       </c>
       <c r="C218" t="n" s="2">
-        <v>45481.0</v>
+        <v>45474.0</v>
       </c>
       <c r="D218" t="n">
         <v>12.0</v>
@@ -3194,10 +3194,10 @@
         <v>2024.0</v>
       </c>
       <c r="C219" t="n" s="2">
-        <v>45488.0</v>
+        <v>45481.0</v>
       </c>
       <c r="D219" t="n">
-        <v>4.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="220">
@@ -3208,10 +3208,10 @@
         <v>2024.0</v>
       </c>
       <c r="C220" t="n" s="2">
-        <v>45495.0</v>
+        <v>45488.0</v>
       </c>
       <c r="D220" t="n">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="221">
@@ -3222,10 +3222,10 @@
         <v>2024.0</v>
       </c>
       <c r="C221" t="n" s="2">
-        <v>45502.0</v>
+        <v>45495.0</v>
       </c>
       <c r="D221" t="n">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="222">
@@ -3236,10 +3236,10 @@
         <v>2024.0</v>
       </c>
       <c r="C222" t="n" s="2">
-        <v>45509.0</v>
+        <v>45502.0</v>
       </c>
       <c r="D222" t="n">
-        <v>2.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="223">
@@ -3250,10 +3250,10 @@
         <v>2024.0</v>
       </c>
       <c r="C223" t="n" s="2">
-        <v>45516.0</v>
+        <v>45509.0</v>
       </c>
       <c r="D223" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="224">
@@ -3264,7 +3264,7 @@
         <v>2024.0</v>
       </c>
       <c r="C224" t="n" s="2">
-        <v>45523.0</v>
+        <v>45516.0</v>
       </c>
       <c r="D224" t="n">
         <v>4.0</v>
@@ -3278,7 +3278,7 @@
         <v>2024.0</v>
       </c>
       <c r="C225" t="n" s="2">
-        <v>45530.0</v>
+        <v>45523.0</v>
       </c>
       <c r="D225" t="n">
         <v>4.0</v>
@@ -3292,7 +3292,7 @@
         <v>2024.0</v>
       </c>
       <c r="C226" t="n" s="2">
-        <v>45537.0</v>
+        <v>45530.0</v>
       </c>
       <c r="D226" t="n">
         <v>4.0</v>
@@ -3306,10 +3306,10 @@
         <v>2024.0</v>
       </c>
       <c r="C227" t="n" s="2">
-        <v>45544.0</v>
+        <v>45537.0</v>
       </c>
       <c r="D227" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="228">
@@ -3320,10 +3320,10 @@
         <v>2024.0</v>
       </c>
       <c r="C228" t="n" s="2">
-        <v>45551.0</v>
+        <v>45544.0</v>
       </c>
       <c r="D228" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="229">
@@ -3334,10 +3334,10 @@
         <v>2024.0</v>
       </c>
       <c r="C229" t="n" s="2">
-        <v>45558.0</v>
+        <v>45551.0</v>
       </c>
       <c r="D229" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="230">
@@ -3348,10 +3348,10 @@
         <v>2024.0</v>
       </c>
       <c r="C230" t="n" s="2">
-        <v>45600.0</v>
+        <v>45558.0</v>
       </c>
       <c r="D230" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="231">
@@ -3362,10 +3362,10 @@
         <v>2024.0</v>
       </c>
       <c r="C231" t="n" s="2">
-        <v>45607.0</v>
+        <v>45600.0</v>
       </c>
       <c r="D231" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="232">
@@ -3376,10 +3376,10 @@
         <v>2024.0</v>
       </c>
       <c r="C232" t="n" s="2">
-        <v>45628.0</v>
+        <v>45607.0</v>
       </c>
       <c r="D232" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="233">
@@ -3390,10 +3390,10 @@
         <v>2024.0</v>
       </c>
       <c r="C233" t="n" s="2">
-        <v>45635.0</v>
+        <v>45628.0</v>
       </c>
       <c r="D233" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="234">
@@ -3404,7 +3404,7 @@
         <v>2024.0</v>
       </c>
       <c r="C234" t="n" s="2">
-        <v>45642.0</v>
+        <v>45635.0</v>
       </c>
       <c r="D234" t="n">
         <v>3.0</v>
@@ -3418,10 +3418,10 @@
         <v>2024.0</v>
       </c>
       <c r="C235" t="n" s="2">
-        <v>45649.0</v>
+        <v>45642.0</v>
       </c>
       <c r="D235" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="236">
@@ -3432,7 +3432,7 @@
         <v>2024.0</v>
       </c>
       <c r="C236" t="n" s="2">
-        <v>45656.0</v>
+        <v>45649.0</v>
       </c>
       <c r="D236" t="n">
         <v>1.0</v>
@@ -3443,13 +3443,13 @@
         <v>5</v>
       </c>
       <c r="B237" t="n">
-        <v>2025.0</v>
+        <v>2024.0</v>
       </c>
       <c r="C237" t="n" s="2">
-        <v>45672.0</v>
+        <v>45656.0</v>
       </c>
       <c r="D237" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="238">
@@ -3460,10 +3460,10 @@
         <v>2025.0</v>
       </c>
       <c r="C238" t="n" s="2">
-        <v>45679.0</v>
+        <v>45672.0</v>
       </c>
       <c r="D238" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="239">
@@ -3474,7 +3474,7 @@
         <v>2025.0</v>
       </c>
       <c r="C239" t="n" s="2">
-        <v>45686.0</v>
+        <v>45679.0</v>
       </c>
       <c r="D239" t="n">
         <v>1.0</v>
@@ -3488,10 +3488,10 @@
         <v>2025.0</v>
       </c>
       <c r="C240" t="n" s="2">
-        <v>45721.0</v>
+        <v>45686.0</v>
       </c>
       <c r="D240" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="241">
@@ -3502,10 +3502,10 @@
         <v>2025.0</v>
       </c>
       <c r="C241" t="n" s="2">
-        <v>45728.0</v>
+        <v>45721.0</v>
       </c>
       <c r="D241" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="242">
@@ -3516,10 +3516,10 @@
         <v>2025.0</v>
       </c>
       <c r="C242" t="n" s="2">
-        <v>45742.0</v>
+        <v>45728.0</v>
       </c>
       <c r="D242" t="n">
-        <v>9.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="243">
@@ -3530,10 +3530,10 @@
         <v>2025.0</v>
       </c>
       <c r="C243" t="n" s="2">
-        <v>45749.0</v>
+        <v>45742.0</v>
       </c>
       <c r="D243" t="n">
-        <v>5.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="244">
@@ -3544,10 +3544,10 @@
         <v>2025.0</v>
       </c>
       <c r="C244" t="n" s="2">
-        <v>45756.0</v>
+        <v>45749.0</v>
       </c>
       <c r="D244" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="245">
@@ -3558,10 +3558,10 @@
         <v>2025.0</v>
       </c>
       <c r="C245" t="n" s="2">
-        <v>45763.0</v>
+        <v>45756.0</v>
       </c>
       <c r="D245" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="246">
@@ -3572,10 +3572,10 @@
         <v>2025.0</v>
       </c>
       <c r="C246" t="n" s="2">
-        <v>45770.0</v>
+        <v>45763.0</v>
       </c>
       <c r="D246" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="247">
@@ -3586,10 +3586,10 @@
         <v>2025.0</v>
       </c>
       <c r="C247" t="n" s="2">
-        <v>45777.0</v>
+        <v>45770.0</v>
       </c>
       <c r="D247" t="n">
-        <v>7.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="248">
@@ -3600,10 +3600,10 @@
         <v>2025.0</v>
       </c>
       <c r="C248" t="n" s="2">
-        <v>45784.0</v>
+        <v>45777.0</v>
       </c>
       <c r="D248" t="n">
-        <v>2.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="249">
@@ -3614,10 +3614,10 @@
         <v>2025.0</v>
       </c>
       <c r="C249" t="n" s="2">
-        <v>45791.0</v>
+        <v>45784.0</v>
       </c>
       <c r="D249" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="250">
@@ -3628,10 +3628,10 @@
         <v>2025.0</v>
       </c>
       <c r="C250" t="n" s="2">
-        <v>45798.0</v>
+        <v>45791.0</v>
       </c>
       <c r="D250" t="n">
-        <v>8.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="251">
@@ -3642,10 +3642,10 @@
         <v>2025.0</v>
       </c>
       <c r="C251" t="n" s="2">
-        <v>45805.0</v>
+        <v>45798.0</v>
       </c>
       <c r="D251" t="n">
-        <v>4.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="252">
@@ -3656,10 +3656,10 @@
         <v>2025.0</v>
       </c>
       <c r="C252" t="n" s="2">
-        <v>45812.0</v>
+        <v>45805.0</v>
       </c>
       <c r="D252" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="253">
@@ -3670,10 +3670,10 @@
         <v>2025.0</v>
       </c>
       <c r="C253" t="n" s="2">
-        <v>45819.0</v>
+        <v>45812.0</v>
       </c>
       <c r="D253" t="n">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="254">
@@ -3684,10 +3684,10 @@
         <v>2025.0</v>
       </c>
       <c r="C254" t="n" s="2">
-        <v>45826.0</v>
+        <v>45819.0</v>
       </c>
       <c r="D254" t="n">
-        <v>13.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="255">
@@ -3698,10 +3698,10 @@
         <v>2025.0</v>
       </c>
       <c r="C255" t="n" s="2">
-        <v>45833.0</v>
+        <v>45826.0</v>
       </c>
       <c r="D255" t="n">
-        <v>1.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="256">
@@ -3712,10 +3712,10 @@
         <v>2025.0</v>
       </c>
       <c r="C256" t="n" s="2">
-        <v>45840.0</v>
+        <v>45833.0</v>
       </c>
       <c r="D256" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="257">
@@ -3726,7 +3726,7 @@
         <v>2025.0</v>
       </c>
       <c r="C257" t="n" s="2">
-        <v>45847.0</v>
+        <v>45840.0</v>
       </c>
       <c r="D257" t="n">
         <v>4.0</v>
@@ -3740,10 +3740,10 @@
         <v>2025.0</v>
       </c>
       <c r="C258" t="n" s="2">
-        <v>45854.0</v>
+        <v>45847.0</v>
       </c>
       <c r="D258" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="259">
@@ -3754,10 +3754,10 @@
         <v>2025.0</v>
       </c>
       <c r="C259" t="n" s="2">
-        <v>45861.0</v>
+        <v>45854.0</v>
       </c>
       <c r="D259" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="260">
@@ -3768,10 +3768,10 @@
         <v>2025.0</v>
       </c>
       <c r="C260" t="n" s="2">
-        <v>45868.0</v>
+        <v>45861.0</v>
       </c>
       <c r="D260" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="261">
@@ -3782,10 +3782,10 @@
         <v>2025.0</v>
       </c>
       <c r="C261" t="n" s="2">
-        <v>45882.0</v>
+        <v>45868.0</v>
       </c>
       <c r="D261" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="262">
@@ -3796,7 +3796,7 @@
         <v>2025.0</v>
       </c>
       <c r="C262" t="n" s="2">
-        <v>45889.0</v>
+        <v>45882.0</v>
       </c>
       <c r="D262" t="n">
         <v>1.0</v>
@@ -3810,10 +3810,10 @@
         <v>2025.0</v>
       </c>
       <c r="C263" t="n" s="2">
-        <v>45896.0</v>
+        <v>45889.0</v>
       </c>
       <c r="D263" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="264">
@@ -3824,7 +3824,7 @@
         <v>2025.0</v>
       </c>
       <c r="C264" t="n" s="2">
-        <v>45903.0</v>
+        <v>45896.0</v>
       </c>
       <c r="D264" t="n">
         <v>3.0</v>
@@ -3838,10 +3838,10 @@
         <v>2025.0</v>
       </c>
       <c r="C265" t="n" s="2">
-        <v>45910.0</v>
+        <v>45903.0</v>
       </c>
       <c r="D265" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="266">
@@ -3852,7 +3852,7 @@
         <v>2025.0</v>
       </c>
       <c r="C266" t="n" s="2">
-        <v>45973.0</v>
+        <v>45910.0</v>
       </c>
       <c r="D266" t="n">
         <v>1.0</v>
@@ -3866,10 +3866,10 @@
         <v>2025.0</v>
       </c>
       <c r="C267" t="n" s="2">
-        <v>45987.0</v>
+        <v>45973.0</v>
       </c>
       <c r="D267" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="268">
@@ -3880,10 +3880,10 @@
         <v>2025.0</v>
       </c>
       <c r="C268" t="n" s="2">
-        <v>45994.0</v>
+        <v>45987.0</v>
       </c>
       <c r="D268" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="269">
@@ -3894,10 +3894,10 @@
         <v>2025.0</v>
       </c>
       <c r="C269" t="n" s="2">
-        <v>46001.0</v>
+        <v>45994.0</v>
       </c>
       <c r="D269" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="270">
@@ -3908,10 +3908,10 @@
         <v>2025.0</v>
       </c>
       <c r="C270" t="n" s="2">
-        <v>46008.0</v>
+        <v>46001.0</v>
       </c>
       <c r="D270" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="271">
@@ -3922,10 +3922,10 @@
         <v>2025.0</v>
       </c>
       <c r="C271" t="n" s="2">
-        <v>46022.0</v>
+        <v>46008.0</v>
       </c>
       <c r="D271" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="272">
@@ -3936,10 +3936,10 @@
         <v>2025.0</v>
       </c>
       <c r="C272" t="n" s="2">
-        <v>46029.0</v>
+        <v>46022.0</v>
       </c>
       <c r="D272" t="n">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="273">
@@ -3947,13 +3947,13 @@
         <v>5</v>
       </c>
       <c r="B273" t="n">
-        <v>2026.0</v>
+        <v>2025.0</v>
       </c>
       <c r="C273" t="n" s="2">
-        <v>46030.0</v>
+        <v>46029.0</v>
       </c>
       <c r="D273" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="274">
@@ -3964,10 +3964,10 @@
         <v>2026.0</v>
       </c>
       <c r="C274" t="n" s="2">
-        <v>46037.0</v>
+        <v>46030.0</v>
       </c>
       <c r="D274" t="n">
-        <v>12.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="275">
@@ -3978,10 +3978,10 @@
         <v>2026.0</v>
       </c>
       <c r="C275" t="n" s="2">
-        <v>46044.0</v>
+        <v>46037.0</v>
       </c>
       <c r="D275" t="n">
-        <v>9.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="276">
@@ -3992,10 +3992,10 @@
         <v>2026.0</v>
       </c>
       <c r="C276" t="n" s="2">
-        <v>46051.0</v>
+        <v>46044.0</v>
       </c>
       <c r="D276" t="n">
-        <v>10.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="277">
@@ -4006,10 +4006,10 @@
         <v>2026.0</v>
       </c>
       <c r="C277" t="n" s="2">
-        <v>46058.0</v>
+        <v>46051.0</v>
       </c>
       <c r="D277" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="278">
@@ -4020,10 +4020,10 @@
         <v>2026.0</v>
       </c>
       <c r="C278" t="n" s="2">
-        <v>46065.0</v>
+        <v>46058.0</v>
       </c>
       <c r="D278" t="n">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="279">
@@ -4034,10 +4034,10 @@
         <v>2026.0</v>
       </c>
       <c r="C279" t="n" s="2">
-        <v>46072.0</v>
+        <v>46065.0</v>
       </c>
       <c r="D279" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="280">
@@ -4048,10 +4048,10 @@
         <v>2026.0</v>
       </c>
       <c r="C280" t="n" s="2">
-        <v>46079.0</v>
+        <v>46072.0</v>
       </c>
       <c r="D280" t="n">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="281">
@@ -4062,10 +4062,10 @@
         <v>2026.0</v>
       </c>
       <c r="C281" t="n" s="2">
-        <v>46086.0</v>
+        <v>46079.0</v>
       </c>
       <c r="D281" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="282">
@@ -4076,7 +4076,7 @@
         <v>2026.0</v>
       </c>
       <c r="C282" t="n" s="2">
-        <v>46093.0</v>
+        <v>46086.0</v>
       </c>
       <c r="D282" t="n">
         <v>2.0</v>
@@ -4084,16 +4084,16 @@
     </row>
     <row r="283">
       <c r="A283" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B283" t="n">
-        <v>2023.0</v>
+        <v>2026.0</v>
       </c>
       <c r="C283" t="n" s="2">
-        <v>45095.0</v>
+        <v>46093.0</v>
       </c>
       <c r="D283" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="284">
@@ -4104,7 +4104,7 @@
         <v>2023.0</v>
       </c>
       <c r="C284" t="n" s="2">
-        <v>45102.0</v>
+        <v>45095.0</v>
       </c>
       <c r="D284" t="n">
         <v>1.0</v>
@@ -4118,7 +4118,7 @@
         <v>2023.0</v>
       </c>
       <c r="C285" t="n" s="2">
-        <v>45158.0</v>
+        <v>45102.0</v>
       </c>
       <c r="D285" t="n">
         <v>1.0</v>
@@ -4132,10 +4132,10 @@
         <v>2023.0</v>
       </c>
       <c r="C286" t="n" s="2">
-        <v>45207.0</v>
+        <v>45158.0</v>
       </c>
       <c r="D286" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="287">
@@ -4146,7 +4146,7 @@
         <v>2023.0</v>
       </c>
       <c r="C287" t="n" s="2">
-        <v>45214.0</v>
+        <v>45207.0</v>
       </c>
       <c r="D287" t="n">
         <v>3.0</v>
@@ -4160,10 +4160,10 @@
         <v>2023.0</v>
       </c>
       <c r="C288" t="n" s="2">
-        <v>45221.0</v>
+        <v>45214.0</v>
       </c>
       <c r="D288" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="289">
@@ -4174,7 +4174,7 @@
         <v>2023.0</v>
       </c>
       <c r="C289" t="n" s="2">
-        <v>45249.0</v>
+        <v>45221.0</v>
       </c>
       <c r="D289" t="n">
         <v>1.0</v>
@@ -4188,10 +4188,10 @@
         <v>2023.0</v>
       </c>
       <c r="C290" t="n" s="2">
-        <v>45256.0</v>
+        <v>45249.0</v>
       </c>
       <c r="D290" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="291">
@@ -4202,10 +4202,10 @@
         <v>2023.0</v>
       </c>
       <c r="C291" t="n" s="2">
-        <v>45263.0</v>
+        <v>45256.0</v>
       </c>
       <c r="D291" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="292">
@@ -4216,10 +4216,10 @@
         <v>2023.0</v>
       </c>
       <c r="C292" t="n" s="2">
-        <v>45270.0</v>
+        <v>45263.0</v>
       </c>
       <c r="D292" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="293">
@@ -4230,10 +4230,10 @@
         <v>2023.0</v>
       </c>
       <c r="C293" t="n" s="2">
-        <v>45277.0</v>
+        <v>45270.0</v>
       </c>
       <c r="D293" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="294">
@@ -4244,10 +4244,10 @@
         <v>2023.0</v>
       </c>
       <c r="C294" t="n" s="2">
-        <v>45284.0</v>
+        <v>45277.0</v>
       </c>
       <c r="D294" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="295">
@@ -4258,10 +4258,10 @@
         <v>2023.0</v>
       </c>
       <c r="C295" t="n" s="2">
-        <v>45291.0</v>
+        <v>45284.0</v>
       </c>
       <c r="D295" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="296">
@@ -4269,13 +4269,13 @@
         <v>6</v>
       </c>
       <c r="B296" t="n">
-        <v>2024.0</v>
+        <v>2023.0</v>
       </c>
       <c r="C296" t="n" s="2">
-        <v>45306.0</v>
+        <v>45291.0</v>
       </c>
       <c r="D296" t="n">
-        <v>7.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="297">
@@ -4286,10 +4286,10 @@
         <v>2024.0</v>
       </c>
       <c r="C297" t="n" s="2">
-        <v>45313.0</v>
+        <v>45306.0</v>
       </c>
       <c r="D297" t="n">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="298">
@@ -4300,10 +4300,10 @@
         <v>2024.0</v>
       </c>
       <c r="C298" t="n" s="2">
-        <v>45320.0</v>
+        <v>45313.0</v>
       </c>
       <c r="D298" t="n">
-        <v>19.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="299">
@@ -4314,10 +4314,10 @@
         <v>2024.0</v>
       </c>
       <c r="C299" t="n" s="2">
-        <v>45327.0</v>
+        <v>45320.0</v>
       </c>
       <c r="D299" t="n">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="300">
@@ -4328,10 +4328,10 @@
         <v>2024.0</v>
       </c>
       <c r="C300" t="n" s="2">
-        <v>45334.0</v>
+        <v>45327.0</v>
       </c>
       <c r="D300" t="n">
-        <v>9.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="301">
@@ -4342,10 +4342,10 @@
         <v>2024.0</v>
       </c>
       <c r="C301" t="n" s="2">
-        <v>45341.0</v>
+        <v>45334.0</v>
       </c>
       <c r="D301" t="n">
-        <v>12.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="302">
@@ -4356,7 +4356,7 @@
         <v>2024.0</v>
       </c>
       <c r="C302" t="n" s="2">
-        <v>45348.0</v>
+        <v>45341.0</v>
       </c>
       <c r="D302" t="n">
         <v>12.0</v>
@@ -4370,10 +4370,10 @@
         <v>2024.0</v>
       </c>
       <c r="C303" t="n" s="2">
-        <v>45355.0</v>
+        <v>45348.0</v>
       </c>
       <c r="D303" t="n">
-        <v>10.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="304">
@@ -4384,10 +4384,10 @@
         <v>2024.0</v>
       </c>
       <c r="C304" t="n" s="2">
-        <v>45362.0</v>
+        <v>45355.0</v>
       </c>
       <c r="D304" t="n">
-        <v>12.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="305">
@@ -4398,10 +4398,10 @@
         <v>2024.0</v>
       </c>
       <c r="C305" t="n" s="2">
-        <v>45369.0</v>
+        <v>45362.0</v>
       </c>
       <c r="D305" t="n">
-        <v>13.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="306">
@@ -4412,10 +4412,10 @@
         <v>2024.0</v>
       </c>
       <c r="C306" t="n" s="2">
-        <v>45376.0</v>
+        <v>45369.0</v>
       </c>
       <c r="D306" t="n">
-        <v>18.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="307">
@@ -4426,10 +4426,10 @@
         <v>2024.0</v>
       </c>
       <c r="C307" t="n" s="2">
-        <v>45383.0</v>
+        <v>45376.0</v>
       </c>
       <c r="D307" t="n">
-        <v>12.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="308">
@@ -4440,10 +4440,10 @@
         <v>2024.0</v>
       </c>
       <c r="C308" t="n" s="2">
-        <v>45390.0</v>
+        <v>45383.0</v>
       </c>
       <c r="D308" t="n">
-        <v>6.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="309">
@@ -4454,10 +4454,10 @@
         <v>2024.0</v>
       </c>
       <c r="C309" t="n" s="2">
-        <v>45397.0</v>
+        <v>45390.0</v>
       </c>
       <c r="D309" t="n">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="310">
@@ -4468,10 +4468,10 @@
         <v>2024.0</v>
       </c>
       <c r="C310" t="n" s="2">
-        <v>45404.0</v>
+        <v>45397.0</v>
       </c>
       <c r="D310" t="n">
-        <v>3.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="311">
@@ -4482,10 +4482,10 @@
         <v>2024.0</v>
       </c>
       <c r="C311" t="n" s="2">
-        <v>45411.0</v>
+        <v>45404.0</v>
       </c>
       <c r="D311" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="312">
@@ -4496,10 +4496,10 @@
         <v>2024.0</v>
       </c>
       <c r="C312" t="n" s="2">
-        <v>45418.0</v>
+        <v>45411.0</v>
       </c>
       <c r="D312" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="313">
@@ -4510,10 +4510,10 @@
         <v>2024.0</v>
       </c>
       <c r="C313" t="n" s="2">
-        <v>45425.0</v>
+        <v>45418.0</v>
       </c>
       <c r="D313" t="n">
-        <v>9.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="314">
@@ -4524,10 +4524,10 @@
         <v>2024.0</v>
       </c>
       <c r="C314" t="n" s="2">
-        <v>45432.0</v>
+        <v>45425.0</v>
       </c>
       <c r="D314" t="n">
-        <v>6.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="315">
@@ -4538,7 +4538,7 @@
         <v>2024.0</v>
       </c>
       <c r="C315" t="n" s="2">
-        <v>45439.0</v>
+        <v>45432.0</v>
       </c>
       <c r="D315" t="n">
         <v>6.0</v>
@@ -4552,10 +4552,10 @@
         <v>2024.0</v>
       </c>
       <c r="C316" t="n" s="2">
-        <v>45446.0</v>
+        <v>45439.0</v>
       </c>
       <c r="D316" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="317">
@@ -4566,10 +4566,10 @@
         <v>2024.0</v>
       </c>
       <c r="C317" t="n" s="2">
-        <v>45453.0</v>
+        <v>45446.0</v>
       </c>
       <c r="D317" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="318">
@@ -4580,7 +4580,7 @@
         <v>2024.0</v>
       </c>
       <c r="C318" t="n" s="2">
-        <v>45460.0</v>
+        <v>45453.0</v>
       </c>
       <c r="D318" t="n">
         <v>4.0</v>
@@ -4594,7 +4594,7 @@
         <v>2024.0</v>
       </c>
       <c r="C319" t="n" s="2">
-        <v>45467.0</v>
+        <v>45460.0</v>
       </c>
       <c r="D319" t="n">
         <v>4.0</v>
@@ -4608,10 +4608,10 @@
         <v>2024.0</v>
       </c>
       <c r="C320" t="n" s="2">
-        <v>45474.0</v>
+        <v>45467.0</v>
       </c>
       <c r="D320" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="321">
@@ -4622,10 +4622,10 @@
         <v>2024.0</v>
       </c>
       <c r="C321" t="n" s="2">
-        <v>45481.0</v>
+        <v>45474.0</v>
       </c>
       <c r="D321" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="322">
@@ -4636,10 +4636,10 @@
         <v>2024.0</v>
       </c>
       <c r="C322" t="n" s="2">
-        <v>45488.0</v>
+        <v>45481.0</v>
       </c>
       <c r="D322" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="323">
@@ -4650,10 +4650,10 @@
         <v>2024.0</v>
       </c>
       <c r="C323" t="n" s="2">
-        <v>45495.0</v>
+        <v>45488.0</v>
       </c>
       <c r="D323" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="324">
@@ -4664,10 +4664,10 @@
         <v>2024.0</v>
       </c>
       <c r="C324" t="n" s="2">
-        <v>45502.0</v>
+        <v>45495.0</v>
       </c>
       <c r="D324" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="325">
@@ -4678,10 +4678,10 @@
         <v>2024.0</v>
       </c>
       <c r="C325" t="n" s="2">
-        <v>45509.0</v>
+        <v>45502.0</v>
       </c>
       <c r="D325" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="326">
@@ -4692,7 +4692,7 @@
         <v>2024.0</v>
       </c>
       <c r="C326" t="n" s="2">
-        <v>45523.0</v>
+        <v>45509.0</v>
       </c>
       <c r="D326" t="n">
         <v>1.0</v>
@@ -4706,7 +4706,7 @@
         <v>2024.0</v>
       </c>
       <c r="C327" t="n" s="2">
-        <v>45551.0</v>
+        <v>45523.0</v>
       </c>
       <c r="D327" t="n">
         <v>1.0</v>
@@ -4720,7 +4720,7 @@
         <v>2024.0</v>
       </c>
       <c r="C328" t="n" s="2">
-        <v>45558.0</v>
+        <v>45551.0</v>
       </c>
       <c r="D328" t="n">
         <v>1.0</v>
@@ -4734,10 +4734,10 @@
         <v>2024.0</v>
       </c>
       <c r="C329" t="n" s="2">
-        <v>45572.0</v>
+        <v>45558.0</v>
       </c>
       <c r="D329" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="330">
@@ -4748,10 +4748,10 @@
         <v>2024.0</v>
       </c>
       <c r="C330" t="n" s="2">
-        <v>45593.0</v>
+        <v>45572.0</v>
       </c>
       <c r="D330" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="331">
@@ -4762,10 +4762,10 @@
         <v>2024.0</v>
       </c>
       <c r="C331" t="n" s="2">
-        <v>45614.0</v>
+        <v>45593.0</v>
       </c>
       <c r="D331" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="332">
@@ -4776,10 +4776,10 @@
         <v>2024.0</v>
       </c>
       <c r="C332" t="n" s="2">
-        <v>45621.0</v>
+        <v>45614.0</v>
       </c>
       <c r="D332" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="333">
@@ -4790,7 +4790,7 @@
         <v>2024.0</v>
       </c>
       <c r="C333" t="n" s="2">
-        <v>45635.0</v>
+        <v>45621.0</v>
       </c>
       <c r="D333" t="n">
         <v>1.0</v>
@@ -4804,7 +4804,7 @@
         <v>2024.0</v>
       </c>
       <c r="C334" t="n" s="2">
-        <v>45649.0</v>
+        <v>45635.0</v>
       </c>
       <c r="D334" t="n">
         <v>1.0</v>
@@ -4815,13 +4815,13 @@
         <v>6</v>
       </c>
       <c r="B335" t="n">
-        <v>2025.0</v>
+        <v>2024.0</v>
       </c>
       <c r="C335" t="n" s="2">
-        <v>45665.0</v>
+        <v>45649.0</v>
       </c>
       <c r="D335" t="n">
-        <v>9.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="336">
@@ -4832,10 +4832,10 @@
         <v>2025.0</v>
       </c>
       <c r="C336" t="n" s="2">
-        <v>45672.0</v>
+        <v>45665.0</v>
       </c>
       <c r="D336" t="n">
-        <v>3.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="337">
@@ -4846,10 +4846,10 @@
         <v>2025.0</v>
       </c>
       <c r="C337" t="n" s="2">
-        <v>45679.0</v>
+        <v>45672.0</v>
       </c>
       <c r="D337" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="338">
@@ -4860,10 +4860,10 @@
         <v>2025.0</v>
       </c>
       <c r="C338" t="n" s="2">
-        <v>45686.0</v>
+        <v>45679.0</v>
       </c>
       <c r="D338" t="n">
-        <v>8.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="339">
@@ -4874,10 +4874,10 @@
         <v>2025.0</v>
       </c>
       <c r="C339" t="n" s="2">
-        <v>45693.0</v>
+        <v>45686.0</v>
       </c>
       <c r="D339" t="n">
-        <v>3.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="340">
@@ -4888,10 +4888,10 @@
         <v>2025.0</v>
       </c>
       <c r="C340" t="n" s="2">
-        <v>45700.0</v>
+        <v>45693.0</v>
       </c>
       <c r="D340" t="n">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="341">
@@ -4902,10 +4902,10 @@
         <v>2025.0</v>
       </c>
       <c r="C341" t="n" s="2">
-        <v>45707.0</v>
+        <v>45700.0</v>
       </c>
       <c r="D341" t="n">
-        <v>8.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="342">
@@ -4916,10 +4916,10 @@
         <v>2025.0</v>
       </c>
       <c r="C342" t="n" s="2">
-        <v>45714.0</v>
+        <v>45707.0</v>
       </c>
       <c r="D342" t="n">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="343">
@@ -4930,10 +4930,10 @@
         <v>2025.0</v>
       </c>
       <c r="C343" t="n" s="2">
-        <v>45721.0</v>
+        <v>45714.0</v>
       </c>
       <c r="D343" t="n">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="344">
@@ -4944,10 +4944,10 @@
         <v>2025.0</v>
       </c>
       <c r="C344" t="n" s="2">
-        <v>45728.0</v>
+        <v>45721.0</v>
       </c>
       <c r="D344" t="n">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="345">
@@ -4958,10 +4958,10 @@
         <v>2025.0</v>
       </c>
       <c r="C345" t="n" s="2">
-        <v>45735.0</v>
+        <v>45728.0</v>
       </c>
       <c r="D345" t="n">
-        <v>4.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="346">
@@ -4972,10 +4972,10 @@
         <v>2025.0</v>
       </c>
       <c r="C346" t="n" s="2">
-        <v>45742.0</v>
+        <v>45735.0</v>
       </c>
       <c r="D346" t="n">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="347">
@@ -4986,10 +4986,10 @@
         <v>2025.0</v>
       </c>
       <c r="C347" t="n" s="2">
-        <v>45749.0</v>
+        <v>45742.0</v>
       </c>
       <c r="D347" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="348">
@@ -5000,10 +5000,10 @@
         <v>2025.0</v>
       </c>
       <c r="C348" t="n" s="2">
-        <v>45756.0</v>
+        <v>45749.0</v>
       </c>
       <c r="D348" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="349">
@@ -5014,10 +5014,10 @@
         <v>2025.0</v>
       </c>
       <c r="C349" t="n" s="2">
-        <v>45763.0</v>
+        <v>45756.0</v>
       </c>
       <c r="D349" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="350">
@@ -5028,7 +5028,7 @@
         <v>2025.0</v>
       </c>
       <c r="C350" t="n" s="2">
-        <v>45770.0</v>
+        <v>45763.0</v>
       </c>
       <c r="D350" t="n">
         <v>4.0</v>
@@ -5042,10 +5042,10 @@
         <v>2025.0</v>
       </c>
       <c r="C351" t="n" s="2">
-        <v>45777.0</v>
+        <v>45770.0</v>
       </c>
       <c r="D351" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="352">
@@ -5056,7 +5056,7 @@
         <v>2025.0</v>
       </c>
       <c r="C352" t="n" s="2">
-        <v>45784.0</v>
+        <v>45777.0</v>
       </c>
       <c r="D352" t="n">
         <v>1.0</v>
@@ -5070,7 +5070,7 @@
         <v>2025.0</v>
       </c>
       <c r="C353" t="n" s="2">
-        <v>45791.0</v>
+        <v>45784.0</v>
       </c>
       <c r="D353" t="n">
         <v>1.0</v>
@@ -5084,7 +5084,7 @@
         <v>2025.0</v>
       </c>
       <c r="C354" t="n" s="2">
-        <v>45840.0</v>
+        <v>45791.0</v>
       </c>
       <c r="D354" t="n">
         <v>1.0</v>
@@ -5098,7 +5098,7 @@
         <v>2025.0</v>
       </c>
       <c r="C355" t="n" s="2">
-        <v>46001.0</v>
+        <v>45840.0</v>
       </c>
       <c r="D355" t="n">
         <v>1.0</v>
@@ -5109,10 +5109,10 @@
         <v>6</v>
       </c>
       <c r="B356" t="n">
-        <v>2026.0</v>
+        <v>2025.0</v>
       </c>
       <c r="C356" t="n" s="2">
-        <v>46037.0</v>
+        <v>46001.0</v>
       </c>
       <c r="D356" t="n">
         <v>1.0</v>
@@ -5120,13 +5120,13 @@
     </row>
     <row r="357">
       <c r="A357" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B357" t="n">
-        <v>2021.0</v>
+        <v>2026.0</v>
       </c>
       <c r="C357" t="n" s="2">
-        <v>44561.0</v>
+        <v>46037.0</v>
       </c>
       <c r="D357" t="n">
         <v>1.0</v>
@@ -5137,10 +5137,10 @@
         <v>7</v>
       </c>
       <c r="B358" t="n">
-        <v>2022.0</v>
+        <v>2021.0</v>
       </c>
       <c r="C358" t="n" s="2">
-        <v>44569.0</v>
+        <v>44561.0</v>
       </c>
       <c r="D358" t="n">
         <v>1.0</v>
@@ -5154,10 +5154,10 @@
         <v>2022.0</v>
       </c>
       <c r="C359" t="n" s="2">
-        <v>44576.0</v>
+        <v>44569.0</v>
       </c>
       <c r="D359" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="360">
@@ -5168,10 +5168,10 @@
         <v>2022.0</v>
       </c>
       <c r="C360" t="n" s="2">
-        <v>44583.0</v>
+        <v>44576.0</v>
       </c>
       <c r="D360" t="n">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="361">
@@ -5182,10 +5182,10 @@
         <v>2022.0</v>
       </c>
       <c r="C361" t="n" s="2">
-        <v>44590.0</v>
+        <v>44583.0</v>
       </c>
       <c r="D361" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="362">
@@ -5196,10 +5196,10 @@
         <v>2022.0</v>
       </c>
       <c r="C362" t="n" s="2">
-        <v>44604.0</v>
+        <v>44590.0</v>
       </c>
       <c r="D362" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="363">
@@ -5210,7 +5210,7 @@
         <v>2022.0</v>
       </c>
       <c r="C363" t="n" s="2">
-        <v>44611.0</v>
+        <v>44604.0</v>
       </c>
       <c r="D363" t="n">
         <v>3.0</v>
@@ -5224,10 +5224,10 @@
         <v>2022.0</v>
       </c>
       <c r="C364" t="n" s="2">
-        <v>44618.0</v>
+        <v>44611.0</v>
       </c>
       <c r="D364" t="n">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="365">
@@ -5238,7 +5238,7 @@
         <v>2022.0</v>
       </c>
       <c r="C365" t="n" s="2">
-        <v>44625.0</v>
+        <v>44618.0</v>
       </c>
       <c r="D365" t="n">
         <v>5.0</v>
@@ -5252,10 +5252,10 @@
         <v>2022.0</v>
       </c>
       <c r="C366" t="n" s="2">
-        <v>44632.0</v>
+        <v>44625.0</v>
       </c>
       <c r="D366" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="367">
@@ -5266,10 +5266,10 @@
         <v>2022.0</v>
       </c>
       <c r="C367" t="n" s="2">
-        <v>44639.0</v>
+        <v>44632.0</v>
       </c>
       <c r="D367" t="n">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="368">
@@ -5280,10 +5280,10 @@
         <v>2022.0</v>
       </c>
       <c r="C368" t="n" s="2">
-        <v>44646.0</v>
+        <v>44639.0</v>
       </c>
       <c r="D368" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="369">
@@ -5294,10 +5294,10 @@
         <v>2022.0</v>
       </c>
       <c r="C369" t="n" s="2">
-        <v>44653.0</v>
+        <v>44646.0</v>
       </c>
       <c r="D369" t="n">
-        <v>9.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="370">
@@ -5308,10 +5308,10 @@
         <v>2022.0</v>
       </c>
       <c r="C370" t="n" s="2">
-        <v>44660.0</v>
+        <v>44653.0</v>
       </c>
       <c r="D370" t="n">
-        <v>6.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="371">
@@ -5322,10 +5322,10 @@
         <v>2022.0</v>
       </c>
       <c r="C371" t="n" s="2">
-        <v>44667.0</v>
+        <v>44660.0</v>
       </c>
       <c r="D371" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="372">
@@ -5336,10 +5336,10 @@
         <v>2022.0</v>
       </c>
       <c r="C372" t="n" s="2">
-        <v>44674.0</v>
+        <v>44667.0</v>
       </c>
       <c r="D372" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="373">
@@ -5350,10 +5350,10 @@
         <v>2022.0</v>
       </c>
       <c r="C373" t="n" s="2">
-        <v>44681.0</v>
+        <v>44674.0</v>
       </c>
       <c r="D373" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="374">
@@ -5364,10 +5364,10 @@
         <v>2022.0</v>
       </c>
       <c r="C374" t="n" s="2">
-        <v>44688.0</v>
+        <v>44681.0</v>
       </c>
       <c r="D374" t="n">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="375">
@@ -5378,10 +5378,10 @@
         <v>2022.0</v>
       </c>
       <c r="C375" t="n" s="2">
-        <v>44695.0</v>
+        <v>44688.0</v>
       </c>
       <c r="D375" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="376">
@@ -5392,10 +5392,10 @@
         <v>2022.0</v>
       </c>
       <c r="C376" t="n" s="2">
-        <v>44702.0</v>
+        <v>44695.0</v>
       </c>
       <c r="D376" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="377">
@@ -5406,10 +5406,10 @@
         <v>2022.0</v>
       </c>
       <c r="C377" t="n" s="2">
-        <v>44709.0</v>
+        <v>44702.0</v>
       </c>
       <c r="D377" t="n">
-        <v>8.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="378">
@@ -5420,10 +5420,10 @@
         <v>2022.0</v>
       </c>
       <c r="C378" t="n" s="2">
-        <v>44716.0</v>
+        <v>44709.0</v>
       </c>
       <c r="D378" t="n">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="379">
@@ -5434,10 +5434,10 @@
         <v>2022.0</v>
       </c>
       <c r="C379" t="n" s="2">
-        <v>44723.0</v>
+        <v>44716.0</v>
       </c>
       <c r="D379" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="380">
@@ -5448,10 +5448,10 @@
         <v>2022.0</v>
       </c>
       <c r="C380" t="n" s="2">
-        <v>44730.0</v>
+        <v>44723.0</v>
       </c>
       <c r="D380" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="381">
@@ -5462,7 +5462,7 @@
         <v>2022.0</v>
       </c>
       <c r="C381" t="n" s="2">
-        <v>44737.0</v>
+        <v>44730.0</v>
       </c>
       <c r="D381" t="n">
         <v>4.0</v>
@@ -5476,10 +5476,10 @@
         <v>2022.0</v>
       </c>
       <c r="C382" t="n" s="2">
-        <v>44744.0</v>
+        <v>44737.0</v>
       </c>
       <c r="D382" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="383">
@@ -5490,10 +5490,10 @@
         <v>2022.0</v>
       </c>
       <c r="C383" t="n" s="2">
-        <v>44751.0</v>
+        <v>44744.0</v>
       </c>
       <c r="D383" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="384">
@@ -5504,10 +5504,10 @@
         <v>2022.0</v>
       </c>
       <c r="C384" t="n" s="2">
-        <v>44758.0</v>
+        <v>44751.0</v>
       </c>
       <c r="D384" t="n">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="385">
@@ -5518,10 +5518,10 @@
         <v>2022.0</v>
       </c>
       <c r="C385" t="n" s="2">
-        <v>44765.0</v>
+        <v>44758.0</v>
       </c>
       <c r="D385" t="n">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="386">
@@ -5532,10 +5532,10 @@
         <v>2022.0</v>
       </c>
       <c r="C386" t="n" s="2">
-        <v>44779.0</v>
+        <v>44765.0</v>
       </c>
       <c r="D386" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="387">
@@ -5546,10 +5546,10 @@
         <v>2022.0</v>
       </c>
       <c r="C387" t="n" s="2">
-        <v>44786.0</v>
+        <v>44779.0</v>
       </c>
       <c r="D387" t="n">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="388">
@@ -5560,10 +5560,10 @@
         <v>2022.0</v>
       </c>
       <c r="C388" t="n" s="2">
-        <v>44863.0</v>
+        <v>44786.0</v>
       </c>
       <c r="D388" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="389">
@@ -5574,10 +5574,10 @@
         <v>2022.0</v>
       </c>
       <c r="C389" t="n" s="2">
-        <v>44870.0</v>
+        <v>44863.0</v>
       </c>
       <c r="D389" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="390">
@@ -5588,10 +5588,10 @@
         <v>2022.0</v>
       </c>
       <c r="C390" t="n" s="2">
-        <v>44884.0</v>
+        <v>44870.0</v>
       </c>
       <c r="D390" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="391">
@@ -5602,7 +5602,7 @@
         <v>2022.0</v>
       </c>
       <c r="C391" t="n" s="2">
-        <v>44891.0</v>
+        <v>44884.0</v>
       </c>
       <c r="D391" t="n">
         <v>2.0</v>
@@ -5616,10 +5616,10 @@
         <v>2022.0</v>
       </c>
       <c r="C392" t="n" s="2">
-        <v>44898.0</v>
+        <v>44891.0</v>
       </c>
       <c r="D392" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="393">
@@ -5630,10 +5630,10 @@
         <v>2022.0</v>
       </c>
       <c r="C393" t="n" s="2">
-        <v>44912.0</v>
+        <v>44898.0</v>
       </c>
       <c r="D393" t="n">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="394">
@@ -5644,10 +5644,10 @@
         <v>2022.0</v>
       </c>
       <c r="C394" t="n" s="2">
-        <v>44919.0</v>
+        <v>44912.0</v>
       </c>
       <c r="D394" t="n">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="395">
@@ -5658,10 +5658,10 @@
         <v>2022.0</v>
       </c>
       <c r="C395" t="n" s="2">
-        <v>44926.0</v>
+        <v>44919.0</v>
       </c>
       <c r="D395" t="n">
-        <v>12.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="396">
@@ -5669,13 +5669,13 @@
         <v>7</v>
       </c>
       <c r="B396" t="n">
-        <v>2023.0</v>
+        <v>2022.0</v>
       </c>
       <c r="C396" t="n" s="2">
-        <v>44934.0</v>
+        <v>44926.0</v>
       </c>
       <c r="D396" t="n">
-        <v>4.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="397">
@@ -5686,10 +5686,10 @@
         <v>2023.0</v>
       </c>
       <c r="C397" t="n" s="2">
-        <v>44941.0</v>
+        <v>44934.0</v>
       </c>
       <c r="D397" t="n">
-        <v>16.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="398">
@@ -5700,10 +5700,10 @@
         <v>2023.0</v>
       </c>
       <c r="C398" t="n" s="2">
-        <v>44948.0</v>
+        <v>44941.0</v>
       </c>
       <c r="D398" t="n">
-        <v>5.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="399">
@@ -5714,10 +5714,10 @@
         <v>2023.0</v>
       </c>
       <c r="C399" t="n" s="2">
-        <v>44955.0</v>
+        <v>44948.0</v>
       </c>
       <c r="D399" t="n">
-        <v>19.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="400">
@@ -5728,10 +5728,10 @@
         <v>2023.0</v>
       </c>
       <c r="C400" t="n" s="2">
-        <v>44962.0</v>
+        <v>44955.0</v>
       </c>
       <c r="D400" t="n">
-        <v>22.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="401">
@@ -5742,10 +5742,10 @@
         <v>2023.0</v>
       </c>
       <c r="C401" t="n" s="2">
-        <v>44969.0</v>
+        <v>44962.0</v>
       </c>
       <c r="D401" t="n">
-        <v>9.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="402">
@@ -5756,10 +5756,10 @@
         <v>2023.0</v>
       </c>
       <c r="C402" t="n" s="2">
-        <v>44976.0</v>
+        <v>44969.0</v>
       </c>
       <c r="D402" t="n">
-        <v>22.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="403">
@@ -5770,10 +5770,10 @@
         <v>2023.0</v>
       </c>
       <c r="C403" t="n" s="2">
-        <v>44983.0</v>
+        <v>44976.0</v>
       </c>
       <c r="D403" t="n">
-        <v>29.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="404">
@@ -5784,10 +5784,10 @@
         <v>2023.0</v>
       </c>
       <c r="C404" t="n" s="2">
-        <v>44990.0</v>
+        <v>44983.0</v>
       </c>
       <c r="D404" t="n">
-        <v>5.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="405">
@@ -5798,10 +5798,10 @@
         <v>2023.0</v>
       </c>
       <c r="C405" t="n" s="2">
-        <v>44997.0</v>
+        <v>44990.0</v>
       </c>
       <c r="D405" t="n">
-        <v>24.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="406">
@@ -5812,10 +5812,10 @@
         <v>2023.0</v>
       </c>
       <c r="C406" t="n" s="2">
-        <v>45004.0</v>
+        <v>44997.0</v>
       </c>
       <c r="D406" t="n">
-        <v>8.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="407">
@@ -5826,10 +5826,10 @@
         <v>2023.0</v>
       </c>
       <c r="C407" t="n" s="2">
-        <v>45011.0</v>
+        <v>45004.0</v>
       </c>
       <c r="D407" t="n">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="408">
@@ -5840,10 +5840,10 @@
         <v>2023.0</v>
       </c>
       <c r="C408" t="n" s="2">
-        <v>45018.0</v>
+        <v>45011.0</v>
       </c>
       <c r="D408" t="n">
-        <v>18.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="409">
@@ -5854,10 +5854,10 @@
         <v>2023.0</v>
       </c>
       <c r="C409" t="n" s="2">
-        <v>45025.0</v>
+        <v>45018.0</v>
       </c>
       <c r="D409" t="n">
-        <v>13.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="410">
@@ -5868,10 +5868,10 @@
         <v>2023.0</v>
       </c>
       <c r="C410" t="n" s="2">
-        <v>45032.0</v>
+        <v>45025.0</v>
       </c>
       <c r="D410" t="n">
-        <v>18.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="411">
@@ -5882,10 +5882,10 @@
         <v>2023.0</v>
       </c>
       <c r="C411" t="n" s="2">
-        <v>45039.0</v>
+        <v>45032.0</v>
       </c>
       <c r="D411" t="n">
-        <v>15.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="412">
@@ -5896,10 +5896,10 @@
         <v>2023.0</v>
       </c>
       <c r="C412" t="n" s="2">
-        <v>45046.0</v>
+        <v>45039.0</v>
       </c>
       <c r="D412" t="n">
-        <v>12.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="413">
@@ -5910,10 +5910,10 @@
         <v>2023.0</v>
       </c>
       <c r="C413" t="n" s="2">
-        <v>45053.0</v>
+        <v>45046.0</v>
       </c>
       <c r="D413" t="n">
-        <v>6.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="414">
@@ -5924,10 +5924,10 @@
         <v>2023.0</v>
       </c>
       <c r="C414" t="n" s="2">
-        <v>45060.0</v>
+        <v>45053.0</v>
       </c>
       <c r="D414" t="n">
-        <v>11.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="415">
@@ -5938,10 +5938,10 @@
         <v>2023.0</v>
       </c>
       <c r="C415" t="n" s="2">
-        <v>45067.0</v>
+        <v>45060.0</v>
       </c>
       <c r="D415" t="n">
-        <v>8.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="416">
@@ -5952,7 +5952,7 @@
         <v>2023.0</v>
       </c>
       <c r="C416" t="n" s="2">
-        <v>45074.0</v>
+        <v>45067.0</v>
       </c>
       <c r="D416" t="n">
         <v>8.0</v>
@@ -5966,10 +5966,10 @@
         <v>2023.0</v>
       </c>
       <c r="C417" t="n" s="2">
-        <v>45081.0</v>
+        <v>45074.0</v>
       </c>
       <c r="D417" t="n">
-        <v>5.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="418">
@@ -5980,10 +5980,10 @@
         <v>2023.0</v>
       </c>
       <c r="C418" t="n" s="2">
-        <v>45088.0</v>
+        <v>45081.0</v>
       </c>
       <c r="D418" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="419">
@@ -5994,10 +5994,10 @@
         <v>2023.0</v>
       </c>
       <c r="C419" t="n" s="2">
-        <v>45095.0</v>
+        <v>45088.0</v>
       </c>
       <c r="D419" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="420">
@@ -6008,10 +6008,10 @@
         <v>2023.0</v>
       </c>
       <c r="C420" t="n" s="2">
-        <v>45102.0</v>
+        <v>45095.0</v>
       </c>
       <c r="D420" t="n">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="421">
@@ -6022,10 +6022,10 @@
         <v>2023.0</v>
       </c>
       <c r="C421" t="n" s="2">
-        <v>45109.0</v>
+        <v>45102.0</v>
       </c>
       <c r="D421" t="n">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="422">
@@ -6036,10 +6036,10 @@
         <v>2023.0</v>
       </c>
       <c r="C422" t="n" s="2">
-        <v>45116.0</v>
+        <v>45109.0</v>
       </c>
       <c r="D422" t="n">
-        <v>3.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="423">
@@ -6050,10 +6050,10 @@
         <v>2023.0</v>
       </c>
       <c r="C423" t="n" s="2">
-        <v>45123.0</v>
+        <v>45116.0</v>
       </c>
       <c r="D423" t="n">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="424">
@@ -6064,7 +6064,7 @@
         <v>2023.0</v>
       </c>
       <c r="C424" t="n" s="2">
-        <v>45130.0</v>
+        <v>45123.0</v>
       </c>
       <c r="D424" t="n">
         <v>6.0</v>
@@ -6078,10 +6078,10 @@
         <v>2023.0</v>
       </c>
       <c r="C425" t="n" s="2">
-        <v>45137.0</v>
+        <v>45130.0</v>
       </c>
       <c r="D425" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="426">
@@ -6092,7 +6092,7 @@
         <v>2023.0</v>
       </c>
       <c r="C426" t="n" s="2">
-        <v>45144.0</v>
+        <v>45137.0</v>
       </c>
       <c r="D426" t="n">
         <v>2.0</v>
@@ -6106,7 +6106,7 @@
         <v>2023.0</v>
       </c>
       <c r="C427" t="n" s="2">
-        <v>45151.0</v>
+        <v>45144.0</v>
       </c>
       <c r="D427" t="n">
         <v>2.0</v>
@@ -6120,7 +6120,7 @@
         <v>2023.0</v>
       </c>
       <c r="C428" t="n" s="2">
-        <v>45165.0</v>
+        <v>45151.0</v>
       </c>
       <c r="D428" t="n">
         <v>2.0</v>
@@ -6134,7 +6134,7 @@
         <v>2023.0</v>
       </c>
       <c r="C429" t="n" s="2">
-        <v>45172.0</v>
+        <v>45165.0</v>
       </c>
       <c r="D429" t="n">
         <v>2.0</v>
@@ -6148,10 +6148,10 @@
         <v>2023.0</v>
       </c>
       <c r="C430" t="n" s="2">
-        <v>45179.0</v>
+        <v>45172.0</v>
       </c>
       <c r="D430" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="431">
@@ -6162,7 +6162,7 @@
         <v>2023.0</v>
       </c>
       <c r="C431" t="n" s="2">
-        <v>45186.0</v>
+        <v>45179.0</v>
       </c>
       <c r="D431" t="n">
         <v>1.0</v>
@@ -6176,7 +6176,7 @@
         <v>2023.0</v>
       </c>
       <c r="C432" t="n" s="2">
-        <v>45193.0</v>
+        <v>45186.0</v>
       </c>
       <c r="D432" t="n">
         <v>1.0</v>
@@ -6190,7 +6190,7 @@
         <v>2023.0</v>
       </c>
       <c r="C433" t="n" s="2">
-        <v>45200.0</v>
+        <v>45193.0</v>
       </c>
       <c r="D433" t="n">
         <v>1.0</v>
@@ -6204,7 +6204,7 @@
         <v>2023.0</v>
       </c>
       <c r="C434" t="n" s="2">
-        <v>45207.0</v>
+        <v>45200.0</v>
       </c>
       <c r="D434" t="n">
         <v>1.0</v>
@@ -6218,7 +6218,7 @@
         <v>2023.0</v>
       </c>
       <c r="C435" t="n" s="2">
-        <v>45235.0</v>
+        <v>45207.0</v>
       </c>
       <c r="D435" t="n">
         <v>1.0</v>
@@ -6232,10 +6232,10 @@
         <v>2023.0</v>
       </c>
       <c r="C436" t="n" s="2">
-        <v>45242.0</v>
+        <v>45235.0</v>
       </c>
       <c r="D436" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="437">
@@ -6246,10 +6246,10 @@
         <v>2023.0</v>
       </c>
       <c r="C437" t="n" s="2">
-        <v>45249.0</v>
+        <v>45242.0</v>
       </c>
       <c r="D437" t="n">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="438">
@@ -6260,10 +6260,10 @@
         <v>2023.0</v>
       </c>
       <c r="C438" t="n" s="2">
-        <v>45256.0</v>
+        <v>45249.0</v>
       </c>
       <c r="D438" t="n">
-        <v>9.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="439">
@@ -6274,10 +6274,10 @@
         <v>2023.0</v>
       </c>
       <c r="C439" t="n" s="2">
-        <v>45263.0</v>
+        <v>45256.0</v>
       </c>
       <c r="D439" t="n">
-        <v>12.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="440">
@@ -6288,10 +6288,10 @@
         <v>2023.0</v>
       </c>
       <c r="C440" t="n" s="2">
-        <v>45270.0</v>
+        <v>45263.0</v>
       </c>
       <c r="D440" t="n">
-        <v>6.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="441">
@@ -6302,10 +6302,10 @@
         <v>2023.0</v>
       </c>
       <c r="C441" t="n" s="2">
-        <v>45277.0</v>
+        <v>45270.0</v>
       </c>
       <c r="D441" t="n">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="442">
@@ -6316,7 +6316,7 @@
         <v>2023.0</v>
       </c>
       <c r="C442" t="n" s="2">
-        <v>45284.0</v>
+        <v>45277.0</v>
       </c>
       <c r="D442" t="n">
         <v>7.0</v>
@@ -6330,10 +6330,10 @@
         <v>2023.0</v>
       </c>
       <c r="C443" t="n" s="2">
-        <v>45291.0</v>
+        <v>45284.0</v>
       </c>
       <c r="D443" t="n">
-        <v>13.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="444">
@@ -6341,13 +6341,13 @@
         <v>7</v>
       </c>
       <c r="B444" t="n">
-        <v>2024.0</v>
+        <v>2023.0</v>
       </c>
       <c r="C444" t="n" s="2">
-        <v>45299.0</v>
+        <v>45291.0</v>
       </c>
       <c r="D444" t="n">
-        <v>6.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="445">
@@ -6358,10 +6358,10 @@
         <v>2024.0</v>
       </c>
       <c r="C445" t="n" s="2">
-        <v>45306.0</v>
+        <v>45299.0</v>
       </c>
       <c r="D445" t="n">
-        <v>11.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="446">
@@ -6372,10 +6372,10 @@
         <v>2024.0</v>
       </c>
       <c r="C446" t="n" s="2">
-        <v>45313.0</v>
+        <v>45306.0</v>
       </c>
       <c r="D446" t="n">
-        <v>5.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="447">
@@ -6386,10 +6386,10 @@
         <v>2024.0</v>
       </c>
       <c r="C447" t="n" s="2">
-        <v>45320.0</v>
+        <v>45313.0</v>
       </c>
       <c r="D447" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="448">
@@ -6400,10 +6400,10 @@
         <v>2024.0</v>
       </c>
       <c r="C448" t="n" s="2">
-        <v>45327.0</v>
+        <v>45320.0</v>
       </c>
       <c r="D448" t="n">
-        <v>9.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="449">
@@ -6414,10 +6414,10 @@
         <v>2024.0</v>
       </c>
       <c r="C449" t="n" s="2">
-        <v>45334.0</v>
+        <v>45327.0</v>
       </c>
       <c r="D449" t="n">
-        <v>3.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="450">
@@ -6428,10 +6428,10 @@
         <v>2024.0</v>
       </c>
       <c r="C450" t="n" s="2">
-        <v>45341.0</v>
+        <v>45334.0</v>
       </c>
       <c r="D450" t="n">
-        <v>21.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="451">
@@ -6442,10 +6442,10 @@
         <v>2024.0</v>
       </c>
       <c r="C451" t="n" s="2">
-        <v>45348.0</v>
+        <v>45341.0</v>
       </c>
       <c r="D451" t="n">
-        <v>1.0</v>
+        <v>21.0</v>
       </c>
     </row>
     <row r="452">
@@ -6456,10 +6456,10 @@
         <v>2024.0</v>
       </c>
       <c r="C452" t="n" s="2">
-        <v>45355.0</v>
+        <v>45348.0</v>
       </c>
       <c r="D452" t="n">
-        <v>9.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="453">
@@ -6470,10 +6470,10 @@
         <v>2024.0</v>
       </c>
       <c r="C453" t="n" s="2">
-        <v>45362.0</v>
+        <v>45355.0</v>
       </c>
       <c r="D453" t="n">
-        <v>4.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="454">
@@ -6484,10 +6484,10 @@
         <v>2024.0</v>
       </c>
       <c r="C454" t="n" s="2">
-        <v>45369.0</v>
+        <v>45362.0</v>
       </c>
       <c r="D454" t="n">
-        <v>14.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="455">
@@ -6498,10 +6498,10 @@
         <v>2024.0</v>
       </c>
       <c r="C455" t="n" s="2">
-        <v>45376.0</v>
+        <v>45369.0</v>
       </c>
       <c r="D455" t="n">
-        <v>4.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="456">
@@ -6512,10 +6512,10 @@
         <v>2024.0</v>
       </c>
       <c r="C456" t="n" s="2">
-        <v>45383.0</v>
+        <v>45376.0</v>
       </c>
       <c r="D456" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="457">
@@ -6526,10 +6526,10 @@
         <v>2024.0</v>
       </c>
       <c r="C457" t="n" s="2">
-        <v>45390.0</v>
+        <v>45383.0</v>
       </c>
       <c r="D457" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="458">
@@ -6540,7 +6540,7 @@
         <v>2024.0</v>
       </c>
       <c r="C458" t="n" s="2">
-        <v>45397.0</v>
+        <v>45390.0</v>
       </c>
       <c r="D458" t="n">
         <v>1.0</v>
@@ -6554,10 +6554,10 @@
         <v>2024.0</v>
       </c>
       <c r="C459" t="n" s="2">
-        <v>45404.0</v>
+        <v>45397.0</v>
       </c>
       <c r="D459" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="460">
@@ -6568,10 +6568,10 @@
         <v>2024.0</v>
       </c>
       <c r="C460" t="n" s="2">
-        <v>45411.0</v>
+        <v>45404.0</v>
       </c>
       <c r="D460" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="461">
@@ -6582,10 +6582,10 @@
         <v>2024.0</v>
       </c>
       <c r="C461" t="n" s="2">
-        <v>45439.0</v>
+        <v>45411.0</v>
       </c>
       <c r="D461" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="462">
@@ -6596,10 +6596,10 @@
         <v>2024.0</v>
       </c>
       <c r="C462" t="n" s="2">
-        <v>45446.0</v>
+        <v>45439.0</v>
       </c>
       <c r="D462" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="463">
@@ -6610,7 +6610,7 @@
         <v>2024.0</v>
       </c>
       <c r="C463" t="n" s="2">
-        <v>45460.0</v>
+        <v>45446.0</v>
       </c>
       <c r="D463" t="n">
         <v>1.0</v>
@@ -6624,7 +6624,7 @@
         <v>2024.0</v>
       </c>
       <c r="C464" t="n" s="2">
-        <v>45481.0</v>
+        <v>45460.0</v>
       </c>
       <c r="D464" t="n">
         <v>1.0</v>
@@ -6638,7 +6638,7 @@
         <v>2024.0</v>
       </c>
       <c r="C465" t="n" s="2">
-        <v>45516.0</v>
+        <v>45481.0</v>
       </c>
       <c r="D465" t="n">
         <v>1.0</v>
@@ -6652,7 +6652,7 @@
         <v>2024.0</v>
       </c>
       <c r="C466" t="n" s="2">
-        <v>45551.0</v>
+        <v>45516.0</v>
       </c>
       <c r="D466" t="n">
         <v>1.0</v>
@@ -6666,7 +6666,7 @@
         <v>2024.0</v>
       </c>
       <c r="C467" t="n" s="2">
-        <v>45579.0</v>
+        <v>45551.0</v>
       </c>
       <c r="D467" t="n">
         <v>1.0</v>
@@ -6680,7 +6680,7 @@
         <v>2024.0</v>
       </c>
       <c r="C468" t="n" s="2">
-        <v>45614.0</v>
+        <v>45579.0</v>
       </c>
       <c r="D468" t="n">
         <v>1.0</v>
@@ -6694,10 +6694,10 @@
         <v>2024.0</v>
       </c>
       <c r="C469" t="n" s="2">
-        <v>45635.0</v>
+        <v>45614.0</v>
       </c>
       <c r="D469" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="470">
@@ -6708,10 +6708,10 @@
         <v>2024.0</v>
       </c>
       <c r="C470" t="n" s="2">
-        <v>45642.0</v>
+        <v>45635.0</v>
       </c>
       <c r="D470" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="471">
@@ -6722,10 +6722,10 @@
         <v>2024.0</v>
       </c>
       <c r="C471" t="n" s="2">
-        <v>45649.0</v>
+        <v>45642.0</v>
       </c>
       <c r="D471" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="472">
@@ -6736,10 +6736,10 @@
         <v>2024.0</v>
       </c>
       <c r="C472" t="n" s="2">
-        <v>45656.0</v>
+        <v>45649.0</v>
       </c>
       <c r="D472" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="473">
@@ -6747,13 +6747,13 @@
         <v>7</v>
       </c>
       <c r="B473" t="n">
-        <v>2025.0</v>
+        <v>2024.0</v>
       </c>
       <c r="C473" t="n" s="2">
-        <v>45665.0</v>
+        <v>45656.0</v>
       </c>
       <c r="D473" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="474">
@@ -6764,10 +6764,10 @@
         <v>2025.0</v>
       </c>
       <c r="C474" t="n" s="2">
-        <v>45672.0</v>
+        <v>45665.0</v>
       </c>
       <c r="D474" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="475">
@@ -6778,7 +6778,7 @@
         <v>2025.0</v>
       </c>
       <c r="C475" t="n" s="2">
-        <v>45686.0</v>
+        <v>45672.0</v>
       </c>
       <c r="D475" t="n">
         <v>2.0</v>
@@ -6792,10 +6792,10 @@
         <v>2025.0</v>
       </c>
       <c r="C476" t="n" s="2">
-        <v>45693.0</v>
+        <v>45686.0</v>
       </c>
       <c r="D476" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="477">
@@ -6806,10 +6806,10 @@
         <v>2025.0</v>
       </c>
       <c r="C477" t="n" s="2">
-        <v>45700.0</v>
+        <v>45693.0</v>
       </c>
       <c r="D477" t="n">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="478">
@@ -6820,10 +6820,10 @@
         <v>2025.0</v>
       </c>
       <c r="C478" t="n" s="2">
-        <v>45707.0</v>
+        <v>45700.0</v>
       </c>
       <c r="D478" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="479">
@@ -6834,10 +6834,10 @@
         <v>2025.0</v>
       </c>
       <c r="C479" t="n" s="2">
-        <v>45714.0</v>
+        <v>45707.0</v>
       </c>
       <c r="D479" t="n">
-        <v>8.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="480">
@@ -6848,10 +6848,10 @@
         <v>2025.0</v>
       </c>
       <c r="C480" t="n" s="2">
-        <v>45721.0</v>
+        <v>45714.0</v>
       </c>
       <c r="D480" t="n">
-        <v>11.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="481">
@@ -6862,10 +6862,10 @@
         <v>2025.0</v>
       </c>
       <c r="C481" t="n" s="2">
-        <v>45728.0</v>
+        <v>45721.0</v>
       </c>
       <c r="D481" t="n">
-        <v>6.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="482">
@@ -6876,10 +6876,10 @@
         <v>2025.0</v>
       </c>
       <c r="C482" t="n" s="2">
-        <v>45735.0</v>
+        <v>45728.0</v>
       </c>
       <c r="D482" t="n">
-        <v>19.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="483">
@@ -6890,10 +6890,10 @@
         <v>2025.0</v>
       </c>
       <c r="C483" t="n" s="2">
-        <v>45742.0</v>
+        <v>45735.0</v>
       </c>
       <c r="D483" t="n">
-        <v>17.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="484">
@@ -6904,10 +6904,10 @@
         <v>2025.0</v>
       </c>
       <c r="C484" t="n" s="2">
-        <v>45749.0</v>
+        <v>45742.0</v>
       </c>
       <c r="D484" t="n">
-        <v>5.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="485">
@@ -6918,10 +6918,10 @@
         <v>2025.0</v>
       </c>
       <c r="C485" t="n" s="2">
-        <v>45756.0</v>
+        <v>45749.0</v>
       </c>
       <c r="D485" t="n">
-        <v>9.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="486">
@@ -6932,10 +6932,10 @@
         <v>2025.0</v>
       </c>
       <c r="C486" t="n" s="2">
-        <v>45763.0</v>
+        <v>45756.0</v>
       </c>
       <c r="D486" t="n">
-        <v>1.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="487">
@@ -6946,7 +6946,7 @@
         <v>2025.0</v>
       </c>
       <c r="C487" t="n" s="2">
-        <v>45770.0</v>
+        <v>45763.0</v>
       </c>
       <c r="D487" t="n">
         <v>1.0</v>
@@ -6960,10 +6960,10 @@
         <v>2025.0</v>
       </c>
       <c r="C488" t="n" s="2">
-        <v>45784.0</v>
+        <v>45770.0</v>
       </c>
       <c r="D488" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="489">
@@ -6974,10 +6974,10 @@
         <v>2025.0</v>
       </c>
       <c r="C489" t="n" s="2">
-        <v>45791.0</v>
+        <v>45784.0</v>
       </c>
       <c r="D489" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="490">
@@ -6988,10 +6988,10 @@
         <v>2025.0</v>
       </c>
       <c r="C490" t="n" s="2">
-        <v>45805.0</v>
+        <v>45791.0</v>
       </c>
       <c r="D490" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="491">
@@ -7002,10 +7002,10 @@
         <v>2025.0</v>
       </c>
       <c r="C491" t="n" s="2">
-        <v>45826.0</v>
+        <v>45805.0</v>
       </c>
       <c r="D491" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="492">
@@ -7016,7 +7016,7 @@
         <v>2025.0</v>
       </c>
       <c r="C492" t="n" s="2">
-        <v>45861.0</v>
+        <v>45826.0</v>
       </c>
       <c r="D492" t="n">
         <v>2.0</v>
@@ -7030,10 +7030,10 @@
         <v>2025.0</v>
       </c>
       <c r="C493" t="n" s="2">
-        <v>45868.0</v>
+        <v>45861.0</v>
       </c>
       <c r="D493" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="494">
@@ -7044,7 +7044,7 @@
         <v>2025.0</v>
       </c>
       <c r="C494" t="n" s="2">
-        <v>45889.0</v>
+        <v>45868.0</v>
       </c>
       <c r="D494" t="n">
         <v>1.0</v>
@@ -7058,7 +7058,7 @@
         <v>2025.0</v>
       </c>
       <c r="C495" t="n" s="2">
-        <v>45924.0</v>
+        <v>45889.0</v>
       </c>
       <c r="D495" t="n">
         <v>1.0</v>
@@ -7072,7 +7072,7 @@
         <v>2025.0</v>
       </c>
       <c r="C496" t="n" s="2">
-        <v>45945.0</v>
+        <v>45924.0</v>
       </c>
       <c r="D496" t="n">
         <v>1.0</v>
@@ -7086,10 +7086,10 @@
         <v>2025.0</v>
       </c>
       <c r="C497" t="n" s="2">
-        <v>45959.0</v>
+        <v>45945.0</v>
       </c>
       <c r="D497" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="498">
@@ -7100,7 +7100,7 @@
         <v>2025.0</v>
       </c>
       <c r="C498" t="n" s="2">
-        <v>46001.0</v>
+        <v>45959.0</v>
       </c>
       <c r="D498" t="n">
         <v>2.0</v>
@@ -7114,10 +7114,10 @@
         <v>2025.0</v>
       </c>
       <c r="C499" t="n" s="2">
-        <v>46008.0</v>
+        <v>46001.0</v>
       </c>
       <c r="D499" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="500">
@@ -7128,7 +7128,7 @@
         <v>2025.0</v>
       </c>
       <c r="C500" t="n" s="2">
-        <v>46022.0</v>
+        <v>46008.0</v>
       </c>
       <c r="D500" t="n">
         <v>1.0</v>
@@ -7139,10 +7139,10 @@
         <v>7</v>
       </c>
       <c r="B501" t="n">
-        <v>2026.0</v>
+        <v>2025.0</v>
       </c>
       <c r="C501" t="n" s="2">
-        <v>46030.0</v>
+        <v>46022.0</v>
       </c>
       <c r="D501" t="n">
         <v>1.0</v>
@@ -7156,7 +7156,7 @@
         <v>2026.0</v>
       </c>
       <c r="C502" t="n" s="2">
-        <v>46051.0</v>
+        <v>46030.0</v>
       </c>
       <c r="D502" t="n">
         <v>1.0</v>
@@ -7170,7 +7170,7 @@
         <v>2026.0</v>
       </c>
       <c r="C503" t="n" s="2">
-        <v>46058.0</v>
+        <v>46051.0</v>
       </c>
       <c r="D503" t="n">
         <v>1.0</v>
@@ -7184,24 +7184,24 @@
         <v>2026.0</v>
       </c>
       <c r="C504" t="n" s="2">
-        <v>46065.0</v>
+        <v>46058.0</v>
       </c>
       <c r="D504" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B505" t="n">
-        <v>2024.0</v>
+        <v>2026.0</v>
       </c>
       <c r="C505" t="n" s="2">
-        <v>45495.0</v>
+        <v>46065.0</v>
       </c>
       <c r="D505" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="506">
@@ -7212,10 +7212,10 @@
         <v>2024.0</v>
       </c>
       <c r="C506" t="n" s="2">
-        <v>45502.0</v>
+        <v>45495.0</v>
       </c>
       <c r="D506" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="507">
@@ -7223,13 +7223,13 @@
         <v>8</v>
       </c>
       <c r="B507" t="n">
-        <v>2025.0</v>
+        <v>2024.0</v>
       </c>
       <c r="C507" t="n" s="2">
-        <v>45665.0</v>
+        <v>45502.0</v>
       </c>
       <c r="D507" t="n">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="508">
@@ -7240,10 +7240,10 @@
         <v>2025.0</v>
       </c>
       <c r="C508" t="n" s="2">
-        <v>45672.0</v>
+        <v>45665.0</v>
       </c>
       <c r="D508" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="509">
@@ -7254,10 +7254,10 @@
         <v>2025.0</v>
       </c>
       <c r="C509" t="n" s="2">
-        <v>45679.0</v>
+        <v>45672.0</v>
       </c>
       <c r="D509" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="510">
@@ -7268,10 +7268,10 @@
         <v>2025.0</v>
       </c>
       <c r="C510" t="n" s="2">
-        <v>45686.0</v>
+        <v>45679.0</v>
       </c>
       <c r="D510" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="511">
@@ -7282,10 +7282,10 @@
         <v>2025.0</v>
       </c>
       <c r="C511" t="n" s="2">
-        <v>45693.0</v>
+        <v>45686.0</v>
       </c>
       <c r="D511" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="512">
@@ -7296,10 +7296,10 @@
         <v>2025.0</v>
       </c>
       <c r="C512" t="n" s="2">
-        <v>45700.0</v>
+        <v>45693.0</v>
       </c>
       <c r="D512" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="513">
@@ -7310,10 +7310,10 @@
         <v>2025.0</v>
       </c>
       <c r="C513" t="n" s="2">
-        <v>45707.0</v>
+        <v>45700.0</v>
       </c>
       <c r="D513" t="n">
-        <v>7.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="514">
@@ -7324,10 +7324,10 @@
         <v>2025.0</v>
       </c>
       <c r="C514" t="n" s="2">
-        <v>45714.0</v>
+        <v>45707.0</v>
       </c>
       <c r="D514" t="n">
-        <v>3.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="515">
@@ -7338,10 +7338,10 @@
         <v>2025.0</v>
       </c>
       <c r="C515" t="n" s="2">
-        <v>45721.0</v>
+        <v>45714.0</v>
       </c>
       <c r="D515" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="516">
@@ -7352,10 +7352,10 @@
         <v>2025.0</v>
       </c>
       <c r="C516" t="n" s="2">
-        <v>45728.0</v>
+        <v>45721.0</v>
       </c>
       <c r="D516" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="517">
@@ -7366,7 +7366,7 @@
         <v>2025.0</v>
       </c>
       <c r="C517" t="n" s="2">
-        <v>45742.0</v>
+        <v>45728.0</v>
       </c>
       <c r="D517" t="n">
         <v>1.0</v>
@@ -7380,7 +7380,7 @@
         <v>2025.0</v>
       </c>
       <c r="C518" t="n" s="2">
-        <v>45749.0</v>
+        <v>45742.0</v>
       </c>
       <c r="D518" t="n">
         <v>1.0</v>
@@ -7394,7 +7394,7 @@
         <v>2025.0</v>
       </c>
       <c r="C519" t="n" s="2">
-        <v>45763.0</v>
+        <v>45749.0</v>
       </c>
       <c r="D519" t="n">
         <v>1.0</v>
@@ -7408,10 +7408,10 @@
         <v>2025.0</v>
       </c>
       <c r="C520" t="n" s="2">
-        <v>45777.0</v>
+        <v>45763.0</v>
       </c>
       <c r="D520" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="521">
@@ -7422,10 +7422,10 @@
         <v>2025.0</v>
       </c>
       <c r="C521" t="n" s="2">
-        <v>45784.0</v>
+        <v>45777.0</v>
       </c>
       <c r="D521" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="522">
@@ -7436,7 +7436,7 @@
         <v>2025.0</v>
       </c>
       <c r="C522" t="n" s="2">
-        <v>45798.0</v>
+        <v>45784.0</v>
       </c>
       <c r="D522" t="n">
         <v>1.0</v>
@@ -7450,7 +7450,7 @@
         <v>2025.0</v>
       </c>
       <c r="C523" t="n" s="2">
-        <v>45805.0</v>
+        <v>45798.0</v>
       </c>
       <c r="D523" t="n">
         <v>1.0</v>
@@ -7464,10 +7464,10 @@
         <v>2025.0</v>
       </c>
       <c r="C524" t="n" s="2">
-        <v>45812.0</v>
+        <v>45805.0</v>
       </c>
       <c r="D524" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="525">
@@ -7478,7 +7478,7 @@
         <v>2025.0</v>
       </c>
       <c r="C525" t="n" s="2">
-        <v>45819.0</v>
+        <v>45812.0</v>
       </c>
       <c r="D525" t="n">
         <v>2.0</v>
@@ -7492,7 +7492,7 @@
         <v>2025.0</v>
       </c>
       <c r="C526" t="n" s="2">
-        <v>45833.0</v>
+        <v>45819.0</v>
       </c>
       <c r="D526" t="n">
         <v>2.0</v>
@@ -7506,10 +7506,10 @@
         <v>2025.0</v>
       </c>
       <c r="C527" t="n" s="2">
-        <v>45847.0</v>
+        <v>45833.0</v>
       </c>
       <c r="D527" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="528">
@@ -7520,10 +7520,10 @@
         <v>2025.0</v>
       </c>
       <c r="C528" t="n" s="2">
-        <v>45854.0</v>
+        <v>45847.0</v>
       </c>
       <c r="D528" t="n">
-        <v>8.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="529">
@@ -7534,10 +7534,10 @@
         <v>2025.0</v>
       </c>
       <c r="C529" t="n" s="2">
-        <v>45861.0</v>
+        <v>45854.0</v>
       </c>
       <c r="D529" t="n">
-        <v>12.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="530">
@@ -7548,10 +7548,10 @@
         <v>2025.0</v>
       </c>
       <c r="C530" t="n" s="2">
-        <v>45868.0</v>
+        <v>45861.0</v>
       </c>
       <c r="D530" t="n">
-        <v>6.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="531">
@@ -7562,10 +7562,10 @@
         <v>2025.0</v>
       </c>
       <c r="C531" t="n" s="2">
-        <v>45875.0</v>
+        <v>45868.0</v>
       </c>
       <c r="D531" t="n">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="532">
@@ -7576,7 +7576,7 @@
         <v>2025.0</v>
       </c>
       <c r="C532" t="n" s="2">
-        <v>45896.0</v>
+        <v>45875.0</v>
       </c>
       <c r="D532" t="n">
         <v>1.0</v>
@@ -7590,7 +7590,7 @@
         <v>2025.0</v>
       </c>
       <c r="C533" t="n" s="2">
-        <v>45903.0</v>
+        <v>45896.0</v>
       </c>
       <c r="D533" t="n">
         <v>1.0</v>
@@ -7604,7 +7604,7 @@
         <v>2025.0</v>
       </c>
       <c r="C534" t="n" s="2">
-        <v>45931.0</v>
+        <v>45903.0</v>
       </c>
       <c r="D534" t="n">
         <v>1.0</v>
@@ -7618,10 +7618,10 @@
         <v>2025.0</v>
       </c>
       <c r="C535" t="n" s="2">
-        <v>45938.0</v>
+        <v>45931.0</v>
       </c>
       <c r="D535" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="536">
@@ -7632,10 +7632,10 @@
         <v>2025.0</v>
       </c>
       <c r="C536" t="n" s="2">
-        <v>45945.0</v>
+        <v>45938.0</v>
       </c>
       <c r="D536" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="537">
@@ -7646,7 +7646,7 @@
         <v>2025.0</v>
       </c>
       <c r="C537" t="n" s="2">
-        <v>45966.0</v>
+        <v>45945.0</v>
       </c>
       <c r="D537" t="n">
         <v>2.0</v>
@@ -7660,10 +7660,10 @@
         <v>2025.0</v>
       </c>
       <c r="C538" t="n" s="2">
-        <v>45973.0</v>
+        <v>45966.0</v>
       </c>
       <c r="D538" t="n">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="539">
@@ -7674,10 +7674,10 @@
         <v>2025.0</v>
       </c>
       <c r="C539" t="n" s="2">
-        <v>45980.0</v>
+        <v>45973.0</v>
       </c>
       <c r="D539" t="n">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="540">
@@ -7688,10 +7688,10 @@
         <v>2025.0</v>
       </c>
       <c r="C540" t="n" s="2">
-        <v>45987.0</v>
+        <v>45980.0</v>
       </c>
       <c r="D540" t="n">
-        <v>20.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="541">
@@ -7702,10 +7702,10 @@
         <v>2025.0</v>
       </c>
       <c r="C541" t="n" s="2">
-        <v>45994.0</v>
+        <v>45987.0</v>
       </c>
       <c r="D541" t="n">
-        <v>5.0</v>
+        <v>20.0</v>
       </c>
     </row>
     <row r="542">
@@ -7716,10 +7716,10 @@
         <v>2025.0</v>
       </c>
       <c r="C542" t="n" s="2">
-        <v>46001.0</v>
+        <v>45994.0</v>
       </c>
       <c r="D542" t="n">
-        <v>8.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="543">
@@ -7730,10 +7730,10 @@
         <v>2025.0</v>
       </c>
       <c r="C543" t="n" s="2">
-        <v>46008.0</v>
+        <v>46001.0</v>
       </c>
       <c r="D543" t="n">
-        <v>24.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="544">
@@ -7744,10 +7744,10 @@
         <v>2025.0</v>
       </c>
       <c r="C544" t="n" s="2">
-        <v>46015.0</v>
+        <v>46008.0</v>
       </c>
       <c r="D544" t="n">
-        <v>13.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="545">
@@ -7758,10 +7758,10 @@
         <v>2025.0</v>
       </c>
       <c r="C545" t="n" s="2">
-        <v>46022.0</v>
+        <v>46015.0</v>
       </c>
       <c r="D545" t="n">
-        <v>7.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="546">
@@ -7772,10 +7772,10 @@
         <v>2025.0</v>
       </c>
       <c r="C546" t="n" s="2">
-        <v>46029.0</v>
+        <v>46022.0</v>
       </c>
       <c r="D546" t="n">
-        <v>3.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="547">
@@ -7783,13 +7783,13 @@
         <v>8</v>
       </c>
       <c r="B547" t="n">
-        <v>2026.0</v>
+        <v>2025.0</v>
       </c>
       <c r="C547" t="n" s="2">
-        <v>46030.0</v>
+        <v>46029.0</v>
       </c>
       <c r="D547" t="n">
-        <v>24.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="548">
@@ -7800,10 +7800,10 @@
         <v>2026.0</v>
       </c>
       <c r="C548" t="n" s="2">
-        <v>46037.0</v>
+        <v>46030.0</v>
       </c>
       <c r="D548" t="n">
-        <v>22.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="549">
@@ -7814,10 +7814,10 @@
         <v>2026.0</v>
       </c>
       <c r="C549" t="n" s="2">
-        <v>46044.0</v>
+        <v>46037.0</v>
       </c>
       <c r="D549" t="n">
-        <v>27.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="550">
@@ -7828,10 +7828,10 @@
         <v>2026.0</v>
       </c>
       <c r="C550" t="n" s="2">
-        <v>46051.0</v>
+        <v>46044.0</v>
       </c>
       <c r="D550" t="n">
-        <v>18.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="551">
@@ -7842,10 +7842,10 @@
         <v>2026.0</v>
       </c>
       <c r="C551" t="n" s="2">
-        <v>46058.0</v>
+        <v>46051.0</v>
       </c>
       <c r="D551" t="n">
-        <v>25.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="552">
@@ -7856,10 +7856,10 @@
         <v>2026.0</v>
       </c>
       <c r="C552" t="n" s="2">
-        <v>46065.0</v>
+        <v>46058.0</v>
       </c>
       <c r="D552" t="n">
-        <v>22.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="553">
@@ -7870,10 +7870,10 @@
         <v>2026.0</v>
       </c>
       <c r="C553" t="n" s="2">
-        <v>46072.0</v>
+        <v>46065.0</v>
       </c>
       <c r="D553" t="n">
-        <v>13.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="554">
@@ -7884,10 +7884,10 @@
         <v>2026.0</v>
       </c>
       <c r="C554" t="n" s="2">
-        <v>46079.0</v>
+        <v>46072.0</v>
       </c>
       <c r="D554" t="n">
-        <v>24.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="555">
@@ -7898,10 +7898,10 @@
         <v>2026.0</v>
       </c>
       <c r="C555" t="n" s="2">
-        <v>46086.0</v>
+        <v>46079.0</v>
       </c>
       <c r="D555" t="n">
-        <v>26.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="556">
@@ -7912,9 +7912,23 @@
         <v>2026.0</v>
       </c>
       <c r="C556" t="n" s="2">
+        <v>46086.0</v>
+      </c>
+      <c r="D556" t="n">
+        <v>26.0</v>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="s">
+        <v>8</v>
+      </c>
+      <c r="B557" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C557" t="n" s="2">
         <v>46093.0</v>
       </c>
-      <c r="D556" t="n">
+      <c r="D557" t="n">
         <v>30.0</v>
       </c>
     </row>
@@ -7965,7 +7979,7 @@
         <v>13</v>
       </c>
       <c r="B5" t="n">
-        <v>2007.0</v>
+        <v>2008.0</v>
       </c>
     </row>
   </sheetData>
@@ -8052,7 +8066,7 @@
         <v>19</v>
       </c>
       <c r="C7" t="n">
-        <v>151.0</v>
+        <v>152.0</v>
       </c>
     </row>
     <row r="8">

--- a/Download/Focus_Positivi_ZR.xlsx
+++ b/Download/Focus_Positivi_ZR.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="601" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="602" uniqueCount="23">
   <si>
     <t>NOME_REGIONE</t>
   </si>
@@ -7929,7 +7929,21 @@
         <v>46093.0</v>
       </c>
       <c r="D557" t="n">
-        <v>30.0</v>
+        <v>32.0</v>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="s">
+        <v>8</v>
+      </c>
+      <c r="B558" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C558" t="n" s="2">
+        <v>46100.0</v>
+      </c>
+      <c r="D558" t="n">
+        <v>1.0</v>
       </c>
     </row>
   </sheetData>
@@ -7955,7 +7969,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="n">
-        <v>48.0</v>
+        <v>49.0</v>
       </c>
     </row>
     <row r="3">
@@ -7971,7 +7985,7 @@
         <v>12</v>
       </c>
       <c r="B4" t="n">
-        <v>1131.0</v>
+        <v>1133.0</v>
       </c>
     </row>
     <row r="5">
@@ -8055,7 +8069,7 @@
         <v>22</v>
       </c>
       <c r="C6" t="n">
-        <v>286.0</v>
+        <v>287.0</v>
       </c>
     </row>
     <row r="7">
@@ -8099,7 +8113,7 @@
         <v>19</v>
       </c>
       <c r="C10" t="n">
-        <v>139.0</v>
+        <v>140.0</v>
       </c>
     </row>
     <row r="11">
@@ -8110,7 +8124,7 @@
         <v>19</v>
       </c>
       <c r="C11" t="n">
-        <v>34.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="12">

--- a/Download/Focus_Positivi_ZR.xlsx
+++ b/Download/Focus_Positivi_ZR.xlsx
@@ -4098,13 +4098,13 @@
     </row>
     <row r="284">
       <c r="A284" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B284" t="n">
-        <v>2023.0</v>
+        <v>2026.0</v>
       </c>
       <c r="C284" t="n" s="2">
-        <v>45095.0</v>
+        <v>46100.0</v>
       </c>
       <c r="D284" t="n">
         <v>1.0</v>
@@ -4118,7 +4118,7 @@
         <v>2023.0</v>
       </c>
       <c r="C285" t="n" s="2">
-        <v>45102.0</v>
+        <v>45095.0</v>
       </c>
       <c r="D285" t="n">
         <v>1.0</v>
@@ -4132,7 +4132,7 @@
         <v>2023.0</v>
       </c>
       <c r="C286" t="n" s="2">
-        <v>45158.0</v>
+        <v>45102.0</v>
       </c>
       <c r="D286" t="n">
         <v>1.0</v>
@@ -4146,10 +4146,10 @@
         <v>2023.0</v>
       </c>
       <c r="C287" t="n" s="2">
-        <v>45207.0</v>
+        <v>45158.0</v>
       </c>
       <c r="D287" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="288">
@@ -4160,7 +4160,7 @@
         <v>2023.0</v>
       </c>
       <c r="C288" t="n" s="2">
-        <v>45214.0</v>
+        <v>45207.0</v>
       </c>
       <c r="D288" t="n">
         <v>3.0</v>
@@ -4174,10 +4174,10 @@
         <v>2023.0</v>
       </c>
       <c r="C289" t="n" s="2">
-        <v>45221.0</v>
+        <v>45214.0</v>
       </c>
       <c r="D289" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="290">
@@ -4188,7 +4188,7 @@
         <v>2023.0</v>
       </c>
       <c r="C290" t="n" s="2">
-        <v>45249.0</v>
+        <v>45221.0</v>
       </c>
       <c r="D290" t="n">
         <v>1.0</v>
@@ -4202,10 +4202,10 @@
         <v>2023.0</v>
       </c>
       <c r="C291" t="n" s="2">
-        <v>45256.0</v>
+        <v>45249.0</v>
       </c>
       <c r="D291" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="292">
@@ -4216,10 +4216,10 @@
         <v>2023.0</v>
       </c>
       <c r="C292" t="n" s="2">
-        <v>45263.0</v>
+        <v>45256.0</v>
       </c>
       <c r="D292" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="293">
@@ -4230,10 +4230,10 @@
         <v>2023.0</v>
       </c>
       <c r="C293" t="n" s="2">
-        <v>45270.0</v>
+        <v>45263.0</v>
       </c>
       <c r="D293" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="294">
@@ -4244,10 +4244,10 @@
         <v>2023.0</v>
       </c>
       <c r="C294" t="n" s="2">
-        <v>45277.0</v>
+        <v>45270.0</v>
       </c>
       <c r="D294" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="295">
@@ -4258,10 +4258,10 @@
         <v>2023.0</v>
       </c>
       <c r="C295" t="n" s="2">
-        <v>45284.0</v>
+        <v>45277.0</v>
       </c>
       <c r="D295" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="296">
@@ -4272,10 +4272,10 @@
         <v>2023.0</v>
       </c>
       <c r="C296" t="n" s="2">
-        <v>45291.0</v>
+        <v>45284.0</v>
       </c>
       <c r="D296" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="297">
@@ -4283,13 +4283,13 @@
         <v>6</v>
       </c>
       <c r="B297" t="n">
-        <v>2024.0</v>
+        <v>2023.0</v>
       </c>
       <c r="C297" t="n" s="2">
-        <v>45306.0</v>
+        <v>45291.0</v>
       </c>
       <c r="D297" t="n">
-        <v>7.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="298">
@@ -4300,10 +4300,10 @@
         <v>2024.0</v>
       </c>
       <c r="C298" t="n" s="2">
-        <v>45313.0</v>
+        <v>45306.0</v>
       </c>
       <c r="D298" t="n">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="299">
@@ -4314,10 +4314,10 @@
         <v>2024.0</v>
       </c>
       <c r="C299" t="n" s="2">
-        <v>45320.0</v>
+        <v>45313.0</v>
       </c>
       <c r="D299" t="n">
-        <v>19.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="300">
@@ -4328,10 +4328,10 @@
         <v>2024.0</v>
       </c>
       <c r="C300" t="n" s="2">
-        <v>45327.0</v>
+        <v>45320.0</v>
       </c>
       <c r="D300" t="n">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="301">
@@ -4342,10 +4342,10 @@
         <v>2024.0</v>
       </c>
       <c r="C301" t="n" s="2">
-        <v>45334.0</v>
+        <v>45327.0</v>
       </c>
       <c r="D301" t="n">
-        <v>9.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="302">
@@ -4356,10 +4356,10 @@
         <v>2024.0</v>
       </c>
       <c r="C302" t="n" s="2">
-        <v>45341.0</v>
+        <v>45334.0</v>
       </c>
       <c r="D302" t="n">
-        <v>12.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="303">
@@ -4370,7 +4370,7 @@
         <v>2024.0</v>
       </c>
       <c r="C303" t="n" s="2">
-        <v>45348.0</v>
+        <v>45341.0</v>
       </c>
       <c r="D303" t="n">
         <v>12.0</v>
@@ -4384,10 +4384,10 @@
         <v>2024.0</v>
       </c>
       <c r="C304" t="n" s="2">
-        <v>45355.0</v>
+        <v>45348.0</v>
       </c>
       <c r="D304" t="n">
-        <v>10.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="305">
@@ -4398,10 +4398,10 @@
         <v>2024.0</v>
       </c>
       <c r="C305" t="n" s="2">
-        <v>45362.0</v>
+        <v>45355.0</v>
       </c>
       <c r="D305" t="n">
-        <v>12.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="306">
@@ -4412,10 +4412,10 @@
         <v>2024.0</v>
       </c>
       <c r="C306" t="n" s="2">
-        <v>45369.0</v>
+        <v>45362.0</v>
       </c>
       <c r="D306" t="n">
-        <v>13.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="307">
@@ -4426,10 +4426,10 @@
         <v>2024.0</v>
       </c>
       <c r="C307" t="n" s="2">
-        <v>45376.0</v>
+        <v>45369.0</v>
       </c>
       <c r="D307" t="n">
-        <v>18.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="308">
@@ -4440,10 +4440,10 @@
         <v>2024.0</v>
       </c>
       <c r="C308" t="n" s="2">
-        <v>45383.0</v>
+        <v>45376.0</v>
       </c>
       <c r="D308" t="n">
-        <v>12.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="309">
@@ -4454,10 +4454,10 @@
         <v>2024.0</v>
       </c>
       <c r="C309" t="n" s="2">
-        <v>45390.0</v>
+        <v>45383.0</v>
       </c>
       <c r="D309" t="n">
-        <v>6.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="310">
@@ -4468,10 +4468,10 @@
         <v>2024.0</v>
       </c>
       <c r="C310" t="n" s="2">
-        <v>45397.0</v>
+        <v>45390.0</v>
       </c>
       <c r="D310" t="n">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="311">
@@ -4482,10 +4482,10 @@
         <v>2024.0</v>
       </c>
       <c r="C311" t="n" s="2">
-        <v>45404.0</v>
+        <v>45397.0</v>
       </c>
       <c r="D311" t="n">
-        <v>3.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="312">
@@ -4496,10 +4496,10 @@
         <v>2024.0</v>
       </c>
       <c r="C312" t="n" s="2">
-        <v>45411.0</v>
+        <v>45404.0</v>
       </c>
       <c r="D312" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="313">
@@ -4510,10 +4510,10 @@
         <v>2024.0</v>
       </c>
       <c r="C313" t="n" s="2">
-        <v>45418.0</v>
+        <v>45411.0</v>
       </c>
       <c r="D313" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="314">
@@ -4524,10 +4524,10 @@
         <v>2024.0</v>
       </c>
       <c r="C314" t="n" s="2">
-        <v>45425.0</v>
+        <v>45418.0</v>
       </c>
       <c r="D314" t="n">
-        <v>9.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="315">
@@ -4538,10 +4538,10 @@
         <v>2024.0</v>
       </c>
       <c r="C315" t="n" s="2">
-        <v>45432.0</v>
+        <v>45425.0</v>
       </c>
       <c r="D315" t="n">
-        <v>6.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="316">
@@ -4552,7 +4552,7 @@
         <v>2024.0</v>
       </c>
       <c r="C316" t="n" s="2">
-        <v>45439.0</v>
+        <v>45432.0</v>
       </c>
       <c r="D316" t="n">
         <v>6.0</v>
@@ -4566,10 +4566,10 @@
         <v>2024.0</v>
       </c>
       <c r="C317" t="n" s="2">
-        <v>45446.0</v>
+        <v>45439.0</v>
       </c>
       <c r="D317" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="318">
@@ -4580,10 +4580,10 @@
         <v>2024.0</v>
       </c>
       <c r="C318" t="n" s="2">
-        <v>45453.0</v>
+        <v>45446.0</v>
       </c>
       <c r="D318" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="319">
@@ -4594,7 +4594,7 @@
         <v>2024.0</v>
       </c>
       <c r="C319" t="n" s="2">
-        <v>45460.0</v>
+        <v>45453.0</v>
       </c>
       <c r="D319" t="n">
         <v>4.0</v>
@@ -4608,7 +4608,7 @@
         <v>2024.0</v>
       </c>
       <c r="C320" t="n" s="2">
-        <v>45467.0</v>
+        <v>45460.0</v>
       </c>
       <c r="D320" t="n">
         <v>4.0</v>
@@ -4622,10 +4622,10 @@
         <v>2024.0</v>
       </c>
       <c r="C321" t="n" s="2">
-        <v>45474.0</v>
+        <v>45467.0</v>
       </c>
       <c r="D321" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="322">
@@ -4636,10 +4636,10 @@
         <v>2024.0</v>
       </c>
       <c r="C322" t="n" s="2">
-        <v>45481.0</v>
+        <v>45474.0</v>
       </c>
       <c r="D322" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="323">
@@ -4650,10 +4650,10 @@
         <v>2024.0</v>
       </c>
       <c r="C323" t="n" s="2">
-        <v>45488.0</v>
+        <v>45481.0</v>
       </c>
       <c r="D323" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="324">
@@ -4664,10 +4664,10 @@
         <v>2024.0</v>
       </c>
       <c r="C324" t="n" s="2">
-        <v>45495.0</v>
+        <v>45488.0</v>
       </c>
       <c r="D324" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="325">
@@ -4678,10 +4678,10 @@
         <v>2024.0</v>
       </c>
       <c r="C325" t="n" s="2">
-        <v>45502.0</v>
+        <v>45495.0</v>
       </c>
       <c r="D325" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="326">
@@ -4692,10 +4692,10 @@
         <v>2024.0</v>
       </c>
       <c r="C326" t="n" s="2">
-        <v>45509.0</v>
+        <v>45502.0</v>
       </c>
       <c r="D326" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="327">
@@ -4706,7 +4706,7 @@
         <v>2024.0</v>
       </c>
       <c r="C327" t="n" s="2">
-        <v>45523.0</v>
+        <v>45509.0</v>
       </c>
       <c r="D327" t="n">
         <v>1.0</v>
@@ -4720,7 +4720,7 @@
         <v>2024.0</v>
       </c>
       <c r="C328" t="n" s="2">
-        <v>45551.0</v>
+        <v>45523.0</v>
       </c>
       <c r="D328" t="n">
         <v>1.0</v>
@@ -4734,7 +4734,7 @@
         <v>2024.0</v>
       </c>
       <c r="C329" t="n" s="2">
-        <v>45558.0</v>
+        <v>45551.0</v>
       </c>
       <c r="D329" t="n">
         <v>1.0</v>
@@ -4748,10 +4748,10 @@
         <v>2024.0</v>
       </c>
       <c r="C330" t="n" s="2">
-        <v>45572.0</v>
+        <v>45558.0</v>
       </c>
       <c r="D330" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="331">
@@ -4762,10 +4762,10 @@
         <v>2024.0</v>
       </c>
       <c r="C331" t="n" s="2">
-        <v>45593.0</v>
+        <v>45572.0</v>
       </c>
       <c r="D331" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="332">
@@ -4776,10 +4776,10 @@
         <v>2024.0</v>
       </c>
       <c r="C332" t="n" s="2">
-        <v>45614.0</v>
+        <v>45593.0</v>
       </c>
       <c r="D332" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="333">
@@ -4790,10 +4790,10 @@
         <v>2024.0</v>
       </c>
       <c r="C333" t="n" s="2">
-        <v>45621.0</v>
+        <v>45614.0</v>
       </c>
       <c r="D333" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="334">
@@ -4804,7 +4804,7 @@
         <v>2024.0</v>
       </c>
       <c r="C334" t="n" s="2">
-        <v>45635.0</v>
+        <v>45621.0</v>
       </c>
       <c r="D334" t="n">
         <v>1.0</v>
@@ -4818,7 +4818,7 @@
         <v>2024.0</v>
       </c>
       <c r="C335" t="n" s="2">
-        <v>45649.0</v>
+        <v>45635.0</v>
       </c>
       <c r="D335" t="n">
         <v>1.0</v>
@@ -4829,13 +4829,13 @@
         <v>6</v>
       </c>
       <c r="B336" t="n">
-        <v>2025.0</v>
+        <v>2024.0</v>
       </c>
       <c r="C336" t="n" s="2">
-        <v>45665.0</v>
+        <v>45649.0</v>
       </c>
       <c r="D336" t="n">
-        <v>9.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="337">
@@ -4846,10 +4846,10 @@
         <v>2025.0</v>
       </c>
       <c r="C337" t="n" s="2">
-        <v>45672.0</v>
+        <v>45665.0</v>
       </c>
       <c r="D337" t="n">
-        <v>3.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="338">
@@ -4860,10 +4860,10 @@
         <v>2025.0</v>
       </c>
       <c r="C338" t="n" s="2">
-        <v>45679.0</v>
+        <v>45672.0</v>
       </c>
       <c r="D338" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="339">
@@ -4874,10 +4874,10 @@
         <v>2025.0</v>
       </c>
       <c r="C339" t="n" s="2">
-        <v>45686.0</v>
+        <v>45679.0</v>
       </c>
       <c r="D339" t="n">
-        <v>8.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="340">
@@ -4888,10 +4888,10 @@
         <v>2025.0</v>
       </c>
       <c r="C340" t="n" s="2">
-        <v>45693.0</v>
+        <v>45686.0</v>
       </c>
       <c r="D340" t="n">
-        <v>3.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="341">
@@ -4902,10 +4902,10 @@
         <v>2025.0</v>
       </c>
       <c r="C341" t="n" s="2">
-        <v>45700.0</v>
+        <v>45693.0</v>
       </c>
       <c r="D341" t="n">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="342">
@@ -4916,10 +4916,10 @@
         <v>2025.0</v>
       </c>
       <c r="C342" t="n" s="2">
-        <v>45707.0</v>
+        <v>45700.0</v>
       </c>
       <c r="D342" t="n">
-        <v>8.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="343">
@@ -4930,10 +4930,10 @@
         <v>2025.0</v>
       </c>
       <c r="C343" t="n" s="2">
-        <v>45714.0</v>
+        <v>45707.0</v>
       </c>
       <c r="D343" t="n">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="344">
@@ -4944,10 +4944,10 @@
         <v>2025.0</v>
       </c>
       <c r="C344" t="n" s="2">
-        <v>45721.0</v>
+        <v>45714.0</v>
       </c>
       <c r="D344" t="n">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="345">
@@ -4958,10 +4958,10 @@
         <v>2025.0</v>
       </c>
       <c r="C345" t="n" s="2">
-        <v>45728.0</v>
+        <v>45721.0</v>
       </c>
       <c r="D345" t="n">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="346">
@@ -4972,10 +4972,10 @@
         <v>2025.0</v>
       </c>
       <c r="C346" t="n" s="2">
-        <v>45735.0</v>
+        <v>45728.0</v>
       </c>
       <c r="D346" t="n">
-        <v>4.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="347">
@@ -4986,10 +4986,10 @@
         <v>2025.0</v>
       </c>
       <c r="C347" t="n" s="2">
-        <v>45742.0</v>
+        <v>45735.0</v>
       </c>
       <c r="D347" t="n">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="348">
@@ -5000,10 +5000,10 @@
         <v>2025.0</v>
       </c>
       <c r="C348" t="n" s="2">
-        <v>45749.0</v>
+        <v>45742.0</v>
       </c>
       <c r="D348" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="349">
@@ -5014,10 +5014,10 @@
         <v>2025.0</v>
       </c>
       <c r="C349" t="n" s="2">
-        <v>45756.0</v>
+        <v>45749.0</v>
       </c>
       <c r="D349" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="350">
@@ -5028,10 +5028,10 @@
         <v>2025.0</v>
       </c>
       <c r="C350" t="n" s="2">
-        <v>45763.0</v>
+        <v>45756.0</v>
       </c>
       <c r="D350" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="351">
@@ -5042,7 +5042,7 @@
         <v>2025.0</v>
       </c>
       <c r="C351" t="n" s="2">
-        <v>45770.0</v>
+        <v>45763.0</v>
       </c>
       <c r="D351" t="n">
         <v>4.0</v>
@@ -5056,10 +5056,10 @@
         <v>2025.0</v>
       </c>
       <c r="C352" t="n" s="2">
-        <v>45777.0</v>
+        <v>45770.0</v>
       </c>
       <c r="D352" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="353">
@@ -5070,7 +5070,7 @@
         <v>2025.0</v>
       </c>
       <c r="C353" t="n" s="2">
-        <v>45784.0</v>
+        <v>45777.0</v>
       </c>
       <c r="D353" t="n">
         <v>1.0</v>
@@ -5084,7 +5084,7 @@
         <v>2025.0</v>
       </c>
       <c r="C354" t="n" s="2">
-        <v>45791.0</v>
+        <v>45784.0</v>
       </c>
       <c r="D354" t="n">
         <v>1.0</v>
@@ -5098,7 +5098,7 @@
         <v>2025.0</v>
       </c>
       <c r="C355" t="n" s="2">
-        <v>45840.0</v>
+        <v>45791.0</v>
       </c>
       <c r="D355" t="n">
         <v>1.0</v>
@@ -5112,7 +5112,7 @@
         <v>2025.0</v>
       </c>
       <c r="C356" t="n" s="2">
-        <v>46001.0</v>
+        <v>45840.0</v>
       </c>
       <c r="D356" t="n">
         <v>1.0</v>
@@ -5123,10 +5123,10 @@
         <v>6</v>
       </c>
       <c r="B357" t="n">
-        <v>2026.0</v>
+        <v>2025.0</v>
       </c>
       <c r="C357" t="n" s="2">
-        <v>46037.0</v>
+        <v>46001.0</v>
       </c>
       <c r="D357" t="n">
         <v>1.0</v>
@@ -5134,13 +5134,13 @@
     </row>
     <row r="358">
       <c r="A358" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B358" t="n">
-        <v>2021.0</v>
+        <v>2026.0</v>
       </c>
       <c r="C358" t="n" s="2">
-        <v>44561.0</v>
+        <v>46037.0</v>
       </c>
       <c r="D358" t="n">
         <v>1.0</v>
@@ -5151,10 +5151,10 @@
         <v>7</v>
       </c>
       <c r="B359" t="n">
-        <v>2022.0</v>
+        <v>2021.0</v>
       </c>
       <c r="C359" t="n" s="2">
-        <v>44569.0</v>
+        <v>44561.0</v>
       </c>
       <c r="D359" t="n">
         <v>1.0</v>
@@ -5168,10 +5168,10 @@
         <v>2022.0</v>
       </c>
       <c r="C360" t="n" s="2">
-        <v>44576.0</v>
+        <v>44569.0</v>
       </c>
       <c r="D360" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="361">
@@ -5182,10 +5182,10 @@
         <v>2022.0</v>
       </c>
       <c r="C361" t="n" s="2">
-        <v>44583.0</v>
+        <v>44576.0</v>
       </c>
       <c r="D361" t="n">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="362">
@@ -5196,10 +5196,10 @@
         <v>2022.0</v>
       </c>
       <c r="C362" t="n" s="2">
-        <v>44590.0</v>
+        <v>44583.0</v>
       </c>
       <c r="D362" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="363">
@@ -5210,10 +5210,10 @@
         <v>2022.0</v>
       </c>
       <c r="C363" t="n" s="2">
-        <v>44604.0</v>
+        <v>44590.0</v>
       </c>
       <c r="D363" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="364">
@@ -5224,7 +5224,7 @@
         <v>2022.0</v>
       </c>
       <c r="C364" t="n" s="2">
-        <v>44611.0</v>
+        <v>44604.0</v>
       </c>
       <c r="D364" t="n">
         <v>3.0</v>
@@ -5238,10 +5238,10 @@
         <v>2022.0</v>
       </c>
       <c r="C365" t="n" s="2">
-        <v>44618.0</v>
+        <v>44611.0</v>
       </c>
       <c r="D365" t="n">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="366">
@@ -5252,7 +5252,7 @@
         <v>2022.0</v>
       </c>
       <c r="C366" t="n" s="2">
-        <v>44625.0</v>
+        <v>44618.0</v>
       </c>
       <c r="D366" t="n">
         <v>5.0</v>
@@ -5266,10 +5266,10 @@
         <v>2022.0</v>
       </c>
       <c r="C367" t="n" s="2">
-        <v>44632.0</v>
+        <v>44625.0</v>
       </c>
       <c r="D367" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="368">
@@ -5280,10 +5280,10 @@
         <v>2022.0</v>
       </c>
       <c r="C368" t="n" s="2">
-        <v>44639.0</v>
+        <v>44632.0</v>
       </c>
       <c r="D368" t="n">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="369">
@@ -5294,10 +5294,10 @@
         <v>2022.0</v>
       </c>
       <c r="C369" t="n" s="2">
-        <v>44646.0</v>
+        <v>44639.0</v>
       </c>
       <c r="D369" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="370">
@@ -5308,10 +5308,10 @@
         <v>2022.0</v>
       </c>
       <c r="C370" t="n" s="2">
-        <v>44653.0</v>
+        <v>44646.0</v>
       </c>
       <c r="D370" t="n">
-        <v>9.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="371">
@@ -5322,10 +5322,10 @@
         <v>2022.0</v>
       </c>
       <c r="C371" t="n" s="2">
-        <v>44660.0</v>
+        <v>44653.0</v>
       </c>
       <c r="D371" t="n">
-        <v>6.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="372">
@@ -5336,10 +5336,10 @@
         <v>2022.0</v>
       </c>
       <c r="C372" t="n" s="2">
-        <v>44667.0</v>
+        <v>44660.0</v>
       </c>
       <c r="D372" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="373">
@@ -5350,10 +5350,10 @@
         <v>2022.0</v>
       </c>
       <c r="C373" t="n" s="2">
-        <v>44674.0</v>
+        <v>44667.0</v>
       </c>
       <c r="D373" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="374">
@@ -5364,10 +5364,10 @@
         <v>2022.0</v>
       </c>
       <c r="C374" t="n" s="2">
-        <v>44681.0</v>
+        <v>44674.0</v>
       </c>
       <c r="D374" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="375">
@@ -5378,10 +5378,10 @@
         <v>2022.0</v>
       </c>
       <c r="C375" t="n" s="2">
-        <v>44688.0</v>
+        <v>44681.0</v>
       </c>
       <c r="D375" t="n">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="376">
@@ -5392,10 +5392,10 @@
         <v>2022.0</v>
       </c>
       <c r="C376" t="n" s="2">
-        <v>44695.0</v>
+        <v>44688.0</v>
       </c>
       <c r="D376" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="377">
@@ -5406,10 +5406,10 @@
         <v>2022.0</v>
       </c>
       <c r="C377" t="n" s="2">
-        <v>44702.0</v>
+        <v>44695.0</v>
       </c>
       <c r="D377" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="378">
@@ -5420,10 +5420,10 @@
         <v>2022.0</v>
       </c>
       <c r="C378" t="n" s="2">
-        <v>44709.0</v>
+        <v>44702.0</v>
       </c>
       <c r="D378" t="n">
-        <v>8.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="379">
@@ -5434,10 +5434,10 @@
         <v>2022.0</v>
       </c>
       <c r="C379" t="n" s="2">
-        <v>44716.0</v>
+        <v>44709.0</v>
       </c>
       <c r="D379" t="n">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="380">
@@ -5448,10 +5448,10 @@
         <v>2022.0</v>
       </c>
       <c r="C380" t="n" s="2">
-        <v>44723.0</v>
+        <v>44716.0</v>
       </c>
       <c r="D380" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="381">
@@ -5462,10 +5462,10 @@
         <v>2022.0</v>
       </c>
       <c r="C381" t="n" s="2">
-        <v>44730.0</v>
+        <v>44723.0</v>
       </c>
       <c r="D381" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="382">
@@ -5476,7 +5476,7 @@
         <v>2022.0</v>
       </c>
       <c r="C382" t="n" s="2">
-        <v>44737.0</v>
+        <v>44730.0</v>
       </c>
       <c r="D382" t="n">
         <v>4.0</v>
@@ -5490,10 +5490,10 @@
         <v>2022.0</v>
       </c>
       <c r="C383" t="n" s="2">
-        <v>44744.0</v>
+        <v>44737.0</v>
       </c>
       <c r="D383" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="384">
@@ -5504,10 +5504,10 @@
         <v>2022.0</v>
       </c>
       <c r="C384" t="n" s="2">
-        <v>44751.0</v>
+        <v>44744.0</v>
       </c>
       <c r="D384" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="385">
@@ -5518,10 +5518,10 @@
         <v>2022.0</v>
       </c>
       <c r="C385" t="n" s="2">
-        <v>44758.0</v>
+        <v>44751.0</v>
       </c>
       <c r="D385" t="n">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="386">
@@ -5532,10 +5532,10 @@
         <v>2022.0</v>
       </c>
       <c r="C386" t="n" s="2">
-        <v>44765.0</v>
+        <v>44758.0</v>
       </c>
       <c r="D386" t="n">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="387">
@@ -5546,10 +5546,10 @@
         <v>2022.0</v>
       </c>
       <c r="C387" t="n" s="2">
-        <v>44779.0</v>
+        <v>44765.0</v>
       </c>
       <c r="D387" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="388">
@@ -5560,10 +5560,10 @@
         <v>2022.0</v>
       </c>
       <c r="C388" t="n" s="2">
-        <v>44786.0</v>
+        <v>44779.0</v>
       </c>
       <c r="D388" t="n">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="389">
@@ -5574,10 +5574,10 @@
         <v>2022.0</v>
       </c>
       <c r="C389" t="n" s="2">
-        <v>44863.0</v>
+        <v>44786.0</v>
       </c>
       <c r="D389" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="390">
@@ -5588,10 +5588,10 @@
         <v>2022.0</v>
       </c>
       <c r="C390" t="n" s="2">
-        <v>44870.0</v>
+        <v>44863.0</v>
       </c>
       <c r="D390" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="391">
@@ -5602,10 +5602,10 @@
         <v>2022.0</v>
       </c>
       <c r="C391" t="n" s="2">
-        <v>44884.0</v>
+        <v>44870.0</v>
       </c>
       <c r="D391" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="392">
@@ -5616,7 +5616,7 @@
         <v>2022.0</v>
       </c>
       <c r="C392" t="n" s="2">
-        <v>44891.0</v>
+        <v>44884.0</v>
       </c>
       <c r="D392" t="n">
         <v>2.0</v>
@@ -5630,10 +5630,10 @@
         <v>2022.0</v>
       </c>
       <c r="C393" t="n" s="2">
-        <v>44898.0</v>
+        <v>44891.0</v>
       </c>
       <c r="D393" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="394">
@@ -5644,10 +5644,10 @@
         <v>2022.0</v>
       </c>
       <c r="C394" t="n" s="2">
-        <v>44912.0</v>
+        <v>44898.0</v>
       </c>
       <c r="D394" t="n">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="395">
@@ -5658,10 +5658,10 @@
         <v>2022.0</v>
       </c>
       <c r="C395" t="n" s="2">
-        <v>44919.0</v>
+        <v>44912.0</v>
       </c>
       <c r="D395" t="n">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="396">
@@ -5672,10 +5672,10 @@
         <v>2022.0</v>
       </c>
       <c r="C396" t="n" s="2">
-        <v>44926.0</v>
+        <v>44919.0</v>
       </c>
       <c r="D396" t="n">
-        <v>12.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="397">
@@ -5683,13 +5683,13 @@
         <v>7</v>
       </c>
       <c r="B397" t="n">
-        <v>2023.0</v>
+        <v>2022.0</v>
       </c>
       <c r="C397" t="n" s="2">
-        <v>44934.0</v>
+        <v>44926.0</v>
       </c>
       <c r="D397" t="n">
-        <v>4.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="398">
@@ -5700,10 +5700,10 @@
         <v>2023.0</v>
       </c>
       <c r="C398" t="n" s="2">
-        <v>44941.0</v>
+        <v>44934.0</v>
       </c>
       <c r="D398" t="n">
-        <v>16.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="399">
@@ -5714,10 +5714,10 @@
         <v>2023.0</v>
       </c>
       <c r="C399" t="n" s="2">
-        <v>44948.0</v>
+        <v>44941.0</v>
       </c>
       <c r="D399" t="n">
-        <v>5.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="400">
@@ -5728,10 +5728,10 @@
         <v>2023.0</v>
       </c>
       <c r="C400" t="n" s="2">
-        <v>44955.0</v>
+        <v>44948.0</v>
       </c>
       <c r="D400" t="n">
-        <v>19.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="401">
@@ -5742,10 +5742,10 @@
         <v>2023.0</v>
       </c>
       <c r="C401" t="n" s="2">
-        <v>44962.0</v>
+        <v>44955.0</v>
       </c>
       <c r="D401" t="n">
-        <v>22.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="402">
@@ -5756,10 +5756,10 @@
         <v>2023.0</v>
       </c>
       <c r="C402" t="n" s="2">
-        <v>44969.0</v>
+        <v>44962.0</v>
       </c>
       <c r="D402" t="n">
-        <v>9.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="403">
@@ -5770,10 +5770,10 @@
         <v>2023.0</v>
       </c>
       <c r="C403" t="n" s="2">
-        <v>44976.0</v>
+        <v>44969.0</v>
       </c>
       <c r="D403" t="n">
-        <v>22.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="404">
@@ -5784,10 +5784,10 @@
         <v>2023.0</v>
       </c>
       <c r="C404" t="n" s="2">
-        <v>44983.0</v>
+        <v>44976.0</v>
       </c>
       <c r="D404" t="n">
-        <v>29.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="405">
@@ -5798,10 +5798,10 @@
         <v>2023.0</v>
       </c>
       <c r="C405" t="n" s="2">
-        <v>44990.0</v>
+        <v>44983.0</v>
       </c>
       <c r="D405" t="n">
-        <v>5.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="406">
@@ -5812,10 +5812,10 @@
         <v>2023.0</v>
       </c>
       <c r="C406" t="n" s="2">
-        <v>44997.0</v>
+        <v>44990.0</v>
       </c>
       <c r="D406" t="n">
-        <v>24.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="407">
@@ -5826,10 +5826,10 @@
         <v>2023.0</v>
       </c>
       <c r="C407" t="n" s="2">
-        <v>45004.0</v>
+        <v>44997.0</v>
       </c>
       <c r="D407" t="n">
-        <v>8.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="408">
@@ -5840,10 +5840,10 @@
         <v>2023.0</v>
       </c>
       <c r="C408" t="n" s="2">
-        <v>45011.0</v>
+        <v>45004.0</v>
       </c>
       <c r="D408" t="n">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="409">
@@ -5854,10 +5854,10 @@
         <v>2023.0</v>
       </c>
       <c r="C409" t="n" s="2">
-        <v>45018.0</v>
+        <v>45011.0</v>
       </c>
       <c r="D409" t="n">
-        <v>18.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="410">
@@ -5868,10 +5868,10 @@
         <v>2023.0</v>
       </c>
       <c r="C410" t="n" s="2">
-        <v>45025.0</v>
+        <v>45018.0</v>
       </c>
       <c r="D410" t="n">
-        <v>13.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="411">
@@ -5882,10 +5882,10 @@
         <v>2023.0</v>
       </c>
       <c r="C411" t="n" s="2">
-        <v>45032.0</v>
+        <v>45025.0</v>
       </c>
       <c r="D411" t="n">
-        <v>18.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="412">
@@ -5896,10 +5896,10 @@
         <v>2023.0</v>
       </c>
       <c r="C412" t="n" s="2">
-        <v>45039.0</v>
+        <v>45032.0</v>
       </c>
       <c r="D412" t="n">
-        <v>15.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="413">
@@ -5910,10 +5910,10 @@
         <v>2023.0</v>
       </c>
       <c r="C413" t="n" s="2">
-        <v>45046.0</v>
+        <v>45039.0</v>
       </c>
       <c r="D413" t="n">
-        <v>12.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="414">
@@ -5924,10 +5924,10 @@
         <v>2023.0</v>
       </c>
       <c r="C414" t="n" s="2">
-        <v>45053.0</v>
+        <v>45046.0</v>
       </c>
       <c r="D414" t="n">
-        <v>6.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="415">
@@ -5938,10 +5938,10 @@
         <v>2023.0</v>
       </c>
       <c r="C415" t="n" s="2">
-        <v>45060.0</v>
+        <v>45053.0</v>
       </c>
       <c r="D415" t="n">
-        <v>11.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="416">
@@ -5952,10 +5952,10 @@
         <v>2023.0</v>
       </c>
       <c r="C416" t="n" s="2">
-        <v>45067.0</v>
+        <v>45060.0</v>
       </c>
       <c r="D416" t="n">
-        <v>8.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="417">
@@ -5966,7 +5966,7 @@
         <v>2023.0</v>
       </c>
       <c r="C417" t="n" s="2">
-        <v>45074.0</v>
+        <v>45067.0</v>
       </c>
       <c r="D417" t="n">
         <v>8.0</v>
@@ -5980,10 +5980,10 @@
         <v>2023.0</v>
       </c>
       <c r="C418" t="n" s="2">
-        <v>45081.0</v>
+        <v>45074.0</v>
       </c>
       <c r="D418" t="n">
-        <v>5.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="419">
@@ -5994,10 +5994,10 @@
         <v>2023.0</v>
       </c>
       <c r="C419" t="n" s="2">
-        <v>45088.0</v>
+        <v>45081.0</v>
       </c>
       <c r="D419" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="420">
@@ -6008,10 +6008,10 @@
         <v>2023.0</v>
       </c>
       <c r="C420" t="n" s="2">
-        <v>45095.0</v>
+        <v>45088.0</v>
       </c>
       <c r="D420" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="421">
@@ -6022,10 +6022,10 @@
         <v>2023.0</v>
       </c>
       <c r="C421" t="n" s="2">
-        <v>45102.0</v>
+        <v>45095.0</v>
       </c>
       <c r="D421" t="n">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="422">
@@ -6036,10 +6036,10 @@
         <v>2023.0</v>
       </c>
       <c r="C422" t="n" s="2">
-        <v>45109.0</v>
+        <v>45102.0</v>
       </c>
       <c r="D422" t="n">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="423">
@@ -6050,10 +6050,10 @@
         <v>2023.0</v>
       </c>
       <c r="C423" t="n" s="2">
-        <v>45116.0</v>
+        <v>45109.0</v>
       </c>
       <c r="D423" t="n">
-        <v>3.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="424">
@@ -6064,10 +6064,10 @@
         <v>2023.0</v>
       </c>
       <c r="C424" t="n" s="2">
-        <v>45123.0</v>
+        <v>45116.0</v>
       </c>
       <c r="D424" t="n">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="425">
@@ -6078,7 +6078,7 @@
         <v>2023.0</v>
       </c>
       <c r="C425" t="n" s="2">
-        <v>45130.0</v>
+        <v>45123.0</v>
       </c>
       <c r="D425" t="n">
         <v>6.0</v>
@@ -6092,10 +6092,10 @@
         <v>2023.0</v>
       </c>
       <c r="C426" t="n" s="2">
-        <v>45137.0</v>
+        <v>45130.0</v>
       </c>
       <c r="D426" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="427">
@@ -6106,7 +6106,7 @@
         <v>2023.0</v>
       </c>
       <c r="C427" t="n" s="2">
-        <v>45144.0</v>
+        <v>45137.0</v>
       </c>
       <c r="D427" t="n">
         <v>2.0</v>
@@ -6120,7 +6120,7 @@
         <v>2023.0</v>
       </c>
       <c r="C428" t="n" s="2">
-        <v>45151.0</v>
+        <v>45144.0</v>
       </c>
       <c r="D428" t="n">
         <v>2.0</v>
@@ -6134,7 +6134,7 @@
         <v>2023.0</v>
       </c>
       <c r="C429" t="n" s="2">
-        <v>45165.0</v>
+        <v>45151.0</v>
       </c>
       <c r="D429" t="n">
         <v>2.0</v>
@@ -6148,7 +6148,7 @@
         <v>2023.0</v>
       </c>
       <c r="C430" t="n" s="2">
-        <v>45172.0</v>
+        <v>45165.0</v>
       </c>
       <c r="D430" t="n">
         <v>2.0</v>
@@ -6162,10 +6162,10 @@
         <v>2023.0</v>
       </c>
       <c r="C431" t="n" s="2">
-        <v>45179.0</v>
+        <v>45172.0</v>
       </c>
       <c r="D431" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="432">
@@ -6176,7 +6176,7 @@
         <v>2023.0</v>
       </c>
       <c r="C432" t="n" s="2">
-        <v>45186.0</v>
+        <v>45179.0</v>
       </c>
       <c r="D432" t="n">
         <v>1.0</v>
@@ -6190,7 +6190,7 @@
         <v>2023.0</v>
       </c>
       <c r="C433" t="n" s="2">
-        <v>45193.0</v>
+        <v>45186.0</v>
       </c>
       <c r="D433" t="n">
         <v>1.0</v>
@@ -6204,7 +6204,7 @@
         <v>2023.0</v>
       </c>
       <c r="C434" t="n" s="2">
-        <v>45200.0</v>
+        <v>45193.0</v>
       </c>
       <c r="D434" t="n">
         <v>1.0</v>
@@ -6218,7 +6218,7 @@
         <v>2023.0</v>
       </c>
       <c r="C435" t="n" s="2">
-        <v>45207.0</v>
+        <v>45200.0</v>
       </c>
       <c r="D435" t="n">
         <v>1.0</v>
@@ -6232,7 +6232,7 @@
         <v>2023.0</v>
       </c>
       <c r="C436" t="n" s="2">
-        <v>45235.0</v>
+        <v>45207.0</v>
       </c>
       <c r="D436" t="n">
         <v>1.0</v>
@@ -6246,10 +6246,10 @@
         <v>2023.0</v>
       </c>
       <c r="C437" t="n" s="2">
-        <v>45242.0</v>
+        <v>45235.0</v>
       </c>
       <c r="D437" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="438">
@@ -6260,10 +6260,10 @@
         <v>2023.0</v>
       </c>
       <c r="C438" t="n" s="2">
-        <v>45249.0</v>
+        <v>45242.0</v>
       </c>
       <c r="D438" t="n">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="439">
@@ -6274,10 +6274,10 @@
         <v>2023.0</v>
       </c>
       <c r="C439" t="n" s="2">
-        <v>45256.0</v>
+        <v>45249.0</v>
       </c>
       <c r="D439" t="n">
-        <v>9.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="440">
@@ -6288,10 +6288,10 @@
         <v>2023.0</v>
       </c>
       <c r="C440" t="n" s="2">
-        <v>45263.0</v>
+        <v>45256.0</v>
       </c>
       <c r="D440" t="n">
-        <v>12.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="441">
@@ -6302,10 +6302,10 @@
         <v>2023.0</v>
       </c>
       <c r="C441" t="n" s="2">
-        <v>45270.0</v>
+        <v>45263.0</v>
       </c>
       <c r="D441" t="n">
-        <v>6.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="442">
@@ -6316,10 +6316,10 @@
         <v>2023.0</v>
       </c>
       <c r="C442" t="n" s="2">
-        <v>45277.0</v>
+        <v>45270.0</v>
       </c>
       <c r="D442" t="n">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="443">
@@ -6330,7 +6330,7 @@
         <v>2023.0</v>
       </c>
       <c r="C443" t="n" s="2">
-        <v>45284.0</v>
+        <v>45277.0</v>
       </c>
       <c r="D443" t="n">
         <v>7.0</v>
@@ -6344,10 +6344,10 @@
         <v>2023.0</v>
       </c>
       <c r="C444" t="n" s="2">
-        <v>45291.0</v>
+        <v>45284.0</v>
       </c>
       <c r="D444" t="n">
-        <v>13.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="445">
@@ -6355,13 +6355,13 @@
         <v>7</v>
       </c>
       <c r="B445" t="n">
-        <v>2024.0</v>
+        <v>2023.0</v>
       </c>
       <c r="C445" t="n" s="2">
-        <v>45299.0</v>
+        <v>45291.0</v>
       </c>
       <c r="D445" t="n">
-        <v>6.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="446">
@@ -6372,10 +6372,10 @@
         <v>2024.0</v>
       </c>
       <c r="C446" t="n" s="2">
-        <v>45306.0</v>
+        <v>45299.0</v>
       </c>
       <c r="D446" t="n">
-        <v>11.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="447">
@@ -6386,10 +6386,10 @@
         <v>2024.0</v>
       </c>
       <c r="C447" t="n" s="2">
-        <v>45313.0</v>
+        <v>45306.0</v>
       </c>
       <c r="D447" t="n">
-        <v>5.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="448">
@@ -6400,10 +6400,10 @@
         <v>2024.0</v>
       </c>
       <c r="C448" t="n" s="2">
-        <v>45320.0</v>
+        <v>45313.0</v>
       </c>
       <c r="D448" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="449">
@@ -6414,10 +6414,10 @@
         <v>2024.0</v>
       </c>
       <c r="C449" t="n" s="2">
-        <v>45327.0</v>
+        <v>45320.0</v>
       </c>
       <c r="D449" t="n">
-        <v>9.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="450">
@@ -6428,10 +6428,10 @@
         <v>2024.0</v>
       </c>
       <c r="C450" t="n" s="2">
-        <v>45334.0</v>
+        <v>45327.0</v>
       </c>
       <c r="D450" t="n">
-        <v>3.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="451">
@@ -6442,10 +6442,10 @@
         <v>2024.0</v>
       </c>
       <c r="C451" t="n" s="2">
-        <v>45341.0</v>
+        <v>45334.0</v>
       </c>
       <c r="D451" t="n">
-        <v>21.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="452">
@@ -6456,10 +6456,10 @@
         <v>2024.0</v>
       </c>
       <c r="C452" t="n" s="2">
-        <v>45348.0</v>
+        <v>45341.0</v>
       </c>
       <c r="D452" t="n">
-        <v>1.0</v>
+        <v>21.0</v>
       </c>
     </row>
     <row r="453">
@@ -6470,10 +6470,10 @@
         <v>2024.0</v>
       </c>
       <c r="C453" t="n" s="2">
-        <v>45355.0</v>
+        <v>45348.0</v>
       </c>
       <c r="D453" t="n">
-        <v>9.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="454">
@@ -6484,10 +6484,10 @@
         <v>2024.0</v>
       </c>
       <c r="C454" t="n" s="2">
-        <v>45362.0</v>
+        <v>45355.0</v>
       </c>
       <c r="D454" t="n">
-        <v>4.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="455">
@@ -6498,10 +6498,10 @@
         <v>2024.0</v>
       </c>
       <c r="C455" t="n" s="2">
-        <v>45369.0</v>
+        <v>45362.0</v>
       </c>
       <c r="D455" t="n">
-        <v>14.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="456">
@@ -6512,10 +6512,10 @@
         <v>2024.0</v>
       </c>
       <c r="C456" t="n" s="2">
-        <v>45376.0</v>
+        <v>45369.0</v>
       </c>
       <c r="D456" t="n">
-        <v>4.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="457">
@@ -6526,10 +6526,10 @@
         <v>2024.0</v>
       </c>
       <c r="C457" t="n" s="2">
-        <v>45383.0</v>
+        <v>45376.0</v>
       </c>
       <c r="D457" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="458">
@@ -6540,10 +6540,10 @@
         <v>2024.0</v>
       </c>
       <c r="C458" t="n" s="2">
-        <v>45390.0</v>
+        <v>45383.0</v>
       </c>
       <c r="D458" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="459">
@@ -6554,7 +6554,7 @@
         <v>2024.0</v>
       </c>
       <c r="C459" t="n" s="2">
-        <v>45397.0</v>
+        <v>45390.0</v>
       </c>
       <c r="D459" t="n">
         <v>1.0</v>
@@ -6568,10 +6568,10 @@
         <v>2024.0</v>
       </c>
       <c r="C460" t="n" s="2">
-        <v>45404.0</v>
+        <v>45397.0</v>
       </c>
       <c r="D460" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="461">
@@ -6582,10 +6582,10 @@
         <v>2024.0</v>
       </c>
       <c r="C461" t="n" s="2">
-        <v>45411.0</v>
+        <v>45404.0</v>
       </c>
       <c r="D461" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="462">
@@ -6596,10 +6596,10 @@
         <v>2024.0</v>
       </c>
       <c r="C462" t="n" s="2">
-        <v>45439.0</v>
+        <v>45411.0</v>
       </c>
       <c r="D462" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="463">
@@ -6610,10 +6610,10 @@
         <v>2024.0</v>
       </c>
       <c r="C463" t="n" s="2">
-        <v>45446.0</v>
+        <v>45439.0</v>
       </c>
       <c r="D463" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="464">
@@ -6624,7 +6624,7 @@
         <v>2024.0</v>
       </c>
       <c r="C464" t="n" s="2">
-        <v>45460.0</v>
+        <v>45446.0</v>
       </c>
       <c r="D464" t="n">
         <v>1.0</v>
@@ -6638,7 +6638,7 @@
         <v>2024.0</v>
       </c>
       <c r="C465" t="n" s="2">
-        <v>45481.0</v>
+        <v>45460.0</v>
       </c>
       <c r="D465" t="n">
         <v>1.0</v>
@@ -6652,7 +6652,7 @@
         <v>2024.0</v>
       </c>
       <c r="C466" t="n" s="2">
-        <v>45516.0</v>
+        <v>45481.0</v>
       </c>
       <c r="D466" t="n">
         <v>1.0</v>
@@ -6666,7 +6666,7 @@
         <v>2024.0</v>
       </c>
       <c r="C467" t="n" s="2">
-        <v>45551.0</v>
+        <v>45516.0</v>
       </c>
       <c r="D467" t="n">
         <v>1.0</v>
@@ -6680,7 +6680,7 @@
         <v>2024.0</v>
       </c>
       <c r="C468" t="n" s="2">
-        <v>45579.0</v>
+        <v>45551.0</v>
       </c>
       <c r="D468" t="n">
         <v>1.0</v>
@@ -6694,7 +6694,7 @@
         <v>2024.0</v>
       </c>
       <c r="C469" t="n" s="2">
-        <v>45614.0</v>
+        <v>45579.0</v>
       </c>
       <c r="D469" t="n">
         <v>1.0</v>
@@ -6708,10 +6708,10 @@
         <v>2024.0</v>
       </c>
       <c r="C470" t="n" s="2">
-        <v>45635.0</v>
+        <v>45614.0</v>
       </c>
       <c r="D470" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="471">
@@ -6722,10 +6722,10 @@
         <v>2024.0</v>
       </c>
       <c r="C471" t="n" s="2">
-        <v>45642.0</v>
+        <v>45635.0</v>
       </c>
       <c r="D471" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="472">
@@ -6736,10 +6736,10 @@
         <v>2024.0</v>
       </c>
       <c r="C472" t="n" s="2">
-        <v>45649.0</v>
+        <v>45642.0</v>
       </c>
       <c r="D472" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="473">
@@ -6750,10 +6750,10 @@
         <v>2024.0</v>
       </c>
       <c r="C473" t="n" s="2">
-        <v>45656.0</v>
+        <v>45649.0</v>
       </c>
       <c r="D473" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="474">
@@ -6761,13 +6761,13 @@
         <v>7</v>
       </c>
       <c r="B474" t="n">
-        <v>2025.0</v>
+        <v>2024.0</v>
       </c>
       <c r="C474" t="n" s="2">
-        <v>45665.0</v>
+        <v>45656.0</v>
       </c>
       <c r="D474" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="475">
@@ -6778,10 +6778,10 @@
         <v>2025.0</v>
       </c>
       <c r="C475" t="n" s="2">
-        <v>45672.0</v>
+        <v>45665.0</v>
       </c>
       <c r="D475" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="476">
@@ -6792,7 +6792,7 @@
         <v>2025.0</v>
       </c>
       <c r="C476" t="n" s="2">
-        <v>45686.0</v>
+        <v>45672.0</v>
       </c>
       <c r="D476" t="n">
         <v>2.0</v>
@@ -6806,10 +6806,10 @@
         <v>2025.0</v>
       </c>
       <c r="C477" t="n" s="2">
-        <v>45693.0</v>
+        <v>45686.0</v>
       </c>
       <c r="D477" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="478">
@@ -6820,10 +6820,10 @@
         <v>2025.0</v>
       </c>
       <c r="C478" t="n" s="2">
-        <v>45700.0</v>
+        <v>45693.0</v>
       </c>
       <c r="D478" t="n">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="479">
@@ -6834,10 +6834,10 @@
         <v>2025.0</v>
       </c>
       <c r="C479" t="n" s="2">
-        <v>45707.0</v>
+        <v>45700.0</v>
       </c>
       <c r="D479" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="480">
@@ -6848,10 +6848,10 @@
         <v>2025.0</v>
       </c>
       <c r="C480" t="n" s="2">
-        <v>45714.0</v>
+        <v>45707.0</v>
       </c>
       <c r="D480" t="n">
-        <v>8.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="481">
@@ -6862,10 +6862,10 @@
         <v>2025.0</v>
       </c>
       <c r="C481" t="n" s="2">
-        <v>45721.0</v>
+        <v>45714.0</v>
       </c>
       <c r="D481" t="n">
-        <v>11.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="482">
@@ -6876,10 +6876,10 @@
         <v>2025.0</v>
       </c>
       <c r="C482" t="n" s="2">
-        <v>45728.0</v>
+        <v>45721.0</v>
       </c>
       <c r="D482" t="n">
-        <v>6.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="483">
@@ -6890,10 +6890,10 @@
         <v>2025.0</v>
       </c>
       <c r="C483" t="n" s="2">
-        <v>45735.0</v>
+        <v>45728.0</v>
       </c>
       <c r="D483" t="n">
-        <v>19.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="484">
@@ -6904,10 +6904,10 @@
         <v>2025.0</v>
       </c>
       <c r="C484" t="n" s="2">
-        <v>45742.0</v>
+        <v>45735.0</v>
       </c>
       <c r="D484" t="n">
-        <v>17.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="485">
@@ -6918,10 +6918,10 @@
         <v>2025.0</v>
       </c>
       <c r="C485" t="n" s="2">
-        <v>45749.0</v>
+        <v>45742.0</v>
       </c>
       <c r="D485" t="n">
-        <v>5.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="486">
@@ -6932,10 +6932,10 @@
         <v>2025.0</v>
       </c>
       <c r="C486" t="n" s="2">
-        <v>45756.0</v>
+        <v>45749.0</v>
       </c>
       <c r="D486" t="n">
-        <v>9.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="487">
@@ -6946,10 +6946,10 @@
         <v>2025.0</v>
       </c>
       <c r="C487" t="n" s="2">
-        <v>45763.0</v>
+        <v>45756.0</v>
       </c>
       <c r="D487" t="n">
-        <v>1.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="488">
@@ -6960,7 +6960,7 @@
         <v>2025.0</v>
       </c>
       <c r="C488" t="n" s="2">
-        <v>45770.0</v>
+        <v>45763.0</v>
       </c>
       <c r="D488" t="n">
         <v>1.0</v>
@@ -6974,10 +6974,10 @@
         <v>2025.0</v>
       </c>
       <c r="C489" t="n" s="2">
-        <v>45784.0</v>
+        <v>45770.0</v>
       </c>
       <c r="D489" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="490">
@@ -6988,10 +6988,10 @@
         <v>2025.0</v>
       </c>
       <c r="C490" t="n" s="2">
-        <v>45791.0</v>
+        <v>45784.0</v>
       </c>
       <c r="D490" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="491">
@@ -7002,10 +7002,10 @@
         <v>2025.0</v>
       </c>
       <c r="C491" t="n" s="2">
-        <v>45805.0</v>
+        <v>45791.0</v>
       </c>
       <c r="D491" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="492">
@@ -7016,10 +7016,10 @@
         <v>2025.0</v>
       </c>
       <c r="C492" t="n" s="2">
-        <v>45826.0</v>
+        <v>45805.0</v>
       </c>
       <c r="D492" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="493">
@@ -7030,7 +7030,7 @@
         <v>2025.0</v>
       </c>
       <c r="C493" t="n" s="2">
-        <v>45861.0</v>
+        <v>45826.0</v>
       </c>
       <c r="D493" t="n">
         <v>2.0</v>
@@ -7044,10 +7044,10 @@
         <v>2025.0</v>
       </c>
       <c r="C494" t="n" s="2">
-        <v>45868.0</v>
+        <v>45861.0</v>
       </c>
       <c r="D494" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="495">
@@ -7058,7 +7058,7 @@
         <v>2025.0</v>
       </c>
       <c r="C495" t="n" s="2">
-        <v>45889.0</v>
+        <v>45868.0</v>
       </c>
       <c r="D495" t="n">
         <v>1.0</v>
@@ -7072,7 +7072,7 @@
         <v>2025.0</v>
       </c>
       <c r="C496" t="n" s="2">
-        <v>45924.0</v>
+        <v>45889.0</v>
       </c>
       <c r="D496" t="n">
         <v>1.0</v>
@@ -7086,7 +7086,7 @@
         <v>2025.0</v>
       </c>
       <c r="C497" t="n" s="2">
-        <v>45945.0</v>
+        <v>45924.0</v>
       </c>
       <c r="D497" t="n">
         <v>1.0</v>
@@ -7100,10 +7100,10 @@
         <v>2025.0</v>
       </c>
       <c r="C498" t="n" s="2">
-        <v>45959.0</v>
+        <v>45945.0</v>
       </c>
       <c r="D498" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="499">
@@ -7114,7 +7114,7 @@
         <v>2025.0</v>
       </c>
       <c r="C499" t="n" s="2">
-        <v>46001.0</v>
+        <v>45959.0</v>
       </c>
       <c r="D499" t="n">
         <v>2.0</v>
@@ -7128,10 +7128,10 @@
         <v>2025.0</v>
       </c>
       <c r="C500" t="n" s="2">
-        <v>46008.0</v>
+        <v>46001.0</v>
       </c>
       <c r="D500" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="501">
@@ -7142,7 +7142,7 @@
         <v>2025.0</v>
       </c>
       <c r="C501" t="n" s="2">
-        <v>46022.0</v>
+        <v>46008.0</v>
       </c>
       <c r="D501" t="n">
         <v>1.0</v>
@@ -7153,10 +7153,10 @@
         <v>7</v>
       </c>
       <c r="B502" t="n">
-        <v>2026.0</v>
+        <v>2025.0</v>
       </c>
       <c r="C502" t="n" s="2">
-        <v>46030.0</v>
+        <v>46022.0</v>
       </c>
       <c r="D502" t="n">
         <v>1.0</v>
@@ -7170,7 +7170,7 @@
         <v>2026.0</v>
       </c>
       <c r="C503" t="n" s="2">
-        <v>46051.0</v>
+        <v>46030.0</v>
       </c>
       <c r="D503" t="n">
         <v>1.0</v>
@@ -7184,7 +7184,7 @@
         <v>2026.0</v>
       </c>
       <c r="C504" t="n" s="2">
-        <v>46058.0</v>
+        <v>46051.0</v>
       </c>
       <c r="D504" t="n">
         <v>1.0</v>
@@ -7198,24 +7198,24 @@
         <v>2026.0</v>
       </c>
       <c r="C505" t="n" s="2">
-        <v>46065.0</v>
+        <v>46058.0</v>
       </c>
       <c r="D505" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B506" t="n">
-        <v>2024.0</v>
+        <v>2026.0</v>
       </c>
       <c r="C506" t="n" s="2">
-        <v>45495.0</v>
+        <v>46065.0</v>
       </c>
       <c r="D506" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="507">
@@ -7226,10 +7226,10 @@
         <v>2024.0</v>
       </c>
       <c r="C507" t="n" s="2">
-        <v>45502.0</v>
+        <v>45495.0</v>
       </c>
       <c r="D507" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="508">
@@ -7237,13 +7237,13 @@
         <v>8</v>
       </c>
       <c r="B508" t="n">
-        <v>2025.0</v>
+        <v>2024.0</v>
       </c>
       <c r="C508" t="n" s="2">
-        <v>45665.0</v>
+        <v>45502.0</v>
       </c>
       <c r="D508" t="n">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="509">
@@ -7254,10 +7254,10 @@
         <v>2025.0</v>
       </c>
       <c r="C509" t="n" s="2">
-        <v>45672.0</v>
+        <v>45665.0</v>
       </c>
       <c r="D509" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="510">
@@ -7268,10 +7268,10 @@
         <v>2025.0</v>
       </c>
       <c r="C510" t="n" s="2">
-        <v>45679.0</v>
+        <v>45672.0</v>
       </c>
       <c r="D510" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="511">
@@ -7282,10 +7282,10 @@
         <v>2025.0</v>
       </c>
       <c r="C511" t="n" s="2">
-        <v>45686.0</v>
+        <v>45679.0</v>
       </c>
       <c r="D511" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="512">
@@ -7296,10 +7296,10 @@
         <v>2025.0</v>
       </c>
       <c r="C512" t="n" s="2">
-        <v>45693.0</v>
+        <v>45686.0</v>
       </c>
       <c r="D512" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="513">
@@ -7310,10 +7310,10 @@
         <v>2025.0</v>
       </c>
       <c r="C513" t="n" s="2">
-        <v>45700.0</v>
+        <v>45693.0</v>
       </c>
       <c r="D513" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="514">
@@ -7324,10 +7324,10 @@
         <v>2025.0</v>
       </c>
       <c r="C514" t="n" s="2">
-        <v>45707.0</v>
+        <v>45700.0</v>
       </c>
       <c r="D514" t="n">
-        <v>7.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="515">
@@ -7338,10 +7338,10 @@
         <v>2025.0</v>
       </c>
       <c r="C515" t="n" s="2">
-        <v>45714.0</v>
+        <v>45707.0</v>
       </c>
       <c r="D515" t="n">
-        <v>3.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="516">
@@ -7352,10 +7352,10 @@
         <v>2025.0</v>
       </c>
       <c r="C516" t="n" s="2">
-        <v>45721.0</v>
+        <v>45714.0</v>
       </c>
       <c r="D516" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="517">
@@ -7366,10 +7366,10 @@
         <v>2025.0</v>
       </c>
       <c r="C517" t="n" s="2">
-        <v>45728.0</v>
+        <v>45721.0</v>
       </c>
       <c r="D517" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="518">
@@ -7380,7 +7380,7 @@
         <v>2025.0</v>
       </c>
       <c r="C518" t="n" s="2">
-        <v>45742.0</v>
+        <v>45728.0</v>
       </c>
       <c r="D518" t="n">
         <v>1.0</v>
@@ -7394,7 +7394,7 @@
         <v>2025.0</v>
       </c>
       <c r="C519" t="n" s="2">
-        <v>45749.0</v>
+        <v>45742.0</v>
       </c>
       <c r="D519" t="n">
         <v>1.0</v>
@@ -7408,7 +7408,7 @@
         <v>2025.0</v>
       </c>
       <c r="C520" t="n" s="2">
-        <v>45763.0</v>
+        <v>45749.0</v>
       </c>
       <c r="D520" t="n">
         <v>1.0</v>
@@ -7422,10 +7422,10 @@
         <v>2025.0</v>
       </c>
       <c r="C521" t="n" s="2">
-        <v>45777.0</v>
+        <v>45763.0</v>
       </c>
       <c r="D521" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="522">
@@ -7436,10 +7436,10 @@
         <v>2025.0</v>
       </c>
       <c r="C522" t="n" s="2">
-        <v>45784.0</v>
+        <v>45777.0</v>
       </c>
       <c r="D522" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="523">
@@ -7450,7 +7450,7 @@
         <v>2025.0</v>
       </c>
       <c r="C523" t="n" s="2">
-        <v>45798.0</v>
+        <v>45784.0</v>
       </c>
       <c r="D523" t="n">
         <v>1.0</v>
@@ -7464,7 +7464,7 @@
         <v>2025.0</v>
       </c>
       <c r="C524" t="n" s="2">
-        <v>45805.0</v>
+        <v>45798.0</v>
       </c>
       <c r="D524" t="n">
         <v>1.0</v>
@@ -7478,10 +7478,10 @@
         <v>2025.0</v>
       </c>
       <c r="C525" t="n" s="2">
-        <v>45812.0</v>
+        <v>45805.0</v>
       </c>
       <c r="D525" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="526">
@@ -7492,7 +7492,7 @@
         <v>2025.0</v>
       </c>
       <c r="C526" t="n" s="2">
-        <v>45819.0</v>
+        <v>45812.0</v>
       </c>
       <c r="D526" t="n">
         <v>2.0</v>
@@ -7506,7 +7506,7 @@
         <v>2025.0</v>
       </c>
       <c r="C527" t="n" s="2">
-        <v>45833.0</v>
+        <v>45819.0</v>
       </c>
       <c r="D527" t="n">
         <v>2.0</v>
@@ -7520,10 +7520,10 @@
         <v>2025.0</v>
       </c>
       <c r="C528" t="n" s="2">
-        <v>45847.0</v>
+        <v>45833.0</v>
       </c>
       <c r="D528" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="529">
@@ -7534,10 +7534,10 @@
         <v>2025.0</v>
       </c>
       <c r="C529" t="n" s="2">
-        <v>45854.0</v>
+        <v>45847.0</v>
       </c>
       <c r="D529" t="n">
-        <v>8.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="530">
@@ -7548,10 +7548,10 @@
         <v>2025.0</v>
       </c>
       <c r="C530" t="n" s="2">
-        <v>45861.0</v>
+        <v>45854.0</v>
       </c>
       <c r="D530" t="n">
-        <v>12.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="531">
@@ -7562,10 +7562,10 @@
         <v>2025.0</v>
       </c>
       <c r="C531" t="n" s="2">
-        <v>45868.0</v>
+        <v>45861.0</v>
       </c>
       <c r="D531" t="n">
-        <v>6.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="532">
@@ -7576,10 +7576,10 @@
         <v>2025.0</v>
       </c>
       <c r="C532" t="n" s="2">
-        <v>45875.0</v>
+        <v>45868.0</v>
       </c>
       <c r="D532" t="n">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="533">
@@ -7590,7 +7590,7 @@
         <v>2025.0</v>
       </c>
       <c r="C533" t="n" s="2">
-        <v>45896.0</v>
+        <v>45875.0</v>
       </c>
       <c r="D533" t="n">
         <v>1.0</v>
@@ -7604,7 +7604,7 @@
         <v>2025.0</v>
       </c>
       <c r="C534" t="n" s="2">
-        <v>45903.0</v>
+        <v>45896.0</v>
       </c>
       <c r="D534" t="n">
         <v>1.0</v>
@@ -7618,7 +7618,7 @@
         <v>2025.0</v>
       </c>
       <c r="C535" t="n" s="2">
-        <v>45931.0</v>
+        <v>45903.0</v>
       </c>
       <c r="D535" t="n">
         <v>1.0</v>
@@ -7632,10 +7632,10 @@
         <v>2025.0</v>
       </c>
       <c r="C536" t="n" s="2">
-        <v>45938.0</v>
+        <v>45931.0</v>
       </c>
       <c r="D536" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="537">
@@ -7646,10 +7646,10 @@
         <v>2025.0</v>
       </c>
       <c r="C537" t="n" s="2">
-        <v>45945.0</v>
+        <v>45938.0</v>
       </c>
       <c r="D537" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="538">
@@ -7660,7 +7660,7 @@
         <v>2025.0</v>
       </c>
       <c r="C538" t="n" s="2">
-        <v>45966.0</v>
+        <v>45945.0</v>
       </c>
       <c r="D538" t="n">
         <v>2.0</v>
@@ -7674,10 +7674,10 @@
         <v>2025.0</v>
       </c>
       <c r="C539" t="n" s="2">
-        <v>45973.0</v>
+        <v>45966.0</v>
       </c>
       <c r="D539" t="n">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="540">
@@ -7688,10 +7688,10 @@
         <v>2025.0</v>
       </c>
       <c r="C540" t="n" s="2">
-        <v>45980.0</v>
+        <v>45973.0</v>
       </c>
       <c r="D540" t="n">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="541">
@@ -7702,10 +7702,10 @@
         <v>2025.0</v>
       </c>
       <c r="C541" t="n" s="2">
-        <v>45987.0</v>
+        <v>45980.0</v>
       </c>
       <c r="D541" t="n">
-        <v>20.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="542">
@@ -7716,10 +7716,10 @@
         <v>2025.0</v>
       </c>
       <c r="C542" t="n" s="2">
-        <v>45994.0</v>
+        <v>45987.0</v>
       </c>
       <c r="D542" t="n">
-        <v>5.0</v>
+        <v>20.0</v>
       </c>
     </row>
     <row r="543">
@@ -7730,10 +7730,10 @@
         <v>2025.0</v>
       </c>
       <c r="C543" t="n" s="2">
-        <v>46001.0</v>
+        <v>45994.0</v>
       </c>
       <c r="D543" t="n">
-        <v>8.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="544">
@@ -7744,10 +7744,10 @@
         <v>2025.0</v>
       </c>
       <c r="C544" t="n" s="2">
-        <v>46008.0</v>
+        <v>46001.0</v>
       </c>
       <c r="D544" t="n">
-        <v>24.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="545">
@@ -7758,10 +7758,10 @@
         <v>2025.0</v>
       </c>
       <c r="C545" t="n" s="2">
-        <v>46015.0</v>
+        <v>46008.0</v>
       </c>
       <c r="D545" t="n">
-        <v>13.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="546">
@@ -7772,10 +7772,10 @@
         <v>2025.0</v>
       </c>
       <c r="C546" t="n" s="2">
-        <v>46022.0</v>
+        <v>46015.0</v>
       </c>
       <c r="D546" t="n">
-        <v>7.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="547">
@@ -7786,10 +7786,10 @@
         <v>2025.0</v>
       </c>
       <c r="C547" t="n" s="2">
-        <v>46029.0</v>
+        <v>46022.0</v>
       </c>
       <c r="D547" t="n">
-        <v>3.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="548">
@@ -7797,13 +7797,13 @@
         <v>8</v>
       </c>
       <c r="B548" t="n">
-        <v>2026.0</v>
+        <v>2025.0</v>
       </c>
       <c r="C548" t="n" s="2">
-        <v>46030.0</v>
+        <v>46029.0</v>
       </c>
       <c r="D548" t="n">
-        <v>24.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="549">
@@ -7814,10 +7814,10 @@
         <v>2026.0</v>
       </c>
       <c r="C549" t="n" s="2">
-        <v>46037.0</v>
+        <v>46030.0</v>
       </c>
       <c r="D549" t="n">
-        <v>22.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="550">
@@ -7828,10 +7828,10 @@
         <v>2026.0</v>
       </c>
       <c r="C550" t="n" s="2">
-        <v>46044.0</v>
+        <v>46037.0</v>
       </c>
       <c r="D550" t="n">
-        <v>27.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="551">
@@ -7842,10 +7842,10 @@
         <v>2026.0</v>
       </c>
       <c r="C551" t="n" s="2">
-        <v>46051.0</v>
+        <v>46044.0</v>
       </c>
       <c r="D551" t="n">
-        <v>18.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="552">
@@ -7856,10 +7856,10 @@
         <v>2026.0</v>
       </c>
       <c r="C552" t="n" s="2">
-        <v>46058.0</v>
+        <v>46051.0</v>
       </c>
       <c r="D552" t="n">
-        <v>25.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="553">
@@ -7870,10 +7870,10 @@
         <v>2026.0</v>
       </c>
       <c r="C553" t="n" s="2">
-        <v>46065.0</v>
+        <v>46058.0</v>
       </c>
       <c r="D553" t="n">
-        <v>22.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="554">
@@ -7884,10 +7884,10 @@
         <v>2026.0</v>
       </c>
       <c r="C554" t="n" s="2">
-        <v>46072.0</v>
+        <v>46065.0</v>
       </c>
       <c r="D554" t="n">
-        <v>13.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="555">
@@ -7898,10 +7898,10 @@
         <v>2026.0</v>
       </c>
       <c r="C555" t="n" s="2">
-        <v>46079.0</v>
+        <v>46072.0</v>
       </c>
       <c r="D555" t="n">
-        <v>24.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="556">
@@ -7912,10 +7912,10 @@
         <v>2026.0</v>
       </c>
       <c r="C556" t="n" s="2">
-        <v>46086.0</v>
+        <v>46079.0</v>
       </c>
       <c r="D556" t="n">
-        <v>26.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="557">
@@ -7926,10 +7926,10 @@
         <v>2026.0</v>
       </c>
       <c r="C557" t="n" s="2">
-        <v>46093.0</v>
+        <v>46086.0</v>
       </c>
       <c r="D557" t="n">
-        <v>32.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="558">
@@ -7940,10 +7940,10 @@
         <v>2026.0</v>
       </c>
       <c r="C558" t="n" s="2">
-        <v>46100.0</v>
+        <v>46093.0</v>
       </c>
       <c r="D558" t="n">
-        <v>1.0</v>
+        <v>33.0</v>
       </c>
     </row>
   </sheetData>
@@ -7969,7 +7969,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="n">
-        <v>49.0</v>
+        <v>45.0</v>
       </c>
     </row>
     <row r="3">
@@ -7985,7 +7985,7 @@
         <v>12</v>
       </c>
       <c r="B4" t="n">
-        <v>1133.0</v>
+        <v>1136.0</v>
       </c>
     </row>
     <row r="5">
@@ -7993,7 +7993,7 @@
         <v>13</v>
       </c>
       <c r="B5" t="n">
-        <v>2008.0</v>
+        <v>2010.0</v>
       </c>
     </row>
   </sheetData>
@@ -8102,7 +8102,7 @@
         <v>22</v>
       </c>
       <c r="C9" t="n">
-        <v>322.0</v>
+        <v>323.0</v>
       </c>
     </row>
     <row r="10">
@@ -8124,7 +8124,7 @@
         <v>19</v>
       </c>
       <c r="C11" t="n">
-        <v>35.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="12">
@@ -8157,7 +8157,7 @@
         <v>19</v>
       </c>
       <c r="C14" t="n">
-        <v>340.0</v>
+        <v>343.0</v>
       </c>
     </row>
     <row r="15">
@@ -8168,7 +8168,7 @@
         <v>21</v>
       </c>
       <c r="C15" t="n">
-        <v>353.0</v>
+        <v>354.0</v>
       </c>
     </row>
     <row r="16">

--- a/Download/Focus_Positivi_ZR.xlsx
+++ b/Download/Focus_Positivi_ZR.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="602" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="603" uniqueCount="23">
   <si>
     <t>NOME_REGIONE</t>
   </si>
@@ -1531,7 +1531,7 @@
         <v>46100.0</v>
       </c>
       <c r="D100" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="101">
@@ -4107,7 +4107,7 @@
         <v>46100.0</v>
       </c>
       <c r="D284" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="285">
@@ -7944,6 +7944,20 @@
       </c>
       <c r="D558" t="n">
         <v>33.0</v>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="s">
+        <v>8</v>
+      </c>
+      <c r="B559" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C559" t="n" s="2">
+        <v>46100.0</v>
+      </c>
+      <c r="D559" t="n">
+        <v>15.0</v>
       </c>
     </row>
   </sheetData>
@@ -7969,7 +7983,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="n">
-        <v>45.0</v>
+        <v>49.0</v>
       </c>
     </row>
     <row r="3">
@@ -7977,7 +7991,7 @@
         <v>11</v>
       </c>
       <c r="B3" t="n">
-        <v>180.0</v>
+        <v>181.0</v>
       </c>
     </row>
     <row r="4">
@@ -7985,7 +7999,7 @@
         <v>12</v>
       </c>
       <c r="B4" t="n">
-        <v>1136.0</v>
+        <v>1141.0</v>
       </c>
     </row>
     <row r="5">
@@ -7993,7 +8007,7 @@
         <v>13</v>
       </c>
       <c r="B5" t="n">
-        <v>2010.0</v>
+        <v>2018.0</v>
       </c>
     </row>
   </sheetData>
@@ -8025,7 +8039,7 @@
         <v>21</v>
       </c>
       <c r="C2" t="n">
-        <v>181.0</v>
+        <v>182.0</v>
       </c>
     </row>
     <row r="3">
@@ -8036,7 +8050,7 @@
         <v>22</v>
       </c>
       <c r="C3" t="n">
-        <v>165.0</v>
+        <v>168.0</v>
       </c>
     </row>
     <row r="4">
@@ -8047,7 +8061,7 @@
         <v>19</v>
       </c>
       <c r="C4" t="n">
-        <v>129.0</v>
+        <v>131.0</v>
       </c>
     </row>
     <row r="5">
@@ -8058,7 +8072,7 @@
         <v>21</v>
       </c>
       <c r="C5" t="n">
-        <v>402.0</v>
+        <v>403.0</v>
       </c>
     </row>
     <row r="6">
@@ -8069,7 +8083,7 @@
         <v>22</v>
       </c>
       <c r="C6" t="n">
-        <v>287.0</v>
+        <v>288.0</v>
       </c>
     </row>
     <row r="7">
@@ -8124,7 +8138,7 @@
         <v>19</v>
       </c>
       <c r="C11" t="n">
-        <v>31.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="12">
@@ -8157,7 +8171,7 @@
         <v>19</v>
       </c>
       <c r="C14" t="n">
-        <v>343.0</v>
+        <v>348.0</v>
       </c>
     </row>
     <row r="15">
@@ -8168,7 +8182,7 @@
         <v>21</v>
       </c>
       <c r="C15" t="n">
-        <v>354.0</v>
+        <v>355.0</v>
       </c>
     </row>
     <row r="16">

--- a/Download/Focus_Positivi_ZR.xlsx
+++ b/Download/Focus_Positivi_ZR.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="603" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="604" uniqueCount="23">
   <si>
     <t>NOME_REGIONE</t>
   </si>
@@ -7960,6 +7960,20 @@
         <v>15.0</v>
       </c>
     </row>
+    <row r="560">
+      <c r="A560" t="s">
+        <v>8</v>
+      </c>
+      <c r="B560" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C560" t="n" s="2">
+        <v>46107.0</v>
+      </c>
+      <c r="D560" t="n">
+        <v>9.0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
@@ -7983,7 +7997,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="n">
-        <v>49.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="3">
@@ -7999,7 +8013,7 @@
         <v>12</v>
       </c>
       <c r="B4" t="n">
-        <v>1141.0</v>
+        <v>1144.0</v>
       </c>
     </row>
     <row r="5">
@@ -8007,7 +8021,7 @@
         <v>13</v>
       </c>
       <c r="B5" t="n">
-        <v>2018.0</v>
+        <v>2019.0</v>
       </c>
     </row>
   </sheetData>
@@ -8072,7 +8086,7 @@
         <v>21</v>
       </c>
       <c r="C5" t="n">
-        <v>403.0</v>
+        <v>404.0</v>
       </c>
     </row>
     <row r="6">
@@ -8083,7 +8097,7 @@
         <v>22</v>
       </c>
       <c r="C6" t="n">
-        <v>288.0</v>
+        <v>289.0</v>
       </c>
     </row>
     <row r="7">
@@ -8138,7 +8152,7 @@
         <v>19</v>
       </c>
       <c r="C11" t="n">
-        <v>35.0</v>
+        <v>40.0</v>
       </c>
     </row>
     <row r="12">
@@ -8171,7 +8185,7 @@
         <v>19</v>
       </c>
       <c r="C14" t="n">
-        <v>348.0</v>
+        <v>349.0</v>
       </c>
     </row>
     <row r="15">
@@ -8193,7 +8207,7 @@
         <v>22</v>
       </c>
       <c r="C16" t="n">
-        <v>338.0</v>
+        <v>339.0</v>
       </c>
     </row>
     <row r="17">

--- a/Download/Focus_Positivi_ZR.xlsx
+++ b/Download/Focus_Positivi_ZR.xlsx
@@ -4107,7 +4107,7 @@
         <v>46100.0</v>
       </c>
       <c r="D284" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="285">
@@ -7957,7 +7957,7 @@
         <v>46100.0</v>
       </c>
       <c r="D559" t="n">
-        <v>15.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="560">
@@ -7971,7 +7971,7 @@
         <v>46107.0</v>
       </c>
       <c r="D560" t="n">
-        <v>9.0</v>
+        <v>3.0</v>
       </c>
     </row>
   </sheetData>
@@ -7997,7 +7997,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="n">
-        <v>54.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="3">
@@ -8005,7 +8005,7 @@
         <v>11</v>
       </c>
       <c r="B3" t="n">
-        <v>181.0</v>
+        <v>182.0</v>
       </c>
     </row>
     <row r="4">
@@ -8013,7 +8013,7 @@
         <v>12</v>
       </c>
       <c r="B4" t="n">
-        <v>1144.0</v>
+        <v>1148.0</v>
       </c>
     </row>
     <row r="5">
@@ -8021,7 +8021,7 @@
         <v>13</v>
       </c>
       <c r="B5" t="n">
-        <v>2019.0</v>
+        <v>2025.0</v>
       </c>
     </row>
   </sheetData>
@@ -8064,7 +8064,7 @@
         <v>22</v>
       </c>
       <c r="C3" t="n">
-        <v>168.0</v>
+        <v>169.0</v>
       </c>
     </row>
     <row r="4">
@@ -8086,7 +8086,7 @@
         <v>21</v>
       </c>
       <c r="C5" t="n">
-        <v>404.0</v>
+        <v>405.0</v>
       </c>
     </row>
     <row r="6">
@@ -8152,7 +8152,7 @@
         <v>19</v>
       </c>
       <c r="C11" t="n">
-        <v>40.0</v>
+        <v>34.0</v>
       </c>
     </row>
     <row r="12">
@@ -8185,7 +8185,7 @@
         <v>19</v>
       </c>
       <c r="C14" t="n">
-        <v>349.0</v>
+        <v>357.0</v>
       </c>
     </row>
     <row r="15">
@@ -8207,7 +8207,7 @@
         <v>22</v>
       </c>
       <c r="C16" t="n">
-        <v>339.0</v>
+        <v>340.0</v>
       </c>
     </row>
     <row r="17">

--- a/Download/Focus_Positivi_ZR.xlsx
+++ b/Download/Focus_Positivi_ZR.xlsx
@@ -1531,7 +1531,7 @@
         <v>46100.0</v>
       </c>
       <c r="D100" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="101">
@@ -7957,7 +7957,7 @@
         <v>46100.0</v>
       </c>
       <c r="D559" t="n">
-        <v>24.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="560">
@@ -7971,7 +7971,7 @@
         <v>46107.0</v>
       </c>
       <c r="D560" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
   </sheetData>
@@ -7997,7 +7997,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="n">
-        <v>48.0</v>
+        <v>45.0</v>
       </c>
     </row>
     <row r="3">
@@ -8013,7 +8013,7 @@
         <v>12</v>
       </c>
       <c r="B4" t="n">
-        <v>1148.0</v>
+        <v>1150.0</v>
       </c>
     </row>
     <row r="5">
@@ -8021,7 +8021,7 @@
         <v>13</v>
       </c>
       <c r="B5" t="n">
-        <v>2025.0</v>
+        <v>2029.0</v>
       </c>
     </row>
   </sheetData>
@@ -8053,7 +8053,7 @@
         <v>21</v>
       </c>
       <c r="C2" t="n">
-        <v>182.0</v>
+        <v>183.0</v>
       </c>
     </row>
     <row r="3">
@@ -8108,7 +8108,7 @@
         <v>19</v>
       </c>
       <c r="C7" t="n">
-        <v>152.0</v>
+        <v>154.0</v>
       </c>
     </row>
     <row r="8">
@@ -8152,7 +8152,7 @@
         <v>19</v>
       </c>
       <c r="C11" t="n">
-        <v>34.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="12">
@@ -8185,7 +8185,7 @@
         <v>19</v>
       </c>
       <c r="C14" t="n">
-        <v>357.0</v>
+        <v>358.0</v>
       </c>
     </row>
     <row r="15">
@@ -8196,7 +8196,7 @@
         <v>21</v>
       </c>
       <c r="C15" t="n">
-        <v>355.0</v>
+        <v>356.0</v>
       </c>
     </row>
     <row r="16">
@@ -8207,7 +8207,7 @@
         <v>22</v>
       </c>
       <c r="C16" t="n">
-        <v>340.0</v>
+        <v>341.0</v>
       </c>
     </row>
     <row r="17">

--- a/Download/Focus_Positivi_ZR.xlsx
+++ b/Download/Focus_Positivi_ZR.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="604" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="606" uniqueCount="23">
   <si>
     <t>NOME_REGIONE</t>
   </si>
@@ -1536,16 +1536,16 @@
     </row>
     <row r="101">
       <c r="A101" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B101" t="n">
-        <v>2021.0</v>
+        <v>2026.0</v>
       </c>
       <c r="C101" t="n" s="2">
-        <v>44561.0</v>
+        <v>46107.0</v>
       </c>
       <c r="D101" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="102">
@@ -1553,13 +1553,13 @@
         <v>5</v>
       </c>
       <c r="B102" t="n">
-        <v>2022.0</v>
+        <v>2021.0</v>
       </c>
       <c r="C102" t="n" s="2">
-        <v>44576.0</v>
+        <v>44561.0</v>
       </c>
       <c r="D102" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="103">
@@ -1570,10 +1570,10 @@
         <v>2022.0</v>
       </c>
       <c r="C103" t="n" s="2">
-        <v>44583.0</v>
+        <v>44576.0</v>
       </c>
       <c r="D103" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="104">
@@ -1584,10 +1584,10 @@
         <v>2022.0</v>
       </c>
       <c r="C104" t="n" s="2">
-        <v>44590.0</v>
+        <v>44583.0</v>
       </c>
       <c r="D104" t="n">
-        <v>7.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="105">
@@ -1598,10 +1598,10 @@
         <v>2022.0</v>
       </c>
       <c r="C105" t="n" s="2">
-        <v>44597.0</v>
+        <v>44590.0</v>
       </c>
       <c r="D105" t="n">
-        <v>3.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="106">
@@ -1612,10 +1612,10 @@
         <v>2022.0</v>
       </c>
       <c r="C106" t="n" s="2">
-        <v>44604.0</v>
+        <v>44597.0</v>
       </c>
       <c r="D106" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="107">
@@ -1626,10 +1626,10 @@
         <v>2022.0</v>
       </c>
       <c r="C107" t="n" s="2">
-        <v>44611.0</v>
+        <v>44604.0</v>
       </c>
       <c r="D107" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="108">
@@ -1640,7 +1640,7 @@
         <v>2022.0</v>
       </c>
       <c r="C108" t="n" s="2">
-        <v>44618.0</v>
+        <v>44611.0</v>
       </c>
       <c r="D108" t="n">
         <v>1.0</v>
@@ -1654,10 +1654,10 @@
         <v>2022.0</v>
       </c>
       <c r="C109" t="n" s="2">
-        <v>44625.0</v>
+        <v>44618.0</v>
       </c>
       <c r="D109" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="110">
@@ -1668,10 +1668,10 @@
         <v>2022.0</v>
       </c>
       <c r="C110" t="n" s="2">
-        <v>44632.0</v>
+        <v>44625.0</v>
       </c>
       <c r="D110" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="111">
@@ -1682,10 +1682,10 @@
         <v>2022.0</v>
       </c>
       <c r="C111" t="n" s="2">
-        <v>44639.0</v>
+        <v>44632.0</v>
       </c>
       <c r="D111" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="112">
@@ -1696,7 +1696,7 @@
         <v>2022.0</v>
       </c>
       <c r="C112" t="n" s="2">
-        <v>44646.0</v>
+        <v>44639.0</v>
       </c>
       <c r="D112" t="n">
         <v>2.0</v>
@@ -1710,7 +1710,7 @@
         <v>2022.0</v>
       </c>
       <c r="C113" t="n" s="2">
-        <v>44653.0</v>
+        <v>44646.0</v>
       </c>
       <c r="D113" t="n">
         <v>2.0</v>
@@ -1724,10 +1724,10 @@
         <v>2022.0</v>
       </c>
       <c r="C114" t="n" s="2">
-        <v>44660.0</v>
+        <v>44653.0</v>
       </c>
       <c r="D114" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="115">
@@ -1738,10 +1738,10 @@
         <v>2022.0</v>
       </c>
       <c r="C115" t="n" s="2">
-        <v>44667.0</v>
+        <v>44660.0</v>
       </c>
       <c r="D115" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="116">
@@ -1752,7 +1752,7 @@
         <v>2022.0</v>
       </c>
       <c r="C116" t="n" s="2">
-        <v>44674.0</v>
+        <v>44667.0</v>
       </c>
       <c r="D116" t="n">
         <v>3.0</v>
@@ -1766,10 +1766,10 @@
         <v>2022.0</v>
       </c>
       <c r="C117" t="n" s="2">
-        <v>44681.0</v>
+        <v>44674.0</v>
       </c>
       <c r="D117" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="118">
@@ -1780,10 +1780,10 @@
         <v>2022.0</v>
       </c>
       <c r="C118" t="n" s="2">
-        <v>44688.0</v>
+        <v>44681.0</v>
       </c>
       <c r="D118" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="119">
@@ -1794,7 +1794,7 @@
         <v>2022.0</v>
       </c>
       <c r="C119" t="n" s="2">
-        <v>44695.0</v>
+        <v>44688.0</v>
       </c>
       <c r="D119" t="n">
         <v>3.0</v>
@@ -1808,10 +1808,10 @@
         <v>2022.0</v>
       </c>
       <c r="C120" t="n" s="2">
-        <v>44702.0</v>
+        <v>44695.0</v>
       </c>
       <c r="D120" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="121">
@@ -1822,10 +1822,10 @@
         <v>2022.0</v>
       </c>
       <c r="C121" t="n" s="2">
-        <v>44709.0</v>
+        <v>44702.0</v>
       </c>
       <c r="D121" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="122">
@@ -1836,10 +1836,10 @@
         <v>2022.0</v>
       </c>
       <c r="C122" t="n" s="2">
-        <v>44716.0</v>
+        <v>44709.0</v>
       </c>
       <c r="D122" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="123">
@@ -1850,7 +1850,7 @@
         <v>2022.0</v>
       </c>
       <c r="C123" t="n" s="2">
-        <v>44723.0</v>
+        <v>44716.0</v>
       </c>
       <c r="D123" t="n">
         <v>1.0</v>
@@ -1864,7 +1864,7 @@
         <v>2022.0</v>
       </c>
       <c r="C124" t="n" s="2">
-        <v>44730.0</v>
+        <v>44723.0</v>
       </c>
       <c r="D124" t="n">
         <v>1.0</v>
@@ -1878,7 +1878,7 @@
         <v>2022.0</v>
       </c>
       <c r="C125" t="n" s="2">
-        <v>44737.0</v>
+        <v>44730.0</v>
       </c>
       <c r="D125" t="n">
         <v>1.0</v>
@@ -1892,7 +1892,7 @@
         <v>2022.0</v>
       </c>
       <c r="C126" t="n" s="2">
-        <v>44744.0</v>
+        <v>44737.0</v>
       </c>
       <c r="D126" t="n">
         <v>1.0</v>
@@ -1906,7 +1906,7 @@
         <v>2022.0</v>
       </c>
       <c r="C127" t="n" s="2">
-        <v>44751.0</v>
+        <v>44744.0</v>
       </c>
       <c r="D127" t="n">
         <v>1.0</v>
@@ -1920,7 +1920,7 @@
         <v>2022.0</v>
       </c>
       <c r="C128" t="n" s="2">
-        <v>44758.0</v>
+        <v>44751.0</v>
       </c>
       <c r="D128" t="n">
         <v>1.0</v>
@@ -1934,7 +1934,7 @@
         <v>2022.0</v>
       </c>
       <c r="C129" t="n" s="2">
-        <v>44772.0</v>
+        <v>44758.0</v>
       </c>
       <c r="D129" t="n">
         <v>1.0</v>
@@ -1948,7 +1948,7 @@
         <v>2022.0</v>
       </c>
       <c r="C130" t="n" s="2">
-        <v>44793.0</v>
+        <v>44772.0</v>
       </c>
       <c r="D130" t="n">
         <v>1.0</v>
@@ -1962,7 +1962,7 @@
         <v>2022.0</v>
       </c>
       <c r="C131" t="n" s="2">
-        <v>44800.0</v>
+        <v>44793.0</v>
       </c>
       <c r="D131" t="n">
         <v>1.0</v>
@@ -1976,7 +1976,7 @@
         <v>2022.0</v>
       </c>
       <c r="C132" t="n" s="2">
-        <v>44828.0</v>
+        <v>44800.0</v>
       </c>
       <c r="D132" t="n">
         <v>1.0</v>
@@ -1990,7 +1990,7 @@
         <v>2022.0</v>
       </c>
       <c r="C133" t="n" s="2">
-        <v>44849.0</v>
+        <v>44828.0</v>
       </c>
       <c r="D133" t="n">
         <v>1.0</v>
@@ -2004,7 +2004,7 @@
         <v>2022.0</v>
       </c>
       <c r="C134" t="n" s="2">
-        <v>44856.0</v>
+        <v>44849.0</v>
       </c>
       <c r="D134" t="n">
         <v>1.0</v>
@@ -2018,7 +2018,7 @@
         <v>2022.0</v>
       </c>
       <c r="C135" t="n" s="2">
-        <v>44863.0</v>
+        <v>44856.0</v>
       </c>
       <c r="D135" t="n">
         <v>1.0</v>
@@ -2032,10 +2032,10 @@
         <v>2022.0</v>
       </c>
       <c r="C136" t="n" s="2">
-        <v>44884.0</v>
+        <v>44863.0</v>
       </c>
       <c r="D136" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="137">
@@ -2046,10 +2046,10 @@
         <v>2022.0</v>
       </c>
       <c r="C137" t="n" s="2">
-        <v>44891.0</v>
+        <v>44884.0</v>
       </c>
       <c r="D137" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="138">
@@ -2060,7 +2060,7 @@
         <v>2022.0</v>
       </c>
       <c r="C138" t="n" s="2">
-        <v>44905.0</v>
+        <v>44891.0</v>
       </c>
       <c r="D138" t="n">
         <v>1.0</v>
@@ -2074,7 +2074,7 @@
         <v>2022.0</v>
       </c>
       <c r="C139" t="n" s="2">
-        <v>44912.0</v>
+        <v>44905.0</v>
       </c>
       <c r="D139" t="n">
         <v>1.0</v>
@@ -2088,10 +2088,10 @@
         <v>2022.0</v>
       </c>
       <c r="C140" t="n" s="2">
-        <v>44919.0</v>
+        <v>44912.0</v>
       </c>
       <c r="D140" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="141">
@@ -2099,13 +2099,13 @@
         <v>5</v>
       </c>
       <c r="B141" t="n">
-        <v>2023.0</v>
+        <v>2022.0</v>
       </c>
       <c r="C141" t="n" s="2">
-        <v>44934.0</v>
+        <v>44919.0</v>
       </c>
       <c r="D141" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="142">
@@ -2116,10 +2116,10 @@
         <v>2023.0</v>
       </c>
       <c r="C142" t="n" s="2">
-        <v>44941.0</v>
+        <v>44934.0</v>
       </c>
       <c r="D142" t="n">
-        <v>8.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="143">
@@ -2130,10 +2130,10 @@
         <v>2023.0</v>
       </c>
       <c r="C143" t="n" s="2">
-        <v>44948.0</v>
+        <v>44941.0</v>
       </c>
       <c r="D143" t="n">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="144">
@@ -2144,10 +2144,10 @@
         <v>2023.0</v>
       </c>
       <c r="C144" t="n" s="2">
-        <v>44955.0</v>
+        <v>44948.0</v>
       </c>
       <c r="D144" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="145">
@@ -2158,10 +2158,10 @@
         <v>2023.0</v>
       </c>
       <c r="C145" t="n" s="2">
-        <v>44962.0</v>
+        <v>44955.0</v>
       </c>
       <c r="D145" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="146">
@@ -2172,7 +2172,7 @@
         <v>2023.0</v>
       </c>
       <c r="C146" t="n" s="2">
-        <v>44969.0</v>
+        <v>44962.0</v>
       </c>
       <c r="D146" t="n">
         <v>4.0</v>
@@ -2186,10 +2186,10 @@
         <v>2023.0</v>
       </c>
       <c r="C147" t="n" s="2">
-        <v>44976.0</v>
+        <v>44969.0</v>
       </c>
       <c r="D147" t="n">
-        <v>17.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="148">
@@ -2200,10 +2200,10 @@
         <v>2023.0</v>
       </c>
       <c r="C148" t="n" s="2">
-        <v>44983.0</v>
+        <v>44976.0</v>
       </c>
       <c r="D148" t="n">
-        <v>11.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="149">
@@ -2214,10 +2214,10 @@
         <v>2023.0</v>
       </c>
       <c r="C149" t="n" s="2">
-        <v>44990.0</v>
+        <v>44983.0</v>
       </c>
       <c r="D149" t="n">
-        <v>5.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="150">
@@ -2228,10 +2228,10 @@
         <v>2023.0</v>
       </c>
       <c r="C150" t="n" s="2">
-        <v>44997.0</v>
+        <v>44990.0</v>
       </c>
       <c r="D150" t="n">
-        <v>22.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="151">
@@ -2242,10 +2242,10 @@
         <v>2023.0</v>
       </c>
       <c r="C151" t="n" s="2">
-        <v>45004.0</v>
+        <v>44997.0</v>
       </c>
       <c r="D151" t="n">
-        <v>8.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="152">
@@ -2256,10 +2256,10 @@
         <v>2023.0</v>
       </c>
       <c r="C152" t="n" s="2">
-        <v>45011.0</v>
+        <v>45004.0</v>
       </c>
       <c r="D152" t="n">
-        <v>17.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="153">
@@ -2270,10 +2270,10 @@
         <v>2023.0</v>
       </c>
       <c r="C153" t="n" s="2">
-        <v>45018.0</v>
+        <v>45011.0</v>
       </c>
       <c r="D153" t="n">
-        <v>10.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="154">
@@ -2284,10 +2284,10 @@
         <v>2023.0</v>
       </c>
       <c r="C154" t="n" s="2">
-        <v>45025.0</v>
+        <v>45018.0</v>
       </c>
       <c r="D154" t="n">
-        <v>13.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="155">
@@ -2298,10 +2298,10 @@
         <v>2023.0</v>
       </c>
       <c r="C155" t="n" s="2">
-        <v>45032.0</v>
+        <v>45025.0</v>
       </c>
       <c r="D155" t="n">
-        <v>10.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="156">
@@ -2312,10 +2312,10 @@
         <v>2023.0</v>
       </c>
       <c r="C156" t="n" s="2">
-        <v>45039.0</v>
+        <v>45032.0</v>
       </c>
       <c r="D156" t="n">
-        <v>22.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="157">
@@ -2326,10 +2326,10 @@
         <v>2023.0</v>
       </c>
       <c r="C157" t="n" s="2">
-        <v>45046.0</v>
+        <v>45039.0</v>
       </c>
       <c r="D157" t="n">
-        <v>23.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="158">
@@ -2340,10 +2340,10 @@
         <v>2023.0</v>
       </c>
       <c r="C158" t="n" s="2">
-        <v>45053.0</v>
+        <v>45046.0</v>
       </c>
       <c r="D158" t="n">
-        <v>16.0</v>
+        <v>23.0</v>
       </c>
     </row>
     <row r="159">
@@ -2354,10 +2354,10 @@
         <v>2023.0</v>
       </c>
       <c r="C159" t="n" s="2">
-        <v>45060.0</v>
+        <v>45053.0</v>
       </c>
       <c r="D159" t="n">
-        <v>13.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="160">
@@ -2368,10 +2368,10 @@
         <v>2023.0</v>
       </c>
       <c r="C160" t="n" s="2">
-        <v>45067.0</v>
+        <v>45060.0</v>
       </c>
       <c r="D160" t="n">
-        <v>9.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="161">
@@ -2382,10 +2382,10 @@
         <v>2023.0</v>
       </c>
       <c r="C161" t="n" s="2">
-        <v>45074.0</v>
+        <v>45067.0</v>
       </c>
       <c r="D161" t="n">
-        <v>6.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="162">
@@ -2396,10 +2396,10 @@
         <v>2023.0</v>
       </c>
       <c r="C162" t="n" s="2">
-        <v>45081.0</v>
+        <v>45074.0</v>
       </c>
       <c r="D162" t="n">
-        <v>16.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="163">
@@ -2410,10 +2410,10 @@
         <v>2023.0</v>
       </c>
       <c r="C163" t="n" s="2">
-        <v>45088.0</v>
+        <v>45081.0</v>
       </c>
       <c r="D163" t="n">
-        <v>8.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="164">
@@ -2424,10 +2424,10 @@
         <v>2023.0</v>
       </c>
       <c r="C164" t="n" s="2">
-        <v>45095.0</v>
+        <v>45088.0</v>
       </c>
       <c r="D164" t="n">
-        <v>16.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="165">
@@ -2438,10 +2438,10 @@
         <v>2023.0</v>
       </c>
       <c r="C165" t="n" s="2">
-        <v>45102.0</v>
+        <v>45095.0</v>
       </c>
       <c r="D165" t="n">
-        <v>17.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="166">
@@ -2452,10 +2452,10 @@
         <v>2023.0</v>
       </c>
       <c r="C166" t="n" s="2">
-        <v>45109.0</v>
+        <v>45102.0</v>
       </c>
       <c r="D166" t="n">
-        <v>14.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="167">
@@ -2466,10 +2466,10 @@
         <v>2023.0</v>
       </c>
       <c r="C167" t="n" s="2">
-        <v>45116.0</v>
+        <v>45109.0</v>
       </c>
       <c r="D167" t="n">
-        <v>13.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="168">
@@ -2480,10 +2480,10 @@
         <v>2023.0</v>
       </c>
       <c r="C168" t="n" s="2">
-        <v>45123.0</v>
+        <v>45116.0</v>
       </c>
       <c r="D168" t="n">
-        <v>5.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="169">
@@ -2494,10 +2494,10 @@
         <v>2023.0</v>
       </c>
       <c r="C169" t="n" s="2">
-        <v>45130.0</v>
+        <v>45123.0</v>
       </c>
       <c r="D169" t="n">
-        <v>8.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="170">
@@ -2508,10 +2508,10 @@
         <v>2023.0</v>
       </c>
       <c r="C170" t="n" s="2">
-        <v>45137.0</v>
+        <v>45130.0</v>
       </c>
       <c r="D170" t="n">
-        <v>4.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="171">
@@ -2522,10 +2522,10 @@
         <v>2023.0</v>
       </c>
       <c r="C171" t="n" s="2">
-        <v>45144.0</v>
+        <v>45137.0</v>
       </c>
       <c r="D171" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="172">
@@ -2536,7 +2536,7 @@
         <v>2023.0</v>
       </c>
       <c r="C172" t="n" s="2">
-        <v>45151.0</v>
+        <v>45144.0</v>
       </c>
       <c r="D172" t="n">
         <v>2.0</v>
@@ -2550,10 +2550,10 @@
         <v>2023.0</v>
       </c>
       <c r="C173" t="n" s="2">
-        <v>45158.0</v>
+        <v>45151.0</v>
       </c>
       <c r="D173" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="174">
@@ -2564,7 +2564,7 @@
         <v>2023.0</v>
       </c>
       <c r="C174" t="n" s="2">
-        <v>45165.0</v>
+        <v>45158.0</v>
       </c>
       <c r="D174" t="n">
         <v>5.0</v>
@@ -2578,10 +2578,10 @@
         <v>2023.0</v>
       </c>
       <c r="C175" t="n" s="2">
-        <v>45172.0</v>
+        <v>45165.0</v>
       </c>
       <c r="D175" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="176">
@@ -2592,10 +2592,10 @@
         <v>2023.0</v>
       </c>
       <c r="C176" t="n" s="2">
-        <v>45179.0</v>
+        <v>45172.0</v>
       </c>
       <c r="D176" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="177">
@@ -2606,10 +2606,10 @@
         <v>2023.0</v>
       </c>
       <c r="C177" t="n" s="2">
-        <v>45186.0</v>
+        <v>45179.0</v>
       </c>
       <c r="D177" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="178">
@@ -2620,7 +2620,7 @@
         <v>2023.0</v>
       </c>
       <c r="C178" t="n" s="2">
-        <v>45193.0</v>
+        <v>45186.0</v>
       </c>
       <c r="D178" t="n">
         <v>1.0</v>
@@ -2634,10 +2634,10 @@
         <v>2023.0</v>
       </c>
       <c r="C179" t="n" s="2">
-        <v>45200.0</v>
+        <v>45193.0</v>
       </c>
       <c r="D179" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="180">
@@ -2648,10 +2648,10 @@
         <v>2023.0</v>
       </c>
       <c r="C180" t="n" s="2">
-        <v>45207.0</v>
+        <v>45200.0</v>
       </c>
       <c r="D180" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="181">
@@ -2662,10 +2662,10 @@
         <v>2023.0</v>
       </c>
       <c r="C181" t="n" s="2">
-        <v>45214.0</v>
+        <v>45207.0</v>
       </c>
       <c r="D181" t="n">
-        <v>8.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="182">
@@ -2676,7 +2676,7 @@
         <v>2023.0</v>
       </c>
       <c r="C182" t="n" s="2">
-        <v>45221.0</v>
+        <v>45214.0</v>
       </c>
       <c r="D182" t="n">
         <v>8.0</v>
@@ -2690,10 +2690,10 @@
         <v>2023.0</v>
       </c>
       <c r="C183" t="n" s="2">
-        <v>45228.0</v>
+        <v>45221.0</v>
       </c>
       <c r="D183" t="n">
-        <v>17.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="184">
@@ -2704,10 +2704,10 @@
         <v>2023.0</v>
       </c>
       <c r="C184" t="n" s="2">
-        <v>45235.0</v>
+        <v>45228.0</v>
       </c>
       <c r="D184" t="n">
-        <v>9.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="185">
@@ -2718,7 +2718,7 @@
         <v>2023.0</v>
       </c>
       <c r="C185" t="n" s="2">
-        <v>45242.0</v>
+        <v>45235.0</v>
       </c>
       <c r="D185" t="n">
         <v>9.0</v>
@@ -2732,10 +2732,10 @@
         <v>2023.0</v>
       </c>
       <c r="C186" t="n" s="2">
-        <v>45249.0</v>
+        <v>45242.0</v>
       </c>
       <c r="D186" t="n">
-        <v>14.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="187">
@@ -2746,10 +2746,10 @@
         <v>2023.0</v>
       </c>
       <c r="C187" t="n" s="2">
-        <v>45256.0</v>
+        <v>45249.0</v>
       </c>
       <c r="D187" t="n">
-        <v>17.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="188">
@@ -2760,10 +2760,10 @@
         <v>2023.0</v>
       </c>
       <c r="C188" t="n" s="2">
-        <v>45263.0</v>
+        <v>45256.0</v>
       </c>
       <c r="D188" t="n">
-        <v>14.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="189">
@@ -2774,10 +2774,10 @@
         <v>2023.0</v>
       </c>
       <c r="C189" t="n" s="2">
-        <v>45270.0</v>
+        <v>45263.0</v>
       </c>
       <c r="D189" t="n">
-        <v>26.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="190">
@@ -2788,10 +2788,10 @@
         <v>2023.0</v>
       </c>
       <c r="C190" t="n" s="2">
-        <v>45277.0</v>
+        <v>45270.0</v>
       </c>
       <c r="D190" t="n">
-        <v>19.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="191">
@@ -2802,10 +2802,10 @@
         <v>2023.0</v>
       </c>
       <c r="C191" t="n" s="2">
-        <v>45284.0</v>
+        <v>45277.0</v>
       </c>
       <c r="D191" t="n">
-        <v>21.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="192">
@@ -2816,10 +2816,10 @@
         <v>2023.0</v>
       </c>
       <c r="C192" t="n" s="2">
-        <v>45291.0</v>
+        <v>45284.0</v>
       </c>
       <c r="D192" t="n">
-        <v>9.0</v>
+        <v>21.0</v>
       </c>
     </row>
     <row r="193">
@@ -2827,13 +2827,13 @@
         <v>5</v>
       </c>
       <c r="B193" t="n">
-        <v>2024.0</v>
+        <v>2023.0</v>
       </c>
       <c r="C193" t="n" s="2">
-        <v>45299.0</v>
+        <v>45291.0</v>
       </c>
       <c r="D193" t="n">
-        <v>26.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="194">
@@ -2844,10 +2844,10 @@
         <v>2024.0</v>
       </c>
       <c r="C194" t="n" s="2">
-        <v>45306.0</v>
+        <v>45299.0</v>
       </c>
       <c r="D194" t="n">
-        <v>14.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="195">
@@ -2858,10 +2858,10 @@
         <v>2024.0</v>
       </c>
       <c r="C195" t="n" s="2">
-        <v>45313.0</v>
+        <v>45306.0</v>
       </c>
       <c r="D195" t="n">
-        <v>15.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="196">
@@ -2872,10 +2872,10 @@
         <v>2024.0</v>
       </c>
       <c r="C196" t="n" s="2">
-        <v>45320.0</v>
+        <v>45313.0</v>
       </c>
       <c r="D196" t="n">
-        <v>18.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="197">
@@ -2886,10 +2886,10 @@
         <v>2024.0</v>
       </c>
       <c r="C197" t="n" s="2">
-        <v>45327.0</v>
+        <v>45320.0</v>
       </c>
       <c r="D197" t="n">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="198">
@@ -2900,10 +2900,10 @@
         <v>2024.0</v>
       </c>
       <c r="C198" t="n" s="2">
-        <v>45334.0</v>
+        <v>45327.0</v>
       </c>
       <c r="D198" t="n">
-        <v>13.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="199">
@@ -2914,10 +2914,10 @@
         <v>2024.0</v>
       </c>
       <c r="C199" t="n" s="2">
-        <v>45341.0</v>
+        <v>45334.0</v>
       </c>
       <c r="D199" t="n">
-        <v>11.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="200">
@@ -2928,10 +2928,10 @@
         <v>2024.0</v>
       </c>
       <c r="C200" t="n" s="2">
-        <v>45348.0</v>
+        <v>45341.0</v>
       </c>
       <c r="D200" t="n">
-        <v>8.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="201">
@@ -2942,10 +2942,10 @@
         <v>2024.0</v>
       </c>
       <c r="C201" t="n" s="2">
-        <v>45355.0</v>
+        <v>45348.0</v>
       </c>
       <c r="D201" t="n">
-        <v>1.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="202">
@@ -2956,10 +2956,10 @@
         <v>2024.0</v>
       </c>
       <c r="C202" t="n" s="2">
-        <v>45362.0</v>
+        <v>45355.0</v>
       </c>
       <c r="D202" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="203">
@@ -2970,10 +2970,10 @@
         <v>2024.0</v>
       </c>
       <c r="C203" t="n" s="2">
-        <v>45369.0</v>
+        <v>45362.0</v>
       </c>
       <c r="D203" t="n">
-        <v>8.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="204">
@@ -2984,10 +2984,10 @@
         <v>2024.0</v>
       </c>
       <c r="C204" t="n" s="2">
-        <v>45376.0</v>
+        <v>45369.0</v>
       </c>
       <c r="D204" t="n">
-        <v>9.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="205">
@@ -2998,10 +2998,10 @@
         <v>2024.0</v>
       </c>
       <c r="C205" t="n" s="2">
-        <v>45383.0</v>
+        <v>45376.0</v>
       </c>
       <c r="D205" t="n">
-        <v>5.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="206">
@@ -3012,10 +3012,10 @@
         <v>2024.0</v>
       </c>
       <c r="C206" t="n" s="2">
-        <v>45390.0</v>
+        <v>45383.0</v>
       </c>
       <c r="D206" t="n">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="207">
@@ -3026,10 +3026,10 @@
         <v>2024.0</v>
       </c>
       <c r="C207" t="n" s="2">
-        <v>45397.0</v>
+        <v>45390.0</v>
       </c>
       <c r="D207" t="n">
-        <v>13.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="208">
@@ -3040,10 +3040,10 @@
         <v>2024.0</v>
       </c>
       <c r="C208" t="n" s="2">
-        <v>45404.0</v>
+        <v>45397.0</v>
       </c>
       <c r="D208" t="n">
-        <v>24.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="209">
@@ -3054,10 +3054,10 @@
         <v>2024.0</v>
       </c>
       <c r="C209" t="n" s="2">
-        <v>45411.0</v>
+        <v>45404.0</v>
       </c>
       <c r="D209" t="n">
-        <v>17.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="210">
@@ -3068,10 +3068,10 @@
         <v>2024.0</v>
       </c>
       <c r="C210" t="n" s="2">
-        <v>45418.0</v>
+        <v>45411.0</v>
       </c>
       <c r="D210" t="n">
-        <v>3.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="211">
@@ -3082,10 +3082,10 @@
         <v>2024.0</v>
       </c>
       <c r="C211" t="n" s="2">
-        <v>45425.0</v>
+        <v>45418.0</v>
       </c>
       <c r="D211" t="n">
-        <v>16.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="212">
@@ -3096,10 +3096,10 @@
         <v>2024.0</v>
       </c>
       <c r="C212" t="n" s="2">
-        <v>45432.0</v>
+        <v>45425.0</v>
       </c>
       <c r="D212" t="n">
-        <v>19.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="213">
@@ -3110,10 +3110,10 @@
         <v>2024.0</v>
       </c>
       <c r="C213" t="n" s="2">
-        <v>45439.0</v>
+        <v>45432.0</v>
       </c>
       <c r="D213" t="n">
-        <v>30.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="214">
@@ -3124,10 +3124,10 @@
         <v>2024.0</v>
       </c>
       <c r="C214" t="n" s="2">
-        <v>45446.0</v>
+        <v>45439.0</v>
       </c>
       <c r="D214" t="n">
-        <v>28.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="215">
@@ -3138,10 +3138,10 @@
         <v>2024.0</v>
       </c>
       <c r="C215" t="n" s="2">
-        <v>45453.0</v>
+        <v>45446.0</v>
       </c>
       <c r="D215" t="n">
-        <v>19.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="216">
@@ -3152,10 +3152,10 @@
         <v>2024.0</v>
       </c>
       <c r="C216" t="n" s="2">
-        <v>45460.0</v>
+        <v>45453.0</v>
       </c>
       <c r="D216" t="n">
-        <v>26.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="217">
@@ -3166,10 +3166,10 @@
         <v>2024.0</v>
       </c>
       <c r="C217" t="n" s="2">
-        <v>45467.0</v>
+        <v>45460.0</v>
       </c>
       <c r="D217" t="n">
-        <v>8.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="218">
@@ -3180,10 +3180,10 @@
         <v>2024.0</v>
       </c>
       <c r="C218" t="n" s="2">
-        <v>45474.0</v>
+        <v>45467.0</v>
       </c>
       <c r="D218" t="n">
-        <v>12.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="219">
@@ -3194,7 +3194,7 @@
         <v>2024.0</v>
       </c>
       <c r="C219" t="n" s="2">
-        <v>45481.0</v>
+        <v>45474.0</v>
       </c>
       <c r="D219" t="n">
         <v>12.0</v>
@@ -3208,10 +3208,10 @@
         <v>2024.0</v>
       </c>
       <c r="C220" t="n" s="2">
-        <v>45488.0</v>
+        <v>45481.0</v>
       </c>
       <c r="D220" t="n">
-        <v>4.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="221">
@@ -3222,10 +3222,10 @@
         <v>2024.0</v>
       </c>
       <c r="C221" t="n" s="2">
-        <v>45495.0</v>
+        <v>45488.0</v>
       </c>
       <c r="D221" t="n">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="222">
@@ -3236,10 +3236,10 @@
         <v>2024.0</v>
       </c>
       <c r="C222" t="n" s="2">
-        <v>45502.0</v>
+        <v>45495.0</v>
       </c>
       <c r="D222" t="n">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="223">
@@ -3250,10 +3250,10 @@
         <v>2024.0</v>
       </c>
       <c r="C223" t="n" s="2">
-        <v>45509.0</v>
+        <v>45502.0</v>
       </c>
       <c r="D223" t="n">
-        <v>2.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="224">
@@ -3264,10 +3264,10 @@
         <v>2024.0</v>
       </c>
       <c r="C224" t="n" s="2">
-        <v>45516.0</v>
+        <v>45509.0</v>
       </c>
       <c r="D224" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="225">
@@ -3278,7 +3278,7 @@
         <v>2024.0</v>
       </c>
       <c r="C225" t="n" s="2">
-        <v>45523.0</v>
+        <v>45516.0</v>
       </c>
       <c r="D225" t="n">
         <v>4.0</v>
@@ -3292,7 +3292,7 @@
         <v>2024.0</v>
       </c>
       <c r="C226" t="n" s="2">
-        <v>45530.0</v>
+        <v>45523.0</v>
       </c>
       <c r="D226" t="n">
         <v>4.0</v>
@@ -3306,7 +3306,7 @@
         <v>2024.0</v>
       </c>
       <c r="C227" t="n" s="2">
-        <v>45537.0</v>
+        <v>45530.0</v>
       </c>
       <c r="D227" t="n">
         <v>4.0</v>
@@ -3320,10 +3320,10 @@
         <v>2024.0</v>
       </c>
       <c r="C228" t="n" s="2">
-        <v>45544.0</v>
+        <v>45537.0</v>
       </c>
       <c r="D228" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="229">
@@ -3334,10 +3334,10 @@
         <v>2024.0</v>
       </c>
       <c r="C229" t="n" s="2">
-        <v>45551.0</v>
+        <v>45544.0</v>
       </c>
       <c r="D229" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="230">
@@ -3348,10 +3348,10 @@
         <v>2024.0</v>
       </c>
       <c r="C230" t="n" s="2">
-        <v>45558.0</v>
+        <v>45551.0</v>
       </c>
       <c r="D230" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="231">
@@ -3362,10 +3362,10 @@
         <v>2024.0</v>
       </c>
       <c r="C231" t="n" s="2">
-        <v>45600.0</v>
+        <v>45558.0</v>
       </c>
       <c r="D231" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="232">
@@ -3376,10 +3376,10 @@
         <v>2024.0</v>
       </c>
       <c r="C232" t="n" s="2">
-        <v>45607.0</v>
+        <v>45600.0</v>
       </c>
       <c r="D232" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="233">
@@ -3390,10 +3390,10 @@
         <v>2024.0</v>
       </c>
       <c r="C233" t="n" s="2">
-        <v>45628.0</v>
+        <v>45607.0</v>
       </c>
       <c r="D233" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="234">
@@ -3404,10 +3404,10 @@
         <v>2024.0</v>
       </c>
       <c r="C234" t="n" s="2">
-        <v>45635.0</v>
+        <v>45628.0</v>
       </c>
       <c r="D234" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="235">
@@ -3418,7 +3418,7 @@
         <v>2024.0</v>
       </c>
       <c r="C235" t="n" s="2">
-        <v>45642.0</v>
+        <v>45635.0</v>
       </c>
       <c r="D235" t="n">
         <v>3.0</v>
@@ -3432,10 +3432,10 @@
         <v>2024.0</v>
       </c>
       <c r="C236" t="n" s="2">
-        <v>45649.0</v>
+        <v>45642.0</v>
       </c>
       <c r="D236" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="237">
@@ -3446,7 +3446,7 @@
         <v>2024.0</v>
       </c>
       <c r="C237" t="n" s="2">
-        <v>45656.0</v>
+        <v>45649.0</v>
       </c>
       <c r="D237" t="n">
         <v>1.0</v>
@@ -3457,13 +3457,13 @@
         <v>5</v>
       </c>
       <c r="B238" t="n">
-        <v>2025.0</v>
+        <v>2024.0</v>
       </c>
       <c r="C238" t="n" s="2">
-        <v>45672.0</v>
+        <v>45656.0</v>
       </c>
       <c r="D238" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="239">
@@ -3474,10 +3474,10 @@
         <v>2025.0</v>
       </c>
       <c r="C239" t="n" s="2">
-        <v>45679.0</v>
+        <v>45672.0</v>
       </c>
       <c r="D239" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="240">
@@ -3488,7 +3488,7 @@
         <v>2025.0</v>
       </c>
       <c r="C240" t="n" s="2">
-        <v>45686.0</v>
+        <v>45679.0</v>
       </c>
       <c r="D240" t="n">
         <v>1.0</v>
@@ -3502,10 +3502,10 @@
         <v>2025.0</v>
       </c>
       <c r="C241" t="n" s="2">
-        <v>45721.0</v>
+        <v>45686.0</v>
       </c>
       <c r="D241" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="242">
@@ -3516,10 +3516,10 @@
         <v>2025.0</v>
       </c>
       <c r="C242" t="n" s="2">
-        <v>45728.0</v>
+        <v>45721.0</v>
       </c>
       <c r="D242" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="243">
@@ -3530,10 +3530,10 @@
         <v>2025.0</v>
       </c>
       <c r="C243" t="n" s="2">
-        <v>45742.0</v>
+        <v>45728.0</v>
       </c>
       <c r="D243" t="n">
-        <v>9.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="244">
@@ -3544,10 +3544,10 @@
         <v>2025.0</v>
       </c>
       <c r="C244" t="n" s="2">
-        <v>45749.0</v>
+        <v>45742.0</v>
       </c>
       <c r="D244" t="n">
-        <v>5.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="245">
@@ -3558,10 +3558,10 @@
         <v>2025.0</v>
       </c>
       <c r="C245" t="n" s="2">
-        <v>45756.0</v>
+        <v>45749.0</v>
       </c>
       <c r="D245" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="246">
@@ -3572,10 +3572,10 @@
         <v>2025.0</v>
       </c>
       <c r="C246" t="n" s="2">
-        <v>45763.0</v>
+        <v>45756.0</v>
       </c>
       <c r="D246" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="247">
@@ -3586,10 +3586,10 @@
         <v>2025.0</v>
       </c>
       <c r="C247" t="n" s="2">
-        <v>45770.0</v>
+        <v>45763.0</v>
       </c>
       <c r="D247" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="248">
@@ -3600,10 +3600,10 @@
         <v>2025.0</v>
       </c>
       <c r="C248" t="n" s="2">
-        <v>45777.0</v>
+        <v>45770.0</v>
       </c>
       <c r="D248" t="n">
-        <v>7.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="249">
@@ -3614,10 +3614,10 @@
         <v>2025.0</v>
       </c>
       <c r="C249" t="n" s="2">
-        <v>45784.0</v>
+        <v>45777.0</v>
       </c>
       <c r="D249" t="n">
-        <v>2.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="250">
@@ -3628,10 +3628,10 @@
         <v>2025.0</v>
       </c>
       <c r="C250" t="n" s="2">
-        <v>45791.0</v>
+        <v>45784.0</v>
       </c>
       <c r="D250" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="251">
@@ -3642,10 +3642,10 @@
         <v>2025.0</v>
       </c>
       <c r="C251" t="n" s="2">
-        <v>45798.0</v>
+        <v>45791.0</v>
       </c>
       <c r="D251" t="n">
-        <v>8.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="252">
@@ -3656,10 +3656,10 @@
         <v>2025.0</v>
       </c>
       <c r="C252" t="n" s="2">
-        <v>45805.0</v>
+        <v>45798.0</v>
       </c>
       <c r="D252" t="n">
-        <v>4.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="253">
@@ -3670,10 +3670,10 @@
         <v>2025.0</v>
       </c>
       <c r="C253" t="n" s="2">
-        <v>45812.0</v>
+        <v>45805.0</v>
       </c>
       <c r="D253" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="254">
@@ -3684,10 +3684,10 @@
         <v>2025.0</v>
       </c>
       <c r="C254" t="n" s="2">
-        <v>45819.0</v>
+        <v>45812.0</v>
       </c>
       <c r="D254" t="n">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="255">
@@ -3698,10 +3698,10 @@
         <v>2025.0</v>
       </c>
       <c r="C255" t="n" s="2">
-        <v>45826.0</v>
+        <v>45819.0</v>
       </c>
       <c r="D255" t="n">
-        <v>13.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="256">
@@ -3712,10 +3712,10 @@
         <v>2025.0</v>
       </c>
       <c r="C256" t="n" s="2">
-        <v>45833.0</v>
+        <v>45826.0</v>
       </c>
       <c r="D256" t="n">
-        <v>1.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="257">
@@ -3726,10 +3726,10 @@
         <v>2025.0</v>
       </c>
       <c r="C257" t="n" s="2">
-        <v>45840.0</v>
+        <v>45833.0</v>
       </c>
       <c r="D257" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="258">
@@ -3740,7 +3740,7 @@
         <v>2025.0</v>
       </c>
       <c r="C258" t="n" s="2">
-        <v>45847.0</v>
+        <v>45840.0</v>
       </c>
       <c r="D258" t="n">
         <v>4.0</v>
@@ -3754,10 +3754,10 @@
         <v>2025.0</v>
       </c>
       <c r="C259" t="n" s="2">
-        <v>45854.0</v>
+        <v>45847.0</v>
       </c>
       <c r="D259" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="260">
@@ -3768,10 +3768,10 @@
         <v>2025.0</v>
       </c>
       <c r="C260" t="n" s="2">
-        <v>45861.0</v>
+        <v>45854.0</v>
       </c>
       <c r="D260" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="261">
@@ -3782,10 +3782,10 @@
         <v>2025.0</v>
       </c>
       <c r="C261" t="n" s="2">
-        <v>45868.0</v>
+        <v>45861.0</v>
       </c>
       <c r="D261" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="262">
@@ -3796,10 +3796,10 @@
         <v>2025.0</v>
       </c>
       <c r="C262" t="n" s="2">
-        <v>45882.0</v>
+        <v>45868.0</v>
       </c>
       <c r="D262" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="263">
@@ -3810,7 +3810,7 @@
         <v>2025.0</v>
       </c>
       <c r="C263" t="n" s="2">
-        <v>45889.0</v>
+        <v>45882.0</v>
       </c>
       <c r="D263" t="n">
         <v>1.0</v>
@@ -3824,10 +3824,10 @@
         <v>2025.0</v>
       </c>
       <c r="C264" t="n" s="2">
-        <v>45896.0</v>
+        <v>45889.0</v>
       </c>
       <c r="D264" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="265">
@@ -3838,7 +3838,7 @@
         <v>2025.0</v>
       </c>
       <c r="C265" t="n" s="2">
-        <v>45903.0</v>
+        <v>45896.0</v>
       </c>
       <c r="D265" t="n">
         <v>3.0</v>
@@ -3852,10 +3852,10 @@
         <v>2025.0</v>
       </c>
       <c r="C266" t="n" s="2">
-        <v>45910.0</v>
+        <v>45903.0</v>
       </c>
       <c r="D266" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="267">
@@ -3866,7 +3866,7 @@
         <v>2025.0</v>
       </c>
       <c r="C267" t="n" s="2">
-        <v>45973.0</v>
+        <v>45910.0</v>
       </c>
       <c r="D267" t="n">
         <v>1.0</v>
@@ -3880,10 +3880,10 @@
         <v>2025.0</v>
       </c>
       <c r="C268" t="n" s="2">
-        <v>45987.0</v>
+        <v>45973.0</v>
       </c>
       <c r="D268" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="269">
@@ -3894,10 +3894,10 @@
         <v>2025.0</v>
       </c>
       <c r="C269" t="n" s="2">
-        <v>45994.0</v>
+        <v>45987.0</v>
       </c>
       <c r="D269" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="270">
@@ -3908,10 +3908,10 @@
         <v>2025.0</v>
       </c>
       <c r="C270" t="n" s="2">
-        <v>46001.0</v>
+        <v>45994.0</v>
       </c>
       <c r="D270" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="271">
@@ -3922,10 +3922,10 @@
         <v>2025.0</v>
       </c>
       <c r="C271" t="n" s="2">
-        <v>46008.0</v>
+        <v>46001.0</v>
       </c>
       <c r="D271" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="272">
@@ -3936,10 +3936,10 @@
         <v>2025.0</v>
       </c>
       <c r="C272" t="n" s="2">
-        <v>46022.0</v>
+        <v>46008.0</v>
       </c>
       <c r="D272" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="273">
@@ -3950,10 +3950,10 @@
         <v>2025.0</v>
       </c>
       <c r="C273" t="n" s="2">
-        <v>46029.0</v>
+        <v>46022.0</v>
       </c>
       <c r="D273" t="n">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="274">
@@ -3961,13 +3961,13 @@
         <v>5</v>
       </c>
       <c r="B274" t="n">
-        <v>2026.0</v>
+        <v>2025.0</v>
       </c>
       <c r="C274" t="n" s="2">
-        <v>46030.0</v>
+        <v>46029.0</v>
       </c>
       <c r="D274" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="275">
@@ -3978,10 +3978,10 @@
         <v>2026.0</v>
       </c>
       <c r="C275" t="n" s="2">
-        <v>46037.0</v>
+        <v>46030.0</v>
       </c>
       <c r="D275" t="n">
-        <v>12.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="276">
@@ -3992,10 +3992,10 @@
         <v>2026.0</v>
       </c>
       <c r="C276" t="n" s="2">
-        <v>46044.0</v>
+        <v>46037.0</v>
       </c>
       <c r="D276" t="n">
-        <v>9.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="277">
@@ -4006,10 +4006,10 @@
         <v>2026.0</v>
       </c>
       <c r="C277" t="n" s="2">
-        <v>46051.0</v>
+        <v>46044.0</v>
       </c>
       <c r="D277" t="n">
-        <v>10.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="278">
@@ -4020,10 +4020,10 @@
         <v>2026.0</v>
       </c>
       <c r="C278" t="n" s="2">
-        <v>46058.0</v>
+        <v>46051.0</v>
       </c>
       <c r="D278" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="279">
@@ -4034,10 +4034,10 @@
         <v>2026.0</v>
       </c>
       <c r="C279" t="n" s="2">
-        <v>46065.0</v>
+        <v>46058.0</v>
       </c>
       <c r="D279" t="n">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="280">
@@ -4048,10 +4048,10 @@
         <v>2026.0</v>
       </c>
       <c r="C280" t="n" s="2">
-        <v>46072.0</v>
+        <v>46065.0</v>
       </c>
       <c r="D280" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="281">
@@ -4062,10 +4062,10 @@
         <v>2026.0</v>
       </c>
       <c r="C281" t="n" s="2">
-        <v>46079.0</v>
+        <v>46072.0</v>
       </c>
       <c r="D281" t="n">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="282">
@@ -4076,10 +4076,10 @@
         <v>2026.0</v>
       </c>
       <c r="C282" t="n" s="2">
-        <v>46086.0</v>
+        <v>46079.0</v>
       </c>
       <c r="D282" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="283">
@@ -4090,7 +4090,7 @@
         <v>2026.0</v>
       </c>
       <c r="C283" t="n" s="2">
-        <v>46093.0</v>
+        <v>46086.0</v>
       </c>
       <c r="D283" t="n">
         <v>2.0</v>
@@ -4104,38 +4104,38 @@
         <v>2026.0</v>
       </c>
       <c r="C284" t="n" s="2">
-        <v>46100.0</v>
+        <v>46093.0</v>
       </c>
       <c r="D284" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B285" t="n">
-        <v>2023.0</v>
+        <v>2026.0</v>
       </c>
       <c r="C285" t="n" s="2">
-        <v>45095.0</v>
+        <v>46100.0</v>
       </c>
       <c r="D285" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B286" t="n">
-        <v>2023.0</v>
+        <v>2026.0</v>
       </c>
       <c r="C286" t="n" s="2">
-        <v>45102.0</v>
+        <v>46107.0</v>
       </c>
       <c r="D286" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="287">
@@ -4146,7 +4146,7 @@
         <v>2023.0</v>
       </c>
       <c r="C287" t="n" s="2">
-        <v>45158.0</v>
+        <v>45095.0</v>
       </c>
       <c r="D287" t="n">
         <v>1.0</v>
@@ -4160,10 +4160,10 @@
         <v>2023.0</v>
       </c>
       <c r="C288" t="n" s="2">
-        <v>45207.0</v>
+        <v>45102.0</v>
       </c>
       <c r="D288" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="289">
@@ -4174,10 +4174,10 @@
         <v>2023.0</v>
       </c>
       <c r="C289" t="n" s="2">
-        <v>45214.0</v>
+        <v>45158.0</v>
       </c>
       <c r="D289" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="290">
@@ -4188,10 +4188,10 @@
         <v>2023.0</v>
       </c>
       <c r="C290" t="n" s="2">
-        <v>45221.0</v>
+        <v>45207.0</v>
       </c>
       <c r="D290" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="291">
@@ -4202,10 +4202,10 @@
         <v>2023.0</v>
       </c>
       <c r="C291" t="n" s="2">
-        <v>45249.0</v>
+        <v>45214.0</v>
       </c>
       <c r="D291" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="292">
@@ -4216,10 +4216,10 @@
         <v>2023.0</v>
       </c>
       <c r="C292" t="n" s="2">
-        <v>45256.0</v>
+        <v>45221.0</v>
       </c>
       <c r="D292" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="293">
@@ -4230,10 +4230,10 @@
         <v>2023.0</v>
       </c>
       <c r="C293" t="n" s="2">
-        <v>45263.0</v>
+        <v>45249.0</v>
       </c>
       <c r="D293" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="294">
@@ -4244,10 +4244,10 @@
         <v>2023.0</v>
       </c>
       <c r="C294" t="n" s="2">
-        <v>45270.0</v>
+        <v>45256.0</v>
       </c>
       <c r="D294" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="295">
@@ -4258,7 +4258,7 @@
         <v>2023.0</v>
       </c>
       <c r="C295" t="n" s="2">
-        <v>45277.0</v>
+        <v>45263.0</v>
       </c>
       <c r="D295" t="n">
         <v>4.0</v>
@@ -4272,7 +4272,7 @@
         <v>2023.0</v>
       </c>
       <c r="C296" t="n" s="2">
-        <v>45284.0</v>
+        <v>45270.0</v>
       </c>
       <c r="D296" t="n">
         <v>1.0</v>
@@ -4286,10 +4286,10 @@
         <v>2023.0</v>
       </c>
       <c r="C297" t="n" s="2">
-        <v>45291.0</v>
+        <v>45277.0</v>
       </c>
       <c r="D297" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="298">
@@ -4297,13 +4297,13 @@
         <v>6</v>
       </c>
       <c r="B298" t="n">
-        <v>2024.0</v>
+        <v>2023.0</v>
       </c>
       <c r="C298" t="n" s="2">
-        <v>45306.0</v>
+        <v>45284.0</v>
       </c>
       <c r="D298" t="n">
-        <v>7.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="299">
@@ -4311,13 +4311,13 @@
         <v>6</v>
       </c>
       <c r="B299" t="n">
-        <v>2024.0</v>
+        <v>2023.0</v>
       </c>
       <c r="C299" t="n" s="2">
-        <v>45313.0</v>
+        <v>45291.0</v>
       </c>
       <c r="D299" t="n">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="300">
@@ -4328,10 +4328,10 @@
         <v>2024.0</v>
       </c>
       <c r="C300" t="n" s="2">
-        <v>45320.0</v>
+        <v>45306.0</v>
       </c>
       <c r="D300" t="n">
-        <v>19.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="301">
@@ -4342,10 +4342,10 @@
         <v>2024.0</v>
       </c>
       <c r="C301" t="n" s="2">
-        <v>45327.0</v>
+        <v>45313.0</v>
       </c>
       <c r="D301" t="n">
-        <v>18.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="302">
@@ -4356,10 +4356,10 @@
         <v>2024.0</v>
       </c>
       <c r="C302" t="n" s="2">
-        <v>45334.0</v>
+        <v>45320.0</v>
       </c>
       <c r="D302" t="n">
-        <v>9.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="303">
@@ -4370,10 +4370,10 @@
         <v>2024.0</v>
       </c>
       <c r="C303" t="n" s="2">
-        <v>45341.0</v>
+        <v>45327.0</v>
       </c>
       <c r="D303" t="n">
-        <v>12.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="304">
@@ -4384,10 +4384,10 @@
         <v>2024.0</v>
       </c>
       <c r="C304" t="n" s="2">
-        <v>45348.0</v>
+        <v>45334.0</v>
       </c>
       <c r="D304" t="n">
-        <v>12.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="305">
@@ -4398,10 +4398,10 @@
         <v>2024.0</v>
       </c>
       <c r="C305" t="n" s="2">
-        <v>45355.0</v>
+        <v>45341.0</v>
       </c>
       <c r="D305" t="n">
-        <v>10.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="306">
@@ -4412,7 +4412,7 @@
         <v>2024.0</v>
       </c>
       <c r="C306" t="n" s="2">
-        <v>45362.0</v>
+        <v>45348.0</v>
       </c>
       <c r="D306" t="n">
         <v>12.0</v>
@@ -4426,10 +4426,10 @@
         <v>2024.0</v>
       </c>
       <c r="C307" t="n" s="2">
-        <v>45369.0</v>
+        <v>45355.0</v>
       </c>
       <c r="D307" t="n">
-        <v>13.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="308">
@@ -4440,10 +4440,10 @@
         <v>2024.0</v>
       </c>
       <c r="C308" t="n" s="2">
-        <v>45376.0</v>
+        <v>45362.0</v>
       </c>
       <c r="D308" t="n">
-        <v>18.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="309">
@@ -4454,10 +4454,10 @@
         <v>2024.0</v>
       </c>
       <c r="C309" t="n" s="2">
-        <v>45383.0</v>
+        <v>45369.0</v>
       </c>
       <c r="D309" t="n">
-        <v>12.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="310">
@@ -4468,10 +4468,10 @@
         <v>2024.0</v>
       </c>
       <c r="C310" t="n" s="2">
-        <v>45390.0</v>
+        <v>45376.0</v>
       </c>
       <c r="D310" t="n">
-        <v>6.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="311">
@@ -4482,10 +4482,10 @@
         <v>2024.0</v>
       </c>
       <c r="C311" t="n" s="2">
-        <v>45397.0</v>
+        <v>45383.0</v>
       </c>
       <c r="D311" t="n">
-        <v>10.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="312">
@@ -4496,10 +4496,10 @@
         <v>2024.0</v>
       </c>
       <c r="C312" t="n" s="2">
-        <v>45404.0</v>
+        <v>45390.0</v>
       </c>
       <c r="D312" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="313">
@@ -4510,10 +4510,10 @@
         <v>2024.0</v>
       </c>
       <c r="C313" t="n" s="2">
-        <v>45411.0</v>
+        <v>45397.0</v>
       </c>
       <c r="D313" t="n">
-        <v>2.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="314">
@@ -4524,10 +4524,10 @@
         <v>2024.0</v>
       </c>
       <c r="C314" t="n" s="2">
-        <v>45418.0</v>
+        <v>45404.0</v>
       </c>
       <c r="D314" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="315">
@@ -4538,10 +4538,10 @@
         <v>2024.0</v>
       </c>
       <c r="C315" t="n" s="2">
-        <v>45425.0</v>
+        <v>45411.0</v>
       </c>
       <c r="D315" t="n">
-        <v>9.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="316">
@@ -4552,10 +4552,10 @@
         <v>2024.0</v>
       </c>
       <c r="C316" t="n" s="2">
-        <v>45432.0</v>
+        <v>45418.0</v>
       </c>
       <c r="D316" t="n">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="317">
@@ -4566,10 +4566,10 @@
         <v>2024.0</v>
       </c>
       <c r="C317" t="n" s="2">
-        <v>45439.0</v>
+        <v>45425.0</v>
       </c>
       <c r="D317" t="n">
-        <v>6.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="318">
@@ -4580,10 +4580,10 @@
         <v>2024.0</v>
       </c>
       <c r="C318" t="n" s="2">
-        <v>45446.0</v>
+        <v>45432.0</v>
       </c>
       <c r="D318" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="319">
@@ -4594,10 +4594,10 @@
         <v>2024.0</v>
       </c>
       <c r="C319" t="n" s="2">
-        <v>45453.0</v>
+        <v>45439.0</v>
       </c>
       <c r="D319" t="n">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="320">
@@ -4608,10 +4608,10 @@
         <v>2024.0</v>
       </c>
       <c r="C320" t="n" s="2">
-        <v>45460.0</v>
+        <v>45446.0</v>
       </c>
       <c r="D320" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="321">
@@ -4622,7 +4622,7 @@
         <v>2024.0</v>
       </c>
       <c r="C321" t="n" s="2">
-        <v>45467.0</v>
+        <v>45453.0</v>
       </c>
       <c r="D321" t="n">
         <v>4.0</v>
@@ -4636,10 +4636,10 @@
         <v>2024.0</v>
       </c>
       <c r="C322" t="n" s="2">
-        <v>45474.0</v>
+        <v>45460.0</v>
       </c>
       <c r="D322" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="323">
@@ -4650,10 +4650,10 @@
         <v>2024.0</v>
       </c>
       <c r="C323" t="n" s="2">
-        <v>45481.0</v>
+        <v>45467.0</v>
       </c>
       <c r="D323" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="324">
@@ -4664,7 +4664,7 @@
         <v>2024.0</v>
       </c>
       <c r="C324" t="n" s="2">
-        <v>45488.0</v>
+        <v>45474.0</v>
       </c>
       <c r="D324" t="n">
         <v>2.0</v>
@@ -4678,10 +4678,10 @@
         <v>2024.0</v>
       </c>
       <c r="C325" t="n" s="2">
-        <v>45495.0</v>
+        <v>45481.0</v>
       </c>
       <c r="D325" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="326">
@@ -4692,7 +4692,7 @@
         <v>2024.0</v>
       </c>
       <c r="C326" t="n" s="2">
-        <v>45502.0</v>
+        <v>45488.0</v>
       </c>
       <c r="D326" t="n">
         <v>2.0</v>
@@ -4706,10 +4706,10 @@
         <v>2024.0</v>
       </c>
       <c r="C327" t="n" s="2">
-        <v>45509.0</v>
+        <v>45495.0</v>
       </c>
       <c r="D327" t="n">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="328">
@@ -4720,10 +4720,10 @@
         <v>2024.0</v>
       </c>
       <c r="C328" t="n" s="2">
-        <v>45523.0</v>
+        <v>45502.0</v>
       </c>
       <c r="D328" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="329">
@@ -4734,7 +4734,7 @@
         <v>2024.0</v>
       </c>
       <c r="C329" t="n" s="2">
-        <v>45551.0</v>
+        <v>45509.0</v>
       </c>
       <c r="D329" t="n">
         <v>1.0</v>
@@ -4748,7 +4748,7 @@
         <v>2024.0</v>
       </c>
       <c r="C330" t="n" s="2">
-        <v>45558.0</v>
+        <v>45523.0</v>
       </c>
       <c r="D330" t="n">
         <v>1.0</v>
@@ -4762,10 +4762,10 @@
         <v>2024.0</v>
       </c>
       <c r="C331" t="n" s="2">
-        <v>45572.0</v>
+        <v>45551.0</v>
       </c>
       <c r="D331" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="332">
@@ -4776,7 +4776,7 @@
         <v>2024.0</v>
       </c>
       <c r="C332" t="n" s="2">
-        <v>45593.0</v>
+        <v>45558.0</v>
       </c>
       <c r="D332" t="n">
         <v>1.0</v>
@@ -4790,7 +4790,7 @@
         <v>2024.0</v>
       </c>
       <c r="C333" t="n" s="2">
-        <v>45614.0</v>
+        <v>45572.0</v>
       </c>
       <c r="D333" t="n">
         <v>2.0</v>
@@ -4804,7 +4804,7 @@
         <v>2024.0</v>
       </c>
       <c r="C334" t="n" s="2">
-        <v>45621.0</v>
+        <v>45593.0</v>
       </c>
       <c r="D334" t="n">
         <v>1.0</v>
@@ -4818,10 +4818,10 @@
         <v>2024.0</v>
       </c>
       <c r="C335" t="n" s="2">
-        <v>45635.0</v>
+        <v>45614.0</v>
       </c>
       <c r="D335" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="336">
@@ -4832,7 +4832,7 @@
         <v>2024.0</v>
       </c>
       <c r="C336" t="n" s="2">
-        <v>45649.0</v>
+        <v>45621.0</v>
       </c>
       <c r="D336" t="n">
         <v>1.0</v>
@@ -4843,13 +4843,13 @@
         <v>6</v>
       </c>
       <c r="B337" t="n">
-        <v>2025.0</v>
+        <v>2024.0</v>
       </c>
       <c r="C337" t="n" s="2">
-        <v>45665.0</v>
+        <v>45635.0</v>
       </c>
       <c r="D337" t="n">
-        <v>9.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="338">
@@ -4857,13 +4857,13 @@
         <v>6</v>
       </c>
       <c r="B338" t="n">
-        <v>2025.0</v>
+        <v>2024.0</v>
       </c>
       <c r="C338" t="n" s="2">
-        <v>45672.0</v>
+        <v>45649.0</v>
       </c>
       <c r="D338" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="339">
@@ -4874,10 +4874,10 @@
         <v>2025.0</v>
       </c>
       <c r="C339" t="n" s="2">
-        <v>45679.0</v>
+        <v>45665.0</v>
       </c>
       <c r="D339" t="n">
-        <v>1.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="340">
@@ -4888,10 +4888,10 @@
         <v>2025.0</v>
       </c>
       <c r="C340" t="n" s="2">
-        <v>45686.0</v>
+        <v>45672.0</v>
       </c>
       <c r="D340" t="n">
-        <v>8.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="341">
@@ -4902,10 +4902,10 @@
         <v>2025.0</v>
       </c>
       <c r="C341" t="n" s="2">
-        <v>45693.0</v>
+        <v>45679.0</v>
       </c>
       <c r="D341" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="342">
@@ -4916,10 +4916,10 @@
         <v>2025.0</v>
       </c>
       <c r="C342" t="n" s="2">
-        <v>45700.0</v>
+        <v>45686.0</v>
       </c>
       <c r="D342" t="n">
-        <v>5.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="343">
@@ -4930,10 +4930,10 @@
         <v>2025.0</v>
       </c>
       <c r="C343" t="n" s="2">
-        <v>45707.0</v>
+        <v>45693.0</v>
       </c>
       <c r="D343" t="n">
-        <v>8.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="344">
@@ -4944,10 +4944,10 @@
         <v>2025.0</v>
       </c>
       <c r="C344" t="n" s="2">
-        <v>45714.0</v>
+        <v>45700.0</v>
       </c>
       <c r="D344" t="n">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="345">
@@ -4958,7 +4958,7 @@
         <v>2025.0</v>
       </c>
       <c r="C345" t="n" s="2">
-        <v>45721.0</v>
+        <v>45707.0</v>
       </c>
       <c r="D345" t="n">
         <v>8.0</v>
@@ -4972,10 +4972,10 @@
         <v>2025.0</v>
       </c>
       <c r="C346" t="n" s="2">
-        <v>45728.0</v>
+        <v>45714.0</v>
       </c>
       <c r="D346" t="n">
-        <v>7.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="347">
@@ -4986,10 +4986,10 @@
         <v>2025.0</v>
       </c>
       <c r="C347" t="n" s="2">
-        <v>45735.0</v>
+        <v>45721.0</v>
       </c>
       <c r="D347" t="n">
-        <v>4.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="348">
@@ -5000,10 +5000,10 @@
         <v>2025.0</v>
       </c>
       <c r="C348" t="n" s="2">
-        <v>45742.0</v>
+        <v>45728.0</v>
       </c>
       <c r="D348" t="n">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="349">
@@ -5014,10 +5014,10 @@
         <v>2025.0</v>
       </c>
       <c r="C349" t="n" s="2">
-        <v>45749.0</v>
+        <v>45735.0</v>
       </c>
       <c r="D349" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="350">
@@ -5028,10 +5028,10 @@
         <v>2025.0</v>
       </c>
       <c r="C350" t="n" s="2">
-        <v>45756.0</v>
+        <v>45742.0</v>
       </c>
       <c r="D350" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="351">
@@ -5042,10 +5042,10 @@
         <v>2025.0</v>
       </c>
       <c r="C351" t="n" s="2">
-        <v>45763.0</v>
+        <v>45749.0</v>
       </c>
       <c r="D351" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="352">
@@ -5056,10 +5056,10 @@
         <v>2025.0</v>
       </c>
       <c r="C352" t="n" s="2">
-        <v>45770.0</v>
+        <v>45756.0</v>
       </c>
       <c r="D352" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="353">
@@ -5070,10 +5070,10 @@
         <v>2025.0</v>
       </c>
       <c r="C353" t="n" s="2">
-        <v>45777.0</v>
+        <v>45763.0</v>
       </c>
       <c r="D353" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="354">
@@ -5084,10 +5084,10 @@
         <v>2025.0</v>
       </c>
       <c r="C354" t="n" s="2">
-        <v>45784.0</v>
+        <v>45770.0</v>
       </c>
       <c r="D354" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="355">
@@ -5098,7 +5098,7 @@
         <v>2025.0</v>
       </c>
       <c r="C355" t="n" s="2">
-        <v>45791.0</v>
+        <v>45777.0</v>
       </c>
       <c r="D355" t="n">
         <v>1.0</v>
@@ -5112,7 +5112,7 @@
         <v>2025.0</v>
       </c>
       <c r="C356" t="n" s="2">
-        <v>45840.0</v>
+        <v>45784.0</v>
       </c>
       <c r="D356" t="n">
         <v>1.0</v>
@@ -5126,7 +5126,7 @@
         <v>2025.0</v>
       </c>
       <c r="C357" t="n" s="2">
-        <v>46001.0</v>
+        <v>45791.0</v>
       </c>
       <c r="D357" t="n">
         <v>1.0</v>
@@ -5137,10 +5137,10 @@
         <v>6</v>
       </c>
       <c r="B358" t="n">
-        <v>2026.0</v>
+        <v>2025.0</v>
       </c>
       <c r="C358" t="n" s="2">
-        <v>46037.0</v>
+        <v>45840.0</v>
       </c>
       <c r="D358" t="n">
         <v>1.0</v>
@@ -5148,13 +5148,13 @@
     </row>
     <row r="359">
       <c r="A359" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B359" t="n">
-        <v>2021.0</v>
+        <v>2025.0</v>
       </c>
       <c r="C359" t="n" s="2">
-        <v>44561.0</v>
+        <v>46001.0</v>
       </c>
       <c r="D359" t="n">
         <v>1.0</v>
@@ -5162,13 +5162,13 @@
     </row>
     <row r="360">
       <c r="A360" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B360" t="n">
-        <v>2022.0</v>
+        <v>2026.0</v>
       </c>
       <c r="C360" t="n" s="2">
-        <v>44569.0</v>
+        <v>46037.0</v>
       </c>
       <c r="D360" t="n">
         <v>1.0</v>
@@ -5179,13 +5179,13 @@
         <v>7</v>
       </c>
       <c r="B361" t="n">
-        <v>2022.0</v>
+        <v>2021.0</v>
       </c>
       <c r="C361" t="n" s="2">
-        <v>44576.0</v>
+        <v>44561.0</v>
       </c>
       <c r="D361" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="362">
@@ -5196,10 +5196,10 @@
         <v>2022.0</v>
       </c>
       <c r="C362" t="n" s="2">
-        <v>44583.0</v>
+        <v>44569.0</v>
       </c>
       <c r="D362" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="363">
@@ -5210,10 +5210,10 @@
         <v>2022.0</v>
       </c>
       <c r="C363" t="n" s="2">
-        <v>44590.0</v>
+        <v>44576.0</v>
       </c>
       <c r="D363" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="364">
@@ -5224,10 +5224,10 @@
         <v>2022.0</v>
       </c>
       <c r="C364" t="n" s="2">
-        <v>44604.0</v>
+        <v>44583.0</v>
       </c>
       <c r="D364" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="365">
@@ -5238,10 +5238,10 @@
         <v>2022.0</v>
       </c>
       <c r="C365" t="n" s="2">
-        <v>44611.0</v>
+        <v>44590.0</v>
       </c>
       <c r="D365" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="366">
@@ -5252,10 +5252,10 @@
         <v>2022.0</v>
       </c>
       <c r="C366" t="n" s="2">
-        <v>44618.0</v>
+        <v>44604.0</v>
       </c>
       <c r="D366" t="n">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="367">
@@ -5266,10 +5266,10 @@
         <v>2022.0</v>
       </c>
       <c r="C367" t="n" s="2">
-        <v>44625.0</v>
+        <v>44611.0</v>
       </c>
       <c r="D367" t="n">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="368">
@@ -5280,10 +5280,10 @@
         <v>2022.0</v>
       </c>
       <c r="C368" t="n" s="2">
-        <v>44632.0</v>
+        <v>44618.0</v>
       </c>
       <c r="D368" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="369">
@@ -5294,10 +5294,10 @@
         <v>2022.0</v>
       </c>
       <c r="C369" t="n" s="2">
-        <v>44639.0</v>
+        <v>44625.0</v>
       </c>
       <c r="D369" t="n">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="370">
@@ -5308,7 +5308,7 @@
         <v>2022.0</v>
       </c>
       <c r="C370" t="n" s="2">
-        <v>44646.0</v>
+        <v>44632.0</v>
       </c>
       <c r="D370" t="n">
         <v>3.0</v>
@@ -5322,10 +5322,10 @@
         <v>2022.0</v>
       </c>
       <c r="C371" t="n" s="2">
-        <v>44653.0</v>
+        <v>44639.0</v>
       </c>
       <c r="D371" t="n">
-        <v>9.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="372">
@@ -5336,10 +5336,10 @@
         <v>2022.0</v>
       </c>
       <c r="C372" t="n" s="2">
-        <v>44660.0</v>
+        <v>44646.0</v>
       </c>
       <c r="D372" t="n">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="373">
@@ -5350,10 +5350,10 @@
         <v>2022.0</v>
       </c>
       <c r="C373" t="n" s="2">
-        <v>44667.0</v>
+        <v>44653.0</v>
       </c>
       <c r="D373" t="n">
-        <v>2.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="374">
@@ -5364,10 +5364,10 @@
         <v>2022.0</v>
       </c>
       <c r="C374" t="n" s="2">
-        <v>44674.0</v>
+        <v>44660.0</v>
       </c>
       <c r="D374" t="n">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="375">
@@ -5378,7 +5378,7 @@
         <v>2022.0</v>
       </c>
       <c r="C375" t="n" s="2">
-        <v>44681.0</v>
+        <v>44667.0</v>
       </c>
       <c r="D375" t="n">
         <v>2.0</v>
@@ -5392,10 +5392,10 @@
         <v>2022.0</v>
       </c>
       <c r="C376" t="n" s="2">
-        <v>44688.0</v>
+        <v>44674.0</v>
       </c>
       <c r="D376" t="n">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="377">
@@ -5406,10 +5406,10 @@
         <v>2022.0</v>
       </c>
       <c r="C377" t="n" s="2">
-        <v>44695.0</v>
+        <v>44681.0</v>
       </c>
       <c r="D377" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="378">
@@ -5420,10 +5420,10 @@
         <v>2022.0</v>
       </c>
       <c r="C378" t="n" s="2">
-        <v>44702.0</v>
+        <v>44688.0</v>
       </c>
       <c r="D378" t="n">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="379">
@@ -5434,10 +5434,10 @@
         <v>2022.0</v>
       </c>
       <c r="C379" t="n" s="2">
-        <v>44709.0</v>
+        <v>44695.0</v>
       </c>
       <c r="D379" t="n">
-        <v>8.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="380">
@@ -5448,10 +5448,10 @@
         <v>2022.0</v>
       </c>
       <c r="C380" t="n" s="2">
-        <v>44716.0</v>
+        <v>44702.0</v>
       </c>
       <c r="D380" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="381">
@@ -5462,10 +5462,10 @@
         <v>2022.0</v>
       </c>
       <c r="C381" t="n" s="2">
-        <v>44723.0</v>
+        <v>44709.0</v>
       </c>
       <c r="D381" t="n">
-        <v>2.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="382">
@@ -5476,10 +5476,10 @@
         <v>2022.0</v>
       </c>
       <c r="C382" t="n" s="2">
-        <v>44730.0</v>
+        <v>44716.0</v>
       </c>
       <c r="D382" t="n">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="383">
@@ -5490,10 +5490,10 @@
         <v>2022.0</v>
       </c>
       <c r="C383" t="n" s="2">
-        <v>44737.0</v>
+        <v>44723.0</v>
       </c>
       <c r="D383" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="384">
@@ -5504,10 +5504,10 @@
         <v>2022.0</v>
       </c>
       <c r="C384" t="n" s="2">
-        <v>44744.0</v>
+        <v>44730.0</v>
       </c>
       <c r="D384" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="385">
@@ -5518,7 +5518,7 @@
         <v>2022.0</v>
       </c>
       <c r="C385" t="n" s="2">
-        <v>44751.0</v>
+        <v>44737.0</v>
       </c>
       <c r="D385" t="n">
         <v>4.0</v>
@@ -5532,10 +5532,10 @@
         <v>2022.0</v>
       </c>
       <c r="C386" t="n" s="2">
-        <v>44758.0</v>
+        <v>44744.0</v>
       </c>
       <c r="D386" t="n">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="387">
@@ -5546,10 +5546,10 @@
         <v>2022.0</v>
       </c>
       <c r="C387" t="n" s="2">
-        <v>44765.0</v>
+        <v>44751.0</v>
       </c>
       <c r="D387" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="388">
@@ -5560,10 +5560,10 @@
         <v>2022.0</v>
       </c>
       <c r="C388" t="n" s="2">
-        <v>44779.0</v>
+        <v>44758.0</v>
       </c>
       <c r="D388" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="389">
@@ -5574,7 +5574,7 @@
         <v>2022.0</v>
       </c>
       <c r="C389" t="n" s="2">
-        <v>44786.0</v>
+        <v>44765.0</v>
       </c>
       <c r="D389" t="n">
         <v>1.0</v>
@@ -5588,10 +5588,10 @@
         <v>2022.0</v>
       </c>
       <c r="C390" t="n" s="2">
-        <v>44863.0</v>
+        <v>44779.0</v>
       </c>
       <c r="D390" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="391">
@@ -5602,7 +5602,7 @@
         <v>2022.0</v>
       </c>
       <c r="C391" t="n" s="2">
-        <v>44870.0</v>
+        <v>44786.0</v>
       </c>
       <c r="D391" t="n">
         <v>1.0</v>
@@ -5616,7 +5616,7 @@
         <v>2022.0</v>
       </c>
       <c r="C392" t="n" s="2">
-        <v>44884.0</v>
+        <v>44863.0</v>
       </c>
       <c r="D392" t="n">
         <v>2.0</v>
@@ -5630,10 +5630,10 @@
         <v>2022.0</v>
       </c>
       <c r="C393" t="n" s="2">
-        <v>44891.0</v>
+        <v>44870.0</v>
       </c>
       <c r="D393" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="394">
@@ -5644,10 +5644,10 @@
         <v>2022.0</v>
       </c>
       <c r="C394" t="n" s="2">
-        <v>44898.0</v>
+        <v>44884.0</v>
       </c>
       <c r="D394" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="395">
@@ -5658,10 +5658,10 @@
         <v>2022.0</v>
       </c>
       <c r="C395" t="n" s="2">
-        <v>44912.0</v>
+        <v>44891.0</v>
       </c>
       <c r="D395" t="n">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="396">
@@ -5672,10 +5672,10 @@
         <v>2022.0</v>
       </c>
       <c r="C396" t="n" s="2">
-        <v>44919.0</v>
+        <v>44898.0</v>
       </c>
       <c r="D396" t="n">
-        <v>7.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="397">
@@ -5686,10 +5686,10 @@
         <v>2022.0</v>
       </c>
       <c r="C397" t="n" s="2">
-        <v>44926.0</v>
+        <v>44912.0</v>
       </c>
       <c r="D397" t="n">
-        <v>12.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="398">
@@ -5697,13 +5697,13 @@
         <v>7</v>
       </c>
       <c r="B398" t="n">
-        <v>2023.0</v>
+        <v>2022.0</v>
       </c>
       <c r="C398" t="n" s="2">
-        <v>44934.0</v>
+        <v>44919.0</v>
       </c>
       <c r="D398" t="n">
-        <v>4.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="399">
@@ -5711,13 +5711,13 @@
         <v>7</v>
       </c>
       <c r="B399" t="n">
-        <v>2023.0</v>
+        <v>2022.0</v>
       </c>
       <c r="C399" t="n" s="2">
-        <v>44941.0</v>
+        <v>44926.0</v>
       </c>
       <c r="D399" t="n">
-        <v>16.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="400">
@@ -5728,10 +5728,10 @@
         <v>2023.0</v>
       </c>
       <c r="C400" t="n" s="2">
-        <v>44948.0</v>
+        <v>44934.0</v>
       </c>
       <c r="D400" t="n">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="401">
@@ -5742,10 +5742,10 @@
         <v>2023.0</v>
       </c>
       <c r="C401" t="n" s="2">
-        <v>44955.0</v>
+        <v>44941.0</v>
       </c>
       <c r="D401" t="n">
-        <v>19.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="402">
@@ -5756,10 +5756,10 @@
         <v>2023.0</v>
       </c>
       <c r="C402" t="n" s="2">
-        <v>44962.0</v>
+        <v>44948.0</v>
       </c>
       <c r="D402" t="n">
-        <v>22.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="403">
@@ -5770,10 +5770,10 @@
         <v>2023.0</v>
       </c>
       <c r="C403" t="n" s="2">
-        <v>44969.0</v>
+        <v>44955.0</v>
       </c>
       <c r="D403" t="n">
-        <v>9.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="404">
@@ -5784,7 +5784,7 @@
         <v>2023.0</v>
       </c>
       <c r="C404" t="n" s="2">
-        <v>44976.0</v>
+        <v>44962.0</v>
       </c>
       <c r="D404" t="n">
         <v>22.0</v>
@@ -5798,10 +5798,10 @@
         <v>2023.0</v>
       </c>
       <c r="C405" t="n" s="2">
-        <v>44983.0</v>
+        <v>44969.0</v>
       </c>
       <c r="D405" t="n">
-        <v>29.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="406">
@@ -5812,10 +5812,10 @@
         <v>2023.0</v>
       </c>
       <c r="C406" t="n" s="2">
-        <v>44990.0</v>
+        <v>44976.0</v>
       </c>
       <c r="D406" t="n">
-        <v>5.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="407">
@@ -5826,10 +5826,10 @@
         <v>2023.0</v>
       </c>
       <c r="C407" t="n" s="2">
-        <v>44997.0</v>
+        <v>44983.0</v>
       </c>
       <c r="D407" t="n">
-        <v>24.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="408">
@@ -5840,10 +5840,10 @@
         <v>2023.0</v>
       </c>
       <c r="C408" t="n" s="2">
-        <v>45004.0</v>
+        <v>44990.0</v>
       </c>
       <c r="D408" t="n">
-        <v>8.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="409">
@@ -5854,10 +5854,10 @@
         <v>2023.0</v>
       </c>
       <c r="C409" t="n" s="2">
-        <v>45011.0</v>
+        <v>44997.0</v>
       </c>
       <c r="D409" t="n">
-        <v>10.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="410">
@@ -5868,10 +5868,10 @@
         <v>2023.0</v>
       </c>
       <c r="C410" t="n" s="2">
-        <v>45018.0</v>
+        <v>45004.0</v>
       </c>
       <c r="D410" t="n">
-        <v>18.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="411">
@@ -5882,10 +5882,10 @@
         <v>2023.0</v>
       </c>
       <c r="C411" t="n" s="2">
-        <v>45025.0</v>
+        <v>45011.0</v>
       </c>
       <c r="D411" t="n">
-        <v>13.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="412">
@@ -5896,7 +5896,7 @@
         <v>2023.0</v>
       </c>
       <c r="C412" t="n" s="2">
-        <v>45032.0</v>
+        <v>45018.0</v>
       </c>
       <c r="D412" t="n">
         <v>18.0</v>
@@ -5910,10 +5910,10 @@
         <v>2023.0</v>
       </c>
       <c r="C413" t="n" s="2">
-        <v>45039.0</v>
+        <v>45025.0</v>
       </c>
       <c r="D413" t="n">
-        <v>15.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="414">
@@ -5924,10 +5924,10 @@
         <v>2023.0</v>
       </c>
       <c r="C414" t="n" s="2">
-        <v>45046.0</v>
+        <v>45032.0</v>
       </c>
       <c r="D414" t="n">
-        <v>12.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="415">
@@ -5938,10 +5938,10 @@
         <v>2023.0</v>
       </c>
       <c r="C415" t="n" s="2">
-        <v>45053.0</v>
+        <v>45039.0</v>
       </c>
       <c r="D415" t="n">
-        <v>6.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="416">
@@ -5952,10 +5952,10 @@
         <v>2023.0</v>
       </c>
       <c r="C416" t="n" s="2">
-        <v>45060.0</v>
+        <v>45046.0</v>
       </c>
       <c r="D416" t="n">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="417">
@@ -5966,10 +5966,10 @@
         <v>2023.0</v>
       </c>
       <c r="C417" t="n" s="2">
-        <v>45067.0</v>
+        <v>45053.0</v>
       </c>
       <c r="D417" t="n">
-        <v>8.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="418">
@@ -5980,10 +5980,10 @@
         <v>2023.0</v>
       </c>
       <c r="C418" t="n" s="2">
-        <v>45074.0</v>
+        <v>45060.0</v>
       </c>
       <c r="D418" t="n">
-        <v>8.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="419">
@@ -5994,10 +5994,10 @@
         <v>2023.0</v>
       </c>
       <c r="C419" t="n" s="2">
-        <v>45081.0</v>
+        <v>45067.0</v>
       </c>
       <c r="D419" t="n">
-        <v>5.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="420">
@@ -6008,10 +6008,10 @@
         <v>2023.0</v>
       </c>
       <c r="C420" t="n" s="2">
-        <v>45088.0</v>
+        <v>45074.0</v>
       </c>
       <c r="D420" t="n">
-        <v>2.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="421">
@@ -6022,7 +6022,7 @@
         <v>2023.0</v>
       </c>
       <c r="C421" t="n" s="2">
-        <v>45095.0</v>
+        <v>45081.0</v>
       </c>
       <c r="D421" t="n">
         <v>5.0</v>
@@ -6036,10 +6036,10 @@
         <v>2023.0</v>
       </c>
       <c r="C422" t="n" s="2">
-        <v>45102.0</v>
+        <v>45088.0</v>
       </c>
       <c r="D422" t="n">
-        <v>10.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="423">
@@ -6050,10 +6050,10 @@
         <v>2023.0</v>
       </c>
       <c r="C423" t="n" s="2">
-        <v>45109.0</v>
+        <v>45095.0</v>
       </c>
       <c r="D423" t="n">
-        <v>9.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="424">
@@ -6064,10 +6064,10 @@
         <v>2023.0</v>
       </c>
       <c r="C424" t="n" s="2">
-        <v>45116.0</v>
+        <v>45102.0</v>
       </c>
       <c r="D424" t="n">
-        <v>3.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="425">
@@ -6078,10 +6078,10 @@
         <v>2023.0</v>
       </c>
       <c r="C425" t="n" s="2">
-        <v>45123.0</v>
+        <v>45109.0</v>
       </c>
       <c r="D425" t="n">
-        <v>6.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="426">
@@ -6092,10 +6092,10 @@
         <v>2023.0</v>
       </c>
       <c r="C426" t="n" s="2">
-        <v>45130.0</v>
+        <v>45116.0</v>
       </c>
       <c r="D426" t="n">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="427">
@@ -6106,10 +6106,10 @@
         <v>2023.0</v>
       </c>
       <c r="C427" t="n" s="2">
-        <v>45137.0</v>
+        <v>45123.0</v>
       </c>
       <c r="D427" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="428">
@@ -6120,10 +6120,10 @@
         <v>2023.0</v>
       </c>
       <c r="C428" t="n" s="2">
-        <v>45144.0</v>
+        <v>45130.0</v>
       </c>
       <c r="D428" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="429">
@@ -6134,7 +6134,7 @@
         <v>2023.0</v>
       </c>
       <c r="C429" t="n" s="2">
-        <v>45151.0</v>
+        <v>45137.0</v>
       </c>
       <c r="D429" t="n">
         <v>2.0</v>
@@ -6148,7 +6148,7 @@
         <v>2023.0</v>
       </c>
       <c r="C430" t="n" s="2">
-        <v>45165.0</v>
+        <v>45144.0</v>
       </c>
       <c r="D430" t="n">
         <v>2.0</v>
@@ -6162,7 +6162,7 @@
         <v>2023.0</v>
       </c>
       <c r="C431" t="n" s="2">
-        <v>45172.0</v>
+        <v>45151.0</v>
       </c>
       <c r="D431" t="n">
         <v>2.0</v>
@@ -6176,10 +6176,10 @@
         <v>2023.0</v>
       </c>
       <c r="C432" t="n" s="2">
-        <v>45179.0</v>
+        <v>45165.0</v>
       </c>
       <c r="D432" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="433">
@@ -6190,10 +6190,10 @@
         <v>2023.0</v>
       </c>
       <c r="C433" t="n" s="2">
-        <v>45186.0</v>
+        <v>45172.0</v>
       </c>
       <c r="D433" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="434">
@@ -6204,7 +6204,7 @@
         <v>2023.0</v>
       </c>
       <c r="C434" t="n" s="2">
-        <v>45193.0</v>
+        <v>45179.0</v>
       </c>
       <c r="D434" t="n">
         <v>1.0</v>
@@ -6218,7 +6218,7 @@
         <v>2023.0</v>
       </c>
       <c r="C435" t="n" s="2">
-        <v>45200.0</v>
+        <v>45186.0</v>
       </c>
       <c r="D435" t="n">
         <v>1.0</v>
@@ -6232,7 +6232,7 @@
         <v>2023.0</v>
       </c>
       <c r="C436" t="n" s="2">
-        <v>45207.0</v>
+        <v>45193.0</v>
       </c>
       <c r="D436" t="n">
         <v>1.0</v>
@@ -6246,7 +6246,7 @@
         <v>2023.0</v>
       </c>
       <c r="C437" t="n" s="2">
-        <v>45235.0</v>
+        <v>45200.0</v>
       </c>
       <c r="D437" t="n">
         <v>1.0</v>
@@ -6260,10 +6260,10 @@
         <v>2023.0</v>
       </c>
       <c r="C438" t="n" s="2">
-        <v>45242.0</v>
+        <v>45207.0</v>
       </c>
       <c r="D438" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="439">
@@ -6274,10 +6274,10 @@
         <v>2023.0</v>
       </c>
       <c r="C439" t="n" s="2">
-        <v>45249.0</v>
+        <v>45235.0</v>
       </c>
       <c r="D439" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="440">
@@ -6288,10 +6288,10 @@
         <v>2023.0</v>
       </c>
       <c r="C440" t="n" s="2">
-        <v>45256.0</v>
+        <v>45242.0</v>
       </c>
       <c r="D440" t="n">
-        <v>9.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="441">
@@ -6302,10 +6302,10 @@
         <v>2023.0</v>
       </c>
       <c r="C441" t="n" s="2">
-        <v>45263.0</v>
+        <v>45249.0</v>
       </c>
       <c r="D441" t="n">
-        <v>12.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="442">
@@ -6316,10 +6316,10 @@
         <v>2023.0</v>
       </c>
       <c r="C442" t="n" s="2">
-        <v>45270.0</v>
+        <v>45256.0</v>
       </c>
       <c r="D442" t="n">
-        <v>6.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="443">
@@ -6330,10 +6330,10 @@
         <v>2023.0</v>
       </c>
       <c r="C443" t="n" s="2">
-        <v>45277.0</v>
+        <v>45263.0</v>
       </c>
       <c r="D443" t="n">
-        <v>7.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="444">
@@ -6344,10 +6344,10 @@
         <v>2023.0</v>
       </c>
       <c r="C444" t="n" s="2">
-        <v>45284.0</v>
+        <v>45270.0</v>
       </c>
       <c r="D444" t="n">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="445">
@@ -6358,10 +6358,10 @@
         <v>2023.0</v>
       </c>
       <c r="C445" t="n" s="2">
-        <v>45291.0</v>
+        <v>45277.0</v>
       </c>
       <c r="D445" t="n">
-        <v>13.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="446">
@@ -6369,13 +6369,13 @@
         <v>7</v>
       </c>
       <c r="B446" t="n">
-        <v>2024.0</v>
+        <v>2023.0</v>
       </c>
       <c r="C446" t="n" s="2">
-        <v>45299.0</v>
+        <v>45284.0</v>
       </c>
       <c r="D446" t="n">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="447">
@@ -6383,13 +6383,13 @@
         <v>7</v>
       </c>
       <c r="B447" t="n">
-        <v>2024.0</v>
+        <v>2023.0</v>
       </c>
       <c r="C447" t="n" s="2">
-        <v>45306.0</v>
+        <v>45291.0</v>
       </c>
       <c r="D447" t="n">
-        <v>11.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="448">
@@ -6400,10 +6400,10 @@
         <v>2024.0</v>
       </c>
       <c r="C448" t="n" s="2">
-        <v>45313.0</v>
+        <v>45299.0</v>
       </c>
       <c r="D448" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="449">
@@ -6414,10 +6414,10 @@
         <v>2024.0</v>
       </c>
       <c r="C449" t="n" s="2">
-        <v>45320.0</v>
+        <v>45306.0</v>
       </c>
       <c r="D449" t="n">
-        <v>2.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="450">
@@ -6428,10 +6428,10 @@
         <v>2024.0</v>
       </c>
       <c r="C450" t="n" s="2">
-        <v>45327.0</v>
+        <v>45313.0</v>
       </c>
       <c r="D450" t="n">
-        <v>9.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="451">
@@ -6442,10 +6442,10 @@
         <v>2024.0</v>
       </c>
       <c r="C451" t="n" s="2">
-        <v>45334.0</v>
+        <v>45320.0</v>
       </c>
       <c r="D451" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="452">
@@ -6456,10 +6456,10 @@
         <v>2024.0</v>
       </c>
       <c r="C452" t="n" s="2">
-        <v>45341.0</v>
+        <v>45327.0</v>
       </c>
       <c r="D452" t="n">
-        <v>21.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="453">
@@ -6470,10 +6470,10 @@
         <v>2024.0</v>
       </c>
       <c r="C453" t="n" s="2">
-        <v>45348.0</v>
+        <v>45334.0</v>
       </c>
       <c r="D453" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="454">
@@ -6484,10 +6484,10 @@
         <v>2024.0</v>
       </c>
       <c r="C454" t="n" s="2">
-        <v>45355.0</v>
+        <v>45341.0</v>
       </c>
       <c r="D454" t="n">
-        <v>9.0</v>
+        <v>21.0</v>
       </c>
     </row>
     <row r="455">
@@ -6498,10 +6498,10 @@
         <v>2024.0</v>
       </c>
       <c r="C455" t="n" s="2">
-        <v>45362.0</v>
+        <v>45348.0</v>
       </c>
       <c r="D455" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="456">
@@ -6512,10 +6512,10 @@
         <v>2024.0</v>
       </c>
       <c r="C456" t="n" s="2">
-        <v>45369.0</v>
+        <v>45355.0</v>
       </c>
       <c r="D456" t="n">
-        <v>14.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="457">
@@ -6526,7 +6526,7 @@
         <v>2024.0</v>
       </c>
       <c r="C457" t="n" s="2">
-        <v>45376.0</v>
+        <v>45362.0</v>
       </c>
       <c r="D457" t="n">
         <v>4.0</v>
@@ -6540,10 +6540,10 @@
         <v>2024.0</v>
       </c>
       <c r="C458" t="n" s="2">
-        <v>45383.0</v>
+        <v>45369.0</v>
       </c>
       <c r="D458" t="n">
-        <v>2.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="459">
@@ -6554,10 +6554,10 @@
         <v>2024.0</v>
       </c>
       <c r="C459" t="n" s="2">
-        <v>45390.0</v>
+        <v>45376.0</v>
       </c>
       <c r="D459" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="460">
@@ -6568,10 +6568,10 @@
         <v>2024.0</v>
       </c>
       <c r="C460" t="n" s="2">
-        <v>45397.0</v>
+        <v>45383.0</v>
       </c>
       <c r="D460" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="461">
@@ -6582,10 +6582,10 @@
         <v>2024.0</v>
       </c>
       <c r="C461" t="n" s="2">
-        <v>45404.0</v>
+        <v>45390.0</v>
       </c>
       <c r="D461" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="462">
@@ -6596,7 +6596,7 @@
         <v>2024.0</v>
       </c>
       <c r="C462" t="n" s="2">
-        <v>45411.0</v>
+        <v>45397.0</v>
       </c>
       <c r="D462" t="n">
         <v>1.0</v>
@@ -6610,7 +6610,7 @@
         <v>2024.0</v>
       </c>
       <c r="C463" t="n" s="2">
-        <v>45439.0</v>
+        <v>45404.0</v>
       </c>
       <c r="D463" t="n">
         <v>2.0</v>
@@ -6624,7 +6624,7 @@
         <v>2024.0</v>
       </c>
       <c r="C464" t="n" s="2">
-        <v>45446.0</v>
+        <v>45411.0</v>
       </c>
       <c r="D464" t="n">
         <v>1.0</v>
@@ -6638,10 +6638,10 @@
         <v>2024.0</v>
       </c>
       <c r="C465" t="n" s="2">
-        <v>45460.0</v>
+        <v>45439.0</v>
       </c>
       <c r="D465" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="466">
@@ -6652,7 +6652,7 @@
         <v>2024.0</v>
       </c>
       <c r="C466" t="n" s="2">
-        <v>45481.0</v>
+        <v>45446.0</v>
       </c>
       <c r="D466" t="n">
         <v>1.0</v>
@@ -6666,7 +6666,7 @@
         <v>2024.0</v>
       </c>
       <c r="C467" t="n" s="2">
-        <v>45516.0</v>
+        <v>45460.0</v>
       </c>
       <c r="D467" t="n">
         <v>1.0</v>
@@ -6680,7 +6680,7 @@
         <v>2024.0</v>
       </c>
       <c r="C468" t="n" s="2">
-        <v>45551.0</v>
+        <v>45481.0</v>
       </c>
       <c r="D468" t="n">
         <v>1.0</v>
@@ -6694,7 +6694,7 @@
         <v>2024.0</v>
       </c>
       <c r="C469" t="n" s="2">
-        <v>45579.0</v>
+        <v>45516.0</v>
       </c>
       <c r="D469" t="n">
         <v>1.0</v>
@@ -6708,7 +6708,7 @@
         <v>2024.0</v>
       </c>
       <c r="C470" t="n" s="2">
-        <v>45614.0</v>
+        <v>45551.0</v>
       </c>
       <c r="D470" t="n">
         <v>1.0</v>
@@ -6722,10 +6722,10 @@
         <v>2024.0</v>
       </c>
       <c r="C471" t="n" s="2">
-        <v>45635.0</v>
+        <v>45579.0</v>
       </c>
       <c r="D471" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="472">
@@ -6736,10 +6736,10 @@
         <v>2024.0</v>
       </c>
       <c r="C472" t="n" s="2">
-        <v>45642.0</v>
+        <v>45614.0</v>
       </c>
       <c r="D472" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="473">
@@ -6750,10 +6750,10 @@
         <v>2024.0</v>
       </c>
       <c r="C473" t="n" s="2">
-        <v>45649.0</v>
+        <v>45635.0</v>
       </c>
       <c r="D473" t="n">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="474">
@@ -6764,7 +6764,7 @@
         <v>2024.0</v>
       </c>
       <c r="C474" t="n" s="2">
-        <v>45656.0</v>
+        <v>45642.0</v>
       </c>
       <c r="D474" t="n">
         <v>2.0</v>
@@ -6775,13 +6775,13 @@
         <v>7</v>
       </c>
       <c r="B475" t="n">
-        <v>2025.0</v>
+        <v>2024.0</v>
       </c>
       <c r="C475" t="n" s="2">
-        <v>45665.0</v>
+        <v>45649.0</v>
       </c>
       <c r="D475" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="476">
@@ -6789,10 +6789,10 @@
         <v>7</v>
       </c>
       <c r="B476" t="n">
-        <v>2025.0</v>
+        <v>2024.0</v>
       </c>
       <c r="C476" t="n" s="2">
-        <v>45672.0</v>
+        <v>45656.0</v>
       </c>
       <c r="D476" t="n">
         <v>2.0</v>
@@ -6806,10 +6806,10 @@
         <v>2025.0</v>
       </c>
       <c r="C477" t="n" s="2">
-        <v>45686.0</v>
+        <v>45665.0</v>
       </c>
       <c r="D477" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="478">
@@ -6820,10 +6820,10 @@
         <v>2025.0</v>
       </c>
       <c r="C478" t="n" s="2">
-        <v>45693.0</v>
+        <v>45672.0</v>
       </c>
       <c r="D478" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="479">
@@ -6834,10 +6834,10 @@
         <v>2025.0</v>
       </c>
       <c r="C479" t="n" s="2">
-        <v>45700.0</v>
+        <v>45686.0</v>
       </c>
       <c r="D479" t="n">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="480">
@@ -6848,10 +6848,10 @@
         <v>2025.0</v>
       </c>
       <c r="C480" t="n" s="2">
-        <v>45707.0</v>
+        <v>45693.0</v>
       </c>
       <c r="D480" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="481">
@@ -6862,10 +6862,10 @@
         <v>2025.0</v>
       </c>
       <c r="C481" t="n" s="2">
-        <v>45714.0</v>
+        <v>45700.0</v>
       </c>
       <c r="D481" t="n">
-        <v>8.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="482">
@@ -6876,10 +6876,10 @@
         <v>2025.0</v>
       </c>
       <c r="C482" t="n" s="2">
-        <v>45721.0</v>
+        <v>45707.0</v>
       </c>
       <c r="D482" t="n">
-        <v>11.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="483">
@@ -6890,10 +6890,10 @@
         <v>2025.0</v>
       </c>
       <c r="C483" t="n" s="2">
-        <v>45728.0</v>
+        <v>45714.0</v>
       </c>
       <c r="D483" t="n">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="484">
@@ -6904,10 +6904,10 @@
         <v>2025.0</v>
       </c>
       <c r="C484" t="n" s="2">
-        <v>45735.0</v>
+        <v>45721.0</v>
       </c>
       <c r="D484" t="n">
-        <v>19.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="485">
@@ -6918,10 +6918,10 @@
         <v>2025.0</v>
       </c>
       <c r="C485" t="n" s="2">
-        <v>45742.0</v>
+        <v>45728.0</v>
       </c>
       <c r="D485" t="n">
-        <v>17.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="486">
@@ -6932,10 +6932,10 @@
         <v>2025.0</v>
       </c>
       <c r="C486" t="n" s="2">
-        <v>45749.0</v>
+        <v>45735.0</v>
       </c>
       <c r="D486" t="n">
-        <v>5.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="487">
@@ -6946,10 +6946,10 @@
         <v>2025.0</v>
       </c>
       <c r="C487" t="n" s="2">
-        <v>45756.0</v>
+        <v>45742.0</v>
       </c>
       <c r="D487" t="n">
-        <v>9.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="488">
@@ -6960,10 +6960,10 @@
         <v>2025.0</v>
       </c>
       <c r="C488" t="n" s="2">
-        <v>45763.0</v>
+        <v>45749.0</v>
       </c>
       <c r="D488" t="n">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="489">
@@ -6974,10 +6974,10 @@
         <v>2025.0</v>
       </c>
       <c r="C489" t="n" s="2">
-        <v>45770.0</v>
+        <v>45756.0</v>
       </c>
       <c r="D489" t="n">
-        <v>1.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="490">
@@ -6988,10 +6988,10 @@
         <v>2025.0</v>
       </c>
       <c r="C490" t="n" s="2">
-        <v>45784.0</v>
+        <v>45763.0</v>
       </c>
       <c r="D490" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="491">
@@ -7002,10 +7002,10 @@
         <v>2025.0</v>
       </c>
       <c r="C491" t="n" s="2">
-        <v>45791.0</v>
+        <v>45770.0</v>
       </c>
       <c r="D491" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="492">
@@ -7016,10 +7016,10 @@
         <v>2025.0</v>
       </c>
       <c r="C492" t="n" s="2">
-        <v>45805.0</v>
+        <v>45784.0</v>
       </c>
       <c r="D492" t="n">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="493">
@@ -7030,7 +7030,7 @@
         <v>2025.0</v>
       </c>
       <c r="C493" t="n" s="2">
-        <v>45826.0</v>
+        <v>45791.0</v>
       </c>
       <c r="D493" t="n">
         <v>2.0</v>
@@ -7044,10 +7044,10 @@
         <v>2025.0</v>
       </c>
       <c r="C494" t="n" s="2">
-        <v>45861.0</v>
+        <v>45805.0</v>
       </c>
       <c r="D494" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="495">
@@ -7058,10 +7058,10 @@
         <v>2025.0</v>
       </c>
       <c r="C495" t="n" s="2">
-        <v>45868.0</v>
+        <v>45826.0</v>
       </c>
       <c r="D495" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="496">
@@ -7072,10 +7072,10 @@
         <v>2025.0</v>
       </c>
       <c r="C496" t="n" s="2">
-        <v>45889.0</v>
+        <v>45861.0</v>
       </c>
       <c r="D496" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="497">
@@ -7086,7 +7086,7 @@
         <v>2025.0</v>
       </c>
       <c r="C497" t="n" s="2">
-        <v>45924.0</v>
+        <v>45868.0</v>
       </c>
       <c r="D497" t="n">
         <v>1.0</v>
@@ -7100,7 +7100,7 @@
         <v>2025.0</v>
       </c>
       <c r="C498" t="n" s="2">
-        <v>45945.0</v>
+        <v>45889.0</v>
       </c>
       <c r="D498" t="n">
         <v>1.0</v>
@@ -7114,10 +7114,10 @@
         <v>2025.0</v>
       </c>
       <c r="C499" t="n" s="2">
-        <v>45959.0</v>
+        <v>45924.0</v>
       </c>
       <c r="D499" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="500">
@@ -7128,10 +7128,10 @@
         <v>2025.0</v>
       </c>
       <c r="C500" t="n" s="2">
-        <v>46001.0</v>
+        <v>45945.0</v>
       </c>
       <c r="D500" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="501">
@@ -7142,10 +7142,10 @@
         <v>2025.0</v>
       </c>
       <c r="C501" t="n" s="2">
-        <v>46008.0</v>
+        <v>45959.0</v>
       </c>
       <c r="D501" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="502">
@@ -7156,10 +7156,10 @@
         <v>2025.0</v>
       </c>
       <c r="C502" t="n" s="2">
-        <v>46022.0</v>
+        <v>46001.0</v>
       </c>
       <c r="D502" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="503">
@@ -7167,10 +7167,10 @@
         <v>7</v>
       </c>
       <c r="B503" t="n">
-        <v>2026.0</v>
+        <v>2025.0</v>
       </c>
       <c r="C503" t="n" s="2">
-        <v>46030.0</v>
+        <v>46008.0</v>
       </c>
       <c r="D503" t="n">
         <v>1.0</v>
@@ -7181,10 +7181,10 @@
         <v>7</v>
       </c>
       <c r="B504" t="n">
-        <v>2026.0</v>
+        <v>2025.0</v>
       </c>
       <c r="C504" t="n" s="2">
-        <v>46051.0</v>
+        <v>46022.0</v>
       </c>
       <c r="D504" t="n">
         <v>1.0</v>
@@ -7198,7 +7198,7 @@
         <v>2026.0</v>
       </c>
       <c r="C505" t="n" s="2">
-        <v>46058.0</v>
+        <v>46030.0</v>
       </c>
       <c r="D505" t="n">
         <v>1.0</v>
@@ -7212,21 +7212,21 @@
         <v>2026.0</v>
       </c>
       <c r="C506" t="n" s="2">
-        <v>46065.0</v>
+        <v>46051.0</v>
       </c>
       <c r="D506" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B507" t="n">
-        <v>2024.0</v>
+        <v>2026.0</v>
       </c>
       <c r="C507" t="n" s="2">
-        <v>45495.0</v>
+        <v>46058.0</v>
       </c>
       <c r="D507" t="n">
         <v>1.0</v>
@@ -7234,16 +7234,16 @@
     </row>
     <row r="508">
       <c r="A508" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B508" t="n">
-        <v>2024.0</v>
+        <v>2026.0</v>
       </c>
       <c r="C508" t="n" s="2">
-        <v>45502.0</v>
+        <v>46065.0</v>
       </c>
       <c r="D508" t="n">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="509">
@@ -7251,10 +7251,10 @@
         <v>8</v>
       </c>
       <c r="B509" t="n">
-        <v>2025.0</v>
+        <v>2024.0</v>
       </c>
       <c r="C509" t="n" s="2">
-        <v>45665.0</v>
+        <v>45495.0</v>
       </c>
       <c r="D509" t="n">
         <v>1.0</v>
@@ -7265,13 +7265,13 @@
         <v>8</v>
       </c>
       <c r="B510" t="n">
-        <v>2025.0</v>
+        <v>2024.0</v>
       </c>
       <c r="C510" t="n" s="2">
-        <v>45672.0</v>
+        <v>45502.0</v>
       </c>
       <c r="D510" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="511">
@@ -7282,7 +7282,7 @@
         <v>2025.0</v>
       </c>
       <c r="C511" t="n" s="2">
-        <v>45679.0</v>
+        <v>45665.0</v>
       </c>
       <c r="D511" t="n">
         <v>1.0</v>
@@ -7296,10 +7296,10 @@
         <v>2025.0</v>
       </c>
       <c r="C512" t="n" s="2">
-        <v>45686.0</v>
+        <v>45672.0</v>
       </c>
       <c r="D512" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="513">
@@ -7310,7 +7310,7 @@
         <v>2025.0</v>
       </c>
       <c r="C513" t="n" s="2">
-        <v>45693.0</v>
+        <v>45679.0</v>
       </c>
       <c r="D513" t="n">
         <v>1.0</v>
@@ -7324,10 +7324,10 @@
         <v>2025.0</v>
       </c>
       <c r="C514" t="n" s="2">
-        <v>45700.0</v>
+        <v>45686.0</v>
       </c>
       <c r="D514" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="515">
@@ -7338,10 +7338,10 @@
         <v>2025.0</v>
       </c>
       <c r="C515" t="n" s="2">
-        <v>45707.0</v>
+        <v>45693.0</v>
       </c>
       <c r="D515" t="n">
-        <v>7.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="516">
@@ -7352,10 +7352,10 @@
         <v>2025.0</v>
       </c>
       <c r="C516" t="n" s="2">
-        <v>45714.0</v>
+        <v>45700.0</v>
       </c>
       <c r="D516" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="517">
@@ -7366,10 +7366,10 @@
         <v>2025.0</v>
       </c>
       <c r="C517" t="n" s="2">
-        <v>45721.0</v>
+        <v>45707.0</v>
       </c>
       <c r="D517" t="n">
-        <v>4.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="518">
@@ -7380,10 +7380,10 @@
         <v>2025.0</v>
       </c>
       <c r="C518" t="n" s="2">
-        <v>45728.0</v>
+        <v>45714.0</v>
       </c>
       <c r="D518" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="519">
@@ -7394,10 +7394,10 @@
         <v>2025.0</v>
       </c>
       <c r="C519" t="n" s="2">
-        <v>45742.0</v>
+        <v>45721.0</v>
       </c>
       <c r="D519" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="520">
@@ -7408,7 +7408,7 @@
         <v>2025.0</v>
       </c>
       <c r="C520" t="n" s="2">
-        <v>45749.0</v>
+        <v>45728.0</v>
       </c>
       <c r="D520" t="n">
         <v>1.0</v>
@@ -7422,7 +7422,7 @@
         <v>2025.0</v>
       </c>
       <c r="C521" t="n" s="2">
-        <v>45763.0</v>
+        <v>45742.0</v>
       </c>
       <c r="D521" t="n">
         <v>1.0</v>
@@ -7436,10 +7436,10 @@
         <v>2025.0</v>
       </c>
       <c r="C522" t="n" s="2">
-        <v>45777.0</v>
+        <v>45749.0</v>
       </c>
       <c r="D522" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="523">
@@ -7450,7 +7450,7 @@
         <v>2025.0</v>
       </c>
       <c r="C523" t="n" s="2">
-        <v>45784.0</v>
+        <v>45763.0</v>
       </c>
       <c r="D523" t="n">
         <v>1.0</v>
@@ -7464,10 +7464,10 @@
         <v>2025.0</v>
       </c>
       <c r="C524" t="n" s="2">
-        <v>45798.0</v>
+        <v>45777.0</v>
       </c>
       <c r="D524" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="525">
@@ -7478,7 +7478,7 @@
         <v>2025.0</v>
       </c>
       <c r="C525" t="n" s="2">
-        <v>45805.0</v>
+        <v>45784.0</v>
       </c>
       <c r="D525" t="n">
         <v>1.0</v>
@@ -7492,10 +7492,10 @@
         <v>2025.0</v>
       </c>
       <c r="C526" t="n" s="2">
-        <v>45812.0</v>
+        <v>45798.0</v>
       </c>
       <c r="D526" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="527">
@@ -7506,10 +7506,10 @@
         <v>2025.0</v>
       </c>
       <c r="C527" t="n" s="2">
-        <v>45819.0</v>
+        <v>45805.0</v>
       </c>
       <c r="D527" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="528">
@@ -7520,7 +7520,7 @@
         <v>2025.0</v>
       </c>
       <c r="C528" t="n" s="2">
-        <v>45833.0</v>
+        <v>45812.0</v>
       </c>
       <c r="D528" t="n">
         <v>2.0</v>
@@ -7534,10 +7534,10 @@
         <v>2025.0</v>
       </c>
       <c r="C529" t="n" s="2">
-        <v>45847.0</v>
+        <v>45819.0</v>
       </c>
       <c r="D529" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="530">
@@ -7548,10 +7548,10 @@
         <v>2025.0</v>
       </c>
       <c r="C530" t="n" s="2">
-        <v>45854.0</v>
+        <v>45833.0</v>
       </c>
       <c r="D530" t="n">
-        <v>8.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="531">
@@ -7562,10 +7562,10 @@
         <v>2025.0</v>
       </c>
       <c r="C531" t="n" s="2">
-        <v>45861.0</v>
+        <v>45847.0</v>
       </c>
       <c r="D531" t="n">
-        <v>12.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="532">
@@ -7576,10 +7576,10 @@
         <v>2025.0</v>
       </c>
       <c r="C532" t="n" s="2">
-        <v>45868.0</v>
+        <v>45854.0</v>
       </c>
       <c r="D532" t="n">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="533">
@@ -7590,10 +7590,10 @@
         <v>2025.0</v>
       </c>
       <c r="C533" t="n" s="2">
-        <v>45875.0</v>
+        <v>45861.0</v>
       </c>
       <c r="D533" t="n">
-        <v>1.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="534">
@@ -7604,10 +7604,10 @@
         <v>2025.0</v>
       </c>
       <c r="C534" t="n" s="2">
-        <v>45896.0</v>
+        <v>45868.0</v>
       </c>
       <c r="D534" t="n">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="535">
@@ -7618,7 +7618,7 @@
         <v>2025.0</v>
       </c>
       <c r="C535" t="n" s="2">
-        <v>45903.0</v>
+        <v>45875.0</v>
       </c>
       <c r="D535" t="n">
         <v>1.0</v>
@@ -7632,7 +7632,7 @@
         <v>2025.0</v>
       </c>
       <c r="C536" t="n" s="2">
-        <v>45931.0</v>
+        <v>45896.0</v>
       </c>
       <c r="D536" t="n">
         <v>1.0</v>
@@ -7646,10 +7646,10 @@
         <v>2025.0</v>
       </c>
       <c r="C537" t="n" s="2">
-        <v>45938.0</v>
+        <v>45903.0</v>
       </c>
       <c r="D537" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="538">
@@ -7660,10 +7660,10 @@
         <v>2025.0</v>
       </c>
       <c r="C538" t="n" s="2">
-        <v>45945.0</v>
+        <v>45931.0</v>
       </c>
       <c r="D538" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="539">
@@ -7674,10 +7674,10 @@
         <v>2025.0</v>
       </c>
       <c r="C539" t="n" s="2">
-        <v>45966.0</v>
+        <v>45938.0</v>
       </c>
       <c r="D539" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="540">
@@ -7688,10 +7688,10 @@
         <v>2025.0</v>
       </c>
       <c r="C540" t="n" s="2">
-        <v>45973.0</v>
+        <v>45945.0</v>
       </c>
       <c r="D540" t="n">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="541">
@@ -7702,10 +7702,10 @@
         <v>2025.0</v>
       </c>
       <c r="C541" t="n" s="2">
-        <v>45980.0</v>
+        <v>45966.0</v>
       </c>
       <c r="D541" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="542">
@@ -7716,10 +7716,10 @@
         <v>2025.0</v>
       </c>
       <c r="C542" t="n" s="2">
-        <v>45987.0</v>
+        <v>45973.0</v>
       </c>
       <c r="D542" t="n">
-        <v>20.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="543">
@@ -7730,10 +7730,10 @@
         <v>2025.0</v>
       </c>
       <c r="C543" t="n" s="2">
-        <v>45994.0</v>
+        <v>45980.0</v>
       </c>
       <c r="D543" t="n">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="544">
@@ -7744,10 +7744,10 @@
         <v>2025.0</v>
       </c>
       <c r="C544" t="n" s="2">
-        <v>46001.0</v>
+        <v>45987.0</v>
       </c>
       <c r="D544" t="n">
-        <v>8.0</v>
+        <v>20.0</v>
       </c>
     </row>
     <row r="545">
@@ -7758,10 +7758,10 @@
         <v>2025.0</v>
       </c>
       <c r="C545" t="n" s="2">
-        <v>46008.0</v>
+        <v>45994.0</v>
       </c>
       <c r="D545" t="n">
-        <v>24.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="546">
@@ -7772,10 +7772,10 @@
         <v>2025.0</v>
       </c>
       <c r="C546" t="n" s="2">
-        <v>46015.0</v>
+        <v>46001.0</v>
       </c>
       <c r="D546" t="n">
-        <v>13.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="547">
@@ -7786,10 +7786,10 @@
         <v>2025.0</v>
       </c>
       <c r="C547" t="n" s="2">
-        <v>46022.0</v>
+        <v>46008.0</v>
       </c>
       <c r="D547" t="n">
-        <v>7.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="548">
@@ -7800,10 +7800,10 @@
         <v>2025.0</v>
       </c>
       <c r="C548" t="n" s="2">
-        <v>46029.0</v>
+        <v>46015.0</v>
       </c>
       <c r="D548" t="n">
-        <v>3.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="549">
@@ -7811,13 +7811,13 @@
         <v>8</v>
       </c>
       <c r="B549" t="n">
-        <v>2026.0</v>
+        <v>2025.0</v>
       </c>
       <c r="C549" t="n" s="2">
-        <v>46030.0</v>
+        <v>46022.0</v>
       </c>
       <c r="D549" t="n">
-        <v>24.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="550">
@@ -7825,13 +7825,13 @@
         <v>8</v>
       </c>
       <c r="B550" t="n">
-        <v>2026.0</v>
+        <v>2025.0</v>
       </c>
       <c r="C550" t="n" s="2">
-        <v>46037.0</v>
+        <v>46029.0</v>
       </c>
       <c r="D550" t="n">
-        <v>22.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="551">
@@ -7842,10 +7842,10 @@
         <v>2026.0</v>
       </c>
       <c r="C551" t="n" s="2">
-        <v>46044.0</v>
+        <v>46030.0</v>
       </c>
       <c r="D551" t="n">
-        <v>27.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="552">
@@ -7856,10 +7856,10 @@
         <v>2026.0</v>
       </c>
       <c r="C552" t="n" s="2">
-        <v>46051.0</v>
+        <v>46037.0</v>
       </c>
       <c r="D552" t="n">
-        <v>18.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="553">
@@ -7870,10 +7870,10 @@
         <v>2026.0</v>
       </c>
       <c r="C553" t="n" s="2">
-        <v>46058.0</v>
+        <v>46044.0</v>
       </c>
       <c r="D553" t="n">
-        <v>25.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="554">
@@ -7884,10 +7884,10 @@
         <v>2026.0</v>
       </c>
       <c r="C554" t="n" s="2">
-        <v>46065.0</v>
+        <v>46051.0</v>
       </c>
       <c r="D554" t="n">
-        <v>22.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="555">
@@ -7898,10 +7898,10 @@
         <v>2026.0</v>
       </c>
       <c r="C555" t="n" s="2">
-        <v>46072.0</v>
+        <v>46058.0</v>
       </c>
       <c r="D555" t="n">
-        <v>13.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="556">
@@ -7912,10 +7912,10 @@
         <v>2026.0</v>
       </c>
       <c r="C556" t="n" s="2">
-        <v>46079.0</v>
+        <v>46065.0</v>
       </c>
       <c r="D556" t="n">
-        <v>24.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="557">
@@ -7926,10 +7926,10 @@
         <v>2026.0</v>
       </c>
       <c r="C557" t="n" s="2">
-        <v>46086.0</v>
+        <v>46072.0</v>
       </c>
       <c r="D557" t="n">
-        <v>26.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="558">
@@ -7940,10 +7940,10 @@
         <v>2026.0</v>
       </c>
       <c r="C558" t="n" s="2">
-        <v>46093.0</v>
+        <v>46079.0</v>
       </c>
       <c r="D558" t="n">
-        <v>33.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="559">
@@ -7954,10 +7954,10 @@
         <v>2026.0</v>
       </c>
       <c r="C559" t="n" s="2">
-        <v>46100.0</v>
+        <v>46086.0</v>
       </c>
       <c r="D559" t="n">
-        <v>25.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="560">
@@ -7968,9 +7968,37 @@
         <v>2026.0</v>
       </c>
       <c r="C560" t="n" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="D560" t="n">
+        <v>33.0</v>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="s">
+        <v>8</v>
+      </c>
+      <c r="B561" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C561" t="n" s="2">
+        <v>46100.0</v>
+      </c>
+      <c r="D561" t="n">
+        <v>25.0</v>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="s">
+        <v>8</v>
+      </c>
+      <c r="B562" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C562" t="n" s="2">
         <v>46107.0</v>
       </c>
-      <c r="D560" t="n">
+      <c r="D562" t="n">
         <v>2.0</v>
       </c>
     </row>
@@ -8013,7 +8041,7 @@
         <v>12</v>
       </c>
       <c r="B4" t="n">
-        <v>1150.0</v>
+        <v>1151.0</v>
       </c>
     </row>
     <row r="5">
@@ -8021,7 +8049,7 @@
         <v>13</v>
       </c>
       <c r="B5" t="n">
-        <v>2029.0</v>
+        <v>2034.0</v>
       </c>
     </row>
   </sheetData>
@@ -8086,7 +8114,7 @@
         <v>21</v>
       </c>
       <c r="C5" t="n">
-        <v>405.0</v>
+        <v>407.0</v>
       </c>
     </row>
     <row r="6">
@@ -8130,7 +8158,7 @@
         <v>22</v>
       </c>
       <c r="C9" t="n">
-        <v>323.0</v>
+        <v>325.0</v>
       </c>
     </row>
     <row r="10">
@@ -8185,7 +8213,7 @@
         <v>19</v>
       </c>
       <c r="C14" t="n">
-        <v>358.0</v>
+        <v>359.0</v>
       </c>
     </row>
     <row r="15">
@@ -8218,7 +8246,7 @@
         <v>19</v>
       </c>
       <c r="C17" t="n">
-        <v>100.0</v>
+        <v>101.0</v>
       </c>
     </row>
   </sheetData>

--- a/Download/Focus_Positivi_ZR.xlsx
+++ b/Download/Focus_Positivi_ZR.xlsx
@@ -1545,7 +1545,7 @@
         <v>46107.0</v>
       </c>
       <c r="D101" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="102">
@@ -7999,7 +7999,7 @@
         <v>46107.0</v>
       </c>
       <c r="D562" t="n">
-        <v>2.0</v>
+        <v>16.0</v>
       </c>
     </row>
   </sheetData>
@@ -8025,7 +8025,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="n">
-        <v>45.0</v>
+        <v>47.0</v>
       </c>
     </row>
     <row r="3">
@@ -8033,7 +8033,7 @@
         <v>11</v>
       </c>
       <c r="B3" t="n">
-        <v>182.0</v>
+        <v>185.0</v>
       </c>
     </row>
     <row r="4">
@@ -8041,7 +8041,7 @@
         <v>12</v>
       </c>
       <c r="B4" t="n">
-        <v>1151.0</v>
+        <v>1152.0</v>
       </c>
     </row>
     <row r="5">
@@ -8049,7 +8049,7 @@
         <v>13</v>
       </c>
       <c r="B5" t="n">
-        <v>2034.0</v>
+        <v>2044.0</v>
       </c>
     </row>
   </sheetData>
@@ -8103,7 +8103,7 @@
         <v>19</v>
       </c>
       <c r="C4" t="n">
-        <v>131.0</v>
+        <v>133.0</v>
       </c>
     </row>
     <row r="5">
@@ -8114,7 +8114,7 @@
         <v>21</v>
       </c>
       <c r="C5" t="n">
-        <v>407.0</v>
+        <v>408.0</v>
       </c>
     </row>
     <row r="6">
@@ -8125,7 +8125,7 @@
         <v>22</v>
       </c>
       <c r="C6" t="n">
-        <v>289.0</v>
+        <v>291.0</v>
       </c>
     </row>
     <row r="7">
@@ -8147,7 +8147,7 @@
         <v>21</v>
       </c>
       <c r="C8" t="n">
-        <v>341.0</v>
+        <v>342.0</v>
       </c>
     </row>
     <row r="9">
@@ -8158,7 +8158,7 @@
         <v>22</v>
       </c>
       <c r="C9" t="n">
-        <v>325.0</v>
+        <v>326.0</v>
       </c>
     </row>
     <row r="10">
@@ -8180,7 +8180,7 @@
         <v>19</v>
       </c>
       <c r="C11" t="n">
-        <v>31.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="12">
@@ -8213,7 +8213,7 @@
         <v>19</v>
       </c>
       <c r="C14" t="n">
-        <v>359.0</v>
+        <v>365.0</v>
       </c>
     </row>
     <row r="15">
@@ -8235,7 +8235,7 @@
         <v>22</v>
       </c>
       <c r="C16" t="n">
-        <v>341.0</v>
+        <v>342.0</v>
       </c>
     </row>
     <row r="17">

--- a/Download/Focus_Positivi_ZR.xlsx
+++ b/Download/Focus_Positivi_ZR.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="606" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="607" uniqueCount="23">
   <si>
     <t>NOME_REGIONE</t>
   </si>
@@ -4135,7 +4135,7 @@
         <v>46107.0</v>
       </c>
       <c r="D286" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="287">
@@ -7817,7 +7817,7 @@
         <v>46022.0</v>
       </c>
       <c r="D549" t="n">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="550">
@@ -8000,6 +8000,20 @@
       </c>
       <c r="D562" t="n">
         <v>16.0</v>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="s">
+        <v>8</v>
+      </c>
+      <c r="B563" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C563" t="n" s="2">
+        <v>46114.0</v>
+      </c>
+      <c r="D563" t="n">
+        <v>9.0</v>
       </c>
     </row>
   </sheetData>
@@ -8025,7 +8039,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="n">
-        <v>47.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="3">
@@ -8033,7 +8047,7 @@
         <v>11</v>
       </c>
       <c r="B3" t="n">
-        <v>185.0</v>
+        <v>186.0</v>
       </c>
     </row>
     <row r="4">
@@ -8041,7 +8055,7 @@
         <v>12</v>
       </c>
       <c r="B4" t="n">
-        <v>1152.0</v>
+        <v>1154.0</v>
       </c>
     </row>
     <row r="5">
@@ -8049,7 +8063,7 @@
         <v>13</v>
       </c>
       <c r="B5" t="n">
-        <v>2044.0</v>
+        <v>2045.0</v>
       </c>
     </row>
   </sheetData>
@@ -8136,7 +8150,7 @@
         <v>19</v>
       </c>
       <c r="C7" t="n">
-        <v>154.0</v>
+        <v>155.0</v>
       </c>
     </row>
     <row r="8">
@@ -8180,7 +8194,7 @@
         <v>19</v>
       </c>
       <c r="C11" t="n">
-        <v>33.0</v>
+        <v>40.0</v>
       </c>
     </row>
     <row r="12">
@@ -8213,7 +8227,7 @@
         <v>19</v>
       </c>
       <c r="C14" t="n">
-        <v>365.0</v>
+        <v>367.0</v>
       </c>
     </row>
     <row r="15">
@@ -8235,7 +8249,7 @@
         <v>22</v>
       </c>
       <c r="C16" t="n">
-        <v>342.0</v>
+        <v>343.0</v>
       </c>
     </row>
     <row r="17">

--- a/Download/Focus_Positivi_ZR.xlsx
+++ b/Download/Focus_Positivi_ZR.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="607" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="606" uniqueCount="23">
   <si>
     <t>NOME_REGIONE</t>
   </si>
@@ -7999,21 +7999,7 @@
         <v>46107.0</v>
       </c>
       <c r="D562" t="n">
-        <v>16.0</v>
-      </c>
-    </row>
-    <row r="563">
-      <c r="A563" t="s">
-        <v>8</v>
-      </c>
-      <c r="B563" t="n">
-        <v>2026.0</v>
-      </c>
-      <c r="C563" t="n" s="2">
-        <v>46114.0</v>
-      </c>
-      <c r="D563" t="n">
-        <v>9.0</v>
+        <v>25.0</v>
       </c>
     </row>
   </sheetData>
@@ -8039,7 +8025,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="n">
-        <v>54.0</v>
+        <v>45.0</v>
       </c>
     </row>
     <row r="3">
@@ -8055,7 +8041,7 @@
         <v>12</v>
       </c>
       <c r="B4" t="n">
-        <v>1154.0</v>
+        <v>1156.0</v>
       </c>
     </row>
     <row r="5">
@@ -8063,7 +8049,7 @@
         <v>13</v>
       </c>
       <c r="B5" t="n">
-        <v>2045.0</v>
+        <v>2052.0</v>
       </c>
     </row>
   </sheetData>
@@ -8095,7 +8081,7 @@
         <v>21</v>
       </c>
       <c r="C2" t="n">
-        <v>183.0</v>
+        <v>185.0</v>
       </c>
     </row>
     <row r="3">
@@ -8106,7 +8092,7 @@
         <v>22</v>
       </c>
       <c r="C3" t="n">
-        <v>169.0</v>
+        <v>171.0</v>
       </c>
     </row>
     <row r="4">
@@ -8194,7 +8180,7 @@
         <v>19</v>
       </c>
       <c r="C11" t="n">
-        <v>40.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="12">
@@ -8227,7 +8213,7 @@
         <v>19</v>
       </c>
       <c r="C14" t="n">
-        <v>367.0</v>
+        <v>372.0</v>
       </c>
     </row>
     <row r="15">

--- a/Download/Focus_Positivi_ZR.xlsx
+++ b/Download/Focus_Positivi_ZR.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="606" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="608" uniqueCount="23">
   <si>
     <t>NOME_REGIONE</t>
   </si>
@@ -1550,16 +1550,16 @@
     </row>
     <row r="102">
       <c r="A102" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B102" t="n">
-        <v>2021.0</v>
+        <v>2026.0</v>
       </c>
       <c r="C102" t="n" s="2">
-        <v>44561.0</v>
+        <v>46114.0</v>
       </c>
       <c r="D102" t="n">
-        <v>1.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="103">
@@ -1567,13 +1567,13 @@
         <v>5</v>
       </c>
       <c r="B103" t="n">
-        <v>2022.0</v>
+        <v>2021.0</v>
       </c>
       <c r="C103" t="n" s="2">
-        <v>44576.0</v>
+        <v>44561.0</v>
       </c>
       <c r="D103" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="104">
@@ -1584,10 +1584,10 @@
         <v>2022.0</v>
       </c>
       <c r="C104" t="n" s="2">
-        <v>44583.0</v>
+        <v>44576.0</v>
       </c>
       <c r="D104" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="105">
@@ -1598,10 +1598,10 @@
         <v>2022.0</v>
       </c>
       <c r="C105" t="n" s="2">
-        <v>44590.0</v>
+        <v>44583.0</v>
       </c>
       <c r="D105" t="n">
-        <v>7.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="106">
@@ -1612,10 +1612,10 @@
         <v>2022.0</v>
       </c>
       <c r="C106" t="n" s="2">
-        <v>44597.0</v>
+        <v>44590.0</v>
       </c>
       <c r="D106" t="n">
-        <v>3.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="107">
@@ -1626,10 +1626,10 @@
         <v>2022.0</v>
       </c>
       <c r="C107" t="n" s="2">
-        <v>44604.0</v>
+        <v>44597.0</v>
       </c>
       <c r="D107" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="108">
@@ -1640,10 +1640,10 @@
         <v>2022.0</v>
       </c>
       <c r="C108" t="n" s="2">
-        <v>44611.0</v>
+        <v>44604.0</v>
       </c>
       <c r="D108" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="109">
@@ -1654,7 +1654,7 @@
         <v>2022.0</v>
       </c>
       <c r="C109" t="n" s="2">
-        <v>44618.0</v>
+        <v>44611.0</v>
       </c>
       <c r="D109" t="n">
         <v>1.0</v>
@@ -1668,10 +1668,10 @@
         <v>2022.0</v>
       </c>
       <c r="C110" t="n" s="2">
-        <v>44625.0</v>
+        <v>44618.0</v>
       </c>
       <c r="D110" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="111">
@@ -1682,10 +1682,10 @@
         <v>2022.0</v>
       </c>
       <c r="C111" t="n" s="2">
-        <v>44632.0</v>
+        <v>44625.0</v>
       </c>
       <c r="D111" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="112">
@@ -1696,10 +1696,10 @@
         <v>2022.0</v>
       </c>
       <c r="C112" t="n" s="2">
-        <v>44639.0</v>
+        <v>44632.0</v>
       </c>
       <c r="D112" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="113">
@@ -1710,7 +1710,7 @@
         <v>2022.0</v>
       </c>
       <c r="C113" t="n" s="2">
-        <v>44646.0</v>
+        <v>44639.0</v>
       </c>
       <c r="D113" t="n">
         <v>2.0</v>
@@ -1724,7 +1724,7 @@
         <v>2022.0</v>
       </c>
       <c r="C114" t="n" s="2">
-        <v>44653.0</v>
+        <v>44646.0</v>
       </c>
       <c r="D114" t="n">
         <v>2.0</v>
@@ -1738,10 +1738,10 @@
         <v>2022.0</v>
       </c>
       <c r="C115" t="n" s="2">
-        <v>44660.0</v>
+        <v>44653.0</v>
       </c>
       <c r="D115" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="116">
@@ -1752,10 +1752,10 @@
         <v>2022.0</v>
       </c>
       <c r="C116" t="n" s="2">
-        <v>44667.0</v>
+        <v>44660.0</v>
       </c>
       <c r="D116" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="117">
@@ -1766,7 +1766,7 @@
         <v>2022.0</v>
       </c>
       <c r="C117" t="n" s="2">
-        <v>44674.0</v>
+        <v>44667.0</v>
       </c>
       <c r="D117" t="n">
         <v>3.0</v>
@@ -1780,10 +1780,10 @@
         <v>2022.0</v>
       </c>
       <c r="C118" t="n" s="2">
-        <v>44681.0</v>
+        <v>44674.0</v>
       </c>
       <c r="D118" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="119">
@@ -1794,10 +1794,10 @@
         <v>2022.0</v>
       </c>
       <c r="C119" t="n" s="2">
-        <v>44688.0</v>
+        <v>44681.0</v>
       </c>
       <c r="D119" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="120">
@@ -1808,7 +1808,7 @@
         <v>2022.0</v>
       </c>
       <c r="C120" t="n" s="2">
-        <v>44695.0</v>
+        <v>44688.0</v>
       </c>
       <c r="D120" t="n">
         <v>3.0</v>
@@ -1822,10 +1822,10 @@
         <v>2022.0</v>
       </c>
       <c r="C121" t="n" s="2">
-        <v>44702.0</v>
+        <v>44695.0</v>
       </c>
       <c r="D121" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="122">
@@ -1836,10 +1836,10 @@
         <v>2022.0</v>
       </c>
       <c r="C122" t="n" s="2">
-        <v>44709.0</v>
+        <v>44702.0</v>
       </c>
       <c r="D122" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="123">
@@ -1850,10 +1850,10 @@
         <v>2022.0</v>
       </c>
       <c r="C123" t="n" s="2">
-        <v>44716.0</v>
+        <v>44709.0</v>
       </c>
       <c r="D123" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="124">
@@ -1864,7 +1864,7 @@
         <v>2022.0</v>
       </c>
       <c r="C124" t="n" s="2">
-        <v>44723.0</v>
+        <v>44716.0</v>
       </c>
       <c r="D124" t="n">
         <v>1.0</v>
@@ -1878,7 +1878,7 @@
         <v>2022.0</v>
       </c>
       <c r="C125" t="n" s="2">
-        <v>44730.0</v>
+        <v>44723.0</v>
       </c>
       <c r="D125" t="n">
         <v>1.0</v>
@@ -1892,7 +1892,7 @@
         <v>2022.0</v>
       </c>
       <c r="C126" t="n" s="2">
-        <v>44737.0</v>
+        <v>44730.0</v>
       </c>
       <c r="D126" t="n">
         <v>1.0</v>
@@ -1906,7 +1906,7 @@
         <v>2022.0</v>
       </c>
       <c r="C127" t="n" s="2">
-        <v>44744.0</v>
+        <v>44737.0</v>
       </c>
       <c r="D127" t="n">
         <v>1.0</v>
@@ -1920,7 +1920,7 @@
         <v>2022.0</v>
       </c>
       <c r="C128" t="n" s="2">
-        <v>44751.0</v>
+        <v>44744.0</v>
       </c>
       <c r="D128" t="n">
         <v>1.0</v>
@@ -1934,7 +1934,7 @@
         <v>2022.0</v>
       </c>
       <c r="C129" t="n" s="2">
-        <v>44758.0</v>
+        <v>44751.0</v>
       </c>
       <c r="D129" t="n">
         <v>1.0</v>
@@ -1948,7 +1948,7 @@
         <v>2022.0</v>
       </c>
       <c r="C130" t="n" s="2">
-        <v>44772.0</v>
+        <v>44758.0</v>
       </c>
       <c r="D130" t="n">
         <v>1.0</v>
@@ -1962,7 +1962,7 @@
         <v>2022.0</v>
       </c>
       <c r="C131" t="n" s="2">
-        <v>44793.0</v>
+        <v>44772.0</v>
       </c>
       <c r="D131" t="n">
         <v>1.0</v>
@@ -1976,7 +1976,7 @@
         <v>2022.0</v>
       </c>
       <c r="C132" t="n" s="2">
-        <v>44800.0</v>
+        <v>44793.0</v>
       </c>
       <c r="D132" t="n">
         <v>1.0</v>
@@ -1990,7 +1990,7 @@
         <v>2022.0</v>
       </c>
       <c r="C133" t="n" s="2">
-        <v>44828.0</v>
+        <v>44800.0</v>
       </c>
       <c r="D133" t="n">
         <v>1.0</v>
@@ -2004,7 +2004,7 @@
         <v>2022.0</v>
       </c>
       <c r="C134" t="n" s="2">
-        <v>44849.0</v>
+        <v>44828.0</v>
       </c>
       <c r="D134" t="n">
         <v>1.0</v>
@@ -2018,7 +2018,7 @@
         <v>2022.0</v>
       </c>
       <c r="C135" t="n" s="2">
-        <v>44856.0</v>
+        <v>44849.0</v>
       </c>
       <c r="D135" t="n">
         <v>1.0</v>
@@ -2032,7 +2032,7 @@
         <v>2022.0</v>
       </c>
       <c r="C136" t="n" s="2">
-        <v>44863.0</v>
+        <v>44856.0</v>
       </c>
       <c r="D136" t="n">
         <v>1.0</v>
@@ -2046,10 +2046,10 @@
         <v>2022.0</v>
       </c>
       <c r="C137" t="n" s="2">
-        <v>44884.0</v>
+        <v>44863.0</v>
       </c>
       <c r="D137" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="138">
@@ -2060,10 +2060,10 @@
         <v>2022.0</v>
       </c>
       <c r="C138" t="n" s="2">
-        <v>44891.0</v>
+        <v>44884.0</v>
       </c>
       <c r="D138" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="139">
@@ -2074,7 +2074,7 @@
         <v>2022.0</v>
       </c>
       <c r="C139" t="n" s="2">
-        <v>44905.0</v>
+        <v>44891.0</v>
       </c>
       <c r="D139" t="n">
         <v>1.0</v>
@@ -2088,7 +2088,7 @@
         <v>2022.0</v>
       </c>
       <c r="C140" t="n" s="2">
-        <v>44912.0</v>
+        <v>44905.0</v>
       </c>
       <c r="D140" t="n">
         <v>1.0</v>
@@ -2102,10 +2102,10 @@
         <v>2022.0</v>
       </c>
       <c r="C141" t="n" s="2">
-        <v>44919.0</v>
+        <v>44912.0</v>
       </c>
       <c r="D141" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="142">
@@ -2113,13 +2113,13 @@
         <v>5</v>
       </c>
       <c r="B142" t="n">
-        <v>2023.0</v>
+        <v>2022.0</v>
       </c>
       <c r="C142" t="n" s="2">
-        <v>44934.0</v>
+        <v>44919.0</v>
       </c>
       <c r="D142" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="143">
@@ -2130,10 +2130,10 @@
         <v>2023.0</v>
       </c>
       <c r="C143" t="n" s="2">
-        <v>44941.0</v>
+        <v>44934.0</v>
       </c>
       <c r="D143" t="n">
-        <v>8.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="144">
@@ -2144,10 +2144,10 @@
         <v>2023.0</v>
       </c>
       <c r="C144" t="n" s="2">
-        <v>44948.0</v>
+        <v>44941.0</v>
       </c>
       <c r="D144" t="n">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="145">
@@ -2158,10 +2158,10 @@
         <v>2023.0</v>
       </c>
       <c r="C145" t="n" s="2">
-        <v>44955.0</v>
+        <v>44948.0</v>
       </c>
       <c r="D145" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="146">
@@ -2172,10 +2172,10 @@
         <v>2023.0</v>
       </c>
       <c r="C146" t="n" s="2">
-        <v>44962.0</v>
+        <v>44955.0</v>
       </c>
       <c r="D146" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="147">
@@ -2186,7 +2186,7 @@
         <v>2023.0</v>
       </c>
       <c r="C147" t="n" s="2">
-        <v>44969.0</v>
+        <v>44962.0</v>
       </c>
       <c r="D147" t="n">
         <v>4.0</v>
@@ -2200,10 +2200,10 @@
         <v>2023.0</v>
       </c>
       <c r="C148" t="n" s="2">
-        <v>44976.0</v>
+        <v>44969.0</v>
       </c>
       <c r="D148" t="n">
-        <v>17.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="149">
@@ -2214,10 +2214,10 @@
         <v>2023.0</v>
       </c>
       <c r="C149" t="n" s="2">
-        <v>44983.0</v>
+        <v>44976.0</v>
       </c>
       <c r="D149" t="n">
-        <v>11.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="150">
@@ -2228,10 +2228,10 @@
         <v>2023.0</v>
       </c>
       <c r="C150" t="n" s="2">
-        <v>44990.0</v>
+        <v>44983.0</v>
       </c>
       <c r="D150" t="n">
-        <v>5.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="151">
@@ -2242,10 +2242,10 @@
         <v>2023.0</v>
       </c>
       <c r="C151" t="n" s="2">
-        <v>44997.0</v>
+        <v>44990.0</v>
       </c>
       <c r="D151" t="n">
-        <v>22.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="152">
@@ -2256,10 +2256,10 @@
         <v>2023.0</v>
       </c>
       <c r="C152" t="n" s="2">
-        <v>45004.0</v>
+        <v>44997.0</v>
       </c>
       <c r="D152" t="n">
-        <v>8.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="153">
@@ -2270,10 +2270,10 @@
         <v>2023.0</v>
       </c>
       <c r="C153" t="n" s="2">
-        <v>45011.0</v>
+        <v>45004.0</v>
       </c>
       <c r="D153" t="n">
-        <v>17.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="154">
@@ -2284,10 +2284,10 @@
         <v>2023.0</v>
       </c>
       <c r="C154" t="n" s="2">
-        <v>45018.0</v>
+        <v>45011.0</v>
       </c>
       <c r="D154" t="n">
-        <v>10.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="155">
@@ -2298,10 +2298,10 @@
         <v>2023.0</v>
       </c>
       <c r="C155" t="n" s="2">
-        <v>45025.0</v>
+        <v>45018.0</v>
       </c>
       <c r="D155" t="n">
-        <v>13.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="156">
@@ -2312,10 +2312,10 @@
         <v>2023.0</v>
       </c>
       <c r="C156" t="n" s="2">
-        <v>45032.0</v>
+        <v>45025.0</v>
       </c>
       <c r="D156" t="n">
-        <v>10.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="157">
@@ -2326,10 +2326,10 @@
         <v>2023.0</v>
       </c>
       <c r="C157" t="n" s="2">
-        <v>45039.0</v>
+        <v>45032.0</v>
       </c>
       <c r="D157" t="n">
-        <v>22.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="158">
@@ -2340,10 +2340,10 @@
         <v>2023.0</v>
       </c>
       <c r="C158" t="n" s="2">
-        <v>45046.0</v>
+        <v>45039.0</v>
       </c>
       <c r="D158" t="n">
-        <v>23.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="159">
@@ -2354,10 +2354,10 @@
         <v>2023.0</v>
       </c>
       <c r="C159" t="n" s="2">
-        <v>45053.0</v>
+        <v>45046.0</v>
       </c>
       <c r="D159" t="n">
-        <v>16.0</v>
+        <v>23.0</v>
       </c>
     </row>
     <row r="160">
@@ -2368,10 +2368,10 @@
         <v>2023.0</v>
       </c>
       <c r="C160" t="n" s="2">
-        <v>45060.0</v>
+        <v>45053.0</v>
       </c>
       <c r="D160" t="n">
-        <v>13.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="161">
@@ -2382,10 +2382,10 @@
         <v>2023.0</v>
       </c>
       <c r="C161" t="n" s="2">
-        <v>45067.0</v>
+        <v>45060.0</v>
       </c>
       <c r="D161" t="n">
-        <v>9.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="162">
@@ -2396,10 +2396,10 @@
         <v>2023.0</v>
       </c>
       <c r="C162" t="n" s="2">
-        <v>45074.0</v>
+        <v>45067.0</v>
       </c>
       <c r="D162" t="n">
-        <v>6.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="163">
@@ -2410,10 +2410,10 @@
         <v>2023.0</v>
       </c>
       <c r="C163" t="n" s="2">
-        <v>45081.0</v>
+        <v>45074.0</v>
       </c>
       <c r="D163" t="n">
-        <v>16.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="164">
@@ -2424,10 +2424,10 @@
         <v>2023.0</v>
       </c>
       <c r="C164" t="n" s="2">
-        <v>45088.0</v>
+        <v>45081.0</v>
       </c>
       <c r="D164" t="n">
-        <v>8.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="165">
@@ -2438,10 +2438,10 @@
         <v>2023.0</v>
       </c>
       <c r="C165" t="n" s="2">
-        <v>45095.0</v>
+        <v>45088.0</v>
       </c>
       <c r="D165" t="n">
-        <v>16.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="166">
@@ -2452,10 +2452,10 @@
         <v>2023.0</v>
       </c>
       <c r="C166" t="n" s="2">
-        <v>45102.0</v>
+        <v>45095.0</v>
       </c>
       <c r="D166" t="n">
-        <v>17.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="167">
@@ -2466,10 +2466,10 @@
         <v>2023.0</v>
       </c>
       <c r="C167" t="n" s="2">
-        <v>45109.0</v>
+        <v>45102.0</v>
       </c>
       <c r="D167" t="n">
-        <v>14.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="168">
@@ -2480,10 +2480,10 @@
         <v>2023.0</v>
       </c>
       <c r="C168" t="n" s="2">
-        <v>45116.0</v>
+        <v>45109.0</v>
       </c>
       <c r="D168" t="n">
-        <v>13.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="169">
@@ -2494,10 +2494,10 @@
         <v>2023.0</v>
       </c>
       <c r="C169" t="n" s="2">
-        <v>45123.0</v>
+        <v>45116.0</v>
       </c>
       <c r="D169" t="n">
-        <v>5.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="170">
@@ -2508,10 +2508,10 @@
         <v>2023.0</v>
       </c>
       <c r="C170" t="n" s="2">
-        <v>45130.0</v>
+        <v>45123.0</v>
       </c>
       <c r="D170" t="n">
-        <v>8.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="171">
@@ -2522,10 +2522,10 @@
         <v>2023.0</v>
       </c>
       <c r="C171" t="n" s="2">
-        <v>45137.0</v>
+        <v>45130.0</v>
       </c>
       <c r="D171" t="n">
-        <v>4.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="172">
@@ -2536,10 +2536,10 @@
         <v>2023.0</v>
       </c>
       <c r="C172" t="n" s="2">
-        <v>45144.0</v>
+        <v>45137.0</v>
       </c>
       <c r="D172" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="173">
@@ -2550,7 +2550,7 @@
         <v>2023.0</v>
       </c>
       <c r="C173" t="n" s="2">
-        <v>45151.0</v>
+        <v>45144.0</v>
       </c>
       <c r="D173" t="n">
         <v>2.0</v>
@@ -2564,10 +2564,10 @@
         <v>2023.0</v>
       </c>
       <c r="C174" t="n" s="2">
-        <v>45158.0</v>
+        <v>45151.0</v>
       </c>
       <c r="D174" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="175">
@@ -2578,7 +2578,7 @@
         <v>2023.0</v>
       </c>
       <c r="C175" t="n" s="2">
-        <v>45165.0</v>
+        <v>45158.0</v>
       </c>
       <c r="D175" t="n">
         <v>5.0</v>
@@ -2592,10 +2592,10 @@
         <v>2023.0</v>
       </c>
       <c r="C176" t="n" s="2">
-        <v>45172.0</v>
+        <v>45165.0</v>
       </c>
       <c r="D176" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="177">
@@ -2606,10 +2606,10 @@
         <v>2023.0</v>
       </c>
       <c r="C177" t="n" s="2">
-        <v>45179.0</v>
+        <v>45172.0</v>
       </c>
       <c r="D177" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="178">
@@ -2620,10 +2620,10 @@
         <v>2023.0</v>
       </c>
       <c r="C178" t="n" s="2">
-        <v>45186.0</v>
+        <v>45179.0</v>
       </c>
       <c r="D178" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="179">
@@ -2634,7 +2634,7 @@
         <v>2023.0</v>
       </c>
       <c r="C179" t="n" s="2">
-        <v>45193.0</v>
+        <v>45186.0</v>
       </c>
       <c r="D179" t="n">
         <v>1.0</v>
@@ -2648,10 +2648,10 @@
         <v>2023.0</v>
       </c>
       <c r="C180" t="n" s="2">
-        <v>45200.0</v>
+        <v>45193.0</v>
       </c>
       <c r="D180" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="181">
@@ -2662,10 +2662,10 @@
         <v>2023.0</v>
       </c>
       <c r="C181" t="n" s="2">
-        <v>45207.0</v>
+        <v>45200.0</v>
       </c>
       <c r="D181" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="182">
@@ -2676,10 +2676,10 @@
         <v>2023.0</v>
       </c>
       <c r="C182" t="n" s="2">
-        <v>45214.0</v>
+        <v>45207.0</v>
       </c>
       <c r="D182" t="n">
-        <v>8.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="183">
@@ -2690,7 +2690,7 @@
         <v>2023.0</v>
       </c>
       <c r="C183" t="n" s="2">
-        <v>45221.0</v>
+        <v>45214.0</v>
       </c>
       <c r="D183" t="n">
         <v>8.0</v>
@@ -2704,10 +2704,10 @@
         <v>2023.0</v>
       </c>
       <c r="C184" t="n" s="2">
-        <v>45228.0</v>
+        <v>45221.0</v>
       </c>
       <c r="D184" t="n">
-        <v>17.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="185">
@@ -2718,10 +2718,10 @@
         <v>2023.0</v>
       </c>
       <c r="C185" t="n" s="2">
-        <v>45235.0</v>
+        <v>45228.0</v>
       </c>
       <c r="D185" t="n">
-        <v>9.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="186">
@@ -2732,7 +2732,7 @@
         <v>2023.0</v>
       </c>
       <c r="C186" t="n" s="2">
-        <v>45242.0</v>
+        <v>45235.0</v>
       </c>
       <c r="D186" t="n">
         <v>9.0</v>
@@ -2746,10 +2746,10 @@
         <v>2023.0</v>
       </c>
       <c r="C187" t="n" s="2">
-        <v>45249.0</v>
+        <v>45242.0</v>
       </c>
       <c r="D187" t="n">
-        <v>14.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="188">
@@ -2760,10 +2760,10 @@
         <v>2023.0</v>
       </c>
       <c r="C188" t="n" s="2">
-        <v>45256.0</v>
+        <v>45249.0</v>
       </c>
       <c r="D188" t="n">
-        <v>17.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="189">
@@ -2774,10 +2774,10 @@
         <v>2023.0</v>
       </c>
       <c r="C189" t="n" s="2">
-        <v>45263.0</v>
+        <v>45256.0</v>
       </c>
       <c r="D189" t="n">
-        <v>14.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="190">
@@ -2788,10 +2788,10 @@
         <v>2023.0</v>
       </c>
       <c r="C190" t="n" s="2">
-        <v>45270.0</v>
+        <v>45263.0</v>
       </c>
       <c r="D190" t="n">
-        <v>26.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="191">
@@ -2802,10 +2802,10 @@
         <v>2023.0</v>
       </c>
       <c r="C191" t="n" s="2">
-        <v>45277.0</v>
+        <v>45270.0</v>
       </c>
       <c r="D191" t="n">
-        <v>19.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="192">
@@ -2816,10 +2816,10 @@
         <v>2023.0</v>
       </c>
       <c r="C192" t="n" s="2">
-        <v>45284.0</v>
+        <v>45277.0</v>
       </c>
       <c r="D192" t="n">
-        <v>21.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="193">
@@ -2830,10 +2830,10 @@
         <v>2023.0</v>
       </c>
       <c r="C193" t="n" s="2">
-        <v>45291.0</v>
+        <v>45284.0</v>
       </c>
       <c r="D193" t="n">
-        <v>9.0</v>
+        <v>21.0</v>
       </c>
     </row>
     <row r="194">
@@ -2841,13 +2841,13 @@
         <v>5</v>
       </c>
       <c r="B194" t="n">
-        <v>2024.0</v>
+        <v>2023.0</v>
       </c>
       <c r="C194" t="n" s="2">
-        <v>45299.0</v>
+        <v>45291.0</v>
       </c>
       <c r="D194" t="n">
-        <v>26.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="195">
@@ -2858,10 +2858,10 @@
         <v>2024.0</v>
       </c>
       <c r="C195" t="n" s="2">
-        <v>45306.0</v>
+        <v>45299.0</v>
       </c>
       <c r="D195" t="n">
-        <v>14.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="196">
@@ -2872,10 +2872,10 @@
         <v>2024.0</v>
       </c>
       <c r="C196" t="n" s="2">
-        <v>45313.0</v>
+        <v>45306.0</v>
       </c>
       <c r="D196" t="n">
-        <v>15.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="197">
@@ -2886,10 +2886,10 @@
         <v>2024.0</v>
       </c>
       <c r="C197" t="n" s="2">
-        <v>45320.0</v>
+        <v>45313.0</v>
       </c>
       <c r="D197" t="n">
-        <v>18.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="198">
@@ -2900,10 +2900,10 @@
         <v>2024.0</v>
       </c>
       <c r="C198" t="n" s="2">
-        <v>45327.0</v>
+        <v>45320.0</v>
       </c>
       <c r="D198" t="n">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="199">
@@ -2914,10 +2914,10 @@
         <v>2024.0</v>
       </c>
       <c r="C199" t="n" s="2">
-        <v>45334.0</v>
+        <v>45327.0</v>
       </c>
       <c r="D199" t="n">
-        <v>13.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="200">
@@ -2928,10 +2928,10 @@
         <v>2024.0</v>
       </c>
       <c r="C200" t="n" s="2">
-        <v>45341.0</v>
+        <v>45334.0</v>
       </c>
       <c r="D200" t="n">
-        <v>11.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="201">
@@ -2942,10 +2942,10 @@
         <v>2024.0</v>
       </c>
       <c r="C201" t="n" s="2">
-        <v>45348.0</v>
+        <v>45341.0</v>
       </c>
       <c r="D201" t="n">
-        <v>8.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="202">
@@ -2956,10 +2956,10 @@
         <v>2024.0</v>
       </c>
       <c r="C202" t="n" s="2">
-        <v>45355.0</v>
+        <v>45348.0</v>
       </c>
       <c r="D202" t="n">
-        <v>1.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="203">
@@ -2970,10 +2970,10 @@
         <v>2024.0</v>
       </c>
       <c r="C203" t="n" s="2">
-        <v>45362.0</v>
+        <v>45355.0</v>
       </c>
       <c r="D203" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="204">
@@ -2984,10 +2984,10 @@
         <v>2024.0</v>
       </c>
       <c r="C204" t="n" s="2">
-        <v>45369.0</v>
+        <v>45362.0</v>
       </c>
       <c r="D204" t="n">
-        <v>8.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="205">
@@ -2998,10 +2998,10 @@
         <v>2024.0</v>
       </c>
       <c r="C205" t="n" s="2">
-        <v>45376.0</v>
+        <v>45369.0</v>
       </c>
       <c r="D205" t="n">
-        <v>9.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="206">
@@ -3012,10 +3012,10 @@
         <v>2024.0</v>
       </c>
       <c r="C206" t="n" s="2">
-        <v>45383.0</v>
+        <v>45376.0</v>
       </c>
       <c r="D206" t="n">
-        <v>5.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="207">
@@ -3026,10 +3026,10 @@
         <v>2024.0</v>
       </c>
       <c r="C207" t="n" s="2">
-        <v>45390.0</v>
+        <v>45383.0</v>
       </c>
       <c r="D207" t="n">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="208">
@@ -3040,10 +3040,10 @@
         <v>2024.0</v>
       </c>
       <c r="C208" t="n" s="2">
-        <v>45397.0</v>
+        <v>45390.0</v>
       </c>
       <c r="D208" t="n">
-        <v>13.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="209">
@@ -3054,10 +3054,10 @@
         <v>2024.0</v>
       </c>
       <c r="C209" t="n" s="2">
-        <v>45404.0</v>
+        <v>45397.0</v>
       </c>
       <c r="D209" t="n">
-        <v>24.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="210">
@@ -3068,10 +3068,10 @@
         <v>2024.0</v>
       </c>
       <c r="C210" t="n" s="2">
-        <v>45411.0</v>
+        <v>45404.0</v>
       </c>
       <c r="D210" t="n">
-        <v>17.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="211">
@@ -3082,10 +3082,10 @@
         <v>2024.0</v>
       </c>
       <c r="C211" t="n" s="2">
-        <v>45418.0</v>
+        <v>45411.0</v>
       </c>
       <c r="D211" t="n">
-        <v>3.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="212">
@@ -3096,10 +3096,10 @@
         <v>2024.0</v>
       </c>
       <c r="C212" t="n" s="2">
-        <v>45425.0</v>
+        <v>45418.0</v>
       </c>
       <c r="D212" t="n">
-        <v>16.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="213">
@@ -3110,10 +3110,10 @@
         <v>2024.0</v>
       </c>
       <c r="C213" t="n" s="2">
-        <v>45432.0</v>
+        <v>45425.0</v>
       </c>
       <c r="D213" t="n">
-        <v>19.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="214">
@@ -3124,10 +3124,10 @@
         <v>2024.0</v>
       </c>
       <c r="C214" t="n" s="2">
-        <v>45439.0</v>
+        <v>45432.0</v>
       </c>
       <c r="D214" t="n">
-        <v>30.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="215">
@@ -3138,10 +3138,10 @@
         <v>2024.0</v>
       </c>
       <c r="C215" t="n" s="2">
-        <v>45446.0</v>
+        <v>45439.0</v>
       </c>
       <c r="D215" t="n">
-        <v>28.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="216">
@@ -3152,10 +3152,10 @@
         <v>2024.0</v>
       </c>
       <c r="C216" t="n" s="2">
-        <v>45453.0</v>
+        <v>45446.0</v>
       </c>
       <c r="D216" t="n">
-        <v>19.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="217">
@@ -3166,10 +3166,10 @@
         <v>2024.0</v>
       </c>
       <c r="C217" t="n" s="2">
-        <v>45460.0</v>
+        <v>45453.0</v>
       </c>
       <c r="D217" t="n">
-        <v>26.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="218">
@@ -3180,10 +3180,10 @@
         <v>2024.0</v>
       </c>
       <c r="C218" t="n" s="2">
-        <v>45467.0</v>
+        <v>45460.0</v>
       </c>
       <c r="D218" t="n">
-        <v>8.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="219">
@@ -3194,10 +3194,10 @@
         <v>2024.0</v>
       </c>
       <c r="C219" t="n" s="2">
-        <v>45474.0</v>
+        <v>45467.0</v>
       </c>
       <c r="D219" t="n">
-        <v>12.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="220">
@@ -3208,7 +3208,7 @@
         <v>2024.0</v>
       </c>
       <c r="C220" t="n" s="2">
-        <v>45481.0</v>
+        <v>45474.0</v>
       </c>
       <c r="D220" t="n">
         <v>12.0</v>
@@ -3222,10 +3222,10 @@
         <v>2024.0</v>
       </c>
       <c r="C221" t="n" s="2">
-        <v>45488.0</v>
+        <v>45481.0</v>
       </c>
       <c r="D221" t="n">
-        <v>4.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="222">
@@ -3236,10 +3236,10 @@
         <v>2024.0</v>
       </c>
       <c r="C222" t="n" s="2">
-        <v>45495.0</v>
+        <v>45488.0</v>
       </c>
       <c r="D222" t="n">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="223">
@@ -3250,10 +3250,10 @@
         <v>2024.0</v>
       </c>
       <c r="C223" t="n" s="2">
-        <v>45502.0</v>
+        <v>45495.0</v>
       </c>
       <c r="D223" t="n">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="224">
@@ -3264,10 +3264,10 @@
         <v>2024.0</v>
       </c>
       <c r="C224" t="n" s="2">
-        <v>45509.0</v>
+        <v>45502.0</v>
       </c>
       <c r="D224" t="n">
-        <v>2.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="225">
@@ -3278,10 +3278,10 @@
         <v>2024.0</v>
       </c>
       <c r="C225" t="n" s="2">
-        <v>45516.0</v>
+        <v>45509.0</v>
       </c>
       <c r="D225" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="226">
@@ -3292,7 +3292,7 @@
         <v>2024.0</v>
       </c>
       <c r="C226" t="n" s="2">
-        <v>45523.0</v>
+        <v>45516.0</v>
       </c>
       <c r="D226" t="n">
         <v>4.0</v>
@@ -3306,7 +3306,7 @@
         <v>2024.0</v>
       </c>
       <c r="C227" t="n" s="2">
-        <v>45530.0</v>
+        <v>45523.0</v>
       </c>
       <c r="D227" t="n">
         <v>4.0</v>
@@ -3320,7 +3320,7 @@
         <v>2024.0</v>
       </c>
       <c r="C228" t="n" s="2">
-        <v>45537.0</v>
+        <v>45530.0</v>
       </c>
       <c r="D228" t="n">
         <v>4.0</v>
@@ -3334,10 +3334,10 @@
         <v>2024.0</v>
       </c>
       <c r="C229" t="n" s="2">
-        <v>45544.0</v>
+        <v>45537.0</v>
       </c>
       <c r="D229" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="230">
@@ -3348,10 +3348,10 @@
         <v>2024.0</v>
       </c>
       <c r="C230" t="n" s="2">
-        <v>45551.0</v>
+        <v>45544.0</v>
       </c>
       <c r="D230" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="231">
@@ -3362,10 +3362,10 @@
         <v>2024.0</v>
       </c>
       <c r="C231" t="n" s="2">
-        <v>45558.0</v>
+        <v>45551.0</v>
       </c>
       <c r="D231" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="232">
@@ -3376,10 +3376,10 @@
         <v>2024.0</v>
       </c>
       <c r="C232" t="n" s="2">
-        <v>45600.0</v>
+        <v>45558.0</v>
       </c>
       <c r="D232" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="233">
@@ -3390,10 +3390,10 @@
         <v>2024.0</v>
       </c>
       <c r="C233" t="n" s="2">
-        <v>45607.0</v>
+        <v>45600.0</v>
       </c>
       <c r="D233" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="234">
@@ -3404,10 +3404,10 @@
         <v>2024.0</v>
       </c>
       <c r="C234" t="n" s="2">
-        <v>45628.0</v>
+        <v>45607.0</v>
       </c>
       <c r="D234" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="235">
@@ -3418,10 +3418,10 @@
         <v>2024.0</v>
       </c>
       <c r="C235" t="n" s="2">
-        <v>45635.0</v>
+        <v>45628.0</v>
       </c>
       <c r="D235" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="236">
@@ -3432,7 +3432,7 @@
         <v>2024.0</v>
       </c>
       <c r="C236" t="n" s="2">
-        <v>45642.0</v>
+        <v>45635.0</v>
       </c>
       <c r="D236" t="n">
         <v>3.0</v>
@@ -3446,10 +3446,10 @@
         <v>2024.0</v>
       </c>
       <c r="C237" t="n" s="2">
-        <v>45649.0</v>
+        <v>45642.0</v>
       </c>
       <c r="D237" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="238">
@@ -3460,7 +3460,7 @@
         <v>2024.0</v>
       </c>
       <c r="C238" t="n" s="2">
-        <v>45656.0</v>
+        <v>45649.0</v>
       </c>
       <c r="D238" t="n">
         <v>1.0</v>
@@ -3471,13 +3471,13 @@
         <v>5</v>
       </c>
       <c r="B239" t="n">
-        <v>2025.0</v>
+        <v>2024.0</v>
       </c>
       <c r="C239" t="n" s="2">
-        <v>45672.0</v>
+        <v>45656.0</v>
       </c>
       <c r="D239" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="240">
@@ -3488,10 +3488,10 @@
         <v>2025.0</v>
       </c>
       <c r="C240" t="n" s="2">
-        <v>45679.0</v>
+        <v>45672.0</v>
       </c>
       <c r="D240" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="241">
@@ -3502,7 +3502,7 @@
         <v>2025.0</v>
       </c>
       <c r="C241" t="n" s="2">
-        <v>45686.0</v>
+        <v>45679.0</v>
       </c>
       <c r="D241" t="n">
         <v>1.0</v>
@@ -3516,10 +3516,10 @@
         <v>2025.0</v>
       </c>
       <c r="C242" t="n" s="2">
-        <v>45721.0</v>
+        <v>45686.0</v>
       </c>
       <c r="D242" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="243">
@@ -3530,10 +3530,10 @@
         <v>2025.0</v>
       </c>
       <c r="C243" t="n" s="2">
-        <v>45728.0</v>
+        <v>45721.0</v>
       </c>
       <c r="D243" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="244">
@@ -3544,10 +3544,10 @@
         <v>2025.0</v>
       </c>
       <c r="C244" t="n" s="2">
-        <v>45742.0</v>
+        <v>45728.0</v>
       </c>
       <c r="D244" t="n">
-        <v>9.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="245">
@@ -3558,10 +3558,10 @@
         <v>2025.0</v>
       </c>
       <c r="C245" t="n" s="2">
-        <v>45749.0</v>
+        <v>45742.0</v>
       </c>
       <c r="D245" t="n">
-        <v>5.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="246">
@@ -3572,10 +3572,10 @@
         <v>2025.0</v>
       </c>
       <c r="C246" t="n" s="2">
-        <v>45756.0</v>
+        <v>45749.0</v>
       </c>
       <c r="D246" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="247">
@@ -3586,10 +3586,10 @@
         <v>2025.0</v>
       </c>
       <c r="C247" t="n" s="2">
-        <v>45763.0</v>
+        <v>45756.0</v>
       </c>
       <c r="D247" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="248">
@@ -3600,10 +3600,10 @@
         <v>2025.0</v>
       </c>
       <c r="C248" t="n" s="2">
-        <v>45770.0</v>
+        <v>45763.0</v>
       </c>
       <c r="D248" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="249">
@@ -3614,10 +3614,10 @@
         <v>2025.0</v>
       </c>
       <c r="C249" t="n" s="2">
-        <v>45777.0</v>
+        <v>45770.0</v>
       </c>
       <c r="D249" t="n">
-        <v>7.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="250">
@@ -3628,10 +3628,10 @@
         <v>2025.0</v>
       </c>
       <c r="C250" t="n" s="2">
-        <v>45784.0</v>
+        <v>45777.0</v>
       </c>
       <c r="D250" t="n">
-        <v>2.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="251">
@@ -3642,10 +3642,10 @@
         <v>2025.0</v>
       </c>
       <c r="C251" t="n" s="2">
-        <v>45791.0</v>
+        <v>45784.0</v>
       </c>
       <c r="D251" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="252">
@@ -3656,10 +3656,10 @@
         <v>2025.0</v>
       </c>
       <c r="C252" t="n" s="2">
-        <v>45798.0</v>
+        <v>45791.0</v>
       </c>
       <c r="D252" t="n">
-        <v>8.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="253">
@@ -3670,10 +3670,10 @@
         <v>2025.0</v>
       </c>
       <c r="C253" t="n" s="2">
-        <v>45805.0</v>
+        <v>45798.0</v>
       </c>
       <c r="D253" t="n">
-        <v>4.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="254">
@@ -3684,10 +3684,10 @@
         <v>2025.0</v>
       </c>
       <c r="C254" t="n" s="2">
-        <v>45812.0</v>
+        <v>45805.0</v>
       </c>
       <c r="D254" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="255">
@@ -3698,10 +3698,10 @@
         <v>2025.0</v>
       </c>
       <c r="C255" t="n" s="2">
-        <v>45819.0</v>
+        <v>45812.0</v>
       </c>
       <c r="D255" t="n">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="256">
@@ -3712,10 +3712,10 @@
         <v>2025.0</v>
       </c>
       <c r="C256" t="n" s="2">
-        <v>45826.0</v>
+        <v>45819.0</v>
       </c>
       <c r="D256" t="n">
-        <v>13.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="257">
@@ -3726,10 +3726,10 @@
         <v>2025.0</v>
       </c>
       <c r="C257" t="n" s="2">
-        <v>45833.0</v>
+        <v>45826.0</v>
       </c>
       <c r="D257" t="n">
-        <v>1.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="258">
@@ -3740,10 +3740,10 @@
         <v>2025.0</v>
       </c>
       <c r="C258" t="n" s="2">
-        <v>45840.0</v>
+        <v>45833.0</v>
       </c>
       <c r="D258" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="259">
@@ -3754,7 +3754,7 @@
         <v>2025.0</v>
       </c>
       <c r="C259" t="n" s="2">
-        <v>45847.0</v>
+        <v>45840.0</v>
       </c>
       <c r="D259" t="n">
         <v>4.0</v>
@@ -3768,10 +3768,10 @@
         <v>2025.0</v>
       </c>
       <c r="C260" t="n" s="2">
-        <v>45854.0</v>
+        <v>45847.0</v>
       </c>
       <c r="D260" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="261">
@@ -3782,10 +3782,10 @@
         <v>2025.0</v>
       </c>
       <c r="C261" t="n" s="2">
-        <v>45861.0</v>
+        <v>45854.0</v>
       </c>
       <c r="D261" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="262">
@@ -3796,10 +3796,10 @@
         <v>2025.0</v>
       </c>
       <c r="C262" t="n" s="2">
-        <v>45868.0</v>
+        <v>45861.0</v>
       </c>
       <c r="D262" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="263">
@@ -3810,10 +3810,10 @@
         <v>2025.0</v>
       </c>
       <c r="C263" t="n" s="2">
-        <v>45882.0</v>
+        <v>45868.0</v>
       </c>
       <c r="D263" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="264">
@@ -3824,7 +3824,7 @@
         <v>2025.0</v>
       </c>
       <c r="C264" t="n" s="2">
-        <v>45889.0</v>
+        <v>45882.0</v>
       </c>
       <c r="D264" t="n">
         <v>1.0</v>
@@ -3838,10 +3838,10 @@
         <v>2025.0</v>
       </c>
       <c r="C265" t="n" s="2">
-        <v>45896.0</v>
+        <v>45889.0</v>
       </c>
       <c r="D265" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="266">
@@ -3852,7 +3852,7 @@
         <v>2025.0</v>
       </c>
       <c r="C266" t="n" s="2">
-        <v>45903.0</v>
+        <v>45896.0</v>
       </c>
       <c r="D266" t="n">
         <v>3.0</v>
@@ -3866,10 +3866,10 @@
         <v>2025.0</v>
       </c>
       <c r="C267" t="n" s="2">
-        <v>45910.0</v>
+        <v>45903.0</v>
       </c>
       <c r="D267" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="268">
@@ -3880,7 +3880,7 @@
         <v>2025.0</v>
       </c>
       <c r="C268" t="n" s="2">
-        <v>45973.0</v>
+        <v>45910.0</v>
       </c>
       <c r="D268" t="n">
         <v>1.0</v>
@@ -3894,10 +3894,10 @@
         <v>2025.0</v>
       </c>
       <c r="C269" t="n" s="2">
-        <v>45987.0</v>
+        <v>45973.0</v>
       </c>
       <c r="D269" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="270">
@@ -3908,10 +3908,10 @@
         <v>2025.0</v>
       </c>
       <c r="C270" t="n" s="2">
-        <v>45994.0</v>
+        <v>45987.0</v>
       </c>
       <c r="D270" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="271">
@@ -3922,10 +3922,10 @@
         <v>2025.0</v>
       </c>
       <c r="C271" t="n" s="2">
-        <v>46001.0</v>
+        <v>45994.0</v>
       </c>
       <c r="D271" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="272">
@@ -3936,10 +3936,10 @@
         <v>2025.0</v>
       </c>
       <c r="C272" t="n" s="2">
-        <v>46008.0</v>
+        <v>46001.0</v>
       </c>
       <c r="D272" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="273">
@@ -3950,10 +3950,10 @@
         <v>2025.0</v>
       </c>
       <c r="C273" t="n" s="2">
-        <v>46022.0</v>
+        <v>46008.0</v>
       </c>
       <c r="D273" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="274">
@@ -3964,10 +3964,10 @@
         <v>2025.0</v>
       </c>
       <c r="C274" t="n" s="2">
-        <v>46029.0</v>
+        <v>46022.0</v>
       </c>
       <c r="D274" t="n">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="275">
@@ -3975,13 +3975,13 @@
         <v>5</v>
       </c>
       <c r="B275" t="n">
-        <v>2026.0</v>
+        <v>2025.0</v>
       </c>
       <c r="C275" t="n" s="2">
-        <v>46030.0</v>
+        <v>46029.0</v>
       </c>
       <c r="D275" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="276">
@@ -3992,10 +3992,10 @@
         <v>2026.0</v>
       </c>
       <c r="C276" t="n" s="2">
-        <v>46037.0</v>
+        <v>46030.0</v>
       </c>
       <c r="D276" t="n">
-        <v>12.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="277">
@@ -4006,10 +4006,10 @@
         <v>2026.0</v>
       </c>
       <c r="C277" t="n" s="2">
-        <v>46044.0</v>
+        <v>46037.0</v>
       </c>
       <c r="D277" t="n">
-        <v>9.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="278">
@@ -4020,10 +4020,10 @@
         <v>2026.0</v>
       </c>
       <c r="C278" t="n" s="2">
-        <v>46051.0</v>
+        <v>46044.0</v>
       </c>
       <c r="D278" t="n">
-        <v>10.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="279">
@@ -4034,10 +4034,10 @@
         <v>2026.0</v>
       </c>
       <c r="C279" t="n" s="2">
-        <v>46058.0</v>
+        <v>46051.0</v>
       </c>
       <c r="D279" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="280">
@@ -4048,10 +4048,10 @@
         <v>2026.0</v>
       </c>
       <c r="C280" t="n" s="2">
-        <v>46065.0</v>
+        <v>46058.0</v>
       </c>
       <c r="D280" t="n">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="281">
@@ -4062,10 +4062,10 @@
         <v>2026.0</v>
       </c>
       <c r="C281" t="n" s="2">
-        <v>46072.0</v>
+        <v>46065.0</v>
       </c>
       <c r="D281" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="282">
@@ -4076,10 +4076,10 @@
         <v>2026.0</v>
       </c>
       <c r="C282" t="n" s="2">
-        <v>46079.0</v>
+        <v>46072.0</v>
       </c>
       <c r="D282" t="n">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="283">
@@ -4090,10 +4090,10 @@
         <v>2026.0</v>
       </c>
       <c r="C283" t="n" s="2">
-        <v>46086.0</v>
+        <v>46079.0</v>
       </c>
       <c r="D283" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="284">
@@ -4104,7 +4104,7 @@
         <v>2026.0</v>
       </c>
       <c r="C284" t="n" s="2">
-        <v>46093.0</v>
+        <v>46086.0</v>
       </c>
       <c r="D284" t="n">
         <v>2.0</v>
@@ -4118,10 +4118,10 @@
         <v>2026.0</v>
       </c>
       <c r="C285" t="n" s="2">
-        <v>46100.0</v>
+        <v>46093.0</v>
       </c>
       <c r="D285" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="286">
@@ -4132,7 +4132,7 @@
         <v>2026.0</v>
       </c>
       <c r="C286" t="n" s="2">
-        <v>46107.0</v>
+        <v>46100.0</v>
       </c>
       <c r="D286" t="n">
         <v>4.0</v>
@@ -4140,27 +4140,27 @@
     </row>
     <row r="287">
       <c r="A287" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B287" t="n">
-        <v>2023.0</v>
+        <v>2026.0</v>
       </c>
       <c r="C287" t="n" s="2">
-        <v>45095.0</v>
+        <v>46107.0</v>
       </c>
       <c r="D287" t="n">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B288" t="n">
-        <v>2023.0</v>
+        <v>2026.0</v>
       </c>
       <c r="C288" t="n" s="2">
-        <v>45102.0</v>
+        <v>46114.0</v>
       </c>
       <c r="D288" t="n">
         <v>1.0</v>
@@ -4174,7 +4174,7 @@
         <v>2023.0</v>
       </c>
       <c r="C289" t="n" s="2">
-        <v>45158.0</v>
+        <v>45095.0</v>
       </c>
       <c r="D289" t="n">
         <v>1.0</v>
@@ -4188,10 +4188,10 @@
         <v>2023.0</v>
       </c>
       <c r="C290" t="n" s="2">
-        <v>45207.0</v>
+        <v>45102.0</v>
       </c>
       <c r="D290" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="291">
@@ -4202,10 +4202,10 @@
         <v>2023.0</v>
       </c>
       <c r="C291" t="n" s="2">
-        <v>45214.0</v>
+        <v>45158.0</v>
       </c>
       <c r="D291" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="292">
@@ -4216,10 +4216,10 @@
         <v>2023.0</v>
       </c>
       <c r="C292" t="n" s="2">
-        <v>45221.0</v>
+        <v>45207.0</v>
       </c>
       <c r="D292" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="293">
@@ -4230,10 +4230,10 @@
         <v>2023.0</v>
       </c>
       <c r="C293" t="n" s="2">
-        <v>45249.0</v>
+        <v>45214.0</v>
       </c>
       <c r="D293" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="294">
@@ -4244,10 +4244,10 @@
         <v>2023.0</v>
       </c>
       <c r="C294" t="n" s="2">
-        <v>45256.0</v>
+        <v>45221.0</v>
       </c>
       <c r="D294" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="295">
@@ -4258,10 +4258,10 @@
         <v>2023.0</v>
       </c>
       <c r="C295" t="n" s="2">
-        <v>45263.0</v>
+        <v>45249.0</v>
       </c>
       <c r="D295" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="296">
@@ -4272,10 +4272,10 @@
         <v>2023.0</v>
       </c>
       <c r="C296" t="n" s="2">
-        <v>45270.0</v>
+        <v>45256.0</v>
       </c>
       <c r="D296" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="297">
@@ -4286,7 +4286,7 @@
         <v>2023.0</v>
       </c>
       <c r="C297" t="n" s="2">
-        <v>45277.0</v>
+        <v>45263.0</v>
       </c>
       <c r="D297" t="n">
         <v>4.0</v>
@@ -4300,7 +4300,7 @@
         <v>2023.0</v>
       </c>
       <c r="C298" t="n" s="2">
-        <v>45284.0</v>
+        <v>45270.0</v>
       </c>
       <c r="D298" t="n">
         <v>1.0</v>
@@ -4314,10 +4314,10 @@
         <v>2023.0</v>
       </c>
       <c r="C299" t="n" s="2">
-        <v>45291.0</v>
+        <v>45277.0</v>
       </c>
       <c r="D299" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="300">
@@ -4325,13 +4325,13 @@
         <v>6</v>
       </c>
       <c r="B300" t="n">
-        <v>2024.0</v>
+        <v>2023.0</v>
       </c>
       <c r="C300" t="n" s="2">
-        <v>45306.0</v>
+        <v>45284.0</v>
       </c>
       <c r="D300" t="n">
-        <v>7.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="301">
@@ -4339,13 +4339,13 @@
         <v>6</v>
       </c>
       <c r="B301" t="n">
-        <v>2024.0</v>
+        <v>2023.0</v>
       </c>
       <c r="C301" t="n" s="2">
-        <v>45313.0</v>
+        <v>45291.0</v>
       </c>
       <c r="D301" t="n">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="302">
@@ -4356,10 +4356,10 @@
         <v>2024.0</v>
       </c>
       <c r="C302" t="n" s="2">
-        <v>45320.0</v>
+        <v>45306.0</v>
       </c>
       <c r="D302" t="n">
-        <v>19.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="303">
@@ -4370,10 +4370,10 @@
         <v>2024.0</v>
       </c>
       <c r="C303" t="n" s="2">
-        <v>45327.0</v>
+        <v>45313.0</v>
       </c>
       <c r="D303" t="n">
-        <v>18.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="304">
@@ -4384,10 +4384,10 @@
         <v>2024.0</v>
       </c>
       <c r="C304" t="n" s="2">
-        <v>45334.0</v>
+        <v>45320.0</v>
       </c>
       <c r="D304" t="n">
-        <v>9.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="305">
@@ -4398,10 +4398,10 @@
         <v>2024.0</v>
       </c>
       <c r="C305" t="n" s="2">
-        <v>45341.0</v>
+        <v>45327.0</v>
       </c>
       <c r="D305" t="n">
-        <v>12.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="306">
@@ -4412,10 +4412,10 @@
         <v>2024.0</v>
       </c>
       <c r="C306" t="n" s="2">
-        <v>45348.0</v>
+        <v>45334.0</v>
       </c>
       <c r="D306" t="n">
-        <v>12.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="307">
@@ -4426,10 +4426,10 @@
         <v>2024.0</v>
       </c>
       <c r="C307" t="n" s="2">
-        <v>45355.0</v>
+        <v>45341.0</v>
       </c>
       <c r="D307" t="n">
-        <v>10.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="308">
@@ -4440,7 +4440,7 @@
         <v>2024.0</v>
       </c>
       <c r="C308" t="n" s="2">
-        <v>45362.0</v>
+        <v>45348.0</v>
       </c>
       <c r="D308" t="n">
         <v>12.0</v>
@@ -4454,10 +4454,10 @@
         <v>2024.0</v>
       </c>
       <c r="C309" t="n" s="2">
-        <v>45369.0</v>
+        <v>45355.0</v>
       </c>
       <c r="D309" t="n">
-        <v>13.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="310">
@@ -4468,10 +4468,10 @@
         <v>2024.0</v>
       </c>
       <c r="C310" t="n" s="2">
-        <v>45376.0</v>
+        <v>45362.0</v>
       </c>
       <c r="D310" t="n">
-        <v>18.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="311">
@@ -4482,10 +4482,10 @@
         <v>2024.0</v>
       </c>
       <c r="C311" t="n" s="2">
-        <v>45383.0</v>
+        <v>45369.0</v>
       </c>
       <c r="D311" t="n">
-        <v>12.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="312">
@@ -4496,10 +4496,10 @@
         <v>2024.0</v>
       </c>
       <c r="C312" t="n" s="2">
-        <v>45390.0</v>
+        <v>45376.0</v>
       </c>
       <c r="D312" t="n">
-        <v>6.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="313">
@@ -4510,10 +4510,10 @@
         <v>2024.0</v>
       </c>
       <c r="C313" t="n" s="2">
-        <v>45397.0</v>
+        <v>45383.0</v>
       </c>
       <c r="D313" t="n">
-        <v>10.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="314">
@@ -4524,10 +4524,10 @@
         <v>2024.0</v>
       </c>
       <c r="C314" t="n" s="2">
-        <v>45404.0</v>
+        <v>45390.0</v>
       </c>
       <c r="D314" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="315">
@@ -4538,10 +4538,10 @@
         <v>2024.0</v>
       </c>
       <c r="C315" t="n" s="2">
-        <v>45411.0</v>
+        <v>45397.0</v>
       </c>
       <c r="D315" t="n">
-        <v>2.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="316">
@@ -4552,10 +4552,10 @@
         <v>2024.0</v>
       </c>
       <c r="C316" t="n" s="2">
-        <v>45418.0</v>
+        <v>45404.0</v>
       </c>
       <c r="D316" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="317">
@@ -4566,10 +4566,10 @@
         <v>2024.0</v>
       </c>
       <c r="C317" t="n" s="2">
-        <v>45425.0</v>
+        <v>45411.0</v>
       </c>
       <c r="D317" t="n">
-        <v>9.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="318">
@@ -4580,10 +4580,10 @@
         <v>2024.0</v>
       </c>
       <c r="C318" t="n" s="2">
-        <v>45432.0</v>
+        <v>45418.0</v>
       </c>
       <c r="D318" t="n">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="319">
@@ -4594,10 +4594,10 @@
         <v>2024.0</v>
       </c>
       <c r="C319" t="n" s="2">
-        <v>45439.0</v>
+        <v>45425.0</v>
       </c>
       <c r="D319" t="n">
-        <v>6.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="320">
@@ -4608,10 +4608,10 @@
         <v>2024.0</v>
       </c>
       <c r="C320" t="n" s="2">
-        <v>45446.0</v>
+        <v>45432.0</v>
       </c>
       <c r="D320" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="321">
@@ -4622,10 +4622,10 @@
         <v>2024.0</v>
       </c>
       <c r="C321" t="n" s="2">
-        <v>45453.0</v>
+        <v>45439.0</v>
       </c>
       <c r="D321" t="n">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="322">
@@ -4636,10 +4636,10 @@
         <v>2024.0</v>
       </c>
       <c r="C322" t="n" s="2">
-        <v>45460.0</v>
+        <v>45446.0</v>
       </c>
       <c r="D322" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="323">
@@ -4650,7 +4650,7 @@
         <v>2024.0</v>
       </c>
       <c r="C323" t="n" s="2">
-        <v>45467.0</v>
+        <v>45453.0</v>
       </c>
       <c r="D323" t="n">
         <v>4.0</v>
@@ -4664,10 +4664,10 @@
         <v>2024.0</v>
       </c>
       <c r="C324" t="n" s="2">
-        <v>45474.0</v>
+        <v>45460.0</v>
       </c>
       <c r="D324" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="325">
@@ -4678,10 +4678,10 @@
         <v>2024.0</v>
       </c>
       <c r="C325" t="n" s="2">
-        <v>45481.0</v>
+        <v>45467.0</v>
       </c>
       <c r="D325" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="326">
@@ -4692,7 +4692,7 @@
         <v>2024.0</v>
       </c>
       <c r="C326" t="n" s="2">
-        <v>45488.0</v>
+        <v>45474.0</v>
       </c>
       <c r="D326" t="n">
         <v>2.0</v>
@@ -4706,10 +4706,10 @@
         <v>2024.0</v>
       </c>
       <c r="C327" t="n" s="2">
-        <v>45495.0</v>
+        <v>45481.0</v>
       </c>
       <c r="D327" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="328">
@@ -4720,7 +4720,7 @@
         <v>2024.0</v>
       </c>
       <c r="C328" t="n" s="2">
-        <v>45502.0</v>
+        <v>45488.0</v>
       </c>
       <c r="D328" t="n">
         <v>2.0</v>
@@ -4734,10 +4734,10 @@
         <v>2024.0</v>
       </c>
       <c r="C329" t="n" s="2">
-        <v>45509.0</v>
+        <v>45495.0</v>
       </c>
       <c r="D329" t="n">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="330">
@@ -4748,10 +4748,10 @@
         <v>2024.0</v>
       </c>
       <c r="C330" t="n" s="2">
-        <v>45523.0</v>
+        <v>45502.0</v>
       </c>
       <c r="D330" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="331">
@@ -4762,7 +4762,7 @@
         <v>2024.0</v>
       </c>
       <c r="C331" t="n" s="2">
-        <v>45551.0</v>
+        <v>45509.0</v>
       </c>
       <c r="D331" t="n">
         <v>1.0</v>
@@ -4776,7 +4776,7 @@
         <v>2024.0</v>
       </c>
       <c r="C332" t="n" s="2">
-        <v>45558.0</v>
+        <v>45523.0</v>
       </c>
       <c r="D332" t="n">
         <v>1.0</v>
@@ -4790,10 +4790,10 @@
         <v>2024.0</v>
       </c>
       <c r="C333" t="n" s="2">
-        <v>45572.0</v>
+        <v>45551.0</v>
       </c>
       <c r="D333" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="334">
@@ -4804,7 +4804,7 @@
         <v>2024.0</v>
       </c>
       <c r="C334" t="n" s="2">
-        <v>45593.0</v>
+        <v>45558.0</v>
       </c>
       <c r="D334" t="n">
         <v>1.0</v>
@@ -4818,7 +4818,7 @@
         <v>2024.0</v>
       </c>
       <c r="C335" t="n" s="2">
-        <v>45614.0</v>
+        <v>45572.0</v>
       </c>
       <c r="D335" t="n">
         <v>2.0</v>
@@ -4832,7 +4832,7 @@
         <v>2024.0</v>
       </c>
       <c r="C336" t="n" s="2">
-        <v>45621.0</v>
+        <v>45593.0</v>
       </c>
       <c r="D336" t="n">
         <v>1.0</v>
@@ -4846,10 +4846,10 @@
         <v>2024.0</v>
       </c>
       <c r="C337" t="n" s="2">
-        <v>45635.0</v>
+        <v>45614.0</v>
       </c>
       <c r="D337" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="338">
@@ -4860,7 +4860,7 @@
         <v>2024.0</v>
       </c>
       <c r="C338" t="n" s="2">
-        <v>45649.0</v>
+        <v>45621.0</v>
       </c>
       <c r="D338" t="n">
         <v>1.0</v>
@@ -4871,13 +4871,13 @@
         <v>6</v>
       </c>
       <c r="B339" t="n">
-        <v>2025.0</v>
+        <v>2024.0</v>
       </c>
       <c r="C339" t="n" s="2">
-        <v>45665.0</v>
+        <v>45635.0</v>
       </c>
       <c r="D339" t="n">
-        <v>9.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="340">
@@ -4885,13 +4885,13 @@
         <v>6</v>
       </c>
       <c r="B340" t="n">
-        <v>2025.0</v>
+        <v>2024.0</v>
       </c>
       <c r="C340" t="n" s="2">
-        <v>45672.0</v>
+        <v>45649.0</v>
       </c>
       <c r="D340" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="341">
@@ -4902,10 +4902,10 @@
         <v>2025.0</v>
       </c>
       <c r="C341" t="n" s="2">
-        <v>45679.0</v>
+        <v>45665.0</v>
       </c>
       <c r="D341" t="n">
-        <v>1.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="342">
@@ -4916,10 +4916,10 @@
         <v>2025.0</v>
       </c>
       <c r="C342" t="n" s="2">
-        <v>45686.0</v>
+        <v>45672.0</v>
       </c>
       <c r="D342" t="n">
-        <v>8.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="343">
@@ -4930,10 +4930,10 @@
         <v>2025.0</v>
       </c>
       <c r="C343" t="n" s="2">
-        <v>45693.0</v>
+        <v>45679.0</v>
       </c>
       <c r="D343" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="344">
@@ -4944,10 +4944,10 @@
         <v>2025.0</v>
       </c>
       <c r="C344" t="n" s="2">
-        <v>45700.0</v>
+        <v>45686.0</v>
       </c>
       <c r="D344" t="n">
-        <v>5.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="345">
@@ -4958,10 +4958,10 @@
         <v>2025.0</v>
       </c>
       <c r="C345" t="n" s="2">
-        <v>45707.0</v>
+        <v>45693.0</v>
       </c>
       <c r="D345" t="n">
-        <v>8.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="346">
@@ -4972,10 +4972,10 @@
         <v>2025.0</v>
       </c>
       <c r="C346" t="n" s="2">
-        <v>45714.0</v>
+        <v>45700.0</v>
       </c>
       <c r="D346" t="n">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="347">
@@ -4986,7 +4986,7 @@
         <v>2025.0</v>
       </c>
       <c r="C347" t="n" s="2">
-        <v>45721.0</v>
+        <v>45707.0</v>
       </c>
       <c r="D347" t="n">
         <v>8.0</v>
@@ -5000,10 +5000,10 @@
         <v>2025.0</v>
       </c>
       <c r="C348" t="n" s="2">
-        <v>45728.0</v>
+        <v>45714.0</v>
       </c>
       <c r="D348" t="n">
-        <v>7.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="349">
@@ -5014,10 +5014,10 @@
         <v>2025.0</v>
       </c>
       <c r="C349" t="n" s="2">
-        <v>45735.0</v>
+        <v>45721.0</v>
       </c>
       <c r="D349" t="n">
-        <v>4.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="350">
@@ -5028,10 +5028,10 @@
         <v>2025.0</v>
       </c>
       <c r="C350" t="n" s="2">
-        <v>45742.0</v>
+        <v>45728.0</v>
       </c>
       <c r="D350" t="n">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="351">
@@ -5042,10 +5042,10 @@
         <v>2025.0</v>
       </c>
       <c r="C351" t="n" s="2">
-        <v>45749.0</v>
+        <v>45735.0</v>
       </c>
       <c r="D351" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="352">
@@ -5056,10 +5056,10 @@
         <v>2025.0</v>
       </c>
       <c r="C352" t="n" s="2">
-        <v>45756.0</v>
+        <v>45742.0</v>
       </c>
       <c r="D352" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="353">
@@ -5070,10 +5070,10 @@
         <v>2025.0</v>
       </c>
       <c r="C353" t="n" s="2">
-        <v>45763.0</v>
+        <v>45749.0</v>
       </c>
       <c r="D353" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="354">
@@ -5084,10 +5084,10 @@
         <v>2025.0</v>
       </c>
       <c r="C354" t="n" s="2">
-        <v>45770.0</v>
+        <v>45756.0</v>
       </c>
       <c r="D354" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="355">
@@ -5098,10 +5098,10 @@
         <v>2025.0</v>
       </c>
       <c r="C355" t="n" s="2">
-        <v>45777.0</v>
+        <v>45763.0</v>
       </c>
       <c r="D355" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="356">
@@ -5112,10 +5112,10 @@
         <v>2025.0</v>
       </c>
       <c r="C356" t="n" s="2">
-        <v>45784.0</v>
+        <v>45770.0</v>
       </c>
       <c r="D356" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="357">
@@ -5126,7 +5126,7 @@
         <v>2025.0</v>
       </c>
       <c r="C357" t="n" s="2">
-        <v>45791.0</v>
+        <v>45777.0</v>
       </c>
       <c r="D357" t="n">
         <v>1.0</v>
@@ -5140,7 +5140,7 @@
         <v>2025.0</v>
       </c>
       <c r="C358" t="n" s="2">
-        <v>45840.0</v>
+        <v>45784.0</v>
       </c>
       <c r="D358" t="n">
         <v>1.0</v>
@@ -5154,7 +5154,7 @@
         <v>2025.0</v>
       </c>
       <c r="C359" t="n" s="2">
-        <v>46001.0</v>
+        <v>45791.0</v>
       </c>
       <c r="D359" t="n">
         <v>1.0</v>
@@ -5165,10 +5165,10 @@
         <v>6</v>
       </c>
       <c r="B360" t="n">
-        <v>2026.0</v>
+        <v>2025.0</v>
       </c>
       <c r="C360" t="n" s="2">
-        <v>46037.0</v>
+        <v>45840.0</v>
       </c>
       <c r="D360" t="n">
         <v>1.0</v>
@@ -5176,13 +5176,13 @@
     </row>
     <row r="361">
       <c r="A361" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B361" t="n">
-        <v>2021.0</v>
+        <v>2025.0</v>
       </c>
       <c r="C361" t="n" s="2">
-        <v>44561.0</v>
+        <v>46001.0</v>
       </c>
       <c r="D361" t="n">
         <v>1.0</v>
@@ -5190,13 +5190,13 @@
     </row>
     <row r="362">
       <c r="A362" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B362" t="n">
-        <v>2022.0</v>
+        <v>2026.0</v>
       </c>
       <c r="C362" t="n" s="2">
-        <v>44569.0</v>
+        <v>46037.0</v>
       </c>
       <c r="D362" t="n">
         <v>1.0</v>
@@ -5207,13 +5207,13 @@
         <v>7</v>
       </c>
       <c r="B363" t="n">
-        <v>2022.0</v>
+        <v>2021.0</v>
       </c>
       <c r="C363" t="n" s="2">
-        <v>44576.0</v>
+        <v>44561.0</v>
       </c>
       <c r="D363" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="364">
@@ -5224,10 +5224,10 @@
         <v>2022.0</v>
       </c>
       <c r="C364" t="n" s="2">
-        <v>44583.0</v>
+        <v>44569.0</v>
       </c>
       <c r="D364" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="365">
@@ -5238,10 +5238,10 @@
         <v>2022.0</v>
       </c>
       <c r="C365" t="n" s="2">
-        <v>44590.0</v>
+        <v>44576.0</v>
       </c>
       <c r="D365" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="366">
@@ -5252,10 +5252,10 @@
         <v>2022.0</v>
       </c>
       <c r="C366" t="n" s="2">
-        <v>44604.0</v>
+        <v>44583.0</v>
       </c>
       <c r="D366" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="367">
@@ -5266,10 +5266,10 @@
         <v>2022.0</v>
       </c>
       <c r="C367" t="n" s="2">
-        <v>44611.0</v>
+        <v>44590.0</v>
       </c>
       <c r="D367" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="368">
@@ -5280,10 +5280,10 @@
         <v>2022.0</v>
       </c>
       <c r="C368" t="n" s="2">
-        <v>44618.0</v>
+        <v>44604.0</v>
       </c>
       <c r="D368" t="n">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="369">
@@ -5294,10 +5294,10 @@
         <v>2022.0</v>
       </c>
       <c r="C369" t="n" s="2">
-        <v>44625.0</v>
+        <v>44611.0</v>
       </c>
       <c r="D369" t="n">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="370">
@@ -5308,10 +5308,10 @@
         <v>2022.0</v>
       </c>
       <c r="C370" t="n" s="2">
-        <v>44632.0</v>
+        <v>44618.0</v>
       </c>
       <c r="D370" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="371">
@@ -5322,10 +5322,10 @@
         <v>2022.0</v>
       </c>
       <c r="C371" t="n" s="2">
-        <v>44639.0</v>
+        <v>44625.0</v>
       </c>
       <c r="D371" t="n">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="372">
@@ -5336,7 +5336,7 @@
         <v>2022.0</v>
       </c>
       <c r="C372" t="n" s="2">
-        <v>44646.0</v>
+        <v>44632.0</v>
       </c>
       <c r="D372" t="n">
         <v>3.0</v>
@@ -5350,10 +5350,10 @@
         <v>2022.0</v>
       </c>
       <c r="C373" t="n" s="2">
-        <v>44653.0</v>
+        <v>44639.0</v>
       </c>
       <c r="D373" t="n">
-        <v>9.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="374">
@@ -5364,10 +5364,10 @@
         <v>2022.0</v>
       </c>
       <c r="C374" t="n" s="2">
-        <v>44660.0</v>
+        <v>44646.0</v>
       </c>
       <c r="D374" t="n">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="375">
@@ -5378,10 +5378,10 @@
         <v>2022.0</v>
       </c>
       <c r="C375" t="n" s="2">
-        <v>44667.0</v>
+        <v>44653.0</v>
       </c>
       <c r="D375" t="n">
-        <v>2.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="376">
@@ -5392,10 +5392,10 @@
         <v>2022.0</v>
       </c>
       <c r="C376" t="n" s="2">
-        <v>44674.0</v>
+        <v>44660.0</v>
       </c>
       <c r="D376" t="n">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="377">
@@ -5406,7 +5406,7 @@
         <v>2022.0</v>
       </c>
       <c r="C377" t="n" s="2">
-        <v>44681.0</v>
+        <v>44667.0</v>
       </c>
       <c r="D377" t="n">
         <v>2.0</v>
@@ -5420,10 +5420,10 @@
         <v>2022.0</v>
       </c>
       <c r="C378" t="n" s="2">
-        <v>44688.0</v>
+        <v>44674.0</v>
       </c>
       <c r="D378" t="n">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="379">
@@ -5434,10 +5434,10 @@
         <v>2022.0</v>
       </c>
       <c r="C379" t="n" s="2">
-        <v>44695.0</v>
+        <v>44681.0</v>
       </c>
       <c r="D379" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="380">
@@ -5448,10 +5448,10 @@
         <v>2022.0</v>
       </c>
       <c r="C380" t="n" s="2">
-        <v>44702.0</v>
+        <v>44688.0</v>
       </c>
       <c r="D380" t="n">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="381">
@@ -5462,10 +5462,10 @@
         <v>2022.0</v>
       </c>
       <c r="C381" t="n" s="2">
-        <v>44709.0</v>
+        <v>44695.0</v>
       </c>
       <c r="D381" t="n">
-        <v>8.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="382">
@@ -5476,10 +5476,10 @@
         <v>2022.0</v>
       </c>
       <c r="C382" t="n" s="2">
-        <v>44716.0</v>
+        <v>44702.0</v>
       </c>
       <c r="D382" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="383">
@@ -5490,10 +5490,10 @@
         <v>2022.0</v>
       </c>
       <c r="C383" t="n" s="2">
-        <v>44723.0</v>
+        <v>44709.0</v>
       </c>
       <c r="D383" t="n">
-        <v>2.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="384">
@@ -5504,10 +5504,10 @@
         <v>2022.0</v>
       </c>
       <c r="C384" t="n" s="2">
-        <v>44730.0</v>
+        <v>44716.0</v>
       </c>
       <c r="D384" t="n">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="385">
@@ -5518,10 +5518,10 @@
         <v>2022.0</v>
       </c>
       <c r="C385" t="n" s="2">
-        <v>44737.0</v>
+        <v>44723.0</v>
       </c>
       <c r="D385" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="386">
@@ -5532,10 +5532,10 @@
         <v>2022.0</v>
       </c>
       <c r="C386" t="n" s="2">
-        <v>44744.0</v>
+        <v>44730.0</v>
       </c>
       <c r="D386" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="387">
@@ -5546,7 +5546,7 @@
         <v>2022.0</v>
       </c>
       <c r="C387" t="n" s="2">
-        <v>44751.0</v>
+        <v>44737.0</v>
       </c>
       <c r="D387" t="n">
         <v>4.0</v>
@@ -5560,10 +5560,10 @@
         <v>2022.0</v>
       </c>
       <c r="C388" t="n" s="2">
-        <v>44758.0</v>
+        <v>44744.0</v>
       </c>
       <c r="D388" t="n">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="389">
@@ -5574,10 +5574,10 @@
         <v>2022.0</v>
       </c>
       <c r="C389" t="n" s="2">
-        <v>44765.0</v>
+        <v>44751.0</v>
       </c>
       <c r="D389" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="390">
@@ -5588,10 +5588,10 @@
         <v>2022.0</v>
       </c>
       <c r="C390" t="n" s="2">
-        <v>44779.0</v>
+        <v>44758.0</v>
       </c>
       <c r="D390" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="391">
@@ -5602,7 +5602,7 @@
         <v>2022.0</v>
       </c>
       <c r="C391" t="n" s="2">
-        <v>44786.0</v>
+        <v>44765.0</v>
       </c>
       <c r="D391" t="n">
         <v>1.0</v>
@@ -5616,10 +5616,10 @@
         <v>2022.0</v>
       </c>
       <c r="C392" t="n" s="2">
-        <v>44863.0</v>
+        <v>44779.0</v>
       </c>
       <c r="D392" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="393">
@@ -5630,7 +5630,7 @@
         <v>2022.0</v>
       </c>
       <c r="C393" t="n" s="2">
-        <v>44870.0</v>
+        <v>44786.0</v>
       </c>
       <c r="D393" t="n">
         <v>1.0</v>
@@ -5644,7 +5644,7 @@
         <v>2022.0</v>
       </c>
       <c r="C394" t="n" s="2">
-        <v>44884.0</v>
+        <v>44863.0</v>
       </c>
       <c r="D394" t="n">
         <v>2.0</v>
@@ -5658,10 +5658,10 @@
         <v>2022.0</v>
       </c>
       <c r="C395" t="n" s="2">
-        <v>44891.0</v>
+        <v>44870.0</v>
       </c>
       <c r="D395" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="396">
@@ -5672,10 +5672,10 @@
         <v>2022.0</v>
       </c>
       <c r="C396" t="n" s="2">
-        <v>44898.0</v>
+        <v>44884.0</v>
       </c>
       <c r="D396" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="397">
@@ -5686,10 +5686,10 @@
         <v>2022.0</v>
       </c>
       <c r="C397" t="n" s="2">
-        <v>44912.0</v>
+        <v>44891.0</v>
       </c>
       <c r="D397" t="n">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="398">
@@ -5700,10 +5700,10 @@
         <v>2022.0</v>
       </c>
       <c r="C398" t="n" s="2">
-        <v>44919.0</v>
+        <v>44898.0</v>
       </c>
       <c r="D398" t="n">
-        <v>7.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="399">
@@ -5714,10 +5714,10 @@
         <v>2022.0</v>
       </c>
       <c r="C399" t="n" s="2">
-        <v>44926.0</v>
+        <v>44912.0</v>
       </c>
       <c r="D399" t="n">
-        <v>12.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="400">
@@ -5725,13 +5725,13 @@
         <v>7</v>
       </c>
       <c r="B400" t="n">
-        <v>2023.0</v>
+        <v>2022.0</v>
       </c>
       <c r="C400" t="n" s="2">
-        <v>44934.0</v>
+        <v>44919.0</v>
       </c>
       <c r="D400" t="n">
-        <v>4.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="401">
@@ -5739,13 +5739,13 @@
         <v>7</v>
       </c>
       <c r="B401" t="n">
-        <v>2023.0</v>
+        <v>2022.0</v>
       </c>
       <c r="C401" t="n" s="2">
-        <v>44941.0</v>
+        <v>44926.0</v>
       </c>
       <c r="D401" t="n">
-        <v>16.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="402">
@@ -5756,10 +5756,10 @@
         <v>2023.0</v>
       </c>
       <c r="C402" t="n" s="2">
-        <v>44948.0</v>
+        <v>44934.0</v>
       </c>
       <c r="D402" t="n">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="403">
@@ -5770,10 +5770,10 @@
         <v>2023.0</v>
       </c>
       <c r="C403" t="n" s="2">
-        <v>44955.0</v>
+        <v>44941.0</v>
       </c>
       <c r="D403" t="n">
-        <v>19.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="404">
@@ -5784,10 +5784,10 @@
         <v>2023.0</v>
       </c>
       <c r="C404" t="n" s="2">
-        <v>44962.0</v>
+        <v>44948.0</v>
       </c>
       <c r="D404" t="n">
-        <v>22.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="405">
@@ -5798,10 +5798,10 @@
         <v>2023.0</v>
       </c>
       <c r="C405" t="n" s="2">
-        <v>44969.0</v>
+        <v>44955.0</v>
       </c>
       <c r="D405" t="n">
-        <v>9.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="406">
@@ -5812,7 +5812,7 @@
         <v>2023.0</v>
       </c>
       <c r="C406" t="n" s="2">
-        <v>44976.0</v>
+        <v>44962.0</v>
       </c>
       <c r="D406" t="n">
         <v>22.0</v>
@@ -5826,10 +5826,10 @@
         <v>2023.0</v>
       </c>
       <c r="C407" t="n" s="2">
-        <v>44983.0</v>
+        <v>44969.0</v>
       </c>
       <c r="D407" t="n">
-        <v>29.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="408">
@@ -5840,10 +5840,10 @@
         <v>2023.0</v>
       </c>
       <c r="C408" t="n" s="2">
-        <v>44990.0</v>
+        <v>44976.0</v>
       </c>
       <c r="D408" t="n">
-        <v>5.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="409">
@@ -5854,10 +5854,10 @@
         <v>2023.0</v>
       </c>
       <c r="C409" t="n" s="2">
-        <v>44997.0</v>
+        <v>44983.0</v>
       </c>
       <c r="D409" t="n">
-        <v>24.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="410">
@@ -5868,10 +5868,10 @@
         <v>2023.0</v>
       </c>
       <c r="C410" t="n" s="2">
-        <v>45004.0</v>
+        <v>44990.0</v>
       </c>
       <c r="D410" t="n">
-        <v>8.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="411">
@@ -5882,10 +5882,10 @@
         <v>2023.0</v>
       </c>
       <c r="C411" t="n" s="2">
-        <v>45011.0</v>
+        <v>44997.0</v>
       </c>
       <c r="D411" t="n">
-        <v>10.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="412">
@@ -5896,10 +5896,10 @@
         <v>2023.0</v>
       </c>
       <c r="C412" t="n" s="2">
-        <v>45018.0</v>
+        <v>45004.0</v>
       </c>
       <c r="D412" t="n">
-        <v>18.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="413">
@@ -5910,10 +5910,10 @@
         <v>2023.0</v>
       </c>
       <c r="C413" t="n" s="2">
-        <v>45025.0</v>
+        <v>45011.0</v>
       </c>
       <c r="D413" t="n">
-        <v>13.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="414">
@@ -5924,7 +5924,7 @@
         <v>2023.0</v>
       </c>
       <c r="C414" t="n" s="2">
-        <v>45032.0</v>
+        <v>45018.0</v>
       </c>
       <c r="D414" t="n">
         <v>18.0</v>
@@ -5938,10 +5938,10 @@
         <v>2023.0</v>
       </c>
       <c r="C415" t="n" s="2">
-        <v>45039.0</v>
+        <v>45025.0</v>
       </c>
       <c r="D415" t="n">
-        <v>15.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="416">
@@ -5952,10 +5952,10 @@
         <v>2023.0</v>
       </c>
       <c r="C416" t="n" s="2">
-        <v>45046.0</v>
+        <v>45032.0</v>
       </c>
       <c r="D416" t="n">
-        <v>12.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="417">
@@ -5966,10 +5966,10 @@
         <v>2023.0</v>
       </c>
       <c r="C417" t="n" s="2">
-        <v>45053.0</v>
+        <v>45039.0</v>
       </c>
       <c r="D417" t="n">
-        <v>6.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="418">
@@ -5980,10 +5980,10 @@
         <v>2023.0</v>
       </c>
       <c r="C418" t="n" s="2">
-        <v>45060.0</v>
+        <v>45046.0</v>
       </c>
       <c r="D418" t="n">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="419">
@@ -5994,10 +5994,10 @@
         <v>2023.0</v>
       </c>
       <c r="C419" t="n" s="2">
-        <v>45067.0</v>
+        <v>45053.0</v>
       </c>
       <c r="D419" t="n">
-        <v>8.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="420">
@@ -6008,10 +6008,10 @@
         <v>2023.0</v>
       </c>
       <c r="C420" t="n" s="2">
-        <v>45074.0</v>
+        <v>45060.0</v>
       </c>
       <c r="D420" t="n">
-        <v>8.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="421">
@@ -6022,10 +6022,10 @@
         <v>2023.0</v>
       </c>
       <c r="C421" t="n" s="2">
-        <v>45081.0</v>
+        <v>45067.0</v>
       </c>
       <c r="D421" t="n">
-        <v>5.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="422">
@@ -6036,10 +6036,10 @@
         <v>2023.0</v>
       </c>
       <c r="C422" t="n" s="2">
-        <v>45088.0</v>
+        <v>45074.0</v>
       </c>
       <c r="D422" t="n">
-        <v>2.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="423">
@@ -6050,7 +6050,7 @@
         <v>2023.0</v>
       </c>
       <c r="C423" t="n" s="2">
-        <v>45095.0</v>
+        <v>45081.0</v>
       </c>
       <c r="D423" t="n">
         <v>5.0</v>
@@ -6064,10 +6064,10 @@
         <v>2023.0</v>
       </c>
       <c r="C424" t="n" s="2">
-        <v>45102.0</v>
+        <v>45088.0</v>
       </c>
       <c r="D424" t="n">
-        <v>10.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="425">
@@ -6078,10 +6078,10 @@
         <v>2023.0</v>
       </c>
       <c r="C425" t="n" s="2">
-        <v>45109.0</v>
+        <v>45095.0</v>
       </c>
       <c r="D425" t="n">
-        <v>9.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="426">
@@ -6092,10 +6092,10 @@
         <v>2023.0</v>
       </c>
       <c r="C426" t="n" s="2">
-        <v>45116.0</v>
+        <v>45102.0</v>
       </c>
       <c r="D426" t="n">
-        <v>3.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="427">
@@ -6106,10 +6106,10 @@
         <v>2023.0</v>
       </c>
       <c r="C427" t="n" s="2">
-        <v>45123.0</v>
+        <v>45109.0</v>
       </c>
       <c r="D427" t="n">
-        <v>6.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="428">
@@ -6120,10 +6120,10 @@
         <v>2023.0</v>
       </c>
       <c r="C428" t="n" s="2">
-        <v>45130.0</v>
+        <v>45116.0</v>
       </c>
       <c r="D428" t="n">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="429">
@@ -6134,10 +6134,10 @@
         <v>2023.0</v>
       </c>
       <c r="C429" t="n" s="2">
-        <v>45137.0</v>
+        <v>45123.0</v>
       </c>
       <c r="D429" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="430">
@@ -6148,10 +6148,10 @@
         <v>2023.0</v>
       </c>
       <c r="C430" t="n" s="2">
-        <v>45144.0</v>
+        <v>45130.0</v>
       </c>
       <c r="D430" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="431">
@@ -6162,7 +6162,7 @@
         <v>2023.0</v>
       </c>
       <c r="C431" t="n" s="2">
-        <v>45151.0</v>
+        <v>45137.0</v>
       </c>
       <c r="D431" t="n">
         <v>2.0</v>
@@ -6176,7 +6176,7 @@
         <v>2023.0</v>
       </c>
       <c r="C432" t="n" s="2">
-        <v>45165.0</v>
+        <v>45144.0</v>
       </c>
       <c r="D432" t="n">
         <v>2.0</v>
@@ -6190,7 +6190,7 @@
         <v>2023.0</v>
       </c>
       <c r="C433" t="n" s="2">
-        <v>45172.0</v>
+        <v>45151.0</v>
       </c>
       <c r="D433" t="n">
         <v>2.0</v>
@@ -6204,10 +6204,10 @@
         <v>2023.0</v>
       </c>
       <c r="C434" t="n" s="2">
-        <v>45179.0</v>
+        <v>45165.0</v>
       </c>
       <c r="D434" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="435">
@@ -6218,10 +6218,10 @@
         <v>2023.0</v>
       </c>
       <c r="C435" t="n" s="2">
-        <v>45186.0</v>
+        <v>45172.0</v>
       </c>
       <c r="D435" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="436">
@@ -6232,7 +6232,7 @@
         <v>2023.0</v>
       </c>
       <c r="C436" t="n" s="2">
-        <v>45193.0</v>
+        <v>45179.0</v>
       </c>
       <c r="D436" t="n">
         <v>1.0</v>
@@ -6246,7 +6246,7 @@
         <v>2023.0</v>
       </c>
       <c r="C437" t="n" s="2">
-        <v>45200.0</v>
+        <v>45186.0</v>
       </c>
       <c r="D437" t="n">
         <v>1.0</v>
@@ -6260,7 +6260,7 @@
         <v>2023.0</v>
       </c>
       <c r="C438" t="n" s="2">
-        <v>45207.0</v>
+        <v>45193.0</v>
       </c>
       <c r="D438" t="n">
         <v>1.0</v>
@@ -6274,7 +6274,7 @@
         <v>2023.0</v>
       </c>
       <c r="C439" t="n" s="2">
-        <v>45235.0</v>
+        <v>45200.0</v>
       </c>
       <c r="D439" t="n">
         <v>1.0</v>
@@ -6288,10 +6288,10 @@
         <v>2023.0</v>
       </c>
       <c r="C440" t="n" s="2">
-        <v>45242.0</v>
+        <v>45207.0</v>
       </c>
       <c r="D440" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="441">
@@ -6302,10 +6302,10 @@
         <v>2023.0</v>
       </c>
       <c r="C441" t="n" s="2">
-        <v>45249.0</v>
+        <v>45235.0</v>
       </c>
       <c r="D441" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="442">
@@ -6316,10 +6316,10 @@
         <v>2023.0</v>
       </c>
       <c r="C442" t="n" s="2">
-        <v>45256.0</v>
+        <v>45242.0</v>
       </c>
       <c r="D442" t="n">
-        <v>9.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="443">
@@ -6330,10 +6330,10 @@
         <v>2023.0</v>
       </c>
       <c r="C443" t="n" s="2">
-        <v>45263.0</v>
+        <v>45249.0</v>
       </c>
       <c r="D443" t="n">
-        <v>12.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="444">
@@ -6344,10 +6344,10 @@
         <v>2023.0</v>
       </c>
       <c r="C444" t="n" s="2">
-        <v>45270.0</v>
+        <v>45256.0</v>
       </c>
       <c r="D444" t="n">
-        <v>6.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="445">
@@ -6358,10 +6358,10 @@
         <v>2023.0</v>
       </c>
       <c r="C445" t="n" s="2">
-        <v>45277.0</v>
+        <v>45263.0</v>
       </c>
       <c r="D445" t="n">
-        <v>7.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="446">
@@ -6372,10 +6372,10 @@
         <v>2023.0</v>
       </c>
       <c r="C446" t="n" s="2">
-        <v>45284.0</v>
+        <v>45270.0</v>
       </c>
       <c r="D446" t="n">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="447">
@@ -6386,10 +6386,10 @@
         <v>2023.0</v>
       </c>
       <c r="C447" t="n" s="2">
-        <v>45291.0</v>
+        <v>45277.0</v>
       </c>
       <c r="D447" t="n">
-        <v>13.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="448">
@@ -6397,13 +6397,13 @@
         <v>7</v>
       </c>
       <c r="B448" t="n">
-        <v>2024.0</v>
+        <v>2023.0</v>
       </c>
       <c r="C448" t="n" s="2">
-        <v>45299.0</v>
+        <v>45284.0</v>
       </c>
       <c r="D448" t="n">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="449">
@@ -6411,13 +6411,13 @@
         <v>7</v>
       </c>
       <c r="B449" t="n">
-        <v>2024.0</v>
+        <v>2023.0</v>
       </c>
       <c r="C449" t="n" s="2">
-        <v>45306.0</v>
+        <v>45291.0</v>
       </c>
       <c r="D449" t="n">
-        <v>11.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="450">
@@ -6428,10 +6428,10 @@
         <v>2024.0</v>
       </c>
       <c r="C450" t="n" s="2">
-        <v>45313.0</v>
+        <v>45299.0</v>
       </c>
       <c r="D450" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="451">
@@ -6442,10 +6442,10 @@
         <v>2024.0</v>
       </c>
       <c r="C451" t="n" s="2">
-        <v>45320.0</v>
+        <v>45306.0</v>
       </c>
       <c r="D451" t="n">
-        <v>2.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="452">
@@ -6456,10 +6456,10 @@
         <v>2024.0</v>
       </c>
       <c r="C452" t="n" s="2">
-        <v>45327.0</v>
+        <v>45313.0</v>
       </c>
       <c r="D452" t="n">
-        <v>9.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="453">
@@ -6470,10 +6470,10 @@
         <v>2024.0</v>
       </c>
       <c r="C453" t="n" s="2">
-        <v>45334.0</v>
+        <v>45320.0</v>
       </c>
       <c r="D453" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="454">
@@ -6484,10 +6484,10 @@
         <v>2024.0</v>
       </c>
       <c r="C454" t="n" s="2">
-        <v>45341.0</v>
+        <v>45327.0</v>
       </c>
       <c r="D454" t="n">
-        <v>21.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="455">
@@ -6498,10 +6498,10 @@
         <v>2024.0</v>
       </c>
       <c r="C455" t="n" s="2">
-        <v>45348.0</v>
+        <v>45334.0</v>
       </c>
       <c r="D455" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="456">
@@ -6512,10 +6512,10 @@
         <v>2024.0</v>
       </c>
       <c r="C456" t="n" s="2">
-        <v>45355.0</v>
+        <v>45341.0</v>
       </c>
       <c r="D456" t="n">
-        <v>9.0</v>
+        <v>21.0</v>
       </c>
     </row>
     <row r="457">
@@ -6526,10 +6526,10 @@
         <v>2024.0</v>
       </c>
       <c r="C457" t="n" s="2">
-        <v>45362.0</v>
+        <v>45348.0</v>
       </c>
       <c r="D457" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="458">
@@ -6540,10 +6540,10 @@
         <v>2024.0</v>
       </c>
       <c r="C458" t="n" s="2">
-        <v>45369.0</v>
+        <v>45355.0</v>
       </c>
       <c r="D458" t="n">
-        <v>14.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="459">
@@ -6554,7 +6554,7 @@
         <v>2024.0</v>
       </c>
       <c r="C459" t="n" s="2">
-        <v>45376.0</v>
+        <v>45362.0</v>
       </c>
       <c r="D459" t="n">
         <v>4.0</v>
@@ -6568,10 +6568,10 @@
         <v>2024.0</v>
       </c>
       <c r="C460" t="n" s="2">
-        <v>45383.0</v>
+        <v>45369.0</v>
       </c>
       <c r="D460" t="n">
-        <v>2.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="461">
@@ -6582,10 +6582,10 @@
         <v>2024.0</v>
       </c>
       <c r="C461" t="n" s="2">
-        <v>45390.0</v>
+        <v>45376.0</v>
       </c>
       <c r="D461" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="462">
@@ -6596,10 +6596,10 @@
         <v>2024.0</v>
       </c>
       <c r="C462" t="n" s="2">
-        <v>45397.0</v>
+        <v>45383.0</v>
       </c>
       <c r="D462" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="463">
@@ -6610,10 +6610,10 @@
         <v>2024.0</v>
       </c>
       <c r="C463" t="n" s="2">
-        <v>45404.0</v>
+        <v>45390.0</v>
       </c>
       <c r="D463" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="464">
@@ -6624,7 +6624,7 @@
         <v>2024.0</v>
       </c>
       <c r="C464" t="n" s="2">
-        <v>45411.0</v>
+        <v>45397.0</v>
       </c>
       <c r="D464" t="n">
         <v>1.0</v>
@@ -6638,7 +6638,7 @@
         <v>2024.0</v>
       </c>
       <c r="C465" t="n" s="2">
-        <v>45439.0</v>
+        <v>45404.0</v>
       </c>
       <c r="D465" t="n">
         <v>2.0</v>
@@ -6652,7 +6652,7 @@
         <v>2024.0</v>
       </c>
       <c r="C466" t="n" s="2">
-        <v>45446.0</v>
+        <v>45411.0</v>
       </c>
       <c r="D466" t="n">
         <v>1.0</v>
@@ -6666,10 +6666,10 @@
         <v>2024.0</v>
       </c>
       <c r="C467" t="n" s="2">
-        <v>45460.0</v>
+        <v>45439.0</v>
       </c>
       <c r="D467" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="468">
@@ -6680,7 +6680,7 @@
         <v>2024.0</v>
       </c>
       <c r="C468" t="n" s="2">
-        <v>45481.0</v>
+        <v>45446.0</v>
       </c>
       <c r="D468" t="n">
         <v>1.0</v>
@@ -6694,7 +6694,7 @@
         <v>2024.0</v>
       </c>
       <c r="C469" t="n" s="2">
-        <v>45516.0</v>
+        <v>45460.0</v>
       </c>
       <c r="D469" t="n">
         <v>1.0</v>
@@ -6708,7 +6708,7 @@
         <v>2024.0</v>
       </c>
       <c r="C470" t="n" s="2">
-        <v>45551.0</v>
+        <v>45481.0</v>
       </c>
       <c r="D470" t="n">
         <v>1.0</v>
@@ -6722,7 +6722,7 @@
         <v>2024.0</v>
       </c>
       <c r="C471" t="n" s="2">
-        <v>45579.0</v>
+        <v>45516.0</v>
       </c>
       <c r="D471" t="n">
         <v>1.0</v>
@@ -6736,7 +6736,7 @@
         <v>2024.0</v>
       </c>
       <c r="C472" t="n" s="2">
-        <v>45614.0</v>
+        <v>45551.0</v>
       </c>
       <c r="D472" t="n">
         <v>1.0</v>
@@ -6750,10 +6750,10 @@
         <v>2024.0</v>
       </c>
       <c r="C473" t="n" s="2">
-        <v>45635.0</v>
+        <v>45579.0</v>
       </c>
       <c r="D473" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="474">
@@ -6764,10 +6764,10 @@
         <v>2024.0</v>
       </c>
       <c r="C474" t="n" s="2">
-        <v>45642.0</v>
+        <v>45614.0</v>
       </c>
       <c r="D474" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="475">
@@ -6778,10 +6778,10 @@
         <v>2024.0</v>
       </c>
       <c r="C475" t="n" s="2">
-        <v>45649.0</v>
+        <v>45635.0</v>
       </c>
       <c r="D475" t="n">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="476">
@@ -6792,7 +6792,7 @@
         <v>2024.0</v>
       </c>
       <c r="C476" t="n" s="2">
-        <v>45656.0</v>
+        <v>45642.0</v>
       </c>
       <c r="D476" t="n">
         <v>2.0</v>
@@ -6803,13 +6803,13 @@
         <v>7</v>
       </c>
       <c r="B477" t="n">
-        <v>2025.0</v>
+        <v>2024.0</v>
       </c>
       <c r="C477" t="n" s="2">
-        <v>45665.0</v>
+        <v>45649.0</v>
       </c>
       <c r="D477" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="478">
@@ -6817,10 +6817,10 @@
         <v>7</v>
       </c>
       <c r="B478" t="n">
-        <v>2025.0</v>
+        <v>2024.0</v>
       </c>
       <c r="C478" t="n" s="2">
-        <v>45672.0</v>
+        <v>45656.0</v>
       </c>
       <c r="D478" t="n">
         <v>2.0</v>
@@ -6834,10 +6834,10 @@
         <v>2025.0</v>
       </c>
       <c r="C479" t="n" s="2">
-        <v>45686.0</v>
+        <v>45665.0</v>
       </c>
       <c r="D479" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="480">
@@ -6848,10 +6848,10 @@
         <v>2025.0</v>
       </c>
       <c r="C480" t="n" s="2">
-        <v>45693.0</v>
+        <v>45672.0</v>
       </c>
       <c r="D480" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="481">
@@ -6862,10 +6862,10 @@
         <v>2025.0</v>
       </c>
       <c r="C481" t="n" s="2">
-        <v>45700.0</v>
+        <v>45686.0</v>
       </c>
       <c r="D481" t="n">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="482">
@@ -6876,10 +6876,10 @@
         <v>2025.0</v>
       </c>
       <c r="C482" t="n" s="2">
-        <v>45707.0</v>
+        <v>45693.0</v>
       </c>
       <c r="D482" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="483">
@@ -6890,10 +6890,10 @@
         <v>2025.0</v>
       </c>
       <c r="C483" t="n" s="2">
-        <v>45714.0</v>
+        <v>45700.0</v>
       </c>
       <c r="D483" t="n">
-        <v>8.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="484">
@@ -6904,10 +6904,10 @@
         <v>2025.0</v>
       </c>
       <c r="C484" t="n" s="2">
-        <v>45721.0</v>
+        <v>45707.0</v>
       </c>
       <c r="D484" t="n">
-        <v>11.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="485">
@@ -6918,10 +6918,10 @@
         <v>2025.0</v>
       </c>
       <c r="C485" t="n" s="2">
-        <v>45728.0</v>
+        <v>45714.0</v>
       </c>
       <c r="D485" t="n">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="486">
@@ -6932,10 +6932,10 @@
         <v>2025.0</v>
       </c>
       <c r="C486" t="n" s="2">
-        <v>45735.0</v>
+        <v>45721.0</v>
       </c>
       <c r="D486" t="n">
-        <v>19.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="487">
@@ -6946,10 +6946,10 @@
         <v>2025.0</v>
       </c>
       <c r="C487" t="n" s="2">
-        <v>45742.0</v>
+        <v>45728.0</v>
       </c>
       <c r="D487" t="n">
-        <v>17.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="488">
@@ -6960,10 +6960,10 @@
         <v>2025.0</v>
       </c>
       <c r="C488" t="n" s="2">
-        <v>45749.0</v>
+        <v>45735.0</v>
       </c>
       <c r="D488" t="n">
-        <v>5.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="489">
@@ -6974,10 +6974,10 @@
         <v>2025.0</v>
       </c>
       <c r="C489" t="n" s="2">
-        <v>45756.0</v>
+        <v>45742.0</v>
       </c>
       <c r="D489" t="n">
-        <v>9.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="490">
@@ -6988,10 +6988,10 @@
         <v>2025.0</v>
       </c>
       <c r="C490" t="n" s="2">
-        <v>45763.0</v>
+        <v>45749.0</v>
       </c>
       <c r="D490" t="n">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="491">
@@ -7002,10 +7002,10 @@
         <v>2025.0</v>
       </c>
       <c r="C491" t="n" s="2">
-        <v>45770.0</v>
+        <v>45756.0</v>
       </c>
       <c r="D491" t="n">
-        <v>1.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="492">
@@ -7016,10 +7016,10 @@
         <v>2025.0</v>
       </c>
       <c r="C492" t="n" s="2">
-        <v>45784.0</v>
+        <v>45763.0</v>
       </c>
       <c r="D492" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="493">
@@ -7030,10 +7030,10 @@
         <v>2025.0</v>
       </c>
       <c r="C493" t="n" s="2">
-        <v>45791.0</v>
+        <v>45770.0</v>
       </c>
       <c r="D493" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="494">
@@ -7044,10 +7044,10 @@
         <v>2025.0</v>
       </c>
       <c r="C494" t="n" s="2">
-        <v>45805.0</v>
+        <v>45784.0</v>
       </c>
       <c r="D494" t="n">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="495">
@@ -7058,7 +7058,7 @@
         <v>2025.0</v>
       </c>
       <c r="C495" t="n" s="2">
-        <v>45826.0</v>
+        <v>45791.0</v>
       </c>
       <c r="D495" t="n">
         <v>2.0</v>
@@ -7072,10 +7072,10 @@
         <v>2025.0</v>
       </c>
       <c r="C496" t="n" s="2">
-        <v>45861.0</v>
+        <v>45805.0</v>
       </c>
       <c r="D496" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="497">
@@ -7086,10 +7086,10 @@
         <v>2025.0</v>
       </c>
       <c r="C497" t="n" s="2">
-        <v>45868.0</v>
+        <v>45826.0</v>
       </c>
       <c r="D497" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="498">
@@ -7100,10 +7100,10 @@
         <v>2025.0</v>
       </c>
       <c r="C498" t="n" s="2">
-        <v>45889.0</v>
+        <v>45861.0</v>
       </c>
       <c r="D498" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="499">
@@ -7114,7 +7114,7 @@
         <v>2025.0</v>
       </c>
       <c r="C499" t="n" s="2">
-        <v>45924.0</v>
+        <v>45868.0</v>
       </c>
       <c r="D499" t="n">
         <v>1.0</v>
@@ -7128,7 +7128,7 @@
         <v>2025.0</v>
       </c>
       <c r="C500" t="n" s="2">
-        <v>45945.0</v>
+        <v>45889.0</v>
       </c>
       <c r="D500" t="n">
         <v>1.0</v>
@@ -7142,10 +7142,10 @@
         <v>2025.0</v>
       </c>
       <c r="C501" t="n" s="2">
-        <v>45959.0</v>
+        <v>45924.0</v>
       </c>
       <c r="D501" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="502">
@@ -7156,10 +7156,10 @@
         <v>2025.0</v>
       </c>
       <c r="C502" t="n" s="2">
-        <v>46001.0</v>
+        <v>45945.0</v>
       </c>
       <c r="D502" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="503">
@@ -7170,10 +7170,10 @@
         <v>2025.0</v>
       </c>
       <c r="C503" t="n" s="2">
-        <v>46008.0</v>
+        <v>45959.0</v>
       </c>
       <c r="D503" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="504">
@@ -7184,10 +7184,10 @@
         <v>2025.0</v>
       </c>
       <c r="C504" t="n" s="2">
-        <v>46022.0</v>
+        <v>46001.0</v>
       </c>
       <c r="D504" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="505">
@@ -7195,10 +7195,10 @@
         <v>7</v>
       </c>
       <c r="B505" t="n">
-        <v>2026.0</v>
+        <v>2025.0</v>
       </c>
       <c r="C505" t="n" s="2">
-        <v>46030.0</v>
+        <v>46008.0</v>
       </c>
       <c r="D505" t="n">
         <v>1.0</v>
@@ -7209,10 +7209,10 @@
         <v>7</v>
       </c>
       <c r="B506" t="n">
-        <v>2026.0</v>
+        <v>2025.0</v>
       </c>
       <c r="C506" t="n" s="2">
-        <v>46051.0</v>
+        <v>46022.0</v>
       </c>
       <c r="D506" t="n">
         <v>1.0</v>
@@ -7226,7 +7226,7 @@
         <v>2026.0</v>
       </c>
       <c r="C507" t="n" s="2">
-        <v>46058.0</v>
+        <v>46030.0</v>
       </c>
       <c r="D507" t="n">
         <v>1.0</v>
@@ -7240,21 +7240,21 @@
         <v>2026.0</v>
       </c>
       <c r="C508" t="n" s="2">
-        <v>46065.0</v>
+        <v>46051.0</v>
       </c>
       <c r="D508" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B509" t="n">
-        <v>2024.0</v>
+        <v>2026.0</v>
       </c>
       <c r="C509" t="n" s="2">
-        <v>45495.0</v>
+        <v>46058.0</v>
       </c>
       <c r="D509" t="n">
         <v>1.0</v>
@@ -7262,16 +7262,16 @@
     </row>
     <row r="510">
       <c r="A510" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B510" t="n">
-        <v>2024.0</v>
+        <v>2026.0</v>
       </c>
       <c r="C510" t="n" s="2">
-        <v>45502.0</v>
+        <v>46065.0</v>
       </c>
       <c r="D510" t="n">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="511">
@@ -7279,10 +7279,10 @@
         <v>8</v>
       </c>
       <c r="B511" t="n">
-        <v>2025.0</v>
+        <v>2024.0</v>
       </c>
       <c r="C511" t="n" s="2">
-        <v>45665.0</v>
+        <v>45495.0</v>
       </c>
       <c r="D511" t="n">
         <v>1.0</v>
@@ -7293,13 +7293,13 @@
         <v>8</v>
       </c>
       <c r="B512" t="n">
-        <v>2025.0</v>
+        <v>2024.0</v>
       </c>
       <c r="C512" t="n" s="2">
-        <v>45672.0</v>
+        <v>45502.0</v>
       </c>
       <c r="D512" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="513">
@@ -7310,7 +7310,7 @@
         <v>2025.0</v>
       </c>
       <c r="C513" t="n" s="2">
-        <v>45679.0</v>
+        <v>45665.0</v>
       </c>
       <c r="D513" t="n">
         <v>1.0</v>
@@ -7324,10 +7324,10 @@
         <v>2025.0</v>
       </c>
       <c r="C514" t="n" s="2">
-        <v>45686.0</v>
+        <v>45672.0</v>
       </c>
       <c r="D514" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="515">
@@ -7338,7 +7338,7 @@
         <v>2025.0</v>
       </c>
       <c r="C515" t="n" s="2">
-        <v>45693.0</v>
+        <v>45679.0</v>
       </c>
       <c r="D515" t="n">
         <v>1.0</v>
@@ -7352,10 +7352,10 @@
         <v>2025.0</v>
       </c>
       <c r="C516" t="n" s="2">
-        <v>45700.0</v>
+        <v>45686.0</v>
       </c>
       <c r="D516" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="517">
@@ -7366,10 +7366,10 @@
         <v>2025.0</v>
       </c>
       <c r="C517" t="n" s="2">
-        <v>45707.0</v>
+        <v>45693.0</v>
       </c>
       <c r="D517" t="n">
-        <v>7.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="518">
@@ -7380,10 +7380,10 @@
         <v>2025.0</v>
       </c>
       <c r="C518" t="n" s="2">
-        <v>45714.0</v>
+        <v>45700.0</v>
       </c>
       <c r="D518" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="519">
@@ -7394,10 +7394,10 @@
         <v>2025.0</v>
       </c>
       <c r="C519" t="n" s="2">
-        <v>45721.0</v>
+        <v>45707.0</v>
       </c>
       <c r="D519" t="n">
-        <v>4.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="520">
@@ -7408,10 +7408,10 @@
         <v>2025.0</v>
       </c>
       <c r="C520" t="n" s="2">
-        <v>45728.0</v>
+        <v>45714.0</v>
       </c>
       <c r="D520" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="521">
@@ -7422,10 +7422,10 @@
         <v>2025.0</v>
       </c>
       <c r="C521" t="n" s="2">
-        <v>45742.0</v>
+        <v>45721.0</v>
       </c>
       <c r="D521" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="522">
@@ -7436,7 +7436,7 @@
         <v>2025.0</v>
       </c>
       <c r="C522" t="n" s="2">
-        <v>45749.0</v>
+        <v>45728.0</v>
       </c>
       <c r="D522" t="n">
         <v>1.0</v>
@@ -7450,7 +7450,7 @@
         <v>2025.0</v>
       </c>
       <c r="C523" t="n" s="2">
-        <v>45763.0</v>
+        <v>45742.0</v>
       </c>
       <c r="D523" t="n">
         <v>1.0</v>
@@ -7464,10 +7464,10 @@
         <v>2025.0</v>
       </c>
       <c r="C524" t="n" s="2">
-        <v>45777.0</v>
+        <v>45749.0</v>
       </c>
       <c r="D524" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="525">
@@ -7478,7 +7478,7 @@
         <v>2025.0</v>
       </c>
       <c r="C525" t="n" s="2">
-        <v>45784.0</v>
+        <v>45763.0</v>
       </c>
       <c r="D525" t="n">
         <v>1.0</v>
@@ -7492,10 +7492,10 @@
         <v>2025.0</v>
       </c>
       <c r="C526" t="n" s="2">
-        <v>45798.0</v>
+        <v>45777.0</v>
       </c>
       <c r="D526" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="527">
@@ -7506,7 +7506,7 @@
         <v>2025.0</v>
       </c>
       <c r="C527" t="n" s="2">
-        <v>45805.0</v>
+        <v>45784.0</v>
       </c>
       <c r="D527" t="n">
         <v>1.0</v>
@@ -7520,10 +7520,10 @@
         <v>2025.0</v>
       </c>
       <c r="C528" t="n" s="2">
-        <v>45812.0</v>
+        <v>45798.0</v>
       </c>
       <c r="D528" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="529">
@@ -7534,10 +7534,10 @@
         <v>2025.0</v>
       </c>
       <c r="C529" t="n" s="2">
-        <v>45819.0</v>
+        <v>45805.0</v>
       </c>
       <c r="D529" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="530">
@@ -7548,7 +7548,7 @@
         <v>2025.0</v>
       </c>
       <c r="C530" t="n" s="2">
-        <v>45833.0</v>
+        <v>45812.0</v>
       </c>
       <c r="D530" t="n">
         <v>2.0</v>
@@ -7562,10 +7562,10 @@
         <v>2025.0</v>
       </c>
       <c r="C531" t="n" s="2">
-        <v>45847.0</v>
+        <v>45819.0</v>
       </c>
       <c r="D531" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="532">
@@ -7576,10 +7576,10 @@
         <v>2025.0</v>
       </c>
       <c r="C532" t="n" s="2">
-        <v>45854.0</v>
+        <v>45833.0</v>
       </c>
       <c r="D532" t="n">
-        <v>8.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="533">
@@ -7590,10 +7590,10 @@
         <v>2025.0</v>
       </c>
       <c r="C533" t="n" s="2">
-        <v>45861.0</v>
+        <v>45847.0</v>
       </c>
       <c r="D533" t="n">
-        <v>12.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="534">
@@ -7604,10 +7604,10 @@
         <v>2025.0</v>
       </c>
       <c r="C534" t="n" s="2">
-        <v>45868.0</v>
+        <v>45854.0</v>
       </c>
       <c r="D534" t="n">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="535">
@@ -7618,10 +7618,10 @@
         <v>2025.0</v>
       </c>
       <c r="C535" t="n" s="2">
-        <v>45875.0</v>
+        <v>45861.0</v>
       </c>
       <c r="D535" t="n">
-        <v>1.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="536">
@@ -7632,10 +7632,10 @@
         <v>2025.0</v>
       </c>
       <c r="C536" t="n" s="2">
-        <v>45896.0</v>
+        <v>45868.0</v>
       </c>
       <c r="D536" t="n">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="537">
@@ -7646,7 +7646,7 @@
         <v>2025.0</v>
       </c>
       <c r="C537" t="n" s="2">
-        <v>45903.0</v>
+        <v>45875.0</v>
       </c>
       <c r="D537" t="n">
         <v>1.0</v>
@@ -7660,7 +7660,7 @@
         <v>2025.0</v>
       </c>
       <c r="C538" t="n" s="2">
-        <v>45931.0</v>
+        <v>45896.0</v>
       </c>
       <c r="D538" t="n">
         <v>1.0</v>
@@ -7674,10 +7674,10 @@
         <v>2025.0</v>
       </c>
       <c r="C539" t="n" s="2">
-        <v>45938.0</v>
+        <v>45903.0</v>
       </c>
       <c r="D539" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="540">
@@ -7688,10 +7688,10 @@
         <v>2025.0</v>
       </c>
       <c r="C540" t="n" s="2">
-        <v>45945.0</v>
+        <v>45931.0</v>
       </c>
       <c r="D540" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="541">
@@ -7702,10 +7702,10 @@
         <v>2025.0</v>
       </c>
       <c r="C541" t="n" s="2">
-        <v>45966.0</v>
+        <v>45938.0</v>
       </c>
       <c r="D541" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="542">
@@ -7716,10 +7716,10 @@
         <v>2025.0</v>
       </c>
       <c r="C542" t="n" s="2">
-        <v>45973.0</v>
+        <v>45945.0</v>
       </c>
       <c r="D542" t="n">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="543">
@@ -7730,10 +7730,10 @@
         <v>2025.0</v>
       </c>
       <c r="C543" t="n" s="2">
-        <v>45980.0</v>
+        <v>45966.0</v>
       </c>
       <c r="D543" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="544">
@@ -7744,10 +7744,10 @@
         <v>2025.0</v>
       </c>
       <c r="C544" t="n" s="2">
-        <v>45987.0</v>
+        <v>45973.0</v>
       </c>
       <c r="D544" t="n">
-        <v>20.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="545">
@@ -7758,10 +7758,10 @@
         <v>2025.0</v>
       </c>
       <c r="C545" t="n" s="2">
-        <v>45994.0</v>
+        <v>45980.0</v>
       </c>
       <c r="D545" t="n">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="546">
@@ -7772,10 +7772,10 @@
         <v>2025.0</v>
       </c>
       <c r="C546" t="n" s="2">
-        <v>46001.0</v>
+        <v>45987.0</v>
       </c>
       <c r="D546" t="n">
-        <v>8.0</v>
+        <v>20.0</v>
       </c>
     </row>
     <row r="547">
@@ -7786,10 +7786,10 @@
         <v>2025.0</v>
       </c>
       <c r="C547" t="n" s="2">
-        <v>46008.0</v>
+        <v>45994.0</v>
       </c>
       <c r="D547" t="n">
-        <v>24.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="548">
@@ -7800,10 +7800,10 @@
         <v>2025.0</v>
       </c>
       <c r="C548" t="n" s="2">
-        <v>46015.0</v>
+        <v>46001.0</v>
       </c>
       <c r="D548" t="n">
-        <v>13.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="549">
@@ -7814,10 +7814,10 @@
         <v>2025.0</v>
       </c>
       <c r="C549" t="n" s="2">
-        <v>46022.0</v>
+        <v>46008.0</v>
       </c>
       <c r="D549" t="n">
-        <v>8.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="550">
@@ -7828,10 +7828,10 @@
         <v>2025.0</v>
       </c>
       <c r="C550" t="n" s="2">
-        <v>46029.0</v>
+        <v>46015.0</v>
       </c>
       <c r="D550" t="n">
-        <v>3.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="551">
@@ -7839,13 +7839,13 @@
         <v>8</v>
       </c>
       <c r="B551" t="n">
-        <v>2026.0</v>
+        <v>2025.0</v>
       </c>
       <c r="C551" t="n" s="2">
-        <v>46030.0</v>
+        <v>46022.0</v>
       </c>
       <c r="D551" t="n">
-        <v>24.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="552">
@@ -7853,13 +7853,13 @@
         <v>8</v>
       </c>
       <c r="B552" t="n">
-        <v>2026.0</v>
+        <v>2025.0</v>
       </c>
       <c r="C552" t="n" s="2">
-        <v>46037.0</v>
+        <v>46029.0</v>
       </c>
       <c r="D552" t="n">
-        <v>22.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="553">
@@ -7870,10 +7870,10 @@
         <v>2026.0</v>
       </c>
       <c r="C553" t="n" s="2">
-        <v>46044.0</v>
+        <v>46030.0</v>
       </c>
       <c r="D553" t="n">
-        <v>27.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="554">
@@ -7884,10 +7884,10 @@
         <v>2026.0</v>
       </c>
       <c r="C554" t="n" s="2">
-        <v>46051.0</v>
+        <v>46037.0</v>
       </c>
       <c r="D554" t="n">
-        <v>18.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="555">
@@ -7898,10 +7898,10 @@
         <v>2026.0</v>
       </c>
       <c r="C555" t="n" s="2">
-        <v>46058.0</v>
+        <v>46044.0</v>
       </c>
       <c r="D555" t="n">
-        <v>25.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="556">
@@ -7912,10 +7912,10 @@
         <v>2026.0</v>
       </c>
       <c r="C556" t="n" s="2">
-        <v>46065.0</v>
+        <v>46051.0</v>
       </c>
       <c r="D556" t="n">
-        <v>22.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="557">
@@ -7926,10 +7926,10 @@
         <v>2026.0</v>
       </c>
       <c r="C557" t="n" s="2">
-        <v>46072.0</v>
+        <v>46058.0</v>
       </c>
       <c r="D557" t="n">
-        <v>13.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="558">
@@ -7940,10 +7940,10 @@
         <v>2026.0</v>
       </c>
       <c r="C558" t="n" s="2">
-        <v>46079.0</v>
+        <v>46065.0</v>
       </c>
       <c r="D558" t="n">
-        <v>24.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="559">
@@ -7954,10 +7954,10 @@
         <v>2026.0</v>
       </c>
       <c r="C559" t="n" s="2">
-        <v>46086.0</v>
+        <v>46072.0</v>
       </c>
       <c r="D559" t="n">
-        <v>26.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="560">
@@ -7968,10 +7968,10 @@
         <v>2026.0</v>
       </c>
       <c r="C560" t="n" s="2">
-        <v>46093.0</v>
+        <v>46079.0</v>
       </c>
       <c r="D560" t="n">
-        <v>33.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="561">
@@ -7982,10 +7982,10 @@
         <v>2026.0</v>
       </c>
       <c r="C561" t="n" s="2">
-        <v>46100.0</v>
+        <v>46086.0</v>
       </c>
       <c r="D561" t="n">
-        <v>25.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="562">
@@ -7996,9 +7996,37 @@
         <v>2026.0</v>
       </c>
       <c r="C562" t="n" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="D562" t="n">
+        <v>33.0</v>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="s">
+        <v>8</v>
+      </c>
+      <c r="B563" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C563" t="n" s="2">
+        <v>46100.0</v>
+      </c>
+      <c r="D563" t="n">
+        <v>25.0</v>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="s">
+        <v>8</v>
+      </c>
+      <c r="B564" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C564" t="n" s="2">
         <v>46107.0</v>
       </c>
-      <c r="D562" t="n">
+      <c r="D564" t="n">
         <v>25.0</v>
       </c>
     </row>
@@ -8025,7 +8053,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="n">
-        <v>45.0</v>
+        <v>46.0</v>
       </c>
     </row>
     <row r="3">
@@ -8033,7 +8061,7 @@
         <v>11</v>
       </c>
       <c r="B3" t="n">
-        <v>186.0</v>
+        <v>187.0</v>
       </c>
     </row>
     <row r="4">
@@ -8041,7 +8069,7 @@
         <v>12</v>
       </c>
       <c r="B4" t="n">
-        <v>1156.0</v>
+        <v>1162.0</v>
       </c>
     </row>
     <row r="5">
@@ -8049,7 +8077,7 @@
         <v>13</v>
       </c>
       <c r="B5" t="n">
-        <v>2052.0</v>
+        <v>2054.0</v>
       </c>
     </row>
   </sheetData>
@@ -8147,7 +8175,7 @@
         <v>21</v>
       </c>
       <c r="C8" t="n">
-        <v>342.0</v>
+        <v>343.0</v>
       </c>
     </row>
     <row r="9">
@@ -8180,7 +8208,7 @@
         <v>19</v>
       </c>
       <c r="C11" t="n">
-        <v>31.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="12">
@@ -8235,7 +8263,7 @@
         <v>22</v>
       </c>
       <c r="C16" t="n">
-        <v>343.0</v>
+        <v>345.0</v>
       </c>
     </row>
     <row r="17">
@@ -8246,7 +8274,7 @@
         <v>19</v>
       </c>
       <c r="C17" t="n">
-        <v>101.0</v>
+        <v>107.0</v>
       </c>
     </row>
   </sheetData>

--- a/Download/Focus_Positivi_ZR.xlsx
+++ b/Download/Focus_Positivi_ZR.xlsx
@@ -8053,7 +8053,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="n">
-        <v>46.0</v>
+        <v>45.0</v>
       </c>
     </row>
     <row r="3">
@@ -8077,7 +8077,7 @@
         <v>13</v>
       </c>
       <c r="B5" t="n">
-        <v>2054.0</v>
+        <v>2055.0</v>
       </c>
     </row>
   </sheetData>
@@ -8208,7 +8208,7 @@
         <v>19</v>
       </c>
       <c r="C11" t="n">
-        <v>32.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="12">
@@ -8252,7 +8252,7 @@
         <v>21</v>
       </c>
       <c r="C15" t="n">
-        <v>356.0</v>
+        <v>357.0</v>
       </c>
     </row>
     <row r="16">

--- a/Download/Focus_Positivi_ZR.xlsx
+++ b/Download/Focus_Positivi_ZR.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="608" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="609" uniqueCount="23">
   <si>
     <t>NOME_REGIONE</t>
   </si>
@@ -8027,7 +8027,21 @@
         <v>46107.0</v>
       </c>
       <c r="D564" t="n">
-        <v>25.0</v>
+        <v>31.0</v>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="s">
+        <v>8</v>
+      </c>
+      <c r="B565" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C565" t="n" s="2">
+        <v>46114.0</v>
+      </c>
+      <c r="D565" t="n">
+        <v>7.0</v>
       </c>
     </row>
   </sheetData>
@@ -8069,7 +8083,7 @@
         <v>12</v>
       </c>
       <c r="B4" t="n">
-        <v>1162.0</v>
+        <v>1175.0</v>
       </c>
     </row>
     <row r="5">
@@ -8142,7 +8156,7 @@
         <v>21</v>
       </c>
       <c r="C5" t="n">
-        <v>408.0</v>
+        <v>409.0</v>
       </c>
     </row>
     <row r="6">
@@ -8153,7 +8167,7 @@
         <v>22</v>
       </c>
       <c r="C6" t="n">
-        <v>291.0</v>
+        <v>294.0</v>
       </c>
     </row>
     <row r="7">
@@ -8186,7 +8200,7 @@
         <v>22</v>
       </c>
       <c r="C9" t="n">
-        <v>326.0</v>
+        <v>327.0</v>
       </c>
     </row>
     <row r="10">
@@ -8241,7 +8255,7 @@
         <v>19</v>
       </c>
       <c r="C14" t="n">
-        <v>372.0</v>
+        <v>378.0</v>
       </c>
     </row>
     <row r="15">
@@ -8263,7 +8277,7 @@
         <v>22</v>
       </c>
       <c r="C16" t="n">
-        <v>345.0</v>
+        <v>346.0</v>
       </c>
     </row>
     <row r="17">
@@ -8274,7 +8288,7 @@
         <v>19</v>
       </c>
       <c r="C17" t="n">
-        <v>107.0</v>
+        <v>108.0</v>
       </c>
     </row>
   </sheetData>

--- a/Download/Focus_Positivi_ZR.xlsx
+++ b/Download/Focus_Positivi_ZR.xlsx
@@ -1559,7 +1559,7 @@
         <v>46114.0</v>
       </c>
       <c r="D102" t="n">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="103">
@@ -4149,7 +4149,7 @@
         <v>46107.0</v>
       </c>
       <c r="D287" t="n">
-        <v>5.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="288">
@@ -8083,7 +8083,7 @@
         <v>12</v>
       </c>
       <c r="B4" t="n">
-        <v>1175.0</v>
+        <v>1176.0</v>
       </c>
     </row>
     <row r="5">
@@ -8091,7 +8091,7 @@
         <v>13</v>
       </c>
       <c r="B5" t="n">
-        <v>2055.0</v>
+        <v>2059.0</v>
       </c>
     </row>
   </sheetData>
@@ -8123,7 +8123,7 @@
         <v>21</v>
       </c>
       <c r="C2" t="n">
-        <v>185.0</v>
+        <v>186.0</v>
       </c>
     </row>
     <row r="3">
@@ -8167,7 +8167,7 @@
         <v>22</v>
       </c>
       <c r="C6" t="n">
-        <v>294.0</v>
+        <v>295.0</v>
       </c>
     </row>
     <row r="7">
@@ -8233,7 +8233,7 @@
         <v>21</v>
       </c>
       <c r="C12" t="n">
-        <v>53.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="13">
@@ -8266,7 +8266,7 @@
         <v>21</v>
       </c>
       <c r="C15" t="n">
-        <v>357.0</v>
+        <v>359.0</v>
       </c>
     </row>
     <row r="16">

--- a/Download/Focus_Positivi_ZR.xlsx
+++ b/Download/Focus_Positivi_ZR.xlsx
@@ -4163,7 +4163,7 @@
         <v>46114.0</v>
       </c>
       <c r="D288" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="289">
@@ -8083,7 +8083,7 @@
         <v>12</v>
       </c>
       <c r="B4" t="n">
-        <v>1176.0</v>
+        <v>1177.0</v>
       </c>
     </row>
     <row r="5">
@@ -8091,7 +8091,7 @@
         <v>13</v>
       </c>
       <c r="B5" t="n">
-        <v>2059.0</v>
+        <v>2061.0</v>
       </c>
     </row>
   </sheetData>
@@ -8156,7 +8156,7 @@
         <v>21</v>
       </c>
       <c r="C5" t="n">
-        <v>409.0</v>
+        <v>410.0</v>
       </c>
     </row>
     <row r="6">
@@ -8200,7 +8200,7 @@
         <v>22</v>
       </c>
       <c r="C9" t="n">
-        <v>327.0</v>
+        <v>328.0</v>
       </c>
     </row>
     <row r="10">
@@ -8211,7 +8211,7 @@
         <v>19</v>
       </c>
       <c r="C10" t="n">
-        <v>140.0</v>
+        <v>141.0</v>
       </c>
     </row>
     <row r="11">

--- a/Download/Focus_Positivi_ZR.xlsx
+++ b/Download/Focus_Positivi_ZR.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="609" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="610" uniqueCount="23">
   <si>
     <t>NOME_REGIONE</t>
   </si>
@@ -1559,18 +1559,18 @@
         <v>46114.0</v>
       </c>
       <c r="D102" t="n">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B103" t="n">
-        <v>2021.0</v>
+        <v>2026.0</v>
       </c>
       <c r="C103" t="n" s="2">
-        <v>44561.0</v>
+        <v>46121.0</v>
       </c>
       <c r="D103" t="n">
         <v>1.0</v>
@@ -1581,13 +1581,13 @@
         <v>5</v>
       </c>
       <c r="B104" t="n">
-        <v>2022.0</v>
+        <v>2021.0</v>
       </c>
       <c r="C104" t="n" s="2">
-        <v>44576.0</v>
+        <v>44561.0</v>
       </c>
       <c r="D104" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="105">
@@ -1598,10 +1598,10 @@
         <v>2022.0</v>
       </c>
       <c r="C105" t="n" s="2">
-        <v>44583.0</v>
+        <v>44576.0</v>
       </c>
       <c r="D105" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="106">
@@ -1612,10 +1612,10 @@
         <v>2022.0</v>
       </c>
       <c r="C106" t="n" s="2">
-        <v>44590.0</v>
+        <v>44583.0</v>
       </c>
       <c r="D106" t="n">
-        <v>7.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="107">
@@ -1626,10 +1626,10 @@
         <v>2022.0</v>
       </c>
       <c r="C107" t="n" s="2">
-        <v>44597.0</v>
+        <v>44590.0</v>
       </c>
       <c r="D107" t="n">
-        <v>3.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="108">
@@ -1640,10 +1640,10 @@
         <v>2022.0</v>
       </c>
       <c r="C108" t="n" s="2">
-        <v>44604.0</v>
+        <v>44597.0</v>
       </c>
       <c r="D108" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="109">
@@ -1654,10 +1654,10 @@
         <v>2022.0</v>
       </c>
       <c r="C109" t="n" s="2">
-        <v>44611.0</v>
+        <v>44604.0</v>
       </c>
       <c r="D109" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="110">
@@ -1668,7 +1668,7 @@
         <v>2022.0</v>
       </c>
       <c r="C110" t="n" s="2">
-        <v>44618.0</v>
+        <v>44611.0</v>
       </c>
       <c r="D110" t="n">
         <v>1.0</v>
@@ -1682,10 +1682,10 @@
         <v>2022.0</v>
       </c>
       <c r="C111" t="n" s="2">
-        <v>44625.0</v>
+        <v>44618.0</v>
       </c>
       <c r="D111" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="112">
@@ -1696,10 +1696,10 @@
         <v>2022.0</v>
       </c>
       <c r="C112" t="n" s="2">
-        <v>44632.0</v>
+        <v>44625.0</v>
       </c>
       <c r="D112" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="113">
@@ -1710,10 +1710,10 @@
         <v>2022.0</v>
       </c>
       <c r="C113" t="n" s="2">
-        <v>44639.0</v>
+        <v>44632.0</v>
       </c>
       <c r="D113" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="114">
@@ -1724,7 +1724,7 @@
         <v>2022.0</v>
       </c>
       <c r="C114" t="n" s="2">
-        <v>44646.0</v>
+        <v>44639.0</v>
       </c>
       <c r="D114" t="n">
         <v>2.0</v>
@@ -1738,7 +1738,7 @@
         <v>2022.0</v>
       </c>
       <c r="C115" t="n" s="2">
-        <v>44653.0</v>
+        <v>44646.0</v>
       </c>
       <c r="D115" t="n">
         <v>2.0</v>
@@ -1752,10 +1752,10 @@
         <v>2022.0</v>
       </c>
       <c r="C116" t="n" s="2">
-        <v>44660.0</v>
+        <v>44653.0</v>
       </c>
       <c r="D116" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="117">
@@ -1766,10 +1766,10 @@
         <v>2022.0</v>
       </c>
       <c r="C117" t="n" s="2">
-        <v>44667.0</v>
+        <v>44660.0</v>
       </c>
       <c r="D117" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="118">
@@ -1780,7 +1780,7 @@
         <v>2022.0</v>
       </c>
       <c r="C118" t="n" s="2">
-        <v>44674.0</v>
+        <v>44667.0</v>
       </c>
       <c r="D118" t="n">
         <v>3.0</v>
@@ -1794,10 +1794,10 @@
         <v>2022.0</v>
       </c>
       <c r="C119" t="n" s="2">
-        <v>44681.0</v>
+        <v>44674.0</v>
       </c>
       <c r="D119" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="120">
@@ -1808,10 +1808,10 @@
         <v>2022.0</v>
       </c>
       <c r="C120" t="n" s="2">
-        <v>44688.0</v>
+        <v>44681.0</v>
       </c>
       <c r="D120" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="121">
@@ -1822,7 +1822,7 @@
         <v>2022.0</v>
       </c>
       <c r="C121" t="n" s="2">
-        <v>44695.0</v>
+        <v>44688.0</v>
       </c>
       <c r="D121" t="n">
         <v>3.0</v>
@@ -1836,10 +1836,10 @@
         <v>2022.0</v>
       </c>
       <c r="C122" t="n" s="2">
-        <v>44702.0</v>
+        <v>44695.0</v>
       </c>
       <c r="D122" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="123">
@@ -1850,10 +1850,10 @@
         <v>2022.0</v>
       </c>
       <c r="C123" t="n" s="2">
-        <v>44709.0</v>
+        <v>44702.0</v>
       </c>
       <c r="D123" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="124">
@@ -1864,10 +1864,10 @@
         <v>2022.0</v>
       </c>
       <c r="C124" t="n" s="2">
-        <v>44716.0</v>
+        <v>44709.0</v>
       </c>
       <c r="D124" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="125">
@@ -1878,7 +1878,7 @@
         <v>2022.0</v>
       </c>
       <c r="C125" t="n" s="2">
-        <v>44723.0</v>
+        <v>44716.0</v>
       </c>
       <c r="D125" t="n">
         <v>1.0</v>
@@ -1892,7 +1892,7 @@
         <v>2022.0</v>
       </c>
       <c r="C126" t="n" s="2">
-        <v>44730.0</v>
+        <v>44723.0</v>
       </c>
       <c r="D126" t="n">
         <v>1.0</v>
@@ -1906,7 +1906,7 @@
         <v>2022.0</v>
       </c>
       <c r="C127" t="n" s="2">
-        <v>44737.0</v>
+        <v>44730.0</v>
       </c>
       <c r="D127" t="n">
         <v>1.0</v>
@@ -1920,7 +1920,7 @@
         <v>2022.0</v>
       </c>
       <c r="C128" t="n" s="2">
-        <v>44744.0</v>
+        <v>44737.0</v>
       </c>
       <c r="D128" t="n">
         <v>1.0</v>
@@ -1934,7 +1934,7 @@
         <v>2022.0</v>
       </c>
       <c r="C129" t="n" s="2">
-        <v>44751.0</v>
+        <v>44744.0</v>
       </c>
       <c r="D129" t="n">
         <v>1.0</v>
@@ -1948,7 +1948,7 @@
         <v>2022.0</v>
       </c>
       <c r="C130" t="n" s="2">
-        <v>44758.0</v>
+        <v>44751.0</v>
       </c>
       <c r="D130" t="n">
         <v>1.0</v>
@@ -1962,7 +1962,7 @@
         <v>2022.0</v>
       </c>
       <c r="C131" t="n" s="2">
-        <v>44772.0</v>
+        <v>44758.0</v>
       </c>
       <c r="D131" t="n">
         <v>1.0</v>
@@ -1976,7 +1976,7 @@
         <v>2022.0</v>
       </c>
       <c r="C132" t="n" s="2">
-        <v>44793.0</v>
+        <v>44772.0</v>
       </c>
       <c r="D132" t="n">
         <v>1.0</v>
@@ -1990,7 +1990,7 @@
         <v>2022.0</v>
       </c>
       <c r="C133" t="n" s="2">
-        <v>44800.0</v>
+        <v>44793.0</v>
       </c>
       <c r="D133" t="n">
         <v>1.0</v>
@@ -2004,7 +2004,7 @@
         <v>2022.0</v>
       </c>
       <c r="C134" t="n" s="2">
-        <v>44828.0</v>
+        <v>44800.0</v>
       </c>
       <c r="D134" t="n">
         <v>1.0</v>
@@ -2018,7 +2018,7 @@
         <v>2022.0</v>
       </c>
       <c r="C135" t="n" s="2">
-        <v>44849.0</v>
+        <v>44828.0</v>
       </c>
       <c r="D135" t="n">
         <v>1.0</v>
@@ -2032,7 +2032,7 @@
         <v>2022.0</v>
       </c>
       <c r="C136" t="n" s="2">
-        <v>44856.0</v>
+        <v>44849.0</v>
       </c>
       <c r="D136" t="n">
         <v>1.0</v>
@@ -2046,7 +2046,7 @@
         <v>2022.0</v>
       </c>
       <c r="C137" t="n" s="2">
-        <v>44863.0</v>
+        <v>44856.0</v>
       </c>
       <c r="D137" t="n">
         <v>1.0</v>
@@ -2060,10 +2060,10 @@
         <v>2022.0</v>
       </c>
       <c r="C138" t="n" s="2">
-        <v>44884.0</v>
+        <v>44863.0</v>
       </c>
       <c r="D138" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="139">
@@ -2074,10 +2074,10 @@
         <v>2022.0</v>
       </c>
       <c r="C139" t="n" s="2">
-        <v>44891.0</v>
+        <v>44884.0</v>
       </c>
       <c r="D139" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="140">
@@ -2088,7 +2088,7 @@
         <v>2022.0</v>
       </c>
       <c r="C140" t="n" s="2">
-        <v>44905.0</v>
+        <v>44891.0</v>
       </c>
       <c r="D140" t="n">
         <v>1.0</v>
@@ -2102,7 +2102,7 @@
         <v>2022.0</v>
       </c>
       <c r="C141" t="n" s="2">
-        <v>44912.0</v>
+        <v>44905.0</v>
       </c>
       <c r="D141" t="n">
         <v>1.0</v>
@@ -2116,10 +2116,10 @@
         <v>2022.0</v>
       </c>
       <c r="C142" t="n" s="2">
-        <v>44919.0</v>
+        <v>44912.0</v>
       </c>
       <c r="D142" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="143">
@@ -2127,13 +2127,13 @@
         <v>5</v>
       </c>
       <c r="B143" t="n">
-        <v>2023.0</v>
+        <v>2022.0</v>
       </c>
       <c r="C143" t="n" s="2">
-        <v>44934.0</v>
+        <v>44919.0</v>
       </c>
       <c r="D143" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="144">
@@ -2144,10 +2144,10 @@
         <v>2023.0</v>
       </c>
       <c r="C144" t="n" s="2">
-        <v>44941.0</v>
+        <v>44934.0</v>
       </c>
       <c r="D144" t="n">
-        <v>8.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="145">
@@ -2158,10 +2158,10 @@
         <v>2023.0</v>
       </c>
       <c r="C145" t="n" s="2">
-        <v>44948.0</v>
+        <v>44941.0</v>
       </c>
       <c r="D145" t="n">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="146">
@@ -2172,10 +2172,10 @@
         <v>2023.0</v>
       </c>
       <c r="C146" t="n" s="2">
-        <v>44955.0</v>
+        <v>44948.0</v>
       </c>
       <c r="D146" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="147">
@@ -2186,10 +2186,10 @@
         <v>2023.0</v>
       </c>
       <c r="C147" t="n" s="2">
-        <v>44962.0</v>
+        <v>44955.0</v>
       </c>
       <c r="D147" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="148">
@@ -2200,7 +2200,7 @@
         <v>2023.0</v>
       </c>
       <c r="C148" t="n" s="2">
-        <v>44969.0</v>
+        <v>44962.0</v>
       </c>
       <c r="D148" t="n">
         <v>4.0</v>
@@ -2214,10 +2214,10 @@
         <v>2023.0</v>
       </c>
       <c r="C149" t="n" s="2">
-        <v>44976.0</v>
+        <v>44969.0</v>
       </c>
       <c r="D149" t="n">
-        <v>17.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="150">
@@ -2228,10 +2228,10 @@
         <v>2023.0</v>
       </c>
       <c r="C150" t="n" s="2">
-        <v>44983.0</v>
+        <v>44976.0</v>
       </c>
       <c r="D150" t="n">
-        <v>11.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="151">
@@ -2242,10 +2242,10 @@
         <v>2023.0</v>
       </c>
       <c r="C151" t="n" s="2">
-        <v>44990.0</v>
+        <v>44983.0</v>
       </c>
       <c r="D151" t="n">
-        <v>5.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="152">
@@ -2256,10 +2256,10 @@
         <v>2023.0</v>
       </c>
       <c r="C152" t="n" s="2">
-        <v>44997.0</v>
+        <v>44990.0</v>
       </c>
       <c r="D152" t="n">
-        <v>22.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="153">
@@ -2270,10 +2270,10 @@
         <v>2023.0</v>
       </c>
       <c r="C153" t="n" s="2">
-        <v>45004.0</v>
+        <v>44997.0</v>
       </c>
       <c r="D153" t="n">
-        <v>8.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="154">
@@ -2284,10 +2284,10 @@
         <v>2023.0</v>
       </c>
       <c r="C154" t="n" s="2">
-        <v>45011.0</v>
+        <v>45004.0</v>
       </c>
       <c r="D154" t="n">
-        <v>17.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="155">
@@ -2298,10 +2298,10 @@
         <v>2023.0</v>
       </c>
       <c r="C155" t="n" s="2">
-        <v>45018.0</v>
+        <v>45011.0</v>
       </c>
       <c r="D155" t="n">
-        <v>10.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="156">
@@ -2312,10 +2312,10 @@
         <v>2023.0</v>
       </c>
       <c r="C156" t="n" s="2">
-        <v>45025.0</v>
+        <v>45018.0</v>
       </c>
       <c r="D156" t="n">
-        <v>13.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="157">
@@ -2326,10 +2326,10 @@
         <v>2023.0</v>
       </c>
       <c r="C157" t="n" s="2">
-        <v>45032.0</v>
+        <v>45025.0</v>
       </c>
       <c r="D157" t="n">
-        <v>10.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="158">
@@ -2340,10 +2340,10 @@
         <v>2023.0</v>
       </c>
       <c r="C158" t="n" s="2">
-        <v>45039.0</v>
+        <v>45032.0</v>
       </c>
       <c r="D158" t="n">
-        <v>22.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="159">
@@ -2354,10 +2354,10 @@
         <v>2023.0</v>
       </c>
       <c r="C159" t="n" s="2">
-        <v>45046.0</v>
+        <v>45039.0</v>
       </c>
       <c r="D159" t="n">
-        <v>23.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="160">
@@ -2368,10 +2368,10 @@
         <v>2023.0</v>
       </c>
       <c r="C160" t="n" s="2">
-        <v>45053.0</v>
+        <v>45046.0</v>
       </c>
       <c r="D160" t="n">
-        <v>16.0</v>
+        <v>23.0</v>
       </c>
     </row>
     <row r="161">
@@ -2382,10 +2382,10 @@
         <v>2023.0</v>
       </c>
       <c r="C161" t="n" s="2">
-        <v>45060.0</v>
+        <v>45053.0</v>
       </c>
       <c r="D161" t="n">
-        <v>13.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="162">
@@ -2396,10 +2396,10 @@
         <v>2023.0</v>
       </c>
       <c r="C162" t="n" s="2">
-        <v>45067.0</v>
+        <v>45060.0</v>
       </c>
       <c r="D162" t="n">
-        <v>9.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="163">
@@ -2410,10 +2410,10 @@
         <v>2023.0</v>
       </c>
       <c r="C163" t="n" s="2">
-        <v>45074.0</v>
+        <v>45067.0</v>
       </c>
       <c r="D163" t="n">
-        <v>6.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="164">
@@ -2424,10 +2424,10 @@
         <v>2023.0</v>
       </c>
       <c r="C164" t="n" s="2">
-        <v>45081.0</v>
+        <v>45074.0</v>
       </c>
       <c r="D164" t="n">
-        <v>16.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="165">
@@ -2438,10 +2438,10 @@
         <v>2023.0</v>
       </c>
       <c r="C165" t="n" s="2">
-        <v>45088.0</v>
+        <v>45081.0</v>
       </c>
       <c r="D165" t="n">
-        <v>8.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="166">
@@ -2452,10 +2452,10 @@
         <v>2023.0</v>
       </c>
       <c r="C166" t="n" s="2">
-        <v>45095.0</v>
+        <v>45088.0</v>
       </c>
       <c r="D166" t="n">
-        <v>16.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="167">
@@ -2466,10 +2466,10 @@
         <v>2023.0</v>
       </c>
       <c r="C167" t="n" s="2">
-        <v>45102.0</v>
+        <v>45095.0</v>
       </c>
       <c r="D167" t="n">
-        <v>17.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="168">
@@ -2480,10 +2480,10 @@
         <v>2023.0</v>
       </c>
       <c r="C168" t="n" s="2">
-        <v>45109.0</v>
+        <v>45102.0</v>
       </c>
       <c r="D168" t="n">
-        <v>14.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="169">
@@ -2494,10 +2494,10 @@
         <v>2023.0</v>
       </c>
       <c r="C169" t="n" s="2">
-        <v>45116.0</v>
+        <v>45109.0</v>
       </c>
       <c r="D169" t="n">
-        <v>13.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="170">
@@ -2508,10 +2508,10 @@
         <v>2023.0</v>
       </c>
       <c r="C170" t="n" s="2">
-        <v>45123.0</v>
+        <v>45116.0</v>
       </c>
       <c r="D170" t="n">
-        <v>5.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="171">
@@ -2522,10 +2522,10 @@
         <v>2023.0</v>
       </c>
       <c r="C171" t="n" s="2">
-        <v>45130.0</v>
+        <v>45123.0</v>
       </c>
       <c r="D171" t="n">
-        <v>8.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="172">
@@ -2536,10 +2536,10 @@
         <v>2023.0</v>
       </c>
       <c r="C172" t="n" s="2">
-        <v>45137.0</v>
+        <v>45130.0</v>
       </c>
       <c r="D172" t="n">
-        <v>4.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="173">
@@ -2550,10 +2550,10 @@
         <v>2023.0</v>
       </c>
       <c r="C173" t="n" s="2">
-        <v>45144.0</v>
+        <v>45137.0</v>
       </c>
       <c r="D173" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="174">
@@ -2564,7 +2564,7 @@
         <v>2023.0</v>
       </c>
       <c r="C174" t="n" s="2">
-        <v>45151.0</v>
+        <v>45144.0</v>
       </c>
       <c r="D174" t="n">
         <v>2.0</v>
@@ -2578,10 +2578,10 @@
         <v>2023.0</v>
       </c>
       <c r="C175" t="n" s="2">
-        <v>45158.0</v>
+        <v>45151.0</v>
       </c>
       <c r="D175" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="176">
@@ -2592,7 +2592,7 @@
         <v>2023.0</v>
       </c>
       <c r="C176" t="n" s="2">
-        <v>45165.0</v>
+        <v>45158.0</v>
       </c>
       <c r="D176" t="n">
         <v>5.0</v>
@@ -2606,10 +2606,10 @@
         <v>2023.0</v>
       </c>
       <c r="C177" t="n" s="2">
-        <v>45172.0</v>
+        <v>45165.0</v>
       </c>
       <c r="D177" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="178">
@@ -2620,10 +2620,10 @@
         <v>2023.0</v>
       </c>
       <c r="C178" t="n" s="2">
-        <v>45179.0</v>
+        <v>45172.0</v>
       </c>
       <c r="D178" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="179">
@@ -2634,10 +2634,10 @@
         <v>2023.0</v>
       </c>
       <c r="C179" t="n" s="2">
-        <v>45186.0</v>
+        <v>45179.0</v>
       </c>
       <c r="D179" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="180">
@@ -2648,7 +2648,7 @@
         <v>2023.0</v>
       </c>
       <c r="C180" t="n" s="2">
-        <v>45193.0</v>
+        <v>45186.0</v>
       </c>
       <c r="D180" t="n">
         <v>1.0</v>
@@ -2662,10 +2662,10 @@
         <v>2023.0</v>
       </c>
       <c r="C181" t="n" s="2">
-        <v>45200.0</v>
+        <v>45193.0</v>
       </c>
       <c r="D181" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="182">
@@ -2676,10 +2676,10 @@
         <v>2023.0</v>
       </c>
       <c r="C182" t="n" s="2">
-        <v>45207.0</v>
+        <v>45200.0</v>
       </c>
       <c r="D182" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="183">
@@ -2690,10 +2690,10 @@
         <v>2023.0</v>
       </c>
       <c r="C183" t="n" s="2">
-        <v>45214.0</v>
+        <v>45207.0</v>
       </c>
       <c r="D183" t="n">
-        <v>8.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="184">
@@ -2704,7 +2704,7 @@
         <v>2023.0</v>
       </c>
       <c r="C184" t="n" s="2">
-        <v>45221.0</v>
+        <v>45214.0</v>
       </c>
       <c r="D184" t="n">
         <v>8.0</v>
@@ -2718,10 +2718,10 @@
         <v>2023.0</v>
       </c>
       <c r="C185" t="n" s="2">
-        <v>45228.0</v>
+        <v>45221.0</v>
       </c>
       <c r="D185" t="n">
-        <v>17.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="186">
@@ -2732,10 +2732,10 @@
         <v>2023.0</v>
       </c>
       <c r="C186" t="n" s="2">
-        <v>45235.0</v>
+        <v>45228.0</v>
       </c>
       <c r="D186" t="n">
-        <v>9.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="187">
@@ -2746,7 +2746,7 @@
         <v>2023.0</v>
       </c>
       <c r="C187" t="n" s="2">
-        <v>45242.0</v>
+        <v>45235.0</v>
       </c>
       <c r="D187" t="n">
         <v>9.0</v>
@@ -2760,10 +2760,10 @@
         <v>2023.0</v>
       </c>
       <c r="C188" t="n" s="2">
-        <v>45249.0</v>
+        <v>45242.0</v>
       </c>
       <c r="D188" t="n">
-        <v>14.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="189">
@@ -2774,10 +2774,10 @@
         <v>2023.0</v>
       </c>
       <c r="C189" t="n" s="2">
-        <v>45256.0</v>
+        <v>45249.0</v>
       </c>
       <c r="D189" t="n">
-        <v>17.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="190">
@@ -2788,10 +2788,10 @@
         <v>2023.0</v>
       </c>
       <c r="C190" t="n" s="2">
-        <v>45263.0</v>
+        <v>45256.0</v>
       </c>
       <c r="D190" t="n">
-        <v>14.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="191">
@@ -2802,10 +2802,10 @@
         <v>2023.0</v>
       </c>
       <c r="C191" t="n" s="2">
-        <v>45270.0</v>
+        <v>45263.0</v>
       </c>
       <c r="D191" t="n">
-        <v>26.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="192">
@@ -2816,10 +2816,10 @@
         <v>2023.0</v>
       </c>
       <c r="C192" t="n" s="2">
-        <v>45277.0</v>
+        <v>45270.0</v>
       </c>
       <c r="D192" t="n">
-        <v>19.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="193">
@@ -2830,10 +2830,10 @@
         <v>2023.0</v>
       </c>
       <c r="C193" t="n" s="2">
-        <v>45284.0</v>
+        <v>45277.0</v>
       </c>
       <c r="D193" t="n">
-        <v>21.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="194">
@@ -2844,10 +2844,10 @@
         <v>2023.0</v>
       </c>
       <c r="C194" t="n" s="2">
-        <v>45291.0</v>
+        <v>45284.0</v>
       </c>
       <c r="D194" t="n">
-        <v>9.0</v>
+        <v>21.0</v>
       </c>
     </row>
     <row r="195">
@@ -2855,13 +2855,13 @@
         <v>5</v>
       </c>
       <c r="B195" t="n">
-        <v>2024.0</v>
+        <v>2023.0</v>
       </c>
       <c r="C195" t="n" s="2">
-        <v>45299.0</v>
+        <v>45291.0</v>
       </c>
       <c r="D195" t="n">
-        <v>26.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="196">
@@ -2872,10 +2872,10 @@
         <v>2024.0</v>
       </c>
       <c r="C196" t="n" s="2">
-        <v>45306.0</v>
+        <v>45299.0</v>
       </c>
       <c r="D196" t="n">
-        <v>14.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="197">
@@ -2886,10 +2886,10 @@
         <v>2024.0</v>
       </c>
       <c r="C197" t="n" s="2">
-        <v>45313.0</v>
+        <v>45306.0</v>
       </c>
       <c r="D197" t="n">
-        <v>15.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="198">
@@ -2900,10 +2900,10 @@
         <v>2024.0</v>
       </c>
       <c r="C198" t="n" s="2">
-        <v>45320.0</v>
+        <v>45313.0</v>
       </c>
       <c r="D198" t="n">
-        <v>18.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="199">
@@ -2914,10 +2914,10 @@
         <v>2024.0</v>
       </c>
       <c r="C199" t="n" s="2">
-        <v>45327.0</v>
+        <v>45320.0</v>
       </c>
       <c r="D199" t="n">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="200">
@@ -2928,10 +2928,10 @@
         <v>2024.0</v>
       </c>
       <c r="C200" t="n" s="2">
-        <v>45334.0</v>
+        <v>45327.0</v>
       </c>
       <c r="D200" t="n">
-        <v>13.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="201">
@@ -2942,10 +2942,10 @@
         <v>2024.0</v>
       </c>
       <c r="C201" t="n" s="2">
-        <v>45341.0</v>
+        <v>45334.0</v>
       </c>
       <c r="D201" t="n">
-        <v>11.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="202">
@@ -2956,10 +2956,10 @@
         <v>2024.0</v>
       </c>
       <c r="C202" t="n" s="2">
-        <v>45348.0</v>
+        <v>45341.0</v>
       </c>
       <c r="D202" t="n">
-        <v>8.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="203">
@@ -2970,10 +2970,10 @@
         <v>2024.0</v>
       </c>
       <c r="C203" t="n" s="2">
-        <v>45355.0</v>
+        <v>45348.0</v>
       </c>
       <c r="D203" t="n">
-        <v>1.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="204">
@@ -2984,10 +2984,10 @@
         <v>2024.0</v>
       </c>
       <c r="C204" t="n" s="2">
-        <v>45362.0</v>
+        <v>45355.0</v>
       </c>
       <c r="D204" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="205">
@@ -2998,10 +2998,10 @@
         <v>2024.0</v>
       </c>
       <c r="C205" t="n" s="2">
-        <v>45369.0</v>
+        <v>45362.0</v>
       </c>
       <c r="D205" t="n">
-        <v>8.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="206">
@@ -3012,10 +3012,10 @@
         <v>2024.0</v>
       </c>
       <c r="C206" t="n" s="2">
-        <v>45376.0</v>
+        <v>45369.0</v>
       </c>
       <c r="D206" t="n">
-        <v>9.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="207">
@@ -3026,10 +3026,10 @@
         <v>2024.0</v>
       </c>
       <c r="C207" t="n" s="2">
-        <v>45383.0</v>
+        <v>45376.0</v>
       </c>
       <c r="D207" t="n">
-        <v>5.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="208">
@@ -3040,10 +3040,10 @@
         <v>2024.0</v>
       </c>
       <c r="C208" t="n" s="2">
-        <v>45390.0</v>
+        <v>45383.0</v>
       </c>
       <c r="D208" t="n">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="209">
@@ -3054,10 +3054,10 @@
         <v>2024.0</v>
       </c>
       <c r="C209" t="n" s="2">
-        <v>45397.0</v>
+        <v>45390.0</v>
       </c>
       <c r="D209" t="n">
-        <v>13.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="210">
@@ -3068,10 +3068,10 @@
         <v>2024.0</v>
       </c>
       <c r="C210" t="n" s="2">
-        <v>45404.0</v>
+        <v>45397.0</v>
       </c>
       <c r="D210" t="n">
-        <v>24.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="211">
@@ -3082,10 +3082,10 @@
         <v>2024.0</v>
       </c>
       <c r="C211" t="n" s="2">
-        <v>45411.0</v>
+        <v>45404.0</v>
       </c>
       <c r="D211" t="n">
-        <v>17.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="212">
@@ -3096,10 +3096,10 @@
         <v>2024.0</v>
       </c>
       <c r="C212" t="n" s="2">
-        <v>45418.0</v>
+        <v>45411.0</v>
       </c>
       <c r="D212" t="n">
-        <v>3.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="213">
@@ -3110,10 +3110,10 @@
         <v>2024.0</v>
       </c>
       <c r="C213" t="n" s="2">
-        <v>45425.0</v>
+        <v>45418.0</v>
       </c>
       <c r="D213" t="n">
-        <v>16.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="214">
@@ -3124,10 +3124,10 @@
         <v>2024.0</v>
       </c>
       <c r="C214" t="n" s="2">
-        <v>45432.0</v>
+        <v>45425.0</v>
       </c>
       <c r="D214" t="n">
-        <v>19.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="215">
@@ -3138,10 +3138,10 @@
         <v>2024.0</v>
       </c>
       <c r="C215" t="n" s="2">
-        <v>45439.0</v>
+        <v>45432.0</v>
       </c>
       <c r="D215" t="n">
-        <v>30.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="216">
@@ -3152,10 +3152,10 @@
         <v>2024.0</v>
       </c>
       <c r="C216" t="n" s="2">
-        <v>45446.0</v>
+        <v>45439.0</v>
       </c>
       <c r="D216" t="n">
-        <v>28.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="217">
@@ -3166,10 +3166,10 @@
         <v>2024.0</v>
       </c>
       <c r="C217" t="n" s="2">
-        <v>45453.0</v>
+        <v>45446.0</v>
       </c>
       <c r="D217" t="n">
-        <v>19.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="218">
@@ -3180,10 +3180,10 @@
         <v>2024.0</v>
       </c>
       <c r="C218" t="n" s="2">
-        <v>45460.0</v>
+        <v>45453.0</v>
       </c>
       <c r="D218" t="n">
-        <v>26.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="219">
@@ -3194,10 +3194,10 @@
         <v>2024.0</v>
       </c>
       <c r="C219" t="n" s="2">
-        <v>45467.0</v>
+        <v>45460.0</v>
       </c>
       <c r="D219" t="n">
-        <v>8.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="220">
@@ -3208,10 +3208,10 @@
         <v>2024.0</v>
       </c>
       <c r="C220" t="n" s="2">
-        <v>45474.0</v>
+        <v>45467.0</v>
       </c>
       <c r="D220" t="n">
-        <v>12.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="221">
@@ -3222,7 +3222,7 @@
         <v>2024.0</v>
       </c>
       <c r="C221" t="n" s="2">
-        <v>45481.0</v>
+        <v>45474.0</v>
       </c>
       <c r="D221" t="n">
         <v>12.0</v>
@@ -3236,10 +3236,10 @@
         <v>2024.0</v>
       </c>
       <c r="C222" t="n" s="2">
-        <v>45488.0</v>
+        <v>45481.0</v>
       </c>
       <c r="D222" t="n">
-        <v>4.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="223">
@@ -3250,10 +3250,10 @@
         <v>2024.0</v>
       </c>
       <c r="C223" t="n" s="2">
-        <v>45495.0</v>
+        <v>45488.0</v>
       </c>
       <c r="D223" t="n">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="224">
@@ -3264,10 +3264,10 @@
         <v>2024.0</v>
       </c>
       <c r="C224" t="n" s="2">
-        <v>45502.0</v>
+        <v>45495.0</v>
       </c>
       <c r="D224" t="n">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="225">
@@ -3278,10 +3278,10 @@
         <v>2024.0</v>
       </c>
       <c r="C225" t="n" s="2">
-        <v>45509.0</v>
+        <v>45502.0</v>
       </c>
       <c r="D225" t="n">
-        <v>2.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="226">
@@ -3292,10 +3292,10 @@
         <v>2024.0</v>
       </c>
       <c r="C226" t="n" s="2">
-        <v>45516.0</v>
+        <v>45509.0</v>
       </c>
       <c r="D226" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="227">
@@ -3306,7 +3306,7 @@
         <v>2024.0</v>
       </c>
       <c r="C227" t="n" s="2">
-        <v>45523.0</v>
+        <v>45516.0</v>
       </c>
       <c r="D227" t="n">
         <v>4.0</v>
@@ -3320,7 +3320,7 @@
         <v>2024.0</v>
       </c>
       <c r="C228" t="n" s="2">
-        <v>45530.0</v>
+        <v>45523.0</v>
       </c>
       <c r="D228" t="n">
         <v>4.0</v>
@@ -3334,7 +3334,7 @@
         <v>2024.0</v>
       </c>
       <c r="C229" t="n" s="2">
-        <v>45537.0</v>
+        <v>45530.0</v>
       </c>
       <c r="D229" t="n">
         <v>4.0</v>
@@ -3348,10 +3348,10 @@
         <v>2024.0</v>
       </c>
       <c r="C230" t="n" s="2">
-        <v>45544.0</v>
+        <v>45537.0</v>
       </c>
       <c r="D230" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="231">
@@ -3362,10 +3362,10 @@
         <v>2024.0</v>
       </c>
       <c r="C231" t="n" s="2">
-        <v>45551.0</v>
+        <v>45544.0</v>
       </c>
       <c r="D231" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="232">
@@ -3376,10 +3376,10 @@
         <v>2024.0</v>
       </c>
       <c r="C232" t="n" s="2">
-        <v>45558.0</v>
+        <v>45551.0</v>
       </c>
       <c r="D232" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="233">
@@ -3390,10 +3390,10 @@
         <v>2024.0</v>
       </c>
       <c r="C233" t="n" s="2">
-        <v>45600.0</v>
+        <v>45558.0</v>
       </c>
       <c r="D233" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="234">
@@ -3404,10 +3404,10 @@
         <v>2024.0</v>
       </c>
       <c r="C234" t="n" s="2">
-        <v>45607.0</v>
+        <v>45600.0</v>
       </c>
       <c r="D234" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="235">
@@ -3418,10 +3418,10 @@
         <v>2024.0</v>
       </c>
       <c r="C235" t="n" s="2">
-        <v>45628.0</v>
+        <v>45607.0</v>
       </c>
       <c r="D235" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="236">
@@ -3432,10 +3432,10 @@
         <v>2024.0</v>
       </c>
       <c r="C236" t="n" s="2">
-        <v>45635.0</v>
+        <v>45628.0</v>
       </c>
       <c r="D236" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="237">
@@ -3446,7 +3446,7 @@
         <v>2024.0</v>
       </c>
       <c r="C237" t="n" s="2">
-        <v>45642.0</v>
+        <v>45635.0</v>
       </c>
       <c r="D237" t="n">
         <v>3.0</v>
@@ -3460,10 +3460,10 @@
         <v>2024.0</v>
       </c>
       <c r="C238" t="n" s="2">
-        <v>45649.0</v>
+        <v>45642.0</v>
       </c>
       <c r="D238" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="239">
@@ -3474,7 +3474,7 @@
         <v>2024.0</v>
       </c>
       <c r="C239" t="n" s="2">
-        <v>45656.0</v>
+        <v>45649.0</v>
       </c>
       <c r="D239" t="n">
         <v>1.0</v>
@@ -3485,13 +3485,13 @@
         <v>5</v>
       </c>
       <c r="B240" t="n">
-        <v>2025.0</v>
+        <v>2024.0</v>
       </c>
       <c r="C240" t="n" s="2">
-        <v>45672.0</v>
+        <v>45656.0</v>
       </c>
       <c r="D240" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="241">
@@ -3502,10 +3502,10 @@
         <v>2025.0</v>
       </c>
       <c r="C241" t="n" s="2">
-        <v>45679.0</v>
+        <v>45672.0</v>
       </c>
       <c r="D241" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="242">
@@ -3516,7 +3516,7 @@
         <v>2025.0</v>
       </c>
       <c r="C242" t="n" s="2">
-        <v>45686.0</v>
+        <v>45679.0</v>
       </c>
       <c r="D242" t="n">
         <v>1.0</v>
@@ -3530,10 +3530,10 @@
         <v>2025.0</v>
       </c>
       <c r="C243" t="n" s="2">
-        <v>45721.0</v>
+        <v>45686.0</v>
       </c>
       <c r="D243" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="244">
@@ -3544,10 +3544,10 @@
         <v>2025.0</v>
       </c>
       <c r="C244" t="n" s="2">
-        <v>45728.0</v>
+        <v>45721.0</v>
       </c>
       <c r="D244" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="245">
@@ -3558,10 +3558,10 @@
         <v>2025.0</v>
       </c>
       <c r="C245" t="n" s="2">
-        <v>45742.0</v>
+        <v>45728.0</v>
       </c>
       <c r="D245" t="n">
-        <v>9.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="246">
@@ -3572,10 +3572,10 @@
         <v>2025.0</v>
       </c>
       <c r="C246" t="n" s="2">
-        <v>45749.0</v>
+        <v>45742.0</v>
       </c>
       <c r="D246" t="n">
-        <v>5.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="247">
@@ -3586,10 +3586,10 @@
         <v>2025.0</v>
       </c>
       <c r="C247" t="n" s="2">
-        <v>45756.0</v>
+        <v>45749.0</v>
       </c>
       <c r="D247" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="248">
@@ -3600,10 +3600,10 @@
         <v>2025.0</v>
       </c>
       <c r="C248" t="n" s="2">
-        <v>45763.0</v>
+        <v>45756.0</v>
       </c>
       <c r="D248" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="249">
@@ -3614,10 +3614,10 @@
         <v>2025.0</v>
       </c>
       <c r="C249" t="n" s="2">
-        <v>45770.0</v>
+        <v>45763.0</v>
       </c>
       <c r="D249" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="250">
@@ -3628,10 +3628,10 @@
         <v>2025.0</v>
       </c>
       <c r="C250" t="n" s="2">
-        <v>45777.0</v>
+        <v>45770.0</v>
       </c>
       <c r="D250" t="n">
-        <v>7.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="251">
@@ -3642,10 +3642,10 @@
         <v>2025.0</v>
       </c>
       <c r="C251" t="n" s="2">
-        <v>45784.0</v>
+        <v>45777.0</v>
       </c>
       <c r="D251" t="n">
-        <v>2.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="252">
@@ -3656,10 +3656,10 @@
         <v>2025.0</v>
       </c>
       <c r="C252" t="n" s="2">
-        <v>45791.0</v>
+        <v>45784.0</v>
       </c>
       <c r="D252" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="253">
@@ -3670,10 +3670,10 @@
         <v>2025.0</v>
       </c>
       <c r="C253" t="n" s="2">
-        <v>45798.0</v>
+        <v>45791.0</v>
       </c>
       <c r="D253" t="n">
-        <v>8.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="254">
@@ -3684,10 +3684,10 @@
         <v>2025.0</v>
       </c>
       <c r="C254" t="n" s="2">
-        <v>45805.0</v>
+        <v>45798.0</v>
       </c>
       <c r="D254" t="n">
-        <v>4.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="255">
@@ -3698,10 +3698,10 @@
         <v>2025.0</v>
       </c>
       <c r="C255" t="n" s="2">
-        <v>45812.0</v>
+        <v>45805.0</v>
       </c>
       <c r="D255" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="256">
@@ -3712,10 +3712,10 @@
         <v>2025.0</v>
       </c>
       <c r="C256" t="n" s="2">
-        <v>45819.0</v>
+        <v>45812.0</v>
       </c>
       <c r="D256" t="n">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="257">
@@ -3726,10 +3726,10 @@
         <v>2025.0</v>
       </c>
       <c r="C257" t="n" s="2">
-        <v>45826.0</v>
+        <v>45819.0</v>
       </c>
       <c r="D257" t="n">
-        <v>13.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="258">
@@ -3740,10 +3740,10 @@
         <v>2025.0</v>
       </c>
       <c r="C258" t="n" s="2">
-        <v>45833.0</v>
+        <v>45826.0</v>
       </c>
       <c r="D258" t="n">
-        <v>1.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="259">
@@ -3754,10 +3754,10 @@
         <v>2025.0</v>
       </c>
       <c r="C259" t="n" s="2">
-        <v>45840.0</v>
+        <v>45833.0</v>
       </c>
       <c r="D259" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="260">
@@ -3768,7 +3768,7 @@
         <v>2025.0</v>
       </c>
       <c r="C260" t="n" s="2">
-        <v>45847.0</v>
+        <v>45840.0</v>
       </c>
       <c r="D260" t="n">
         <v>4.0</v>
@@ -3782,10 +3782,10 @@
         <v>2025.0</v>
       </c>
       <c r="C261" t="n" s="2">
-        <v>45854.0</v>
+        <v>45847.0</v>
       </c>
       <c r="D261" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="262">
@@ -3796,10 +3796,10 @@
         <v>2025.0</v>
       </c>
       <c r="C262" t="n" s="2">
-        <v>45861.0</v>
+        <v>45854.0</v>
       </c>
       <c r="D262" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="263">
@@ -3810,10 +3810,10 @@
         <v>2025.0</v>
       </c>
       <c r="C263" t="n" s="2">
-        <v>45868.0</v>
+        <v>45861.0</v>
       </c>
       <c r="D263" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="264">
@@ -3824,10 +3824,10 @@
         <v>2025.0</v>
       </c>
       <c r="C264" t="n" s="2">
-        <v>45882.0</v>
+        <v>45868.0</v>
       </c>
       <c r="D264" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="265">
@@ -3838,7 +3838,7 @@
         <v>2025.0</v>
       </c>
       <c r="C265" t="n" s="2">
-        <v>45889.0</v>
+        <v>45882.0</v>
       </c>
       <c r="D265" t="n">
         <v>1.0</v>
@@ -3852,10 +3852,10 @@
         <v>2025.0</v>
       </c>
       <c r="C266" t="n" s="2">
-        <v>45896.0</v>
+        <v>45889.0</v>
       </c>
       <c r="D266" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="267">
@@ -3866,7 +3866,7 @@
         <v>2025.0</v>
       </c>
       <c r="C267" t="n" s="2">
-        <v>45903.0</v>
+        <v>45896.0</v>
       </c>
       <c r="D267" t="n">
         <v>3.0</v>
@@ -3880,10 +3880,10 @@
         <v>2025.0</v>
       </c>
       <c r="C268" t="n" s="2">
-        <v>45910.0</v>
+        <v>45903.0</v>
       </c>
       <c r="D268" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="269">
@@ -3894,7 +3894,7 @@
         <v>2025.0</v>
       </c>
       <c r="C269" t="n" s="2">
-        <v>45973.0</v>
+        <v>45910.0</v>
       </c>
       <c r="D269" t="n">
         <v>1.0</v>
@@ -3908,10 +3908,10 @@
         <v>2025.0</v>
       </c>
       <c r="C270" t="n" s="2">
-        <v>45987.0</v>
+        <v>45973.0</v>
       </c>
       <c r="D270" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="271">
@@ -3922,10 +3922,10 @@
         <v>2025.0</v>
       </c>
       <c r="C271" t="n" s="2">
-        <v>45994.0</v>
+        <v>45987.0</v>
       </c>
       <c r="D271" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="272">
@@ -3936,10 +3936,10 @@
         <v>2025.0</v>
       </c>
       <c r="C272" t="n" s="2">
-        <v>46001.0</v>
+        <v>45994.0</v>
       </c>
       <c r="D272" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="273">
@@ -3950,10 +3950,10 @@
         <v>2025.0</v>
       </c>
       <c r="C273" t="n" s="2">
-        <v>46008.0</v>
+        <v>46001.0</v>
       </c>
       <c r="D273" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="274">
@@ -3964,10 +3964,10 @@
         <v>2025.0</v>
       </c>
       <c r="C274" t="n" s="2">
-        <v>46022.0</v>
+        <v>46008.0</v>
       </c>
       <c r="D274" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="275">
@@ -3978,10 +3978,10 @@
         <v>2025.0</v>
       </c>
       <c r="C275" t="n" s="2">
-        <v>46029.0</v>
+        <v>46022.0</v>
       </c>
       <c r="D275" t="n">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="276">
@@ -3989,13 +3989,13 @@
         <v>5</v>
       </c>
       <c r="B276" t="n">
-        <v>2026.0</v>
+        <v>2025.0</v>
       </c>
       <c r="C276" t="n" s="2">
-        <v>46030.0</v>
+        <v>46029.0</v>
       </c>
       <c r="D276" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="277">
@@ -4006,10 +4006,10 @@
         <v>2026.0</v>
       </c>
       <c r="C277" t="n" s="2">
-        <v>46037.0</v>
+        <v>46030.0</v>
       </c>
       <c r="D277" t="n">
-        <v>12.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="278">
@@ -4020,10 +4020,10 @@
         <v>2026.0</v>
       </c>
       <c r="C278" t="n" s="2">
-        <v>46044.0</v>
+        <v>46037.0</v>
       </c>
       <c r="D278" t="n">
-        <v>9.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="279">
@@ -4034,10 +4034,10 @@
         <v>2026.0</v>
       </c>
       <c r="C279" t="n" s="2">
-        <v>46051.0</v>
+        <v>46044.0</v>
       </c>
       <c r="D279" t="n">
-        <v>10.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="280">
@@ -4048,10 +4048,10 @@
         <v>2026.0</v>
       </c>
       <c r="C280" t="n" s="2">
-        <v>46058.0</v>
+        <v>46051.0</v>
       </c>
       <c r="D280" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="281">
@@ -4062,10 +4062,10 @@
         <v>2026.0</v>
       </c>
       <c r="C281" t="n" s="2">
-        <v>46065.0</v>
+        <v>46058.0</v>
       </c>
       <c r="D281" t="n">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="282">
@@ -4076,10 +4076,10 @@
         <v>2026.0</v>
       </c>
       <c r="C282" t="n" s="2">
-        <v>46072.0</v>
+        <v>46065.0</v>
       </c>
       <c r="D282" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="283">
@@ -4090,10 +4090,10 @@
         <v>2026.0</v>
       </c>
       <c r="C283" t="n" s="2">
-        <v>46079.0</v>
+        <v>46072.0</v>
       </c>
       <c r="D283" t="n">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="284">
@@ -4104,10 +4104,10 @@
         <v>2026.0</v>
       </c>
       <c r="C284" t="n" s="2">
-        <v>46086.0</v>
+        <v>46079.0</v>
       </c>
       <c r="D284" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="285">
@@ -4118,7 +4118,7 @@
         <v>2026.0</v>
       </c>
       <c r="C285" t="n" s="2">
-        <v>46093.0</v>
+        <v>46086.0</v>
       </c>
       <c r="D285" t="n">
         <v>2.0</v>
@@ -4132,10 +4132,10 @@
         <v>2026.0</v>
       </c>
       <c r="C286" t="n" s="2">
-        <v>46100.0</v>
+        <v>46093.0</v>
       </c>
       <c r="D286" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="287">
@@ -4146,10 +4146,10 @@
         <v>2026.0</v>
       </c>
       <c r="C287" t="n" s="2">
-        <v>46107.0</v>
+        <v>46100.0</v>
       </c>
       <c r="D287" t="n">
-        <v>9.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="288">
@@ -4160,24 +4160,24 @@
         <v>2026.0</v>
       </c>
       <c r="C288" t="n" s="2">
-        <v>46114.0</v>
+        <v>46107.0</v>
       </c>
       <c r="D288" t="n">
-        <v>4.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B289" t="n">
-        <v>2023.0</v>
+        <v>2026.0</v>
       </c>
       <c r="C289" t="n" s="2">
-        <v>45095.0</v>
+        <v>46114.0</v>
       </c>
       <c r="D289" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="290">
@@ -4188,7 +4188,7 @@
         <v>2023.0</v>
       </c>
       <c r="C290" t="n" s="2">
-        <v>45102.0</v>
+        <v>45095.0</v>
       </c>
       <c r="D290" t="n">
         <v>1.0</v>
@@ -4202,7 +4202,7 @@
         <v>2023.0</v>
       </c>
       <c r="C291" t="n" s="2">
-        <v>45158.0</v>
+        <v>45102.0</v>
       </c>
       <c r="D291" t="n">
         <v>1.0</v>
@@ -4216,10 +4216,10 @@
         <v>2023.0</v>
       </c>
       <c r="C292" t="n" s="2">
-        <v>45207.0</v>
+        <v>45158.0</v>
       </c>
       <c r="D292" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="293">
@@ -4230,7 +4230,7 @@
         <v>2023.0</v>
       </c>
       <c r="C293" t="n" s="2">
-        <v>45214.0</v>
+        <v>45207.0</v>
       </c>
       <c r="D293" t="n">
         <v>3.0</v>
@@ -4244,10 +4244,10 @@
         <v>2023.0</v>
       </c>
       <c r="C294" t="n" s="2">
-        <v>45221.0</v>
+        <v>45214.0</v>
       </c>
       <c r="D294" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="295">
@@ -4258,7 +4258,7 @@
         <v>2023.0</v>
       </c>
       <c r="C295" t="n" s="2">
-        <v>45249.0</v>
+        <v>45221.0</v>
       </c>
       <c r="D295" t="n">
         <v>1.0</v>
@@ -4272,10 +4272,10 @@
         <v>2023.0</v>
       </c>
       <c r="C296" t="n" s="2">
-        <v>45256.0</v>
+        <v>45249.0</v>
       </c>
       <c r="D296" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="297">
@@ -4286,10 +4286,10 @@
         <v>2023.0</v>
       </c>
       <c r="C297" t="n" s="2">
-        <v>45263.0</v>
+        <v>45256.0</v>
       </c>
       <c r="D297" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="298">
@@ -4300,10 +4300,10 @@
         <v>2023.0</v>
       </c>
       <c r="C298" t="n" s="2">
-        <v>45270.0</v>
+        <v>45263.0</v>
       </c>
       <c r="D298" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="299">
@@ -4314,10 +4314,10 @@
         <v>2023.0</v>
       </c>
       <c r="C299" t="n" s="2">
-        <v>45277.0</v>
+        <v>45270.0</v>
       </c>
       <c r="D299" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="300">
@@ -4328,10 +4328,10 @@
         <v>2023.0</v>
       </c>
       <c r="C300" t="n" s="2">
-        <v>45284.0</v>
+        <v>45277.0</v>
       </c>
       <c r="D300" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="301">
@@ -4342,10 +4342,10 @@
         <v>2023.0</v>
       </c>
       <c r="C301" t="n" s="2">
-        <v>45291.0</v>
+        <v>45284.0</v>
       </c>
       <c r="D301" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="302">
@@ -4353,13 +4353,13 @@
         <v>6</v>
       </c>
       <c r="B302" t="n">
-        <v>2024.0</v>
+        <v>2023.0</v>
       </c>
       <c r="C302" t="n" s="2">
-        <v>45306.0</v>
+        <v>45291.0</v>
       </c>
       <c r="D302" t="n">
-        <v>7.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="303">
@@ -4370,10 +4370,10 @@
         <v>2024.0</v>
       </c>
       <c r="C303" t="n" s="2">
-        <v>45313.0</v>
+        <v>45306.0</v>
       </c>
       <c r="D303" t="n">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="304">
@@ -4384,10 +4384,10 @@
         <v>2024.0</v>
       </c>
       <c r="C304" t="n" s="2">
-        <v>45320.0</v>
+        <v>45313.0</v>
       </c>
       <c r="D304" t="n">
-        <v>19.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="305">
@@ -4398,10 +4398,10 @@
         <v>2024.0</v>
       </c>
       <c r="C305" t="n" s="2">
-        <v>45327.0</v>
+        <v>45320.0</v>
       </c>
       <c r="D305" t="n">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="306">
@@ -4412,10 +4412,10 @@
         <v>2024.0</v>
       </c>
       <c r="C306" t="n" s="2">
-        <v>45334.0</v>
+        <v>45327.0</v>
       </c>
       <c r="D306" t="n">
-        <v>9.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="307">
@@ -4426,10 +4426,10 @@
         <v>2024.0</v>
       </c>
       <c r="C307" t="n" s="2">
-        <v>45341.0</v>
+        <v>45334.0</v>
       </c>
       <c r="D307" t="n">
-        <v>12.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="308">
@@ -4440,7 +4440,7 @@
         <v>2024.0</v>
       </c>
       <c r="C308" t="n" s="2">
-        <v>45348.0</v>
+        <v>45341.0</v>
       </c>
       <c r="D308" t="n">
         <v>12.0</v>
@@ -4454,10 +4454,10 @@
         <v>2024.0</v>
       </c>
       <c r="C309" t="n" s="2">
-        <v>45355.0</v>
+        <v>45348.0</v>
       </c>
       <c r="D309" t="n">
-        <v>10.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="310">
@@ -4468,10 +4468,10 @@
         <v>2024.0</v>
       </c>
       <c r="C310" t="n" s="2">
-        <v>45362.0</v>
+        <v>45355.0</v>
       </c>
       <c r="D310" t="n">
-        <v>12.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="311">
@@ -4482,10 +4482,10 @@
         <v>2024.0</v>
       </c>
       <c r="C311" t="n" s="2">
-        <v>45369.0</v>
+        <v>45362.0</v>
       </c>
       <c r="D311" t="n">
-        <v>13.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="312">
@@ -4496,10 +4496,10 @@
         <v>2024.0</v>
       </c>
       <c r="C312" t="n" s="2">
-        <v>45376.0</v>
+        <v>45369.0</v>
       </c>
       <c r="D312" t="n">
-        <v>18.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="313">
@@ -4510,10 +4510,10 @@
         <v>2024.0</v>
       </c>
       <c r="C313" t="n" s="2">
-        <v>45383.0</v>
+        <v>45376.0</v>
       </c>
       <c r="D313" t="n">
-        <v>12.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="314">
@@ -4524,10 +4524,10 @@
         <v>2024.0</v>
       </c>
       <c r="C314" t="n" s="2">
-        <v>45390.0</v>
+        <v>45383.0</v>
       </c>
       <c r="D314" t="n">
-        <v>6.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="315">
@@ -4538,10 +4538,10 @@
         <v>2024.0</v>
       </c>
       <c r="C315" t="n" s="2">
-        <v>45397.0</v>
+        <v>45390.0</v>
       </c>
       <c r="D315" t="n">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="316">
@@ -4552,10 +4552,10 @@
         <v>2024.0</v>
       </c>
       <c r="C316" t="n" s="2">
-        <v>45404.0</v>
+        <v>45397.0</v>
       </c>
       <c r="D316" t="n">
-        <v>3.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="317">
@@ -4566,10 +4566,10 @@
         <v>2024.0</v>
       </c>
       <c r="C317" t="n" s="2">
-        <v>45411.0</v>
+        <v>45404.0</v>
       </c>
       <c r="D317" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="318">
@@ -4580,10 +4580,10 @@
         <v>2024.0</v>
       </c>
       <c r="C318" t="n" s="2">
-        <v>45418.0</v>
+        <v>45411.0</v>
       </c>
       <c r="D318" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="319">
@@ -4594,10 +4594,10 @@
         <v>2024.0</v>
       </c>
       <c r="C319" t="n" s="2">
-        <v>45425.0</v>
+        <v>45418.0</v>
       </c>
       <c r="D319" t="n">
-        <v>9.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="320">
@@ -4608,10 +4608,10 @@
         <v>2024.0</v>
       </c>
       <c r="C320" t="n" s="2">
-        <v>45432.0</v>
+        <v>45425.0</v>
       </c>
       <c r="D320" t="n">
-        <v>6.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="321">
@@ -4622,7 +4622,7 @@
         <v>2024.0</v>
       </c>
       <c r="C321" t="n" s="2">
-        <v>45439.0</v>
+        <v>45432.0</v>
       </c>
       <c r="D321" t="n">
         <v>6.0</v>
@@ -4636,10 +4636,10 @@
         <v>2024.0</v>
       </c>
       <c r="C322" t="n" s="2">
-        <v>45446.0</v>
+        <v>45439.0</v>
       </c>
       <c r="D322" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="323">
@@ -4650,10 +4650,10 @@
         <v>2024.0</v>
       </c>
       <c r="C323" t="n" s="2">
-        <v>45453.0</v>
+        <v>45446.0</v>
       </c>
       <c r="D323" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="324">
@@ -4664,7 +4664,7 @@
         <v>2024.0</v>
       </c>
       <c r="C324" t="n" s="2">
-        <v>45460.0</v>
+        <v>45453.0</v>
       </c>
       <c r="D324" t="n">
         <v>4.0</v>
@@ -4678,7 +4678,7 @@
         <v>2024.0</v>
       </c>
       <c r="C325" t="n" s="2">
-        <v>45467.0</v>
+        <v>45460.0</v>
       </c>
       <c r="D325" t="n">
         <v>4.0</v>
@@ -4692,10 +4692,10 @@
         <v>2024.0</v>
       </c>
       <c r="C326" t="n" s="2">
-        <v>45474.0</v>
+        <v>45467.0</v>
       </c>
       <c r="D326" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="327">
@@ -4706,10 +4706,10 @@
         <v>2024.0</v>
       </c>
       <c r="C327" t="n" s="2">
-        <v>45481.0</v>
+        <v>45474.0</v>
       </c>
       <c r="D327" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="328">
@@ -4720,10 +4720,10 @@
         <v>2024.0</v>
       </c>
       <c r="C328" t="n" s="2">
-        <v>45488.0</v>
+        <v>45481.0</v>
       </c>
       <c r="D328" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="329">
@@ -4734,10 +4734,10 @@
         <v>2024.0</v>
       </c>
       <c r="C329" t="n" s="2">
-        <v>45495.0</v>
+        <v>45488.0</v>
       </c>
       <c r="D329" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="330">
@@ -4748,10 +4748,10 @@
         <v>2024.0</v>
       </c>
       <c r="C330" t="n" s="2">
-        <v>45502.0</v>
+        <v>45495.0</v>
       </c>
       <c r="D330" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="331">
@@ -4762,10 +4762,10 @@
         <v>2024.0</v>
       </c>
       <c r="C331" t="n" s="2">
-        <v>45509.0</v>
+        <v>45502.0</v>
       </c>
       <c r="D331" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="332">
@@ -4776,7 +4776,7 @@
         <v>2024.0</v>
       </c>
       <c r="C332" t="n" s="2">
-        <v>45523.0</v>
+        <v>45509.0</v>
       </c>
       <c r="D332" t="n">
         <v>1.0</v>
@@ -4790,7 +4790,7 @@
         <v>2024.0</v>
       </c>
       <c r="C333" t="n" s="2">
-        <v>45551.0</v>
+        <v>45523.0</v>
       </c>
       <c r="D333" t="n">
         <v>1.0</v>
@@ -4804,7 +4804,7 @@
         <v>2024.0</v>
       </c>
       <c r="C334" t="n" s="2">
-        <v>45558.0</v>
+        <v>45551.0</v>
       </c>
       <c r="D334" t="n">
         <v>1.0</v>
@@ -4818,10 +4818,10 @@
         <v>2024.0</v>
       </c>
       <c r="C335" t="n" s="2">
-        <v>45572.0</v>
+        <v>45558.0</v>
       </c>
       <c r="D335" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="336">
@@ -4832,10 +4832,10 @@
         <v>2024.0</v>
       </c>
       <c r="C336" t="n" s="2">
-        <v>45593.0</v>
+        <v>45572.0</v>
       </c>
       <c r="D336" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="337">
@@ -4846,10 +4846,10 @@
         <v>2024.0</v>
       </c>
       <c r="C337" t="n" s="2">
-        <v>45614.0</v>
+        <v>45593.0</v>
       </c>
       <c r="D337" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="338">
@@ -4860,10 +4860,10 @@
         <v>2024.0</v>
       </c>
       <c r="C338" t="n" s="2">
-        <v>45621.0</v>
+        <v>45614.0</v>
       </c>
       <c r="D338" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="339">
@@ -4874,7 +4874,7 @@
         <v>2024.0</v>
       </c>
       <c r="C339" t="n" s="2">
-        <v>45635.0</v>
+        <v>45621.0</v>
       </c>
       <c r="D339" t="n">
         <v>1.0</v>
@@ -4888,7 +4888,7 @@
         <v>2024.0</v>
       </c>
       <c r="C340" t="n" s="2">
-        <v>45649.0</v>
+        <v>45635.0</v>
       </c>
       <c r="D340" t="n">
         <v>1.0</v>
@@ -4899,13 +4899,13 @@
         <v>6</v>
       </c>
       <c r="B341" t="n">
-        <v>2025.0</v>
+        <v>2024.0</v>
       </c>
       <c r="C341" t="n" s="2">
-        <v>45665.0</v>
+        <v>45649.0</v>
       </c>
       <c r="D341" t="n">
-        <v>9.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="342">
@@ -4916,10 +4916,10 @@
         <v>2025.0</v>
       </c>
       <c r="C342" t="n" s="2">
-        <v>45672.0</v>
+        <v>45665.0</v>
       </c>
       <c r="D342" t="n">
-        <v>3.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="343">
@@ -4930,10 +4930,10 @@
         <v>2025.0</v>
       </c>
       <c r="C343" t="n" s="2">
-        <v>45679.0</v>
+        <v>45672.0</v>
       </c>
       <c r="D343" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="344">
@@ -4944,10 +4944,10 @@
         <v>2025.0</v>
       </c>
       <c r="C344" t="n" s="2">
-        <v>45686.0</v>
+        <v>45679.0</v>
       </c>
       <c r="D344" t="n">
-        <v>8.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="345">
@@ -4958,10 +4958,10 @@
         <v>2025.0</v>
       </c>
       <c r="C345" t="n" s="2">
-        <v>45693.0</v>
+        <v>45686.0</v>
       </c>
       <c r="D345" t="n">
-        <v>3.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="346">
@@ -4972,10 +4972,10 @@
         <v>2025.0</v>
       </c>
       <c r="C346" t="n" s="2">
-        <v>45700.0</v>
+        <v>45693.0</v>
       </c>
       <c r="D346" t="n">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="347">
@@ -4986,10 +4986,10 @@
         <v>2025.0</v>
       </c>
       <c r="C347" t="n" s="2">
-        <v>45707.0</v>
+        <v>45700.0</v>
       </c>
       <c r="D347" t="n">
-        <v>8.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="348">
@@ -5000,10 +5000,10 @@
         <v>2025.0</v>
       </c>
       <c r="C348" t="n" s="2">
-        <v>45714.0</v>
+        <v>45707.0</v>
       </c>
       <c r="D348" t="n">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="349">
@@ -5014,10 +5014,10 @@
         <v>2025.0</v>
       </c>
       <c r="C349" t="n" s="2">
-        <v>45721.0</v>
+        <v>45714.0</v>
       </c>
       <c r="D349" t="n">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="350">
@@ -5028,10 +5028,10 @@
         <v>2025.0</v>
       </c>
       <c r="C350" t="n" s="2">
-        <v>45728.0</v>
+        <v>45721.0</v>
       </c>
       <c r="D350" t="n">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="351">
@@ -5042,10 +5042,10 @@
         <v>2025.0</v>
       </c>
       <c r="C351" t="n" s="2">
-        <v>45735.0</v>
+        <v>45728.0</v>
       </c>
       <c r="D351" t="n">
-        <v>4.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="352">
@@ -5056,10 +5056,10 @@
         <v>2025.0</v>
       </c>
       <c r="C352" t="n" s="2">
-        <v>45742.0</v>
+        <v>45735.0</v>
       </c>
       <c r="D352" t="n">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="353">
@@ -5070,10 +5070,10 @@
         <v>2025.0</v>
       </c>
       <c r="C353" t="n" s="2">
-        <v>45749.0</v>
+        <v>45742.0</v>
       </c>
       <c r="D353" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="354">
@@ -5084,10 +5084,10 @@
         <v>2025.0</v>
       </c>
       <c r="C354" t="n" s="2">
-        <v>45756.0</v>
+        <v>45749.0</v>
       </c>
       <c r="D354" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="355">
@@ -5098,10 +5098,10 @@
         <v>2025.0</v>
       </c>
       <c r="C355" t="n" s="2">
-        <v>45763.0</v>
+        <v>45756.0</v>
       </c>
       <c r="D355" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="356">
@@ -5112,7 +5112,7 @@
         <v>2025.0</v>
       </c>
       <c r="C356" t="n" s="2">
-        <v>45770.0</v>
+        <v>45763.0</v>
       </c>
       <c r="D356" t="n">
         <v>4.0</v>
@@ -5126,10 +5126,10 @@
         <v>2025.0</v>
       </c>
       <c r="C357" t="n" s="2">
-        <v>45777.0</v>
+        <v>45770.0</v>
       </c>
       <c r="D357" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="358">
@@ -5140,7 +5140,7 @@
         <v>2025.0</v>
       </c>
       <c r="C358" t="n" s="2">
-        <v>45784.0</v>
+        <v>45777.0</v>
       </c>
       <c r="D358" t="n">
         <v>1.0</v>
@@ -5154,7 +5154,7 @@
         <v>2025.0</v>
       </c>
       <c r="C359" t="n" s="2">
-        <v>45791.0</v>
+        <v>45784.0</v>
       </c>
       <c r="D359" t="n">
         <v>1.0</v>
@@ -5168,7 +5168,7 @@
         <v>2025.0</v>
       </c>
       <c r="C360" t="n" s="2">
-        <v>45840.0</v>
+        <v>45791.0</v>
       </c>
       <c r="D360" t="n">
         <v>1.0</v>
@@ -5182,7 +5182,7 @@
         <v>2025.0</v>
       </c>
       <c r="C361" t="n" s="2">
-        <v>46001.0</v>
+        <v>45840.0</v>
       </c>
       <c r="D361" t="n">
         <v>1.0</v>
@@ -5193,10 +5193,10 @@
         <v>6</v>
       </c>
       <c r="B362" t="n">
-        <v>2026.0</v>
+        <v>2025.0</v>
       </c>
       <c r="C362" t="n" s="2">
-        <v>46037.0</v>
+        <v>46001.0</v>
       </c>
       <c r="D362" t="n">
         <v>1.0</v>
@@ -5204,13 +5204,13 @@
     </row>
     <row r="363">
       <c r="A363" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B363" t="n">
-        <v>2021.0</v>
+        <v>2026.0</v>
       </c>
       <c r="C363" t="n" s="2">
-        <v>44561.0</v>
+        <v>46037.0</v>
       </c>
       <c r="D363" t="n">
         <v>1.0</v>
@@ -5221,10 +5221,10 @@
         <v>7</v>
       </c>
       <c r="B364" t="n">
-        <v>2022.0</v>
+        <v>2021.0</v>
       </c>
       <c r="C364" t="n" s="2">
-        <v>44569.0</v>
+        <v>44561.0</v>
       </c>
       <c r="D364" t="n">
         <v>1.0</v>
@@ -5238,10 +5238,10 @@
         <v>2022.0</v>
       </c>
       <c r="C365" t="n" s="2">
-        <v>44576.0</v>
+        <v>44569.0</v>
       </c>
       <c r="D365" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="366">
@@ -5252,10 +5252,10 @@
         <v>2022.0</v>
       </c>
       <c r="C366" t="n" s="2">
-        <v>44583.0</v>
+        <v>44576.0</v>
       </c>
       <c r="D366" t="n">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="367">
@@ -5266,10 +5266,10 @@
         <v>2022.0</v>
       </c>
       <c r="C367" t="n" s="2">
-        <v>44590.0</v>
+        <v>44583.0</v>
       </c>
       <c r="D367" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="368">
@@ -5280,10 +5280,10 @@
         <v>2022.0</v>
       </c>
       <c r="C368" t="n" s="2">
-        <v>44604.0</v>
+        <v>44590.0</v>
       </c>
       <c r="D368" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="369">
@@ -5294,7 +5294,7 @@
         <v>2022.0</v>
       </c>
       <c r="C369" t="n" s="2">
-        <v>44611.0</v>
+        <v>44604.0</v>
       </c>
       <c r="D369" t="n">
         <v>3.0</v>
@@ -5308,10 +5308,10 @@
         <v>2022.0</v>
       </c>
       <c r="C370" t="n" s="2">
-        <v>44618.0</v>
+        <v>44611.0</v>
       </c>
       <c r="D370" t="n">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="371">
@@ -5322,7 +5322,7 @@
         <v>2022.0</v>
       </c>
       <c r="C371" t="n" s="2">
-        <v>44625.0</v>
+        <v>44618.0</v>
       </c>
       <c r="D371" t="n">
         <v>5.0</v>
@@ -5336,10 +5336,10 @@
         <v>2022.0</v>
       </c>
       <c r="C372" t="n" s="2">
-        <v>44632.0</v>
+        <v>44625.0</v>
       </c>
       <c r="D372" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="373">
@@ -5350,10 +5350,10 @@
         <v>2022.0</v>
       </c>
       <c r="C373" t="n" s="2">
-        <v>44639.0</v>
+        <v>44632.0</v>
       </c>
       <c r="D373" t="n">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="374">
@@ -5364,10 +5364,10 @@
         <v>2022.0</v>
       </c>
       <c r="C374" t="n" s="2">
-        <v>44646.0</v>
+        <v>44639.0</v>
       </c>
       <c r="D374" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="375">
@@ -5378,10 +5378,10 @@
         <v>2022.0</v>
       </c>
       <c r="C375" t="n" s="2">
-        <v>44653.0</v>
+        <v>44646.0</v>
       </c>
       <c r="D375" t="n">
-        <v>9.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="376">
@@ -5392,10 +5392,10 @@
         <v>2022.0</v>
       </c>
       <c r="C376" t="n" s="2">
-        <v>44660.0</v>
+        <v>44653.0</v>
       </c>
       <c r="D376" t="n">
-        <v>6.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="377">
@@ -5406,10 +5406,10 @@
         <v>2022.0</v>
       </c>
       <c r="C377" t="n" s="2">
-        <v>44667.0</v>
+        <v>44660.0</v>
       </c>
       <c r="D377" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="378">
@@ -5420,10 +5420,10 @@
         <v>2022.0</v>
       </c>
       <c r="C378" t="n" s="2">
-        <v>44674.0</v>
+        <v>44667.0</v>
       </c>
       <c r="D378" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="379">
@@ -5434,10 +5434,10 @@
         <v>2022.0</v>
       </c>
       <c r="C379" t="n" s="2">
-        <v>44681.0</v>
+        <v>44674.0</v>
       </c>
       <c r="D379" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="380">
@@ -5448,10 +5448,10 @@
         <v>2022.0</v>
       </c>
       <c r="C380" t="n" s="2">
-        <v>44688.0</v>
+        <v>44681.0</v>
       </c>
       <c r="D380" t="n">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="381">
@@ -5462,10 +5462,10 @@
         <v>2022.0</v>
       </c>
       <c r="C381" t="n" s="2">
-        <v>44695.0</v>
+        <v>44688.0</v>
       </c>
       <c r="D381" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="382">
@@ -5476,10 +5476,10 @@
         <v>2022.0</v>
       </c>
       <c r="C382" t="n" s="2">
-        <v>44702.0</v>
+        <v>44695.0</v>
       </c>
       <c r="D382" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="383">
@@ -5490,10 +5490,10 @@
         <v>2022.0</v>
       </c>
       <c r="C383" t="n" s="2">
-        <v>44709.0</v>
+        <v>44702.0</v>
       </c>
       <c r="D383" t="n">
-        <v>8.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="384">
@@ -5504,10 +5504,10 @@
         <v>2022.0</v>
       </c>
       <c r="C384" t="n" s="2">
-        <v>44716.0</v>
+        <v>44709.0</v>
       </c>
       <c r="D384" t="n">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="385">
@@ -5518,10 +5518,10 @@
         <v>2022.0</v>
       </c>
       <c r="C385" t="n" s="2">
-        <v>44723.0</v>
+        <v>44716.0</v>
       </c>
       <c r="D385" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="386">
@@ -5532,10 +5532,10 @@
         <v>2022.0</v>
       </c>
       <c r="C386" t="n" s="2">
-        <v>44730.0</v>
+        <v>44723.0</v>
       </c>
       <c r="D386" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="387">
@@ -5546,7 +5546,7 @@
         <v>2022.0</v>
       </c>
       <c r="C387" t="n" s="2">
-        <v>44737.0</v>
+        <v>44730.0</v>
       </c>
       <c r="D387" t="n">
         <v>4.0</v>
@@ -5560,10 +5560,10 @@
         <v>2022.0</v>
       </c>
       <c r="C388" t="n" s="2">
-        <v>44744.0</v>
+        <v>44737.0</v>
       </c>
       <c r="D388" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="389">
@@ -5574,10 +5574,10 @@
         <v>2022.0</v>
       </c>
       <c r="C389" t="n" s="2">
-        <v>44751.0</v>
+        <v>44744.0</v>
       </c>
       <c r="D389" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="390">
@@ -5588,10 +5588,10 @@
         <v>2022.0</v>
       </c>
       <c r="C390" t="n" s="2">
-        <v>44758.0</v>
+        <v>44751.0</v>
       </c>
       <c r="D390" t="n">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="391">
@@ -5602,10 +5602,10 @@
         <v>2022.0</v>
       </c>
       <c r="C391" t="n" s="2">
-        <v>44765.0</v>
+        <v>44758.0</v>
       </c>
       <c r="D391" t="n">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="392">
@@ -5616,10 +5616,10 @@
         <v>2022.0</v>
       </c>
       <c r="C392" t="n" s="2">
-        <v>44779.0</v>
+        <v>44765.0</v>
       </c>
       <c r="D392" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="393">
@@ -5630,10 +5630,10 @@
         <v>2022.0</v>
       </c>
       <c r="C393" t="n" s="2">
-        <v>44786.0</v>
+        <v>44779.0</v>
       </c>
       <c r="D393" t="n">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="394">
@@ -5644,10 +5644,10 @@
         <v>2022.0</v>
       </c>
       <c r="C394" t="n" s="2">
-        <v>44863.0</v>
+        <v>44786.0</v>
       </c>
       <c r="D394" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="395">
@@ -5658,10 +5658,10 @@
         <v>2022.0</v>
       </c>
       <c r="C395" t="n" s="2">
-        <v>44870.0</v>
+        <v>44863.0</v>
       </c>
       <c r="D395" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="396">
@@ -5672,10 +5672,10 @@
         <v>2022.0</v>
       </c>
       <c r="C396" t="n" s="2">
-        <v>44884.0</v>
+        <v>44870.0</v>
       </c>
       <c r="D396" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="397">
@@ -5686,7 +5686,7 @@
         <v>2022.0</v>
       </c>
       <c r="C397" t="n" s="2">
-        <v>44891.0</v>
+        <v>44884.0</v>
       </c>
       <c r="D397" t="n">
         <v>2.0</v>
@@ -5700,10 +5700,10 @@
         <v>2022.0</v>
       </c>
       <c r="C398" t="n" s="2">
-        <v>44898.0</v>
+        <v>44891.0</v>
       </c>
       <c r="D398" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="399">
@@ -5714,10 +5714,10 @@
         <v>2022.0</v>
       </c>
       <c r="C399" t="n" s="2">
-        <v>44912.0</v>
+        <v>44898.0</v>
       </c>
       <c r="D399" t="n">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="400">
@@ -5728,10 +5728,10 @@
         <v>2022.0</v>
       </c>
       <c r="C400" t="n" s="2">
-        <v>44919.0</v>
+        <v>44912.0</v>
       </c>
       <c r="D400" t="n">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="401">
@@ -5742,10 +5742,10 @@
         <v>2022.0</v>
       </c>
       <c r="C401" t="n" s="2">
-        <v>44926.0</v>
+        <v>44919.0</v>
       </c>
       <c r="D401" t="n">
-        <v>12.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="402">
@@ -5753,13 +5753,13 @@
         <v>7</v>
       </c>
       <c r="B402" t="n">
-        <v>2023.0</v>
+        <v>2022.0</v>
       </c>
       <c r="C402" t="n" s="2">
-        <v>44934.0</v>
+        <v>44926.0</v>
       </c>
       <c r="D402" t="n">
-        <v>4.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="403">
@@ -5770,10 +5770,10 @@
         <v>2023.0</v>
       </c>
       <c r="C403" t="n" s="2">
-        <v>44941.0</v>
+        <v>44934.0</v>
       </c>
       <c r="D403" t="n">
-        <v>16.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="404">
@@ -5784,10 +5784,10 @@
         <v>2023.0</v>
       </c>
       <c r="C404" t="n" s="2">
-        <v>44948.0</v>
+        <v>44941.0</v>
       </c>
       <c r="D404" t="n">
-        <v>5.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="405">
@@ -5798,10 +5798,10 @@
         <v>2023.0</v>
       </c>
       <c r="C405" t="n" s="2">
-        <v>44955.0</v>
+        <v>44948.0</v>
       </c>
       <c r="D405" t="n">
-        <v>19.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="406">
@@ -5812,10 +5812,10 @@
         <v>2023.0</v>
       </c>
       <c r="C406" t="n" s="2">
-        <v>44962.0</v>
+        <v>44955.0</v>
       </c>
       <c r="D406" t="n">
-        <v>22.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="407">
@@ -5826,10 +5826,10 @@
         <v>2023.0</v>
       </c>
       <c r="C407" t="n" s="2">
-        <v>44969.0</v>
+        <v>44962.0</v>
       </c>
       <c r="D407" t="n">
-        <v>9.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="408">
@@ -5840,10 +5840,10 @@
         <v>2023.0</v>
       </c>
       <c r="C408" t="n" s="2">
-        <v>44976.0</v>
+        <v>44969.0</v>
       </c>
       <c r="D408" t="n">
-        <v>22.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="409">
@@ -5854,10 +5854,10 @@
         <v>2023.0</v>
       </c>
       <c r="C409" t="n" s="2">
-        <v>44983.0</v>
+        <v>44976.0</v>
       </c>
       <c r="D409" t="n">
-        <v>29.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="410">
@@ -5868,10 +5868,10 @@
         <v>2023.0</v>
       </c>
       <c r="C410" t="n" s="2">
-        <v>44990.0</v>
+        <v>44983.0</v>
       </c>
       <c r="D410" t="n">
-        <v>5.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="411">
@@ -5882,10 +5882,10 @@
         <v>2023.0</v>
       </c>
       <c r="C411" t="n" s="2">
-        <v>44997.0</v>
+        <v>44990.0</v>
       </c>
       <c r="D411" t="n">
-        <v>24.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="412">
@@ -5896,10 +5896,10 @@
         <v>2023.0</v>
       </c>
       <c r="C412" t="n" s="2">
-        <v>45004.0</v>
+        <v>44997.0</v>
       </c>
       <c r="D412" t="n">
-        <v>8.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="413">
@@ -5910,10 +5910,10 @@
         <v>2023.0</v>
       </c>
       <c r="C413" t="n" s="2">
-        <v>45011.0</v>
+        <v>45004.0</v>
       </c>
       <c r="D413" t="n">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="414">
@@ -5924,10 +5924,10 @@
         <v>2023.0</v>
       </c>
       <c r="C414" t="n" s="2">
-        <v>45018.0</v>
+        <v>45011.0</v>
       </c>
       <c r="D414" t="n">
-        <v>18.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="415">
@@ -5938,10 +5938,10 @@
         <v>2023.0</v>
       </c>
       <c r="C415" t="n" s="2">
-        <v>45025.0</v>
+        <v>45018.0</v>
       </c>
       <c r="D415" t="n">
-        <v>13.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="416">
@@ -5952,10 +5952,10 @@
         <v>2023.0</v>
       </c>
       <c r="C416" t="n" s="2">
-        <v>45032.0</v>
+        <v>45025.0</v>
       </c>
       <c r="D416" t="n">
-        <v>18.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="417">
@@ -5966,10 +5966,10 @@
         <v>2023.0</v>
       </c>
       <c r="C417" t="n" s="2">
-        <v>45039.0</v>
+        <v>45032.0</v>
       </c>
       <c r="D417" t="n">
-        <v>15.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="418">
@@ -5980,10 +5980,10 @@
         <v>2023.0</v>
       </c>
       <c r="C418" t="n" s="2">
-        <v>45046.0</v>
+        <v>45039.0</v>
       </c>
       <c r="D418" t="n">
-        <v>12.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="419">
@@ -5994,10 +5994,10 @@
         <v>2023.0</v>
       </c>
       <c r="C419" t="n" s="2">
-        <v>45053.0</v>
+        <v>45046.0</v>
       </c>
       <c r="D419" t="n">
-        <v>6.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="420">
@@ -6008,10 +6008,10 @@
         <v>2023.0</v>
       </c>
       <c r="C420" t="n" s="2">
-        <v>45060.0</v>
+        <v>45053.0</v>
       </c>
       <c r="D420" t="n">
-        <v>11.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="421">
@@ -6022,10 +6022,10 @@
         <v>2023.0</v>
       </c>
       <c r="C421" t="n" s="2">
-        <v>45067.0</v>
+        <v>45060.0</v>
       </c>
       <c r="D421" t="n">
-        <v>8.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="422">
@@ -6036,7 +6036,7 @@
         <v>2023.0</v>
       </c>
       <c r="C422" t="n" s="2">
-        <v>45074.0</v>
+        <v>45067.0</v>
       </c>
       <c r="D422" t="n">
         <v>8.0</v>
@@ -6050,10 +6050,10 @@
         <v>2023.0</v>
       </c>
       <c r="C423" t="n" s="2">
-        <v>45081.0</v>
+        <v>45074.0</v>
       </c>
       <c r="D423" t="n">
-        <v>5.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="424">
@@ -6064,10 +6064,10 @@
         <v>2023.0</v>
       </c>
       <c r="C424" t="n" s="2">
-        <v>45088.0</v>
+        <v>45081.0</v>
       </c>
       <c r="D424" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="425">
@@ -6078,10 +6078,10 @@
         <v>2023.0</v>
       </c>
       <c r="C425" t="n" s="2">
-        <v>45095.0</v>
+        <v>45088.0</v>
       </c>
       <c r="D425" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="426">
@@ -6092,10 +6092,10 @@
         <v>2023.0</v>
       </c>
       <c r="C426" t="n" s="2">
-        <v>45102.0</v>
+        <v>45095.0</v>
       </c>
       <c r="D426" t="n">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="427">
@@ -6106,10 +6106,10 @@
         <v>2023.0</v>
       </c>
       <c r="C427" t="n" s="2">
-        <v>45109.0</v>
+        <v>45102.0</v>
       </c>
       <c r="D427" t="n">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="428">
@@ -6120,10 +6120,10 @@
         <v>2023.0</v>
       </c>
       <c r="C428" t="n" s="2">
-        <v>45116.0</v>
+        <v>45109.0</v>
       </c>
       <c r="D428" t="n">
-        <v>3.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="429">
@@ -6134,10 +6134,10 @@
         <v>2023.0</v>
       </c>
       <c r="C429" t="n" s="2">
-        <v>45123.0</v>
+        <v>45116.0</v>
       </c>
       <c r="D429" t="n">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="430">
@@ -6148,7 +6148,7 @@
         <v>2023.0</v>
       </c>
       <c r="C430" t="n" s="2">
-        <v>45130.0</v>
+        <v>45123.0</v>
       </c>
       <c r="D430" t="n">
         <v>6.0</v>
@@ -6162,10 +6162,10 @@
         <v>2023.0</v>
       </c>
       <c r="C431" t="n" s="2">
-        <v>45137.0</v>
+        <v>45130.0</v>
       </c>
       <c r="D431" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="432">
@@ -6176,7 +6176,7 @@
         <v>2023.0</v>
       </c>
       <c r="C432" t="n" s="2">
-        <v>45144.0</v>
+        <v>45137.0</v>
       </c>
       <c r="D432" t="n">
         <v>2.0</v>
@@ -6190,7 +6190,7 @@
         <v>2023.0</v>
       </c>
       <c r="C433" t="n" s="2">
-        <v>45151.0</v>
+        <v>45144.0</v>
       </c>
       <c r="D433" t="n">
         <v>2.0</v>
@@ -6204,7 +6204,7 @@
         <v>2023.0</v>
       </c>
       <c r="C434" t="n" s="2">
-        <v>45165.0</v>
+        <v>45151.0</v>
       </c>
       <c r="D434" t="n">
         <v>2.0</v>
@@ -6218,7 +6218,7 @@
         <v>2023.0</v>
       </c>
       <c r="C435" t="n" s="2">
-        <v>45172.0</v>
+        <v>45165.0</v>
       </c>
       <c r="D435" t="n">
         <v>2.0</v>
@@ -6232,10 +6232,10 @@
         <v>2023.0</v>
       </c>
       <c r="C436" t="n" s="2">
-        <v>45179.0</v>
+        <v>45172.0</v>
       </c>
       <c r="D436" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="437">
@@ -6246,7 +6246,7 @@
         <v>2023.0</v>
       </c>
       <c r="C437" t="n" s="2">
-        <v>45186.0</v>
+        <v>45179.0</v>
       </c>
       <c r="D437" t="n">
         <v>1.0</v>
@@ -6260,7 +6260,7 @@
         <v>2023.0</v>
       </c>
       <c r="C438" t="n" s="2">
-        <v>45193.0</v>
+        <v>45186.0</v>
       </c>
       <c r="D438" t="n">
         <v>1.0</v>
@@ -6274,7 +6274,7 @@
         <v>2023.0</v>
       </c>
       <c r="C439" t="n" s="2">
-        <v>45200.0</v>
+        <v>45193.0</v>
       </c>
       <c r="D439" t="n">
         <v>1.0</v>
@@ -6288,7 +6288,7 @@
         <v>2023.0</v>
       </c>
       <c r="C440" t="n" s="2">
-        <v>45207.0</v>
+        <v>45200.0</v>
       </c>
       <c r="D440" t="n">
         <v>1.0</v>
@@ -6302,7 +6302,7 @@
         <v>2023.0</v>
       </c>
       <c r="C441" t="n" s="2">
-        <v>45235.0</v>
+        <v>45207.0</v>
       </c>
       <c r="D441" t="n">
         <v>1.0</v>
@@ -6316,10 +6316,10 @@
         <v>2023.0</v>
       </c>
       <c r="C442" t="n" s="2">
-        <v>45242.0</v>
+        <v>45235.0</v>
       </c>
       <c r="D442" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="443">
@@ -6330,10 +6330,10 @@
         <v>2023.0</v>
       </c>
       <c r="C443" t="n" s="2">
-        <v>45249.0</v>
+        <v>45242.0</v>
       </c>
       <c r="D443" t="n">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="444">
@@ -6344,10 +6344,10 @@
         <v>2023.0</v>
       </c>
       <c r="C444" t="n" s="2">
-        <v>45256.0</v>
+        <v>45249.0</v>
       </c>
       <c r="D444" t="n">
-        <v>9.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="445">
@@ -6358,10 +6358,10 @@
         <v>2023.0</v>
       </c>
       <c r="C445" t="n" s="2">
-        <v>45263.0</v>
+        <v>45256.0</v>
       </c>
       <c r="D445" t="n">
-        <v>12.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="446">
@@ -6372,10 +6372,10 @@
         <v>2023.0</v>
       </c>
       <c r="C446" t="n" s="2">
-        <v>45270.0</v>
+        <v>45263.0</v>
       </c>
       <c r="D446" t="n">
-        <v>6.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="447">
@@ -6386,10 +6386,10 @@
         <v>2023.0</v>
       </c>
       <c r="C447" t="n" s="2">
-        <v>45277.0</v>
+        <v>45270.0</v>
       </c>
       <c r="D447" t="n">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="448">
@@ -6400,7 +6400,7 @@
         <v>2023.0</v>
       </c>
       <c r="C448" t="n" s="2">
-        <v>45284.0</v>
+        <v>45277.0</v>
       </c>
       <c r="D448" t="n">
         <v>7.0</v>
@@ -6414,10 +6414,10 @@
         <v>2023.0</v>
       </c>
       <c r="C449" t="n" s="2">
-        <v>45291.0</v>
+        <v>45284.0</v>
       </c>
       <c r="D449" t="n">
-        <v>13.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="450">
@@ -6425,13 +6425,13 @@
         <v>7</v>
       </c>
       <c r="B450" t="n">
-        <v>2024.0</v>
+        <v>2023.0</v>
       </c>
       <c r="C450" t="n" s="2">
-        <v>45299.0</v>
+        <v>45291.0</v>
       </c>
       <c r="D450" t="n">
-        <v>6.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="451">
@@ -6442,10 +6442,10 @@
         <v>2024.0</v>
       </c>
       <c r="C451" t="n" s="2">
-        <v>45306.0</v>
+        <v>45299.0</v>
       </c>
       <c r="D451" t="n">
-        <v>11.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="452">
@@ -6456,10 +6456,10 @@
         <v>2024.0</v>
       </c>
       <c r="C452" t="n" s="2">
-        <v>45313.0</v>
+        <v>45306.0</v>
       </c>
       <c r="D452" t="n">
-        <v>5.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="453">
@@ -6470,10 +6470,10 @@
         <v>2024.0</v>
       </c>
       <c r="C453" t="n" s="2">
-        <v>45320.0</v>
+        <v>45313.0</v>
       </c>
       <c r="D453" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="454">
@@ -6484,10 +6484,10 @@
         <v>2024.0</v>
       </c>
       <c r="C454" t="n" s="2">
-        <v>45327.0</v>
+        <v>45320.0</v>
       </c>
       <c r="D454" t="n">
-        <v>9.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="455">
@@ -6498,10 +6498,10 @@
         <v>2024.0</v>
       </c>
       <c r="C455" t="n" s="2">
-        <v>45334.0</v>
+        <v>45327.0</v>
       </c>
       <c r="D455" t="n">
-        <v>3.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="456">
@@ -6512,10 +6512,10 @@
         <v>2024.0</v>
       </c>
       <c r="C456" t="n" s="2">
-        <v>45341.0</v>
+        <v>45334.0</v>
       </c>
       <c r="D456" t="n">
-        <v>21.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="457">
@@ -6526,10 +6526,10 @@
         <v>2024.0</v>
       </c>
       <c r="C457" t="n" s="2">
-        <v>45348.0</v>
+        <v>45341.0</v>
       </c>
       <c r="D457" t="n">
-        <v>1.0</v>
+        <v>21.0</v>
       </c>
     </row>
     <row r="458">
@@ -6540,10 +6540,10 @@
         <v>2024.0</v>
       </c>
       <c r="C458" t="n" s="2">
-        <v>45355.0</v>
+        <v>45348.0</v>
       </c>
       <c r="D458" t="n">
-        <v>9.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="459">
@@ -6554,10 +6554,10 @@
         <v>2024.0</v>
       </c>
       <c r="C459" t="n" s="2">
-        <v>45362.0</v>
+        <v>45355.0</v>
       </c>
       <c r="D459" t="n">
-        <v>4.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="460">
@@ -6568,10 +6568,10 @@
         <v>2024.0</v>
       </c>
       <c r="C460" t="n" s="2">
-        <v>45369.0</v>
+        <v>45362.0</v>
       </c>
       <c r="D460" t="n">
-        <v>14.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="461">
@@ -6582,10 +6582,10 @@
         <v>2024.0</v>
       </c>
       <c r="C461" t="n" s="2">
-        <v>45376.0</v>
+        <v>45369.0</v>
       </c>
       <c r="D461" t="n">
-        <v>4.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="462">
@@ -6596,10 +6596,10 @@
         <v>2024.0</v>
       </c>
       <c r="C462" t="n" s="2">
-        <v>45383.0</v>
+        <v>45376.0</v>
       </c>
       <c r="D462" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="463">
@@ -6610,10 +6610,10 @@
         <v>2024.0</v>
       </c>
       <c r="C463" t="n" s="2">
-        <v>45390.0</v>
+        <v>45383.0</v>
       </c>
       <c r="D463" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="464">
@@ -6624,7 +6624,7 @@
         <v>2024.0</v>
       </c>
       <c r="C464" t="n" s="2">
-        <v>45397.0</v>
+        <v>45390.0</v>
       </c>
       <c r="D464" t="n">
         <v>1.0</v>
@@ -6638,10 +6638,10 @@
         <v>2024.0</v>
       </c>
       <c r="C465" t="n" s="2">
-        <v>45404.0</v>
+        <v>45397.0</v>
       </c>
       <c r="D465" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="466">
@@ -6652,10 +6652,10 @@
         <v>2024.0</v>
       </c>
       <c r="C466" t="n" s="2">
-        <v>45411.0</v>
+        <v>45404.0</v>
       </c>
       <c r="D466" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="467">
@@ -6666,10 +6666,10 @@
         <v>2024.0</v>
       </c>
       <c r="C467" t="n" s="2">
-        <v>45439.0</v>
+        <v>45411.0</v>
       </c>
       <c r="D467" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="468">
@@ -6680,10 +6680,10 @@
         <v>2024.0</v>
       </c>
       <c r="C468" t="n" s="2">
-        <v>45446.0</v>
+        <v>45439.0</v>
       </c>
       <c r="D468" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="469">
@@ -6694,7 +6694,7 @@
         <v>2024.0</v>
       </c>
       <c r="C469" t="n" s="2">
-        <v>45460.0</v>
+        <v>45446.0</v>
       </c>
       <c r="D469" t="n">
         <v>1.0</v>
@@ -6708,7 +6708,7 @@
         <v>2024.0</v>
       </c>
       <c r="C470" t="n" s="2">
-        <v>45481.0</v>
+        <v>45460.0</v>
       </c>
       <c r="D470" t="n">
         <v>1.0</v>
@@ -6722,7 +6722,7 @@
         <v>2024.0</v>
       </c>
       <c r="C471" t="n" s="2">
-        <v>45516.0</v>
+        <v>45481.0</v>
       </c>
       <c r="D471" t="n">
         <v>1.0</v>
@@ -6736,7 +6736,7 @@
         <v>2024.0</v>
       </c>
       <c r="C472" t="n" s="2">
-        <v>45551.0</v>
+        <v>45516.0</v>
       </c>
       <c r="D472" t="n">
         <v>1.0</v>
@@ -6750,7 +6750,7 @@
         <v>2024.0</v>
       </c>
       <c r="C473" t="n" s="2">
-        <v>45579.0</v>
+        <v>45551.0</v>
       </c>
       <c r="D473" t="n">
         <v>1.0</v>
@@ -6764,7 +6764,7 @@
         <v>2024.0</v>
       </c>
       <c r="C474" t="n" s="2">
-        <v>45614.0</v>
+        <v>45579.0</v>
       </c>
       <c r="D474" t="n">
         <v>1.0</v>
@@ -6778,10 +6778,10 @@
         <v>2024.0</v>
       </c>
       <c r="C475" t="n" s="2">
-        <v>45635.0</v>
+        <v>45614.0</v>
       </c>
       <c r="D475" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="476">
@@ -6792,10 +6792,10 @@
         <v>2024.0</v>
       </c>
       <c r="C476" t="n" s="2">
-        <v>45642.0</v>
+        <v>45635.0</v>
       </c>
       <c r="D476" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="477">
@@ -6806,10 +6806,10 @@
         <v>2024.0</v>
       </c>
       <c r="C477" t="n" s="2">
-        <v>45649.0</v>
+        <v>45642.0</v>
       </c>
       <c r="D477" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="478">
@@ -6820,10 +6820,10 @@
         <v>2024.0</v>
       </c>
       <c r="C478" t="n" s="2">
-        <v>45656.0</v>
+        <v>45649.0</v>
       </c>
       <c r="D478" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="479">
@@ -6831,13 +6831,13 @@
         <v>7</v>
       </c>
       <c r="B479" t="n">
-        <v>2025.0</v>
+        <v>2024.0</v>
       </c>
       <c r="C479" t="n" s="2">
-        <v>45665.0</v>
+        <v>45656.0</v>
       </c>
       <c r="D479" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="480">
@@ -6848,10 +6848,10 @@
         <v>2025.0</v>
       </c>
       <c r="C480" t="n" s="2">
-        <v>45672.0</v>
+        <v>45665.0</v>
       </c>
       <c r="D480" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="481">
@@ -6862,7 +6862,7 @@
         <v>2025.0</v>
       </c>
       <c r="C481" t="n" s="2">
-        <v>45686.0</v>
+        <v>45672.0</v>
       </c>
       <c r="D481" t="n">
         <v>2.0</v>
@@ -6876,10 +6876,10 @@
         <v>2025.0</v>
       </c>
       <c r="C482" t="n" s="2">
-        <v>45693.0</v>
+        <v>45686.0</v>
       </c>
       <c r="D482" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="483">
@@ -6890,10 +6890,10 @@
         <v>2025.0</v>
       </c>
       <c r="C483" t="n" s="2">
-        <v>45700.0</v>
+        <v>45693.0</v>
       </c>
       <c r="D483" t="n">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="484">
@@ -6904,10 +6904,10 @@
         <v>2025.0</v>
       </c>
       <c r="C484" t="n" s="2">
-        <v>45707.0</v>
+        <v>45700.0</v>
       </c>
       <c r="D484" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="485">
@@ -6918,10 +6918,10 @@
         <v>2025.0</v>
       </c>
       <c r="C485" t="n" s="2">
-        <v>45714.0</v>
+        <v>45707.0</v>
       </c>
       <c r="D485" t="n">
-        <v>8.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="486">
@@ -6932,10 +6932,10 @@
         <v>2025.0</v>
       </c>
       <c r="C486" t="n" s="2">
-        <v>45721.0</v>
+        <v>45714.0</v>
       </c>
       <c r="D486" t="n">
-        <v>11.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="487">
@@ -6946,10 +6946,10 @@
         <v>2025.0</v>
       </c>
       <c r="C487" t="n" s="2">
-        <v>45728.0</v>
+        <v>45721.0</v>
       </c>
       <c r="D487" t="n">
-        <v>6.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="488">
@@ -6960,10 +6960,10 @@
         <v>2025.0</v>
       </c>
       <c r="C488" t="n" s="2">
-        <v>45735.0</v>
+        <v>45728.0</v>
       </c>
       <c r="D488" t="n">
-        <v>19.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="489">
@@ -6974,10 +6974,10 @@
         <v>2025.0</v>
       </c>
       <c r="C489" t="n" s="2">
-        <v>45742.0</v>
+        <v>45735.0</v>
       </c>
       <c r="D489" t="n">
-        <v>17.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="490">
@@ -6988,10 +6988,10 @@
         <v>2025.0</v>
       </c>
       <c r="C490" t="n" s="2">
-        <v>45749.0</v>
+        <v>45742.0</v>
       </c>
       <c r="D490" t="n">
-        <v>5.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="491">
@@ -7002,10 +7002,10 @@
         <v>2025.0</v>
       </c>
       <c r="C491" t="n" s="2">
-        <v>45756.0</v>
+        <v>45749.0</v>
       </c>
       <c r="D491" t="n">
-        <v>9.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="492">
@@ -7016,10 +7016,10 @@
         <v>2025.0</v>
       </c>
       <c r="C492" t="n" s="2">
-        <v>45763.0</v>
+        <v>45756.0</v>
       </c>
       <c r="D492" t="n">
-        <v>1.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="493">
@@ -7030,7 +7030,7 @@
         <v>2025.0</v>
       </c>
       <c r="C493" t="n" s="2">
-        <v>45770.0</v>
+        <v>45763.0</v>
       </c>
       <c r="D493" t="n">
         <v>1.0</v>
@@ -7044,10 +7044,10 @@
         <v>2025.0</v>
       </c>
       <c r="C494" t="n" s="2">
-        <v>45784.0</v>
+        <v>45770.0</v>
       </c>
       <c r="D494" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="495">
@@ -7058,10 +7058,10 @@
         <v>2025.0</v>
       </c>
       <c r="C495" t="n" s="2">
-        <v>45791.0</v>
+        <v>45784.0</v>
       </c>
       <c r="D495" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="496">
@@ -7072,10 +7072,10 @@
         <v>2025.0</v>
       </c>
       <c r="C496" t="n" s="2">
-        <v>45805.0</v>
+        <v>45791.0</v>
       </c>
       <c r="D496" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="497">
@@ -7086,10 +7086,10 @@
         <v>2025.0</v>
       </c>
       <c r="C497" t="n" s="2">
-        <v>45826.0</v>
+        <v>45805.0</v>
       </c>
       <c r="D497" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="498">
@@ -7100,7 +7100,7 @@
         <v>2025.0</v>
       </c>
       <c r="C498" t="n" s="2">
-        <v>45861.0</v>
+        <v>45826.0</v>
       </c>
       <c r="D498" t="n">
         <v>2.0</v>
@@ -7114,10 +7114,10 @@
         <v>2025.0</v>
       </c>
       <c r="C499" t="n" s="2">
-        <v>45868.0</v>
+        <v>45861.0</v>
       </c>
       <c r="D499" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="500">
@@ -7128,7 +7128,7 @@
         <v>2025.0</v>
       </c>
       <c r="C500" t="n" s="2">
-        <v>45889.0</v>
+        <v>45868.0</v>
       </c>
       <c r="D500" t="n">
         <v>1.0</v>
@@ -7142,7 +7142,7 @@
         <v>2025.0</v>
       </c>
       <c r="C501" t="n" s="2">
-        <v>45924.0</v>
+        <v>45889.0</v>
       </c>
       <c r="D501" t="n">
         <v>1.0</v>
@@ -7156,7 +7156,7 @@
         <v>2025.0</v>
       </c>
       <c r="C502" t="n" s="2">
-        <v>45945.0</v>
+        <v>45924.0</v>
       </c>
       <c r="D502" t="n">
         <v>1.0</v>
@@ -7170,10 +7170,10 @@
         <v>2025.0</v>
       </c>
       <c r="C503" t="n" s="2">
-        <v>45959.0</v>
+        <v>45945.0</v>
       </c>
       <c r="D503" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="504">
@@ -7184,7 +7184,7 @@
         <v>2025.0</v>
       </c>
       <c r="C504" t="n" s="2">
-        <v>46001.0</v>
+        <v>45959.0</v>
       </c>
       <c r="D504" t="n">
         <v>2.0</v>
@@ -7198,10 +7198,10 @@
         <v>2025.0</v>
       </c>
       <c r="C505" t="n" s="2">
-        <v>46008.0</v>
+        <v>46001.0</v>
       </c>
       <c r="D505" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="506">
@@ -7212,7 +7212,7 @@
         <v>2025.0</v>
       </c>
       <c r="C506" t="n" s="2">
-        <v>46022.0</v>
+        <v>46008.0</v>
       </c>
       <c r="D506" t="n">
         <v>1.0</v>
@@ -7223,10 +7223,10 @@
         <v>7</v>
       </c>
       <c r="B507" t="n">
-        <v>2026.0</v>
+        <v>2025.0</v>
       </c>
       <c r="C507" t="n" s="2">
-        <v>46030.0</v>
+        <v>46022.0</v>
       </c>
       <c r="D507" t="n">
         <v>1.0</v>
@@ -7240,7 +7240,7 @@
         <v>2026.0</v>
       </c>
       <c r="C508" t="n" s="2">
-        <v>46051.0</v>
+        <v>46030.0</v>
       </c>
       <c r="D508" t="n">
         <v>1.0</v>
@@ -7254,7 +7254,7 @@
         <v>2026.0</v>
       </c>
       <c r="C509" t="n" s="2">
-        <v>46058.0</v>
+        <v>46051.0</v>
       </c>
       <c r="D509" t="n">
         <v>1.0</v>
@@ -7268,24 +7268,24 @@
         <v>2026.0</v>
       </c>
       <c r="C510" t="n" s="2">
-        <v>46065.0</v>
+        <v>46058.0</v>
       </c>
       <c r="D510" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B511" t="n">
-        <v>2024.0</v>
+        <v>2026.0</v>
       </c>
       <c r="C511" t="n" s="2">
-        <v>45495.0</v>
+        <v>46065.0</v>
       </c>
       <c r="D511" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="512">
@@ -7296,10 +7296,10 @@
         <v>2024.0</v>
       </c>
       <c r="C512" t="n" s="2">
-        <v>45502.0</v>
+        <v>45495.0</v>
       </c>
       <c r="D512" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="513">
@@ -7307,13 +7307,13 @@
         <v>8</v>
       </c>
       <c r="B513" t="n">
-        <v>2025.0</v>
+        <v>2024.0</v>
       </c>
       <c r="C513" t="n" s="2">
-        <v>45665.0</v>
+        <v>45502.0</v>
       </c>
       <c r="D513" t="n">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="514">
@@ -7324,10 +7324,10 @@
         <v>2025.0</v>
       </c>
       <c r="C514" t="n" s="2">
-        <v>45672.0</v>
+        <v>45665.0</v>
       </c>
       <c r="D514" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="515">
@@ -7338,10 +7338,10 @@
         <v>2025.0</v>
       </c>
       <c r="C515" t="n" s="2">
-        <v>45679.0</v>
+        <v>45672.0</v>
       </c>
       <c r="D515" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="516">
@@ -7352,10 +7352,10 @@
         <v>2025.0</v>
       </c>
       <c r="C516" t="n" s="2">
-        <v>45686.0</v>
+        <v>45679.0</v>
       </c>
       <c r="D516" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="517">
@@ -7366,10 +7366,10 @@
         <v>2025.0</v>
       </c>
       <c r="C517" t="n" s="2">
-        <v>45693.0</v>
+        <v>45686.0</v>
       </c>
       <c r="D517" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="518">
@@ -7380,10 +7380,10 @@
         <v>2025.0</v>
       </c>
       <c r="C518" t="n" s="2">
-        <v>45700.0</v>
+        <v>45693.0</v>
       </c>
       <c r="D518" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="519">
@@ -7394,10 +7394,10 @@
         <v>2025.0</v>
       </c>
       <c r="C519" t="n" s="2">
-        <v>45707.0</v>
+        <v>45700.0</v>
       </c>
       <c r="D519" t="n">
-        <v>7.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="520">
@@ -7408,10 +7408,10 @@
         <v>2025.0</v>
       </c>
       <c r="C520" t="n" s="2">
-        <v>45714.0</v>
+        <v>45707.0</v>
       </c>
       <c r="D520" t="n">
-        <v>3.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="521">
@@ -7422,10 +7422,10 @@
         <v>2025.0</v>
       </c>
       <c r="C521" t="n" s="2">
-        <v>45721.0</v>
+        <v>45714.0</v>
       </c>
       <c r="D521" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="522">
@@ -7436,10 +7436,10 @@
         <v>2025.0</v>
       </c>
       <c r="C522" t="n" s="2">
-        <v>45728.0</v>
+        <v>45721.0</v>
       </c>
       <c r="D522" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="523">
@@ -7450,7 +7450,7 @@
         <v>2025.0</v>
       </c>
       <c r="C523" t="n" s="2">
-        <v>45742.0</v>
+        <v>45728.0</v>
       </c>
       <c r="D523" t="n">
         <v>1.0</v>
@@ -7464,7 +7464,7 @@
         <v>2025.0</v>
       </c>
       <c r="C524" t="n" s="2">
-        <v>45749.0</v>
+        <v>45742.0</v>
       </c>
       <c r="D524" t="n">
         <v>1.0</v>
@@ -7478,7 +7478,7 @@
         <v>2025.0</v>
       </c>
       <c r="C525" t="n" s="2">
-        <v>45763.0</v>
+        <v>45749.0</v>
       </c>
       <c r="D525" t="n">
         <v>1.0</v>
@@ -7492,10 +7492,10 @@
         <v>2025.0</v>
       </c>
       <c r="C526" t="n" s="2">
-        <v>45777.0</v>
+        <v>45763.0</v>
       </c>
       <c r="D526" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="527">
@@ -7506,10 +7506,10 @@
         <v>2025.0</v>
       </c>
       <c r="C527" t="n" s="2">
-        <v>45784.0</v>
+        <v>45777.0</v>
       </c>
       <c r="D527" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="528">
@@ -7520,7 +7520,7 @@
         <v>2025.0</v>
       </c>
       <c r="C528" t="n" s="2">
-        <v>45798.0</v>
+        <v>45784.0</v>
       </c>
       <c r="D528" t="n">
         <v>1.0</v>
@@ -7534,7 +7534,7 @@
         <v>2025.0</v>
       </c>
       <c r="C529" t="n" s="2">
-        <v>45805.0</v>
+        <v>45798.0</v>
       </c>
       <c r="D529" t="n">
         <v>1.0</v>
@@ -7548,10 +7548,10 @@
         <v>2025.0</v>
       </c>
       <c r="C530" t="n" s="2">
-        <v>45812.0</v>
+        <v>45805.0</v>
       </c>
       <c r="D530" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="531">
@@ -7562,7 +7562,7 @@
         <v>2025.0</v>
       </c>
       <c r="C531" t="n" s="2">
-        <v>45819.0</v>
+        <v>45812.0</v>
       </c>
       <c r="D531" t="n">
         <v>2.0</v>
@@ -7576,7 +7576,7 @@
         <v>2025.0</v>
       </c>
       <c r="C532" t="n" s="2">
-        <v>45833.0</v>
+        <v>45819.0</v>
       </c>
       <c r="D532" t="n">
         <v>2.0</v>
@@ -7590,10 +7590,10 @@
         <v>2025.0</v>
       </c>
       <c r="C533" t="n" s="2">
-        <v>45847.0</v>
+        <v>45833.0</v>
       </c>
       <c r="D533" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="534">
@@ -7604,10 +7604,10 @@
         <v>2025.0</v>
       </c>
       <c r="C534" t="n" s="2">
-        <v>45854.0</v>
+        <v>45847.0</v>
       </c>
       <c r="D534" t="n">
-        <v>8.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="535">
@@ -7618,10 +7618,10 @@
         <v>2025.0</v>
       </c>
       <c r="C535" t="n" s="2">
-        <v>45861.0</v>
+        <v>45854.0</v>
       </c>
       <c r="D535" t="n">
-        <v>12.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="536">
@@ -7632,10 +7632,10 @@
         <v>2025.0</v>
       </c>
       <c r="C536" t="n" s="2">
-        <v>45868.0</v>
+        <v>45861.0</v>
       </c>
       <c r="D536" t="n">
-        <v>6.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="537">
@@ -7646,10 +7646,10 @@
         <v>2025.0</v>
       </c>
       <c r="C537" t="n" s="2">
-        <v>45875.0</v>
+        <v>45868.0</v>
       </c>
       <c r="D537" t="n">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="538">
@@ -7660,7 +7660,7 @@
         <v>2025.0</v>
       </c>
       <c r="C538" t="n" s="2">
-        <v>45896.0</v>
+        <v>45875.0</v>
       </c>
       <c r="D538" t="n">
         <v>1.0</v>
@@ -7674,7 +7674,7 @@
         <v>2025.0</v>
       </c>
       <c r="C539" t="n" s="2">
-        <v>45903.0</v>
+        <v>45896.0</v>
       </c>
       <c r="D539" t="n">
         <v>1.0</v>
@@ -7688,7 +7688,7 @@
         <v>2025.0</v>
       </c>
       <c r="C540" t="n" s="2">
-        <v>45931.0</v>
+        <v>45903.0</v>
       </c>
       <c r="D540" t="n">
         <v>1.0</v>
@@ -7702,10 +7702,10 @@
         <v>2025.0</v>
       </c>
       <c r="C541" t="n" s="2">
-        <v>45938.0</v>
+        <v>45931.0</v>
       </c>
       <c r="D541" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="542">
@@ -7716,10 +7716,10 @@
         <v>2025.0</v>
       </c>
       <c r="C542" t="n" s="2">
-        <v>45945.0</v>
+        <v>45938.0</v>
       </c>
       <c r="D542" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="543">
@@ -7730,7 +7730,7 @@
         <v>2025.0</v>
       </c>
       <c r="C543" t="n" s="2">
-        <v>45966.0</v>
+        <v>45945.0</v>
       </c>
       <c r="D543" t="n">
         <v>2.0</v>
@@ -7744,10 +7744,10 @@
         <v>2025.0</v>
       </c>
       <c r="C544" t="n" s="2">
-        <v>45973.0</v>
+        <v>45966.0</v>
       </c>
       <c r="D544" t="n">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="545">
@@ -7758,10 +7758,10 @@
         <v>2025.0</v>
       </c>
       <c r="C545" t="n" s="2">
-        <v>45980.0</v>
+        <v>45973.0</v>
       </c>
       <c r="D545" t="n">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="546">
@@ -7772,10 +7772,10 @@
         <v>2025.0</v>
       </c>
       <c r="C546" t="n" s="2">
-        <v>45987.0</v>
+        <v>45980.0</v>
       </c>
       <c r="D546" t="n">
-        <v>20.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="547">
@@ -7786,10 +7786,10 @@
         <v>2025.0</v>
       </c>
       <c r="C547" t="n" s="2">
-        <v>45994.0</v>
+        <v>45987.0</v>
       </c>
       <c r="D547" t="n">
-        <v>5.0</v>
+        <v>20.0</v>
       </c>
     </row>
     <row r="548">
@@ -7800,10 +7800,10 @@
         <v>2025.0</v>
       </c>
       <c r="C548" t="n" s="2">
-        <v>46001.0</v>
+        <v>45994.0</v>
       </c>
       <c r="D548" t="n">
-        <v>8.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="549">
@@ -7814,10 +7814,10 @@
         <v>2025.0</v>
       </c>
       <c r="C549" t="n" s="2">
-        <v>46008.0</v>
+        <v>46001.0</v>
       </c>
       <c r="D549" t="n">
-        <v>24.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="550">
@@ -7828,10 +7828,10 @@
         <v>2025.0</v>
       </c>
       <c r="C550" t="n" s="2">
-        <v>46015.0</v>
+        <v>46008.0</v>
       </c>
       <c r="D550" t="n">
-        <v>13.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="551">
@@ -7842,10 +7842,10 @@
         <v>2025.0</v>
       </c>
       <c r="C551" t="n" s="2">
-        <v>46022.0</v>
+        <v>46015.0</v>
       </c>
       <c r="D551" t="n">
-        <v>8.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="552">
@@ -7856,10 +7856,10 @@
         <v>2025.0</v>
       </c>
       <c r="C552" t="n" s="2">
-        <v>46029.0</v>
+        <v>46022.0</v>
       </c>
       <c r="D552" t="n">
-        <v>3.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="553">
@@ -7867,13 +7867,13 @@
         <v>8</v>
       </c>
       <c r="B553" t="n">
-        <v>2026.0</v>
+        <v>2025.0</v>
       </c>
       <c r="C553" t="n" s="2">
-        <v>46030.0</v>
+        <v>46029.0</v>
       </c>
       <c r="D553" t="n">
-        <v>24.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="554">
@@ -7884,10 +7884,10 @@
         <v>2026.0</v>
       </c>
       <c r="C554" t="n" s="2">
-        <v>46037.0</v>
+        <v>46030.0</v>
       </c>
       <c r="D554" t="n">
-        <v>22.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="555">
@@ -7898,10 +7898,10 @@
         <v>2026.0</v>
       </c>
       <c r="C555" t="n" s="2">
-        <v>46044.0</v>
+        <v>46037.0</v>
       </c>
       <c r="D555" t="n">
-        <v>27.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="556">
@@ -7912,10 +7912,10 @@
         <v>2026.0</v>
       </c>
       <c r="C556" t="n" s="2">
-        <v>46051.0</v>
+        <v>46044.0</v>
       </c>
       <c r="D556" t="n">
-        <v>18.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="557">
@@ -7926,10 +7926,10 @@
         <v>2026.0</v>
       </c>
       <c r="C557" t="n" s="2">
-        <v>46058.0</v>
+        <v>46051.0</v>
       </c>
       <c r="D557" t="n">
-        <v>25.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="558">
@@ -7940,10 +7940,10 @@
         <v>2026.0</v>
       </c>
       <c r="C558" t="n" s="2">
-        <v>46065.0</v>
+        <v>46058.0</v>
       </c>
       <c r="D558" t="n">
-        <v>22.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="559">
@@ -7954,10 +7954,10 @@
         <v>2026.0</v>
       </c>
       <c r="C559" t="n" s="2">
-        <v>46072.0</v>
+        <v>46065.0</v>
       </c>
       <c r="D559" t="n">
-        <v>13.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="560">
@@ -7968,10 +7968,10 @@
         <v>2026.0</v>
       </c>
       <c r="C560" t="n" s="2">
-        <v>46079.0</v>
+        <v>46072.0</v>
       </c>
       <c r="D560" t="n">
-        <v>24.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="561">
@@ -7982,10 +7982,10 @@
         <v>2026.0</v>
       </c>
       <c r="C561" t="n" s="2">
-        <v>46086.0</v>
+        <v>46079.0</v>
       </c>
       <c r="D561" t="n">
-        <v>26.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="562">
@@ -7996,10 +7996,10 @@
         <v>2026.0</v>
       </c>
       <c r="C562" t="n" s="2">
-        <v>46093.0</v>
+        <v>46086.0</v>
       </c>
       <c r="D562" t="n">
-        <v>33.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="563">
@@ -8010,10 +8010,10 @@
         <v>2026.0</v>
       </c>
       <c r="C563" t="n" s="2">
-        <v>46100.0</v>
+        <v>46093.0</v>
       </c>
       <c r="D563" t="n">
-        <v>25.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="564">
@@ -8024,10 +8024,10 @@
         <v>2026.0</v>
       </c>
       <c r="C564" t="n" s="2">
-        <v>46107.0</v>
+        <v>46100.0</v>
       </c>
       <c r="D564" t="n">
-        <v>31.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="565">
@@ -8038,9 +8038,23 @@
         <v>2026.0</v>
       </c>
       <c r="C565" t="n" s="2">
+        <v>46107.0</v>
+      </c>
+      <c r="D565" t="n">
+        <v>31.0</v>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="s">
+        <v>8</v>
+      </c>
+      <c r="B566" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C566" t="n" s="2">
         <v>46114.0</v>
       </c>
-      <c r="D565" t="n">
+      <c r="D566" t="n">
         <v>7.0</v>
       </c>
     </row>
@@ -8091,7 +8105,7 @@
         <v>13</v>
       </c>
       <c r="B5" t="n">
-        <v>2061.0</v>
+        <v>2063.0</v>
       </c>
     </row>
   </sheetData>
@@ -8156,7 +8170,7 @@
         <v>21</v>
       </c>
       <c r="C5" t="n">
-        <v>410.0</v>
+        <v>411.0</v>
       </c>
     </row>
     <row r="6">
@@ -8255,7 +8269,7 @@
         <v>19</v>
       </c>
       <c r="C14" t="n">
-        <v>378.0</v>
+        <v>379.0</v>
       </c>
     </row>
     <row r="15">

--- a/Download/Focus_Positivi_ZR.xlsx
+++ b/Download/Focus_Positivi_ZR.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="610" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="612" uniqueCount="23">
   <si>
     <t>NOME_REGIONE</t>
   </si>
@@ -1573,7 +1573,7 @@
         <v>46121.0</v>
       </c>
       <c r="D103" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="104">
@@ -4182,16 +4182,16 @@
     </row>
     <row r="290">
       <c r="A290" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B290" t="n">
-        <v>2023.0</v>
+        <v>2026.0</v>
       </c>
       <c r="C290" t="n" s="2">
-        <v>45095.0</v>
+        <v>46121.0</v>
       </c>
       <c r="D290" t="n">
-        <v>1.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="291">
@@ -4202,7 +4202,7 @@
         <v>2023.0</v>
       </c>
       <c r="C291" t="n" s="2">
-        <v>45102.0</v>
+        <v>45095.0</v>
       </c>
       <c r="D291" t="n">
         <v>1.0</v>
@@ -4216,7 +4216,7 @@
         <v>2023.0</v>
       </c>
       <c r="C292" t="n" s="2">
-        <v>45158.0</v>
+        <v>45102.0</v>
       </c>
       <c r="D292" t="n">
         <v>1.0</v>
@@ -4230,10 +4230,10 @@
         <v>2023.0</v>
       </c>
       <c r="C293" t="n" s="2">
-        <v>45207.0</v>
+        <v>45158.0</v>
       </c>
       <c r="D293" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="294">
@@ -4244,7 +4244,7 @@
         <v>2023.0</v>
       </c>
       <c r="C294" t="n" s="2">
-        <v>45214.0</v>
+        <v>45207.0</v>
       </c>
       <c r="D294" t="n">
         <v>3.0</v>
@@ -4258,10 +4258,10 @@
         <v>2023.0</v>
       </c>
       <c r="C295" t="n" s="2">
-        <v>45221.0</v>
+        <v>45214.0</v>
       </c>
       <c r="D295" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="296">
@@ -4272,7 +4272,7 @@
         <v>2023.0</v>
       </c>
       <c r="C296" t="n" s="2">
-        <v>45249.0</v>
+        <v>45221.0</v>
       </c>
       <c r="D296" t="n">
         <v>1.0</v>
@@ -4286,10 +4286,10 @@
         <v>2023.0</v>
       </c>
       <c r="C297" t="n" s="2">
-        <v>45256.0</v>
+        <v>45249.0</v>
       </c>
       <c r="D297" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="298">
@@ -4300,10 +4300,10 @@
         <v>2023.0</v>
       </c>
       <c r="C298" t="n" s="2">
-        <v>45263.0</v>
+        <v>45256.0</v>
       </c>
       <c r="D298" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="299">
@@ -4314,10 +4314,10 @@
         <v>2023.0</v>
       </c>
       <c r="C299" t="n" s="2">
-        <v>45270.0</v>
+        <v>45263.0</v>
       </c>
       <c r="D299" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="300">
@@ -4328,10 +4328,10 @@
         <v>2023.0</v>
       </c>
       <c r="C300" t="n" s="2">
-        <v>45277.0</v>
+        <v>45270.0</v>
       </c>
       <c r="D300" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="301">
@@ -4342,10 +4342,10 @@
         <v>2023.0</v>
       </c>
       <c r="C301" t="n" s="2">
-        <v>45284.0</v>
+        <v>45277.0</v>
       </c>
       <c r="D301" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="302">
@@ -4356,10 +4356,10 @@
         <v>2023.0</v>
       </c>
       <c r="C302" t="n" s="2">
-        <v>45291.0</v>
+        <v>45284.0</v>
       </c>
       <c r="D302" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="303">
@@ -4367,13 +4367,13 @@
         <v>6</v>
       </c>
       <c r="B303" t="n">
-        <v>2024.0</v>
+        <v>2023.0</v>
       </c>
       <c r="C303" t="n" s="2">
-        <v>45306.0</v>
+        <v>45291.0</v>
       </c>
       <c r="D303" t="n">
-        <v>7.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="304">
@@ -4384,10 +4384,10 @@
         <v>2024.0</v>
       </c>
       <c r="C304" t="n" s="2">
-        <v>45313.0</v>
+        <v>45306.0</v>
       </c>
       <c r="D304" t="n">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="305">
@@ -4398,10 +4398,10 @@
         <v>2024.0</v>
       </c>
       <c r="C305" t="n" s="2">
-        <v>45320.0</v>
+        <v>45313.0</v>
       </c>
       <c r="D305" t="n">
-        <v>19.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="306">
@@ -4412,10 +4412,10 @@
         <v>2024.0</v>
       </c>
       <c r="C306" t="n" s="2">
-        <v>45327.0</v>
+        <v>45320.0</v>
       </c>
       <c r="D306" t="n">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="307">
@@ -4426,10 +4426,10 @@
         <v>2024.0</v>
       </c>
       <c r="C307" t="n" s="2">
-        <v>45334.0</v>
+        <v>45327.0</v>
       </c>
       <c r="D307" t="n">
-        <v>9.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="308">
@@ -4440,10 +4440,10 @@
         <v>2024.0</v>
       </c>
       <c r="C308" t="n" s="2">
-        <v>45341.0</v>
+        <v>45334.0</v>
       </c>
       <c r="D308" t="n">
-        <v>12.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="309">
@@ -4454,7 +4454,7 @@
         <v>2024.0</v>
       </c>
       <c r="C309" t="n" s="2">
-        <v>45348.0</v>
+        <v>45341.0</v>
       </c>
       <c r="D309" t="n">
         <v>12.0</v>
@@ -4468,10 +4468,10 @@
         <v>2024.0</v>
       </c>
       <c r="C310" t="n" s="2">
-        <v>45355.0</v>
+        <v>45348.0</v>
       </c>
       <c r="D310" t="n">
-        <v>10.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="311">
@@ -4482,10 +4482,10 @@
         <v>2024.0</v>
       </c>
       <c r="C311" t="n" s="2">
-        <v>45362.0</v>
+        <v>45355.0</v>
       </c>
       <c r="D311" t="n">
-        <v>12.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="312">
@@ -4496,10 +4496,10 @@
         <v>2024.0</v>
       </c>
       <c r="C312" t="n" s="2">
-        <v>45369.0</v>
+        <v>45362.0</v>
       </c>
       <c r="D312" t="n">
-        <v>13.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="313">
@@ -4510,10 +4510,10 @@
         <v>2024.0</v>
       </c>
       <c r="C313" t="n" s="2">
-        <v>45376.0</v>
+        <v>45369.0</v>
       </c>
       <c r="D313" t="n">
-        <v>18.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="314">
@@ -4524,10 +4524,10 @@
         <v>2024.0</v>
       </c>
       <c r="C314" t="n" s="2">
-        <v>45383.0</v>
+        <v>45376.0</v>
       </c>
       <c r="D314" t="n">
-        <v>12.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="315">
@@ -4538,10 +4538,10 @@
         <v>2024.0</v>
       </c>
       <c r="C315" t="n" s="2">
-        <v>45390.0</v>
+        <v>45383.0</v>
       </c>
       <c r="D315" t="n">
-        <v>6.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="316">
@@ -4552,10 +4552,10 @@
         <v>2024.0</v>
       </c>
       <c r="C316" t="n" s="2">
-        <v>45397.0</v>
+        <v>45390.0</v>
       </c>
       <c r="D316" t="n">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="317">
@@ -4566,10 +4566,10 @@
         <v>2024.0</v>
       </c>
       <c r="C317" t="n" s="2">
-        <v>45404.0</v>
+        <v>45397.0</v>
       </c>
       <c r="D317" t="n">
-        <v>3.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="318">
@@ -4580,10 +4580,10 @@
         <v>2024.0</v>
       </c>
       <c r="C318" t="n" s="2">
-        <v>45411.0</v>
+        <v>45404.0</v>
       </c>
       <c r="D318" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="319">
@@ -4594,10 +4594,10 @@
         <v>2024.0</v>
       </c>
       <c r="C319" t="n" s="2">
-        <v>45418.0</v>
+        <v>45411.0</v>
       </c>
       <c r="D319" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="320">
@@ -4608,10 +4608,10 @@
         <v>2024.0</v>
       </c>
       <c r="C320" t="n" s="2">
-        <v>45425.0</v>
+        <v>45418.0</v>
       </c>
       <c r="D320" t="n">
-        <v>9.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="321">
@@ -4622,10 +4622,10 @@
         <v>2024.0</v>
       </c>
       <c r="C321" t="n" s="2">
-        <v>45432.0</v>
+        <v>45425.0</v>
       </c>
       <c r="D321" t="n">
-        <v>6.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="322">
@@ -4636,7 +4636,7 @@
         <v>2024.0</v>
       </c>
       <c r="C322" t="n" s="2">
-        <v>45439.0</v>
+        <v>45432.0</v>
       </c>
       <c r="D322" t="n">
         <v>6.0</v>
@@ -4650,10 +4650,10 @@
         <v>2024.0</v>
       </c>
       <c r="C323" t="n" s="2">
-        <v>45446.0</v>
+        <v>45439.0</v>
       </c>
       <c r="D323" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="324">
@@ -4664,10 +4664,10 @@
         <v>2024.0</v>
       </c>
       <c r="C324" t="n" s="2">
-        <v>45453.0</v>
+        <v>45446.0</v>
       </c>
       <c r="D324" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="325">
@@ -4678,7 +4678,7 @@
         <v>2024.0</v>
       </c>
       <c r="C325" t="n" s="2">
-        <v>45460.0</v>
+        <v>45453.0</v>
       </c>
       <c r="D325" t="n">
         <v>4.0</v>
@@ -4692,7 +4692,7 @@
         <v>2024.0</v>
       </c>
       <c r="C326" t="n" s="2">
-        <v>45467.0</v>
+        <v>45460.0</v>
       </c>
       <c r="D326" t="n">
         <v>4.0</v>
@@ -4706,10 +4706,10 @@
         <v>2024.0</v>
       </c>
       <c r="C327" t="n" s="2">
-        <v>45474.0</v>
+        <v>45467.0</v>
       </c>
       <c r="D327" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="328">
@@ -4720,10 +4720,10 @@
         <v>2024.0</v>
       </c>
       <c r="C328" t="n" s="2">
-        <v>45481.0</v>
+        <v>45474.0</v>
       </c>
       <c r="D328" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="329">
@@ -4734,10 +4734,10 @@
         <v>2024.0</v>
       </c>
       <c r="C329" t="n" s="2">
-        <v>45488.0</v>
+        <v>45481.0</v>
       </c>
       <c r="D329" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="330">
@@ -4748,10 +4748,10 @@
         <v>2024.0</v>
       </c>
       <c r="C330" t="n" s="2">
-        <v>45495.0</v>
+        <v>45488.0</v>
       </c>
       <c r="D330" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="331">
@@ -4762,10 +4762,10 @@
         <v>2024.0</v>
       </c>
       <c r="C331" t="n" s="2">
-        <v>45502.0</v>
+        <v>45495.0</v>
       </c>
       <c r="D331" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="332">
@@ -4776,10 +4776,10 @@
         <v>2024.0</v>
       </c>
       <c r="C332" t="n" s="2">
-        <v>45509.0</v>
+        <v>45502.0</v>
       </c>
       <c r="D332" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="333">
@@ -4790,7 +4790,7 @@
         <v>2024.0</v>
       </c>
       <c r="C333" t="n" s="2">
-        <v>45523.0</v>
+        <v>45509.0</v>
       </c>
       <c r="D333" t="n">
         <v>1.0</v>
@@ -4804,7 +4804,7 @@
         <v>2024.0</v>
       </c>
       <c r="C334" t="n" s="2">
-        <v>45551.0</v>
+        <v>45523.0</v>
       </c>
       <c r="D334" t="n">
         <v>1.0</v>
@@ -4818,7 +4818,7 @@
         <v>2024.0</v>
       </c>
       <c r="C335" t="n" s="2">
-        <v>45558.0</v>
+        <v>45551.0</v>
       </c>
       <c r="D335" t="n">
         <v>1.0</v>
@@ -4832,10 +4832,10 @@
         <v>2024.0</v>
       </c>
       <c r="C336" t="n" s="2">
-        <v>45572.0</v>
+        <v>45558.0</v>
       </c>
       <c r="D336" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="337">
@@ -4846,10 +4846,10 @@
         <v>2024.0</v>
       </c>
       <c r="C337" t="n" s="2">
-        <v>45593.0</v>
+        <v>45572.0</v>
       </c>
       <c r="D337" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="338">
@@ -4860,10 +4860,10 @@
         <v>2024.0</v>
       </c>
       <c r="C338" t="n" s="2">
-        <v>45614.0</v>
+        <v>45593.0</v>
       </c>
       <c r="D338" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="339">
@@ -4874,10 +4874,10 @@
         <v>2024.0</v>
       </c>
       <c r="C339" t="n" s="2">
-        <v>45621.0</v>
+        <v>45614.0</v>
       </c>
       <c r="D339" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="340">
@@ -4888,7 +4888,7 @@
         <v>2024.0</v>
       </c>
       <c r="C340" t="n" s="2">
-        <v>45635.0</v>
+        <v>45621.0</v>
       </c>
       <c r="D340" t="n">
         <v>1.0</v>
@@ -4902,7 +4902,7 @@
         <v>2024.0</v>
       </c>
       <c r="C341" t="n" s="2">
-        <v>45649.0</v>
+        <v>45635.0</v>
       </c>
       <c r="D341" t="n">
         <v>1.0</v>
@@ -4913,13 +4913,13 @@
         <v>6</v>
       </c>
       <c r="B342" t="n">
-        <v>2025.0</v>
+        <v>2024.0</v>
       </c>
       <c r="C342" t="n" s="2">
-        <v>45665.0</v>
+        <v>45649.0</v>
       </c>
       <c r="D342" t="n">
-        <v>9.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="343">
@@ -4930,10 +4930,10 @@
         <v>2025.0</v>
       </c>
       <c r="C343" t="n" s="2">
-        <v>45672.0</v>
+        <v>45665.0</v>
       </c>
       <c r="D343" t="n">
-        <v>3.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="344">
@@ -4944,10 +4944,10 @@
         <v>2025.0</v>
       </c>
       <c r="C344" t="n" s="2">
-        <v>45679.0</v>
+        <v>45672.0</v>
       </c>
       <c r="D344" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="345">
@@ -4958,10 +4958,10 @@
         <v>2025.0</v>
       </c>
       <c r="C345" t="n" s="2">
-        <v>45686.0</v>
+        <v>45679.0</v>
       </c>
       <c r="D345" t="n">
-        <v>8.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="346">
@@ -4972,10 +4972,10 @@
         <v>2025.0</v>
       </c>
       <c r="C346" t="n" s="2">
-        <v>45693.0</v>
+        <v>45686.0</v>
       </c>
       <c r="D346" t="n">
-        <v>3.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="347">
@@ -4986,10 +4986,10 @@
         <v>2025.0</v>
       </c>
       <c r="C347" t="n" s="2">
-        <v>45700.0</v>
+        <v>45693.0</v>
       </c>
       <c r="D347" t="n">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="348">
@@ -5000,10 +5000,10 @@
         <v>2025.0</v>
       </c>
       <c r="C348" t="n" s="2">
-        <v>45707.0</v>
+        <v>45700.0</v>
       </c>
       <c r="D348" t="n">
-        <v>8.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="349">
@@ -5014,10 +5014,10 @@
         <v>2025.0</v>
       </c>
       <c r="C349" t="n" s="2">
-        <v>45714.0</v>
+        <v>45707.0</v>
       </c>
       <c r="D349" t="n">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="350">
@@ -5028,10 +5028,10 @@
         <v>2025.0</v>
       </c>
       <c r="C350" t="n" s="2">
-        <v>45721.0</v>
+        <v>45714.0</v>
       </c>
       <c r="D350" t="n">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="351">
@@ -5042,10 +5042,10 @@
         <v>2025.0</v>
       </c>
       <c r="C351" t="n" s="2">
-        <v>45728.0</v>
+        <v>45721.0</v>
       </c>
       <c r="D351" t="n">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="352">
@@ -5056,10 +5056,10 @@
         <v>2025.0</v>
       </c>
       <c r="C352" t="n" s="2">
-        <v>45735.0</v>
+        <v>45728.0</v>
       </c>
       <c r="D352" t="n">
-        <v>4.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="353">
@@ -5070,10 +5070,10 @@
         <v>2025.0</v>
       </c>
       <c r="C353" t="n" s="2">
-        <v>45742.0</v>
+        <v>45735.0</v>
       </c>
       <c r="D353" t="n">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="354">
@@ -5084,10 +5084,10 @@
         <v>2025.0</v>
       </c>
       <c r="C354" t="n" s="2">
-        <v>45749.0</v>
+        <v>45742.0</v>
       </c>
       <c r="D354" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="355">
@@ -5098,10 +5098,10 @@
         <v>2025.0</v>
       </c>
       <c r="C355" t="n" s="2">
-        <v>45756.0</v>
+        <v>45749.0</v>
       </c>
       <c r="D355" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="356">
@@ -5112,10 +5112,10 @@
         <v>2025.0</v>
       </c>
       <c r="C356" t="n" s="2">
-        <v>45763.0</v>
+        <v>45756.0</v>
       </c>
       <c r="D356" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="357">
@@ -5126,7 +5126,7 @@
         <v>2025.0</v>
       </c>
       <c r="C357" t="n" s="2">
-        <v>45770.0</v>
+        <v>45763.0</v>
       </c>
       <c r="D357" t="n">
         <v>4.0</v>
@@ -5140,10 +5140,10 @@
         <v>2025.0</v>
       </c>
       <c r="C358" t="n" s="2">
-        <v>45777.0</v>
+        <v>45770.0</v>
       </c>
       <c r="D358" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="359">
@@ -5154,7 +5154,7 @@
         <v>2025.0</v>
       </c>
       <c r="C359" t="n" s="2">
-        <v>45784.0</v>
+        <v>45777.0</v>
       </c>
       <c r="D359" t="n">
         <v>1.0</v>
@@ -5168,7 +5168,7 @@
         <v>2025.0</v>
       </c>
       <c r="C360" t="n" s="2">
-        <v>45791.0</v>
+        <v>45784.0</v>
       </c>
       <c r="D360" t="n">
         <v>1.0</v>
@@ -5182,7 +5182,7 @@
         <v>2025.0</v>
       </c>
       <c r="C361" t="n" s="2">
-        <v>45840.0</v>
+        <v>45791.0</v>
       </c>
       <c r="D361" t="n">
         <v>1.0</v>
@@ -5196,7 +5196,7 @@
         <v>2025.0</v>
       </c>
       <c r="C362" t="n" s="2">
-        <v>46001.0</v>
+        <v>45840.0</v>
       </c>
       <c r="D362" t="n">
         <v>1.0</v>
@@ -5207,10 +5207,10 @@
         <v>6</v>
       </c>
       <c r="B363" t="n">
-        <v>2026.0</v>
+        <v>2025.0</v>
       </c>
       <c r="C363" t="n" s="2">
-        <v>46037.0</v>
+        <v>46001.0</v>
       </c>
       <c r="D363" t="n">
         <v>1.0</v>
@@ -5218,13 +5218,13 @@
     </row>
     <row r="364">
       <c r="A364" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B364" t="n">
-        <v>2021.0</v>
+        <v>2026.0</v>
       </c>
       <c r="C364" t="n" s="2">
-        <v>44561.0</v>
+        <v>46037.0</v>
       </c>
       <c r="D364" t="n">
         <v>1.0</v>
@@ -5235,10 +5235,10 @@
         <v>7</v>
       </c>
       <c r="B365" t="n">
-        <v>2022.0</v>
+        <v>2021.0</v>
       </c>
       <c r="C365" t="n" s="2">
-        <v>44569.0</v>
+        <v>44561.0</v>
       </c>
       <c r="D365" t="n">
         <v>1.0</v>
@@ -5252,10 +5252,10 @@
         <v>2022.0</v>
       </c>
       <c r="C366" t="n" s="2">
-        <v>44576.0</v>
+        <v>44569.0</v>
       </c>
       <c r="D366" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="367">
@@ -5266,10 +5266,10 @@
         <v>2022.0</v>
       </c>
       <c r="C367" t="n" s="2">
-        <v>44583.0</v>
+        <v>44576.0</v>
       </c>
       <c r="D367" t="n">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="368">
@@ -5280,10 +5280,10 @@
         <v>2022.0</v>
       </c>
       <c r="C368" t="n" s="2">
-        <v>44590.0</v>
+        <v>44583.0</v>
       </c>
       <c r="D368" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="369">
@@ -5294,10 +5294,10 @@
         <v>2022.0</v>
       </c>
       <c r="C369" t="n" s="2">
-        <v>44604.0</v>
+        <v>44590.0</v>
       </c>
       <c r="D369" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="370">
@@ -5308,7 +5308,7 @@
         <v>2022.0</v>
       </c>
       <c r="C370" t="n" s="2">
-        <v>44611.0</v>
+        <v>44604.0</v>
       </c>
       <c r="D370" t="n">
         <v>3.0</v>
@@ -5322,10 +5322,10 @@
         <v>2022.0</v>
       </c>
       <c r="C371" t="n" s="2">
-        <v>44618.0</v>
+        <v>44611.0</v>
       </c>
       <c r="D371" t="n">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="372">
@@ -5336,7 +5336,7 @@
         <v>2022.0</v>
       </c>
       <c r="C372" t="n" s="2">
-        <v>44625.0</v>
+        <v>44618.0</v>
       </c>
       <c r="D372" t="n">
         <v>5.0</v>
@@ -5350,10 +5350,10 @@
         <v>2022.0</v>
       </c>
       <c r="C373" t="n" s="2">
-        <v>44632.0</v>
+        <v>44625.0</v>
       </c>
       <c r="D373" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="374">
@@ -5364,10 +5364,10 @@
         <v>2022.0</v>
       </c>
       <c r="C374" t="n" s="2">
-        <v>44639.0</v>
+        <v>44632.0</v>
       </c>
       <c r="D374" t="n">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="375">
@@ -5378,10 +5378,10 @@
         <v>2022.0</v>
       </c>
       <c r="C375" t="n" s="2">
-        <v>44646.0</v>
+        <v>44639.0</v>
       </c>
       <c r="D375" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="376">
@@ -5392,10 +5392,10 @@
         <v>2022.0</v>
       </c>
       <c r="C376" t="n" s="2">
-        <v>44653.0</v>
+        <v>44646.0</v>
       </c>
       <c r="D376" t="n">
-        <v>9.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="377">
@@ -5406,10 +5406,10 @@
         <v>2022.0</v>
       </c>
       <c r="C377" t="n" s="2">
-        <v>44660.0</v>
+        <v>44653.0</v>
       </c>
       <c r="D377" t="n">
-        <v>6.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="378">
@@ -5420,10 +5420,10 @@
         <v>2022.0</v>
       </c>
       <c r="C378" t="n" s="2">
-        <v>44667.0</v>
+        <v>44660.0</v>
       </c>
       <c r="D378" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="379">
@@ -5434,10 +5434,10 @@
         <v>2022.0</v>
       </c>
       <c r="C379" t="n" s="2">
-        <v>44674.0</v>
+        <v>44667.0</v>
       </c>
       <c r="D379" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="380">
@@ -5448,10 +5448,10 @@
         <v>2022.0</v>
       </c>
       <c r="C380" t="n" s="2">
-        <v>44681.0</v>
+        <v>44674.0</v>
       </c>
       <c r="D380" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="381">
@@ -5462,10 +5462,10 @@
         <v>2022.0</v>
       </c>
       <c r="C381" t="n" s="2">
-        <v>44688.0</v>
+        <v>44681.0</v>
       </c>
       <c r="D381" t="n">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="382">
@@ -5476,10 +5476,10 @@
         <v>2022.0</v>
       </c>
       <c r="C382" t="n" s="2">
-        <v>44695.0</v>
+        <v>44688.0</v>
       </c>
       <c r="D382" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="383">
@@ -5490,10 +5490,10 @@
         <v>2022.0</v>
       </c>
       <c r="C383" t="n" s="2">
-        <v>44702.0</v>
+        <v>44695.0</v>
       </c>
       <c r="D383" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="384">
@@ -5504,10 +5504,10 @@
         <v>2022.0</v>
       </c>
       <c r="C384" t="n" s="2">
-        <v>44709.0</v>
+        <v>44702.0</v>
       </c>
       <c r="D384" t="n">
-        <v>8.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="385">
@@ -5518,10 +5518,10 @@
         <v>2022.0</v>
       </c>
       <c r="C385" t="n" s="2">
-        <v>44716.0</v>
+        <v>44709.0</v>
       </c>
       <c r="D385" t="n">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="386">
@@ -5532,10 +5532,10 @@
         <v>2022.0</v>
       </c>
       <c r="C386" t="n" s="2">
-        <v>44723.0</v>
+        <v>44716.0</v>
       </c>
       <c r="D386" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="387">
@@ -5546,10 +5546,10 @@
         <v>2022.0</v>
       </c>
       <c r="C387" t="n" s="2">
-        <v>44730.0</v>
+        <v>44723.0</v>
       </c>
       <c r="D387" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="388">
@@ -5560,7 +5560,7 @@
         <v>2022.0</v>
       </c>
       <c r="C388" t="n" s="2">
-        <v>44737.0</v>
+        <v>44730.0</v>
       </c>
       <c r="D388" t="n">
         <v>4.0</v>
@@ -5574,10 +5574,10 @@
         <v>2022.0</v>
       </c>
       <c r="C389" t="n" s="2">
-        <v>44744.0</v>
+        <v>44737.0</v>
       </c>
       <c r="D389" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="390">
@@ -5588,10 +5588,10 @@
         <v>2022.0</v>
       </c>
       <c r="C390" t="n" s="2">
-        <v>44751.0</v>
+        <v>44744.0</v>
       </c>
       <c r="D390" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="391">
@@ -5602,10 +5602,10 @@
         <v>2022.0</v>
       </c>
       <c r="C391" t="n" s="2">
-        <v>44758.0</v>
+        <v>44751.0</v>
       </c>
       <c r="D391" t="n">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="392">
@@ -5616,10 +5616,10 @@
         <v>2022.0</v>
       </c>
       <c r="C392" t="n" s="2">
-        <v>44765.0</v>
+        <v>44758.0</v>
       </c>
       <c r="D392" t="n">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="393">
@@ -5630,10 +5630,10 @@
         <v>2022.0</v>
       </c>
       <c r="C393" t="n" s="2">
-        <v>44779.0</v>
+        <v>44765.0</v>
       </c>
       <c r="D393" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="394">
@@ -5644,10 +5644,10 @@
         <v>2022.0</v>
       </c>
       <c r="C394" t="n" s="2">
-        <v>44786.0</v>
+        <v>44779.0</v>
       </c>
       <c r="D394" t="n">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="395">
@@ -5658,10 +5658,10 @@
         <v>2022.0</v>
       </c>
       <c r="C395" t="n" s="2">
-        <v>44863.0</v>
+        <v>44786.0</v>
       </c>
       <c r="D395" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="396">
@@ -5672,10 +5672,10 @@
         <v>2022.0</v>
       </c>
       <c r="C396" t="n" s="2">
-        <v>44870.0</v>
+        <v>44863.0</v>
       </c>
       <c r="D396" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="397">
@@ -5686,10 +5686,10 @@
         <v>2022.0</v>
       </c>
       <c r="C397" t="n" s="2">
-        <v>44884.0</v>
+        <v>44870.0</v>
       </c>
       <c r="D397" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="398">
@@ -5700,7 +5700,7 @@
         <v>2022.0</v>
       </c>
       <c r="C398" t="n" s="2">
-        <v>44891.0</v>
+        <v>44884.0</v>
       </c>
       <c r="D398" t="n">
         <v>2.0</v>
@@ -5714,10 +5714,10 @@
         <v>2022.0</v>
       </c>
       <c r="C399" t="n" s="2">
-        <v>44898.0</v>
+        <v>44891.0</v>
       </c>
       <c r="D399" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="400">
@@ -5728,10 +5728,10 @@
         <v>2022.0</v>
       </c>
       <c r="C400" t="n" s="2">
-        <v>44912.0</v>
+        <v>44898.0</v>
       </c>
       <c r="D400" t="n">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="401">
@@ -5742,10 +5742,10 @@
         <v>2022.0</v>
       </c>
       <c r="C401" t="n" s="2">
-        <v>44919.0</v>
+        <v>44912.0</v>
       </c>
       <c r="D401" t="n">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="402">
@@ -5756,10 +5756,10 @@
         <v>2022.0</v>
       </c>
       <c r="C402" t="n" s="2">
-        <v>44926.0</v>
+        <v>44919.0</v>
       </c>
       <c r="D402" t="n">
-        <v>12.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="403">
@@ -5767,13 +5767,13 @@
         <v>7</v>
       </c>
       <c r="B403" t="n">
-        <v>2023.0</v>
+        <v>2022.0</v>
       </c>
       <c r="C403" t="n" s="2">
-        <v>44934.0</v>
+        <v>44926.0</v>
       </c>
       <c r="D403" t="n">
-        <v>4.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="404">
@@ -5784,10 +5784,10 @@
         <v>2023.0</v>
       </c>
       <c r="C404" t="n" s="2">
-        <v>44941.0</v>
+        <v>44934.0</v>
       </c>
       <c r="D404" t="n">
-        <v>16.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="405">
@@ -5798,10 +5798,10 @@
         <v>2023.0</v>
       </c>
       <c r="C405" t="n" s="2">
-        <v>44948.0</v>
+        <v>44941.0</v>
       </c>
       <c r="D405" t="n">
-        <v>5.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="406">
@@ -5812,10 +5812,10 @@
         <v>2023.0</v>
       </c>
       <c r="C406" t="n" s="2">
-        <v>44955.0</v>
+        <v>44948.0</v>
       </c>
       <c r="D406" t="n">
-        <v>19.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="407">
@@ -5826,10 +5826,10 @@
         <v>2023.0</v>
       </c>
       <c r="C407" t="n" s="2">
-        <v>44962.0</v>
+        <v>44955.0</v>
       </c>
       <c r="D407" t="n">
-        <v>22.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="408">
@@ -5840,10 +5840,10 @@
         <v>2023.0</v>
       </c>
       <c r="C408" t="n" s="2">
-        <v>44969.0</v>
+        <v>44962.0</v>
       </c>
       <c r="D408" t="n">
-        <v>9.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="409">
@@ -5854,10 +5854,10 @@
         <v>2023.0</v>
       </c>
       <c r="C409" t="n" s="2">
-        <v>44976.0</v>
+        <v>44969.0</v>
       </c>
       <c r="D409" t="n">
-        <v>22.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="410">
@@ -5868,10 +5868,10 @@
         <v>2023.0</v>
       </c>
       <c r="C410" t="n" s="2">
-        <v>44983.0</v>
+        <v>44976.0</v>
       </c>
       <c r="D410" t="n">
-        <v>29.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="411">
@@ -5882,10 +5882,10 @@
         <v>2023.0</v>
       </c>
       <c r="C411" t="n" s="2">
-        <v>44990.0</v>
+        <v>44983.0</v>
       </c>
       <c r="D411" t="n">
-        <v>5.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="412">
@@ -5896,10 +5896,10 @@
         <v>2023.0</v>
       </c>
       <c r="C412" t="n" s="2">
-        <v>44997.0</v>
+        <v>44990.0</v>
       </c>
       <c r="D412" t="n">
-        <v>24.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="413">
@@ -5910,10 +5910,10 @@
         <v>2023.0</v>
       </c>
       <c r="C413" t="n" s="2">
-        <v>45004.0</v>
+        <v>44997.0</v>
       </c>
       <c r="D413" t="n">
-        <v>8.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="414">
@@ -5924,10 +5924,10 @@
         <v>2023.0</v>
       </c>
       <c r="C414" t="n" s="2">
-        <v>45011.0</v>
+        <v>45004.0</v>
       </c>
       <c r="D414" t="n">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="415">
@@ -5938,10 +5938,10 @@
         <v>2023.0</v>
       </c>
       <c r="C415" t="n" s="2">
-        <v>45018.0</v>
+        <v>45011.0</v>
       </c>
       <c r="D415" t="n">
-        <v>18.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="416">
@@ -5952,10 +5952,10 @@
         <v>2023.0</v>
       </c>
       <c r="C416" t="n" s="2">
-        <v>45025.0</v>
+        <v>45018.0</v>
       </c>
       <c r="D416" t="n">
-        <v>13.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="417">
@@ -5966,10 +5966,10 @@
         <v>2023.0</v>
       </c>
       <c r="C417" t="n" s="2">
-        <v>45032.0</v>
+        <v>45025.0</v>
       </c>
       <c r="D417" t="n">
-        <v>18.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="418">
@@ -5980,10 +5980,10 @@
         <v>2023.0</v>
       </c>
       <c r="C418" t="n" s="2">
-        <v>45039.0</v>
+        <v>45032.0</v>
       </c>
       <c r="D418" t="n">
-        <v>15.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="419">
@@ -5994,10 +5994,10 @@
         <v>2023.0</v>
       </c>
       <c r="C419" t="n" s="2">
-        <v>45046.0</v>
+        <v>45039.0</v>
       </c>
       <c r="D419" t="n">
-        <v>12.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="420">
@@ -6008,10 +6008,10 @@
         <v>2023.0</v>
       </c>
       <c r="C420" t="n" s="2">
-        <v>45053.0</v>
+        <v>45046.0</v>
       </c>
       <c r="D420" t="n">
-        <v>6.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="421">
@@ -6022,10 +6022,10 @@
         <v>2023.0</v>
       </c>
       <c r="C421" t="n" s="2">
-        <v>45060.0</v>
+        <v>45053.0</v>
       </c>
       <c r="D421" t="n">
-        <v>11.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="422">
@@ -6036,10 +6036,10 @@
         <v>2023.0</v>
       </c>
       <c r="C422" t="n" s="2">
-        <v>45067.0</v>
+        <v>45060.0</v>
       </c>
       <c r="D422" t="n">
-        <v>8.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="423">
@@ -6050,7 +6050,7 @@
         <v>2023.0</v>
       </c>
       <c r="C423" t="n" s="2">
-        <v>45074.0</v>
+        <v>45067.0</v>
       </c>
       <c r="D423" t="n">
         <v>8.0</v>
@@ -6064,10 +6064,10 @@
         <v>2023.0</v>
       </c>
       <c r="C424" t="n" s="2">
-        <v>45081.0</v>
+        <v>45074.0</v>
       </c>
       <c r="D424" t="n">
-        <v>5.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="425">
@@ -6078,10 +6078,10 @@
         <v>2023.0</v>
       </c>
       <c r="C425" t="n" s="2">
-        <v>45088.0</v>
+        <v>45081.0</v>
       </c>
       <c r="D425" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="426">
@@ -6092,10 +6092,10 @@
         <v>2023.0</v>
       </c>
       <c r="C426" t="n" s="2">
-        <v>45095.0</v>
+        <v>45088.0</v>
       </c>
       <c r="D426" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="427">
@@ -6106,10 +6106,10 @@
         <v>2023.0</v>
       </c>
       <c r="C427" t="n" s="2">
-        <v>45102.0</v>
+        <v>45095.0</v>
       </c>
       <c r="D427" t="n">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="428">
@@ -6120,10 +6120,10 @@
         <v>2023.0</v>
       </c>
       <c r="C428" t="n" s="2">
-        <v>45109.0</v>
+        <v>45102.0</v>
       </c>
       <c r="D428" t="n">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="429">
@@ -6134,10 +6134,10 @@
         <v>2023.0</v>
       </c>
       <c r="C429" t="n" s="2">
-        <v>45116.0</v>
+        <v>45109.0</v>
       </c>
       <c r="D429" t="n">
-        <v>3.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="430">
@@ -6148,10 +6148,10 @@
         <v>2023.0</v>
       </c>
       <c r="C430" t="n" s="2">
-        <v>45123.0</v>
+        <v>45116.0</v>
       </c>
       <c r="D430" t="n">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="431">
@@ -6162,7 +6162,7 @@
         <v>2023.0</v>
       </c>
       <c r="C431" t="n" s="2">
-        <v>45130.0</v>
+        <v>45123.0</v>
       </c>
       <c r="D431" t="n">
         <v>6.0</v>
@@ -6176,10 +6176,10 @@
         <v>2023.0</v>
       </c>
       <c r="C432" t="n" s="2">
-        <v>45137.0</v>
+        <v>45130.0</v>
       </c>
       <c r="D432" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="433">
@@ -6190,7 +6190,7 @@
         <v>2023.0</v>
       </c>
       <c r="C433" t="n" s="2">
-        <v>45144.0</v>
+        <v>45137.0</v>
       </c>
       <c r="D433" t="n">
         <v>2.0</v>
@@ -6204,7 +6204,7 @@
         <v>2023.0</v>
       </c>
       <c r="C434" t="n" s="2">
-        <v>45151.0</v>
+        <v>45144.0</v>
       </c>
       <c r="D434" t="n">
         <v>2.0</v>
@@ -6218,7 +6218,7 @@
         <v>2023.0</v>
       </c>
       <c r="C435" t="n" s="2">
-        <v>45165.0</v>
+        <v>45151.0</v>
       </c>
       <c r="D435" t="n">
         <v>2.0</v>
@@ -6232,7 +6232,7 @@
         <v>2023.0</v>
       </c>
       <c r="C436" t="n" s="2">
-        <v>45172.0</v>
+        <v>45165.0</v>
       </c>
       <c r="D436" t="n">
         <v>2.0</v>
@@ -6246,10 +6246,10 @@
         <v>2023.0</v>
       </c>
       <c r="C437" t="n" s="2">
-        <v>45179.0</v>
+        <v>45172.0</v>
       </c>
       <c r="D437" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="438">
@@ -6260,7 +6260,7 @@
         <v>2023.0</v>
       </c>
       <c r="C438" t="n" s="2">
-        <v>45186.0</v>
+        <v>45179.0</v>
       </c>
       <c r="D438" t="n">
         <v>1.0</v>
@@ -6274,7 +6274,7 @@
         <v>2023.0</v>
       </c>
       <c r="C439" t="n" s="2">
-        <v>45193.0</v>
+        <v>45186.0</v>
       </c>
       <c r="D439" t="n">
         <v>1.0</v>
@@ -6288,7 +6288,7 @@
         <v>2023.0</v>
       </c>
       <c r="C440" t="n" s="2">
-        <v>45200.0</v>
+        <v>45193.0</v>
       </c>
       <c r="D440" t="n">
         <v>1.0</v>
@@ -6302,7 +6302,7 @@
         <v>2023.0</v>
       </c>
       <c r="C441" t="n" s="2">
-        <v>45207.0</v>
+        <v>45200.0</v>
       </c>
       <c r="D441" t="n">
         <v>1.0</v>
@@ -6316,7 +6316,7 @@
         <v>2023.0</v>
       </c>
       <c r="C442" t="n" s="2">
-        <v>45235.0</v>
+        <v>45207.0</v>
       </c>
       <c r="D442" t="n">
         <v>1.0</v>
@@ -6330,10 +6330,10 @@
         <v>2023.0</v>
       </c>
       <c r="C443" t="n" s="2">
-        <v>45242.0</v>
+        <v>45235.0</v>
       </c>
       <c r="D443" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="444">
@@ -6344,10 +6344,10 @@
         <v>2023.0</v>
       </c>
       <c r="C444" t="n" s="2">
-        <v>45249.0</v>
+        <v>45242.0</v>
       </c>
       <c r="D444" t="n">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="445">
@@ -6358,10 +6358,10 @@
         <v>2023.0</v>
       </c>
       <c r="C445" t="n" s="2">
-        <v>45256.0</v>
+        <v>45249.0</v>
       </c>
       <c r="D445" t="n">
-        <v>9.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="446">
@@ -6372,10 +6372,10 @@
         <v>2023.0</v>
       </c>
       <c r="C446" t="n" s="2">
-        <v>45263.0</v>
+        <v>45256.0</v>
       </c>
       <c r="D446" t="n">
-        <v>12.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="447">
@@ -6386,10 +6386,10 @@
         <v>2023.0</v>
       </c>
       <c r="C447" t="n" s="2">
-        <v>45270.0</v>
+        <v>45263.0</v>
       </c>
       <c r="D447" t="n">
-        <v>6.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="448">
@@ -6400,10 +6400,10 @@
         <v>2023.0</v>
       </c>
       <c r="C448" t="n" s="2">
-        <v>45277.0</v>
+        <v>45270.0</v>
       </c>
       <c r="D448" t="n">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="449">
@@ -6414,7 +6414,7 @@
         <v>2023.0</v>
       </c>
       <c r="C449" t="n" s="2">
-        <v>45284.0</v>
+        <v>45277.0</v>
       </c>
       <c r="D449" t="n">
         <v>7.0</v>
@@ -6428,10 +6428,10 @@
         <v>2023.0</v>
       </c>
       <c r="C450" t="n" s="2">
-        <v>45291.0</v>
+        <v>45284.0</v>
       </c>
       <c r="D450" t="n">
-        <v>13.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="451">
@@ -6439,13 +6439,13 @@
         <v>7</v>
       </c>
       <c r="B451" t="n">
-        <v>2024.0</v>
+        <v>2023.0</v>
       </c>
       <c r="C451" t="n" s="2">
-        <v>45299.0</v>
+        <v>45291.0</v>
       </c>
       <c r="D451" t="n">
-        <v>6.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="452">
@@ -6456,10 +6456,10 @@
         <v>2024.0</v>
       </c>
       <c r="C452" t="n" s="2">
-        <v>45306.0</v>
+        <v>45299.0</v>
       </c>
       <c r="D452" t="n">
-        <v>11.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="453">
@@ -6470,10 +6470,10 @@
         <v>2024.0</v>
       </c>
       <c r="C453" t="n" s="2">
-        <v>45313.0</v>
+        <v>45306.0</v>
       </c>
       <c r="D453" t="n">
-        <v>5.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="454">
@@ -6484,10 +6484,10 @@
         <v>2024.0</v>
       </c>
       <c r="C454" t="n" s="2">
-        <v>45320.0</v>
+        <v>45313.0</v>
       </c>
       <c r="D454" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="455">
@@ -6498,10 +6498,10 @@
         <v>2024.0</v>
       </c>
       <c r="C455" t="n" s="2">
-        <v>45327.0</v>
+        <v>45320.0</v>
       </c>
       <c r="D455" t="n">
-        <v>9.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="456">
@@ -6512,10 +6512,10 @@
         <v>2024.0</v>
       </c>
       <c r="C456" t="n" s="2">
-        <v>45334.0</v>
+        <v>45327.0</v>
       </c>
       <c r="D456" t="n">
-        <v>3.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="457">
@@ -6526,10 +6526,10 @@
         <v>2024.0</v>
       </c>
       <c r="C457" t="n" s="2">
-        <v>45341.0</v>
+        <v>45334.0</v>
       </c>
       <c r="D457" t="n">
-        <v>21.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="458">
@@ -6540,10 +6540,10 @@
         <v>2024.0</v>
       </c>
       <c r="C458" t="n" s="2">
-        <v>45348.0</v>
+        <v>45341.0</v>
       </c>
       <c r="D458" t="n">
-        <v>1.0</v>
+        <v>21.0</v>
       </c>
     </row>
     <row r="459">
@@ -6554,10 +6554,10 @@
         <v>2024.0</v>
       </c>
       <c r="C459" t="n" s="2">
-        <v>45355.0</v>
+        <v>45348.0</v>
       </c>
       <c r="D459" t="n">
-        <v>9.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="460">
@@ -6568,10 +6568,10 @@
         <v>2024.0</v>
       </c>
       <c r="C460" t="n" s="2">
-        <v>45362.0</v>
+        <v>45355.0</v>
       </c>
       <c r="D460" t="n">
-        <v>4.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="461">
@@ -6582,10 +6582,10 @@
         <v>2024.0</v>
       </c>
       <c r="C461" t="n" s="2">
-        <v>45369.0</v>
+        <v>45362.0</v>
       </c>
       <c r="D461" t="n">
-        <v>14.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="462">
@@ -6596,10 +6596,10 @@
         <v>2024.0</v>
       </c>
       <c r="C462" t="n" s="2">
-        <v>45376.0</v>
+        <v>45369.0</v>
       </c>
       <c r="D462" t="n">
-        <v>4.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="463">
@@ -6610,10 +6610,10 @@
         <v>2024.0</v>
       </c>
       <c r="C463" t="n" s="2">
-        <v>45383.0</v>
+        <v>45376.0</v>
       </c>
       <c r="D463" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="464">
@@ -6624,10 +6624,10 @@
         <v>2024.0</v>
       </c>
       <c r="C464" t="n" s="2">
-        <v>45390.0</v>
+        <v>45383.0</v>
       </c>
       <c r="D464" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="465">
@@ -6638,7 +6638,7 @@
         <v>2024.0</v>
       </c>
       <c r="C465" t="n" s="2">
-        <v>45397.0</v>
+        <v>45390.0</v>
       </c>
       <c r="D465" t="n">
         <v>1.0</v>
@@ -6652,10 +6652,10 @@
         <v>2024.0</v>
       </c>
       <c r="C466" t="n" s="2">
-        <v>45404.0</v>
+        <v>45397.0</v>
       </c>
       <c r="D466" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="467">
@@ -6666,10 +6666,10 @@
         <v>2024.0</v>
       </c>
       <c r="C467" t="n" s="2">
-        <v>45411.0</v>
+        <v>45404.0</v>
       </c>
       <c r="D467" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="468">
@@ -6680,10 +6680,10 @@
         <v>2024.0</v>
       </c>
       <c r="C468" t="n" s="2">
-        <v>45439.0</v>
+        <v>45411.0</v>
       </c>
       <c r="D468" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="469">
@@ -6694,10 +6694,10 @@
         <v>2024.0</v>
       </c>
       <c r="C469" t="n" s="2">
-        <v>45446.0</v>
+        <v>45439.0</v>
       </c>
       <c r="D469" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="470">
@@ -6708,7 +6708,7 @@
         <v>2024.0</v>
       </c>
       <c r="C470" t="n" s="2">
-        <v>45460.0</v>
+        <v>45446.0</v>
       </c>
       <c r="D470" t="n">
         <v>1.0</v>
@@ -6722,7 +6722,7 @@
         <v>2024.0</v>
       </c>
       <c r="C471" t="n" s="2">
-        <v>45481.0</v>
+        <v>45460.0</v>
       </c>
       <c r="D471" t="n">
         <v>1.0</v>
@@ -6736,7 +6736,7 @@
         <v>2024.0</v>
       </c>
       <c r="C472" t="n" s="2">
-        <v>45516.0</v>
+        <v>45481.0</v>
       </c>
       <c r="D472" t="n">
         <v>1.0</v>
@@ -6750,7 +6750,7 @@
         <v>2024.0</v>
       </c>
       <c r="C473" t="n" s="2">
-        <v>45551.0</v>
+        <v>45516.0</v>
       </c>
       <c r="D473" t="n">
         <v>1.0</v>
@@ -6764,7 +6764,7 @@
         <v>2024.0</v>
       </c>
       <c r="C474" t="n" s="2">
-        <v>45579.0</v>
+        <v>45551.0</v>
       </c>
       <c r="D474" t="n">
         <v>1.0</v>
@@ -6778,7 +6778,7 @@
         <v>2024.0</v>
       </c>
       <c r="C475" t="n" s="2">
-        <v>45614.0</v>
+        <v>45579.0</v>
       </c>
       <c r="D475" t="n">
         <v>1.0</v>
@@ -6792,10 +6792,10 @@
         <v>2024.0</v>
       </c>
       <c r="C476" t="n" s="2">
-        <v>45635.0</v>
+        <v>45614.0</v>
       </c>
       <c r="D476" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="477">
@@ -6806,10 +6806,10 @@
         <v>2024.0</v>
       </c>
       <c r="C477" t="n" s="2">
-        <v>45642.0</v>
+        <v>45635.0</v>
       </c>
       <c r="D477" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="478">
@@ -6820,10 +6820,10 @@
         <v>2024.0</v>
       </c>
       <c r="C478" t="n" s="2">
-        <v>45649.0</v>
+        <v>45642.0</v>
       </c>
       <c r="D478" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="479">
@@ -6834,10 +6834,10 @@
         <v>2024.0</v>
       </c>
       <c r="C479" t="n" s="2">
-        <v>45656.0</v>
+        <v>45649.0</v>
       </c>
       <c r="D479" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="480">
@@ -6845,13 +6845,13 @@
         <v>7</v>
       </c>
       <c r="B480" t="n">
-        <v>2025.0</v>
+        <v>2024.0</v>
       </c>
       <c r="C480" t="n" s="2">
-        <v>45665.0</v>
+        <v>45656.0</v>
       </c>
       <c r="D480" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="481">
@@ -6862,10 +6862,10 @@
         <v>2025.0</v>
       </c>
       <c r="C481" t="n" s="2">
-        <v>45672.0</v>
+        <v>45665.0</v>
       </c>
       <c r="D481" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="482">
@@ -6876,7 +6876,7 @@
         <v>2025.0</v>
       </c>
       <c r="C482" t="n" s="2">
-        <v>45686.0</v>
+        <v>45672.0</v>
       </c>
       <c r="D482" t="n">
         <v>2.0</v>
@@ -6890,10 +6890,10 @@
         <v>2025.0</v>
       </c>
       <c r="C483" t="n" s="2">
-        <v>45693.0</v>
+        <v>45686.0</v>
       </c>
       <c r="D483" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="484">
@@ -6904,10 +6904,10 @@
         <v>2025.0</v>
       </c>
       <c r="C484" t="n" s="2">
-        <v>45700.0</v>
+        <v>45693.0</v>
       </c>
       <c r="D484" t="n">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="485">
@@ -6918,10 +6918,10 @@
         <v>2025.0</v>
       </c>
       <c r="C485" t="n" s="2">
-        <v>45707.0</v>
+        <v>45700.0</v>
       </c>
       <c r="D485" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="486">
@@ -6932,10 +6932,10 @@
         <v>2025.0</v>
       </c>
       <c r="C486" t="n" s="2">
-        <v>45714.0</v>
+        <v>45707.0</v>
       </c>
       <c r="D486" t="n">
-        <v>8.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="487">
@@ -6946,10 +6946,10 @@
         <v>2025.0</v>
       </c>
       <c r="C487" t="n" s="2">
-        <v>45721.0</v>
+        <v>45714.0</v>
       </c>
       <c r="D487" t="n">
-        <v>11.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="488">
@@ -6960,10 +6960,10 @@
         <v>2025.0</v>
       </c>
       <c r="C488" t="n" s="2">
-        <v>45728.0</v>
+        <v>45721.0</v>
       </c>
       <c r="D488" t="n">
-        <v>6.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="489">
@@ -6974,10 +6974,10 @@
         <v>2025.0</v>
       </c>
       <c r="C489" t="n" s="2">
-        <v>45735.0</v>
+        <v>45728.0</v>
       </c>
       <c r="D489" t="n">
-        <v>19.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="490">
@@ -6988,10 +6988,10 @@
         <v>2025.0</v>
       </c>
       <c r="C490" t="n" s="2">
-        <v>45742.0</v>
+        <v>45735.0</v>
       </c>
       <c r="D490" t="n">
-        <v>17.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="491">
@@ -7002,10 +7002,10 @@
         <v>2025.0</v>
       </c>
       <c r="C491" t="n" s="2">
-        <v>45749.0</v>
+        <v>45742.0</v>
       </c>
       <c r="D491" t="n">
-        <v>5.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="492">
@@ -7016,10 +7016,10 @@
         <v>2025.0</v>
       </c>
       <c r="C492" t="n" s="2">
-        <v>45756.0</v>
+        <v>45749.0</v>
       </c>
       <c r="D492" t="n">
-        <v>9.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="493">
@@ -7030,10 +7030,10 @@
         <v>2025.0</v>
       </c>
       <c r="C493" t="n" s="2">
-        <v>45763.0</v>
+        <v>45756.0</v>
       </c>
       <c r="D493" t="n">
-        <v>1.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="494">
@@ -7044,7 +7044,7 @@
         <v>2025.0</v>
       </c>
       <c r="C494" t="n" s="2">
-        <v>45770.0</v>
+        <v>45763.0</v>
       </c>
       <c r="D494" t="n">
         <v>1.0</v>
@@ -7058,10 +7058,10 @@
         <v>2025.0</v>
       </c>
       <c r="C495" t="n" s="2">
-        <v>45784.0</v>
+        <v>45770.0</v>
       </c>
       <c r="D495" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="496">
@@ -7072,10 +7072,10 @@
         <v>2025.0</v>
       </c>
       <c r="C496" t="n" s="2">
-        <v>45791.0</v>
+        <v>45784.0</v>
       </c>
       <c r="D496" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="497">
@@ -7086,10 +7086,10 @@
         <v>2025.0</v>
       </c>
       <c r="C497" t="n" s="2">
-        <v>45805.0</v>
+        <v>45791.0</v>
       </c>
       <c r="D497" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="498">
@@ -7100,10 +7100,10 @@
         <v>2025.0</v>
       </c>
       <c r="C498" t="n" s="2">
-        <v>45826.0</v>
+        <v>45805.0</v>
       </c>
       <c r="D498" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="499">
@@ -7114,7 +7114,7 @@
         <v>2025.0</v>
       </c>
       <c r="C499" t="n" s="2">
-        <v>45861.0</v>
+        <v>45826.0</v>
       </c>
       <c r="D499" t="n">
         <v>2.0</v>
@@ -7128,10 +7128,10 @@
         <v>2025.0</v>
       </c>
       <c r="C500" t="n" s="2">
-        <v>45868.0</v>
+        <v>45861.0</v>
       </c>
       <c r="D500" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="501">
@@ -7142,7 +7142,7 @@
         <v>2025.0</v>
       </c>
       <c r="C501" t="n" s="2">
-        <v>45889.0</v>
+        <v>45868.0</v>
       </c>
       <c r="D501" t="n">
         <v>1.0</v>
@@ -7156,7 +7156,7 @@
         <v>2025.0</v>
       </c>
       <c r="C502" t="n" s="2">
-        <v>45924.0</v>
+        <v>45889.0</v>
       </c>
       <c r="D502" t="n">
         <v>1.0</v>
@@ -7170,7 +7170,7 @@
         <v>2025.0</v>
       </c>
       <c r="C503" t="n" s="2">
-        <v>45945.0</v>
+        <v>45924.0</v>
       </c>
       <c r="D503" t="n">
         <v>1.0</v>
@@ -7184,10 +7184,10 @@
         <v>2025.0</v>
       </c>
       <c r="C504" t="n" s="2">
-        <v>45959.0</v>
+        <v>45945.0</v>
       </c>
       <c r="D504" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="505">
@@ -7198,7 +7198,7 @@
         <v>2025.0</v>
       </c>
       <c r="C505" t="n" s="2">
-        <v>46001.0</v>
+        <v>45959.0</v>
       </c>
       <c r="D505" t="n">
         <v>2.0</v>
@@ -7212,10 +7212,10 @@
         <v>2025.0</v>
       </c>
       <c r="C506" t="n" s="2">
-        <v>46008.0</v>
+        <v>46001.0</v>
       </c>
       <c r="D506" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="507">
@@ -7226,7 +7226,7 @@
         <v>2025.0</v>
       </c>
       <c r="C507" t="n" s="2">
-        <v>46022.0</v>
+        <v>46008.0</v>
       </c>
       <c r="D507" t="n">
         <v>1.0</v>
@@ -7237,10 +7237,10 @@
         <v>7</v>
       </c>
       <c r="B508" t="n">
-        <v>2026.0</v>
+        <v>2025.0</v>
       </c>
       <c r="C508" t="n" s="2">
-        <v>46030.0</v>
+        <v>46022.0</v>
       </c>
       <c r="D508" t="n">
         <v>1.0</v>
@@ -7254,7 +7254,7 @@
         <v>2026.0</v>
       </c>
       <c r="C509" t="n" s="2">
-        <v>46051.0</v>
+        <v>46030.0</v>
       </c>
       <c r="D509" t="n">
         <v>1.0</v>
@@ -7268,7 +7268,7 @@
         <v>2026.0</v>
       </c>
       <c r="C510" t="n" s="2">
-        <v>46058.0</v>
+        <v>46051.0</v>
       </c>
       <c r="D510" t="n">
         <v>1.0</v>
@@ -7282,24 +7282,24 @@
         <v>2026.0</v>
       </c>
       <c r="C511" t="n" s="2">
-        <v>46065.0</v>
+        <v>46058.0</v>
       </c>
       <c r="D511" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B512" t="n">
-        <v>2024.0</v>
+        <v>2026.0</v>
       </c>
       <c r="C512" t="n" s="2">
-        <v>45495.0</v>
+        <v>46065.0</v>
       </c>
       <c r="D512" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="513">
@@ -7310,10 +7310,10 @@
         <v>2024.0</v>
       </c>
       <c r="C513" t="n" s="2">
-        <v>45502.0</v>
+        <v>45495.0</v>
       </c>
       <c r="D513" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="514">
@@ -7321,13 +7321,13 @@
         <v>8</v>
       </c>
       <c r="B514" t="n">
-        <v>2025.0</v>
+        <v>2024.0</v>
       </c>
       <c r="C514" t="n" s="2">
-        <v>45665.0</v>
+        <v>45502.0</v>
       </c>
       <c r="D514" t="n">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="515">
@@ -7338,10 +7338,10 @@
         <v>2025.0</v>
       </c>
       <c r="C515" t="n" s="2">
-        <v>45672.0</v>
+        <v>45665.0</v>
       </c>
       <c r="D515" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="516">
@@ -7352,10 +7352,10 @@
         <v>2025.0</v>
       </c>
       <c r="C516" t="n" s="2">
-        <v>45679.0</v>
+        <v>45672.0</v>
       </c>
       <c r="D516" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="517">
@@ -7366,10 +7366,10 @@
         <v>2025.0</v>
       </c>
       <c r="C517" t="n" s="2">
-        <v>45686.0</v>
+        <v>45679.0</v>
       </c>
       <c r="D517" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="518">
@@ -7380,10 +7380,10 @@
         <v>2025.0</v>
       </c>
       <c r="C518" t="n" s="2">
-        <v>45693.0</v>
+        <v>45686.0</v>
       </c>
       <c r="D518" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="519">
@@ -7394,10 +7394,10 @@
         <v>2025.0</v>
       </c>
       <c r="C519" t="n" s="2">
-        <v>45700.0</v>
+        <v>45693.0</v>
       </c>
       <c r="D519" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="520">
@@ -7408,10 +7408,10 @@
         <v>2025.0</v>
       </c>
       <c r="C520" t="n" s="2">
-        <v>45707.0</v>
+        <v>45700.0</v>
       </c>
       <c r="D520" t="n">
-        <v>7.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="521">
@@ -7422,10 +7422,10 @@
         <v>2025.0</v>
       </c>
       <c r="C521" t="n" s="2">
-        <v>45714.0</v>
+        <v>45707.0</v>
       </c>
       <c r="D521" t="n">
-        <v>3.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="522">
@@ -7436,10 +7436,10 @@
         <v>2025.0</v>
       </c>
       <c r="C522" t="n" s="2">
-        <v>45721.0</v>
+        <v>45714.0</v>
       </c>
       <c r="D522" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="523">
@@ -7450,10 +7450,10 @@
         <v>2025.0</v>
       </c>
       <c r="C523" t="n" s="2">
-        <v>45728.0</v>
+        <v>45721.0</v>
       </c>
       <c r="D523" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="524">
@@ -7464,7 +7464,7 @@
         <v>2025.0</v>
       </c>
       <c r="C524" t="n" s="2">
-        <v>45742.0</v>
+        <v>45728.0</v>
       </c>
       <c r="D524" t="n">
         <v>1.0</v>
@@ -7478,7 +7478,7 @@
         <v>2025.0</v>
       </c>
       <c r="C525" t="n" s="2">
-        <v>45749.0</v>
+        <v>45742.0</v>
       </c>
       <c r="D525" t="n">
         <v>1.0</v>
@@ -7492,7 +7492,7 @@
         <v>2025.0</v>
       </c>
       <c r="C526" t="n" s="2">
-        <v>45763.0</v>
+        <v>45749.0</v>
       </c>
       <c r="D526" t="n">
         <v>1.0</v>
@@ -7506,10 +7506,10 @@
         <v>2025.0</v>
       </c>
       <c r="C527" t="n" s="2">
-        <v>45777.0</v>
+        <v>45763.0</v>
       </c>
       <c r="D527" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="528">
@@ -7520,10 +7520,10 @@
         <v>2025.0</v>
       </c>
       <c r="C528" t="n" s="2">
-        <v>45784.0</v>
+        <v>45777.0</v>
       </c>
       <c r="D528" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="529">
@@ -7534,7 +7534,7 @@
         <v>2025.0</v>
       </c>
       <c r="C529" t="n" s="2">
-        <v>45798.0</v>
+        <v>45784.0</v>
       </c>
       <c r="D529" t="n">
         <v>1.0</v>
@@ -7548,7 +7548,7 @@
         <v>2025.0</v>
       </c>
       <c r="C530" t="n" s="2">
-        <v>45805.0</v>
+        <v>45798.0</v>
       </c>
       <c r="D530" t="n">
         <v>1.0</v>
@@ -7562,10 +7562,10 @@
         <v>2025.0</v>
       </c>
       <c r="C531" t="n" s="2">
-        <v>45812.0</v>
+        <v>45805.0</v>
       </c>
       <c r="D531" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="532">
@@ -7576,7 +7576,7 @@
         <v>2025.0</v>
       </c>
       <c r="C532" t="n" s="2">
-        <v>45819.0</v>
+        <v>45812.0</v>
       </c>
       <c r="D532" t="n">
         <v>2.0</v>
@@ -7590,7 +7590,7 @@
         <v>2025.0</v>
       </c>
       <c r="C533" t="n" s="2">
-        <v>45833.0</v>
+        <v>45819.0</v>
       </c>
       <c r="D533" t="n">
         <v>2.0</v>
@@ -7604,10 +7604,10 @@
         <v>2025.0</v>
       </c>
       <c r="C534" t="n" s="2">
-        <v>45847.0</v>
+        <v>45833.0</v>
       </c>
       <c r="D534" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="535">
@@ -7618,10 +7618,10 @@
         <v>2025.0</v>
       </c>
       <c r="C535" t="n" s="2">
-        <v>45854.0</v>
+        <v>45847.0</v>
       </c>
       <c r="D535" t="n">
-        <v>8.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="536">
@@ -7632,10 +7632,10 @@
         <v>2025.0</v>
       </c>
       <c r="C536" t="n" s="2">
-        <v>45861.0</v>
+        <v>45854.0</v>
       </c>
       <c r="D536" t="n">
-        <v>12.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="537">
@@ -7646,10 +7646,10 @@
         <v>2025.0</v>
       </c>
       <c r="C537" t="n" s="2">
-        <v>45868.0</v>
+        <v>45861.0</v>
       </c>
       <c r="D537" t="n">
-        <v>6.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="538">
@@ -7660,10 +7660,10 @@
         <v>2025.0</v>
       </c>
       <c r="C538" t="n" s="2">
-        <v>45875.0</v>
+        <v>45868.0</v>
       </c>
       <c r="D538" t="n">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="539">
@@ -7674,7 +7674,7 @@
         <v>2025.0</v>
       </c>
       <c r="C539" t="n" s="2">
-        <v>45896.0</v>
+        <v>45875.0</v>
       </c>
       <c r="D539" t="n">
         <v>1.0</v>
@@ -7688,7 +7688,7 @@
         <v>2025.0</v>
       </c>
       <c r="C540" t="n" s="2">
-        <v>45903.0</v>
+        <v>45896.0</v>
       </c>
       <c r="D540" t="n">
         <v>1.0</v>
@@ -7702,7 +7702,7 @@
         <v>2025.0</v>
       </c>
       <c r="C541" t="n" s="2">
-        <v>45931.0</v>
+        <v>45903.0</v>
       </c>
       <c r="D541" t="n">
         <v>1.0</v>
@@ -7716,10 +7716,10 @@
         <v>2025.0</v>
       </c>
       <c r="C542" t="n" s="2">
-        <v>45938.0</v>
+        <v>45931.0</v>
       </c>
       <c r="D542" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="543">
@@ -7730,10 +7730,10 @@
         <v>2025.0</v>
       </c>
       <c r="C543" t="n" s="2">
-        <v>45945.0</v>
+        <v>45938.0</v>
       </c>
       <c r="D543" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="544">
@@ -7744,7 +7744,7 @@
         <v>2025.0</v>
       </c>
       <c r="C544" t="n" s="2">
-        <v>45966.0</v>
+        <v>45945.0</v>
       </c>
       <c r="D544" t="n">
         <v>2.0</v>
@@ -7758,10 +7758,10 @@
         <v>2025.0</v>
       </c>
       <c r="C545" t="n" s="2">
-        <v>45973.0</v>
+        <v>45966.0</v>
       </c>
       <c r="D545" t="n">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="546">
@@ -7772,10 +7772,10 @@
         <v>2025.0</v>
       </c>
       <c r="C546" t="n" s="2">
-        <v>45980.0</v>
+        <v>45973.0</v>
       </c>
       <c r="D546" t="n">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="547">
@@ -7786,10 +7786,10 @@
         <v>2025.0</v>
       </c>
       <c r="C547" t="n" s="2">
-        <v>45987.0</v>
+        <v>45980.0</v>
       </c>
       <c r="D547" t="n">
-        <v>20.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="548">
@@ -7800,10 +7800,10 @@
         <v>2025.0</v>
       </c>
       <c r="C548" t="n" s="2">
-        <v>45994.0</v>
+        <v>45987.0</v>
       </c>
       <c r="D548" t="n">
-        <v>5.0</v>
+        <v>20.0</v>
       </c>
     </row>
     <row r="549">
@@ -7814,10 +7814,10 @@
         <v>2025.0</v>
       </c>
       <c r="C549" t="n" s="2">
-        <v>46001.0</v>
+        <v>45994.0</v>
       </c>
       <c r="D549" t="n">
-        <v>8.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="550">
@@ -7828,10 +7828,10 @@
         <v>2025.0</v>
       </c>
       <c r="C550" t="n" s="2">
-        <v>46008.0</v>
+        <v>46001.0</v>
       </c>
       <c r="D550" t="n">
-        <v>24.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="551">
@@ -7842,10 +7842,10 @@
         <v>2025.0</v>
       </c>
       <c r="C551" t="n" s="2">
-        <v>46015.0</v>
+        <v>46008.0</v>
       </c>
       <c r="D551" t="n">
-        <v>13.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="552">
@@ -7856,10 +7856,10 @@
         <v>2025.0</v>
       </c>
       <c r="C552" t="n" s="2">
-        <v>46022.0</v>
+        <v>46015.0</v>
       </c>
       <c r="D552" t="n">
-        <v>8.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="553">
@@ -7870,10 +7870,10 @@
         <v>2025.0</v>
       </c>
       <c r="C553" t="n" s="2">
-        <v>46029.0</v>
+        <v>46022.0</v>
       </c>
       <c r="D553" t="n">
-        <v>3.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="554">
@@ -7881,13 +7881,13 @@
         <v>8</v>
       </c>
       <c r="B554" t="n">
-        <v>2026.0</v>
+        <v>2025.0</v>
       </c>
       <c r="C554" t="n" s="2">
-        <v>46030.0</v>
+        <v>46029.0</v>
       </c>
       <c r="D554" t="n">
-        <v>24.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="555">
@@ -7898,10 +7898,10 @@
         <v>2026.0</v>
       </c>
       <c r="C555" t="n" s="2">
-        <v>46037.0</v>
+        <v>46030.0</v>
       </c>
       <c r="D555" t="n">
-        <v>22.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="556">
@@ -7912,10 +7912,10 @@
         <v>2026.0</v>
       </c>
       <c r="C556" t="n" s="2">
-        <v>46044.0</v>
+        <v>46037.0</v>
       </c>
       <c r="D556" t="n">
-        <v>27.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="557">
@@ -7926,10 +7926,10 @@
         <v>2026.0</v>
       </c>
       <c r="C557" t="n" s="2">
-        <v>46051.0</v>
+        <v>46044.0</v>
       </c>
       <c r="D557" t="n">
-        <v>18.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="558">
@@ -7940,10 +7940,10 @@
         <v>2026.0</v>
       </c>
       <c r="C558" t="n" s="2">
-        <v>46058.0</v>
+        <v>46051.0</v>
       </c>
       <c r="D558" t="n">
-        <v>25.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="559">
@@ -7954,10 +7954,10 @@
         <v>2026.0</v>
       </c>
       <c r="C559" t="n" s="2">
-        <v>46065.0</v>
+        <v>46058.0</v>
       </c>
       <c r="D559" t="n">
-        <v>22.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="560">
@@ -7968,10 +7968,10 @@
         <v>2026.0</v>
       </c>
       <c r="C560" t="n" s="2">
-        <v>46072.0</v>
+        <v>46065.0</v>
       </c>
       <c r="D560" t="n">
-        <v>13.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="561">
@@ -7982,10 +7982,10 @@
         <v>2026.0</v>
       </c>
       <c r="C561" t="n" s="2">
-        <v>46079.0</v>
+        <v>46072.0</v>
       </c>
       <c r="D561" t="n">
-        <v>24.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="562">
@@ -7996,10 +7996,10 @@
         <v>2026.0</v>
       </c>
       <c r="C562" t="n" s="2">
-        <v>46086.0</v>
+        <v>46079.0</v>
       </c>
       <c r="D562" t="n">
-        <v>26.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="563">
@@ -8010,10 +8010,10 @@
         <v>2026.0</v>
       </c>
       <c r="C563" t="n" s="2">
-        <v>46093.0</v>
+        <v>46086.0</v>
       </c>
       <c r="D563" t="n">
-        <v>33.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="564">
@@ -8024,10 +8024,10 @@
         <v>2026.0</v>
       </c>
       <c r="C564" t="n" s="2">
-        <v>46100.0</v>
+        <v>46093.0</v>
       </c>
       <c r="D564" t="n">
-        <v>25.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="565">
@@ -8038,10 +8038,10 @@
         <v>2026.0</v>
       </c>
       <c r="C565" t="n" s="2">
-        <v>46107.0</v>
+        <v>46100.0</v>
       </c>
       <c r="D565" t="n">
-        <v>31.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="566">
@@ -8052,10 +8052,38 @@
         <v>2026.0</v>
       </c>
       <c r="C566" t="n" s="2">
+        <v>46107.0</v>
+      </c>
+      <c r="D566" t="n">
+        <v>31.0</v>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="s">
+        <v>8</v>
+      </c>
+      <c r="B567" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C567" t="n" s="2">
         <v>46114.0</v>
       </c>
-      <c r="D566" t="n">
+      <c r="D567" t="n">
         <v>7.0</v>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="s">
+        <v>8</v>
+      </c>
+      <c r="B568" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C568" t="n" s="2">
+        <v>46121.0</v>
+      </c>
+      <c r="D568" t="n">
+        <v>6.0</v>
       </c>
     </row>
   </sheetData>
@@ -8081,7 +8109,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="n">
-        <v>45.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="3">
@@ -8097,7 +8125,7 @@
         <v>12</v>
       </c>
       <c r="B4" t="n">
-        <v>1177.0</v>
+        <v>1183.0</v>
       </c>
     </row>
     <row r="5">
@@ -8105,7 +8133,7 @@
         <v>13</v>
       </c>
       <c r="B5" t="n">
-        <v>2063.0</v>
+        <v>2064.0</v>
       </c>
     </row>
   </sheetData>
@@ -8159,7 +8187,7 @@
         <v>19</v>
       </c>
       <c r="C4" t="n">
-        <v>133.0</v>
+        <v>135.0</v>
       </c>
     </row>
     <row r="5">
@@ -8192,7 +8220,7 @@
         <v>19</v>
       </c>
       <c r="C7" t="n">
-        <v>155.0</v>
+        <v>156.0</v>
       </c>
     </row>
     <row r="8">
@@ -8225,7 +8253,7 @@
         <v>19</v>
       </c>
       <c r="C10" t="n">
-        <v>141.0</v>
+        <v>143.0</v>
       </c>
     </row>
     <row r="11">
@@ -8236,7 +8264,7 @@
         <v>19</v>
       </c>
       <c r="C11" t="n">
-        <v>31.0</v>
+        <v>38.0</v>
       </c>
     </row>
     <row r="12">
@@ -8269,7 +8297,7 @@
         <v>19</v>
       </c>
       <c r="C14" t="n">
-        <v>379.0</v>
+        <v>380.0</v>
       </c>
     </row>
     <row r="15">
@@ -8302,7 +8330,7 @@
         <v>19</v>
       </c>
       <c r="C17" t="n">
-        <v>108.0</v>
+        <v>109.0</v>
       </c>
     </row>
   </sheetData>

--- a/Download/Focus_Positivi_ZR.xlsx
+++ b/Download/Focus_Positivi_ZR.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="612" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="615" uniqueCount="23">
   <si>
     <t>NOME_REGIONE</t>
   </si>
@@ -1573,21 +1573,21 @@
         <v>46121.0</v>
       </c>
       <c r="D103" t="n">
-        <v>2.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B104" t="n">
-        <v>2021.0</v>
+        <v>2026.0</v>
       </c>
       <c r="C104" t="n" s="2">
-        <v>44561.0</v>
+        <v>46128.0</v>
       </c>
       <c r="D104" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="105">
@@ -1595,13 +1595,13 @@
         <v>5</v>
       </c>
       <c r="B105" t="n">
-        <v>2022.0</v>
+        <v>2021.0</v>
       </c>
       <c r="C105" t="n" s="2">
-        <v>44576.0</v>
+        <v>44561.0</v>
       </c>
       <c r="D105" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="106">
@@ -1612,10 +1612,10 @@
         <v>2022.0</v>
       </c>
       <c r="C106" t="n" s="2">
-        <v>44583.0</v>
+        <v>44576.0</v>
       </c>
       <c r="D106" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="107">
@@ -1626,10 +1626,10 @@
         <v>2022.0</v>
       </c>
       <c r="C107" t="n" s="2">
-        <v>44590.0</v>
+        <v>44583.0</v>
       </c>
       <c r="D107" t="n">
-        <v>7.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="108">
@@ -1640,10 +1640,10 @@
         <v>2022.0</v>
       </c>
       <c r="C108" t="n" s="2">
-        <v>44597.0</v>
+        <v>44590.0</v>
       </c>
       <c r="D108" t="n">
-        <v>3.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="109">
@@ -1654,10 +1654,10 @@
         <v>2022.0</v>
       </c>
       <c r="C109" t="n" s="2">
-        <v>44604.0</v>
+        <v>44597.0</v>
       </c>
       <c r="D109" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="110">
@@ -1668,10 +1668,10 @@
         <v>2022.0</v>
       </c>
       <c r="C110" t="n" s="2">
-        <v>44611.0</v>
+        <v>44604.0</v>
       </c>
       <c r="D110" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="111">
@@ -1682,7 +1682,7 @@
         <v>2022.0</v>
       </c>
       <c r="C111" t="n" s="2">
-        <v>44618.0</v>
+        <v>44611.0</v>
       </c>
       <c r="D111" t="n">
         <v>1.0</v>
@@ -1696,10 +1696,10 @@
         <v>2022.0</v>
       </c>
       <c r="C112" t="n" s="2">
-        <v>44625.0</v>
+        <v>44618.0</v>
       </c>
       <c r="D112" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="113">
@@ -1710,10 +1710,10 @@
         <v>2022.0</v>
       </c>
       <c r="C113" t="n" s="2">
-        <v>44632.0</v>
+        <v>44625.0</v>
       </c>
       <c r="D113" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="114">
@@ -1724,10 +1724,10 @@
         <v>2022.0</v>
       </c>
       <c r="C114" t="n" s="2">
-        <v>44639.0</v>
+        <v>44632.0</v>
       </c>
       <c r="D114" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="115">
@@ -1738,7 +1738,7 @@
         <v>2022.0</v>
       </c>
       <c r="C115" t="n" s="2">
-        <v>44646.0</v>
+        <v>44639.0</v>
       </c>
       <c r="D115" t="n">
         <v>2.0</v>
@@ -1752,7 +1752,7 @@
         <v>2022.0</v>
       </c>
       <c r="C116" t="n" s="2">
-        <v>44653.0</v>
+        <v>44646.0</v>
       </c>
       <c r="D116" t="n">
         <v>2.0</v>
@@ -1766,10 +1766,10 @@
         <v>2022.0</v>
       </c>
       <c r="C117" t="n" s="2">
-        <v>44660.0</v>
+        <v>44653.0</v>
       </c>
       <c r="D117" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="118">
@@ -1780,10 +1780,10 @@
         <v>2022.0</v>
       </c>
       <c r="C118" t="n" s="2">
-        <v>44667.0</v>
+        <v>44660.0</v>
       </c>
       <c r="D118" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="119">
@@ -1794,7 +1794,7 @@
         <v>2022.0</v>
       </c>
       <c r="C119" t="n" s="2">
-        <v>44674.0</v>
+        <v>44667.0</v>
       </c>
       <c r="D119" t="n">
         <v>3.0</v>
@@ -1808,10 +1808,10 @@
         <v>2022.0</v>
       </c>
       <c r="C120" t="n" s="2">
-        <v>44681.0</v>
+        <v>44674.0</v>
       </c>
       <c r="D120" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="121">
@@ -1822,10 +1822,10 @@
         <v>2022.0</v>
       </c>
       <c r="C121" t="n" s="2">
-        <v>44688.0</v>
+        <v>44681.0</v>
       </c>
       <c r="D121" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="122">
@@ -1836,7 +1836,7 @@
         <v>2022.0</v>
       </c>
       <c r="C122" t="n" s="2">
-        <v>44695.0</v>
+        <v>44688.0</v>
       </c>
       <c r="D122" t="n">
         <v>3.0</v>
@@ -1850,10 +1850,10 @@
         <v>2022.0</v>
       </c>
       <c r="C123" t="n" s="2">
-        <v>44702.0</v>
+        <v>44695.0</v>
       </c>
       <c r="D123" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="124">
@@ -1864,10 +1864,10 @@
         <v>2022.0</v>
       </c>
       <c r="C124" t="n" s="2">
-        <v>44709.0</v>
+        <v>44702.0</v>
       </c>
       <c r="D124" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="125">
@@ -1878,10 +1878,10 @@
         <v>2022.0</v>
       </c>
       <c r="C125" t="n" s="2">
-        <v>44716.0</v>
+        <v>44709.0</v>
       </c>
       <c r="D125" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="126">
@@ -1892,7 +1892,7 @@
         <v>2022.0</v>
       </c>
       <c r="C126" t="n" s="2">
-        <v>44723.0</v>
+        <v>44716.0</v>
       </c>
       <c r="D126" t="n">
         <v>1.0</v>
@@ -1906,7 +1906,7 @@
         <v>2022.0</v>
       </c>
       <c r="C127" t="n" s="2">
-        <v>44730.0</v>
+        <v>44723.0</v>
       </c>
       <c r="D127" t="n">
         <v>1.0</v>
@@ -1920,7 +1920,7 @@
         <v>2022.0</v>
       </c>
       <c r="C128" t="n" s="2">
-        <v>44737.0</v>
+        <v>44730.0</v>
       </c>
       <c r="D128" t="n">
         <v>1.0</v>
@@ -1934,7 +1934,7 @@
         <v>2022.0</v>
       </c>
       <c r="C129" t="n" s="2">
-        <v>44744.0</v>
+        <v>44737.0</v>
       </c>
       <c r="D129" t="n">
         <v>1.0</v>
@@ -1948,7 +1948,7 @@
         <v>2022.0</v>
       </c>
       <c r="C130" t="n" s="2">
-        <v>44751.0</v>
+        <v>44744.0</v>
       </c>
       <c r="D130" t="n">
         <v>1.0</v>
@@ -1962,7 +1962,7 @@
         <v>2022.0</v>
       </c>
       <c r="C131" t="n" s="2">
-        <v>44758.0</v>
+        <v>44751.0</v>
       </c>
       <c r="D131" t="n">
         <v>1.0</v>
@@ -1976,7 +1976,7 @@
         <v>2022.0</v>
       </c>
       <c r="C132" t="n" s="2">
-        <v>44772.0</v>
+        <v>44758.0</v>
       </c>
       <c r="D132" t="n">
         <v>1.0</v>
@@ -1990,7 +1990,7 @@
         <v>2022.0</v>
       </c>
       <c r="C133" t="n" s="2">
-        <v>44793.0</v>
+        <v>44772.0</v>
       </c>
       <c r="D133" t="n">
         <v>1.0</v>
@@ -2004,7 +2004,7 @@
         <v>2022.0</v>
       </c>
       <c r="C134" t="n" s="2">
-        <v>44800.0</v>
+        <v>44793.0</v>
       </c>
       <c r="D134" t="n">
         <v>1.0</v>
@@ -2018,7 +2018,7 @@
         <v>2022.0</v>
       </c>
       <c r="C135" t="n" s="2">
-        <v>44828.0</v>
+        <v>44800.0</v>
       </c>
       <c r="D135" t="n">
         <v>1.0</v>
@@ -2032,7 +2032,7 @@
         <v>2022.0</v>
       </c>
       <c r="C136" t="n" s="2">
-        <v>44849.0</v>
+        <v>44828.0</v>
       </c>
       <c r="D136" t="n">
         <v>1.0</v>
@@ -2046,7 +2046,7 @@
         <v>2022.0</v>
       </c>
       <c r="C137" t="n" s="2">
-        <v>44856.0</v>
+        <v>44849.0</v>
       </c>
       <c r="D137" t="n">
         <v>1.0</v>
@@ -2060,7 +2060,7 @@
         <v>2022.0</v>
       </c>
       <c r="C138" t="n" s="2">
-        <v>44863.0</v>
+        <v>44856.0</v>
       </c>
       <c r="D138" t="n">
         <v>1.0</v>
@@ -2074,10 +2074,10 @@
         <v>2022.0</v>
       </c>
       <c r="C139" t="n" s="2">
-        <v>44884.0</v>
+        <v>44863.0</v>
       </c>
       <c r="D139" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="140">
@@ -2088,10 +2088,10 @@
         <v>2022.0</v>
       </c>
       <c r="C140" t="n" s="2">
-        <v>44891.0</v>
+        <v>44884.0</v>
       </c>
       <c r="D140" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="141">
@@ -2102,7 +2102,7 @@
         <v>2022.0</v>
       </c>
       <c r="C141" t="n" s="2">
-        <v>44905.0</v>
+        <v>44891.0</v>
       </c>
       <c r="D141" t="n">
         <v>1.0</v>
@@ -2116,7 +2116,7 @@
         <v>2022.0</v>
       </c>
       <c r="C142" t="n" s="2">
-        <v>44912.0</v>
+        <v>44905.0</v>
       </c>
       <c r="D142" t="n">
         <v>1.0</v>
@@ -2130,10 +2130,10 @@
         <v>2022.0</v>
       </c>
       <c r="C143" t="n" s="2">
-        <v>44919.0</v>
+        <v>44912.0</v>
       </c>
       <c r="D143" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="144">
@@ -2141,13 +2141,13 @@
         <v>5</v>
       </c>
       <c r="B144" t="n">
-        <v>2023.0</v>
+        <v>2022.0</v>
       </c>
       <c r="C144" t="n" s="2">
-        <v>44934.0</v>
+        <v>44919.0</v>
       </c>
       <c r="D144" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="145">
@@ -2158,10 +2158,10 @@
         <v>2023.0</v>
       </c>
       <c r="C145" t="n" s="2">
-        <v>44941.0</v>
+        <v>44934.0</v>
       </c>
       <c r="D145" t="n">
-        <v>8.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="146">
@@ -2172,10 +2172,10 @@
         <v>2023.0</v>
       </c>
       <c r="C146" t="n" s="2">
-        <v>44948.0</v>
+        <v>44941.0</v>
       </c>
       <c r="D146" t="n">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="147">
@@ -2186,10 +2186,10 @@
         <v>2023.0</v>
       </c>
       <c r="C147" t="n" s="2">
-        <v>44955.0</v>
+        <v>44948.0</v>
       </c>
       <c r="D147" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="148">
@@ -2200,10 +2200,10 @@
         <v>2023.0</v>
       </c>
       <c r="C148" t="n" s="2">
-        <v>44962.0</v>
+        <v>44955.0</v>
       </c>
       <c r="D148" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="149">
@@ -2214,7 +2214,7 @@
         <v>2023.0</v>
       </c>
       <c r="C149" t="n" s="2">
-        <v>44969.0</v>
+        <v>44962.0</v>
       </c>
       <c r="D149" t="n">
         <v>4.0</v>
@@ -2228,10 +2228,10 @@
         <v>2023.0</v>
       </c>
       <c r="C150" t="n" s="2">
-        <v>44976.0</v>
+        <v>44969.0</v>
       </c>
       <c r="D150" t="n">
-        <v>17.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="151">
@@ -2242,10 +2242,10 @@
         <v>2023.0</v>
       </c>
       <c r="C151" t="n" s="2">
-        <v>44983.0</v>
+        <v>44976.0</v>
       </c>
       <c r="D151" t="n">
-        <v>11.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="152">
@@ -2256,10 +2256,10 @@
         <v>2023.0</v>
       </c>
       <c r="C152" t="n" s="2">
-        <v>44990.0</v>
+        <v>44983.0</v>
       </c>
       <c r="D152" t="n">
-        <v>5.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="153">
@@ -2270,10 +2270,10 @@
         <v>2023.0</v>
       </c>
       <c r="C153" t="n" s="2">
-        <v>44997.0</v>
+        <v>44990.0</v>
       </c>
       <c r="D153" t="n">
-        <v>22.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="154">
@@ -2284,10 +2284,10 @@
         <v>2023.0</v>
       </c>
       <c r="C154" t="n" s="2">
-        <v>45004.0</v>
+        <v>44997.0</v>
       </c>
       <c r="D154" t="n">
-        <v>8.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="155">
@@ -2298,10 +2298,10 @@
         <v>2023.0</v>
       </c>
       <c r="C155" t="n" s="2">
-        <v>45011.0</v>
+        <v>45004.0</v>
       </c>
       <c r="D155" t="n">
-        <v>17.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="156">
@@ -2312,10 +2312,10 @@
         <v>2023.0</v>
       </c>
       <c r="C156" t="n" s="2">
-        <v>45018.0</v>
+        <v>45011.0</v>
       </c>
       <c r="D156" t="n">
-        <v>10.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="157">
@@ -2326,10 +2326,10 @@
         <v>2023.0</v>
       </c>
       <c r="C157" t="n" s="2">
-        <v>45025.0</v>
+        <v>45018.0</v>
       </c>
       <c r="D157" t="n">
-        <v>13.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="158">
@@ -2340,10 +2340,10 @@
         <v>2023.0</v>
       </c>
       <c r="C158" t="n" s="2">
-        <v>45032.0</v>
+        <v>45025.0</v>
       </c>
       <c r="D158" t="n">
-        <v>10.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="159">
@@ -2354,10 +2354,10 @@
         <v>2023.0</v>
       </c>
       <c r="C159" t="n" s="2">
-        <v>45039.0</v>
+        <v>45032.0</v>
       </c>
       <c r="D159" t="n">
-        <v>22.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="160">
@@ -2368,10 +2368,10 @@
         <v>2023.0</v>
       </c>
       <c r="C160" t="n" s="2">
-        <v>45046.0</v>
+        <v>45039.0</v>
       </c>
       <c r="D160" t="n">
-        <v>23.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="161">
@@ -2382,10 +2382,10 @@
         <v>2023.0</v>
       </c>
       <c r="C161" t="n" s="2">
-        <v>45053.0</v>
+        <v>45046.0</v>
       </c>
       <c r="D161" t="n">
-        <v>16.0</v>
+        <v>23.0</v>
       </c>
     </row>
     <row r="162">
@@ -2396,10 +2396,10 @@
         <v>2023.0</v>
       </c>
       <c r="C162" t="n" s="2">
-        <v>45060.0</v>
+        <v>45053.0</v>
       </c>
       <c r="D162" t="n">
-        <v>13.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="163">
@@ -2410,10 +2410,10 @@
         <v>2023.0</v>
       </c>
       <c r="C163" t="n" s="2">
-        <v>45067.0</v>
+        <v>45060.0</v>
       </c>
       <c r="D163" t="n">
-        <v>9.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="164">
@@ -2424,10 +2424,10 @@
         <v>2023.0</v>
       </c>
       <c r="C164" t="n" s="2">
-        <v>45074.0</v>
+        <v>45067.0</v>
       </c>
       <c r="D164" t="n">
-        <v>6.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="165">
@@ -2438,10 +2438,10 @@
         <v>2023.0</v>
       </c>
       <c r="C165" t="n" s="2">
-        <v>45081.0</v>
+        <v>45074.0</v>
       </c>
       <c r="D165" t="n">
-        <v>16.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="166">
@@ -2452,10 +2452,10 @@
         <v>2023.0</v>
       </c>
       <c r="C166" t="n" s="2">
-        <v>45088.0</v>
+        <v>45081.0</v>
       </c>
       <c r="D166" t="n">
-        <v>8.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="167">
@@ -2466,10 +2466,10 @@
         <v>2023.0</v>
       </c>
       <c r="C167" t="n" s="2">
-        <v>45095.0</v>
+        <v>45088.0</v>
       </c>
       <c r="D167" t="n">
-        <v>16.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="168">
@@ -2480,10 +2480,10 @@
         <v>2023.0</v>
       </c>
       <c r="C168" t="n" s="2">
-        <v>45102.0</v>
+        <v>45095.0</v>
       </c>
       <c r="D168" t="n">
-        <v>17.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="169">
@@ -2494,10 +2494,10 @@
         <v>2023.0</v>
       </c>
       <c r="C169" t="n" s="2">
-        <v>45109.0</v>
+        <v>45102.0</v>
       </c>
       <c r="D169" t="n">
-        <v>14.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="170">
@@ -2508,10 +2508,10 @@
         <v>2023.0</v>
       </c>
       <c r="C170" t="n" s="2">
-        <v>45116.0</v>
+        <v>45109.0</v>
       </c>
       <c r="D170" t="n">
-        <v>13.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="171">
@@ -2522,10 +2522,10 @@
         <v>2023.0</v>
       </c>
       <c r="C171" t="n" s="2">
-        <v>45123.0</v>
+        <v>45116.0</v>
       </c>
       <c r="D171" t="n">
-        <v>5.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="172">
@@ -2536,10 +2536,10 @@
         <v>2023.0</v>
       </c>
       <c r="C172" t="n" s="2">
-        <v>45130.0</v>
+        <v>45123.0</v>
       </c>
       <c r="D172" t="n">
-        <v>8.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="173">
@@ -2550,10 +2550,10 @@
         <v>2023.0</v>
       </c>
       <c r="C173" t="n" s="2">
-        <v>45137.0</v>
+        <v>45130.0</v>
       </c>
       <c r="D173" t="n">
-        <v>4.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="174">
@@ -2564,10 +2564,10 @@
         <v>2023.0</v>
       </c>
       <c r="C174" t="n" s="2">
-        <v>45144.0</v>
+        <v>45137.0</v>
       </c>
       <c r="D174" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="175">
@@ -2578,7 +2578,7 @@
         <v>2023.0</v>
       </c>
       <c r="C175" t="n" s="2">
-        <v>45151.0</v>
+        <v>45144.0</v>
       </c>
       <c r="D175" t="n">
         <v>2.0</v>
@@ -2592,10 +2592,10 @@
         <v>2023.0</v>
       </c>
       <c r="C176" t="n" s="2">
-        <v>45158.0</v>
+        <v>45151.0</v>
       </c>
       <c r="D176" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="177">
@@ -2606,7 +2606,7 @@
         <v>2023.0</v>
       </c>
       <c r="C177" t="n" s="2">
-        <v>45165.0</v>
+        <v>45158.0</v>
       </c>
       <c r="D177" t="n">
         <v>5.0</v>
@@ -2620,10 +2620,10 @@
         <v>2023.0</v>
       </c>
       <c r="C178" t="n" s="2">
-        <v>45172.0</v>
+        <v>45165.0</v>
       </c>
       <c r="D178" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="179">
@@ -2634,10 +2634,10 @@
         <v>2023.0</v>
       </c>
       <c r="C179" t="n" s="2">
-        <v>45179.0</v>
+        <v>45172.0</v>
       </c>
       <c r="D179" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="180">
@@ -2648,10 +2648,10 @@
         <v>2023.0</v>
       </c>
       <c r="C180" t="n" s="2">
-        <v>45186.0</v>
+        <v>45179.0</v>
       </c>
       <c r="D180" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="181">
@@ -2662,7 +2662,7 @@
         <v>2023.0</v>
       </c>
       <c r="C181" t="n" s="2">
-        <v>45193.0</v>
+        <v>45186.0</v>
       </c>
       <c r="D181" t="n">
         <v>1.0</v>
@@ -2676,10 +2676,10 @@
         <v>2023.0</v>
       </c>
       <c r="C182" t="n" s="2">
-        <v>45200.0</v>
+        <v>45193.0</v>
       </c>
       <c r="D182" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="183">
@@ -2690,10 +2690,10 @@
         <v>2023.0</v>
       </c>
       <c r="C183" t="n" s="2">
-        <v>45207.0</v>
+        <v>45200.0</v>
       </c>
       <c r="D183" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="184">
@@ -2704,10 +2704,10 @@
         <v>2023.0</v>
       </c>
       <c r="C184" t="n" s="2">
-        <v>45214.0</v>
+        <v>45207.0</v>
       </c>
       <c r="D184" t="n">
-        <v>8.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="185">
@@ -2718,7 +2718,7 @@
         <v>2023.0</v>
       </c>
       <c r="C185" t="n" s="2">
-        <v>45221.0</v>
+        <v>45214.0</v>
       </c>
       <c r="D185" t="n">
         <v>8.0</v>
@@ -2732,10 +2732,10 @@
         <v>2023.0</v>
       </c>
       <c r="C186" t="n" s="2">
-        <v>45228.0</v>
+        <v>45221.0</v>
       </c>
       <c r="D186" t="n">
-        <v>17.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="187">
@@ -2746,10 +2746,10 @@
         <v>2023.0</v>
       </c>
       <c r="C187" t="n" s="2">
-        <v>45235.0</v>
+        <v>45228.0</v>
       </c>
       <c r="D187" t="n">
-        <v>9.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="188">
@@ -2760,7 +2760,7 @@
         <v>2023.0</v>
       </c>
       <c r="C188" t="n" s="2">
-        <v>45242.0</v>
+        <v>45235.0</v>
       </c>
       <c r="D188" t="n">
         <v>9.0</v>
@@ -2774,10 +2774,10 @@
         <v>2023.0</v>
       </c>
       <c r="C189" t="n" s="2">
-        <v>45249.0</v>
+        <v>45242.0</v>
       </c>
       <c r="D189" t="n">
-        <v>14.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="190">
@@ -2788,10 +2788,10 @@
         <v>2023.0</v>
       </c>
       <c r="C190" t="n" s="2">
-        <v>45256.0</v>
+        <v>45249.0</v>
       </c>
       <c r="D190" t="n">
-        <v>17.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="191">
@@ -2802,10 +2802,10 @@
         <v>2023.0</v>
       </c>
       <c r="C191" t="n" s="2">
-        <v>45263.0</v>
+        <v>45256.0</v>
       </c>
       <c r="D191" t="n">
-        <v>14.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="192">
@@ -2816,10 +2816,10 @@
         <v>2023.0</v>
       </c>
       <c r="C192" t="n" s="2">
-        <v>45270.0</v>
+        <v>45263.0</v>
       </c>
       <c r="D192" t="n">
-        <v>26.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="193">
@@ -2830,10 +2830,10 @@
         <v>2023.0</v>
       </c>
       <c r="C193" t="n" s="2">
-        <v>45277.0</v>
+        <v>45270.0</v>
       </c>
       <c r="D193" t="n">
-        <v>19.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="194">
@@ -2844,10 +2844,10 @@
         <v>2023.0</v>
       </c>
       <c r="C194" t="n" s="2">
-        <v>45284.0</v>
+        <v>45277.0</v>
       </c>
       <c r="D194" t="n">
-        <v>21.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="195">
@@ -2858,10 +2858,10 @@
         <v>2023.0</v>
       </c>
       <c r="C195" t="n" s="2">
-        <v>45291.0</v>
+        <v>45284.0</v>
       </c>
       <c r="D195" t="n">
-        <v>9.0</v>
+        <v>21.0</v>
       </c>
     </row>
     <row r="196">
@@ -2869,13 +2869,13 @@
         <v>5</v>
       </c>
       <c r="B196" t="n">
-        <v>2024.0</v>
+        <v>2023.0</v>
       </c>
       <c r="C196" t="n" s="2">
-        <v>45299.0</v>
+        <v>45291.0</v>
       </c>
       <c r="D196" t="n">
-        <v>26.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="197">
@@ -2886,10 +2886,10 @@
         <v>2024.0</v>
       </c>
       <c r="C197" t="n" s="2">
-        <v>45306.0</v>
+        <v>45299.0</v>
       </c>
       <c r="D197" t="n">
-        <v>14.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="198">
@@ -2900,10 +2900,10 @@
         <v>2024.0</v>
       </c>
       <c r="C198" t="n" s="2">
-        <v>45313.0</v>
+        <v>45306.0</v>
       </c>
       <c r="D198" t="n">
-        <v>15.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="199">
@@ -2914,10 +2914,10 @@
         <v>2024.0</v>
       </c>
       <c r="C199" t="n" s="2">
-        <v>45320.0</v>
+        <v>45313.0</v>
       </c>
       <c r="D199" t="n">
-        <v>18.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="200">
@@ -2928,10 +2928,10 @@
         <v>2024.0</v>
       </c>
       <c r="C200" t="n" s="2">
-        <v>45327.0</v>
+        <v>45320.0</v>
       </c>
       <c r="D200" t="n">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="201">
@@ -2942,10 +2942,10 @@
         <v>2024.0</v>
       </c>
       <c r="C201" t="n" s="2">
-        <v>45334.0</v>
+        <v>45327.0</v>
       </c>
       <c r="D201" t="n">
-        <v>13.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="202">
@@ -2956,10 +2956,10 @@
         <v>2024.0</v>
       </c>
       <c r="C202" t="n" s="2">
-        <v>45341.0</v>
+        <v>45334.0</v>
       </c>
       <c r="D202" t="n">
-        <v>11.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="203">
@@ -2970,10 +2970,10 @@
         <v>2024.0</v>
       </c>
       <c r="C203" t="n" s="2">
-        <v>45348.0</v>
+        <v>45341.0</v>
       </c>
       <c r="D203" t="n">
-        <v>8.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="204">
@@ -2984,10 +2984,10 @@
         <v>2024.0</v>
       </c>
       <c r="C204" t="n" s="2">
-        <v>45355.0</v>
+        <v>45348.0</v>
       </c>
       <c r="D204" t="n">
-        <v>1.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="205">
@@ -2998,10 +2998,10 @@
         <v>2024.0</v>
       </c>
       <c r="C205" t="n" s="2">
-        <v>45362.0</v>
+        <v>45355.0</v>
       </c>
       <c r="D205" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="206">
@@ -3012,10 +3012,10 @@
         <v>2024.0</v>
       </c>
       <c r="C206" t="n" s="2">
-        <v>45369.0</v>
+        <v>45362.0</v>
       </c>
       <c r="D206" t="n">
-        <v>8.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="207">
@@ -3026,10 +3026,10 @@
         <v>2024.0</v>
       </c>
       <c r="C207" t="n" s="2">
-        <v>45376.0</v>
+        <v>45369.0</v>
       </c>
       <c r="D207" t="n">
-        <v>9.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="208">
@@ -3040,10 +3040,10 @@
         <v>2024.0</v>
       </c>
       <c r="C208" t="n" s="2">
-        <v>45383.0</v>
+        <v>45376.0</v>
       </c>
       <c r="D208" t="n">
-        <v>5.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="209">
@@ -3054,10 +3054,10 @@
         <v>2024.0</v>
       </c>
       <c r="C209" t="n" s="2">
-        <v>45390.0</v>
+        <v>45383.0</v>
       </c>
       <c r="D209" t="n">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="210">
@@ -3068,10 +3068,10 @@
         <v>2024.0</v>
       </c>
       <c r="C210" t="n" s="2">
-        <v>45397.0</v>
+        <v>45390.0</v>
       </c>
       <c r="D210" t="n">
-        <v>13.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="211">
@@ -3082,10 +3082,10 @@
         <v>2024.0</v>
       </c>
       <c r="C211" t="n" s="2">
-        <v>45404.0</v>
+        <v>45397.0</v>
       </c>
       <c r="D211" t="n">
-        <v>24.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="212">
@@ -3096,10 +3096,10 @@
         <v>2024.0</v>
       </c>
       <c r="C212" t="n" s="2">
-        <v>45411.0</v>
+        <v>45404.0</v>
       </c>
       <c r="D212" t="n">
-        <v>17.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="213">
@@ -3110,10 +3110,10 @@
         <v>2024.0</v>
       </c>
       <c r="C213" t="n" s="2">
-        <v>45418.0</v>
+        <v>45411.0</v>
       </c>
       <c r="D213" t="n">
-        <v>3.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="214">
@@ -3124,10 +3124,10 @@
         <v>2024.0</v>
       </c>
       <c r="C214" t="n" s="2">
-        <v>45425.0</v>
+        <v>45418.0</v>
       </c>
       <c r="D214" t="n">
-        <v>16.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="215">
@@ -3138,10 +3138,10 @@
         <v>2024.0</v>
       </c>
       <c r="C215" t="n" s="2">
-        <v>45432.0</v>
+        <v>45425.0</v>
       </c>
       <c r="D215" t="n">
-        <v>19.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="216">
@@ -3152,10 +3152,10 @@
         <v>2024.0</v>
       </c>
       <c r="C216" t="n" s="2">
-        <v>45439.0</v>
+        <v>45432.0</v>
       </c>
       <c r="D216" t="n">
-        <v>30.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="217">
@@ -3166,10 +3166,10 @@
         <v>2024.0</v>
       </c>
       <c r="C217" t="n" s="2">
-        <v>45446.0</v>
+        <v>45439.0</v>
       </c>
       <c r="D217" t="n">
-        <v>28.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="218">
@@ -3180,10 +3180,10 @@
         <v>2024.0</v>
       </c>
       <c r="C218" t="n" s="2">
-        <v>45453.0</v>
+        <v>45446.0</v>
       </c>
       <c r="D218" t="n">
-        <v>19.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="219">
@@ -3194,10 +3194,10 @@
         <v>2024.0</v>
       </c>
       <c r="C219" t="n" s="2">
-        <v>45460.0</v>
+        <v>45453.0</v>
       </c>
       <c r="D219" t="n">
-        <v>26.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="220">
@@ -3208,10 +3208,10 @@
         <v>2024.0</v>
       </c>
       <c r="C220" t="n" s="2">
-        <v>45467.0</v>
+        <v>45460.0</v>
       </c>
       <c r="D220" t="n">
-        <v>8.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="221">
@@ -3222,10 +3222,10 @@
         <v>2024.0</v>
       </c>
       <c r="C221" t="n" s="2">
-        <v>45474.0</v>
+        <v>45467.0</v>
       </c>
       <c r="D221" t="n">
-        <v>12.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="222">
@@ -3236,7 +3236,7 @@
         <v>2024.0</v>
       </c>
       <c r="C222" t="n" s="2">
-        <v>45481.0</v>
+        <v>45474.0</v>
       </c>
       <c r="D222" t="n">
         <v>12.0</v>
@@ -3250,10 +3250,10 @@
         <v>2024.0</v>
       </c>
       <c r="C223" t="n" s="2">
-        <v>45488.0</v>
+        <v>45481.0</v>
       </c>
       <c r="D223" t="n">
-        <v>4.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="224">
@@ -3264,10 +3264,10 @@
         <v>2024.0</v>
       </c>
       <c r="C224" t="n" s="2">
-        <v>45495.0</v>
+        <v>45488.0</v>
       </c>
       <c r="D224" t="n">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="225">
@@ -3278,10 +3278,10 @@
         <v>2024.0</v>
       </c>
       <c r="C225" t="n" s="2">
-        <v>45502.0</v>
+        <v>45495.0</v>
       </c>
       <c r="D225" t="n">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="226">
@@ -3292,10 +3292,10 @@
         <v>2024.0</v>
       </c>
       <c r="C226" t="n" s="2">
-        <v>45509.0</v>
+        <v>45502.0</v>
       </c>
       <c r="D226" t="n">
-        <v>2.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="227">
@@ -3306,10 +3306,10 @@
         <v>2024.0</v>
       </c>
       <c r="C227" t="n" s="2">
-        <v>45516.0</v>
+        <v>45509.0</v>
       </c>
       <c r="D227" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="228">
@@ -3320,7 +3320,7 @@
         <v>2024.0</v>
       </c>
       <c r="C228" t="n" s="2">
-        <v>45523.0</v>
+        <v>45516.0</v>
       </c>
       <c r="D228" t="n">
         <v>4.0</v>
@@ -3334,7 +3334,7 @@
         <v>2024.0</v>
       </c>
       <c r="C229" t="n" s="2">
-        <v>45530.0</v>
+        <v>45523.0</v>
       </c>
       <c r="D229" t="n">
         <v>4.0</v>
@@ -3348,7 +3348,7 @@
         <v>2024.0</v>
       </c>
       <c r="C230" t="n" s="2">
-        <v>45537.0</v>
+        <v>45530.0</v>
       </c>
       <c r="D230" t="n">
         <v>4.0</v>
@@ -3362,10 +3362,10 @@
         <v>2024.0</v>
       </c>
       <c r="C231" t="n" s="2">
-        <v>45544.0</v>
+        <v>45537.0</v>
       </c>
       <c r="D231" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="232">
@@ -3376,10 +3376,10 @@
         <v>2024.0</v>
       </c>
       <c r="C232" t="n" s="2">
-        <v>45551.0</v>
+        <v>45544.0</v>
       </c>
       <c r="D232" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="233">
@@ -3390,10 +3390,10 @@
         <v>2024.0</v>
       </c>
       <c r="C233" t="n" s="2">
-        <v>45558.0</v>
+        <v>45551.0</v>
       </c>
       <c r="D233" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="234">
@@ -3404,10 +3404,10 @@
         <v>2024.0</v>
       </c>
       <c r="C234" t="n" s="2">
-        <v>45600.0</v>
+        <v>45558.0</v>
       </c>
       <c r="D234" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="235">
@@ -3418,10 +3418,10 @@
         <v>2024.0</v>
       </c>
       <c r="C235" t="n" s="2">
-        <v>45607.0</v>
+        <v>45600.0</v>
       </c>
       <c r="D235" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="236">
@@ -3432,10 +3432,10 @@
         <v>2024.0</v>
       </c>
       <c r="C236" t="n" s="2">
-        <v>45628.0</v>
+        <v>45607.0</v>
       </c>
       <c r="D236" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="237">
@@ -3446,10 +3446,10 @@
         <v>2024.0</v>
       </c>
       <c r="C237" t="n" s="2">
-        <v>45635.0</v>
+        <v>45628.0</v>
       </c>
       <c r="D237" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="238">
@@ -3460,7 +3460,7 @@
         <v>2024.0</v>
       </c>
       <c r="C238" t="n" s="2">
-        <v>45642.0</v>
+        <v>45635.0</v>
       </c>
       <c r="D238" t="n">
         <v>3.0</v>
@@ -3474,10 +3474,10 @@
         <v>2024.0</v>
       </c>
       <c r="C239" t="n" s="2">
-        <v>45649.0</v>
+        <v>45642.0</v>
       </c>
       <c r="D239" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="240">
@@ -3488,7 +3488,7 @@
         <v>2024.0</v>
       </c>
       <c r="C240" t="n" s="2">
-        <v>45656.0</v>
+        <v>45649.0</v>
       </c>
       <c r="D240" t="n">
         <v>1.0</v>
@@ -3499,13 +3499,13 @@
         <v>5</v>
       </c>
       <c r="B241" t="n">
-        <v>2025.0</v>
+        <v>2024.0</v>
       </c>
       <c r="C241" t="n" s="2">
-        <v>45672.0</v>
+        <v>45656.0</v>
       </c>
       <c r="D241" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="242">
@@ -3516,10 +3516,10 @@
         <v>2025.0</v>
       </c>
       <c r="C242" t="n" s="2">
-        <v>45679.0</v>
+        <v>45672.0</v>
       </c>
       <c r="D242" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="243">
@@ -3530,7 +3530,7 @@
         <v>2025.0</v>
       </c>
       <c r="C243" t="n" s="2">
-        <v>45686.0</v>
+        <v>45679.0</v>
       </c>
       <c r="D243" t="n">
         <v>1.0</v>
@@ -3544,10 +3544,10 @@
         <v>2025.0</v>
       </c>
       <c r="C244" t="n" s="2">
-        <v>45721.0</v>
+        <v>45686.0</v>
       </c>
       <c r="D244" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="245">
@@ -3558,10 +3558,10 @@
         <v>2025.0</v>
       </c>
       <c r="C245" t="n" s="2">
-        <v>45728.0</v>
+        <v>45721.0</v>
       </c>
       <c r="D245" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="246">
@@ -3572,10 +3572,10 @@
         <v>2025.0</v>
       </c>
       <c r="C246" t="n" s="2">
-        <v>45742.0</v>
+        <v>45728.0</v>
       </c>
       <c r="D246" t="n">
-        <v>9.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="247">
@@ -3586,10 +3586,10 @@
         <v>2025.0</v>
       </c>
       <c r="C247" t="n" s="2">
-        <v>45749.0</v>
+        <v>45742.0</v>
       </c>
       <c r="D247" t="n">
-        <v>5.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="248">
@@ -3600,10 +3600,10 @@
         <v>2025.0</v>
       </c>
       <c r="C248" t="n" s="2">
-        <v>45756.0</v>
+        <v>45749.0</v>
       </c>
       <c r="D248" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="249">
@@ -3614,10 +3614,10 @@
         <v>2025.0</v>
       </c>
       <c r="C249" t="n" s="2">
-        <v>45763.0</v>
+        <v>45756.0</v>
       </c>
       <c r="D249" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="250">
@@ -3628,10 +3628,10 @@
         <v>2025.0</v>
       </c>
       <c r="C250" t="n" s="2">
-        <v>45770.0</v>
+        <v>45763.0</v>
       </c>
       <c r="D250" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="251">
@@ -3642,10 +3642,10 @@
         <v>2025.0</v>
       </c>
       <c r="C251" t="n" s="2">
-        <v>45777.0</v>
+        <v>45770.0</v>
       </c>
       <c r="D251" t="n">
-        <v>7.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="252">
@@ -3656,10 +3656,10 @@
         <v>2025.0</v>
       </c>
       <c r="C252" t="n" s="2">
-        <v>45784.0</v>
+        <v>45777.0</v>
       </c>
       <c r="D252" t="n">
-        <v>2.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="253">
@@ -3670,10 +3670,10 @@
         <v>2025.0</v>
       </c>
       <c r="C253" t="n" s="2">
-        <v>45791.0</v>
+        <v>45784.0</v>
       </c>
       <c r="D253" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="254">
@@ -3684,10 +3684,10 @@
         <v>2025.0</v>
       </c>
       <c r="C254" t="n" s="2">
-        <v>45798.0</v>
+        <v>45791.0</v>
       </c>
       <c r="D254" t="n">
-        <v>8.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="255">
@@ -3698,10 +3698,10 @@
         <v>2025.0</v>
       </c>
       <c r="C255" t="n" s="2">
-        <v>45805.0</v>
+        <v>45798.0</v>
       </c>
       <c r="D255" t="n">
-        <v>4.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="256">
@@ -3712,10 +3712,10 @@
         <v>2025.0</v>
       </c>
       <c r="C256" t="n" s="2">
-        <v>45812.0</v>
+        <v>45805.0</v>
       </c>
       <c r="D256" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="257">
@@ -3726,10 +3726,10 @@
         <v>2025.0</v>
       </c>
       <c r="C257" t="n" s="2">
-        <v>45819.0</v>
+        <v>45812.0</v>
       </c>
       <c r="D257" t="n">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="258">
@@ -3740,10 +3740,10 @@
         <v>2025.0</v>
       </c>
       <c r="C258" t="n" s="2">
-        <v>45826.0</v>
+        <v>45819.0</v>
       </c>
       <c r="D258" t="n">
-        <v>13.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="259">
@@ -3754,10 +3754,10 @@
         <v>2025.0</v>
       </c>
       <c r="C259" t="n" s="2">
-        <v>45833.0</v>
+        <v>45826.0</v>
       </c>
       <c r="D259" t="n">
-        <v>1.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="260">
@@ -3768,10 +3768,10 @@
         <v>2025.0</v>
       </c>
       <c r="C260" t="n" s="2">
-        <v>45840.0</v>
+        <v>45833.0</v>
       </c>
       <c r="D260" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="261">
@@ -3782,7 +3782,7 @@
         <v>2025.0</v>
       </c>
       <c r="C261" t="n" s="2">
-        <v>45847.0</v>
+        <v>45840.0</v>
       </c>
       <c r="D261" t="n">
         <v>4.0</v>
@@ -3796,10 +3796,10 @@
         <v>2025.0</v>
       </c>
       <c r="C262" t="n" s="2">
-        <v>45854.0</v>
+        <v>45847.0</v>
       </c>
       <c r="D262" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="263">
@@ -3810,10 +3810,10 @@
         <v>2025.0</v>
       </c>
       <c r="C263" t="n" s="2">
-        <v>45861.0</v>
+        <v>45854.0</v>
       </c>
       <c r="D263" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="264">
@@ -3824,10 +3824,10 @@
         <v>2025.0</v>
       </c>
       <c r="C264" t="n" s="2">
-        <v>45868.0</v>
+        <v>45861.0</v>
       </c>
       <c r="D264" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="265">
@@ -3838,10 +3838,10 @@
         <v>2025.0</v>
       </c>
       <c r="C265" t="n" s="2">
-        <v>45882.0</v>
+        <v>45868.0</v>
       </c>
       <c r="D265" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="266">
@@ -3852,7 +3852,7 @@
         <v>2025.0</v>
       </c>
       <c r="C266" t="n" s="2">
-        <v>45889.0</v>
+        <v>45882.0</v>
       </c>
       <c r="D266" t="n">
         <v>1.0</v>
@@ -3866,10 +3866,10 @@
         <v>2025.0</v>
       </c>
       <c r="C267" t="n" s="2">
-        <v>45896.0</v>
+        <v>45889.0</v>
       </c>
       <c r="D267" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="268">
@@ -3880,7 +3880,7 @@
         <v>2025.0</v>
       </c>
       <c r="C268" t="n" s="2">
-        <v>45903.0</v>
+        <v>45896.0</v>
       </c>
       <c r="D268" t="n">
         <v>3.0</v>
@@ -3894,10 +3894,10 @@
         <v>2025.0</v>
       </c>
       <c r="C269" t="n" s="2">
-        <v>45910.0</v>
+        <v>45903.0</v>
       </c>
       <c r="D269" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="270">
@@ -3908,7 +3908,7 @@
         <v>2025.0</v>
       </c>
       <c r="C270" t="n" s="2">
-        <v>45973.0</v>
+        <v>45910.0</v>
       </c>
       <c r="D270" t="n">
         <v>1.0</v>
@@ -3922,10 +3922,10 @@
         <v>2025.0</v>
       </c>
       <c r="C271" t="n" s="2">
-        <v>45987.0</v>
+        <v>45973.0</v>
       </c>
       <c r="D271" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="272">
@@ -3936,10 +3936,10 @@
         <v>2025.0</v>
       </c>
       <c r="C272" t="n" s="2">
-        <v>45994.0</v>
+        <v>45987.0</v>
       </c>
       <c r="D272" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="273">
@@ -3950,10 +3950,10 @@
         <v>2025.0</v>
       </c>
       <c r="C273" t="n" s="2">
-        <v>46001.0</v>
+        <v>45994.0</v>
       </c>
       <c r="D273" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="274">
@@ -3964,10 +3964,10 @@
         <v>2025.0</v>
       </c>
       <c r="C274" t="n" s="2">
-        <v>46008.0</v>
+        <v>46001.0</v>
       </c>
       <c r="D274" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="275">
@@ -3978,10 +3978,10 @@
         <v>2025.0</v>
       </c>
       <c r="C275" t="n" s="2">
-        <v>46022.0</v>
+        <v>46008.0</v>
       </c>
       <c r="D275" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="276">
@@ -3992,10 +3992,10 @@
         <v>2025.0</v>
       </c>
       <c r="C276" t="n" s="2">
-        <v>46029.0</v>
+        <v>46022.0</v>
       </c>
       <c r="D276" t="n">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="277">
@@ -4003,13 +4003,13 @@
         <v>5</v>
       </c>
       <c r="B277" t="n">
-        <v>2026.0</v>
+        <v>2025.0</v>
       </c>
       <c r="C277" t="n" s="2">
-        <v>46030.0</v>
+        <v>46029.0</v>
       </c>
       <c r="D277" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="278">
@@ -4020,10 +4020,10 @@
         <v>2026.0</v>
       </c>
       <c r="C278" t="n" s="2">
-        <v>46037.0</v>
+        <v>46030.0</v>
       </c>
       <c r="D278" t="n">
-        <v>12.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="279">
@@ -4034,10 +4034,10 @@
         <v>2026.0</v>
       </c>
       <c r="C279" t="n" s="2">
-        <v>46044.0</v>
+        <v>46037.0</v>
       </c>
       <c r="D279" t="n">
-        <v>9.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="280">
@@ -4048,10 +4048,10 @@
         <v>2026.0</v>
       </c>
       <c r="C280" t="n" s="2">
-        <v>46051.0</v>
+        <v>46044.0</v>
       </c>
       <c r="D280" t="n">
-        <v>10.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="281">
@@ -4062,10 +4062,10 @@
         <v>2026.0</v>
       </c>
       <c r="C281" t="n" s="2">
-        <v>46058.0</v>
+        <v>46051.0</v>
       </c>
       <c r="D281" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="282">
@@ -4076,10 +4076,10 @@
         <v>2026.0</v>
       </c>
       <c r="C282" t="n" s="2">
-        <v>46065.0</v>
+        <v>46058.0</v>
       </c>
       <c r="D282" t="n">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="283">
@@ -4090,10 +4090,10 @@
         <v>2026.0</v>
       </c>
       <c r="C283" t="n" s="2">
-        <v>46072.0</v>
+        <v>46065.0</v>
       </c>
       <c r="D283" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="284">
@@ -4104,10 +4104,10 @@
         <v>2026.0</v>
       </c>
       <c r="C284" t="n" s="2">
-        <v>46079.0</v>
+        <v>46072.0</v>
       </c>
       <c r="D284" t="n">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="285">
@@ -4118,10 +4118,10 @@
         <v>2026.0</v>
       </c>
       <c r="C285" t="n" s="2">
-        <v>46086.0</v>
+        <v>46079.0</v>
       </c>
       <c r="D285" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="286">
@@ -4132,7 +4132,7 @@
         <v>2026.0</v>
       </c>
       <c r="C286" t="n" s="2">
-        <v>46093.0</v>
+        <v>46086.0</v>
       </c>
       <c r="D286" t="n">
         <v>2.0</v>
@@ -4146,10 +4146,10 @@
         <v>2026.0</v>
       </c>
       <c r="C287" t="n" s="2">
-        <v>46100.0</v>
+        <v>46093.0</v>
       </c>
       <c r="D287" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="288">
@@ -4160,10 +4160,10 @@
         <v>2026.0</v>
       </c>
       <c r="C288" t="n" s="2">
-        <v>46107.0</v>
+        <v>46100.0</v>
       </c>
       <c r="D288" t="n">
-        <v>9.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="289">
@@ -4174,10 +4174,10 @@
         <v>2026.0</v>
       </c>
       <c r="C289" t="n" s="2">
-        <v>46114.0</v>
+        <v>46107.0</v>
       </c>
       <c r="D289" t="n">
-        <v>4.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="290">
@@ -4188,38 +4188,38 @@
         <v>2026.0</v>
       </c>
       <c r="C290" t="n" s="2">
-        <v>46121.0</v>
+        <v>46114.0</v>
       </c>
       <c r="D290" t="n">
-        <v>7.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B291" t="n">
-        <v>2023.0</v>
+        <v>2026.0</v>
       </c>
       <c r="C291" t="n" s="2">
-        <v>45095.0</v>
+        <v>46121.0</v>
       </c>
       <c r="D291" t="n">
-        <v>1.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B292" t="n">
-        <v>2023.0</v>
+        <v>2026.0</v>
       </c>
       <c r="C292" t="n" s="2">
-        <v>45102.0</v>
+        <v>46128.0</v>
       </c>
       <c r="D292" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="293">
@@ -4230,7 +4230,7 @@
         <v>2023.0</v>
       </c>
       <c r="C293" t="n" s="2">
-        <v>45158.0</v>
+        <v>45095.0</v>
       </c>
       <c r="D293" t="n">
         <v>1.0</v>
@@ -4244,10 +4244,10 @@
         <v>2023.0</v>
       </c>
       <c r="C294" t="n" s="2">
-        <v>45207.0</v>
+        <v>45102.0</v>
       </c>
       <c r="D294" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="295">
@@ -4258,10 +4258,10 @@
         <v>2023.0</v>
       </c>
       <c r="C295" t="n" s="2">
-        <v>45214.0</v>
+        <v>45158.0</v>
       </c>
       <c r="D295" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="296">
@@ -4272,10 +4272,10 @@
         <v>2023.0</v>
       </c>
       <c r="C296" t="n" s="2">
-        <v>45221.0</v>
+        <v>45207.0</v>
       </c>
       <c r="D296" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="297">
@@ -4286,10 +4286,10 @@
         <v>2023.0</v>
       </c>
       <c r="C297" t="n" s="2">
-        <v>45249.0</v>
+        <v>45214.0</v>
       </c>
       <c r="D297" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="298">
@@ -4300,10 +4300,10 @@
         <v>2023.0</v>
       </c>
       <c r="C298" t="n" s="2">
-        <v>45256.0</v>
+        <v>45221.0</v>
       </c>
       <c r="D298" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="299">
@@ -4314,10 +4314,10 @@
         <v>2023.0</v>
       </c>
       <c r="C299" t="n" s="2">
-        <v>45263.0</v>
+        <v>45249.0</v>
       </c>
       <c r="D299" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="300">
@@ -4328,10 +4328,10 @@
         <v>2023.0</v>
       </c>
       <c r="C300" t="n" s="2">
-        <v>45270.0</v>
+        <v>45256.0</v>
       </c>
       <c r="D300" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="301">
@@ -4342,7 +4342,7 @@
         <v>2023.0</v>
       </c>
       <c r="C301" t="n" s="2">
-        <v>45277.0</v>
+        <v>45263.0</v>
       </c>
       <c r="D301" t="n">
         <v>4.0</v>
@@ -4356,7 +4356,7 @@
         <v>2023.0</v>
       </c>
       <c r="C302" t="n" s="2">
-        <v>45284.0</v>
+        <v>45270.0</v>
       </c>
       <c r="D302" t="n">
         <v>1.0</v>
@@ -4370,10 +4370,10 @@
         <v>2023.0</v>
       </c>
       <c r="C303" t="n" s="2">
-        <v>45291.0</v>
+        <v>45277.0</v>
       </c>
       <c r="D303" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="304">
@@ -4381,13 +4381,13 @@
         <v>6</v>
       </c>
       <c r="B304" t="n">
-        <v>2024.0</v>
+        <v>2023.0</v>
       </c>
       <c r="C304" t="n" s="2">
-        <v>45306.0</v>
+        <v>45284.0</v>
       </c>
       <c r="D304" t="n">
-        <v>7.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="305">
@@ -4395,13 +4395,13 @@
         <v>6</v>
       </c>
       <c r="B305" t="n">
-        <v>2024.0</v>
+        <v>2023.0</v>
       </c>
       <c r="C305" t="n" s="2">
-        <v>45313.0</v>
+        <v>45291.0</v>
       </c>
       <c r="D305" t="n">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="306">
@@ -4412,10 +4412,10 @@
         <v>2024.0</v>
       </c>
       <c r="C306" t="n" s="2">
-        <v>45320.0</v>
+        <v>45306.0</v>
       </c>
       <c r="D306" t="n">
-        <v>19.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="307">
@@ -4426,10 +4426,10 @@
         <v>2024.0</v>
       </c>
       <c r="C307" t="n" s="2">
-        <v>45327.0</v>
+        <v>45313.0</v>
       </c>
       <c r="D307" t="n">
-        <v>18.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="308">
@@ -4440,10 +4440,10 @@
         <v>2024.0</v>
       </c>
       <c r="C308" t="n" s="2">
-        <v>45334.0</v>
+        <v>45320.0</v>
       </c>
       <c r="D308" t="n">
-        <v>9.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="309">
@@ -4454,10 +4454,10 @@
         <v>2024.0</v>
       </c>
       <c r="C309" t="n" s="2">
-        <v>45341.0</v>
+        <v>45327.0</v>
       </c>
       <c r="D309" t="n">
-        <v>12.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="310">
@@ -4468,10 +4468,10 @@
         <v>2024.0</v>
       </c>
       <c r="C310" t="n" s="2">
-        <v>45348.0</v>
+        <v>45334.0</v>
       </c>
       <c r="D310" t="n">
-        <v>12.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="311">
@@ -4482,10 +4482,10 @@
         <v>2024.0</v>
       </c>
       <c r="C311" t="n" s="2">
-        <v>45355.0</v>
+        <v>45341.0</v>
       </c>
       <c r="D311" t="n">
-        <v>10.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="312">
@@ -4496,7 +4496,7 @@
         <v>2024.0</v>
       </c>
       <c r="C312" t="n" s="2">
-        <v>45362.0</v>
+        <v>45348.0</v>
       </c>
       <c r="D312" t="n">
         <v>12.0</v>
@@ -4510,10 +4510,10 @@
         <v>2024.0</v>
       </c>
       <c r="C313" t="n" s="2">
-        <v>45369.0</v>
+        <v>45355.0</v>
       </c>
       <c r="D313" t="n">
-        <v>13.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="314">
@@ -4524,10 +4524,10 @@
         <v>2024.0</v>
       </c>
       <c r="C314" t="n" s="2">
-        <v>45376.0</v>
+        <v>45362.0</v>
       </c>
       <c r="D314" t="n">
-        <v>18.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="315">
@@ -4538,10 +4538,10 @@
         <v>2024.0</v>
       </c>
       <c r="C315" t="n" s="2">
-        <v>45383.0</v>
+        <v>45369.0</v>
       </c>
       <c r="D315" t="n">
-        <v>12.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="316">
@@ -4552,10 +4552,10 @@
         <v>2024.0</v>
       </c>
       <c r="C316" t="n" s="2">
-        <v>45390.0</v>
+        <v>45376.0</v>
       </c>
       <c r="D316" t="n">
-        <v>6.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="317">
@@ -4566,10 +4566,10 @@
         <v>2024.0</v>
       </c>
       <c r="C317" t="n" s="2">
-        <v>45397.0</v>
+        <v>45383.0</v>
       </c>
       <c r="D317" t="n">
-        <v>10.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="318">
@@ -4580,10 +4580,10 @@
         <v>2024.0</v>
       </c>
       <c r="C318" t="n" s="2">
-        <v>45404.0</v>
+        <v>45390.0</v>
       </c>
       <c r="D318" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="319">
@@ -4594,10 +4594,10 @@
         <v>2024.0</v>
       </c>
       <c r="C319" t="n" s="2">
-        <v>45411.0</v>
+        <v>45397.0</v>
       </c>
       <c r="D319" t="n">
-        <v>2.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="320">
@@ -4608,10 +4608,10 @@
         <v>2024.0</v>
       </c>
       <c r="C320" t="n" s="2">
-        <v>45418.0</v>
+        <v>45404.0</v>
       </c>
       <c r="D320" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="321">
@@ -4622,10 +4622,10 @@
         <v>2024.0</v>
       </c>
       <c r="C321" t="n" s="2">
-        <v>45425.0</v>
+        <v>45411.0</v>
       </c>
       <c r="D321" t="n">
-        <v>9.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="322">
@@ -4636,10 +4636,10 @@
         <v>2024.0</v>
       </c>
       <c r="C322" t="n" s="2">
-        <v>45432.0</v>
+        <v>45418.0</v>
       </c>
       <c r="D322" t="n">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="323">
@@ -4650,10 +4650,10 @@
         <v>2024.0</v>
       </c>
       <c r="C323" t="n" s="2">
-        <v>45439.0</v>
+        <v>45425.0</v>
       </c>
       <c r="D323" t="n">
-        <v>6.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="324">
@@ -4664,10 +4664,10 @@
         <v>2024.0</v>
       </c>
       <c r="C324" t="n" s="2">
-        <v>45446.0</v>
+        <v>45432.0</v>
       </c>
       <c r="D324" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="325">
@@ -4678,10 +4678,10 @@
         <v>2024.0</v>
       </c>
       <c r="C325" t="n" s="2">
-        <v>45453.0</v>
+        <v>45439.0</v>
       </c>
       <c r="D325" t="n">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="326">
@@ -4692,10 +4692,10 @@
         <v>2024.0</v>
       </c>
       <c r="C326" t="n" s="2">
-        <v>45460.0</v>
+        <v>45446.0</v>
       </c>
       <c r="D326" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="327">
@@ -4706,7 +4706,7 @@
         <v>2024.0</v>
       </c>
       <c r="C327" t="n" s="2">
-        <v>45467.0</v>
+        <v>45453.0</v>
       </c>
       <c r="D327" t="n">
         <v>4.0</v>
@@ -4720,10 +4720,10 @@
         <v>2024.0</v>
       </c>
       <c r="C328" t="n" s="2">
-        <v>45474.0</v>
+        <v>45460.0</v>
       </c>
       <c r="D328" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="329">
@@ -4734,10 +4734,10 @@
         <v>2024.0</v>
       </c>
       <c r="C329" t="n" s="2">
-        <v>45481.0</v>
+        <v>45467.0</v>
       </c>
       <c r="D329" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="330">
@@ -4748,7 +4748,7 @@
         <v>2024.0</v>
       </c>
       <c r="C330" t="n" s="2">
-        <v>45488.0</v>
+        <v>45474.0</v>
       </c>
       <c r="D330" t="n">
         <v>2.0</v>
@@ -4762,10 +4762,10 @@
         <v>2024.0</v>
       </c>
       <c r="C331" t="n" s="2">
-        <v>45495.0</v>
+        <v>45481.0</v>
       </c>
       <c r="D331" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="332">
@@ -4776,7 +4776,7 @@
         <v>2024.0</v>
       </c>
       <c r="C332" t="n" s="2">
-        <v>45502.0</v>
+        <v>45488.0</v>
       </c>
       <c r="D332" t="n">
         <v>2.0</v>
@@ -4790,10 +4790,10 @@
         <v>2024.0</v>
       </c>
       <c r="C333" t="n" s="2">
-        <v>45509.0</v>
+        <v>45495.0</v>
       </c>
       <c r="D333" t="n">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="334">
@@ -4804,10 +4804,10 @@
         <v>2024.0</v>
       </c>
       <c r="C334" t="n" s="2">
-        <v>45523.0</v>
+        <v>45502.0</v>
       </c>
       <c r="D334" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="335">
@@ -4818,7 +4818,7 @@
         <v>2024.0</v>
       </c>
       <c r="C335" t="n" s="2">
-        <v>45551.0</v>
+        <v>45509.0</v>
       </c>
       <c r="D335" t="n">
         <v>1.0</v>
@@ -4832,7 +4832,7 @@
         <v>2024.0</v>
       </c>
       <c r="C336" t="n" s="2">
-        <v>45558.0</v>
+        <v>45523.0</v>
       </c>
       <c r="D336" t="n">
         <v>1.0</v>
@@ -4846,10 +4846,10 @@
         <v>2024.0</v>
       </c>
       <c r="C337" t="n" s="2">
-        <v>45572.0</v>
+        <v>45551.0</v>
       </c>
       <c r="D337" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="338">
@@ -4860,7 +4860,7 @@
         <v>2024.0</v>
       </c>
       <c r="C338" t="n" s="2">
-        <v>45593.0</v>
+        <v>45558.0</v>
       </c>
       <c r="D338" t="n">
         <v>1.0</v>
@@ -4874,7 +4874,7 @@
         <v>2024.0</v>
       </c>
       <c r="C339" t="n" s="2">
-        <v>45614.0</v>
+        <v>45572.0</v>
       </c>
       <c r="D339" t="n">
         <v>2.0</v>
@@ -4888,7 +4888,7 @@
         <v>2024.0</v>
       </c>
       <c r="C340" t="n" s="2">
-        <v>45621.0</v>
+        <v>45593.0</v>
       </c>
       <c r="D340" t="n">
         <v>1.0</v>
@@ -4902,10 +4902,10 @@
         <v>2024.0</v>
       </c>
       <c r="C341" t="n" s="2">
-        <v>45635.0</v>
+        <v>45614.0</v>
       </c>
       <c r="D341" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="342">
@@ -4916,7 +4916,7 @@
         <v>2024.0</v>
       </c>
       <c r="C342" t="n" s="2">
-        <v>45649.0</v>
+        <v>45621.0</v>
       </c>
       <c r="D342" t="n">
         <v>1.0</v>
@@ -4927,13 +4927,13 @@
         <v>6</v>
       </c>
       <c r="B343" t="n">
-        <v>2025.0</v>
+        <v>2024.0</v>
       </c>
       <c r="C343" t="n" s="2">
-        <v>45665.0</v>
+        <v>45635.0</v>
       </c>
       <c r="D343" t="n">
-        <v>9.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="344">
@@ -4941,13 +4941,13 @@
         <v>6</v>
       </c>
       <c r="B344" t="n">
-        <v>2025.0</v>
+        <v>2024.0</v>
       </c>
       <c r="C344" t="n" s="2">
-        <v>45672.0</v>
+        <v>45649.0</v>
       </c>
       <c r="D344" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="345">
@@ -4958,10 +4958,10 @@
         <v>2025.0</v>
       </c>
       <c r="C345" t="n" s="2">
-        <v>45679.0</v>
+        <v>45665.0</v>
       </c>
       <c r="D345" t="n">
-        <v>1.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="346">
@@ -4972,10 +4972,10 @@
         <v>2025.0</v>
       </c>
       <c r="C346" t="n" s="2">
-        <v>45686.0</v>
+        <v>45672.0</v>
       </c>
       <c r="D346" t="n">
-        <v>8.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="347">
@@ -4986,10 +4986,10 @@
         <v>2025.0</v>
       </c>
       <c r="C347" t="n" s="2">
-        <v>45693.0</v>
+        <v>45679.0</v>
       </c>
       <c r="D347" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="348">
@@ -5000,10 +5000,10 @@
         <v>2025.0</v>
       </c>
       <c r="C348" t="n" s="2">
-        <v>45700.0</v>
+        <v>45686.0</v>
       </c>
       <c r="D348" t="n">
-        <v>5.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="349">
@@ -5014,10 +5014,10 @@
         <v>2025.0</v>
       </c>
       <c r="C349" t="n" s="2">
-        <v>45707.0</v>
+        <v>45693.0</v>
       </c>
       <c r="D349" t="n">
-        <v>8.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="350">
@@ -5028,10 +5028,10 @@
         <v>2025.0</v>
       </c>
       <c r="C350" t="n" s="2">
-        <v>45714.0</v>
+        <v>45700.0</v>
       </c>
       <c r="D350" t="n">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="351">
@@ -5042,7 +5042,7 @@
         <v>2025.0</v>
       </c>
       <c r="C351" t="n" s="2">
-        <v>45721.0</v>
+        <v>45707.0</v>
       </c>
       <c r="D351" t="n">
         <v>8.0</v>
@@ -5056,10 +5056,10 @@
         <v>2025.0</v>
       </c>
       <c r="C352" t="n" s="2">
-        <v>45728.0</v>
+        <v>45714.0</v>
       </c>
       <c r="D352" t="n">
-        <v>7.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="353">
@@ -5070,10 +5070,10 @@
         <v>2025.0</v>
       </c>
       <c r="C353" t="n" s="2">
-        <v>45735.0</v>
+        <v>45721.0</v>
       </c>
       <c r="D353" t="n">
-        <v>4.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="354">
@@ -5084,10 +5084,10 @@
         <v>2025.0</v>
       </c>
       <c r="C354" t="n" s="2">
-        <v>45742.0</v>
+        <v>45728.0</v>
       </c>
       <c r="D354" t="n">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="355">
@@ -5098,10 +5098,10 @@
         <v>2025.0</v>
       </c>
       <c r="C355" t="n" s="2">
-        <v>45749.0</v>
+        <v>45735.0</v>
       </c>
       <c r="D355" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="356">
@@ -5112,10 +5112,10 @@
         <v>2025.0</v>
       </c>
       <c r="C356" t="n" s="2">
-        <v>45756.0</v>
+        <v>45742.0</v>
       </c>
       <c r="D356" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="357">
@@ -5126,10 +5126,10 @@
         <v>2025.0</v>
       </c>
       <c r="C357" t="n" s="2">
-        <v>45763.0</v>
+        <v>45749.0</v>
       </c>
       <c r="D357" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="358">
@@ -5140,10 +5140,10 @@
         <v>2025.0</v>
       </c>
       <c r="C358" t="n" s="2">
-        <v>45770.0</v>
+        <v>45756.0</v>
       </c>
       <c r="D358" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="359">
@@ -5154,10 +5154,10 @@
         <v>2025.0</v>
       </c>
       <c r="C359" t="n" s="2">
-        <v>45777.0</v>
+        <v>45763.0</v>
       </c>
       <c r="D359" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="360">
@@ -5168,10 +5168,10 @@
         <v>2025.0</v>
       </c>
       <c r="C360" t="n" s="2">
-        <v>45784.0</v>
+        <v>45770.0</v>
       </c>
       <c r="D360" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="361">
@@ -5182,7 +5182,7 @@
         <v>2025.0</v>
       </c>
       <c r="C361" t="n" s="2">
-        <v>45791.0</v>
+        <v>45777.0</v>
       </c>
       <c r="D361" t="n">
         <v>1.0</v>
@@ -5196,7 +5196,7 @@
         <v>2025.0</v>
       </c>
       <c r="C362" t="n" s="2">
-        <v>45840.0</v>
+        <v>45784.0</v>
       </c>
       <c r="D362" t="n">
         <v>1.0</v>
@@ -5210,7 +5210,7 @@
         <v>2025.0</v>
       </c>
       <c r="C363" t="n" s="2">
-        <v>46001.0</v>
+        <v>45791.0</v>
       </c>
       <c r="D363" t="n">
         <v>1.0</v>
@@ -5221,10 +5221,10 @@
         <v>6</v>
       </c>
       <c r="B364" t="n">
-        <v>2026.0</v>
+        <v>2025.0</v>
       </c>
       <c r="C364" t="n" s="2">
-        <v>46037.0</v>
+        <v>45840.0</v>
       </c>
       <c r="D364" t="n">
         <v>1.0</v>
@@ -5232,13 +5232,13 @@
     </row>
     <row r="365">
       <c r="A365" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B365" t="n">
-        <v>2021.0</v>
+        <v>2025.0</v>
       </c>
       <c r="C365" t="n" s="2">
-        <v>44561.0</v>
+        <v>46001.0</v>
       </c>
       <c r="D365" t="n">
         <v>1.0</v>
@@ -5246,13 +5246,13 @@
     </row>
     <row r="366">
       <c r="A366" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B366" t="n">
-        <v>2022.0</v>
+        <v>2026.0</v>
       </c>
       <c r="C366" t="n" s="2">
-        <v>44569.0</v>
+        <v>46037.0</v>
       </c>
       <c r="D366" t="n">
         <v>1.0</v>
@@ -5263,13 +5263,13 @@
         <v>7</v>
       </c>
       <c r="B367" t="n">
-        <v>2022.0</v>
+        <v>2021.0</v>
       </c>
       <c r="C367" t="n" s="2">
-        <v>44576.0</v>
+        <v>44561.0</v>
       </c>
       <c r="D367" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="368">
@@ -5280,10 +5280,10 @@
         <v>2022.0</v>
       </c>
       <c r="C368" t="n" s="2">
-        <v>44583.0</v>
+        <v>44569.0</v>
       </c>
       <c r="D368" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="369">
@@ -5294,10 +5294,10 @@
         <v>2022.0</v>
       </c>
       <c r="C369" t="n" s="2">
-        <v>44590.0</v>
+        <v>44576.0</v>
       </c>
       <c r="D369" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="370">
@@ -5308,10 +5308,10 @@
         <v>2022.0</v>
       </c>
       <c r="C370" t="n" s="2">
-        <v>44604.0</v>
+        <v>44583.0</v>
       </c>
       <c r="D370" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="371">
@@ -5322,10 +5322,10 @@
         <v>2022.0</v>
       </c>
       <c r="C371" t="n" s="2">
-        <v>44611.0</v>
+        <v>44590.0</v>
       </c>
       <c r="D371" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="372">
@@ -5336,10 +5336,10 @@
         <v>2022.0</v>
       </c>
       <c r="C372" t="n" s="2">
-        <v>44618.0</v>
+        <v>44604.0</v>
       </c>
       <c r="D372" t="n">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="373">
@@ -5350,10 +5350,10 @@
         <v>2022.0</v>
       </c>
       <c r="C373" t="n" s="2">
-        <v>44625.0</v>
+        <v>44611.0</v>
       </c>
       <c r="D373" t="n">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="374">
@@ -5364,10 +5364,10 @@
         <v>2022.0</v>
       </c>
       <c r="C374" t="n" s="2">
-        <v>44632.0</v>
+        <v>44618.0</v>
       </c>
       <c r="D374" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="375">
@@ -5378,10 +5378,10 @@
         <v>2022.0</v>
       </c>
       <c r="C375" t="n" s="2">
-        <v>44639.0</v>
+        <v>44625.0</v>
       </c>
       <c r="D375" t="n">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="376">
@@ -5392,7 +5392,7 @@
         <v>2022.0</v>
       </c>
       <c r="C376" t="n" s="2">
-        <v>44646.0</v>
+        <v>44632.0</v>
       </c>
       <c r="D376" t="n">
         <v>3.0</v>
@@ -5406,10 +5406,10 @@
         <v>2022.0</v>
       </c>
       <c r="C377" t="n" s="2">
-        <v>44653.0</v>
+        <v>44639.0</v>
       </c>
       <c r="D377" t="n">
-        <v>9.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="378">
@@ -5420,10 +5420,10 @@
         <v>2022.0</v>
       </c>
       <c r="C378" t="n" s="2">
-        <v>44660.0</v>
+        <v>44646.0</v>
       </c>
       <c r="D378" t="n">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="379">
@@ -5434,10 +5434,10 @@
         <v>2022.0</v>
       </c>
       <c r="C379" t="n" s="2">
-        <v>44667.0</v>
+        <v>44653.0</v>
       </c>
       <c r="D379" t="n">
-        <v>2.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="380">
@@ -5448,10 +5448,10 @@
         <v>2022.0</v>
       </c>
       <c r="C380" t="n" s="2">
-        <v>44674.0</v>
+        <v>44660.0</v>
       </c>
       <c r="D380" t="n">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="381">
@@ -5462,7 +5462,7 @@
         <v>2022.0</v>
       </c>
       <c r="C381" t="n" s="2">
-        <v>44681.0</v>
+        <v>44667.0</v>
       </c>
       <c r="D381" t="n">
         <v>2.0</v>
@@ -5476,10 +5476,10 @@
         <v>2022.0</v>
       </c>
       <c r="C382" t="n" s="2">
-        <v>44688.0</v>
+        <v>44674.0</v>
       </c>
       <c r="D382" t="n">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="383">
@@ -5490,10 +5490,10 @@
         <v>2022.0</v>
       </c>
       <c r="C383" t="n" s="2">
-        <v>44695.0</v>
+        <v>44681.0</v>
       </c>
       <c r="D383" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="384">
@@ -5504,10 +5504,10 @@
         <v>2022.0</v>
       </c>
       <c r="C384" t="n" s="2">
-        <v>44702.0</v>
+        <v>44688.0</v>
       </c>
       <c r="D384" t="n">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="385">
@@ -5518,10 +5518,10 @@
         <v>2022.0</v>
       </c>
       <c r="C385" t="n" s="2">
-        <v>44709.0</v>
+        <v>44695.0</v>
       </c>
       <c r="D385" t="n">
-        <v>8.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="386">
@@ -5532,10 +5532,10 @@
         <v>2022.0</v>
       </c>
       <c r="C386" t="n" s="2">
-        <v>44716.0</v>
+        <v>44702.0</v>
       </c>
       <c r="D386" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="387">
@@ -5546,10 +5546,10 @@
         <v>2022.0</v>
       </c>
       <c r="C387" t="n" s="2">
-        <v>44723.0</v>
+        <v>44709.0</v>
       </c>
       <c r="D387" t="n">
-        <v>2.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="388">
@@ -5560,10 +5560,10 @@
         <v>2022.0</v>
       </c>
       <c r="C388" t="n" s="2">
-        <v>44730.0</v>
+        <v>44716.0</v>
       </c>
       <c r="D388" t="n">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="389">
@@ -5574,10 +5574,10 @@
         <v>2022.0</v>
       </c>
       <c r="C389" t="n" s="2">
-        <v>44737.0</v>
+        <v>44723.0</v>
       </c>
       <c r="D389" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="390">
@@ -5588,10 +5588,10 @@
         <v>2022.0</v>
       </c>
       <c r="C390" t="n" s="2">
-        <v>44744.0</v>
+        <v>44730.0</v>
       </c>
       <c r="D390" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="391">
@@ -5602,7 +5602,7 @@
         <v>2022.0</v>
       </c>
       <c r="C391" t="n" s="2">
-        <v>44751.0</v>
+        <v>44737.0</v>
       </c>
       <c r="D391" t="n">
         <v>4.0</v>
@@ -5616,10 +5616,10 @@
         <v>2022.0</v>
       </c>
       <c r="C392" t="n" s="2">
-        <v>44758.0</v>
+        <v>44744.0</v>
       </c>
       <c r="D392" t="n">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="393">
@@ -5630,10 +5630,10 @@
         <v>2022.0</v>
       </c>
       <c r="C393" t="n" s="2">
-        <v>44765.0</v>
+        <v>44751.0</v>
       </c>
       <c r="D393" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="394">
@@ -5644,10 +5644,10 @@
         <v>2022.0</v>
       </c>
       <c r="C394" t="n" s="2">
-        <v>44779.0</v>
+        <v>44758.0</v>
       </c>
       <c r="D394" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="395">
@@ -5658,7 +5658,7 @@
         <v>2022.0</v>
       </c>
       <c r="C395" t="n" s="2">
-        <v>44786.0</v>
+        <v>44765.0</v>
       </c>
       <c r="D395" t="n">
         <v>1.0</v>
@@ -5672,10 +5672,10 @@
         <v>2022.0</v>
       </c>
       <c r="C396" t="n" s="2">
-        <v>44863.0</v>
+        <v>44779.0</v>
       </c>
       <c r="D396" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="397">
@@ -5686,7 +5686,7 @@
         <v>2022.0</v>
       </c>
       <c r="C397" t="n" s="2">
-        <v>44870.0</v>
+        <v>44786.0</v>
       </c>
       <c r="D397" t="n">
         <v>1.0</v>
@@ -5700,7 +5700,7 @@
         <v>2022.0</v>
       </c>
       <c r="C398" t="n" s="2">
-        <v>44884.0</v>
+        <v>44863.0</v>
       </c>
       <c r="D398" t="n">
         <v>2.0</v>
@@ -5714,10 +5714,10 @@
         <v>2022.0</v>
       </c>
       <c r="C399" t="n" s="2">
-        <v>44891.0</v>
+        <v>44870.0</v>
       </c>
       <c r="D399" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="400">
@@ -5728,10 +5728,10 @@
         <v>2022.0</v>
       </c>
       <c r="C400" t="n" s="2">
-        <v>44898.0</v>
+        <v>44884.0</v>
       </c>
       <c r="D400" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="401">
@@ -5742,10 +5742,10 @@
         <v>2022.0</v>
       </c>
       <c r="C401" t="n" s="2">
-        <v>44912.0</v>
+        <v>44891.0</v>
       </c>
       <c r="D401" t="n">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="402">
@@ -5756,10 +5756,10 @@
         <v>2022.0</v>
       </c>
       <c r="C402" t="n" s="2">
-        <v>44919.0</v>
+        <v>44898.0</v>
       </c>
       <c r="D402" t="n">
-        <v>7.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="403">
@@ -5770,10 +5770,10 @@
         <v>2022.0</v>
       </c>
       <c r="C403" t="n" s="2">
-        <v>44926.0</v>
+        <v>44912.0</v>
       </c>
       <c r="D403" t="n">
-        <v>12.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="404">
@@ -5781,13 +5781,13 @@
         <v>7</v>
       </c>
       <c r="B404" t="n">
-        <v>2023.0</v>
+        <v>2022.0</v>
       </c>
       <c r="C404" t="n" s="2">
-        <v>44934.0</v>
+        <v>44919.0</v>
       </c>
       <c r="D404" t="n">
-        <v>4.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="405">
@@ -5795,13 +5795,13 @@
         <v>7</v>
       </c>
       <c r="B405" t="n">
-        <v>2023.0</v>
+        <v>2022.0</v>
       </c>
       <c r="C405" t="n" s="2">
-        <v>44941.0</v>
+        <v>44926.0</v>
       </c>
       <c r="D405" t="n">
-        <v>16.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="406">
@@ -5812,10 +5812,10 @@
         <v>2023.0</v>
       </c>
       <c r="C406" t="n" s="2">
-        <v>44948.0</v>
+        <v>44934.0</v>
       </c>
       <c r="D406" t="n">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="407">
@@ -5826,10 +5826,10 @@
         <v>2023.0</v>
       </c>
       <c r="C407" t="n" s="2">
-        <v>44955.0</v>
+        <v>44941.0</v>
       </c>
       <c r="D407" t="n">
-        <v>19.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="408">
@@ -5840,10 +5840,10 @@
         <v>2023.0</v>
       </c>
       <c r="C408" t="n" s="2">
-        <v>44962.0</v>
+        <v>44948.0</v>
       </c>
       <c r="D408" t="n">
-        <v>22.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="409">
@@ -5854,10 +5854,10 @@
         <v>2023.0</v>
       </c>
       <c r="C409" t="n" s="2">
-        <v>44969.0</v>
+        <v>44955.0</v>
       </c>
       <c r="D409" t="n">
-        <v>9.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="410">
@@ -5868,7 +5868,7 @@
         <v>2023.0</v>
       </c>
       <c r="C410" t="n" s="2">
-        <v>44976.0</v>
+        <v>44962.0</v>
       </c>
       <c r="D410" t="n">
         <v>22.0</v>
@@ -5882,10 +5882,10 @@
         <v>2023.0</v>
       </c>
       <c r="C411" t="n" s="2">
-        <v>44983.0</v>
+        <v>44969.0</v>
       </c>
       <c r="D411" t="n">
-        <v>29.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="412">
@@ -5896,10 +5896,10 @@
         <v>2023.0</v>
       </c>
       <c r="C412" t="n" s="2">
-        <v>44990.0</v>
+        <v>44976.0</v>
       </c>
       <c r="D412" t="n">
-        <v>5.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="413">
@@ -5910,10 +5910,10 @@
         <v>2023.0</v>
       </c>
       <c r="C413" t="n" s="2">
-        <v>44997.0</v>
+        <v>44983.0</v>
       </c>
       <c r="D413" t="n">
-        <v>24.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="414">
@@ -5924,10 +5924,10 @@
         <v>2023.0</v>
       </c>
       <c r="C414" t="n" s="2">
-        <v>45004.0</v>
+        <v>44990.0</v>
       </c>
       <c r="D414" t="n">
-        <v>8.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="415">
@@ -5938,10 +5938,10 @@
         <v>2023.0</v>
       </c>
       <c r="C415" t="n" s="2">
-        <v>45011.0</v>
+        <v>44997.0</v>
       </c>
       <c r="D415" t="n">
-        <v>10.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="416">
@@ -5952,10 +5952,10 @@
         <v>2023.0</v>
       </c>
       <c r="C416" t="n" s="2">
-        <v>45018.0</v>
+        <v>45004.0</v>
       </c>
       <c r="D416" t="n">
-        <v>18.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="417">
@@ -5966,10 +5966,10 @@
         <v>2023.0</v>
       </c>
       <c r="C417" t="n" s="2">
-        <v>45025.0</v>
+        <v>45011.0</v>
       </c>
       <c r="D417" t="n">
-        <v>13.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="418">
@@ -5980,7 +5980,7 @@
         <v>2023.0</v>
       </c>
       <c r="C418" t="n" s="2">
-        <v>45032.0</v>
+        <v>45018.0</v>
       </c>
       <c r="D418" t="n">
         <v>18.0</v>
@@ -5994,10 +5994,10 @@
         <v>2023.0</v>
       </c>
       <c r="C419" t="n" s="2">
-        <v>45039.0</v>
+        <v>45025.0</v>
       </c>
       <c r="D419" t="n">
-        <v>15.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="420">
@@ -6008,10 +6008,10 @@
         <v>2023.0</v>
       </c>
       <c r="C420" t="n" s="2">
-        <v>45046.0</v>
+        <v>45032.0</v>
       </c>
       <c r="D420" t="n">
-        <v>12.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="421">
@@ -6022,10 +6022,10 @@
         <v>2023.0</v>
       </c>
       <c r="C421" t="n" s="2">
-        <v>45053.0</v>
+        <v>45039.0</v>
       </c>
       <c r="D421" t="n">
-        <v>6.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="422">
@@ -6036,10 +6036,10 @@
         <v>2023.0</v>
       </c>
       <c r="C422" t="n" s="2">
-        <v>45060.0</v>
+        <v>45046.0</v>
       </c>
       <c r="D422" t="n">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="423">
@@ -6050,10 +6050,10 @@
         <v>2023.0</v>
       </c>
       <c r="C423" t="n" s="2">
-        <v>45067.0</v>
+        <v>45053.0</v>
       </c>
       <c r="D423" t="n">
-        <v>8.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="424">
@@ -6064,10 +6064,10 @@
         <v>2023.0</v>
       </c>
       <c r="C424" t="n" s="2">
-        <v>45074.0</v>
+        <v>45060.0</v>
       </c>
       <c r="D424" t="n">
-        <v>8.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="425">
@@ -6078,10 +6078,10 @@
         <v>2023.0</v>
       </c>
       <c r="C425" t="n" s="2">
-        <v>45081.0</v>
+        <v>45067.0</v>
       </c>
       <c r="D425" t="n">
-        <v>5.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="426">
@@ -6092,10 +6092,10 @@
         <v>2023.0</v>
       </c>
       <c r="C426" t="n" s="2">
-        <v>45088.0</v>
+        <v>45074.0</v>
       </c>
       <c r="D426" t="n">
-        <v>2.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="427">
@@ -6106,7 +6106,7 @@
         <v>2023.0</v>
       </c>
       <c r="C427" t="n" s="2">
-        <v>45095.0</v>
+        <v>45081.0</v>
       </c>
       <c r="D427" t="n">
         <v>5.0</v>
@@ -6120,10 +6120,10 @@
         <v>2023.0</v>
       </c>
       <c r="C428" t="n" s="2">
-        <v>45102.0</v>
+        <v>45088.0</v>
       </c>
       <c r="D428" t="n">
-        <v>10.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="429">
@@ -6134,10 +6134,10 @@
         <v>2023.0</v>
       </c>
       <c r="C429" t="n" s="2">
-        <v>45109.0</v>
+        <v>45095.0</v>
       </c>
       <c r="D429" t="n">
-        <v>9.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="430">
@@ -6148,10 +6148,10 @@
         <v>2023.0</v>
       </c>
       <c r="C430" t="n" s="2">
-        <v>45116.0</v>
+        <v>45102.0</v>
       </c>
       <c r="D430" t="n">
-        <v>3.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="431">
@@ -6162,10 +6162,10 @@
         <v>2023.0</v>
       </c>
       <c r="C431" t="n" s="2">
-        <v>45123.0</v>
+        <v>45109.0</v>
       </c>
       <c r="D431" t="n">
-        <v>6.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="432">
@@ -6176,10 +6176,10 @@
         <v>2023.0</v>
       </c>
       <c r="C432" t="n" s="2">
-        <v>45130.0</v>
+        <v>45116.0</v>
       </c>
       <c r="D432" t="n">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="433">
@@ -6190,10 +6190,10 @@
         <v>2023.0</v>
       </c>
       <c r="C433" t="n" s="2">
-        <v>45137.0</v>
+        <v>45123.0</v>
       </c>
       <c r="D433" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="434">
@@ -6204,10 +6204,10 @@
         <v>2023.0</v>
       </c>
       <c r="C434" t="n" s="2">
-        <v>45144.0</v>
+        <v>45130.0</v>
       </c>
       <c r="D434" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="435">
@@ -6218,7 +6218,7 @@
         <v>2023.0</v>
       </c>
       <c r="C435" t="n" s="2">
-        <v>45151.0</v>
+        <v>45137.0</v>
       </c>
       <c r="D435" t="n">
         <v>2.0</v>
@@ -6232,7 +6232,7 @@
         <v>2023.0</v>
       </c>
       <c r="C436" t="n" s="2">
-        <v>45165.0</v>
+        <v>45144.0</v>
       </c>
       <c r="D436" t="n">
         <v>2.0</v>
@@ -6246,7 +6246,7 @@
         <v>2023.0</v>
       </c>
       <c r="C437" t="n" s="2">
-        <v>45172.0</v>
+        <v>45151.0</v>
       </c>
       <c r="D437" t="n">
         <v>2.0</v>
@@ -6260,10 +6260,10 @@
         <v>2023.0</v>
       </c>
       <c r="C438" t="n" s="2">
-        <v>45179.0</v>
+        <v>45165.0</v>
       </c>
       <c r="D438" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="439">
@@ -6274,10 +6274,10 @@
         <v>2023.0</v>
       </c>
       <c r="C439" t="n" s="2">
-        <v>45186.0</v>
+        <v>45172.0</v>
       </c>
       <c r="D439" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="440">
@@ -6288,7 +6288,7 @@
         <v>2023.0</v>
       </c>
       <c r="C440" t="n" s="2">
-        <v>45193.0</v>
+        <v>45179.0</v>
       </c>
       <c r="D440" t="n">
         <v>1.0</v>
@@ -6302,7 +6302,7 @@
         <v>2023.0</v>
       </c>
       <c r="C441" t="n" s="2">
-        <v>45200.0</v>
+        <v>45186.0</v>
       </c>
       <c r="D441" t="n">
         <v>1.0</v>
@@ -6316,7 +6316,7 @@
         <v>2023.0</v>
       </c>
       <c r="C442" t="n" s="2">
-        <v>45207.0</v>
+        <v>45193.0</v>
       </c>
       <c r="D442" t="n">
         <v>1.0</v>
@@ -6330,7 +6330,7 @@
         <v>2023.0</v>
       </c>
       <c r="C443" t="n" s="2">
-        <v>45235.0</v>
+        <v>45200.0</v>
       </c>
       <c r="D443" t="n">
         <v>1.0</v>
@@ -6344,10 +6344,10 @@
         <v>2023.0</v>
       </c>
       <c r="C444" t="n" s="2">
-        <v>45242.0</v>
+        <v>45207.0</v>
       </c>
       <c r="D444" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="445">
@@ -6358,10 +6358,10 @@
         <v>2023.0</v>
       </c>
       <c r="C445" t="n" s="2">
-        <v>45249.0</v>
+        <v>45235.0</v>
       </c>
       <c r="D445" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="446">
@@ -6372,10 +6372,10 @@
         <v>2023.0</v>
       </c>
       <c r="C446" t="n" s="2">
-        <v>45256.0</v>
+        <v>45242.0</v>
       </c>
       <c r="D446" t="n">
-        <v>9.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="447">
@@ -6386,10 +6386,10 @@
         <v>2023.0</v>
       </c>
       <c r="C447" t="n" s="2">
-        <v>45263.0</v>
+        <v>45249.0</v>
       </c>
       <c r="D447" t="n">
-        <v>12.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="448">
@@ -6400,10 +6400,10 @@
         <v>2023.0</v>
       </c>
       <c r="C448" t="n" s="2">
-        <v>45270.0</v>
+        <v>45256.0</v>
       </c>
       <c r="D448" t="n">
-        <v>6.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="449">
@@ -6414,10 +6414,10 @@
         <v>2023.0</v>
       </c>
       <c r="C449" t="n" s="2">
-        <v>45277.0</v>
+        <v>45263.0</v>
       </c>
       <c r="D449" t="n">
-        <v>7.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="450">
@@ -6428,10 +6428,10 @@
         <v>2023.0</v>
       </c>
       <c r="C450" t="n" s="2">
-        <v>45284.0</v>
+        <v>45270.0</v>
       </c>
       <c r="D450" t="n">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="451">
@@ -6442,10 +6442,10 @@
         <v>2023.0</v>
       </c>
       <c r="C451" t="n" s="2">
-        <v>45291.0</v>
+        <v>45277.0</v>
       </c>
       <c r="D451" t="n">
-        <v>13.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="452">
@@ -6453,13 +6453,13 @@
         <v>7</v>
       </c>
       <c r="B452" t="n">
-        <v>2024.0</v>
+        <v>2023.0</v>
       </c>
       <c r="C452" t="n" s="2">
-        <v>45299.0</v>
+        <v>45284.0</v>
       </c>
       <c r="D452" t="n">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="453">
@@ -6467,13 +6467,13 @@
         <v>7</v>
       </c>
       <c r="B453" t="n">
-        <v>2024.0</v>
+        <v>2023.0</v>
       </c>
       <c r="C453" t="n" s="2">
-        <v>45306.0</v>
+        <v>45291.0</v>
       </c>
       <c r="D453" t="n">
-        <v>11.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="454">
@@ -6484,10 +6484,10 @@
         <v>2024.0</v>
       </c>
       <c r="C454" t="n" s="2">
-        <v>45313.0</v>
+        <v>45299.0</v>
       </c>
       <c r="D454" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="455">
@@ -6498,10 +6498,10 @@
         <v>2024.0</v>
       </c>
       <c r="C455" t="n" s="2">
-        <v>45320.0</v>
+        <v>45306.0</v>
       </c>
       <c r="D455" t="n">
-        <v>2.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="456">
@@ -6512,10 +6512,10 @@
         <v>2024.0</v>
       </c>
       <c r="C456" t="n" s="2">
-        <v>45327.0</v>
+        <v>45313.0</v>
       </c>
       <c r="D456" t="n">
-        <v>9.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="457">
@@ -6526,10 +6526,10 @@
         <v>2024.0</v>
       </c>
       <c r="C457" t="n" s="2">
-        <v>45334.0</v>
+        <v>45320.0</v>
       </c>
       <c r="D457" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="458">
@@ -6540,10 +6540,10 @@
         <v>2024.0</v>
       </c>
       <c r="C458" t="n" s="2">
-        <v>45341.0</v>
+        <v>45327.0</v>
       </c>
       <c r="D458" t="n">
-        <v>21.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="459">
@@ -6554,10 +6554,10 @@
         <v>2024.0</v>
       </c>
       <c r="C459" t="n" s="2">
-        <v>45348.0</v>
+        <v>45334.0</v>
       </c>
       <c r="D459" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="460">
@@ -6568,10 +6568,10 @@
         <v>2024.0</v>
       </c>
       <c r="C460" t="n" s="2">
-        <v>45355.0</v>
+        <v>45341.0</v>
       </c>
       <c r="D460" t="n">
-        <v>9.0</v>
+        <v>21.0</v>
       </c>
     </row>
     <row r="461">
@@ -6582,10 +6582,10 @@
         <v>2024.0</v>
       </c>
       <c r="C461" t="n" s="2">
-        <v>45362.0</v>
+        <v>45348.0</v>
       </c>
       <c r="D461" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="462">
@@ -6596,10 +6596,10 @@
         <v>2024.0</v>
       </c>
       <c r="C462" t="n" s="2">
-        <v>45369.0</v>
+        <v>45355.0</v>
       </c>
       <c r="D462" t="n">
-        <v>14.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="463">
@@ -6610,7 +6610,7 @@
         <v>2024.0</v>
       </c>
       <c r="C463" t="n" s="2">
-        <v>45376.0</v>
+        <v>45362.0</v>
       </c>
       <c r="D463" t="n">
         <v>4.0</v>
@@ -6624,10 +6624,10 @@
         <v>2024.0</v>
       </c>
       <c r="C464" t="n" s="2">
-        <v>45383.0</v>
+        <v>45369.0</v>
       </c>
       <c r="D464" t="n">
-        <v>2.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="465">
@@ -6638,10 +6638,10 @@
         <v>2024.0</v>
       </c>
       <c r="C465" t="n" s="2">
-        <v>45390.0</v>
+        <v>45376.0</v>
       </c>
       <c r="D465" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="466">
@@ -6652,10 +6652,10 @@
         <v>2024.0</v>
       </c>
       <c r="C466" t="n" s="2">
-        <v>45397.0</v>
+        <v>45383.0</v>
       </c>
       <c r="D466" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="467">
@@ -6666,10 +6666,10 @@
         <v>2024.0</v>
       </c>
       <c r="C467" t="n" s="2">
-        <v>45404.0</v>
+        <v>45390.0</v>
       </c>
       <c r="D467" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="468">
@@ -6680,7 +6680,7 @@
         <v>2024.0</v>
       </c>
       <c r="C468" t="n" s="2">
-        <v>45411.0</v>
+        <v>45397.0</v>
       </c>
       <c r="D468" t="n">
         <v>1.0</v>
@@ -6694,7 +6694,7 @@
         <v>2024.0</v>
       </c>
       <c r="C469" t="n" s="2">
-        <v>45439.0</v>
+        <v>45404.0</v>
       </c>
       <c r="D469" t="n">
         <v>2.0</v>
@@ -6708,7 +6708,7 @@
         <v>2024.0</v>
       </c>
       <c r="C470" t="n" s="2">
-        <v>45446.0</v>
+        <v>45411.0</v>
       </c>
       <c r="D470" t="n">
         <v>1.0</v>
@@ -6722,10 +6722,10 @@
         <v>2024.0</v>
       </c>
       <c r="C471" t="n" s="2">
-        <v>45460.0</v>
+        <v>45439.0</v>
       </c>
       <c r="D471" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="472">
@@ -6736,7 +6736,7 @@
         <v>2024.0</v>
       </c>
       <c r="C472" t="n" s="2">
-        <v>45481.0</v>
+        <v>45446.0</v>
       </c>
       <c r="D472" t="n">
         <v>1.0</v>
@@ -6750,7 +6750,7 @@
         <v>2024.0</v>
       </c>
       <c r="C473" t="n" s="2">
-        <v>45516.0</v>
+        <v>45460.0</v>
       </c>
       <c r="D473" t="n">
         <v>1.0</v>
@@ -6764,7 +6764,7 @@
         <v>2024.0</v>
       </c>
       <c r="C474" t="n" s="2">
-        <v>45551.0</v>
+        <v>45481.0</v>
       </c>
       <c r="D474" t="n">
         <v>1.0</v>
@@ -6778,7 +6778,7 @@
         <v>2024.0</v>
       </c>
       <c r="C475" t="n" s="2">
-        <v>45579.0</v>
+        <v>45516.0</v>
       </c>
       <c r="D475" t="n">
         <v>1.0</v>
@@ -6792,7 +6792,7 @@
         <v>2024.0</v>
       </c>
       <c r="C476" t="n" s="2">
-        <v>45614.0</v>
+        <v>45551.0</v>
       </c>
       <c r="D476" t="n">
         <v>1.0</v>
@@ -6806,10 +6806,10 @@
         <v>2024.0</v>
       </c>
       <c r="C477" t="n" s="2">
-        <v>45635.0</v>
+        <v>45579.0</v>
       </c>
       <c r="D477" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="478">
@@ -6820,10 +6820,10 @@
         <v>2024.0</v>
       </c>
       <c r="C478" t="n" s="2">
-        <v>45642.0</v>
+        <v>45614.0</v>
       </c>
       <c r="D478" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="479">
@@ -6834,10 +6834,10 @@
         <v>2024.0</v>
       </c>
       <c r="C479" t="n" s="2">
-        <v>45649.0</v>
+        <v>45635.0</v>
       </c>
       <c r="D479" t="n">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="480">
@@ -6848,7 +6848,7 @@
         <v>2024.0</v>
       </c>
       <c r="C480" t="n" s="2">
-        <v>45656.0</v>
+        <v>45642.0</v>
       </c>
       <c r="D480" t="n">
         <v>2.0</v>
@@ -6859,13 +6859,13 @@
         <v>7</v>
       </c>
       <c r="B481" t="n">
-        <v>2025.0</v>
+        <v>2024.0</v>
       </c>
       <c r="C481" t="n" s="2">
-        <v>45665.0</v>
+        <v>45649.0</v>
       </c>
       <c r="D481" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="482">
@@ -6873,10 +6873,10 @@
         <v>7</v>
       </c>
       <c r="B482" t="n">
-        <v>2025.0</v>
+        <v>2024.0</v>
       </c>
       <c r="C482" t="n" s="2">
-        <v>45672.0</v>
+        <v>45656.0</v>
       </c>
       <c r="D482" t="n">
         <v>2.0</v>
@@ -6890,10 +6890,10 @@
         <v>2025.0</v>
       </c>
       <c r="C483" t="n" s="2">
-        <v>45686.0</v>
+        <v>45665.0</v>
       </c>
       <c r="D483" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="484">
@@ -6904,10 +6904,10 @@
         <v>2025.0</v>
       </c>
       <c r="C484" t="n" s="2">
-        <v>45693.0</v>
+        <v>45672.0</v>
       </c>
       <c r="D484" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="485">
@@ -6918,10 +6918,10 @@
         <v>2025.0</v>
       </c>
       <c r="C485" t="n" s="2">
-        <v>45700.0</v>
+        <v>45686.0</v>
       </c>
       <c r="D485" t="n">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="486">
@@ -6932,10 +6932,10 @@
         <v>2025.0</v>
       </c>
       <c r="C486" t="n" s="2">
-        <v>45707.0</v>
+        <v>45693.0</v>
       </c>
       <c r="D486" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="487">
@@ -6946,10 +6946,10 @@
         <v>2025.0</v>
       </c>
       <c r="C487" t="n" s="2">
-        <v>45714.0</v>
+        <v>45700.0</v>
       </c>
       <c r="D487" t="n">
-        <v>8.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="488">
@@ -6960,10 +6960,10 @@
         <v>2025.0</v>
       </c>
       <c r="C488" t="n" s="2">
-        <v>45721.0</v>
+        <v>45707.0</v>
       </c>
       <c r="D488" t="n">
-        <v>11.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="489">
@@ -6974,10 +6974,10 @@
         <v>2025.0</v>
       </c>
       <c r="C489" t="n" s="2">
-        <v>45728.0</v>
+        <v>45714.0</v>
       </c>
       <c r="D489" t="n">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="490">
@@ -6988,10 +6988,10 @@
         <v>2025.0</v>
       </c>
       <c r="C490" t="n" s="2">
-        <v>45735.0</v>
+        <v>45721.0</v>
       </c>
       <c r="D490" t="n">
-        <v>19.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="491">
@@ -7002,10 +7002,10 @@
         <v>2025.0</v>
       </c>
       <c r="C491" t="n" s="2">
-        <v>45742.0</v>
+        <v>45728.0</v>
       </c>
       <c r="D491" t="n">
-        <v>17.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="492">
@@ -7016,10 +7016,10 @@
         <v>2025.0</v>
       </c>
       <c r="C492" t="n" s="2">
-        <v>45749.0</v>
+        <v>45735.0</v>
       </c>
       <c r="D492" t="n">
-        <v>5.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="493">
@@ -7030,10 +7030,10 @@
         <v>2025.0</v>
       </c>
       <c r="C493" t="n" s="2">
-        <v>45756.0</v>
+        <v>45742.0</v>
       </c>
       <c r="D493" t="n">
-        <v>9.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="494">
@@ -7044,10 +7044,10 @@
         <v>2025.0</v>
       </c>
       <c r="C494" t="n" s="2">
-        <v>45763.0</v>
+        <v>45749.0</v>
       </c>
       <c r="D494" t="n">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="495">
@@ -7058,10 +7058,10 @@
         <v>2025.0</v>
       </c>
       <c r="C495" t="n" s="2">
-        <v>45770.0</v>
+        <v>45756.0</v>
       </c>
       <c r="D495" t="n">
-        <v>1.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="496">
@@ -7072,10 +7072,10 @@
         <v>2025.0</v>
       </c>
       <c r="C496" t="n" s="2">
-        <v>45784.0</v>
+        <v>45763.0</v>
       </c>
       <c r="D496" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="497">
@@ -7086,10 +7086,10 @@
         <v>2025.0</v>
       </c>
       <c r="C497" t="n" s="2">
-        <v>45791.0</v>
+        <v>45770.0</v>
       </c>
       <c r="D497" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="498">
@@ -7100,10 +7100,10 @@
         <v>2025.0</v>
       </c>
       <c r="C498" t="n" s="2">
-        <v>45805.0</v>
+        <v>45784.0</v>
       </c>
       <c r="D498" t="n">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="499">
@@ -7114,7 +7114,7 @@
         <v>2025.0</v>
       </c>
       <c r="C499" t="n" s="2">
-        <v>45826.0</v>
+        <v>45791.0</v>
       </c>
       <c r="D499" t="n">
         <v>2.0</v>
@@ -7128,10 +7128,10 @@
         <v>2025.0</v>
       </c>
       <c r="C500" t="n" s="2">
-        <v>45861.0</v>
+        <v>45805.0</v>
       </c>
       <c r="D500" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="501">
@@ -7142,10 +7142,10 @@
         <v>2025.0</v>
       </c>
       <c r="C501" t="n" s="2">
-        <v>45868.0</v>
+        <v>45826.0</v>
       </c>
       <c r="D501" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="502">
@@ -7156,10 +7156,10 @@
         <v>2025.0</v>
       </c>
       <c r="C502" t="n" s="2">
-        <v>45889.0</v>
+        <v>45861.0</v>
       </c>
       <c r="D502" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="503">
@@ -7170,7 +7170,7 @@
         <v>2025.0</v>
       </c>
       <c r="C503" t="n" s="2">
-        <v>45924.0</v>
+        <v>45868.0</v>
       </c>
       <c r="D503" t="n">
         <v>1.0</v>
@@ -7184,7 +7184,7 @@
         <v>2025.0</v>
       </c>
       <c r="C504" t="n" s="2">
-        <v>45945.0</v>
+        <v>45889.0</v>
       </c>
       <c r="D504" t="n">
         <v>1.0</v>
@@ -7198,10 +7198,10 @@
         <v>2025.0</v>
       </c>
       <c r="C505" t="n" s="2">
-        <v>45959.0</v>
+        <v>45924.0</v>
       </c>
       <c r="D505" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="506">
@@ -7212,10 +7212,10 @@
         <v>2025.0</v>
       </c>
       <c r="C506" t="n" s="2">
-        <v>46001.0</v>
+        <v>45945.0</v>
       </c>
       <c r="D506" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="507">
@@ -7226,10 +7226,10 @@
         <v>2025.0</v>
       </c>
       <c r="C507" t="n" s="2">
-        <v>46008.0</v>
+        <v>45959.0</v>
       </c>
       <c r="D507" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="508">
@@ -7240,10 +7240,10 @@
         <v>2025.0</v>
       </c>
       <c r="C508" t="n" s="2">
-        <v>46022.0</v>
+        <v>46001.0</v>
       </c>
       <c r="D508" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="509">
@@ -7251,10 +7251,10 @@
         <v>7</v>
       </c>
       <c r="B509" t="n">
-        <v>2026.0</v>
+        <v>2025.0</v>
       </c>
       <c r="C509" t="n" s="2">
-        <v>46030.0</v>
+        <v>46008.0</v>
       </c>
       <c r="D509" t="n">
         <v>1.0</v>
@@ -7265,10 +7265,10 @@
         <v>7</v>
       </c>
       <c r="B510" t="n">
-        <v>2026.0</v>
+        <v>2025.0</v>
       </c>
       <c r="C510" t="n" s="2">
-        <v>46051.0</v>
+        <v>46022.0</v>
       </c>
       <c r="D510" t="n">
         <v>1.0</v>
@@ -7282,7 +7282,7 @@
         <v>2026.0</v>
       </c>
       <c r="C511" t="n" s="2">
-        <v>46058.0</v>
+        <v>46030.0</v>
       </c>
       <c r="D511" t="n">
         <v>1.0</v>
@@ -7296,21 +7296,21 @@
         <v>2026.0</v>
       </c>
       <c r="C512" t="n" s="2">
-        <v>46065.0</v>
+        <v>46051.0</v>
       </c>
       <c r="D512" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B513" t="n">
-        <v>2024.0</v>
+        <v>2026.0</v>
       </c>
       <c r="C513" t="n" s="2">
-        <v>45495.0</v>
+        <v>46058.0</v>
       </c>
       <c r="D513" t="n">
         <v>1.0</v>
@@ -7318,16 +7318,16 @@
     </row>
     <row r="514">
       <c r="A514" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B514" t="n">
-        <v>2024.0</v>
+        <v>2026.0</v>
       </c>
       <c r="C514" t="n" s="2">
-        <v>45502.0</v>
+        <v>46065.0</v>
       </c>
       <c r="D514" t="n">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="515">
@@ -7335,10 +7335,10 @@
         <v>8</v>
       </c>
       <c r="B515" t="n">
-        <v>2025.0</v>
+        <v>2024.0</v>
       </c>
       <c r="C515" t="n" s="2">
-        <v>45665.0</v>
+        <v>45495.0</v>
       </c>
       <c r="D515" t="n">
         <v>1.0</v>
@@ -7349,13 +7349,13 @@
         <v>8</v>
       </c>
       <c r="B516" t="n">
-        <v>2025.0</v>
+        <v>2024.0</v>
       </c>
       <c r="C516" t="n" s="2">
-        <v>45672.0</v>
+        <v>45502.0</v>
       </c>
       <c r="D516" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="517">
@@ -7366,7 +7366,7 @@
         <v>2025.0</v>
       </c>
       <c r="C517" t="n" s="2">
-        <v>45679.0</v>
+        <v>45665.0</v>
       </c>
       <c r="D517" t="n">
         <v>1.0</v>
@@ -7380,10 +7380,10 @@
         <v>2025.0</v>
       </c>
       <c r="C518" t="n" s="2">
-        <v>45686.0</v>
+        <v>45672.0</v>
       </c>
       <c r="D518" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="519">
@@ -7394,7 +7394,7 @@
         <v>2025.0</v>
       </c>
       <c r="C519" t="n" s="2">
-        <v>45693.0</v>
+        <v>45679.0</v>
       </c>
       <c r="D519" t="n">
         <v>1.0</v>
@@ -7408,10 +7408,10 @@
         <v>2025.0</v>
       </c>
       <c r="C520" t="n" s="2">
-        <v>45700.0</v>
+        <v>45686.0</v>
       </c>
       <c r="D520" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="521">
@@ -7422,10 +7422,10 @@
         <v>2025.0</v>
       </c>
       <c r="C521" t="n" s="2">
-        <v>45707.0</v>
+        <v>45693.0</v>
       </c>
       <c r="D521" t="n">
-        <v>7.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="522">
@@ -7436,10 +7436,10 @@
         <v>2025.0</v>
       </c>
       <c r="C522" t="n" s="2">
-        <v>45714.0</v>
+        <v>45700.0</v>
       </c>
       <c r="D522" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="523">
@@ -7450,10 +7450,10 @@
         <v>2025.0</v>
       </c>
       <c r="C523" t="n" s="2">
-        <v>45721.0</v>
+        <v>45707.0</v>
       </c>
       <c r="D523" t="n">
-        <v>4.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="524">
@@ -7464,10 +7464,10 @@
         <v>2025.0</v>
       </c>
       <c r="C524" t="n" s="2">
-        <v>45728.0</v>
+        <v>45714.0</v>
       </c>
       <c r="D524" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="525">
@@ -7478,10 +7478,10 @@
         <v>2025.0</v>
       </c>
       <c r="C525" t="n" s="2">
-        <v>45742.0</v>
+        <v>45721.0</v>
       </c>
       <c r="D525" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="526">
@@ -7492,7 +7492,7 @@
         <v>2025.0</v>
       </c>
       <c r="C526" t="n" s="2">
-        <v>45749.0</v>
+        <v>45728.0</v>
       </c>
       <c r="D526" t="n">
         <v>1.0</v>
@@ -7506,7 +7506,7 @@
         <v>2025.0</v>
       </c>
       <c r="C527" t="n" s="2">
-        <v>45763.0</v>
+        <v>45742.0</v>
       </c>
       <c r="D527" t="n">
         <v>1.0</v>
@@ -7520,10 +7520,10 @@
         <v>2025.0</v>
       </c>
       <c r="C528" t="n" s="2">
-        <v>45777.0</v>
+        <v>45749.0</v>
       </c>
       <c r="D528" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="529">
@@ -7534,7 +7534,7 @@
         <v>2025.0</v>
       </c>
       <c r="C529" t="n" s="2">
-        <v>45784.0</v>
+        <v>45763.0</v>
       </c>
       <c r="D529" t="n">
         <v>1.0</v>
@@ -7548,10 +7548,10 @@
         <v>2025.0</v>
       </c>
       <c r="C530" t="n" s="2">
-        <v>45798.0</v>
+        <v>45777.0</v>
       </c>
       <c r="D530" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="531">
@@ -7562,7 +7562,7 @@
         <v>2025.0</v>
       </c>
       <c r="C531" t="n" s="2">
-        <v>45805.0</v>
+        <v>45784.0</v>
       </c>
       <c r="D531" t="n">
         <v>1.0</v>
@@ -7576,10 +7576,10 @@
         <v>2025.0</v>
       </c>
       <c r="C532" t="n" s="2">
-        <v>45812.0</v>
+        <v>45798.0</v>
       </c>
       <c r="D532" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="533">
@@ -7590,10 +7590,10 @@
         <v>2025.0</v>
       </c>
       <c r="C533" t="n" s="2">
-        <v>45819.0</v>
+        <v>45805.0</v>
       </c>
       <c r="D533" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="534">
@@ -7604,7 +7604,7 @@
         <v>2025.0</v>
       </c>
       <c r="C534" t="n" s="2">
-        <v>45833.0</v>
+        <v>45812.0</v>
       </c>
       <c r="D534" t="n">
         <v>2.0</v>
@@ -7618,10 +7618,10 @@
         <v>2025.0</v>
       </c>
       <c r="C535" t="n" s="2">
-        <v>45847.0</v>
+        <v>45819.0</v>
       </c>
       <c r="D535" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="536">
@@ -7632,10 +7632,10 @@
         <v>2025.0</v>
       </c>
       <c r="C536" t="n" s="2">
-        <v>45854.0</v>
+        <v>45833.0</v>
       </c>
       <c r="D536" t="n">
-        <v>8.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="537">
@@ -7646,10 +7646,10 @@
         <v>2025.0</v>
       </c>
       <c r="C537" t="n" s="2">
-        <v>45861.0</v>
+        <v>45847.0</v>
       </c>
       <c r="D537" t="n">
-        <v>12.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="538">
@@ -7660,10 +7660,10 @@
         <v>2025.0</v>
       </c>
       <c r="C538" t="n" s="2">
-        <v>45868.0</v>
+        <v>45854.0</v>
       </c>
       <c r="D538" t="n">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="539">
@@ -7674,10 +7674,10 @@
         <v>2025.0</v>
       </c>
       <c r="C539" t="n" s="2">
-        <v>45875.0</v>
+        <v>45861.0</v>
       </c>
       <c r="D539" t="n">
-        <v>1.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="540">
@@ -7688,10 +7688,10 @@
         <v>2025.0</v>
       </c>
       <c r="C540" t="n" s="2">
-        <v>45896.0</v>
+        <v>45868.0</v>
       </c>
       <c r="D540" t="n">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="541">
@@ -7702,7 +7702,7 @@
         <v>2025.0</v>
       </c>
       <c r="C541" t="n" s="2">
-        <v>45903.0</v>
+        <v>45875.0</v>
       </c>
       <c r="D541" t="n">
         <v>1.0</v>
@@ -7716,7 +7716,7 @@
         <v>2025.0</v>
       </c>
       <c r="C542" t="n" s="2">
-        <v>45931.0</v>
+        <v>45896.0</v>
       </c>
       <c r="D542" t="n">
         <v>1.0</v>
@@ -7730,10 +7730,10 @@
         <v>2025.0</v>
       </c>
       <c r="C543" t="n" s="2">
-        <v>45938.0</v>
+        <v>45903.0</v>
       </c>
       <c r="D543" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="544">
@@ -7744,10 +7744,10 @@
         <v>2025.0</v>
       </c>
       <c r="C544" t="n" s="2">
-        <v>45945.0</v>
+        <v>45931.0</v>
       </c>
       <c r="D544" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="545">
@@ -7758,10 +7758,10 @@
         <v>2025.0</v>
       </c>
       <c r="C545" t="n" s="2">
-        <v>45966.0</v>
+        <v>45938.0</v>
       </c>
       <c r="D545" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="546">
@@ -7772,10 +7772,10 @@
         <v>2025.0</v>
       </c>
       <c r="C546" t="n" s="2">
-        <v>45973.0</v>
+        <v>45945.0</v>
       </c>
       <c r="D546" t="n">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="547">
@@ -7786,10 +7786,10 @@
         <v>2025.0</v>
       </c>
       <c r="C547" t="n" s="2">
-        <v>45980.0</v>
+        <v>45966.0</v>
       </c>
       <c r="D547" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="548">
@@ -7800,10 +7800,10 @@
         <v>2025.0</v>
       </c>
       <c r="C548" t="n" s="2">
-        <v>45987.0</v>
+        <v>45973.0</v>
       </c>
       <c r="D548" t="n">
-        <v>20.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="549">
@@ -7814,10 +7814,10 @@
         <v>2025.0</v>
       </c>
       <c r="C549" t="n" s="2">
-        <v>45994.0</v>
+        <v>45980.0</v>
       </c>
       <c r="D549" t="n">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="550">
@@ -7828,10 +7828,10 @@
         <v>2025.0</v>
       </c>
       <c r="C550" t="n" s="2">
-        <v>46001.0</v>
+        <v>45987.0</v>
       </c>
       <c r="D550" t="n">
-        <v>8.0</v>
+        <v>20.0</v>
       </c>
     </row>
     <row r="551">
@@ -7842,10 +7842,10 @@
         <v>2025.0</v>
       </c>
       <c r="C551" t="n" s="2">
-        <v>46008.0</v>
+        <v>45994.0</v>
       </c>
       <c r="D551" t="n">
-        <v>24.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="552">
@@ -7856,10 +7856,10 @@
         <v>2025.0</v>
       </c>
       <c r="C552" t="n" s="2">
-        <v>46015.0</v>
+        <v>46001.0</v>
       </c>
       <c r="D552" t="n">
-        <v>13.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="553">
@@ -7870,10 +7870,10 @@
         <v>2025.0</v>
       </c>
       <c r="C553" t="n" s="2">
-        <v>46022.0</v>
+        <v>46008.0</v>
       </c>
       <c r="D553" t="n">
-        <v>8.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="554">
@@ -7884,10 +7884,10 @@
         <v>2025.0</v>
       </c>
       <c r="C554" t="n" s="2">
-        <v>46029.0</v>
+        <v>46015.0</v>
       </c>
       <c r="D554" t="n">
-        <v>3.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="555">
@@ -7895,13 +7895,13 @@
         <v>8</v>
       </c>
       <c r="B555" t="n">
-        <v>2026.0</v>
+        <v>2025.0</v>
       </c>
       <c r="C555" t="n" s="2">
-        <v>46030.0</v>
+        <v>46022.0</v>
       </c>
       <c r="D555" t="n">
-        <v>24.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="556">
@@ -7909,13 +7909,13 @@
         <v>8</v>
       </c>
       <c r="B556" t="n">
-        <v>2026.0</v>
+        <v>2025.0</v>
       </c>
       <c r="C556" t="n" s="2">
-        <v>46037.0</v>
+        <v>46029.0</v>
       </c>
       <c r="D556" t="n">
-        <v>22.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="557">
@@ -7926,10 +7926,10 @@
         <v>2026.0</v>
       </c>
       <c r="C557" t="n" s="2">
-        <v>46044.0</v>
+        <v>46030.0</v>
       </c>
       <c r="D557" t="n">
-        <v>27.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="558">
@@ -7940,10 +7940,10 @@
         <v>2026.0</v>
       </c>
       <c r="C558" t="n" s="2">
-        <v>46051.0</v>
+        <v>46037.0</v>
       </c>
       <c r="D558" t="n">
-        <v>18.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="559">
@@ -7954,10 +7954,10 @@
         <v>2026.0</v>
       </c>
       <c r="C559" t="n" s="2">
-        <v>46058.0</v>
+        <v>46044.0</v>
       </c>
       <c r="D559" t="n">
-        <v>25.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="560">
@@ -7968,10 +7968,10 @@
         <v>2026.0</v>
       </c>
       <c r="C560" t="n" s="2">
-        <v>46065.0</v>
+        <v>46051.0</v>
       </c>
       <c r="D560" t="n">
-        <v>22.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="561">
@@ -7982,10 +7982,10 @@
         <v>2026.0</v>
       </c>
       <c r="C561" t="n" s="2">
-        <v>46072.0</v>
+        <v>46058.0</v>
       </c>
       <c r="D561" t="n">
-        <v>13.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="562">
@@ -7996,10 +7996,10 @@
         <v>2026.0</v>
       </c>
       <c r="C562" t="n" s="2">
-        <v>46079.0</v>
+        <v>46065.0</v>
       </c>
       <c r="D562" t="n">
-        <v>24.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="563">
@@ -8010,10 +8010,10 @@
         <v>2026.0</v>
       </c>
       <c r="C563" t="n" s="2">
-        <v>46086.0</v>
+        <v>46072.0</v>
       </c>
       <c r="D563" t="n">
-        <v>26.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="564">
@@ -8024,10 +8024,10 @@
         <v>2026.0</v>
       </c>
       <c r="C564" t="n" s="2">
-        <v>46093.0</v>
+        <v>46079.0</v>
       </c>
       <c r="D564" t="n">
-        <v>33.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="565">
@@ -8038,10 +8038,10 @@
         <v>2026.0</v>
       </c>
       <c r="C565" t="n" s="2">
-        <v>46100.0</v>
+        <v>46086.0</v>
       </c>
       <c r="D565" t="n">
-        <v>25.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="566">
@@ -8052,10 +8052,10 @@
         <v>2026.0</v>
       </c>
       <c r="C566" t="n" s="2">
-        <v>46107.0</v>
+        <v>46093.0</v>
       </c>
       <c r="D566" t="n">
-        <v>31.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="567">
@@ -8066,10 +8066,10 @@
         <v>2026.0</v>
       </c>
       <c r="C567" t="n" s="2">
-        <v>46114.0</v>
+        <v>46100.0</v>
       </c>
       <c r="D567" t="n">
-        <v>7.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="568">
@@ -8080,10 +8080,52 @@
         <v>2026.0</v>
       </c>
       <c r="C568" t="n" s="2">
+        <v>46107.0</v>
+      </c>
+      <c r="D568" t="n">
+        <v>31.0</v>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="s">
+        <v>8</v>
+      </c>
+      <c r="B569" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C569" t="n" s="2">
+        <v>46114.0</v>
+      </c>
+      <c r="D569" t="n">
+        <v>10.0</v>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="s">
+        <v>8</v>
+      </c>
+      <c r="B570" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C570" t="n" s="2">
         <v>46121.0</v>
       </c>
-      <c r="D568" t="n">
-        <v>6.0</v>
+      <c r="D570" t="n">
+        <v>8.0</v>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="s">
+        <v>8</v>
+      </c>
+      <c r="B571" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C571" t="n" s="2">
+        <v>46128.0</v>
+      </c>
+      <c r="D571" t="n">
+        <v>8.0</v>
       </c>
     </row>
   </sheetData>
@@ -8109,7 +8151,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="n">
-        <v>52.0</v>
+        <v>50.0</v>
       </c>
     </row>
     <row r="3">
@@ -8117,7 +8159,7 @@
         <v>11</v>
       </c>
       <c r="B3" t="n">
-        <v>187.0</v>
+        <v>190.0</v>
       </c>
     </row>
     <row r="4">
@@ -8125,7 +8167,7 @@
         <v>12</v>
       </c>
       <c r="B4" t="n">
-        <v>1183.0</v>
+        <v>1198.0</v>
       </c>
     </row>
     <row r="5">
@@ -8133,7 +8175,7 @@
         <v>13</v>
       </c>
       <c r="B5" t="n">
-        <v>2064.0</v>
+        <v>2078.0</v>
       </c>
     </row>
   </sheetData>
@@ -8165,7 +8207,7 @@
         <v>21</v>
       </c>
       <c r="C2" t="n">
-        <v>186.0</v>
+        <v>188.0</v>
       </c>
     </row>
     <row r="3">
@@ -8187,7 +8229,7 @@
         <v>19</v>
       </c>
       <c r="C4" t="n">
-        <v>135.0</v>
+        <v>137.0</v>
       </c>
     </row>
     <row r="5">
@@ -8198,7 +8240,7 @@
         <v>21</v>
       </c>
       <c r="C5" t="n">
-        <v>411.0</v>
+        <v>414.0</v>
       </c>
     </row>
     <row r="6">
@@ -8209,7 +8251,7 @@
         <v>22</v>
       </c>
       <c r="C6" t="n">
-        <v>295.0</v>
+        <v>297.0</v>
       </c>
     </row>
     <row r="7">
@@ -8220,7 +8262,7 @@
         <v>19</v>
       </c>
       <c r="C7" t="n">
-        <v>156.0</v>
+        <v>158.0</v>
       </c>
     </row>
     <row r="8">
@@ -8231,7 +8273,7 @@
         <v>21</v>
       </c>
       <c r="C8" t="n">
-        <v>343.0</v>
+        <v>345.0</v>
       </c>
     </row>
     <row r="9">
@@ -8242,7 +8284,7 @@
         <v>22</v>
       </c>
       <c r="C9" t="n">
-        <v>328.0</v>
+        <v>329.0</v>
       </c>
     </row>
     <row r="10">
@@ -8253,7 +8295,7 @@
         <v>19</v>
       </c>
       <c r="C10" t="n">
-        <v>143.0</v>
+        <v>145.0</v>
       </c>
     </row>
     <row r="11">
@@ -8264,7 +8306,7 @@
         <v>19</v>
       </c>
       <c r="C11" t="n">
-        <v>38.0</v>
+        <v>36.0</v>
       </c>
     </row>
     <row r="12">
@@ -8275,7 +8317,7 @@
         <v>21</v>
       </c>
       <c r="C12" t="n">
-        <v>54.0</v>
+        <v>56.0</v>
       </c>
     </row>
     <row r="13">
@@ -8286,7 +8328,7 @@
         <v>22</v>
       </c>
       <c r="C13" t="n">
-        <v>32.0</v>
+        <v>34.0</v>
       </c>
     </row>
     <row r="14">
@@ -8297,7 +8339,7 @@
         <v>19</v>
       </c>
       <c r="C14" t="n">
-        <v>380.0</v>
+        <v>385.0</v>
       </c>
     </row>
     <row r="15">
@@ -8319,7 +8361,7 @@
         <v>22</v>
       </c>
       <c r="C16" t="n">
-        <v>346.0</v>
+        <v>351.0</v>
       </c>
     </row>
     <row r="17">
@@ -8330,7 +8372,7 @@
         <v>19</v>
       </c>
       <c r="C17" t="n">
-        <v>109.0</v>
+        <v>111.0</v>
       </c>
     </row>
   </sheetData>

--- a/Download/Focus_Positivi_ZR.xlsx
+++ b/Download/Focus_Positivi_ZR.xlsx
@@ -8151,7 +8151,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="n">
-        <v>50.0</v>
+        <v>45.0</v>
       </c>
     </row>
     <row r="3">
@@ -8167,7 +8167,7 @@
         <v>12</v>
       </c>
       <c r="B4" t="n">
-        <v>1198.0</v>
+        <v>1201.0</v>
       </c>
     </row>
     <row r="5">
@@ -8175,7 +8175,7 @@
         <v>13</v>
       </c>
       <c r="B5" t="n">
-        <v>2078.0</v>
+        <v>2080.0</v>
       </c>
     </row>
   </sheetData>
@@ -8306,7 +8306,7 @@
         <v>19</v>
       </c>
       <c r="C11" t="n">
-        <v>36.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="12">
@@ -8339,7 +8339,7 @@
         <v>19</v>
       </c>
       <c r="C14" t="n">
-        <v>385.0</v>
+        <v>387.0</v>
       </c>
     </row>
     <row r="15">
@@ -8350,7 +8350,7 @@
         <v>21</v>
       </c>
       <c r="C15" t="n">
-        <v>359.0</v>
+        <v>361.0</v>
       </c>
     </row>
     <row r="16">
@@ -8361,7 +8361,7 @@
         <v>22</v>
       </c>
       <c r="C16" t="n">
-        <v>351.0</v>
+        <v>352.0</v>
       </c>
     </row>
     <row r="17">

--- a/Download/Focus_Positivi_ZR.xlsx
+++ b/Download/Focus_Positivi_ZR.xlsx
@@ -8111,7 +8111,7 @@
         <v>46121.0</v>
       </c>
       <c r="D570" t="n">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="571">
@@ -8125,7 +8125,7 @@
         <v>46128.0</v>
       </c>
       <c r="D571" t="n">
-        <v>8.0</v>
+        <v>15.0</v>
       </c>
     </row>
   </sheetData>
@@ -8167,7 +8167,7 @@
         <v>12</v>
       </c>
       <c r="B4" t="n">
-        <v>1201.0</v>
+        <v>1206.0</v>
       </c>
     </row>
     <row r="5">
@@ -8175,7 +8175,7 @@
         <v>13</v>
       </c>
       <c r="B5" t="n">
-        <v>2080.0</v>
+        <v>2083.0</v>
       </c>
     </row>
   </sheetData>
@@ -8207,7 +8207,7 @@
         <v>21</v>
       </c>
       <c r="C2" t="n">
-        <v>188.0</v>
+        <v>189.0</v>
       </c>
     </row>
     <row r="3">
@@ -8317,7 +8317,7 @@
         <v>21</v>
       </c>
       <c r="C12" t="n">
-        <v>56.0</v>
+        <v>59.0</v>
       </c>
     </row>
     <row r="13">
@@ -8328,7 +8328,7 @@
         <v>22</v>
       </c>
       <c r="C13" t="n">
-        <v>34.0</v>
+        <v>36.0</v>
       </c>
     </row>
     <row r="14">
@@ -8361,7 +8361,7 @@
         <v>22</v>
       </c>
       <c r="C16" t="n">
-        <v>352.0</v>
+        <v>354.0</v>
       </c>
     </row>
     <row r="17">

--- a/Download/Focus_Positivi_ZR.xlsx
+++ b/Download/Focus_Positivi_ZR.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="615" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="616" uniqueCount="23">
   <si>
     <t>NOME_REGIONE</t>
   </si>
@@ -4219,7 +4219,7 @@
         <v>46128.0</v>
       </c>
       <c r="D292" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="293">
@@ -7332,13 +7332,13 @@
     </row>
     <row r="515">
       <c r="A515" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B515" t="n">
-        <v>2024.0</v>
+        <v>2026.0</v>
       </c>
       <c r="C515" t="n" s="2">
-        <v>45495.0</v>
+        <v>46135.0</v>
       </c>
       <c r="D515" t="n">
         <v>1.0</v>
@@ -7352,10 +7352,10 @@
         <v>2024.0</v>
       </c>
       <c r="C516" t="n" s="2">
-        <v>45502.0</v>
+        <v>45495.0</v>
       </c>
       <c r="D516" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="517">
@@ -7363,13 +7363,13 @@
         <v>8</v>
       </c>
       <c r="B517" t="n">
-        <v>2025.0</v>
+        <v>2024.0</v>
       </c>
       <c r="C517" t="n" s="2">
-        <v>45665.0</v>
+        <v>45502.0</v>
       </c>
       <c r="D517" t="n">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="518">
@@ -7380,10 +7380,10 @@
         <v>2025.0</v>
       </c>
       <c r="C518" t="n" s="2">
-        <v>45672.0</v>
+        <v>45665.0</v>
       </c>
       <c r="D518" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="519">
@@ -7394,10 +7394,10 @@
         <v>2025.0</v>
       </c>
       <c r="C519" t="n" s="2">
-        <v>45679.0</v>
+        <v>45672.0</v>
       </c>
       <c r="D519" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="520">
@@ -7408,10 +7408,10 @@
         <v>2025.0</v>
       </c>
       <c r="C520" t="n" s="2">
-        <v>45686.0</v>
+        <v>45679.0</v>
       </c>
       <c r="D520" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="521">
@@ -7422,10 +7422,10 @@
         <v>2025.0</v>
       </c>
       <c r="C521" t="n" s="2">
-        <v>45693.0</v>
+        <v>45686.0</v>
       </c>
       <c r="D521" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="522">
@@ -7436,10 +7436,10 @@
         <v>2025.0</v>
       </c>
       <c r="C522" t="n" s="2">
-        <v>45700.0</v>
+        <v>45693.0</v>
       </c>
       <c r="D522" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="523">
@@ -7450,10 +7450,10 @@
         <v>2025.0</v>
       </c>
       <c r="C523" t="n" s="2">
-        <v>45707.0</v>
+        <v>45700.0</v>
       </c>
       <c r="D523" t="n">
-        <v>7.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="524">
@@ -7464,10 +7464,10 @@
         <v>2025.0</v>
       </c>
       <c r="C524" t="n" s="2">
-        <v>45714.0</v>
+        <v>45707.0</v>
       </c>
       <c r="D524" t="n">
-        <v>3.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="525">
@@ -7478,10 +7478,10 @@
         <v>2025.0</v>
       </c>
       <c r="C525" t="n" s="2">
-        <v>45721.0</v>
+        <v>45714.0</v>
       </c>
       <c r="D525" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="526">
@@ -7492,10 +7492,10 @@
         <v>2025.0</v>
       </c>
       <c r="C526" t="n" s="2">
-        <v>45728.0</v>
+        <v>45721.0</v>
       </c>
       <c r="D526" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="527">
@@ -7506,7 +7506,7 @@
         <v>2025.0</v>
       </c>
       <c r="C527" t="n" s="2">
-        <v>45742.0</v>
+        <v>45728.0</v>
       </c>
       <c r="D527" t="n">
         <v>1.0</v>
@@ -7520,7 +7520,7 @@
         <v>2025.0</v>
       </c>
       <c r="C528" t="n" s="2">
-        <v>45749.0</v>
+        <v>45742.0</v>
       </c>
       <c r="D528" t="n">
         <v>1.0</v>
@@ -7534,7 +7534,7 @@
         <v>2025.0</v>
       </c>
       <c r="C529" t="n" s="2">
-        <v>45763.0</v>
+        <v>45749.0</v>
       </c>
       <c r="D529" t="n">
         <v>1.0</v>
@@ -7548,10 +7548,10 @@
         <v>2025.0</v>
       </c>
       <c r="C530" t="n" s="2">
-        <v>45777.0</v>
+        <v>45763.0</v>
       </c>
       <c r="D530" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="531">
@@ -7562,10 +7562,10 @@
         <v>2025.0</v>
       </c>
       <c r="C531" t="n" s="2">
-        <v>45784.0</v>
+        <v>45777.0</v>
       </c>
       <c r="D531" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="532">
@@ -7576,7 +7576,7 @@
         <v>2025.0</v>
       </c>
       <c r="C532" t="n" s="2">
-        <v>45798.0</v>
+        <v>45784.0</v>
       </c>
       <c r="D532" t="n">
         <v>1.0</v>
@@ -7590,7 +7590,7 @@
         <v>2025.0</v>
       </c>
       <c r="C533" t="n" s="2">
-        <v>45805.0</v>
+        <v>45798.0</v>
       </c>
       <c r="D533" t="n">
         <v>1.0</v>
@@ -7604,10 +7604,10 @@
         <v>2025.0</v>
       </c>
       <c r="C534" t="n" s="2">
-        <v>45812.0</v>
+        <v>45805.0</v>
       </c>
       <c r="D534" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="535">
@@ -7618,7 +7618,7 @@
         <v>2025.0</v>
       </c>
       <c r="C535" t="n" s="2">
-        <v>45819.0</v>
+        <v>45812.0</v>
       </c>
       <c r="D535" t="n">
         <v>2.0</v>
@@ -7632,7 +7632,7 @@
         <v>2025.0</v>
       </c>
       <c r="C536" t="n" s="2">
-        <v>45833.0</v>
+        <v>45819.0</v>
       </c>
       <c r="D536" t="n">
         <v>2.0</v>
@@ -7646,10 +7646,10 @@
         <v>2025.0</v>
       </c>
       <c r="C537" t="n" s="2">
-        <v>45847.0</v>
+        <v>45833.0</v>
       </c>
       <c r="D537" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="538">
@@ -7660,10 +7660,10 @@
         <v>2025.0</v>
       </c>
       <c r="C538" t="n" s="2">
-        <v>45854.0</v>
+        <v>45847.0</v>
       </c>
       <c r="D538" t="n">
-        <v>8.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="539">
@@ -7674,10 +7674,10 @@
         <v>2025.0</v>
       </c>
       <c r="C539" t="n" s="2">
-        <v>45861.0</v>
+        <v>45854.0</v>
       </c>
       <c r="D539" t="n">
-        <v>12.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="540">
@@ -7688,10 +7688,10 @@
         <v>2025.0</v>
       </c>
       <c r="C540" t="n" s="2">
-        <v>45868.0</v>
+        <v>45861.0</v>
       </c>
       <c r="D540" t="n">
-        <v>6.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="541">
@@ -7702,10 +7702,10 @@
         <v>2025.0</v>
       </c>
       <c r="C541" t="n" s="2">
-        <v>45875.0</v>
+        <v>45868.0</v>
       </c>
       <c r="D541" t="n">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="542">
@@ -7716,7 +7716,7 @@
         <v>2025.0</v>
       </c>
       <c r="C542" t="n" s="2">
-        <v>45896.0</v>
+        <v>45875.0</v>
       </c>
       <c r="D542" t="n">
         <v>1.0</v>
@@ -7730,7 +7730,7 @@
         <v>2025.0</v>
       </c>
       <c r="C543" t="n" s="2">
-        <v>45903.0</v>
+        <v>45896.0</v>
       </c>
       <c r="D543" t="n">
         <v>1.0</v>
@@ -7744,7 +7744,7 @@
         <v>2025.0</v>
       </c>
       <c r="C544" t="n" s="2">
-        <v>45931.0</v>
+        <v>45903.0</v>
       </c>
       <c r="D544" t="n">
         <v>1.0</v>
@@ -7758,10 +7758,10 @@
         <v>2025.0</v>
       </c>
       <c r="C545" t="n" s="2">
-        <v>45938.0</v>
+        <v>45931.0</v>
       </c>
       <c r="D545" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="546">
@@ -7772,10 +7772,10 @@
         <v>2025.0</v>
       </c>
       <c r="C546" t="n" s="2">
-        <v>45945.0</v>
+        <v>45938.0</v>
       </c>
       <c r="D546" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="547">
@@ -7786,7 +7786,7 @@
         <v>2025.0</v>
       </c>
       <c r="C547" t="n" s="2">
-        <v>45966.0</v>
+        <v>45945.0</v>
       </c>
       <c r="D547" t="n">
         <v>2.0</v>
@@ -7800,10 +7800,10 @@
         <v>2025.0</v>
       </c>
       <c r="C548" t="n" s="2">
-        <v>45973.0</v>
+        <v>45966.0</v>
       </c>
       <c r="D548" t="n">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="549">
@@ -7814,10 +7814,10 @@
         <v>2025.0</v>
       </c>
       <c r="C549" t="n" s="2">
-        <v>45980.0</v>
+        <v>45973.0</v>
       </c>
       <c r="D549" t="n">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="550">
@@ -7828,10 +7828,10 @@
         <v>2025.0</v>
       </c>
       <c r="C550" t="n" s="2">
-        <v>45987.0</v>
+        <v>45980.0</v>
       </c>
       <c r="D550" t="n">
-        <v>20.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="551">
@@ -7842,10 +7842,10 @@
         <v>2025.0</v>
       </c>
       <c r="C551" t="n" s="2">
-        <v>45994.0</v>
+        <v>45987.0</v>
       </c>
       <c r="D551" t="n">
-        <v>5.0</v>
+        <v>20.0</v>
       </c>
     </row>
     <row r="552">
@@ -7856,10 +7856,10 @@
         <v>2025.0</v>
       </c>
       <c r="C552" t="n" s="2">
-        <v>46001.0</v>
+        <v>45994.0</v>
       </c>
       <c r="D552" t="n">
-        <v>8.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="553">
@@ -7870,10 +7870,10 @@
         <v>2025.0</v>
       </c>
       <c r="C553" t="n" s="2">
-        <v>46008.0</v>
+        <v>46001.0</v>
       </c>
       <c r="D553" t="n">
-        <v>24.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="554">
@@ -7884,10 +7884,10 @@
         <v>2025.0</v>
       </c>
       <c r="C554" t="n" s="2">
-        <v>46015.0</v>
+        <v>46008.0</v>
       </c>
       <c r="D554" t="n">
-        <v>13.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="555">
@@ -7898,10 +7898,10 @@
         <v>2025.0</v>
       </c>
       <c r="C555" t="n" s="2">
-        <v>46022.0</v>
+        <v>46015.0</v>
       </c>
       <c r="D555" t="n">
-        <v>8.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="556">
@@ -7912,10 +7912,10 @@
         <v>2025.0</v>
       </c>
       <c r="C556" t="n" s="2">
-        <v>46029.0</v>
+        <v>46022.0</v>
       </c>
       <c r="D556" t="n">
-        <v>3.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="557">
@@ -7923,13 +7923,13 @@
         <v>8</v>
       </c>
       <c r="B557" t="n">
-        <v>2026.0</v>
+        <v>2025.0</v>
       </c>
       <c r="C557" t="n" s="2">
-        <v>46030.0</v>
+        <v>46029.0</v>
       </c>
       <c r="D557" t="n">
-        <v>24.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="558">
@@ -7940,10 +7940,10 @@
         <v>2026.0</v>
       </c>
       <c r="C558" t="n" s="2">
-        <v>46037.0</v>
+        <v>46030.0</v>
       </c>
       <c r="D558" t="n">
-        <v>22.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="559">
@@ -7954,10 +7954,10 @@
         <v>2026.0</v>
       </c>
       <c r="C559" t="n" s="2">
-        <v>46044.0</v>
+        <v>46037.0</v>
       </c>
       <c r="D559" t="n">
-        <v>27.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="560">
@@ -7968,10 +7968,10 @@
         <v>2026.0</v>
       </c>
       <c r="C560" t="n" s="2">
-        <v>46051.0</v>
+        <v>46044.0</v>
       </c>
       <c r="D560" t="n">
-        <v>18.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="561">
@@ -7982,10 +7982,10 @@
         <v>2026.0</v>
       </c>
       <c r="C561" t="n" s="2">
-        <v>46058.0</v>
+        <v>46051.0</v>
       </c>
       <c r="D561" t="n">
-        <v>25.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="562">
@@ -7996,10 +7996,10 @@
         <v>2026.0</v>
       </c>
       <c r="C562" t="n" s="2">
-        <v>46065.0</v>
+        <v>46058.0</v>
       </c>
       <c r="D562" t="n">
-        <v>22.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="563">
@@ -8010,10 +8010,10 @@
         <v>2026.0</v>
       </c>
       <c r="C563" t="n" s="2">
-        <v>46072.0</v>
+        <v>46065.0</v>
       </c>
       <c r="D563" t="n">
-        <v>13.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="564">
@@ -8024,10 +8024,10 @@
         <v>2026.0</v>
       </c>
       <c r="C564" t="n" s="2">
-        <v>46079.0</v>
+        <v>46072.0</v>
       </c>
       <c r="D564" t="n">
-        <v>24.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="565">
@@ -8038,10 +8038,10 @@
         <v>2026.0</v>
       </c>
       <c r="C565" t="n" s="2">
-        <v>46086.0</v>
+        <v>46079.0</v>
       </c>
       <c r="D565" t="n">
-        <v>26.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="566">
@@ -8052,10 +8052,10 @@
         <v>2026.0</v>
       </c>
       <c r="C566" t="n" s="2">
-        <v>46093.0</v>
+        <v>46086.0</v>
       </c>
       <c r="D566" t="n">
-        <v>33.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="567">
@@ -8066,10 +8066,10 @@
         <v>2026.0</v>
       </c>
       <c r="C567" t="n" s="2">
-        <v>46100.0</v>
+        <v>46093.0</v>
       </c>
       <c r="D567" t="n">
-        <v>25.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="568">
@@ -8080,10 +8080,10 @@
         <v>2026.0</v>
       </c>
       <c r="C568" t="n" s="2">
-        <v>46107.0</v>
+        <v>46100.0</v>
       </c>
       <c r="D568" t="n">
-        <v>31.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="569">
@@ -8094,10 +8094,10 @@
         <v>2026.0</v>
       </c>
       <c r="C569" t="n" s="2">
-        <v>46114.0</v>
+        <v>46107.0</v>
       </c>
       <c r="D569" t="n">
-        <v>10.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="570">
@@ -8108,10 +8108,10 @@
         <v>2026.0</v>
       </c>
       <c r="C570" t="n" s="2">
-        <v>46121.0</v>
+        <v>46114.0</v>
       </c>
       <c r="D570" t="n">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="571">
@@ -8122,9 +8122,23 @@
         <v>2026.0</v>
       </c>
       <c r="C571" t="n" s="2">
+        <v>46121.0</v>
+      </c>
+      <c r="D571" t="n">
+        <v>9.0</v>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="s">
+        <v>8</v>
+      </c>
+      <c r="B572" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C572" t="n" s="2">
         <v>46128.0</v>
       </c>
-      <c r="D571" t="n">
+      <c r="D572" t="n">
         <v>15.0</v>
       </c>
     </row>
@@ -8159,7 +8173,7 @@
         <v>11</v>
       </c>
       <c r="B3" t="n">
-        <v>190.0</v>
+        <v>191.0</v>
       </c>
     </row>
     <row r="4">
@@ -8167,7 +8181,7 @@
         <v>12</v>
       </c>
       <c r="B4" t="n">
-        <v>1206.0</v>
+        <v>1207.0</v>
       </c>
     </row>
     <row r="5">
@@ -8317,7 +8331,7 @@
         <v>21</v>
       </c>
       <c r="C12" t="n">
-        <v>59.0</v>
+        <v>60.0</v>
       </c>
     </row>
     <row r="13">
@@ -8339,7 +8353,7 @@
         <v>19</v>
       </c>
       <c r="C14" t="n">
-        <v>387.0</v>
+        <v>388.0</v>
       </c>
     </row>
     <row r="15">

--- a/Download/Focus_Positivi_ZR.xlsx
+++ b/Download/Focus_Positivi_ZR.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="616" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="617" uniqueCount="23">
   <si>
     <t>NOME_REGIONE</t>
   </si>
@@ -8142,6 +8142,20 @@
         <v>15.0</v>
       </c>
     </row>
+    <row r="573">
+      <c r="A573" t="s">
+        <v>8</v>
+      </c>
+      <c r="B573" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C573" t="n" s="2">
+        <v>46135.0</v>
+      </c>
+      <c r="D573" t="n">
+        <v>16.0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
@@ -8165,7 +8179,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="n">
-        <v>45.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="3">
@@ -8173,7 +8187,7 @@
         <v>11</v>
       </c>
       <c r="B3" t="n">
-        <v>191.0</v>
+        <v>193.0</v>
       </c>
     </row>
     <row r="4">
@@ -8181,7 +8195,7 @@
         <v>12</v>
       </c>
       <c r="B4" t="n">
-        <v>1207.0</v>
+        <v>1215.0</v>
       </c>
     </row>
     <row r="5">
@@ -8189,7 +8203,7 @@
         <v>13</v>
       </c>
       <c r="B5" t="n">
-        <v>2083.0</v>
+        <v>2086.0</v>
       </c>
     </row>
   </sheetData>
@@ -8221,7 +8235,7 @@
         <v>21</v>
       </c>
       <c r="C2" t="n">
-        <v>189.0</v>
+        <v>191.0</v>
       </c>
     </row>
     <row r="3">
@@ -8232,7 +8246,7 @@
         <v>22</v>
       </c>
       <c r="C3" t="n">
-        <v>171.0</v>
+        <v>172.0</v>
       </c>
     </row>
     <row r="4">
@@ -8320,7 +8334,7 @@
         <v>19</v>
       </c>
       <c r="C11" t="n">
-        <v>31.0</v>
+        <v>34.0</v>
       </c>
     </row>
     <row r="12">
@@ -8331,7 +8345,7 @@
         <v>21</v>
       </c>
       <c r="C12" t="n">
-        <v>60.0</v>
+        <v>65.0</v>
       </c>
     </row>
     <row r="13">
@@ -8342,7 +8356,7 @@
         <v>22</v>
       </c>
       <c r="C13" t="n">
-        <v>36.0</v>
+        <v>39.0</v>
       </c>
     </row>
     <row r="14">
@@ -8353,7 +8367,7 @@
         <v>19</v>
       </c>
       <c r="C14" t="n">
-        <v>388.0</v>
+        <v>390.0</v>
       </c>
     </row>
     <row r="15">

--- a/Download/Focus_Positivi_ZR.xlsx
+++ b/Download/Focus_Positivi_ZR.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="617" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="618" uniqueCount="23">
   <si>
     <t>NOME_REGIONE</t>
   </si>
@@ -4224,13 +4224,13 @@
     </row>
     <row r="293">
       <c r="A293" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B293" t="n">
-        <v>2023.0</v>
+        <v>2026.0</v>
       </c>
       <c r="C293" t="n" s="2">
-        <v>45095.0</v>
+        <v>46135.0</v>
       </c>
       <c r="D293" t="n">
         <v>1.0</v>
@@ -4244,7 +4244,7 @@
         <v>2023.0</v>
       </c>
       <c r="C294" t="n" s="2">
-        <v>45102.0</v>
+        <v>45095.0</v>
       </c>
       <c r="D294" t="n">
         <v>1.0</v>
@@ -4258,7 +4258,7 @@
         <v>2023.0</v>
       </c>
       <c r="C295" t="n" s="2">
-        <v>45158.0</v>
+        <v>45102.0</v>
       </c>
       <c r="D295" t="n">
         <v>1.0</v>
@@ -4272,10 +4272,10 @@
         <v>2023.0</v>
       </c>
       <c r="C296" t="n" s="2">
-        <v>45207.0</v>
+        <v>45158.0</v>
       </c>
       <c r="D296" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="297">
@@ -4286,7 +4286,7 @@
         <v>2023.0</v>
       </c>
       <c r="C297" t="n" s="2">
-        <v>45214.0</v>
+        <v>45207.0</v>
       </c>
       <c r="D297" t="n">
         <v>3.0</v>
@@ -4300,10 +4300,10 @@
         <v>2023.0</v>
       </c>
       <c r="C298" t="n" s="2">
-        <v>45221.0</v>
+        <v>45214.0</v>
       </c>
       <c r="D298" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="299">
@@ -4314,7 +4314,7 @@
         <v>2023.0</v>
       </c>
       <c r="C299" t="n" s="2">
-        <v>45249.0</v>
+        <v>45221.0</v>
       </c>
       <c r="D299" t="n">
         <v>1.0</v>
@@ -4328,10 +4328,10 @@
         <v>2023.0</v>
       </c>
       <c r="C300" t="n" s="2">
-        <v>45256.0</v>
+        <v>45249.0</v>
       </c>
       <c r="D300" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="301">
@@ -4342,10 +4342,10 @@
         <v>2023.0</v>
       </c>
       <c r="C301" t="n" s="2">
-        <v>45263.0</v>
+        <v>45256.0</v>
       </c>
       <c r="D301" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="302">
@@ -4356,10 +4356,10 @@
         <v>2023.0</v>
       </c>
       <c r="C302" t="n" s="2">
-        <v>45270.0</v>
+        <v>45263.0</v>
       </c>
       <c r="D302" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="303">
@@ -4370,10 +4370,10 @@
         <v>2023.0</v>
       </c>
       <c r="C303" t="n" s="2">
-        <v>45277.0</v>
+        <v>45270.0</v>
       </c>
       <c r="D303" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="304">
@@ -4384,10 +4384,10 @@
         <v>2023.0</v>
       </c>
       <c r="C304" t="n" s="2">
-        <v>45284.0</v>
+        <v>45277.0</v>
       </c>
       <c r="D304" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="305">
@@ -4398,10 +4398,10 @@
         <v>2023.0</v>
       </c>
       <c r="C305" t="n" s="2">
-        <v>45291.0</v>
+        <v>45284.0</v>
       </c>
       <c r="D305" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="306">
@@ -4409,13 +4409,13 @@
         <v>6</v>
       </c>
       <c r="B306" t="n">
-        <v>2024.0</v>
+        <v>2023.0</v>
       </c>
       <c r="C306" t="n" s="2">
-        <v>45306.0</v>
+        <v>45291.0</v>
       </c>
       <c r="D306" t="n">
-        <v>7.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="307">
@@ -4426,10 +4426,10 @@
         <v>2024.0</v>
       </c>
       <c r="C307" t="n" s="2">
-        <v>45313.0</v>
+        <v>45306.0</v>
       </c>
       <c r="D307" t="n">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="308">
@@ -4440,10 +4440,10 @@
         <v>2024.0</v>
       </c>
       <c r="C308" t="n" s="2">
-        <v>45320.0</v>
+        <v>45313.0</v>
       </c>
       <c r="D308" t="n">
-        <v>19.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="309">
@@ -4454,10 +4454,10 @@
         <v>2024.0</v>
       </c>
       <c r="C309" t="n" s="2">
-        <v>45327.0</v>
+        <v>45320.0</v>
       </c>
       <c r="D309" t="n">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="310">
@@ -4468,10 +4468,10 @@
         <v>2024.0</v>
       </c>
       <c r="C310" t="n" s="2">
-        <v>45334.0</v>
+        <v>45327.0</v>
       </c>
       <c r="D310" t="n">
-        <v>9.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="311">
@@ -4482,10 +4482,10 @@
         <v>2024.0</v>
       </c>
       <c r="C311" t="n" s="2">
-        <v>45341.0</v>
+        <v>45334.0</v>
       </c>
       <c r="D311" t="n">
-        <v>12.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="312">
@@ -4496,7 +4496,7 @@
         <v>2024.0</v>
       </c>
       <c r="C312" t="n" s="2">
-        <v>45348.0</v>
+        <v>45341.0</v>
       </c>
       <c r="D312" t="n">
         <v>12.0</v>
@@ -4510,10 +4510,10 @@
         <v>2024.0</v>
       </c>
       <c r="C313" t="n" s="2">
-        <v>45355.0</v>
+        <v>45348.0</v>
       </c>
       <c r="D313" t="n">
-        <v>10.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="314">
@@ -4524,10 +4524,10 @@
         <v>2024.0</v>
       </c>
       <c r="C314" t="n" s="2">
-        <v>45362.0</v>
+        <v>45355.0</v>
       </c>
       <c r="D314" t="n">
-        <v>12.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="315">
@@ -4538,10 +4538,10 @@
         <v>2024.0</v>
       </c>
       <c r="C315" t="n" s="2">
-        <v>45369.0</v>
+        <v>45362.0</v>
       </c>
       <c r="D315" t="n">
-        <v>13.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="316">
@@ -4552,10 +4552,10 @@
         <v>2024.0</v>
       </c>
       <c r="C316" t="n" s="2">
-        <v>45376.0</v>
+        <v>45369.0</v>
       </c>
       <c r="D316" t="n">
-        <v>18.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="317">
@@ -4566,10 +4566,10 @@
         <v>2024.0</v>
       </c>
       <c r="C317" t="n" s="2">
-        <v>45383.0</v>
+        <v>45376.0</v>
       </c>
       <c r="D317" t="n">
-        <v>12.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="318">
@@ -4580,10 +4580,10 @@
         <v>2024.0</v>
       </c>
       <c r="C318" t="n" s="2">
-        <v>45390.0</v>
+        <v>45383.0</v>
       </c>
       <c r="D318" t="n">
-        <v>6.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="319">
@@ -4594,10 +4594,10 @@
         <v>2024.0</v>
       </c>
       <c r="C319" t="n" s="2">
-        <v>45397.0</v>
+        <v>45390.0</v>
       </c>
       <c r="D319" t="n">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="320">
@@ -4608,10 +4608,10 @@
         <v>2024.0</v>
       </c>
       <c r="C320" t="n" s="2">
-        <v>45404.0</v>
+        <v>45397.0</v>
       </c>
       <c r="D320" t="n">
-        <v>3.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="321">
@@ -4622,10 +4622,10 @@
         <v>2024.0</v>
       </c>
       <c r="C321" t="n" s="2">
-        <v>45411.0</v>
+        <v>45404.0</v>
       </c>
       <c r="D321" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="322">
@@ -4636,10 +4636,10 @@
         <v>2024.0</v>
       </c>
       <c r="C322" t="n" s="2">
-        <v>45418.0</v>
+        <v>45411.0</v>
       </c>
       <c r="D322" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="323">
@@ -4650,10 +4650,10 @@
         <v>2024.0</v>
       </c>
       <c r="C323" t="n" s="2">
-        <v>45425.0</v>
+        <v>45418.0</v>
       </c>
       <c r="D323" t="n">
-        <v>9.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="324">
@@ -4664,10 +4664,10 @@
         <v>2024.0</v>
       </c>
       <c r="C324" t="n" s="2">
-        <v>45432.0</v>
+        <v>45425.0</v>
       </c>
       <c r="D324" t="n">
-        <v>6.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="325">
@@ -4678,7 +4678,7 @@
         <v>2024.0</v>
       </c>
       <c r="C325" t="n" s="2">
-        <v>45439.0</v>
+        <v>45432.0</v>
       </c>
       <c r="D325" t="n">
         <v>6.0</v>
@@ -4692,10 +4692,10 @@
         <v>2024.0</v>
       </c>
       <c r="C326" t="n" s="2">
-        <v>45446.0</v>
+        <v>45439.0</v>
       </c>
       <c r="D326" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="327">
@@ -4706,10 +4706,10 @@
         <v>2024.0</v>
       </c>
       <c r="C327" t="n" s="2">
-        <v>45453.0</v>
+        <v>45446.0</v>
       </c>
       <c r="D327" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="328">
@@ -4720,7 +4720,7 @@
         <v>2024.0</v>
       </c>
       <c r="C328" t="n" s="2">
-        <v>45460.0</v>
+        <v>45453.0</v>
       </c>
       <c r="D328" t="n">
         <v>4.0</v>
@@ -4734,7 +4734,7 @@
         <v>2024.0</v>
       </c>
       <c r="C329" t="n" s="2">
-        <v>45467.0</v>
+        <v>45460.0</v>
       </c>
       <c r="D329" t="n">
         <v>4.0</v>
@@ -4748,10 +4748,10 @@
         <v>2024.0</v>
       </c>
       <c r="C330" t="n" s="2">
-        <v>45474.0</v>
+        <v>45467.0</v>
       </c>
       <c r="D330" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="331">
@@ -4762,10 +4762,10 @@
         <v>2024.0</v>
       </c>
       <c r="C331" t="n" s="2">
-        <v>45481.0</v>
+        <v>45474.0</v>
       </c>
       <c r="D331" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="332">
@@ -4776,10 +4776,10 @@
         <v>2024.0</v>
       </c>
       <c r="C332" t="n" s="2">
-        <v>45488.0</v>
+        <v>45481.0</v>
       </c>
       <c r="D332" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="333">
@@ -4790,10 +4790,10 @@
         <v>2024.0</v>
       </c>
       <c r="C333" t="n" s="2">
-        <v>45495.0</v>
+        <v>45488.0</v>
       </c>
       <c r="D333" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="334">
@@ -4804,10 +4804,10 @@
         <v>2024.0</v>
       </c>
       <c r="C334" t="n" s="2">
-        <v>45502.0</v>
+        <v>45495.0</v>
       </c>
       <c r="D334" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="335">
@@ -4818,10 +4818,10 @@
         <v>2024.0</v>
       </c>
       <c r="C335" t="n" s="2">
-        <v>45509.0</v>
+        <v>45502.0</v>
       </c>
       <c r="D335" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="336">
@@ -4832,7 +4832,7 @@
         <v>2024.0</v>
       </c>
       <c r="C336" t="n" s="2">
-        <v>45523.0</v>
+        <v>45509.0</v>
       </c>
       <c r="D336" t="n">
         <v>1.0</v>
@@ -4846,7 +4846,7 @@
         <v>2024.0</v>
       </c>
       <c r="C337" t="n" s="2">
-        <v>45551.0</v>
+        <v>45523.0</v>
       </c>
       <c r="D337" t="n">
         <v>1.0</v>
@@ -4860,7 +4860,7 @@
         <v>2024.0</v>
       </c>
       <c r="C338" t="n" s="2">
-        <v>45558.0</v>
+        <v>45551.0</v>
       </c>
       <c r="D338" t="n">
         <v>1.0</v>
@@ -4874,10 +4874,10 @@
         <v>2024.0</v>
       </c>
       <c r="C339" t="n" s="2">
-        <v>45572.0</v>
+        <v>45558.0</v>
       </c>
       <c r="D339" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="340">
@@ -4888,10 +4888,10 @@
         <v>2024.0</v>
       </c>
       <c r="C340" t="n" s="2">
-        <v>45593.0</v>
+        <v>45572.0</v>
       </c>
       <c r="D340" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="341">
@@ -4902,10 +4902,10 @@
         <v>2024.0</v>
       </c>
       <c r="C341" t="n" s="2">
-        <v>45614.0</v>
+        <v>45593.0</v>
       </c>
       <c r="D341" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="342">
@@ -4916,10 +4916,10 @@
         <v>2024.0</v>
       </c>
       <c r="C342" t="n" s="2">
-        <v>45621.0</v>
+        <v>45614.0</v>
       </c>
       <c r="D342" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="343">
@@ -4930,7 +4930,7 @@
         <v>2024.0</v>
       </c>
       <c r="C343" t="n" s="2">
-        <v>45635.0</v>
+        <v>45621.0</v>
       </c>
       <c r="D343" t="n">
         <v>1.0</v>
@@ -4944,7 +4944,7 @@
         <v>2024.0</v>
       </c>
       <c r="C344" t="n" s="2">
-        <v>45649.0</v>
+        <v>45635.0</v>
       </c>
       <c r="D344" t="n">
         <v>1.0</v>
@@ -4955,13 +4955,13 @@
         <v>6</v>
       </c>
       <c r="B345" t="n">
-        <v>2025.0</v>
+        <v>2024.0</v>
       </c>
       <c r="C345" t="n" s="2">
-        <v>45665.0</v>
+        <v>45649.0</v>
       </c>
       <c r="D345" t="n">
-        <v>9.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="346">
@@ -4972,10 +4972,10 @@
         <v>2025.0</v>
       </c>
       <c r="C346" t="n" s="2">
-        <v>45672.0</v>
+        <v>45665.0</v>
       </c>
       <c r="D346" t="n">
-        <v>3.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="347">
@@ -4986,10 +4986,10 @@
         <v>2025.0</v>
       </c>
       <c r="C347" t="n" s="2">
-        <v>45679.0</v>
+        <v>45672.0</v>
       </c>
       <c r="D347" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="348">
@@ -5000,10 +5000,10 @@
         <v>2025.0</v>
       </c>
       <c r="C348" t="n" s="2">
-        <v>45686.0</v>
+        <v>45679.0</v>
       </c>
       <c r="D348" t="n">
-        <v>8.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="349">
@@ -5014,10 +5014,10 @@
         <v>2025.0</v>
       </c>
       <c r="C349" t="n" s="2">
-        <v>45693.0</v>
+        <v>45686.0</v>
       </c>
       <c r="D349" t="n">
-        <v>3.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="350">
@@ -5028,10 +5028,10 @@
         <v>2025.0</v>
       </c>
       <c r="C350" t="n" s="2">
-        <v>45700.0</v>
+        <v>45693.0</v>
       </c>
       <c r="D350" t="n">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="351">
@@ -5042,10 +5042,10 @@
         <v>2025.0</v>
       </c>
       <c r="C351" t="n" s="2">
-        <v>45707.0</v>
+        <v>45700.0</v>
       </c>
       <c r="D351" t="n">
-        <v>8.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="352">
@@ -5056,10 +5056,10 @@
         <v>2025.0</v>
       </c>
       <c r="C352" t="n" s="2">
-        <v>45714.0</v>
+        <v>45707.0</v>
       </c>
       <c r="D352" t="n">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="353">
@@ -5070,10 +5070,10 @@
         <v>2025.0</v>
       </c>
       <c r="C353" t="n" s="2">
-        <v>45721.0</v>
+        <v>45714.0</v>
       </c>
       <c r="D353" t="n">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="354">
@@ -5084,10 +5084,10 @@
         <v>2025.0</v>
       </c>
       <c r="C354" t="n" s="2">
-        <v>45728.0</v>
+        <v>45721.0</v>
       </c>
       <c r="D354" t="n">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="355">
@@ -5098,10 +5098,10 @@
         <v>2025.0</v>
       </c>
       <c r="C355" t="n" s="2">
-        <v>45735.0</v>
+        <v>45728.0</v>
       </c>
       <c r="D355" t="n">
-        <v>4.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="356">
@@ -5112,10 +5112,10 @@
         <v>2025.0</v>
       </c>
       <c r="C356" t="n" s="2">
-        <v>45742.0</v>
+        <v>45735.0</v>
       </c>
       <c r="D356" t="n">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="357">
@@ -5126,10 +5126,10 @@
         <v>2025.0</v>
       </c>
       <c r="C357" t="n" s="2">
-        <v>45749.0</v>
+        <v>45742.0</v>
       </c>
       <c r="D357" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="358">
@@ -5140,10 +5140,10 @@
         <v>2025.0</v>
       </c>
       <c r="C358" t="n" s="2">
-        <v>45756.0</v>
+        <v>45749.0</v>
       </c>
       <c r="D358" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="359">
@@ -5154,10 +5154,10 @@
         <v>2025.0</v>
       </c>
       <c r="C359" t="n" s="2">
-        <v>45763.0</v>
+        <v>45756.0</v>
       </c>
       <c r="D359" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="360">
@@ -5168,7 +5168,7 @@
         <v>2025.0</v>
       </c>
       <c r="C360" t="n" s="2">
-        <v>45770.0</v>
+        <v>45763.0</v>
       </c>
       <c r="D360" t="n">
         <v>4.0</v>
@@ -5182,10 +5182,10 @@
         <v>2025.0</v>
       </c>
       <c r="C361" t="n" s="2">
-        <v>45777.0</v>
+        <v>45770.0</v>
       </c>
       <c r="D361" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="362">
@@ -5196,7 +5196,7 @@
         <v>2025.0</v>
       </c>
       <c r="C362" t="n" s="2">
-        <v>45784.0</v>
+        <v>45777.0</v>
       </c>
       <c r="D362" t="n">
         <v>1.0</v>
@@ -5210,7 +5210,7 @@
         <v>2025.0</v>
       </c>
       <c r="C363" t="n" s="2">
-        <v>45791.0</v>
+        <v>45784.0</v>
       </c>
       <c r="D363" t="n">
         <v>1.0</v>
@@ -5224,7 +5224,7 @@
         <v>2025.0</v>
       </c>
       <c r="C364" t="n" s="2">
-        <v>45840.0</v>
+        <v>45791.0</v>
       </c>
       <c r="D364" t="n">
         <v>1.0</v>
@@ -5238,7 +5238,7 @@
         <v>2025.0</v>
       </c>
       <c r="C365" t="n" s="2">
-        <v>46001.0</v>
+        <v>45840.0</v>
       </c>
       <c r="D365" t="n">
         <v>1.0</v>
@@ -5249,10 +5249,10 @@
         <v>6</v>
       </c>
       <c r="B366" t="n">
-        <v>2026.0</v>
+        <v>2025.0</v>
       </c>
       <c r="C366" t="n" s="2">
-        <v>46037.0</v>
+        <v>46001.0</v>
       </c>
       <c r="D366" t="n">
         <v>1.0</v>
@@ -5260,13 +5260,13 @@
     </row>
     <row r="367">
       <c r="A367" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B367" t="n">
-        <v>2021.0</v>
+        <v>2026.0</v>
       </c>
       <c r="C367" t="n" s="2">
-        <v>44561.0</v>
+        <v>46037.0</v>
       </c>
       <c r="D367" t="n">
         <v>1.0</v>
@@ -5277,10 +5277,10 @@
         <v>7</v>
       </c>
       <c r="B368" t="n">
-        <v>2022.0</v>
+        <v>2021.0</v>
       </c>
       <c r="C368" t="n" s="2">
-        <v>44569.0</v>
+        <v>44561.0</v>
       </c>
       <c r="D368" t="n">
         <v>1.0</v>
@@ -5294,10 +5294,10 @@
         <v>2022.0</v>
       </c>
       <c r="C369" t="n" s="2">
-        <v>44576.0</v>
+        <v>44569.0</v>
       </c>
       <c r="D369" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="370">
@@ -5308,10 +5308,10 @@
         <v>2022.0</v>
       </c>
       <c r="C370" t="n" s="2">
-        <v>44583.0</v>
+        <v>44576.0</v>
       </c>
       <c r="D370" t="n">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="371">
@@ -5322,10 +5322,10 @@
         <v>2022.0</v>
       </c>
       <c r="C371" t="n" s="2">
-        <v>44590.0</v>
+        <v>44583.0</v>
       </c>
       <c r="D371" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="372">
@@ -5336,10 +5336,10 @@
         <v>2022.0</v>
       </c>
       <c r="C372" t="n" s="2">
-        <v>44604.0</v>
+        <v>44590.0</v>
       </c>
       <c r="D372" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="373">
@@ -5350,7 +5350,7 @@
         <v>2022.0</v>
       </c>
       <c r="C373" t="n" s="2">
-        <v>44611.0</v>
+        <v>44604.0</v>
       </c>
       <c r="D373" t="n">
         <v>3.0</v>
@@ -5364,10 +5364,10 @@
         <v>2022.0</v>
       </c>
       <c r="C374" t="n" s="2">
-        <v>44618.0</v>
+        <v>44611.0</v>
       </c>
       <c r="D374" t="n">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="375">
@@ -5378,7 +5378,7 @@
         <v>2022.0</v>
       </c>
       <c r="C375" t="n" s="2">
-        <v>44625.0</v>
+        <v>44618.0</v>
       </c>
       <c r="D375" t="n">
         <v>5.0</v>
@@ -5392,10 +5392,10 @@
         <v>2022.0</v>
       </c>
       <c r="C376" t="n" s="2">
-        <v>44632.0</v>
+        <v>44625.0</v>
       </c>
       <c r="D376" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="377">
@@ -5406,10 +5406,10 @@
         <v>2022.0</v>
       </c>
       <c r="C377" t="n" s="2">
-        <v>44639.0</v>
+        <v>44632.0</v>
       </c>
       <c r="D377" t="n">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="378">
@@ -5420,10 +5420,10 @@
         <v>2022.0</v>
       </c>
       <c r="C378" t="n" s="2">
-        <v>44646.0</v>
+        <v>44639.0</v>
       </c>
       <c r="D378" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="379">
@@ -5434,10 +5434,10 @@
         <v>2022.0</v>
       </c>
       <c r="C379" t="n" s="2">
-        <v>44653.0</v>
+        <v>44646.0</v>
       </c>
       <c r="D379" t="n">
-        <v>9.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="380">
@@ -5448,10 +5448,10 @@
         <v>2022.0</v>
       </c>
       <c r="C380" t="n" s="2">
-        <v>44660.0</v>
+        <v>44653.0</v>
       </c>
       <c r="D380" t="n">
-        <v>6.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="381">
@@ -5462,10 +5462,10 @@
         <v>2022.0</v>
       </c>
       <c r="C381" t="n" s="2">
-        <v>44667.0</v>
+        <v>44660.0</v>
       </c>
       <c r="D381" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="382">
@@ -5476,10 +5476,10 @@
         <v>2022.0</v>
       </c>
       <c r="C382" t="n" s="2">
-        <v>44674.0</v>
+        <v>44667.0</v>
       </c>
       <c r="D382" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="383">
@@ -5490,10 +5490,10 @@
         <v>2022.0</v>
       </c>
       <c r="C383" t="n" s="2">
-        <v>44681.0</v>
+        <v>44674.0</v>
       </c>
       <c r="D383" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="384">
@@ -5504,10 +5504,10 @@
         <v>2022.0</v>
       </c>
       <c r="C384" t="n" s="2">
-        <v>44688.0</v>
+        <v>44681.0</v>
       </c>
       <c r="D384" t="n">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="385">
@@ -5518,10 +5518,10 @@
         <v>2022.0</v>
       </c>
       <c r="C385" t="n" s="2">
-        <v>44695.0</v>
+        <v>44688.0</v>
       </c>
       <c r="D385" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="386">
@@ -5532,10 +5532,10 @@
         <v>2022.0</v>
       </c>
       <c r="C386" t="n" s="2">
-        <v>44702.0</v>
+        <v>44695.0</v>
       </c>
       <c r="D386" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="387">
@@ -5546,10 +5546,10 @@
         <v>2022.0</v>
       </c>
       <c r="C387" t="n" s="2">
-        <v>44709.0</v>
+        <v>44702.0</v>
       </c>
       <c r="D387" t="n">
-        <v>8.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="388">
@@ -5560,10 +5560,10 @@
         <v>2022.0</v>
       </c>
       <c r="C388" t="n" s="2">
-        <v>44716.0</v>
+        <v>44709.0</v>
       </c>
       <c r="D388" t="n">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="389">
@@ -5574,10 +5574,10 @@
         <v>2022.0</v>
       </c>
       <c r="C389" t="n" s="2">
-        <v>44723.0</v>
+        <v>44716.0</v>
       </c>
       <c r="D389" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="390">
@@ -5588,10 +5588,10 @@
         <v>2022.0</v>
       </c>
       <c r="C390" t="n" s="2">
-        <v>44730.0</v>
+        <v>44723.0</v>
       </c>
       <c r="D390" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="391">
@@ -5602,7 +5602,7 @@
         <v>2022.0</v>
       </c>
       <c r="C391" t="n" s="2">
-        <v>44737.0</v>
+        <v>44730.0</v>
       </c>
       <c r="D391" t="n">
         <v>4.0</v>
@@ -5616,10 +5616,10 @@
         <v>2022.0</v>
       </c>
       <c r="C392" t="n" s="2">
-        <v>44744.0</v>
+        <v>44737.0</v>
       </c>
       <c r="D392" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="393">
@@ -5630,10 +5630,10 @@
         <v>2022.0</v>
       </c>
       <c r="C393" t="n" s="2">
-        <v>44751.0</v>
+        <v>44744.0</v>
       </c>
       <c r="D393" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="394">
@@ -5644,10 +5644,10 @@
         <v>2022.0</v>
       </c>
       <c r="C394" t="n" s="2">
-        <v>44758.0</v>
+        <v>44751.0</v>
       </c>
       <c r="D394" t="n">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="395">
@@ -5658,10 +5658,10 @@
         <v>2022.0</v>
       </c>
       <c r="C395" t="n" s="2">
-        <v>44765.0</v>
+        <v>44758.0</v>
       </c>
       <c r="D395" t="n">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="396">
@@ -5672,10 +5672,10 @@
         <v>2022.0</v>
       </c>
       <c r="C396" t="n" s="2">
-        <v>44779.0</v>
+        <v>44765.0</v>
       </c>
       <c r="D396" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="397">
@@ -5686,10 +5686,10 @@
         <v>2022.0</v>
       </c>
       <c r="C397" t="n" s="2">
-        <v>44786.0</v>
+        <v>44779.0</v>
       </c>
       <c r="D397" t="n">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="398">
@@ -5700,10 +5700,10 @@
         <v>2022.0</v>
       </c>
       <c r="C398" t="n" s="2">
-        <v>44863.0</v>
+        <v>44786.0</v>
       </c>
       <c r="D398" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="399">
@@ -5714,10 +5714,10 @@
         <v>2022.0</v>
       </c>
       <c r="C399" t="n" s="2">
-        <v>44870.0</v>
+        <v>44863.0</v>
       </c>
       <c r="D399" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="400">
@@ -5728,10 +5728,10 @@
         <v>2022.0</v>
       </c>
       <c r="C400" t="n" s="2">
-        <v>44884.0</v>
+        <v>44870.0</v>
       </c>
       <c r="D400" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="401">
@@ -5742,7 +5742,7 @@
         <v>2022.0</v>
       </c>
       <c r="C401" t="n" s="2">
-        <v>44891.0</v>
+        <v>44884.0</v>
       </c>
       <c r="D401" t="n">
         <v>2.0</v>
@@ -5756,10 +5756,10 @@
         <v>2022.0</v>
       </c>
       <c r="C402" t="n" s="2">
-        <v>44898.0</v>
+        <v>44891.0</v>
       </c>
       <c r="D402" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="403">
@@ -5770,10 +5770,10 @@
         <v>2022.0</v>
       </c>
       <c r="C403" t="n" s="2">
-        <v>44912.0</v>
+        <v>44898.0</v>
       </c>
       <c r="D403" t="n">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="404">
@@ -5784,10 +5784,10 @@
         <v>2022.0</v>
       </c>
       <c r="C404" t="n" s="2">
-        <v>44919.0</v>
+        <v>44912.0</v>
       </c>
       <c r="D404" t="n">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="405">
@@ -5798,10 +5798,10 @@
         <v>2022.0</v>
       </c>
       <c r="C405" t="n" s="2">
-        <v>44926.0</v>
+        <v>44919.0</v>
       </c>
       <c r="D405" t="n">
-        <v>12.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="406">
@@ -5809,13 +5809,13 @@
         <v>7</v>
       </c>
       <c r="B406" t="n">
-        <v>2023.0</v>
+        <v>2022.0</v>
       </c>
       <c r="C406" t="n" s="2">
-        <v>44934.0</v>
+        <v>44926.0</v>
       </c>
       <c r="D406" t="n">
-        <v>4.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="407">
@@ -5826,10 +5826,10 @@
         <v>2023.0</v>
       </c>
       <c r="C407" t="n" s="2">
-        <v>44941.0</v>
+        <v>44934.0</v>
       </c>
       <c r="D407" t="n">
-        <v>16.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="408">
@@ -5840,10 +5840,10 @@
         <v>2023.0</v>
       </c>
       <c r="C408" t="n" s="2">
-        <v>44948.0</v>
+        <v>44941.0</v>
       </c>
       <c r="D408" t="n">
-        <v>5.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="409">
@@ -5854,10 +5854,10 @@
         <v>2023.0</v>
       </c>
       <c r="C409" t="n" s="2">
-        <v>44955.0</v>
+        <v>44948.0</v>
       </c>
       <c r="D409" t="n">
-        <v>19.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="410">
@@ -5868,10 +5868,10 @@
         <v>2023.0</v>
       </c>
       <c r="C410" t="n" s="2">
-        <v>44962.0</v>
+        <v>44955.0</v>
       </c>
       <c r="D410" t="n">
-        <v>22.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="411">
@@ -5882,10 +5882,10 @@
         <v>2023.0</v>
       </c>
       <c r="C411" t="n" s="2">
-        <v>44969.0</v>
+        <v>44962.0</v>
       </c>
       <c r="D411" t="n">
-        <v>9.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="412">
@@ -5896,10 +5896,10 @@
         <v>2023.0</v>
       </c>
       <c r="C412" t="n" s="2">
-        <v>44976.0</v>
+        <v>44969.0</v>
       </c>
       <c r="D412" t="n">
-        <v>22.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="413">
@@ -5910,10 +5910,10 @@
         <v>2023.0</v>
       </c>
       <c r="C413" t="n" s="2">
-        <v>44983.0</v>
+        <v>44976.0</v>
       </c>
       <c r="D413" t="n">
-        <v>29.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="414">
@@ -5924,10 +5924,10 @@
         <v>2023.0</v>
       </c>
       <c r="C414" t="n" s="2">
-        <v>44990.0</v>
+        <v>44983.0</v>
       </c>
       <c r="D414" t="n">
-        <v>5.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="415">
@@ -5938,10 +5938,10 @@
         <v>2023.0</v>
       </c>
       <c r="C415" t="n" s="2">
-        <v>44997.0</v>
+        <v>44990.0</v>
       </c>
       <c r="D415" t="n">
-        <v>24.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="416">
@@ -5952,10 +5952,10 @@
         <v>2023.0</v>
       </c>
       <c r="C416" t="n" s="2">
-        <v>45004.0</v>
+        <v>44997.0</v>
       </c>
       <c r="D416" t="n">
-        <v>8.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="417">
@@ -5966,10 +5966,10 @@
         <v>2023.0</v>
       </c>
       <c r="C417" t="n" s="2">
-        <v>45011.0</v>
+        <v>45004.0</v>
       </c>
       <c r="D417" t="n">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="418">
@@ -5980,10 +5980,10 @@
         <v>2023.0</v>
       </c>
       <c r="C418" t="n" s="2">
-        <v>45018.0</v>
+        <v>45011.0</v>
       </c>
       <c r="D418" t="n">
-        <v>18.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="419">
@@ -5994,10 +5994,10 @@
         <v>2023.0</v>
       </c>
       <c r="C419" t="n" s="2">
-        <v>45025.0</v>
+        <v>45018.0</v>
       </c>
       <c r="D419" t="n">
-        <v>13.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="420">
@@ -6008,10 +6008,10 @@
         <v>2023.0</v>
       </c>
       <c r="C420" t="n" s="2">
-        <v>45032.0</v>
+        <v>45025.0</v>
       </c>
       <c r="D420" t="n">
-        <v>18.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="421">
@@ -6022,10 +6022,10 @@
         <v>2023.0</v>
       </c>
       <c r="C421" t="n" s="2">
-        <v>45039.0</v>
+        <v>45032.0</v>
       </c>
       <c r="D421" t="n">
-        <v>15.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="422">
@@ -6036,10 +6036,10 @@
         <v>2023.0</v>
       </c>
       <c r="C422" t="n" s="2">
-        <v>45046.0</v>
+        <v>45039.0</v>
       </c>
       <c r="D422" t="n">
-        <v>12.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="423">
@@ -6050,10 +6050,10 @@
         <v>2023.0</v>
       </c>
       <c r="C423" t="n" s="2">
-        <v>45053.0</v>
+        <v>45046.0</v>
       </c>
       <c r="D423" t="n">
-        <v>6.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="424">
@@ -6064,10 +6064,10 @@
         <v>2023.0</v>
       </c>
       <c r="C424" t="n" s="2">
-        <v>45060.0</v>
+        <v>45053.0</v>
       </c>
       <c r="D424" t="n">
-        <v>11.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="425">
@@ -6078,10 +6078,10 @@
         <v>2023.0</v>
       </c>
       <c r="C425" t="n" s="2">
-        <v>45067.0</v>
+        <v>45060.0</v>
       </c>
       <c r="D425" t="n">
-        <v>8.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="426">
@@ -6092,7 +6092,7 @@
         <v>2023.0</v>
       </c>
       <c r="C426" t="n" s="2">
-        <v>45074.0</v>
+        <v>45067.0</v>
       </c>
       <c r="D426" t="n">
         <v>8.0</v>
@@ -6106,10 +6106,10 @@
         <v>2023.0</v>
       </c>
       <c r="C427" t="n" s="2">
-        <v>45081.0</v>
+        <v>45074.0</v>
       </c>
       <c r="D427" t="n">
-        <v>5.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="428">
@@ -6120,10 +6120,10 @@
         <v>2023.0</v>
       </c>
       <c r="C428" t="n" s="2">
-        <v>45088.0</v>
+        <v>45081.0</v>
       </c>
       <c r="D428" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="429">
@@ -6134,10 +6134,10 @@
         <v>2023.0</v>
       </c>
       <c r="C429" t="n" s="2">
-        <v>45095.0</v>
+        <v>45088.0</v>
       </c>
       <c r="D429" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="430">
@@ -6148,10 +6148,10 @@
         <v>2023.0</v>
       </c>
       <c r="C430" t="n" s="2">
-        <v>45102.0</v>
+        <v>45095.0</v>
       </c>
       <c r="D430" t="n">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="431">
@@ -6162,10 +6162,10 @@
         <v>2023.0</v>
       </c>
       <c r="C431" t="n" s="2">
-        <v>45109.0</v>
+        <v>45102.0</v>
       </c>
       <c r="D431" t="n">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="432">
@@ -6176,10 +6176,10 @@
         <v>2023.0</v>
       </c>
       <c r="C432" t="n" s="2">
-        <v>45116.0</v>
+        <v>45109.0</v>
       </c>
       <c r="D432" t="n">
-        <v>3.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="433">
@@ -6190,10 +6190,10 @@
         <v>2023.0</v>
       </c>
       <c r="C433" t="n" s="2">
-        <v>45123.0</v>
+        <v>45116.0</v>
       </c>
       <c r="D433" t="n">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="434">
@@ -6204,7 +6204,7 @@
         <v>2023.0</v>
       </c>
       <c r="C434" t="n" s="2">
-        <v>45130.0</v>
+        <v>45123.0</v>
       </c>
       <c r="D434" t="n">
         <v>6.0</v>
@@ -6218,10 +6218,10 @@
         <v>2023.0</v>
       </c>
       <c r="C435" t="n" s="2">
-        <v>45137.0</v>
+        <v>45130.0</v>
       </c>
       <c r="D435" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="436">
@@ -6232,7 +6232,7 @@
         <v>2023.0</v>
       </c>
       <c r="C436" t="n" s="2">
-        <v>45144.0</v>
+        <v>45137.0</v>
       </c>
       <c r="D436" t="n">
         <v>2.0</v>
@@ -6246,7 +6246,7 @@
         <v>2023.0</v>
       </c>
       <c r="C437" t="n" s="2">
-        <v>45151.0</v>
+        <v>45144.0</v>
       </c>
       <c r="D437" t="n">
         <v>2.0</v>
@@ -6260,7 +6260,7 @@
         <v>2023.0</v>
       </c>
       <c r="C438" t="n" s="2">
-        <v>45165.0</v>
+        <v>45151.0</v>
       </c>
       <c r="D438" t="n">
         <v>2.0</v>
@@ -6274,7 +6274,7 @@
         <v>2023.0</v>
       </c>
       <c r="C439" t="n" s="2">
-        <v>45172.0</v>
+        <v>45165.0</v>
       </c>
       <c r="D439" t="n">
         <v>2.0</v>
@@ -6288,10 +6288,10 @@
         <v>2023.0</v>
       </c>
       <c r="C440" t="n" s="2">
-        <v>45179.0</v>
+        <v>45172.0</v>
       </c>
       <c r="D440" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="441">
@@ -6302,7 +6302,7 @@
         <v>2023.0</v>
       </c>
       <c r="C441" t="n" s="2">
-        <v>45186.0</v>
+        <v>45179.0</v>
       </c>
       <c r="D441" t="n">
         <v>1.0</v>
@@ -6316,7 +6316,7 @@
         <v>2023.0</v>
       </c>
       <c r="C442" t="n" s="2">
-        <v>45193.0</v>
+        <v>45186.0</v>
       </c>
       <c r="D442" t="n">
         <v>1.0</v>
@@ -6330,7 +6330,7 @@
         <v>2023.0</v>
       </c>
       <c r="C443" t="n" s="2">
-        <v>45200.0</v>
+        <v>45193.0</v>
       </c>
       <c r="D443" t="n">
         <v>1.0</v>
@@ -6344,7 +6344,7 @@
         <v>2023.0</v>
       </c>
       <c r="C444" t="n" s="2">
-        <v>45207.0</v>
+        <v>45200.0</v>
       </c>
       <c r="D444" t="n">
         <v>1.0</v>
@@ -6358,7 +6358,7 @@
         <v>2023.0</v>
       </c>
       <c r="C445" t="n" s="2">
-        <v>45235.0</v>
+        <v>45207.0</v>
       </c>
       <c r="D445" t="n">
         <v>1.0</v>
@@ -6372,10 +6372,10 @@
         <v>2023.0</v>
       </c>
       <c r="C446" t="n" s="2">
-        <v>45242.0</v>
+        <v>45235.0</v>
       </c>
       <c r="D446" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="447">
@@ -6386,10 +6386,10 @@
         <v>2023.0</v>
       </c>
       <c r="C447" t="n" s="2">
-        <v>45249.0</v>
+        <v>45242.0</v>
       </c>
       <c r="D447" t="n">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="448">
@@ -6400,10 +6400,10 @@
         <v>2023.0</v>
       </c>
       <c r="C448" t="n" s="2">
-        <v>45256.0</v>
+        <v>45249.0</v>
       </c>
       <c r="D448" t="n">
-        <v>9.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="449">
@@ -6414,10 +6414,10 @@
         <v>2023.0</v>
       </c>
       <c r="C449" t="n" s="2">
-        <v>45263.0</v>
+        <v>45256.0</v>
       </c>
       <c r="D449" t="n">
-        <v>12.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="450">
@@ -6428,10 +6428,10 @@
         <v>2023.0</v>
       </c>
       <c r="C450" t="n" s="2">
-        <v>45270.0</v>
+        <v>45263.0</v>
       </c>
       <c r="D450" t="n">
-        <v>6.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="451">
@@ -6442,10 +6442,10 @@
         <v>2023.0</v>
       </c>
       <c r="C451" t="n" s="2">
-        <v>45277.0</v>
+        <v>45270.0</v>
       </c>
       <c r="D451" t="n">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="452">
@@ -6456,7 +6456,7 @@
         <v>2023.0</v>
       </c>
       <c r="C452" t="n" s="2">
-        <v>45284.0</v>
+        <v>45277.0</v>
       </c>
       <c r="D452" t="n">
         <v>7.0</v>
@@ -6470,10 +6470,10 @@
         <v>2023.0</v>
       </c>
       <c r="C453" t="n" s="2">
-        <v>45291.0</v>
+        <v>45284.0</v>
       </c>
       <c r="D453" t="n">
-        <v>13.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="454">
@@ -6481,13 +6481,13 @@
         <v>7</v>
       </c>
       <c r="B454" t="n">
-        <v>2024.0</v>
+        <v>2023.0</v>
       </c>
       <c r="C454" t="n" s="2">
-        <v>45299.0</v>
+        <v>45291.0</v>
       </c>
       <c r="D454" t="n">
-        <v>6.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="455">
@@ -6498,10 +6498,10 @@
         <v>2024.0</v>
       </c>
       <c r="C455" t="n" s="2">
-        <v>45306.0</v>
+        <v>45299.0</v>
       </c>
       <c r="D455" t="n">
-        <v>11.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="456">
@@ -6512,10 +6512,10 @@
         <v>2024.0</v>
       </c>
       <c r="C456" t="n" s="2">
-        <v>45313.0</v>
+        <v>45306.0</v>
       </c>
       <c r="D456" t="n">
-        <v>5.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="457">
@@ -6526,10 +6526,10 @@
         <v>2024.0</v>
       </c>
       <c r="C457" t="n" s="2">
-        <v>45320.0</v>
+        <v>45313.0</v>
       </c>
       <c r="D457" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="458">
@@ -6540,10 +6540,10 @@
         <v>2024.0</v>
       </c>
       <c r="C458" t="n" s="2">
-        <v>45327.0</v>
+        <v>45320.0</v>
       </c>
       <c r="D458" t="n">
-        <v>9.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="459">
@@ -6554,10 +6554,10 @@
         <v>2024.0</v>
       </c>
       <c r="C459" t="n" s="2">
-        <v>45334.0</v>
+        <v>45327.0</v>
       </c>
       <c r="D459" t="n">
-        <v>3.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="460">
@@ -6568,10 +6568,10 @@
         <v>2024.0</v>
       </c>
       <c r="C460" t="n" s="2">
-        <v>45341.0</v>
+        <v>45334.0</v>
       </c>
       <c r="D460" t="n">
-        <v>21.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="461">
@@ -6582,10 +6582,10 @@
         <v>2024.0</v>
       </c>
       <c r="C461" t="n" s="2">
-        <v>45348.0</v>
+        <v>45341.0</v>
       </c>
       <c r="D461" t="n">
-        <v>1.0</v>
+        <v>21.0</v>
       </c>
     </row>
     <row r="462">
@@ -6596,10 +6596,10 @@
         <v>2024.0</v>
       </c>
       <c r="C462" t="n" s="2">
-        <v>45355.0</v>
+        <v>45348.0</v>
       </c>
       <c r="D462" t="n">
-        <v>9.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="463">
@@ -6610,10 +6610,10 @@
         <v>2024.0</v>
       </c>
       <c r="C463" t="n" s="2">
-        <v>45362.0</v>
+        <v>45355.0</v>
       </c>
       <c r="D463" t="n">
-        <v>4.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="464">
@@ -6624,10 +6624,10 @@
         <v>2024.0</v>
       </c>
       <c r="C464" t="n" s="2">
-        <v>45369.0</v>
+        <v>45362.0</v>
       </c>
       <c r="D464" t="n">
-        <v>14.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="465">
@@ -6638,10 +6638,10 @@
         <v>2024.0</v>
       </c>
       <c r="C465" t="n" s="2">
-        <v>45376.0</v>
+        <v>45369.0</v>
       </c>
       <c r="D465" t="n">
-        <v>4.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="466">
@@ -6652,10 +6652,10 @@
         <v>2024.0</v>
       </c>
       <c r="C466" t="n" s="2">
-        <v>45383.0</v>
+        <v>45376.0</v>
       </c>
       <c r="D466" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="467">
@@ -6666,10 +6666,10 @@
         <v>2024.0</v>
       </c>
       <c r="C467" t="n" s="2">
-        <v>45390.0</v>
+        <v>45383.0</v>
       </c>
       <c r="D467" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="468">
@@ -6680,7 +6680,7 @@
         <v>2024.0</v>
       </c>
       <c r="C468" t="n" s="2">
-        <v>45397.0</v>
+        <v>45390.0</v>
       </c>
       <c r="D468" t="n">
         <v>1.0</v>
@@ -6694,10 +6694,10 @@
         <v>2024.0</v>
       </c>
       <c r="C469" t="n" s="2">
-        <v>45404.0</v>
+        <v>45397.0</v>
       </c>
       <c r="D469" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="470">
@@ -6708,10 +6708,10 @@
         <v>2024.0</v>
       </c>
       <c r="C470" t="n" s="2">
-        <v>45411.0</v>
+        <v>45404.0</v>
       </c>
       <c r="D470" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="471">
@@ -6722,10 +6722,10 @@
         <v>2024.0</v>
       </c>
       <c r="C471" t="n" s="2">
-        <v>45439.0</v>
+        <v>45411.0</v>
       </c>
       <c r="D471" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="472">
@@ -6736,10 +6736,10 @@
         <v>2024.0</v>
       </c>
       <c r="C472" t="n" s="2">
-        <v>45446.0</v>
+        <v>45439.0</v>
       </c>
       <c r="D472" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="473">
@@ -6750,7 +6750,7 @@
         <v>2024.0</v>
       </c>
       <c r="C473" t="n" s="2">
-        <v>45460.0</v>
+        <v>45446.0</v>
       </c>
       <c r="D473" t="n">
         <v>1.0</v>
@@ -6764,7 +6764,7 @@
         <v>2024.0</v>
       </c>
       <c r="C474" t="n" s="2">
-        <v>45481.0</v>
+        <v>45460.0</v>
       </c>
       <c r="D474" t="n">
         <v>1.0</v>
@@ -6778,7 +6778,7 @@
         <v>2024.0</v>
       </c>
       <c r="C475" t="n" s="2">
-        <v>45516.0</v>
+        <v>45481.0</v>
       </c>
       <c r="D475" t="n">
         <v>1.0</v>
@@ -6792,7 +6792,7 @@
         <v>2024.0</v>
       </c>
       <c r="C476" t="n" s="2">
-        <v>45551.0</v>
+        <v>45516.0</v>
       </c>
       <c r="D476" t="n">
         <v>1.0</v>
@@ -6806,7 +6806,7 @@
         <v>2024.0</v>
       </c>
       <c r="C477" t="n" s="2">
-        <v>45579.0</v>
+        <v>45551.0</v>
       </c>
       <c r="D477" t="n">
         <v>1.0</v>
@@ -6820,7 +6820,7 @@
         <v>2024.0</v>
       </c>
       <c r="C478" t="n" s="2">
-        <v>45614.0</v>
+        <v>45579.0</v>
       </c>
       <c r="D478" t="n">
         <v>1.0</v>
@@ -6834,10 +6834,10 @@
         <v>2024.0</v>
       </c>
       <c r="C479" t="n" s="2">
-        <v>45635.0</v>
+        <v>45614.0</v>
       </c>
       <c r="D479" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="480">
@@ -6848,10 +6848,10 @@
         <v>2024.0</v>
       </c>
       <c r="C480" t="n" s="2">
-        <v>45642.0</v>
+        <v>45635.0</v>
       </c>
       <c r="D480" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="481">
@@ -6862,10 +6862,10 @@
         <v>2024.0</v>
       </c>
       <c r="C481" t="n" s="2">
-        <v>45649.0</v>
+        <v>45642.0</v>
       </c>
       <c r="D481" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="482">
@@ -6876,10 +6876,10 @@
         <v>2024.0</v>
       </c>
       <c r="C482" t="n" s="2">
-        <v>45656.0</v>
+        <v>45649.0</v>
       </c>
       <c r="D482" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="483">
@@ -6887,13 +6887,13 @@
         <v>7</v>
       </c>
       <c r="B483" t="n">
-        <v>2025.0</v>
+        <v>2024.0</v>
       </c>
       <c r="C483" t="n" s="2">
-        <v>45665.0</v>
+        <v>45656.0</v>
       </c>
       <c r="D483" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="484">
@@ -6904,10 +6904,10 @@
         <v>2025.0</v>
       </c>
       <c r="C484" t="n" s="2">
-        <v>45672.0</v>
+        <v>45665.0</v>
       </c>
       <c r="D484" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="485">
@@ -6918,7 +6918,7 @@
         <v>2025.0</v>
       </c>
       <c r="C485" t="n" s="2">
-        <v>45686.0</v>
+        <v>45672.0</v>
       </c>
       <c r="D485" t="n">
         <v>2.0</v>
@@ -6932,10 +6932,10 @@
         <v>2025.0</v>
       </c>
       <c r="C486" t="n" s="2">
-        <v>45693.0</v>
+        <v>45686.0</v>
       </c>
       <c r="D486" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="487">
@@ -6946,10 +6946,10 @@
         <v>2025.0</v>
       </c>
       <c r="C487" t="n" s="2">
-        <v>45700.0</v>
+        <v>45693.0</v>
       </c>
       <c r="D487" t="n">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="488">
@@ -6960,10 +6960,10 @@
         <v>2025.0</v>
       </c>
       <c r="C488" t="n" s="2">
-        <v>45707.0</v>
+        <v>45700.0</v>
       </c>
       <c r="D488" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="489">
@@ -6974,10 +6974,10 @@
         <v>2025.0</v>
       </c>
       <c r="C489" t="n" s="2">
-        <v>45714.0</v>
+        <v>45707.0</v>
       </c>
       <c r="D489" t="n">
-        <v>8.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="490">
@@ -6988,10 +6988,10 @@
         <v>2025.0</v>
       </c>
       <c r="C490" t="n" s="2">
-        <v>45721.0</v>
+        <v>45714.0</v>
       </c>
       <c r="D490" t="n">
-        <v>11.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="491">
@@ -7002,10 +7002,10 @@
         <v>2025.0</v>
       </c>
       <c r="C491" t="n" s="2">
-        <v>45728.0</v>
+        <v>45721.0</v>
       </c>
       <c r="D491" t="n">
-        <v>6.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="492">
@@ -7016,10 +7016,10 @@
         <v>2025.0</v>
       </c>
       <c r="C492" t="n" s="2">
-        <v>45735.0</v>
+        <v>45728.0</v>
       </c>
       <c r="D492" t="n">
-        <v>19.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="493">
@@ -7030,10 +7030,10 @@
         <v>2025.0</v>
       </c>
       <c r="C493" t="n" s="2">
-        <v>45742.0</v>
+        <v>45735.0</v>
       </c>
       <c r="D493" t="n">
-        <v>17.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="494">
@@ -7044,10 +7044,10 @@
         <v>2025.0</v>
       </c>
       <c r="C494" t="n" s="2">
-        <v>45749.0</v>
+        <v>45742.0</v>
       </c>
       <c r="D494" t="n">
-        <v>5.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="495">
@@ -7058,10 +7058,10 @@
         <v>2025.0</v>
       </c>
       <c r="C495" t="n" s="2">
-        <v>45756.0</v>
+        <v>45749.0</v>
       </c>
       <c r="D495" t="n">
-        <v>9.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="496">
@@ -7072,10 +7072,10 @@
         <v>2025.0</v>
       </c>
       <c r="C496" t="n" s="2">
-        <v>45763.0</v>
+        <v>45756.0</v>
       </c>
       <c r="D496" t="n">
-        <v>1.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="497">
@@ -7086,7 +7086,7 @@
         <v>2025.0</v>
       </c>
       <c r="C497" t="n" s="2">
-        <v>45770.0</v>
+        <v>45763.0</v>
       </c>
       <c r="D497" t="n">
         <v>1.0</v>
@@ -7100,10 +7100,10 @@
         <v>2025.0</v>
       </c>
       <c r="C498" t="n" s="2">
-        <v>45784.0</v>
+        <v>45770.0</v>
       </c>
       <c r="D498" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="499">
@@ -7114,10 +7114,10 @@
         <v>2025.0</v>
       </c>
       <c r="C499" t="n" s="2">
-        <v>45791.0</v>
+        <v>45784.0</v>
       </c>
       <c r="D499" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="500">
@@ -7128,10 +7128,10 @@
         <v>2025.0</v>
       </c>
       <c r="C500" t="n" s="2">
-        <v>45805.0</v>
+        <v>45791.0</v>
       </c>
       <c r="D500" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="501">
@@ -7142,10 +7142,10 @@
         <v>2025.0</v>
       </c>
       <c r="C501" t="n" s="2">
-        <v>45826.0</v>
+        <v>45805.0</v>
       </c>
       <c r="D501" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="502">
@@ -7156,7 +7156,7 @@
         <v>2025.0</v>
       </c>
       <c r="C502" t="n" s="2">
-        <v>45861.0</v>
+        <v>45826.0</v>
       </c>
       <c r="D502" t="n">
         <v>2.0</v>
@@ -7170,10 +7170,10 @@
         <v>2025.0</v>
       </c>
       <c r="C503" t="n" s="2">
-        <v>45868.0</v>
+        <v>45861.0</v>
       </c>
       <c r="D503" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="504">
@@ -7184,7 +7184,7 @@
         <v>2025.0</v>
       </c>
       <c r="C504" t="n" s="2">
-        <v>45889.0</v>
+        <v>45868.0</v>
       </c>
       <c r="D504" t="n">
         <v>1.0</v>
@@ -7198,7 +7198,7 @@
         <v>2025.0</v>
       </c>
       <c r="C505" t="n" s="2">
-        <v>45924.0</v>
+        <v>45889.0</v>
       </c>
       <c r="D505" t="n">
         <v>1.0</v>
@@ -7212,7 +7212,7 @@
         <v>2025.0</v>
       </c>
       <c r="C506" t="n" s="2">
-        <v>45945.0</v>
+        <v>45924.0</v>
       </c>
       <c r="D506" t="n">
         <v>1.0</v>
@@ -7226,10 +7226,10 @@
         <v>2025.0</v>
       </c>
       <c r="C507" t="n" s="2">
-        <v>45959.0</v>
+        <v>45945.0</v>
       </c>
       <c r="D507" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="508">
@@ -7240,7 +7240,7 @@
         <v>2025.0</v>
       </c>
       <c r="C508" t="n" s="2">
-        <v>46001.0</v>
+        <v>45959.0</v>
       </c>
       <c r="D508" t="n">
         <v>2.0</v>
@@ -7254,10 +7254,10 @@
         <v>2025.0</v>
       </c>
       <c r="C509" t="n" s="2">
-        <v>46008.0</v>
+        <v>46001.0</v>
       </c>
       <c r="D509" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="510">
@@ -7268,7 +7268,7 @@
         <v>2025.0</v>
       </c>
       <c r="C510" t="n" s="2">
-        <v>46022.0</v>
+        <v>46008.0</v>
       </c>
       <c r="D510" t="n">
         <v>1.0</v>
@@ -7279,10 +7279,10 @@
         <v>7</v>
       </c>
       <c r="B511" t="n">
-        <v>2026.0</v>
+        <v>2025.0</v>
       </c>
       <c r="C511" t="n" s="2">
-        <v>46030.0</v>
+        <v>46022.0</v>
       </c>
       <c r="D511" t="n">
         <v>1.0</v>
@@ -7296,7 +7296,7 @@
         <v>2026.0</v>
       </c>
       <c r="C512" t="n" s="2">
-        <v>46051.0</v>
+        <v>46030.0</v>
       </c>
       <c r="D512" t="n">
         <v>1.0</v>
@@ -7310,7 +7310,7 @@
         <v>2026.0</v>
       </c>
       <c r="C513" t="n" s="2">
-        <v>46058.0</v>
+        <v>46051.0</v>
       </c>
       <c r="D513" t="n">
         <v>1.0</v>
@@ -7324,10 +7324,10 @@
         <v>2026.0</v>
       </c>
       <c r="C514" t="n" s="2">
-        <v>46065.0</v>
+        <v>46058.0</v>
       </c>
       <c r="D514" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="515">
@@ -7338,21 +7338,21 @@
         <v>2026.0</v>
       </c>
       <c r="C515" t="n" s="2">
-        <v>46135.0</v>
+        <v>46065.0</v>
       </c>
       <c r="D515" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B516" t="n">
-        <v>2024.0</v>
+        <v>2026.0</v>
       </c>
       <c r="C516" t="n" s="2">
-        <v>45495.0</v>
+        <v>46135.0</v>
       </c>
       <c r="D516" t="n">
         <v>1.0</v>
@@ -7366,10 +7366,10 @@
         <v>2024.0</v>
       </c>
       <c r="C517" t="n" s="2">
-        <v>45502.0</v>
+        <v>45495.0</v>
       </c>
       <c r="D517" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="518">
@@ -7377,13 +7377,13 @@
         <v>8</v>
       </c>
       <c r="B518" t="n">
-        <v>2025.0</v>
+        <v>2024.0</v>
       </c>
       <c r="C518" t="n" s="2">
-        <v>45665.0</v>
+        <v>45502.0</v>
       </c>
       <c r="D518" t="n">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="519">
@@ -7394,10 +7394,10 @@
         <v>2025.0</v>
       </c>
       <c r="C519" t="n" s="2">
-        <v>45672.0</v>
+        <v>45665.0</v>
       </c>
       <c r="D519" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="520">
@@ -7408,10 +7408,10 @@
         <v>2025.0</v>
       </c>
       <c r="C520" t="n" s="2">
-        <v>45679.0</v>
+        <v>45672.0</v>
       </c>
       <c r="D520" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="521">
@@ -7422,10 +7422,10 @@
         <v>2025.0</v>
       </c>
       <c r="C521" t="n" s="2">
-        <v>45686.0</v>
+        <v>45679.0</v>
       </c>
       <c r="D521" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="522">
@@ -7436,10 +7436,10 @@
         <v>2025.0</v>
       </c>
       <c r="C522" t="n" s="2">
-        <v>45693.0</v>
+        <v>45686.0</v>
       </c>
       <c r="D522" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="523">
@@ -7450,10 +7450,10 @@
         <v>2025.0</v>
       </c>
       <c r="C523" t="n" s="2">
-        <v>45700.0</v>
+        <v>45693.0</v>
       </c>
       <c r="D523" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="524">
@@ -7464,10 +7464,10 @@
         <v>2025.0</v>
       </c>
       <c r="C524" t="n" s="2">
-        <v>45707.0</v>
+        <v>45700.0</v>
       </c>
       <c r="D524" t="n">
-        <v>7.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="525">
@@ -7478,10 +7478,10 @@
         <v>2025.0</v>
       </c>
       <c r="C525" t="n" s="2">
-        <v>45714.0</v>
+        <v>45707.0</v>
       </c>
       <c r="D525" t="n">
-        <v>3.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="526">
@@ -7492,10 +7492,10 @@
         <v>2025.0</v>
       </c>
       <c r="C526" t="n" s="2">
-        <v>45721.0</v>
+        <v>45714.0</v>
       </c>
       <c r="D526" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="527">
@@ -7506,10 +7506,10 @@
         <v>2025.0</v>
       </c>
       <c r="C527" t="n" s="2">
-        <v>45728.0</v>
+        <v>45721.0</v>
       </c>
       <c r="D527" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="528">
@@ -7520,7 +7520,7 @@
         <v>2025.0</v>
       </c>
       <c r="C528" t="n" s="2">
-        <v>45742.0</v>
+        <v>45728.0</v>
       </c>
       <c r="D528" t="n">
         <v>1.0</v>
@@ -7534,7 +7534,7 @@
         <v>2025.0</v>
       </c>
       <c r="C529" t="n" s="2">
-        <v>45749.0</v>
+        <v>45742.0</v>
       </c>
       <c r="D529" t="n">
         <v>1.0</v>
@@ -7548,7 +7548,7 @@
         <v>2025.0</v>
       </c>
       <c r="C530" t="n" s="2">
-        <v>45763.0</v>
+        <v>45749.0</v>
       </c>
       <c r="D530" t="n">
         <v>1.0</v>
@@ -7562,10 +7562,10 @@
         <v>2025.0</v>
       </c>
       <c r="C531" t="n" s="2">
-        <v>45777.0</v>
+        <v>45763.0</v>
       </c>
       <c r="D531" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="532">
@@ -7576,10 +7576,10 @@
         <v>2025.0</v>
       </c>
       <c r="C532" t="n" s="2">
-        <v>45784.0</v>
+        <v>45777.0</v>
       </c>
       <c r="D532" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="533">
@@ -7590,7 +7590,7 @@
         <v>2025.0</v>
       </c>
       <c r="C533" t="n" s="2">
-        <v>45798.0</v>
+        <v>45784.0</v>
       </c>
       <c r="D533" t="n">
         <v>1.0</v>
@@ -7604,7 +7604,7 @@
         <v>2025.0</v>
       </c>
       <c r="C534" t="n" s="2">
-        <v>45805.0</v>
+        <v>45798.0</v>
       </c>
       <c r="D534" t="n">
         <v>1.0</v>
@@ -7618,10 +7618,10 @@
         <v>2025.0</v>
       </c>
       <c r="C535" t="n" s="2">
-        <v>45812.0</v>
+        <v>45805.0</v>
       </c>
       <c r="D535" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="536">
@@ -7632,7 +7632,7 @@
         <v>2025.0</v>
       </c>
       <c r="C536" t="n" s="2">
-        <v>45819.0</v>
+        <v>45812.0</v>
       </c>
       <c r="D536" t="n">
         <v>2.0</v>
@@ -7646,7 +7646,7 @@
         <v>2025.0</v>
       </c>
       <c r="C537" t="n" s="2">
-        <v>45833.0</v>
+        <v>45819.0</v>
       </c>
       <c r="D537" t="n">
         <v>2.0</v>
@@ -7660,10 +7660,10 @@
         <v>2025.0</v>
       </c>
       <c r="C538" t="n" s="2">
-        <v>45847.0</v>
+        <v>45833.0</v>
       </c>
       <c r="D538" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="539">
@@ -7674,10 +7674,10 @@
         <v>2025.0</v>
       </c>
       <c r="C539" t="n" s="2">
-        <v>45854.0</v>
+        <v>45847.0</v>
       </c>
       <c r="D539" t="n">
-        <v>8.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="540">
@@ -7688,10 +7688,10 @@
         <v>2025.0</v>
       </c>
       <c r="C540" t="n" s="2">
-        <v>45861.0</v>
+        <v>45854.0</v>
       </c>
       <c r="D540" t="n">
-        <v>12.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="541">
@@ -7702,10 +7702,10 @@
         <v>2025.0</v>
       </c>
       <c r="C541" t="n" s="2">
-        <v>45868.0</v>
+        <v>45861.0</v>
       </c>
       <c r="D541" t="n">
-        <v>6.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="542">
@@ -7716,10 +7716,10 @@
         <v>2025.0</v>
       </c>
       <c r="C542" t="n" s="2">
-        <v>45875.0</v>
+        <v>45868.0</v>
       </c>
       <c r="D542" t="n">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="543">
@@ -7730,7 +7730,7 @@
         <v>2025.0</v>
       </c>
       <c r="C543" t="n" s="2">
-        <v>45896.0</v>
+        <v>45875.0</v>
       </c>
       <c r="D543" t="n">
         <v>1.0</v>
@@ -7744,7 +7744,7 @@
         <v>2025.0</v>
       </c>
       <c r="C544" t="n" s="2">
-        <v>45903.0</v>
+        <v>45896.0</v>
       </c>
       <c r="D544" t="n">
         <v>1.0</v>
@@ -7758,7 +7758,7 @@
         <v>2025.0</v>
       </c>
       <c r="C545" t="n" s="2">
-        <v>45931.0</v>
+        <v>45903.0</v>
       </c>
       <c r="D545" t="n">
         <v>1.0</v>
@@ -7772,10 +7772,10 @@
         <v>2025.0</v>
       </c>
       <c r="C546" t="n" s="2">
-        <v>45938.0</v>
+        <v>45931.0</v>
       </c>
       <c r="D546" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="547">
@@ -7786,10 +7786,10 @@
         <v>2025.0</v>
       </c>
       <c r="C547" t="n" s="2">
-        <v>45945.0</v>
+        <v>45938.0</v>
       </c>
       <c r="D547" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="548">
@@ -7800,7 +7800,7 @@
         <v>2025.0</v>
       </c>
       <c r="C548" t="n" s="2">
-        <v>45966.0</v>
+        <v>45945.0</v>
       </c>
       <c r="D548" t="n">
         <v>2.0</v>
@@ -7814,10 +7814,10 @@
         <v>2025.0</v>
       </c>
       <c r="C549" t="n" s="2">
-        <v>45973.0</v>
+        <v>45966.0</v>
       </c>
       <c r="D549" t="n">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="550">
@@ -7828,10 +7828,10 @@
         <v>2025.0</v>
       </c>
       <c r="C550" t="n" s="2">
-        <v>45980.0</v>
+        <v>45973.0</v>
       </c>
       <c r="D550" t="n">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="551">
@@ -7842,10 +7842,10 @@
         <v>2025.0</v>
       </c>
       <c r="C551" t="n" s="2">
-        <v>45987.0</v>
+        <v>45980.0</v>
       </c>
       <c r="D551" t="n">
-        <v>20.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="552">
@@ -7856,10 +7856,10 @@
         <v>2025.0</v>
       </c>
       <c r="C552" t="n" s="2">
-        <v>45994.0</v>
+        <v>45987.0</v>
       </c>
       <c r="D552" t="n">
-        <v>5.0</v>
+        <v>20.0</v>
       </c>
     </row>
     <row r="553">
@@ -7870,10 +7870,10 @@
         <v>2025.0</v>
       </c>
       <c r="C553" t="n" s="2">
-        <v>46001.0</v>
+        <v>45994.0</v>
       </c>
       <c r="D553" t="n">
-        <v>8.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="554">
@@ -7884,10 +7884,10 @@
         <v>2025.0</v>
       </c>
       <c r="C554" t="n" s="2">
-        <v>46008.0</v>
+        <v>46001.0</v>
       </c>
       <c r="D554" t="n">
-        <v>24.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="555">
@@ -7898,10 +7898,10 @@
         <v>2025.0</v>
       </c>
       <c r="C555" t="n" s="2">
-        <v>46015.0</v>
+        <v>46008.0</v>
       </c>
       <c r="D555" t="n">
-        <v>13.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="556">
@@ -7912,10 +7912,10 @@
         <v>2025.0</v>
       </c>
       <c r="C556" t="n" s="2">
-        <v>46022.0</v>
+        <v>46015.0</v>
       </c>
       <c r="D556" t="n">
-        <v>8.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="557">
@@ -7926,10 +7926,10 @@
         <v>2025.0</v>
       </c>
       <c r="C557" t="n" s="2">
-        <v>46029.0</v>
+        <v>46022.0</v>
       </c>
       <c r="D557" t="n">
-        <v>3.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="558">
@@ -7937,13 +7937,13 @@
         <v>8</v>
       </c>
       <c r="B558" t="n">
-        <v>2026.0</v>
+        <v>2025.0</v>
       </c>
       <c r="C558" t="n" s="2">
-        <v>46030.0</v>
+        <v>46029.0</v>
       </c>
       <c r="D558" t="n">
-        <v>24.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="559">
@@ -7954,10 +7954,10 @@
         <v>2026.0</v>
       </c>
       <c r="C559" t="n" s="2">
-        <v>46037.0</v>
+        <v>46030.0</v>
       </c>
       <c r="D559" t="n">
-        <v>22.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="560">
@@ -7968,10 +7968,10 @@
         <v>2026.0</v>
       </c>
       <c r="C560" t="n" s="2">
-        <v>46044.0</v>
+        <v>46037.0</v>
       </c>
       <c r="D560" t="n">
-        <v>27.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="561">
@@ -7982,10 +7982,10 @@
         <v>2026.0</v>
       </c>
       <c r="C561" t="n" s="2">
-        <v>46051.0</v>
+        <v>46044.0</v>
       </c>
       <c r="D561" t="n">
-        <v>18.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="562">
@@ -7996,10 +7996,10 @@
         <v>2026.0</v>
       </c>
       <c r="C562" t="n" s="2">
-        <v>46058.0</v>
+        <v>46051.0</v>
       </c>
       <c r="D562" t="n">
-        <v>25.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="563">
@@ -8010,10 +8010,10 @@
         <v>2026.0</v>
       </c>
       <c r="C563" t="n" s="2">
-        <v>46065.0</v>
+        <v>46058.0</v>
       </c>
       <c r="D563" t="n">
-        <v>22.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="564">
@@ -8024,10 +8024,10 @@
         <v>2026.0</v>
       </c>
       <c r="C564" t="n" s="2">
-        <v>46072.0</v>
+        <v>46065.0</v>
       </c>
       <c r="D564" t="n">
-        <v>13.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="565">
@@ -8038,10 +8038,10 @@
         <v>2026.0</v>
       </c>
       <c r="C565" t="n" s="2">
-        <v>46079.0</v>
+        <v>46072.0</v>
       </c>
       <c r="D565" t="n">
-        <v>24.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="566">
@@ -8052,10 +8052,10 @@
         <v>2026.0</v>
       </c>
       <c r="C566" t="n" s="2">
-        <v>46086.0</v>
+        <v>46079.0</v>
       </c>
       <c r="D566" t="n">
-        <v>26.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="567">
@@ -8066,10 +8066,10 @@
         <v>2026.0</v>
       </c>
       <c r="C567" t="n" s="2">
-        <v>46093.0</v>
+        <v>46086.0</v>
       </c>
       <c r="D567" t="n">
-        <v>33.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="568">
@@ -8080,10 +8080,10 @@
         <v>2026.0</v>
       </c>
       <c r="C568" t="n" s="2">
-        <v>46100.0</v>
+        <v>46093.0</v>
       </c>
       <c r="D568" t="n">
-        <v>25.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="569">
@@ -8094,10 +8094,10 @@
         <v>2026.0</v>
       </c>
       <c r="C569" t="n" s="2">
-        <v>46107.0</v>
+        <v>46100.0</v>
       </c>
       <c r="D569" t="n">
-        <v>31.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="570">
@@ -8108,10 +8108,10 @@
         <v>2026.0</v>
       </c>
       <c r="C570" t="n" s="2">
-        <v>46114.0</v>
+        <v>46107.0</v>
       </c>
       <c r="D570" t="n">
-        <v>10.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="571">
@@ -8122,10 +8122,10 @@
         <v>2026.0</v>
       </c>
       <c r="C571" t="n" s="2">
-        <v>46121.0</v>
+        <v>46114.0</v>
       </c>
       <c r="D571" t="n">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="572">
@@ -8136,10 +8136,10 @@
         <v>2026.0</v>
       </c>
       <c r="C572" t="n" s="2">
-        <v>46128.0</v>
+        <v>46121.0</v>
       </c>
       <c r="D572" t="n">
-        <v>15.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="573">
@@ -8150,10 +8150,24 @@
         <v>2026.0</v>
       </c>
       <c r="C573" t="n" s="2">
+        <v>46128.0</v>
+      </c>
+      <c r="D573" t="n">
+        <v>15.0</v>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="s">
+        <v>8</v>
+      </c>
+      <c r="B574" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C574" t="n" s="2">
         <v>46135.0</v>
       </c>
-      <c r="D573" t="n">
-        <v>16.0</v>
+      <c r="D574" t="n">
+        <v>19.0</v>
       </c>
     </row>
   </sheetData>
@@ -8179,7 +8193,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="n">
-        <v>48.0</v>
+        <v>45.0</v>
       </c>
     </row>
     <row r="3">
@@ -8195,7 +8209,7 @@
         <v>12</v>
       </c>
       <c r="B4" t="n">
-        <v>1215.0</v>
+        <v>1222.0</v>
       </c>
     </row>
     <row r="5">
@@ -8235,7 +8249,7 @@
         <v>21</v>
       </c>
       <c r="C2" t="n">
-        <v>191.0</v>
+        <v>192.0</v>
       </c>
     </row>
     <row r="3">
@@ -8246,7 +8260,7 @@
         <v>22</v>
       </c>
       <c r="C3" t="n">
-        <v>172.0</v>
+        <v>173.0</v>
       </c>
     </row>
     <row r="4">
@@ -8257,7 +8271,7 @@
         <v>19</v>
       </c>
       <c r="C4" t="n">
-        <v>137.0</v>
+        <v>138.0</v>
       </c>
     </row>
     <row r="5">
@@ -8301,7 +8315,7 @@
         <v>21</v>
       </c>
       <c r="C8" t="n">
-        <v>345.0</v>
+        <v>346.0</v>
       </c>
     </row>
     <row r="9">
@@ -8334,7 +8348,7 @@
         <v>19</v>
       </c>
       <c r="C11" t="n">
-        <v>34.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="12">
@@ -8378,7 +8392,7 @@
         <v>21</v>
       </c>
       <c r="C15" t="n">
-        <v>361.0</v>
+        <v>364.0</v>
       </c>
     </row>
     <row r="16">

--- a/Download/Focus_Positivi_ZR.xlsx
+++ b/Download/Focus_Positivi_ZR.xlsx
@@ -4233,7 +4233,7 @@
         <v>46135.0</v>
       </c>
       <c r="D293" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="294">
@@ -8209,7 +8209,7 @@
         <v>12</v>
       </c>
       <c r="B4" t="n">
-        <v>1222.0</v>
+        <v>1223.0</v>
       </c>
     </row>
     <row r="5">
@@ -8217,7 +8217,7 @@
         <v>13</v>
       </c>
       <c r="B5" t="n">
-        <v>2086.0</v>
+        <v>2088.0</v>
       </c>
     </row>
   </sheetData>
@@ -8293,7 +8293,7 @@
         <v>22</v>
       </c>
       <c r="C6" t="n">
-        <v>297.0</v>
+        <v>298.0</v>
       </c>
     </row>
     <row r="7">
@@ -8326,7 +8326,7 @@
         <v>22</v>
       </c>
       <c r="C9" t="n">
-        <v>329.0</v>
+        <v>330.0</v>
       </c>
     </row>
     <row r="10">
@@ -8392,7 +8392,7 @@
         <v>21</v>
       </c>
       <c r="C15" t="n">
-        <v>364.0</v>
+        <v>365.0</v>
       </c>
     </row>
     <row r="16">

--- a/Download/Focus_Positivi_ZR.xlsx
+++ b/Download/Focus_Positivi_ZR.xlsx
@@ -8167,7 +8167,7 @@
         <v>46135.0</v>
       </c>
       <c r="D574" t="n">
-        <v>19.0</v>
+        <v>23.0</v>
       </c>
     </row>
   </sheetData>
@@ -8209,7 +8209,7 @@
         <v>12</v>
       </c>
       <c r="B4" t="n">
-        <v>1223.0</v>
+        <v>1227.0</v>
       </c>
     </row>
     <row r="5">
@@ -8282,7 +8282,7 @@
         <v>21</v>
       </c>
       <c r="C5" t="n">
-        <v>414.0</v>
+        <v>416.0</v>
       </c>
     </row>
     <row r="6">
@@ -8293,7 +8293,7 @@
         <v>22</v>
       </c>
       <c r="C6" t="n">
-        <v>298.0</v>
+        <v>299.0</v>
       </c>
     </row>
     <row r="7">
@@ -8403,7 +8403,7 @@
         <v>22</v>
       </c>
       <c r="C16" t="n">
-        <v>354.0</v>
+        <v>355.0</v>
       </c>
     </row>
     <row r="17">

--- a/Download/Focus_Positivi_ZR.xlsx
+++ b/Download/Focus_Positivi_ZR.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="618" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="619" uniqueCount="23">
   <si>
     <t>NOME_REGIONE</t>
   </si>
@@ -1592,13 +1592,13 @@
     </row>
     <row r="105">
       <c r="A105" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B105" t="n">
-        <v>2021.0</v>
+        <v>2026.0</v>
       </c>
       <c r="C105" t="n" s="2">
-        <v>44561.0</v>
+        <v>46142.0</v>
       </c>
       <c r="D105" t="n">
         <v>1.0</v>
@@ -1609,13 +1609,13 @@
         <v>5</v>
       </c>
       <c r="B106" t="n">
-        <v>2022.0</v>
+        <v>2021.0</v>
       </c>
       <c r="C106" t="n" s="2">
-        <v>44576.0</v>
+        <v>44561.0</v>
       </c>
       <c r="D106" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="107">
@@ -1626,10 +1626,10 @@
         <v>2022.0</v>
       </c>
       <c r="C107" t="n" s="2">
-        <v>44583.0</v>
+        <v>44576.0</v>
       </c>
       <c r="D107" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="108">
@@ -1640,10 +1640,10 @@
         <v>2022.0</v>
       </c>
       <c r="C108" t="n" s="2">
-        <v>44590.0</v>
+        <v>44583.0</v>
       </c>
       <c r="D108" t="n">
-        <v>7.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="109">
@@ -1654,10 +1654,10 @@
         <v>2022.0</v>
       </c>
       <c r="C109" t="n" s="2">
-        <v>44597.0</v>
+        <v>44590.0</v>
       </c>
       <c r="D109" t="n">
-        <v>3.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="110">
@@ -1668,10 +1668,10 @@
         <v>2022.0</v>
       </c>
       <c r="C110" t="n" s="2">
-        <v>44604.0</v>
+        <v>44597.0</v>
       </c>
       <c r="D110" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="111">
@@ -1682,10 +1682,10 @@
         <v>2022.0</v>
       </c>
       <c r="C111" t="n" s="2">
-        <v>44611.0</v>
+        <v>44604.0</v>
       </c>
       <c r="D111" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="112">
@@ -1696,7 +1696,7 @@
         <v>2022.0</v>
       </c>
       <c r="C112" t="n" s="2">
-        <v>44618.0</v>
+        <v>44611.0</v>
       </c>
       <c r="D112" t="n">
         <v>1.0</v>
@@ -1710,10 +1710,10 @@
         <v>2022.0</v>
       </c>
       <c r="C113" t="n" s="2">
-        <v>44625.0</v>
+        <v>44618.0</v>
       </c>
       <c r="D113" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="114">
@@ -1724,10 +1724,10 @@
         <v>2022.0</v>
       </c>
       <c r="C114" t="n" s="2">
-        <v>44632.0</v>
+        <v>44625.0</v>
       </c>
       <c r="D114" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="115">
@@ -1738,10 +1738,10 @@
         <v>2022.0</v>
       </c>
       <c r="C115" t="n" s="2">
-        <v>44639.0</v>
+        <v>44632.0</v>
       </c>
       <c r="D115" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="116">
@@ -1752,7 +1752,7 @@
         <v>2022.0</v>
       </c>
       <c r="C116" t="n" s="2">
-        <v>44646.0</v>
+        <v>44639.0</v>
       </c>
       <c r="D116" t="n">
         <v>2.0</v>
@@ -1766,7 +1766,7 @@
         <v>2022.0</v>
       </c>
       <c r="C117" t="n" s="2">
-        <v>44653.0</v>
+        <v>44646.0</v>
       </c>
       <c r="D117" t="n">
         <v>2.0</v>
@@ -1780,10 +1780,10 @@
         <v>2022.0</v>
       </c>
       <c r="C118" t="n" s="2">
-        <v>44660.0</v>
+        <v>44653.0</v>
       </c>
       <c r="D118" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="119">
@@ -1794,10 +1794,10 @@
         <v>2022.0</v>
       </c>
       <c r="C119" t="n" s="2">
-        <v>44667.0</v>
+        <v>44660.0</v>
       </c>
       <c r="D119" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="120">
@@ -1808,7 +1808,7 @@
         <v>2022.0</v>
       </c>
       <c r="C120" t="n" s="2">
-        <v>44674.0</v>
+        <v>44667.0</v>
       </c>
       <c r="D120" t="n">
         <v>3.0</v>
@@ -1822,10 +1822,10 @@
         <v>2022.0</v>
       </c>
       <c r="C121" t="n" s="2">
-        <v>44681.0</v>
+        <v>44674.0</v>
       </c>
       <c r="D121" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="122">
@@ -1836,10 +1836,10 @@
         <v>2022.0</v>
       </c>
       <c r="C122" t="n" s="2">
-        <v>44688.0</v>
+        <v>44681.0</v>
       </c>
       <c r="D122" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="123">
@@ -1850,7 +1850,7 @@
         <v>2022.0</v>
       </c>
       <c r="C123" t="n" s="2">
-        <v>44695.0</v>
+        <v>44688.0</v>
       </c>
       <c r="D123" t="n">
         <v>3.0</v>
@@ -1864,10 +1864,10 @@
         <v>2022.0</v>
       </c>
       <c r="C124" t="n" s="2">
-        <v>44702.0</v>
+        <v>44695.0</v>
       </c>
       <c r="D124" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="125">
@@ -1878,10 +1878,10 @@
         <v>2022.0</v>
       </c>
       <c r="C125" t="n" s="2">
-        <v>44709.0</v>
+        <v>44702.0</v>
       </c>
       <c r="D125" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="126">
@@ -1892,10 +1892,10 @@
         <v>2022.0</v>
       </c>
       <c r="C126" t="n" s="2">
-        <v>44716.0</v>
+        <v>44709.0</v>
       </c>
       <c r="D126" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="127">
@@ -1906,7 +1906,7 @@
         <v>2022.0</v>
       </c>
       <c r="C127" t="n" s="2">
-        <v>44723.0</v>
+        <v>44716.0</v>
       </c>
       <c r="D127" t="n">
         <v>1.0</v>
@@ -1920,7 +1920,7 @@
         <v>2022.0</v>
       </c>
       <c r="C128" t="n" s="2">
-        <v>44730.0</v>
+        <v>44723.0</v>
       </c>
       <c r="D128" t="n">
         <v>1.0</v>
@@ -1934,7 +1934,7 @@
         <v>2022.0</v>
       </c>
       <c r="C129" t="n" s="2">
-        <v>44737.0</v>
+        <v>44730.0</v>
       </c>
       <c r="D129" t="n">
         <v>1.0</v>
@@ -1948,7 +1948,7 @@
         <v>2022.0</v>
       </c>
       <c r="C130" t="n" s="2">
-        <v>44744.0</v>
+        <v>44737.0</v>
       </c>
       <c r="D130" t="n">
         <v>1.0</v>
@@ -1962,7 +1962,7 @@
         <v>2022.0</v>
       </c>
       <c r="C131" t="n" s="2">
-        <v>44751.0</v>
+        <v>44744.0</v>
       </c>
       <c r="D131" t="n">
         <v>1.0</v>
@@ -1976,7 +1976,7 @@
         <v>2022.0</v>
       </c>
       <c r="C132" t="n" s="2">
-        <v>44758.0</v>
+        <v>44751.0</v>
       </c>
       <c r="D132" t="n">
         <v>1.0</v>
@@ -1990,7 +1990,7 @@
         <v>2022.0</v>
       </c>
       <c r="C133" t="n" s="2">
-        <v>44772.0</v>
+        <v>44758.0</v>
       </c>
       <c r="D133" t="n">
         <v>1.0</v>
@@ -2004,7 +2004,7 @@
         <v>2022.0</v>
       </c>
       <c r="C134" t="n" s="2">
-        <v>44793.0</v>
+        <v>44772.0</v>
       </c>
       <c r="D134" t="n">
         <v>1.0</v>
@@ -2018,7 +2018,7 @@
         <v>2022.0</v>
       </c>
       <c r="C135" t="n" s="2">
-        <v>44800.0</v>
+        <v>44793.0</v>
       </c>
       <c r="D135" t="n">
         <v>1.0</v>
@@ -2032,7 +2032,7 @@
         <v>2022.0</v>
       </c>
       <c r="C136" t="n" s="2">
-        <v>44828.0</v>
+        <v>44800.0</v>
       </c>
       <c r="D136" t="n">
         <v>1.0</v>
@@ -2046,7 +2046,7 @@
         <v>2022.0</v>
       </c>
       <c r="C137" t="n" s="2">
-        <v>44849.0</v>
+        <v>44828.0</v>
       </c>
       <c r="D137" t="n">
         <v>1.0</v>
@@ -2060,7 +2060,7 @@
         <v>2022.0</v>
       </c>
       <c r="C138" t="n" s="2">
-        <v>44856.0</v>
+        <v>44849.0</v>
       </c>
       <c r="D138" t="n">
         <v>1.0</v>
@@ -2074,7 +2074,7 @@
         <v>2022.0</v>
       </c>
       <c r="C139" t="n" s="2">
-        <v>44863.0</v>
+        <v>44856.0</v>
       </c>
       <c r="D139" t="n">
         <v>1.0</v>
@@ -2088,10 +2088,10 @@
         <v>2022.0</v>
       </c>
       <c r="C140" t="n" s="2">
-        <v>44884.0</v>
+        <v>44863.0</v>
       </c>
       <c r="D140" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="141">
@@ -2102,10 +2102,10 @@
         <v>2022.0</v>
       </c>
       <c r="C141" t="n" s="2">
-        <v>44891.0</v>
+        <v>44884.0</v>
       </c>
       <c r="D141" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="142">
@@ -2116,7 +2116,7 @@
         <v>2022.0</v>
       </c>
       <c r="C142" t="n" s="2">
-        <v>44905.0</v>
+        <v>44891.0</v>
       </c>
       <c r="D142" t="n">
         <v>1.0</v>
@@ -2130,7 +2130,7 @@
         <v>2022.0</v>
       </c>
       <c r="C143" t="n" s="2">
-        <v>44912.0</v>
+        <v>44905.0</v>
       </c>
       <c r="D143" t="n">
         <v>1.0</v>
@@ -2144,10 +2144,10 @@
         <v>2022.0</v>
       </c>
       <c r="C144" t="n" s="2">
-        <v>44919.0</v>
+        <v>44912.0</v>
       </c>
       <c r="D144" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="145">
@@ -2155,13 +2155,13 @@
         <v>5</v>
       </c>
       <c r="B145" t="n">
-        <v>2023.0</v>
+        <v>2022.0</v>
       </c>
       <c r="C145" t="n" s="2">
-        <v>44934.0</v>
+        <v>44919.0</v>
       </c>
       <c r="D145" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="146">
@@ -2172,10 +2172,10 @@
         <v>2023.0</v>
       </c>
       <c r="C146" t="n" s="2">
-        <v>44941.0</v>
+        <v>44934.0</v>
       </c>
       <c r="D146" t="n">
-        <v>8.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="147">
@@ -2186,10 +2186,10 @@
         <v>2023.0</v>
       </c>
       <c r="C147" t="n" s="2">
-        <v>44948.0</v>
+        <v>44941.0</v>
       </c>
       <c r="D147" t="n">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="148">
@@ -2200,10 +2200,10 @@
         <v>2023.0</v>
       </c>
       <c r="C148" t="n" s="2">
-        <v>44955.0</v>
+        <v>44948.0</v>
       </c>
       <c r="D148" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="149">
@@ -2214,10 +2214,10 @@
         <v>2023.0</v>
       </c>
       <c r="C149" t="n" s="2">
-        <v>44962.0</v>
+        <v>44955.0</v>
       </c>
       <c r="D149" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="150">
@@ -2228,7 +2228,7 @@
         <v>2023.0</v>
       </c>
       <c r="C150" t="n" s="2">
-        <v>44969.0</v>
+        <v>44962.0</v>
       </c>
       <c r="D150" t="n">
         <v>4.0</v>
@@ -2242,10 +2242,10 @@
         <v>2023.0</v>
       </c>
       <c r="C151" t="n" s="2">
-        <v>44976.0</v>
+        <v>44969.0</v>
       </c>
       <c r="D151" t="n">
-        <v>17.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="152">
@@ -2256,10 +2256,10 @@
         <v>2023.0</v>
       </c>
       <c r="C152" t="n" s="2">
-        <v>44983.0</v>
+        <v>44976.0</v>
       </c>
       <c r="D152" t="n">
-        <v>11.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="153">
@@ -2270,10 +2270,10 @@
         <v>2023.0</v>
       </c>
       <c r="C153" t="n" s="2">
-        <v>44990.0</v>
+        <v>44983.0</v>
       </c>
       <c r="D153" t="n">
-        <v>5.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="154">
@@ -2284,10 +2284,10 @@
         <v>2023.0</v>
       </c>
       <c r="C154" t="n" s="2">
-        <v>44997.0</v>
+        <v>44990.0</v>
       </c>
       <c r="D154" t="n">
-        <v>22.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="155">
@@ -2298,10 +2298,10 @@
         <v>2023.0</v>
       </c>
       <c r="C155" t="n" s="2">
-        <v>45004.0</v>
+        <v>44997.0</v>
       </c>
       <c r="D155" t="n">
-        <v>8.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="156">
@@ -2312,10 +2312,10 @@
         <v>2023.0</v>
       </c>
       <c r="C156" t="n" s="2">
-        <v>45011.0</v>
+        <v>45004.0</v>
       </c>
       <c r="D156" t="n">
-        <v>17.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="157">
@@ -2326,10 +2326,10 @@
         <v>2023.0</v>
       </c>
       <c r="C157" t="n" s="2">
-        <v>45018.0</v>
+        <v>45011.0</v>
       </c>
       <c r="D157" t="n">
-        <v>10.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="158">
@@ -2340,10 +2340,10 @@
         <v>2023.0</v>
       </c>
       <c r="C158" t="n" s="2">
-        <v>45025.0</v>
+        <v>45018.0</v>
       </c>
       <c r="D158" t="n">
-        <v>13.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="159">
@@ -2354,10 +2354,10 @@
         <v>2023.0</v>
       </c>
       <c r="C159" t="n" s="2">
-        <v>45032.0</v>
+        <v>45025.0</v>
       </c>
       <c r="D159" t="n">
-        <v>10.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="160">
@@ -2368,10 +2368,10 @@
         <v>2023.0</v>
       </c>
       <c r="C160" t="n" s="2">
-        <v>45039.0</v>
+        <v>45032.0</v>
       </c>
       <c r="D160" t="n">
-        <v>22.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="161">
@@ -2382,10 +2382,10 @@
         <v>2023.0</v>
       </c>
       <c r="C161" t="n" s="2">
-        <v>45046.0</v>
+        <v>45039.0</v>
       </c>
       <c r="D161" t="n">
-        <v>23.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="162">
@@ -2396,10 +2396,10 @@
         <v>2023.0</v>
       </c>
       <c r="C162" t="n" s="2">
-        <v>45053.0</v>
+        <v>45046.0</v>
       </c>
       <c r="D162" t="n">
-        <v>16.0</v>
+        <v>23.0</v>
       </c>
     </row>
     <row r="163">
@@ -2410,10 +2410,10 @@
         <v>2023.0</v>
       </c>
       <c r="C163" t="n" s="2">
-        <v>45060.0</v>
+        <v>45053.0</v>
       </c>
       <c r="D163" t="n">
-        <v>13.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="164">
@@ -2424,10 +2424,10 @@
         <v>2023.0</v>
       </c>
       <c r="C164" t="n" s="2">
-        <v>45067.0</v>
+        <v>45060.0</v>
       </c>
       <c r="D164" t="n">
-        <v>9.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="165">
@@ -2438,10 +2438,10 @@
         <v>2023.0</v>
       </c>
       <c r="C165" t="n" s="2">
-        <v>45074.0</v>
+        <v>45067.0</v>
       </c>
       <c r="D165" t="n">
-        <v>6.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="166">
@@ -2452,10 +2452,10 @@
         <v>2023.0</v>
       </c>
       <c r="C166" t="n" s="2">
-        <v>45081.0</v>
+        <v>45074.0</v>
       </c>
       <c r="D166" t="n">
-        <v>16.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="167">
@@ -2466,10 +2466,10 @@
         <v>2023.0</v>
       </c>
       <c r="C167" t="n" s="2">
-        <v>45088.0</v>
+        <v>45081.0</v>
       </c>
       <c r="D167" t="n">
-        <v>8.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="168">
@@ -2480,10 +2480,10 @@
         <v>2023.0</v>
       </c>
       <c r="C168" t="n" s="2">
-        <v>45095.0</v>
+        <v>45088.0</v>
       </c>
       <c r="D168" t="n">
-        <v>16.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="169">
@@ -2494,10 +2494,10 @@
         <v>2023.0</v>
       </c>
       <c r="C169" t="n" s="2">
-        <v>45102.0</v>
+        <v>45095.0</v>
       </c>
       <c r="D169" t="n">
-        <v>17.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="170">
@@ -2508,10 +2508,10 @@
         <v>2023.0</v>
       </c>
       <c r="C170" t="n" s="2">
-        <v>45109.0</v>
+        <v>45102.0</v>
       </c>
       <c r="D170" t="n">
-        <v>14.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="171">
@@ -2522,10 +2522,10 @@
         <v>2023.0</v>
       </c>
       <c r="C171" t="n" s="2">
-        <v>45116.0</v>
+        <v>45109.0</v>
       </c>
       <c r="D171" t="n">
-        <v>13.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="172">
@@ -2536,10 +2536,10 @@
         <v>2023.0</v>
       </c>
       <c r="C172" t="n" s="2">
-        <v>45123.0</v>
+        <v>45116.0</v>
       </c>
       <c r="D172" t="n">
-        <v>5.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="173">
@@ -2550,10 +2550,10 @@
         <v>2023.0</v>
       </c>
       <c r="C173" t="n" s="2">
-        <v>45130.0</v>
+        <v>45123.0</v>
       </c>
       <c r="D173" t="n">
-        <v>8.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="174">
@@ -2564,10 +2564,10 @@
         <v>2023.0</v>
       </c>
       <c r="C174" t="n" s="2">
-        <v>45137.0</v>
+        <v>45130.0</v>
       </c>
       <c r="D174" t="n">
-        <v>4.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="175">
@@ -2578,10 +2578,10 @@
         <v>2023.0</v>
       </c>
       <c r="C175" t="n" s="2">
-        <v>45144.0</v>
+        <v>45137.0</v>
       </c>
       <c r="D175" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="176">
@@ -2592,7 +2592,7 @@
         <v>2023.0</v>
       </c>
       <c r="C176" t="n" s="2">
-        <v>45151.0</v>
+        <v>45144.0</v>
       </c>
       <c r="D176" t="n">
         <v>2.0</v>
@@ -2606,10 +2606,10 @@
         <v>2023.0</v>
       </c>
       <c r="C177" t="n" s="2">
-        <v>45158.0</v>
+        <v>45151.0</v>
       </c>
       <c r="D177" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="178">
@@ -2620,7 +2620,7 @@
         <v>2023.0</v>
       </c>
       <c r="C178" t="n" s="2">
-        <v>45165.0</v>
+        <v>45158.0</v>
       </c>
       <c r="D178" t="n">
         <v>5.0</v>
@@ -2634,10 +2634,10 @@
         <v>2023.0</v>
       </c>
       <c r="C179" t="n" s="2">
-        <v>45172.0</v>
+        <v>45165.0</v>
       </c>
       <c r="D179" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="180">
@@ -2648,10 +2648,10 @@
         <v>2023.0</v>
       </c>
       <c r="C180" t="n" s="2">
-        <v>45179.0</v>
+        <v>45172.0</v>
       </c>
       <c r="D180" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="181">
@@ -2662,10 +2662,10 @@
         <v>2023.0</v>
       </c>
       <c r="C181" t="n" s="2">
-        <v>45186.0</v>
+        <v>45179.0</v>
       </c>
       <c r="D181" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="182">
@@ -2676,7 +2676,7 @@
         <v>2023.0</v>
       </c>
       <c r="C182" t="n" s="2">
-        <v>45193.0</v>
+        <v>45186.0</v>
       </c>
       <c r="D182" t="n">
         <v>1.0</v>
@@ -2690,10 +2690,10 @@
         <v>2023.0</v>
       </c>
       <c r="C183" t="n" s="2">
-        <v>45200.0</v>
+        <v>45193.0</v>
       </c>
       <c r="D183" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="184">
@@ -2704,10 +2704,10 @@
         <v>2023.0</v>
       </c>
       <c r="C184" t="n" s="2">
-        <v>45207.0</v>
+        <v>45200.0</v>
       </c>
       <c r="D184" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="185">
@@ -2718,10 +2718,10 @@
         <v>2023.0</v>
       </c>
       <c r="C185" t="n" s="2">
-        <v>45214.0</v>
+        <v>45207.0</v>
       </c>
       <c r="D185" t="n">
-        <v>8.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="186">
@@ -2732,7 +2732,7 @@
         <v>2023.0</v>
       </c>
       <c r="C186" t="n" s="2">
-        <v>45221.0</v>
+        <v>45214.0</v>
       </c>
       <c r="D186" t="n">
         <v>8.0</v>
@@ -2746,10 +2746,10 @@
         <v>2023.0</v>
       </c>
       <c r="C187" t="n" s="2">
-        <v>45228.0</v>
+        <v>45221.0</v>
       </c>
       <c r="D187" t="n">
-        <v>17.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="188">
@@ -2760,10 +2760,10 @@
         <v>2023.0</v>
       </c>
       <c r="C188" t="n" s="2">
-        <v>45235.0</v>
+        <v>45228.0</v>
       </c>
       <c r="D188" t="n">
-        <v>9.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="189">
@@ -2774,7 +2774,7 @@
         <v>2023.0</v>
       </c>
       <c r="C189" t="n" s="2">
-        <v>45242.0</v>
+        <v>45235.0</v>
       </c>
       <c r="D189" t="n">
         <v>9.0</v>
@@ -2788,10 +2788,10 @@
         <v>2023.0</v>
       </c>
       <c r="C190" t="n" s="2">
-        <v>45249.0</v>
+        <v>45242.0</v>
       </c>
       <c r="D190" t="n">
-        <v>14.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="191">
@@ -2802,10 +2802,10 @@
         <v>2023.0</v>
       </c>
       <c r="C191" t="n" s="2">
-        <v>45256.0</v>
+        <v>45249.0</v>
       </c>
       <c r="D191" t="n">
-        <v>17.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="192">
@@ -2816,10 +2816,10 @@
         <v>2023.0</v>
       </c>
       <c r="C192" t="n" s="2">
-        <v>45263.0</v>
+        <v>45256.0</v>
       </c>
       <c r="D192" t="n">
-        <v>14.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="193">
@@ -2830,10 +2830,10 @@
         <v>2023.0</v>
       </c>
       <c r="C193" t="n" s="2">
-        <v>45270.0</v>
+        <v>45263.0</v>
       </c>
       <c r="D193" t="n">
-        <v>26.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="194">
@@ -2844,10 +2844,10 @@
         <v>2023.0</v>
       </c>
       <c r="C194" t="n" s="2">
-        <v>45277.0</v>
+        <v>45270.0</v>
       </c>
       <c r="D194" t="n">
-        <v>19.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="195">
@@ -2858,10 +2858,10 @@
         <v>2023.0</v>
       </c>
       <c r="C195" t="n" s="2">
-        <v>45284.0</v>
+        <v>45277.0</v>
       </c>
       <c r="D195" t="n">
-        <v>21.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="196">
@@ -2872,10 +2872,10 @@
         <v>2023.0</v>
       </c>
       <c r="C196" t="n" s="2">
-        <v>45291.0</v>
+        <v>45284.0</v>
       </c>
       <c r="D196" t="n">
-        <v>9.0</v>
+        <v>21.0</v>
       </c>
     </row>
     <row r="197">
@@ -2883,13 +2883,13 @@
         <v>5</v>
       </c>
       <c r="B197" t="n">
-        <v>2024.0</v>
+        <v>2023.0</v>
       </c>
       <c r="C197" t="n" s="2">
-        <v>45299.0</v>
+        <v>45291.0</v>
       </c>
       <c r="D197" t="n">
-        <v>26.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="198">
@@ -2900,10 +2900,10 @@
         <v>2024.0</v>
       </c>
       <c r="C198" t="n" s="2">
-        <v>45306.0</v>
+        <v>45299.0</v>
       </c>
       <c r="D198" t="n">
-        <v>14.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="199">
@@ -2914,10 +2914,10 @@
         <v>2024.0</v>
       </c>
       <c r="C199" t="n" s="2">
-        <v>45313.0</v>
+        <v>45306.0</v>
       </c>
       <c r="D199" t="n">
-        <v>15.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="200">
@@ -2928,10 +2928,10 @@
         <v>2024.0</v>
       </c>
       <c r="C200" t="n" s="2">
-        <v>45320.0</v>
+        <v>45313.0</v>
       </c>
       <c r="D200" t="n">
-        <v>18.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="201">
@@ -2942,10 +2942,10 @@
         <v>2024.0</v>
       </c>
       <c r="C201" t="n" s="2">
-        <v>45327.0</v>
+        <v>45320.0</v>
       </c>
       <c r="D201" t="n">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="202">
@@ -2956,10 +2956,10 @@
         <v>2024.0</v>
       </c>
       <c r="C202" t="n" s="2">
-        <v>45334.0</v>
+        <v>45327.0</v>
       </c>
       <c r="D202" t="n">
-        <v>13.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="203">
@@ -2970,10 +2970,10 @@
         <v>2024.0</v>
       </c>
       <c r="C203" t="n" s="2">
-        <v>45341.0</v>
+        <v>45334.0</v>
       </c>
       <c r="D203" t="n">
-        <v>11.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="204">
@@ -2984,10 +2984,10 @@
         <v>2024.0</v>
       </c>
       <c r="C204" t="n" s="2">
-        <v>45348.0</v>
+        <v>45341.0</v>
       </c>
       <c r="D204" t="n">
-        <v>8.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="205">
@@ -2998,10 +2998,10 @@
         <v>2024.0</v>
       </c>
       <c r="C205" t="n" s="2">
-        <v>45355.0</v>
+        <v>45348.0</v>
       </c>
       <c r="D205" t="n">
-        <v>1.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="206">
@@ -3012,10 +3012,10 @@
         <v>2024.0</v>
       </c>
       <c r="C206" t="n" s="2">
-        <v>45362.0</v>
+        <v>45355.0</v>
       </c>
       <c r="D206" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="207">
@@ -3026,10 +3026,10 @@
         <v>2024.0</v>
       </c>
       <c r="C207" t="n" s="2">
-        <v>45369.0</v>
+        <v>45362.0</v>
       </c>
       <c r="D207" t="n">
-        <v>8.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="208">
@@ -3040,10 +3040,10 @@
         <v>2024.0</v>
       </c>
       <c r="C208" t="n" s="2">
-        <v>45376.0</v>
+        <v>45369.0</v>
       </c>
       <c r="D208" t="n">
-        <v>9.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="209">
@@ -3054,10 +3054,10 @@
         <v>2024.0</v>
       </c>
       <c r="C209" t="n" s="2">
-        <v>45383.0</v>
+        <v>45376.0</v>
       </c>
       <c r="D209" t="n">
-        <v>5.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="210">
@@ -3068,10 +3068,10 @@
         <v>2024.0</v>
       </c>
       <c r="C210" t="n" s="2">
-        <v>45390.0</v>
+        <v>45383.0</v>
       </c>
       <c r="D210" t="n">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="211">
@@ -3082,10 +3082,10 @@
         <v>2024.0</v>
       </c>
       <c r="C211" t="n" s="2">
-        <v>45397.0</v>
+        <v>45390.0</v>
       </c>
       <c r="D211" t="n">
-        <v>13.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="212">
@@ -3096,10 +3096,10 @@
         <v>2024.0</v>
       </c>
       <c r="C212" t="n" s="2">
-        <v>45404.0</v>
+        <v>45397.0</v>
       </c>
       <c r="D212" t="n">
-        <v>24.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="213">
@@ -3110,10 +3110,10 @@
         <v>2024.0</v>
       </c>
       <c r="C213" t="n" s="2">
-        <v>45411.0</v>
+        <v>45404.0</v>
       </c>
       <c r="D213" t="n">
-        <v>17.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="214">
@@ -3124,10 +3124,10 @@
         <v>2024.0</v>
       </c>
       <c r="C214" t="n" s="2">
-        <v>45418.0</v>
+        <v>45411.0</v>
       </c>
       <c r="D214" t="n">
-        <v>3.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="215">
@@ -3138,10 +3138,10 @@
         <v>2024.0</v>
       </c>
       <c r="C215" t="n" s="2">
-        <v>45425.0</v>
+        <v>45418.0</v>
       </c>
       <c r="D215" t="n">
-        <v>16.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="216">
@@ -3152,10 +3152,10 @@
         <v>2024.0</v>
       </c>
       <c r="C216" t="n" s="2">
-        <v>45432.0</v>
+        <v>45425.0</v>
       </c>
       <c r="D216" t="n">
-        <v>19.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="217">
@@ -3166,10 +3166,10 @@
         <v>2024.0</v>
       </c>
       <c r="C217" t="n" s="2">
-        <v>45439.0</v>
+        <v>45432.0</v>
       </c>
       <c r="D217" t="n">
-        <v>30.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="218">
@@ -3180,10 +3180,10 @@
         <v>2024.0</v>
       </c>
       <c r="C218" t="n" s="2">
-        <v>45446.0</v>
+        <v>45439.0</v>
       </c>
       <c r="D218" t="n">
-        <v>28.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="219">
@@ -3194,10 +3194,10 @@
         <v>2024.0</v>
       </c>
       <c r="C219" t="n" s="2">
-        <v>45453.0</v>
+        <v>45446.0</v>
       </c>
       <c r="D219" t="n">
-        <v>19.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="220">
@@ -3208,10 +3208,10 @@
         <v>2024.0</v>
       </c>
       <c r="C220" t="n" s="2">
-        <v>45460.0</v>
+        <v>45453.0</v>
       </c>
       <c r="D220" t="n">
-        <v>26.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="221">
@@ -3222,10 +3222,10 @@
         <v>2024.0</v>
       </c>
       <c r="C221" t="n" s="2">
-        <v>45467.0</v>
+        <v>45460.0</v>
       </c>
       <c r="D221" t="n">
-        <v>8.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="222">
@@ -3236,10 +3236,10 @@
         <v>2024.0</v>
       </c>
       <c r="C222" t="n" s="2">
-        <v>45474.0</v>
+        <v>45467.0</v>
       </c>
       <c r="D222" t="n">
-        <v>12.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="223">
@@ -3250,7 +3250,7 @@
         <v>2024.0</v>
       </c>
       <c r="C223" t="n" s="2">
-        <v>45481.0</v>
+        <v>45474.0</v>
       </c>
       <c r="D223" t="n">
         <v>12.0</v>
@@ -3264,10 +3264,10 @@
         <v>2024.0</v>
       </c>
       <c r="C224" t="n" s="2">
-        <v>45488.0</v>
+        <v>45481.0</v>
       </c>
       <c r="D224" t="n">
-        <v>4.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="225">
@@ -3278,10 +3278,10 @@
         <v>2024.0</v>
       </c>
       <c r="C225" t="n" s="2">
-        <v>45495.0</v>
+        <v>45488.0</v>
       </c>
       <c r="D225" t="n">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="226">
@@ -3292,10 +3292,10 @@
         <v>2024.0</v>
       </c>
       <c r="C226" t="n" s="2">
-        <v>45502.0</v>
+        <v>45495.0</v>
       </c>
       <c r="D226" t="n">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="227">
@@ -3306,10 +3306,10 @@
         <v>2024.0</v>
       </c>
       <c r="C227" t="n" s="2">
-        <v>45509.0</v>
+        <v>45502.0</v>
       </c>
       <c r="D227" t="n">
-        <v>2.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="228">
@@ -3320,10 +3320,10 @@
         <v>2024.0</v>
       </c>
       <c r="C228" t="n" s="2">
-        <v>45516.0</v>
+        <v>45509.0</v>
       </c>
       <c r="D228" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="229">
@@ -3334,7 +3334,7 @@
         <v>2024.0</v>
       </c>
       <c r="C229" t="n" s="2">
-        <v>45523.0</v>
+        <v>45516.0</v>
       </c>
       <c r="D229" t="n">
         <v>4.0</v>
@@ -3348,7 +3348,7 @@
         <v>2024.0</v>
       </c>
       <c r="C230" t="n" s="2">
-        <v>45530.0</v>
+        <v>45523.0</v>
       </c>
       <c r="D230" t="n">
         <v>4.0</v>
@@ -3362,7 +3362,7 @@
         <v>2024.0</v>
       </c>
       <c r="C231" t="n" s="2">
-        <v>45537.0</v>
+        <v>45530.0</v>
       </c>
       <c r="D231" t="n">
         <v>4.0</v>
@@ -3376,10 +3376,10 @@
         <v>2024.0</v>
       </c>
       <c r="C232" t="n" s="2">
-        <v>45544.0</v>
+        <v>45537.0</v>
       </c>
       <c r="D232" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="233">
@@ -3390,10 +3390,10 @@
         <v>2024.0</v>
       </c>
       <c r="C233" t="n" s="2">
-        <v>45551.0</v>
+        <v>45544.0</v>
       </c>
       <c r="D233" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="234">
@@ -3404,10 +3404,10 @@
         <v>2024.0</v>
       </c>
       <c r="C234" t="n" s="2">
-        <v>45558.0</v>
+        <v>45551.0</v>
       </c>
       <c r="D234" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="235">
@@ -3418,10 +3418,10 @@
         <v>2024.0</v>
       </c>
       <c r="C235" t="n" s="2">
-        <v>45600.0</v>
+        <v>45558.0</v>
       </c>
       <c r="D235" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="236">
@@ -3432,10 +3432,10 @@
         <v>2024.0</v>
       </c>
       <c r="C236" t="n" s="2">
-        <v>45607.0</v>
+        <v>45600.0</v>
       </c>
       <c r="D236" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="237">
@@ -3446,10 +3446,10 @@
         <v>2024.0</v>
       </c>
       <c r="C237" t="n" s="2">
-        <v>45628.0</v>
+        <v>45607.0</v>
       </c>
       <c r="D237" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="238">
@@ -3460,10 +3460,10 @@
         <v>2024.0</v>
       </c>
       <c r="C238" t="n" s="2">
-        <v>45635.0</v>
+        <v>45628.0</v>
       </c>
       <c r="D238" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="239">
@@ -3474,7 +3474,7 @@
         <v>2024.0</v>
       </c>
       <c r="C239" t="n" s="2">
-        <v>45642.0</v>
+        <v>45635.0</v>
       </c>
       <c r="D239" t="n">
         <v>3.0</v>
@@ -3488,10 +3488,10 @@
         <v>2024.0</v>
       </c>
       <c r="C240" t="n" s="2">
-        <v>45649.0</v>
+        <v>45642.0</v>
       </c>
       <c r="D240" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="241">
@@ -3502,7 +3502,7 @@
         <v>2024.0</v>
       </c>
       <c r="C241" t="n" s="2">
-        <v>45656.0</v>
+        <v>45649.0</v>
       </c>
       <c r="D241" t="n">
         <v>1.0</v>
@@ -3513,13 +3513,13 @@
         <v>5</v>
       </c>
       <c r="B242" t="n">
-        <v>2025.0</v>
+        <v>2024.0</v>
       </c>
       <c r="C242" t="n" s="2">
-        <v>45672.0</v>
+        <v>45656.0</v>
       </c>
       <c r="D242" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="243">
@@ -3530,10 +3530,10 @@
         <v>2025.0</v>
       </c>
       <c r="C243" t="n" s="2">
-        <v>45679.0</v>
+        <v>45672.0</v>
       </c>
       <c r="D243" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="244">
@@ -3544,7 +3544,7 @@
         <v>2025.0</v>
       </c>
       <c r="C244" t="n" s="2">
-        <v>45686.0</v>
+        <v>45679.0</v>
       </c>
       <c r="D244" t="n">
         <v>1.0</v>
@@ -3558,10 +3558,10 @@
         <v>2025.0</v>
       </c>
       <c r="C245" t="n" s="2">
-        <v>45721.0</v>
+        <v>45686.0</v>
       </c>
       <c r="D245" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="246">
@@ -3572,10 +3572,10 @@
         <v>2025.0</v>
       </c>
       <c r="C246" t="n" s="2">
-        <v>45728.0</v>
+        <v>45721.0</v>
       </c>
       <c r="D246" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="247">
@@ -3586,10 +3586,10 @@
         <v>2025.0</v>
       </c>
       <c r="C247" t="n" s="2">
-        <v>45742.0</v>
+        <v>45728.0</v>
       </c>
       <c r="D247" t="n">
-        <v>9.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="248">
@@ -3600,10 +3600,10 @@
         <v>2025.0</v>
       </c>
       <c r="C248" t="n" s="2">
-        <v>45749.0</v>
+        <v>45742.0</v>
       </c>
       <c r="D248" t="n">
-        <v>5.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="249">
@@ -3614,10 +3614,10 @@
         <v>2025.0</v>
       </c>
       <c r="C249" t="n" s="2">
-        <v>45756.0</v>
+        <v>45749.0</v>
       </c>
       <c r="D249" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="250">
@@ -3628,10 +3628,10 @@
         <v>2025.0</v>
       </c>
       <c r="C250" t="n" s="2">
-        <v>45763.0</v>
+        <v>45756.0</v>
       </c>
       <c r="D250" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="251">
@@ -3642,10 +3642,10 @@
         <v>2025.0</v>
       </c>
       <c r="C251" t="n" s="2">
-        <v>45770.0</v>
+        <v>45763.0</v>
       </c>
       <c r="D251" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="252">
@@ -3656,10 +3656,10 @@
         <v>2025.0</v>
       </c>
       <c r="C252" t="n" s="2">
-        <v>45777.0</v>
+        <v>45770.0</v>
       </c>
       <c r="D252" t="n">
-        <v>7.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="253">
@@ -3670,10 +3670,10 @@
         <v>2025.0</v>
       </c>
       <c r="C253" t="n" s="2">
-        <v>45784.0</v>
+        <v>45777.0</v>
       </c>
       <c r="D253" t="n">
-        <v>2.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="254">
@@ -3684,10 +3684,10 @@
         <v>2025.0</v>
       </c>
       <c r="C254" t="n" s="2">
-        <v>45791.0</v>
+        <v>45784.0</v>
       </c>
       <c r="D254" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="255">
@@ -3698,10 +3698,10 @@
         <v>2025.0</v>
       </c>
       <c r="C255" t="n" s="2">
-        <v>45798.0</v>
+        <v>45791.0</v>
       </c>
       <c r="D255" t="n">
-        <v>8.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="256">
@@ -3712,10 +3712,10 @@
         <v>2025.0</v>
       </c>
       <c r="C256" t="n" s="2">
-        <v>45805.0</v>
+        <v>45798.0</v>
       </c>
       <c r="D256" t="n">
-        <v>4.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="257">
@@ -3726,10 +3726,10 @@
         <v>2025.0</v>
       </c>
       <c r="C257" t="n" s="2">
-        <v>45812.0</v>
+        <v>45805.0</v>
       </c>
       <c r="D257" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="258">
@@ -3740,10 +3740,10 @@
         <v>2025.0</v>
       </c>
       <c r="C258" t="n" s="2">
-        <v>45819.0</v>
+        <v>45812.0</v>
       </c>
       <c r="D258" t="n">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="259">
@@ -3754,10 +3754,10 @@
         <v>2025.0</v>
       </c>
       <c r="C259" t="n" s="2">
-        <v>45826.0</v>
+        <v>45819.0</v>
       </c>
       <c r="D259" t="n">
-        <v>13.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="260">
@@ -3768,10 +3768,10 @@
         <v>2025.0</v>
       </c>
       <c r="C260" t="n" s="2">
-        <v>45833.0</v>
+        <v>45826.0</v>
       </c>
       <c r="D260" t="n">
-        <v>1.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="261">
@@ -3782,10 +3782,10 @@
         <v>2025.0</v>
       </c>
       <c r="C261" t="n" s="2">
-        <v>45840.0</v>
+        <v>45833.0</v>
       </c>
       <c r="D261" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="262">
@@ -3796,7 +3796,7 @@
         <v>2025.0</v>
       </c>
       <c r="C262" t="n" s="2">
-        <v>45847.0</v>
+        <v>45840.0</v>
       </c>
       <c r="D262" t="n">
         <v>4.0</v>
@@ -3810,10 +3810,10 @@
         <v>2025.0</v>
       </c>
       <c r="C263" t="n" s="2">
-        <v>45854.0</v>
+        <v>45847.0</v>
       </c>
       <c r="D263" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="264">
@@ -3824,10 +3824,10 @@
         <v>2025.0</v>
       </c>
       <c r="C264" t="n" s="2">
-        <v>45861.0</v>
+        <v>45854.0</v>
       </c>
       <c r="D264" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="265">
@@ -3838,10 +3838,10 @@
         <v>2025.0</v>
       </c>
       <c r="C265" t="n" s="2">
-        <v>45868.0</v>
+        <v>45861.0</v>
       </c>
       <c r="D265" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="266">
@@ -3852,10 +3852,10 @@
         <v>2025.0</v>
       </c>
       <c r="C266" t="n" s="2">
-        <v>45882.0</v>
+        <v>45868.0</v>
       </c>
       <c r="D266" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="267">
@@ -3866,7 +3866,7 @@
         <v>2025.0</v>
       </c>
       <c r="C267" t="n" s="2">
-        <v>45889.0</v>
+        <v>45882.0</v>
       </c>
       <c r="D267" t="n">
         <v>1.0</v>
@@ -3880,10 +3880,10 @@
         <v>2025.0</v>
       </c>
       <c r="C268" t="n" s="2">
-        <v>45896.0</v>
+        <v>45889.0</v>
       </c>
       <c r="D268" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="269">
@@ -3894,7 +3894,7 @@
         <v>2025.0</v>
       </c>
       <c r="C269" t="n" s="2">
-        <v>45903.0</v>
+        <v>45896.0</v>
       </c>
       <c r="D269" t="n">
         <v>3.0</v>
@@ -3908,10 +3908,10 @@
         <v>2025.0</v>
       </c>
       <c r="C270" t="n" s="2">
-        <v>45910.0</v>
+        <v>45903.0</v>
       </c>
       <c r="D270" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="271">
@@ -3922,7 +3922,7 @@
         <v>2025.0</v>
       </c>
       <c r="C271" t="n" s="2">
-        <v>45973.0</v>
+        <v>45910.0</v>
       </c>
       <c r="D271" t="n">
         <v>1.0</v>
@@ -3936,10 +3936,10 @@
         <v>2025.0</v>
       </c>
       <c r="C272" t="n" s="2">
-        <v>45987.0</v>
+        <v>45973.0</v>
       </c>
       <c r="D272" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="273">
@@ -3950,10 +3950,10 @@
         <v>2025.0</v>
       </c>
       <c r="C273" t="n" s="2">
-        <v>45994.0</v>
+        <v>45987.0</v>
       </c>
       <c r="D273" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="274">
@@ -3964,10 +3964,10 @@
         <v>2025.0</v>
       </c>
       <c r="C274" t="n" s="2">
-        <v>46001.0</v>
+        <v>45994.0</v>
       </c>
       <c r="D274" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="275">
@@ -3978,10 +3978,10 @@
         <v>2025.0</v>
       </c>
       <c r="C275" t="n" s="2">
-        <v>46008.0</v>
+        <v>46001.0</v>
       </c>
       <c r="D275" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="276">
@@ -3992,10 +3992,10 @@
         <v>2025.0</v>
       </c>
       <c r="C276" t="n" s="2">
-        <v>46022.0</v>
+        <v>46008.0</v>
       </c>
       <c r="D276" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="277">
@@ -4006,10 +4006,10 @@
         <v>2025.0</v>
       </c>
       <c r="C277" t="n" s="2">
-        <v>46029.0</v>
+        <v>46022.0</v>
       </c>
       <c r="D277" t="n">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="278">
@@ -4017,13 +4017,13 @@
         <v>5</v>
       </c>
       <c r="B278" t="n">
-        <v>2026.0</v>
+        <v>2025.0</v>
       </c>
       <c r="C278" t="n" s="2">
-        <v>46030.0</v>
+        <v>46029.0</v>
       </c>
       <c r="D278" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="279">
@@ -4034,10 +4034,10 @@
         <v>2026.0</v>
       </c>
       <c r="C279" t="n" s="2">
-        <v>46037.0</v>
+        <v>46030.0</v>
       </c>
       <c r="D279" t="n">
-        <v>12.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="280">
@@ -4048,10 +4048,10 @@
         <v>2026.0</v>
       </c>
       <c r="C280" t="n" s="2">
-        <v>46044.0</v>
+        <v>46037.0</v>
       </c>
       <c r="D280" t="n">
-        <v>9.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="281">
@@ -4062,10 +4062,10 @@
         <v>2026.0</v>
       </c>
       <c r="C281" t="n" s="2">
-        <v>46051.0</v>
+        <v>46044.0</v>
       </c>
       <c r="D281" t="n">
-        <v>10.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="282">
@@ -4076,10 +4076,10 @@
         <v>2026.0</v>
       </c>
       <c r="C282" t="n" s="2">
-        <v>46058.0</v>
+        <v>46051.0</v>
       </c>
       <c r="D282" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="283">
@@ -4090,10 +4090,10 @@
         <v>2026.0</v>
       </c>
       <c r="C283" t="n" s="2">
-        <v>46065.0</v>
+        <v>46058.0</v>
       </c>
       <c r="D283" t="n">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="284">
@@ -4104,10 +4104,10 @@
         <v>2026.0</v>
       </c>
       <c r="C284" t="n" s="2">
-        <v>46072.0</v>
+        <v>46065.0</v>
       </c>
       <c r="D284" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="285">
@@ -4118,7 +4118,7 @@
         <v>2026.0</v>
       </c>
       <c r="C285" t="n" s="2">
-        <v>46079.0</v>
+        <v>46072.0</v>
       </c>
       <c r="D285" t="n">
         <v>5.0</v>
@@ -4132,10 +4132,10 @@
         <v>2026.0</v>
       </c>
       <c r="C286" t="n" s="2">
-        <v>46086.0</v>
+        <v>46079.0</v>
       </c>
       <c r="D286" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="287">
@@ -4146,7 +4146,7 @@
         <v>2026.0</v>
       </c>
       <c r="C287" t="n" s="2">
-        <v>46093.0</v>
+        <v>46086.0</v>
       </c>
       <c r="D287" t="n">
         <v>2.0</v>
@@ -4160,10 +4160,10 @@
         <v>2026.0</v>
       </c>
       <c r="C288" t="n" s="2">
-        <v>46100.0</v>
+        <v>46093.0</v>
       </c>
       <c r="D288" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="289">
@@ -4174,10 +4174,10 @@
         <v>2026.0</v>
       </c>
       <c r="C289" t="n" s="2">
-        <v>46107.0</v>
+        <v>46100.0</v>
       </c>
       <c r="D289" t="n">
-        <v>9.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="290">
@@ -4188,10 +4188,10 @@
         <v>2026.0</v>
       </c>
       <c r="C290" t="n" s="2">
-        <v>46114.0</v>
+        <v>46107.0</v>
       </c>
       <c r="D290" t="n">
-        <v>5.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="291">
@@ -4202,10 +4202,10 @@
         <v>2026.0</v>
       </c>
       <c r="C291" t="n" s="2">
-        <v>46121.0</v>
+        <v>46114.0</v>
       </c>
       <c r="D291" t="n">
-        <v>13.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="292">
@@ -4216,10 +4216,10 @@
         <v>2026.0</v>
       </c>
       <c r="C292" t="n" s="2">
-        <v>46128.0</v>
+        <v>46121.0</v>
       </c>
       <c r="D292" t="n">
-        <v>4.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="293">
@@ -4230,7 +4230,7 @@
         <v>2026.0</v>
       </c>
       <c r="C293" t="n" s="2">
-        <v>46135.0</v>
+        <v>46128.0</v>
       </c>
       <c r="D293" t="n">
         <v>4.0</v>
@@ -4238,16 +4238,16 @@
     </row>
     <row r="294">
       <c r="A294" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B294" t="n">
-        <v>2023.0</v>
+        <v>2026.0</v>
       </c>
       <c r="C294" t="n" s="2">
-        <v>45095.0</v>
+        <v>46135.0</v>
       </c>
       <c r="D294" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="295">
@@ -4258,7 +4258,7 @@
         <v>2023.0</v>
       </c>
       <c r="C295" t="n" s="2">
-        <v>45102.0</v>
+        <v>45095.0</v>
       </c>
       <c r="D295" t="n">
         <v>1.0</v>
@@ -4272,7 +4272,7 @@
         <v>2023.0</v>
       </c>
       <c r="C296" t="n" s="2">
-        <v>45158.0</v>
+        <v>45102.0</v>
       </c>
       <c r="D296" t="n">
         <v>1.0</v>
@@ -4286,10 +4286,10 @@
         <v>2023.0</v>
       </c>
       <c r="C297" t="n" s="2">
-        <v>45207.0</v>
+        <v>45158.0</v>
       </c>
       <c r="D297" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="298">
@@ -4300,7 +4300,7 @@
         <v>2023.0</v>
       </c>
       <c r="C298" t="n" s="2">
-        <v>45214.0</v>
+        <v>45207.0</v>
       </c>
       <c r="D298" t="n">
         <v>3.0</v>
@@ -4314,10 +4314,10 @@
         <v>2023.0</v>
       </c>
       <c r="C299" t="n" s="2">
-        <v>45221.0</v>
+        <v>45214.0</v>
       </c>
       <c r="D299" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="300">
@@ -4328,7 +4328,7 @@
         <v>2023.0</v>
       </c>
       <c r="C300" t="n" s="2">
-        <v>45249.0</v>
+        <v>45221.0</v>
       </c>
       <c r="D300" t="n">
         <v>1.0</v>
@@ -4342,10 +4342,10 @@
         <v>2023.0</v>
       </c>
       <c r="C301" t="n" s="2">
-        <v>45256.0</v>
+        <v>45249.0</v>
       </c>
       <c r="D301" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="302">
@@ -4356,10 +4356,10 @@
         <v>2023.0</v>
       </c>
       <c r="C302" t="n" s="2">
-        <v>45263.0</v>
+        <v>45256.0</v>
       </c>
       <c r="D302" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="303">
@@ -4370,10 +4370,10 @@
         <v>2023.0</v>
       </c>
       <c r="C303" t="n" s="2">
-        <v>45270.0</v>
+        <v>45263.0</v>
       </c>
       <c r="D303" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="304">
@@ -4384,10 +4384,10 @@
         <v>2023.0</v>
       </c>
       <c r="C304" t="n" s="2">
-        <v>45277.0</v>
+        <v>45270.0</v>
       </c>
       <c r="D304" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="305">
@@ -4398,10 +4398,10 @@
         <v>2023.0</v>
       </c>
       <c r="C305" t="n" s="2">
-        <v>45284.0</v>
+        <v>45277.0</v>
       </c>
       <c r="D305" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="306">
@@ -4412,10 +4412,10 @@
         <v>2023.0</v>
       </c>
       <c r="C306" t="n" s="2">
-        <v>45291.0</v>
+        <v>45284.0</v>
       </c>
       <c r="D306" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="307">
@@ -4423,13 +4423,13 @@
         <v>6</v>
       </c>
       <c r="B307" t="n">
-        <v>2024.0</v>
+        <v>2023.0</v>
       </c>
       <c r="C307" t="n" s="2">
-        <v>45306.0</v>
+        <v>45291.0</v>
       </c>
       <c r="D307" t="n">
-        <v>7.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="308">
@@ -4440,10 +4440,10 @@
         <v>2024.0</v>
       </c>
       <c r="C308" t="n" s="2">
-        <v>45313.0</v>
+        <v>45306.0</v>
       </c>
       <c r="D308" t="n">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="309">
@@ -4454,10 +4454,10 @@
         <v>2024.0</v>
       </c>
       <c r="C309" t="n" s="2">
-        <v>45320.0</v>
+        <v>45313.0</v>
       </c>
       <c r="D309" t="n">
-        <v>19.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="310">
@@ -4468,10 +4468,10 @@
         <v>2024.0</v>
       </c>
       <c r="C310" t="n" s="2">
-        <v>45327.0</v>
+        <v>45320.0</v>
       </c>
       <c r="D310" t="n">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="311">
@@ -4482,10 +4482,10 @@
         <v>2024.0</v>
       </c>
       <c r="C311" t="n" s="2">
-        <v>45334.0</v>
+        <v>45327.0</v>
       </c>
       <c r="D311" t="n">
-        <v>9.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="312">
@@ -4496,10 +4496,10 @@
         <v>2024.0</v>
       </c>
       <c r="C312" t="n" s="2">
-        <v>45341.0</v>
+        <v>45334.0</v>
       </c>
       <c r="D312" t="n">
-        <v>12.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="313">
@@ -4510,7 +4510,7 @@
         <v>2024.0</v>
       </c>
       <c r="C313" t="n" s="2">
-        <v>45348.0</v>
+        <v>45341.0</v>
       </c>
       <c r="D313" t="n">
         <v>12.0</v>
@@ -4524,10 +4524,10 @@
         <v>2024.0</v>
       </c>
       <c r="C314" t="n" s="2">
-        <v>45355.0</v>
+        <v>45348.0</v>
       </c>
       <c r="D314" t="n">
-        <v>10.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="315">
@@ -4538,10 +4538,10 @@
         <v>2024.0</v>
       </c>
       <c r="C315" t="n" s="2">
-        <v>45362.0</v>
+        <v>45355.0</v>
       </c>
       <c r="D315" t="n">
-        <v>12.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="316">
@@ -4552,10 +4552,10 @@
         <v>2024.0</v>
       </c>
       <c r="C316" t="n" s="2">
-        <v>45369.0</v>
+        <v>45362.0</v>
       </c>
       <c r="D316" t="n">
-        <v>13.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="317">
@@ -4566,10 +4566,10 @@
         <v>2024.0</v>
       </c>
       <c r="C317" t="n" s="2">
-        <v>45376.0</v>
+        <v>45369.0</v>
       </c>
       <c r="D317" t="n">
-        <v>18.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="318">
@@ -4580,10 +4580,10 @@
         <v>2024.0</v>
       </c>
       <c r="C318" t="n" s="2">
-        <v>45383.0</v>
+        <v>45376.0</v>
       </c>
       <c r="D318" t="n">
-        <v>12.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="319">
@@ -4594,10 +4594,10 @@
         <v>2024.0</v>
       </c>
       <c r="C319" t="n" s="2">
-        <v>45390.0</v>
+        <v>45383.0</v>
       </c>
       <c r="D319" t="n">
-        <v>6.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="320">
@@ -4608,10 +4608,10 @@
         <v>2024.0</v>
       </c>
       <c r="C320" t="n" s="2">
-        <v>45397.0</v>
+        <v>45390.0</v>
       </c>
       <c r="D320" t="n">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="321">
@@ -4622,10 +4622,10 @@
         <v>2024.0</v>
       </c>
       <c r="C321" t="n" s="2">
-        <v>45404.0</v>
+        <v>45397.0</v>
       </c>
       <c r="D321" t="n">
-        <v>3.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="322">
@@ -4636,10 +4636,10 @@
         <v>2024.0</v>
       </c>
       <c r="C322" t="n" s="2">
-        <v>45411.0</v>
+        <v>45404.0</v>
       </c>
       <c r="D322" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="323">
@@ -4650,10 +4650,10 @@
         <v>2024.0</v>
       </c>
       <c r="C323" t="n" s="2">
-        <v>45418.0</v>
+        <v>45411.0</v>
       </c>
       <c r="D323" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="324">
@@ -4664,10 +4664,10 @@
         <v>2024.0</v>
       </c>
       <c r="C324" t="n" s="2">
-        <v>45425.0</v>
+        <v>45418.0</v>
       </c>
       <c r="D324" t="n">
-        <v>9.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="325">
@@ -4678,10 +4678,10 @@
         <v>2024.0</v>
       </c>
       <c r="C325" t="n" s="2">
-        <v>45432.0</v>
+        <v>45425.0</v>
       </c>
       <c r="D325" t="n">
-        <v>6.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="326">
@@ -4692,7 +4692,7 @@
         <v>2024.0</v>
       </c>
       <c r="C326" t="n" s="2">
-        <v>45439.0</v>
+        <v>45432.0</v>
       </c>
       <c r="D326" t="n">
         <v>6.0</v>
@@ -4706,10 +4706,10 @@
         <v>2024.0</v>
       </c>
       <c r="C327" t="n" s="2">
-        <v>45446.0</v>
+        <v>45439.0</v>
       </c>
       <c r="D327" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="328">
@@ -4720,10 +4720,10 @@
         <v>2024.0</v>
       </c>
       <c r="C328" t="n" s="2">
-        <v>45453.0</v>
+        <v>45446.0</v>
       </c>
       <c r="D328" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="329">
@@ -4734,7 +4734,7 @@
         <v>2024.0</v>
       </c>
       <c r="C329" t="n" s="2">
-        <v>45460.0</v>
+        <v>45453.0</v>
       </c>
       <c r="D329" t="n">
         <v>4.0</v>
@@ -4748,7 +4748,7 @@
         <v>2024.0</v>
       </c>
       <c r="C330" t="n" s="2">
-        <v>45467.0</v>
+        <v>45460.0</v>
       </c>
       <c r="D330" t="n">
         <v>4.0</v>
@@ -4762,10 +4762,10 @@
         <v>2024.0</v>
       </c>
       <c r="C331" t="n" s="2">
-        <v>45474.0</v>
+        <v>45467.0</v>
       </c>
       <c r="D331" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="332">
@@ -4776,10 +4776,10 @@
         <v>2024.0</v>
       </c>
       <c r="C332" t="n" s="2">
-        <v>45481.0</v>
+        <v>45474.0</v>
       </c>
       <c r="D332" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="333">
@@ -4790,10 +4790,10 @@
         <v>2024.0</v>
       </c>
       <c r="C333" t="n" s="2">
-        <v>45488.0</v>
+        <v>45481.0</v>
       </c>
       <c r="D333" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="334">
@@ -4804,10 +4804,10 @@
         <v>2024.0</v>
       </c>
       <c r="C334" t="n" s="2">
-        <v>45495.0</v>
+        <v>45488.0</v>
       </c>
       <c r="D334" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="335">
@@ -4818,10 +4818,10 @@
         <v>2024.0</v>
       </c>
       <c r="C335" t="n" s="2">
-        <v>45502.0</v>
+        <v>45495.0</v>
       </c>
       <c r="D335" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="336">
@@ -4832,10 +4832,10 @@
         <v>2024.0</v>
       </c>
       <c r="C336" t="n" s="2">
-        <v>45509.0</v>
+        <v>45502.0</v>
       </c>
       <c r="D336" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="337">
@@ -4846,7 +4846,7 @@
         <v>2024.0</v>
       </c>
       <c r="C337" t="n" s="2">
-        <v>45523.0</v>
+        <v>45509.0</v>
       </c>
       <c r="D337" t="n">
         <v>1.0</v>
@@ -4860,7 +4860,7 @@
         <v>2024.0</v>
       </c>
       <c r="C338" t="n" s="2">
-        <v>45551.0</v>
+        <v>45523.0</v>
       </c>
       <c r="D338" t="n">
         <v>1.0</v>
@@ -4874,7 +4874,7 @@
         <v>2024.0</v>
       </c>
       <c r="C339" t="n" s="2">
-        <v>45558.0</v>
+        <v>45551.0</v>
       </c>
       <c r="D339" t="n">
         <v>1.0</v>
@@ -4888,10 +4888,10 @@
         <v>2024.0</v>
       </c>
       <c r="C340" t="n" s="2">
-        <v>45572.0</v>
+        <v>45558.0</v>
       </c>
       <c r="D340" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="341">
@@ -4902,10 +4902,10 @@
         <v>2024.0</v>
       </c>
       <c r="C341" t="n" s="2">
-        <v>45593.0</v>
+        <v>45572.0</v>
       </c>
       <c r="D341" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="342">
@@ -4916,10 +4916,10 @@
         <v>2024.0</v>
       </c>
       <c r="C342" t="n" s="2">
-        <v>45614.0</v>
+        <v>45593.0</v>
       </c>
       <c r="D342" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="343">
@@ -4930,10 +4930,10 @@
         <v>2024.0</v>
       </c>
       <c r="C343" t="n" s="2">
-        <v>45621.0</v>
+        <v>45614.0</v>
       </c>
       <c r="D343" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="344">
@@ -4944,7 +4944,7 @@
         <v>2024.0</v>
       </c>
       <c r="C344" t="n" s="2">
-        <v>45635.0</v>
+        <v>45621.0</v>
       </c>
       <c r="D344" t="n">
         <v>1.0</v>
@@ -4958,7 +4958,7 @@
         <v>2024.0</v>
       </c>
       <c r="C345" t="n" s="2">
-        <v>45649.0</v>
+        <v>45635.0</v>
       </c>
       <c r="D345" t="n">
         <v>1.0</v>
@@ -4969,13 +4969,13 @@
         <v>6</v>
       </c>
       <c r="B346" t="n">
-        <v>2025.0</v>
+        <v>2024.0</v>
       </c>
       <c r="C346" t="n" s="2">
-        <v>45665.0</v>
+        <v>45649.0</v>
       </c>
       <c r="D346" t="n">
-        <v>9.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="347">
@@ -4986,10 +4986,10 @@
         <v>2025.0</v>
       </c>
       <c r="C347" t="n" s="2">
-        <v>45672.0</v>
+        <v>45665.0</v>
       </c>
       <c r="D347" t="n">
-        <v>3.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="348">
@@ -5000,10 +5000,10 @@
         <v>2025.0</v>
       </c>
       <c r="C348" t="n" s="2">
-        <v>45679.0</v>
+        <v>45672.0</v>
       </c>
       <c r="D348" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="349">
@@ -5014,10 +5014,10 @@
         <v>2025.0</v>
       </c>
       <c r="C349" t="n" s="2">
-        <v>45686.0</v>
+        <v>45679.0</v>
       </c>
       <c r="D349" t="n">
-        <v>8.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="350">
@@ -5028,10 +5028,10 @@
         <v>2025.0</v>
       </c>
       <c r="C350" t="n" s="2">
-        <v>45693.0</v>
+        <v>45686.0</v>
       </c>
       <c r="D350" t="n">
-        <v>3.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="351">
@@ -5042,10 +5042,10 @@
         <v>2025.0</v>
       </c>
       <c r="C351" t="n" s="2">
-        <v>45700.0</v>
+        <v>45693.0</v>
       </c>
       <c r="D351" t="n">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="352">
@@ -5056,10 +5056,10 @@
         <v>2025.0</v>
       </c>
       <c r="C352" t="n" s="2">
-        <v>45707.0</v>
+        <v>45700.0</v>
       </c>
       <c r="D352" t="n">
-        <v>8.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="353">
@@ -5070,10 +5070,10 @@
         <v>2025.0</v>
       </c>
       <c r="C353" t="n" s="2">
-        <v>45714.0</v>
+        <v>45707.0</v>
       </c>
       <c r="D353" t="n">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="354">
@@ -5084,10 +5084,10 @@
         <v>2025.0</v>
       </c>
       <c r="C354" t="n" s="2">
-        <v>45721.0</v>
+        <v>45714.0</v>
       </c>
       <c r="D354" t="n">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="355">
@@ -5098,10 +5098,10 @@
         <v>2025.0</v>
       </c>
       <c r="C355" t="n" s="2">
-        <v>45728.0</v>
+        <v>45721.0</v>
       </c>
       <c r="D355" t="n">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="356">
@@ -5112,10 +5112,10 @@
         <v>2025.0</v>
       </c>
       <c r="C356" t="n" s="2">
-        <v>45735.0</v>
+        <v>45728.0</v>
       </c>
       <c r="D356" t="n">
-        <v>4.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="357">
@@ -5126,10 +5126,10 @@
         <v>2025.0</v>
       </c>
       <c r="C357" t="n" s="2">
-        <v>45742.0</v>
+        <v>45735.0</v>
       </c>
       <c r="D357" t="n">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="358">
@@ -5140,10 +5140,10 @@
         <v>2025.0</v>
       </c>
       <c r="C358" t="n" s="2">
-        <v>45749.0</v>
+        <v>45742.0</v>
       </c>
       <c r="D358" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="359">
@@ -5154,10 +5154,10 @@
         <v>2025.0</v>
       </c>
       <c r="C359" t="n" s="2">
-        <v>45756.0</v>
+        <v>45749.0</v>
       </c>
       <c r="D359" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="360">
@@ -5168,10 +5168,10 @@
         <v>2025.0</v>
       </c>
       <c r="C360" t="n" s="2">
-        <v>45763.0</v>
+        <v>45756.0</v>
       </c>
       <c r="D360" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="361">
@@ -5182,7 +5182,7 @@
         <v>2025.0</v>
       </c>
       <c r="C361" t="n" s="2">
-        <v>45770.0</v>
+        <v>45763.0</v>
       </c>
       <c r="D361" t="n">
         <v>4.0</v>
@@ -5196,10 +5196,10 @@
         <v>2025.0</v>
       </c>
       <c r="C362" t="n" s="2">
-        <v>45777.0</v>
+        <v>45770.0</v>
       </c>
       <c r="D362" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="363">
@@ -5210,7 +5210,7 @@
         <v>2025.0</v>
       </c>
       <c r="C363" t="n" s="2">
-        <v>45784.0</v>
+        <v>45777.0</v>
       </c>
       <c r="D363" t="n">
         <v>1.0</v>
@@ -5224,7 +5224,7 @@
         <v>2025.0</v>
       </c>
       <c r="C364" t="n" s="2">
-        <v>45791.0</v>
+        <v>45784.0</v>
       </c>
       <c r="D364" t="n">
         <v>1.0</v>
@@ -5238,7 +5238,7 @@
         <v>2025.0</v>
       </c>
       <c r="C365" t="n" s="2">
-        <v>45840.0</v>
+        <v>45791.0</v>
       </c>
       <c r="D365" t="n">
         <v>1.0</v>
@@ -5252,7 +5252,7 @@
         <v>2025.0</v>
       </c>
       <c r="C366" t="n" s="2">
-        <v>46001.0</v>
+        <v>45840.0</v>
       </c>
       <c r="D366" t="n">
         <v>1.0</v>
@@ -5263,10 +5263,10 @@
         <v>6</v>
       </c>
       <c r="B367" t="n">
-        <v>2026.0</v>
+        <v>2025.0</v>
       </c>
       <c r="C367" t="n" s="2">
-        <v>46037.0</v>
+        <v>46001.0</v>
       </c>
       <c r="D367" t="n">
         <v>1.0</v>
@@ -5274,13 +5274,13 @@
     </row>
     <row r="368">
       <c r="A368" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B368" t="n">
-        <v>2021.0</v>
+        <v>2026.0</v>
       </c>
       <c r="C368" t="n" s="2">
-        <v>44561.0</v>
+        <v>46037.0</v>
       </c>
       <c r="D368" t="n">
         <v>1.0</v>
@@ -5291,10 +5291,10 @@
         <v>7</v>
       </c>
       <c r="B369" t="n">
-        <v>2022.0</v>
+        <v>2021.0</v>
       </c>
       <c r="C369" t="n" s="2">
-        <v>44569.0</v>
+        <v>44561.0</v>
       </c>
       <c r="D369" t="n">
         <v>1.0</v>
@@ -5308,10 +5308,10 @@
         <v>2022.0</v>
       </c>
       <c r="C370" t="n" s="2">
-        <v>44576.0</v>
+        <v>44569.0</v>
       </c>
       <c r="D370" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="371">
@@ -5322,10 +5322,10 @@
         <v>2022.0</v>
       </c>
       <c r="C371" t="n" s="2">
-        <v>44583.0</v>
+        <v>44576.0</v>
       </c>
       <c r="D371" t="n">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="372">
@@ -5336,10 +5336,10 @@
         <v>2022.0</v>
       </c>
       <c r="C372" t="n" s="2">
-        <v>44590.0</v>
+        <v>44583.0</v>
       </c>
       <c r="D372" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="373">
@@ -5350,10 +5350,10 @@
         <v>2022.0</v>
       </c>
       <c r="C373" t="n" s="2">
-        <v>44604.0</v>
+        <v>44590.0</v>
       </c>
       <c r="D373" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="374">
@@ -5364,7 +5364,7 @@
         <v>2022.0</v>
       </c>
       <c r="C374" t="n" s="2">
-        <v>44611.0</v>
+        <v>44604.0</v>
       </c>
       <c r="D374" t="n">
         <v>3.0</v>
@@ -5378,10 +5378,10 @@
         <v>2022.0</v>
       </c>
       <c r="C375" t="n" s="2">
-        <v>44618.0</v>
+        <v>44611.0</v>
       </c>
       <c r="D375" t="n">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="376">
@@ -5392,7 +5392,7 @@
         <v>2022.0</v>
       </c>
       <c r="C376" t="n" s="2">
-        <v>44625.0</v>
+        <v>44618.0</v>
       </c>
       <c r="D376" t="n">
         <v>5.0</v>
@@ -5406,10 +5406,10 @@
         <v>2022.0</v>
       </c>
       <c r="C377" t="n" s="2">
-        <v>44632.0</v>
+        <v>44625.0</v>
       </c>
       <c r="D377" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="378">
@@ -5420,10 +5420,10 @@
         <v>2022.0</v>
       </c>
       <c r="C378" t="n" s="2">
-        <v>44639.0</v>
+        <v>44632.0</v>
       </c>
       <c r="D378" t="n">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="379">
@@ -5434,10 +5434,10 @@
         <v>2022.0</v>
       </c>
       <c r="C379" t="n" s="2">
-        <v>44646.0</v>
+        <v>44639.0</v>
       </c>
       <c r="D379" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="380">
@@ -5448,10 +5448,10 @@
         <v>2022.0</v>
       </c>
       <c r="C380" t="n" s="2">
-        <v>44653.0</v>
+        <v>44646.0</v>
       </c>
       <c r="D380" t="n">
-        <v>9.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="381">
@@ -5462,10 +5462,10 @@
         <v>2022.0</v>
       </c>
       <c r="C381" t="n" s="2">
-        <v>44660.0</v>
+        <v>44653.0</v>
       </c>
       <c r="D381" t="n">
-        <v>6.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="382">
@@ -5476,10 +5476,10 @@
         <v>2022.0</v>
       </c>
       <c r="C382" t="n" s="2">
-        <v>44667.0</v>
+        <v>44660.0</v>
       </c>
       <c r="D382" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="383">
@@ -5490,10 +5490,10 @@
         <v>2022.0</v>
       </c>
       <c r="C383" t="n" s="2">
-        <v>44674.0</v>
+        <v>44667.0</v>
       </c>
       <c r="D383" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="384">
@@ -5504,10 +5504,10 @@
         <v>2022.0</v>
       </c>
       <c r="C384" t="n" s="2">
-        <v>44681.0</v>
+        <v>44674.0</v>
       </c>
       <c r="D384" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="385">
@@ -5518,10 +5518,10 @@
         <v>2022.0</v>
       </c>
       <c r="C385" t="n" s="2">
-        <v>44688.0</v>
+        <v>44681.0</v>
       </c>
       <c r="D385" t="n">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="386">
@@ -5532,10 +5532,10 @@
         <v>2022.0</v>
       </c>
       <c r="C386" t="n" s="2">
-        <v>44695.0</v>
+        <v>44688.0</v>
       </c>
       <c r="D386" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="387">
@@ -5546,10 +5546,10 @@
         <v>2022.0</v>
       </c>
       <c r="C387" t="n" s="2">
-        <v>44702.0</v>
+        <v>44695.0</v>
       </c>
       <c r="D387" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="388">
@@ -5560,10 +5560,10 @@
         <v>2022.0</v>
       </c>
       <c r="C388" t="n" s="2">
-        <v>44709.0</v>
+        <v>44702.0</v>
       </c>
       <c r="D388" t="n">
-        <v>8.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="389">
@@ -5574,10 +5574,10 @@
         <v>2022.0</v>
       </c>
       <c r="C389" t="n" s="2">
-        <v>44716.0</v>
+        <v>44709.0</v>
       </c>
       <c r="D389" t="n">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="390">
@@ -5588,10 +5588,10 @@
         <v>2022.0</v>
       </c>
       <c r="C390" t="n" s="2">
-        <v>44723.0</v>
+        <v>44716.0</v>
       </c>
       <c r="D390" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="391">
@@ -5602,10 +5602,10 @@
         <v>2022.0</v>
       </c>
       <c r="C391" t="n" s="2">
-        <v>44730.0</v>
+        <v>44723.0</v>
       </c>
       <c r="D391" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="392">
@@ -5616,7 +5616,7 @@
         <v>2022.0</v>
       </c>
       <c r="C392" t="n" s="2">
-        <v>44737.0</v>
+        <v>44730.0</v>
       </c>
       <c r="D392" t="n">
         <v>4.0</v>
@@ -5630,10 +5630,10 @@
         <v>2022.0</v>
       </c>
       <c r="C393" t="n" s="2">
-        <v>44744.0</v>
+        <v>44737.0</v>
       </c>
       <c r="D393" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="394">
@@ -5644,10 +5644,10 @@
         <v>2022.0</v>
       </c>
       <c r="C394" t="n" s="2">
-        <v>44751.0</v>
+        <v>44744.0</v>
       </c>
       <c r="D394" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="395">
@@ -5658,10 +5658,10 @@
         <v>2022.0</v>
       </c>
       <c r="C395" t="n" s="2">
-        <v>44758.0</v>
+        <v>44751.0</v>
       </c>
       <c r="D395" t="n">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="396">
@@ -5672,10 +5672,10 @@
         <v>2022.0</v>
       </c>
       <c r="C396" t="n" s="2">
-        <v>44765.0</v>
+        <v>44758.0</v>
       </c>
       <c r="D396" t="n">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="397">
@@ -5686,10 +5686,10 @@
         <v>2022.0</v>
       </c>
       <c r="C397" t="n" s="2">
-        <v>44779.0</v>
+        <v>44765.0</v>
       </c>
       <c r="D397" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="398">
@@ -5700,10 +5700,10 @@
         <v>2022.0</v>
       </c>
       <c r="C398" t="n" s="2">
-        <v>44786.0</v>
+        <v>44779.0</v>
       </c>
       <c r="D398" t="n">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="399">
@@ -5714,10 +5714,10 @@
         <v>2022.0</v>
       </c>
       <c r="C399" t="n" s="2">
-        <v>44863.0</v>
+        <v>44786.0</v>
       </c>
       <c r="D399" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="400">
@@ -5728,10 +5728,10 @@
         <v>2022.0</v>
       </c>
       <c r="C400" t="n" s="2">
-        <v>44870.0</v>
+        <v>44863.0</v>
       </c>
       <c r="D400" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="401">
@@ -5742,10 +5742,10 @@
         <v>2022.0</v>
       </c>
       <c r="C401" t="n" s="2">
-        <v>44884.0</v>
+        <v>44870.0</v>
       </c>
       <c r="D401" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="402">
@@ -5756,7 +5756,7 @@
         <v>2022.0</v>
       </c>
       <c r="C402" t="n" s="2">
-        <v>44891.0</v>
+        <v>44884.0</v>
       </c>
       <c r="D402" t="n">
         <v>2.0</v>
@@ -5770,10 +5770,10 @@
         <v>2022.0</v>
       </c>
       <c r="C403" t="n" s="2">
-        <v>44898.0</v>
+        <v>44891.0</v>
       </c>
       <c r="D403" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="404">
@@ -5784,10 +5784,10 @@
         <v>2022.0</v>
       </c>
       <c r="C404" t="n" s="2">
-        <v>44912.0</v>
+        <v>44898.0</v>
       </c>
       <c r="D404" t="n">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="405">
@@ -5798,10 +5798,10 @@
         <v>2022.0</v>
       </c>
       <c r="C405" t="n" s="2">
-        <v>44919.0</v>
+        <v>44912.0</v>
       </c>
       <c r="D405" t="n">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="406">
@@ -5812,10 +5812,10 @@
         <v>2022.0</v>
       </c>
       <c r="C406" t="n" s="2">
-        <v>44926.0</v>
+        <v>44919.0</v>
       </c>
       <c r="D406" t="n">
-        <v>12.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="407">
@@ -5823,13 +5823,13 @@
         <v>7</v>
       </c>
       <c r="B407" t="n">
-        <v>2023.0</v>
+        <v>2022.0</v>
       </c>
       <c r="C407" t="n" s="2">
-        <v>44934.0</v>
+        <v>44926.0</v>
       </c>
       <c r="D407" t="n">
-        <v>4.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="408">
@@ -5840,10 +5840,10 @@
         <v>2023.0</v>
       </c>
       <c r="C408" t="n" s="2">
-        <v>44941.0</v>
+        <v>44934.0</v>
       </c>
       <c r="D408" t="n">
-        <v>16.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="409">
@@ -5854,10 +5854,10 @@
         <v>2023.0</v>
       </c>
       <c r="C409" t="n" s="2">
-        <v>44948.0</v>
+        <v>44941.0</v>
       </c>
       <c r="D409" t="n">
-        <v>5.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="410">
@@ -5868,10 +5868,10 @@
         <v>2023.0</v>
       </c>
       <c r="C410" t="n" s="2">
-        <v>44955.0</v>
+        <v>44948.0</v>
       </c>
       <c r="D410" t="n">
-        <v>19.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="411">
@@ -5882,10 +5882,10 @@
         <v>2023.0</v>
       </c>
       <c r="C411" t="n" s="2">
-        <v>44962.0</v>
+        <v>44955.0</v>
       </c>
       <c r="D411" t="n">
-        <v>22.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="412">
@@ -5896,10 +5896,10 @@
         <v>2023.0</v>
       </c>
       <c r="C412" t="n" s="2">
-        <v>44969.0</v>
+        <v>44962.0</v>
       </c>
       <c r="D412" t="n">
-        <v>9.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="413">
@@ -5910,10 +5910,10 @@
         <v>2023.0</v>
       </c>
       <c r="C413" t="n" s="2">
-        <v>44976.0</v>
+        <v>44969.0</v>
       </c>
       <c r="D413" t="n">
-        <v>22.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="414">
@@ -5924,10 +5924,10 @@
         <v>2023.0</v>
       </c>
       <c r="C414" t="n" s="2">
-        <v>44983.0</v>
+        <v>44976.0</v>
       </c>
       <c r="D414" t="n">
-        <v>29.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="415">
@@ -5938,10 +5938,10 @@
         <v>2023.0</v>
       </c>
       <c r="C415" t="n" s="2">
-        <v>44990.0</v>
+        <v>44983.0</v>
       </c>
       <c r="D415" t="n">
-        <v>5.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="416">
@@ -5952,10 +5952,10 @@
         <v>2023.0</v>
       </c>
       <c r="C416" t="n" s="2">
-        <v>44997.0</v>
+        <v>44990.0</v>
       </c>
       <c r="D416" t="n">
-        <v>24.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="417">
@@ -5966,10 +5966,10 @@
         <v>2023.0</v>
       </c>
       <c r="C417" t="n" s="2">
-        <v>45004.0</v>
+        <v>44997.0</v>
       </c>
       <c r="D417" t="n">
-        <v>8.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="418">
@@ -5980,10 +5980,10 @@
         <v>2023.0</v>
       </c>
       <c r="C418" t="n" s="2">
-        <v>45011.0</v>
+        <v>45004.0</v>
       </c>
       <c r="D418" t="n">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="419">
@@ -5994,10 +5994,10 @@
         <v>2023.0</v>
       </c>
       <c r="C419" t="n" s="2">
-        <v>45018.0</v>
+        <v>45011.0</v>
       </c>
       <c r="D419" t="n">
-        <v>18.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="420">
@@ -6008,10 +6008,10 @@
         <v>2023.0</v>
       </c>
       <c r="C420" t="n" s="2">
-        <v>45025.0</v>
+        <v>45018.0</v>
       </c>
       <c r="D420" t="n">
-        <v>13.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="421">
@@ -6022,10 +6022,10 @@
         <v>2023.0</v>
       </c>
       <c r="C421" t="n" s="2">
-        <v>45032.0</v>
+        <v>45025.0</v>
       </c>
       <c r="D421" t="n">
-        <v>18.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="422">
@@ -6036,10 +6036,10 @@
         <v>2023.0</v>
       </c>
       <c r="C422" t="n" s="2">
-        <v>45039.0</v>
+        <v>45032.0</v>
       </c>
       <c r="D422" t="n">
-        <v>15.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="423">
@@ -6050,10 +6050,10 @@
         <v>2023.0</v>
       </c>
       <c r="C423" t="n" s="2">
-        <v>45046.0</v>
+        <v>45039.0</v>
       </c>
       <c r="D423" t="n">
-        <v>12.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="424">
@@ -6064,10 +6064,10 @@
         <v>2023.0</v>
       </c>
       <c r="C424" t="n" s="2">
-        <v>45053.0</v>
+        <v>45046.0</v>
       </c>
       <c r="D424" t="n">
-        <v>6.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="425">
@@ -6078,10 +6078,10 @@
         <v>2023.0</v>
       </c>
       <c r="C425" t="n" s="2">
-        <v>45060.0</v>
+        <v>45053.0</v>
       </c>
       <c r="D425" t="n">
-        <v>11.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="426">
@@ -6092,10 +6092,10 @@
         <v>2023.0</v>
       </c>
       <c r="C426" t="n" s="2">
-        <v>45067.0</v>
+        <v>45060.0</v>
       </c>
       <c r="D426" t="n">
-        <v>8.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="427">
@@ -6106,7 +6106,7 @@
         <v>2023.0</v>
       </c>
       <c r="C427" t="n" s="2">
-        <v>45074.0</v>
+        <v>45067.0</v>
       </c>
       <c r="D427" t="n">
         <v>8.0</v>
@@ -6120,10 +6120,10 @@
         <v>2023.0</v>
       </c>
       <c r="C428" t="n" s="2">
-        <v>45081.0</v>
+        <v>45074.0</v>
       </c>
       <c r="D428" t="n">
-        <v>5.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="429">
@@ -6134,10 +6134,10 @@
         <v>2023.0</v>
       </c>
       <c r="C429" t="n" s="2">
-        <v>45088.0</v>
+        <v>45081.0</v>
       </c>
       <c r="D429" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="430">
@@ -6148,10 +6148,10 @@
         <v>2023.0</v>
       </c>
       <c r="C430" t="n" s="2">
-        <v>45095.0</v>
+        <v>45088.0</v>
       </c>
       <c r="D430" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="431">
@@ -6162,10 +6162,10 @@
         <v>2023.0</v>
       </c>
       <c r="C431" t="n" s="2">
-        <v>45102.0</v>
+        <v>45095.0</v>
       </c>
       <c r="D431" t="n">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="432">
@@ -6176,10 +6176,10 @@
         <v>2023.0</v>
       </c>
       <c r="C432" t="n" s="2">
-        <v>45109.0</v>
+        <v>45102.0</v>
       </c>
       <c r="D432" t="n">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="433">
@@ -6190,10 +6190,10 @@
         <v>2023.0</v>
       </c>
       <c r="C433" t="n" s="2">
-        <v>45116.0</v>
+        <v>45109.0</v>
       </c>
       <c r="D433" t="n">
-        <v>3.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="434">
@@ -6204,10 +6204,10 @@
         <v>2023.0</v>
       </c>
       <c r="C434" t="n" s="2">
-        <v>45123.0</v>
+        <v>45116.0</v>
       </c>
       <c r="D434" t="n">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="435">
@@ -6218,7 +6218,7 @@
         <v>2023.0</v>
       </c>
       <c r="C435" t="n" s="2">
-        <v>45130.0</v>
+        <v>45123.0</v>
       </c>
       <c r="D435" t="n">
         <v>6.0</v>
@@ -6232,10 +6232,10 @@
         <v>2023.0</v>
       </c>
       <c r="C436" t="n" s="2">
-        <v>45137.0</v>
+        <v>45130.0</v>
       </c>
       <c r="D436" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="437">
@@ -6246,7 +6246,7 @@
         <v>2023.0</v>
       </c>
       <c r="C437" t="n" s="2">
-        <v>45144.0</v>
+        <v>45137.0</v>
       </c>
       <c r="D437" t="n">
         <v>2.0</v>
@@ -6260,7 +6260,7 @@
         <v>2023.0</v>
       </c>
       <c r="C438" t="n" s="2">
-        <v>45151.0</v>
+        <v>45144.0</v>
       </c>
       <c r="D438" t="n">
         <v>2.0</v>
@@ -6274,7 +6274,7 @@
         <v>2023.0</v>
       </c>
       <c r="C439" t="n" s="2">
-        <v>45165.0</v>
+        <v>45151.0</v>
       </c>
       <c r="D439" t="n">
         <v>2.0</v>
@@ -6288,7 +6288,7 @@
         <v>2023.0</v>
       </c>
       <c r="C440" t="n" s="2">
-        <v>45172.0</v>
+        <v>45165.0</v>
       </c>
       <c r="D440" t="n">
         <v>2.0</v>
@@ -6302,10 +6302,10 @@
         <v>2023.0</v>
       </c>
       <c r="C441" t="n" s="2">
-        <v>45179.0</v>
+        <v>45172.0</v>
       </c>
       <c r="D441" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="442">
@@ -6316,7 +6316,7 @@
         <v>2023.0</v>
       </c>
       <c r="C442" t="n" s="2">
-        <v>45186.0</v>
+        <v>45179.0</v>
       </c>
       <c r="D442" t="n">
         <v>1.0</v>
@@ -6330,7 +6330,7 @@
         <v>2023.0</v>
       </c>
       <c r="C443" t="n" s="2">
-        <v>45193.0</v>
+        <v>45186.0</v>
       </c>
       <c r="D443" t="n">
         <v>1.0</v>
@@ -6344,7 +6344,7 @@
         <v>2023.0</v>
       </c>
       <c r="C444" t="n" s="2">
-        <v>45200.0</v>
+        <v>45193.0</v>
       </c>
       <c r="D444" t="n">
         <v>1.0</v>
@@ -6358,7 +6358,7 @@
         <v>2023.0</v>
       </c>
       <c r="C445" t="n" s="2">
-        <v>45207.0</v>
+        <v>45200.0</v>
       </c>
       <c r="D445" t="n">
         <v>1.0</v>
@@ -6372,7 +6372,7 @@
         <v>2023.0</v>
       </c>
       <c r="C446" t="n" s="2">
-        <v>45235.0</v>
+        <v>45207.0</v>
       </c>
       <c r="D446" t="n">
         <v>1.0</v>
@@ -6386,10 +6386,10 @@
         <v>2023.0</v>
       </c>
       <c r="C447" t="n" s="2">
-        <v>45242.0</v>
+        <v>45235.0</v>
       </c>
       <c r="D447" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="448">
@@ -6400,10 +6400,10 @@
         <v>2023.0</v>
       </c>
       <c r="C448" t="n" s="2">
-        <v>45249.0</v>
+        <v>45242.0</v>
       </c>
       <c r="D448" t="n">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="449">
@@ -6414,10 +6414,10 @@
         <v>2023.0</v>
       </c>
       <c r="C449" t="n" s="2">
-        <v>45256.0</v>
+        <v>45249.0</v>
       </c>
       <c r="D449" t="n">
-        <v>9.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="450">
@@ -6428,10 +6428,10 @@
         <v>2023.0</v>
       </c>
       <c r="C450" t="n" s="2">
-        <v>45263.0</v>
+        <v>45256.0</v>
       </c>
       <c r="D450" t="n">
-        <v>12.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="451">
@@ -6442,10 +6442,10 @@
         <v>2023.0</v>
       </c>
       <c r="C451" t="n" s="2">
-        <v>45270.0</v>
+        <v>45263.0</v>
       </c>
       <c r="D451" t="n">
-        <v>6.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="452">
@@ -6456,10 +6456,10 @@
         <v>2023.0</v>
       </c>
       <c r="C452" t="n" s="2">
-        <v>45277.0</v>
+        <v>45270.0</v>
       </c>
       <c r="D452" t="n">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="453">
@@ -6470,7 +6470,7 @@
         <v>2023.0</v>
       </c>
       <c r="C453" t="n" s="2">
-        <v>45284.0</v>
+        <v>45277.0</v>
       </c>
       <c r="D453" t="n">
         <v>7.0</v>
@@ -6484,10 +6484,10 @@
         <v>2023.0</v>
       </c>
       <c r="C454" t="n" s="2">
-        <v>45291.0</v>
+        <v>45284.0</v>
       </c>
       <c r="D454" t="n">
-        <v>13.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="455">
@@ -6495,13 +6495,13 @@
         <v>7</v>
       </c>
       <c r="B455" t="n">
-        <v>2024.0</v>
+        <v>2023.0</v>
       </c>
       <c r="C455" t="n" s="2">
-        <v>45299.0</v>
+        <v>45291.0</v>
       </c>
       <c r="D455" t="n">
-        <v>6.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="456">
@@ -6512,10 +6512,10 @@
         <v>2024.0</v>
       </c>
       <c r="C456" t="n" s="2">
-        <v>45306.0</v>
+        <v>45299.0</v>
       </c>
       <c r="D456" t="n">
-        <v>11.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="457">
@@ -6526,10 +6526,10 @@
         <v>2024.0</v>
       </c>
       <c r="C457" t="n" s="2">
-        <v>45313.0</v>
+        <v>45306.0</v>
       </c>
       <c r="D457" t="n">
-        <v>5.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="458">
@@ -6540,10 +6540,10 @@
         <v>2024.0</v>
       </c>
       <c r="C458" t="n" s="2">
-        <v>45320.0</v>
+        <v>45313.0</v>
       </c>
       <c r="D458" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="459">
@@ -6554,10 +6554,10 @@
         <v>2024.0</v>
       </c>
       <c r="C459" t="n" s="2">
-        <v>45327.0</v>
+        <v>45320.0</v>
       </c>
       <c r="D459" t="n">
-        <v>9.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="460">
@@ -6568,10 +6568,10 @@
         <v>2024.0</v>
       </c>
       <c r="C460" t="n" s="2">
-        <v>45334.0</v>
+        <v>45327.0</v>
       </c>
       <c r="D460" t="n">
-        <v>3.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="461">
@@ -6582,10 +6582,10 @@
         <v>2024.0</v>
       </c>
       <c r="C461" t="n" s="2">
-        <v>45341.0</v>
+        <v>45334.0</v>
       </c>
       <c r="D461" t="n">
-        <v>21.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="462">
@@ -6596,10 +6596,10 @@
         <v>2024.0</v>
       </c>
       <c r="C462" t="n" s="2">
-        <v>45348.0</v>
+        <v>45341.0</v>
       </c>
       <c r="D462" t="n">
-        <v>1.0</v>
+        <v>21.0</v>
       </c>
     </row>
     <row r="463">
@@ -6610,10 +6610,10 @@
         <v>2024.0</v>
       </c>
       <c r="C463" t="n" s="2">
-        <v>45355.0</v>
+        <v>45348.0</v>
       </c>
       <c r="D463" t="n">
-        <v>9.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="464">
@@ -6624,10 +6624,10 @@
         <v>2024.0</v>
       </c>
       <c r="C464" t="n" s="2">
-        <v>45362.0</v>
+        <v>45355.0</v>
       </c>
       <c r="D464" t="n">
-        <v>4.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="465">
@@ -6638,10 +6638,10 @@
         <v>2024.0</v>
       </c>
       <c r="C465" t="n" s="2">
-        <v>45369.0</v>
+        <v>45362.0</v>
       </c>
       <c r="D465" t="n">
-        <v>14.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="466">
@@ -6652,10 +6652,10 @@
         <v>2024.0</v>
       </c>
       <c r="C466" t="n" s="2">
-        <v>45376.0</v>
+        <v>45369.0</v>
       </c>
       <c r="D466" t="n">
-        <v>4.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="467">
@@ -6666,10 +6666,10 @@
         <v>2024.0</v>
       </c>
       <c r="C467" t="n" s="2">
-        <v>45383.0</v>
+        <v>45376.0</v>
       </c>
       <c r="D467" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="468">
@@ -6680,10 +6680,10 @@
         <v>2024.0</v>
       </c>
       <c r="C468" t="n" s="2">
-        <v>45390.0</v>
+        <v>45383.0</v>
       </c>
       <c r="D468" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="469">
@@ -6694,7 +6694,7 @@
         <v>2024.0</v>
       </c>
       <c r="C469" t="n" s="2">
-        <v>45397.0</v>
+        <v>45390.0</v>
       </c>
       <c r="D469" t="n">
         <v>1.0</v>
@@ -6708,10 +6708,10 @@
         <v>2024.0</v>
       </c>
       <c r="C470" t="n" s="2">
-        <v>45404.0</v>
+        <v>45397.0</v>
       </c>
       <c r="D470" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="471">
@@ -6722,10 +6722,10 @@
         <v>2024.0</v>
       </c>
       <c r="C471" t="n" s="2">
-        <v>45411.0</v>
+        <v>45404.0</v>
       </c>
       <c r="D471" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="472">
@@ -6736,10 +6736,10 @@
         <v>2024.0</v>
       </c>
       <c r="C472" t="n" s="2">
-        <v>45439.0</v>
+        <v>45411.0</v>
       </c>
       <c r="D472" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="473">
@@ -6750,10 +6750,10 @@
         <v>2024.0</v>
       </c>
       <c r="C473" t="n" s="2">
-        <v>45446.0</v>
+        <v>45439.0</v>
       </c>
       <c r="D473" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="474">
@@ -6764,7 +6764,7 @@
         <v>2024.0</v>
       </c>
       <c r="C474" t="n" s="2">
-        <v>45460.0</v>
+        <v>45446.0</v>
       </c>
       <c r="D474" t="n">
         <v>1.0</v>
@@ -6778,7 +6778,7 @@
         <v>2024.0</v>
       </c>
       <c r="C475" t="n" s="2">
-        <v>45481.0</v>
+        <v>45460.0</v>
       </c>
       <c r="D475" t="n">
         <v>1.0</v>
@@ -6792,7 +6792,7 @@
         <v>2024.0</v>
       </c>
       <c r="C476" t="n" s="2">
-        <v>45516.0</v>
+        <v>45481.0</v>
       </c>
       <c r="D476" t="n">
         <v>1.0</v>
@@ -6806,7 +6806,7 @@
         <v>2024.0</v>
       </c>
       <c r="C477" t="n" s="2">
-        <v>45551.0</v>
+        <v>45516.0</v>
       </c>
       <c r="D477" t="n">
         <v>1.0</v>
@@ -6820,7 +6820,7 @@
         <v>2024.0</v>
       </c>
       <c r="C478" t="n" s="2">
-        <v>45579.0</v>
+        <v>45551.0</v>
       </c>
       <c r="D478" t="n">
         <v>1.0</v>
@@ -6834,7 +6834,7 @@
         <v>2024.0</v>
       </c>
       <c r="C479" t="n" s="2">
-        <v>45614.0</v>
+        <v>45579.0</v>
       </c>
       <c r="D479" t="n">
         <v>1.0</v>
@@ -6848,10 +6848,10 @@
         <v>2024.0</v>
       </c>
       <c r="C480" t="n" s="2">
-        <v>45635.0</v>
+        <v>45614.0</v>
       </c>
       <c r="D480" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="481">
@@ -6862,10 +6862,10 @@
         <v>2024.0</v>
       </c>
       <c r="C481" t="n" s="2">
-        <v>45642.0</v>
+        <v>45635.0</v>
       </c>
       <c r="D481" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="482">
@@ -6876,10 +6876,10 @@
         <v>2024.0</v>
       </c>
       <c r="C482" t="n" s="2">
-        <v>45649.0</v>
+        <v>45642.0</v>
       </c>
       <c r="D482" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="483">
@@ -6890,10 +6890,10 @@
         <v>2024.0</v>
       </c>
       <c r="C483" t="n" s="2">
-        <v>45656.0</v>
+        <v>45649.0</v>
       </c>
       <c r="D483" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="484">
@@ -6901,13 +6901,13 @@
         <v>7</v>
       </c>
       <c r="B484" t="n">
-        <v>2025.0</v>
+        <v>2024.0</v>
       </c>
       <c r="C484" t="n" s="2">
-        <v>45665.0</v>
+        <v>45656.0</v>
       </c>
       <c r="D484" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="485">
@@ -6918,10 +6918,10 @@
         <v>2025.0</v>
       </c>
       <c r="C485" t="n" s="2">
-        <v>45672.0</v>
+        <v>45665.0</v>
       </c>
       <c r="D485" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="486">
@@ -6932,7 +6932,7 @@
         <v>2025.0</v>
       </c>
       <c r="C486" t="n" s="2">
-        <v>45686.0</v>
+        <v>45672.0</v>
       </c>
       <c r="D486" t="n">
         <v>2.0</v>
@@ -6946,10 +6946,10 @@
         <v>2025.0</v>
       </c>
       <c r="C487" t="n" s="2">
-        <v>45693.0</v>
+        <v>45686.0</v>
       </c>
       <c r="D487" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="488">
@@ -6960,10 +6960,10 @@
         <v>2025.0</v>
       </c>
       <c r="C488" t="n" s="2">
-        <v>45700.0</v>
+        <v>45693.0</v>
       </c>
       <c r="D488" t="n">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="489">
@@ -6974,10 +6974,10 @@
         <v>2025.0</v>
       </c>
       <c r="C489" t="n" s="2">
-        <v>45707.0</v>
+        <v>45700.0</v>
       </c>
       <c r="D489" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="490">
@@ -6988,10 +6988,10 @@
         <v>2025.0</v>
       </c>
       <c r="C490" t="n" s="2">
-        <v>45714.0</v>
+        <v>45707.0</v>
       </c>
       <c r="D490" t="n">
-        <v>8.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="491">
@@ -7002,10 +7002,10 @@
         <v>2025.0</v>
       </c>
       <c r="C491" t="n" s="2">
-        <v>45721.0</v>
+        <v>45714.0</v>
       </c>
       <c r="D491" t="n">
-        <v>11.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="492">
@@ -7016,10 +7016,10 @@
         <v>2025.0</v>
       </c>
       <c r="C492" t="n" s="2">
-        <v>45728.0</v>
+        <v>45721.0</v>
       </c>
       <c r="D492" t="n">
-        <v>6.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="493">
@@ -7030,10 +7030,10 @@
         <v>2025.0</v>
       </c>
       <c r="C493" t="n" s="2">
-        <v>45735.0</v>
+        <v>45728.0</v>
       </c>
       <c r="D493" t="n">
-        <v>19.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="494">
@@ -7044,10 +7044,10 @@
         <v>2025.0</v>
       </c>
       <c r="C494" t="n" s="2">
-        <v>45742.0</v>
+        <v>45735.0</v>
       </c>
       <c r="D494" t="n">
-        <v>17.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="495">
@@ -7058,10 +7058,10 @@
         <v>2025.0</v>
       </c>
       <c r="C495" t="n" s="2">
-        <v>45749.0</v>
+        <v>45742.0</v>
       </c>
       <c r="D495" t="n">
-        <v>5.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="496">
@@ -7072,10 +7072,10 @@
         <v>2025.0</v>
       </c>
       <c r="C496" t="n" s="2">
-        <v>45756.0</v>
+        <v>45749.0</v>
       </c>
       <c r="D496" t="n">
-        <v>9.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="497">
@@ -7086,10 +7086,10 @@
         <v>2025.0</v>
       </c>
       <c r="C497" t="n" s="2">
-        <v>45763.0</v>
+        <v>45756.0</v>
       </c>
       <c r="D497" t="n">
-        <v>1.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="498">
@@ -7100,7 +7100,7 @@
         <v>2025.0</v>
       </c>
       <c r="C498" t="n" s="2">
-        <v>45770.0</v>
+        <v>45763.0</v>
       </c>
       <c r="D498" t="n">
         <v>1.0</v>
@@ -7114,10 +7114,10 @@
         <v>2025.0</v>
       </c>
       <c r="C499" t="n" s="2">
-        <v>45784.0</v>
+        <v>45770.0</v>
       </c>
       <c r="D499" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="500">
@@ -7128,10 +7128,10 @@
         <v>2025.0</v>
       </c>
       <c r="C500" t="n" s="2">
-        <v>45791.0</v>
+        <v>45784.0</v>
       </c>
       <c r="D500" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="501">
@@ -7142,10 +7142,10 @@
         <v>2025.0</v>
       </c>
       <c r="C501" t="n" s="2">
-        <v>45805.0</v>
+        <v>45791.0</v>
       </c>
       <c r="D501" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="502">
@@ -7156,10 +7156,10 @@
         <v>2025.0</v>
       </c>
       <c r="C502" t="n" s="2">
-        <v>45826.0</v>
+        <v>45805.0</v>
       </c>
       <c r="D502" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="503">
@@ -7170,7 +7170,7 @@
         <v>2025.0</v>
       </c>
       <c r="C503" t="n" s="2">
-        <v>45861.0</v>
+        <v>45826.0</v>
       </c>
       <c r="D503" t="n">
         <v>2.0</v>
@@ -7184,10 +7184,10 @@
         <v>2025.0</v>
       </c>
       <c r="C504" t="n" s="2">
-        <v>45868.0</v>
+        <v>45861.0</v>
       </c>
       <c r="D504" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="505">
@@ -7198,7 +7198,7 @@
         <v>2025.0</v>
       </c>
       <c r="C505" t="n" s="2">
-        <v>45889.0</v>
+        <v>45868.0</v>
       </c>
       <c r="D505" t="n">
         <v>1.0</v>
@@ -7212,7 +7212,7 @@
         <v>2025.0</v>
       </c>
       <c r="C506" t="n" s="2">
-        <v>45924.0</v>
+        <v>45889.0</v>
       </c>
       <c r="D506" t="n">
         <v>1.0</v>
@@ -7226,7 +7226,7 @@
         <v>2025.0</v>
       </c>
       <c r="C507" t="n" s="2">
-        <v>45945.0</v>
+        <v>45924.0</v>
       </c>
       <c r="D507" t="n">
         <v>1.0</v>
@@ -7240,10 +7240,10 @@
         <v>2025.0</v>
       </c>
       <c r="C508" t="n" s="2">
-        <v>45959.0</v>
+        <v>45945.0</v>
       </c>
       <c r="D508" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="509">
@@ -7254,7 +7254,7 @@
         <v>2025.0</v>
       </c>
       <c r="C509" t="n" s="2">
-        <v>46001.0</v>
+        <v>45959.0</v>
       </c>
       <c r="D509" t="n">
         <v>2.0</v>
@@ -7268,10 +7268,10 @@
         <v>2025.0</v>
       </c>
       <c r="C510" t="n" s="2">
-        <v>46008.0</v>
+        <v>46001.0</v>
       </c>
       <c r="D510" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="511">
@@ -7282,7 +7282,7 @@
         <v>2025.0</v>
       </c>
       <c r="C511" t="n" s="2">
-        <v>46022.0</v>
+        <v>46008.0</v>
       </c>
       <c r="D511" t="n">
         <v>1.0</v>
@@ -7293,10 +7293,10 @@
         <v>7</v>
       </c>
       <c r="B512" t="n">
-        <v>2026.0</v>
+        <v>2025.0</v>
       </c>
       <c r="C512" t="n" s="2">
-        <v>46030.0</v>
+        <v>46022.0</v>
       </c>
       <c r="D512" t="n">
         <v>1.0</v>
@@ -7310,7 +7310,7 @@
         <v>2026.0</v>
       </c>
       <c r="C513" t="n" s="2">
-        <v>46051.0</v>
+        <v>46030.0</v>
       </c>
       <c r="D513" t="n">
         <v>1.0</v>
@@ -7324,7 +7324,7 @@
         <v>2026.0</v>
       </c>
       <c r="C514" t="n" s="2">
-        <v>46058.0</v>
+        <v>46051.0</v>
       </c>
       <c r="D514" t="n">
         <v>1.0</v>
@@ -7338,10 +7338,10 @@
         <v>2026.0</v>
       </c>
       <c r="C515" t="n" s="2">
-        <v>46065.0</v>
+        <v>46058.0</v>
       </c>
       <c r="D515" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="516">
@@ -7352,24 +7352,24 @@
         <v>2026.0</v>
       </c>
       <c r="C516" t="n" s="2">
-        <v>46135.0</v>
+        <v>46065.0</v>
       </c>
       <c r="D516" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B517" t="n">
-        <v>2024.0</v>
+        <v>2026.0</v>
       </c>
       <c r="C517" t="n" s="2">
-        <v>45495.0</v>
+        <v>46135.0</v>
       </c>
       <c r="D517" t="n">
-        <v>1.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="518">
@@ -7380,10 +7380,10 @@
         <v>2024.0</v>
       </c>
       <c r="C518" t="n" s="2">
-        <v>45502.0</v>
+        <v>45495.0</v>
       </c>
       <c r="D518" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="519">
@@ -7391,13 +7391,13 @@
         <v>8</v>
       </c>
       <c r="B519" t="n">
-        <v>2025.0</v>
+        <v>2024.0</v>
       </c>
       <c r="C519" t="n" s="2">
-        <v>45665.0</v>
+        <v>45502.0</v>
       </c>
       <c r="D519" t="n">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="520">
@@ -7408,10 +7408,10 @@
         <v>2025.0</v>
       </c>
       <c r="C520" t="n" s="2">
-        <v>45672.0</v>
+        <v>45665.0</v>
       </c>
       <c r="D520" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="521">
@@ -7422,10 +7422,10 @@
         <v>2025.0</v>
       </c>
       <c r="C521" t="n" s="2">
-        <v>45679.0</v>
+        <v>45672.0</v>
       </c>
       <c r="D521" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="522">
@@ -7436,10 +7436,10 @@
         <v>2025.0</v>
       </c>
       <c r="C522" t="n" s="2">
-        <v>45686.0</v>
+        <v>45679.0</v>
       </c>
       <c r="D522" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="523">
@@ -7450,10 +7450,10 @@
         <v>2025.0</v>
       </c>
       <c r="C523" t="n" s="2">
-        <v>45693.0</v>
+        <v>45686.0</v>
       </c>
       <c r="D523" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="524">
@@ -7464,10 +7464,10 @@
         <v>2025.0</v>
       </c>
       <c r="C524" t="n" s="2">
-        <v>45700.0</v>
+        <v>45693.0</v>
       </c>
       <c r="D524" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="525">
@@ -7478,10 +7478,10 @@
         <v>2025.0</v>
       </c>
       <c r="C525" t="n" s="2">
-        <v>45707.0</v>
+        <v>45700.0</v>
       </c>
       <c r="D525" t="n">
-        <v>7.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="526">
@@ -7492,10 +7492,10 @@
         <v>2025.0</v>
       </c>
       <c r="C526" t="n" s="2">
-        <v>45714.0</v>
+        <v>45707.0</v>
       </c>
       <c r="D526" t="n">
-        <v>3.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="527">
@@ -7506,10 +7506,10 @@
         <v>2025.0</v>
       </c>
       <c r="C527" t="n" s="2">
-        <v>45721.0</v>
+        <v>45714.0</v>
       </c>
       <c r="D527" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="528">
@@ -7520,10 +7520,10 @@
         <v>2025.0</v>
       </c>
       <c r="C528" t="n" s="2">
-        <v>45728.0</v>
+        <v>45721.0</v>
       </c>
       <c r="D528" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="529">
@@ -7534,7 +7534,7 @@
         <v>2025.0</v>
       </c>
       <c r="C529" t="n" s="2">
-        <v>45742.0</v>
+        <v>45728.0</v>
       </c>
       <c r="D529" t="n">
         <v>1.0</v>
@@ -7548,7 +7548,7 @@
         <v>2025.0</v>
       </c>
       <c r="C530" t="n" s="2">
-        <v>45749.0</v>
+        <v>45742.0</v>
       </c>
       <c r="D530" t="n">
         <v>1.0</v>
@@ -7562,7 +7562,7 @@
         <v>2025.0</v>
       </c>
       <c r="C531" t="n" s="2">
-        <v>45763.0</v>
+        <v>45749.0</v>
       </c>
       <c r="D531" t="n">
         <v>1.0</v>
@@ -7576,10 +7576,10 @@
         <v>2025.0</v>
       </c>
       <c r="C532" t="n" s="2">
-        <v>45777.0</v>
+        <v>45763.0</v>
       </c>
       <c r="D532" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="533">
@@ -7590,10 +7590,10 @@
         <v>2025.0</v>
       </c>
       <c r="C533" t="n" s="2">
-        <v>45784.0</v>
+        <v>45777.0</v>
       </c>
       <c r="D533" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="534">
@@ -7604,7 +7604,7 @@
         <v>2025.0</v>
       </c>
       <c r="C534" t="n" s="2">
-        <v>45798.0</v>
+        <v>45784.0</v>
       </c>
       <c r="D534" t="n">
         <v>1.0</v>
@@ -7618,7 +7618,7 @@
         <v>2025.0</v>
       </c>
       <c r="C535" t="n" s="2">
-        <v>45805.0</v>
+        <v>45798.0</v>
       </c>
       <c r="D535" t="n">
         <v>1.0</v>
@@ -7632,10 +7632,10 @@
         <v>2025.0</v>
       </c>
       <c r="C536" t="n" s="2">
-        <v>45812.0</v>
+        <v>45805.0</v>
       </c>
       <c r="D536" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="537">
@@ -7646,7 +7646,7 @@
         <v>2025.0</v>
       </c>
       <c r="C537" t="n" s="2">
-        <v>45819.0</v>
+        <v>45812.0</v>
       </c>
       <c r="D537" t="n">
         <v>2.0</v>
@@ -7660,7 +7660,7 @@
         <v>2025.0</v>
       </c>
       <c r="C538" t="n" s="2">
-        <v>45833.0</v>
+        <v>45819.0</v>
       </c>
       <c r="D538" t="n">
         <v>2.0</v>
@@ -7674,10 +7674,10 @@
         <v>2025.0</v>
       </c>
       <c r="C539" t="n" s="2">
-        <v>45847.0</v>
+        <v>45833.0</v>
       </c>
       <c r="D539" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="540">
@@ -7688,10 +7688,10 @@
         <v>2025.0</v>
       </c>
       <c r="C540" t="n" s="2">
-        <v>45854.0</v>
+        <v>45847.0</v>
       </c>
       <c r="D540" t="n">
-        <v>8.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="541">
@@ -7702,10 +7702,10 @@
         <v>2025.0</v>
       </c>
       <c r="C541" t="n" s="2">
-        <v>45861.0</v>
+        <v>45854.0</v>
       </c>
       <c r="D541" t="n">
-        <v>12.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="542">
@@ -7716,10 +7716,10 @@
         <v>2025.0</v>
       </c>
       <c r="C542" t="n" s="2">
-        <v>45868.0</v>
+        <v>45861.0</v>
       </c>
       <c r="D542" t="n">
-        <v>6.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="543">
@@ -7730,10 +7730,10 @@
         <v>2025.0</v>
       </c>
       <c r="C543" t="n" s="2">
-        <v>45875.0</v>
+        <v>45868.0</v>
       </c>
       <c r="D543" t="n">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="544">
@@ -7744,7 +7744,7 @@
         <v>2025.0</v>
       </c>
       <c r="C544" t="n" s="2">
-        <v>45896.0</v>
+        <v>45875.0</v>
       </c>
       <c r="D544" t="n">
         <v>1.0</v>
@@ -7758,7 +7758,7 @@
         <v>2025.0</v>
       </c>
       <c r="C545" t="n" s="2">
-        <v>45903.0</v>
+        <v>45896.0</v>
       </c>
       <c r="D545" t="n">
         <v>1.0</v>
@@ -7772,7 +7772,7 @@
         <v>2025.0</v>
       </c>
       <c r="C546" t="n" s="2">
-        <v>45931.0</v>
+        <v>45903.0</v>
       </c>
       <c r="D546" t="n">
         <v>1.0</v>
@@ -7786,10 +7786,10 @@
         <v>2025.0</v>
       </c>
       <c r="C547" t="n" s="2">
-        <v>45938.0</v>
+        <v>45931.0</v>
       </c>
       <c r="D547" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="548">
@@ -7800,10 +7800,10 @@
         <v>2025.0</v>
       </c>
       <c r="C548" t="n" s="2">
-        <v>45945.0</v>
+        <v>45938.0</v>
       </c>
       <c r="D548" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="549">
@@ -7814,7 +7814,7 @@
         <v>2025.0</v>
       </c>
       <c r="C549" t="n" s="2">
-        <v>45966.0</v>
+        <v>45945.0</v>
       </c>
       <c r="D549" t="n">
         <v>2.0</v>
@@ -7828,10 +7828,10 @@
         <v>2025.0</v>
       </c>
       <c r="C550" t="n" s="2">
-        <v>45973.0</v>
+        <v>45966.0</v>
       </c>
       <c r="D550" t="n">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="551">
@@ -7842,10 +7842,10 @@
         <v>2025.0</v>
       </c>
       <c r="C551" t="n" s="2">
-        <v>45980.0</v>
+        <v>45973.0</v>
       </c>
       <c r="D551" t="n">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="552">
@@ -7856,10 +7856,10 @@
         <v>2025.0</v>
       </c>
       <c r="C552" t="n" s="2">
-        <v>45987.0</v>
+        <v>45980.0</v>
       </c>
       <c r="D552" t="n">
-        <v>20.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="553">
@@ -7870,10 +7870,10 @@
         <v>2025.0</v>
       </c>
       <c r="C553" t="n" s="2">
-        <v>45994.0</v>
+        <v>45987.0</v>
       </c>
       <c r="D553" t="n">
-        <v>5.0</v>
+        <v>20.0</v>
       </c>
     </row>
     <row r="554">
@@ -7884,10 +7884,10 @@
         <v>2025.0</v>
       </c>
       <c r="C554" t="n" s="2">
-        <v>46001.0</v>
+        <v>45994.0</v>
       </c>
       <c r="D554" t="n">
-        <v>8.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="555">
@@ -7898,10 +7898,10 @@
         <v>2025.0</v>
       </c>
       <c r="C555" t="n" s="2">
-        <v>46008.0</v>
+        <v>46001.0</v>
       </c>
       <c r="D555" t="n">
-        <v>24.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="556">
@@ -7912,10 +7912,10 @@
         <v>2025.0</v>
       </c>
       <c r="C556" t="n" s="2">
-        <v>46015.0</v>
+        <v>46008.0</v>
       </c>
       <c r="D556" t="n">
-        <v>13.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="557">
@@ -7926,10 +7926,10 @@
         <v>2025.0</v>
       </c>
       <c r="C557" t="n" s="2">
-        <v>46022.0</v>
+        <v>46015.0</v>
       </c>
       <c r="D557" t="n">
-        <v>8.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="558">
@@ -7940,10 +7940,10 @@
         <v>2025.0</v>
       </c>
       <c r="C558" t="n" s="2">
-        <v>46029.0</v>
+        <v>46022.0</v>
       </c>
       <c r="D558" t="n">
-        <v>3.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="559">
@@ -7951,13 +7951,13 @@
         <v>8</v>
       </c>
       <c r="B559" t="n">
-        <v>2026.0</v>
+        <v>2025.0</v>
       </c>
       <c r="C559" t="n" s="2">
-        <v>46030.0</v>
+        <v>46029.0</v>
       </c>
       <c r="D559" t="n">
-        <v>24.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="560">
@@ -7968,10 +7968,10 @@
         <v>2026.0</v>
       </c>
       <c r="C560" t="n" s="2">
-        <v>46037.0</v>
+        <v>46030.0</v>
       </c>
       <c r="D560" t="n">
-        <v>22.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="561">
@@ -7982,10 +7982,10 @@
         <v>2026.0</v>
       </c>
       <c r="C561" t="n" s="2">
-        <v>46044.0</v>
+        <v>46037.0</v>
       </c>
       <c r="D561" t="n">
-        <v>27.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="562">
@@ -7996,10 +7996,10 @@
         <v>2026.0</v>
       </c>
       <c r="C562" t="n" s="2">
-        <v>46051.0</v>
+        <v>46044.0</v>
       </c>
       <c r="D562" t="n">
-        <v>18.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="563">
@@ -8010,10 +8010,10 @@
         <v>2026.0</v>
       </c>
       <c r="C563" t="n" s="2">
-        <v>46058.0</v>
+        <v>46051.0</v>
       </c>
       <c r="D563" t="n">
-        <v>25.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="564">
@@ -8024,10 +8024,10 @@
         <v>2026.0</v>
       </c>
       <c r="C564" t="n" s="2">
-        <v>46065.0</v>
+        <v>46058.0</v>
       </c>
       <c r="D564" t="n">
-        <v>22.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="565">
@@ -8038,10 +8038,10 @@
         <v>2026.0</v>
       </c>
       <c r="C565" t="n" s="2">
-        <v>46072.0</v>
+        <v>46065.0</v>
       </c>
       <c r="D565" t="n">
-        <v>13.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="566">
@@ -8052,10 +8052,10 @@
         <v>2026.0</v>
       </c>
       <c r="C566" t="n" s="2">
-        <v>46079.0</v>
+        <v>46072.0</v>
       </c>
       <c r="D566" t="n">
-        <v>24.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="567">
@@ -8066,10 +8066,10 @@
         <v>2026.0</v>
       </c>
       <c r="C567" t="n" s="2">
-        <v>46086.0</v>
+        <v>46079.0</v>
       </c>
       <c r="D567" t="n">
-        <v>26.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="568">
@@ -8080,10 +8080,10 @@
         <v>2026.0</v>
       </c>
       <c r="C568" t="n" s="2">
-        <v>46093.0</v>
+        <v>46086.0</v>
       </c>
       <c r="D568" t="n">
-        <v>33.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="569">
@@ -8094,10 +8094,10 @@
         <v>2026.0</v>
       </c>
       <c r="C569" t="n" s="2">
-        <v>46100.0</v>
+        <v>46093.0</v>
       </c>
       <c r="D569" t="n">
-        <v>25.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="570">
@@ -8108,10 +8108,10 @@
         <v>2026.0</v>
       </c>
       <c r="C570" t="n" s="2">
-        <v>46107.0</v>
+        <v>46100.0</v>
       </c>
       <c r="D570" t="n">
-        <v>31.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="571">
@@ -8122,10 +8122,10 @@
         <v>2026.0</v>
       </c>
       <c r="C571" t="n" s="2">
-        <v>46114.0</v>
+        <v>46107.0</v>
       </c>
       <c r="D571" t="n">
-        <v>10.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="572">
@@ -8136,10 +8136,10 @@
         <v>2026.0</v>
       </c>
       <c r="C572" t="n" s="2">
-        <v>46121.0</v>
+        <v>46114.0</v>
       </c>
       <c r="D572" t="n">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="573">
@@ -8150,10 +8150,10 @@
         <v>2026.0</v>
       </c>
       <c r="C573" t="n" s="2">
-        <v>46128.0</v>
+        <v>46121.0</v>
       </c>
       <c r="D573" t="n">
-        <v>15.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="574">
@@ -8164,9 +8164,23 @@
         <v>2026.0</v>
       </c>
       <c r="C574" t="n" s="2">
+        <v>46128.0</v>
+      </c>
+      <c r="D574" t="n">
+        <v>15.0</v>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="s">
+        <v>8</v>
+      </c>
+      <c r="B575" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C575" t="n" s="2">
         <v>46135.0</v>
       </c>
-      <c r="D574" t="n">
+      <c r="D575" t="n">
         <v>23.0</v>
       </c>
     </row>
@@ -8209,7 +8223,7 @@
         <v>12</v>
       </c>
       <c r="B4" t="n">
-        <v>1227.0</v>
+        <v>1235.0</v>
       </c>
     </row>
     <row r="5">
@@ -8381,7 +8395,7 @@
         <v>19</v>
       </c>
       <c r="C14" t="n">
-        <v>390.0</v>
+        <v>398.0</v>
       </c>
     </row>
     <row r="15">

--- a/Download/Focus_Positivi_ZR.xlsx
+++ b/Download/Focus_Positivi_ZR.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="619" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="621" uniqueCount="23">
   <si>
     <t>NOME_REGIONE</t>
   </si>
@@ -4252,16 +4252,16 @@
     </row>
     <row r="295">
       <c r="A295" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B295" t="n">
-        <v>2023.0</v>
+        <v>2026.0</v>
       </c>
       <c r="C295" t="n" s="2">
-        <v>45095.0</v>
+        <v>46142.0</v>
       </c>
       <c r="D295" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="296">
@@ -4272,7 +4272,7 @@
         <v>2023.0</v>
       </c>
       <c r="C296" t="n" s="2">
-        <v>45102.0</v>
+        <v>45095.0</v>
       </c>
       <c r="D296" t="n">
         <v>1.0</v>
@@ -4286,7 +4286,7 @@
         <v>2023.0</v>
       </c>
       <c r="C297" t="n" s="2">
-        <v>45158.0</v>
+        <v>45102.0</v>
       </c>
       <c r="D297" t="n">
         <v>1.0</v>
@@ -4300,10 +4300,10 @@
         <v>2023.0</v>
       </c>
       <c r="C298" t="n" s="2">
-        <v>45207.0</v>
+        <v>45158.0</v>
       </c>
       <c r="D298" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="299">
@@ -4314,7 +4314,7 @@
         <v>2023.0</v>
       </c>
       <c r="C299" t="n" s="2">
-        <v>45214.0</v>
+        <v>45207.0</v>
       </c>
       <c r="D299" t="n">
         <v>3.0</v>
@@ -4328,10 +4328,10 @@
         <v>2023.0</v>
       </c>
       <c r="C300" t="n" s="2">
-        <v>45221.0</v>
+        <v>45214.0</v>
       </c>
       <c r="D300" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="301">
@@ -4342,7 +4342,7 @@
         <v>2023.0</v>
       </c>
       <c r="C301" t="n" s="2">
-        <v>45249.0</v>
+        <v>45221.0</v>
       </c>
       <c r="D301" t="n">
         <v>1.0</v>
@@ -4356,10 +4356,10 @@
         <v>2023.0</v>
       </c>
       <c r="C302" t="n" s="2">
-        <v>45256.0</v>
+        <v>45249.0</v>
       </c>
       <c r="D302" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="303">
@@ -4370,10 +4370,10 @@
         <v>2023.0</v>
       </c>
       <c r="C303" t="n" s="2">
-        <v>45263.0</v>
+        <v>45256.0</v>
       </c>
       <c r="D303" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="304">
@@ -4384,10 +4384,10 @@
         <v>2023.0</v>
       </c>
       <c r="C304" t="n" s="2">
-        <v>45270.0</v>
+        <v>45263.0</v>
       </c>
       <c r="D304" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="305">
@@ -4398,10 +4398,10 @@
         <v>2023.0</v>
       </c>
       <c r="C305" t="n" s="2">
-        <v>45277.0</v>
+        <v>45270.0</v>
       </c>
       <c r="D305" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="306">
@@ -4412,10 +4412,10 @@
         <v>2023.0</v>
       </c>
       <c r="C306" t="n" s="2">
-        <v>45284.0</v>
+        <v>45277.0</v>
       </c>
       <c r="D306" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="307">
@@ -4426,10 +4426,10 @@
         <v>2023.0</v>
       </c>
       <c r="C307" t="n" s="2">
-        <v>45291.0</v>
+        <v>45284.0</v>
       </c>
       <c r="D307" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="308">
@@ -4437,13 +4437,13 @@
         <v>6</v>
       </c>
       <c r="B308" t="n">
-        <v>2024.0</v>
+        <v>2023.0</v>
       </c>
       <c r="C308" t="n" s="2">
-        <v>45306.0</v>
+        <v>45291.0</v>
       </c>
       <c r="D308" t="n">
-        <v>7.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="309">
@@ -4454,10 +4454,10 @@
         <v>2024.0</v>
       </c>
       <c r="C309" t="n" s="2">
-        <v>45313.0</v>
+        <v>45306.0</v>
       </c>
       <c r="D309" t="n">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="310">
@@ -4468,10 +4468,10 @@
         <v>2024.0</v>
       </c>
       <c r="C310" t="n" s="2">
-        <v>45320.0</v>
+        <v>45313.0</v>
       </c>
       <c r="D310" t="n">
-        <v>19.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="311">
@@ -4482,10 +4482,10 @@
         <v>2024.0</v>
       </c>
       <c r="C311" t="n" s="2">
-        <v>45327.0</v>
+        <v>45320.0</v>
       </c>
       <c r="D311" t="n">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="312">
@@ -4496,10 +4496,10 @@
         <v>2024.0</v>
       </c>
       <c r="C312" t="n" s="2">
-        <v>45334.0</v>
+        <v>45327.0</v>
       </c>
       <c r="D312" t="n">
-        <v>9.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="313">
@@ -4510,10 +4510,10 @@
         <v>2024.0</v>
       </c>
       <c r="C313" t="n" s="2">
-        <v>45341.0</v>
+        <v>45334.0</v>
       </c>
       <c r="D313" t="n">
-        <v>12.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="314">
@@ -4524,7 +4524,7 @@
         <v>2024.0</v>
       </c>
       <c r="C314" t="n" s="2">
-        <v>45348.0</v>
+        <v>45341.0</v>
       </c>
       <c r="D314" t="n">
         <v>12.0</v>
@@ -4538,10 +4538,10 @@
         <v>2024.0</v>
       </c>
       <c r="C315" t="n" s="2">
-        <v>45355.0</v>
+        <v>45348.0</v>
       </c>
       <c r="D315" t="n">
-        <v>10.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="316">
@@ -4552,10 +4552,10 @@
         <v>2024.0</v>
       </c>
       <c r="C316" t="n" s="2">
-        <v>45362.0</v>
+        <v>45355.0</v>
       </c>
       <c r="D316" t="n">
-        <v>12.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="317">
@@ -4566,10 +4566,10 @@
         <v>2024.0</v>
       </c>
       <c r="C317" t="n" s="2">
-        <v>45369.0</v>
+        <v>45362.0</v>
       </c>
       <c r="D317" t="n">
-        <v>13.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="318">
@@ -4580,10 +4580,10 @@
         <v>2024.0</v>
       </c>
       <c r="C318" t="n" s="2">
-        <v>45376.0</v>
+        <v>45369.0</v>
       </c>
       <c r="D318" t="n">
-        <v>18.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="319">
@@ -4594,10 +4594,10 @@
         <v>2024.0</v>
       </c>
       <c r="C319" t="n" s="2">
-        <v>45383.0</v>
+        <v>45376.0</v>
       </c>
       <c r="D319" t="n">
-        <v>12.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="320">
@@ -4608,10 +4608,10 @@
         <v>2024.0</v>
       </c>
       <c r="C320" t="n" s="2">
-        <v>45390.0</v>
+        <v>45383.0</v>
       </c>
       <c r="D320" t="n">
-        <v>6.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="321">
@@ -4622,10 +4622,10 @@
         <v>2024.0</v>
       </c>
       <c r="C321" t="n" s="2">
-        <v>45397.0</v>
+        <v>45390.0</v>
       </c>
       <c r="D321" t="n">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="322">
@@ -4636,10 +4636,10 @@
         <v>2024.0</v>
       </c>
       <c r="C322" t="n" s="2">
-        <v>45404.0</v>
+        <v>45397.0</v>
       </c>
       <c r="D322" t="n">
-        <v>3.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="323">
@@ -4650,10 +4650,10 @@
         <v>2024.0</v>
       </c>
       <c r="C323" t="n" s="2">
-        <v>45411.0</v>
+        <v>45404.0</v>
       </c>
       <c r="D323" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="324">
@@ -4664,10 +4664,10 @@
         <v>2024.0</v>
       </c>
       <c r="C324" t="n" s="2">
-        <v>45418.0</v>
+        <v>45411.0</v>
       </c>
       <c r="D324" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="325">
@@ -4678,10 +4678,10 @@
         <v>2024.0</v>
       </c>
       <c r="C325" t="n" s="2">
-        <v>45425.0</v>
+        <v>45418.0</v>
       </c>
       <c r="D325" t="n">
-        <v>9.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="326">
@@ -4692,10 +4692,10 @@
         <v>2024.0</v>
       </c>
       <c r="C326" t="n" s="2">
-        <v>45432.0</v>
+        <v>45425.0</v>
       </c>
       <c r="D326" t="n">
-        <v>6.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="327">
@@ -4706,7 +4706,7 @@
         <v>2024.0</v>
       </c>
       <c r="C327" t="n" s="2">
-        <v>45439.0</v>
+        <v>45432.0</v>
       </c>
       <c r="D327" t="n">
         <v>6.0</v>
@@ -4720,10 +4720,10 @@
         <v>2024.0</v>
       </c>
       <c r="C328" t="n" s="2">
-        <v>45446.0</v>
+        <v>45439.0</v>
       </c>
       <c r="D328" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="329">
@@ -4734,10 +4734,10 @@
         <v>2024.0</v>
       </c>
       <c r="C329" t="n" s="2">
-        <v>45453.0</v>
+        <v>45446.0</v>
       </c>
       <c r="D329" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="330">
@@ -4748,7 +4748,7 @@
         <v>2024.0</v>
       </c>
       <c r="C330" t="n" s="2">
-        <v>45460.0</v>
+        <v>45453.0</v>
       </c>
       <c r="D330" t="n">
         <v>4.0</v>
@@ -4762,7 +4762,7 @@
         <v>2024.0</v>
       </c>
       <c r="C331" t="n" s="2">
-        <v>45467.0</v>
+        <v>45460.0</v>
       </c>
       <c r="D331" t="n">
         <v>4.0</v>
@@ -4776,10 +4776,10 @@
         <v>2024.0</v>
       </c>
       <c r="C332" t="n" s="2">
-        <v>45474.0</v>
+        <v>45467.0</v>
       </c>
       <c r="D332" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="333">
@@ -4790,10 +4790,10 @@
         <v>2024.0</v>
       </c>
       <c r="C333" t="n" s="2">
-        <v>45481.0</v>
+        <v>45474.0</v>
       </c>
       <c r="D333" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="334">
@@ -4804,10 +4804,10 @@
         <v>2024.0</v>
       </c>
       <c r="C334" t="n" s="2">
-        <v>45488.0</v>
+        <v>45481.0</v>
       </c>
       <c r="D334" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="335">
@@ -4818,10 +4818,10 @@
         <v>2024.0</v>
       </c>
       <c r="C335" t="n" s="2">
-        <v>45495.0</v>
+        <v>45488.0</v>
       </c>
       <c r="D335" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="336">
@@ -4832,10 +4832,10 @@
         <v>2024.0</v>
       </c>
       <c r="C336" t="n" s="2">
-        <v>45502.0</v>
+        <v>45495.0</v>
       </c>
       <c r="D336" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="337">
@@ -4846,10 +4846,10 @@
         <v>2024.0</v>
       </c>
       <c r="C337" t="n" s="2">
-        <v>45509.0</v>
+        <v>45502.0</v>
       </c>
       <c r="D337" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="338">
@@ -4860,7 +4860,7 @@
         <v>2024.0</v>
       </c>
       <c r="C338" t="n" s="2">
-        <v>45523.0</v>
+        <v>45509.0</v>
       </c>
       <c r="D338" t="n">
         <v>1.0</v>
@@ -4874,7 +4874,7 @@
         <v>2024.0</v>
       </c>
       <c r="C339" t="n" s="2">
-        <v>45551.0</v>
+        <v>45523.0</v>
       </c>
       <c r="D339" t="n">
         <v>1.0</v>
@@ -4888,7 +4888,7 @@
         <v>2024.0</v>
       </c>
       <c r="C340" t="n" s="2">
-        <v>45558.0</v>
+        <v>45551.0</v>
       </c>
       <c r="D340" t="n">
         <v>1.0</v>
@@ -4902,10 +4902,10 @@
         <v>2024.0</v>
       </c>
       <c r="C341" t="n" s="2">
-        <v>45572.0</v>
+        <v>45558.0</v>
       </c>
       <c r="D341" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="342">
@@ -4916,10 +4916,10 @@
         <v>2024.0</v>
       </c>
       <c r="C342" t="n" s="2">
-        <v>45593.0</v>
+        <v>45572.0</v>
       </c>
       <c r="D342" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="343">
@@ -4930,10 +4930,10 @@
         <v>2024.0</v>
       </c>
       <c r="C343" t="n" s="2">
-        <v>45614.0</v>
+        <v>45593.0</v>
       </c>
       <c r="D343" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="344">
@@ -4944,10 +4944,10 @@
         <v>2024.0</v>
       </c>
       <c r="C344" t="n" s="2">
-        <v>45621.0</v>
+        <v>45614.0</v>
       </c>
       <c r="D344" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="345">
@@ -4958,7 +4958,7 @@
         <v>2024.0</v>
       </c>
       <c r="C345" t="n" s="2">
-        <v>45635.0</v>
+        <v>45621.0</v>
       </c>
       <c r="D345" t="n">
         <v>1.0</v>
@@ -4972,7 +4972,7 @@
         <v>2024.0</v>
       </c>
       <c r="C346" t="n" s="2">
-        <v>45649.0</v>
+        <v>45635.0</v>
       </c>
       <c r="D346" t="n">
         <v>1.0</v>
@@ -4983,13 +4983,13 @@
         <v>6</v>
       </c>
       <c r="B347" t="n">
-        <v>2025.0</v>
+        <v>2024.0</v>
       </c>
       <c r="C347" t="n" s="2">
-        <v>45665.0</v>
+        <v>45649.0</v>
       </c>
       <c r="D347" t="n">
-        <v>9.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="348">
@@ -5000,10 +5000,10 @@
         <v>2025.0</v>
       </c>
       <c r="C348" t="n" s="2">
-        <v>45672.0</v>
+        <v>45665.0</v>
       </c>
       <c r="D348" t="n">
-        <v>3.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="349">
@@ -5014,10 +5014,10 @@
         <v>2025.0</v>
       </c>
       <c r="C349" t="n" s="2">
-        <v>45679.0</v>
+        <v>45672.0</v>
       </c>
       <c r="D349" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="350">
@@ -5028,10 +5028,10 @@
         <v>2025.0</v>
       </c>
       <c r="C350" t="n" s="2">
-        <v>45686.0</v>
+        <v>45679.0</v>
       </c>
       <c r="D350" t="n">
-        <v>8.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="351">
@@ -5042,10 +5042,10 @@
         <v>2025.0</v>
       </c>
       <c r="C351" t="n" s="2">
-        <v>45693.0</v>
+        <v>45686.0</v>
       </c>
       <c r="D351" t="n">
-        <v>3.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="352">
@@ -5056,10 +5056,10 @@
         <v>2025.0</v>
       </c>
       <c r="C352" t="n" s="2">
-        <v>45700.0</v>
+        <v>45693.0</v>
       </c>
       <c r="D352" t="n">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="353">
@@ -5070,10 +5070,10 @@
         <v>2025.0</v>
       </c>
       <c r="C353" t="n" s="2">
-        <v>45707.0</v>
+        <v>45700.0</v>
       </c>
       <c r="D353" t="n">
-        <v>8.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="354">
@@ -5084,10 +5084,10 @@
         <v>2025.0</v>
       </c>
       <c r="C354" t="n" s="2">
-        <v>45714.0</v>
+        <v>45707.0</v>
       </c>
       <c r="D354" t="n">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="355">
@@ -5098,10 +5098,10 @@
         <v>2025.0</v>
       </c>
       <c r="C355" t="n" s="2">
-        <v>45721.0</v>
+        <v>45714.0</v>
       </c>
       <c r="D355" t="n">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="356">
@@ -5112,10 +5112,10 @@
         <v>2025.0</v>
       </c>
       <c r="C356" t="n" s="2">
-        <v>45728.0</v>
+        <v>45721.0</v>
       </c>
       <c r="D356" t="n">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="357">
@@ -5126,10 +5126,10 @@
         <v>2025.0</v>
       </c>
       <c r="C357" t="n" s="2">
-        <v>45735.0</v>
+        <v>45728.0</v>
       </c>
       <c r="D357" t="n">
-        <v>4.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="358">
@@ -5140,10 +5140,10 @@
         <v>2025.0</v>
       </c>
       <c r="C358" t="n" s="2">
-        <v>45742.0</v>
+        <v>45735.0</v>
       </c>
       <c r="D358" t="n">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="359">
@@ -5154,10 +5154,10 @@
         <v>2025.0</v>
       </c>
       <c r="C359" t="n" s="2">
-        <v>45749.0</v>
+        <v>45742.0</v>
       </c>
       <c r="D359" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="360">
@@ -5168,10 +5168,10 @@
         <v>2025.0</v>
       </c>
       <c r="C360" t="n" s="2">
-        <v>45756.0</v>
+        <v>45749.0</v>
       </c>
       <c r="D360" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="361">
@@ -5182,10 +5182,10 @@
         <v>2025.0</v>
       </c>
       <c r="C361" t="n" s="2">
-        <v>45763.0</v>
+        <v>45756.0</v>
       </c>
       <c r="D361" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="362">
@@ -5196,7 +5196,7 @@
         <v>2025.0</v>
       </c>
       <c r="C362" t="n" s="2">
-        <v>45770.0</v>
+        <v>45763.0</v>
       </c>
       <c r="D362" t="n">
         <v>4.0</v>
@@ -5210,10 +5210,10 @@
         <v>2025.0</v>
       </c>
       <c r="C363" t="n" s="2">
-        <v>45777.0</v>
+        <v>45770.0</v>
       </c>
       <c r="D363" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="364">
@@ -5224,7 +5224,7 @@
         <v>2025.0</v>
       </c>
       <c r="C364" t="n" s="2">
-        <v>45784.0</v>
+        <v>45777.0</v>
       </c>
       <c r="D364" t="n">
         <v>1.0</v>
@@ -5238,7 +5238,7 @@
         <v>2025.0</v>
       </c>
       <c r="C365" t="n" s="2">
-        <v>45791.0</v>
+        <v>45784.0</v>
       </c>
       <c r="D365" t="n">
         <v>1.0</v>
@@ -5252,7 +5252,7 @@
         <v>2025.0</v>
       </c>
       <c r="C366" t="n" s="2">
-        <v>45840.0</v>
+        <v>45791.0</v>
       </c>
       <c r="D366" t="n">
         <v>1.0</v>
@@ -5266,7 +5266,7 @@
         <v>2025.0</v>
       </c>
       <c r="C367" t="n" s="2">
-        <v>46001.0</v>
+        <v>45840.0</v>
       </c>
       <c r="D367" t="n">
         <v>1.0</v>
@@ -5277,10 +5277,10 @@
         <v>6</v>
       </c>
       <c r="B368" t="n">
-        <v>2026.0</v>
+        <v>2025.0</v>
       </c>
       <c r="C368" t="n" s="2">
-        <v>46037.0</v>
+        <v>46001.0</v>
       </c>
       <c r="D368" t="n">
         <v>1.0</v>
@@ -5288,13 +5288,13 @@
     </row>
     <row r="369">
       <c r="A369" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B369" t="n">
-        <v>2021.0</v>
+        <v>2026.0</v>
       </c>
       <c r="C369" t="n" s="2">
-        <v>44561.0</v>
+        <v>46037.0</v>
       </c>
       <c r="D369" t="n">
         <v>1.0</v>
@@ -5305,10 +5305,10 @@
         <v>7</v>
       </c>
       <c r="B370" t="n">
-        <v>2022.0</v>
+        <v>2021.0</v>
       </c>
       <c r="C370" t="n" s="2">
-        <v>44569.0</v>
+        <v>44561.0</v>
       </c>
       <c r="D370" t="n">
         <v>1.0</v>
@@ -5322,10 +5322,10 @@
         <v>2022.0</v>
       </c>
       <c r="C371" t="n" s="2">
-        <v>44576.0</v>
+        <v>44569.0</v>
       </c>
       <c r="D371" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="372">
@@ -5336,10 +5336,10 @@
         <v>2022.0</v>
       </c>
       <c r="C372" t="n" s="2">
-        <v>44583.0</v>
+        <v>44576.0</v>
       </c>
       <c r="D372" t="n">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="373">
@@ -5350,10 +5350,10 @@
         <v>2022.0</v>
       </c>
       <c r="C373" t="n" s="2">
-        <v>44590.0</v>
+        <v>44583.0</v>
       </c>
       <c r="D373" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="374">
@@ -5364,10 +5364,10 @@
         <v>2022.0</v>
       </c>
       <c r="C374" t="n" s="2">
-        <v>44604.0</v>
+        <v>44590.0</v>
       </c>
       <c r="D374" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="375">
@@ -5378,7 +5378,7 @@
         <v>2022.0</v>
       </c>
       <c r="C375" t="n" s="2">
-        <v>44611.0</v>
+        <v>44604.0</v>
       </c>
       <c r="D375" t="n">
         <v>3.0</v>
@@ -5392,10 +5392,10 @@
         <v>2022.0</v>
       </c>
       <c r="C376" t="n" s="2">
-        <v>44618.0</v>
+        <v>44611.0</v>
       </c>
       <c r="D376" t="n">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="377">
@@ -5406,7 +5406,7 @@
         <v>2022.0</v>
       </c>
       <c r="C377" t="n" s="2">
-        <v>44625.0</v>
+        <v>44618.0</v>
       </c>
       <c r="D377" t="n">
         <v>5.0</v>
@@ -5420,10 +5420,10 @@
         <v>2022.0</v>
       </c>
       <c r="C378" t="n" s="2">
-        <v>44632.0</v>
+        <v>44625.0</v>
       </c>
       <c r="D378" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="379">
@@ -5434,10 +5434,10 @@
         <v>2022.0</v>
       </c>
       <c r="C379" t="n" s="2">
-        <v>44639.0</v>
+        <v>44632.0</v>
       </c>
       <c r="D379" t="n">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="380">
@@ -5448,10 +5448,10 @@
         <v>2022.0</v>
       </c>
       <c r="C380" t="n" s="2">
-        <v>44646.0</v>
+        <v>44639.0</v>
       </c>
       <c r="D380" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="381">
@@ -5462,10 +5462,10 @@
         <v>2022.0</v>
       </c>
       <c r="C381" t="n" s="2">
-        <v>44653.0</v>
+        <v>44646.0</v>
       </c>
       <c r="D381" t="n">
-        <v>9.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="382">
@@ -5476,10 +5476,10 @@
         <v>2022.0</v>
       </c>
       <c r="C382" t="n" s="2">
-        <v>44660.0</v>
+        <v>44653.0</v>
       </c>
       <c r="D382" t="n">
-        <v>6.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="383">
@@ -5490,10 +5490,10 @@
         <v>2022.0</v>
       </c>
       <c r="C383" t="n" s="2">
-        <v>44667.0</v>
+        <v>44660.0</v>
       </c>
       <c r="D383" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="384">
@@ -5504,10 +5504,10 @@
         <v>2022.0</v>
       </c>
       <c r="C384" t="n" s="2">
-        <v>44674.0</v>
+        <v>44667.0</v>
       </c>
       <c r="D384" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="385">
@@ -5518,10 +5518,10 @@
         <v>2022.0</v>
       </c>
       <c r="C385" t="n" s="2">
-        <v>44681.0</v>
+        <v>44674.0</v>
       </c>
       <c r="D385" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="386">
@@ -5532,10 +5532,10 @@
         <v>2022.0</v>
       </c>
       <c r="C386" t="n" s="2">
-        <v>44688.0</v>
+        <v>44681.0</v>
       </c>
       <c r="D386" t="n">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="387">
@@ -5546,10 +5546,10 @@
         <v>2022.0</v>
       </c>
       <c r="C387" t="n" s="2">
-        <v>44695.0</v>
+        <v>44688.0</v>
       </c>
       <c r="D387" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="388">
@@ -5560,10 +5560,10 @@
         <v>2022.0</v>
       </c>
       <c r="C388" t="n" s="2">
-        <v>44702.0</v>
+        <v>44695.0</v>
       </c>
       <c r="D388" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="389">
@@ -5574,10 +5574,10 @@
         <v>2022.0</v>
       </c>
       <c r="C389" t="n" s="2">
-        <v>44709.0</v>
+        <v>44702.0</v>
       </c>
       <c r="D389" t="n">
-        <v>8.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="390">
@@ -5588,10 +5588,10 @@
         <v>2022.0</v>
       </c>
       <c r="C390" t="n" s="2">
-        <v>44716.0</v>
+        <v>44709.0</v>
       </c>
       <c r="D390" t="n">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="391">
@@ -5602,10 +5602,10 @@
         <v>2022.0</v>
       </c>
       <c r="C391" t="n" s="2">
-        <v>44723.0</v>
+        <v>44716.0</v>
       </c>
       <c r="D391" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="392">
@@ -5616,10 +5616,10 @@
         <v>2022.0</v>
       </c>
       <c r="C392" t="n" s="2">
-        <v>44730.0</v>
+        <v>44723.0</v>
       </c>
       <c r="D392" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="393">
@@ -5630,7 +5630,7 @@
         <v>2022.0</v>
       </c>
       <c r="C393" t="n" s="2">
-        <v>44737.0</v>
+        <v>44730.0</v>
       </c>
       <c r="D393" t="n">
         <v>4.0</v>
@@ -5644,10 +5644,10 @@
         <v>2022.0</v>
       </c>
       <c r="C394" t="n" s="2">
-        <v>44744.0</v>
+        <v>44737.0</v>
       </c>
       <c r="D394" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="395">
@@ -5658,10 +5658,10 @@
         <v>2022.0</v>
       </c>
       <c r="C395" t="n" s="2">
-        <v>44751.0</v>
+        <v>44744.0</v>
       </c>
       <c r="D395" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="396">
@@ -5672,10 +5672,10 @@
         <v>2022.0</v>
       </c>
       <c r="C396" t="n" s="2">
-        <v>44758.0</v>
+        <v>44751.0</v>
       </c>
       <c r="D396" t="n">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="397">
@@ -5686,10 +5686,10 @@
         <v>2022.0</v>
       </c>
       <c r="C397" t="n" s="2">
-        <v>44765.0</v>
+        <v>44758.0</v>
       </c>
       <c r="D397" t="n">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="398">
@@ -5700,10 +5700,10 @@
         <v>2022.0</v>
       </c>
       <c r="C398" t="n" s="2">
-        <v>44779.0</v>
+        <v>44765.0</v>
       </c>
       <c r="D398" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="399">
@@ -5714,10 +5714,10 @@
         <v>2022.0</v>
       </c>
       <c r="C399" t="n" s="2">
-        <v>44786.0</v>
+        <v>44779.0</v>
       </c>
       <c r="D399" t="n">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="400">
@@ -5728,10 +5728,10 @@
         <v>2022.0</v>
       </c>
       <c r="C400" t="n" s="2">
-        <v>44863.0</v>
+        <v>44786.0</v>
       </c>
       <c r="D400" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="401">
@@ -5742,10 +5742,10 @@
         <v>2022.0</v>
       </c>
       <c r="C401" t="n" s="2">
-        <v>44870.0</v>
+        <v>44863.0</v>
       </c>
       <c r="D401" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="402">
@@ -5756,10 +5756,10 @@
         <v>2022.0</v>
       </c>
       <c r="C402" t="n" s="2">
-        <v>44884.0</v>
+        <v>44870.0</v>
       </c>
       <c r="D402" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="403">
@@ -5770,7 +5770,7 @@
         <v>2022.0</v>
       </c>
       <c r="C403" t="n" s="2">
-        <v>44891.0</v>
+        <v>44884.0</v>
       </c>
       <c r="D403" t="n">
         <v>2.0</v>
@@ -5784,10 +5784,10 @@
         <v>2022.0</v>
       </c>
       <c r="C404" t="n" s="2">
-        <v>44898.0</v>
+        <v>44891.0</v>
       </c>
       <c r="D404" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="405">
@@ -5798,10 +5798,10 @@
         <v>2022.0</v>
       </c>
       <c r="C405" t="n" s="2">
-        <v>44912.0</v>
+        <v>44898.0</v>
       </c>
       <c r="D405" t="n">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="406">
@@ -5812,10 +5812,10 @@
         <v>2022.0</v>
       </c>
       <c r="C406" t="n" s="2">
-        <v>44919.0</v>
+        <v>44912.0</v>
       </c>
       <c r="D406" t="n">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="407">
@@ -5826,10 +5826,10 @@
         <v>2022.0</v>
       </c>
       <c r="C407" t="n" s="2">
-        <v>44926.0</v>
+        <v>44919.0</v>
       </c>
       <c r="D407" t="n">
-        <v>12.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="408">
@@ -5837,13 +5837,13 @@
         <v>7</v>
       </c>
       <c r="B408" t="n">
-        <v>2023.0</v>
+        <v>2022.0</v>
       </c>
       <c r="C408" t="n" s="2">
-        <v>44934.0</v>
+        <v>44926.0</v>
       </c>
       <c r="D408" t="n">
-        <v>4.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="409">
@@ -5854,10 +5854,10 @@
         <v>2023.0</v>
       </c>
       <c r="C409" t="n" s="2">
-        <v>44941.0</v>
+        <v>44934.0</v>
       </c>
       <c r="D409" t="n">
-        <v>16.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="410">
@@ -5868,10 +5868,10 @@
         <v>2023.0</v>
       </c>
       <c r="C410" t="n" s="2">
-        <v>44948.0</v>
+        <v>44941.0</v>
       </c>
       <c r="D410" t="n">
-        <v>5.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="411">
@@ -5882,10 +5882,10 @@
         <v>2023.0</v>
       </c>
       <c r="C411" t="n" s="2">
-        <v>44955.0</v>
+        <v>44948.0</v>
       </c>
       <c r="D411" t="n">
-        <v>19.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="412">
@@ -5896,10 +5896,10 @@
         <v>2023.0</v>
       </c>
       <c r="C412" t="n" s="2">
-        <v>44962.0</v>
+        <v>44955.0</v>
       </c>
       <c r="D412" t="n">
-        <v>22.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="413">
@@ -5910,10 +5910,10 @@
         <v>2023.0</v>
       </c>
       <c r="C413" t="n" s="2">
-        <v>44969.0</v>
+        <v>44962.0</v>
       </c>
       <c r="D413" t="n">
-        <v>9.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="414">
@@ -5924,10 +5924,10 @@
         <v>2023.0</v>
       </c>
       <c r="C414" t="n" s="2">
-        <v>44976.0</v>
+        <v>44969.0</v>
       </c>
       <c r="D414" t="n">
-        <v>22.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="415">
@@ -5938,10 +5938,10 @@
         <v>2023.0</v>
       </c>
       <c r="C415" t="n" s="2">
-        <v>44983.0</v>
+        <v>44976.0</v>
       </c>
       <c r="D415" t="n">
-        <v>29.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="416">
@@ -5952,10 +5952,10 @@
         <v>2023.0</v>
       </c>
       <c r="C416" t="n" s="2">
-        <v>44990.0</v>
+        <v>44983.0</v>
       </c>
       <c r="D416" t="n">
-        <v>5.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="417">
@@ -5966,10 +5966,10 @@
         <v>2023.0</v>
       </c>
       <c r="C417" t="n" s="2">
-        <v>44997.0</v>
+        <v>44990.0</v>
       </c>
       <c r="D417" t="n">
-        <v>24.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="418">
@@ -5980,10 +5980,10 @@
         <v>2023.0</v>
       </c>
       <c r="C418" t="n" s="2">
-        <v>45004.0</v>
+        <v>44997.0</v>
       </c>
       <c r="D418" t="n">
-        <v>8.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="419">
@@ -5994,10 +5994,10 @@
         <v>2023.0</v>
       </c>
       <c r="C419" t="n" s="2">
-        <v>45011.0</v>
+        <v>45004.0</v>
       </c>
       <c r="D419" t="n">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="420">
@@ -6008,10 +6008,10 @@
         <v>2023.0</v>
       </c>
       <c r="C420" t="n" s="2">
-        <v>45018.0</v>
+        <v>45011.0</v>
       </c>
       <c r="D420" t="n">
-        <v>18.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="421">
@@ -6022,10 +6022,10 @@
         <v>2023.0</v>
       </c>
       <c r="C421" t="n" s="2">
-        <v>45025.0</v>
+        <v>45018.0</v>
       </c>
       <c r="D421" t="n">
-        <v>13.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="422">
@@ -6036,10 +6036,10 @@
         <v>2023.0</v>
       </c>
       <c r="C422" t="n" s="2">
-        <v>45032.0</v>
+        <v>45025.0</v>
       </c>
       <c r="D422" t="n">
-        <v>18.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="423">
@@ -6050,10 +6050,10 @@
         <v>2023.0</v>
       </c>
       <c r="C423" t="n" s="2">
-        <v>45039.0</v>
+        <v>45032.0</v>
       </c>
       <c r="D423" t="n">
-        <v>15.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="424">
@@ -6064,10 +6064,10 @@
         <v>2023.0</v>
       </c>
       <c r="C424" t="n" s="2">
-        <v>45046.0</v>
+        <v>45039.0</v>
       </c>
       <c r="D424" t="n">
-        <v>12.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="425">
@@ -6078,10 +6078,10 @@
         <v>2023.0</v>
       </c>
       <c r="C425" t="n" s="2">
-        <v>45053.0</v>
+        <v>45046.0</v>
       </c>
       <c r="D425" t="n">
-        <v>6.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="426">
@@ -6092,10 +6092,10 @@
         <v>2023.0</v>
       </c>
       <c r="C426" t="n" s="2">
-        <v>45060.0</v>
+        <v>45053.0</v>
       </c>
       <c r="D426" t="n">
-        <v>11.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="427">
@@ -6106,10 +6106,10 @@
         <v>2023.0</v>
       </c>
       <c r="C427" t="n" s="2">
-        <v>45067.0</v>
+        <v>45060.0</v>
       </c>
       <c r="D427" t="n">
-        <v>8.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="428">
@@ -6120,7 +6120,7 @@
         <v>2023.0</v>
       </c>
       <c r="C428" t="n" s="2">
-        <v>45074.0</v>
+        <v>45067.0</v>
       </c>
       <c r="D428" t="n">
         <v>8.0</v>
@@ -6134,10 +6134,10 @@
         <v>2023.0</v>
       </c>
       <c r="C429" t="n" s="2">
-        <v>45081.0</v>
+        <v>45074.0</v>
       </c>
       <c r="D429" t="n">
-        <v>5.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="430">
@@ -6148,10 +6148,10 @@
         <v>2023.0</v>
       </c>
       <c r="C430" t="n" s="2">
-        <v>45088.0</v>
+        <v>45081.0</v>
       </c>
       <c r="D430" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="431">
@@ -6162,10 +6162,10 @@
         <v>2023.0</v>
       </c>
       <c r="C431" t="n" s="2">
-        <v>45095.0</v>
+        <v>45088.0</v>
       </c>
       <c r="D431" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="432">
@@ -6176,10 +6176,10 @@
         <v>2023.0</v>
       </c>
       <c r="C432" t="n" s="2">
-        <v>45102.0</v>
+        <v>45095.0</v>
       </c>
       <c r="D432" t="n">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="433">
@@ -6190,10 +6190,10 @@
         <v>2023.0</v>
       </c>
       <c r="C433" t="n" s="2">
-        <v>45109.0</v>
+        <v>45102.0</v>
       </c>
       <c r="D433" t="n">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="434">
@@ -6204,10 +6204,10 @@
         <v>2023.0</v>
       </c>
       <c r="C434" t="n" s="2">
-        <v>45116.0</v>
+        <v>45109.0</v>
       </c>
       <c r="D434" t="n">
-        <v>3.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="435">
@@ -6218,10 +6218,10 @@
         <v>2023.0</v>
       </c>
       <c r="C435" t="n" s="2">
-        <v>45123.0</v>
+        <v>45116.0</v>
       </c>
       <c r="D435" t="n">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="436">
@@ -6232,7 +6232,7 @@
         <v>2023.0</v>
       </c>
       <c r="C436" t="n" s="2">
-        <v>45130.0</v>
+        <v>45123.0</v>
       </c>
       <c r="D436" t="n">
         <v>6.0</v>
@@ -6246,10 +6246,10 @@
         <v>2023.0</v>
       </c>
       <c r="C437" t="n" s="2">
-        <v>45137.0</v>
+        <v>45130.0</v>
       </c>
       <c r="D437" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="438">
@@ -6260,7 +6260,7 @@
         <v>2023.0</v>
       </c>
       <c r="C438" t="n" s="2">
-        <v>45144.0</v>
+        <v>45137.0</v>
       </c>
       <c r="D438" t="n">
         <v>2.0</v>
@@ -6274,7 +6274,7 @@
         <v>2023.0</v>
       </c>
       <c r="C439" t="n" s="2">
-        <v>45151.0</v>
+        <v>45144.0</v>
       </c>
       <c r="D439" t="n">
         <v>2.0</v>
@@ -6288,7 +6288,7 @@
         <v>2023.0</v>
       </c>
       <c r="C440" t="n" s="2">
-        <v>45165.0</v>
+        <v>45151.0</v>
       </c>
       <c r="D440" t="n">
         <v>2.0</v>
@@ -6302,7 +6302,7 @@
         <v>2023.0</v>
       </c>
       <c r="C441" t="n" s="2">
-        <v>45172.0</v>
+        <v>45165.0</v>
       </c>
       <c r="D441" t="n">
         <v>2.0</v>
@@ -6316,10 +6316,10 @@
         <v>2023.0</v>
       </c>
       <c r="C442" t="n" s="2">
-        <v>45179.0</v>
+        <v>45172.0</v>
       </c>
       <c r="D442" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="443">
@@ -6330,7 +6330,7 @@
         <v>2023.0</v>
       </c>
       <c r="C443" t="n" s="2">
-        <v>45186.0</v>
+        <v>45179.0</v>
       </c>
       <c r="D443" t="n">
         <v>1.0</v>
@@ -6344,7 +6344,7 @@
         <v>2023.0</v>
       </c>
       <c r="C444" t="n" s="2">
-        <v>45193.0</v>
+        <v>45186.0</v>
       </c>
       <c r="D444" t="n">
         <v>1.0</v>
@@ -6358,7 +6358,7 @@
         <v>2023.0</v>
       </c>
       <c r="C445" t="n" s="2">
-        <v>45200.0</v>
+        <v>45193.0</v>
       </c>
       <c r="D445" t="n">
         <v>1.0</v>
@@ -6372,7 +6372,7 @@
         <v>2023.0</v>
       </c>
       <c r="C446" t="n" s="2">
-        <v>45207.0</v>
+        <v>45200.0</v>
       </c>
       <c r="D446" t="n">
         <v>1.0</v>
@@ -6386,7 +6386,7 @@
         <v>2023.0</v>
       </c>
       <c r="C447" t="n" s="2">
-        <v>45235.0</v>
+        <v>45207.0</v>
       </c>
       <c r="D447" t="n">
         <v>1.0</v>
@@ -6400,10 +6400,10 @@
         <v>2023.0</v>
       </c>
       <c r="C448" t="n" s="2">
-        <v>45242.0</v>
+        <v>45235.0</v>
       </c>
       <c r="D448" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="449">
@@ -6414,10 +6414,10 @@
         <v>2023.0</v>
       </c>
       <c r="C449" t="n" s="2">
-        <v>45249.0</v>
+        <v>45242.0</v>
       </c>
       <c r="D449" t="n">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="450">
@@ -6428,10 +6428,10 @@
         <v>2023.0</v>
       </c>
       <c r="C450" t="n" s="2">
-        <v>45256.0</v>
+        <v>45249.0</v>
       </c>
       <c r="D450" t="n">
-        <v>9.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="451">
@@ -6442,10 +6442,10 @@
         <v>2023.0</v>
       </c>
       <c r="C451" t="n" s="2">
-        <v>45263.0</v>
+        <v>45256.0</v>
       </c>
       <c r="D451" t="n">
-        <v>12.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="452">
@@ -6456,10 +6456,10 @@
         <v>2023.0</v>
       </c>
       <c r="C452" t="n" s="2">
-        <v>45270.0</v>
+        <v>45263.0</v>
       </c>
       <c r="D452" t="n">
-        <v>6.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="453">
@@ -6470,10 +6470,10 @@
         <v>2023.0</v>
       </c>
       <c r="C453" t="n" s="2">
-        <v>45277.0</v>
+        <v>45270.0</v>
       </c>
       <c r="D453" t="n">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="454">
@@ -6484,7 +6484,7 @@
         <v>2023.0</v>
       </c>
       <c r="C454" t="n" s="2">
-        <v>45284.0</v>
+        <v>45277.0</v>
       </c>
       <c r="D454" t="n">
         <v>7.0</v>
@@ -6498,10 +6498,10 @@
         <v>2023.0</v>
       </c>
       <c r="C455" t="n" s="2">
-        <v>45291.0</v>
+        <v>45284.0</v>
       </c>
       <c r="D455" t="n">
-        <v>13.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="456">
@@ -6509,13 +6509,13 @@
         <v>7</v>
       </c>
       <c r="B456" t="n">
-        <v>2024.0</v>
+        <v>2023.0</v>
       </c>
       <c r="C456" t="n" s="2">
-        <v>45299.0</v>
+        <v>45291.0</v>
       </c>
       <c r="D456" t="n">
-        <v>6.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="457">
@@ -6526,10 +6526,10 @@
         <v>2024.0</v>
       </c>
       <c r="C457" t="n" s="2">
-        <v>45306.0</v>
+        <v>45299.0</v>
       </c>
       <c r="D457" t="n">
-        <v>11.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="458">
@@ -6540,10 +6540,10 @@
         <v>2024.0</v>
       </c>
       <c r="C458" t="n" s="2">
-        <v>45313.0</v>
+        <v>45306.0</v>
       </c>
       <c r="D458" t="n">
-        <v>5.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="459">
@@ -6554,10 +6554,10 @@
         <v>2024.0</v>
       </c>
       <c r="C459" t="n" s="2">
-        <v>45320.0</v>
+        <v>45313.0</v>
       </c>
       <c r="D459" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="460">
@@ -6568,10 +6568,10 @@
         <v>2024.0</v>
       </c>
       <c r="C460" t="n" s="2">
-        <v>45327.0</v>
+        <v>45320.0</v>
       </c>
       <c r="D460" t="n">
-        <v>9.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="461">
@@ -6582,10 +6582,10 @@
         <v>2024.0</v>
       </c>
       <c r="C461" t="n" s="2">
-        <v>45334.0</v>
+        <v>45327.0</v>
       </c>
       <c r="D461" t="n">
-        <v>3.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="462">
@@ -6596,10 +6596,10 @@
         <v>2024.0</v>
       </c>
       <c r="C462" t="n" s="2">
-        <v>45341.0</v>
+        <v>45334.0</v>
       </c>
       <c r="D462" t="n">
-        <v>21.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="463">
@@ -6610,10 +6610,10 @@
         <v>2024.0</v>
       </c>
       <c r="C463" t="n" s="2">
-        <v>45348.0</v>
+        <v>45341.0</v>
       </c>
       <c r="D463" t="n">
-        <v>1.0</v>
+        <v>21.0</v>
       </c>
     </row>
     <row r="464">
@@ -6624,10 +6624,10 @@
         <v>2024.0</v>
       </c>
       <c r="C464" t="n" s="2">
-        <v>45355.0</v>
+        <v>45348.0</v>
       </c>
       <c r="D464" t="n">
-        <v>9.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="465">
@@ -6638,10 +6638,10 @@
         <v>2024.0</v>
       </c>
       <c r="C465" t="n" s="2">
-        <v>45362.0</v>
+        <v>45355.0</v>
       </c>
       <c r="D465" t="n">
-        <v>4.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="466">
@@ -6652,10 +6652,10 @@
         <v>2024.0</v>
       </c>
       <c r="C466" t="n" s="2">
-        <v>45369.0</v>
+        <v>45362.0</v>
       </c>
       <c r="D466" t="n">
-        <v>14.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="467">
@@ -6666,10 +6666,10 @@
         <v>2024.0</v>
       </c>
       <c r="C467" t="n" s="2">
-        <v>45376.0</v>
+        <v>45369.0</v>
       </c>
       <c r="D467" t="n">
-        <v>4.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="468">
@@ -6680,10 +6680,10 @@
         <v>2024.0</v>
       </c>
       <c r="C468" t="n" s="2">
-        <v>45383.0</v>
+        <v>45376.0</v>
       </c>
       <c r="D468" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="469">
@@ -6694,10 +6694,10 @@
         <v>2024.0</v>
       </c>
       <c r="C469" t="n" s="2">
-        <v>45390.0</v>
+        <v>45383.0</v>
       </c>
       <c r="D469" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="470">
@@ -6708,7 +6708,7 @@
         <v>2024.0</v>
       </c>
       <c r="C470" t="n" s="2">
-        <v>45397.0</v>
+        <v>45390.0</v>
       </c>
       <c r="D470" t="n">
         <v>1.0</v>
@@ -6722,10 +6722,10 @@
         <v>2024.0</v>
       </c>
       <c r="C471" t="n" s="2">
-        <v>45404.0</v>
+        <v>45397.0</v>
       </c>
       <c r="D471" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="472">
@@ -6736,10 +6736,10 @@
         <v>2024.0</v>
       </c>
       <c r="C472" t="n" s="2">
-        <v>45411.0</v>
+        <v>45404.0</v>
       </c>
       <c r="D472" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="473">
@@ -6750,10 +6750,10 @@
         <v>2024.0</v>
       </c>
       <c r="C473" t="n" s="2">
-        <v>45439.0</v>
+        <v>45411.0</v>
       </c>
       <c r="D473" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="474">
@@ -6764,10 +6764,10 @@
         <v>2024.0</v>
       </c>
       <c r="C474" t="n" s="2">
-        <v>45446.0</v>
+        <v>45439.0</v>
       </c>
       <c r="D474" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="475">
@@ -6778,7 +6778,7 @@
         <v>2024.0</v>
       </c>
       <c r="C475" t="n" s="2">
-        <v>45460.0</v>
+        <v>45446.0</v>
       </c>
       <c r="D475" t="n">
         <v>1.0</v>
@@ -6792,7 +6792,7 @@
         <v>2024.0</v>
       </c>
       <c r="C476" t="n" s="2">
-        <v>45481.0</v>
+        <v>45460.0</v>
       </c>
       <c r="D476" t="n">
         <v>1.0</v>
@@ -6806,7 +6806,7 @@
         <v>2024.0</v>
       </c>
       <c r="C477" t="n" s="2">
-        <v>45516.0</v>
+        <v>45481.0</v>
       </c>
       <c r="D477" t="n">
         <v>1.0</v>
@@ -6820,7 +6820,7 @@
         <v>2024.0</v>
       </c>
       <c r="C478" t="n" s="2">
-        <v>45551.0</v>
+        <v>45516.0</v>
       </c>
       <c r="D478" t="n">
         <v>1.0</v>
@@ -6834,7 +6834,7 @@
         <v>2024.0</v>
       </c>
       <c r="C479" t="n" s="2">
-        <v>45579.0</v>
+        <v>45551.0</v>
       </c>
       <c r="D479" t="n">
         <v>1.0</v>
@@ -6848,7 +6848,7 @@
         <v>2024.0</v>
       </c>
       <c r="C480" t="n" s="2">
-        <v>45614.0</v>
+        <v>45579.0</v>
       </c>
       <c r="D480" t="n">
         <v>1.0</v>
@@ -6862,10 +6862,10 @@
         <v>2024.0</v>
       </c>
       <c r="C481" t="n" s="2">
-        <v>45635.0</v>
+        <v>45614.0</v>
       </c>
       <c r="D481" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="482">
@@ -6876,10 +6876,10 @@
         <v>2024.0</v>
       </c>
       <c r="C482" t="n" s="2">
-        <v>45642.0</v>
+        <v>45635.0</v>
       </c>
       <c r="D482" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="483">
@@ -6890,10 +6890,10 @@
         <v>2024.0</v>
       </c>
       <c r="C483" t="n" s="2">
-        <v>45649.0</v>
+        <v>45642.0</v>
       </c>
       <c r="D483" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="484">
@@ -6904,10 +6904,10 @@
         <v>2024.0</v>
       </c>
       <c r="C484" t="n" s="2">
-        <v>45656.0</v>
+        <v>45649.0</v>
       </c>
       <c r="D484" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="485">
@@ -6915,13 +6915,13 @@
         <v>7</v>
       </c>
       <c r="B485" t="n">
-        <v>2025.0</v>
+        <v>2024.0</v>
       </c>
       <c r="C485" t="n" s="2">
-        <v>45665.0</v>
+        <v>45656.0</v>
       </c>
       <c r="D485" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="486">
@@ -6932,10 +6932,10 @@
         <v>2025.0</v>
       </c>
       <c r="C486" t="n" s="2">
-        <v>45672.0</v>
+        <v>45665.0</v>
       </c>
       <c r="D486" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="487">
@@ -6946,7 +6946,7 @@
         <v>2025.0</v>
       </c>
       <c r="C487" t="n" s="2">
-        <v>45686.0</v>
+        <v>45672.0</v>
       </c>
       <c r="D487" t="n">
         <v>2.0</v>
@@ -6960,10 +6960,10 @@
         <v>2025.0</v>
       </c>
       <c r="C488" t="n" s="2">
-        <v>45693.0</v>
+        <v>45686.0</v>
       </c>
       <c r="D488" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="489">
@@ -6974,10 +6974,10 @@
         <v>2025.0</v>
       </c>
       <c r="C489" t="n" s="2">
-        <v>45700.0</v>
+        <v>45693.0</v>
       </c>
       <c r="D489" t="n">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="490">
@@ -6988,10 +6988,10 @@
         <v>2025.0</v>
       </c>
       <c r="C490" t="n" s="2">
-        <v>45707.0</v>
+        <v>45700.0</v>
       </c>
       <c r="D490" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="491">
@@ -7002,10 +7002,10 @@
         <v>2025.0</v>
       </c>
       <c r="C491" t="n" s="2">
-        <v>45714.0</v>
+        <v>45707.0</v>
       </c>
       <c r="D491" t="n">
-        <v>8.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="492">
@@ -7016,10 +7016,10 @@
         <v>2025.0</v>
       </c>
       <c r="C492" t="n" s="2">
-        <v>45721.0</v>
+        <v>45714.0</v>
       </c>
       <c r="D492" t="n">
-        <v>11.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="493">
@@ -7030,10 +7030,10 @@
         <v>2025.0</v>
       </c>
       <c r="C493" t="n" s="2">
-        <v>45728.0</v>
+        <v>45721.0</v>
       </c>
       <c r="D493" t="n">
-        <v>6.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="494">
@@ -7044,10 +7044,10 @@
         <v>2025.0</v>
       </c>
       <c r="C494" t="n" s="2">
-        <v>45735.0</v>
+        <v>45728.0</v>
       </c>
       <c r="D494" t="n">
-        <v>19.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="495">
@@ -7058,10 +7058,10 @@
         <v>2025.0</v>
       </c>
       <c r="C495" t="n" s="2">
-        <v>45742.0</v>
+        <v>45735.0</v>
       </c>
       <c r="D495" t="n">
-        <v>17.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="496">
@@ -7072,10 +7072,10 @@
         <v>2025.0</v>
       </c>
       <c r="C496" t="n" s="2">
-        <v>45749.0</v>
+        <v>45742.0</v>
       </c>
       <c r="D496" t="n">
-        <v>5.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="497">
@@ -7086,10 +7086,10 @@
         <v>2025.0</v>
       </c>
       <c r="C497" t="n" s="2">
-        <v>45756.0</v>
+        <v>45749.0</v>
       </c>
       <c r="D497" t="n">
-        <v>9.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="498">
@@ -7100,10 +7100,10 @@
         <v>2025.0</v>
       </c>
       <c r="C498" t="n" s="2">
-        <v>45763.0</v>
+        <v>45756.0</v>
       </c>
       <c r="D498" t="n">
-        <v>1.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="499">
@@ -7114,7 +7114,7 @@
         <v>2025.0</v>
       </c>
       <c r="C499" t="n" s="2">
-        <v>45770.0</v>
+        <v>45763.0</v>
       </c>
       <c r="D499" t="n">
         <v>1.0</v>
@@ -7128,10 +7128,10 @@
         <v>2025.0</v>
       </c>
       <c r="C500" t="n" s="2">
-        <v>45784.0</v>
+        <v>45770.0</v>
       </c>
       <c r="D500" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="501">
@@ -7142,10 +7142,10 @@
         <v>2025.0</v>
       </c>
       <c r="C501" t="n" s="2">
-        <v>45791.0</v>
+        <v>45784.0</v>
       </c>
       <c r="D501" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="502">
@@ -7156,10 +7156,10 @@
         <v>2025.0</v>
       </c>
       <c r="C502" t="n" s="2">
-        <v>45805.0</v>
+        <v>45791.0</v>
       </c>
       <c r="D502" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="503">
@@ -7170,10 +7170,10 @@
         <v>2025.0</v>
       </c>
       <c r="C503" t="n" s="2">
-        <v>45826.0</v>
+        <v>45805.0</v>
       </c>
       <c r="D503" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="504">
@@ -7184,7 +7184,7 @@
         <v>2025.0</v>
       </c>
       <c r="C504" t="n" s="2">
-        <v>45861.0</v>
+        <v>45826.0</v>
       </c>
       <c r="D504" t="n">
         <v>2.0</v>
@@ -7198,10 +7198,10 @@
         <v>2025.0</v>
       </c>
       <c r="C505" t="n" s="2">
-        <v>45868.0</v>
+        <v>45861.0</v>
       </c>
       <c r="D505" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="506">
@@ -7212,7 +7212,7 @@
         <v>2025.0</v>
       </c>
       <c r="C506" t="n" s="2">
-        <v>45889.0</v>
+        <v>45868.0</v>
       </c>
       <c r="D506" t="n">
         <v>1.0</v>
@@ -7226,7 +7226,7 @@
         <v>2025.0</v>
       </c>
       <c r="C507" t="n" s="2">
-        <v>45924.0</v>
+        <v>45889.0</v>
       </c>
       <c r="D507" t="n">
         <v>1.0</v>
@@ -7240,7 +7240,7 @@
         <v>2025.0</v>
       </c>
       <c r="C508" t="n" s="2">
-        <v>45945.0</v>
+        <v>45924.0</v>
       </c>
       <c r="D508" t="n">
         <v>1.0</v>
@@ -7254,10 +7254,10 @@
         <v>2025.0</v>
       </c>
       <c r="C509" t="n" s="2">
-        <v>45959.0</v>
+        <v>45945.0</v>
       </c>
       <c r="D509" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="510">
@@ -7268,7 +7268,7 @@
         <v>2025.0</v>
       </c>
       <c r="C510" t="n" s="2">
-        <v>46001.0</v>
+        <v>45959.0</v>
       </c>
       <c r="D510" t="n">
         <v>2.0</v>
@@ -7282,10 +7282,10 @@
         <v>2025.0</v>
       </c>
       <c r="C511" t="n" s="2">
-        <v>46008.0</v>
+        <v>46001.0</v>
       </c>
       <c r="D511" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="512">
@@ -7296,7 +7296,7 @@
         <v>2025.0</v>
       </c>
       <c r="C512" t="n" s="2">
-        <v>46022.0</v>
+        <v>46008.0</v>
       </c>
       <c r="D512" t="n">
         <v>1.0</v>
@@ -7307,10 +7307,10 @@
         <v>7</v>
       </c>
       <c r="B513" t="n">
-        <v>2026.0</v>
+        <v>2025.0</v>
       </c>
       <c r="C513" t="n" s="2">
-        <v>46030.0</v>
+        <v>46022.0</v>
       </c>
       <c r="D513" t="n">
         <v>1.0</v>
@@ -7324,7 +7324,7 @@
         <v>2026.0</v>
       </c>
       <c r="C514" t="n" s="2">
-        <v>46051.0</v>
+        <v>46030.0</v>
       </c>
       <c r="D514" t="n">
         <v>1.0</v>
@@ -7338,7 +7338,7 @@
         <v>2026.0</v>
       </c>
       <c r="C515" t="n" s="2">
-        <v>46058.0</v>
+        <v>46051.0</v>
       </c>
       <c r="D515" t="n">
         <v>1.0</v>
@@ -7352,10 +7352,10 @@
         <v>2026.0</v>
       </c>
       <c r="C516" t="n" s="2">
-        <v>46065.0</v>
+        <v>46058.0</v>
       </c>
       <c r="D516" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="517">
@@ -7366,24 +7366,24 @@
         <v>2026.0</v>
       </c>
       <c r="C517" t="n" s="2">
-        <v>46135.0</v>
+        <v>46065.0</v>
       </c>
       <c r="D517" t="n">
-        <v>8.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B518" t="n">
-        <v>2024.0</v>
+        <v>2026.0</v>
       </c>
       <c r="C518" t="n" s="2">
-        <v>45495.0</v>
+        <v>46135.0</v>
       </c>
       <c r="D518" t="n">
-        <v>1.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="519">
@@ -7394,10 +7394,10 @@
         <v>2024.0</v>
       </c>
       <c r="C519" t="n" s="2">
-        <v>45502.0</v>
+        <v>45495.0</v>
       </c>
       <c r="D519" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="520">
@@ -7405,13 +7405,13 @@
         <v>8</v>
       </c>
       <c r="B520" t="n">
-        <v>2025.0</v>
+        <v>2024.0</v>
       </c>
       <c r="C520" t="n" s="2">
-        <v>45665.0</v>
+        <v>45502.0</v>
       </c>
       <c r="D520" t="n">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="521">
@@ -7422,10 +7422,10 @@
         <v>2025.0</v>
       </c>
       <c r="C521" t="n" s="2">
-        <v>45672.0</v>
+        <v>45665.0</v>
       </c>
       <c r="D521" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="522">
@@ -7436,10 +7436,10 @@
         <v>2025.0</v>
       </c>
       <c r="C522" t="n" s="2">
-        <v>45679.0</v>
+        <v>45672.0</v>
       </c>
       <c r="D522" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="523">
@@ -7450,10 +7450,10 @@
         <v>2025.0</v>
       </c>
       <c r="C523" t="n" s="2">
-        <v>45686.0</v>
+        <v>45679.0</v>
       </c>
       <c r="D523" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="524">
@@ -7464,10 +7464,10 @@
         <v>2025.0</v>
       </c>
       <c r="C524" t="n" s="2">
-        <v>45693.0</v>
+        <v>45686.0</v>
       </c>
       <c r="D524" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="525">
@@ -7478,10 +7478,10 @@
         <v>2025.0</v>
       </c>
       <c r="C525" t="n" s="2">
-        <v>45700.0</v>
+        <v>45693.0</v>
       </c>
       <c r="D525" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="526">
@@ -7492,10 +7492,10 @@
         <v>2025.0</v>
       </c>
       <c r="C526" t="n" s="2">
-        <v>45707.0</v>
+        <v>45700.0</v>
       </c>
       <c r="D526" t="n">
-        <v>7.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="527">
@@ -7506,10 +7506,10 @@
         <v>2025.0</v>
       </c>
       <c r="C527" t="n" s="2">
-        <v>45714.0</v>
+        <v>45707.0</v>
       </c>
       <c r="D527" t="n">
-        <v>3.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="528">
@@ -7520,10 +7520,10 @@
         <v>2025.0</v>
       </c>
       <c r="C528" t="n" s="2">
-        <v>45721.0</v>
+        <v>45714.0</v>
       </c>
       <c r="D528" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="529">
@@ -7534,10 +7534,10 @@
         <v>2025.0</v>
       </c>
       <c r="C529" t="n" s="2">
-        <v>45728.0</v>
+        <v>45721.0</v>
       </c>
       <c r="D529" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="530">
@@ -7548,7 +7548,7 @@
         <v>2025.0</v>
       </c>
       <c r="C530" t="n" s="2">
-        <v>45742.0</v>
+        <v>45728.0</v>
       </c>
       <c r="D530" t="n">
         <v>1.0</v>
@@ -7562,7 +7562,7 @@
         <v>2025.0</v>
       </c>
       <c r="C531" t="n" s="2">
-        <v>45749.0</v>
+        <v>45742.0</v>
       </c>
       <c r="D531" t="n">
         <v>1.0</v>
@@ -7576,7 +7576,7 @@
         <v>2025.0</v>
       </c>
       <c r="C532" t="n" s="2">
-        <v>45763.0</v>
+        <v>45749.0</v>
       </c>
       <c r="D532" t="n">
         <v>1.0</v>
@@ -7590,10 +7590,10 @@
         <v>2025.0</v>
       </c>
       <c r="C533" t="n" s="2">
-        <v>45777.0</v>
+        <v>45763.0</v>
       </c>
       <c r="D533" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="534">
@@ -7604,10 +7604,10 @@
         <v>2025.0</v>
       </c>
       <c r="C534" t="n" s="2">
-        <v>45784.0</v>
+        <v>45777.0</v>
       </c>
       <c r="D534" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="535">
@@ -7618,7 +7618,7 @@
         <v>2025.0</v>
       </c>
       <c r="C535" t="n" s="2">
-        <v>45798.0</v>
+        <v>45784.0</v>
       </c>
       <c r="D535" t="n">
         <v>1.0</v>
@@ -7632,7 +7632,7 @@
         <v>2025.0</v>
       </c>
       <c r="C536" t="n" s="2">
-        <v>45805.0</v>
+        <v>45798.0</v>
       </c>
       <c r="D536" t="n">
         <v>1.0</v>
@@ -7646,10 +7646,10 @@
         <v>2025.0</v>
       </c>
       <c r="C537" t="n" s="2">
-        <v>45812.0</v>
+        <v>45805.0</v>
       </c>
       <c r="D537" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="538">
@@ -7660,7 +7660,7 @@
         <v>2025.0</v>
       </c>
       <c r="C538" t="n" s="2">
-        <v>45819.0</v>
+        <v>45812.0</v>
       </c>
       <c r="D538" t="n">
         <v>2.0</v>
@@ -7674,7 +7674,7 @@
         <v>2025.0</v>
       </c>
       <c r="C539" t="n" s="2">
-        <v>45833.0</v>
+        <v>45819.0</v>
       </c>
       <c r="D539" t="n">
         <v>2.0</v>
@@ -7688,10 +7688,10 @@
         <v>2025.0</v>
       </c>
       <c r="C540" t="n" s="2">
-        <v>45847.0</v>
+        <v>45833.0</v>
       </c>
       <c r="D540" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="541">
@@ -7702,10 +7702,10 @@
         <v>2025.0</v>
       </c>
       <c r="C541" t="n" s="2">
-        <v>45854.0</v>
+        <v>45847.0</v>
       </c>
       <c r="D541" t="n">
-        <v>8.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="542">
@@ -7716,10 +7716,10 @@
         <v>2025.0</v>
       </c>
       <c r="C542" t="n" s="2">
-        <v>45861.0</v>
+        <v>45854.0</v>
       </c>
       <c r="D542" t="n">
-        <v>12.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="543">
@@ -7730,10 +7730,10 @@
         <v>2025.0</v>
       </c>
       <c r="C543" t="n" s="2">
-        <v>45868.0</v>
+        <v>45861.0</v>
       </c>
       <c r="D543" t="n">
-        <v>6.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="544">
@@ -7744,10 +7744,10 @@
         <v>2025.0</v>
       </c>
       <c r="C544" t="n" s="2">
-        <v>45875.0</v>
+        <v>45868.0</v>
       </c>
       <c r="D544" t="n">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="545">
@@ -7758,7 +7758,7 @@
         <v>2025.0</v>
       </c>
       <c r="C545" t="n" s="2">
-        <v>45896.0</v>
+        <v>45875.0</v>
       </c>
       <c r="D545" t="n">
         <v>1.0</v>
@@ -7772,7 +7772,7 @@
         <v>2025.0</v>
       </c>
       <c r="C546" t="n" s="2">
-        <v>45903.0</v>
+        <v>45896.0</v>
       </c>
       <c r="D546" t="n">
         <v>1.0</v>
@@ -7786,7 +7786,7 @@
         <v>2025.0</v>
       </c>
       <c r="C547" t="n" s="2">
-        <v>45931.0</v>
+        <v>45903.0</v>
       </c>
       <c r="D547" t="n">
         <v>1.0</v>
@@ -7800,10 +7800,10 @@
         <v>2025.0</v>
       </c>
       <c r="C548" t="n" s="2">
-        <v>45938.0</v>
+        <v>45931.0</v>
       </c>
       <c r="D548" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="549">
@@ -7814,10 +7814,10 @@
         <v>2025.0</v>
       </c>
       <c r="C549" t="n" s="2">
-        <v>45945.0</v>
+        <v>45938.0</v>
       </c>
       <c r="D549" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="550">
@@ -7828,7 +7828,7 @@
         <v>2025.0</v>
       </c>
       <c r="C550" t="n" s="2">
-        <v>45966.0</v>
+        <v>45945.0</v>
       </c>
       <c r="D550" t="n">
         <v>2.0</v>
@@ -7842,10 +7842,10 @@
         <v>2025.0</v>
       </c>
       <c r="C551" t="n" s="2">
-        <v>45973.0</v>
+        <v>45966.0</v>
       </c>
       <c r="D551" t="n">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="552">
@@ -7856,10 +7856,10 @@
         <v>2025.0</v>
       </c>
       <c r="C552" t="n" s="2">
-        <v>45980.0</v>
+        <v>45973.0</v>
       </c>
       <c r="D552" t="n">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="553">
@@ -7870,10 +7870,10 @@
         <v>2025.0</v>
       </c>
       <c r="C553" t="n" s="2">
-        <v>45987.0</v>
+        <v>45980.0</v>
       </c>
       <c r="D553" t="n">
-        <v>20.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="554">
@@ -7884,10 +7884,10 @@
         <v>2025.0</v>
       </c>
       <c r="C554" t="n" s="2">
-        <v>45994.0</v>
+        <v>45987.0</v>
       </c>
       <c r="D554" t="n">
-        <v>5.0</v>
+        <v>20.0</v>
       </c>
     </row>
     <row r="555">
@@ -7898,10 +7898,10 @@
         <v>2025.0</v>
       </c>
       <c r="C555" t="n" s="2">
-        <v>46001.0</v>
+        <v>45994.0</v>
       </c>
       <c r="D555" t="n">
-        <v>8.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="556">
@@ -7912,10 +7912,10 @@
         <v>2025.0</v>
       </c>
       <c r="C556" t="n" s="2">
-        <v>46008.0</v>
+        <v>46001.0</v>
       </c>
       <c r="D556" t="n">
-        <v>24.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="557">
@@ -7926,10 +7926,10 @@
         <v>2025.0</v>
       </c>
       <c r="C557" t="n" s="2">
-        <v>46015.0</v>
+        <v>46008.0</v>
       </c>
       <c r="D557" t="n">
-        <v>13.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="558">
@@ -7940,10 +7940,10 @@
         <v>2025.0</v>
       </c>
       <c r="C558" t="n" s="2">
-        <v>46022.0</v>
+        <v>46015.0</v>
       </c>
       <c r="D558" t="n">
-        <v>8.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="559">
@@ -7954,10 +7954,10 @@
         <v>2025.0</v>
       </c>
       <c r="C559" t="n" s="2">
-        <v>46029.0</v>
+        <v>46022.0</v>
       </c>
       <c r="D559" t="n">
-        <v>3.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="560">
@@ -7965,13 +7965,13 @@
         <v>8</v>
       </c>
       <c r="B560" t="n">
-        <v>2026.0</v>
+        <v>2025.0</v>
       </c>
       <c r="C560" t="n" s="2">
-        <v>46030.0</v>
+        <v>46029.0</v>
       </c>
       <c r="D560" t="n">
-        <v>24.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="561">
@@ -7982,10 +7982,10 @@
         <v>2026.0</v>
       </c>
       <c r="C561" t="n" s="2">
-        <v>46037.0</v>
+        <v>46030.0</v>
       </c>
       <c r="D561" t="n">
-        <v>22.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="562">
@@ -7996,10 +7996,10 @@
         <v>2026.0</v>
       </c>
       <c r="C562" t="n" s="2">
-        <v>46044.0</v>
+        <v>46037.0</v>
       </c>
       <c r="D562" t="n">
-        <v>27.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="563">
@@ -8010,10 +8010,10 @@
         <v>2026.0</v>
       </c>
       <c r="C563" t="n" s="2">
-        <v>46051.0</v>
+        <v>46044.0</v>
       </c>
       <c r="D563" t="n">
-        <v>18.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="564">
@@ -8024,10 +8024,10 @@
         <v>2026.0</v>
       </c>
       <c r="C564" t="n" s="2">
-        <v>46058.0</v>
+        <v>46051.0</v>
       </c>
       <c r="D564" t="n">
-        <v>25.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="565">
@@ -8038,10 +8038,10 @@
         <v>2026.0</v>
       </c>
       <c r="C565" t="n" s="2">
-        <v>46065.0</v>
+        <v>46058.0</v>
       </c>
       <c r="D565" t="n">
-        <v>22.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="566">
@@ -8052,10 +8052,10 @@
         <v>2026.0</v>
       </c>
       <c r="C566" t="n" s="2">
-        <v>46072.0</v>
+        <v>46065.0</v>
       </c>
       <c r="D566" t="n">
-        <v>13.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="567">
@@ -8066,10 +8066,10 @@
         <v>2026.0</v>
       </c>
       <c r="C567" t="n" s="2">
-        <v>46079.0</v>
+        <v>46072.0</v>
       </c>
       <c r="D567" t="n">
-        <v>24.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="568">
@@ -8080,10 +8080,10 @@
         <v>2026.0</v>
       </c>
       <c r="C568" t="n" s="2">
-        <v>46086.0</v>
+        <v>46079.0</v>
       </c>
       <c r="D568" t="n">
-        <v>26.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="569">
@@ -8094,10 +8094,10 @@
         <v>2026.0</v>
       </c>
       <c r="C569" t="n" s="2">
-        <v>46093.0</v>
+        <v>46086.0</v>
       </c>
       <c r="D569" t="n">
-        <v>33.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="570">
@@ -8108,10 +8108,10 @@
         <v>2026.0</v>
       </c>
       <c r="C570" t="n" s="2">
-        <v>46100.0</v>
+        <v>46093.0</v>
       </c>
       <c r="D570" t="n">
-        <v>25.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="571">
@@ -8122,10 +8122,10 @@
         <v>2026.0</v>
       </c>
       <c r="C571" t="n" s="2">
-        <v>46107.0</v>
+        <v>46100.0</v>
       </c>
       <c r="D571" t="n">
-        <v>31.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="572">
@@ -8136,10 +8136,10 @@
         <v>2026.0</v>
       </c>
       <c r="C572" t="n" s="2">
-        <v>46114.0</v>
+        <v>46107.0</v>
       </c>
       <c r="D572" t="n">
-        <v>10.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="573">
@@ -8150,10 +8150,10 @@
         <v>2026.0</v>
       </c>
       <c r="C573" t="n" s="2">
-        <v>46121.0</v>
+        <v>46114.0</v>
       </c>
       <c r="D573" t="n">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="574">
@@ -8164,10 +8164,10 @@
         <v>2026.0</v>
       </c>
       <c r="C574" t="n" s="2">
-        <v>46128.0</v>
+        <v>46121.0</v>
       </c>
       <c r="D574" t="n">
-        <v>15.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="575">
@@ -8178,10 +8178,38 @@
         <v>2026.0</v>
       </c>
       <c r="C575" t="n" s="2">
+        <v>46128.0</v>
+      </c>
+      <c r="D575" t="n">
+        <v>15.0</v>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="s">
+        <v>8</v>
+      </c>
+      <c r="B576" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C576" t="n" s="2">
         <v>46135.0</v>
       </c>
-      <c r="D575" t="n">
+      <c r="D576" t="n">
         <v>23.0</v>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="s">
+        <v>8</v>
+      </c>
+      <c r="B577" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C577" t="n" s="2">
+        <v>46142.0</v>
+      </c>
+      <c r="D577" t="n">
+        <v>3.0</v>
       </c>
     </row>
   </sheetData>
@@ -8207,7 +8235,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="n">
-        <v>45.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="3">
@@ -8231,7 +8259,7 @@
         <v>13</v>
       </c>
       <c r="B5" t="n">
-        <v>2088.0</v>
+        <v>2090.0</v>
       </c>
     </row>
   </sheetData>
@@ -8296,7 +8324,7 @@
         <v>21</v>
       </c>
       <c r="C5" t="n">
-        <v>416.0</v>
+        <v>418.0</v>
       </c>
     </row>
     <row r="6">
@@ -8362,7 +8390,7 @@
         <v>19</v>
       </c>
       <c r="C11" t="n">
-        <v>31.0</v>
+        <v>34.0</v>
       </c>
     </row>
     <row r="12">

--- a/Download/Focus_Positivi_ZR.xlsx
+++ b/Download/Focus_Positivi_ZR.xlsx
@@ -1601,7 +1601,7 @@
         <v>46142.0</v>
       </c>
       <c r="D105" t="n">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="106">
@@ -4261,7 +4261,7 @@
         <v>46142.0</v>
       </c>
       <c r="D295" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="296">
@@ -8235,7 +8235,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="n">
-        <v>48.0</v>
+        <v>45.0</v>
       </c>
     </row>
     <row r="3">
@@ -8251,7 +8251,7 @@
         <v>12</v>
       </c>
       <c r="B4" t="n">
-        <v>1235.0</v>
+        <v>1241.0</v>
       </c>
     </row>
     <row r="5">
@@ -8259,7 +8259,7 @@
         <v>13</v>
       </c>
       <c r="B5" t="n">
-        <v>2090.0</v>
+        <v>2092.0</v>
       </c>
     </row>
   </sheetData>
@@ -8346,7 +8346,7 @@
         <v>19</v>
       </c>
       <c r="C7" t="n">
-        <v>158.0</v>
+        <v>159.0</v>
       </c>
     </row>
     <row r="8">
@@ -8390,7 +8390,7 @@
         <v>19</v>
       </c>
       <c r="C11" t="n">
-        <v>34.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="12">
@@ -8401,7 +8401,7 @@
         <v>21</v>
       </c>
       <c r="C12" t="n">
-        <v>65.0</v>
+        <v>68.0</v>
       </c>
     </row>
     <row r="13">
@@ -8423,7 +8423,7 @@
         <v>19</v>
       </c>
       <c r="C14" t="n">
-        <v>398.0</v>
+        <v>402.0</v>
       </c>
     </row>
     <row r="15">

--- a/Download/Focus_Positivi_ZR.xlsx
+++ b/Download/Focus_Positivi_ZR.xlsx
@@ -1601,7 +1601,7 @@
         <v>46142.0</v>
       </c>
       <c r="D105" t="n">
-        <v>5.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="106">
@@ -8209,7 +8209,7 @@
         <v>46142.0</v>
       </c>
       <c r="D577" t="n">
-        <v>3.0</v>
+        <v>20.0</v>
       </c>
     </row>
   </sheetData>
@@ -8243,7 +8243,7 @@
         <v>11</v>
       </c>
       <c r="B3" t="n">
-        <v>193.0</v>
+        <v>195.0</v>
       </c>
     </row>
     <row r="4">
@@ -8251,7 +8251,7 @@
         <v>12</v>
       </c>
       <c r="B4" t="n">
-        <v>1241.0</v>
+        <v>1251.0</v>
       </c>
     </row>
     <row r="5">
@@ -8259,7 +8259,7 @@
         <v>13</v>
       </c>
       <c r="B5" t="n">
-        <v>2092.0</v>
+        <v>2099.0</v>
       </c>
     </row>
   </sheetData>
@@ -8291,7 +8291,7 @@
         <v>21</v>
       </c>
       <c r="C2" t="n">
-        <v>192.0</v>
+        <v>194.0</v>
       </c>
     </row>
     <row r="3">
@@ -8302,7 +8302,7 @@
         <v>22</v>
       </c>
       <c r="C3" t="n">
-        <v>173.0</v>
+        <v>176.0</v>
       </c>
     </row>
     <row r="4">
@@ -8324,7 +8324,7 @@
         <v>21</v>
       </c>
       <c r="C5" t="n">
-        <v>418.0</v>
+        <v>419.0</v>
       </c>
     </row>
     <row r="6">
@@ -8335,7 +8335,7 @@
         <v>22</v>
       </c>
       <c r="C6" t="n">
-        <v>299.0</v>
+        <v>305.0</v>
       </c>
     </row>
     <row r="7">
@@ -8357,7 +8357,7 @@
         <v>21</v>
       </c>
       <c r="C8" t="n">
-        <v>346.0</v>
+        <v>347.0</v>
       </c>
     </row>
     <row r="9">
@@ -8423,7 +8423,7 @@
         <v>19</v>
       </c>
       <c r="C14" t="n">
-        <v>402.0</v>
+        <v>404.0</v>
       </c>
     </row>
     <row r="15">
@@ -8434,7 +8434,7 @@
         <v>21</v>
       </c>
       <c r="C15" t="n">
-        <v>365.0</v>
+        <v>367.0</v>
       </c>
     </row>
     <row r="16">
@@ -8445,7 +8445,7 @@
         <v>22</v>
       </c>
       <c r="C16" t="n">
-        <v>355.0</v>
+        <v>357.0</v>
       </c>
     </row>
     <row r="17">

--- a/Download/Focus_Positivi_ZR.xlsx
+++ b/Download/Focus_Positivi_ZR.xlsx
@@ -4261,7 +4261,7 @@
         <v>46142.0</v>
       </c>
       <c r="D295" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="296">
@@ -8251,7 +8251,7 @@
         <v>12</v>
       </c>
       <c r="B4" t="n">
-        <v>1251.0</v>
+        <v>1252.0</v>
       </c>
     </row>
     <row r="5">
@@ -8445,7 +8445,7 @@
         <v>22</v>
       </c>
       <c r="C16" t="n">
-        <v>357.0</v>
+        <v>358.0</v>
       </c>
     </row>
     <row r="17">

--- a/Download/Focus_Positivi_ZR.xlsx
+++ b/Download/Focus_Positivi_ZR.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="621" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="623" uniqueCount="23">
   <si>
     <t>NOME_REGIONE</t>
   </si>
@@ -1601,21 +1601,21 @@
         <v>46142.0</v>
       </c>
       <c r="D105" t="n">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B106" t="n">
-        <v>2021.0</v>
+        <v>2026.0</v>
       </c>
       <c r="C106" t="n" s="2">
-        <v>44561.0</v>
+        <v>46149.0</v>
       </c>
       <c r="D106" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="107">
@@ -1623,13 +1623,13 @@
         <v>5</v>
       </c>
       <c r="B107" t="n">
-        <v>2022.0</v>
+        <v>2021.0</v>
       </c>
       <c r="C107" t="n" s="2">
-        <v>44576.0</v>
+        <v>44561.0</v>
       </c>
       <c r="D107" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="108">
@@ -1640,10 +1640,10 @@
         <v>2022.0</v>
       </c>
       <c r="C108" t="n" s="2">
-        <v>44583.0</v>
+        <v>44576.0</v>
       </c>
       <c r="D108" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="109">
@@ -1654,10 +1654,10 @@
         <v>2022.0</v>
       </c>
       <c r="C109" t="n" s="2">
-        <v>44590.0</v>
+        <v>44583.0</v>
       </c>
       <c r="D109" t="n">
-        <v>7.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="110">
@@ -1668,10 +1668,10 @@
         <v>2022.0</v>
       </c>
       <c r="C110" t="n" s="2">
-        <v>44597.0</v>
+        <v>44590.0</v>
       </c>
       <c r="D110" t="n">
-        <v>3.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="111">
@@ -1682,10 +1682,10 @@
         <v>2022.0</v>
       </c>
       <c r="C111" t="n" s="2">
-        <v>44604.0</v>
+        <v>44597.0</v>
       </c>
       <c r="D111" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="112">
@@ -1696,10 +1696,10 @@
         <v>2022.0</v>
       </c>
       <c r="C112" t="n" s="2">
-        <v>44611.0</v>
+        <v>44604.0</v>
       </c>
       <c r="D112" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="113">
@@ -1710,7 +1710,7 @@
         <v>2022.0</v>
       </c>
       <c r="C113" t="n" s="2">
-        <v>44618.0</v>
+        <v>44611.0</v>
       </c>
       <c r="D113" t="n">
         <v>1.0</v>
@@ -1724,10 +1724,10 @@
         <v>2022.0</v>
       </c>
       <c r="C114" t="n" s="2">
-        <v>44625.0</v>
+        <v>44618.0</v>
       </c>
       <c r="D114" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="115">
@@ -1738,10 +1738,10 @@
         <v>2022.0</v>
       </c>
       <c r="C115" t="n" s="2">
-        <v>44632.0</v>
+        <v>44625.0</v>
       </c>
       <c r="D115" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="116">
@@ -1752,10 +1752,10 @@
         <v>2022.0</v>
       </c>
       <c r="C116" t="n" s="2">
-        <v>44639.0</v>
+        <v>44632.0</v>
       </c>
       <c r="D116" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="117">
@@ -1766,7 +1766,7 @@
         <v>2022.0</v>
       </c>
       <c r="C117" t="n" s="2">
-        <v>44646.0</v>
+        <v>44639.0</v>
       </c>
       <c r="D117" t="n">
         <v>2.0</v>
@@ -1780,7 +1780,7 @@
         <v>2022.0</v>
       </c>
       <c r="C118" t="n" s="2">
-        <v>44653.0</v>
+        <v>44646.0</v>
       </c>
       <c r="D118" t="n">
         <v>2.0</v>
@@ -1794,10 +1794,10 @@
         <v>2022.0</v>
       </c>
       <c r="C119" t="n" s="2">
-        <v>44660.0</v>
+        <v>44653.0</v>
       </c>
       <c r="D119" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="120">
@@ -1808,10 +1808,10 @@
         <v>2022.0</v>
       </c>
       <c r="C120" t="n" s="2">
-        <v>44667.0</v>
+        <v>44660.0</v>
       </c>
       <c r="D120" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="121">
@@ -1822,7 +1822,7 @@
         <v>2022.0</v>
       </c>
       <c r="C121" t="n" s="2">
-        <v>44674.0</v>
+        <v>44667.0</v>
       </c>
       <c r="D121" t="n">
         <v>3.0</v>
@@ -1836,10 +1836,10 @@
         <v>2022.0</v>
       </c>
       <c r="C122" t="n" s="2">
-        <v>44681.0</v>
+        <v>44674.0</v>
       </c>
       <c r="D122" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="123">
@@ -1850,10 +1850,10 @@
         <v>2022.0</v>
       </c>
       <c r="C123" t="n" s="2">
-        <v>44688.0</v>
+        <v>44681.0</v>
       </c>
       <c r="D123" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="124">
@@ -1864,7 +1864,7 @@
         <v>2022.0</v>
       </c>
       <c r="C124" t="n" s="2">
-        <v>44695.0</v>
+        <v>44688.0</v>
       </c>
       <c r="D124" t="n">
         <v>3.0</v>
@@ -1878,10 +1878,10 @@
         <v>2022.0</v>
       </c>
       <c r="C125" t="n" s="2">
-        <v>44702.0</v>
+        <v>44695.0</v>
       </c>
       <c r="D125" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="126">
@@ -1892,10 +1892,10 @@
         <v>2022.0</v>
       </c>
       <c r="C126" t="n" s="2">
-        <v>44709.0</v>
+        <v>44702.0</v>
       </c>
       <c r="D126" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="127">
@@ -1906,10 +1906,10 @@
         <v>2022.0</v>
       </c>
       <c r="C127" t="n" s="2">
-        <v>44716.0</v>
+        <v>44709.0</v>
       </c>
       <c r="D127" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="128">
@@ -1920,7 +1920,7 @@
         <v>2022.0</v>
       </c>
       <c r="C128" t="n" s="2">
-        <v>44723.0</v>
+        <v>44716.0</v>
       </c>
       <c r="D128" t="n">
         <v>1.0</v>
@@ -1934,7 +1934,7 @@
         <v>2022.0</v>
       </c>
       <c r="C129" t="n" s="2">
-        <v>44730.0</v>
+        <v>44723.0</v>
       </c>
       <c r="D129" t="n">
         <v>1.0</v>
@@ -1948,7 +1948,7 @@
         <v>2022.0</v>
       </c>
       <c r="C130" t="n" s="2">
-        <v>44737.0</v>
+        <v>44730.0</v>
       </c>
       <c r="D130" t="n">
         <v>1.0</v>
@@ -1962,7 +1962,7 @@
         <v>2022.0</v>
       </c>
       <c r="C131" t="n" s="2">
-        <v>44744.0</v>
+        <v>44737.0</v>
       </c>
       <c r="D131" t="n">
         <v>1.0</v>
@@ -1976,7 +1976,7 @@
         <v>2022.0</v>
       </c>
       <c r="C132" t="n" s="2">
-        <v>44751.0</v>
+        <v>44744.0</v>
       </c>
       <c r="D132" t="n">
         <v>1.0</v>
@@ -1990,7 +1990,7 @@
         <v>2022.0</v>
       </c>
       <c r="C133" t="n" s="2">
-        <v>44758.0</v>
+        <v>44751.0</v>
       </c>
       <c r="D133" t="n">
         <v>1.0</v>
@@ -2004,7 +2004,7 @@
         <v>2022.0</v>
       </c>
       <c r="C134" t="n" s="2">
-        <v>44772.0</v>
+        <v>44758.0</v>
       </c>
       <c r="D134" t="n">
         <v>1.0</v>
@@ -2018,7 +2018,7 @@
         <v>2022.0</v>
       </c>
       <c r="C135" t="n" s="2">
-        <v>44793.0</v>
+        <v>44772.0</v>
       </c>
       <c r="D135" t="n">
         <v>1.0</v>
@@ -2032,7 +2032,7 @@
         <v>2022.0</v>
       </c>
       <c r="C136" t="n" s="2">
-        <v>44800.0</v>
+        <v>44793.0</v>
       </c>
       <c r="D136" t="n">
         <v>1.0</v>
@@ -2046,7 +2046,7 @@
         <v>2022.0</v>
       </c>
       <c r="C137" t="n" s="2">
-        <v>44828.0</v>
+        <v>44800.0</v>
       </c>
       <c r="D137" t="n">
         <v>1.0</v>
@@ -2060,7 +2060,7 @@
         <v>2022.0</v>
       </c>
       <c r="C138" t="n" s="2">
-        <v>44849.0</v>
+        <v>44828.0</v>
       </c>
       <c r="D138" t="n">
         <v>1.0</v>
@@ -2074,7 +2074,7 @@
         <v>2022.0</v>
       </c>
       <c r="C139" t="n" s="2">
-        <v>44856.0</v>
+        <v>44849.0</v>
       </c>
       <c r="D139" t="n">
         <v>1.0</v>
@@ -2088,7 +2088,7 @@
         <v>2022.0</v>
       </c>
       <c r="C140" t="n" s="2">
-        <v>44863.0</v>
+        <v>44856.0</v>
       </c>
       <c r="D140" t="n">
         <v>1.0</v>
@@ -2102,10 +2102,10 @@
         <v>2022.0</v>
       </c>
       <c r="C141" t="n" s="2">
-        <v>44884.0</v>
+        <v>44863.0</v>
       </c>
       <c r="D141" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="142">
@@ -2116,10 +2116,10 @@
         <v>2022.0</v>
       </c>
       <c r="C142" t="n" s="2">
-        <v>44891.0</v>
+        <v>44884.0</v>
       </c>
       <c r="D142" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="143">
@@ -2130,7 +2130,7 @@
         <v>2022.0</v>
       </c>
       <c r="C143" t="n" s="2">
-        <v>44905.0</v>
+        <v>44891.0</v>
       </c>
       <c r="D143" t="n">
         <v>1.0</v>
@@ -2144,7 +2144,7 @@
         <v>2022.0</v>
       </c>
       <c r="C144" t="n" s="2">
-        <v>44912.0</v>
+        <v>44905.0</v>
       </c>
       <c r="D144" t="n">
         <v>1.0</v>
@@ -2158,10 +2158,10 @@
         <v>2022.0</v>
       </c>
       <c r="C145" t="n" s="2">
-        <v>44919.0</v>
+        <v>44912.0</v>
       </c>
       <c r="D145" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="146">
@@ -2169,13 +2169,13 @@
         <v>5</v>
       </c>
       <c r="B146" t="n">
-        <v>2023.0</v>
+        <v>2022.0</v>
       </c>
       <c r="C146" t="n" s="2">
-        <v>44934.0</v>
+        <v>44919.0</v>
       </c>
       <c r="D146" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="147">
@@ -2186,10 +2186,10 @@
         <v>2023.0</v>
       </c>
       <c r="C147" t="n" s="2">
-        <v>44941.0</v>
+        <v>44934.0</v>
       </c>
       <c r="D147" t="n">
-        <v>8.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="148">
@@ -2200,10 +2200,10 @@
         <v>2023.0</v>
       </c>
       <c r="C148" t="n" s="2">
-        <v>44948.0</v>
+        <v>44941.0</v>
       </c>
       <c r="D148" t="n">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="149">
@@ -2214,10 +2214,10 @@
         <v>2023.0</v>
       </c>
       <c r="C149" t="n" s="2">
-        <v>44955.0</v>
+        <v>44948.0</v>
       </c>
       <c r="D149" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="150">
@@ -2228,10 +2228,10 @@
         <v>2023.0</v>
       </c>
       <c r="C150" t="n" s="2">
-        <v>44962.0</v>
+        <v>44955.0</v>
       </c>
       <c r="D150" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="151">
@@ -2242,7 +2242,7 @@
         <v>2023.0</v>
       </c>
       <c r="C151" t="n" s="2">
-        <v>44969.0</v>
+        <v>44962.0</v>
       </c>
       <c r="D151" t="n">
         <v>4.0</v>
@@ -2256,10 +2256,10 @@
         <v>2023.0</v>
       </c>
       <c r="C152" t="n" s="2">
-        <v>44976.0</v>
+        <v>44969.0</v>
       </c>
       <c r="D152" t="n">
-        <v>17.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="153">
@@ -2270,10 +2270,10 @@
         <v>2023.0</v>
       </c>
       <c r="C153" t="n" s="2">
-        <v>44983.0</v>
+        <v>44976.0</v>
       </c>
       <c r="D153" t="n">
-        <v>11.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="154">
@@ -2284,10 +2284,10 @@
         <v>2023.0</v>
       </c>
       <c r="C154" t="n" s="2">
-        <v>44990.0</v>
+        <v>44983.0</v>
       </c>
       <c r="D154" t="n">
-        <v>5.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="155">
@@ -2298,10 +2298,10 @@
         <v>2023.0</v>
       </c>
       <c r="C155" t="n" s="2">
-        <v>44997.0</v>
+        <v>44990.0</v>
       </c>
       <c r="D155" t="n">
-        <v>22.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="156">
@@ -2312,10 +2312,10 @@
         <v>2023.0</v>
       </c>
       <c r="C156" t="n" s="2">
-        <v>45004.0</v>
+        <v>44997.0</v>
       </c>
       <c r="D156" t="n">
-        <v>8.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="157">
@@ -2326,10 +2326,10 @@
         <v>2023.0</v>
       </c>
       <c r="C157" t="n" s="2">
-        <v>45011.0</v>
+        <v>45004.0</v>
       </c>
       <c r="D157" t="n">
-        <v>17.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="158">
@@ -2340,10 +2340,10 @@
         <v>2023.0</v>
       </c>
       <c r="C158" t="n" s="2">
-        <v>45018.0</v>
+        <v>45011.0</v>
       </c>
       <c r="D158" t="n">
-        <v>10.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="159">
@@ -2354,10 +2354,10 @@
         <v>2023.0</v>
       </c>
       <c r="C159" t="n" s="2">
-        <v>45025.0</v>
+        <v>45018.0</v>
       </c>
       <c r="D159" t="n">
-        <v>13.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="160">
@@ -2368,10 +2368,10 @@
         <v>2023.0</v>
       </c>
       <c r="C160" t="n" s="2">
-        <v>45032.0</v>
+        <v>45025.0</v>
       </c>
       <c r="D160" t="n">
-        <v>10.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="161">
@@ -2382,10 +2382,10 @@
         <v>2023.0</v>
       </c>
       <c r="C161" t="n" s="2">
-        <v>45039.0</v>
+        <v>45032.0</v>
       </c>
       <c r="D161" t="n">
-        <v>22.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="162">
@@ -2396,10 +2396,10 @@
         <v>2023.0</v>
       </c>
       <c r="C162" t="n" s="2">
-        <v>45046.0</v>
+        <v>45039.0</v>
       </c>
       <c r="D162" t="n">
-        <v>23.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="163">
@@ -2410,10 +2410,10 @@
         <v>2023.0</v>
       </c>
       <c r="C163" t="n" s="2">
-        <v>45053.0</v>
+        <v>45046.0</v>
       </c>
       <c r="D163" t="n">
-        <v>16.0</v>
+        <v>23.0</v>
       </c>
     </row>
     <row r="164">
@@ -2424,10 +2424,10 @@
         <v>2023.0</v>
       </c>
       <c r="C164" t="n" s="2">
-        <v>45060.0</v>
+        <v>45053.0</v>
       </c>
       <c r="D164" t="n">
-        <v>13.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="165">
@@ -2438,10 +2438,10 @@
         <v>2023.0</v>
       </c>
       <c r="C165" t="n" s="2">
-        <v>45067.0</v>
+        <v>45060.0</v>
       </c>
       <c r="D165" t="n">
-        <v>9.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="166">
@@ -2452,10 +2452,10 @@
         <v>2023.0</v>
       </c>
       <c r="C166" t="n" s="2">
-        <v>45074.0</v>
+        <v>45067.0</v>
       </c>
       <c r="D166" t="n">
-        <v>6.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="167">
@@ -2466,10 +2466,10 @@
         <v>2023.0</v>
       </c>
       <c r="C167" t="n" s="2">
-        <v>45081.0</v>
+        <v>45074.0</v>
       </c>
       <c r="D167" t="n">
-        <v>16.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="168">
@@ -2480,10 +2480,10 @@
         <v>2023.0</v>
       </c>
       <c r="C168" t="n" s="2">
-        <v>45088.0</v>
+        <v>45081.0</v>
       </c>
       <c r="D168" t="n">
-        <v>8.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="169">
@@ -2494,10 +2494,10 @@
         <v>2023.0</v>
       </c>
       <c r="C169" t="n" s="2">
-        <v>45095.0</v>
+        <v>45088.0</v>
       </c>
       <c r="D169" t="n">
-        <v>16.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="170">
@@ -2508,10 +2508,10 @@
         <v>2023.0</v>
       </c>
       <c r="C170" t="n" s="2">
-        <v>45102.0</v>
+        <v>45095.0</v>
       </c>
       <c r="D170" t="n">
-        <v>17.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="171">
@@ -2522,10 +2522,10 @@
         <v>2023.0</v>
       </c>
       <c r="C171" t="n" s="2">
-        <v>45109.0</v>
+        <v>45102.0</v>
       </c>
       <c r="D171" t="n">
-        <v>14.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="172">
@@ -2536,10 +2536,10 @@
         <v>2023.0</v>
       </c>
       <c r="C172" t="n" s="2">
-        <v>45116.0</v>
+        <v>45109.0</v>
       </c>
       <c r="D172" t="n">
-        <v>13.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="173">
@@ -2550,10 +2550,10 @@
         <v>2023.0</v>
       </c>
       <c r="C173" t="n" s="2">
-        <v>45123.0</v>
+        <v>45116.0</v>
       </c>
       <c r="D173" t="n">
-        <v>5.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="174">
@@ -2564,10 +2564,10 @@
         <v>2023.0</v>
       </c>
       <c r="C174" t="n" s="2">
-        <v>45130.0</v>
+        <v>45123.0</v>
       </c>
       <c r="D174" t="n">
-        <v>8.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="175">
@@ -2578,10 +2578,10 @@
         <v>2023.0</v>
       </c>
       <c r="C175" t="n" s="2">
-        <v>45137.0</v>
+        <v>45130.0</v>
       </c>
       <c r="D175" t="n">
-        <v>4.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="176">
@@ -2592,10 +2592,10 @@
         <v>2023.0</v>
       </c>
       <c r="C176" t="n" s="2">
-        <v>45144.0</v>
+        <v>45137.0</v>
       </c>
       <c r="D176" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="177">
@@ -2606,7 +2606,7 @@
         <v>2023.0</v>
       </c>
       <c r="C177" t="n" s="2">
-        <v>45151.0</v>
+        <v>45144.0</v>
       </c>
       <c r="D177" t="n">
         <v>2.0</v>
@@ -2620,10 +2620,10 @@
         <v>2023.0</v>
       </c>
       <c r="C178" t="n" s="2">
-        <v>45158.0</v>
+        <v>45151.0</v>
       </c>
       <c r="D178" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="179">
@@ -2634,7 +2634,7 @@
         <v>2023.0</v>
       </c>
       <c r="C179" t="n" s="2">
-        <v>45165.0</v>
+        <v>45158.0</v>
       </c>
       <c r="D179" t="n">
         <v>5.0</v>
@@ -2648,10 +2648,10 @@
         <v>2023.0</v>
       </c>
       <c r="C180" t="n" s="2">
-        <v>45172.0</v>
+        <v>45165.0</v>
       </c>
       <c r="D180" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="181">
@@ -2662,10 +2662,10 @@
         <v>2023.0</v>
       </c>
       <c r="C181" t="n" s="2">
-        <v>45179.0</v>
+        <v>45172.0</v>
       </c>
       <c r="D181" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="182">
@@ -2676,10 +2676,10 @@
         <v>2023.0</v>
       </c>
       <c r="C182" t="n" s="2">
-        <v>45186.0</v>
+        <v>45179.0</v>
       </c>
       <c r="D182" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="183">
@@ -2690,7 +2690,7 @@
         <v>2023.0</v>
       </c>
       <c r="C183" t="n" s="2">
-        <v>45193.0</v>
+        <v>45186.0</v>
       </c>
       <c r="D183" t="n">
         <v>1.0</v>
@@ -2704,10 +2704,10 @@
         <v>2023.0</v>
       </c>
       <c r="C184" t="n" s="2">
-        <v>45200.0</v>
+        <v>45193.0</v>
       </c>
       <c r="D184" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="185">
@@ -2718,10 +2718,10 @@
         <v>2023.0</v>
       </c>
       <c r="C185" t="n" s="2">
-        <v>45207.0</v>
+        <v>45200.0</v>
       </c>
       <c r="D185" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="186">
@@ -2732,10 +2732,10 @@
         <v>2023.0</v>
       </c>
       <c r="C186" t="n" s="2">
-        <v>45214.0</v>
+        <v>45207.0</v>
       </c>
       <c r="D186" t="n">
-        <v>8.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="187">
@@ -2746,7 +2746,7 @@
         <v>2023.0</v>
       </c>
       <c r="C187" t="n" s="2">
-        <v>45221.0</v>
+        <v>45214.0</v>
       </c>
       <c r="D187" t="n">
         <v>8.0</v>
@@ -2760,10 +2760,10 @@
         <v>2023.0</v>
       </c>
       <c r="C188" t="n" s="2">
-        <v>45228.0</v>
+        <v>45221.0</v>
       </c>
       <c r="D188" t="n">
-        <v>17.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="189">
@@ -2774,10 +2774,10 @@
         <v>2023.0</v>
       </c>
       <c r="C189" t="n" s="2">
-        <v>45235.0</v>
+        <v>45228.0</v>
       </c>
       <c r="D189" t="n">
-        <v>9.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="190">
@@ -2788,7 +2788,7 @@
         <v>2023.0</v>
       </c>
       <c r="C190" t="n" s="2">
-        <v>45242.0</v>
+        <v>45235.0</v>
       </c>
       <c r="D190" t="n">
         <v>9.0</v>
@@ -2802,10 +2802,10 @@
         <v>2023.0</v>
       </c>
       <c r="C191" t="n" s="2">
-        <v>45249.0</v>
+        <v>45242.0</v>
       </c>
       <c r="D191" t="n">
-        <v>14.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="192">
@@ -2816,10 +2816,10 @@
         <v>2023.0</v>
       </c>
       <c r="C192" t="n" s="2">
-        <v>45256.0</v>
+        <v>45249.0</v>
       </c>
       <c r="D192" t="n">
-        <v>17.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="193">
@@ -2830,10 +2830,10 @@
         <v>2023.0</v>
       </c>
       <c r="C193" t="n" s="2">
-        <v>45263.0</v>
+        <v>45256.0</v>
       </c>
       <c r="D193" t="n">
-        <v>14.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="194">
@@ -2844,10 +2844,10 @@
         <v>2023.0</v>
       </c>
       <c r="C194" t="n" s="2">
-        <v>45270.0</v>
+        <v>45263.0</v>
       </c>
       <c r="D194" t="n">
-        <v>26.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="195">
@@ -2858,10 +2858,10 @@
         <v>2023.0</v>
       </c>
       <c r="C195" t="n" s="2">
-        <v>45277.0</v>
+        <v>45270.0</v>
       </c>
       <c r="D195" t="n">
-        <v>19.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="196">
@@ -2872,10 +2872,10 @@
         <v>2023.0</v>
       </c>
       <c r="C196" t="n" s="2">
-        <v>45284.0</v>
+        <v>45277.0</v>
       </c>
       <c r="D196" t="n">
-        <v>21.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="197">
@@ -2886,10 +2886,10 @@
         <v>2023.0</v>
       </c>
       <c r="C197" t="n" s="2">
-        <v>45291.0</v>
+        <v>45284.0</v>
       </c>
       <c r="D197" t="n">
-        <v>9.0</v>
+        <v>21.0</v>
       </c>
     </row>
     <row r="198">
@@ -2897,13 +2897,13 @@
         <v>5</v>
       </c>
       <c r="B198" t="n">
-        <v>2024.0</v>
+        <v>2023.0</v>
       </c>
       <c r="C198" t="n" s="2">
-        <v>45299.0</v>
+        <v>45291.0</v>
       </c>
       <c r="D198" t="n">
-        <v>26.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="199">
@@ -2914,10 +2914,10 @@
         <v>2024.0</v>
       </c>
       <c r="C199" t="n" s="2">
-        <v>45306.0</v>
+        <v>45299.0</v>
       </c>
       <c r="D199" t="n">
-        <v>14.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="200">
@@ -2928,10 +2928,10 @@
         <v>2024.0</v>
       </c>
       <c r="C200" t="n" s="2">
-        <v>45313.0</v>
+        <v>45306.0</v>
       </c>
       <c r="D200" t="n">
-        <v>15.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="201">
@@ -2942,10 +2942,10 @@
         <v>2024.0</v>
       </c>
       <c r="C201" t="n" s="2">
-        <v>45320.0</v>
+        <v>45313.0</v>
       </c>
       <c r="D201" t="n">
-        <v>18.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="202">
@@ -2956,10 +2956,10 @@
         <v>2024.0</v>
       </c>
       <c r="C202" t="n" s="2">
-        <v>45327.0</v>
+        <v>45320.0</v>
       </c>
       <c r="D202" t="n">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="203">
@@ -2970,10 +2970,10 @@
         <v>2024.0</v>
       </c>
       <c r="C203" t="n" s="2">
-        <v>45334.0</v>
+        <v>45327.0</v>
       </c>
       <c r="D203" t="n">
-        <v>13.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="204">
@@ -2984,10 +2984,10 @@
         <v>2024.0</v>
       </c>
       <c r="C204" t="n" s="2">
-        <v>45341.0</v>
+        <v>45334.0</v>
       </c>
       <c r="D204" t="n">
-        <v>11.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="205">
@@ -2998,10 +2998,10 @@
         <v>2024.0</v>
       </c>
       <c r="C205" t="n" s="2">
-        <v>45348.0</v>
+        <v>45341.0</v>
       </c>
       <c r="D205" t="n">
-        <v>8.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="206">
@@ -3012,10 +3012,10 @@
         <v>2024.0</v>
       </c>
       <c r="C206" t="n" s="2">
-        <v>45355.0</v>
+        <v>45348.0</v>
       </c>
       <c r="D206" t="n">
-        <v>1.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="207">
@@ -3026,10 +3026,10 @@
         <v>2024.0</v>
       </c>
       <c r="C207" t="n" s="2">
-        <v>45362.0</v>
+        <v>45355.0</v>
       </c>
       <c r="D207" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="208">
@@ -3040,10 +3040,10 @@
         <v>2024.0</v>
       </c>
       <c r="C208" t="n" s="2">
-        <v>45369.0</v>
+        <v>45362.0</v>
       </c>
       <c r="D208" t="n">
-        <v>8.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="209">
@@ -3054,10 +3054,10 @@
         <v>2024.0</v>
       </c>
       <c r="C209" t="n" s="2">
-        <v>45376.0</v>
+        <v>45369.0</v>
       </c>
       <c r="D209" t="n">
-        <v>9.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="210">
@@ -3068,10 +3068,10 @@
         <v>2024.0</v>
       </c>
       <c r="C210" t="n" s="2">
-        <v>45383.0</v>
+        <v>45376.0</v>
       </c>
       <c r="D210" t="n">
-        <v>5.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="211">
@@ -3082,10 +3082,10 @@
         <v>2024.0</v>
       </c>
       <c r="C211" t="n" s="2">
-        <v>45390.0</v>
+        <v>45383.0</v>
       </c>
       <c r="D211" t="n">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="212">
@@ -3096,10 +3096,10 @@
         <v>2024.0</v>
       </c>
       <c r="C212" t="n" s="2">
-        <v>45397.0</v>
+        <v>45390.0</v>
       </c>
       <c r="D212" t="n">
-        <v>13.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="213">
@@ -3110,10 +3110,10 @@
         <v>2024.0</v>
       </c>
       <c r="C213" t="n" s="2">
-        <v>45404.0</v>
+        <v>45397.0</v>
       </c>
       <c r="D213" t="n">
-        <v>24.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="214">
@@ -3124,10 +3124,10 @@
         <v>2024.0</v>
       </c>
       <c r="C214" t="n" s="2">
-        <v>45411.0</v>
+        <v>45404.0</v>
       </c>
       <c r="D214" t="n">
-        <v>17.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="215">
@@ -3138,10 +3138,10 @@
         <v>2024.0</v>
       </c>
       <c r="C215" t="n" s="2">
-        <v>45418.0</v>
+        <v>45411.0</v>
       </c>
       <c r="D215" t="n">
-        <v>3.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="216">
@@ -3152,10 +3152,10 @@
         <v>2024.0</v>
       </c>
       <c r="C216" t="n" s="2">
-        <v>45425.0</v>
+        <v>45418.0</v>
       </c>
       <c r="D216" t="n">
-        <v>16.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="217">
@@ -3166,10 +3166,10 @@
         <v>2024.0</v>
       </c>
       <c r="C217" t="n" s="2">
-        <v>45432.0</v>
+        <v>45425.0</v>
       </c>
       <c r="D217" t="n">
-        <v>19.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="218">
@@ -3180,10 +3180,10 @@
         <v>2024.0</v>
       </c>
       <c r="C218" t="n" s="2">
-        <v>45439.0</v>
+        <v>45432.0</v>
       </c>
       <c r="D218" t="n">
-        <v>30.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="219">
@@ -3194,10 +3194,10 @@
         <v>2024.0</v>
       </c>
       <c r="C219" t="n" s="2">
-        <v>45446.0</v>
+        <v>45439.0</v>
       </c>
       <c r="D219" t="n">
-        <v>28.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="220">
@@ -3208,10 +3208,10 @@
         <v>2024.0</v>
       </c>
       <c r="C220" t="n" s="2">
-        <v>45453.0</v>
+        <v>45446.0</v>
       </c>
       <c r="D220" t="n">
-        <v>19.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="221">
@@ -3222,10 +3222,10 @@
         <v>2024.0</v>
       </c>
       <c r="C221" t="n" s="2">
-        <v>45460.0</v>
+        <v>45453.0</v>
       </c>
       <c r="D221" t="n">
-        <v>26.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="222">
@@ -3236,10 +3236,10 @@
         <v>2024.0</v>
       </c>
       <c r="C222" t="n" s="2">
-        <v>45467.0</v>
+        <v>45460.0</v>
       </c>
       <c r="D222" t="n">
-        <v>8.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="223">
@@ -3250,10 +3250,10 @@
         <v>2024.0</v>
       </c>
       <c r="C223" t="n" s="2">
-        <v>45474.0</v>
+        <v>45467.0</v>
       </c>
       <c r="D223" t="n">
-        <v>12.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="224">
@@ -3264,7 +3264,7 @@
         <v>2024.0</v>
       </c>
       <c r="C224" t="n" s="2">
-        <v>45481.0</v>
+        <v>45474.0</v>
       </c>
       <c r="D224" t="n">
         <v>12.0</v>
@@ -3278,10 +3278,10 @@
         <v>2024.0</v>
       </c>
       <c r="C225" t="n" s="2">
-        <v>45488.0</v>
+        <v>45481.0</v>
       </c>
       <c r="D225" t="n">
-        <v>4.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="226">
@@ -3292,10 +3292,10 @@
         <v>2024.0</v>
       </c>
       <c r="C226" t="n" s="2">
-        <v>45495.0</v>
+        <v>45488.0</v>
       </c>
       <c r="D226" t="n">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="227">
@@ -3306,10 +3306,10 @@
         <v>2024.0</v>
       </c>
       <c r="C227" t="n" s="2">
-        <v>45502.0</v>
+        <v>45495.0</v>
       </c>
       <c r="D227" t="n">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="228">
@@ -3320,10 +3320,10 @@
         <v>2024.0</v>
       </c>
       <c r="C228" t="n" s="2">
-        <v>45509.0</v>
+        <v>45502.0</v>
       </c>
       <c r="D228" t="n">
-        <v>2.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="229">
@@ -3334,10 +3334,10 @@
         <v>2024.0</v>
       </c>
       <c r="C229" t="n" s="2">
-        <v>45516.0</v>
+        <v>45509.0</v>
       </c>
       <c r="D229" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="230">
@@ -3348,7 +3348,7 @@
         <v>2024.0</v>
       </c>
       <c r="C230" t="n" s="2">
-        <v>45523.0</v>
+        <v>45516.0</v>
       </c>
       <c r="D230" t="n">
         <v>4.0</v>
@@ -3362,7 +3362,7 @@
         <v>2024.0</v>
       </c>
       <c r="C231" t="n" s="2">
-        <v>45530.0</v>
+        <v>45523.0</v>
       </c>
       <c r="D231" t="n">
         <v>4.0</v>
@@ -3376,7 +3376,7 @@
         <v>2024.0</v>
       </c>
       <c r="C232" t="n" s="2">
-        <v>45537.0</v>
+        <v>45530.0</v>
       </c>
       <c r="D232" t="n">
         <v>4.0</v>
@@ -3390,10 +3390,10 @@
         <v>2024.0</v>
       </c>
       <c r="C233" t="n" s="2">
-        <v>45544.0</v>
+        <v>45537.0</v>
       </c>
       <c r="D233" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="234">
@@ -3404,10 +3404,10 @@
         <v>2024.0</v>
       </c>
       <c r="C234" t="n" s="2">
-        <v>45551.0</v>
+        <v>45544.0</v>
       </c>
       <c r="D234" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="235">
@@ -3418,10 +3418,10 @@
         <v>2024.0</v>
       </c>
       <c r="C235" t="n" s="2">
-        <v>45558.0</v>
+        <v>45551.0</v>
       </c>
       <c r="D235" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="236">
@@ -3432,10 +3432,10 @@
         <v>2024.0</v>
       </c>
       <c r="C236" t="n" s="2">
-        <v>45600.0</v>
+        <v>45558.0</v>
       </c>
       <c r="D236" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="237">
@@ -3446,10 +3446,10 @@
         <v>2024.0</v>
       </c>
       <c r="C237" t="n" s="2">
-        <v>45607.0</v>
+        <v>45600.0</v>
       </c>
       <c r="D237" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="238">
@@ -3460,10 +3460,10 @@
         <v>2024.0</v>
       </c>
       <c r="C238" t="n" s="2">
-        <v>45628.0</v>
+        <v>45607.0</v>
       </c>
       <c r="D238" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="239">
@@ -3474,10 +3474,10 @@
         <v>2024.0</v>
       </c>
       <c r="C239" t="n" s="2">
-        <v>45635.0</v>
+        <v>45628.0</v>
       </c>
       <c r="D239" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="240">
@@ -3488,7 +3488,7 @@
         <v>2024.0</v>
       </c>
       <c r="C240" t="n" s="2">
-        <v>45642.0</v>
+        <v>45635.0</v>
       </c>
       <c r="D240" t="n">
         <v>3.0</v>
@@ -3502,10 +3502,10 @@
         <v>2024.0</v>
       </c>
       <c r="C241" t="n" s="2">
-        <v>45649.0</v>
+        <v>45642.0</v>
       </c>
       <c r="D241" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="242">
@@ -3516,7 +3516,7 @@
         <v>2024.0</v>
       </c>
       <c r="C242" t="n" s="2">
-        <v>45656.0</v>
+        <v>45649.0</v>
       </c>
       <c r="D242" t="n">
         <v>1.0</v>
@@ -3527,13 +3527,13 @@
         <v>5</v>
       </c>
       <c r="B243" t="n">
-        <v>2025.0</v>
+        <v>2024.0</v>
       </c>
       <c r="C243" t="n" s="2">
-        <v>45672.0</v>
+        <v>45656.0</v>
       </c>
       <c r="D243" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="244">
@@ -3544,10 +3544,10 @@
         <v>2025.0</v>
       </c>
       <c r="C244" t="n" s="2">
-        <v>45679.0</v>
+        <v>45672.0</v>
       </c>
       <c r="D244" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="245">
@@ -3558,7 +3558,7 @@
         <v>2025.0</v>
       </c>
       <c r="C245" t="n" s="2">
-        <v>45686.0</v>
+        <v>45679.0</v>
       </c>
       <c r="D245" t="n">
         <v>1.0</v>
@@ -3572,10 +3572,10 @@
         <v>2025.0</v>
       </c>
       <c r="C246" t="n" s="2">
-        <v>45721.0</v>
+        <v>45686.0</v>
       </c>
       <c r="D246" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="247">
@@ -3586,10 +3586,10 @@
         <v>2025.0</v>
       </c>
       <c r="C247" t="n" s="2">
-        <v>45728.0</v>
+        <v>45721.0</v>
       </c>
       <c r="D247" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="248">
@@ -3600,10 +3600,10 @@
         <v>2025.0</v>
       </c>
       <c r="C248" t="n" s="2">
-        <v>45742.0</v>
+        <v>45728.0</v>
       </c>
       <c r="D248" t="n">
-        <v>9.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="249">
@@ -3614,10 +3614,10 @@
         <v>2025.0</v>
       </c>
       <c r="C249" t="n" s="2">
-        <v>45749.0</v>
+        <v>45742.0</v>
       </c>
       <c r="D249" t="n">
-        <v>5.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="250">
@@ -3628,10 +3628,10 @@
         <v>2025.0</v>
       </c>
       <c r="C250" t="n" s="2">
-        <v>45756.0</v>
+        <v>45749.0</v>
       </c>
       <c r="D250" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="251">
@@ -3642,10 +3642,10 @@
         <v>2025.0</v>
       </c>
       <c r="C251" t="n" s="2">
-        <v>45763.0</v>
+        <v>45756.0</v>
       </c>
       <c r="D251" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="252">
@@ -3656,10 +3656,10 @@
         <v>2025.0</v>
       </c>
       <c r="C252" t="n" s="2">
-        <v>45770.0</v>
+        <v>45763.0</v>
       </c>
       <c r="D252" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="253">
@@ -3670,10 +3670,10 @@
         <v>2025.0</v>
       </c>
       <c r="C253" t="n" s="2">
-        <v>45777.0</v>
+        <v>45770.0</v>
       </c>
       <c r="D253" t="n">
-        <v>7.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="254">
@@ -3684,10 +3684,10 @@
         <v>2025.0</v>
       </c>
       <c r="C254" t="n" s="2">
-        <v>45784.0</v>
+        <v>45777.0</v>
       </c>
       <c r="D254" t="n">
-        <v>2.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="255">
@@ -3698,10 +3698,10 @@
         <v>2025.0</v>
       </c>
       <c r="C255" t="n" s="2">
-        <v>45791.0</v>
+        <v>45784.0</v>
       </c>
       <c r="D255" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="256">
@@ -3712,10 +3712,10 @@
         <v>2025.0</v>
       </c>
       <c r="C256" t="n" s="2">
-        <v>45798.0</v>
+        <v>45791.0</v>
       </c>
       <c r="D256" t="n">
-        <v>8.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="257">
@@ -3726,10 +3726,10 @@
         <v>2025.0</v>
       </c>
       <c r="C257" t="n" s="2">
-        <v>45805.0</v>
+        <v>45798.0</v>
       </c>
       <c r="D257" t="n">
-        <v>4.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="258">
@@ -3740,10 +3740,10 @@
         <v>2025.0</v>
       </c>
       <c r="C258" t="n" s="2">
-        <v>45812.0</v>
+        <v>45805.0</v>
       </c>
       <c r="D258" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="259">
@@ -3754,10 +3754,10 @@
         <v>2025.0</v>
       </c>
       <c r="C259" t="n" s="2">
-        <v>45819.0</v>
+        <v>45812.0</v>
       </c>
       <c r="D259" t="n">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="260">
@@ -3768,10 +3768,10 @@
         <v>2025.0</v>
       </c>
       <c r="C260" t="n" s="2">
-        <v>45826.0</v>
+        <v>45819.0</v>
       </c>
       <c r="D260" t="n">
-        <v>13.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="261">
@@ -3782,10 +3782,10 @@
         <v>2025.0</v>
       </c>
       <c r="C261" t="n" s="2">
-        <v>45833.0</v>
+        <v>45826.0</v>
       </c>
       <c r="D261" t="n">
-        <v>1.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="262">
@@ -3796,10 +3796,10 @@
         <v>2025.0</v>
       </c>
       <c r="C262" t="n" s="2">
-        <v>45840.0</v>
+        <v>45833.0</v>
       </c>
       <c r="D262" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="263">
@@ -3810,7 +3810,7 @@
         <v>2025.0</v>
       </c>
       <c r="C263" t="n" s="2">
-        <v>45847.0</v>
+        <v>45840.0</v>
       </c>
       <c r="D263" t="n">
         <v>4.0</v>
@@ -3824,10 +3824,10 @@
         <v>2025.0</v>
       </c>
       <c r="C264" t="n" s="2">
-        <v>45854.0</v>
+        <v>45847.0</v>
       </c>
       <c r="D264" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="265">
@@ -3838,10 +3838,10 @@
         <v>2025.0</v>
       </c>
       <c r="C265" t="n" s="2">
-        <v>45861.0</v>
+        <v>45854.0</v>
       </c>
       <c r="D265" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="266">
@@ -3852,10 +3852,10 @@
         <v>2025.0</v>
       </c>
       <c r="C266" t="n" s="2">
-        <v>45868.0</v>
+        <v>45861.0</v>
       </c>
       <c r="D266" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="267">
@@ -3866,10 +3866,10 @@
         <v>2025.0</v>
       </c>
       <c r="C267" t="n" s="2">
-        <v>45882.0</v>
+        <v>45868.0</v>
       </c>
       <c r="D267" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="268">
@@ -3880,7 +3880,7 @@
         <v>2025.0</v>
       </c>
       <c r="C268" t="n" s="2">
-        <v>45889.0</v>
+        <v>45882.0</v>
       </c>
       <c r="D268" t="n">
         <v>1.0</v>
@@ -3894,10 +3894,10 @@
         <v>2025.0</v>
       </c>
       <c r="C269" t="n" s="2">
-        <v>45896.0</v>
+        <v>45889.0</v>
       </c>
       <c r="D269" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="270">
@@ -3908,7 +3908,7 @@
         <v>2025.0</v>
       </c>
       <c r="C270" t="n" s="2">
-        <v>45903.0</v>
+        <v>45896.0</v>
       </c>
       <c r="D270" t="n">
         <v>3.0</v>
@@ -3922,10 +3922,10 @@
         <v>2025.0</v>
       </c>
       <c r="C271" t="n" s="2">
-        <v>45910.0</v>
+        <v>45903.0</v>
       </c>
       <c r="D271" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="272">
@@ -3936,7 +3936,7 @@
         <v>2025.0</v>
       </c>
       <c r="C272" t="n" s="2">
-        <v>45973.0</v>
+        <v>45910.0</v>
       </c>
       <c r="D272" t="n">
         <v>1.0</v>
@@ -3950,10 +3950,10 @@
         <v>2025.0</v>
       </c>
       <c r="C273" t="n" s="2">
-        <v>45987.0</v>
+        <v>45973.0</v>
       </c>
       <c r="D273" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="274">
@@ -3964,10 +3964,10 @@
         <v>2025.0</v>
       </c>
       <c r="C274" t="n" s="2">
-        <v>45994.0</v>
+        <v>45987.0</v>
       </c>
       <c r="D274" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="275">
@@ -3978,10 +3978,10 @@
         <v>2025.0</v>
       </c>
       <c r="C275" t="n" s="2">
-        <v>46001.0</v>
+        <v>45994.0</v>
       </c>
       <c r="D275" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="276">
@@ -3992,10 +3992,10 @@
         <v>2025.0</v>
       </c>
       <c r="C276" t="n" s="2">
-        <v>46008.0</v>
+        <v>46001.0</v>
       </c>
       <c r="D276" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="277">
@@ -4006,10 +4006,10 @@
         <v>2025.0</v>
       </c>
       <c r="C277" t="n" s="2">
-        <v>46022.0</v>
+        <v>46008.0</v>
       </c>
       <c r="D277" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="278">
@@ -4020,10 +4020,10 @@
         <v>2025.0</v>
       </c>
       <c r="C278" t="n" s="2">
-        <v>46029.0</v>
+        <v>46022.0</v>
       </c>
       <c r="D278" t="n">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="279">
@@ -4031,13 +4031,13 @@
         <v>5</v>
       </c>
       <c r="B279" t="n">
-        <v>2026.0</v>
+        <v>2025.0</v>
       </c>
       <c r="C279" t="n" s="2">
-        <v>46030.0</v>
+        <v>46029.0</v>
       </c>
       <c r="D279" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="280">
@@ -4048,10 +4048,10 @@
         <v>2026.0</v>
       </c>
       <c r="C280" t="n" s="2">
-        <v>46037.0</v>
+        <v>46030.0</v>
       </c>
       <c r="D280" t="n">
-        <v>12.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="281">
@@ -4062,10 +4062,10 @@
         <v>2026.0</v>
       </c>
       <c r="C281" t="n" s="2">
-        <v>46044.0</v>
+        <v>46037.0</v>
       </c>
       <c r="D281" t="n">
-        <v>9.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="282">
@@ -4076,10 +4076,10 @@
         <v>2026.0</v>
       </c>
       <c r="C282" t="n" s="2">
-        <v>46051.0</v>
+        <v>46044.0</v>
       </c>
       <c r="D282" t="n">
-        <v>10.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="283">
@@ -4090,10 +4090,10 @@
         <v>2026.0</v>
       </c>
       <c r="C283" t="n" s="2">
-        <v>46058.0</v>
+        <v>46051.0</v>
       </c>
       <c r="D283" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="284">
@@ -4104,10 +4104,10 @@
         <v>2026.0</v>
       </c>
       <c r="C284" t="n" s="2">
-        <v>46065.0</v>
+        <v>46058.0</v>
       </c>
       <c r="D284" t="n">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="285">
@@ -4118,10 +4118,10 @@
         <v>2026.0</v>
       </c>
       <c r="C285" t="n" s="2">
-        <v>46072.0</v>
+        <v>46065.0</v>
       </c>
       <c r="D285" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="286">
@@ -4132,7 +4132,7 @@
         <v>2026.0</v>
       </c>
       <c r="C286" t="n" s="2">
-        <v>46079.0</v>
+        <v>46072.0</v>
       </c>
       <c r="D286" t="n">
         <v>5.0</v>
@@ -4146,10 +4146,10 @@
         <v>2026.0</v>
       </c>
       <c r="C287" t="n" s="2">
-        <v>46086.0</v>
+        <v>46079.0</v>
       </c>
       <c r="D287" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="288">
@@ -4160,7 +4160,7 @@
         <v>2026.0</v>
       </c>
       <c r="C288" t="n" s="2">
-        <v>46093.0</v>
+        <v>46086.0</v>
       </c>
       <c r="D288" t="n">
         <v>2.0</v>
@@ -4174,10 +4174,10 @@
         <v>2026.0</v>
       </c>
       <c r="C289" t="n" s="2">
-        <v>46100.0</v>
+        <v>46093.0</v>
       </c>
       <c r="D289" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="290">
@@ -4188,10 +4188,10 @@
         <v>2026.0</v>
       </c>
       <c r="C290" t="n" s="2">
-        <v>46107.0</v>
+        <v>46100.0</v>
       </c>
       <c r="D290" t="n">
-        <v>9.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="291">
@@ -4202,10 +4202,10 @@
         <v>2026.0</v>
       </c>
       <c r="C291" t="n" s="2">
-        <v>46114.0</v>
+        <v>46107.0</v>
       </c>
       <c r="D291" t="n">
-        <v>5.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="292">
@@ -4216,10 +4216,10 @@
         <v>2026.0</v>
       </c>
       <c r="C292" t="n" s="2">
-        <v>46121.0</v>
+        <v>46114.0</v>
       </c>
       <c r="D292" t="n">
-        <v>13.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="293">
@@ -4230,10 +4230,10 @@
         <v>2026.0</v>
       </c>
       <c r="C293" t="n" s="2">
-        <v>46128.0</v>
+        <v>46121.0</v>
       </c>
       <c r="D293" t="n">
-        <v>4.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="294">
@@ -4244,7 +4244,7 @@
         <v>2026.0</v>
       </c>
       <c r="C294" t="n" s="2">
-        <v>46135.0</v>
+        <v>46128.0</v>
       </c>
       <c r="D294" t="n">
         <v>4.0</v>
@@ -4258,7 +4258,7 @@
         <v>2026.0</v>
       </c>
       <c r="C295" t="n" s="2">
-        <v>46142.0</v>
+        <v>46135.0</v>
       </c>
       <c r="D295" t="n">
         <v>4.0</v>
@@ -4266,16 +4266,16 @@
     </row>
     <row r="296">
       <c r="A296" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B296" t="n">
-        <v>2023.0</v>
+        <v>2026.0</v>
       </c>
       <c r="C296" t="n" s="2">
-        <v>45095.0</v>
+        <v>46142.0</v>
       </c>
       <c r="D296" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="297">
@@ -4286,7 +4286,7 @@
         <v>2023.0</v>
       </c>
       <c r="C297" t="n" s="2">
-        <v>45102.0</v>
+        <v>45095.0</v>
       </c>
       <c r="D297" t="n">
         <v>1.0</v>
@@ -4300,7 +4300,7 @@
         <v>2023.0</v>
       </c>
       <c r="C298" t="n" s="2">
-        <v>45158.0</v>
+        <v>45102.0</v>
       </c>
       <c r="D298" t="n">
         <v>1.0</v>
@@ -4314,10 +4314,10 @@
         <v>2023.0</v>
       </c>
       <c r="C299" t="n" s="2">
-        <v>45207.0</v>
+        <v>45158.0</v>
       </c>
       <c r="D299" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="300">
@@ -4328,7 +4328,7 @@
         <v>2023.0</v>
       </c>
       <c r="C300" t="n" s="2">
-        <v>45214.0</v>
+        <v>45207.0</v>
       </c>
       <c r="D300" t="n">
         <v>3.0</v>
@@ -4342,10 +4342,10 @@
         <v>2023.0</v>
       </c>
       <c r="C301" t="n" s="2">
-        <v>45221.0</v>
+        <v>45214.0</v>
       </c>
       <c r="D301" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="302">
@@ -4356,7 +4356,7 @@
         <v>2023.0</v>
       </c>
       <c r="C302" t="n" s="2">
-        <v>45249.0</v>
+        <v>45221.0</v>
       </c>
       <c r="D302" t="n">
         <v>1.0</v>
@@ -4370,10 +4370,10 @@
         <v>2023.0</v>
       </c>
       <c r="C303" t="n" s="2">
-        <v>45256.0</v>
+        <v>45249.0</v>
       </c>
       <c r="D303" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="304">
@@ -4384,10 +4384,10 @@
         <v>2023.0</v>
       </c>
       <c r="C304" t="n" s="2">
-        <v>45263.0</v>
+        <v>45256.0</v>
       </c>
       <c r="D304" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="305">
@@ -4398,10 +4398,10 @@
         <v>2023.0</v>
       </c>
       <c r="C305" t="n" s="2">
-        <v>45270.0</v>
+        <v>45263.0</v>
       </c>
       <c r="D305" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="306">
@@ -4412,10 +4412,10 @@
         <v>2023.0</v>
       </c>
       <c r="C306" t="n" s="2">
-        <v>45277.0</v>
+        <v>45270.0</v>
       </c>
       <c r="D306" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="307">
@@ -4426,10 +4426,10 @@
         <v>2023.0</v>
       </c>
       <c r="C307" t="n" s="2">
-        <v>45284.0</v>
+        <v>45277.0</v>
       </c>
       <c r="D307" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="308">
@@ -4440,10 +4440,10 @@
         <v>2023.0</v>
       </c>
       <c r="C308" t="n" s="2">
-        <v>45291.0</v>
+        <v>45284.0</v>
       </c>
       <c r="D308" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="309">
@@ -4451,13 +4451,13 @@
         <v>6</v>
       </c>
       <c r="B309" t="n">
-        <v>2024.0</v>
+        <v>2023.0</v>
       </c>
       <c r="C309" t="n" s="2">
-        <v>45306.0</v>
+        <v>45291.0</v>
       </c>
       <c r="D309" t="n">
-        <v>7.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="310">
@@ -4468,10 +4468,10 @@
         <v>2024.0</v>
       </c>
       <c r="C310" t="n" s="2">
-        <v>45313.0</v>
+        <v>45306.0</v>
       </c>
       <c r="D310" t="n">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="311">
@@ -4482,10 +4482,10 @@
         <v>2024.0</v>
       </c>
       <c r="C311" t="n" s="2">
-        <v>45320.0</v>
+        <v>45313.0</v>
       </c>
       <c r="D311" t="n">
-        <v>19.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="312">
@@ -4496,10 +4496,10 @@
         <v>2024.0</v>
       </c>
       <c r="C312" t="n" s="2">
-        <v>45327.0</v>
+        <v>45320.0</v>
       </c>
       <c r="D312" t="n">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="313">
@@ -4510,10 +4510,10 @@
         <v>2024.0</v>
       </c>
       <c r="C313" t="n" s="2">
-        <v>45334.0</v>
+        <v>45327.0</v>
       </c>
       <c r="D313" t="n">
-        <v>9.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="314">
@@ -4524,10 +4524,10 @@
         <v>2024.0</v>
       </c>
       <c r="C314" t="n" s="2">
-        <v>45341.0</v>
+        <v>45334.0</v>
       </c>
       <c r="D314" t="n">
-        <v>12.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="315">
@@ -4538,7 +4538,7 @@
         <v>2024.0</v>
       </c>
       <c r="C315" t="n" s="2">
-        <v>45348.0</v>
+        <v>45341.0</v>
       </c>
       <c r="D315" t="n">
         <v>12.0</v>
@@ -4552,10 +4552,10 @@
         <v>2024.0</v>
       </c>
       <c r="C316" t="n" s="2">
-        <v>45355.0</v>
+        <v>45348.0</v>
       </c>
       <c r="D316" t="n">
-        <v>10.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="317">
@@ -4566,10 +4566,10 @@
         <v>2024.0</v>
       </c>
       <c r="C317" t="n" s="2">
-        <v>45362.0</v>
+        <v>45355.0</v>
       </c>
       <c r="D317" t="n">
-        <v>12.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="318">
@@ -4580,10 +4580,10 @@
         <v>2024.0</v>
       </c>
       <c r="C318" t="n" s="2">
-        <v>45369.0</v>
+        <v>45362.0</v>
       </c>
       <c r="D318" t="n">
-        <v>13.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="319">
@@ -4594,10 +4594,10 @@
         <v>2024.0</v>
       </c>
       <c r="C319" t="n" s="2">
-        <v>45376.0</v>
+        <v>45369.0</v>
       </c>
       <c r="D319" t="n">
-        <v>18.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="320">
@@ -4608,10 +4608,10 @@
         <v>2024.0</v>
       </c>
       <c r="C320" t="n" s="2">
-        <v>45383.0</v>
+        <v>45376.0</v>
       </c>
       <c r="D320" t="n">
-        <v>12.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="321">
@@ -4622,10 +4622,10 @@
         <v>2024.0</v>
       </c>
       <c r="C321" t="n" s="2">
-        <v>45390.0</v>
+        <v>45383.0</v>
       </c>
       <c r="D321" t="n">
-        <v>6.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="322">
@@ -4636,10 +4636,10 @@
         <v>2024.0</v>
       </c>
       <c r="C322" t="n" s="2">
-        <v>45397.0</v>
+        <v>45390.0</v>
       </c>
       <c r="D322" t="n">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="323">
@@ -4650,10 +4650,10 @@
         <v>2024.0</v>
       </c>
       <c r="C323" t="n" s="2">
-        <v>45404.0</v>
+        <v>45397.0</v>
       </c>
       <c r="D323" t="n">
-        <v>3.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="324">
@@ -4664,10 +4664,10 @@
         <v>2024.0</v>
       </c>
       <c r="C324" t="n" s="2">
-        <v>45411.0</v>
+        <v>45404.0</v>
       </c>
       <c r="D324" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="325">
@@ -4678,10 +4678,10 @@
         <v>2024.0</v>
       </c>
       <c r="C325" t="n" s="2">
-        <v>45418.0</v>
+        <v>45411.0</v>
       </c>
       <c r="D325" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="326">
@@ -4692,10 +4692,10 @@
         <v>2024.0</v>
       </c>
       <c r="C326" t="n" s="2">
-        <v>45425.0</v>
+        <v>45418.0</v>
       </c>
       <c r="D326" t="n">
-        <v>9.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="327">
@@ -4706,10 +4706,10 @@
         <v>2024.0</v>
       </c>
       <c r="C327" t="n" s="2">
-        <v>45432.0</v>
+        <v>45425.0</v>
       </c>
       <c r="D327" t="n">
-        <v>6.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="328">
@@ -4720,7 +4720,7 @@
         <v>2024.0</v>
       </c>
       <c r="C328" t="n" s="2">
-        <v>45439.0</v>
+        <v>45432.0</v>
       </c>
       <c r="D328" t="n">
         <v>6.0</v>
@@ -4734,10 +4734,10 @@
         <v>2024.0</v>
       </c>
       <c r="C329" t="n" s="2">
-        <v>45446.0</v>
+        <v>45439.0</v>
       </c>
       <c r="D329" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="330">
@@ -4748,10 +4748,10 @@
         <v>2024.0</v>
       </c>
       <c r="C330" t="n" s="2">
-        <v>45453.0</v>
+        <v>45446.0</v>
       </c>
       <c r="D330" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="331">
@@ -4762,7 +4762,7 @@
         <v>2024.0</v>
       </c>
       <c r="C331" t="n" s="2">
-        <v>45460.0</v>
+        <v>45453.0</v>
       </c>
       <c r="D331" t="n">
         <v>4.0</v>
@@ -4776,7 +4776,7 @@
         <v>2024.0</v>
       </c>
       <c r="C332" t="n" s="2">
-        <v>45467.0</v>
+        <v>45460.0</v>
       </c>
       <c r="D332" t="n">
         <v>4.0</v>
@@ -4790,10 +4790,10 @@
         <v>2024.0</v>
       </c>
       <c r="C333" t="n" s="2">
-        <v>45474.0</v>
+        <v>45467.0</v>
       </c>
       <c r="D333" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="334">
@@ -4804,10 +4804,10 @@
         <v>2024.0</v>
       </c>
       <c r="C334" t="n" s="2">
-        <v>45481.0</v>
+        <v>45474.0</v>
       </c>
       <c r="D334" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="335">
@@ -4818,10 +4818,10 @@
         <v>2024.0</v>
       </c>
       <c r="C335" t="n" s="2">
-        <v>45488.0</v>
+        <v>45481.0</v>
       </c>
       <c r="D335" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="336">
@@ -4832,10 +4832,10 @@
         <v>2024.0</v>
       </c>
       <c r="C336" t="n" s="2">
-        <v>45495.0</v>
+        <v>45488.0</v>
       </c>
       <c r="D336" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="337">
@@ -4846,10 +4846,10 @@
         <v>2024.0</v>
       </c>
       <c r="C337" t="n" s="2">
-        <v>45502.0</v>
+        <v>45495.0</v>
       </c>
       <c r="D337" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="338">
@@ -4860,10 +4860,10 @@
         <v>2024.0</v>
       </c>
       <c r="C338" t="n" s="2">
-        <v>45509.0</v>
+        <v>45502.0</v>
       </c>
       <c r="D338" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="339">
@@ -4874,7 +4874,7 @@
         <v>2024.0</v>
       </c>
       <c r="C339" t="n" s="2">
-        <v>45523.0</v>
+        <v>45509.0</v>
       </c>
       <c r="D339" t="n">
         <v>1.0</v>
@@ -4888,7 +4888,7 @@
         <v>2024.0</v>
       </c>
       <c r="C340" t="n" s="2">
-        <v>45551.0</v>
+        <v>45523.0</v>
       </c>
       <c r="D340" t="n">
         <v>1.0</v>
@@ -4902,7 +4902,7 @@
         <v>2024.0</v>
       </c>
       <c r="C341" t="n" s="2">
-        <v>45558.0</v>
+        <v>45551.0</v>
       </c>
       <c r="D341" t="n">
         <v>1.0</v>
@@ -4916,10 +4916,10 @@
         <v>2024.0</v>
       </c>
       <c r="C342" t="n" s="2">
-        <v>45572.0</v>
+        <v>45558.0</v>
       </c>
       <c r="D342" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="343">
@@ -4930,10 +4930,10 @@
         <v>2024.0</v>
       </c>
       <c r="C343" t="n" s="2">
-        <v>45593.0</v>
+        <v>45572.0</v>
       </c>
       <c r="D343" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="344">
@@ -4944,10 +4944,10 @@
         <v>2024.0</v>
       </c>
       <c r="C344" t="n" s="2">
-        <v>45614.0</v>
+        <v>45593.0</v>
       </c>
       <c r="D344" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="345">
@@ -4958,10 +4958,10 @@
         <v>2024.0</v>
       </c>
       <c r="C345" t="n" s="2">
-        <v>45621.0</v>
+        <v>45614.0</v>
       </c>
       <c r="D345" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="346">
@@ -4972,7 +4972,7 @@
         <v>2024.0</v>
       </c>
       <c r="C346" t="n" s="2">
-        <v>45635.0</v>
+        <v>45621.0</v>
       </c>
       <c r="D346" t="n">
         <v>1.0</v>
@@ -4986,7 +4986,7 @@
         <v>2024.0</v>
       </c>
       <c r="C347" t="n" s="2">
-        <v>45649.0</v>
+        <v>45635.0</v>
       </c>
       <c r="D347" t="n">
         <v>1.0</v>
@@ -4997,13 +4997,13 @@
         <v>6</v>
       </c>
       <c r="B348" t="n">
-        <v>2025.0</v>
+        <v>2024.0</v>
       </c>
       <c r="C348" t="n" s="2">
-        <v>45665.0</v>
+        <v>45649.0</v>
       </c>
       <c r="D348" t="n">
-        <v>9.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="349">
@@ -5014,10 +5014,10 @@
         <v>2025.0</v>
       </c>
       <c r="C349" t="n" s="2">
-        <v>45672.0</v>
+        <v>45665.0</v>
       </c>
       <c r="D349" t="n">
-        <v>3.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="350">
@@ -5028,10 +5028,10 @@
         <v>2025.0</v>
       </c>
       <c r="C350" t="n" s="2">
-        <v>45679.0</v>
+        <v>45672.0</v>
       </c>
       <c r="D350" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="351">
@@ -5042,10 +5042,10 @@
         <v>2025.0</v>
       </c>
       <c r="C351" t="n" s="2">
-        <v>45686.0</v>
+        <v>45679.0</v>
       </c>
       <c r="D351" t="n">
-        <v>8.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="352">
@@ -5056,10 +5056,10 @@
         <v>2025.0</v>
       </c>
       <c r="C352" t="n" s="2">
-        <v>45693.0</v>
+        <v>45686.0</v>
       </c>
       <c r="D352" t="n">
-        <v>3.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="353">
@@ -5070,10 +5070,10 @@
         <v>2025.0</v>
       </c>
       <c r="C353" t="n" s="2">
-        <v>45700.0</v>
+        <v>45693.0</v>
       </c>
       <c r="D353" t="n">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="354">
@@ -5084,10 +5084,10 @@
         <v>2025.0</v>
       </c>
       <c r="C354" t="n" s="2">
-        <v>45707.0</v>
+        <v>45700.0</v>
       </c>
       <c r="D354" t="n">
-        <v>8.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="355">
@@ -5098,10 +5098,10 @@
         <v>2025.0</v>
       </c>
       <c r="C355" t="n" s="2">
-        <v>45714.0</v>
+        <v>45707.0</v>
       </c>
       <c r="D355" t="n">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="356">
@@ -5112,10 +5112,10 @@
         <v>2025.0</v>
       </c>
       <c r="C356" t="n" s="2">
-        <v>45721.0</v>
+        <v>45714.0</v>
       </c>
       <c r="D356" t="n">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="357">
@@ -5126,10 +5126,10 @@
         <v>2025.0</v>
       </c>
       <c r="C357" t="n" s="2">
-        <v>45728.0</v>
+        <v>45721.0</v>
       </c>
       <c r="D357" t="n">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="358">
@@ -5140,10 +5140,10 @@
         <v>2025.0</v>
       </c>
       <c r="C358" t="n" s="2">
-        <v>45735.0</v>
+        <v>45728.0</v>
       </c>
       <c r="D358" t="n">
-        <v>4.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="359">
@@ -5154,10 +5154,10 @@
         <v>2025.0</v>
       </c>
       <c r="C359" t="n" s="2">
-        <v>45742.0</v>
+        <v>45735.0</v>
       </c>
       <c r="D359" t="n">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="360">
@@ -5168,10 +5168,10 @@
         <v>2025.0</v>
       </c>
       <c r="C360" t="n" s="2">
-        <v>45749.0</v>
+        <v>45742.0</v>
       </c>
       <c r="D360" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="361">
@@ -5182,10 +5182,10 @@
         <v>2025.0</v>
       </c>
       <c r="C361" t="n" s="2">
-        <v>45756.0</v>
+        <v>45749.0</v>
       </c>
       <c r="D361" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="362">
@@ -5196,10 +5196,10 @@
         <v>2025.0</v>
       </c>
       <c r="C362" t="n" s="2">
-        <v>45763.0</v>
+        <v>45756.0</v>
       </c>
       <c r="D362" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="363">
@@ -5210,7 +5210,7 @@
         <v>2025.0</v>
       </c>
       <c r="C363" t="n" s="2">
-        <v>45770.0</v>
+        <v>45763.0</v>
       </c>
       <c r="D363" t="n">
         <v>4.0</v>
@@ -5224,10 +5224,10 @@
         <v>2025.0</v>
       </c>
       <c r="C364" t="n" s="2">
-        <v>45777.0</v>
+        <v>45770.0</v>
       </c>
       <c r="D364" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="365">
@@ -5238,7 +5238,7 @@
         <v>2025.0</v>
       </c>
       <c r="C365" t="n" s="2">
-        <v>45784.0</v>
+        <v>45777.0</v>
       </c>
       <c r="D365" t="n">
         <v>1.0</v>
@@ -5252,7 +5252,7 @@
         <v>2025.0</v>
       </c>
       <c r="C366" t="n" s="2">
-        <v>45791.0</v>
+        <v>45784.0</v>
       </c>
       <c r="D366" t="n">
         <v>1.0</v>
@@ -5266,7 +5266,7 @@
         <v>2025.0</v>
       </c>
       <c r="C367" t="n" s="2">
-        <v>45840.0</v>
+        <v>45791.0</v>
       </c>
       <c r="D367" t="n">
         <v>1.0</v>
@@ -5280,7 +5280,7 @@
         <v>2025.0</v>
       </c>
       <c r="C368" t="n" s="2">
-        <v>46001.0</v>
+        <v>45840.0</v>
       </c>
       <c r="D368" t="n">
         <v>1.0</v>
@@ -5291,10 +5291,10 @@
         <v>6</v>
       </c>
       <c r="B369" t="n">
-        <v>2026.0</v>
+        <v>2025.0</v>
       </c>
       <c r="C369" t="n" s="2">
-        <v>46037.0</v>
+        <v>46001.0</v>
       </c>
       <c r="D369" t="n">
         <v>1.0</v>
@@ -5302,13 +5302,13 @@
     </row>
     <row r="370">
       <c r="A370" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B370" t="n">
-        <v>2021.0</v>
+        <v>2026.0</v>
       </c>
       <c r="C370" t="n" s="2">
-        <v>44561.0</v>
+        <v>46037.0</v>
       </c>
       <c r="D370" t="n">
         <v>1.0</v>
@@ -5319,10 +5319,10 @@
         <v>7</v>
       </c>
       <c r="B371" t="n">
-        <v>2022.0</v>
+        <v>2021.0</v>
       </c>
       <c r="C371" t="n" s="2">
-        <v>44569.0</v>
+        <v>44561.0</v>
       </c>
       <c r="D371" t="n">
         <v>1.0</v>
@@ -5336,10 +5336,10 @@
         <v>2022.0</v>
       </c>
       <c r="C372" t="n" s="2">
-        <v>44576.0</v>
+        <v>44569.0</v>
       </c>
       <c r="D372" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="373">
@@ -5350,10 +5350,10 @@
         <v>2022.0</v>
       </c>
       <c r="C373" t="n" s="2">
-        <v>44583.0</v>
+        <v>44576.0</v>
       </c>
       <c r="D373" t="n">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="374">
@@ -5364,10 +5364,10 @@
         <v>2022.0</v>
       </c>
       <c r="C374" t="n" s="2">
-        <v>44590.0</v>
+        <v>44583.0</v>
       </c>
       <c r="D374" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="375">
@@ -5378,10 +5378,10 @@
         <v>2022.0</v>
       </c>
       <c r="C375" t="n" s="2">
-        <v>44604.0</v>
+        <v>44590.0</v>
       </c>
       <c r="D375" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="376">
@@ -5392,7 +5392,7 @@
         <v>2022.0</v>
       </c>
       <c r="C376" t="n" s="2">
-        <v>44611.0</v>
+        <v>44604.0</v>
       </c>
       <c r="D376" t="n">
         <v>3.0</v>
@@ -5406,10 +5406,10 @@
         <v>2022.0</v>
       </c>
       <c r="C377" t="n" s="2">
-        <v>44618.0</v>
+        <v>44611.0</v>
       </c>
       <c r="D377" t="n">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="378">
@@ -5420,7 +5420,7 @@
         <v>2022.0</v>
       </c>
       <c r="C378" t="n" s="2">
-        <v>44625.0</v>
+        <v>44618.0</v>
       </c>
       <c r="D378" t="n">
         <v>5.0</v>
@@ -5434,10 +5434,10 @@
         <v>2022.0</v>
       </c>
       <c r="C379" t="n" s="2">
-        <v>44632.0</v>
+        <v>44625.0</v>
       </c>
       <c r="D379" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="380">
@@ -5448,10 +5448,10 @@
         <v>2022.0</v>
       </c>
       <c r="C380" t="n" s="2">
-        <v>44639.0</v>
+        <v>44632.0</v>
       </c>
       <c r="D380" t="n">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="381">
@@ -5462,10 +5462,10 @@
         <v>2022.0</v>
       </c>
       <c r="C381" t="n" s="2">
-        <v>44646.0</v>
+        <v>44639.0</v>
       </c>
       <c r="D381" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="382">
@@ -5476,10 +5476,10 @@
         <v>2022.0</v>
       </c>
       <c r="C382" t="n" s="2">
-        <v>44653.0</v>
+        <v>44646.0</v>
       </c>
       <c r="D382" t="n">
-        <v>9.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="383">
@@ -5490,10 +5490,10 @@
         <v>2022.0</v>
       </c>
       <c r="C383" t="n" s="2">
-        <v>44660.0</v>
+        <v>44653.0</v>
       </c>
       <c r="D383" t="n">
-        <v>6.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="384">
@@ -5504,10 +5504,10 @@
         <v>2022.0</v>
       </c>
       <c r="C384" t="n" s="2">
-        <v>44667.0</v>
+        <v>44660.0</v>
       </c>
       <c r="D384" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="385">
@@ -5518,10 +5518,10 @@
         <v>2022.0</v>
       </c>
       <c r="C385" t="n" s="2">
-        <v>44674.0</v>
+        <v>44667.0</v>
       </c>
       <c r="D385" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="386">
@@ -5532,10 +5532,10 @@
         <v>2022.0</v>
       </c>
       <c r="C386" t="n" s="2">
-        <v>44681.0</v>
+        <v>44674.0</v>
       </c>
       <c r="D386" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="387">
@@ -5546,10 +5546,10 @@
         <v>2022.0</v>
       </c>
       <c r="C387" t="n" s="2">
-        <v>44688.0</v>
+        <v>44681.0</v>
       </c>
       <c r="D387" t="n">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="388">
@@ -5560,10 +5560,10 @@
         <v>2022.0</v>
       </c>
       <c r="C388" t="n" s="2">
-        <v>44695.0</v>
+        <v>44688.0</v>
       </c>
       <c r="D388" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="389">
@@ -5574,10 +5574,10 @@
         <v>2022.0</v>
       </c>
       <c r="C389" t="n" s="2">
-        <v>44702.0</v>
+        <v>44695.0</v>
       </c>
       <c r="D389" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="390">
@@ -5588,10 +5588,10 @@
         <v>2022.0</v>
       </c>
       <c r="C390" t="n" s="2">
-        <v>44709.0</v>
+        <v>44702.0</v>
       </c>
       <c r="D390" t="n">
-        <v>8.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="391">
@@ -5602,10 +5602,10 @@
         <v>2022.0</v>
       </c>
       <c r="C391" t="n" s="2">
-        <v>44716.0</v>
+        <v>44709.0</v>
       </c>
       <c r="D391" t="n">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="392">
@@ -5616,10 +5616,10 @@
         <v>2022.0</v>
       </c>
       <c r="C392" t="n" s="2">
-        <v>44723.0</v>
+        <v>44716.0</v>
       </c>
       <c r="D392" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="393">
@@ -5630,10 +5630,10 @@
         <v>2022.0</v>
       </c>
       <c r="C393" t="n" s="2">
-        <v>44730.0</v>
+        <v>44723.0</v>
       </c>
       <c r="D393" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="394">
@@ -5644,7 +5644,7 @@
         <v>2022.0</v>
       </c>
       <c r="C394" t="n" s="2">
-        <v>44737.0</v>
+        <v>44730.0</v>
       </c>
       <c r="D394" t="n">
         <v>4.0</v>
@@ -5658,10 +5658,10 @@
         <v>2022.0</v>
       </c>
       <c r="C395" t="n" s="2">
-        <v>44744.0</v>
+        <v>44737.0</v>
       </c>
       <c r="D395" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="396">
@@ -5672,10 +5672,10 @@
         <v>2022.0</v>
       </c>
       <c r="C396" t="n" s="2">
-        <v>44751.0</v>
+        <v>44744.0</v>
       </c>
       <c r="D396" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="397">
@@ -5686,10 +5686,10 @@
         <v>2022.0</v>
       </c>
       <c r="C397" t="n" s="2">
-        <v>44758.0</v>
+        <v>44751.0</v>
       </c>
       <c r="D397" t="n">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="398">
@@ -5700,10 +5700,10 @@
         <v>2022.0</v>
       </c>
       <c r="C398" t="n" s="2">
-        <v>44765.0</v>
+        <v>44758.0</v>
       </c>
       <c r="D398" t="n">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="399">
@@ -5714,10 +5714,10 @@
         <v>2022.0</v>
       </c>
       <c r="C399" t="n" s="2">
-        <v>44779.0</v>
+        <v>44765.0</v>
       </c>
       <c r="D399" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="400">
@@ -5728,10 +5728,10 @@
         <v>2022.0</v>
       </c>
       <c r="C400" t="n" s="2">
-        <v>44786.0</v>
+        <v>44779.0</v>
       </c>
       <c r="D400" t="n">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="401">
@@ -5742,10 +5742,10 @@
         <v>2022.0</v>
       </c>
       <c r="C401" t="n" s="2">
-        <v>44863.0</v>
+        <v>44786.0</v>
       </c>
       <c r="D401" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="402">
@@ -5756,10 +5756,10 @@
         <v>2022.0</v>
       </c>
       <c r="C402" t="n" s="2">
-        <v>44870.0</v>
+        <v>44863.0</v>
       </c>
       <c r="D402" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="403">
@@ -5770,10 +5770,10 @@
         <v>2022.0</v>
       </c>
       <c r="C403" t="n" s="2">
-        <v>44884.0</v>
+        <v>44870.0</v>
       </c>
       <c r="D403" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="404">
@@ -5784,7 +5784,7 @@
         <v>2022.0</v>
       </c>
       <c r="C404" t="n" s="2">
-        <v>44891.0</v>
+        <v>44884.0</v>
       </c>
       <c r="D404" t="n">
         <v>2.0</v>
@@ -5798,10 +5798,10 @@
         <v>2022.0</v>
       </c>
       <c r="C405" t="n" s="2">
-        <v>44898.0</v>
+        <v>44891.0</v>
       </c>
       <c r="D405" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="406">
@@ -5812,10 +5812,10 @@
         <v>2022.0</v>
       </c>
       <c r="C406" t="n" s="2">
-        <v>44912.0</v>
+        <v>44898.0</v>
       </c>
       <c r="D406" t="n">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="407">
@@ -5826,10 +5826,10 @@
         <v>2022.0</v>
       </c>
       <c r="C407" t="n" s="2">
-        <v>44919.0</v>
+        <v>44912.0</v>
       </c>
       <c r="D407" t="n">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="408">
@@ -5840,10 +5840,10 @@
         <v>2022.0</v>
       </c>
       <c r="C408" t="n" s="2">
-        <v>44926.0</v>
+        <v>44919.0</v>
       </c>
       <c r="D408" t="n">
-        <v>12.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="409">
@@ -5851,13 +5851,13 @@
         <v>7</v>
       </c>
       <c r="B409" t="n">
-        <v>2023.0</v>
+        <v>2022.0</v>
       </c>
       <c r="C409" t="n" s="2">
-        <v>44934.0</v>
+        <v>44926.0</v>
       </c>
       <c r="D409" t="n">
-        <v>4.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="410">
@@ -5868,10 +5868,10 @@
         <v>2023.0</v>
       </c>
       <c r="C410" t="n" s="2">
-        <v>44941.0</v>
+        <v>44934.0</v>
       </c>
       <c r="D410" t="n">
-        <v>16.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="411">
@@ -5882,10 +5882,10 @@
         <v>2023.0</v>
       </c>
       <c r="C411" t="n" s="2">
-        <v>44948.0</v>
+        <v>44941.0</v>
       </c>
       <c r="D411" t="n">
-        <v>5.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="412">
@@ -5896,10 +5896,10 @@
         <v>2023.0</v>
       </c>
       <c r="C412" t="n" s="2">
-        <v>44955.0</v>
+        <v>44948.0</v>
       </c>
       <c r="D412" t="n">
-        <v>19.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="413">
@@ -5910,10 +5910,10 @@
         <v>2023.0</v>
       </c>
       <c r="C413" t="n" s="2">
-        <v>44962.0</v>
+        <v>44955.0</v>
       </c>
       <c r="D413" t="n">
-        <v>22.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="414">
@@ -5924,10 +5924,10 @@
         <v>2023.0</v>
       </c>
       <c r="C414" t="n" s="2">
-        <v>44969.0</v>
+        <v>44962.0</v>
       </c>
       <c r="D414" t="n">
-        <v>9.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="415">
@@ -5938,10 +5938,10 @@
         <v>2023.0</v>
       </c>
       <c r="C415" t="n" s="2">
-        <v>44976.0</v>
+        <v>44969.0</v>
       </c>
       <c r="D415" t="n">
-        <v>22.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="416">
@@ -5952,10 +5952,10 @@
         <v>2023.0</v>
       </c>
       <c r="C416" t="n" s="2">
-        <v>44983.0</v>
+        <v>44976.0</v>
       </c>
       <c r="D416" t="n">
-        <v>29.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="417">
@@ -5966,10 +5966,10 @@
         <v>2023.0</v>
       </c>
       <c r="C417" t="n" s="2">
-        <v>44990.0</v>
+        <v>44983.0</v>
       </c>
       <c r="D417" t="n">
-        <v>5.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="418">
@@ -5980,10 +5980,10 @@
         <v>2023.0</v>
       </c>
       <c r="C418" t="n" s="2">
-        <v>44997.0</v>
+        <v>44990.0</v>
       </c>
       <c r="D418" t="n">
-        <v>24.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="419">
@@ -5994,10 +5994,10 @@
         <v>2023.0</v>
       </c>
       <c r="C419" t="n" s="2">
-        <v>45004.0</v>
+        <v>44997.0</v>
       </c>
       <c r="D419" t="n">
-        <v>8.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="420">
@@ -6008,10 +6008,10 @@
         <v>2023.0</v>
       </c>
       <c r="C420" t="n" s="2">
-        <v>45011.0</v>
+        <v>45004.0</v>
       </c>
       <c r="D420" t="n">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="421">
@@ -6022,10 +6022,10 @@
         <v>2023.0</v>
       </c>
       <c r="C421" t="n" s="2">
-        <v>45018.0</v>
+        <v>45011.0</v>
       </c>
       <c r="D421" t="n">
-        <v>18.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="422">
@@ -6036,10 +6036,10 @@
         <v>2023.0</v>
       </c>
       <c r="C422" t="n" s="2">
-        <v>45025.0</v>
+        <v>45018.0</v>
       </c>
       <c r="D422" t="n">
-        <v>13.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="423">
@@ -6050,10 +6050,10 @@
         <v>2023.0</v>
       </c>
       <c r="C423" t="n" s="2">
-        <v>45032.0</v>
+        <v>45025.0</v>
       </c>
       <c r="D423" t="n">
-        <v>18.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="424">
@@ -6064,10 +6064,10 @@
         <v>2023.0</v>
       </c>
       <c r="C424" t="n" s="2">
-        <v>45039.0</v>
+        <v>45032.0</v>
       </c>
       <c r="D424" t="n">
-        <v>15.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="425">
@@ -6078,10 +6078,10 @@
         <v>2023.0</v>
       </c>
       <c r="C425" t="n" s="2">
-        <v>45046.0</v>
+        <v>45039.0</v>
       </c>
       <c r="D425" t="n">
-        <v>12.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="426">
@@ -6092,10 +6092,10 @@
         <v>2023.0</v>
       </c>
       <c r="C426" t="n" s="2">
-        <v>45053.0</v>
+        <v>45046.0</v>
       </c>
       <c r="D426" t="n">
-        <v>6.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="427">
@@ -6106,10 +6106,10 @@
         <v>2023.0</v>
       </c>
       <c r="C427" t="n" s="2">
-        <v>45060.0</v>
+        <v>45053.0</v>
       </c>
       <c r="D427" t="n">
-        <v>11.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="428">
@@ -6120,10 +6120,10 @@
         <v>2023.0</v>
       </c>
       <c r="C428" t="n" s="2">
-        <v>45067.0</v>
+        <v>45060.0</v>
       </c>
       <c r="D428" t="n">
-        <v>8.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="429">
@@ -6134,7 +6134,7 @@
         <v>2023.0</v>
       </c>
       <c r="C429" t="n" s="2">
-        <v>45074.0</v>
+        <v>45067.0</v>
       </c>
       <c r="D429" t="n">
         <v>8.0</v>
@@ -6148,10 +6148,10 @@
         <v>2023.0</v>
       </c>
       <c r="C430" t="n" s="2">
-        <v>45081.0</v>
+        <v>45074.0</v>
       </c>
       <c r="D430" t="n">
-        <v>5.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="431">
@@ -6162,10 +6162,10 @@
         <v>2023.0</v>
       </c>
       <c r="C431" t="n" s="2">
-        <v>45088.0</v>
+        <v>45081.0</v>
       </c>
       <c r="D431" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="432">
@@ -6176,10 +6176,10 @@
         <v>2023.0</v>
       </c>
       <c r="C432" t="n" s="2">
-        <v>45095.0</v>
+        <v>45088.0</v>
       </c>
       <c r="D432" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="433">
@@ -6190,10 +6190,10 @@
         <v>2023.0</v>
       </c>
       <c r="C433" t="n" s="2">
-        <v>45102.0</v>
+        <v>45095.0</v>
       </c>
       <c r="D433" t="n">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="434">
@@ -6204,10 +6204,10 @@
         <v>2023.0</v>
       </c>
       <c r="C434" t="n" s="2">
-        <v>45109.0</v>
+        <v>45102.0</v>
       </c>
       <c r="D434" t="n">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="435">
@@ -6218,10 +6218,10 @@
         <v>2023.0</v>
       </c>
       <c r="C435" t="n" s="2">
-        <v>45116.0</v>
+        <v>45109.0</v>
       </c>
       <c r="D435" t="n">
-        <v>3.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="436">
@@ -6232,10 +6232,10 @@
         <v>2023.0</v>
       </c>
       <c r="C436" t="n" s="2">
-        <v>45123.0</v>
+        <v>45116.0</v>
       </c>
       <c r="D436" t="n">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="437">
@@ -6246,7 +6246,7 @@
         <v>2023.0</v>
       </c>
       <c r="C437" t="n" s="2">
-        <v>45130.0</v>
+        <v>45123.0</v>
       </c>
       <c r="D437" t="n">
         <v>6.0</v>
@@ -6260,10 +6260,10 @@
         <v>2023.0</v>
       </c>
       <c r="C438" t="n" s="2">
-        <v>45137.0</v>
+        <v>45130.0</v>
       </c>
       <c r="D438" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="439">
@@ -6274,7 +6274,7 @@
         <v>2023.0</v>
       </c>
       <c r="C439" t="n" s="2">
-        <v>45144.0</v>
+        <v>45137.0</v>
       </c>
       <c r="D439" t="n">
         <v>2.0</v>
@@ -6288,7 +6288,7 @@
         <v>2023.0</v>
       </c>
       <c r="C440" t="n" s="2">
-        <v>45151.0</v>
+        <v>45144.0</v>
       </c>
       <c r="D440" t="n">
         <v>2.0</v>
@@ -6302,7 +6302,7 @@
         <v>2023.0</v>
       </c>
       <c r="C441" t="n" s="2">
-        <v>45165.0</v>
+        <v>45151.0</v>
       </c>
       <c r="D441" t="n">
         <v>2.0</v>
@@ -6316,7 +6316,7 @@
         <v>2023.0</v>
       </c>
       <c r="C442" t="n" s="2">
-        <v>45172.0</v>
+        <v>45165.0</v>
       </c>
       <c r="D442" t="n">
         <v>2.0</v>
@@ -6330,10 +6330,10 @@
         <v>2023.0</v>
       </c>
       <c r="C443" t="n" s="2">
-        <v>45179.0</v>
+        <v>45172.0</v>
       </c>
       <c r="D443" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="444">
@@ -6344,7 +6344,7 @@
         <v>2023.0</v>
       </c>
       <c r="C444" t="n" s="2">
-        <v>45186.0</v>
+        <v>45179.0</v>
       </c>
       <c r="D444" t="n">
         <v>1.0</v>
@@ -6358,7 +6358,7 @@
         <v>2023.0</v>
       </c>
       <c r="C445" t="n" s="2">
-        <v>45193.0</v>
+        <v>45186.0</v>
       </c>
       <c r="D445" t="n">
         <v>1.0</v>
@@ -6372,7 +6372,7 @@
         <v>2023.0</v>
       </c>
       <c r="C446" t="n" s="2">
-        <v>45200.0</v>
+        <v>45193.0</v>
       </c>
       <c r="D446" t="n">
         <v>1.0</v>
@@ -6386,7 +6386,7 @@
         <v>2023.0</v>
       </c>
       <c r="C447" t="n" s="2">
-        <v>45207.0</v>
+        <v>45200.0</v>
       </c>
       <c r="D447" t="n">
         <v>1.0</v>
@@ -6400,7 +6400,7 @@
         <v>2023.0</v>
       </c>
       <c r="C448" t="n" s="2">
-        <v>45235.0</v>
+        <v>45207.0</v>
       </c>
       <c r="D448" t="n">
         <v>1.0</v>
@@ -6414,10 +6414,10 @@
         <v>2023.0</v>
       </c>
       <c r="C449" t="n" s="2">
-        <v>45242.0</v>
+        <v>45235.0</v>
       </c>
       <c r="D449" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="450">
@@ -6428,10 +6428,10 @@
         <v>2023.0</v>
       </c>
       <c r="C450" t="n" s="2">
-        <v>45249.0</v>
+        <v>45242.0</v>
       </c>
       <c r="D450" t="n">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="451">
@@ -6442,10 +6442,10 @@
         <v>2023.0</v>
       </c>
       <c r="C451" t="n" s="2">
-        <v>45256.0</v>
+        <v>45249.0</v>
       </c>
       <c r="D451" t="n">
-        <v>9.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="452">
@@ -6456,10 +6456,10 @@
         <v>2023.0</v>
       </c>
       <c r="C452" t="n" s="2">
-        <v>45263.0</v>
+        <v>45256.0</v>
       </c>
       <c r="D452" t="n">
-        <v>12.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="453">
@@ -6470,10 +6470,10 @@
         <v>2023.0</v>
       </c>
       <c r="C453" t="n" s="2">
-        <v>45270.0</v>
+        <v>45263.0</v>
       </c>
       <c r="D453" t="n">
-        <v>6.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="454">
@@ -6484,10 +6484,10 @@
         <v>2023.0</v>
       </c>
       <c r="C454" t="n" s="2">
-        <v>45277.0</v>
+        <v>45270.0</v>
       </c>
       <c r="D454" t="n">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="455">
@@ -6498,7 +6498,7 @@
         <v>2023.0</v>
       </c>
       <c r="C455" t="n" s="2">
-        <v>45284.0</v>
+        <v>45277.0</v>
       </c>
       <c r="D455" t="n">
         <v>7.0</v>
@@ -6512,10 +6512,10 @@
         <v>2023.0</v>
       </c>
       <c r="C456" t="n" s="2">
-        <v>45291.0</v>
+        <v>45284.0</v>
       </c>
       <c r="D456" t="n">
-        <v>13.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="457">
@@ -6523,13 +6523,13 @@
         <v>7</v>
       </c>
       <c r="B457" t="n">
-        <v>2024.0</v>
+        <v>2023.0</v>
       </c>
       <c r="C457" t="n" s="2">
-        <v>45299.0</v>
+        <v>45291.0</v>
       </c>
       <c r="D457" t="n">
-        <v>6.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="458">
@@ -6540,10 +6540,10 @@
         <v>2024.0</v>
       </c>
       <c r="C458" t="n" s="2">
-        <v>45306.0</v>
+        <v>45299.0</v>
       </c>
       <c r="D458" t="n">
-        <v>11.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="459">
@@ -6554,10 +6554,10 @@
         <v>2024.0</v>
       </c>
       <c r="C459" t="n" s="2">
-        <v>45313.0</v>
+        <v>45306.0</v>
       </c>
       <c r="D459" t="n">
-        <v>5.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="460">
@@ -6568,10 +6568,10 @@
         <v>2024.0</v>
       </c>
       <c r="C460" t="n" s="2">
-        <v>45320.0</v>
+        <v>45313.0</v>
       </c>
       <c r="D460" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="461">
@@ -6582,10 +6582,10 @@
         <v>2024.0</v>
       </c>
       <c r="C461" t="n" s="2">
-        <v>45327.0</v>
+        <v>45320.0</v>
       </c>
       <c r="D461" t="n">
-        <v>9.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="462">
@@ -6596,10 +6596,10 @@
         <v>2024.0</v>
       </c>
       <c r="C462" t="n" s="2">
-        <v>45334.0</v>
+        <v>45327.0</v>
       </c>
       <c r="D462" t="n">
-        <v>3.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="463">
@@ -6610,10 +6610,10 @@
         <v>2024.0</v>
       </c>
       <c r="C463" t="n" s="2">
-        <v>45341.0</v>
+        <v>45334.0</v>
       </c>
       <c r="D463" t="n">
-        <v>21.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="464">
@@ -6624,10 +6624,10 @@
         <v>2024.0</v>
       </c>
       <c r="C464" t="n" s="2">
-        <v>45348.0</v>
+        <v>45341.0</v>
       </c>
       <c r="D464" t="n">
-        <v>1.0</v>
+        <v>21.0</v>
       </c>
     </row>
     <row r="465">
@@ -6638,10 +6638,10 @@
         <v>2024.0</v>
       </c>
       <c r="C465" t="n" s="2">
-        <v>45355.0</v>
+        <v>45348.0</v>
       </c>
       <c r="D465" t="n">
-        <v>9.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="466">
@@ -6652,10 +6652,10 @@
         <v>2024.0</v>
       </c>
       <c r="C466" t="n" s="2">
-        <v>45362.0</v>
+        <v>45355.0</v>
       </c>
       <c r="D466" t="n">
-        <v>4.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="467">
@@ -6666,10 +6666,10 @@
         <v>2024.0</v>
       </c>
       <c r="C467" t="n" s="2">
-        <v>45369.0</v>
+        <v>45362.0</v>
       </c>
       <c r="D467" t="n">
-        <v>14.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="468">
@@ -6680,10 +6680,10 @@
         <v>2024.0</v>
       </c>
       <c r="C468" t="n" s="2">
-        <v>45376.0</v>
+        <v>45369.0</v>
       </c>
       <c r="D468" t="n">
-        <v>4.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="469">
@@ -6694,10 +6694,10 @@
         <v>2024.0</v>
       </c>
       <c r="C469" t="n" s="2">
-        <v>45383.0</v>
+        <v>45376.0</v>
       </c>
       <c r="D469" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="470">
@@ -6708,10 +6708,10 @@
         <v>2024.0</v>
       </c>
       <c r="C470" t="n" s="2">
-        <v>45390.0</v>
+        <v>45383.0</v>
       </c>
       <c r="D470" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="471">
@@ -6722,7 +6722,7 @@
         <v>2024.0</v>
       </c>
       <c r="C471" t="n" s="2">
-        <v>45397.0</v>
+        <v>45390.0</v>
       </c>
       <c r="D471" t="n">
         <v>1.0</v>
@@ -6736,10 +6736,10 @@
         <v>2024.0</v>
       </c>
       <c r="C472" t="n" s="2">
-        <v>45404.0</v>
+        <v>45397.0</v>
       </c>
       <c r="D472" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="473">
@@ -6750,10 +6750,10 @@
         <v>2024.0</v>
       </c>
       <c r="C473" t="n" s="2">
-        <v>45411.0</v>
+        <v>45404.0</v>
       </c>
       <c r="D473" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="474">
@@ -6764,10 +6764,10 @@
         <v>2024.0</v>
       </c>
       <c r="C474" t="n" s="2">
-        <v>45439.0</v>
+        <v>45411.0</v>
       </c>
       <c r="D474" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="475">
@@ -6778,10 +6778,10 @@
         <v>2024.0</v>
       </c>
       <c r="C475" t="n" s="2">
-        <v>45446.0</v>
+        <v>45439.0</v>
       </c>
       <c r="D475" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="476">
@@ -6792,7 +6792,7 @@
         <v>2024.0</v>
       </c>
       <c r="C476" t="n" s="2">
-        <v>45460.0</v>
+        <v>45446.0</v>
       </c>
       <c r="D476" t="n">
         <v>1.0</v>
@@ -6806,7 +6806,7 @@
         <v>2024.0</v>
       </c>
       <c r="C477" t="n" s="2">
-        <v>45481.0</v>
+        <v>45460.0</v>
       </c>
       <c r="D477" t="n">
         <v>1.0</v>
@@ -6820,7 +6820,7 @@
         <v>2024.0</v>
       </c>
       <c r="C478" t="n" s="2">
-        <v>45516.0</v>
+        <v>45481.0</v>
       </c>
       <c r="D478" t="n">
         <v>1.0</v>
@@ -6834,7 +6834,7 @@
         <v>2024.0</v>
       </c>
       <c r="C479" t="n" s="2">
-        <v>45551.0</v>
+        <v>45516.0</v>
       </c>
       <c r="D479" t="n">
         <v>1.0</v>
@@ -6848,7 +6848,7 @@
         <v>2024.0</v>
       </c>
       <c r="C480" t="n" s="2">
-        <v>45579.0</v>
+        <v>45551.0</v>
       </c>
       <c r="D480" t="n">
         <v>1.0</v>
@@ -6862,7 +6862,7 @@
         <v>2024.0</v>
       </c>
       <c r="C481" t="n" s="2">
-        <v>45614.0</v>
+        <v>45579.0</v>
       </c>
       <c r="D481" t="n">
         <v>1.0</v>
@@ -6876,10 +6876,10 @@
         <v>2024.0</v>
       </c>
       <c r="C482" t="n" s="2">
-        <v>45635.0</v>
+        <v>45614.0</v>
       </c>
       <c r="D482" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="483">
@@ -6890,10 +6890,10 @@
         <v>2024.0</v>
       </c>
       <c r="C483" t="n" s="2">
-        <v>45642.0</v>
+        <v>45635.0</v>
       </c>
       <c r="D483" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="484">
@@ -6904,10 +6904,10 @@
         <v>2024.0</v>
       </c>
       <c r="C484" t="n" s="2">
-        <v>45649.0</v>
+        <v>45642.0</v>
       </c>
       <c r="D484" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="485">
@@ -6918,10 +6918,10 @@
         <v>2024.0</v>
       </c>
       <c r="C485" t="n" s="2">
-        <v>45656.0</v>
+        <v>45649.0</v>
       </c>
       <c r="D485" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="486">
@@ -6929,13 +6929,13 @@
         <v>7</v>
       </c>
       <c r="B486" t="n">
-        <v>2025.0</v>
+        <v>2024.0</v>
       </c>
       <c r="C486" t="n" s="2">
-        <v>45665.0</v>
+        <v>45656.0</v>
       </c>
       <c r="D486" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="487">
@@ -6946,10 +6946,10 @@
         <v>2025.0</v>
       </c>
       <c r="C487" t="n" s="2">
-        <v>45672.0</v>
+        <v>45665.0</v>
       </c>
       <c r="D487" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="488">
@@ -6960,7 +6960,7 @@
         <v>2025.0</v>
       </c>
       <c r="C488" t="n" s="2">
-        <v>45686.0</v>
+        <v>45672.0</v>
       </c>
       <c r="D488" t="n">
         <v>2.0</v>
@@ -6974,10 +6974,10 @@
         <v>2025.0</v>
       </c>
       <c r="C489" t="n" s="2">
-        <v>45693.0</v>
+        <v>45686.0</v>
       </c>
       <c r="D489" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="490">
@@ -6988,10 +6988,10 @@
         <v>2025.0</v>
       </c>
       <c r="C490" t="n" s="2">
-        <v>45700.0</v>
+        <v>45693.0</v>
       </c>
       <c r="D490" t="n">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="491">
@@ -7002,10 +7002,10 @@
         <v>2025.0</v>
       </c>
       <c r="C491" t="n" s="2">
-        <v>45707.0</v>
+        <v>45700.0</v>
       </c>
       <c r="D491" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="492">
@@ -7016,10 +7016,10 @@
         <v>2025.0</v>
       </c>
       <c r="C492" t="n" s="2">
-        <v>45714.0</v>
+        <v>45707.0</v>
       </c>
       <c r="D492" t="n">
-        <v>8.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="493">
@@ -7030,10 +7030,10 @@
         <v>2025.0</v>
       </c>
       <c r="C493" t="n" s="2">
-        <v>45721.0</v>
+        <v>45714.0</v>
       </c>
       <c r="D493" t="n">
-        <v>11.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="494">
@@ -7044,10 +7044,10 @@
         <v>2025.0</v>
       </c>
       <c r="C494" t="n" s="2">
-        <v>45728.0</v>
+        <v>45721.0</v>
       </c>
       <c r="D494" t="n">
-        <v>6.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="495">
@@ -7058,10 +7058,10 @@
         <v>2025.0</v>
       </c>
       <c r="C495" t="n" s="2">
-        <v>45735.0</v>
+        <v>45728.0</v>
       </c>
       <c r="D495" t="n">
-        <v>19.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="496">
@@ -7072,10 +7072,10 @@
         <v>2025.0</v>
       </c>
       <c r="C496" t="n" s="2">
-        <v>45742.0</v>
+        <v>45735.0</v>
       </c>
       <c r="D496" t="n">
-        <v>17.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="497">
@@ -7086,10 +7086,10 @@
         <v>2025.0</v>
       </c>
       <c r="C497" t="n" s="2">
-        <v>45749.0</v>
+        <v>45742.0</v>
       </c>
       <c r="D497" t="n">
-        <v>5.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="498">
@@ -7100,10 +7100,10 @@
         <v>2025.0</v>
       </c>
       <c r="C498" t="n" s="2">
-        <v>45756.0</v>
+        <v>45749.0</v>
       </c>
       <c r="D498" t="n">
-        <v>9.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="499">
@@ -7114,10 +7114,10 @@
         <v>2025.0</v>
       </c>
       <c r="C499" t="n" s="2">
-        <v>45763.0</v>
+        <v>45756.0</v>
       </c>
       <c r="D499" t="n">
-        <v>1.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="500">
@@ -7128,7 +7128,7 @@
         <v>2025.0</v>
       </c>
       <c r="C500" t="n" s="2">
-        <v>45770.0</v>
+        <v>45763.0</v>
       </c>
       <c r="D500" t="n">
         <v>1.0</v>
@@ -7142,10 +7142,10 @@
         <v>2025.0</v>
       </c>
       <c r="C501" t="n" s="2">
-        <v>45784.0</v>
+        <v>45770.0</v>
       </c>
       <c r="D501" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="502">
@@ -7156,10 +7156,10 @@
         <v>2025.0</v>
       </c>
       <c r="C502" t="n" s="2">
-        <v>45791.0</v>
+        <v>45784.0</v>
       </c>
       <c r="D502" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="503">
@@ -7170,10 +7170,10 @@
         <v>2025.0</v>
       </c>
       <c r="C503" t="n" s="2">
-        <v>45805.0</v>
+        <v>45791.0</v>
       </c>
       <c r="D503" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="504">
@@ -7184,10 +7184,10 @@
         <v>2025.0</v>
       </c>
       <c r="C504" t="n" s="2">
-        <v>45826.0</v>
+        <v>45805.0</v>
       </c>
       <c r="D504" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="505">
@@ -7198,7 +7198,7 @@
         <v>2025.0</v>
       </c>
       <c r="C505" t="n" s="2">
-        <v>45861.0</v>
+        <v>45826.0</v>
       </c>
       <c r="D505" t="n">
         <v>2.0</v>
@@ -7212,10 +7212,10 @@
         <v>2025.0</v>
       </c>
       <c r="C506" t="n" s="2">
-        <v>45868.0</v>
+        <v>45861.0</v>
       </c>
       <c r="D506" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="507">
@@ -7226,7 +7226,7 @@
         <v>2025.0</v>
       </c>
       <c r="C507" t="n" s="2">
-        <v>45889.0</v>
+        <v>45868.0</v>
       </c>
       <c r="D507" t="n">
         <v>1.0</v>
@@ -7240,7 +7240,7 @@
         <v>2025.0</v>
       </c>
       <c r="C508" t="n" s="2">
-        <v>45924.0</v>
+        <v>45889.0</v>
       </c>
       <c r="D508" t="n">
         <v>1.0</v>
@@ -7254,7 +7254,7 @@
         <v>2025.0</v>
       </c>
       <c r="C509" t="n" s="2">
-        <v>45945.0</v>
+        <v>45924.0</v>
       </c>
       <c r="D509" t="n">
         <v>1.0</v>
@@ -7268,10 +7268,10 @@
         <v>2025.0</v>
       </c>
       <c r="C510" t="n" s="2">
-        <v>45959.0</v>
+        <v>45945.0</v>
       </c>
       <c r="D510" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="511">
@@ -7282,7 +7282,7 @@
         <v>2025.0</v>
       </c>
       <c r="C511" t="n" s="2">
-        <v>46001.0</v>
+        <v>45959.0</v>
       </c>
       <c r="D511" t="n">
         <v>2.0</v>
@@ -7296,10 +7296,10 @@
         <v>2025.0</v>
       </c>
       <c r="C512" t="n" s="2">
-        <v>46008.0</v>
+        <v>46001.0</v>
       </c>
       <c r="D512" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="513">
@@ -7310,7 +7310,7 @@
         <v>2025.0</v>
       </c>
       <c r="C513" t="n" s="2">
-        <v>46022.0</v>
+        <v>46008.0</v>
       </c>
       <c r="D513" t="n">
         <v>1.0</v>
@@ -7321,10 +7321,10 @@
         <v>7</v>
       </c>
       <c r="B514" t="n">
-        <v>2026.0</v>
+        <v>2025.0</v>
       </c>
       <c r="C514" t="n" s="2">
-        <v>46030.0</v>
+        <v>46022.0</v>
       </c>
       <c r="D514" t="n">
         <v>1.0</v>
@@ -7338,7 +7338,7 @@
         <v>2026.0</v>
       </c>
       <c r="C515" t="n" s="2">
-        <v>46051.0</v>
+        <v>46030.0</v>
       </c>
       <c r="D515" t="n">
         <v>1.0</v>
@@ -7352,7 +7352,7 @@
         <v>2026.0</v>
       </c>
       <c r="C516" t="n" s="2">
-        <v>46058.0</v>
+        <v>46051.0</v>
       </c>
       <c r="D516" t="n">
         <v>1.0</v>
@@ -7366,10 +7366,10 @@
         <v>2026.0</v>
       </c>
       <c r="C517" t="n" s="2">
-        <v>46065.0</v>
+        <v>46058.0</v>
       </c>
       <c r="D517" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="518">
@@ -7380,24 +7380,24 @@
         <v>2026.0</v>
       </c>
       <c r="C518" t="n" s="2">
-        <v>46135.0</v>
+        <v>46065.0</v>
       </c>
       <c r="D518" t="n">
-        <v>8.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B519" t="n">
-        <v>2024.0</v>
+        <v>2026.0</v>
       </c>
       <c r="C519" t="n" s="2">
-        <v>45495.0</v>
+        <v>46135.0</v>
       </c>
       <c r="D519" t="n">
-        <v>1.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="520">
@@ -7408,10 +7408,10 @@
         <v>2024.0</v>
       </c>
       <c r="C520" t="n" s="2">
-        <v>45502.0</v>
+        <v>45495.0</v>
       </c>
       <c r="D520" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="521">
@@ -7419,13 +7419,13 @@
         <v>8</v>
       </c>
       <c r="B521" t="n">
-        <v>2025.0</v>
+        <v>2024.0</v>
       </c>
       <c r="C521" t="n" s="2">
-        <v>45665.0</v>
+        <v>45502.0</v>
       </c>
       <c r="D521" t="n">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="522">
@@ -7436,10 +7436,10 @@
         <v>2025.0</v>
       </c>
       <c r="C522" t="n" s="2">
-        <v>45672.0</v>
+        <v>45665.0</v>
       </c>
       <c r="D522" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="523">
@@ -7450,10 +7450,10 @@
         <v>2025.0</v>
       </c>
       <c r="C523" t="n" s="2">
-        <v>45679.0</v>
+        <v>45672.0</v>
       </c>
       <c r="D523" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="524">
@@ -7464,10 +7464,10 @@
         <v>2025.0</v>
       </c>
       <c r="C524" t="n" s="2">
-        <v>45686.0</v>
+        <v>45679.0</v>
       </c>
       <c r="D524" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="525">
@@ -7478,10 +7478,10 @@
         <v>2025.0</v>
       </c>
       <c r="C525" t="n" s="2">
-        <v>45693.0</v>
+        <v>45686.0</v>
       </c>
       <c r="D525" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="526">
@@ -7492,10 +7492,10 @@
         <v>2025.0</v>
       </c>
       <c r="C526" t="n" s="2">
-        <v>45700.0</v>
+        <v>45693.0</v>
       </c>
       <c r="D526" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="527">
@@ -7506,10 +7506,10 @@
         <v>2025.0</v>
       </c>
       <c r="C527" t="n" s="2">
-        <v>45707.0</v>
+        <v>45700.0</v>
       </c>
       <c r="D527" t="n">
-        <v>7.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="528">
@@ -7520,10 +7520,10 @@
         <v>2025.0</v>
       </c>
       <c r="C528" t="n" s="2">
-        <v>45714.0</v>
+        <v>45707.0</v>
       </c>
       <c r="D528" t="n">
-        <v>3.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="529">
@@ -7534,10 +7534,10 @@
         <v>2025.0</v>
       </c>
       <c r="C529" t="n" s="2">
-        <v>45721.0</v>
+        <v>45714.0</v>
       </c>
       <c r="D529" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="530">
@@ -7548,10 +7548,10 @@
         <v>2025.0</v>
       </c>
       <c r="C530" t="n" s="2">
-        <v>45728.0</v>
+        <v>45721.0</v>
       </c>
       <c r="D530" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="531">
@@ -7562,7 +7562,7 @@
         <v>2025.0</v>
       </c>
       <c r="C531" t="n" s="2">
-        <v>45742.0</v>
+        <v>45728.0</v>
       </c>
       <c r="D531" t="n">
         <v>1.0</v>
@@ -7576,7 +7576,7 @@
         <v>2025.0</v>
       </c>
       <c r="C532" t="n" s="2">
-        <v>45749.0</v>
+        <v>45742.0</v>
       </c>
       <c r="D532" t="n">
         <v>1.0</v>
@@ -7590,7 +7590,7 @@
         <v>2025.0</v>
       </c>
       <c r="C533" t="n" s="2">
-        <v>45763.0</v>
+        <v>45749.0</v>
       </c>
       <c r="D533" t="n">
         <v>1.0</v>
@@ -7604,10 +7604,10 @@
         <v>2025.0</v>
       </c>
       <c r="C534" t="n" s="2">
-        <v>45777.0</v>
+        <v>45763.0</v>
       </c>
       <c r="D534" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="535">
@@ -7618,10 +7618,10 @@
         <v>2025.0</v>
       </c>
       <c r="C535" t="n" s="2">
-        <v>45784.0</v>
+        <v>45777.0</v>
       </c>
       <c r="D535" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="536">
@@ -7632,7 +7632,7 @@
         <v>2025.0</v>
       </c>
       <c r="C536" t="n" s="2">
-        <v>45798.0</v>
+        <v>45784.0</v>
       </c>
       <c r="D536" t="n">
         <v>1.0</v>
@@ -7646,7 +7646,7 @@
         <v>2025.0</v>
       </c>
       <c r="C537" t="n" s="2">
-        <v>45805.0</v>
+        <v>45798.0</v>
       </c>
       <c r="D537" t="n">
         <v>1.0</v>
@@ -7660,10 +7660,10 @@
         <v>2025.0</v>
       </c>
       <c r="C538" t="n" s="2">
-        <v>45812.0</v>
+        <v>45805.0</v>
       </c>
       <c r="D538" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="539">
@@ -7674,7 +7674,7 @@
         <v>2025.0</v>
       </c>
       <c r="C539" t="n" s="2">
-        <v>45819.0</v>
+        <v>45812.0</v>
       </c>
       <c r="D539" t="n">
         <v>2.0</v>
@@ -7688,7 +7688,7 @@
         <v>2025.0</v>
       </c>
       <c r="C540" t="n" s="2">
-        <v>45833.0</v>
+        <v>45819.0</v>
       </c>
       <c r="D540" t="n">
         <v>2.0</v>
@@ -7702,10 +7702,10 @@
         <v>2025.0</v>
       </c>
       <c r="C541" t="n" s="2">
-        <v>45847.0</v>
+        <v>45833.0</v>
       </c>
       <c r="D541" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="542">
@@ -7716,10 +7716,10 @@
         <v>2025.0</v>
       </c>
       <c r="C542" t="n" s="2">
-        <v>45854.0</v>
+        <v>45847.0</v>
       </c>
       <c r="D542" t="n">
-        <v>8.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="543">
@@ -7730,10 +7730,10 @@
         <v>2025.0</v>
       </c>
       <c r="C543" t="n" s="2">
-        <v>45861.0</v>
+        <v>45854.0</v>
       </c>
       <c r="D543" t="n">
-        <v>12.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="544">
@@ -7744,10 +7744,10 @@
         <v>2025.0</v>
       </c>
       <c r="C544" t="n" s="2">
-        <v>45868.0</v>
+        <v>45861.0</v>
       </c>
       <c r="D544" t="n">
-        <v>6.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="545">
@@ -7758,10 +7758,10 @@
         <v>2025.0</v>
       </c>
       <c r="C545" t="n" s="2">
-        <v>45875.0</v>
+        <v>45868.0</v>
       </c>
       <c r="D545" t="n">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="546">
@@ -7772,7 +7772,7 @@
         <v>2025.0</v>
       </c>
       <c r="C546" t="n" s="2">
-        <v>45896.0</v>
+        <v>45875.0</v>
       </c>
       <c r="D546" t="n">
         <v>1.0</v>
@@ -7786,7 +7786,7 @@
         <v>2025.0</v>
       </c>
       <c r="C547" t="n" s="2">
-        <v>45903.0</v>
+        <v>45896.0</v>
       </c>
       <c r="D547" t="n">
         <v>1.0</v>
@@ -7800,7 +7800,7 @@
         <v>2025.0</v>
       </c>
       <c r="C548" t="n" s="2">
-        <v>45931.0</v>
+        <v>45903.0</v>
       </c>
       <c r="D548" t="n">
         <v>1.0</v>
@@ -7814,10 +7814,10 @@
         <v>2025.0</v>
       </c>
       <c r="C549" t="n" s="2">
-        <v>45938.0</v>
+        <v>45931.0</v>
       </c>
       <c r="D549" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="550">
@@ -7828,10 +7828,10 @@
         <v>2025.0</v>
       </c>
       <c r="C550" t="n" s="2">
-        <v>45945.0</v>
+        <v>45938.0</v>
       </c>
       <c r="D550" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="551">
@@ -7842,7 +7842,7 @@
         <v>2025.0</v>
       </c>
       <c r="C551" t="n" s="2">
-        <v>45966.0</v>
+        <v>45945.0</v>
       </c>
       <c r="D551" t="n">
         <v>2.0</v>
@@ -7856,10 +7856,10 @@
         <v>2025.0</v>
       </c>
       <c r="C552" t="n" s="2">
-        <v>45973.0</v>
+        <v>45966.0</v>
       </c>
       <c r="D552" t="n">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="553">
@@ -7870,10 +7870,10 @@
         <v>2025.0</v>
       </c>
       <c r="C553" t="n" s="2">
-        <v>45980.0</v>
+        <v>45973.0</v>
       </c>
       <c r="D553" t="n">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="554">
@@ -7884,10 +7884,10 @@
         <v>2025.0</v>
       </c>
       <c r="C554" t="n" s="2">
-        <v>45987.0</v>
+        <v>45980.0</v>
       </c>
       <c r="D554" t="n">
-        <v>20.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="555">
@@ -7898,10 +7898,10 @@
         <v>2025.0</v>
       </c>
       <c r="C555" t="n" s="2">
-        <v>45994.0</v>
+        <v>45987.0</v>
       </c>
       <c r="D555" t="n">
-        <v>5.0</v>
+        <v>20.0</v>
       </c>
     </row>
     <row r="556">
@@ -7912,10 +7912,10 @@
         <v>2025.0</v>
       </c>
       <c r="C556" t="n" s="2">
-        <v>46001.0</v>
+        <v>45994.0</v>
       </c>
       <c r="D556" t="n">
-        <v>8.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="557">
@@ -7926,10 +7926,10 @@
         <v>2025.0</v>
       </c>
       <c r="C557" t="n" s="2">
-        <v>46008.0</v>
+        <v>46001.0</v>
       </c>
       <c r="D557" t="n">
-        <v>24.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="558">
@@ -7940,10 +7940,10 @@
         <v>2025.0</v>
       </c>
       <c r="C558" t="n" s="2">
-        <v>46015.0</v>
+        <v>46008.0</v>
       </c>
       <c r="D558" t="n">
-        <v>13.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="559">
@@ -7954,10 +7954,10 @@
         <v>2025.0</v>
       </c>
       <c r="C559" t="n" s="2">
-        <v>46022.0</v>
+        <v>46015.0</v>
       </c>
       <c r="D559" t="n">
-        <v>8.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="560">
@@ -7968,10 +7968,10 @@
         <v>2025.0</v>
       </c>
       <c r="C560" t="n" s="2">
-        <v>46029.0</v>
+        <v>46022.0</v>
       </c>
       <c r="D560" t="n">
-        <v>3.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="561">
@@ -7979,13 +7979,13 @@
         <v>8</v>
       </c>
       <c r="B561" t="n">
-        <v>2026.0</v>
+        <v>2025.0</v>
       </c>
       <c r="C561" t="n" s="2">
-        <v>46030.0</v>
+        <v>46029.0</v>
       </c>
       <c r="D561" t="n">
-        <v>24.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="562">
@@ -7996,10 +7996,10 @@
         <v>2026.0</v>
       </c>
       <c r="C562" t="n" s="2">
-        <v>46037.0</v>
+        <v>46030.0</v>
       </c>
       <c r="D562" t="n">
-        <v>22.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="563">
@@ -8010,10 +8010,10 @@
         <v>2026.0</v>
       </c>
       <c r="C563" t="n" s="2">
-        <v>46044.0</v>
+        <v>46037.0</v>
       </c>
       <c r="D563" t="n">
-        <v>27.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="564">
@@ -8024,10 +8024,10 @@
         <v>2026.0</v>
       </c>
       <c r="C564" t="n" s="2">
-        <v>46051.0</v>
+        <v>46044.0</v>
       </c>
       <c r="D564" t="n">
-        <v>18.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="565">
@@ -8038,10 +8038,10 @@
         <v>2026.0</v>
       </c>
       <c r="C565" t="n" s="2">
-        <v>46058.0</v>
+        <v>46051.0</v>
       </c>
       <c r="D565" t="n">
-        <v>25.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="566">
@@ -8052,10 +8052,10 @@
         <v>2026.0</v>
       </c>
       <c r="C566" t="n" s="2">
-        <v>46065.0</v>
+        <v>46058.0</v>
       </c>
       <c r="D566" t="n">
-        <v>22.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="567">
@@ -8066,10 +8066,10 @@
         <v>2026.0</v>
       </c>
       <c r="C567" t="n" s="2">
-        <v>46072.0</v>
+        <v>46065.0</v>
       </c>
       <c r="D567" t="n">
-        <v>13.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="568">
@@ -8080,10 +8080,10 @@
         <v>2026.0</v>
       </c>
       <c r="C568" t="n" s="2">
-        <v>46079.0</v>
+        <v>46072.0</v>
       </c>
       <c r="D568" t="n">
-        <v>24.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="569">
@@ -8094,10 +8094,10 @@
         <v>2026.0</v>
       </c>
       <c r="C569" t="n" s="2">
-        <v>46086.0</v>
+        <v>46079.0</v>
       </c>
       <c r="D569" t="n">
-        <v>26.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="570">
@@ -8108,10 +8108,10 @@
         <v>2026.0</v>
       </c>
       <c r="C570" t="n" s="2">
-        <v>46093.0</v>
+        <v>46086.0</v>
       </c>
       <c r="D570" t="n">
-        <v>33.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="571">
@@ -8122,10 +8122,10 @@
         <v>2026.0</v>
       </c>
       <c r="C571" t="n" s="2">
-        <v>46100.0</v>
+        <v>46093.0</v>
       </c>
       <c r="D571" t="n">
-        <v>25.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="572">
@@ -8136,10 +8136,10 @@
         <v>2026.0</v>
       </c>
       <c r="C572" t="n" s="2">
-        <v>46107.0</v>
+        <v>46100.0</v>
       </c>
       <c r="D572" t="n">
-        <v>31.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="573">
@@ -8150,10 +8150,10 @@
         <v>2026.0</v>
       </c>
       <c r="C573" t="n" s="2">
-        <v>46114.0</v>
+        <v>46107.0</v>
       </c>
       <c r="D573" t="n">
-        <v>10.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="574">
@@ -8164,10 +8164,10 @@
         <v>2026.0</v>
       </c>
       <c r="C574" t="n" s="2">
-        <v>46121.0</v>
+        <v>46114.0</v>
       </c>
       <c r="D574" t="n">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="575">
@@ -8178,10 +8178,10 @@
         <v>2026.0</v>
       </c>
       <c r="C575" t="n" s="2">
-        <v>46128.0</v>
+        <v>46121.0</v>
       </c>
       <c r="D575" t="n">
-        <v>15.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="576">
@@ -8192,10 +8192,10 @@
         <v>2026.0</v>
       </c>
       <c r="C576" t="n" s="2">
-        <v>46135.0</v>
+        <v>46128.0</v>
       </c>
       <c r="D576" t="n">
-        <v>23.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="577">
@@ -8206,10 +8206,38 @@
         <v>2026.0</v>
       </c>
       <c r="C577" t="n" s="2">
+        <v>46135.0</v>
+      </c>
+      <c r="D577" t="n">
+        <v>23.0</v>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="s">
+        <v>8</v>
+      </c>
+      <c r="B578" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C578" t="n" s="2">
         <v>46142.0</v>
       </c>
-      <c r="D577" t="n">
+      <c r="D578" t="n">
         <v>20.0</v>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="s">
+        <v>8</v>
+      </c>
+      <c r="B579" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C579" t="n" s="2">
+        <v>46149.0</v>
+      </c>
+      <c r="D579" t="n">
+        <v>1.0</v>
       </c>
     </row>
   </sheetData>
@@ -8235,7 +8263,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="n">
-        <v>45.0</v>
+        <v>46.0</v>
       </c>
     </row>
     <row r="3">
@@ -8251,7 +8279,7 @@
         <v>12</v>
       </c>
       <c r="B4" t="n">
-        <v>1252.0</v>
+        <v>1255.0</v>
       </c>
     </row>
     <row r="5">
@@ -8259,7 +8287,7 @@
         <v>13</v>
       </c>
       <c r="B5" t="n">
-        <v>2099.0</v>
+        <v>2101.0</v>
       </c>
     </row>
   </sheetData>
@@ -8357,7 +8385,7 @@
         <v>21</v>
       </c>
       <c r="C8" t="n">
-        <v>347.0</v>
+        <v>348.0</v>
       </c>
     </row>
     <row r="9">
@@ -8379,7 +8407,7 @@
         <v>19</v>
       </c>
       <c r="C10" t="n">
-        <v>145.0</v>
+        <v>146.0</v>
       </c>
     </row>
     <row r="11">
@@ -8390,7 +8418,7 @@
         <v>19</v>
       </c>
       <c r="C11" t="n">
-        <v>31.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="12">
@@ -8423,7 +8451,7 @@
         <v>19</v>
       </c>
       <c r="C14" t="n">
-        <v>404.0</v>
+        <v>406.0</v>
       </c>
     </row>
     <row r="15">
@@ -8434,7 +8462,7 @@
         <v>21</v>
       </c>
       <c r="C15" t="n">
-        <v>367.0</v>
+        <v>368.0</v>
       </c>
     </row>
     <row r="16">

--- a/Download/Focus_Positivi_ZR.xlsx
+++ b/Download/Focus_Positivi_ZR.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="623" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="622" uniqueCount="23">
   <si>
     <t>NOME_REGIONE</t>
   </si>
@@ -8223,21 +8223,7 @@
         <v>46142.0</v>
       </c>
       <c r="D578" t="n">
-        <v>20.0</v>
-      </c>
-    </row>
-    <row r="579">
-      <c r="A579" t="s">
-        <v>8</v>
-      </c>
-      <c r="B579" t="n">
-        <v>2026.0</v>
-      </c>
-      <c r="C579" t="n" s="2">
-        <v>46149.0</v>
-      </c>
-      <c r="D579" t="n">
-        <v>1.0</v>
+        <v>21.0</v>
       </c>
     </row>
   </sheetData>
@@ -8263,7 +8249,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="n">
-        <v>46.0</v>
+        <v>45.0</v>
       </c>
     </row>
     <row r="3">
@@ -8279,7 +8265,7 @@
         <v>12</v>
       </c>
       <c r="B4" t="n">
-        <v>1255.0</v>
+        <v>1256.0</v>
       </c>
     </row>
     <row r="5">
@@ -8418,7 +8404,7 @@
         <v>19</v>
       </c>
       <c r="C11" t="n">
-        <v>32.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="12">
@@ -8440,7 +8426,7 @@
         <v>22</v>
       </c>
       <c r="C13" t="n">
-        <v>39.0</v>
+        <v>40.0</v>
       </c>
     </row>
     <row r="14">

--- a/Download/Focus_Positivi_ZR.xlsx
+++ b/Download/Focus_Positivi_ZR.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="622" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="624" uniqueCount="23">
   <si>
     <t>NOME_REGIONE</t>
   </si>
@@ -4275,7 +4275,7 @@
         <v>46142.0</v>
       </c>
       <c r="D296" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="297">
@@ -8224,6 +8224,34 @@
       </c>
       <c r="D578" t="n">
         <v>21.0</v>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="s">
+        <v>8</v>
+      </c>
+      <c r="B579" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C579" t="n" s="2">
+        <v>46149.0</v>
+      </c>
+      <c r="D579" t="n">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="s">
+        <v>8</v>
+      </c>
+      <c r="B580" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C580" t="n" s="2">
+        <v>46156.0</v>
+      </c>
+      <c r="D580" t="n">
+        <v>4.0</v>
       </c>
     </row>
   </sheetData>
@@ -8249,7 +8277,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="n">
-        <v>45.0</v>
+        <v>51.0</v>
       </c>
     </row>
     <row r="3">
@@ -8265,7 +8293,7 @@
         <v>12</v>
       </c>
       <c r="B4" t="n">
-        <v>1256.0</v>
+        <v>1257.0</v>
       </c>
     </row>
     <row r="5">
@@ -8404,7 +8432,7 @@
         <v>19</v>
       </c>
       <c r="C11" t="n">
-        <v>31.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="12">
@@ -8437,7 +8465,7 @@
         <v>19</v>
       </c>
       <c r="C14" t="n">
-        <v>406.0</v>
+        <v>407.0</v>
       </c>
     </row>
     <row r="15">

--- a/Download/Focus_Positivi_ZR.xlsx
+++ b/Download/Focus_Positivi_ZR.xlsx
@@ -4280,13 +4280,13 @@
     </row>
     <row r="297">
       <c r="A297" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B297" t="n">
-        <v>2023.0</v>
+        <v>2026.0</v>
       </c>
       <c r="C297" t="n" s="2">
-        <v>45095.0</v>
+        <v>46149.0</v>
       </c>
       <c r="D297" t="n">
         <v>1.0</v>
@@ -4300,7 +4300,7 @@
         <v>2023.0</v>
       </c>
       <c r="C298" t="n" s="2">
-        <v>45102.0</v>
+        <v>45095.0</v>
       </c>
       <c r="D298" t="n">
         <v>1.0</v>
@@ -4314,7 +4314,7 @@
         <v>2023.0</v>
       </c>
       <c r="C299" t="n" s="2">
-        <v>45158.0</v>
+        <v>45102.0</v>
       </c>
       <c r="D299" t="n">
         <v>1.0</v>
@@ -4328,10 +4328,10 @@
         <v>2023.0</v>
       </c>
       <c r="C300" t="n" s="2">
-        <v>45207.0</v>
+        <v>45158.0</v>
       </c>
       <c r="D300" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="301">
@@ -4342,7 +4342,7 @@
         <v>2023.0</v>
       </c>
       <c r="C301" t="n" s="2">
-        <v>45214.0</v>
+        <v>45207.0</v>
       </c>
       <c r="D301" t="n">
         <v>3.0</v>
@@ -4356,10 +4356,10 @@
         <v>2023.0</v>
       </c>
       <c r="C302" t="n" s="2">
-        <v>45221.0</v>
+        <v>45214.0</v>
       </c>
       <c r="D302" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="303">
@@ -4370,7 +4370,7 @@
         <v>2023.0</v>
       </c>
       <c r="C303" t="n" s="2">
-        <v>45249.0</v>
+        <v>45221.0</v>
       </c>
       <c r="D303" t="n">
         <v>1.0</v>
@@ -4384,10 +4384,10 @@
         <v>2023.0</v>
       </c>
       <c r="C304" t="n" s="2">
-        <v>45256.0</v>
+        <v>45249.0</v>
       </c>
       <c r="D304" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="305">
@@ -4398,10 +4398,10 @@
         <v>2023.0</v>
       </c>
       <c r="C305" t="n" s="2">
-        <v>45263.0</v>
+        <v>45256.0</v>
       </c>
       <c r="D305" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="306">
@@ -4412,10 +4412,10 @@
         <v>2023.0</v>
       </c>
       <c r="C306" t="n" s="2">
-        <v>45270.0</v>
+        <v>45263.0</v>
       </c>
       <c r="D306" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="307">
@@ -4426,10 +4426,10 @@
         <v>2023.0</v>
       </c>
       <c r="C307" t="n" s="2">
-        <v>45277.0</v>
+        <v>45270.0</v>
       </c>
       <c r="D307" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="308">
@@ -4440,10 +4440,10 @@
         <v>2023.0</v>
       </c>
       <c r="C308" t="n" s="2">
-        <v>45284.0</v>
+        <v>45277.0</v>
       </c>
       <c r="D308" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="309">
@@ -4454,10 +4454,10 @@
         <v>2023.0</v>
       </c>
       <c r="C309" t="n" s="2">
-        <v>45291.0</v>
+        <v>45284.0</v>
       </c>
       <c r="D309" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="310">
@@ -4465,13 +4465,13 @@
         <v>6</v>
       </c>
       <c r="B310" t="n">
-        <v>2024.0</v>
+        <v>2023.0</v>
       </c>
       <c r="C310" t="n" s="2">
-        <v>45306.0</v>
+        <v>45291.0</v>
       </c>
       <c r="D310" t="n">
-        <v>7.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="311">
@@ -4482,10 +4482,10 @@
         <v>2024.0</v>
       </c>
       <c r="C311" t="n" s="2">
-        <v>45313.0</v>
+        <v>45306.0</v>
       </c>
       <c r="D311" t="n">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="312">
@@ -4496,10 +4496,10 @@
         <v>2024.0</v>
       </c>
       <c r="C312" t="n" s="2">
-        <v>45320.0</v>
+        <v>45313.0</v>
       </c>
       <c r="D312" t="n">
-        <v>19.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="313">
@@ -4510,10 +4510,10 @@
         <v>2024.0</v>
       </c>
       <c r="C313" t="n" s="2">
-        <v>45327.0</v>
+        <v>45320.0</v>
       </c>
       <c r="D313" t="n">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="314">
@@ -4524,10 +4524,10 @@
         <v>2024.0</v>
       </c>
       <c r="C314" t="n" s="2">
-        <v>45334.0</v>
+        <v>45327.0</v>
       </c>
       <c r="D314" t="n">
-        <v>9.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="315">
@@ -4538,10 +4538,10 @@
         <v>2024.0</v>
       </c>
       <c r="C315" t="n" s="2">
-        <v>45341.0</v>
+        <v>45334.0</v>
       </c>
       <c r="D315" t="n">
-        <v>12.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="316">
@@ -4552,7 +4552,7 @@
         <v>2024.0</v>
       </c>
       <c r="C316" t="n" s="2">
-        <v>45348.0</v>
+        <v>45341.0</v>
       </c>
       <c r="D316" t="n">
         <v>12.0</v>
@@ -4566,10 +4566,10 @@
         <v>2024.0</v>
       </c>
       <c r="C317" t="n" s="2">
-        <v>45355.0</v>
+        <v>45348.0</v>
       </c>
       <c r="D317" t="n">
-        <v>10.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="318">
@@ -4580,10 +4580,10 @@
         <v>2024.0</v>
       </c>
       <c r="C318" t="n" s="2">
-        <v>45362.0</v>
+        <v>45355.0</v>
       </c>
       <c r="D318" t="n">
-        <v>12.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="319">
@@ -4594,10 +4594,10 @@
         <v>2024.0</v>
       </c>
       <c r="C319" t="n" s="2">
-        <v>45369.0</v>
+        <v>45362.0</v>
       </c>
       <c r="D319" t="n">
-        <v>13.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="320">
@@ -4608,10 +4608,10 @@
         <v>2024.0</v>
       </c>
       <c r="C320" t="n" s="2">
-        <v>45376.0</v>
+        <v>45369.0</v>
       </c>
       <c r="D320" t="n">
-        <v>18.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="321">
@@ -4622,10 +4622,10 @@
         <v>2024.0</v>
       </c>
       <c r="C321" t="n" s="2">
-        <v>45383.0</v>
+        <v>45376.0</v>
       </c>
       <c r="D321" t="n">
-        <v>12.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="322">
@@ -4636,10 +4636,10 @@
         <v>2024.0</v>
       </c>
       <c r="C322" t="n" s="2">
-        <v>45390.0</v>
+        <v>45383.0</v>
       </c>
       <c r="D322" t="n">
-        <v>6.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="323">
@@ -4650,10 +4650,10 @@
         <v>2024.0</v>
       </c>
       <c r="C323" t="n" s="2">
-        <v>45397.0</v>
+        <v>45390.0</v>
       </c>
       <c r="D323" t="n">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="324">
@@ -4664,10 +4664,10 @@
         <v>2024.0</v>
       </c>
       <c r="C324" t="n" s="2">
-        <v>45404.0</v>
+        <v>45397.0</v>
       </c>
       <c r="D324" t="n">
-        <v>3.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="325">
@@ -4678,10 +4678,10 @@
         <v>2024.0</v>
       </c>
       <c r="C325" t="n" s="2">
-        <v>45411.0</v>
+        <v>45404.0</v>
       </c>
       <c r="D325" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="326">
@@ -4692,10 +4692,10 @@
         <v>2024.0</v>
       </c>
       <c r="C326" t="n" s="2">
-        <v>45418.0</v>
+        <v>45411.0</v>
       </c>
       <c r="D326" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="327">
@@ -4706,10 +4706,10 @@
         <v>2024.0</v>
       </c>
       <c r="C327" t="n" s="2">
-        <v>45425.0</v>
+        <v>45418.0</v>
       </c>
       <c r="D327" t="n">
-        <v>9.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="328">
@@ -4720,10 +4720,10 @@
         <v>2024.0</v>
       </c>
       <c r="C328" t="n" s="2">
-        <v>45432.0</v>
+        <v>45425.0</v>
       </c>
       <c r="D328" t="n">
-        <v>6.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="329">
@@ -4734,7 +4734,7 @@
         <v>2024.0</v>
       </c>
       <c r="C329" t="n" s="2">
-        <v>45439.0</v>
+        <v>45432.0</v>
       </c>
       <c r="D329" t="n">
         <v>6.0</v>
@@ -4748,10 +4748,10 @@
         <v>2024.0</v>
       </c>
       <c r="C330" t="n" s="2">
-        <v>45446.0</v>
+        <v>45439.0</v>
       </c>
       <c r="D330" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="331">
@@ -4762,10 +4762,10 @@
         <v>2024.0</v>
       </c>
       <c r="C331" t="n" s="2">
-        <v>45453.0</v>
+        <v>45446.0</v>
       </c>
       <c r="D331" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="332">
@@ -4776,7 +4776,7 @@
         <v>2024.0</v>
       </c>
       <c r="C332" t="n" s="2">
-        <v>45460.0</v>
+        <v>45453.0</v>
       </c>
       <c r="D332" t="n">
         <v>4.0</v>
@@ -4790,7 +4790,7 @@
         <v>2024.0</v>
       </c>
       <c r="C333" t="n" s="2">
-        <v>45467.0</v>
+        <v>45460.0</v>
       </c>
       <c r="D333" t="n">
         <v>4.0</v>
@@ -4804,10 +4804,10 @@
         <v>2024.0</v>
       </c>
       <c r="C334" t="n" s="2">
-        <v>45474.0</v>
+        <v>45467.0</v>
       </c>
       <c r="D334" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="335">
@@ -4818,10 +4818,10 @@
         <v>2024.0</v>
       </c>
       <c r="C335" t="n" s="2">
-        <v>45481.0</v>
+        <v>45474.0</v>
       </c>
       <c r="D335" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="336">
@@ -4832,10 +4832,10 @@
         <v>2024.0</v>
       </c>
       <c r="C336" t="n" s="2">
-        <v>45488.0</v>
+        <v>45481.0</v>
       </c>
       <c r="D336" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="337">
@@ -4846,10 +4846,10 @@
         <v>2024.0</v>
       </c>
       <c r="C337" t="n" s="2">
-        <v>45495.0</v>
+        <v>45488.0</v>
       </c>
       <c r="D337" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="338">
@@ -4860,10 +4860,10 @@
         <v>2024.0</v>
       </c>
       <c r="C338" t="n" s="2">
-        <v>45502.0</v>
+        <v>45495.0</v>
       </c>
       <c r="D338" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="339">
@@ -4874,10 +4874,10 @@
         <v>2024.0</v>
       </c>
       <c r="C339" t="n" s="2">
-        <v>45509.0</v>
+        <v>45502.0</v>
       </c>
       <c r="D339" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="340">
@@ -4888,7 +4888,7 @@
         <v>2024.0</v>
       </c>
       <c r="C340" t="n" s="2">
-        <v>45523.0</v>
+        <v>45509.0</v>
       </c>
       <c r="D340" t="n">
         <v>1.0</v>
@@ -4902,7 +4902,7 @@
         <v>2024.0</v>
       </c>
       <c r="C341" t="n" s="2">
-        <v>45551.0</v>
+        <v>45523.0</v>
       </c>
       <c r="D341" t="n">
         <v>1.0</v>
@@ -4916,7 +4916,7 @@
         <v>2024.0</v>
       </c>
       <c r="C342" t="n" s="2">
-        <v>45558.0</v>
+        <v>45551.0</v>
       </c>
       <c r="D342" t="n">
         <v>1.0</v>
@@ -4930,10 +4930,10 @@
         <v>2024.0</v>
       </c>
       <c r="C343" t="n" s="2">
-        <v>45572.0</v>
+        <v>45558.0</v>
       </c>
       <c r="D343" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="344">
@@ -4944,10 +4944,10 @@
         <v>2024.0</v>
       </c>
       <c r="C344" t="n" s="2">
-        <v>45593.0</v>
+        <v>45572.0</v>
       </c>
       <c r="D344" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="345">
@@ -4958,10 +4958,10 @@
         <v>2024.0</v>
       </c>
       <c r="C345" t="n" s="2">
-        <v>45614.0</v>
+        <v>45593.0</v>
       </c>
       <c r="D345" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="346">
@@ -4972,10 +4972,10 @@
         <v>2024.0</v>
       </c>
       <c r="C346" t="n" s="2">
-        <v>45621.0</v>
+        <v>45614.0</v>
       </c>
       <c r="D346" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="347">
@@ -4986,7 +4986,7 @@
         <v>2024.0</v>
       </c>
       <c r="C347" t="n" s="2">
-        <v>45635.0</v>
+        <v>45621.0</v>
       </c>
       <c r="D347" t="n">
         <v>1.0</v>
@@ -5000,7 +5000,7 @@
         <v>2024.0</v>
       </c>
       <c r="C348" t="n" s="2">
-        <v>45649.0</v>
+        <v>45635.0</v>
       </c>
       <c r="D348" t="n">
         <v>1.0</v>
@@ -5011,13 +5011,13 @@
         <v>6</v>
       </c>
       <c r="B349" t="n">
-        <v>2025.0</v>
+        <v>2024.0</v>
       </c>
       <c r="C349" t="n" s="2">
-        <v>45665.0</v>
+        <v>45649.0</v>
       </c>
       <c r="D349" t="n">
-        <v>9.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="350">
@@ -5028,10 +5028,10 @@
         <v>2025.0</v>
       </c>
       <c r="C350" t="n" s="2">
-        <v>45672.0</v>
+        <v>45665.0</v>
       </c>
       <c r="D350" t="n">
-        <v>3.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="351">
@@ -5042,10 +5042,10 @@
         <v>2025.0</v>
       </c>
       <c r="C351" t="n" s="2">
-        <v>45679.0</v>
+        <v>45672.0</v>
       </c>
       <c r="D351" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="352">
@@ -5056,10 +5056,10 @@
         <v>2025.0</v>
       </c>
       <c r="C352" t="n" s="2">
-        <v>45686.0</v>
+        <v>45679.0</v>
       </c>
       <c r="D352" t="n">
-        <v>8.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="353">
@@ -5070,10 +5070,10 @@
         <v>2025.0</v>
       </c>
       <c r="C353" t="n" s="2">
-        <v>45693.0</v>
+        <v>45686.0</v>
       </c>
       <c r="D353" t="n">
-        <v>3.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="354">
@@ -5084,10 +5084,10 @@
         <v>2025.0</v>
       </c>
       <c r="C354" t="n" s="2">
-        <v>45700.0</v>
+        <v>45693.0</v>
       </c>
       <c r="D354" t="n">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="355">
@@ -5098,10 +5098,10 @@
         <v>2025.0</v>
       </c>
       <c r="C355" t="n" s="2">
-        <v>45707.0</v>
+        <v>45700.0</v>
       </c>
       <c r="D355" t="n">
-        <v>8.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="356">
@@ -5112,10 +5112,10 @@
         <v>2025.0</v>
       </c>
       <c r="C356" t="n" s="2">
-        <v>45714.0</v>
+        <v>45707.0</v>
       </c>
       <c r="D356" t="n">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="357">
@@ -5126,10 +5126,10 @@
         <v>2025.0</v>
       </c>
       <c r="C357" t="n" s="2">
-        <v>45721.0</v>
+        <v>45714.0</v>
       </c>
       <c r="D357" t="n">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="358">
@@ -5140,10 +5140,10 @@
         <v>2025.0</v>
       </c>
       <c r="C358" t="n" s="2">
-        <v>45728.0</v>
+        <v>45721.0</v>
       </c>
       <c r="D358" t="n">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="359">
@@ -5154,10 +5154,10 @@
         <v>2025.0</v>
       </c>
       <c r="C359" t="n" s="2">
-        <v>45735.0</v>
+        <v>45728.0</v>
       </c>
       <c r="D359" t="n">
-        <v>4.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="360">
@@ -5168,10 +5168,10 @@
         <v>2025.0</v>
       </c>
       <c r="C360" t="n" s="2">
-        <v>45742.0</v>
+        <v>45735.0</v>
       </c>
       <c r="D360" t="n">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="361">
@@ -5182,10 +5182,10 @@
         <v>2025.0</v>
       </c>
       <c r="C361" t="n" s="2">
-        <v>45749.0</v>
+        <v>45742.0</v>
       </c>
       <c r="D361" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="362">
@@ -5196,10 +5196,10 @@
         <v>2025.0</v>
       </c>
       <c r="C362" t="n" s="2">
-        <v>45756.0</v>
+        <v>45749.0</v>
       </c>
       <c r="D362" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="363">
@@ -5210,10 +5210,10 @@
         <v>2025.0</v>
       </c>
       <c r="C363" t="n" s="2">
-        <v>45763.0</v>
+        <v>45756.0</v>
       </c>
       <c r="D363" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="364">
@@ -5224,7 +5224,7 @@
         <v>2025.0</v>
       </c>
       <c r="C364" t="n" s="2">
-        <v>45770.0</v>
+        <v>45763.0</v>
       </c>
       <c r="D364" t="n">
         <v>4.0</v>
@@ -5238,10 +5238,10 @@
         <v>2025.0</v>
       </c>
       <c r="C365" t="n" s="2">
-        <v>45777.0</v>
+        <v>45770.0</v>
       </c>
       <c r="D365" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="366">
@@ -5252,7 +5252,7 @@
         <v>2025.0</v>
       </c>
       <c r="C366" t="n" s="2">
-        <v>45784.0</v>
+        <v>45777.0</v>
       </c>
       <c r="D366" t="n">
         <v>1.0</v>
@@ -5266,7 +5266,7 @@
         <v>2025.0</v>
       </c>
       <c r="C367" t="n" s="2">
-        <v>45791.0</v>
+        <v>45784.0</v>
       </c>
       <c r="D367" t="n">
         <v>1.0</v>
@@ -5280,7 +5280,7 @@
         <v>2025.0</v>
       </c>
       <c r="C368" t="n" s="2">
-        <v>45840.0</v>
+        <v>45791.0</v>
       </c>
       <c r="D368" t="n">
         <v>1.0</v>
@@ -5294,7 +5294,7 @@
         <v>2025.0</v>
       </c>
       <c r="C369" t="n" s="2">
-        <v>46001.0</v>
+        <v>45840.0</v>
       </c>
       <c r="D369" t="n">
         <v>1.0</v>
@@ -5305,10 +5305,10 @@
         <v>6</v>
       </c>
       <c r="B370" t="n">
-        <v>2026.0</v>
+        <v>2025.0</v>
       </c>
       <c r="C370" t="n" s="2">
-        <v>46037.0</v>
+        <v>46001.0</v>
       </c>
       <c r="D370" t="n">
         <v>1.0</v>
@@ -5316,13 +5316,13 @@
     </row>
     <row r="371">
       <c r="A371" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B371" t="n">
-        <v>2021.0</v>
+        <v>2026.0</v>
       </c>
       <c r="C371" t="n" s="2">
-        <v>44561.0</v>
+        <v>46037.0</v>
       </c>
       <c r="D371" t="n">
         <v>1.0</v>
@@ -5333,10 +5333,10 @@
         <v>7</v>
       </c>
       <c r="B372" t="n">
-        <v>2022.0</v>
+        <v>2021.0</v>
       </c>
       <c r="C372" t="n" s="2">
-        <v>44569.0</v>
+        <v>44561.0</v>
       </c>
       <c r="D372" t="n">
         <v>1.0</v>
@@ -5350,10 +5350,10 @@
         <v>2022.0</v>
       </c>
       <c r="C373" t="n" s="2">
-        <v>44576.0</v>
+        <v>44569.0</v>
       </c>
       <c r="D373" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="374">
@@ -5364,10 +5364,10 @@
         <v>2022.0</v>
       </c>
       <c r="C374" t="n" s="2">
-        <v>44583.0</v>
+        <v>44576.0</v>
       </c>
       <c r="D374" t="n">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="375">
@@ -5378,10 +5378,10 @@
         <v>2022.0</v>
       </c>
       <c r="C375" t="n" s="2">
-        <v>44590.0</v>
+        <v>44583.0</v>
       </c>
       <c r="D375" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="376">
@@ -5392,10 +5392,10 @@
         <v>2022.0</v>
       </c>
       <c r="C376" t="n" s="2">
-        <v>44604.0</v>
+        <v>44590.0</v>
       </c>
       <c r="D376" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="377">
@@ -5406,7 +5406,7 @@
         <v>2022.0</v>
       </c>
       <c r="C377" t="n" s="2">
-        <v>44611.0</v>
+        <v>44604.0</v>
       </c>
       <c r="D377" t="n">
         <v>3.0</v>
@@ -5420,10 +5420,10 @@
         <v>2022.0</v>
       </c>
       <c r="C378" t="n" s="2">
-        <v>44618.0</v>
+        <v>44611.0</v>
       </c>
       <c r="D378" t="n">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="379">
@@ -5434,7 +5434,7 @@
         <v>2022.0</v>
       </c>
       <c r="C379" t="n" s="2">
-        <v>44625.0</v>
+        <v>44618.0</v>
       </c>
       <c r="D379" t="n">
         <v>5.0</v>
@@ -5448,10 +5448,10 @@
         <v>2022.0</v>
       </c>
       <c r="C380" t="n" s="2">
-        <v>44632.0</v>
+        <v>44625.0</v>
       </c>
       <c r="D380" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="381">
@@ -5462,10 +5462,10 @@
         <v>2022.0</v>
       </c>
       <c r="C381" t="n" s="2">
-        <v>44639.0</v>
+        <v>44632.0</v>
       </c>
       <c r="D381" t="n">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="382">
@@ -5476,10 +5476,10 @@
         <v>2022.0</v>
       </c>
       <c r="C382" t="n" s="2">
-        <v>44646.0</v>
+        <v>44639.0</v>
       </c>
       <c r="D382" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="383">
@@ -5490,10 +5490,10 @@
         <v>2022.0</v>
       </c>
       <c r="C383" t="n" s="2">
-        <v>44653.0</v>
+        <v>44646.0</v>
       </c>
       <c r="D383" t="n">
-        <v>9.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="384">
@@ -5504,10 +5504,10 @@
         <v>2022.0</v>
       </c>
       <c r="C384" t="n" s="2">
-        <v>44660.0</v>
+        <v>44653.0</v>
       </c>
       <c r="D384" t="n">
-        <v>6.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="385">
@@ -5518,10 +5518,10 @@
         <v>2022.0</v>
       </c>
       <c r="C385" t="n" s="2">
-        <v>44667.0</v>
+        <v>44660.0</v>
       </c>
       <c r="D385" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="386">
@@ -5532,10 +5532,10 @@
         <v>2022.0</v>
       </c>
       <c r="C386" t="n" s="2">
-        <v>44674.0</v>
+        <v>44667.0</v>
       </c>
       <c r="D386" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="387">
@@ -5546,10 +5546,10 @@
         <v>2022.0</v>
       </c>
       <c r="C387" t="n" s="2">
-        <v>44681.0</v>
+        <v>44674.0</v>
       </c>
       <c r="D387" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="388">
@@ -5560,10 +5560,10 @@
         <v>2022.0</v>
       </c>
       <c r="C388" t="n" s="2">
-        <v>44688.0</v>
+        <v>44681.0</v>
       </c>
       <c r="D388" t="n">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="389">
@@ -5574,10 +5574,10 @@
         <v>2022.0</v>
       </c>
       <c r="C389" t="n" s="2">
-        <v>44695.0</v>
+        <v>44688.0</v>
       </c>
       <c r="D389" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="390">
@@ -5588,10 +5588,10 @@
         <v>2022.0</v>
       </c>
       <c r="C390" t="n" s="2">
-        <v>44702.0</v>
+        <v>44695.0</v>
       </c>
       <c r="D390" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="391">
@@ -5602,10 +5602,10 @@
         <v>2022.0</v>
       </c>
       <c r="C391" t="n" s="2">
-        <v>44709.0</v>
+        <v>44702.0</v>
       </c>
       <c r="D391" t="n">
-        <v>8.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="392">
@@ -5616,10 +5616,10 @@
         <v>2022.0</v>
       </c>
       <c r="C392" t="n" s="2">
-        <v>44716.0</v>
+        <v>44709.0</v>
       </c>
       <c r="D392" t="n">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="393">
@@ -5630,10 +5630,10 @@
         <v>2022.0</v>
       </c>
       <c r="C393" t="n" s="2">
-        <v>44723.0</v>
+        <v>44716.0</v>
       </c>
       <c r="D393" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="394">
@@ -5644,10 +5644,10 @@
         <v>2022.0</v>
       </c>
       <c r="C394" t="n" s="2">
-        <v>44730.0</v>
+        <v>44723.0</v>
       </c>
       <c r="D394" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="395">
@@ -5658,7 +5658,7 @@
         <v>2022.0</v>
       </c>
       <c r="C395" t="n" s="2">
-        <v>44737.0</v>
+        <v>44730.0</v>
       </c>
       <c r="D395" t="n">
         <v>4.0</v>
@@ -5672,10 +5672,10 @@
         <v>2022.0</v>
       </c>
       <c r="C396" t="n" s="2">
-        <v>44744.0</v>
+        <v>44737.0</v>
       </c>
       <c r="D396" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="397">
@@ -5686,10 +5686,10 @@
         <v>2022.0</v>
       </c>
       <c r="C397" t="n" s="2">
-        <v>44751.0</v>
+        <v>44744.0</v>
       </c>
       <c r="D397" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="398">
@@ -5700,10 +5700,10 @@
         <v>2022.0</v>
       </c>
       <c r="C398" t="n" s="2">
-        <v>44758.0</v>
+        <v>44751.0</v>
       </c>
       <c r="D398" t="n">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="399">
@@ -5714,10 +5714,10 @@
         <v>2022.0</v>
       </c>
       <c r="C399" t="n" s="2">
-        <v>44765.0</v>
+        <v>44758.0</v>
       </c>
       <c r="D399" t="n">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="400">
@@ -5728,10 +5728,10 @@
         <v>2022.0</v>
       </c>
       <c r="C400" t="n" s="2">
-        <v>44779.0</v>
+        <v>44765.0</v>
       </c>
       <c r="D400" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="401">
@@ -5742,10 +5742,10 @@
         <v>2022.0</v>
       </c>
       <c r="C401" t="n" s="2">
-        <v>44786.0</v>
+        <v>44779.0</v>
       </c>
       <c r="D401" t="n">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="402">
@@ -5756,10 +5756,10 @@
         <v>2022.0</v>
       </c>
       <c r="C402" t="n" s="2">
-        <v>44863.0</v>
+        <v>44786.0</v>
       </c>
       <c r="D402" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="403">
@@ -5770,10 +5770,10 @@
         <v>2022.0</v>
       </c>
       <c r="C403" t="n" s="2">
-        <v>44870.0</v>
+        <v>44863.0</v>
       </c>
       <c r="D403" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="404">
@@ -5784,10 +5784,10 @@
         <v>2022.0</v>
       </c>
       <c r="C404" t="n" s="2">
-        <v>44884.0</v>
+        <v>44870.0</v>
       </c>
       <c r="D404" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="405">
@@ -5798,7 +5798,7 @@
         <v>2022.0</v>
       </c>
       <c r="C405" t="n" s="2">
-        <v>44891.0</v>
+        <v>44884.0</v>
       </c>
       <c r="D405" t="n">
         <v>2.0</v>
@@ -5812,10 +5812,10 @@
         <v>2022.0</v>
       </c>
       <c r="C406" t="n" s="2">
-        <v>44898.0</v>
+        <v>44891.0</v>
       </c>
       <c r="D406" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="407">
@@ -5826,10 +5826,10 @@
         <v>2022.0</v>
       </c>
       <c r="C407" t="n" s="2">
-        <v>44912.0</v>
+        <v>44898.0</v>
       </c>
       <c r="D407" t="n">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="408">
@@ -5840,10 +5840,10 @@
         <v>2022.0</v>
       </c>
       <c r="C408" t="n" s="2">
-        <v>44919.0</v>
+        <v>44912.0</v>
       </c>
       <c r="D408" t="n">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="409">
@@ -5854,10 +5854,10 @@
         <v>2022.0</v>
       </c>
       <c r="C409" t="n" s="2">
-        <v>44926.0</v>
+        <v>44919.0</v>
       </c>
       <c r="D409" t="n">
-        <v>12.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="410">
@@ -5865,13 +5865,13 @@
         <v>7</v>
       </c>
       <c r="B410" t="n">
-        <v>2023.0</v>
+        <v>2022.0</v>
       </c>
       <c r="C410" t="n" s="2">
-        <v>44934.0</v>
+        <v>44926.0</v>
       </c>
       <c r="D410" t="n">
-        <v>4.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="411">
@@ -5882,10 +5882,10 @@
         <v>2023.0</v>
       </c>
       <c r="C411" t="n" s="2">
-        <v>44941.0</v>
+        <v>44934.0</v>
       </c>
       <c r="D411" t="n">
-        <v>16.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="412">
@@ -5896,10 +5896,10 @@
         <v>2023.0</v>
       </c>
       <c r="C412" t="n" s="2">
-        <v>44948.0</v>
+        <v>44941.0</v>
       </c>
       <c r="D412" t="n">
-        <v>5.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="413">
@@ -5910,10 +5910,10 @@
         <v>2023.0</v>
       </c>
       <c r="C413" t="n" s="2">
-        <v>44955.0</v>
+        <v>44948.0</v>
       </c>
       <c r="D413" t="n">
-        <v>19.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="414">
@@ -5924,10 +5924,10 @@
         <v>2023.0</v>
       </c>
       <c r="C414" t="n" s="2">
-        <v>44962.0</v>
+        <v>44955.0</v>
       </c>
       <c r="D414" t="n">
-        <v>22.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="415">
@@ -5938,10 +5938,10 @@
         <v>2023.0</v>
       </c>
       <c r="C415" t="n" s="2">
-        <v>44969.0</v>
+        <v>44962.0</v>
       </c>
       <c r="D415" t="n">
-        <v>9.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="416">
@@ -5952,10 +5952,10 @@
         <v>2023.0</v>
       </c>
       <c r="C416" t="n" s="2">
-        <v>44976.0</v>
+        <v>44969.0</v>
       </c>
       <c r="D416" t="n">
-        <v>22.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="417">
@@ -5966,10 +5966,10 @@
         <v>2023.0</v>
       </c>
       <c r="C417" t="n" s="2">
-        <v>44983.0</v>
+        <v>44976.0</v>
       </c>
       <c r="D417" t="n">
-        <v>29.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="418">
@@ -5980,10 +5980,10 @@
         <v>2023.0</v>
       </c>
       <c r="C418" t="n" s="2">
-        <v>44990.0</v>
+        <v>44983.0</v>
       </c>
       <c r="D418" t="n">
-        <v>5.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="419">
@@ -5994,10 +5994,10 @@
         <v>2023.0</v>
       </c>
       <c r="C419" t="n" s="2">
-        <v>44997.0</v>
+        <v>44990.0</v>
       </c>
       <c r="D419" t="n">
-        <v>24.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="420">
@@ -6008,10 +6008,10 @@
         <v>2023.0</v>
       </c>
       <c r="C420" t="n" s="2">
-        <v>45004.0</v>
+        <v>44997.0</v>
       </c>
       <c r="D420" t="n">
-        <v>8.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="421">
@@ -6022,10 +6022,10 @@
         <v>2023.0</v>
       </c>
       <c r="C421" t="n" s="2">
-        <v>45011.0</v>
+        <v>45004.0</v>
       </c>
       <c r="D421" t="n">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="422">
@@ -6036,10 +6036,10 @@
         <v>2023.0</v>
       </c>
       <c r="C422" t="n" s="2">
-        <v>45018.0</v>
+        <v>45011.0</v>
       </c>
       <c r="D422" t="n">
-        <v>18.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="423">
@@ -6050,10 +6050,10 @@
         <v>2023.0</v>
       </c>
       <c r="C423" t="n" s="2">
-        <v>45025.0</v>
+        <v>45018.0</v>
       </c>
       <c r="D423" t="n">
-        <v>13.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="424">
@@ -6064,10 +6064,10 @@
         <v>2023.0</v>
       </c>
       <c r="C424" t="n" s="2">
-        <v>45032.0</v>
+        <v>45025.0</v>
       </c>
       <c r="D424" t="n">
-        <v>18.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="425">
@@ -6078,10 +6078,10 @@
         <v>2023.0</v>
       </c>
       <c r="C425" t="n" s="2">
-        <v>45039.0</v>
+        <v>45032.0</v>
       </c>
       <c r="D425" t="n">
-        <v>15.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="426">
@@ -6092,10 +6092,10 @@
         <v>2023.0</v>
       </c>
       <c r="C426" t="n" s="2">
-        <v>45046.0</v>
+        <v>45039.0</v>
       </c>
       <c r="D426" t="n">
-        <v>12.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="427">
@@ -6106,10 +6106,10 @@
         <v>2023.0</v>
       </c>
       <c r="C427" t="n" s="2">
-        <v>45053.0</v>
+        <v>45046.0</v>
       </c>
       <c r="D427" t="n">
-        <v>6.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="428">
@@ -6120,10 +6120,10 @@
         <v>2023.0</v>
       </c>
       <c r="C428" t="n" s="2">
-        <v>45060.0</v>
+        <v>45053.0</v>
       </c>
       <c r="D428" t="n">
-        <v>11.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="429">
@@ -6134,10 +6134,10 @@
         <v>2023.0</v>
       </c>
       <c r="C429" t="n" s="2">
-        <v>45067.0</v>
+        <v>45060.0</v>
       </c>
       <c r="D429" t="n">
-        <v>8.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="430">
@@ -6148,7 +6148,7 @@
         <v>2023.0</v>
       </c>
       <c r="C430" t="n" s="2">
-        <v>45074.0</v>
+        <v>45067.0</v>
       </c>
       <c r="D430" t="n">
         <v>8.0</v>
@@ -6162,10 +6162,10 @@
         <v>2023.0</v>
       </c>
       <c r="C431" t="n" s="2">
-        <v>45081.0</v>
+        <v>45074.0</v>
       </c>
       <c r="D431" t="n">
-        <v>5.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="432">
@@ -6176,10 +6176,10 @@
         <v>2023.0</v>
       </c>
       <c r="C432" t="n" s="2">
-        <v>45088.0</v>
+        <v>45081.0</v>
       </c>
       <c r="D432" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="433">
@@ -6190,10 +6190,10 @@
         <v>2023.0</v>
       </c>
       <c r="C433" t="n" s="2">
-        <v>45095.0</v>
+        <v>45088.0</v>
       </c>
       <c r="D433" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="434">
@@ -6204,10 +6204,10 @@
         <v>2023.0</v>
       </c>
       <c r="C434" t="n" s="2">
-        <v>45102.0</v>
+        <v>45095.0</v>
       </c>
       <c r="D434" t="n">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="435">
@@ -6218,10 +6218,10 @@
         <v>2023.0</v>
       </c>
       <c r="C435" t="n" s="2">
-        <v>45109.0</v>
+        <v>45102.0</v>
       </c>
       <c r="D435" t="n">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="436">
@@ -6232,10 +6232,10 @@
         <v>2023.0</v>
       </c>
       <c r="C436" t="n" s="2">
-        <v>45116.0</v>
+        <v>45109.0</v>
       </c>
       <c r="D436" t="n">
-        <v>3.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="437">
@@ -6246,10 +6246,10 @@
         <v>2023.0</v>
       </c>
       <c r="C437" t="n" s="2">
-        <v>45123.0</v>
+        <v>45116.0</v>
       </c>
       <c r="D437" t="n">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="438">
@@ -6260,7 +6260,7 @@
         <v>2023.0</v>
       </c>
       <c r="C438" t="n" s="2">
-        <v>45130.0</v>
+        <v>45123.0</v>
       </c>
       <c r="D438" t="n">
         <v>6.0</v>
@@ -6274,10 +6274,10 @@
         <v>2023.0</v>
       </c>
       <c r="C439" t="n" s="2">
-        <v>45137.0</v>
+        <v>45130.0</v>
       </c>
       <c r="D439" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="440">
@@ -6288,7 +6288,7 @@
         <v>2023.0</v>
       </c>
       <c r="C440" t="n" s="2">
-        <v>45144.0</v>
+        <v>45137.0</v>
       </c>
       <c r="D440" t="n">
         <v>2.0</v>
@@ -6302,7 +6302,7 @@
         <v>2023.0</v>
       </c>
       <c r="C441" t="n" s="2">
-        <v>45151.0</v>
+        <v>45144.0</v>
       </c>
       <c r="D441" t="n">
         <v>2.0</v>
@@ -6316,7 +6316,7 @@
         <v>2023.0</v>
       </c>
       <c r="C442" t="n" s="2">
-        <v>45165.0</v>
+        <v>45151.0</v>
       </c>
       <c r="D442" t="n">
         <v>2.0</v>
@@ -6330,7 +6330,7 @@
         <v>2023.0</v>
       </c>
       <c r="C443" t="n" s="2">
-        <v>45172.0</v>
+        <v>45165.0</v>
       </c>
       <c r="D443" t="n">
         <v>2.0</v>
@@ -6344,10 +6344,10 @@
         <v>2023.0</v>
       </c>
       <c r="C444" t="n" s="2">
-        <v>45179.0</v>
+        <v>45172.0</v>
       </c>
       <c r="D444" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="445">
@@ -6358,7 +6358,7 @@
         <v>2023.0</v>
       </c>
       <c r="C445" t="n" s="2">
-        <v>45186.0</v>
+        <v>45179.0</v>
       </c>
       <c r="D445" t="n">
         <v>1.0</v>
@@ -6372,7 +6372,7 @@
         <v>2023.0</v>
       </c>
       <c r="C446" t="n" s="2">
-        <v>45193.0</v>
+        <v>45186.0</v>
       </c>
       <c r="D446" t="n">
         <v>1.0</v>
@@ -6386,7 +6386,7 @@
         <v>2023.0</v>
       </c>
       <c r="C447" t="n" s="2">
-        <v>45200.0</v>
+        <v>45193.0</v>
       </c>
       <c r="D447" t="n">
         <v>1.0</v>
@@ -6400,7 +6400,7 @@
         <v>2023.0</v>
       </c>
       <c r="C448" t="n" s="2">
-        <v>45207.0</v>
+        <v>45200.0</v>
       </c>
       <c r="D448" t="n">
         <v>1.0</v>
@@ -6414,7 +6414,7 @@
         <v>2023.0</v>
       </c>
       <c r="C449" t="n" s="2">
-        <v>45235.0</v>
+        <v>45207.0</v>
       </c>
       <c r="D449" t="n">
         <v>1.0</v>
@@ -6428,10 +6428,10 @@
         <v>2023.0</v>
       </c>
       <c r="C450" t="n" s="2">
-        <v>45242.0</v>
+        <v>45235.0</v>
       </c>
       <c r="D450" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="451">
@@ -6442,10 +6442,10 @@
         <v>2023.0</v>
       </c>
       <c r="C451" t="n" s="2">
-        <v>45249.0</v>
+        <v>45242.0</v>
       </c>
       <c r="D451" t="n">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="452">
@@ -6456,10 +6456,10 @@
         <v>2023.0</v>
       </c>
       <c r="C452" t="n" s="2">
-        <v>45256.0</v>
+        <v>45249.0</v>
       </c>
       <c r="D452" t="n">
-        <v>9.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="453">
@@ -6470,10 +6470,10 @@
         <v>2023.0</v>
       </c>
       <c r="C453" t="n" s="2">
-        <v>45263.0</v>
+        <v>45256.0</v>
       </c>
       <c r="D453" t="n">
-        <v>12.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="454">
@@ -6484,10 +6484,10 @@
         <v>2023.0</v>
       </c>
       <c r="C454" t="n" s="2">
-        <v>45270.0</v>
+        <v>45263.0</v>
       </c>
       <c r="D454" t="n">
-        <v>6.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="455">
@@ -6498,10 +6498,10 @@
         <v>2023.0</v>
       </c>
       <c r="C455" t="n" s="2">
-        <v>45277.0</v>
+        <v>45270.0</v>
       </c>
       <c r="D455" t="n">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="456">
@@ -6512,7 +6512,7 @@
         <v>2023.0</v>
       </c>
       <c r="C456" t="n" s="2">
-        <v>45284.0</v>
+        <v>45277.0</v>
       </c>
       <c r="D456" t="n">
         <v>7.0</v>
@@ -6526,10 +6526,10 @@
         <v>2023.0</v>
       </c>
       <c r="C457" t="n" s="2">
-        <v>45291.0</v>
+        <v>45284.0</v>
       </c>
       <c r="D457" t="n">
-        <v>13.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="458">
@@ -6537,13 +6537,13 @@
         <v>7</v>
       </c>
       <c r="B458" t="n">
-        <v>2024.0</v>
+        <v>2023.0</v>
       </c>
       <c r="C458" t="n" s="2">
-        <v>45299.0</v>
+        <v>45291.0</v>
       </c>
       <c r="D458" t="n">
-        <v>6.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="459">
@@ -6554,10 +6554,10 @@
         <v>2024.0</v>
       </c>
       <c r="C459" t="n" s="2">
-        <v>45306.0</v>
+        <v>45299.0</v>
       </c>
       <c r="D459" t="n">
-        <v>11.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="460">
@@ -6568,10 +6568,10 @@
         <v>2024.0</v>
       </c>
       <c r="C460" t="n" s="2">
-        <v>45313.0</v>
+        <v>45306.0</v>
       </c>
       <c r="D460" t="n">
-        <v>5.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="461">
@@ -6582,10 +6582,10 @@
         <v>2024.0</v>
       </c>
       <c r="C461" t="n" s="2">
-        <v>45320.0</v>
+        <v>45313.0</v>
       </c>
       <c r="D461" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="462">
@@ -6596,10 +6596,10 @@
         <v>2024.0</v>
       </c>
       <c r="C462" t="n" s="2">
-        <v>45327.0</v>
+        <v>45320.0</v>
       </c>
       <c r="D462" t="n">
-        <v>9.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="463">
@@ -6610,10 +6610,10 @@
         <v>2024.0</v>
       </c>
       <c r="C463" t="n" s="2">
-        <v>45334.0</v>
+        <v>45327.0</v>
       </c>
       <c r="D463" t="n">
-        <v>3.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="464">
@@ -6624,10 +6624,10 @@
         <v>2024.0</v>
       </c>
       <c r="C464" t="n" s="2">
-        <v>45341.0</v>
+        <v>45334.0</v>
       </c>
       <c r="D464" t="n">
-        <v>21.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="465">
@@ -6638,10 +6638,10 @@
         <v>2024.0</v>
       </c>
       <c r="C465" t="n" s="2">
-        <v>45348.0</v>
+        <v>45341.0</v>
       </c>
       <c r="D465" t="n">
-        <v>1.0</v>
+        <v>21.0</v>
       </c>
     </row>
     <row r="466">
@@ -6652,10 +6652,10 @@
         <v>2024.0</v>
       </c>
       <c r="C466" t="n" s="2">
-        <v>45355.0</v>
+        <v>45348.0</v>
       </c>
       <c r="D466" t="n">
-        <v>9.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="467">
@@ -6666,10 +6666,10 @@
         <v>2024.0</v>
       </c>
       <c r="C467" t="n" s="2">
-        <v>45362.0</v>
+        <v>45355.0</v>
       </c>
       <c r="D467" t="n">
-        <v>4.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="468">
@@ -6680,10 +6680,10 @@
         <v>2024.0</v>
       </c>
       <c r="C468" t="n" s="2">
-        <v>45369.0</v>
+        <v>45362.0</v>
       </c>
       <c r="D468" t="n">
-        <v>14.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="469">
@@ -6694,10 +6694,10 @@
         <v>2024.0</v>
       </c>
       <c r="C469" t="n" s="2">
-        <v>45376.0</v>
+        <v>45369.0</v>
       </c>
       <c r="D469" t="n">
-        <v>4.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="470">
@@ -6708,10 +6708,10 @@
         <v>2024.0</v>
       </c>
       <c r="C470" t="n" s="2">
-        <v>45383.0</v>
+        <v>45376.0</v>
       </c>
       <c r="D470" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="471">
@@ -6722,10 +6722,10 @@
         <v>2024.0</v>
       </c>
       <c r="C471" t="n" s="2">
-        <v>45390.0</v>
+        <v>45383.0</v>
       </c>
       <c r="D471" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="472">
@@ -6736,7 +6736,7 @@
         <v>2024.0</v>
       </c>
       <c r="C472" t="n" s="2">
-        <v>45397.0</v>
+        <v>45390.0</v>
       </c>
       <c r="D472" t="n">
         <v>1.0</v>
@@ -6750,10 +6750,10 @@
         <v>2024.0</v>
       </c>
       <c r="C473" t="n" s="2">
-        <v>45404.0</v>
+        <v>45397.0</v>
       </c>
       <c r="D473" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="474">
@@ -6764,10 +6764,10 @@
         <v>2024.0</v>
       </c>
       <c r="C474" t="n" s="2">
-        <v>45411.0</v>
+        <v>45404.0</v>
       </c>
       <c r="D474" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="475">
@@ -6778,10 +6778,10 @@
         <v>2024.0</v>
       </c>
       <c r="C475" t="n" s="2">
-        <v>45439.0</v>
+        <v>45411.0</v>
       </c>
       <c r="D475" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="476">
@@ -6792,10 +6792,10 @@
         <v>2024.0</v>
       </c>
       <c r="C476" t="n" s="2">
-        <v>45446.0</v>
+        <v>45439.0</v>
       </c>
       <c r="D476" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="477">
@@ -6806,7 +6806,7 @@
         <v>2024.0</v>
       </c>
       <c r="C477" t="n" s="2">
-        <v>45460.0</v>
+        <v>45446.0</v>
       </c>
       <c r="D477" t="n">
         <v>1.0</v>
@@ -6820,7 +6820,7 @@
         <v>2024.0</v>
       </c>
       <c r="C478" t="n" s="2">
-        <v>45481.0</v>
+        <v>45460.0</v>
       </c>
       <c r="D478" t="n">
         <v>1.0</v>
@@ -6834,7 +6834,7 @@
         <v>2024.0</v>
       </c>
       <c r="C479" t="n" s="2">
-        <v>45516.0</v>
+        <v>45481.0</v>
       </c>
       <c r="D479" t="n">
         <v>1.0</v>
@@ -6848,7 +6848,7 @@
         <v>2024.0</v>
       </c>
       <c r="C480" t="n" s="2">
-        <v>45551.0</v>
+        <v>45516.0</v>
       </c>
       <c r="D480" t="n">
         <v>1.0</v>
@@ -6862,7 +6862,7 @@
         <v>2024.0</v>
       </c>
       <c r="C481" t="n" s="2">
-        <v>45579.0</v>
+        <v>45551.0</v>
       </c>
       <c r="D481" t="n">
         <v>1.0</v>
@@ -6876,7 +6876,7 @@
         <v>2024.0</v>
       </c>
       <c r="C482" t="n" s="2">
-        <v>45614.0</v>
+        <v>45579.0</v>
       </c>
       <c r="D482" t="n">
         <v>1.0</v>
@@ -6890,10 +6890,10 @@
         <v>2024.0</v>
       </c>
       <c r="C483" t="n" s="2">
-        <v>45635.0</v>
+        <v>45614.0</v>
       </c>
       <c r="D483" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="484">
@@ -6904,10 +6904,10 @@
         <v>2024.0</v>
       </c>
       <c r="C484" t="n" s="2">
-        <v>45642.0</v>
+        <v>45635.0</v>
       </c>
       <c r="D484" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="485">
@@ -6918,10 +6918,10 @@
         <v>2024.0</v>
       </c>
       <c r="C485" t="n" s="2">
-        <v>45649.0</v>
+        <v>45642.0</v>
       </c>
       <c r="D485" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="486">
@@ -6932,10 +6932,10 @@
         <v>2024.0</v>
       </c>
       <c r="C486" t="n" s="2">
-        <v>45656.0</v>
+        <v>45649.0</v>
       </c>
       <c r="D486" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="487">
@@ -6943,13 +6943,13 @@
         <v>7</v>
       </c>
       <c r="B487" t="n">
-        <v>2025.0</v>
+        <v>2024.0</v>
       </c>
       <c r="C487" t="n" s="2">
-        <v>45665.0</v>
+        <v>45656.0</v>
       </c>
       <c r="D487" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="488">
@@ -6960,10 +6960,10 @@
         <v>2025.0</v>
       </c>
       <c r="C488" t="n" s="2">
-        <v>45672.0</v>
+        <v>45665.0</v>
       </c>
       <c r="D488" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="489">
@@ -6974,7 +6974,7 @@
         <v>2025.0</v>
       </c>
       <c r="C489" t="n" s="2">
-        <v>45686.0</v>
+        <v>45672.0</v>
       </c>
       <c r="D489" t="n">
         <v>2.0</v>
@@ -6988,10 +6988,10 @@
         <v>2025.0</v>
       </c>
       <c r="C490" t="n" s="2">
-        <v>45693.0</v>
+        <v>45686.0</v>
       </c>
       <c r="D490" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="491">
@@ -7002,10 +7002,10 @@
         <v>2025.0</v>
       </c>
       <c r="C491" t="n" s="2">
-        <v>45700.0</v>
+        <v>45693.0</v>
       </c>
       <c r="D491" t="n">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="492">
@@ -7016,10 +7016,10 @@
         <v>2025.0</v>
       </c>
       <c r="C492" t="n" s="2">
-        <v>45707.0</v>
+        <v>45700.0</v>
       </c>
       <c r="D492" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="493">
@@ -7030,10 +7030,10 @@
         <v>2025.0</v>
       </c>
       <c r="C493" t="n" s="2">
-        <v>45714.0</v>
+        <v>45707.0</v>
       </c>
       <c r="D493" t="n">
-        <v>8.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="494">
@@ -7044,10 +7044,10 @@
         <v>2025.0</v>
       </c>
       <c r="C494" t="n" s="2">
-        <v>45721.0</v>
+        <v>45714.0</v>
       </c>
       <c r="D494" t="n">
-        <v>11.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="495">
@@ -7058,10 +7058,10 @@
         <v>2025.0</v>
       </c>
       <c r="C495" t="n" s="2">
-        <v>45728.0</v>
+        <v>45721.0</v>
       </c>
       <c r="D495" t="n">
-        <v>6.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="496">
@@ -7072,10 +7072,10 @@
         <v>2025.0</v>
       </c>
       <c r="C496" t="n" s="2">
-        <v>45735.0</v>
+        <v>45728.0</v>
       </c>
       <c r="D496" t="n">
-        <v>19.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="497">
@@ -7086,10 +7086,10 @@
         <v>2025.0</v>
       </c>
       <c r="C497" t="n" s="2">
-        <v>45742.0</v>
+        <v>45735.0</v>
       </c>
       <c r="D497" t="n">
-        <v>17.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="498">
@@ -7100,10 +7100,10 @@
         <v>2025.0</v>
       </c>
       <c r="C498" t="n" s="2">
-        <v>45749.0</v>
+        <v>45742.0</v>
       </c>
       <c r="D498" t="n">
-        <v>5.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="499">
@@ -7114,10 +7114,10 @@
         <v>2025.0</v>
       </c>
       <c r="C499" t="n" s="2">
-        <v>45756.0</v>
+        <v>45749.0</v>
       </c>
       <c r="D499" t="n">
-        <v>9.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="500">
@@ -7128,10 +7128,10 @@
         <v>2025.0</v>
       </c>
       <c r="C500" t="n" s="2">
-        <v>45763.0</v>
+        <v>45756.0</v>
       </c>
       <c r="D500" t="n">
-        <v>1.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="501">
@@ -7142,7 +7142,7 @@
         <v>2025.0</v>
       </c>
       <c r="C501" t="n" s="2">
-        <v>45770.0</v>
+        <v>45763.0</v>
       </c>
       <c r="D501" t="n">
         <v>1.0</v>
@@ -7156,10 +7156,10 @@
         <v>2025.0</v>
       </c>
       <c r="C502" t="n" s="2">
-        <v>45784.0</v>
+        <v>45770.0</v>
       </c>
       <c r="D502" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="503">
@@ -7170,10 +7170,10 @@
         <v>2025.0</v>
       </c>
       <c r="C503" t="n" s="2">
-        <v>45791.0</v>
+        <v>45784.0</v>
       </c>
       <c r="D503" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="504">
@@ -7184,10 +7184,10 @@
         <v>2025.0</v>
       </c>
       <c r="C504" t="n" s="2">
-        <v>45805.0</v>
+        <v>45791.0</v>
       </c>
       <c r="D504" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="505">
@@ -7198,10 +7198,10 @@
         <v>2025.0</v>
       </c>
       <c r="C505" t="n" s="2">
-        <v>45826.0</v>
+        <v>45805.0</v>
       </c>
       <c r="D505" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="506">
@@ -7212,7 +7212,7 @@
         <v>2025.0</v>
       </c>
       <c r="C506" t="n" s="2">
-        <v>45861.0</v>
+        <v>45826.0</v>
       </c>
       <c r="D506" t="n">
         <v>2.0</v>
@@ -7226,10 +7226,10 @@
         <v>2025.0</v>
       </c>
       <c r="C507" t="n" s="2">
-        <v>45868.0</v>
+        <v>45861.0</v>
       </c>
       <c r="D507" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="508">
@@ -7240,7 +7240,7 @@
         <v>2025.0</v>
       </c>
       <c r="C508" t="n" s="2">
-        <v>45889.0</v>
+        <v>45868.0</v>
       </c>
       <c r="D508" t="n">
         <v>1.0</v>
@@ -7254,7 +7254,7 @@
         <v>2025.0</v>
       </c>
       <c r="C509" t="n" s="2">
-        <v>45924.0</v>
+        <v>45889.0</v>
       </c>
       <c r="D509" t="n">
         <v>1.0</v>
@@ -7268,7 +7268,7 @@
         <v>2025.0</v>
       </c>
       <c r="C510" t="n" s="2">
-        <v>45945.0</v>
+        <v>45924.0</v>
       </c>
       <c r="D510" t="n">
         <v>1.0</v>
@@ -7282,10 +7282,10 @@
         <v>2025.0</v>
       </c>
       <c r="C511" t="n" s="2">
-        <v>45959.0</v>
+        <v>45945.0</v>
       </c>
       <c r="D511" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="512">
@@ -7296,7 +7296,7 @@
         <v>2025.0</v>
       </c>
       <c r="C512" t="n" s="2">
-        <v>46001.0</v>
+        <v>45959.0</v>
       </c>
       <c r="D512" t="n">
         <v>2.0</v>
@@ -7310,10 +7310,10 @@
         <v>2025.0</v>
       </c>
       <c r="C513" t="n" s="2">
-        <v>46008.0</v>
+        <v>46001.0</v>
       </c>
       <c r="D513" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="514">
@@ -7324,7 +7324,7 @@
         <v>2025.0</v>
       </c>
       <c r="C514" t="n" s="2">
-        <v>46022.0</v>
+        <v>46008.0</v>
       </c>
       <c r="D514" t="n">
         <v>1.0</v>
@@ -7335,10 +7335,10 @@
         <v>7</v>
       </c>
       <c r="B515" t="n">
-        <v>2026.0</v>
+        <v>2025.0</v>
       </c>
       <c r="C515" t="n" s="2">
-        <v>46030.0</v>
+        <v>46022.0</v>
       </c>
       <c r="D515" t="n">
         <v>1.0</v>
@@ -7352,7 +7352,7 @@
         <v>2026.0</v>
       </c>
       <c r="C516" t="n" s="2">
-        <v>46051.0</v>
+        <v>46030.0</v>
       </c>
       <c r="D516" t="n">
         <v>1.0</v>
@@ -7366,7 +7366,7 @@
         <v>2026.0</v>
       </c>
       <c r="C517" t="n" s="2">
-        <v>46058.0</v>
+        <v>46051.0</v>
       </c>
       <c r="D517" t="n">
         <v>1.0</v>
@@ -7380,10 +7380,10 @@
         <v>2026.0</v>
       </c>
       <c r="C518" t="n" s="2">
-        <v>46065.0</v>
+        <v>46058.0</v>
       </c>
       <c r="D518" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="519">
@@ -7394,24 +7394,24 @@
         <v>2026.0</v>
       </c>
       <c r="C519" t="n" s="2">
-        <v>46135.0</v>
+        <v>46065.0</v>
       </c>
       <c r="D519" t="n">
-        <v>8.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B520" t="n">
-        <v>2024.0</v>
+        <v>2026.0</v>
       </c>
       <c r="C520" t="n" s="2">
-        <v>45495.0</v>
+        <v>46135.0</v>
       </c>
       <c r="D520" t="n">
-        <v>1.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="521">
@@ -7422,10 +7422,10 @@
         <v>2024.0</v>
       </c>
       <c r="C521" t="n" s="2">
-        <v>45502.0</v>
+        <v>45495.0</v>
       </c>
       <c r="D521" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="522">
@@ -7433,13 +7433,13 @@
         <v>8</v>
       </c>
       <c r="B522" t="n">
-        <v>2025.0</v>
+        <v>2024.0</v>
       </c>
       <c r="C522" t="n" s="2">
-        <v>45665.0</v>
+        <v>45502.0</v>
       </c>
       <c r="D522" t="n">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="523">
@@ -7450,10 +7450,10 @@
         <v>2025.0</v>
       </c>
       <c r="C523" t="n" s="2">
-        <v>45672.0</v>
+        <v>45665.0</v>
       </c>
       <c r="D523" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="524">
@@ -7464,10 +7464,10 @@
         <v>2025.0</v>
       </c>
       <c r="C524" t="n" s="2">
-        <v>45679.0</v>
+        <v>45672.0</v>
       </c>
       <c r="D524" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="525">
@@ -7478,10 +7478,10 @@
         <v>2025.0</v>
       </c>
       <c r="C525" t="n" s="2">
-        <v>45686.0</v>
+        <v>45679.0</v>
       </c>
       <c r="D525" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="526">
@@ -7492,10 +7492,10 @@
         <v>2025.0</v>
       </c>
       <c r="C526" t="n" s="2">
-        <v>45693.0</v>
+        <v>45686.0</v>
       </c>
       <c r="D526" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="527">
@@ -7506,10 +7506,10 @@
         <v>2025.0</v>
       </c>
       <c r="C527" t="n" s="2">
-        <v>45700.0</v>
+        <v>45693.0</v>
       </c>
       <c r="D527" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="528">
@@ -7520,10 +7520,10 @@
         <v>2025.0</v>
       </c>
       <c r="C528" t="n" s="2">
-        <v>45707.0</v>
+        <v>45700.0</v>
       </c>
       <c r="D528" t="n">
-        <v>7.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="529">
@@ -7534,10 +7534,10 @@
         <v>2025.0</v>
       </c>
       <c r="C529" t="n" s="2">
-        <v>45714.0</v>
+        <v>45707.0</v>
       </c>
       <c r="D529" t="n">
-        <v>3.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="530">
@@ -7548,10 +7548,10 @@
         <v>2025.0</v>
       </c>
       <c r="C530" t="n" s="2">
-        <v>45721.0</v>
+        <v>45714.0</v>
       </c>
       <c r="D530" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="531">
@@ -7562,10 +7562,10 @@
         <v>2025.0</v>
       </c>
       <c r="C531" t="n" s="2">
-        <v>45728.0</v>
+        <v>45721.0</v>
       </c>
       <c r="D531" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="532">
@@ -7576,7 +7576,7 @@
         <v>2025.0</v>
       </c>
       <c r="C532" t="n" s="2">
-        <v>45742.0</v>
+        <v>45728.0</v>
       </c>
       <c r="D532" t="n">
         <v>1.0</v>
@@ -7590,7 +7590,7 @@
         <v>2025.0</v>
       </c>
       <c r="C533" t="n" s="2">
-        <v>45749.0</v>
+        <v>45742.0</v>
       </c>
       <c r="D533" t="n">
         <v>1.0</v>
@@ -7604,7 +7604,7 @@
         <v>2025.0</v>
       </c>
       <c r="C534" t="n" s="2">
-        <v>45763.0</v>
+        <v>45749.0</v>
       </c>
       <c r="D534" t="n">
         <v>1.0</v>
@@ -7618,10 +7618,10 @@
         <v>2025.0</v>
       </c>
       <c r="C535" t="n" s="2">
-        <v>45777.0</v>
+        <v>45763.0</v>
       </c>
       <c r="D535" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="536">
@@ -7632,10 +7632,10 @@
         <v>2025.0</v>
       </c>
       <c r="C536" t="n" s="2">
-        <v>45784.0</v>
+        <v>45777.0</v>
       </c>
       <c r="D536" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="537">
@@ -7646,7 +7646,7 @@
         <v>2025.0</v>
       </c>
       <c r="C537" t="n" s="2">
-        <v>45798.0</v>
+        <v>45784.0</v>
       </c>
       <c r="D537" t="n">
         <v>1.0</v>
@@ -7660,7 +7660,7 @@
         <v>2025.0</v>
       </c>
       <c r="C538" t="n" s="2">
-        <v>45805.0</v>
+        <v>45798.0</v>
       </c>
       <c r="D538" t="n">
         <v>1.0</v>
@@ -7674,10 +7674,10 @@
         <v>2025.0</v>
       </c>
       <c r="C539" t="n" s="2">
-        <v>45812.0</v>
+        <v>45805.0</v>
       </c>
       <c r="D539" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="540">
@@ -7688,7 +7688,7 @@
         <v>2025.0</v>
       </c>
       <c r="C540" t="n" s="2">
-        <v>45819.0</v>
+        <v>45812.0</v>
       </c>
       <c r="D540" t="n">
         <v>2.0</v>
@@ -7702,7 +7702,7 @@
         <v>2025.0</v>
       </c>
       <c r="C541" t="n" s="2">
-        <v>45833.0</v>
+        <v>45819.0</v>
       </c>
       <c r="D541" t="n">
         <v>2.0</v>
@@ -7716,10 +7716,10 @@
         <v>2025.0</v>
       </c>
       <c r="C542" t="n" s="2">
-        <v>45847.0</v>
+        <v>45833.0</v>
       </c>
       <c r="D542" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="543">
@@ -7730,10 +7730,10 @@
         <v>2025.0</v>
       </c>
       <c r="C543" t="n" s="2">
-        <v>45854.0</v>
+        <v>45847.0</v>
       </c>
       <c r="D543" t="n">
-        <v>8.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="544">
@@ -7744,10 +7744,10 @@
         <v>2025.0</v>
       </c>
       <c r="C544" t="n" s="2">
-        <v>45861.0</v>
+        <v>45854.0</v>
       </c>
       <c r="D544" t="n">
-        <v>12.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="545">
@@ -7758,10 +7758,10 @@
         <v>2025.0</v>
       </c>
       <c r="C545" t="n" s="2">
-        <v>45868.0</v>
+        <v>45861.0</v>
       </c>
       <c r="D545" t="n">
-        <v>6.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="546">
@@ -7772,10 +7772,10 @@
         <v>2025.0</v>
       </c>
       <c r="C546" t="n" s="2">
-        <v>45875.0</v>
+        <v>45868.0</v>
       </c>
       <c r="D546" t="n">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="547">
@@ -7786,7 +7786,7 @@
         <v>2025.0</v>
       </c>
       <c r="C547" t="n" s="2">
-        <v>45896.0</v>
+        <v>45875.0</v>
       </c>
       <c r="D547" t="n">
         <v>1.0</v>
@@ -7800,7 +7800,7 @@
         <v>2025.0</v>
       </c>
       <c r="C548" t="n" s="2">
-        <v>45903.0</v>
+        <v>45896.0</v>
       </c>
       <c r="D548" t="n">
         <v>1.0</v>
@@ -7814,7 +7814,7 @@
         <v>2025.0</v>
       </c>
       <c r="C549" t="n" s="2">
-        <v>45931.0</v>
+        <v>45903.0</v>
       </c>
       <c r="D549" t="n">
         <v>1.0</v>
@@ -7828,10 +7828,10 @@
         <v>2025.0</v>
       </c>
       <c r="C550" t="n" s="2">
-        <v>45938.0</v>
+        <v>45931.0</v>
       </c>
       <c r="D550" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="551">
@@ -7842,10 +7842,10 @@
         <v>2025.0</v>
       </c>
       <c r="C551" t="n" s="2">
-        <v>45945.0</v>
+        <v>45938.0</v>
       </c>
       <c r="D551" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="552">
@@ -7856,7 +7856,7 @@
         <v>2025.0</v>
       </c>
       <c r="C552" t="n" s="2">
-        <v>45966.0</v>
+        <v>45945.0</v>
       </c>
       <c r="D552" t="n">
         <v>2.0</v>
@@ -7870,10 +7870,10 @@
         <v>2025.0</v>
       </c>
       <c r="C553" t="n" s="2">
-        <v>45973.0</v>
+        <v>45966.0</v>
       </c>
       <c r="D553" t="n">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="554">
@@ -7884,10 +7884,10 @@
         <v>2025.0</v>
       </c>
       <c r="C554" t="n" s="2">
-        <v>45980.0</v>
+        <v>45973.0</v>
       </c>
       <c r="D554" t="n">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="555">
@@ -7898,10 +7898,10 @@
         <v>2025.0</v>
       </c>
       <c r="C555" t="n" s="2">
-        <v>45987.0</v>
+        <v>45980.0</v>
       </c>
       <c r="D555" t="n">
-        <v>20.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="556">
@@ -7912,10 +7912,10 @@
         <v>2025.0</v>
       </c>
       <c r="C556" t="n" s="2">
-        <v>45994.0</v>
+        <v>45987.0</v>
       </c>
       <c r="D556" t="n">
-        <v>5.0</v>
+        <v>20.0</v>
       </c>
     </row>
     <row r="557">
@@ -7926,10 +7926,10 @@
         <v>2025.0</v>
       </c>
       <c r="C557" t="n" s="2">
-        <v>46001.0</v>
+        <v>45994.0</v>
       </c>
       <c r="D557" t="n">
-        <v>8.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="558">
@@ -7940,10 +7940,10 @@
         <v>2025.0</v>
       </c>
       <c r="C558" t="n" s="2">
-        <v>46008.0</v>
+        <v>46001.0</v>
       </c>
       <c r="D558" t="n">
-        <v>24.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="559">
@@ -7954,10 +7954,10 @@
         <v>2025.0</v>
       </c>
       <c r="C559" t="n" s="2">
-        <v>46015.0</v>
+        <v>46008.0</v>
       </c>
       <c r="D559" t="n">
-        <v>13.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="560">
@@ -7968,10 +7968,10 @@
         <v>2025.0</v>
       </c>
       <c r="C560" t="n" s="2">
-        <v>46022.0</v>
+        <v>46015.0</v>
       </c>
       <c r="D560" t="n">
-        <v>8.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="561">
@@ -7982,10 +7982,10 @@
         <v>2025.0</v>
       </c>
       <c r="C561" t="n" s="2">
-        <v>46029.0</v>
+        <v>46022.0</v>
       </c>
       <c r="D561" t="n">
-        <v>3.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="562">
@@ -7993,13 +7993,13 @@
         <v>8</v>
       </c>
       <c r="B562" t="n">
-        <v>2026.0</v>
+        <v>2025.0</v>
       </c>
       <c r="C562" t="n" s="2">
-        <v>46030.0</v>
+        <v>46029.0</v>
       </c>
       <c r="D562" t="n">
-        <v>24.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="563">
@@ -8010,10 +8010,10 @@
         <v>2026.0</v>
       </c>
       <c r="C563" t="n" s="2">
-        <v>46037.0</v>
+        <v>46030.0</v>
       </c>
       <c r="D563" t="n">
-        <v>22.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="564">
@@ -8024,10 +8024,10 @@
         <v>2026.0</v>
       </c>
       <c r="C564" t="n" s="2">
-        <v>46044.0</v>
+        <v>46037.0</v>
       </c>
       <c r="D564" t="n">
-        <v>27.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="565">
@@ -8038,10 +8038,10 @@
         <v>2026.0</v>
       </c>
       <c r="C565" t="n" s="2">
-        <v>46051.0</v>
+        <v>46044.0</v>
       </c>
       <c r="D565" t="n">
-        <v>18.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="566">
@@ -8052,10 +8052,10 @@
         <v>2026.0</v>
       </c>
       <c r="C566" t="n" s="2">
-        <v>46058.0</v>
+        <v>46051.0</v>
       </c>
       <c r="D566" t="n">
-        <v>25.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="567">
@@ -8066,10 +8066,10 @@
         <v>2026.0</v>
       </c>
       <c r="C567" t="n" s="2">
-        <v>46065.0</v>
+        <v>46058.0</v>
       </c>
       <c r="D567" t="n">
-        <v>22.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="568">
@@ -8080,10 +8080,10 @@
         <v>2026.0</v>
       </c>
       <c r="C568" t="n" s="2">
-        <v>46072.0</v>
+        <v>46065.0</v>
       </c>
       <c r="D568" t="n">
-        <v>13.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="569">
@@ -8094,10 +8094,10 @@
         <v>2026.0</v>
       </c>
       <c r="C569" t="n" s="2">
-        <v>46079.0</v>
+        <v>46072.0</v>
       </c>
       <c r="D569" t="n">
-        <v>24.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="570">
@@ -8108,10 +8108,10 @@
         <v>2026.0</v>
       </c>
       <c r="C570" t="n" s="2">
-        <v>46086.0</v>
+        <v>46079.0</v>
       </c>
       <c r="D570" t="n">
-        <v>26.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="571">
@@ -8122,10 +8122,10 @@
         <v>2026.0</v>
       </c>
       <c r="C571" t="n" s="2">
-        <v>46093.0</v>
+        <v>46086.0</v>
       </c>
       <c r="D571" t="n">
-        <v>33.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="572">
@@ -8136,10 +8136,10 @@
         <v>2026.0</v>
       </c>
       <c r="C572" t="n" s="2">
-        <v>46100.0</v>
+        <v>46093.0</v>
       </c>
       <c r="D572" t="n">
-        <v>25.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="573">
@@ -8150,10 +8150,10 @@
         <v>2026.0</v>
       </c>
       <c r="C573" t="n" s="2">
-        <v>46107.0</v>
+        <v>46100.0</v>
       </c>
       <c r="D573" t="n">
-        <v>31.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="574">
@@ -8164,10 +8164,10 @@
         <v>2026.0</v>
       </c>
       <c r="C574" t="n" s="2">
-        <v>46114.0</v>
+        <v>46107.0</v>
       </c>
       <c r="D574" t="n">
-        <v>10.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="575">
@@ -8178,10 +8178,10 @@
         <v>2026.0</v>
       </c>
       <c r="C575" t="n" s="2">
-        <v>46121.0</v>
+        <v>46114.0</v>
       </c>
       <c r="D575" t="n">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="576">
@@ -8192,10 +8192,10 @@
         <v>2026.0</v>
       </c>
       <c r="C576" t="n" s="2">
-        <v>46128.0</v>
+        <v>46121.0</v>
       </c>
       <c r="D576" t="n">
-        <v>15.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="577">
@@ -8206,10 +8206,10 @@
         <v>2026.0</v>
       </c>
       <c r="C577" t="n" s="2">
-        <v>46135.0</v>
+        <v>46128.0</v>
       </c>
       <c r="D577" t="n">
-        <v>23.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="578">
@@ -8220,10 +8220,10 @@
         <v>2026.0</v>
       </c>
       <c r="C578" t="n" s="2">
-        <v>46142.0</v>
+        <v>46135.0</v>
       </c>
       <c r="D578" t="n">
-        <v>21.0</v>
+        <v>23.0</v>
       </c>
     </row>
     <row r="579">
@@ -8234,10 +8234,10 @@
         <v>2026.0</v>
       </c>
       <c r="C579" t="n" s="2">
-        <v>46149.0</v>
+        <v>46142.0</v>
       </c>
       <c r="D579" t="n">
-        <v>2.0</v>
+        <v>21.0</v>
       </c>
     </row>
     <row r="580">
@@ -8248,10 +8248,10 @@
         <v>2026.0</v>
       </c>
       <c r="C580" t="n" s="2">
-        <v>46156.0</v>
+        <v>46149.0</v>
       </c>
       <c r="D580" t="n">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
     </row>
   </sheetData>
@@ -8277,7 +8277,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="n">
-        <v>51.0</v>
+        <v>47.0</v>
       </c>
     </row>
     <row r="3">
@@ -8293,7 +8293,7 @@
         <v>12</v>
       </c>
       <c r="B4" t="n">
-        <v>1257.0</v>
+        <v>1259.0</v>
       </c>
     </row>
     <row r="5">
@@ -8301,7 +8301,7 @@
         <v>13</v>
       </c>
       <c r="B5" t="n">
-        <v>2101.0</v>
+        <v>2104.0</v>
       </c>
     </row>
   </sheetData>
@@ -8355,7 +8355,7 @@
         <v>19</v>
       </c>
       <c r="C4" t="n">
-        <v>138.0</v>
+        <v>140.0</v>
       </c>
     </row>
     <row r="5">
@@ -8366,7 +8366,7 @@
         <v>21</v>
       </c>
       <c r="C5" t="n">
-        <v>419.0</v>
+        <v>420.0</v>
       </c>
     </row>
     <row r="6">
@@ -8432,7 +8432,7 @@
         <v>19</v>
       </c>
       <c r="C11" t="n">
-        <v>37.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="12">
@@ -8443,7 +8443,7 @@
         <v>21</v>
       </c>
       <c r="C12" t="n">
-        <v>68.0</v>
+        <v>70.0</v>
       </c>
     </row>
     <row r="13">

--- a/Download/Focus_Positivi_ZR.xlsx
+++ b/Download/Focus_Positivi_ZR.xlsx
@@ -4289,7 +4289,7 @@
         <v>46149.0</v>
       </c>
       <c r="D297" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="298">
@@ -8301,7 +8301,7 @@
         <v>13</v>
       </c>
       <c r="B5" t="n">
-        <v>2104.0</v>
+        <v>2106.0</v>
       </c>
     </row>
   </sheetData>
@@ -8333,7 +8333,7 @@
         <v>21</v>
       </c>
       <c r="C2" t="n">
-        <v>194.0</v>
+        <v>196.0</v>
       </c>
     </row>
     <row r="3">

--- a/Download/Focus_Positivi_ZR.xlsx
+++ b/Download/Focus_Positivi_ZR.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="624" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="626" uniqueCount="23">
   <si>
     <t>NOME_REGIONE</t>
   </si>
@@ -1620,13 +1620,13 @@
     </row>
     <row r="107">
       <c r="A107" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B107" t="n">
-        <v>2021.0</v>
+        <v>2026.0</v>
       </c>
       <c r="C107" t="n" s="2">
-        <v>44561.0</v>
+        <v>46156.0</v>
       </c>
       <c r="D107" t="n">
         <v>1.0</v>
@@ -1637,13 +1637,13 @@
         <v>5</v>
       </c>
       <c r="B108" t="n">
-        <v>2022.0</v>
+        <v>2021.0</v>
       </c>
       <c r="C108" t="n" s="2">
-        <v>44576.0</v>
+        <v>44561.0</v>
       </c>
       <c r="D108" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="109">
@@ -1654,10 +1654,10 @@
         <v>2022.0</v>
       </c>
       <c r="C109" t="n" s="2">
-        <v>44583.0</v>
+        <v>44576.0</v>
       </c>
       <c r="D109" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="110">
@@ -1668,10 +1668,10 @@
         <v>2022.0</v>
       </c>
       <c r="C110" t="n" s="2">
-        <v>44590.0</v>
+        <v>44583.0</v>
       </c>
       <c r="D110" t="n">
-        <v>7.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="111">
@@ -1682,10 +1682,10 @@
         <v>2022.0</v>
       </c>
       <c r="C111" t="n" s="2">
-        <v>44597.0</v>
+        <v>44590.0</v>
       </c>
       <c r="D111" t="n">
-        <v>3.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="112">
@@ -1696,10 +1696,10 @@
         <v>2022.0</v>
       </c>
       <c r="C112" t="n" s="2">
-        <v>44604.0</v>
+        <v>44597.0</v>
       </c>
       <c r="D112" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="113">
@@ -1710,10 +1710,10 @@
         <v>2022.0</v>
       </c>
       <c r="C113" t="n" s="2">
-        <v>44611.0</v>
+        <v>44604.0</v>
       </c>
       <c r="D113" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="114">
@@ -1724,7 +1724,7 @@
         <v>2022.0</v>
       </c>
       <c r="C114" t="n" s="2">
-        <v>44618.0</v>
+        <v>44611.0</v>
       </c>
       <c r="D114" t="n">
         <v>1.0</v>
@@ -1738,10 +1738,10 @@
         <v>2022.0</v>
       </c>
       <c r="C115" t="n" s="2">
-        <v>44625.0</v>
+        <v>44618.0</v>
       </c>
       <c r="D115" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="116">
@@ -1752,10 +1752,10 @@
         <v>2022.0</v>
       </c>
       <c r="C116" t="n" s="2">
-        <v>44632.0</v>
+        <v>44625.0</v>
       </c>
       <c r="D116" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="117">
@@ -1766,10 +1766,10 @@
         <v>2022.0</v>
       </c>
       <c r="C117" t="n" s="2">
-        <v>44639.0</v>
+        <v>44632.0</v>
       </c>
       <c r="D117" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="118">
@@ -1780,7 +1780,7 @@
         <v>2022.0</v>
       </c>
       <c r="C118" t="n" s="2">
-        <v>44646.0</v>
+        <v>44639.0</v>
       </c>
       <c r="D118" t="n">
         <v>2.0</v>
@@ -1794,7 +1794,7 @@
         <v>2022.0</v>
       </c>
       <c r="C119" t="n" s="2">
-        <v>44653.0</v>
+        <v>44646.0</v>
       </c>
       <c r="D119" t="n">
         <v>2.0</v>
@@ -1808,10 +1808,10 @@
         <v>2022.0</v>
       </c>
       <c r="C120" t="n" s="2">
-        <v>44660.0</v>
+        <v>44653.0</v>
       </c>
       <c r="D120" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="121">
@@ -1822,10 +1822,10 @@
         <v>2022.0</v>
       </c>
       <c r="C121" t="n" s="2">
-        <v>44667.0</v>
+        <v>44660.0</v>
       </c>
       <c r="D121" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="122">
@@ -1836,7 +1836,7 @@
         <v>2022.0</v>
       </c>
       <c r="C122" t="n" s="2">
-        <v>44674.0</v>
+        <v>44667.0</v>
       </c>
       <c r="D122" t="n">
         <v>3.0</v>
@@ -1850,10 +1850,10 @@
         <v>2022.0</v>
       </c>
       <c r="C123" t="n" s="2">
-        <v>44681.0</v>
+        <v>44674.0</v>
       </c>
       <c r="D123" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="124">
@@ -1864,10 +1864,10 @@
         <v>2022.0</v>
       </c>
       <c r="C124" t="n" s="2">
-        <v>44688.0</v>
+        <v>44681.0</v>
       </c>
       <c r="D124" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="125">
@@ -1878,7 +1878,7 @@
         <v>2022.0</v>
       </c>
       <c r="C125" t="n" s="2">
-        <v>44695.0</v>
+        <v>44688.0</v>
       </c>
       <c r="D125" t="n">
         <v>3.0</v>
@@ -1892,10 +1892,10 @@
         <v>2022.0</v>
       </c>
       <c r="C126" t="n" s="2">
-        <v>44702.0</v>
+        <v>44695.0</v>
       </c>
       <c r="D126" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="127">
@@ -1906,10 +1906,10 @@
         <v>2022.0</v>
       </c>
       <c r="C127" t="n" s="2">
-        <v>44709.0</v>
+        <v>44702.0</v>
       </c>
       <c r="D127" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="128">
@@ -1920,10 +1920,10 @@
         <v>2022.0</v>
       </c>
       <c r="C128" t="n" s="2">
-        <v>44716.0</v>
+        <v>44709.0</v>
       </c>
       <c r="D128" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="129">
@@ -1934,7 +1934,7 @@
         <v>2022.0</v>
       </c>
       <c r="C129" t="n" s="2">
-        <v>44723.0</v>
+        <v>44716.0</v>
       </c>
       <c r="D129" t="n">
         <v>1.0</v>
@@ -1948,7 +1948,7 @@
         <v>2022.0</v>
       </c>
       <c r="C130" t="n" s="2">
-        <v>44730.0</v>
+        <v>44723.0</v>
       </c>
       <c r="D130" t="n">
         <v>1.0</v>
@@ -1962,7 +1962,7 @@
         <v>2022.0</v>
       </c>
       <c r="C131" t="n" s="2">
-        <v>44737.0</v>
+        <v>44730.0</v>
       </c>
       <c r="D131" t="n">
         <v>1.0</v>
@@ -1976,7 +1976,7 @@
         <v>2022.0</v>
       </c>
       <c r="C132" t="n" s="2">
-        <v>44744.0</v>
+        <v>44737.0</v>
       </c>
       <c r="D132" t="n">
         <v>1.0</v>
@@ -1990,7 +1990,7 @@
         <v>2022.0</v>
       </c>
       <c r="C133" t="n" s="2">
-        <v>44751.0</v>
+        <v>44744.0</v>
       </c>
       <c r="D133" t="n">
         <v>1.0</v>
@@ -2004,7 +2004,7 @@
         <v>2022.0</v>
       </c>
       <c r="C134" t="n" s="2">
-        <v>44758.0</v>
+        <v>44751.0</v>
       </c>
       <c r="D134" t="n">
         <v>1.0</v>
@@ -2018,7 +2018,7 @@
         <v>2022.0</v>
       </c>
       <c r="C135" t="n" s="2">
-        <v>44772.0</v>
+        <v>44758.0</v>
       </c>
       <c r="D135" t="n">
         <v>1.0</v>
@@ -2032,7 +2032,7 @@
         <v>2022.0</v>
       </c>
       <c r="C136" t="n" s="2">
-        <v>44793.0</v>
+        <v>44772.0</v>
       </c>
       <c r="D136" t="n">
         <v>1.0</v>
@@ -2046,7 +2046,7 @@
         <v>2022.0</v>
       </c>
       <c r="C137" t="n" s="2">
-        <v>44800.0</v>
+        <v>44793.0</v>
       </c>
       <c r="D137" t="n">
         <v>1.0</v>
@@ -2060,7 +2060,7 @@
         <v>2022.0</v>
       </c>
       <c r="C138" t="n" s="2">
-        <v>44828.0</v>
+        <v>44800.0</v>
       </c>
       <c r="D138" t="n">
         <v>1.0</v>
@@ -2074,7 +2074,7 @@
         <v>2022.0</v>
       </c>
       <c r="C139" t="n" s="2">
-        <v>44849.0</v>
+        <v>44828.0</v>
       </c>
       <c r="D139" t="n">
         <v>1.0</v>
@@ -2088,7 +2088,7 @@
         <v>2022.0</v>
       </c>
       <c r="C140" t="n" s="2">
-        <v>44856.0</v>
+        <v>44849.0</v>
       </c>
       <c r="D140" t="n">
         <v>1.0</v>
@@ -2102,7 +2102,7 @@
         <v>2022.0</v>
       </c>
       <c r="C141" t="n" s="2">
-        <v>44863.0</v>
+        <v>44856.0</v>
       </c>
       <c r="D141" t="n">
         <v>1.0</v>
@@ -2116,10 +2116,10 @@
         <v>2022.0</v>
       </c>
       <c r="C142" t="n" s="2">
-        <v>44884.0</v>
+        <v>44863.0</v>
       </c>
       <c r="D142" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="143">
@@ -2130,10 +2130,10 @@
         <v>2022.0</v>
       </c>
       <c r="C143" t="n" s="2">
-        <v>44891.0</v>
+        <v>44884.0</v>
       </c>
       <c r="D143" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="144">
@@ -2144,7 +2144,7 @@
         <v>2022.0</v>
       </c>
       <c r="C144" t="n" s="2">
-        <v>44905.0</v>
+        <v>44891.0</v>
       </c>
       <c r="D144" t="n">
         <v>1.0</v>
@@ -2158,7 +2158,7 @@
         <v>2022.0</v>
       </c>
       <c r="C145" t="n" s="2">
-        <v>44912.0</v>
+        <v>44905.0</v>
       </c>
       <c r="D145" t="n">
         <v>1.0</v>
@@ -2172,10 +2172,10 @@
         <v>2022.0</v>
       </c>
       <c r="C146" t="n" s="2">
-        <v>44919.0</v>
+        <v>44912.0</v>
       </c>
       <c r="D146" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="147">
@@ -2183,13 +2183,13 @@
         <v>5</v>
       </c>
       <c r="B147" t="n">
-        <v>2023.0</v>
+        <v>2022.0</v>
       </c>
       <c r="C147" t="n" s="2">
-        <v>44934.0</v>
+        <v>44919.0</v>
       </c>
       <c r="D147" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="148">
@@ -2200,10 +2200,10 @@
         <v>2023.0</v>
       </c>
       <c r="C148" t="n" s="2">
-        <v>44941.0</v>
+        <v>44934.0</v>
       </c>
       <c r="D148" t="n">
-        <v>8.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="149">
@@ -2214,10 +2214,10 @@
         <v>2023.0</v>
       </c>
       <c r="C149" t="n" s="2">
-        <v>44948.0</v>
+        <v>44941.0</v>
       </c>
       <c r="D149" t="n">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="150">
@@ -2228,10 +2228,10 @@
         <v>2023.0</v>
       </c>
       <c r="C150" t="n" s="2">
-        <v>44955.0</v>
+        <v>44948.0</v>
       </c>
       <c r="D150" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="151">
@@ -2242,10 +2242,10 @@
         <v>2023.0</v>
       </c>
       <c r="C151" t="n" s="2">
-        <v>44962.0</v>
+        <v>44955.0</v>
       </c>
       <c r="D151" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="152">
@@ -2256,7 +2256,7 @@
         <v>2023.0</v>
       </c>
       <c r="C152" t="n" s="2">
-        <v>44969.0</v>
+        <v>44962.0</v>
       </c>
       <c r="D152" t="n">
         <v>4.0</v>
@@ -2270,10 +2270,10 @@
         <v>2023.0</v>
       </c>
       <c r="C153" t="n" s="2">
-        <v>44976.0</v>
+        <v>44969.0</v>
       </c>
       <c r="D153" t="n">
-        <v>17.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="154">
@@ -2284,10 +2284,10 @@
         <v>2023.0</v>
       </c>
       <c r="C154" t="n" s="2">
-        <v>44983.0</v>
+        <v>44976.0</v>
       </c>
       <c r="D154" t="n">
-        <v>11.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="155">
@@ -2298,10 +2298,10 @@
         <v>2023.0</v>
       </c>
       <c r="C155" t="n" s="2">
-        <v>44990.0</v>
+        <v>44983.0</v>
       </c>
       <c r="D155" t="n">
-        <v>5.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="156">
@@ -2312,10 +2312,10 @@
         <v>2023.0</v>
       </c>
       <c r="C156" t="n" s="2">
-        <v>44997.0</v>
+        <v>44990.0</v>
       </c>
       <c r="D156" t="n">
-        <v>22.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="157">
@@ -2326,10 +2326,10 @@
         <v>2023.0</v>
       </c>
       <c r="C157" t="n" s="2">
-        <v>45004.0</v>
+        <v>44997.0</v>
       </c>
       <c r="D157" t="n">
-        <v>8.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="158">
@@ -2340,10 +2340,10 @@
         <v>2023.0</v>
       </c>
       <c r="C158" t="n" s="2">
-        <v>45011.0</v>
+        <v>45004.0</v>
       </c>
       <c r="D158" t="n">
-        <v>17.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="159">
@@ -2354,10 +2354,10 @@
         <v>2023.0</v>
       </c>
       <c r="C159" t="n" s="2">
-        <v>45018.0</v>
+        <v>45011.0</v>
       </c>
       <c r="D159" t="n">
-        <v>10.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="160">
@@ -2368,10 +2368,10 @@
         <v>2023.0</v>
       </c>
       <c r="C160" t="n" s="2">
-        <v>45025.0</v>
+        <v>45018.0</v>
       </c>
       <c r="D160" t="n">
-        <v>13.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="161">
@@ -2382,10 +2382,10 @@
         <v>2023.0</v>
       </c>
       <c r="C161" t="n" s="2">
-        <v>45032.0</v>
+        <v>45025.0</v>
       </c>
       <c r="D161" t="n">
-        <v>10.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="162">
@@ -2396,10 +2396,10 @@
         <v>2023.0</v>
       </c>
       <c r="C162" t="n" s="2">
-        <v>45039.0</v>
+        <v>45032.0</v>
       </c>
       <c r="D162" t="n">
-        <v>22.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="163">
@@ -2410,10 +2410,10 @@
         <v>2023.0</v>
       </c>
       <c r="C163" t="n" s="2">
-        <v>45046.0</v>
+        <v>45039.0</v>
       </c>
       <c r="D163" t="n">
-        <v>23.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="164">
@@ -2424,10 +2424,10 @@
         <v>2023.0</v>
       </c>
       <c r="C164" t="n" s="2">
-        <v>45053.0</v>
+        <v>45046.0</v>
       </c>
       <c r="D164" t="n">
-        <v>16.0</v>
+        <v>23.0</v>
       </c>
     </row>
     <row r="165">
@@ -2438,10 +2438,10 @@
         <v>2023.0</v>
       </c>
       <c r="C165" t="n" s="2">
-        <v>45060.0</v>
+        <v>45053.0</v>
       </c>
       <c r="D165" t="n">
-        <v>13.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="166">
@@ -2452,10 +2452,10 @@
         <v>2023.0</v>
       </c>
       <c r="C166" t="n" s="2">
-        <v>45067.0</v>
+        <v>45060.0</v>
       </c>
       <c r="D166" t="n">
-        <v>9.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="167">
@@ -2466,10 +2466,10 @@
         <v>2023.0</v>
       </c>
       <c r="C167" t="n" s="2">
-        <v>45074.0</v>
+        <v>45067.0</v>
       </c>
       <c r="D167" t="n">
-        <v>6.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="168">
@@ -2480,10 +2480,10 @@
         <v>2023.0</v>
       </c>
       <c r="C168" t="n" s="2">
-        <v>45081.0</v>
+        <v>45074.0</v>
       </c>
       <c r="D168" t="n">
-        <v>16.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="169">
@@ -2494,10 +2494,10 @@
         <v>2023.0</v>
       </c>
       <c r="C169" t="n" s="2">
-        <v>45088.0</v>
+        <v>45081.0</v>
       </c>
       <c r="D169" t="n">
-        <v>8.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="170">
@@ -2508,10 +2508,10 @@
         <v>2023.0</v>
       </c>
       <c r="C170" t="n" s="2">
-        <v>45095.0</v>
+        <v>45088.0</v>
       </c>
       <c r="D170" t="n">
-        <v>16.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="171">
@@ -2522,10 +2522,10 @@
         <v>2023.0</v>
       </c>
       <c r="C171" t="n" s="2">
-        <v>45102.0</v>
+        <v>45095.0</v>
       </c>
       <c r="D171" t="n">
-        <v>17.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="172">
@@ -2536,10 +2536,10 @@
         <v>2023.0</v>
       </c>
       <c r="C172" t="n" s="2">
-        <v>45109.0</v>
+        <v>45102.0</v>
       </c>
       <c r="D172" t="n">
-        <v>14.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="173">
@@ -2550,10 +2550,10 @@
         <v>2023.0</v>
       </c>
       <c r="C173" t="n" s="2">
-        <v>45116.0</v>
+        <v>45109.0</v>
       </c>
       <c r="D173" t="n">
-        <v>13.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="174">
@@ -2564,10 +2564,10 @@
         <v>2023.0</v>
       </c>
       <c r="C174" t="n" s="2">
-        <v>45123.0</v>
+        <v>45116.0</v>
       </c>
       <c r="D174" t="n">
-        <v>5.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="175">
@@ -2578,10 +2578,10 @@
         <v>2023.0</v>
       </c>
       <c r="C175" t="n" s="2">
-        <v>45130.0</v>
+        <v>45123.0</v>
       </c>
       <c r="D175" t="n">
-        <v>8.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="176">
@@ -2592,10 +2592,10 @@
         <v>2023.0</v>
       </c>
       <c r="C176" t="n" s="2">
-        <v>45137.0</v>
+        <v>45130.0</v>
       </c>
       <c r="D176" t="n">
-        <v>4.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="177">
@@ -2606,10 +2606,10 @@
         <v>2023.0</v>
       </c>
       <c r="C177" t="n" s="2">
-        <v>45144.0</v>
+        <v>45137.0</v>
       </c>
       <c r="D177" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="178">
@@ -2620,7 +2620,7 @@
         <v>2023.0</v>
       </c>
       <c r="C178" t="n" s="2">
-        <v>45151.0</v>
+        <v>45144.0</v>
       </c>
       <c r="D178" t="n">
         <v>2.0</v>
@@ -2634,10 +2634,10 @@
         <v>2023.0</v>
       </c>
       <c r="C179" t="n" s="2">
-        <v>45158.0</v>
+        <v>45151.0</v>
       </c>
       <c r="D179" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="180">
@@ -2648,7 +2648,7 @@
         <v>2023.0</v>
       </c>
       <c r="C180" t="n" s="2">
-        <v>45165.0</v>
+        <v>45158.0</v>
       </c>
       <c r="D180" t="n">
         <v>5.0</v>
@@ -2662,10 +2662,10 @@
         <v>2023.0</v>
       </c>
       <c r="C181" t="n" s="2">
-        <v>45172.0</v>
+        <v>45165.0</v>
       </c>
       <c r="D181" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="182">
@@ -2676,10 +2676,10 @@
         <v>2023.0</v>
       </c>
       <c r="C182" t="n" s="2">
-        <v>45179.0</v>
+        <v>45172.0</v>
       </c>
       <c r="D182" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="183">
@@ -2690,10 +2690,10 @@
         <v>2023.0</v>
       </c>
       <c r="C183" t="n" s="2">
-        <v>45186.0</v>
+        <v>45179.0</v>
       </c>
       <c r="D183" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="184">
@@ -2704,7 +2704,7 @@
         <v>2023.0</v>
       </c>
       <c r="C184" t="n" s="2">
-        <v>45193.0</v>
+        <v>45186.0</v>
       </c>
       <c r="D184" t="n">
         <v>1.0</v>
@@ -2718,10 +2718,10 @@
         <v>2023.0</v>
       </c>
       <c r="C185" t="n" s="2">
-        <v>45200.0</v>
+        <v>45193.0</v>
       </c>
       <c r="D185" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="186">
@@ -2732,10 +2732,10 @@
         <v>2023.0</v>
       </c>
       <c r="C186" t="n" s="2">
-        <v>45207.0</v>
+        <v>45200.0</v>
       </c>
       <c r="D186" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="187">
@@ -2746,10 +2746,10 @@
         <v>2023.0</v>
       </c>
       <c r="C187" t="n" s="2">
-        <v>45214.0</v>
+        <v>45207.0</v>
       </c>
       <c r="D187" t="n">
-        <v>8.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="188">
@@ -2760,7 +2760,7 @@
         <v>2023.0</v>
       </c>
       <c r="C188" t="n" s="2">
-        <v>45221.0</v>
+        <v>45214.0</v>
       </c>
       <c r="D188" t="n">
         <v>8.0</v>
@@ -2774,10 +2774,10 @@
         <v>2023.0</v>
       </c>
       <c r="C189" t="n" s="2">
-        <v>45228.0</v>
+        <v>45221.0</v>
       </c>
       <c r="D189" t="n">
-        <v>17.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="190">
@@ -2788,10 +2788,10 @@
         <v>2023.0</v>
       </c>
       <c r="C190" t="n" s="2">
-        <v>45235.0</v>
+        <v>45228.0</v>
       </c>
       <c r="D190" t="n">
-        <v>9.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="191">
@@ -2802,7 +2802,7 @@
         <v>2023.0</v>
       </c>
       <c r="C191" t="n" s="2">
-        <v>45242.0</v>
+        <v>45235.0</v>
       </c>
       <c r="D191" t="n">
         <v>9.0</v>
@@ -2816,10 +2816,10 @@
         <v>2023.0</v>
       </c>
       <c r="C192" t="n" s="2">
-        <v>45249.0</v>
+        <v>45242.0</v>
       </c>
       <c r="D192" t="n">
-        <v>14.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="193">
@@ -2830,10 +2830,10 @@
         <v>2023.0</v>
       </c>
       <c r="C193" t="n" s="2">
-        <v>45256.0</v>
+        <v>45249.0</v>
       </c>
       <c r="D193" t="n">
-        <v>17.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="194">
@@ -2844,10 +2844,10 @@
         <v>2023.0</v>
       </c>
       <c r="C194" t="n" s="2">
-        <v>45263.0</v>
+        <v>45256.0</v>
       </c>
       <c r="D194" t="n">
-        <v>14.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="195">
@@ -2858,10 +2858,10 @@
         <v>2023.0</v>
       </c>
       <c r="C195" t="n" s="2">
-        <v>45270.0</v>
+        <v>45263.0</v>
       </c>
       <c r="D195" t="n">
-        <v>26.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="196">
@@ -2872,10 +2872,10 @@
         <v>2023.0</v>
       </c>
       <c r="C196" t="n" s="2">
-        <v>45277.0</v>
+        <v>45270.0</v>
       </c>
       <c r="D196" t="n">
-        <v>19.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="197">
@@ -2886,10 +2886,10 @@
         <v>2023.0</v>
       </c>
       <c r="C197" t="n" s="2">
-        <v>45284.0</v>
+        <v>45277.0</v>
       </c>
       <c r="D197" t="n">
-        <v>21.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="198">
@@ -2900,10 +2900,10 @@
         <v>2023.0</v>
       </c>
       <c r="C198" t="n" s="2">
-        <v>45291.0</v>
+        <v>45284.0</v>
       </c>
       <c r="D198" t="n">
-        <v>9.0</v>
+        <v>21.0</v>
       </c>
     </row>
     <row r="199">
@@ -2911,13 +2911,13 @@
         <v>5</v>
       </c>
       <c r="B199" t="n">
-        <v>2024.0</v>
+        <v>2023.0</v>
       </c>
       <c r="C199" t="n" s="2">
-        <v>45299.0</v>
+        <v>45291.0</v>
       </c>
       <c r="D199" t="n">
-        <v>26.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="200">
@@ -2928,10 +2928,10 @@
         <v>2024.0</v>
       </c>
       <c r="C200" t="n" s="2">
-        <v>45306.0</v>
+        <v>45299.0</v>
       </c>
       <c r="D200" t="n">
-        <v>14.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="201">
@@ -2942,10 +2942,10 @@
         <v>2024.0</v>
       </c>
       <c r="C201" t="n" s="2">
-        <v>45313.0</v>
+        <v>45306.0</v>
       </c>
       <c r="D201" t="n">
-        <v>15.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="202">
@@ -2956,10 +2956,10 @@
         <v>2024.0</v>
       </c>
       <c r="C202" t="n" s="2">
-        <v>45320.0</v>
+        <v>45313.0</v>
       </c>
       <c r="D202" t="n">
-        <v>18.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="203">
@@ -2970,10 +2970,10 @@
         <v>2024.0</v>
       </c>
       <c r="C203" t="n" s="2">
-        <v>45327.0</v>
+        <v>45320.0</v>
       </c>
       <c r="D203" t="n">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="204">
@@ -2984,10 +2984,10 @@
         <v>2024.0</v>
       </c>
       <c r="C204" t="n" s="2">
-        <v>45334.0</v>
+        <v>45327.0</v>
       </c>
       <c r="D204" t="n">
-        <v>13.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="205">
@@ -2998,10 +2998,10 @@
         <v>2024.0</v>
       </c>
       <c r="C205" t="n" s="2">
-        <v>45341.0</v>
+        <v>45334.0</v>
       </c>
       <c r="D205" t="n">
-        <v>11.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="206">
@@ -3012,10 +3012,10 @@
         <v>2024.0</v>
       </c>
       <c r="C206" t="n" s="2">
-        <v>45348.0</v>
+        <v>45341.0</v>
       </c>
       <c r="D206" t="n">
-        <v>8.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="207">
@@ -3026,10 +3026,10 @@
         <v>2024.0</v>
       </c>
       <c r="C207" t="n" s="2">
-        <v>45355.0</v>
+        <v>45348.0</v>
       </c>
       <c r="D207" t="n">
-        <v>1.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="208">
@@ -3040,10 +3040,10 @@
         <v>2024.0</v>
       </c>
       <c r="C208" t="n" s="2">
-        <v>45362.0</v>
+        <v>45355.0</v>
       </c>
       <c r="D208" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="209">
@@ -3054,10 +3054,10 @@
         <v>2024.0</v>
       </c>
       <c r="C209" t="n" s="2">
-        <v>45369.0</v>
+        <v>45362.0</v>
       </c>
       <c r="D209" t="n">
-        <v>8.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="210">
@@ -3068,10 +3068,10 @@
         <v>2024.0</v>
       </c>
       <c r="C210" t="n" s="2">
-        <v>45376.0</v>
+        <v>45369.0</v>
       </c>
       <c r="D210" t="n">
-        <v>9.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="211">
@@ -3082,10 +3082,10 @@
         <v>2024.0</v>
       </c>
       <c r="C211" t="n" s="2">
-        <v>45383.0</v>
+        <v>45376.0</v>
       </c>
       <c r="D211" t="n">
-        <v>5.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="212">
@@ -3096,10 +3096,10 @@
         <v>2024.0</v>
       </c>
       <c r="C212" t="n" s="2">
-        <v>45390.0</v>
+        <v>45383.0</v>
       </c>
       <c r="D212" t="n">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="213">
@@ -3110,10 +3110,10 @@
         <v>2024.0</v>
       </c>
       <c r="C213" t="n" s="2">
-        <v>45397.0</v>
+        <v>45390.0</v>
       </c>
       <c r="D213" t="n">
-        <v>13.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="214">
@@ -3124,10 +3124,10 @@
         <v>2024.0</v>
       </c>
       <c r="C214" t="n" s="2">
-        <v>45404.0</v>
+        <v>45397.0</v>
       </c>
       <c r="D214" t="n">
-        <v>24.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="215">
@@ -3138,10 +3138,10 @@
         <v>2024.0</v>
       </c>
       <c r="C215" t="n" s="2">
-        <v>45411.0</v>
+        <v>45404.0</v>
       </c>
       <c r="D215" t="n">
-        <v>17.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="216">
@@ -3152,10 +3152,10 @@
         <v>2024.0</v>
       </c>
       <c r="C216" t="n" s="2">
-        <v>45418.0</v>
+        <v>45411.0</v>
       </c>
       <c r="D216" t="n">
-        <v>3.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="217">
@@ -3166,10 +3166,10 @@
         <v>2024.0</v>
       </c>
       <c r="C217" t="n" s="2">
-        <v>45425.0</v>
+        <v>45418.0</v>
       </c>
       <c r="D217" t="n">
-        <v>16.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="218">
@@ -3180,10 +3180,10 @@
         <v>2024.0</v>
       </c>
       <c r="C218" t="n" s="2">
-        <v>45432.0</v>
+        <v>45425.0</v>
       </c>
       <c r="D218" t="n">
-        <v>19.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="219">
@@ -3194,10 +3194,10 @@
         <v>2024.0</v>
       </c>
       <c r="C219" t="n" s="2">
-        <v>45439.0</v>
+        <v>45432.0</v>
       </c>
       <c r="D219" t="n">
-        <v>30.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="220">
@@ -3208,10 +3208,10 @@
         <v>2024.0</v>
       </c>
       <c r="C220" t="n" s="2">
-        <v>45446.0</v>
+        <v>45439.0</v>
       </c>
       <c r="D220" t="n">
-        <v>28.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="221">
@@ -3222,10 +3222,10 @@
         <v>2024.0</v>
       </c>
       <c r="C221" t="n" s="2">
-        <v>45453.0</v>
+        <v>45446.0</v>
       </c>
       <c r="D221" t="n">
-        <v>19.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="222">
@@ -3236,10 +3236,10 @@
         <v>2024.0</v>
       </c>
       <c r="C222" t="n" s="2">
-        <v>45460.0</v>
+        <v>45453.0</v>
       </c>
       <c r="D222" t="n">
-        <v>26.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="223">
@@ -3250,10 +3250,10 @@
         <v>2024.0</v>
       </c>
       <c r="C223" t="n" s="2">
-        <v>45467.0</v>
+        <v>45460.0</v>
       </c>
       <c r="D223" t="n">
-        <v>8.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="224">
@@ -3264,10 +3264,10 @@
         <v>2024.0</v>
       </c>
       <c r="C224" t="n" s="2">
-        <v>45474.0</v>
+        <v>45467.0</v>
       </c>
       <c r="D224" t="n">
-        <v>12.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="225">
@@ -3278,7 +3278,7 @@
         <v>2024.0</v>
       </c>
       <c r="C225" t="n" s="2">
-        <v>45481.0</v>
+        <v>45474.0</v>
       </c>
       <c r="D225" t="n">
         <v>12.0</v>
@@ -3292,10 +3292,10 @@
         <v>2024.0</v>
       </c>
       <c r="C226" t="n" s="2">
-        <v>45488.0</v>
+        <v>45481.0</v>
       </c>
       <c r="D226" t="n">
-        <v>4.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="227">
@@ -3306,10 +3306,10 @@
         <v>2024.0</v>
       </c>
       <c r="C227" t="n" s="2">
-        <v>45495.0</v>
+        <v>45488.0</v>
       </c>
       <c r="D227" t="n">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="228">
@@ -3320,10 +3320,10 @@
         <v>2024.0</v>
       </c>
       <c r="C228" t="n" s="2">
-        <v>45502.0</v>
+        <v>45495.0</v>
       </c>
       <c r="D228" t="n">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="229">
@@ -3334,10 +3334,10 @@
         <v>2024.0</v>
       </c>
       <c r="C229" t="n" s="2">
-        <v>45509.0</v>
+        <v>45502.0</v>
       </c>
       <c r="D229" t="n">
-        <v>2.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="230">
@@ -3348,10 +3348,10 @@
         <v>2024.0</v>
       </c>
       <c r="C230" t="n" s="2">
-        <v>45516.0</v>
+        <v>45509.0</v>
       </c>
       <c r="D230" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="231">
@@ -3362,7 +3362,7 @@
         <v>2024.0</v>
       </c>
       <c r="C231" t="n" s="2">
-        <v>45523.0</v>
+        <v>45516.0</v>
       </c>
       <c r="D231" t="n">
         <v>4.0</v>
@@ -3376,7 +3376,7 @@
         <v>2024.0</v>
       </c>
       <c r="C232" t="n" s="2">
-        <v>45530.0</v>
+        <v>45523.0</v>
       </c>
       <c r="D232" t="n">
         <v>4.0</v>
@@ -3390,7 +3390,7 @@
         <v>2024.0</v>
       </c>
       <c r="C233" t="n" s="2">
-        <v>45537.0</v>
+        <v>45530.0</v>
       </c>
       <c r="D233" t="n">
         <v>4.0</v>
@@ -3404,10 +3404,10 @@
         <v>2024.0</v>
       </c>
       <c r="C234" t="n" s="2">
-        <v>45544.0</v>
+        <v>45537.0</v>
       </c>
       <c r="D234" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="235">
@@ -3418,10 +3418,10 @@
         <v>2024.0</v>
       </c>
       <c r="C235" t="n" s="2">
-        <v>45551.0</v>
+        <v>45544.0</v>
       </c>
       <c r="D235" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="236">
@@ -3432,10 +3432,10 @@
         <v>2024.0</v>
       </c>
       <c r="C236" t="n" s="2">
-        <v>45558.0</v>
+        <v>45551.0</v>
       </c>
       <c r="D236" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="237">
@@ -3446,10 +3446,10 @@
         <v>2024.0</v>
       </c>
       <c r="C237" t="n" s="2">
-        <v>45600.0</v>
+        <v>45558.0</v>
       </c>
       <c r="D237" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="238">
@@ -3460,10 +3460,10 @@
         <v>2024.0</v>
       </c>
       <c r="C238" t="n" s="2">
-        <v>45607.0</v>
+        <v>45600.0</v>
       </c>
       <c r="D238" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="239">
@@ -3474,10 +3474,10 @@
         <v>2024.0</v>
       </c>
       <c r="C239" t="n" s="2">
-        <v>45628.0</v>
+        <v>45607.0</v>
       </c>
       <c r="D239" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="240">
@@ -3488,10 +3488,10 @@
         <v>2024.0</v>
       </c>
       <c r="C240" t="n" s="2">
-        <v>45635.0</v>
+        <v>45628.0</v>
       </c>
       <c r="D240" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="241">
@@ -3502,7 +3502,7 @@
         <v>2024.0</v>
       </c>
       <c r="C241" t="n" s="2">
-        <v>45642.0</v>
+        <v>45635.0</v>
       </c>
       <c r="D241" t="n">
         <v>3.0</v>
@@ -3516,10 +3516,10 @@
         <v>2024.0</v>
       </c>
       <c r="C242" t="n" s="2">
-        <v>45649.0</v>
+        <v>45642.0</v>
       </c>
       <c r="D242" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="243">
@@ -3530,7 +3530,7 @@
         <v>2024.0</v>
       </c>
       <c r="C243" t="n" s="2">
-        <v>45656.0</v>
+        <v>45649.0</v>
       </c>
       <c r="D243" t="n">
         <v>1.0</v>
@@ -3541,13 +3541,13 @@
         <v>5</v>
       </c>
       <c r="B244" t="n">
-        <v>2025.0</v>
+        <v>2024.0</v>
       </c>
       <c r="C244" t="n" s="2">
-        <v>45672.0</v>
+        <v>45656.0</v>
       </c>
       <c r="D244" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="245">
@@ -3558,10 +3558,10 @@
         <v>2025.0</v>
       </c>
       <c r="C245" t="n" s="2">
-        <v>45679.0</v>
+        <v>45672.0</v>
       </c>
       <c r="D245" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="246">
@@ -3572,7 +3572,7 @@
         <v>2025.0</v>
       </c>
       <c r="C246" t="n" s="2">
-        <v>45686.0</v>
+        <v>45679.0</v>
       </c>
       <c r="D246" t="n">
         <v>1.0</v>
@@ -3586,10 +3586,10 @@
         <v>2025.0</v>
       </c>
       <c r="C247" t="n" s="2">
-        <v>45721.0</v>
+        <v>45686.0</v>
       </c>
       <c r="D247" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="248">
@@ -3600,10 +3600,10 @@
         <v>2025.0</v>
       </c>
       <c r="C248" t="n" s="2">
-        <v>45728.0</v>
+        <v>45721.0</v>
       </c>
       <c r="D248" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="249">
@@ -3614,10 +3614,10 @@
         <v>2025.0</v>
       </c>
       <c r="C249" t="n" s="2">
-        <v>45742.0</v>
+        <v>45728.0</v>
       </c>
       <c r="D249" t="n">
-        <v>9.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="250">
@@ -3628,10 +3628,10 @@
         <v>2025.0</v>
       </c>
       <c r="C250" t="n" s="2">
-        <v>45749.0</v>
+        <v>45742.0</v>
       </c>
       <c r="D250" t="n">
-        <v>5.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="251">
@@ -3642,10 +3642,10 @@
         <v>2025.0</v>
       </c>
       <c r="C251" t="n" s="2">
-        <v>45756.0</v>
+        <v>45749.0</v>
       </c>
       <c r="D251" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="252">
@@ -3656,10 +3656,10 @@
         <v>2025.0</v>
       </c>
       <c r="C252" t="n" s="2">
-        <v>45763.0</v>
+        <v>45756.0</v>
       </c>
       <c r="D252" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="253">
@@ -3670,10 +3670,10 @@
         <v>2025.0</v>
       </c>
       <c r="C253" t="n" s="2">
-        <v>45770.0</v>
+        <v>45763.0</v>
       </c>
       <c r="D253" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="254">
@@ -3684,10 +3684,10 @@
         <v>2025.0</v>
       </c>
       <c r="C254" t="n" s="2">
-        <v>45777.0</v>
+        <v>45770.0</v>
       </c>
       <c r="D254" t="n">
-        <v>7.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="255">
@@ -3698,10 +3698,10 @@
         <v>2025.0</v>
       </c>
       <c r="C255" t="n" s="2">
-        <v>45784.0</v>
+        <v>45777.0</v>
       </c>
       <c r="D255" t="n">
-        <v>2.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="256">
@@ -3712,10 +3712,10 @@
         <v>2025.0</v>
       </c>
       <c r="C256" t="n" s="2">
-        <v>45791.0</v>
+        <v>45784.0</v>
       </c>
       <c r="D256" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="257">
@@ -3726,10 +3726,10 @@
         <v>2025.0</v>
       </c>
       <c r="C257" t="n" s="2">
-        <v>45798.0</v>
+        <v>45791.0</v>
       </c>
       <c r="D257" t="n">
-        <v>8.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="258">
@@ -3740,10 +3740,10 @@
         <v>2025.0</v>
       </c>
       <c r="C258" t="n" s="2">
-        <v>45805.0</v>
+        <v>45798.0</v>
       </c>
       <c r="D258" t="n">
-        <v>4.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="259">
@@ -3754,10 +3754,10 @@
         <v>2025.0</v>
       </c>
       <c r="C259" t="n" s="2">
-        <v>45812.0</v>
+        <v>45805.0</v>
       </c>
       <c r="D259" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="260">
@@ -3768,10 +3768,10 @@
         <v>2025.0</v>
       </c>
       <c r="C260" t="n" s="2">
-        <v>45819.0</v>
+        <v>45812.0</v>
       </c>
       <c r="D260" t="n">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="261">
@@ -3782,10 +3782,10 @@
         <v>2025.0</v>
       </c>
       <c r="C261" t="n" s="2">
-        <v>45826.0</v>
+        <v>45819.0</v>
       </c>
       <c r="D261" t="n">
-        <v>13.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="262">
@@ -3796,10 +3796,10 @@
         <v>2025.0</v>
       </c>
       <c r="C262" t="n" s="2">
-        <v>45833.0</v>
+        <v>45826.0</v>
       </c>
       <c r="D262" t="n">
-        <v>1.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="263">
@@ -3810,10 +3810,10 @@
         <v>2025.0</v>
       </c>
       <c r="C263" t="n" s="2">
-        <v>45840.0</v>
+        <v>45833.0</v>
       </c>
       <c r="D263" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="264">
@@ -3824,7 +3824,7 @@
         <v>2025.0</v>
       </c>
       <c r="C264" t="n" s="2">
-        <v>45847.0</v>
+        <v>45840.0</v>
       </c>
       <c r="D264" t="n">
         <v>4.0</v>
@@ -3838,10 +3838,10 @@
         <v>2025.0</v>
       </c>
       <c r="C265" t="n" s="2">
-        <v>45854.0</v>
+        <v>45847.0</v>
       </c>
       <c r="D265" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="266">
@@ -3852,10 +3852,10 @@
         <v>2025.0</v>
       </c>
       <c r="C266" t="n" s="2">
-        <v>45861.0</v>
+        <v>45854.0</v>
       </c>
       <c r="D266" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="267">
@@ -3866,10 +3866,10 @@
         <v>2025.0</v>
       </c>
       <c r="C267" t="n" s="2">
-        <v>45868.0</v>
+        <v>45861.0</v>
       </c>
       <c r="D267" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="268">
@@ -3880,10 +3880,10 @@
         <v>2025.0</v>
       </c>
       <c r="C268" t="n" s="2">
-        <v>45882.0</v>
+        <v>45868.0</v>
       </c>
       <c r="D268" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="269">
@@ -3894,7 +3894,7 @@
         <v>2025.0</v>
       </c>
       <c r="C269" t="n" s="2">
-        <v>45889.0</v>
+        <v>45882.0</v>
       </c>
       <c r="D269" t="n">
         <v>1.0</v>
@@ -3908,10 +3908,10 @@
         <v>2025.0</v>
       </c>
       <c r="C270" t="n" s="2">
-        <v>45896.0</v>
+        <v>45889.0</v>
       </c>
       <c r="D270" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="271">
@@ -3922,7 +3922,7 @@
         <v>2025.0</v>
       </c>
       <c r="C271" t="n" s="2">
-        <v>45903.0</v>
+        <v>45896.0</v>
       </c>
       <c r="D271" t="n">
         <v>3.0</v>
@@ -3936,10 +3936,10 @@
         <v>2025.0</v>
       </c>
       <c r="C272" t="n" s="2">
-        <v>45910.0</v>
+        <v>45903.0</v>
       </c>
       <c r="D272" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="273">
@@ -3950,7 +3950,7 @@
         <v>2025.0</v>
       </c>
       <c r="C273" t="n" s="2">
-        <v>45973.0</v>
+        <v>45910.0</v>
       </c>
       <c r="D273" t="n">
         <v>1.0</v>
@@ -3964,10 +3964,10 @@
         <v>2025.0</v>
       </c>
       <c r="C274" t="n" s="2">
-        <v>45987.0</v>
+        <v>45973.0</v>
       </c>
       <c r="D274" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="275">
@@ -3978,10 +3978,10 @@
         <v>2025.0</v>
       </c>
       <c r="C275" t="n" s="2">
-        <v>45994.0</v>
+        <v>45987.0</v>
       </c>
       <c r="D275" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="276">
@@ -3992,10 +3992,10 @@
         <v>2025.0</v>
       </c>
       <c r="C276" t="n" s="2">
-        <v>46001.0</v>
+        <v>45994.0</v>
       </c>
       <c r="D276" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="277">
@@ -4006,10 +4006,10 @@
         <v>2025.0</v>
       </c>
       <c r="C277" t="n" s="2">
-        <v>46008.0</v>
+        <v>46001.0</v>
       </c>
       <c r="D277" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="278">
@@ -4020,10 +4020,10 @@
         <v>2025.0</v>
       </c>
       <c r="C278" t="n" s="2">
-        <v>46022.0</v>
+        <v>46008.0</v>
       </c>
       <c r="D278" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="279">
@@ -4034,10 +4034,10 @@
         <v>2025.0</v>
       </c>
       <c r="C279" t="n" s="2">
-        <v>46029.0</v>
+        <v>46022.0</v>
       </c>
       <c r="D279" t="n">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="280">
@@ -4045,13 +4045,13 @@
         <v>5</v>
       </c>
       <c r="B280" t="n">
-        <v>2026.0</v>
+        <v>2025.0</v>
       </c>
       <c r="C280" t="n" s="2">
-        <v>46030.0</v>
+        <v>46029.0</v>
       </c>
       <c r="D280" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="281">
@@ -4062,10 +4062,10 @@
         <v>2026.0</v>
       </c>
       <c r="C281" t="n" s="2">
-        <v>46037.0</v>
+        <v>46030.0</v>
       </c>
       <c r="D281" t="n">
-        <v>12.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="282">
@@ -4076,10 +4076,10 @@
         <v>2026.0</v>
       </c>
       <c r="C282" t="n" s="2">
-        <v>46044.0</v>
+        <v>46037.0</v>
       </c>
       <c r="D282" t="n">
-        <v>9.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="283">
@@ -4090,10 +4090,10 @@
         <v>2026.0</v>
       </c>
       <c r="C283" t="n" s="2">
-        <v>46051.0</v>
+        <v>46044.0</v>
       </c>
       <c r="D283" t="n">
-        <v>10.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="284">
@@ -4104,10 +4104,10 @@
         <v>2026.0</v>
       </c>
       <c r="C284" t="n" s="2">
-        <v>46058.0</v>
+        <v>46051.0</v>
       </c>
       <c r="D284" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="285">
@@ -4118,10 +4118,10 @@
         <v>2026.0</v>
       </c>
       <c r="C285" t="n" s="2">
-        <v>46065.0</v>
+        <v>46058.0</v>
       </c>
       <c r="D285" t="n">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="286">
@@ -4132,10 +4132,10 @@
         <v>2026.0</v>
       </c>
       <c r="C286" t="n" s="2">
-        <v>46072.0</v>
+        <v>46065.0</v>
       </c>
       <c r="D286" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="287">
@@ -4146,7 +4146,7 @@
         <v>2026.0</v>
       </c>
       <c r="C287" t="n" s="2">
-        <v>46079.0</v>
+        <v>46072.0</v>
       </c>
       <c r="D287" t="n">
         <v>5.0</v>
@@ -4160,10 +4160,10 @@
         <v>2026.0</v>
       </c>
       <c r="C288" t="n" s="2">
-        <v>46086.0</v>
+        <v>46079.0</v>
       </c>
       <c r="D288" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="289">
@@ -4174,7 +4174,7 @@
         <v>2026.0</v>
       </c>
       <c r="C289" t="n" s="2">
-        <v>46093.0</v>
+        <v>46086.0</v>
       </c>
       <c r="D289" t="n">
         <v>2.0</v>
@@ -4188,10 +4188,10 @@
         <v>2026.0</v>
       </c>
       <c r="C290" t="n" s="2">
-        <v>46100.0</v>
+        <v>46093.0</v>
       </c>
       <c r="D290" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="291">
@@ -4202,10 +4202,10 @@
         <v>2026.0</v>
       </c>
       <c r="C291" t="n" s="2">
-        <v>46107.0</v>
+        <v>46100.0</v>
       </c>
       <c r="D291" t="n">
-        <v>9.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="292">
@@ -4216,10 +4216,10 @@
         <v>2026.0</v>
       </c>
       <c r="C292" t="n" s="2">
-        <v>46114.0</v>
+        <v>46107.0</v>
       </c>
       <c r="D292" t="n">
-        <v>5.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="293">
@@ -4230,10 +4230,10 @@
         <v>2026.0</v>
       </c>
       <c r="C293" t="n" s="2">
-        <v>46121.0</v>
+        <v>46114.0</v>
       </c>
       <c r="D293" t="n">
-        <v>13.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="294">
@@ -4244,10 +4244,10 @@
         <v>2026.0</v>
       </c>
       <c r="C294" t="n" s="2">
-        <v>46128.0</v>
+        <v>46121.0</v>
       </c>
       <c r="D294" t="n">
-        <v>4.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="295">
@@ -4258,7 +4258,7 @@
         <v>2026.0</v>
       </c>
       <c r="C295" t="n" s="2">
-        <v>46135.0</v>
+        <v>46128.0</v>
       </c>
       <c r="D295" t="n">
         <v>4.0</v>
@@ -4272,10 +4272,10 @@
         <v>2026.0</v>
       </c>
       <c r="C296" t="n" s="2">
-        <v>46142.0</v>
+        <v>46135.0</v>
       </c>
       <c r="D296" t="n">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="297">
@@ -4286,38 +4286,38 @@
         <v>2026.0</v>
       </c>
       <c r="C297" t="n" s="2">
-        <v>46149.0</v>
+        <v>46142.0</v>
       </c>
       <c r="D297" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B298" t="n">
-        <v>2023.0</v>
+        <v>2026.0</v>
       </c>
       <c r="C298" t="n" s="2">
-        <v>45095.0</v>
+        <v>46149.0</v>
       </c>
       <c r="D298" t="n">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B299" t="n">
-        <v>2023.0</v>
+        <v>2026.0</v>
       </c>
       <c r="C299" t="n" s="2">
-        <v>45102.0</v>
+        <v>46156.0</v>
       </c>
       <c r="D299" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="300">
@@ -4328,7 +4328,7 @@
         <v>2023.0</v>
       </c>
       <c r="C300" t="n" s="2">
-        <v>45158.0</v>
+        <v>45095.0</v>
       </c>
       <c r="D300" t="n">
         <v>1.0</v>
@@ -4342,10 +4342,10 @@
         <v>2023.0</v>
       </c>
       <c r="C301" t="n" s="2">
-        <v>45207.0</v>
+        <v>45102.0</v>
       </c>
       <c r="D301" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="302">
@@ -4356,10 +4356,10 @@
         <v>2023.0</v>
       </c>
       <c r="C302" t="n" s="2">
-        <v>45214.0</v>
+        <v>45158.0</v>
       </c>
       <c r="D302" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="303">
@@ -4370,10 +4370,10 @@
         <v>2023.0</v>
       </c>
       <c r="C303" t="n" s="2">
-        <v>45221.0</v>
+        <v>45207.0</v>
       </c>
       <c r="D303" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="304">
@@ -4384,10 +4384,10 @@
         <v>2023.0</v>
       </c>
       <c r="C304" t="n" s="2">
-        <v>45249.0</v>
+        <v>45214.0</v>
       </c>
       <c r="D304" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="305">
@@ -4398,10 +4398,10 @@
         <v>2023.0</v>
       </c>
       <c r="C305" t="n" s="2">
-        <v>45256.0</v>
+        <v>45221.0</v>
       </c>
       <c r="D305" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="306">
@@ -4412,10 +4412,10 @@
         <v>2023.0</v>
       </c>
       <c r="C306" t="n" s="2">
-        <v>45263.0</v>
+        <v>45249.0</v>
       </c>
       <c r="D306" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="307">
@@ -4426,10 +4426,10 @@
         <v>2023.0</v>
       </c>
       <c r="C307" t="n" s="2">
-        <v>45270.0</v>
+        <v>45256.0</v>
       </c>
       <c r="D307" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="308">
@@ -4440,7 +4440,7 @@
         <v>2023.0</v>
       </c>
       <c r="C308" t="n" s="2">
-        <v>45277.0</v>
+        <v>45263.0</v>
       </c>
       <c r="D308" t="n">
         <v>4.0</v>
@@ -4454,7 +4454,7 @@
         <v>2023.0</v>
       </c>
       <c r="C309" t="n" s="2">
-        <v>45284.0</v>
+        <v>45270.0</v>
       </c>
       <c r="D309" t="n">
         <v>1.0</v>
@@ -4468,10 +4468,10 @@
         <v>2023.0</v>
       </c>
       <c r="C310" t="n" s="2">
-        <v>45291.0</v>
+        <v>45277.0</v>
       </c>
       <c r="D310" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="311">
@@ -4479,13 +4479,13 @@
         <v>6</v>
       </c>
       <c r="B311" t="n">
-        <v>2024.0</v>
+        <v>2023.0</v>
       </c>
       <c r="C311" t="n" s="2">
-        <v>45306.0</v>
+        <v>45284.0</v>
       </c>
       <c r="D311" t="n">
-        <v>7.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="312">
@@ -4493,13 +4493,13 @@
         <v>6</v>
       </c>
       <c r="B312" t="n">
-        <v>2024.0</v>
+        <v>2023.0</v>
       </c>
       <c r="C312" t="n" s="2">
-        <v>45313.0</v>
+        <v>45291.0</v>
       </c>
       <c r="D312" t="n">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="313">
@@ -4510,10 +4510,10 @@
         <v>2024.0</v>
       </c>
       <c r="C313" t="n" s="2">
-        <v>45320.0</v>
+        <v>45306.0</v>
       </c>
       <c r="D313" t="n">
-        <v>19.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="314">
@@ -4524,10 +4524,10 @@
         <v>2024.0</v>
       </c>
       <c r="C314" t="n" s="2">
-        <v>45327.0</v>
+        <v>45313.0</v>
       </c>
       <c r="D314" t="n">
-        <v>18.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="315">
@@ -4538,10 +4538,10 @@
         <v>2024.0</v>
       </c>
       <c r="C315" t="n" s="2">
-        <v>45334.0</v>
+        <v>45320.0</v>
       </c>
       <c r="D315" t="n">
-        <v>9.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="316">
@@ -4552,10 +4552,10 @@
         <v>2024.0</v>
       </c>
       <c r="C316" t="n" s="2">
-        <v>45341.0</v>
+        <v>45327.0</v>
       </c>
       <c r="D316" t="n">
-        <v>12.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="317">
@@ -4566,10 +4566,10 @@
         <v>2024.0</v>
       </c>
       <c r="C317" t="n" s="2">
-        <v>45348.0</v>
+        <v>45334.0</v>
       </c>
       <c r="D317" t="n">
-        <v>12.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="318">
@@ -4580,10 +4580,10 @@
         <v>2024.0</v>
       </c>
       <c r="C318" t="n" s="2">
-        <v>45355.0</v>
+        <v>45341.0</v>
       </c>
       <c r="D318" t="n">
-        <v>10.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="319">
@@ -4594,7 +4594,7 @@
         <v>2024.0</v>
       </c>
       <c r="C319" t="n" s="2">
-        <v>45362.0</v>
+        <v>45348.0</v>
       </c>
       <c r="D319" t="n">
         <v>12.0</v>
@@ -4608,10 +4608,10 @@
         <v>2024.0</v>
       </c>
       <c r="C320" t="n" s="2">
-        <v>45369.0</v>
+        <v>45355.0</v>
       </c>
       <c r="D320" t="n">
-        <v>13.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="321">
@@ -4622,10 +4622,10 @@
         <v>2024.0</v>
       </c>
       <c r="C321" t="n" s="2">
-        <v>45376.0</v>
+        <v>45362.0</v>
       </c>
       <c r="D321" t="n">
-        <v>18.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="322">
@@ -4636,10 +4636,10 @@
         <v>2024.0</v>
       </c>
       <c r="C322" t="n" s="2">
-        <v>45383.0</v>
+        <v>45369.0</v>
       </c>
       <c r="D322" t="n">
-        <v>12.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="323">
@@ -4650,10 +4650,10 @@
         <v>2024.0</v>
       </c>
       <c r="C323" t="n" s="2">
-        <v>45390.0</v>
+        <v>45376.0</v>
       </c>
       <c r="D323" t="n">
-        <v>6.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="324">
@@ -4664,10 +4664,10 @@
         <v>2024.0</v>
       </c>
       <c r="C324" t="n" s="2">
-        <v>45397.0</v>
+        <v>45383.0</v>
       </c>
       <c r="D324" t="n">
-        <v>10.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="325">
@@ -4678,10 +4678,10 @@
         <v>2024.0</v>
       </c>
       <c r="C325" t="n" s="2">
-        <v>45404.0</v>
+        <v>45390.0</v>
       </c>
       <c r="D325" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="326">
@@ -4692,10 +4692,10 @@
         <v>2024.0</v>
       </c>
       <c r="C326" t="n" s="2">
-        <v>45411.0</v>
+        <v>45397.0</v>
       </c>
       <c r="D326" t="n">
-        <v>2.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="327">
@@ -4706,10 +4706,10 @@
         <v>2024.0</v>
       </c>
       <c r="C327" t="n" s="2">
-        <v>45418.0</v>
+        <v>45404.0</v>
       </c>
       <c r="D327" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="328">
@@ -4720,10 +4720,10 @@
         <v>2024.0</v>
       </c>
       <c r="C328" t="n" s="2">
-        <v>45425.0</v>
+        <v>45411.0</v>
       </c>
       <c r="D328" t="n">
-        <v>9.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="329">
@@ -4734,10 +4734,10 @@
         <v>2024.0</v>
       </c>
       <c r="C329" t="n" s="2">
-        <v>45432.0</v>
+        <v>45418.0</v>
       </c>
       <c r="D329" t="n">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="330">
@@ -4748,10 +4748,10 @@
         <v>2024.0</v>
       </c>
       <c r="C330" t="n" s="2">
-        <v>45439.0</v>
+        <v>45425.0</v>
       </c>
       <c r="D330" t="n">
-        <v>6.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="331">
@@ -4762,10 +4762,10 @@
         <v>2024.0</v>
       </c>
       <c r="C331" t="n" s="2">
-        <v>45446.0</v>
+        <v>45432.0</v>
       </c>
       <c r="D331" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="332">
@@ -4776,10 +4776,10 @@
         <v>2024.0</v>
       </c>
       <c r="C332" t="n" s="2">
-        <v>45453.0</v>
+        <v>45439.0</v>
       </c>
       <c r="D332" t="n">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="333">
@@ -4790,10 +4790,10 @@
         <v>2024.0</v>
       </c>
       <c r="C333" t="n" s="2">
-        <v>45460.0</v>
+        <v>45446.0</v>
       </c>
       <c r="D333" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="334">
@@ -4804,7 +4804,7 @@
         <v>2024.0</v>
       </c>
       <c r="C334" t="n" s="2">
-        <v>45467.0</v>
+        <v>45453.0</v>
       </c>
       <c r="D334" t="n">
         <v>4.0</v>
@@ -4818,10 +4818,10 @@
         <v>2024.0</v>
       </c>
       <c r="C335" t="n" s="2">
-        <v>45474.0</v>
+        <v>45460.0</v>
       </c>
       <c r="D335" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="336">
@@ -4832,10 +4832,10 @@
         <v>2024.0</v>
       </c>
       <c r="C336" t="n" s="2">
-        <v>45481.0</v>
+        <v>45467.0</v>
       </c>
       <c r="D336" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="337">
@@ -4846,7 +4846,7 @@
         <v>2024.0</v>
       </c>
       <c r="C337" t="n" s="2">
-        <v>45488.0</v>
+        <v>45474.0</v>
       </c>
       <c r="D337" t="n">
         <v>2.0</v>
@@ -4860,10 +4860,10 @@
         <v>2024.0</v>
       </c>
       <c r="C338" t="n" s="2">
-        <v>45495.0</v>
+        <v>45481.0</v>
       </c>
       <c r="D338" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="339">
@@ -4874,7 +4874,7 @@
         <v>2024.0</v>
       </c>
       <c r="C339" t="n" s="2">
-        <v>45502.0</v>
+        <v>45488.0</v>
       </c>
       <c r="D339" t="n">
         <v>2.0</v>
@@ -4888,10 +4888,10 @@
         <v>2024.0</v>
       </c>
       <c r="C340" t="n" s="2">
-        <v>45509.0</v>
+        <v>45495.0</v>
       </c>
       <c r="D340" t="n">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="341">
@@ -4902,10 +4902,10 @@
         <v>2024.0</v>
       </c>
       <c r="C341" t="n" s="2">
-        <v>45523.0</v>
+        <v>45502.0</v>
       </c>
       <c r="D341" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="342">
@@ -4916,7 +4916,7 @@
         <v>2024.0</v>
       </c>
       <c r="C342" t="n" s="2">
-        <v>45551.0</v>
+        <v>45509.0</v>
       </c>
       <c r="D342" t="n">
         <v>1.0</v>
@@ -4930,7 +4930,7 @@
         <v>2024.0</v>
       </c>
       <c r="C343" t="n" s="2">
-        <v>45558.0</v>
+        <v>45523.0</v>
       </c>
       <c r="D343" t="n">
         <v>1.0</v>
@@ -4944,10 +4944,10 @@
         <v>2024.0</v>
       </c>
       <c r="C344" t="n" s="2">
-        <v>45572.0</v>
+        <v>45551.0</v>
       </c>
       <c r="D344" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="345">
@@ -4958,7 +4958,7 @@
         <v>2024.0</v>
       </c>
       <c r="C345" t="n" s="2">
-        <v>45593.0</v>
+        <v>45558.0</v>
       </c>
       <c r="D345" t="n">
         <v>1.0</v>
@@ -4972,7 +4972,7 @@
         <v>2024.0</v>
       </c>
       <c r="C346" t="n" s="2">
-        <v>45614.0</v>
+        <v>45572.0</v>
       </c>
       <c r="D346" t="n">
         <v>2.0</v>
@@ -4986,7 +4986,7 @@
         <v>2024.0</v>
       </c>
       <c r="C347" t="n" s="2">
-        <v>45621.0</v>
+        <v>45593.0</v>
       </c>
       <c r="D347" t="n">
         <v>1.0</v>
@@ -5000,10 +5000,10 @@
         <v>2024.0</v>
       </c>
       <c r="C348" t="n" s="2">
-        <v>45635.0</v>
+        <v>45614.0</v>
       </c>
       <c r="D348" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="349">
@@ -5014,7 +5014,7 @@
         <v>2024.0</v>
       </c>
       <c r="C349" t="n" s="2">
-        <v>45649.0</v>
+        <v>45621.0</v>
       </c>
       <c r="D349" t="n">
         <v>1.0</v>
@@ -5025,13 +5025,13 @@
         <v>6</v>
       </c>
       <c r="B350" t="n">
-        <v>2025.0</v>
+        <v>2024.0</v>
       </c>
       <c r="C350" t="n" s="2">
-        <v>45665.0</v>
+        <v>45635.0</v>
       </c>
       <c r="D350" t="n">
-        <v>9.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="351">
@@ -5039,13 +5039,13 @@
         <v>6</v>
       </c>
       <c r="B351" t="n">
-        <v>2025.0</v>
+        <v>2024.0</v>
       </c>
       <c r="C351" t="n" s="2">
-        <v>45672.0</v>
+        <v>45649.0</v>
       </c>
       <c r="D351" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="352">
@@ -5056,10 +5056,10 @@
         <v>2025.0</v>
       </c>
       <c r="C352" t="n" s="2">
-        <v>45679.0</v>
+        <v>45665.0</v>
       </c>
       <c r="D352" t="n">
-        <v>1.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="353">
@@ -5070,10 +5070,10 @@
         <v>2025.0</v>
       </c>
       <c r="C353" t="n" s="2">
-        <v>45686.0</v>
+        <v>45672.0</v>
       </c>
       <c r="D353" t="n">
-        <v>8.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="354">
@@ -5084,10 +5084,10 @@
         <v>2025.0</v>
       </c>
       <c r="C354" t="n" s="2">
-        <v>45693.0</v>
+        <v>45679.0</v>
       </c>
       <c r="D354" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="355">
@@ -5098,10 +5098,10 @@
         <v>2025.0</v>
       </c>
       <c r="C355" t="n" s="2">
-        <v>45700.0</v>
+        <v>45686.0</v>
       </c>
       <c r="D355" t="n">
-        <v>5.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="356">
@@ -5112,10 +5112,10 @@
         <v>2025.0</v>
       </c>
       <c r="C356" t="n" s="2">
-        <v>45707.0</v>
+        <v>45693.0</v>
       </c>
       <c r="D356" t="n">
-        <v>8.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="357">
@@ -5126,10 +5126,10 @@
         <v>2025.0</v>
       </c>
       <c r="C357" t="n" s="2">
-        <v>45714.0</v>
+        <v>45700.0</v>
       </c>
       <c r="D357" t="n">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="358">
@@ -5140,7 +5140,7 @@
         <v>2025.0</v>
       </c>
       <c r="C358" t="n" s="2">
-        <v>45721.0</v>
+        <v>45707.0</v>
       </c>
       <c r="D358" t="n">
         <v>8.0</v>
@@ -5154,10 +5154,10 @@
         <v>2025.0</v>
       </c>
       <c r="C359" t="n" s="2">
-        <v>45728.0</v>
+        <v>45714.0</v>
       </c>
       <c r="D359" t="n">
-        <v>7.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="360">
@@ -5168,10 +5168,10 @@
         <v>2025.0</v>
       </c>
       <c r="C360" t="n" s="2">
-        <v>45735.0</v>
+        <v>45721.0</v>
       </c>
       <c r="D360" t="n">
-        <v>4.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="361">
@@ -5182,10 +5182,10 @@
         <v>2025.0</v>
       </c>
       <c r="C361" t="n" s="2">
-        <v>45742.0</v>
+        <v>45728.0</v>
       </c>
       <c r="D361" t="n">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="362">
@@ -5196,10 +5196,10 @@
         <v>2025.0</v>
       </c>
       <c r="C362" t="n" s="2">
-        <v>45749.0</v>
+        <v>45735.0</v>
       </c>
       <c r="D362" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="363">
@@ -5210,10 +5210,10 @@
         <v>2025.0</v>
       </c>
       <c r="C363" t="n" s="2">
-        <v>45756.0</v>
+        <v>45742.0</v>
       </c>
       <c r="D363" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="364">
@@ -5224,10 +5224,10 @@
         <v>2025.0</v>
       </c>
       <c r="C364" t="n" s="2">
-        <v>45763.0</v>
+        <v>45749.0</v>
       </c>
       <c r="D364" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="365">
@@ -5238,10 +5238,10 @@
         <v>2025.0</v>
       </c>
       <c r="C365" t="n" s="2">
-        <v>45770.0</v>
+        <v>45756.0</v>
       </c>
       <c r="D365" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="366">
@@ -5252,10 +5252,10 @@
         <v>2025.0</v>
       </c>
       <c r="C366" t="n" s="2">
-        <v>45777.0</v>
+        <v>45763.0</v>
       </c>
       <c r="D366" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="367">
@@ -5266,10 +5266,10 @@
         <v>2025.0</v>
       </c>
       <c r="C367" t="n" s="2">
-        <v>45784.0</v>
+        <v>45770.0</v>
       </c>
       <c r="D367" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="368">
@@ -5280,7 +5280,7 @@
         <v>2025.0</v>
       </c>
       <c r="C368" t="n" s="2">
-        <v>45791.0</v>
+        <v>45777.0</v>
       </c>
       <c r="D368" t="n">
         <v>1.0</v>
@@ -5294,7 +5294,7 @@
         <v>2025.0</v>
       </c>
       <c r="C369" t="n" s="2">
-        <v>45840.0</v>
+        <v>45784.0</v>
       </c>
       <c r="D369" t="n">
         <v>1.0</v>
@@ -5308,7 +5308,7 @@
         <v>2025.0</v>
       </c>
       <c r="C370" t="n" s="2">
-        <v>46001.0</v>
+        <v>45791.0</v>
       </c>
       <c r="D370" t="n">
         <v>1.0</v>
@@ -5319,10 +5319,10 @@
         <v>6</v>
       </c>
       <c r="B371" t="n">
-        <v>2026.0</v>
+        <v>2025.0</v>
       </c>
       <c r="C371" t="n" s="2">
-        <v>46037.0</v>
+        <v>45840.0</v>
       </c>
       <c r="D371" t="n">
         <v>1.0</v>
@@ -5330,13 +5330,13 @@
     </row>
     <row r="372">
       <c r="A372" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B372" t="n">
-        <v>2021.0</v>
+        <v>2025.0</v>
       </c>
       <c r="C372" t="n" s="2">
-        <v>44561.0</v>
+        <v>46001.0</v>
       </c>
       <c r="D372" t="n">
         <v>1.0</v>
@@ -5344,13 +5344,13 @@
     </row>
     <row r="373">
       <c r="A373" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B373" t="n">
-        <v>2022.0</v>
+        <v>2026.0</v>
       </c>
       <c r="C373" t="n" s="2">
-        <v>44569.0</v>
+        <v>46037.0</v>
       </c>
       <c r="D373" t="n">
         <v>1.0</v>
@@ -5361,13 +5361,13 @@
         <v>7</v>
       </c>
       <c r="B374" t="n">
-        <v>2022.0</v>
+        <v>2021.0</v>
       </c>
       <c r="C374" t="n" s="2">
-        <v>44576.0</v>
+        <v>44561.0</v>
       </c>
       <c r="D374" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="375">
@@ -5378,10 +5378,10 @@
         <v>2022.0</v>
       </c>
       <c r="C375" t="n" s="2">
-        <v>44583.0</v>
+        <v>44569.0</v>
       </c>
       <c r="D375" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="376">
@@ -5392,10 +5392,10 @@
         <v>2022.0</v>
       </c>
       <c r="C376" t="n" s="2">
-        <v>44590.0</v>
+        <v>44576.0</v>
       </c>
       <c r="D376" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="377">
@@ -5406,10 +5406,10 @@
         <v>2022.0</v>
       </c>
       <c r="C377" t="n" s="2">
-        <v>44604.0</v>
+        <v>44583.0</v>
       </c>
       <c r="D377" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="378">
@@ -5420,10 +5420,10 @@
         <v>2022.0</v>
       </c>
       <c r="C378" t="n" s="2">
-        <v>44611.0</v>
+        <v>44590.0</v>
       </c>
       <c r="D378" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="379">
@@ -5434,10 +5434,10 @@
         <v>2022.0</v>
       </c>
       <c r="C379" t="n" s="2">
-        <v>44618.0</v>
+        <v>44604.0</v>
       </c>
       <c r="D379" t="n">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="380">
@@ -5448,10 +5448,10 @@
         <v>2022.0</v>
       </c>
       <c r="C380" t="n" s="2">
-        <v>44625.0</v>
+        <v>44611.0</v>
       </c>
       <c r="D380" t="n">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="381">
@@ -5462,10 +5462,10 @@
         <v>2022.0</v>
       </c>
       <c r="C381" t="n" s="2">
-        <v>44632.0</v>
+        <v>44618.0</v>
       </c>
       <c r="D381" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="382">
@@ -5476,10 +5476,10 @@
         <v>2022.0</v>
       </c>
       <c r="C382" t="n" s="2">
-        <v>44639.0</v>
+        <v>44625.0</v>
       </c>
       <c r="D382" t="n">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="383">
@@ -5490,7 +5490,7 @@
         <v>2022.0</v>
       </c>
       <c r="C383" t="n" s="2">
-        <v>44646.0</v>
+        <v>44632.0</v>
       </c>
       <c r="D383" t="n">
         <v>3.0</v>
@@ -5504,10 +5504,10 @@
         <v>2022.0</v>
       </c>
       <c r="C384" t="n" s="2">
-        <v>44653.0</v>
+        <v>44639.0</v>
       </c>
       <c r="D384" t="n">
-        <v>9.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="385">
@@ -5518,10 +5518,10 @@
         <v>2022.0</v>
       </c>
       <c r="C385" t="n" s="2">
-        <v>44660.0</v>
+        <v>44646.0</v>
       </c>
       <c r="D385" t="n">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="386">
@@ -5532,10 +5532,10 @@
         <v>2022.0</v>
       </c>
       <c r="C386" t="n" s="2">
-        <v>44667.0</v>
+        <v>44653.0</v>
       </c>
       <c r="D386" t="n">
-        <v>2.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="387">
@@ -5546,10 +5546,10 @@
         <v>2022.0</v>
       </c>
       <c r="C387" t="n" s="2">
-        <v>44674.0</v>
+        <v>44660.0</v>
       </c>
       <c r="D387" t="n">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="388">
@@ -5560,7 +5560,7 @@
         <v>2022.0</v>
       </c>
       <c r="C388" t="n" s="2">
-        <v>44681.0</v>
+        <v>44667.0</v>
       </c>
       <c r="D388" t="n">
         <v>2.0</v>
@@ -5574,10 +5574,10 @@
         <v>2022.0</v>
       </c>
       <c r="C389" t="n" s="2">
-        <v>44688.0</v>
+        <v>44674.0</v>
       </c>
       <c r="D389" t="n">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="390">
@@ -5588,10 +5588,10 @@
         <v>2022.0</v>
       </c>
       <c r="C390" t="n" s="2">
-        <v>44695.0</v>
+        <v>44681.0</v>
       </c>
       <c r="D390" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="391">
@@ -5602,10 +5602,10 @@
         <v>2022.0</v>
       </c>
       <c r="C391" t="n" s="2">
-        <v>44702.0</v>
+        <v>44688.0</v>
       </c>
       <c r="D391" t="n">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="392">
@@ -5616,10 +5616,10 @@
         <v>2022.0</v>
       </c>
       <c r="C392" t="n" s="2">
-        <v>44709.0</v>
+        <v>44695.0</v>
       </c>
       <c r="D392" t="n">
-        <v>8.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="393">
@@ -5630,10 +5630,10 @@
         <v>2022.0</v>
       </c>
       <c r="C393" t="n" s="2">
-        <v>44716.0</v>
+        <v>44702.0</v>
       </c>
       <c r="D393" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="394">
@@ -5644,10 +5644,10 @@
         <v>2022.0</v>
       </c>
       <c r="C394" t="n" s="2">
-        <v>44723.0</v>
+        <v>44709.0</v>
       </c>
       <c r="D394" t="n">
-        <v>2.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="395">
@@ -5658,10 +5658,10 @@
         <v>2022.0</v>
       </c>
       <c r="C395" t="n" s="2">
-        <v>44730.0</v>
+        <v>44716.0</v>
       </c>
       <c r="D395" t="n">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="396">
@@ -5672,10 +5672,10 @@
         <v>2022.0</v>
       </c>
       <c r="C396" t="n" s="2">
-        <v>44737.0</v>
+        <v>44723.0</v>
       </c>
       <c r="D396" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="397">
@@ -5686,10 +5686,10 @@
         <v>2022.0</v>
       </c>
       <c r="C397" t="n" s="2">
-        <v>44744.0</v>
+        <v>44730.0</v>
       </c>
       <c r="D397" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="398">
@@ -5700,7 +5700,7 @@
         <v>2022.0</v>
       </c>
       <c r="C398" t="n" s="2">
-        <v>44751.0</v>
+        <v>44737.0</v>
       </c>
       <c r="D398" t="n">
         <v>4.0</v>
@@ -5714,10 +5714,10 @@
         <v>2022.0</v>
       </c>
       <c r="C399" t="n" s="2">
-        <v>44758.0</v>
+        <v>44744.0</v>
       </c>
       <c r="D399" t="n">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="400">
@@ -5728,10 +5728,10 @@
         <v>2022.0</v>
       </c>
       <c r="C400" t="n" s="2">
-        <v>44765.0</v>
+        <v>44751.0</v>
       </c>
       <c r="D400" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="401">
@@ -5742,10 +5742,10 @@
         <v>2022.0</v>
       </c>
       <c r="C401" t="n" s="2">
-        <v>44779.0</v>
+        <v>44758.0</v>
       </c>
       <c r="D401" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="402">
@@ -5756,7 +5756,7 @@
         <v>2022.0</v>
       </c>
       <c r="C402" t="n" s="2">
-        <v>44786.0</v>
+        <v>44765.0</v>
       </c>
       <c r="D402" t="n">
         <v>1.0</v>
@@ -5770,10 +5770,10 @@
         <v>2022.0</v>
       </c>
       <c r="C403" t="n" s="2">
-        <v>44863.0</v>
+        <v>44779.0</v>
       </c>
       <c r="D403" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="404">
@@ -5784,7 +5784,7 @@
         <v>2022.0</v>
       </c>
       <c r="C404" t="n" s="2">
-        <v>44870.0</v>
+        <v>44786.0</v>
       </c>
       <c r="D404" t="n">
         <v>1.0</v>
@@ -5798,7 +5798,7 @@
         <v>2022.0</v>
       </c>
       <c r="C405" t="n" s="2">
-        <v>44884.0</v>
+        <v>44863.0</v>
       </c>
       <c r="D405" t="n">
         <v>2.0</v>
@@ -5812,10 +5812,10 @@
         <v>2022.0</v>
       </c>
       <c r="C406" t="n" s="2">
-        <v>44891.0</v>
+        <v>44870.0</v>
       </c>
       <c r="D406" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="407">
@@ -5826,10 +5826,10 @@
         <v>2022.0</v>
       </c>
       <c r="C407" t="n" s="2">
-        <v>44898.0</v>
+        <v>44884.0</v>
       </c>
       <c r="D407" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="408">
@@ -5840,10 +5840,10 @@
         <v>2022.0</v>
       </c>
       <c r="C408" t="n" s="2">
-        <v>44912.0</v>
+        <v>44891.0</v>
       </c>
       <c r="D408" t="n">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="409">
@@ -5854,10 +5854,10 @@
         <v>2022.0</v>
       </c>
       <c r="C409" t="n" s="2">
-        <v>44919.0</v>
+        <v>44898.0</v>
       </c>
       <c r="D409" t="n">
-        <v>7.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="410">
@@ -5868,10 +5868,10 @@
         <v>2022.0</v>
       </c>
       <c r="C410" t="n" s="2">
-        <v>44926.0</v>
+        <v>44912.0</v>
       </c>
       <c r="D410" t="n">
-        <v>12.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="411">
@@ -5879,13 +5879,13 @@
         <v>7</v>
       </c>
       <c r="B411" t="n">
-        <v>2023.0</v>
+        <v>2022.0</v>
       </c>
       <c r="C411" t="n" s="2">
-        <v>44934.0</v>
+        <v>44919.0</v>
       </c>
       <c r="D411" t="n">
-        <v>4.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="412">
@@ -5893,13 +5893,13 @@
         <v>7</v>
       </c>
       <c r="B412" t="n">
-        <v>2023.0</v>
+        <v>2022.0</v>
       </c>
       <c r="C412" t="n" s="2">
-        <v>44941.0</v>
+        <v>44926.0</v>
       </c>
       <c r="D412" t="n">
-        <v>16.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="413">
@@ -5910,10 +5910,10 @@
         <v>2023.0</v>
       </c>
       <c r="C413" t="n" s="2">
-        <v>44948.0</v>
+        <v>44934.0</v>
       </c>
       <c r="D413" t="n">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="414">
@@ -5924,10 +5924,10 @@
         <v>2023.0</v>
       </c>
       <c r="C414" t="n" s="2">
-        <v>44955.0</v>
+        <v>44941.0</v>
       </c>
       <c r="D414" t="n">
-        <v>19.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="415">
@@ -5938,10 +5938,10 @@
         <v>2023.0</v>
       </c>
       <c r="C415" t="n" s="2">
-        <v>44962.0</v>
+        <v>44948.0</v>
       </c>
       <c r="D415" t="n">
-        <v>22.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="416">
@@ -5952,10 +5952,10 @@
         <v>2023.0</v>
       </c>
       <c r="C416" t="n" s="2">
-        <v>44969.0</v>
+        <v>44955.0</v>
       </c>
       <c r="D416" t="n">
-        <v>9.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="417">
@@ -5966,7 +5966,7 @@
         <v>2023.0</v>
       </c>
       <c r="C417" t="n" s="2">
-        <v>44976.0</v>
+        <v>44962.0</v>
       </c>
       <c r="D417" t="n">
         <v>22.0</v>
@@ -5980,10 +5980,10 @@
         <v>2023.0</v>
       </c>
       <c r="C418" t="n" s="2">
-        <v>44983.0</v>
+        <v>44969.0</v>
       </c>
       <c r="D418" t="n">
-        <v>29.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="419">
@@ -5994,10 +5994,10 @@
         <v>2023.0</v>
       </c>
       <c r="C419" t="n" s="2">
-        <v>44990.0</v>
+        <v>44976.0</v>
       </c>
       <c r="D419" t="n">
-        <v>5.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="420">
@@ -6008,10 +6008,10 @@
         <v>2023.0</v>
       </c>
       <c r="C420" t="n" s="2">
-        <v>44997.0</v>
+        <v>44983.0</v>
       </c>
       <c r="D420" t="n">
-        <v>24.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="421">
@@ -6022,10 +6022,10 @@
         <v>2023.0</v>
       </c>
       <c r="C421" t="n" s="2">
-        <v>45004.0</v>
+        <v>44990.0</v>
       </c>
       <c r="D421" t="n">
-        <v>8.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="422">
@@ -6036,10 +6036,10 @@
         <v>2023.0</v>
       </c>
       <c r="C422" t="n" s="2">
-        <v>45011.0</v>
+        <v>44997.0</v>
       </c>
       <c r="D422" t="n">
-        <v>10.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="423">
@@ -6050,10 +6050,10 @@
         <v>2023.0</v>
       </c>
       <c r="C423" t="n" s="2">
-        <v>45018.0</v>
+        <v>45004.0</v>
       </c>
       <c r="D423" t="n">
-        <v>18.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="424">
@@ -6064,10 +6064,10 @@
         <v>2023.0</v>
       </c>
       <c r="C424" t="n" s="2">
-        <v>45025.0</v>
+        <v>45011.0</v>
       </c>
       <c r="D424" t="n">
-        <v>13.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="425">
@@ -6078,7 +6078,7 @@
         <v>2023.0</v>
       </c>
       <c r="C425" t="n" s="2">
-        <v>45032.0</v>
+        <v>45018.0</v>
       </c>
       <c r="D425" t="n">
         <v>18.0</v>
@@ -6092,10 +6092,10 @@
         <v>2023.0</v>
       </c>
       <c r="C426" t="n" s="2">
-        <v>45039.0</v>
+        <v>45025.0</v>
       </c>
       <c r="D426" t="n">
-        <v>15.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="427">
@@ -6106,10 +6106,10 @@
         <v>2023.0</v>
       </c>
       <c r="C427" t="n" s="2">
-        <v>45046.0</v>
+        <v>45032.0</v>
       </c>
       <c r="D427" t="n">
-        <v>12.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="428">
@@ -6120,10 +6120,10 @@
         <v>2023.0</v>
       </c>
       <c r="C428" t="n" s="2">
-        <v>45053.0</v>
+        <v>45039.0</v>
       </c>
       <c r="D428" t="n">
-        <v>6.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="429">
@@ -6134,10 +6134,10 @@
         <v>2023.0</v>
       </c>
       <c r="C429" t="n" s="2">
-        <v>45060.0</v>
+        <v>45046.0</v>
       </c>
       <c r="D429" t="n">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="430">
@@ -6148,10 +6148,10 @@
         <v>2023.0</v>
       </c>
       <c r="C430" t="n" s="2">
-        <v>45067.0</v>
+        <v>45053.0</v>
       </c>
       <c r="D430" t="n">
-        <v>8.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="431">
@@ -6162,10 +6162,10 @@
         <v>2023.0</v>
       </c>
       <c r="C431" t="n" s="2">
-        <v>45074.0</v>
+        <v>45060.0</v>
       </c>
       <c r="D431" t="n">
-        <v>8.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="432">
@@ -6176,10 +6176,10 @@
         <v>2023.0</v>
       </c>
       <c r="C432" t="n" s="2">
-        <v>45081.0</v>
+        <v>45067.0</v>
       </c>
       <c r="D432" t="n">
-        <v>5.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="433">
@@ -6190,10 +6190,10 @@
         <v>2023.0</v>
       </c>
       <c r="C433" t="n" s="2">
-        <v>45088.0</v>
+        <v>45074.0</v>
       </c>
       <c r="D433" t="n">
-        <v>2.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="434">
@@ -6204,7 +6204,7 @@
         <v>2023.0</v>
       </c>
       <c r="C434" t="n" s="2">
-        <v>45095.0</v>
+        <v>45081.0</v>
       </c>
       <c r="D434" t="n">
         <v>5.0</v>
@@ -6218,10 +6218,10 @@
         <v>2023.0</v>
       </c>
       <c r="C435" t="n" s="2">
-        <v>45102.0</v>
+        <v>45088.0</v>
       </c>
       <c r="D435" t="n">
-        <v>10.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="436">
@@ -6232,10 +6232,10 @@
         <v>2023.0</v>
       </c>
       <c r="C436" t="n" s="2">
-        <v>45109.0</v>
+        <v>45095.0</v>
       </c>
       <c r="D436" t="n">
-        <v>9.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="437">
@@ -6246,10 +6246,10 @@
         <v>2023.0</v>
       </c>
       <c r="C437" t="n" s="2">
-        <v>45116.0</v>
+        <v>45102.0</v>
       </c>
       <c r="D437" t="n">
-        <v>3.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="438">
@@ -6260,10 +6260,10 @@
         <v>2023.0</v>
       </c>
       <c r="C438" t="n" s="2">
-        <v>45123.0</v>
+        <v>45109.0</v>
       </c>
       <c r="D438" t="n">
-        <v>6.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="439">
@@ -6274,10 +6274,10 @@
         <v>2023.0</v>
       </c>
       <c r="C439" t="n" s="2">
-        <v>45130.0</v>
+        <v>45116.0</v>
       </c>
       <c r="D439" t="n">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="440">
@@ -6288,10 +6288,10 @@
         <v>2023.0</v>
       </c>
       <c r="C440" t="n" s="2">
-        <v>45137.0</v>
+        <v>45123.0</v>
       </c>
       <c r="D440" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="441">
@@ -6302,10 +6302,10 @@
         <v>2023.0</v>
       </c>
       <c r="C441" t="n" s="2">
-        <v>45144.0</v>
+        <v>45130.0</v>
       </c>
       <c r="D441" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="442">
@@ -6316,7 +6316,7 @@
         <v>2023.0</v>
       </c>
       <c r="C442" t="n" s="2">
-        <v>45151.0</v>
+        <v>45137.0</v>
       </c>
       <c r="D442" t="n">
         <v>2.0</v>
@@ -6330,7 +6330,7 @@
         <v>2023.0</v>
       </c>
       <c r="C443" t="n" s="2">
-        <v>45165.0</v>
+        <v>45144.0</v>
       </c>
       <c r="D443" t="n">
         <v>2.0</v>
@@ -6344,7 +6344,7 @@
         <v>2023.0</v>
       </c>
       <c r="C444" t="n" s="2">
-        <v>45172.0</v>
+        <v>45151.0</v>
       </c>
       <c r="D444" t="n">
         <v>2.0</v>
@@ -6358,10 +6358,10 @@
         <v>2023.0</v>
       </c>
       <c r="C445" t="n" s="2">
-        <v>45179.0</v>
+        <v>45165.0</v>
       </c>
       <c r="D445" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="446">
@@ -6372,10 +6372,10 @@
         <v>2023.0</v>
       </c>
       <c r="C446" t="n" s="2">
-        <v>45186.0</v>
+        <v>45172.0</v>
       </c>
       <c r="D446" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="447">
@@ -6386,7 +6386,7 @@
         <v>2023.0</v>
       </c>
       <c r="C447" t="n" s="2">
-        <v>45193.0</v>
+        <v>45179.0</v>
       </c>
       <c r="D447" t="n">
         <v>1.0</v>
@@ -6400,7 +6400,7 @@
         <v>2023.0</v>
       </c>
       <c r="C448" t="n" s="2">
-        <v>45200.0</v>
+        <v>45186.0</v>
       </c>
       <c r="D448" t="n">
         <v>1.0</v>
@@ -6414,7 +6414,7 @@
         <v>2023.0</v>
       </c>
       <c r="C449" t="n" s="2">
-        <v>45207.0</v>
+        <v>45193.0</v>
       </c>
       <c r="D449" t="n">
         <v>1.0</v>
@@ -6428,7 +6428,7 @@
         <v>2023.0</v>
       </c>
       <c r="C450" t="n" s="2">
-        <v>45235.0</v>
+        <v>45200.0</v>
       </c>
       <c r="D450" t="n">
         <v>1.0</v>
@@ -6442,10 +6442,10 @@
         <v>2023.0</v>
       </c>
       <c r="C451" t="n" s="2">
-        <v>45242.0</v>
+        <v>45207.0</v>
       </c>
       <c r="D451" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="452">
@@ -6456,10 +6456,10 @@
         <v>2023.0</v>
       </c>
       <c r="C452" t="n" s="2">
-        <v>45249.0</v>
+        <v>45235.0</v>
       </c>
       <c r="D452" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="453">
@@ -6470,10 +6470,10 @@
         <v>2023.0</v>
       </c>
       <c r="C453" t="n" s="2">
-        <v>45256.0</v>
+        <v>45242.0</v>
       </c>
       <c r="D453" t="n">
-        <v>9.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="454">
@@ -6484,10 +6484,10 @@
         <v>2023.0</v>
       </c>
       <c r="C454" t="n" s="2">
-        <v>45263.0</v>
+        <v>45249.0</v>
       </c>
       <c r="D454" t="n">
-        <v>12.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="455">
@@ -6498,10 +6498,10 @@
         <v>2023.0</v>
       </c>
       <c r="C455" t="n" s="2">
-        <v>45270.0</v>
+        <v>45256.0</v>
       </c>
       <c r="D455" t="n">
-        <v>6.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="456">
@@ -6512,10 +6512,10 @@
         <v>2023.0</v>
       </c>
       <c r="C456" t="n" s="2">
-        <v>45277.0</v>
+        <v>45263.0</v>
       </c>
       <c r="D456" t="n">
-        <v>7.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="457">
@@ -6526,10 +6526,10 @@
         <v>2023.0</v>
       </c>
       <c r="C457" t="n" s="2">
-        <v>45284.0</v>
+        <v>45270.0</v>
       </c>
       <c r="D457" t="n">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="458">
@@ -6540,10 +6540,10 @@
         <v>2023.0</v>
       </c>
       <c r="C458" t="n" s="2">
-        <v>45291.0</v>
+        <v>45277.0</v>
       </c>
       <c r="D458" t="n">
-        <v>13.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="459">
@@ -6551,13 +6551,13 @@
         <v>7</v>
       </c>
       <c r="B459" t="n">
-        <v>2024.0</v>
+        <v>2023.0</v>
       </c>
       <c r="C459" t="n" s="2">
-        <v>45299.0</v>
+        <v>45284.0</v>
       </c>
       <c r="D459" t="n">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="460">
@@ -6565,13 +6565,13 @@
         <v>7</v>
       </c>
       <c r="B460" t="n">
-        <v>2024.0</v>
+        <v>2023.0</v>
       </c>
       <c r="C460" t="n" s="2">
-        <v>45306.0</v>
+        <v>45291.0</v>
       </c>
       <c r="D460" t="n">
-        <v>11.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="461">
@@ -6582,10 +6582,10 @@
         <v>2024.0</v>
       </c>
       <c r="C461" t="n" s="2">
-        <v>45313.0</v>
+        <v>45299.0</v>
       </c>
       <c r="D461" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="462">
@@ -6596,10 +6596,10 @@
         <v>2024.0</v>
       </c>
       <c r="C462" t="n" s="2">
-        <v>45320.0</v>
+        <v>45306.0</v>
       </c>
       <c r="D462" t="n">
-        <v>2.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="463">
@@ -6610,10 +6610,10 @@
         <v>2024.0</v>
       </c>
       <c r="C463" t="n" s="2">
-        <v>45327.0</v>
+        <v>45313.0</v>
       </c>
       <c r="D463" t="n">
-        <v>9.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="464">
@@ -6624,10 +6624,10 @@
         <v>2024.0</v>
       </c>
       <c r="C464" t="n" s="2">
-        <v>45334.0</v>
+        <v>45320.0</v>
       </c>
       <c r="D464" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="465">
@@ -6638,10 +6638,10 @@
         <v>2024.0</v>
       </c>
       <c r="C465" t="n" s="2">
-        <v>45341.0</v>
+        <v>45327.0</v>
       </c>
       <c r="D465" t="n">
-        <v>21.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="466">
@@ -6652,10 +6652,10 @@
         <v>2024.0</v>
       </c>
       <c r="C466" t="n" s="2">
-        <v>45348.0</v>
+        <v>45334.0</v>
       </c>
       <c r="D466" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="467">
@@ -6666,10 +6666,10 @@
         <v>2024.0</v>
       </c>
       <c r="C467" t="n" s="2">
-        <v>45355.0</v>
+        <v>45341.0</v>
       </c>
       <c r="D467" t="n">
-        <v>9.0</v>
+        <v>21.0</v>
       </c>
     </row>
     <row r="468">
@@ -6680,10 +6680,10 @@
         <v>2024.0</v>
       </c>
       <c r="C468" t="n" s="2">
-        <v>45362.0</v>
+        <v>45348.0</v>
       </c>
       <c r="D468" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="469">
@@ -6694,10 +6694,10 @@
         <v>2024.0</v>
       </c>
       <c r="C469" t="n" s="2">
-        <v>45369.0</v>
+        <v>45355.0</v>
       </c>
       <c r="D469" t="n">
-        <v>14.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="470">
@@ -6708,7 +6708,7 @@
         <v>2024.0</v>
       </c>
       <c r="C470" t="n" s="2">
-        <v>45376.0</v>
+        <v>45362.0</v>
       </c>
       <c r="D470" t="n">
         <v>4.0</v>
@@ -6722,10 +6722,10 @@
         <v>2024.0</v>
       </c>
       <c r="C471" t="n" s="2">
-        <v>45383.0</v>
+        <v>45369.0</v>
       </c>
       <c r="D471" t="n">
-        <v>2.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="472">
@@ -6736,10 +6736,10 @@
         <v>2024.0</v>
       </c>
       <c r="C472" t="n" s="2">
-        <v>45390.0</v>
+        <v>45376.0</v>
       </c>
       <c r="D472" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="473">
@@ -6750,10 +6750,10 @@
         <v>2024.0</v>
       </c>
       <c r="C473" t="n" s="2">
-        <v>45397.0</v>
+        <v>45383.0</v>
       </c>
       <c r="D473" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="474">
@@ -6764,10 +6764,10 @@
         <v>2024.0</v>
       </c>
       <c r="C474" t="n" s="2">
-        <v>45404.0</v>
+        <v>45390.0</v>
       </c>
       <c r="D474" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="475">
@@ -6778,7 +6778,7 @@
         <v>2024.0</v>
       </c>
       <c r="C475" t="n" s="2">
-        <v>45411.0</v>
+        <v>45397.0</v>
       </c>
       <c r="D475" t="n">
         <v>1.0</v>
@@ -6792,7 +6792,7 @@
         <v>2024.0</v>
       </c>
       <c r="C476" t="n" s="2">
-        <v>45439.0</v>
+        <v>45404.0</v>
       </c>
       <c r="D476" t="n">
         <v>2.0</v>
@@ -6806,7 +6806,7 @@
         <v>2024.0</v>
       </c>
       <c r="C477" t="n" s="2">
-        <v>45446.0</v>
+        <v>45411.0</v>
       </c>
       <c r="D477" t="n">
         <v>1.0</v>
@@ -6820,10 +6820,10 @@
         <v>2024.0</v>
       </c>
       <c r="C478" t="n" s="2">
-        <v>45460.0</v>
+        <v>45439.0</v>
       </c>
       <c r="D478" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="479">
@@ -6834,7 +6834,7 @@
         <v>2024.0</v>
       </c>
       <c r="C479" t="n" s="2">
-        <v>45481.0</v>
+        <v>45446.0</v>
       </c>
       <c r="D479" t="n">
         <v>1.0</v>
@@ -6848,7 +6848,7 @@
         <v>2024.0</v>
       </c>
       <c r="C480" t="n" s="2">
-        <v>45516.0</v>
+        <v>45460.0</v>
       </c>
       <c r="D480" t="n">
         <v>1.0</v>
@@ -6862,7 +6862,7 @@
         <v>2024.0</v>
       </c>
       <c r="C481" t="n" s="2">
-        <v>45551.0</v>
+        <v>45481.0</v>
       </c>
       <c r="D481" t="n">
         <v>1.0</v>
@@ -6876,7 +6876,7 @@
         <v>2024.0</v>
       </c>
       <c r="C482" t="n" s="2">
-        <v>45579.0</v>
+        <v>45516.0</v>
       </c>
       <c r="D482" t="n">
         <v>1.0</v>
@@ -6890,7 +6890,7 @@
         <v>2024.0</v>
       </c>
       <c r="C483" t="n" s="2">
-        <v>45614.0</v>
+        <v>45551.0</v>
       </c>
       <c r="D483" t="n">
         <v>1.0</v>
@@ -6904,10 +6904,10 @@
         <v>2024.0</v>
       </c>
       <c r="C484" t="n" s="2">
-        <v>45635.0</v>
+        <v>45579.0</v>
       </c>
       <c r="D484" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="485">
@@ -6918,10 +6918,10 @@
         <v>2024.0</v>
       </c>
       <c r="C485" t="n" s="2">
-        <v>45642.0</v>
+        <v>45614.0</v>
       </c>
       <c r="D485" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="486">
@@ -6932,10 +6932,10 @@
         <v>2024.0</v>
       </c>
       <c r="C486" t="n" s="2">
-        <v>45649.0</v>
+        <v>45635.0</v>
       </c>
       <c r="D486" t="n">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="487">
@@ -6946,7 +6946,7 @@
         <v>2024.0</v>
       </c>
       <c r="C487" t="n" s="2">
-        <v>45656.0</v>
+        <v>45642.0</v>
       </c>
       <c r="D487" t="n">
         <v>2.0</v>
@@ -6957,13 +6957,13 @@
         <v>7</v>
       </c>
       <c r="B488" t="n">
-        <v>2025.0</v>
+        <v>2024.0</v>
       </c>
       <c r="C488" t="n" s="2">
-        <v>45665.0</v>
+        <v>45649.0</v>
       </c>
       <c r="D488" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="489">
@@ -6971,10 +6971,10 @@
         <v>7</v>
       </c>
       <c r="B489" t="n">
-        <v>2025.0</v>
+        <v>2024.0</v>
       </c>
       <c r="C489" t="n" s="2">
-        <v>45672.0</v>
+        <v>45656.0</v>
       </c>
       <c r="D489" t="n">
         <v>2.0</v>
@@ -6988,10 +6988,10 @@
         <v>2025.0</v>
       </c>
       <c r="C490" t="n" s="2">
-        <v>45686.0</v>
+        <v>45665.0</v>
       </c>
       <c r="D490" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="491">
@@ -7002,10 +7002,10 @@
         <v>2025.0</v>
       </c>
       <c r="C491" t="n" s="2">
-        <v>45693.0</v>
+        <v>45672.0</v>
       </c>
       <c r="D491" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="492">
@@ -7016,10 +7016,10 @@
         <v>2025.0</v>
       </c>
       <c r="C492" t="n" s="2">
-        <v>45700.0</v>
+        <v>45686.0</v>
       </c>
       <c r="D492" t="n">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="493">
@@ -7030,10 +7030,10 @@
         <v>2025.0</v>
       </c>
       <c r="C493" t="n" s="2">
-        <v>45707.0</v>
+        <v>45693.0</v>
       </c>
       <c r="D493" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="494">
@@ -7044,10 +7044,10 @@
         <v>2025.0</v>
       </c>
       <c r="C494" t="n" s="2">
-        <v>45714.0</v>
+        <v>45700.0</v>
       </c>
       <c r="D494" t="n">
-        <v>8.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="495">
@@ -7058,10 +7058,10 @@
         <v>2025.0</v>
       </c>
       <c r="C495" t="n" s="2">
-        <v>45721.0</v>
+        <v>45707.0</v>
       </c>
       <c r="D495" t="n">
-        <v>11.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="496">
@@ -7072,10 +7072,10 @@
         <v>2025.0</v>
       </c>
       <c r="C496" t="n" s="2">
-        <v>45728.0</v>
+        <v>45714.0</v>
       </c>
       <c r="D496" t="n">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="497">
@@ -7086,10 +7086,10 @@
         <v>2025.0</v>
       </c>
       <c r="C497" t="n" s="2">
-        <v>45735.0</v>
+        <v>45721.0</v>
       </c>
       <c r="D497" t="n">
-        <v>19.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="498">
@@ -7100,10 +7100,10 @@
         <v>2025.0</v>
       </c>
       <c r="C498" t="n" s="2">
-        <v>45742.0</v>
+        <v>45728.0</v>
       </c>
       <c r="D498" t="n">
-        <v>17.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="499">
@@ -7114,10 +7114,10 @@
         <v>2025.0</v>
       </c>
       <c r="C499" t="n" s="2">
-        <v>45749.0</v>
+        <v>45735.0</v>
       </c>
       <c r="D499" t="n">
-        <v>5.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="500">
@@ -7128,10 +7128,10 @@
         <v>2025.0</v>
       </c>
       <c r="C500" t="n" s="2">
-        <v>45756.0</v>
+        <v>45742.0</v>
       </c>
       <c r="D500" t="n">
-        <v>9.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="501">
@@ -7142,10 +7142,10 @@
         <v>2025.0</v>
       </c>
       <c r="C501" t="n" s="2">
-        <v>45763.0</v>
+        <v>45749.0</v>
       </c>
       <c r="D501" t="n">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="502">
@@ -7156,10 +7156,10 @@
         <v>2025.0</v>
       </c>
       <c r="C502" t="n" s="2">
-        <v>45770.0</v>
+        <v>45756.0</v>
       </c>
       <c r="D502" t="n">
-        <v>1.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="503">
@@ -7170,10 +7170,10 @@
         <v>2025.0</v>
       </c>
       <c r="C503" t="n" s="2">
-        <v>45784.0</v>
+        <v>45763.0</v>
       </c>
       <c r="D503" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="504">
@@ -7184,10 +7184,10 @@
         <v>2025.0</v>
       </c>
       <c r="C504" t="n" s="2">
-        <v>45791.0</v>
+        <v>45770.0</v>
       </c>
       <c r="D504" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="505">
@@ -7198,10 +7198,10 @@
         <v>2025.0</v>
       </c>
       <c r="C505" t="n" s="2">
-        <v>45805.0</v>
+        <v>45784.0</v>
       </c>
       <c r="D505" t="n">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="506">
@@ -7212,7 +7212,7 @@
         <v>2025.0</v>
       </c>
       <c r="C506" t="n" s="2">
-        <v>45826.0</v>
+        <v>45791.0</v>
       </c>
       <c r="D506" t="n">
         <v>2.0</v>
@@ -7226,10 +7226,10 @@
         <v>2025.0</v>
       </c>
       <c r="C507" t="n" s="2">
-        <v>45861.0</v>
+        <v>45805.0</v>
       </c>
       <c r="D507" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="508">
@@ -7240,10 +7240,10 @@
         <v>2025.0</v>
       </c>
       <c r="C508" t="n" s="2">
-        <v>45868.0</v>
+        <v>45826.0</v>
       </c>
       <c r="D508" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="509">
@@ -7254,10 +7254,10 @@
         <v>2025.0</v>
       </c>
       <c r="C509" t="n" s="2">
-        <v>45889.0</v>
+        <v>45861.0</v>
       </c>
       <c r="D509" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="510">
@@ -7268,7 +7268,7 @@
         <v>2025.0</v>
       </c>
       <c r="C510" t="n" s="2">
-        <v>45924.0</v>
+        <v>45868.0</v>
       </c>
       <c r="D510" t="n">
         <v>1.0</v>
@@ -7282,7 +7282,7 @@
         <v>2025.0</v>
       </c>
       <c r="C511" t="n" s="2">
-        <v>45945.0</v>
+        <v>45889.0</v>
       </c>
       <c r="D511" t="n">
         <v>1.0</v>
@@ -7296,10 +7296,10 @@
         <v>2025.0</v>
       </c>
       <c r="C512" t="n" s="2">
-        <v>45959.0</v>
+        <v>45924.0</v>
       </c>
       <c r="D512" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="513">
@@ -7310,10 +7310,10 @@
         <v>2025.0</v>
       </c>
       <c r="C513" t="n" s="2">
-        <v>46001.0</v>
+        <v>45945.0</v>
       </c>
       <c r="D513" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="514">
@@ -7324,10 +7324,10 @@
         <v>2025.0</v>
       </c>
       <c r="C514" t="n" s="2">
-        <v>46008.0</v>
+        <v>45959.0</v>
       </c>
       <c r="D514" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="515">
@@ -7338,10 +7338,10 @@
         <v>2025.0</v>
       </c>
       <c r="C515" t="n" s="2">
-        <v>46022.0</v>
+        <v>46001.0</v>
       </c>
       <c r="D515" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="516">
@@ -7349,10 +7349,10 @@
         <v>7</v>
       </c>
       <c r="B516" t="n">
-        <v>2026.0</v>
+        <v>2025.0</v>
       </c>
       <c r="C516" t="n" s="2">
-        <v>46030.0</v>
+        <v>46008.0</v>
       </c>
       <c r="D516" t="n">
         <v>1.0</v>
@@ -7363,10 +7363,10 @@
         <v>7</v>
       </c>
       <c r="B517" t="n">
-        <v>2026.0</v>
+        <v>2025.0</v>
       </c>
       <c r="C517" t="n" s="2">
-        <v>46051.0</v>
+        <v>46022.0</v>
       </c>
       <c r="D517" t="n">
         <v>1.0</v>
@@ -7380,7 +7380,7 @@
         <v>2026.0</v>
       </c>
       <c r="C518" t="n" s="2">
-        <v>46058.0</v>
+        <v>46030.0</v>
       </c>
       <c r="D518" t="n">
         <v>1.0</v>
@@ -7394,10 +7394,10 @@
         <v>2026.0</v>
       </c>
       <c r="C519" t="n" s="2">
-        <v>46065.0</v>
+        <v>46051.0</v>
       </c>
       <c r="D519" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="520">
@@ -7408,38 +7408,38 @@
         <v>2026.0</v>
       </c>
       <c r="C520" t="n" s="2">
-        <v>46135.0</v>
+        <v>46058.0</v>
       </c>
       <c r="D520" t="n">
-        <v>8.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B521" t="n">
-        <v>2024.0</v>
+        <v>2026.0</v>
       </c>
       <c r="C521" t="n" s="2">
-        <v>45495.0</v>
+        <v>46065.0</v>
       </c>
       <c r="D521" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B522" t="n">
-        <v>2024.0</v>
+        <v>2026.0</v>
       </c>
       <c r="C522" t="n" s="2">
-        <v>45502.0</v>
+        <v>46135.0</v>
       </c>
       <c r="D522" t="n">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="523">
@@ -7447,10 +7447,10 @@
         <v>8</v>
       </c>
       <c r="B523" t="n">
-        <v>2025.0</v>
+        <v>2024.0</v>
       </c>
       <c r="C523" t="n" s="2">
-        <v>45665.0</v>
+        <v>45495.0</v>
       </c>
       <c r="D523" t="n">
         <v>1.0</v>
@@ -7461,13 +7461,13 @@
         <v>8</v>
       </c>
       <c r="B524" t="n">
-        <v>2025.0</v>
+        <v>2024.0</v>
       </c>
       <c r="C524" t="n" s="2">
-        <v>45672.0</v>
+        <v>45502.0</v>
       </c>
       <c r="D524" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="525">
@@ -7478,7 +7478,7 @@
         <v>2025.0</v>
       </c>
       <c r="C525" t="n" s="2">
-        <v>45679.0</v>
+        <v>45665.0</v>
       </c>
       <c r="D525" t="n">
         <v>1.0</v>
@@ -7492,10 +7492,10 @@
         <v>2025.0</v>
       </c>
       <c r="C526" t="n" s="2">
-        <v>45686.0</v>
+        <v>45672.0</v>
       </c>
       <c r="D526" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="527">
@@ -7506,7 +7506,7 @@
         <v>2025.0</v>
       </c>
       <c r="C527" t="n" s="2">
-        <v>45693.0</v>
+        <v>45679.0</v>
       </c>
       <c r="D527" t="n">
         <v>1.0</v>
@@ -7520,10 +7520,10 @@
         <v>2025.0</v>
       </c>
       <c r="C528" t="n" s="2">
-        <v>45700.0</v>
+        <v>45686.0</v>
       </c>
       <c r="D528" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="529">
@@ -7534,10 +7534,10 @@
         <v>2025.0</v>
       </c>
       <c r="C529" t="n" s="2">
-        <v>45707.0</v>
+        <v>45693.0</v>
       </c>
       <c r="D529" t="n">
-        <v>7.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="530">
@@ -7548,10 +7548,10 @@
         <v>2025.0</v>
       </c>
       <c r="C530" t="n" s="2">
-        <v>45714.0</v>
+        <v>45700.0</v>
       </c>
       <c r="D530" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="531">
@@ -7562,10 +7562,10 @@
         <v>2025.0</v>
       </c>
       <c r="C531" t="n" s="2">
-        <v>45721.0</v>
+        <v>45707.0</v>
       </c>
       <c r="D531" t="n">
-        <v>4.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="532">
@@ -7576,10 +7576,10 @@
         <v>2025.0</v>
       </c>
       <c r="C532" t="n" s="2">
-        <v>45728.0</v>
+        <v>45714.0</v>
       </c>
       <c r="D532" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="533">
@@ -7590,10 +7590,10 @@
         <v>2025.0</v>
       </c>
       <c r="C533" t="n" s="2">
-        <v>45742.0</v>
+        <v>45721.0</v>
       </c>
       <c r="D533" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="534">
@@ -7604,7 +7604,7 @@
         <v>2025.0</v>
       </c>
       <c r="C534" t="n" s="2">
-        <v>45749.0</v>
+        <v>45728.0</v>
       </c>
       <c r="D534" t="n">
         <v>1.0</v>
@@ -7618,7 +7618,7 @@
         <v>2025.0</v>
       </c>
       <c r="C535" t="n" s="2">
-        <v>45763.0</v>
+        <v>45742.0</v>
       </c>
       <c r="D535" t="n">
         <v>1.0</v>
@@ -7632,10 +7632,10 @@
         <v>2025.0</v>
       </c>
       <c r="C536" t="n" s="2">
-        <v>45777.0</v>
+        <v>45749.0</v>
       </c>
       <c r="D536" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="537">
@@ -7646,7 +7646,7 @@
         <v>2025.0</v>
       </c>
       <c r="C537" t="n" s="2">
-        <v>45784.0</v>
+        <v>45763.0</v>
       </c>
       <c r="D537" t="n">
         <v>1.0</v>
@@ -7660,10 +7660,10 @@
         <v>2025.0</v>
       </c>
       <c r="C538" t="n" s="2">
-        <v>45798.0</v>
+        <v>45777.0</v>
       </c>
       <c r="D538" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="539">
@@ -7674,7 +7674,7 @@
         <v>2025.0</v>
       </c>
       <c r="C539" t="n" s="2">
-        <v>45805.0</v>
+        <v>45784.0</v>
       </c>
       <c r="D539" t="n">
         <v>1.0</v>
@@ -7688,10 +7688,10 @@
         <v>2025.0</v>
       </c>
       <c r="C540" t="n" s="2">
-        <v>45812.0</v>
+        <v>45798.0</v>
       </c>
       <c r="D540" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="541">
@@ -7702,10 +7702,10 @@
         <v>2025.0</v>
       </c>
       <c r="C541" t="n" s="2">
-        <v>45819.0</v>
+        <v>45805.0</v>
       </c>
       <c r="D541" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="542">
@@ -7716,7 +7716,7 @@
         <v>2025.0</v>
       </c>
       <c r="C542" t="n" s="2">
-        <v>45833.0</v>
+        <v>45812.0</v>
       </c>
       <c r="D542" t="n">
         <v>2.0</v>
@@ -7730,10 +7730,10 @@
         <v>2025.0</v>
       </c>
       <c r="C543" t="n" s="2">
-        <v>45847.0</v>
+        <v>45819.0</v>
       </c>
       <c r="D543" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="544">
@@ -7744,10 +7744,10 @@
         <v>2025.0</v>
       </c>
       <c r="C544" t="n" s="2">
-        <v>45854.0</v>
+        <v>45833.0</v>
       </c>
       <c r="D544" t="n">
-        <v>8.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="545">
@@ -7758,10 +7758,10 @@
         <v>2025.0</v>
       </c>
       <c r="C545" t="n" s="2">
-        <v>45861.0</v>
+        <v>45847.0</v>
       </c>
       <c r="D545" t="n">
-        <v>12.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="546">
@@ -7772,10 +7772,10 @@
         <v>2025.0</v>
       </c>
       <c r="C546" t="n" s="2">
-        <v>45868.0</v>
+        <v>45854.0</v>
       </c>
       <c r="D546" t="n">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="547">
@@ -7786,10 +7786,10 @@
         <v>2025.0</v>
       </c>
       <c r="C547" t="n" s="2">
-        <v>45875.0</v>
+        <v>45861.0</v>
       </c>
       <c r="D547" t="n">
-        <v>1.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="548">
@@ -7800,10 +7800,10 @@
         <v>2025.0</v>
       </c>
       <c r="C548" t="n" s="2">
-        <v>45896.0</v>
+        <v>45868.0</v>
       </c>
       <c r="D548" t="n">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="549">
@@ -7814,7 +7814,7 @@
         <v>2025.0</v>
       </c>
       <c r="C549" t="n" s="2">
-        <v>45903.0</v>
+        <v>45875.0</v>
       </c>
       <c r="D549" t="n">
         <v>1.0</v>
@@ -7828,7 +7828,7 @@
         <v>2025.0</v>
       </c>
       <c r="C550" t="n" s="2">
-        <v>45931.0</v>
+        <v>45896.0</v>
       </c>
       <c r="D550" t="n">
         <v>1.0</v>
@@ -7842,10 +7842,10 @@
         <v>2025.0</v>
       </c>
       <c r="C551" t="n" s="2">
-        <v>45938.0</v>
+        <v>45903.0</v>
       </c>
       <c r="D551" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="552">
@@ -7856,10 +7856,10 @@
         <v>2025.0</v>
       </c>
       <c r="C552" t="n" s="2">
-        <v>45945.0</v>
+        <v>45931.0</v>
       </c>
       <c r="D552" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="553">
@@ -7870,10 +7870,10 @@
         <v>2025.0</v>
       </c>
       <c r="C553" t="n" s="2">
-        <v>45966.0</v>
+        <v>45938.0</v>
       </c>
       <c r="D553" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="554">
@@ -7884,10 +7884,10 @@
         <v>2025.0</v>
       </c>
       <c r="C554" t="n" s="2">
-        <v>45973.0</v>
+        <v>45945.0</v>
       </c>
       <c r="D554" t="n">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="555">
@@ -7898,10 +7898,10 @@
         <v>2025.0</v>
       </c>
       <c r="C555" t="n" s="2">
-        <v>45980.0</v>
+        <v>45966.0</v>
       </c>
       <c r="D555" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="556">
@@ -7912,10 +7912,10 @@
         <v>2025.0</v>
       </c>
       <c r="C556" t="n" s="2">
-        <v>45987.0</v>
+        <v>45973.0</v>
       </c>
       <c r="D556" t="n">
-        <v>20.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="557">
@@ -7926,10 +7926,10 @@
         <v>2025.0</v>
       </c>
       <c r="C557" t="n" s="2">
-        <v>45994.0</v>
+        <v>45980.0</v>
       </c>
       <c r="D557" t="n">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="558">
@@ -7940,10 +7940,10 @@
         <v>2025.0</v>
       </c>
       <c r="C558" t="n" s="2">
-        <v>46001.0</v>
+        <v>45987.0</v>
       </c>
       <c r="D558" t="n">
-        <v>8.0</v>
+        <v>20.0</v>
       </c>
     </row>
     <row r="559">
@@ -7954,10 +7954,10 @@
         <v>2025.0</v>
       </c>
       <c r="C559" t="n" s="2">
-        <v>46008.0</v>
+        <v>45994.0</v>
       </c>
       <c r="D559" t="n">
-        <v>24.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="560">
@@ -7968,10 +7968,10 @@
         <v>2025.0</v>
       </c>
       <c r="C560" t="n" s="2">
-        <v>46015.0</v>
+        <v>46001.0</v>
       </c>
       <c r="D560" t="n">
-        <v>13.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="561">
@@ -7982,10 +7982,10 @@
         <v>2025.0</v>
       </c>
       <c r="C561" t="n" s="2">
-        <v>46022.0</v>
+        <v>46008.0</v>
       </c>
       <c r="D561" t="n">
-        <v>8.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="562">
@@ -7996,10 +7996,10 @@
         <v>2025.0</v>
       </c>
       <c r="C562" t="n" s="2">
-        <v>46029.0</v>
+        <v>46015.0</v>
       </c>
       <c r="D562" t="n">
-        <v>3.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="563">
@@ -8007,13 +8007,13 @@
         <v>8</v>
       </c>
       <c r="B563" t="n">
-        <v>2026.0</v>
+        <v>2025.0</v>
       </c>
       <c r="C563" t="n" s="2">
-        <v>46030.0</v>
+        <v>46022.0</v>
       </c>
       <c r="D563" t="n">
-        <v>24.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="564">
@@ -8021,13 +8021,13 @@
         <v>8</v>
       </c>
       <c r="B564" t="n">
-        <v>2026.0</v>
+        <v>2025.0</v>
       </c>
       <c r="C564" t="n" s="2">
-        <v>46037.0</v>
+        <v>46029.0</v>
       </c>
       <c r="D564" t="n">
-        <v>22.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="565">
@@ -8038,10 +8038,10 @@
         <v>2026.0</v>
       </c>
       <c r="C565" t="n" s="2">
-        <v>46044.0</v>
+        <v>46030.0</v>
       </c>
       <c r="D565" t="n">
-        <v>27.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="566">
@@ -8052,10 +8052,10 @@
         <v>2026.0</v>
       </c>
       <c r="C566" t="n" s="2">
-        <v>46051.0</v>
+        <v>46037.0</v>
       </c>
       <c r="D566" t="n">
-        <v>18.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="567">
@@ -8066,10 +8066,10 @@
         <v>2026.0</v>
       </c>
       <c r="C567" t="n" s="2">
-        <v>46058.0</v>
+        <v>46044.0</v>
       </c>
       <c r="D567" t="n">
-        <v>25.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="568">
@@ -8080,10 +8080,10 @@
         <v>2026.0</v>
       </c>
       <c r="C568" t="n" s="2">
-        <v>46065.0</v>
+        <v>46051.0</v>
       </c>
       <c r="D568" t="n">
-        <v>22.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="569">
@@ -8094,10 +8094,10 @@
         <v>2026.0</v>
       </c>
       <c r="C569" t="n" s="2">
-        <v>46072.0</v>
+        <v>46058.0</v>
       </c>
       <c r="D569" t="n">
-        <v>13.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="570">
@@ -8108,10 +8108,10 @@
         <v>2026.0</v>
       </c>
       <c r="C570" t="n" s="2">
-        <v>46079.0</v>
+        <v>46065.0</v>
       </c>
       <c r="D570" t="n">
-        <v>24.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="571">
@@ -8122,10 +8122,10 @@
         <v>2026.0</v>
       </c>
       <c r="C571" t="n" s="2">
-        <v>46086.0</v>
+        <v>46072.0</v>
       </c>
       <c r="D571" t="n">
-        <v>26.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="572">
@@ -8136,10 +8136,10 @@
         <v>2026.0</v>
       </c>
       <c r="C572" t="n" s="2">
-        <v>46093.0</v>
+        <v>46079.0</v>
       </c>
       <c r="D572" t="n">
-        <v>33.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="573">
@@ -8150,10 +8150,10 @@
         <v>2026.0</v>
       </c>
       <c r="C573" t="n" s="2">
-        <v>46100.0</v>
+        <v>46086.0</v>
       </c>
       <c r="D573" t="n">
-        <v>25.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="574">
@@ -8164,10 +8164,10 @@
         <v>2026.0</v>
       </c>
       <c r="C574" t="n" s="2">
-        <v>46107.0</v>
+        <v>46093.0</v>
       </c>
       <c r="D574" t="n">
-        <v>31.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="575">
@@ -8178,10 +8178,10 @@
         <v>2026.0</v>
       </c>
       <c r="C575" t="n" s="2">
-        <v>46114.0</v>
+        <v>46100.0</v>
       </c>
       <c r="D575" t="n">
-        <v>10.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="576">
@@ -8192,10 +8192,10 @@
         <v>2026.0</v>
       </c>
       <c r="C576" t="n" s="2">
-        <v>46121.0</v>
+        <v>46107.0</v>
       </c>
       <c r="D576" t="n">
-        <v>9.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="577">
@@ -8206,10 +8206,10 @@
         <v>2026.0</v>
       </c>
       <c r="C577" t="n" s="2">
-        <v>46128.0</v>
+        <v>46114.0</v>
       </c>
       <c r="D577" t="n">
-        <v>15.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="578">
@@ -8220,10 +8220,10 @@
         <v>2026.0</v>
       </c>
       <c r="C578" t="n" s="2">
-        <v>46135.0</v>
+        <v>46121.0</v>
       </c>
       <c r="D578" t="n">
-        <v>23.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="579">
@@ -8234,10 +8234,10 @@
         <v>2026.0</v>
       </c>
       <c r="C579" t="n" s="2">
-        <v>46142.0</v>
+        <v>46128.0</v>
       </c>
       <c r="D579" t="n">
-        <v>21.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="580">
@@ -8248,9 +8248,37 @@
         <v>2026.0</v>
       </c>
       <c r="C580" t="n" s="2">
+        <v>46135.0</v>
+      </c>
+      <c r="D580" t="n">
+        <v>23.0</v>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="s">
+        <v>8</v>
+      </c>
+      <c r="B581" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C581" t="n" s="2">
+        <v>46142.0</v>
+      </c>
+      <c r="D581" t="n">
+        <v>21.0</v>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="s">
+        <v>8</v>
+      </c>
+      <c r="B582" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C582" t="n" s="2">
         <v>46149.0</v>
       </c>
-      <c r="D580" t="n">
+      <c r="D582" t="n">
         <v>6.0</v>
       </c>
     </row>
@@ -8277,7 +8305,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="n">
-        <v>47.0</v>
+        <v>49.0</v>
       </c>
     </row>
     <row r="3">
@@ -8293,7 +8321,7 @@
         <v>12</v>
       </c>
       <c r="B4" t="n">
-        <v>1259.0</v>
+        <v>1260.0</v>
       </c>
     </row>
     <row r="5">
@@ -8301,7 +8329,7 @@
         <v>13</v>
       </c>
       <c r="B5" t="n">
-        <v>2106.0</v>
+        <v>2108.0</v>
       </c>
     </row>
   </sheetData>
@@ -8366,7 +8394,7 @@
         <v>21</v>
       </c>
       <c r="C5" t="n">
-        <v>420.0</v>
+        <v>421.0</v>
       </c>
     </row>
     <row r="6">
@@ -8432,7 +8460,7 @@
         <v>19</v>
       </c>
       <c r="C11" t="n">
-        <v>33.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="12">
@@ -8465,7 +8493,7 @@
         <v>19</v>
       </c>
       <c r="C14" t="n">
-        <v>407.0</v>
+        <v>409.0</v>
       </c>
     </row>
     <row r="15">

--- a/Download/Focus_Positivi_ZR.xlsx
+++ b/Download/Focus_Positivi_ZR.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="626" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="627" uniqueCount="23">
   <si>
     <t>NOME_REGIONE</t>
   </si>
@@ -1615,7 +1615,7 @@
         <v>46149.0</v>
       </c>
       <c r="D106" t="n">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="107">
@@ -8280,6 +8280,20 @@
       </c>
       <c r="D582" t="n">
         <v>6.0</v>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="s">
+        <v>8</v>
+      </c>
+      <c r="B583" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C583" t="n" s="2">
+        <v>46156.0</v>
+      </c>
+      <c r="D583" t="n">
+        <v>14.0</v>
       </c>
     </row>
   </sheetData>
@@ -8321,7 +8335,7 @@
         <v>12</v>
       </c>
       <c r="B4" t="n">
-        <v>1260.0</v>
+        <v>1265.0</v>
       </c>
     </row>
     <row r="5">
@@ -8329,7 +8343,7 @@
         <v>13</v>
       </c>
       <c r="B5" t="n">
-        <v>2108.0</v>
+        <v>2119.0</v>
       </c>
     </row>
   </sheetData>
@@ -8361,7 +8375,7 @@
         <v>21</v>
       </c>
       <c r="C2" t="n">
-        <v>196.0</v>
+        <v>197.0</v>
       </c>
     </row>
     <row r="3">
@@ -8383,7 +8397,7 @@
         <v>19</v>
       </c>
       <c r="C4" t="n">
-        <v>140.0</v>
+        <v>143.0</v>
       </c>
     </row>
     <row r="5">
@@ -8427,7 +8441,7 @@
         <v>21</v>
       </c>
       <c r="C8" t="n">
-        <v>348.0</v>
+        <v>349.0</v>
       </c>
     </row>
     <row r="9">
@@ -8471,7 +8485,7 @@
         <v>21</v>
       </c>
       <c r="C12" t="n">
-        <v>70.0</v>
+        <v>74.0</v>
       </c>
     </row>
     <row r="13">
@@ -8482,7 +8496,7 @@
         <v>22</v>
       </c>
       <c r="C13" t="n">
-        <v>40.0</v>
+        <v>42.0</v>
       </c>
     </row>
     <row r="14">
@@ -8493,7 +8507,7 @@
         <v>19</v>
       </c>
       <c r="C14" t="n">
-        <v>409.0</v>
+        <v>413.0</v>
       </c>
     </row>
     <row r="15">
@@ -8515,7 +8529,7 @@
         <v>22</v>
       </c>
       <c r="C16" t="n">
-        <v>358.0</v>
+        <v>359.0</v>
       </c>
     </row>
     <row r="17">

--- a/Download/Focus_Positivi_ZR.xlsx
+++ b/Download/Focus_Positivi_ZR.xlsx
@@ -4317,7 +4317,7 @@
         <v>46156.0</v>
       </c>
       <c r="D299" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="300">
@@ -8293,7 +8293,7 @@
         <v>46156.0</v>
       </c>
       <c r="D583" t="n">
-        <v>14.0</v>
+        <v>19.0</v>
       </c>
     </row>
   </sheetData>
@@ -8335,7 +8335,7 @@
         <v>12</v>
       </c>
       <c r="B4" t="n">
-        <v>1265.0</v>
+        <v>1270.0</v>
       </c>
     </row>
     <row r="5">
@@ -8343,7 +8343,7 @@
         <v>13</v>
       </c>
       <c r="B5" t="n">
-        <v>2119.0</v>
+        <v>2121.0</v>
       </c>
     </row>
   </sheetData>
@@ -8375,7 +8375,7 @@
         <v>21</v>
       </c>
       <c r="C2" t="n">
-        <v>197.0</v>
+        <v>198.0</v>
       </c>
     </row>
     <row r="3">
@@ -8386,7 +8386,7 @@
         <v>22</v>
       </c>
       <c r="C3" t="n">
-        <v>176.0</v>
+        <v>177.0</v>
       </c>
     </row>
     <row r="4">
@@ -8408,7 +8408,7 @@
         <v>21</v>
       </c>
       <c r="C5" t="n">
-        <v>421.0</v>
+        <v>423.0</v>
       </c>
     </row>
     <row r="6">
@@ -8419,7 +8419,7 @@
         <v>22</v>
       </c>
       <c r="C6" t="n">
-        <v>305.0</v>
+        <v>306.0</v>
       </c>
     </row>
     <row r="7">
@@ -8441,7 +8441,7 @@
         <v>21</v>
       </c>
       <c r="C8" t="n">
-        <v>349.0</v>
+        <v>351.0</v>
       </c>
     </row>
     <row r="9">

--- a/Download/Focus_Positivi_ZR.xlsx
+++ b/Download/Focus_Positivi_ZR.xlsx
@@ -4289,7 +4289,7 @@
         <v>46142.0</v>
       </c>
       <c r="D297" t="n">
-        <v>5.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="298">
@@ -4303,7 +4303,7 @@
         <v>46149.0</v>
       </c>
       <c r="D298" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="299">
@@ -4317,7 +4317,7 @@
         <v>46156.0</v>
       </c>
       <c r="D299" t="n">
-        <v>4.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="300">
@@ -8293,7 +8293,7 @@
         <v>46156.0</v>
       </c>
       <c r="D583" t="n">
-        <v>19.0</v>
+        <v>22.0</v>
       </c>
     </row>
   </sheetData>
@@ -8335,7 +8335,7 @@
         <v>12</v>
       </c>
       <c r="B4" t="n">
-        <v>1270.0</v>
+        <v>1273.0</v>
       </c>
     </row>
     <row r="5">
@@ -8343,7 +8343,7 @@
         <v>13</v>
       </c>
       <c r="B5" t="n">
-        <v>2121.0</v>
+        <v>2127.0</v>
       </c>
     </row>
   </sheetData>
@@ -8375,7 +8375,7 @@
         <v>21</v>
       </c>
       <c r="C2" t="n">
-        <v>198.0</v>
+        <v>202.0</v>
       </c>
     </row>
     <row r="3">
@@ -8386,7 +8386,7 @@
         <v>22</v>
       </c>
       <c r="C3" t="n">
-        <v>177.0</v>
+        <v>179.0</v>
       </c>
     </row>
     <row r="4">
@@ -8441,7 +8441,7 @@
         <v>21</v>
       </c>
       <c r="C8" t="n">
-        <v>351.0</v>
+        <v>353.0</v>
       </c>
     </row>
     <row r="9">
@@ -8485,7 +8485,7 @@
         <v>21</v>
       </c>
       <c r="C12" t="n">
-        <v>74.0</v>
+        <v>75.0</v>
       </c>
     </row>
     <row r="13">

--- a/Download/Focus_Positivi_ZR.xlsx
+++ b/Download/Focus_Positivi_ZR.xlsx
@@ -1629,7 +1629,7 @@
         <v>46156.0</v>
       </c>
       <c r="D107" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="108">
@@ -4317,7 +4317,7 @@
         <v>46156.0</v>
       </c>
       <c r="D299" t="n">
-        <v>7.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="300">
@@ -8319,7 +8319,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="n">
-        <v>49.0</v>
+        <v>51.0</v>
       </c>
     </row>
     <row r="3">
@@ -8327,7 +8327,7 @@
         <v>11</v>
       </c>
       <c r="B3" t="n">
-        <v>195.0</v>
+        <v>196.0</v>
       </c>
     </row>
     <row r="4">
@@ -8335,7 +8335,7 @@
         <v>12</v>
       </c>
       <c r="B4" t="n">
-        <v>1273.0</v>
+        <v>1275.0</v>
       </c>
     </row>
     <row r="5">
@@ -8408,7 +8408,7 @@
         <v>21</v>
       </c>
       <c r="C5" t="n">
-        <v>423.0</v>
+        <v>424.0</v>
       </c>
     </row>
     <row r="6">
@@ -8474,7 +8474,7 @@
         <v>19</v>
       </c>
       <c r="C11" t="n">
-        <v>35.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="12">
@@ -8540,7 +8540,7 @@
         <v>19</v>
       </c>
       <c r="C17" t="n">
-        <v>111.0</v>
+        <v>113.0</v>
       </c>
     </row>
   </sheetData>

--- a/Download/Focus_Positivi_ZR.xlsx
+++ b/Download/Focus_Positivi_ZR.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="627" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="628" uniqueCount="23">
   <si>
     <t>NOME_REGIONE</t>
   </si>
@@ -8293,7 +8293,21 @@
         <v>46156.0</v>
       </c>
       <c r="D583" t="n">
-        <v>22.0</v>
+        <v>26.0</v>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="s">
+        <v>8</v>
+      </c>
+      <c r="B584" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C584" t="n" s="2">
+        <v>46163.0</v>
+      </c>
+      <c r="D584" t="n">
+        <v>2.0</v>
       </c>
     </row>
   </sheetData>
@@ -8319,7 +8333,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="n">
-        <v>51.0</v>
+        <v>55.0</v>
       </c>
     </row>
     <row r="3">
@@ -8327,7 +8341,7 @@
         <v>11</v>
       </c>
       <c r="B3" t="n">
-        <v>196.0</v>
+        <v>197.0</v>
       </c>
     </row>
     <row r="4">
@@ -8335,7 +8349,7 @@
         <v>12</v>
       </c>
       <c r="B4" t="n">
-        <v>1275.0</v>
+        <v>1276.0</v>
       </c>
     </row>
     <row r="5">
@@ -8397,7 +8411,7 @@
         <v>19</v>
       </c>
       <c r="C4" t="n">
-        <v>143.0</v>
+        <v>144.0</v>
       </c>
     </row>
     <row r="5">
@@ -8474,7 +8488,7 @@
         <v>19</v>
       </c>
       <c r="C11" t="n">
-        <v>37.0</v>
+        <v>41.0</v>
       </c>
     </row>
     <row r="12">
@@ -8507,7 +8521,7 @@
         <v>19</v>
       </c>
       <c r="C14" t="n">
-        <v>413.0</v>
+        <v>414.0</v>
       </c>
     </row>
     <row r="15">

--- a/Download/Focus_Positivi_ZR.xlsx
+++ b/Download/Focus_Positivi_ZR.xlsx
@@ -1629,7 +1629,7 @@
         <v>46156.0</v>
       </c>
       <c r="D107" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="108">
@@ -8293,7 +8293,7 @@
         <v>46156.0</v>
       </c>
       <c r="D583" t="n">
-        <v>26.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="584">
@@ -8307,7 +8307,7 @@
         <v>46163.0</v>
       </c>
       <c r="D584" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
   </sheetData>
@@ -8333,7 +8333,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="n">
-        <v>55.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="3">
@@ -8341,7 +8341,7 @@
         <v>11</v>
       </c>
       <c r="B3" t="n">
-        <v>197.0</v>
+        <v>198.0</v>
       </c>
     </row>
     <row r="4">
@@ -8357,7 +8357,7 @@
         <v>13</v>
       </c>
       <c r="B5" t="n">
-        <v>2127.0</v>
+        <v>2133.0</v>
       </c>
     </row>
   </sheetData>
@@ -8389,7 +8389,7 @@
         <v>21</v>
       </c>
       <c r="C2" t="n">
-        <v>202.0</v>
+        <v>204.0</v>
       </c>
     </row>
     <row r="3">
@@ -8400,7 +8400,7 @@
         <v>22</v>
       </c>
       <c r="C3" t="n">
-        <v>179.0</v>
+        <v>181.0</v>
       </c>
     </row>
     <row r="4">
@@ -8411,7 +8411,7 @@
         <v>19</v>
       </c>
       <c r="C4" t="n">
-        <v>144.0</v>
+        <v>146.0</v>
       </c>
     </row>
     <row r="5">
@@ -8488,7 +8488,7 @@
         <v>19</v>
       </c>
       <c r="C11" t="n">
-        <v>41.0</v>
+        <v>38.0</v>
       </c>
     </row>
     <row r="12">
@@ -8521,7 +8521,7 @@
         <v>19</v>
       </c>
       <c r="C14" t="n">
-        <v>414.0</v>
+        <v>415.0</v>
       </c>
     </row>
     <row r="15">

--- a/Download/Focus_Positivi_ZR.xlsx
+++ b/Download/Focus_Positivi_ZR.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="628" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="629" uniqueCount="23">
   <si>
     <t>NOME_REGIONE</t>
   </si>
@@ -4322,13 +4322,13 @@
     </row>
     <row r="300">
       <c r="A300" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B300" t="n">
-        <v>2023.0</v>
+        <v>2026.0</v>
       </c>
       <c r="C300" t="n" s="2">
-        <v>45095.0</v>
+        <v>46163.0</v>
       </c>
       <c r="D300" t="n">
         <v>1.0</v>
@@ -4342,7 +4342,7 @@
         <v>2023.0</v>
       </c>
       <c r="C301" t="n" s="2">
-        <v>45102.0</v>
+        <v>45095.0</v>
       </c>
       <c r="D301" t="n">
         <v>1.0</v>
@@ -4356,7 +4356,7 @@
         <v>2023.0</v>
       </c>
       <c r="C302" t="n" s="2">
-        <v>45158.0</v>
+        <v>45102.0</v>
       </c>
       <c r="D302" t="n">
         <v>1.0</v>
@@ -4370,10 +4370,10 @@
         <v>2023.0</v>
       </c>
       <c r="C303" t="n" s="2">
-        <v>45207.0</v>
+        <v>45158.0</v>
       </c>
       <c r="D303" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="304">
@@ -4384,7 +4384,7 @@
         <v>2023.0</v>
       </c>
       <c r="C304" t="n" s="2">
-        <v>45214.0</v>
+        <v>45207.0</v>
       </c>
       <c r="D304" t="n">
         <v>3.0</v>
@@ -4398,10 +4398,10 @@
         <v>2023.0</v>
       </c>
       <c r="C305" t="n" s="2">
-        <v>45221.0</v>
+        <v>45214.0</v>
       </c>
       <c r="D305" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="306">
@@ -4412,7 +4412,7 @@
         <v>2023.0</v>
       </c>
       <c r="C306" t="n" s="2">
-        <v>45249.0</v>
+        <v>45221.0</v>
       </c>
       <c r="D306" t="n">
         <v>1.0</v>
@@ -4426,10 +4426,10 @@
         <v>2023.0</v>
       </c>
       <c r="C307" t="n" s="2">
-        <v>45256.0</v>
+        <v>45249.0</v>
       </c>
       <c r="D307" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="308">
@@ -4440,10 +4440,10 @@
         <v>2023.0</v>
       </c>
       <c r="C308" t="n" s="2">
-        <v>45263.0</v>
+        <v>45256.0</v>
       </c>
       <c r="D308" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="309">
@@ -4454,10 +4454,10 @@
         <v>2023.0</v>
       </c>
       <c r="C309" t="n" s="2">
-        <v>45270.0</v>
+        <v>45263.0</v>
       </c>
       <c r="D309" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="310">
@@ -4468,10 +4468,10 @@
         <v>2023.0</v>
       </c>
       <c r="C310" t="n" s="2">
-        <v>45277.0</v>
+        <v>45270.0</v>
       </c>
       <c r="D310" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="311">
@@ -4482,10 +4482,10 @@
         <v>2023.0</v>
       </c>
       <c r="C311" t="n" s="2">
-        <v>45284.0</v>
+        <v>45277.0</v>
       </c>
       <c r="D311" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="312">
@@ -4496,10 +4496,10 @@
         <v>2023.0</v>
       </c>
       <c r="C312" t="n" s="2">
-        <v>45291.0</v>
+        <v>45284.0</v>
       </c>
       <c r="D312" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="313">
@@ -4507,13 +4507,13 @@
         <v>6</v>
       </c>
       <c r="B313" t="n">
-        <v>2024.0</v>
+        <v>2023.0</v>
       </c>
       <c r="C313" t="n" s="2">
-        <v>45306.0</v>
+        <v>45291.0</v>
       </c>
       <c r="D313" t="n">
-        <v>7.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="314">
@@ -4524,10 +4524,10 @@
         <v>2024.0</v>
       </c>
       <c r="C314" t="n" s="2">
-        <v>45313.0</v>
+        <v>45306.0</v>
       </c>
       <c r="D314" t="n">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="315">
@@ -4538,10 +4538,10 @@
         <v>2024.0</v>
       </c>
       <c r="C315" t="n" s="2">
-        <v>45320.0</v>
+        <v>45313.0</v>
       </c>
       <c r="D315" t="n">
-        <v>19.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="316">
@@ -4552,10 +4552,10 @@
         <v>2024.0</v>
       </c>
       <c r="C316" t="n" s="2">
-        <v>45327.0</v>
+        <v>45320.0</v>
       </c>
       <c r="D316" t="n">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="317">
@@ -4566,10 +4566,10 @@
         <v>2024.0</v>
       </c>
       <c r="C317" t="n" s="2">
-        <v>45334.0</v>
+        <v>45327.0</v>
       </c>
       <c r="D317" t="n">
-        <v>9.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="318">
@@ -4580,10 +4580,10 @@
         <v>2024.0</v>
       </c>
       <c r="C318" t="n" s="2">
-        <v>45341.0</v>
+        <v>45334.0</v>
       </c>
       <c r="D318" t="n">
-        <v>12.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="319">
@@ -4594,7 +4594,7 @@
         <v>2024.0</v>
       </c>
       <c r="C319" t="n" s="2">
-        <v>45348.0</v>
+        <v>45341.0</v>
       </c>
       <c r="D319" t="n">
         <v>12.0</v>
@@ -4608,10 +4608,10 @@
         <v>2024.0</v>
       </c>
       <c r="C320" t="n" s="2">
-        <v>45355.0</v>
+        <v>45348.0</v>
       </c>
       <c r="D320" t="n">
-        <v>10.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="321">
@@ -4622,10 +4622,10 @@
         <v>2024.0</v>
       </c>
       <c r="C321" t="n" s="2">
-        <v>45362.0</v>
+        <v>45355.0</v>
       </c>
       <c r="D321" t="n">
-        <v>12.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="322">
@@ -4636,10 +4636,10 @@
         <v>2024.0</v>
       </c>
       <c r="C322" t="n" s="2">
-        <v>45369.0</v>
+        <v>45362.0</v>
       </c>
       <c r="D322" t="n">
-        <v>13.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="323">
@@ -4650,10 +4650,10 @@
         <v>2024.0</v>
       </c>
       <c r="C323" t="n" s="2">
-        <v>45376.0</v>
+        <v>45369.0</v>
       </c>
       <c r="D323" t="n">
-        <v>18.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="324">
@@ -4664,10 +4664,10 @@
         <v>2024.0</v>
       </c>
       <c r="C324" t="n" s="2">
-        <v>45383.0</v>
+        <v>45376.0</v>
       </c>
       <c r="D324" t="n">
-        <v>12.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="325">
@@ -4678,10 +4678,10 @@
         <v>2024.0</v>
       </c>
       <c r="C325" t="n" s="2">
-        <v>45390.0</v>
+        <v>45383.0</v>
       </c>
       <c r="D325" t="n">
-        <v>6.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="326">
@@ -4692,10 +4692,10 @@
         <v>2024.0</v>
       </c>
       <c r="C326" t="n" s="2">
-        <v>45397.0</v>
+        <v>45390.0</v>
       </c>
       <c r="D326" t="n">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="327">
@@ -4706,10 +4706,10 @@
         <v>2024.0</v>
       </c>
       <c r="C327" t="n" s="2">
-        <v>45404.0</v>
+        <v>45397.0</v>
       </c>
       <c r="D327" t="n">
-        <v>3.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="328">
@@ -4720,10 +4720,10 @@
         <v>2024.0</v>
       </c>
       <c r="C328" t="n" s="2">
-        <v>45411.0</v>
+        <v>45404.0</v>
       </c>
       <c r="D328" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="329">
@@ -4734,10 +4734,10 @@
         <v>2024.0</v>
       </c>
       <c r="C329" t="n" s="2">
-        <v>45418.0</v>
+        <v>45411.0</v>
       </c>
       <c r="D329" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="330">
@@ -4748,10 +4748,10 @@
         <v>2024.0</v>
       </c>
       <c r="C330" t="n" s="2">
-        <v>45425.0</v>
+        <v>45418.0</v>
       </c>
       <c r="D330" t="n">
-        <v>9.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="331">
@@ -4762,10 +4762,10 @@
         <v>2024.0</v>
       </c>
       <c r="C331" t="n" s="2">
-        <v>45432.0</v>
+        <v>45425.0</v>
       </c>
       <c r="D331" t="n">
-        <v>6.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="332">
@@ -4776,7 +4776,7 @@
         <v>2024.0</v>
       </c>
       <c r="C332" t="n" s="2">
-        <v>45439.0</v>
+        <v>45432.0</v>
       </c>
       <c r="D332" t="n">
         <v>6.0</v>
@@ -4790,10 +4790,10 @@
         <v>2024.0</v>
       </c>
       <c r="C333" t="n" s="2">
-        <v>45446.0</v>
+        <v>45439.0</v>
       </c>
       <c r="D333" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="334">
@@ -4804,10 +4804,10 @@
         <v>2024.0</v>
       </c>
       <c r="C334" t="n" s="2">
-        <v>45453.0</v>
+        <v>45446.0</v>
       </c>
       <c r="D334" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="335">
@@ -4818,7 +4818,7 @@
         <v>2024.0</v>
       </c>
       <c r="C335" t="n" s="2">
-        <v>45460.0</v>
+        <v>45453.0</v>
       </c>
       <c r="D335" t="n">
         <v>4.0</v>
@@ -4832,7 +4832,7 @@
         <v>2024.0</v>
       </c>
       <c r="C336" t="n" s="2">
-        <v>45467.0</v>
+        <v>45460.0</v>
       </c>
       <c r="D336" t="n">
         <v>4.0</v>
@@ -4846,10 +4846,10 @@
         <v>2024.0</v>
       </c>
       <c r="C337" t="n" s="2">
-        <v>45474.0</v>
+        <v>45467.0</v>
       </c>
       <c r="D337" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="338">
@@ -4860,10 +4860,10 @@
         <v>2024.0</v>
       </c>
       <c r="C338" t="n" s="2">
-        <v>45481.0</v>
+        <v>45474.0</v>
       </c>
       <c r="D338" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="339">
@@ -4874,10 +4874,10 @@
         <v>2024.0</v>
       </c>
       <c r="C339" t="n" s="2">
-        <v>45488.0</v>
+        <v>45481.0</v>
       </c>
       <c r="D339" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="340">
@@ -4888,10 +4888,10 @@
         <v>2024.0</v>
       </c>
       <c r="C340" t="n" s="2">
-        <v>45495.0</v>
+        <v>45488.0</v>
       </c>
       <c r="D340" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="341">
@@ -4902,10 +4902,10 @@
         <v>2024.0</v>
       </c>
       <c r="C341" t="n" s="2">
-        <v>45502.0</v>
+        <v>45495.0</v>
       </c>
       <c r="D341" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="342">
@@ -4916,10 +4916,10 @@
         <v>2024.0</v>
       </c>
       <c r="C342" t="n" s="2">
-        <v>45509.0</v>
+        <v>45502.0</v>
       </c>
       <c r="D342" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="343">
@@ -4930,7 +4930,7 @@
         <v>2024.0</v>
       </c>
       <c r="C343" t="n" s="2">
-        <v>45523.0</v>
+        <v>45509.0</v>
       </c>
       <c r="D343" t="n">
         <v>1.0</v>
@@ -4944,7 +4944,7 @@
         <v>2024.0</v>
       </c>
       <c r="C344" t="n" s="2">
-        <v>45551.0</v>
+        <v>45523.0</v>
       </c>
       <c r="D344" t="n">
         <v>1.0</v>
@@ -4958,7 +4958,7 @@
         <v>2024.0</v>
       </c>
       <c r="C345" t="n" s="2">
-        <v>45558.0</v>
+        <v>45551.0</v>
       </c>
       <c r="D345" t="n">
         <v>1.0</v>
@@ -4972,10 +4972,10 @@
         <v>2024.0</v>
       </c>
       <c r="C346" t="n" s="2">
-        <v>45572.0</v>
+        <v>45558.0</v>
       </c>
       <c r="D346" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="347">
@@ -4986,10 +4986,10 @@
         <v>2024.0</v>
       </c>
       <c r="C347" t="n" s="2">
-        <v>45593.0</v>
+        <v>45572.0</v>
       </c>
       <c r="D347" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="348">
@@ -5000,10 +5000,10 @@
         <v>2024.0</v>
       </c>
       <c r="C348" t="n" s="2">
-        <v>45614.0</v>
+        <v>45593.0</v>
       </c>
       <c r="D348" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="349">
@@ -5014,10 +5014,10 @@
         <v>2024.0</v>
       </c>
       <c r="C349" t="n" s="2">
-        <v>45621.0</v>
+        <v>45614.0</v>
       </c>
       <c r="D349" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="350">
@@ -5028,7 +5028,7 @@
         <v>2024.0</v>
       </c>
       <c r="C350" t="n" s="2">
-        <v>45635.0</v>
+        <v>45621.0</v>
       </c>
       <c r="D350" t="n">
         <v>1.0</v>
@@ -5042,7 +5042,7 @@
         <v>2024.0</v>
       </c>
       <c r="C351" t="n" s="2">
-        <v>45649.0</v>
+        <v>45635.0</v>
       </c>
       <c r="D351" t="n">
         <v>1.0</v>
@@ -5053,13 +5053,13 @@
         <v>6</v>
       </c>
       <c r="B352" t="n">
-        <v>2025.0</v>
+        <v>2024.0</v>
       </c>
       <c r="C352" t="n" s="2">
-        <v>45665.0</v>
+        <v>45649.0</v>
       </c>
       <c r="D352" t="n">
-        <v>9.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="353">
@@ -5070,10 +5070,10 @@
         <v>2025.0</v>
       </c>
       <c r="C353" t="n" s="2">
-        <v>45672.0</v>
+        <v>45665.0</v>
       </c>
       <c r="D353" t="n">
-        <v>3.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="354">
@@ -5084,10 +5084,10 @@
         <v>2025.0</v>
       </c>
       <c r="C354" t="n" s="2">
-        <v>45679.0</v>
+        <v>45672.0</v>
       </c>
       <c r="D354" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="355">
@@ -5098,10 +5098,10 @@
         <v>2025.0</v>
       </c>
       <c r="C355" t="n" s="2">
-        <v>45686.0</v>
+        <v>45679.0</v>
       </c>
       <c r="D355" t="n">
-        <v>8.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="356">
@@ -5112,10 +5112,10 @@
         <v>2025.0</v>
       </c>
       <c r="C356" t="n" s="2">
-        <v>45693.0</v>
+        <v>45686.0</v>
       </c>
       <c r="D356" t="n">
-        <v>3.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="357">
@@ -5126,10 +5126,10 @@
         <v>2025.0</v>
       </c>
       <c r="C357" t="n" s="2">
-        <v>45700.0</v>
+        <v>45693.0</v>
       </c>
       <c r="D357" t="n">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="358">
@@ -5140,10 +5140,10 @@
         <v>2025.0</v>
       </c>
       <c r="C358" t="n" s="2">
-        <v>45707.0</v>
+        <v>45700.0</v>
       </c>
       <c r="D358" t="n">
-        <v>8.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="359">
@@ -5154,10 +5154,10 @@
         <v>2025.0</v>
       </c>
       <c r="C359" t="n" s="2">
-        <v>45714.0</v>
+        <v>45707.0</v>
       </c>
       <c r="D359" t="n">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="360">
@@ -5168,10 +5168,10 @@
         <v>2025.0</v>
       </c>
       <c r="C360" t="n" s="2">
-        <v>45721.0</v>
+        <v>45714.0</v>
       </c>
       <c r="D360" t="n">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="361">
@@ -5182,10 +5182,10 @@
         <v>2025.0</v>
       </c>
       <c r="C361" t="n" s="2">
-        <v>45728.0</v>
+        <v>45721.0</v>
       </c>
       <c r="D361" t="n">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="362">
@@ -5196,10 +5196,10 @@
         <v>2025.0</v>
       </c>
       <c r="C362" t="n" s="2">
-        <v>45735.0</v>
+        <v>45728.0</v>
       </c>
       <c r="D362" t="n">
-        <v>4.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="363">
@@ -5210,10 +5210,10 @@
         <v>2025.0</v>
       </c>
       <c r="C363" t="n" s="2">
-        <v>45742.0</v>
+        <v>45735.0</v>
       </c>
       <c r="D363" t="n">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="364">
@@ -5224,10 +5224,10 @@
         <v>2025.0</v>
       </c>
       <c r="C364" t="n" s="2">
-        <v>45749.0</v>
+        <v>45742.0</v>
       </c>
       <c r="D364" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="365">
@@ -5238,10 +5238,10 @@
         <v>2025.0</v>
       </c>
       <c r="C365" t="n" s="2">
-        <v>45756.0</v>
+        <v>45749.0</v>
       </c>
       <c r="D365" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="366">
@@ -5252,10 +5252,10 @@
         <v>2025.0</v>
       </c>
       <c r="C366" t="n" s="2">
-        <v>45763.0</v>
+        <v>45756.0</v>
       </c>
       <c r="D366" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="367">
@@ -5266,7 +5266,7 @@
         <v>2025.0</v>
       </c>
       <c r="C367" t="n" s="2">
-        <v>45770.0</v>
+        <v>45763.0</v>
       </c>
       <c r="D367" t="n">
         <v>4.0</v>
@@ -5280,10 +5280,10 @@
         <v>2025.0</v>
       </c>
       <c r="C368" t="n" s="2">
-        <v>45777.0</v>
+        <v>45770.0</v>
       </c>
       <c r="D368" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="369">
@@ -5294,7 +5294,7 @@
         <v>2025.0</v>
       </c>
       <c r="C369" t="n" s="2">
-        <v>45784.0</v>
+        <v>45777.0</v>
       </c>
       <c r="D369" t="n">
         <v>1.0</v>
@@ -5308,7 +5308,7 @@
         <v>2025.0</v>
       </c>
       <c r="C370" t="n" s="2">
-        <v>45791.0</v>
+        <v>45784.0</v>
       </c>
       <c r="D370" t="n">
         <v>1.0</v>
@@ -5322,7 +5322,7 @@
         <v>2025.0</v>
       </c>
       <c r="C371" t="n" s="2">
-        <v>45840.0</v>
+        <v>45791.0</v>
       </c>
       <c r="D371" t="n">
         <v>1.0</v>
@@ -5336,7 +5336,7 @@
         <v>2025.0</v>
       </c>
       <c r="C372" t="n" s="2">
-        <v>46001.0</v>
+        <v>45840.0</v>
       </c>
       <c r="D372" t="n">
         <v>1.0</v>
@@ -5347,10 +5347,10 @@
         <v>6</v>
       </c>
       <c r="B373" t="n">
-        <v>2026.0</v>
+        <v>2025.0</v>
       </c>
       <c r="C373" t="n" s="2">
-        <v>46037.0</v>
+        <v>46001.0</v>
       </c>
       <c r="D373" t="n">
         <v>1.0</v>
@@ -5358,13 +5358,13 @@
     </row>
     <row r="374">
       <c r="A374" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B374" t="n">
-        <v>2021.0</v>
+        <v>2026.0</v>
       </c>
       <c r="C374" t="n" s="2">
-        <v>44561.0</v>
+        <v>46037.0</v>
       </c>
       <c r="D374" t="n">
         <v>1.0</v>
@@ -5375,10 +5375,10 @@
         <v>7</v>
       </c>
       <c r="B375" t="n">
-        <v>2022.0</v>
+        <v>2021.0</v>
       </c>
       <c r="C375" t="n" s="2">
-        <v>44569.0</v>
+        <v>44561.0</v>
       </c>
       <c r="D375" t="n">
         <v>1.0</v>
@@ -5392,10 +5392,10 @@
         <v>2022.0</v>
       </c>
       <c r="C376" t="n" s="2">
-        <v>44576.0</v>
+        <v>44569.0</v>
       </c>
       <c r="D376" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="377">
@@ -5406,10 +5406,10 @@
         <v>2022.0</v>
       </c>
       <c r="C377" t="n" s="2">
-        <v>44583.0</v>
+        <v>44576.0</v>
       </c>
       <c r="D377" t="n">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="378">
@@ -5420,10 +5420,10 @@
         <v>2022.0</v>
       </c>
       <c r="C378" t="n" s="2">
-        <v>44590.0</v>
+        <v>44583.0</v>
       </c>
       <c r="D378" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="379">
@@ -5434,10 +5434,10 @@
         <v>2022.0</v>
       </c>
       <c r="C379" t="n" s="2">
-        <v>44604.0</v>
+        <v>44590.0</v>
       </c>
       <c r="D379" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="380">
@@ -5448,7 +5448,7 @@
         <v>2022.0</v>
       </c>
       <c r="C380" t="n" s="2">
-        <v>44611.0</v>
+        <v>44604.0</v>
       </c>
       <c r="D380" t="n">
         <v>3.0</v>
@@ -5462,10 +5462,10 @@
         <v>2022.0</v>
       </c>
       <c r="C381" t="n" s="2">
-        <v>44618.0</v>
+        <v>44611.0</v>
       </c>
       <c r="D381" t="n">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="382">
@@ -5476,7 +5476,7 @@
         <v>2022.0</v>
       </c>
       <c r="C382" t="n" s="2">
-        <v>44625.0</v>
+        <v>44618.0</v>
       </c>
       <c r="D382" t="n">
         <v>5.0</v>
@@ -5490,10 +5490,10 @@
         <v>2022.0</v>
       </c>
       <c r="C383" t="n" s="2">
-        <v>44632.0</v>
+        <v>44625.0</v>
       </c>
       <c r="D383" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="384">
@@ -5504,10 +5504,10 @@
         <v>2022.0</v>
       </c>
       <c r="C384" t="n" s="2">
-        <v>44639.0</v>
+        <v>44632.0</v>
       </c>
       <c r="D384" t="n">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="385">
@@ -5518,10 +5518,10 @@
         <v>2022.0</v>
       </c>
       <c r="C385" t="n" s="2">
-        <v>44646.0</v>
+        <v>44639.0</v>
       </c>
       <c r="D385" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="386">
@@ -5532,10 +5532,10 @@
         <v>2022.0</v>
       </c>
       <c r="C386" t="n" s="2">
-        <v>44653.0</v>
+        <v>44646.0</v>
       </c>
       <c r="D386" t="n">
-        <v>9.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="387">
@@ -5546,10 +5546,10 @@
         <v>2022.0</v>
       </c>
       <c r="C387" t="n" s="2">
-        <v>44660.0</v>
+        <v>44653.0</v>
       </c>
       <c r="D387" t="n">
-        <v>6.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="388">
@@ -5560,10 +5560,10 @@
         <v>2022.0</v>
       </c>
       <c r="C388" t="n" s="2">
-        <v>44667.0</v>
+        <v>44660.0</v>
       </c>
       <c r="D388" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="389">
@@ -5574,10 +5574,10 @@
         <v>2022.0</v>
       </c>
       <c r="C389" t="n" s="2">
-        <v>44674.0</v>
+        <v>44667.0</v>
       </c>
       <c r="D389" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="390">
@@ -5588,10 +5588,10 @@
         <v>2022.0</v>
       </c>
       <c r="C390" t="n" s="2">
-        <v>44681.0</v>
+        <v>44674.0</v>
       </c>
       <c r="D390" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="391">
@@ -5602,10 +5602,10 @@
         <v>2022.0</v>
       </c>
       <c r="C391" t="n" s="2">
-        <v>44688.0</v>
+        <v>44681.0</v>
       </c>
       <c r="D391" t="n">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="392">
@@ -5616,10 +5616,10 @@
         <v>2022.0</v>
       </c>
       <c r="C392" t="n" s="2">
-        <v>44695.0</v>
+        <v>44688.0</v>
       </c>
       <c r="D392" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="393">
@@ -5630,10 +5630,10 @@
         <v>2022.0</v>
       </c>
       <c r="C393" t="n" s="2">
-        <v>44702.0</v>
+        <v>44695.0</v>
       </c>
       <c r="D393" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="394">
@@ -5644,10 +5644,10 @@
         <v>2022.0</v>
       </c>
       <c r="C394" t="n" s="2">
-        <v>44709.0</v>
+        <v>44702.0</v>
       </c>
       <c r="D394" t="n">
-        <v>8.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="395">
@@ -5658,10 +5658,10 @@
         <v>2022.0</v>
       </c>
       <c r="C395" t="n" s="2">
-        <v>44716.0</v>
+        <v>44709.0</v>
       </c>
       <c r="D395" t="n">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="396">
@@ -5672,10 +5672,10 @@
         <v>2022.0</v>
       </c>
       <c r="C396" t="n" s="2">
-        <v>44723.0</v>
+        <v>44716.0</v>
       </c>
       <c r="D396" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="397">
@@ -5686,10 +5686,10 @@
         <v>2022.0</v>
       </c>
       <c r="C397" t="n" s="2">
-        <v>44730.0</v>
+        <v>44723.0</v>
       </c>
       <c r="D397" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="398">
@@ -5700,7 +5700,7 @@
         <v>2022.0</v>
       </c>
       <c r="C398" t="n" s="2">
-        <v>44737.0</v>
+        <v>44730.0</v>
       </c>
       <c r="D398" t="n">
         <v>4.0</v>
@@ -5714,10 +5714,10 @@
         <v>2022.0</v>
       </c>
       <c r="C399" t="n" s="2">
-        <v>44744.0</v>
+        <v>44737.0</v>
       </c>
       <c r="D399" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="400">
@@ -5728,10 +5728,10 @@
         <v>2022.0</v>
       </c>
       <c r="C400" t="n" s="2">
-        <v>44751.0</v>
+        <v>44744.0</v>
       </c>
       <c r="D400" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="401">
@@ -5742,10 +5742,10 @@
         <v>2022.0</v>
       </c>
       <c r="C401" t="n" s="2">
-        <v>44758.0</v>
+        <v>44751.0</v>
       </c>
       <c r="D401" t="n">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="402">
@@ -5756,10 +5756,10 @@
         <v>2022.0</v>
       </c>
       <c r="C402" t="n" s="2">
-        <v>44765.0</v>
+        <v>44758.0</v>
       </c>
       <c r="D402" t="n">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="403">
@@ -5770,10 +5770,10 @@
         <v>2022.0</v>
       </c>
       <c r="C403" t="n" s="2">
-        <v>44779.0</v>
+        <v>44765.0</v>
       </c>
       <c r="D403" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="404">
@@ -5784,10 +5784,10 @@
         <v>2022.0</v>
       </c>
       <c r="C404" t="n" s="2">
-        <v>44786.0</v>
+        <v>44779.0</v>
       </c>
       <c r="D404" t="n">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="405">
@@ -5798,10 +5798,10 @@
         <v>2022.0</v>
       </c>
       <c r="C405" t="n" s="2">
-        <v>44863.0</v>
+        <v>44786.0</v>
       </c>
       <c r="D405" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="406">
@@ -5812,10 +5812,10 @@
         <v>2022.0</v>
       </c>
       <c r="C406" t="n" s="2">
-        <v>44870.0</v>
+        <v>44863.0</v>
       </c>
       <c r="D406" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="407">
@@ -5826,10 +5826,10 @@
         <v>2022.0</v>
       </c>
       <c r="C407" t="n" s="2">
-        <v>44884.0</v>
+        <v>44870.0</v>
       </c>
       <c r="D407" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="408">
@@ -5840,7 +5840,7 @@
         <v>2022.0</v>
       </c>
       <c r="C408" t="n" s="2">
-        <v>44891.0</v>
+        <v>44884.0</v>
       </c>
       <c r="D408" t="n">
         <v>2.0</v>
@@ -5854,10 +5854,10 @@
         <v>2022.0</v>
       </c>
       <c r="C409" t="n" s="2">
-        <v>44898.0</v>
+        <v>44891.0</v>
       </c>
       <c r="D409" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="410">
@@ -5868,10 +5868,10 @@
         <v>2022.0</v>
       </c>
       <c r="C410" t="n" s="2">
-        <v>44912.0</v>
+        <v>44898.0</v>
       </c>
       <c r="D410" t="n">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="411">
@@ -5882,10 +5882,10 @@
         <v>2022.0</v>
       </c>
       <c r="C411" t="n" s="2">
-        <v>44919.0</v>
+        <v>44912.0</v>
       </c>
       <c r="D411" t="n">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="412">
@@ -5896,10 +5896,10 @@
         <v>2022.0</v>
       </c>
       <c r="C412" t="n" s="2">
-        <v>44926.0</v>
+        <v>44919.0</v>
       </c>
       <c r="D412" t="n">
-        <v>12.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="413">
@@ -5907,13 +5907,13 @@
         <v>7</v>
       </c>
       <c r="B413" t="n">
-        <v>2023.0</v>
+        <v>2022.0</v>
       </c>
       <c r="C413" t="n" s="2">
-        <v>44934.0</v>
+        <v>44926.0</v>
       </c>
       <c r="D413" t="n">
-        <v>4.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="414">
@@ -5924,10 +5924,10 @@
         <v>2023.0</v>
       </c>
       <c r="C414" t="n" s="2">
-        <v>44941.0</v>
+        <v>44934.0</v>
       </c>
       <c r="D414" t="n">
-        <v>16.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="415">
@@ -5938,10 +5938,10 @@
         <v>2023.0</v>
       </c>
       <c r="C415" t="n" s="2">
-        <v>44948.0</v>
+        <v>44941.0</v>
       </c>
       <c r="D415" t="n">
-        <v>5.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="416">
@@ -5952,10 +5952,10 @@
         <v>2023.0</v>
       </c>
       <c r="C416" t="n" s="2">
-        <v>44955.0</v>
+        <v>44948.0</v>
       </c>
       <c r="D416" t="n">
-        <v>19.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="417">
@@ -5966,10 +5966,10 @@
         <v>2023.0</v>
       </c>
       <c r="C417" t="n" s="2">
-        <v>44962.0</v>
+        <v>44955.0</v>
       </c>
       <c r="D417" t="n">
-        <v>22.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="418">
@@ -5980,10 +5980,10 @@
         <v>2023.0</v>
       </c>
       <c r="C418" t="n" s="2">
-        <v>44969.0</v>
+        <v>44962.0</v>
       </c>
       <c r="D418" t="n">
-        <v>9.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="419">
@@ -5994,10 +5994,10 @@
         <v>2023.0</v>
       </c>
       <c r="C419" t="n" s="2">
-        <v>44976.0</v>
+        <v>44969.0</v>
       </c>
       <c r="D419" t="n">
-        <v>22.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="420">
@@ -6008,10 +6008,10 @@
         <v>2023.0</v>
       </c>
       <c r="C420" t="n" s="2">
-        <v>44983.0</v>
+        <v>44976.0</v>
       </c>
       <c r="D420" t="n">
-        <v>29.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="421">
@@ -6022,10 +6022,10 @@
         <v>2023.0</v>
       </c>
       <c r="C421" t="n" s="2">
-        <v>44990.0</v>
+        <v>44983.0</v>
       </c>
       <c r="D421" t="n">
-        <v>5.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="422">
@@ -6036,10 +6036,10 @@
         <v>2023.0</v>
       </c>
       <c r="C422" t="n" s="2">
-        <v>44997.0</v>
+        <v>44990.0</v>
       </c>
       <c r="D422" t="n">
-        <v>24.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="423">
@@ -6050,10 +6050,10 @@
         <v>2023.0</v>
       </c>
       <c r="C423" t="n" s="2">
-        <v>45004.0</v>
+        <v>44997.0</v>
       </c>
       <c r="D423" t="n">
-        <v>8.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="424">
@@ -6064,10 +6064,10 @@
         <v>2023.0</v>
       </c>
       <c r="C424" t="n" s="2">
-        <v>45011.0</v>
+        <v>45004.0</v>
       </c>
       <c r="D424" t="n">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="425">
@@ -6078,10 +6078,10 @@
         <v>2023.0</v>
       </c>
       <c r="C425" t="n" s="2">
-        <v>45018.0</v>
+        <v>45011.0</v>
       </c>
       <c r="D425" t="n">
-        <v>18.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="426">
@@ -6092,10 +6092,10 @@
         <v>2023.0</v>
       </c>
       <c r="C426" t="n" s="2">
-        <v>45025.0</v>
+        <v>45018.0</v>
       </c>
       <c r="D426" t="n">
-        <v>13.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="427">
@@ -6106,10 +6106,10 @@
         <v>2023.0</v>
       </c>
       <c r="C427" t="n" s="2">
-        <v>45032.0</v>
+        <v>45025.0</v>
       </c>
       <c r="D427" t="n">
-        <v>18.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="428">
@@ -6120,10 +6120,10 @@
         <v>2023.0</v>
       </c>
       <c r="C428" t="n" s="2">
-        <v>45039.0</v>
+        <v>45032.0</v>
       </c>
       <c r="D428" t="n">
-        <v>15.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="429">
@@ -6134,10 +6134,10 @@
         <v>2023.0</v>
       </c>
       <c r="C429" t="n" s="2">
-        <v>45046.0</v>
+        <v>45039.0</v>
       </c>
       <c r="D429" t="n">
-        <v>12.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="430">
@@ -6148,10 +6148,10 @@
         <v>2023.0</v>
       </c>
       <c r="C430" t="n" s="2">
-        <v>45053.0</v>
+        <v>45046.0</v>
       </c>
       <c r="D430" t="n">
-        <v>6.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="431">
@@ -6162,10 +6162,10 @@
         <v>2023.0</v>
       </c>
       <c r="C431" t="n" s="2">
-        <v>45060.0</v>
+        <v>45053.0</v>
       </c>
       <c r="D431" t="n">
-        <v>11.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="432">
@@ -6176,10 +6176,10 @@
         <v>2023.0</v>
       </c>
       <c r="C432" t="n" s="2">
-        <v>45067.0</v>
+        <v>45060.0</v>
       </c>
       <c r="D432" t="n">
-        <v>8.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="433">
@@ -6190,7 +6190,7 @@
         <v>2023.0</v>
       </c>
       <c r="C433" t="n" s="2">
-        <v>45074.0</v>
+        <v>45067.0</v>
       </c>
       <c r="D433" t="n">
         <v>8.0</v>
@@ -6204,10 +6204,10 @@
         <v>2023.0</v>
       </c>
       <c r="C434" t="n" s="2">
-        <v>45081.0</v>
+        <v>45074.0</v>
       </c>
       <c r="D434" t="n">
-        <v>5.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="435">
@@ -6218,10 +6218,10 @@
         <v>2023.0</v>
       </c>
       <c r="C435" t="n" s="2">
-        <v>45088.0</v>
+        <v>45081.0</v>
       </c>
       <c r="D435" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="436">
@@ -6232,10 +6232,10 @@
         <v>2023.0</v>
       </c>
       <c r="C436" t="n" s="2">
-        <v>45095.0</v>
+        <v>45088.0</v>
       </c>
       <c r="D436" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="437">
@@ -6246,10 +6246,10 @@
         <v>2023.0</v>
       </c>
       <c r="C437" t="n" s="2">
-        <v>45102.0</v>
+        <v>45095.0</v>
       </c>
       <c r="D437" t="n">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="438">
@@ -6260,10 +6260,10 @@
         <v>2023.0</v>
       </c>
       <c r="C438" t="n" s="2">
-        <v>45109.0</v>
+        <v>45102.0</v>
       </c>
       <c r="D438" t="n">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="439">
@@ -6274,10 +6274,10 @@
         <v>2023.0</v>
       </c>
       <c r="C439" t="n" s="2">
-        <v>45116.0</v>
+        <v>45109.0</v>
       </c>
       <c r="D439" t="n">
-        <v>3.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="440">
@@ -6288,10 +6288,10 @@
         <v>2023.0</v>
       </c>
       <c r="C440" t="n" s="2">
-        <v>45123.0</v>
+        <v>45116.0</v>
       </c>
       <c r="D440" t="n">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="441">
@@ -6302,7 +6302,7 @@
         <v>2023.0</v>
       </c>
       <c r="C441" t="n" s="2">
-        <v>45130.0</v>
+        <v>45123.0</v>
       </c>
       <c r="D441" t="n">
         <v>6.0</v>
@@ -6316,10 +6316,10 @@
         <v>2023.0</v>
       </c>
       <c r="C442" t="n" s="2">
-        <v>45137.0</v>
+        <v>45130.0</v>
       </c>
       <c r="D442" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="443">
@@ -6330,7 +6330,7 @@
         <v>2023.0</v>
       </c>
       <c r="C443" t="n" s="2">
-        <v>45144.0</v>
+        <v>45137.0</v>
       </c>
       <c r="D443" t="n">
         <v>2.0</v>
@@ -6344,7 +6344,7 @@
         <v>2023.0</v>
       </c>
       <c r="C444" t="n" s="2">
-        <v>45151.0</v>
+        <v>45144.0</v>
       </c>
       <c r="D444" t="n">
         <v>2.0</v>
@@ -6358,7 +6358,7 @@
         <v>2023.0</v>
       </c>
       <c r="C445" t="n" s="2">
-        <v>45165.0</v>
+        <v>45151.0</v>
       </c>
       <c r="D445" t="n">
         <v>2.0</v>
@@ -6372,7 +6372,7 @@
         <v>2023.0</v>
       </c>
       <c r="C446" t="n" s="2">
-        <v>45172.0</v>
+        <v>45165.0</v>
       </c>
       <c r="D446" t="n">
         <v>2.0</v>
@@ -6386,10 +6386,10 @@
         <v>2023.0</v>
       </c>
       <c r="C447" t="n" s="2">
-        <v>45179.0</v>
+        <v>45172.0</v>
       </c>
       <c r="D447" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="448">
@@ -6400,7 +6400,7 @@
         <v>2023.0</v>
       </c>
       <c r="C448" t="n" s="2">
-        <v>45186.0</v>
+        <v>45179.0</v>
       </c>
       <c r="D448" t="n">
         <v>1.0</v>
@@ -6414,7 +6414,7 @@
         <v>2023.0</v>
       </c>
       <c r="C449" t="n" s="2">
-        <v>45193.0</v>
+        <v>45186.0</v>
       </c>
       <c r="D449" t="n">
         <v>1.0</v>
@@ -6428,7 +6428,7 @@
         <v>2023.0</v>
       </c>
       <c r="C450" t="n" s="2">
-        <v>45200.0</v>
+        <v>45193.0</v>
       </c>
       <c r="D450" t="n">
         <v>1.0</v>
@@ -6442,7 +6442,7 @@
         <v>2023.0</v>
       </c>
       <c r="C451" t="n" s="2">
-        <v>45207.0</v>
+        <v>45200.0</v>
       </c>
       <c r="D451" t="n">
         <v>1.0</v>
@@ -6456,7 +6456,7 @@
         <v>2023.0</v>
       </c>
       <c r="C452" t="n" s="2">
-        <v>45235.0</v>
+        <v>45207.0</v>
       </c>
       <c r="D452" t="n">
         <v>1.0</v>
@@ -6470,10 +6470,10 @@
         <v>2023.0</v>
       </c>
       <c r="C453" t="n" s="2">
-        <v>45242.0</v>
+        <v>45235.0</v>
       </c>
       <c r="D453" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="454">
@@ -6484,10 +6484,10 @@
         <v>2023.0</v>
       </c>
       <c r="C454" t="n" s="2">
-        <v>45249.0</v>
+        <v>45242.0</v>
       </c>
       <c r="D454" t="n">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="455">
@@ -6498,10 +6498,10 @@
         <v>2023.0</v>
       </c>
       <c r="C455" t="n" s="2">
-        <v>45256.0</v>
+        <v>45249.0</v>
       </c>
       <c r="D455" t="n">
-        <v>9.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="456">
@@ -6512,10 +6512,10 @@
         <v>2023.0</v>
       </c>
       <c r="C456" t="n" s="2">
-        <v>45263.0</v>
+        <v>45256.0</v>
       </c>
       <c r="D456" t="n">
-        <v>12.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="457">
@@ -6526,10 +6526,10 @@
         <v>2023.0</v>
       </c>
       <c r="C457" t="n" s="2">
-        <v>45270.0</v>
+        <v>45263.0</v>
       </c>
       <c r="D457" t="n">
-        <v>6.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="458">
@@ -6540,10 +6540,10 @@
         <v>2023.0</v>
       </c>
       <c r="C458" t="n" s="2">
-        <v>45277.0</v>
+        <v>45270.0</v>
       </c>
       <c r="D458" t="n">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="459">
@@ -6554,7 +6554,7 @@
         <v>2023.0</v>
       </c>
       <c r="C459" t="n" s="2">
-        <v>45284.0</v>
+        <v>45277.0</v>
       </c>
       <c r="D459" t="n">
         <v>7.0</v>
@@ -6568,10 +6568,10 @@
         <v>2023.0</v>
       </c>
       <c r="C460" t="n" s="2">
-        <v>45291.0</v>
+        <v>45284.0</v>
       </c>
       <c r="D460" t="n">
-        <v>13.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="461">
@@ -6579,13 +6579,13 @@
         <v>7</v>
       </c>
       <c r="B461" t="n">
-        <v>2024.0</v>
+        <v>2023.0</v>
       </c>
       <c r="C461" t="n" s="2">
-        <v>45299.0</v>
+        <v>45291.0</v>
       </c>
       <c r="D461" t="n">
-        <v>6.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="462">
@@ -6596,10 +6596,10 @@
         <v>2024.0</v>
       </c>
       <c r="C462" t="n" s="2">
-        <v>45306.0</v>
+        <v>45299.0</v>
       </c>
       <c r="D462" t="n">
-        <v>11.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="463">
@@ -6610,10 +6610,10 @@
         <v>2024.0</v>
       </c>
       <c r="C463" t="n" s="2">
-        <v>45313.0</v>
+        <v>45306.0</v>
       </c>
       <c r="D463" t="n">
-        <v>5.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="464">
@@ -6624,10 +6624,10 @@
         <v>2024.0</v>
       </c>
       <c r="C464" t="n" s="2">
-        <v>45320.0</v>
+        <v>45313.0</v>
       </c>
       <c r="D464" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="465">
@@ -6638,10 +6638,10 @@
         <v>2024.0</v>
       </c>
       <c r="C465" t="n" s="2">
-        <v>45327.0</v>
+        <v>45320.0</v>
       </c>
       <c r="D465" t="n">
-        <v>9.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="466">
@@ -6652,10 +6652,10 @@
         <v>2024.0</v>
       </c>
       <c r="C466" t="n" s="2">
-        <v>45334.0</v>
+        <v>45327.0</v>
       </c>
       <c r="D466" t="n">
-        <v>3.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="467">
@@ -6666,10 +6666,10 @@
         <v>2024.0</v>
       </c>
       <c r="C467" t="n" s="2">
-        <v>45341.0</v>
+        <v>45334.0</v>
       </c>
       <c r="D467" t="n">
-        <v>21.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="468">
@@ -6680,10 +6680,10 @@
         <v>2024.0</v>
       </c>
       <c r="C468" t="n" s="2">
-        <v>45348.0</v>
+        <v>45341.0</v>
       </c>
       <c r="D468" t="n">
-        <v>1.0</v>
+        <v>21.0</v>
       </c>
     </row>
     <row r="469">
@@ -6694,10 +6694,10 @@
         <v>2024.0</v>
       </c>
       <c r="C469" t="n" s="2">
-        <v>45355.0</v>
+        <v>45348.0</v>
       </c>
       <c r="D469" t="n">
-        <v>9.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="470">
@@ -6708,10 +6708,10 @@
         <v>2024.0</v>
       </c>
       <c r="C470" t="n" s="2">
-        <v>45362.0</v>
+        <v>45355.0</v>
       </c>
       <c r="D470" t="n">
-        <v>4.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="471">
@@ -6722,10 +6722,10 @@
         <v>2024.0</v>
       </c>
       <c r="C471" t="n" s="2">
-        <v>45369.0</v>
+        <v>45362.0</v>
       </c>
       <c r="D471" t="n">
-        <v>14.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="472">
@@ -6736,10 +6736,10 @@
         <v>2024.0</v>
       </c>
       <c r="C472" t="n" s="2">
-        <v>45376.0</v>
+        <v>45369.0</v>
       </c>
       <c r="D472" t="n">
-        <v>4.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="473">
@@ -6750,10 +6750,10 @@
         <v>2024.0</v>
       </c>
       <c r="C473" t="n" s="2">
-        <v>45383.0</v>
+        <v>45376.0</v>
       </c>
       <c r="D473" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="474">
@@ -6764,10 +6764,10 @@
         <v>2024.0</v>
       </c>
       <c r="C474" t="n" s="2">
-        <v>45390.0</v>
+        <v>45383.0</v>
       </c>
       <c r="D474" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="475">
@@ -6778,7 +6778,7 @@
         <v>2024.0</v>
       </c>
       <c r="C475" t="n" s="2">
-        <v>45397.0</v>
+        <v>45390.0</v>
       </c>
       <c r="D475" t="n">
         <v>1.0</v>
@@ -6792,10 +6792,10 @@
         <v>2024.0</v>
       </c>
       <c r="C476" t="n" s="2">
-        <v>45404.0</v>
+        <v>45397.0</v>
       </c>
       <c r="D476" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="477">
@@ -6806,10 +6806,10 @@
         <v>2024.0</v>
       </c>
       <c r="C477" t="n" s="2">
-        <v>45411.0</v>
+        <v>45404.0</v>
       </c>
       <c r="D477" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="478">
@@ -6820,10 +6820,10 @@
         <v>2024.0</v>
       </c>
       <c r="C478" t="n" s="2">
-        <v>45439.0</v>
+        <v>45411.0</v>
       </c>
       <c r="D478" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="479">
@@ -6834,10 +6834,10 @@
         <v>2024.0</v>
       </c>
       <c r="C479" t="n" s="2">
-        <v>45446.0</v>
+        <v>45439.0</v>
       </c>
       <c r="D479" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="480">
@@ -6848,7 +6848,7 @@
         <v>2024.0</v>
       </c>
       <c r="C480" t="n" s="2">
-        <v>45460.0</v>
+        <v>45446.0</v>
       </c>
       <c r="D480" t="n">
         <v>1.0</v>
@@ -6862,7 +6862,7 @@
         <v>2024.0</v>
       </c>
       <c r="C481" t="n" s="2">
-        <v>45481.0</v>
+        <v>45460.0</v>
       </c>
       <c r="D481" t="n">
         <v>1.0</v>
@@ -6876,7 +6876,7 @@
         <v>2024.0</v>
       </c>
       <c r="C482" t="n" s="2">
-        <v>45516.0</v>
+        <v>45481.0</v>
       </c>
       <c r="D482" t="n">
         <v>1.0</v>
@@ -6890,7 +6890,7 @@
         <v>2024.0</v>
       </c>
       <c r="C483" t="n" s="2">
-        <v>45551.0</v>
+        <v>45516.0</v>
       </c>
       <c r="D483" t="n">
         <v>1.0</v>
@@ -6904,7 +6904,7 @@
         <v>2024.0</v>
       </c>
       <c r="C484" t="n" s="2">
-        <v>45579.0</v>
+        <v>45551.0</v>
       </c>
       <c r="D484" t="n">
         <v>1.0</v>
@@ -6918,7 +6918,7 @@
         <v>2024.0</v>
       </c>
       <c r="C485" t="n" s="2">
-        <v>45614.0</v>
+        <v>45579.0</v>
       </c>
       <c r="D485" t="n">
         <v>1.0</v>
@@ -6932,10 +6932,10 @@
         <v>2024.0</v>
       </c>
       <c r="C486" t="n" s="2">
-        <v>45635.0</v>
+        <v>45614.0</v>
       </c>
       <c r="D486" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="487">
@@ -6946,10 +6946,10 @@
         <v>2024.0</v>
       </c>
       <c r="C487" t="n" s="2">
-        <v>45642.0</v>
+        <v>45635.0</v>
       </c>
       <c r="D487" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="488">
@@ -6960,10 +6960,10 @@
         <v>2024.0</v>
       </c>
       <c r="C488" t="n" s="2">
-        <v>45649.0</v>
+        <v>45642.0</v>
       </c>
       <c r="D488" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="489">
@@ -6974,10 +6974,10 @@
         <v>2024.0</v>
       </c>
       <c r="C489" t="n" s="2">
-        <v>45656.0</v>
+        <v>45649.0</v>
       </c>
       <c r="D489" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="490">
@@ -6985,13 +6985,13 @@
         <v>7</v>
       </c>
       <c r="B490" t="n">
-        <v>2025.0</v>
+        <v>2024.0</v>
       </c>
       <c r="C490" t="n" s="2">
-        <v>45665.0</v>
+        <v>45656.0</v>
       </c>
       <c r="D490" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="491">
@@ -7002,10 +7002,10 @@
         <v>2025.0</v>
       </c>
       <c r="C491" t="n" s="2">
-        <v>45672.0</v>
+        <v>45665.0</v>
       </c>
       <c r="D491" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="492">
@@ -7016,7 +7016,7 @@
         <v>2025.0</v>
       </c>
       <c r="C492" t="n" s="2">
-        <v>45686.0</v>
+        <v>45672.0</v>
       </c>
       <c r="D492" t="n">
         <v>2.0</v>
@@ -7030,10 +7030,10 @@
         <v>2025.0</v>
       </c>
       <c r="C493" t="n" s="2">
-        <v>45693.0</v>
+        <v>45686.0</v>
       </c>
       <c r="D493" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="494">
@@ -7044,10 +7044,10 @@
         <v>2025.0</v>
       </c>
       <c r="C494" t="n" s="2">
-        <v>45700.0</v>
+        <v>45693.0</v>
       </c>
       <c r="D494" t="n">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="495">
@@ -7058,10 +7058,10 @@
         <v>2025.0</v>
       </c>
       <c r="C495" t="n" s="2">
-        <v>45707.0</v>
+        <v>45700.0</v>
       </c>
       <c r="D495" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="496">
@@ -7072,10 +7072,10 @@
         <v>2025.0</v>
       </c>
       <c r="C496" t="n" s="2">
-        <v>45714.0</v>
+        <v>45707.0</v>
       </c>
       <c r="D496" t="n">
-        <v>8.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="497">
@@ -7086,10 +7086,10 @@
         <v>2025.0</v>
       </c>
       <c r="C497" t="n" s="2">
-        <v>45721.0</v>
+        <v>45714.0</v>
       </c>
       <c r="D497" t="n">
-        <v>11.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="498">
@@ -7100,10 +7100,10 @@
         <v>2025.0</v>
       </c>
       <c r="C498" t="n" s="2">
-        <v>45728.0</v>
+        <v>45721.0</v>
       </c>
       <c r="D498" t="n">
-        <v>6.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="499">
@@ -7114,10 +7114,10 @@
         <v>2025.0</v>
       </c>
       <c r="C499" t="n" s="2">
-        <v>45735.0</v>
+        <v>45728.0</v>
       </c>
       <c r="D499" t="n">
-        <v>19.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="500">
@@ -7128,10 +7128,10 @@
         <v>2025.0</v>
       </c>
       <c r="C500" t="n" s="2">
-        <v>45742.0</v>
+        <v>45735.0</v>
       </c>
       <c r="D500" t="n">
-        <v>17.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="501">
@@ -7142,10 +7142,10 @@
         <v>2025.0</v>
       </c>
       <c r="C501" t="n" s="2">
-        <v>45749.0</v>
+        <v>45742.0</v>
       </c>
       <c r="D501" t="n">
-        <v>5.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="502">
@@ -7156,10 +7156,10 @@
         <v>2025.0</v>
       </c>
       <c r="C502" t="n" s="2">
-        <v>45756.0</v>
+        <v>45749.0</v>
       </c>
       <c r="D502" t="n">
-        <v>9.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="503">
@@ -7170,10 +7170,10 @@
         <v>2025.0</v>
       </c>
       <c r="C503" t="n" s="2">
-        <v>45763.0</v>
+        <v>45756.0</v>
       </c>
       <c r="D503" t="n">
-        <v>1.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="504">
@@ -7184,7 +7184,7 @@
         <v>2025.0</v>
       </c>
       <c r="C504" t="n" s="2">
-        <v>45770.0</v>
+        <v>45763.0</v>
       </c>
       <c r="D504" t="n">
         <v>1.0</v>
@@ -7198,10 +7198,10 @@
         <v>2025.0</v>
       </c>
       <c r="C505" t="n" s="2">
-        <v>45784.0</v>
+        <v>45770.0</v>
       </c>
       <c r="D505" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="506">
@@ -7212,10 +7212,10 @@
         <v>2025.0</v>
       </c>
       <c r="C506" t="n" s="2">
-        <v>45791.0</v>
+        <v>45784.0</v>
       </c>
       <c r="D506" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="507">
@@ -7226,10 +7226,10 @@
         <v>2025.0</v>
       </c>
       <c r="C507" t="n" s="2">
-        <v>45805.0</v>
+        <v>45791.0</v>
       </c>
       <c r="D507" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="508">
@@ -7240,10 +7240,10 @@
         <v>2025.0</v>
       </c>
       <c r="C508" t="n" s="2">
-        <v>45826.0</v>
+        <v>45805.0</v>
       </c>
       <c r="D508" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="509">
@@ -7254,7 +7254,7 @@
         <v>2025.0</v>
       </c>
       <c r="C509" t="n" s="2">
-        <v>45861.0</v>
+        <v>45826.0</v>
       </c>
       <c r="D509" t="n">
         <v>2.0</v>
@@ -7268,10 +7268,10 @@
         <v>2025.0</v>
       </c>
       <c r="C510" t="n" s="2">
-        <v>45868.0</v>
+        <v>45861.0</v>
       </c>
       <c r="D510" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="511">
@@ -7282,7 +7282,7 @@
         <v>2025.0</v>
       </c>
       <c r="C511" t="n" s="2">
-        <v>45889.0</v>
+        <v>45868.0</v>
       </c>
       <c r="D511" t="n">
         <v>1.0</v>
@@ -7296,7 +7296,7 @@
         <v>2025.0</v>
       </c>
       <c r="C512" t="n" s="2">
-        <v>45924.0</v>
+        <v>45889.0</v>
       </c>
       <c r="D512" t="n">
         <v>1.0</v>
@@ -7310,7 +7310,7 @@
         <v>2025.0</v>
       </c>
       <c r="C513" t="n" s="2">
-        <v>45945.0</v>
+        <v>45924.0</v>
       </c>
       <c r="D513" t="n">
         <v>1.0</v>
@@ -7324,10 +7324,10 @@
         <v>2025.0</v>
       </c>
       <c r="C514" t="n" s="2">
-        <v>45959.0</v>
+        <v>45945.0</v>
       </c>
       <c r="D514" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="515">
@@ -7338,7 +7338,7 @@
         <v>2025.0</v>
       </c>
       <c r="C515" t="n" s="2">
-        <v>46001.0</v>
+        <v>45959.0</v>
       </c>
       <c r="D515" t="n">
         <v>2.0</v>
@@ -7352,10 +7352,10 @@
         <v>2025.0</v>
       </c>
       <c r="C516" t="n" s="2">
-        <v>46008.0</v>
+        <v>46001.0</v>
       </c>
       <c r="D516" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="517">
@@ -7366,7 +7366,7 @@
         <v>2025.0</v>
       </c>
       <c r="C517" t="n" s="2">
-        <v>46022.0</v>
+        <v>46008.0</v>
       </c>
       <c r="D517" t="n">
         <v>1.0</v>
@@ -7377,10 +7377,10 @@
         <v>7</v>
       </c>
       <c r="B518" t="n">
-        <v>2026.0</v>
+        <v>2025.0</v>
       </c>
       <c r="C518" t="n" s="2">
-        <v>46030.0</v>
+        <v>46022.0</v>
       </c>
       <c r="D518" t="n">
         <v>1.0</v>
@@ -7394,7 +7394,7 @@
         <v>2026.0</v>
       </c>
       <c r="C519" t="n" s="2">
-        <v>46051.0</v>
+        <v>46030.0</v>
       </c>
       <c r="D519" t="n">
         <v>1.0</v>
@@ -7408,7 +7408,7 @@
         <v>2026.0</v>
       </c>
       <c r="C520" t="n" s="2">
-        <v>46058.0</v>
+        <v>46051.0</v>
       </c>
       <c r="D520" t="n">
         <v>1.0</v>
@@ -7422,10 +7422,10 @@
         <v>2026.0</v>
       </c>
       <c r="C521" t="n" s="2">
-        <v>46065.0</v>
+        <v>46058.0</v>
       </c>
       <c r="D521" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="522">
@@ -7436,24 +7436,24 @@
         <v>2026.0</v>
       </c>
       <c r="C522" t="n" s="2">
-        <v>46135.0</v>
+        <v>46065.0</v>
       </c>
       <c r="D522" t="n">
-        <v>8.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B523" t="n">
-        <v>2024.0</v>
+        <v>2026.0</v>
       </c>
       <c r="C523" t="n" s="2">
-        <v>45495.0</v>
+        <v>46135.0</v>
       </c>
       <c r="D523" t="n">
-        <v>1.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="524">
@@ -7464,10 +7464,10 @@
         <v>2024.0</v>
       </c>
       <c r="C524" t="n" s="2">
-        <v>45502.0</v>
+        <v>45495.0</v>
       </c>
       <c r="D524" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="525">
@@ -7475,13 +7475,13 @@
         <v>8</v>
       </c>
       <c r="B525" t="n">
-        <v>2025.0</v>
+        <v>2024.0</v>
       </c>
       <c r="C525" t="n" s="2">
-        <v>45665.0</v>
+        <v>45502.0</v>
       </c>
       <c r="D525" t="n">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="526">
@@ -7492,10 +7492,10 @@
         <v>2025.0</v>
       </c>
       <c r="C526" t="n" s="2">
-        <v>45672.0</v>
+        <v>45665.0</v>
       </c>
       <c r="D526" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="527">
@@ -7506,10 +7506,10 @@
         <v>2025.0</v>
       </c>
       <c r="C527" t="n" s="2">
-        <v>45679.0</v>
+        <v>45672.0</v>
       </c>
       <c r="D527" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="528">
@@ -7520,10 +7520,10 @@
         <v>2025.0</v>
       </c>
       <c r="C528" t="n" s="2">
-        <v>45686.0</v>
+        <v>45679.0</v>
       </c>
       <c r="D528" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="529">
@@ -7534,10 +7534,10 @@
         <v>2025.0</v>
       </c>
       <c r="C529" t="n" s="2">
-        <v>45693.0</v>
+        <v>45686.0</v>
       </c>
       <c r="D529" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="530">
@@ -7548,10 +7548,10 @@
         <v>2025.0</v>
       </c>
       <c r="C530" t="n" s="2">
-        <v>45700.0</v>
+        <v>45693.0</v>
       </c>
       <c r="D530" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="531">
@@ -7562,10 +7562,10 @@
         <v>2025.0</v>
       </c>
       <c r="C531" t="n" s="2">
-        <v>45707.0</v>
+        <v>45700.0</v>
       </c>
       <c r="D531" t="n">
-        <v>7.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="532">
@@ -7576,10 +7576,10 @@
         <v>2025.0</v>
       </c>
       <c r="C532" t="n" s="2">
-        <v>45714.0</v>
+        <v>45707.0</v>
       </c>
       <c r="D532" t="n">
-        <v>3.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="533">
@@ -7590,10 +7590,10 @@
         <v>2025.0</v>
       </c>
       <c r="C533" t="n" s="2">
-        <v>45721.0</v>
+        <v>45714.0</v>
       </c>
       <c r="D533" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="534">
@@ -7604,10 +7604,10 @@
         <v>2025.0</v>
       </c>
       <c r="C534" t="n" s="2">
-        <v>45728.0</v>
+        <v>45721.0</v>
       </c>
       <c r="D534" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="535">
@@ -7618,7 +7618,7 @@
         <v>2025.0</v>
       </c>
       <c r="C535" t="n" s="2">
-        <v>45742.0</v>
+        <v>45728.0</v>
       </c>
       <c r="D535" t="n">
         <v>1.0</v>
@@ -7632,7 +7632,7 @@
         <v>2025.0</v>
       </c>
       <c r="C536" t="n" s="2">
-        <v>45749.0</v>
+        <v>45742.0</v>
       </c>
       <c r="D536" t="n">
         <v>1.0</v>
@@ -7646,7 +7646,7 @@
         <v>2025.0</v>
       </c>
       <c r="C537" t="n" s="2">
-        <v>45763.0</v>
+        <v>45749.0</v>
       </c>
       <c r="D537" t="n">
         <v>1.0</v>
@@ -7660,10 +7660,10 @@
         <v>2025.0</v>
       </c>
       <c r="C538" t="n" s="2">
-        <v>45777.0</v>
+        <v>45763.0</v>
       </c>
       <c r="D538" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="539">
@@ -7674,10 +7674,10 @@
         <v>2025.0</v>
       </c>
       <c r="C539" t="n" s="2">
-        <v>45784.0</v>
+        <v>45777.0</v>
       </c>
       <c r="D539" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="540">
@@ -7688,7 +7688,7 @@
         <v>2025.0</v>
       </c>
       <c r="C540" t="n" s="2">
-        <v>45798.0</v>
+        <v>45784.0</v>
       </c>
       <c r="D540" t="n">
         <v>1.0</v>
@@ -7702,7 +7702,7 @@
         <v>2025.0</v>
       </c>
       <c r="C541" t="n" s="2">
-        <v>45805.0</v>
+        <v>45798.0</v>
       </c>
       <c r="D541" t="n">
         <v>1.0</v>
@@ -7716,10 +7716,10 @@
         <v>2025.0</v>
       </c>
       <c r="C542" t="n" s="2">
-        <v>45812.0</v>
+        <v>45805.0</v>
       </c>
       <c r="D542" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="543">
@@ -7730,7 +7730,7 @@
         <v>2025.0</v>
       </c>
       <c r="C543" t="n" s="2">
-        <v>45819.0</v>
+        <v>45812.0</v>
       </c>
       <c r="D543" t="n">
         <v>2.0</v>
@@ -7744,7 +7744,7 @@
         <v>2025.0</v>
       </c>
       <c r="C544" t="n" s="2">
-        <v>45833.0</v>
+        <v>45819.0</v>
       </c>
       <c r="D544" t="n">
         <v>2.0</v>
@@ -7758,10 +7758,10 @@
         <v>2025.0</v>
       </c>
       <c r="C545" t="n" s="2">
-        <v>45847.0</v>
+        <v>45833.0</v>
       </c>
       <c r="D545" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="546">
@@ -7772,10 +7772,10 @@
         <v>2025.0</v>
       </c>
       <c r="C546" t="n" s="2">
-        <v>45854.0</v>
+        <v>45847.0</v>
       </c>
       <c r="D546" t="n">
-        <v>8.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="547">
@@ -7786,10 +7786,10 @@
         <v>2025.0</v>
       </c>
       <c r="C547" t="n" s="2">
-        <v>45861.0</v>
+        <v>45854.0</v>
       </c>
       <c r="D547" t="n">
-        <v>12.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="548">
@@ -7800,10 +7800,10 @@
         <v>2025.0</v>
       </c>
       <c r="C548" t="n" s="2">
-        <v>45868.0</v>
+        <v>45861.0</v>
       </c>
       <c r="D548" t="n">
-        <v>6.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="549">
@@ -7814,10 +7814,10 @@
         <v>2025.0</v>
       </c>
       <c r="C549" t="n" s="2">
-        <v>45875.0</v>
+        <v>45868.0</v>
       </c>
       <c r="D549" t="n">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="550">
@@ -7828,7 +7828,7 @@
         <v>2025.0</v>
       </c>
       <c r="C550" t="n" s="2">
-        <v>45896.0</v>
+        <v>45875.0</v>
       </c>
       <c r="D550" t="n">
         <v>1.0</v>
@@ -7842,7 +7842,7 @@
         <v>2025.0</v>
       </c>
       <c r="C551" t="n" s="2">
-        <v>45903.0</v>
+        <v>45896.0</v>
       </c>
       <c r="D551" t="n">
         <v>1.0</v>
@@ -7856,7 +7856,7 @@
         <v>2025.0</v>
       </c>
       <c r="C552" t="n" s="2">
-        <v>45931.0</v>
+        <v>45903.0</v>
       </c>
       <c r="D552" t="n">
         <v>1.0</v>
@@ -7870,10 +7870,10 @@
         <v>2025.0</v>
       </c>
       <c r="C553" t="n" s="2">
-        <v>45938.0</v>
+        <v>45931.0</v>
       </c>
       <c r="D553" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="554">
@@ -7884,10 +7884,10 @@
         <v>2025.0</v>
       </c>
       <c r="C554" t="n" s="2">
-        <v>45945.0</v>
+        <v>45938.0</v>
       </c>
       <c r="D554" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="555">
@@ -7898,7 +7898,7 @@
         <v>2025.0</v>
       </c>
       <c r="C555" t="n" s="2">
-        <v>45966.0</v>
+        <v>45945.0</v>
       </c>
       <c r="D555" t="n">
         <v>2.0</v>
@@ -7912,10 +7912,10 @@
         <v>2025.0</v>
       </c>
       <c r="C556" t="n" s="2">
-        <v>45973.0</v>
+        <v>45966.0</v>
       </c>
       <c r="D556" t="n">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="557">
@@ -7926,10 +7926,10 @@
         <v>2025.0</v>
       </c>
       <c r="C557" t="n" s="2">
-        <v>45980.0</v>
+        <v>45973.0</v>
       </c>
       <c r="D557" t="n">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="558">
@@ -7940,10 +7940,10 @@
         <v>2025.0</v>
       </c>
       <c r="C558" t="n" s="2">
-        <v>45987.0</v>
+        <v>45980.0</v>
       </c>
       <c r="D558" t="n">
-        <v>20.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="559">
@@ -7954,10 +7954,10 @@
         <v>2025.0</v>
       </c>
       <c r="C559" t="n" s="2">
-        <v>45994.0</v>
+        <v>45987.0</v>
       </c>
       <c r="D559" t="n">
-        <v>5.0</v>
+        <v>20.0</v>
       </c>
     </row>
     <row r="560">
@@ -7968,10 +7968,10 @@
         <v>2025.0</v>
       </c>
       <c r="C560" t="n" s="2">
-        <v>46001.0</v>
+        <v>45994.0</v>
       </c>
       <c r="D560" t="n">
-        <v>8.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="561">
@@ -7982,10 +7982,10 @@
         <v>2025.0</v>
       </c>
       <c r="C561" t="n" s="2">
-        <v>46008.0</v>
+        <v>46001.0</v>
       </c>
       <c r="D561" t="n">
-        <v>24.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="562">
@@ -7996,10 +7996,10 @@
         <v>2025.0</v>
       </c>
       <c r="C562" t="n" s="2">
-        <v>46015.0</v>
+        <v>46008.0</v>
       </c>
       <c r="D562" t="n">
-        <v>13.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="563">
@@ -8010,10 +8010,10 @@
         <v>2025.0</v>
       </c>
       <c r="C563" t="n" s="2">
-        <v>46022.0</v>
+        <v>46015.0</v>
       </c>
       <c r="D563" t="n">
-        <v>8.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="564">
@@ -8024,10 +8024,10 @@
         <v>2025.0</v>
       </c>
       <c r="C564" t="n" s="2">
-        <v>46029.0</v>
+        <v>46022.0</v>
       </c>
       <c r="D564" t="n">
-        <v>3.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="565">
@@ -8035,13 +8035,13 @@
         <v>8</v>
       </c>
       <c r="B565" t="n">
-        <v>2026.0</v>
+        <v>2025.0</v>
       </c>
       <c r="C565" t="n" s="2">
-        <v>46030.0</v>
+        <v>46029.0</v>
       </c>
       <c r="D565" t="n">
-        <v>24.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="566">
@@ -8052,10 +8052,10 @@
         <v>2026.0</v>
       </c>
       <c r="C566" t="n" s="2">
-        <v>46037.0</v>
+        <v>46030.0</v>
       </c>
       <c r="D566" t="n">
-        <v>22.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="567">
@@ -8066,10 +8066,10 @@
         <v>2026.0</v>
       </c>
       <c r="C567" t="n" s="2">
-        <v>46044.0</v>
+        <v>46037.0</v>
       </c>
       <c r="D567" t="n">
-        <v>27.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="568">
@@ -8080,10 +8080,10 @@
         <v>2026.0</v>
       </c>
       <c r="C568" t="n" s="2">
-        <v>46051.0</v>
+        <v>46044.0</v>
       </c>
       <c r="D568" t="n">
-        <v>18.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="569">
@@ -8094,10 +8094,10 @@
         <v>2026.0</v>
       </c>
       <c r="C569" t="n" s="2">
-        <v>46058.0</v>
+        <v>46051.0</v>
       </c>
       <c r="D569" t="n">
-        <v>25.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="570">
@@ -8108,10 +8108,10 @@
         <v>2026.0</v>
       </c>
       <c r="C570" t="n" s="2">
-        <v>46065.0</v>
+        <v>46058.0</v>
       </c>
       <c r="D570" t="n">
-        <v>22.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="571">
@@ -8122,10 +8122,10 @@
         <v>2026.0</v>
       </c>
       <c r="C571" t="n" s="2">
-        <v>46072.0</v>
+        <v>46065.0</v>
       </c>
       <c r="D571" t="n">
-        <v>13.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="572">
@@ -8136,10 +8136,10 @@
         <v>2026.0</v>
       </c>
       <c r="C572" t="n" s="2">
-        <v>46079.0</v>
+        <v>46072.0</v>
       </c>
       <c r="D572" t="n">
-        <v>24.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="573">
@@ -8150,10 +8150,10 @@
         <v>2026.0</v>
       </c>
       <c r="C573" t="n" s="2">
-        <v>46086.0</v>
+        <v>46079.0</v>
       </c>
       <c r="D573" t="n">
-        <v>26.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="574">
@@ -8164,10 +8164,10 @@
         <v>2026.0</v>
       </c>
       <c r="C574" t="n" s="2">
-        <v>46093.0</v>
+        <v>46086.0</v>
       </c>
       <c r="D574" t="n">
-        <v>33.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="575">
@@ -8178,10 +8178,10 @@
         <v>2026.0</v>
       </c>
       <c r="C575" t="n" s="2">
-        <v>46100.0</v>
+        <v>46093.0</v>
       </c>
       <c r="D575" t="n">
-        <v>25.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="576">
@@ -8192,10 +8192,10 @@
         <v>2026.0</v>
       </c>
       <c r="C576" t="n" s="2">
-        <v>46107.0</v>
+        <v>46100.0</v>
       </c>
       <c r="D576" t="n">
-        <v>31.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="577">
@@ -8206,10 +8206,10 @@
         <v>2026.0</v>
       </c>
       <c r="C577" t="n" s="2">
-        <v>46114.0</v>
+        <v>46107.0</v>
       </c>
       <c r="D577" t="n">
-        <v>10.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="578">
@@ -8220,10 +8220,10 @@
         <v>2026.0</v>
       </c>
       <c r="C578" t="n" s="2">
-        <v>46121.0</v>
+        <v>46114.0</v>
       </c>
       <c r="D578" t="n">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="579">
@@ -8234,10 +8234,10 @@
         <v>2026.0</v>
       </c>
       <c r="C579" t="n" s="2">
-        <v>46128.0</v>
+        <v>46121.0</v>
       </c>
       <c r="D579" t="n">
-        <v>15.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="580">
@@ -8248,10 +8248,10 @@
         <v>2026.0</v>
       </c>
       <c r="C580" t="n" s="2">
-        <v>46135.0</v>
+        <v>46128.0</v>
       </c>
       <c r="D580" t="n">
-        <v>23.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="581">
@@ -8262,10 +8262,10 @@
         <v>2026.0</v>
       </c>
       <c r="C581" t="n" s="2">
-        <v>46142.0</v>
+        <v>46135.0</v>
       </c>
       <c r="D581" t="n">
-        <v>21.0</v>
+        <v>23.0</v>
       </c>
     </row>
     <row r="582">
@@ -8276,10 +8276,10 @@
         <v>2026.0</v>
       </c>
       <c r="C582" t="n" s="2">
-        <v>46149.0</v>
+        <v>46142.0</v>
       </c>
       <c r="D582" t="n">
-        <v>6.0</v>
+        <v>21.0</v>
       </c>
     </row>
     <row r="583">
@@ -8290,10 +8290,10 @@
         <v>2026.0</v>
       </c>
       <c r="C583" t="n" s="2">
-        <v>46156.0</v>
+        <v>46149.0</v>
       </c>
       <c r="D583" t="n">
-        <v>27.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="584">
@@ -8304,10 +8304,24 @@
         <v>2026.0</v>
       </c>
       <c r="C584" t="n" s="2">
+        <v>46156.0</v>
+      </c>
+      <c r="D584" t="n">
+        <v>27.0</v>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="s">
+        <v>8</v>
+      </c>
+      <c r="B585" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C585" t="n" s="2">
         <v>46163.0</v>
       </c>
-      <c r="D584" t="n">
-        <v>4.0</v>
+      <c r="D585" t="n">
+        <v>12.0</v>
       </c>
     </row>
   </sheetData>
@@ -8333,7 +8347,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="n">
-        <v>52.0</v>
+        <v>50.0</v>
       </c>
     </row>
     <row r="3">
@@ -8349,7 +8363,7 @@
         <v>12</v>
       </c>
       <c r="B4" t="n">
-        <v>1276.0</v>
+        <v>1280.0</v>
       </c>
     </row>
     <row r="5">
@@ -8357,7 +8371,7 @@
         <v>13</v>
       </c>
       <c r="B5" t="n">
-        <v>2133.0</v>
+        <v>2140.0</v>
       </c>
     </row>
   </sheetData>
@@ -8389,7 +8403,7 @@
         <v>21</v>
       </c>
       <c r="C2" t="n">
-        <v>204.0</v>
+        <v>206.0</v>
       </c>
     </row>
     <row r="3">
@@ -8400,7 +8414,7 @@
         <v>22</v>
       </c>
       <c r="C3" t="n">
-        <v>181.0</v>
+        <v>183.0</v>
       </c>
     </row>
     <row r="4">
@@ -8422,7 +8436,7 @@
         <v>21</v>
       </c>
       <c r="C5" t="n">
-        <v>424.0</v>
+        <v>427.0</v>
       </c>
     </row>
     <row r="6">
@@ -8433,7 +8447,7 @@
         <v>22</v>
       </c>
       <c r="C6" t="n">
-        <v>306.0</v>
+        <v>307.0</v>
       </c>
     </row>
     <row r="7">
@@ -8488,7 +8502,7 @@
         <v>19</v>
       </c>
       <c r="C11" t="n">
-        <v>38.0</v>
+        <v>36.0</v>
       </c>
     </row>
     <row r="12">
@@ -8499,7 +8513,7 @@
         <v>21</v>
       </c>
       <c r="C12" t="n">
-        <v>75.0</v>
+        <v>76.0</v>
       </c>
     </row>
     <row r="13">
@@ -8532,7 +8546,7 @@
         <v>21</v>
       </c>
       <c r="C15" t="n">
-        <v>368.0</v>
+        <v>370.0</v>
       </c>
     </row>
     <row r="16">

--- a/Download/Focus_Positivi_ZR.xlsx
+++ b/Download/Focus_Positivi_ZR.xlsx
@@ -4331,7 +4331,7 @@
         <v>46163.0</v>
       </c>
       <c r="D300" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="301">
@@ -8347,7 +8347,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="n">
-        <v>50.0</v>
+        <v>49.0</v>
       </c>
     </row>
     <row r="3">
@@ -8355,7 +8355,7 @@
         <v>11</v>
       </c>
       <c r="B3" t="n">
-        <v>198.0</v>
+        <v>199.0</v>
       </c>
     </row>
     <row r="4">
@@ -8363,7 +8363,7 @@
         <v>12</v>
       </c>
       <c r="B4" t="n">
-        <v>1280.0</v>
+        <v>1281.0</v>
       </c>
     </row>
     <row r="5">
@@ -8414,7 +8414,7 @@
         <v>22</v>
       </c>
       <c r="C3" t="n">
-        <v>183.0</v>
+        <v>184.0</v>
       </c>
     </row>
     <row r="4">
@@ -8502,7 +8502,7 @@
         <v>19</v>
       </c>
       <c r="C11" t="n">
-        <v>36.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="12">
@@ -8535,7 +8535,7 @@
         <v>19</v>
       </c>
       <c r="C14" t="n">
-        <v>415.0</v>
+        <v>416.0</v>
       </c>
     </row>
     <row r="15">

--- a/Download/Focus_Positivi_ZR.xlsx
+++ b/Download/Focus_Positivi_ZR.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="629" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="631" uniqueCount="23">
   <si>
     <t>NOME_REGIONE</t>
   </si>
@@ -4331,7 +4331,7 @@
         <v>46163.0</v>
       </c>
       <c r="D300" t="n">
-        <v>2.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="301">
@@ -7458,13 +7458,13 @@
     </row>
     <row r="524">
       <c r="A524" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B524" t="n">
-        <v>2024.0</v>
+        <v>2026.0</v>
       </c>
       <c r="C524" t="n" s="2">
-        <v>45495.0</v>
+        <v>46156.0</v>
       </c>
       <c r="D524" t="n">
         <v>1.0</v>
@@ -7472,16 +7472,16 @@
     </row>
     <row r="525">
       <c r="A525" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B525" t="n">
-        <v>2024.0</v>
+        <v>2026.0</v>
       </c>
       <c r="C525" t="n" s="2">
-        <v>45502.0</v>
+        <v>46163.0</v>
       </c>
       <c r="D525" t="n">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="526">
@@ -7489,10 +7489,10 @@
         <v>8</v>
       </c>
       <c r="B526" t="n">
-        <v>2025.0</v>
+        <v>2024.0</v>
       </c>
       <c r="C526" t="n" s="2">
-        <v>45665.0</v>
+        <v>45495.0</v>
       </c>
       <c r="D526" t="n">
         <v>1.0</v>
@@ -7503,13 +7503,13 @@
         <v>8</v>
       </c>
       <c r="B527" t="n">
-        <v>2025.0</v>
+        <v>2024.0</v>
       </c>
       <c r="C527" t="n" s="2">
-        <v>45672.0</v>
+        <v>45502.0</v>
       </c>
       <c r="D527" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="528">
@@ -7520,7 +7520,7 @@
         <v>2025.0</v>
       </c>
       <c r="C528" t="n" s="2">
-        <v>45679.0</v>
+        <v>45665.0</v>
       </c>
       <c r="D528" t="n">
         <v>1.0</v>
@@ -7534,10 +7534,10 @@
         <v>2025.0</v>
       </c>
       <c r="C529" t="n" s="2">
-        <v>45686.0</v>
+        <v>45672.0</v>
       </c>
       <c r="D529" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="530">
@@ -7548,7 +7548,7 @@
         <v>2025.0</v>
       </c>
       <c r="C530" t="n" s="2">
-        <v>45693.0</v>
+        <v>45679.0</v>
       </c>
       <c r="D530" t="n">
         <v>1.0</v>
@@ -7562,10 +7562,10 @@
         <v>2025.0</v>
       </c>
       <c r="C531" t="n" s="2">
-        <v>45700.0</v>
+        <v>45686.0</v>
       </c>
       <c r="D531" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="532">
@@ -7576,10 +7576,10 @@
         <v>2025.0</v>
       </c>
       <c r="C532" t="n" s="2">
-        <v>45707.0</v>
+        <v>45693.0</v>
       </c>
       <c r="D532" t="n">
-        <v>7.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="533">
@@ -7590,10 +7590,10 @@
         <v>2025.0</v>
       </c>
       <c r="C533" t="n" s="2">
-        <v>45714.0</v>
+        <v>45700.0</v>
       </c>
       <c r="D533" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="534">
@@ -7604,10 +7604,10 @@
         <v>2025.0</v>
       </c>
       <c r="C534" t="n" s="2">
-        <v>45721.0</v>
+        <v>45707.0</v>
       </c>
       <c r="D534" t="n">
-        <v>4.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="535">
@@ -7618,10 +7618,10 @@
         <v>2025.0</v>
       </c>
       <c r="C535" t="n" s="2">
-        <v>45728.0</v>
+        <v>45714.0</v>
       </c>
       <c r="D535" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="536">
@@ -7632,10 +7632,10 @@
         <v>2025.0</v>
       </c>
       <c r="C536" t="n" s="2">
-        <v>45742.0</v>
+        <v>45721.0</v>
       </c>
       <c r="D536" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="537">
@@ -7646,7 +7646,7 @@
         <v>2025.0</v>
       </c>
       <c r="C537" t="n" s="2">
-        <v>45749.0</v>
+        <v>45728.0</v>
       </c>
       <c r="D537" t="n">
         <v>1.0</v>
@@ -7660,7 +7660,7 @@
         <v>2025.0</v>
       </c>
       <c r="C538" t="n" s="2">
-        <v>45763.0</v>
+        <v>45742.0</v>
       </c>
       <c r="D538" t="n">
         <v>1.0</v>
@@ -7674,10 +7674,10 @@
         <v>2025.0</v>
       </c>
       <c r="C539" t="n" s="2">
-        <v>45777.0</v>
+        <v>45749.0</v>
       </c>
       <c r="D539" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="540">
@@ -7688,7 +7688,7 @@
         <v>2025.0</v>
       </c>
       <c r="C540" t="n" s="2">
-        <v>45784.0</v>
+        <v>45763.0</v>
       </c>
       <c r="D540" t="n">
         <v>1.0</v>
@@ -7702,10 +7702,10 @@
         <v>2025.0</v>
       </c>
       <c r="C541" t="n" s="2">
-        <v>45798.0</v>
+        <v>45777.0</v>
       </c>
       <c r="D541" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="542">
@@ -7716,7 +7716,7 @@
         <v>2025.0</v>
       </c>
       <c r="C542" t="n" s="2">
-        <v>45805.0</v>
+        <v>45784.0</v>
       </c>
       <c r="D542" t="n">
         <v>1.0</v>
@@ -7730,10 +7730,10 @@
         <v>2025.0</v>
       </c>
       <c r="C543" t="n" s="2">
-        <v>45812.0</v>
+        <v>45798.0</v>
       </c>
       <c r="D543" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="544">
@@ -7744,10 +7744,10 @@
         <v>2025.0</v>
       </c>
       <c r="C544" t="n" s="2">
-        <v>45819.0</v>
+        <v>45805.0</v>
       </c>
       <c r="D544" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="545">
@@ -7758,7 +7758,7 @@
         <v>2025.0</v>
       </c>
       <c r="C545" t="n" s="2">
-        <v>45833.0</v>
+        <v>45812.0</v>
       </c>
       <c r="D545" t="n">
         <v>2.0</v>
@@ -7772,10 +7772,10 @@
         <v>2025.0</v>
       </c>
       <c r="C546" t="n" s="2">
-        <v>45847.0</v>
+        <v>45819.0</v>
       </c>
       <c r="D546" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="547">
@@ -7786,10 +7786,10 @@
         <v>2025.0</v>
       </c>
       <c r="C547" t="n" s="2">
-        <v>45854.0</v>
+        <v>45833.0</v>
       </c>
       <c r="D547" t="n">
-        <v>8.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="548">
@@ -7800,10 +7800,10 @@
         <v>2025.0</v>
       </c>
       <c r="C548" t="n" s="2">
-        <v>45861.0</v>
+        <v>45847.0</v>
       </c>
       <c r="D548" t="n">
-        <v>12.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="549">
@@ -7814,10 +7814,10 @@
         <v>2025.0</v>
       </c>
       <c r="C549" t="n" s="2">
-        <v>45868.0</v>
+        <v>45854.0</v>
       </c>
       <c r="D549" t="n">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="550">
@@ -7828,10 +7828,10 @@
         <v>2025.0</v>
       </c>
       <c r="C550" t="n" s="2">
-        <v>45875.0</v>
+        <v>45861.0</v>
       </c>
       <c r="D550" t="n">
-        <v>1.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="551">
@@ -7842,10 +7842,10 @@
         <v>2025.0</v>
       </c>
       <c r="C551" t="n" s="2">
-        <v>45896.0</v>
+        <v>45868.0</v>
       </c>
       <c r="D551" t="n">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="552">
@@ -7856,7 +7856,7 @@
         <v>2025.0</v>
       </c>
       <c r="C552" t="n" s="2">
-        <v>45903.0</v>
+        <v>45875.0</v>
       </c>
       <c r="D552" t="n">
         <v>1.0</v>
@@ -7870,7 +7870,7 @@
         <v>2025.0</v>
       </c>
       <c r="C553" t="n" s="2">
-        <v>45931.0</v>
+        <v>45896.0</v>
       </c>
       <c r="D553" t="n">
         <v>1.0</v>
@@ -7884,10 +7884,10 @@
         <v>2025.0</v>
       </c>
       <c r="C554" t="n" s="2">
-        <v>45938.0</v>
+        <v>45903.0</v>
       </c>
       <c r="D554" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="555">
@@ -7898,10 +7898,10 @@
         <v>2025.0</v>
       </c>
       <c r="C555" t="n" s="2">
-        <v>45945.0</v>
+        <v>45931.0</v>
       </c>
       <c r="D555" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="556">
@@ -7912,10 +7912,10 @@
         <v>2025.0</v>
       </c>
       <c r="C556" t="n" s="2">
-        <v>45966.0</v>
+        <v>45938.0</v>
       </c>
       <c r="D556" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="557">
@@ -7926,10 +7926,10 @@
         <v>2025.0</v>
       </c>
       <c r="C557" t="n" s="2">
-        <v>45973.0</v>
+        <v>45945.0</v>
       </c>
       <c r="D557" t="n">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="558">
@@ -7940,10 +7940,10 @@
         <v>2025.0</v>
       </c>
       <c r="C558" t="n" s="2">
-        <v>45980.0</v>
+        <v>45966.0</v>
       </c>
       <c r="D558" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="559">
@@ -7954,10 +7954,10 @@
         <v>2025.0</v>
       </c>
       <c r="C559" t="n" s="2">
-        <v>45987.0</v>
+        <v>45973.0</v>
       </c>
       <c r="D559" t="n">
-        <v>20.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="560">
@@ -7968,10 +7968,10 @@
         <v>2025.0</v>
       </c>
       <c r="C560" t="n" s="2">
-        <v>45994.0</v>
+        <v>45980.0</v>
       </c>
       <c r="D560" t="n">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="561">
@@ -7982,10 +7982,10 @@
         <v>2025.0</v>
       </c>
       <c r="C561" t="n" s="2">
-        <v>46001.0</v>
+        <v>45987.0</v>
       </c>
       <c r="D561" t="n">
-        <v>8.0</v>
+        <v>20.0</v>
       </c>
     </row>
     <row r="562">
@@ -7996,10 +7996,10 @@
         <v>2025.0</v>
       </c>
       <c r="C562" t="n" s="2">
-        <v>46008.0</v>
+        <v>45994.0</v>
       </c>
       <c r="D562" t="n">
-        <v>24.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="563">
@@ -8010,10 +8010,10 @@
         <v>2025.0</v>
       </c>
       <c r="C563" t="n" s="2">
-        <v>46015.0</v>
+        <v>46001.0</v>
       </c>
       <c r="D563" t="n">
-        <v>13.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="564">
@@ -8024,10 +8024,10 @@
         <v>2025.0</v>
       </c>
       <c r="C564" t="n" s="2">
-        <v>46022.0</v>
+        <v>46008.0</v>
       </c>
       <c r="D564" t="n">
-        <v>8.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="565">
@@ -8038,10 +8038,10 @@
         <v>2025.0</v>
       </c>
       <c r="C565" t="n" s="2">
-        <v>46029.0</v>
+        <v>46015.0</v>
       </c>
       <c r="D565" t="n">
-        <v>3.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="566">
@@ -8049,13 +8049,13 @@
         <v>8</v>
       </c>
       <c r="B566" t="n">
-        <v>2026.0</v>
+        <v>2025.0</v>
       </c>
       <c r="C566" t="n" s="2">
-        <v>46030.0</v>
+        <v>46022.0</v>
       </c>
       <c r="D566" t="n">
-        <v>24.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="567">
@@ -8063,13 +8063,13 @@
         <v>8</v>
       </c>
       <c r="B567" t="n">
-        <v>2026.0</v>
+        <v>2025.0</v>
       </c>
       <c r="C567" t="n" s="2">
-        <v>46037.0</v>
+        <v>46029.0</v>
       </c>
       <c r="D567" t="n">
-        <v>22.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="568">
@@ -8080,10 +8080,10 @@
         <v>2026.0</v>
       </c>
       <c r="C568" t="n" s="2">
-        <v>46044.0</v>
+        <v>46030.0</v>
       </c>
       <c r="D568" t="n">
-        <v>27.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="569">
@@ -8094,10 +8094,10 @@
         <v>2026.0</v>
       </c>
       <c r="C569" t="n" s="2">
-        <v>46051.0</v>
+        <v>46037.0</v>
       </c>
       <c r="D569" t="n">
-        <v>18.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="570">
@@ -8108,10 +8108,10 @@
         <v>2026.0</v>
       </c>
       <c r="C570" t="n" s="2">
-        <v>46058.0</v>
+        <v>46044.0</v>
       </c>
       <c r="D570" t="n">
-        <v>25.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="571">
@@ -8122,10 +8122,10 @@
         <v>2026.0</v>
       </c>
       <c r="C571" t="n" s="2">
-        <v>46065.0</v>
+        <v>46051.0</v>
       </c>
       <c r="D571" t="n">
-        <v>22.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="572">
@@ -8136,10 +8136,10 @@
         <v>2026.0</v>
       </c>
       <c r="C572" t="n" s="2">
-        <v>46072.0</v>
+        <v>46058.0</v>
       </c>
       <c r="D572" t="n">
-        <v>13.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="573">
@@ -8150,10 +8150,10 @@
         <v>2026.0</v>
       </c>
       <c r="C573" t="n" s="2">
-        <v>46079.0</v>
+        <v>46065.0</v>
       </c>
       <c r="D573" t="n">
-        <v>24.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="574">
@@ -8164,10 +8164,10 @@
         <v>2026.0</v>
       </c>
       <c r="C574" t="n" s="2">
-        <v>46086.0</v>
+        <v>46072.0</v>
       </c>
       <c r="D574" t="n">
-        <v>26.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="575">
@@ -8178,10 +8178,10 @@
         <v>2026.0</v>
       </c>
       <c r="C575" t="n" s="2">
-        <v>46093.0</v>
+        <v>46079.0</v>
       </c>
       <c r="D575" t="n">
-        <v>33.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="576">
@@ -8192,10 +8192,10 @@
         <v>2026.0</v>
       </c>
       <c r="C576" t="n" s="2">
-        <v>46100.0</v>
+        <v>46086.0</v>
       </c>
       <c r="D576" t="n">
-        <v>25.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="577">
@@ -8206,10 +8206,10 @@
         <v>2026.0</v>
       </c>
       <c r="C577" t="n" s="2">
-        <v>46107.0</v>
+        <v>46093.0</v>
       </c>
       <c r="D577" t="n">
-        <v>31.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="578">
@@ -8220,10 +8220,10 @@
         <v>2026.0</v>
       </c>
       <c r="C578" t="n" s="2">
-        <v>46114.0</v>
+        <v>46100.0</v>
       </c>
       <c r="D578" t="n">
-        <v>10.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="579">
@@ -8234,10 +8234,10 @@
         <v>2026.0</v>
       </c>
       <c r="C579" t="n" s="2">
-        <v>46121.0</v>
+        <v>46107.0</v>
       </c>
       <c r="D579" t="n">
-        <v>9.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="580">
@@ -8248,10 +8248,10 @@
         <v>2026.0</v>
       </c>
       <c r="C580" t="n" s="2">
-        <v>46128.0</v>
+        <v>46114.0</v>
       </c>
       <c r="D580" t="n">
-        <v>15.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="581">
@@ -8262,10 +8262,10 @@
         <v>2026.0</v>
       </c>
       <c r="C581" t="n" s="2">
-        <v>46135.0</v>
+        <v>46121.0</v>
       </c>
       <c r="D581" t="n">
-        <v>23.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="582">
@@ -8276,10 +8276,10 @@
         <v>2026.0</v>
       </c>
       <c r="C582" t="n" s="2">
-        <v>46142.0</v>
+        <v>46128.0</v>
       </c>
       <c r="D582" t="n">
-        <v>21.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="583">
@@ -8290,10 +8290,10 @@
         <v>2026.0</v>
       </c>
       <c r="C583" t="n" s="2">
-        <v>46149.0</v>
+        <v>46135.0</v>
       </c>
       <c r="D583" t="n">
-        <v>6.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="584">
@@ -8304,10 +8304,10 @@
         <v>2026.0</v>
       </c>
       <c r="C584" t="n" s="2">
-        <v>46156.0</v>
+        <v>46142.0</v>
       </c>
       <c r="D584" t="n">
-        <v>27.0</v>
+        <v>21.0</v>
       </c>
     </row>
     <row r="585">
@@ -8318,9 +8318,37 @@
         <v>2026.0</v>
       </c>
       <c r="C585" t="n" s="2">
+        <v>46149.0</v>
+      </c>
+      <c r="D585" t="n">
+        <v>6.0</v>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="s">
+        <v>8</v>
+      </c>
+      <c r="B586" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C586" t="n" s="2">
+        <v>46156.0</v>
+      </c>
+      <c r="D586" t="n">
+        <v>27.0</v>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="s">
+        <v>8</v>
+      </c>
+      <c r="B587" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C587" t="n" s="2">
         <v>46163.0</v>
       </c>
-      <c r="D585" t="n">
+      <c r="D587" t="n">
         <v>12.0</v>
       </c>
     </row>
@@ -8363,7 +8391,7 @@
         <v>12</v>
       </c>
       <c r="B4" t="n">
-        <v>1281.0</v>
+        <v>1295.0</v>
       </c>
     </row>
     <row r="5">
@@ -8371,7 +8399,7 @@
         <v>13</v>
       </c>
       <c r="B5" t="n">
-        <v>2140.0</v>
+        <v>2146.0</v>
       </c>
     </row>
   </sheetData>
@@ -8403,7 +8431,7 @@
         <v>21</v>
       </c>
       <c r="C2" t="n">
-        <v>206.0</v>
+        <v>208.0</v>
       </c>
     </row>
     <row r="3">
@@ -8414,7 +8442,7 @@
         <v>22</v>
       </c>
       <c r="C3" t="n">
-        <v>184.0</v>
+        <v>186.0</v>
       </c>
     </row>
     <row r="4">
@@ -8436,7 +8464,7 @@
         <v>21</v>
       </c>
       <c r="C5" t="n">
-        <v>427.0</v>
+        <v>433.0</v>
       </c>
     </row>
     <row r="6">
@@ -8513,7 +8541,7 @@
         <v>21</v>
       </c>
       <c r="C12" t="n">
-        <v>76.0</v>
+        <v>77.0</v>
       </c>
     </row>
     <row r="13">
@@ -8535,7 +8563,7 @@
         <v>19</v>
       </c>
       <c r="C14" t="n">
-        <v>416.0</v>
+        <v>417.0</v>
       </c>
     </row>
     <row r="15">
@@ -8557,7 +8585,7 @@
         <v>22</v>
       </c>
       <c r="C16" t="n">
-        <v>359.0</v>
+        <v>366.0</v>
       </c>
     </row>
     <row r="17">
@@ -8568,7 +8596,7 @@
         <v>19</v>
       </c>
       <c r="C17" t="n">
-        <v>113.0</v>
+        <v>114.0</v>
       </c>
     </row>
   </sheetData>

--- a/Download/Focus_Positivi_ZR.xlsx
+++ b/Download/Focus_Positivi_ZR.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="631" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="634" uniqueCount="23">
   <si>
     <t>NOME_REGIONE</t>
   </si>
@@ -1634,16 +1634,16 @@
     </row>
     <row r="108">
       <c r="A108" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B108" t="n">
-        <v>2021.0</v>
+        <v>2026.0</v>
       </c>
       <c r="C108" t="n" s="2">
-        <v>44561.0</v>
+        <v>46170.0</v>
       </c>
       <c r="D108" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="109">
@@ -1651,13 +1651,13 @@
         <v>5</v>
       </c>
       <c r="B109" t="n">
-        <v>2022.0</v>
+        <v>2021.0</v>
       </c>
       <c r="C109" t="n" s="2">
-        <v>44576.0</v>
+        <v>44561.0</v>
       </c>
       <c r="D109" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="110">
@@ -1668,10 +1668,10 @@
         <v>2022.0</v>
       </c>
       <c r="C110" t="n" s="2">
-        <v>44583.0</v>
+        <v>44576.0</v>
       </c>
       <c r="D110" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="111">
@@ -1682,10 +1682,10 @@
         <v>2022.0</v>
       </c>
       <c r="C111" t="n" s="2">
-        <v>44590.0</v>
+        <v>44583.0</v>
       </c>
       <c r="D111" t="n">
-        <v>7.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="112">
@@ -1696,10 +1696,10 @@
         <v>2022.0</v>
       </c>
       <c r="C112" t="n" s="2">
-        <v>44597.0</v>
+        <v>44590.0</v>
       </c>
       <c r="D112" t="n">
-        <v>3.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="113">
@@ -1710,10 +1710,10 @@
         <v>2022.0</v>
       </c>
       <c r="C113" t="n" s="2">
-        <v>44604.0</v>
+        <v>44597.0</v>
       </c>
       <c r="D113" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="114">
@@ -1724,10 +1724,10 @@
         <v>2022.0</v>
       </c>
       <c r="C114" t="n" s="2">
-        <v>44611.0</v>
+        <v>44604.0</v>
       </c>
       <c r="D114" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="115">
@@ -1738,7 +1738,7 @@
         <v>2022.0</v>
       </c>
       <c r="C115" t="n" s="2">
-        <v>44618.0</v>
+        <v>44611.0</v>
       </c>
       <c r="D115" t="n">
         <v>1.0</v>
@@ -1752,10 +1752,10 @@
         <v>2022.0</v>
       </c>
       <c r="C116" t="n" s="2">
-        <v>44625.0</v>
+        <v>44618.0</v>
       </c>
       <c r="D116" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="117">
@@ -1766,10 +1766,10 @@
         <v>2022.0</v>
       </c>
       <c r="C117" t="n" s="2">
-        <v>44632.0</v>
+        <v>44625.0</v>
       </c>
       <c r="D117" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="118">
@@ -1780,10 +1780,10 @@
         <v>2022.0</v>
       </c>
       <c r="C118" t="n" s="2">
-        <v>44639.0</v>
+        <v>44632.0</v>
       </c>
       <c r="D118" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="119">
@@ -1794,7 +1794,7 @@
         <v>2022.0</v>
       </c>
       <c r="C119" t="n" s="2">
-        <v>44646.0</v>
+        <v>44639.0</v>
       </c>
       <c r="D119" t="n">
         <v>2.0</v>
@@ -1808,7 +1808,7 @@
         <v>2022.0</v>
       </c>
       <c r="C120" t="n" s="2">
-        <v>44653.0</v>
+        <v>44646.0</v>
       </c>
       <c r="D120" t="n">
         <v>2.0</v>
@@ -1822,10 +1822,10 @@
         <v>2022.0</v>
       </c>
       <c r="C121" t="n" s="2">
-        <v>44660.0</v>
+        <v>44653.0</v>
       </c>
       <c r="D121" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="122">
@@ -1836,10 +1836,10 @@
         <v>2022.0</v>
       </c>
       <c r="C122" t="n" s="2">
-        <v>44667.0</v>
+        <v>44660.0</v>
       </c>
       <c r="D122" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="123">
@@ -1850,7 +1850,7 @@
         <v>2022.0</v>
       </c>
       <c r="C123" t="n" s="2">
-        <v>44674.0</v>
+        <v>44667.0</v>
       </c>
       <c r="D123" t="n">
         <v>3.0</v>
@@ -1864,10 +1864,10 @@
         <v>2022.0</v>
       </c>
       <c r="C124" t="n" s="2">
-        <v>44681.0</v>
+        <v>44674.0</v>
       </c>
       <c r="D124" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="125">
@@ -1878,10 +1878,10 @@
         <v>2022.0</v>
       </c>
       <c r="C125" t="n" s="2">
-        <v>44688.0</v>
+        <v>44681.0</v>
       </c>
       <c r="D125" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="126">
@@ -1892,7 +1892,7 @@
         <v>2022.0</v>
       </c>
       <c r="C126" t="n" s="2">
-        <v>44695.0</v>
+        <v>44688.0</v>
       </c>
       <c r="D126" t="n">
         <v>3.0</v>
@@ -1906,10 +1906,10 @@
         <v>2022.0</v>
       </c>
       <c r="C127" t="n" s="2">
-        <v>44702.0</v>
+        <v>44695.0</v>
       </c>
       <c r="D127" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="128">
@@ -1920,10 +1920,10 @@
         <v>2022.0</v>
       </c>
       <c r="C128" t="n" s="2">
-        <v>44709.0</v>
+        <v>44702.0</v>
       </c>
       <c r="D128" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="129">
@@ -1934,10 +1934,10 @@
         <v>2022.0</v>
       </c>
       <c r="C129" t="n" s="2">
-        <v>44716.0</v>
+        <v>44709.0</v>
       </c>
       <c r="D129" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="130">
@@ -1948,7 +1948,7 @@
         <v>2022.0</v>
       </c>
       <c r="C130" t="n" s="2">
-        <v>44723.0</v>
+        <v>44716.0</v>
       </c>
       <c r="D130" t="n">
         <v>1.0</v>
@@ -1962,7 +1962,7 @@
         <v>2022.0</v>
       </c>
       <c r="C131" t="n" s="2">
-        <v>44730.0</v>
+        <v>44723.0</v>
       </c>
       <c r="D131" t="n">
         <v>1.0</v>
@@ -1976,7 +1976,7 @@
         <v>2022.0</v>
       </c>
       <c r="C132" t="n" s="2">
-        <v>44737.0</v>
+        <v>44730.0</v>
       </c>
       <c r="D132" t="n">
         <v>1.0</v>
@@ -1990,7 +1990,7 @@
         <v>2022.0</v>
       </c>
       <c r="C133" t="n" s="2">
-        <v>44744.0</v>
+        <v>44737.0</v>
       </c>
       <c r="D133" t="n">
         <v>1.0</v>
@@ -2004,7 +2004,7 @@
         <v>2022.0</v>
       </c>
       <c r="C134" t="n" s="2">
-        <v>44751.0</v>
+        <v>44744.0</v>
       </c>
       <c r="D134" t="n">
         <v>1.0</v>
@@ -2018,7 +2018,7 @@
         <v>2022.0</v>
       </c>
       <c r="C135" t="n" s="2">
-        <v>44758.0</v>
+        <v>44751.0</v>
       </c>
       <c r="D135" t="n">
         <v>1.0</v>
@@ -2032,7 +2032,7 @@
         <v>2022.0</v>
       </c>
       <c r="C136" t="n" s="2">
-        <v>44772.0</v>
+        <v>44758.0</v>
       </c>
       <c r="D136" t="n">
         <v>1.0</v>
@@ -2046,7 +2046,7 @@
         <v>2022.0</v>
       </c>
       <c r="C137" t="n" s="2">
-        <v>44793.0</v>
+        <v>44772.0</v>
       </c>
       <c r="D137" t="n">
         <v>1.0</v>
@@ -2060,7 +2060,7 @@
         <v>2022.0</v>
       </c>
       <c r="C138" t="n" s="2">
-        <v>44800.0</v>
+        <v>44793.0</v>
       </c>
       <c r="D138" t="n">
         <v>1.0</v>
@@ -2074,7 +2074,7 @@
         <v>2022.0</v>
       </c>
       <c r="C139" t="n" s="2">
-        <v>44828.0</v>
+        <v>44800.0</v>
       </c>
       <c r="D139" t="n">
         <v>1.0</v>
@@ -2088,7 +2088,7 @@
         <v>2022.0</v>
       </c>
       <c r="C140" t="n" s="2">
-        <v>44849.0</v>
+        <v>44828.0</v>
       </c>
       <c r="D140" t="n">
         <v>1.0</v>
@@ -2102,7 +2102,7 @@
         <v>2022.0</v>
       </c>
       <c r="C141" t="n" s="2">
-        <v>44856.0</v>
+        <v>44849.0</v>
       </c>
       <c r="D141" t="n">
         <v>1.0</v>
@@ -2116,7 +2116,7 @@
         <v>2022.0</v>
       </c>
       <c r="C142" t="n" s="2">
-        <v>44863.0</v>
+        <v>44856.0</v>
       </c>
       <c r="D142" t="n">
         <v>1.0</v>
@@ -2130,10 +2130,10 @@
         <v>2022.0</v>
       </c>
       <c r="C143" t="n" s="2">
-        <v>44884.0</v>
+        <v>44863.0</v>
       </c>
       <c r="D143" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="144">
@@ -2144,10 +2144,10 @@
         <v>2022.0</v>
       </c>
       <c r="C144" t="n" s="2">
-        <v>44891.0</v>
+        <v>44884.0</v>
       </c>
       <c r="D144" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="145">
@@ -2158,7 +2158,7 @@
         <v>2022.0</v>
       </c>
       <c r="C145" t="n" s="2">
-        <v>44905.0</v>
+        <v>44891.0</v>
       </c>
       <c r="D145" t="n">
         <v>1.0</v>
@@ -2172,7 +2172,7 @@
         <v>2022.0</v>
       </c>
       <c r="C146" t="n" s="2">
-        <v>44912.0</v>
+        <v>44905.0</v>
       </c>
       <c r="D146" t="n">
         <v>1.0</v>
@@ -2186,10 +2186,10 @@
         <v>2022.0</v>
       </c>
       <c r="C147" t="n" s="2">
-        <v>44919.0</v>
+        <v>44912.0</v>
       </c>
       <c r="D147" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="148">
@@ -2197,13 +2197,13 @@
         <v>5</v>
       </c>
       <c r="B148" t="n">
-        <v>2023.0</v>
+        <v>2022.0</v>
       </c>
       <c r="C148" t="n" s="2">
-        <v>44934.0</v>
+        <v>44919.0</v>
       </c>
       <c r="D148" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="149">
@@ -2214,10 +2214,10 @@
         <v>2023.0</v>
       </c>
       <c r="C149" t="n" s="2">
-        <v>44941.0</v>
+        <v>44934.0</v>
       </c>
       <c r="D149" t="n">
-        <v>8.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="150">
@@ -2228,10 +2228,10 @@
         <v>2023.0</v>
       </c>
       <c r="C150" t="n" s="2">
-        <v>44948.0</v>
+        <v>44941.0</v>
       </c>
       <c r="D150" t="n">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="151">
@@ -2242,10 +2242,10 @@
         <v>2023.0</v>
       </c>
       <c r="C151" t="n" s="2">
-        <v>44955.0</v>
+        <v>44948.0</v>
       </c>
       <c r="D151" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="152">
@@ -2256,10 +2256,10 @@
         <v>2023.0</v>
       </c>
       <c r="C152" t="n" s="2">
-        <v>44962.0</v>
+        <v>44955.0</v>
       </c>
       <c r="D152" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="153">
@@ -2270,7 +2270,7 @@
         <v>2023.0</v>
       </c>
       <c r="C153" t="n" s="2">
-        <v>44969.0</v>
+        <v>44962.0</v>
       </c>
       <c r="D153" t="n">
         <v>4.0</v>
@@ -2284,10 +2284,10 @@
         <v>2023.0</v>
       </c>
       <c r="C154" t="n" s="2">
-        <v>44976.0</v>
+        <v>44969.0</v>
       </c>
       <c r="D154" t="n">
-        <v>17.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="155">
@@ -2298,10 +2298,10 @@
         <v>2023.0</v>
       </c>
       <c r="C155" t="n" s="2">
-        <v>44983.0</v>
+        <v>44976.0</v>
       </c>
       <c r="D155" t="n">
-        <v>11.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="156">
@@ -2312,10 +2312,10 @@
         <v>2023.0</v>
       </c>
       <c r="C156" t="n" s="2">
-        <v>44990.0</v>
+        <v>44983.0</v>
       </c>
       <c r="D156" t="n">
-        <v>5.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="157">
@@ -2326,10 +2326,10 @@
         <v>2023.0</v>
       </c>
       <c r="C157" t="n" s="2">
-        <v>44997.0</v>
+        <v>44990.0</v>
       </c>
       <c r="D157" t="n">
-        <v>22.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="158">
@@ -2340,10 +2340,10 @@
         <v>2023.0</v>
       </c>
       <c r="C158" t="n" s="2">
-        <v>45004.0</v>
+        <v>44997.0</v>
       </c>
       <c r="D158" t="n">
-        <v>8.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="159">
@@ -2354,10 +2354,10 @@
         <v>2023.0</v>
       </c>
       <c r="C159" t="n" s="2">
-        <v>45011.0</v>
+        <v>45004.0</v>
       </c>
       <c r="D159" t="n">
-        <v>17.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="160">
@@ -2368,10 +2368,10 @@
         <v>2023.0</v>
       </c>
       <c r="C160" t="n" s="2">
-        <v>45018.0</v>
+        <v>45011.0</v>
       </c>
       <c r="D160" t="n">
-        <v>10.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="161">
@@ -2382,10 +2382,10 @@
         <v>2023.0</v>
       </c>
       <c r="C161" t="n" s="2">
-        <v>45025.0</v>
+        <v>45018.0</v>
       </c>
       <c r="D161" t="n">
-        <v>13.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="162">
@@ -2396,10 +2396,10 @@
         <v>2023.0</v>
       </c>
       <c r="C162" t="n" s="2">
-        <v>45032.0</v>
+        <v>45025.0</v>
       </c>
       <c r="D162" t="n">
-        <v>10.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="163">
@@ -2410,10 +2410,10 @@
         <v>2023.0</v>
       </c>
       <c r="C163" t="n" s="2">
-        <v>45039.0</v>
+        <v>45032.0</v>
       </c>
       <c r="D163" t="n">
-        <v>22.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="164">
@@ -2424,10 +2424,10 @@
         <v>2023.0</v>
       </c>
       <c r="C164" t="n" s="2">
-        <v>45046.0</v>
+        <v>45039.0</v>
       </c>
       <c r="D164" t="n">
-        <v>23.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="165">
@@ -2438,10 +2438,10 @@
         <v>2023.0</v>
       </c>
       <c r="C165" t="n" s="2">
-        <v>45053.0</v>
+        <v>45046.0</v>
       </c>
       <c r="D165" t="n">
-        <v>16.0</v>
+        <v>23.0</v>
       </c>
     </row>
     <row r="166">
@@ -2452,10 +2452,10 @@
         <v>2023.0</v>
       </c>
       <c r="C166" t="n" s="2">
-        <v>45060.0</v>
+        <v>45053.0</v>
       </c>
       <c r="D166" t="n">
-        <v>13.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="167">
@@ -2466,10 +2466,10 @@
         <v>2023.0</v>
       </c>
       <c r="C167" t="n" s="2">
-        <v>45067.0</v>
+        <v>45060.0</v>
       </c>
       <c r="D167" t="n">
-        <v>9.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="168">
@@ -2480,10 +2480,10 @@
         <v>2023.0</v>
       </c>
       <c r="C168" t="n" s="2">
-        <v>45074.0</v>
+        <v>45067.0</v>
       </c>
       <c r="D168" t="n">
-        <v>6.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="169">
@@ -2494,10 +2494,10 @@
         <v>2023.0</v>
       </c>
       <c r="C169" t="n" s="2">
-        <v>45081.0</v>
+        <v>45074.0</v>
       </c>
       <c r="D169" t="n">
-        <v>16.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="170">
@@ -2508,10 +2508,10 @@
         <v>2023.0</v>
       </c>
       <c r="C170" t="n" s="2">
-        <v>45088.0</v>
+        <v>45081.0</v>
       </c>
       <c r="D170" t="n">
-        <v>8.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="171">
@@ -2522,10 +2522,10 @@
         <v>2023.0</v>
       </c>
       <c r="C171" t="n" s="2">
-        <v>45095.0</v>
+        <v>45088.0</v>
       </c>
       <c r="D171" t="n">
-        <v>16.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="172">
@@ -2536,10 +2536,10 @@
         <v>2023.0</v>
       </c>
       <c r="C172" t="n" s="2">
-        <v>45102.0</v>
+        <v>45095.0</v>
       </c>
       <c r="D172" t="n">
-        <v>17.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="173">
@@ -2550,10 +2550,10 @@
         <v>2023.0</v>
       </c>
       <c r="C173" t="n" s="2">
-        <v>45109.0</v>
+        <v>45102.0</v>
       </c>
       <c r="D173" t="n">
-        <v>14.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="174">
@@ -2564,10 +2564,10 @@
         <v>2023.0</v>
       </c>
       <c r="C174" t="n" s="2">
-        <v>45116.0</v>
+        <v>45109.0</v>
       </c>
       <c r="D174" t="n">
-        <v>13.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="175">
@@ -2578,10 +2578,10 @@
         <v>2023.0</v>
       </c>
       <c r="C175" t="n" s="2">
-        <v>45123.0</v>
+        <v>45116.0</v>
       </c>
       <c r="D175" t="n">
-        <v>5.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="176">
@@ -2592,10 +2592,10 @@
         <v>2023.0</v>
       </c>
       <c r="C176" t="n" s="2">
-        <v>45130.0</v>
+        <v>45123.0</v>
       </c>
       <c r="D176" t="n">
-        <v>8.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="177">
@@ -2606,10 +2606,10 @@
         <v>2023.0</v>
       </c>
       <c r="C177" t="n" s="2">
-        <v>45137.0</v>
+        <v>45130.0</v>
       </c>
       <c r="D177" t="n">
-        <v>4.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="178">
@@ -2620,10 +2620,10 @@
         <v>2023.0</v>
       </c>
       <c r="C178" t="n" s="2">
-        <v>45144.0</v>
+        <v>45137.0</v>
       </c>
       <c r="D178" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="179">
@@ -2634,7 +2634,7 @@
         <v>2023.0</v>
       </c>
       <c r="C179" t="n" s="2">
-        <v>45151.0</v>
+        <v>45144.0</v>
       </c>
       <c r="D179" t="n">
         <v>2.0</v>
@@ -2648,10 +2648,10 @@
         <v>2023.0</v>
       </c>
       <c r="C180" t="n" s="2">
-        <v>45158.0</v>
+        <v>45151.0</v>
       </c>
       <c r="D180" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="181">
@@ -2662,7 +2662,7 @@
         <v>2023.0</v>
       </c>
       <c r="C181" t="n" s="2">
-        <v>45165.0</v>
+        <v>45158.0</v>
       </c>
       <c r="D181" t="n">
         <v>5.0</v>
@@ -2676,10 +2676,10 @@
         <v>2023.0</v>
       </c>
       <c r="C182" t="n" s="2">
-        <v>45172.0</v>
+        <v>45165.0</v>
       </c>
       <c r="D182" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="183">
@@ -2690,10 +2690,10 @@
         <v>2023.0</v>
       </c>
       <c r="C183" t="n" s="2">
-        <v>45179.0</v>
+        <v>45172.0</v>
       </c>
       <c r="D183" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="184">
@@ -2704,10 +2704,10 @@
         <v>2023.0</v>
       </c>
       <c r="C184" t="n" s="2">
-        <v>45186.0</v>
+        <v>45179.0</v>
       </c>
       <c r="D184" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="185">
@@ -2718,7 +2718,7 @@
         <v>2023.0</v>
       </c>
       <c r="C185" t="n" s="2">
-        <v>45193.0</v>
+        <v>45186.0</v>
       </c>
       <c r="D185" t="n">
         <v>1.0</v>
@@ -2732,10 +2732,10 @@
         <v>2023.0</v>
       </c>
       <c r="C186" t="n" s="2">
-        <v>45200.0</v>
+        <v>45193.0</v>
       </c>
       <c r="D186" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="187">
@@ -2746,10 +2746,10 @@
         <v>2023.0</v>
       </c>
       <c r="C187" t="n" s="2">
-        <v>45207.0</v>
+        <v>45200.0</v>
       </c>
       <c r="D187" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="188">
@@ -2760,10 +2760,10 @@
         <v>2023.0</v>
       </c>
       <c r="C188" t="n" s="2">
-        <v>45214.0</v>
+        <v>45207.0</v>
       </c>
       <c r="D188" t="n">
-        <v>8.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="189">
@@ -2774,7 +2774,7 @@
         <v>2023.0</v>
       </c>
       <c r="C189" t="n" s="2">
-        <v>45221.0</v>
+        <v>45214.0</v>
       </c>
       <c r="D189" t="n">
         <v>8.0</v>
@@ -2788,10 +2788,10 @@
         <v>2023.0</v>
       </c>
       <c r="C190" t="n" s="2">
-        <v>45228.0</v>
+        <v>45221.0</v>
       </c>
       <c r="D190" t="n">
-        <v>17.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="191">
@@ -2802,10 +2802,10 @@
         <v>2023.0</v>
       </c>
       <c r="C191" t="n" s="2">
-        <v>45235.0</v>
+        <v>45228.0</v>
       </c>
       <c r="D191" t="n">
-        <v>9.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="192">
@@ -2816,7 +2816,7 @@
         <v>2023.0</v>
       </c>
       <c r="C192" t="n" s="2">
-        <v>45242.0</v>
+        <v>45235.0</v>
       </c>
       <c r="D192" t="n">
         <v>9.0</v>
@@ -2830,10 +2830,10 @@
         <v>2023.0</v>
       </c>
       <c r="C193" t="n" s="2">
-        <v>45249.0</v>
+        <v>45242.0</v>
       </c>
       <c r="D193" t="n">
-        <v>14.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="194">
@@ -2844,10 +2844,10 @@
         <v>2023.0</v>
       </c>
       <c r="C194" t="n" s="2">
-        <v>45256.0</v>
+        <v>45249.0</v>
       </c>
       <c r="D194" t="n">
-        <v>17.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="195">
@@ -2858,10 +2858,10 @@
         <v>2023.0</v>
       </c>
       <c r="C195" t="n" s="2">
-        <v>45263.0</v>
+        <v>45256.0</v>
       </c>
       <c r="D195" t="n">
-        <v>14.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="196">
@@ -2872,10 +2872,10 @@
         <v>2023.0</v>
       </c>
       <c r="C196" t="n" s="2">
-        <v>45270.0</v>
+        <v>45263.0</v>
       </c>
       <c r="D196" t="n">
-        <v>26.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="197">
@@ -2886,10 +2886,10 @@
         <v>2023.0</v>
       </c>
       <c r="C197" t="n" s="2">
-        <v>45277.0</v>
+        <v>45270.0</v>
       </c>
       <c r="D197" t="n">
-        <v>19.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="198">
@@ -2900,10 +2900,10 @@
         <v>2023.0</v>
       </c>
       <c r="C198" t="n" s="2">
-        <v>45284.0</v>
+        <v>45277.0</v>
       </c>
       <c r="D198" t="n">
-        <v>21.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="199">
@@ -2914,10 +2914,10 @@
         <v>2023.0</v>
       </c>
       <c r="C199" t="n" s="2">
-        <v>45291.0</v>
+        <v>45284.0</v>
       </c>
       <c r="D199" t="n">
-        <v>9.0</v>
+        <v>21.0</v>
       </c>
     </row>
     <row r="200">
@@ -2925,13 +2925,13 @@
         <v>5</v>
       </c>
       <c r="B200" t="n">
-        <v>2024.0</v>
+        <v>2023.0</v>
       </c>
       <c r="C200" t="n" s="2">
-        <v>45299.0</v>
+        <v>45291.0</v>
       </c>
       <c r="D200" t="n">
-        <v>26.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="201">
@@ -2942,10 +2942,10 @@
         <v>2024.0</v>
       </c>
       <c r="C201" t="n" s="2">
-        <v>45306.0</v>
+        <v>45299.0</v>
       </c>
       <c r="D201" t="n">
-        <v>14.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="202">
@@ -2956,10 +2956,10 @@
         <v>2024.0</v>
       </c>
       <c r="C202" t="n" s="2">
-        <v>45313.0</v>
+        <v>45306.0</v>
       </c>
       <c r="D202" t="n">
-        <v>15.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="203">
@@ -2970,10 +2970,10 @@
         <v>2024.0</v>
       </c>
       <c r="C203" t="n" s="2">
-        <v>45320.0</v>
+        <v>45313.0</v>
       </c>
       <c r="D203" t="n">
-        <v>18.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="204">
@@ -2984,10 +2984,10 @@
         <v>2024.0</v>
       </c>
       <c r="C204" t="n" s="2">
-        <v>45327.0</v>
+        <v>45320.0</v>
       </c>
       <c r="D204" t="n">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="205">
@@ -2998,10 +2998,10 @@
         <v>2024.0</v>
       </c>
       <c r="C205" t="n" s="2">
-        <v>45334.0</v>
+        <v>45327.0</v>
       </c>
       <c r="D205" t="n">
-        <v>13.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="206">
@@ -3012,10 +3012,10 @@
         <v>2024.0</v>
       </c>
       <c r="C206" t="n" s="2">
-        <v>45341.0</v>
+        <v>45334.0</v>
       </c>
       <c r="D206" t="n">
-        <v>11.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="207">
@@ -3026,10 +3026,10 @@
         <v>2024.0</v>
       </c>
       <c r="C207" t="n" s="2">
-        <v>45348.0</v>
+        <v>45341.0</v>
       </c>
       <c r="D207" t="n">
-        <v>8.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="208">
@@ -3040,10 +3040,10 @@
         <v>2024.0</v>
       </c>
       <c r="C208" t="n" s="2">
-        <v>45355.0</v>
+        <v>45348.0</v>
       </c>
       <c r="D208" t="n">
-        <v>1.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="209">
@@ -3054,10 +3054,10 @@
         <v>2024.0</v>
       </c>
       <c r="C209" t="n" s="2">
-        <v>45362.0</v>
+        <v>45355.0</v>
       </c>
       <c r="D209" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="210">
@@ -3068,10 +3068,10 @@
         <v>2024.0</v>
       </c>
       <c r="C210" t="n" s="2">
-        <v>45369.0</v>
+        <v>45362.0</v>
       </c>
       <c r="D210" t="n">
-        <v>8.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="211">
@@ -3082,10 +3082,10 @@
         <v>2024.0</v>
       </c>
       <c r="C211" t="n" s="2">
-        <v>45376.0</v>
+        <v>45369.0</v>
       </c>
       <c r="D211" t="n">
-        <v>9.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="212">
@@ -3096,10 +3096,10 @@
         <v>2024.0</v>
       </c>
       <c r="C212" t="n" s="2">
-        <v>45383.0</v>
+        <v>45376.0</v>
       </c>
       <c r="D212" t="n">
-        <v>5.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="213">
@@ -3110,10 +3110,10 @@
         <v>2024.0</v>
       </c>
       <c r="C213" t="n" s="2">
-        <v>45390.0</v>
+        <v>45383.0</v>
       </c>
       <c r="D213" t="n">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="214">
@@ -3124,10 +3124,10 @@
         <v>2024.0</v>
       </c>
       <c r="C214" t="n" s="2">
-        <v>45397.0</v>
+        <v>45390.0</v>
       </c>
       <c r="D214" t="n">
-        <v>13.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="215">
@@ -3138,10 +3138,10 @@
         <v>2024.0</v>
       </c>
       <c r="C215" t="n" s="2">
-        <v>45404.0</v>
+        <v>45397.0</v>
       </c>
       <c r="D215" t="n">
-        <v>24.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="216">
@@ -3152,10 +3152,10 @@
         <v>2024.0</v>
       </c>
       <c r="C216" t="n" s="2">
-        <v>45411.0</v>
+        <v>45404.0</v>
       </c>
       <c r="D216" t="n">
-        <v>17.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="217">
@@ -3166,10 +3166,10 @@
         <v>2024.0</v>
       </c>
       <c r="C217" t="n" s="2">
-        <v>45418.0</v>
+        <v>45411.0</v>
       </c>
       <c r="D217" t="n">
-        <v>3.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="218">
@@ -3180,10 +3180,10 @@
         <v>2024.0</v>
       </c>
       <c r="C218" t="n" s="2">
-        <v>45425.0</v>
+        <v>45418.0</v>
       </c>
       <c r="D218" t="n">
-        <v>16.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="219">
@@ -3194,10 +3194,10 @@
         <v>2024.0</v>
       </c>
       <c r="C219" t="n" s="2">
-        <v>45432.0</v>
+        <v>45425.0</v>
       </c>
       <c r="D219" t="n">
-        <v>19.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="220">
@@ -3208,10 +3208,10 @@
         <v>2024.0</v>
       </c>
       <c r="C220" t="n" s="2">
-        <v>45439.0</v>
+        <v>45432.0</v>
       </c>
       <c r="D220" t="n">
-        <v>30.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="221">
@@ -3222,10 +3222,10 @@
         <v>2024.0</v>
       </c>
       <c r="C221" t="n" s="2">
-        <v>45446.0</v>
+        <v>45439.0</v>
       </c>
       <c r="D221" t="n">
-        <v>28.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="222">
@@ -3236,10 +3236,10 @@
         <v>2024.0</v>
       </c>
       <c r="C222" t="n" s="2">
-        <v>45453.0</v>
+        <v>45446.0</v>
       </c>
       <c r="D222" t="n">
-        <v>19.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="223">
@@ -3250,10 +3250,10 @@
         <v>2024.0</v>
       </c>
       <c r="C223" t="n" s="2">
-        <v>45460.0</v>
+        <v>45453.0</v>
       </c>
       <c r="D223" t="n">
-        <v>26.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="224">
@@ -3264,10 +3264,10 @@
         <v>2024.0</v>
       </c>
       <c r="C224" t="n" s="2">
-        <v>45467.0</v>
+        <v>45460.0</v>
       </c>
       <c r="D224" t="n">
-        <v>8.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="225">
@@ -3278,10 +3278,10 @@
         <v>2024.0</v>
       </c>
       <c r="C225" t="n" s="2">
-        <v>45474.0</v>
+        <v>45467.0</v>
       </c>
       <c r="D225" t="n">
-        <v>12.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="226">
@@ -3292,7 +3292,7 @@
         <v>2024.0</v>
       </c>
       <c r="C226" t="n" s="2">
-        <v>45481.0</v>
+        <v>45474.0</v>
       </c>
       <c r="D226" t="n">
         <v>12.0</v>
@@ -3306,10 +3306,10 @@
         <v>2024.0</v>
       </c>
       <c r="C227" t="n" s="2">
-        <v>45488.0</v>
+        <v>45481.0</v>
       </c>
       <c r="D227" t="n">
-        <v>4.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="228">
@@ -3320,10 +3320,10 @@
         <v>2024.0</v>
       </c>
       <c r="C228" t="n" s="2">
-        <v>45495.0</v>
+        <v>45488.0</v>
       </c>
       <c r="D228" t="n">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="229">
@@ -3334,10 +3334,10 @@
         <v>2024.0</v>
       </c>
       <c r="C229" t="n" s="2">
-        <v>45502.0</v>
+        <v>45495.0</v>
       </c>
       <c r="D229" t="n">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="230">
@@ -3348,10 +3348,10 @@
         <v>2024.0</v>
       </c>
       <c r="C230" t="n" s="2">
-        <v>45509.0</v>
+        <v>45502.0</v>
       </c>
       <c r="D230" t="n">
-        <v>2.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="231">
@@ -3362,10 +3362,10 @@
         <v>2024.0</v>
       </c>
       <c r="C231" t="n" s="2">
-        <v>45516.0</v>
+        <v>45509.0</v>
       </c>
       <c r="D231" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="232">
@@ -3376,7 +3376,7 @@
         <v>2024.0</v>
       </c>
       <c r="C232" t="n" s="2">
-        <v>45523.0</v>
+        <v>45516.0</v>
       </c>
       <c r="D232" t="n">
         <v>4.0</v>
@@ -3390,7 +3390,7 @@
         <v>2024.0</v>
       </c>
       <c r="C233" t="n" s="2">
-        <v>45530.0</v>
+        <v>45523.0</v>
       </c>
       <c r="D233" t="n">
         <v>4.0</v>
@@ -3404,7 +3404,7 @@
         <v>2024.0</v>
       </c>
       <c r="C234" t="n" s="2">
-        <v>45537.0</v>
+        <v>45530.0</v>
       </c>
       <c r="D234" t="n">
         <v>4.0</v>
@@ -3418,10 +3418,10 @@
         <v>2024.0</v>
       </c>
       <c r="C235" t="n" s="2">
-        <v>45544.0</v>
+        <v>45537.0</v>
       </c>
       <c r="D235" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="236">
@@ -3432,10 +3432,10 @@
         <v>2024.0</v>
       </c>
       <c r="C236" t="n" s="2">
-        <v>45551.0</v>
+        <v>45544.0</v>
       </c>
       <c r="D236" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="237">
@@ -3446,10 +3446,10 @@
         <v>2024.0</v>
       </c>
       <c r="C237" t="n" s="2">
-        <v>45558.0</v>
+        <v>45551.0</v>
       </c>
       <c r="D237" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="238">
@@ -3460,10 +3460,10 @@
         <v>2024.0</v>
       </c>
       <c r="C238" t="n" s="2">
-        <v>45600.0</v>
+        <v>45558.0</v>
       </c>
       <c r="D238" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="239">
@@ -3474,10 +3474,10 @@
         <v>2024.0</v>
       </c>
       <c r="C239" t="n" s="2">
-        <v>45607.0</v>
+        <v>45600.0</v>
       </c>
       <c r="D239" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="240">
@@ -3488,10 +3488,10 @@
         <v>2024.0</v>
       </c>
       <c r="C240" t="n" s="2">
-        <v>45628.0</v>
+        <v>45607.0</v>
       </c>
       <c r="D240" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="241">
@@ -3502,10 +3502,10 @@
         <v>2024.0</v>
       </c>
       <c r="C241" t="n" s="2">
-        <v>45635.0</v>
+        <v>45628.0</v>
       </c>
       <c r="D241" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="242">
@@ -3516,7 +3516,7 @@
         <v>2024.0</v>
       </c>
       <c r="C242" t="n" s="2">
-        <v>45642.0</v>
+        <v>45635.0</v>
       </c>
       <c r="D242" t="n">
         <v>3.0</v>
@@ -3530,10 +3530,10 @@
         <v>2024.0</v>
       </c>
       <c r="C243" t="n" s="2">
-        <v>45649.0</v>
+        <v>45642.0</v>
       </c>
       <c r="D243" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="244">
@@ -3544,7 +3544,7 @@
         <v>2024.0</v>
       </c>
       <c r="C244" t="n" s="2">
-        <v>45656.0</v>
+        <v>45649.0</v>
       </c>
       <c r="D244" t="n">
         <v>1.0</v>
@@ -3555,13 +3555,13 @@
         <v>5</v>
       </c>
       <c r="B245" t="n">
-        <v>2025.0</v>
+        <v>2024.0</v>
       </c>
       <c r="C245" t="n" s="2">
-        <v>45672.0</v>
+        <v>45656.0</v>
       </c>
       <c r="D245" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="246">
@@ -3572,10 +3572,10 @@
         <v>2025.0</v>
       </c>
       <c r="C246" t="n" s="2">
-        <v>45679.0</v>
+        <v>45672.0</v>
       </c>
       <c r="D246" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="247">
@@ -3586,7 +3586,7 @@
         <v>2025.0</v>
       </c>
       <c r="C247" t="n" s="2">
-        <v>45686.0</v>
+        <v>45679.0</v>
       </c>
       <c r="D247" t="n">
         <v>1.0</v>
@@ -3600,10 +3600,10 @@
         <v>2025.0</v>
       </c>
       <c r="C248" t="n" s="2">
-        <v>45721.0</v>
+        <v>45686.0</v>
       </c>
       <c r="D248" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="249">
@@ -3614,10 +3614,10 @@
         <v>2025.0</v>
       </c>
       <c r="C249" t="n" s="2">
-        <v>45728.0</v>
+        <v>45721.0</v>
       </c>
       <c r="D249" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="250">
@@ -3628,10 +3628,10 @@
         <v>2025.0</v>
       </c>
       <c r="C250" t="n" s="2">
-        <v>45742.0</v>
+        <v>45728.0</v>
       </c>
       <c r="D250" t="n">
-        <v>9.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="251">
@@ -3642,10 +3642,10 @@
         <v>2025.0</v>
       </c>
       <c r="C251" t="n" s="2">
-        <v>45749.0</v>
+        <v>45742.0</v>
       </c>
       <c r="D251" t="n">
-        <v>5.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="252">
@@ -3656,10 +3656,10 @@
         <v>2025.0</v>
       </c>
       <c r="C252" t="n" s="2">
-        <v>45756.0</v>
+        <v>45749.0</v>
       </c>
       <c r="D252" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="253">
@@ -3670,10 +3670,10 @@
         <v>2025.0</v>
       </c>
       <c r="C253" t="n" s="2">
-        <v>45763.0</v>
+        <v>45756.0</v>
       </c>
       <c r="D253" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="254">
@@ -3684,10 +3684,10 @@
         <v>2025.0</v>
       </c>
       <c r="C254" t="n" s="2">
-        <v>45770.0</v>
+        <v>45763.0</v>
       </c>
       <c r="D254" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="255">
@@ -3698,10 +3698,10 @@
         <v>2025.0</v>
       </c>
       <c r="C255" t="n" s="2">
-        <v>45777.0</v>
+        <v>45770.0</v>
       </c>
       <c r="D255" t="n">
-        <v>7.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="256">
@@ -3712,10 +3712,10 @@
         <v>2025.0</v>
       </c>
       <c r="C256" t="n" s="2">
-        <v>45784.0</v>
+        <v>45777.0</v>
       </c>
       <c r="D256" t="n">
-        <v>2.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="257">
@@ -3726,10 +3726,10 @@
         <v>2025.0</v>
       </c>
       <c r="C257" t="n" s="2">
-        <v>45791.0</v>
+        <v>45784.0</v>
       </c>
       <c r="D257" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="258">
@@ -3740,10 +3740,10 @@
         <v>2025.0</v>
       </c>
       <c r="C258" t="n" s="2">
-        <v>45798.0</v>
+        <v>45791.0</v>
       </c>
       <c r="D258" t="n">
-        <v>8.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="259">
@@ -3754,10 +3754,10 @@
         <v>2025.0</v>
       </c>
       <c r="C259" t="n" s="2">
-        <v>45805.0</v>
+        <v>45798.0</v>
       </c>
       <c r="D259" t="n">
-        <v>4.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="260">
@@ -3768,10 +3768,10 @@
         <v>2025.0</v>
       </c>
       <c r="C260" t="n" s="2">
-        <v>45812.0</v>
+        <v>45805.0</v>
       </c>
       <c r="D260" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="261">
@@ -3782,10 +3782,10 @@
         <v>2025.0</v>
       </c>
       <c r="C261" t="n" s="2">
-        <v>45819.0</v>
+        <v>45812.0</v>
       </c>
       <c r="D261" t="n">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="262">
@@ -3796,10 +3796,10 @@
         <v>2025.0</v>
       </c>
       <c r="C262" t="n" s="2">
-        <v>45826.0</v>
+        <v>45819.0</v>
       </c>
       <c r="D262" t="n">
-        <v>13.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="263">
@@ -3810,10 +3810,10 @@
         <v>2025.0</v>
       </c>
       <c r="C263" t="n" s="2">
-        <v>45833.0</v>
+        <v>45826.0</v>
       </c>
       <c r="D263" t="n">
-        <v>1.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="264">
@@ -3824,10 +3824,10 @@
         <v>2025.0</v>
       </c>
       <c r="C264" t="n" s="2">
-        <v>45840.0</v>
+        <v>45833.0</v>
       </c>
       <c r="D264" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="265">
@@ -3838,7 +3838,7 @@
         <v>2025.0</v>
       </c>
       <c r="C265" t="n" s="2">
-        <v>45847.0</v>
+        <v>45840.0</v>
       </c>
       <c r="D265" t="n">
         <v>4.0</v>
@@ -3852,10 +3852,10 @@
         <v>2025.0</v>
       </c>
       <c r="C266" t="n" s="2">
-        <v>45854.0</v>
+        <v>45847.0</v>
       </c>
       <c r="D266" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="267">
@@ -3866,10 +3866,10 @@
         <v>2025.0</v>
       </c>
       <c r="C267" t="n" s="2">
-        <v>45861.0</v>
+        <v>45854.0</v>
       </c>
       <c r="D267" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="268">
@@ -3880,10 +3880,10 @@
         <v>2025.0</v>
       </c>
       <c r="C268" t="n" s="2">
-        <v>45868.0</v>
+        <v>45861.0</v>
       </c>
       <c r="D268" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="269">
@@ -3894,10 +3894,10 @@
         <v>2025.0</v>
       </c>
       <c r="C269" t="n" s="2">
-        <v>45882.0</v>
+        <v>45868.0</v>
       </c>
       <c r="D269" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="270">
@@ -3908,7 +3908,7 @@
         <v>2025.0</v>
       </c>
       <c r="C270" t="n" s="2">
-        <v>45889.0</v>
+        <v>45882.0</v>
       </c>
       <c r="D270" t="n">
         <v>1.0</v>
@@ -3922,10 +3922,10 @@
         <v>2025.0</v>
       </c>
       <c r="C271" t="n" s="2">
-        <v>45896.0</v>
+        <v>45889.0</v>
       </c>
       <c r="D271" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="272">
@@ -3936,7 +3936,7 @@
         <v>2025.0</v>
       </c>
       <c r="C272" t="n" s="2">
-        <v>45903.0</v>
+        <v>45896.0</v>
       </c>
       <c r="D272" t="n">
         <v>3.0</v>
@@ -3950,10 +3950,10 @@
         <v>2025.0</v>
       </c>
       <c r="C273" t="n" s="2">
-        <v>45910.0</v>
+        <v>45903.0</v>
       </c>
       <c r="D273" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="274">
@@ -3964,7 +3964,7 @@
         <v>2025.0</v>
       </c>
       <c r="C274" t="n" s="2">
-        <v>45973.0</v>
+        <v>45910.0</v>
       </c>
       <c r="D274" t="n">
         <v>1.0</v>
@@ -3978,10 +3978,10 @@
         <v>2025.0</v>
       </c>
       <c r="C275" t="n" s="2">
-        <v>45987.0</v>
+        <v>45973.0</v>
       </c>
       <c r="D275" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="276">
@@ -3992,10 +3992,10 @@
         <v>2025.0</v>
       </c>
       <c r="C276" t="n" s="2">
-        <v>45994.0</v>
+        <v>45987.0</v>
       </c>
       <c r="D276" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="277">
@@ -4006,10 +4006,10 @@
         <v>2025.0</v>
       </c>
       <c r="C277" t="n" s="2">
-        <v>46001.0</v>
+        <v>45994.0</v>
       </c>
       <c r="D277" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="278">
@@ -4020,10 +4020,10 @@
         <v>2025.0</v>
       </c>
       <c r="C278" t="n" s="2">
-        <v>46008.0</v>
+        <v>46001.0</v>
       </c>
       <c r="D278" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="279">
@@ -4034,10 +4034,10 @@
         <v>2025.0</v>
       </c>
       <c r="C279" t="n" s="2">
-        <v>46022.0</v>
+        <v>46008.0</v>
       </c>
       <c r="D279" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="280">
@@ -4048,10 +4048,10 @@
         <v>2025.0</v>
       </c>
       <c r="C280" t="n" s="2">
-        <v>46029.0</v>
+        <v>46022.0</v>
       </c>
       <c r="D280" t="n">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="281">
@@ -4059,13 +4059,13 @@
         <v>5</v>
       </c>
       <c r="B281" t="n">
-        <v>2026.0</v>
+        <v>2025.0</v>
       </c>
       <c r="C281" t="n" s="2">
-        <v>46030.0</v>
+        <v>46029.0</v>
       </c>
       <c r="D281" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="282">
@@ -4076,10 +4076,10 @@
         <v>2026.0</v>
       </c>
       <c r="C282" t="n" s="2">
-        <v>46037.0</v>
+        <v>46030.0</v>
       </c>
       <c r="D282" t="n">
-        <v>12.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="283">
@@ -4090,10 +4090,10 @@
         <v>2026.0</v>
       </c>
       <c r="C283" t="n" s="2">
-        <v>46044.0</v>
+        <v>46037.0</v>
       </c>
       <c r="D283" t="n">
-        <v>9.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="284">
@@ -4104,10 +4104,10 @@
         <v>2026.0</v>
       </c>
       <c r="C284" t="n" s="2">
-        <v>46051.0</v>
+        <v>46044.0</v>
       </c>
       <c r="D284" t="n">
-        <v>10.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="285">
@@ -4118,10 +4118,10 @@
         <v>2026.0</v>
       </c>
       <c r="C285" t="n" s="2">
-        <v>46058.0</v>
+        <v>46051.0</v>
       </c>
       <c r="D285" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="286">
@@ -4132,10 +4132,10 @@
         <v>2026.0</v>
       </c>
       <c r="C286" t="n" s="2">
-        <v>46065.0</v>
+        <v>46058.0</v>
       </c>
       <c r="D286" t="n">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="287">
@@ -4146,10 +4146,10 @@
         <v>2026.0</v>
       </c>
       <c r="C287" t="n" s="2">
-        <v>46072.0</v>
+        <v>46065.0</v>
       </c>
       <c r="D287" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="288">
@@ -4160,7 +4160,7 @@
         <v>2026.0</v>
       </c>
       <c r="C288" t="n" s="2">
-        <v>46079.0</v>
+        <v>46072.0</v>
       </c>
       <c r="D288" t="n">
         <v>5.0</v>
@@ -4174,10 +4174,10 @@
         <v>2026.0</v>
       </c>
       <c r="C289" t="n" s="2">
-        <v>46086.0</v>
+        <v>46079.0</v>
       </c>
       <c r="D289" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="290">
@@ -4188,7 +4188,7 @@
         <v>2026.0</v>
       </c>
       <c r="C290" t="n" s="2">
-        <v>46093.0</v>
+        <v>46086.0</v>
       </c>
       <c r="D290" t="n">
         <v>2.0</v>
@@ -4202,10 +4202,10 @@
         <v>2026.0</v>
       </c>
       <c r="C291" t="n" s="2">
-        <v>46100.0</v>
+        <v>46093.0</v>
       </c>
       <c r="D291" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="292">
@@ -4216,10 +4216,10 @@
         <v>2026.0</v>
       </c>
       <c r="C292" t="n" s="2">
-        <v>46107.0</v>
+        <v>46100.0</v>
       </c>
       <c r="D292" t="n">
-        <v>9.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="293">
@@ -4230,10 +4230,10 @@
         <v>2026.0</v>
       </c>
       <c r="C293" t="n" s="2">
-        <v>46114.0</v>
+        <v>46107.0</v>
       </c>
       <c r="D293" t="n">
-        <v>5.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="294">
@@ -4244,10 +4244,10 @@
         <v>2026.0</v>
       </c>
       <c r="C294" t="n" s="2">
-        <v>46121.0</v>
+        <v>46114.0</v>
       </c>
       <c r="D294" t="n">
-        <v>13.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="295">
@@ -4258,10 +4258,10 @@
         <v>2026.0</v>
       </c>
       <c r="C295" t="n" s="2">
-        <v>46128.0</v>
+        <v>46121.0</v>
       </c>
       <c r="D295" t="n">
-        <v>4.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="296">
@@ -4272,7 +4272,7 @@
         <v>2026.0</v>
       </c>
       <c r="C296" t="n" s="2">
-        <v>46135.0</v>
+        <v>46128.0</v>
       </c>
       <c r="D296" t="n">
         <v>4.0</v>
@@ -4286,10 +4286,10 @@
         <v>2026.0</v>
       </c>
       <c r="C297" t="n" s="2">
-        <v>46142.0</v>
+        <v>46135.0</v>
       </c>
       <c r="D297" t="n">
-        <v>7.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="298">
@@ -4300,10 +4300,10 @@
         <v>2026.0</v>
       </c>
       <c r="C298" t="n" s="2">
-        <v>46149.0</v>
+        <v>46142.0</v>
       </c>
       <c r="D298" t="n">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="299">
@@ -4314,10 +4314,10 @@
         <v>2026.0</v>
       </c>
       <c r="C299" t="n" s="2">
-        <v>46156.0</v>
+        <v>46149.0</v>
       </c>
       <c r="D299" t="n">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="300">
@@ -4328,38 +4328,38 @@
         <v>2026.0</v>
       </c>
       <c r="C300" t="n" s="2">
-        <v>46163.0</v>
+        <v>46156.0</v>
       </c>
       <c r="D300" t="n">
-        <v>7.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B301" t="n">
-        <v>2023.0</v>
+        <v>2026.0</v>
       </c>
       <c r="C301" t="n" s="2">
-        <v>45095.0</v>
+        <v>46163.0</v>
       </c>
       <c r="D301" t="n">
-        <v>1.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B302" t="n">
-        <v>2023.0</v>
+        <v>2026.0</v>
       </c>
       <c r="C302" t="n" s="2">
-        <v>45102.0</v>
+        <v>46170.0</v>
       </c>
       <c r="D302" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="303">
@@ -4370,7 +4370,7 @@
         <v>2023.0</v>
       </c>
       <c r="C303" t="n" s="2">
-        <v>45158.0</v>
+        <v>45095.0</v>
       </c>
       <c r="D303" t="n">
         <v>1.0</v>
@@ -4384,10 +4384,10 @@
         <v>2023.0</v>
       </c>
       <c r="C304" t="n" s="2">
-        <v>45207.0</v>
+        <v>45102.0</v>
       </c>
       <c r="D304" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="305">
@@ -4398,10 +4398,10 @@
         <v>2023.0</v>
       </c>
       <c r="C305" t="n" s="2">
-        <v>45214.0</v>
+        <v>45158.0</v>
       </c>
       <c r="D305" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="306">
@@ -4412,10 +4412,10 @@
         <v>2023.0</v>
       </c>
       <c r="C306" t="n" s="2">
-        <v>45221.0</v>
+        <v>45207.0</v>
       </c>
       <c r="D306" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="307">
@@ -4426,10 +4426,10 @@
         <v>2023.0</v>
       </c>
       <c r="C307" t="n" s="2">
-        <v>45249.0</v>
+        <v>45214.0</v>
       </c>
       <c r="D307" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="308">
@@ -4440,10 +4440,10 @@
         <v>2023.0</v>
       </c>
       <c r="C308" t="n" s="2">
-        <v>45256.0</v>
+        <v>45221.0</v>
       </c>
       <c r="D308" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="309">
@@ -4454,10 +4454,10 @@
         <v>2023.0</v>
       </c>
       <c r="C309" t="n" s="2">
-        <v>45263.0</v>
+        <v>45249.0</v>
       </c>
       <c r="D309" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="310">
@@ -4468,10 +4468,10 @@
         <v>2023.0</v>
       </c>
       <c r="C310" t="n" s="2">
-        <v>45270.0</v>
+        <v>45256.0</v>
       </c>
       <c r="D310" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="311">
@@ -4482,7 +4482,7 @@
         <v>2023.0</v>
       </c>
       <c r="C311" t="n" s="2">
-        <v>45277.0</v>
+        <v>45263.0</v>
       </c>
       <c r="D311" t="n">
         <v>4.0</v>
@@ -4496,7 +4496,7 @@
         <v>2023.0</v>
       </c>
       <c r="C312" t="n" s="2">
-        <v>45284.0</v>
+        <v>45270.0</v>
       </c>
       <c r="D312" t="n">
         <v>1.0</v>
@@ -4510,10 +4510,10 @@
         <v>2023.0</v>
       </c>
       <c r="C313" t="n" s="2">
-        <v>45291.0</v>
+        <v>45277.0</v>
       </c>
       <c r="D313" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="314">
@@ -4521,13 +4521,13 @@
         <v>6</v>
       </c>
       <c r="B314" t="n">
-        <v>2024.0</v>
+        <v>2023.0</v>
       </c>
       <c r="C314" t="n" s="2">
-        <v>45306.0</v>
+        <v>45284.0</v>
       </c>
       <c r="D314" t="n">
-        <v>7.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="315">
@@ -4535,13 +4535,13 @@
         <v>6</v>
       </c>
       <c r="B315" t="n">
-        <v>2024.0</v>
+        <v>2023.0</v>
       </c>
       <c r="C315" t="n" s="2">
-        <v>45313.0</v>
+        <v>45291.0</v>
       </c>
       <c r="D315" t="n">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="316">
@@ -4552,10 +4552,10 @@
         <v>2024.0</v>
       </c>
       <c r="C316" t="n" s="2">
-        <v>45320.0</v>
+        <v>45306.0</v>
       </c>
       <c r="D316" t="n">
-        <v>19.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="317">
@@ -4566,10 +4566,10 @@
         <v>2024.0</v>
       </c>
       <c r="C317" t="n" s="2">
-        <v>45327.0</v>
+        <v>45313.0</v>
       </c>
       <c r="D317" t="n">
-        <v>18.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="318">
@@ -4580,10 +4580,10 @@
         <v>2024.0</v>
       </c>
       <c r="C318" t="n" s="2">
-        <v>45334.0</v>
+        <v>45320.0</v>
       </c>
       <c r="D318" t="n">
-        <v>9.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="319">
@@ -4594,10 +4594,10 @@
         <v>2024.0</v>
       </c>
       <c r="C319" t="n" s="2">
-        <v>45341.0</v>
+        <v>45327.0</v>
       </c>
       <c r="D319" t="n">
-        <v>12.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="320">
@@ -4608,10 +4608,10 @@
         <v>2024.0</v>
       </c>
       <c r="C320" t="n" s="2">
-        <v>45348.0</v>
+        <v>45334.0</v>
       </c>
       <c r="D320" t="n">
-        <v>12.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="321">
@@ -4622,10 +4622,10 @@
         <v>2024.0</v>
       </c>
       <c r="C321" t="n" s="2">
-        <v>45355.0</v>
+        <v>45341.0</v>
       </c>
       <c r="D321" t="n">
-        <v>10.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="322">
@@ -4636,7 +4636,7 @@
         <v>2024.0</v>
       </c>
       <c r="C322" t="n" s="2">
-        <v>45362.0</v>
+        <v>45348.0</v>
       </c>
       <c r="D322" t="n">
         <v>12.0</v>
@@ -4650,10 +4650,10 @@
         <v>2024.0</v>
       </c>
       <c r="C323" t="n" s="2">
-        <v>45369.0</v>
+        <v>45355.0</v>
       </c>
       <c r="D323" t="n">
-        <v>13.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="324">
@@ -4664,10 +4664,10 @@
         <v>2024.0</v>
       </c>
       <c r="C324" t="n" s="2">
-        <v>45376.0</v>
+        <v>45362.0</v>
       </c>
       <c r="D324" t="n">
-        <v>18.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="325">
@@ -4678,10 +4678,10 @@
         <v>2024.0</v>
       </c>
       <c r="C325" t="n" s="2">
-        <v>45383.0</v>
+        <v>45369.0</v>
       </c>
       <c r="D325" t="n">
-        <v>12.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="326">
@@ -4692,10 +4692,10 @@
         <v>2024.0</v>
       </c>
       <c r="C326" t="n" s="2">
-        <v>45390.0</v>
+        <v>45376.0</v>
       </c>
       <c r="D326" t="n">
-        <v>6.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="327">
@@ -4706,10 +4706,10 @@
         <v>2024.0</v>
       </c>
       <c r="C327" t="n" s="2">
-        <v>45397.0</v>
+        <v>45383.0</v>
       </c>
       <c r="D327" t="n">
-        <v>10.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="328">
@@ -4720,10 +4720,10 @@
         <v>2024.0</v>
       </c>
       <c r="C328" t="n" s="2">
-        <v>45404.0</v>
+        <v>45390.0</v>
       </c>
       <c r="D328" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="329">
@@ -4734,10 +4734,10 @@
         <v>2024.0</v>
       </c>
       <c r="C329" t="n" s="2">
-        <v>45411.0</v>
+        <v>45397.0</v>
       </c>
       <c r="D329" t="n">
-        <v>2.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="330">
@@ -4748,10 +4748,10 @@
         <v>2024.0</v>
       </c>
       <c r="C330" t="n" s="2">
-        <v>45418.0</v>
+        <v>45404.0</v>
       </c>
       <c r="D330" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="331">
@@ -4762,10 +4762,10 @@
         <v>2024.0</v>
       </c>
       <c r="C331" t="n" s="2">
-        <v>45425.0</v>
+        <v>45411.0</v>
       </c>
       <c r="D331" t="n">
-        <v>9.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="332">
@@ -4776,10 +4776,10 @@
         <v>2024.0</v>
       </c>
       <c r="C332" t="n" s="2">
-        <v>45432.0</v>
+        <v>45418.0</v>
       </c>
       <c r="D332" t="n">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="333">
@@ -4790,10 +4790,10 @@
         <v>2024.0</v>
       </c>
       <c r="C333" t="n" s="2">
-        <v>45439.0</v>
+        <v>45425.0</v>
       </c>
       <c r="D333" t="n">
-        <v>6.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="334">
@@ -4804,10 +4804,10 @@
         <v>2024.0</v>
       </c>
       <c r="C334" t="n" s="2">
-        <v>45446.0</v>
+        <v>45432.0</v>
       </c>
       <c r="D334" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="335">
@@ -4818,10 +4818,10 @@
         <v>2024.0</v>
       </c>
       <c r="C335" t="n" s="2">
-        <v>45453.0</v>
+        <v>45439.0</v>
       </c>
       <c r="D335" t="n">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="336">
@@ -4832,10 +4832,10 @@
         <v>2024.0</v>
       </c>
       <c r="C336" t="n" s="2">
-        <v>45460.0</v>
+        <v>45446.0</v>
       </c>
       <c r="D336" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="337">
@@ -4846,7 +4846,7 @@
         <v>2024.0</v>
       </c>
       <c r="C337" t="n" s="2">
-        <v>45467.0</v>
+        <v>45453.0</v>
       </c>
       <c r="D337" t="n">
         <v>4.0</v>
@@ -4860,10 +4860,10 @@
         <v>2024.0</v>
       </c>
       <c r="C338" t="n" s="2">
-        <v>45474.0</v>
+        <v>45460.0</v>
       </c>
       <c r="D338" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="339">
@@ -4874,10 +4874,10 @@
         <v>2024.0</v>
       </c>
       <c r="C339" t="n" s="2">
-        <v>45481.0</v>
+        <v>45467.0</v>
       </c>
       <c r="D339" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="340">
@@ -4888,7 +4888,7 @@
         <v>2024.0</v>
       </c>
       <c r="C340" t="n" s="2">
-        <v>45488.0</v>
+        <v>45474.0</v>
       </c>
       <c r="D340" t="n">
         <v>2.0</v>
@@ -4902,10 +4902,10 @@
         <v>2024.0</v>
       </c>
       <c r="C341" t="n" s="2">
-        <v>45495.0</v>
+        <v>45481.0</v>
       </c>
       <c r="D341" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="342">
@@ -4916,7 +4916,7 @@
         <v>2024.0</v>
       </c>
       <c r="C342" t="n" s="2">
-        <v>45502.0</v>
+        <v>45488.0</v>
       </c>
       <c r="D342" t="n">
         <v>2.0</v>
@@ -4930,10 +4930,10 @@
         <v>2024.0</v>
       </c>
       <c r="C343" t="n" s="2">
-        <v>45509.0</v>
+        <v>45495.0</v>
       </c>
       <c r="D343" t="n">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="344">
@@ -4944,10 +4944,10 @@
         <v>2024.0</v>
       </c>
       <c r="C344" t="n" s="2">
-        <v>45523.0</v>
+        <v>45502.0</v>
       </c>
       <c r="D344" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="345">
@@ -4958,7 +4958,7 @@
         <v>2024.0</v>
       </c>
       <c r="C345" t="n" s="2">
-        <v>45551.0</v>
+        <v>45509.0</v>
       </c>
       <c r="D345" t="n">
         <v>1.0</v>
@@ -4972,7 +4972,7 @@
         <v>2024.0</v>
       </c>
       <c r="C346" t="n" s="2">
-        <v>45558.0</v>
+        <v>45523.0</v>
       </c>
       <c r="D346" t="n">
         <v>1.0</v>
@@ -4986,10 +4986,10 @@
         <v>2024.0</v>
       </c>
       <c r="C347" t="n" s="2">
-        <v>45572.0</v>
+        <v>45551.0</v>
       </c>
       <c r="D347" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="348">
@@ -5000,7 +5000,7 @@
         <v>2024.0</v>
       </c>
       <c r="C348" t="n" s="2">
-        <v>45593.0</v>
+        <v>45558.0</v>
       </c>
       <c r="D348" t="n">
         <v>1.0</v>
@@ -5014,7 +5014,7 @@
         <v>2024.0</v>
       </c>
       <c r="C349" t="n" s="2">
-        <v>45614.0</v>
+        <v>45572.0</v>
       </c>
       <c r="D349" t="n">
         <v>2.0</v>
@@ -5028,7 +5028,7 @@
         <v>2024.0</v>
       </c>
       <c r="C350" t="n" s="2">
-        <v>45621.0</v>
+        <v>45593.0</v>
       </c>
       <c r="D350" t="n">
         <v>1.0</v>
@@ -5042,10 +5042,10 @@
         <v>2024.0</v>
       </c>
       <c r="C351" t="n" s="2">
-        <v>45635.0</v>
+        <v>45614.0</v>
       </c>
       <c r="D351" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="352">
@@ -5056,7 +5056,7 @@
         <v>2024.0</v>
       </c>
       <c r="C352" t="n" s="2">
-        <v>45649.0</v>
+        <v>45621.0</v>
       </c>
       <c r="D352" t="n">
         <v>1.0</v>
@@ -5067,13 +5067,13 @@
         <v>6</v>
       </c>
       <c r="B353" t="n">
-        <v>2025.0</v>
+        <v>2024.0</v>
       </c>
       <c r="C353" t="n" s="2">
-        <v>45665.0</v>
+        <v>45635.0</v>
       </c>
       <c r="D353" t="n">
-        <v>9.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="354">
@@ -5081,13 +5081,13 @@
         <v>6</v>
       </c>
       <c r="B354" t="n">
-        <v>2025.0</v>
+        <v>2024.0</v>
       </c>
       <c r="C354" t="n" s="2">
-        <v>45672.0</v>
+        <v>45649.0</v>
       </c>
       <c r="D354" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="355">
@@ -5098,10 +5098,10 @@
         <v>2025.0</v>
       </c>
       <c r="C355" t="n" s="2">
-        <v>45679.0</v>
+        <v>45665.0</v>
       </c>
       <c r="D355" t="n">
-        <v>1.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="356">
@@ -5112,10 +5112,10 @@
         <v>2025.0</v>
       </c>
       <c r="C356" t="n" s="2">
-        <v>45686.0</v>
+        <v>45672.0</v>
       </c>
       <c r="D356" t="n">
-        <v>8.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="357">
@@ -5126,10 +5126,10 @@
         <v>2025.0</v>
       </c>
       <c r="C357" t="n" s="2">
-        <v>45693.0</v>
+        <v>45679.0</v>
       </c>
       <c r="D357" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="358">
@@ -5140,10 +5140,10 @@
         <v>2025.0</v>
       </c>
       <c r="C358" t="n" s="2">
-        <v>45700.0</v>
+        <v>45686.0</v>
       </c>
       <c r="D358" t="n">
-        <v>5.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="359">
@@ -5154,10 +5154,10 @@
         <v>2025.0</v>
       </c>
       <c r="C359" t="n" s="2">
-        <v>45707.0</v>
+        <v>45693.0</v>
       </c>
       <c r="D359" t="n">
-        <v>8.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="360">
@@ -5168,10 +5168,10 @@
         <v>2025.0</v>
       </c>
       <c r="C360" t="n" s="2">
-        <v>45714.0</v>
+        <v>45700.0</v>
       </c>
       <c r="D360" t="n">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="361">
@@ -5182,7 +5182,7 @@
         <v>2025.0</v>
       </c>
       <c r="C361" t="n" s="2">
-        <v>45721.0</v>
+        <v>45707.0</v>
       </c>
       <c r="D361" t="n">
         <v>8.0</v>
@@ -5196,10 +5196,10 @@
         <v>2025.0</v>
       </c>
       <c r="C362" t="n" s="2">
-        <v>45728.0</v>
+        <v>45714.0</v>
       </c>
       <c r="D362" t="n">
-        <v>7.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="363">
@@ -5210,10 +5210,10 @@
         <v>2025.0</v>
       </c>
       <c r="C363" t="n" s="2">
-        <v>45735.0</v>
+        <v>45721.0</v>
       </c>
       <c r="D363" t="n">
-        <v>4.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="364">
@@ -5224,10 +5224,10 @@
         <v>2025.0</v>
       </c>
       <c r="C364" t="n" s="2">
-        <v>45742.0</v>
+        <v>45728.0</v>
       </c>
       <c r="D364" t="n">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="365">
@@ -5238,10 +5238,10 @@
         <v>2025.0</v>
       </c>
       <c r="C365" t="n" s="2">
-        <v>45749.0</v>
+        <v>45735.0</v>
       </c>
       <c r="D365" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="366">
@@ -5252,10 +5252,10 @@
         <v>2025.0</v>
       </c>
       <c r="C366" t="n" s="2">
-        <v>45756.0</v>
+        <v>45742.0</v>
       </c>
       <c r="D366" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="367">
@@ -5266,10 +5266,10 @@
         <v>2025.0</v>
       </c>
       <c r="C367" t="n" s="2">
-        <v>45763.0</v>
+        <v>45749.0</v>
       </c>
       <c r="D367" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="368">
@@ -5280,10 +5280,10 @@
         <v>2025.0</v>
       </c>
       <c r="C368" t="n" s="2">
-        <v>45770.0</v>
+        <v>45756.0</v>
       </c>
       <c r="D368" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="369">
@@ -5294,10 +5294,10 @@
         <v>2025.0</v>
       </c>
       <c r="C369" t="n" s="2">
-        <v>45777.0</v>
+        <v>45763.0</v>
       </c>
       <c r="D369" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="370">
@@ -5308,10 +5308,10 @@
         <v>2025.0</v>
       </c>
       <c r="C370" t="n" s="2">
-        <v>45784.0</v>
+        <v>45770.0</v>
       </c>
       <c r="D370" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="371">
@@ -5322,7 +5322,7 @@
         <v>2025.0</v>
       </c>
       <c r="C371" t="n" s="2">
-        <v>45791.0</v>
+        <v>45777.0</v>
       </c>
       <c r="D371" t="n">
         <v>1.0</v>
@@ -5336,7 +5336,7 @@
         <v>2025.0</v>
       </c>
       <c r="C372" t="n" s="2">
-        <v>45840.0</v>
+        <v>45784.0</v>
       </c>
       <c r="D372" t="n">
         <v>1.0</v>
@@ -5350,7 +5350,7 @@
         <v>2025.0</v>
       </c>
       <c r="C373" t="n" s="2">
-        <v>46001.0</v>
+        <v>45791.0</v>
       </c>
       <c r="D373" t="n">
         <v>1.0</v>
@@ -5361,10 +5361,10 @@
         <v>6</v>
       </c>
       <c r="B374" t="n">
-        <v>2026.0</v>
+        <v>2025.0</v>
       </c>
       <c r="C374" t="n" s="2">
-        <v>46037.0</v>
+        <v>45840.0</v>
       </c>
       <c r="D374" t="n">
         <v>1.0</v>
@@ -5372,13 +5372,13 @@
     </row>
     <row r="375">
       <c r="A375" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B375" t="n">
-        <v>2021.0</v>
+        <v>2025.0</v>
       </c>
       <c r="C375" t="n" s="2">
-        <v>44561.0</v>
+        <v>46001.0</v>
       </c>
       <c r="D375" t="n">
         <v>1.0</v>
@@ -5386,13 +5386,13 @@
     </row>
     <row r="376">
       <c r="A376" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B376" t="n">
-        <v>2022.0</v>
+        <v>2026.0</v>
       </c>
       <c r="C376" t="n" s="2">
-        <v>44569.0</v>
+        <v>46037.0</v>
       </c>
       <c r="D376" t="n">
         <v>1.0</v>
@@ -5403,13 +5403,13 @@
         <v>7</v>
       </c>
       <c r="B377" t="n">
-        <v>2022.0</v>
+        <v>2021.0</v>
       </c>
       <c r="C377" t="n" s="2">
-        <v>44576.0</v>
+        <v>44561.0</v>
       </c>
       <c r="D377" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="378">
@@ -5420,10 +5420,10 @@
         <v>2022.0</v>
       </c>
       <c r="C378" t="n" s="2">
-        <v>44583.0</v>
+        <v>44569.0</v>
       </c>
       <c r="D378" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="379">
@@ -5434,10 +5434,10 @@
         <v>2022.0</v>
       </c>
       <c r="C379" t="n" s="2">
-        <v>44590.0</v>
+        <v>44576.0</v>
       </c>
       <c r="D379" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="380">
@@ -5448,10 +5448,10 @@
         <v>2022.0</v>
       </c>
       <c r="C380" t="n" s="2">
-        <v>44604.0</v>
+        <v>44583.0</v>
       </c>
       <c r="D380" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="381">
@@ -5462,10 +5462,10 @@
         <v>2022.0</v>
       </c>
       <c r="C381" t="n" s="2">
-        <v>44611.0</v>
+        <v>44590.0</v>
       </c>
       <c r="D381" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="382">
@@ -5476,10 +5476,10 @@
         <v>2022.0</v>
       </c>
       <c r="C382" t="n" s="2">
-        <v>44618.0</v>
+        <v>44604.0</v>
       </c>
       <c r="D382" t="n">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="383">
@@ -5490,10 +5490,10 @@
         <v>2022.0</v>
       </c>
       <c r="C383" t="n" s="2">
-        <v>44625.0</v>
+        <v>44611.0</v>
       </c>
       <c r="D383" t="n">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="384">
@@ -5504,10 +5504,10 @@
         <v>2022.0</v>
       </c>
       <c r="C384" t="n" s="2">
-        <v>44632.0</v>
+        <v>44618.0</v>
       </c>
       <c r="D384" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="385">
@@ -5518,10 +5518,10 @@
         <v>2022.0</v>
       </c>
       <c r="C385" t="n" s="2">
-        <v>44639.0</v>
+        <v>44625.0</v>
       </c>
       <c r="D385" t="n">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="386">
@@ -5532,7 +5532,7 @@
         <v>2022.0</v>
       </c>
       <c r="C386" t="n" s="2">
-        <v>44646.0</v>
+        <v>44632.0</v>
       </c>
       <c r="D386" t="n">
         <v>3.0</v>
@@ -5546,10 +5546,10 @@
         <v>2022.0</v>
       </c>
       <c r="C387" t="n" s="2">
-        <v>44653.0</v>
+        <v>44639.0</v>
       </c>
       <c r="D387" t="n">
-        <v>9.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="388">
@@ -5560,10 +5560,10 @@
         <v>2022.0</v>
       </c>
       <c r="C388" t="n" s="2">
-        <v>44660.0</v>
+        <v>44646.0</v>
       </c>
       <c r="D388" t="n">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="389">
@@ -5574,10 +5574,10 @@
         <v>2022.0</v>
       </c>
       <c r="C389" t="n" s="2">
-        <v>44667.0</v>
+        <v>44653.0</v>
       </c>
       <c r="D389" t="n">
-        <v>2.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="390">
@@ -5588,10 +5588,10 @@
         <v>2022.0</v>
       </c>
       <c r="C390" t="n" s="2">
-        <v>44674.0</v>
+        <v>44660.0</v>
       </c>
       <c r="D390" t="n">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="391">
@@ -5602,7 +5602,7 @@
         <v>2022.0</v>
       </c>
       <c r="C391" t="n" s="2">
-        <v>44681.0</v>
+        <v>44667.0</v>
       </c>
       <c r="D391" t="n">
         <v>2.0</v>
@@ -5616,10 +5616,10 @@
         <v>2022.0</v>
       </c>
       <c r="C392" t="n" s="2">
-        <v>44688.0</v>
+        <v>44674.0</v>
       </c>
       <c r="D392" t="n">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="393">
@@ -5630,10 +5630,10 @@
         <v>2022.0</v>
       </c>
       <c r="C393" t="n" s="2">
-        <v>44695.0</v>
+        <v>44681.0</v>
       </c>
       <c r="D393" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="394">
@@ -5644,10 +5644,10 @@
         <v>2022.0</v>
       </c>
       <c r="C394" t="n" s="2">
-        <v>44702.0</v>
+        <v>44688.0</v>
       </c>
       <c r="D394" t="n">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="395">
@@ -5658,10 +5658,10 @@
         <v>2022.0</v>
       </c>
       <c r="C395" t="n" s="2">
-        <v>44709.0</v>
+        <v>44695.0</v>
       </c>
       <c r="D395" t="n">
-        <v>8.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="396">
@@ -5672,10 +5672,10 @@
         <v>2022.0</v>
       </c>
       <c r="C396" t="n" s="2">
-        <v>44716.0</v>
+        <v>44702.0</v>
       </c>
       <c r="D396" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="397">
@@ -5686,10 +5686,10 @@
         <v>2022.0</v>
       </c>
       <c r="C397" t="n" s="2">
-        <v>44723.0</v>
+        <v>44709.0</v>
       </c>
       <c r="D397" t="n">
-        <v>2.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="398">
@@ -5700,10 +5700,10 @@
         <v>2022.0</v>
       </c>
       <c r="C398" t="n" s="2">
-        <v>44730.0</v>
+        <v>44716.0</v>
       </c>
       <c r="D398" t="n">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="399">
@@ -5714,10 +5714,10 @@
         <v>2022.0</v>
       </c>
       <c r="C399" t="n" s="2">
-        <v>44737.0</v>
+        <v>44723.0</v>
       </c>
       <c r="D399" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="400">
@@ -5728,10 +5728,10 @@
         <v>2022.0</v>
       </c>
       <c r="C400" t="n" s="2">
-        <v>44744.0</v>
+        <v>44730.0</v>
       </c>
       <c r="D400" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="401">
@@ -5742,7 +5742,7 @@
         <v>2022.0</v>
       </c>
       <c r="C401" t="n" s="2">
-        <v>44751.0</v>
+        <v>44737.0</v>
       </c>
       <c r="D401" t="n">
         <v>4.0</v>
@@ -5756,10 +5756,10 @@
         <v>2022.0</v>
       </c>
       <c r="C402" t="n" s="2">
-        <v>44758.0</v>
+        <v>44744.0</v>
       </c>
       <c r="D402" t="n">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="403">
@@ -5770,10 +5770,10 @@
         <v>2022.0</v>
       </c>
       <c r="C403" t="n" s="2">
-        <v>44765.0</v>
+        <v>44751.0</v>
       </c>
       <c r="D403" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="404">
@@ -5784,10 +5784,10 @@
         <v>2022.0</v>
       </c>
       <c r="C404" t="n" s="2">
-        <v>44779.0</v>
+        <v>44758.0</v>
       </c>
       <c r="D404" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="405">
@@ -5798,7 +5798,7 @@
         <v>2022.0</v>
       </c>
       <c r="C405" t="n" s="2">
-        <v>44786.0</v>
+        <v>44765.0</v>
       </c>
       <c r="D405" t="n">
         <v>1.0</v>
@@ -5812,10 +5812,10 @@
         <v>2022.0</v>
       </c>
       <c r="C406" t="n" s="2">
-        <v>44863.0</v>
+        <v>44779.0</v>
       </c>
       <c r="D406" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="407">
@@ -5826,7 +5826,7 @@
         <v>2022.0</v>
       </c>
       <c r="C407" t="n" s="2">
-        <v>44870.0</v>
+        <v>44786.0</v>
       </c>
       <c r="D407" t="n">
         <v>1.0</v>
@@ -5840,7 +5840,7 @@
         <v>2022.0</v>
       </c>
       <c r="C408" t="n" s="2">
-        <v>44884.0</v>
+        <v>44863.0</v>
       </c>
       <c r="D408" t="n">
         <v>2.0</v>
@@ -5854,10 +5854,10 @@
         <v>2022.0</v>
       </c>
       <c r="C409" t="n" s="2">
-        <v>44891.0</v>
+        <v>44870.0</v>
       </c>
       <c r="D409" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="410">
@@ -5868,10 +5868,10 @@
         <v>2022.0</v>
       </c>
       <c r="C410" t="n" s="2">
-        <v>44898.0</v>
+        <v>44884.0</v>
       </c>
       <c r="D410" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="411">
@@ -5882,10 +5882,10 @@
         <v>2022.0</v>
       </c>
       <c r="C411" t="n" s="2">
-        <v>44912.0</v>
+        <v>44891.0</v>
       </c>
       <c r="D411" t="n">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="412">
@@ -5896,10 +5896,10 @@
         <v>2022.0</v>
       </c>
       <c r="C412" t="n" s="2">
-        <v>44919.0</v>
+        <v>44898.0</v>
       </c>
       <c r="D412" t="n">
-        <v>7.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="413">
@@ -5910,10 +5910,10 @@
         <v>2022.0</v>
       </c>
       <c r="C413" t="n" s="2">
-        <v>44926.0</v>
+        <v>44912.0</v>
       </c>
       <c r="D413" t="n">
-        <v>12.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="414">
@@ -5921,13 +5921,13 @@
         <v>7</v>
       </c>
       <c r="B414" t="n">
-        <v>2023.0</v>
+        <v>2022.0</v>
       </c>
       <c r="C414" t="n" s="2">
-        <v>44934.0</v>
+        <v>44919.0</v>
       </c>
       <c r="D414" t="n">
-        <v>4.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="415">
@@ -5935,13 +5935,13 @@
         <v>7</v>
       </c>
       <c r="B415" t="n">
-        <v>2023.0</v>
+        <v>2022.0</v>
       </c>
       <c r="C415" t="n" s="2">
-        <v>44941.0</v>
+        <v>44926.0</v>
       </c>
       <c r="D415" t="n">
-        <v>16.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="416">
@@ -5952,10 +5952,10 @@
         <v>2023.0</v>
       </c>
       <c r="C416" t="n" s="2">
-        <v>44948.0</v>
+        <v>44934.0</v>
       </c>
       <c r="D416" t="n">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="417">
@@ -5966,10 +5966,10 @@
         <v>2023.0</v>
       </c>
       <c r="C417" t="n" s="2">
-        <v>44955.0</v>
+        <v>44941.0</v>
       </c>
       <c r="D417" t="n">
-        <v>19.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="418">
@@ -5980,10 +5980,10 @@
         <v>2023.0</v>
       </c>
       <c r="C418" t="n" s="2">
-        <v>44962.0</v>
+        <v>44948.0</v>
       </c>
       <c r="D418" t="n">
-        <v>22.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="419">
@@ -5994,10 +5994,10 @@
         <v>2023.0</v>
       </c>
       <c r="C419" t="n" s="2">
-        <v>44969.0</v>
+        <v>44955.0</v>
       </c>
       <c r="D419" t="n">
-        <v>9.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="420">
@@ -6008,7 +6008,7 @@
         <v>2023.0</v>
       </c>
       <c r="C420" t="n" s="2">
-        <v>44976.0</v>
+        <v>44962.0</v>
       </c>
       <c r="D420" t="n">
         <v>22.0</v>
@@ -6022,10 +6022,10 @@
         <v>2023.0</v>
       </c>
       <c r="C421" t="n" s="2">
-        <v>44983.0</v>
+        <v>44969.0</v>
       </c>
       <c r="D421" t="n">
-        <v>29.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="422">
@@ -6036,10 +6036,10 @@
         <v>2023.0</v>
       </c>
       <c r="C422" t="n" s="2">
-        <v>44990.0</v>
+        <v>44976.0</v>
       </c>
       <c r="D422" t="n">
-        <v>5.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="423">
@@ -6050,10 +6050,10 @@
         <v>2023.0</v>
       </c>
       <c r="C423" t="n" s="2">
-        <v>44997.0</v>
+        <v>44983.0</v>
       </c>
       <c r="D423" t="n">
-        <v>24.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="424">
@@ -6064,10 +6064,10 @@
         <v>2023.0</v>
       </c>
       <c r="C424" t="n" s="2">
-        <v>45004.0</v>
+        <v>44990.0</v>
       </c>
       <c r="D424" t="n">
-        <v>8.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="425">
@@ -6078,10 +6078,10 @@
         <v>2023.0</v>
       </c>
       <c r="C425" t="n" s="2">
-        <v>45011.0</v>
+        <v>44997.0</v>
       </c>
       <c r="D425" t="n">
-        <v>10.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="426">
@@ -6092,10 +6092,10 @@
         <v>2023.0</v>
       </c>
       <c r="C426" t="n" s="2">
-        <v>45018.0</v>
+        <v>45004.0</v>
       </c>
       <c r="D426" t="n">
-        <v>18.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="427">
@@ -6106,10 +6106,10 @@
         <v>2023.0</v>
       </c>
       <c r="C427" t="n" s="2">
-        <v>45025.0</v>
+        <v>45011.0</v>
       </c>
       <c r="D427" t="n">
-        <v>13.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="428">
@@ -6120,7 +6120,7 @@
         <v>2023.0</v>
       </c>
       <c r="C428" t="n" s="2">
-        <v>45032.0</v>
+        <v>45018.0</v>
       </c>
       <c r="D428" t="n">
         <v>18.0</v>
@@ -6134,10 +6134,10 @@
         <v>2023.0</v>
       </c>
       <c r="C429" t="n" s="2">
-        <v>45039.0</v>
+        <v>45025.0</v>
       </c>
       <c r="D429" t="n">
-        <v>15.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="430">
@@ -6148,10 +6148,10 @@
         <v>2023.0</v>
       </c>
       <c r="C430" t="n" s="2">
-        <v>45046.0</v>
+        <v>45032.0</v>
       </c>
       <c r="D430" t="n">
-        <v>12.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="431">
@@ -6162,10 +6162,10 @@
         <v>2023.0</v>
       </c>
       <c r="C431" t="n" s="2">
-        <v>45053.0</v>
+        <v>45039.0</v>
       </c>
       <c r="D431" t="n">
-        <v>6.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="432">
@@ -6176,10 +6176,10 @@
         <v>2023.0</v>
       </c>
       <c r="C432" t="n" s="2">
-        <v>45060.0</v>
+        <v>45046.0</v>
       </c>
       <c r="D432" t="n">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="433">
@@ -6190,10 +6190,10 @@
         <v>2023.0</v>
       </c>
       <c r="C433" t="n" s="2">
-        <v>45067.0</v>
+        <v>45053.0</v>
       </c>
       <c r="D433" t="n">
-        <v>8.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="434">
@@ -6204,10 +6204,10 @@
         <v>2023.0</v>
       </c>
       <c r="C434" t="n" s="2">
-        <v>45074.0</v>
+        <v>45060.0</v>
       </c>
       <c r="D434" t="n">
-        <v>8.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="435">
@@ -6218,10 +6218,10 @@
         <v>2023.0</v>
       </c>
       <c r="C435" t="n" s="2">
-        <v>45081.0</v>
+        <v>45067.0</v>
       </c>
       <c r="D435" t="n">
-        <v>5.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="436">
@@ -6232,10 +6232,10 @@
         <v>2023.0</v>
       </c>
       <c r="C436" t="n" s="2">
-        <v>45088.0</v>
+        <v>45074.0</v>
       </c>
       <c r="D436" t="n">
-        <v>2.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="437">
@@ -6246,7 +6246,7 @@
         <v>2023.0</v>
       </c>
       <c r="C437" t="n" s="2">
-        <v>45095.0</v>
+        <v>45081.0</v>
       </c>
       <c r="D437" t="n">
         <v>5.0</v>
@@ -6260,10 +6260,10 @@
         <v>2023.0</v>
       </c>
       <c r="C438" t="n" s="2">
-        <v>45102.0</v>
+        <v>45088.0</v>
       </c>
       <c r="D438" t="n">
-        <v>10.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="439">
@@ -6274,10 +6274,10 @@
         <v>2023.0</v>
       </c>
       <c r="C439" t="n" s="2">
-        <v>45109.0</v>
+        <v>45095.0</v>
       </c>
       <c r="D439" t="n">
-        <v>9.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="440">
@@ -6288,10 +6288,10 @@
         <v>2023.0</v>
       </c>
       <c r="C440" t="n" s="2">
-        <v>45116.0</v>
+        <v>45102.0</v>
       </c>
       <c r="D440" t="n">
-        <v>3.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="441">
@@ -6302,10 +6302,10 @@
         <v>2023.0</v>
       </c>
       <c r="C441" t="n" s="2">
-        <v>45123.0</v>
+        <v>45109.0</v>
       </c>
       <c r="D441" t="n">
-        <v>6.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="442">
@@ -6316,10 +6316,10 @@
         <v>2023.0</v>
       </c>
       <c r="C442" t="n" s="2">
-        <v>45130.0</v>
+        <v>45116.0</v>
       </c>
       <c r="D442" t="n">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="443">
@@ -6330,10 +6330,10 @@
         <v>2023.0</v>
       </c>
       <c r="C443" t="n" s="2">
-        <v>45137.0</v>
+        <v>45123.0</v>
       </c>
       <c r="D443" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="444">
@@ -6344,10 +6344,10 @@
         <v>2023.0</v>
       </c>
       <c r="C444" t="n" s="2">
-        <v>45144.0</v>
+        <v>45130.0</v>
       </c>
       <c r="D444" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="445">
@@ -6358,7 +6358,7 @@
         <v>2023.0</v>
       </c>
       <c r="C445" t="n" s="2">
-        <v>45151.0</v>
+        <v>45137.0</v>
       </c>
       <c r="D445" t="n">
         <v>2.0</v>
@@ -6372,7 +6372,7 @@
         <v>2023.0</v>
       </c>
       <c r="C446" t="n" s="2">
-        <v>45165.0</v>
+        <v>45144.0</v>
       </c>
       <c r="D446" t="n">
         <v>2.0</v>
@@ -6386,7 +6386,7 @@
         <v>2023.0</v>
       </c>
       <c r="C447" t="n" s="2">
-        <v>45172.0</v>
+        <v>45151.0</v>
       </c>
       <c r="D447" t="n">
         <v>2.0</v>
@@ -6400,10 +6400,10 @@
         <v>2023.0</v>
       </c>
       <c r="C448" t="n" s="2">
-        <v>45179.0</v>
+        <v>45165.0</v>
       </c>
       <c r="D448" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="449">
@@ -6414,10 +6414,10 @@
         <v>2023.0</v>
       </c>
       <c r="C449" t="n" s="2">
-        <v>45186.0</v>
+        <v>45172.0</v>
       </c>
       <c r="D449" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="450">
@@ -6428,7 +6428,7 @@
         <v>2023.0</v>
       </c>
       <c r="C450" t="n" s="2">
-        <v>45193.0</v>
+        <v>45179.0</v>
       </c>
       <c r="D450" t="n">
         <v>1.0</v>
@@ -6442,7 +6442,7 @@
         <v>2023.0</v>
       </c>
       <c r="C451" t="n" s="2">
-        <v>45200.0</v>
+        <v>45186.0</v>
       </c>
       <c r="D451" t="n">
         <v>1.0</v>
@@ -6456,7 +6456,7 @@
         <v>2023.0</v>
       </c>
       <c r="C452" t="n" s="2">
-        <v>45207.0</v>
+        <v>45193.0</v>
       </c>
       <c r="D452" t="n">
         <v>1.0</v>
@@ -6470,7 +6470,7 @@
         <v>2023.0</v>
       </c>
       <c r="C453" t="n" s="2">
-        <v>45235.0</v>
+        <v>45200.0</v>
       </c>
       <c r="D453" t="n">
         <v>1.0</v>
@@ -6484,10 +6484,10 @@
         <v>2023.0</v>
       </c>
       <c r="C454" t="n" s="2">
-        <v>45242.0</v>
+        <v>45207.0</v>
       </c>
       <c r="D454" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="455">
@@ -6498,10 +6498,10 @@
         <v>2023.0</v>
       </c>
       <c r="C455" t="n" s="2">
-        <v>45249.0</v>
+        <v>45235.0</v>
       </c>
       <c r="D455" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="456">
@@ -6512,10 +6512,10 @@
         <v>2023.0</v>
       </c>
       <c r="C456" t="n" s="2">
-        <v>45256.0</v>
+        <v>45242.0</v>
       </c>
       <c r="D456" t="n">
-        <v>9.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="457">
@@ -6526,10 +6526,10 @@
         <v>2023.0</v>
       </c>
       <c r="C457" t="n" s="2">
-        <v>45263.0</v>
+        <v>45249.0</v>
       </c>
       <c r="D457" t="n">
-        <v>12.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="458">
@@ -6540,10 +6540,10 @@
         <v>2023.0</v>
       </c>
       <c r="C458" t="n" s="2">
-        <v>45270.0</v>
+        <v>45256.0</v>
       </c>
       <c r="D458" t="n">
-        <v>6.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="459">
@@ -6554,10 +6554,10 @@
         <v>2023.0</v>
       </c>
       <c r="C459" t="n" s="2">
-        <v>45277.0</v>
+        <v>45263.0</v>
       </c>
       <c r="D459" t="n">
-        <v>7.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="460">
@@ -6568,10 +6568,10 @@
         <v>2023.0</v>
       </c>
       <c r="C460" t="n" s="2">
-        <v>45284.0</v>
+        <v>45270.0</v>
       </c>
       <c r="D460" t="n">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="461">
@@ -6582,10 +6582,10 @@
         <v>2023.0</v>
       </c>
       <c r="C461" t="n" s="2">
-        <v>45291.0</v>
+        <v>45277.0</v>
       </c>
       <c r="D461" t="n">
-        <v>13.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="462">
@@ -6593,13 +6593,13 @@
         <v>7</v>
       </c>
       <c r="B462" t="n">
-        <v>2024.0</v>
+        <v>2023.0</v>
       </c>
       <c r="C462" t="n" s="2">
-        <v>45299.0</v>
+        <v>45284.0</v>
       </c>
       <c r="D462" t="n">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="463">
@@ -6607,13 +6607,13 @@
         <v>7</v>
       </c>
       <c r="B463" t="n">
-        <v>2024.0</v>
+        <v>2023.0</v>
       </c>
       <c r="C463" t="n" s="2">
-        <v>45306.0</v>
+        <v>45291.0</v>
       </c>
       <c r="D463" t="n">
-        <v>11.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="464">
@@ -6624,10 +6624,10 @@
         <v>2024.0</v>
       </c>
       <c r="C464" t="n" s="2">
-        <v>45313.0</v>
+        <v>45299.0</v>
       </c>
       <c r="D464" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="465">
@@ -6638,10 +6638,10 @@
         <v>2024.0</v>
       </c>
       <c r="C465" t="n" s="2">
-        <v>45320.0</v>
+        <v>45306.0</v>
       </c>
       <c r="D465" t="n">
-        <v>2.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="466">
@@ -6652,10 +6652,10 @@
         <v>2024.0</v>
       </c>
       <c r="C466" t="n" s="2">
-        <v>45327.0</v>
+        <v>45313.0</v>
       </c>
       <c r="D466" t="n">
-        <v>9.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="467">
@@ -6666,10 +6666,10 @@
         <v>2024.0</v>
       </c>
       <c r="C467" t="n" s="2">
-        <v>45334.0</v>
+        <v>45320.0</v>
       </c>
       <c r="D467" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="468">
@@ -6680,10 +6680,10 @@
         <v>2024.0</v>
       </c>
       <c r="C468" t="n" s="2">
-        <v>45341.0</v>
+        <v>45327.0</v>
       </c>
       <c r="D468" t="n">
-        <v>21.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="469">
@@ -6694,10 +6694,10 @@
         <v>2024.0</v>
       </c>
       <c r="C469" t="n" s="2">
-        <v>45348.0</v>
+        <v>45334.0</v>
       </c>
       <c r="D469" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="470">
@@ -6708,10 +6708,10 @@
         <v>2024.0</v>
       </c>
       <c r="C470" t="n" s="2">
-        <v>45355.0</v>
+        <v>45341.0</v>
       </c>
       <c r="D470" t="n">
-        <v>9.0</v>
+        <v>21.0</v>
       </c>
     </row>
     <row r="471">
@@ -6722,10 +6722,10 @@
         <v>2024.0</v>
       </c>
       <c r="C471" t="n" s="2">
-        <v>45362.0</v>
+        <v>45348.0</v>
       </c>
       <c r="D471" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="472">
@@ -6736,10 +6736,10 @@
         <v>2024.0</v>
       </c>
       <c r="C472" t="n" s="2">
-        <v>45369.0</v>
+        <v>45355.0</v>
       </c>
       <c r="D472" t="n">
-        <v>14.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="473">
@@ -6750,7 +6750,7 @@
         <v>2024.0</v>
       </c>
       <c r="C473" t="n" s="2">
-        <v>45376.0</v>
+        <v>45362.0</v>
       </c>
       <c r="D473" t="n">
         <v>4.0</v>
@@ -6764,10 +6764,10 @@
         <v>2024.0</v>
       </c>
       <c r="C474" t="n" s="2">
-        <v>45383.0</v>
+        <v>45369.0</v>
       </c>
       <c r="D474" t="n">
-        <v>2.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="475">
@@ -6778,10 +6778,10 @@
         <v>2024.0</v>
       </c>
       <c r="C475" t="n" s="2">
-        <v>45390.0</v>
+        <v>45376.0</v>
       </c>
       <c r="D475" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="476">
@@ -6792,10 +6792,10 @@
         <v>2024.0</v>
       </c>
       <c r="C476" t="n" s="2">
-        <v>45397.0</v>
+        <v>45383.0</v>
       </c>
       <c r="D476" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="477">
@@ -6806,10 +6806,10 @@
         <v>2024.0</v>
       </c>
       <c r="C477" t="n" s="2">
-        <v>45404.0</v>
+        <v>45390.0</v>
       </c>
       <c r="D477" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="478">
@@ -6820,7 +6820,7 @@
         <v>2024.0</v>
       </c>
       <c r="C478" t="n" s="2">
-        <v>45411.0</v>
+        <v>45397.0</v>
       </c>
       <c r="D478" t="n">
         <v>1.0</v>
@@ -6834,7 +6834,7 @@
         <v>2024.0</v>
       </c>
       <c r="C479" t="n" s="2">
-        <v>45439.0</v>
+        <v>45404.0</v>
       </c>
       <c r="D479" t="n">
         <v>2.0</v>
@@ -6848,7 +6848,7 @@
         <v>2024.0</v>
       </c>
       <c r="C480" t="n" s="2">
-        <v>45446.0</v>
+        <v>45411.0</v>
       </c>
       <c r="D480" t="n">
         <v>1.0</v>
@@ -6862,10 +6862,10 @@
         <v>2024.0</v>
       </c>
       <c r="C481" t="n" s="2">
-        <v>45460.0</v>
+        <v>45439.0</v>
       </c>
       <c r="D481" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="482">
@@ -6876,7 +6876,7 @@
         <v>2024.0</v>
       </c>
       <c r="C482" t="n" s="2">
-        <v>45481.0</v>
+        <v>45446.0</v>
       </c>
       <c r="D482" t="n">
         <v>1.0</v>
@@ -6890,7 +6890,7 @@
         <v>2024.0</v>
       </c>
       <c r="C483" t="n" s="2">
-        <v>45516.0</v>
+        <v>45460.0</v>
       </c>
       <c r="D483" t="n">
         <v>1.0</v>
@@ -6904,7 +6904,7 @@
         <v>2024.0</v>
       </c>
       <c r="C484" t="n" s="2">
-        <v>45551.0</v>
+        <v>45481.0</v>
       </c>
       <c r="D484" t="n">
         <v>1.0</v>
@@ -6918,7 +6918,7 @@
         <v>2024.0</v>
       </c>
       <c r="C485" t="n" s="2">
-        <v>45579.0</v>
+        <v>45516.0</v>
       </c>
       <c r="D485" t="n">
         <v>1.0</v>
@@ -6932,7 +6932,7 @@
         <v>2024.0</v>
       </c>
       <c r="C486" t="n" s="2">
-        <v>45614.0</v>
+        <v>45551.0</v>
       </c>
       <c r="D486" t="n">
         <v>1.0</v>
@@ -6946,10 +6946,10 @@
         <v>2024.0</v>
       </c>
       <c r="C487" t="n" s="2">
-        <v>45635.0</v>
+        <v>45579.0</v>
       </c>
       <c r="D487" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="488">
@@ -6960,10 +6960,10 @@
         <v>2024.0</v>
       </c>
       <c r="C488" t="n" s="2">
-        <v>45642.0</v>
+        <v>45614.0</v>
       </c>
       <c r="D488" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="489">
@@ -6974,10 +6974,10 @@
         <v>2024.0</v>
       </c>
       <c r="C489" t="n" s="2">
-        <v>45649.0</v>
+        <v>45635.0</v>
       </c>
       <c r="D489" t="n">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="490">
@@ -6988,7 +6988,7 @@
         <v>2024.0</v>
       </c>
       <c r="C490" t="n" s="2">
-        <v>45656.0</v>
+        <v>45642.0</v>
       </c>
       <c r="D490" t="n">
         <v>2.0</v>
@@ -6999,13 +6999,13 @@
         <v>7</v>
       </c>
       <c r="B491" t="n">
-        <v>2025.0</v>
+        <v>2024.0</v>
       </c>
       <c r="C491" t="n" s="2">
-        <v>45665.0</v>
+        <v>45649.0</v>
       </c>
       <c r="D491" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="492">
@@ -7013,10 +7013,10 @@
         <v>7</v>
       </c>
       <c r="B492" t="n">
-        <v>2025.0</v>
+        <v>2024.0</v>
       </c>
       <c r="C492" t="n" s="2">
-        <v>45672.0</v>
+        <v>45656.0</v>
       </c>
       <c r="D492" t="n">
         <v>2.0</v>
@@ -7030,10 +7030,10 @@
         <v>2025.0</v>
       </c>
       <c r="C493" t="n" s="2">
-        <v>45686.0</v>
+        <v>45665.0</v>
       </c>
       <c r="D493" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="494">
@@ -7044,10 +7044,10 @@
         <v>2025.0</v>
       </c>
       <c r="C494" t="n" s="2">
-        <v>45693.0</v>
+        <v>45672.0</v>
       </c>
       <c r="D494" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="495">
@@ -7058,10 +7058,10 @@
         <v>2025.0</v>
       </c>
       <c r="C495" t="n" s="2">
-        <v>45700.0</v>
+        <v>45686.0</v>
       </c>
       <c r="D495" t="n">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="496">
@@ -7072,10 +7072,10 @@
         <v>2025.0</v>
       </c>
       <c r="C496" t="n" s="2">
-        <v>45707.0</v>
+        <v>45693.0</v>
       </c>
       <c r="D496" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="497">
@@ -7086,10 +7086,10 @@
         <v>2025.0</v>
       </c>
       <c r="C497" t="n" s="2">
-        <v>45714.0</v>
+        <v>45700.0</v>
       </c>
       <c r="D497" t="n">
-        <v>8.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="498">
@@ -7100,10 +7100,10 @@
         <v>2025.0</v>
       </c>
       <c r="C498" t="n" s="2">
-        <v>45721.0</v>
+        <v>45707.0</v>
       </c>
       <c r="D498" t="n">
-        <v>11.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="499">
@@ -7114,10 +7114,10 @@
         <v>2025.0</v>
       </c>
       <c r="C499" t="n" s="2">
-        <v>45728.0</v>
+        <v>45714.0</v>
       </c>
       <c r="D499" t="n">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="500">
@@ -7128,10 +7128,10 @@
         <v>2025.0</v>
       </c>
       <c r="C500" t="n" s="2">
-        <v>45735.0</v>
+        <v>45721.0</v>
       </c>
       <c r="D500" t="n">
-        <v>19.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="501">
@@ -7142,10 +7142,10 @@
         <v>2025.0</v>
       </c>
       <c r="C501" t="n" s="2">
-        <v>45742.0</v>
+        <v>45728.0</v>
       </c>
       <c r="D501" t="n">
-        <v>17.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="502">
@@ -7156,10 +7156,10 @@
         <v>2025.0</v>
       </c>
       <c r="C502" t="n" s="2">
-        <v>45749.0</v>
+        <v>45735.0</v>
       </c>
       <c r="D502" t="n">
-        <v>5.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="503">
@@ -7170,10 +7170,10 @@
         <v>2025.0</v>
       </c>
       <c r="C503" t="n" s="2">
-        <v>45756.0</v>
+        <v>45742.0</v>
       </c>
       <c r="D503" t="n">
-        <v>9.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="504">
@@ -7184,10 +7184,10 @@
         <v>2025.0</v>
       </c>
       <c r="C504" t="n" s="2">
-        <v>45763.0</v>
+        <v>45749.0</v>
       </c>
       <c r="D504" t="n">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="505">
@@ -7198,10 +7198,10 @@
         <v>2025.0</v>
       </c>
       <c r="C505" t="n" s="2">
-        <v>45770.0</v>
+        <v>45756.0</v>
       </c>
       <c r="D505" t="n">
-        <v>1.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="506">
@@ -7212,10 +7212,10 @@
         <v>2025.0</v>
       </c>
       <c r="C506" t="n" s="2">
-        <v>45784.0</v>
+        <v>45763.0</v>
       </c>
       <c r="D506" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="507">
@@ -7226,10 +7226,10 @@
         <v>2025.0</v>
       </c>
       <c r="C507" t="n" s="2">
-        <v>45791.0</v>
+        <v>45770.0</v>
       </c>
       <c r="D507" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="508">
@@ -7240,10 +7240,10 @@
         <v>2025.0</v>
       </c>
       <c r="C508" t="n" s="2">
-        <v>45805.0</v>
+        <v>45784.0</v>
       </c>
       <c r="D508" t="n">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="509">
@@ -7254,7 +7254,7 @@
         <v>2025.0</v>
       </c>
       <c r="C509" t="n" s="2">
-        <v>45826.0</v>
+        <v>45791.0</v>
       </c>
       <c r="D509" t="n">
         <v>2.0</v>
@@ -7268,10 +7268,10 @@
         <v>2025.0</v>
       </c>
       <c r="C510" t="n" s="2">
-        <v>45861.0</v>
+        <v>45805.0</v>
       </c>
       <c r="D510" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="511">
@@ -7282,10 +7282,10 @@
         <v>2025.0</v>
       </c>
       <c r="C511" t="n" s="2">
-        <v>45868.0</v>
+        <v>45826.0</v>
       </c>
       <c r="D511" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="512">
@@ -7296,10 +7296,10 @@
         <v>2025.0</v>
       </c>
       <c r="C512" t="n" s="2">
-        <v>45889.0</v>
+        <v>45861.0</v>
       </c>
       <c r="D512" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="513">
@@ -7310,7 +7310,7 @@
         <v>2025.0</v>
       </c>
       <c r="C513" t="n" s="2">
-        <v>45924.0</v>
+        <v>45868.0</v>
       </c>
       <c r="D513" t="n">
         <v>1.0</v>
@@ -7324,7 +7324,7 @@
         <v>2025.0</v>
       </c>
       <c r="C514" t="n" s="2">
-        <v>45945.0</v>
+        <v>45889.0</v>
       </c>
       <c r="D514" t="n">
         <v>1.0</v>
@@ -7338,10 +7338,10 @@
         <v>2025.0</v>
       </c>
       <c r="C515" t="n" s="2">
-        <v>45959.0</v>
+        <v>45924.0</v>
       </c>
       <c r="D515" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="516">
@@ -7352,10 +7352,10 @@
         <v>2025.0</v>
       </c>
       <c r="C516" t="n" s="2">
-        <v>46001.0</v>
+        <v>45945.0</v>
       </c>
       <c r="D516" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="517">
@@ -7366,10 +7366,10 @@
         <v>2025.0</v>
       </c>
       <c r="C517" t="n" s="2">
-        <v>46008.0</v>
+        <v>45959.0</v>
       </c>
       <c r="D517" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="518">
@@ -7380,10 +7380,10 @@
         <v>2025.0</v>
       </c>
       <c r="C518" t="n" s="2">
-        <v>46022.0</v>
+        <v>46001.0</v>
       </c>
       <c r="D518" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="519">
@@ -7391,10 +7391,10 @@
         <v>7</v>
       </c>
       <c r="B519" t="n">
-        <v>2026.0</v>
+        <v>2025.0</v>
       </c>
       <c r="C519" t="n" s="2">
-        <v>46030.0</v>
+        <v>46008.0</v>
       </c>
       <c r="D519" t="n">
         <v>1.0</v>
@@ -7405,10 +7405,10 @@
         <v>7</v>
       </c>
       <c r="B520" t="n">
-        <v>2026.0</v>
+        <v>2025.0</v>
       </c>
       <c r="C520" t="n" s="2">
-        <v>46051.0</v>
+        <v>46022.0</v>
       </c>
       <c r="D520" t="n">
         <v>1.0</v>
@@ -7422,7 +7422,7 @@
         <v>2026.0</v>
       </c>
       <c r="C521" t="n" s="2">
-        <v>46058.0</v>
+        <v>46030.0</v>
       </c>
       <c r="D521" t="n">
         <v>1.0</v>
@@ -7436,10 +7436,10 @@
         <v>2026.0</v>
       </c>
       <c r="C522" t="n" s="2">
-        <v>46065.0</v>
+        <v>46051.0</v>
       </c>
       <c r="D522" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="523">
@@ -7450,10 +7450,10 @@
         <v>2026.0</v>
       </c>
       <c r="C523" t="n" s="2">
-        <v>46135.0</v>
+        <v>46058.0</v>
       </c>
       <c r="D523" t="n">
-        <v>8.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="524">
@@ -7464,10 +7464,10 @@
         <v>2026.0</v>
       </c>
       <c r="C524" t="n" s="2">
-        <v>46156.0</v>
+        <v>46065.0</v>
       </c>
       <c r="D524" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="525">
@@ -7478,21 +7478,21 @@
         <v>2026.0</v>
       </c>
       <c r="C525" t="n" s="2">
-        <v>46163.0</v>
+        <v>46135.0</v>
       </c>
       <c r="D525" t="n">
-        <v>2.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B526" t="n">
-        <v>2024.0</v>
+        <v>2026.0</v>
       </c>
       <c r="C526" t="n" s="2">
-        <v>45495.0</v>
+        <v>46156.0</v>
       </c>
       <c r="D526" t="n">
         <v>1.0</v>
@@ -7500,16 +7500,16 @@
     </row>
     <row r="527">
       <c r="A527" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B527" t="n">
-        <v>2024.0</v>
+        <v>2026.0</v>
       </c>
       <c r="C527" t="n" s="2">
-        <v>45502.0</v>
+        <v>46163.0</v>
       </c>
       <c r="D527" t="n">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="528">
@@ -7517,10 +7517,10 @@
         <v>8</v>
       </c>
       <c r="B528" t="n">
-        <v>2025.0</v>
+        <v>2024.0</v>
       </c>
       <c r="C528" t="n" s="2">
-        <v>45665.0</v>
+        <v>45495.0</v>
       </c>
       <c r="D528" t="n">
         <v>1.0</v>
@@ -7531,13 +7531,13 @@
         <v>8</v>
       </c>
       <c r="B529" t="n">
-        <v>2025.0</v>
+        <v>2024.0</v>
       </c>
       <c r="C529" t="n" s="2">
-        <v>45672.0</v>
+        <v>45502.0</v>
       </c>
       <c r="D529" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="530">
@@ -7548,7 +7548,7 @@
         <v>2025.0</v>
       </c>
       <c r="C530" t="n" s="2">
-        <v>45679.0</v>
+        <v>45665.0</v>
       </c>
       <c r="D530" t="n">
         <v>1.0</v>
@@ -7562,10 +7562,10 @@
         <v>2025.0</v>
       </c>
       <c r="C531" t="n" s="2">
-        <v>45686.0</v>
+        <v>45672.0</v>
       </c>
       <c r="D531" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="532">
@@ -7576,7 +7576,7 @@
         <v>2025.0</v>
       </c>
       <c r="C532" t="n" s="2">
-        <v>45693.0</v>
+        <v>45679.0</v>
       </c>
       <c r="D532" t="n">
         <v>1.0</v>
@@ -7590,10 +7590,10 @@
         <v>2025.0</v>
       </c>
       <c r="C533" t="n" s="2">
-        <v>45700.0</v>
+        <v>45686.0</v>
       </c>
       <c r="D533" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="534">
@@ -7604,10 +7604,10 @@
         <v>2025.0</v>
       </c>
       <c r="C534" t="n" s="2">
-        <v>45707.0</v>
+        <v>45693.0</v>
       </c>
       <c r="D534" t="n">
-        <v>7.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="535">
@@ -7618,10 +7618,10 @@
         <v>2025.0</v>
       </c>
       <c r="C535" t="n" s="2">
-        <v>45714.0</v>
+        <v>45700.0</v>
       </c>
       <c r="D535" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="536">
@@ -7632,10 +7632,10 @@
         <v>2025.0</v>
       </c>
       <c r="C536" t="n" s="2">
-        <v>45721.0</v>
+        <v>45707.0</v>
       </c>
       <c r="D536" t="n">
-        <v>4.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="537">
@@ -7646,10 +7646,10 @@
         <v>2025.0</v>
       </c>
       <c r="C537" t="n" s="2">
-        <v>45728.0</v>
+        <v>45714.0</v>
       </c>
       <c r="D537" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="538">
@@ -7660,10 +7660,10 @@
         <v>2025.0</v>
       </c>
       <c r="C538" t="n" s="2">
-        <v>45742.0</v>
+        <v>45721.0</v>
       </c>
       <c r="D538" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="539">
@@ -7674,7 +7674,7 @@
         <v>2025.0</v>
       </c>
       <c r="C539" t="n" s="2">
-        <v>45749.0</v>
+        <v>45728.0</v>
       </c>
       <c r="D539" t="n">
         <v>1.0</v>
@@ -7688,7 +7688,7 @@
         <v>2025.0</v>
       </c>
       <c r="C540" t="n" s="2">
-        <v>45763.0</v>
+        <v>45742.0</v>
       </c>
       <c r="D540" t="n">
         <v>1.0</v>
@@ -7702,10 +7702,10 @@
         <v>2025.0</v>
       </c>
       <c r="C541" t="n" s="2">
-        <v>45777.0</v>
+        <v>45749.0</v>
       </c>
       <c r="D541" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="542">
@@ -7716,7 +7716,7 @@
         <v>2025.0</v>
       </c>
       <c r="C542" t="n" s="2">
-        <v>45784.0</v>
+        <v>45763.0</v>
       </c>
       <c r="D542" t="n">
         <v>1.0</v>
@@ -7730,10 +7730,10 @@
         <v>2025.0</v>
       </c>
       <c r="C543" t="n" s="2">
-        <v>45798.0</v>
+        <v>45777.0</v>
       </c>
       <c r="D543" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="544">
@@ -7744,7 +7744,7 @@
         <v>2025.0</v>
       </c>
       <c r="C544" t="n" s="2">
-        <v>45805.0</v>
+        <v>45784.0</v>
       </c>
       <c r="D544" t="n">
         <v>1.0</v>
@@ -7758,10 +7758,10 @@
         <v>2025.0</v>
       </c>
       <c r="C545" t="n" s="2">
-        <v>45812.0</v>
+        <v>45798.0</v>
       </c>
       <c r="D545" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="546">
@@ -7772,10 +7772,10 @@
         <v>2025.0</v>
       </c>
       <c r="C546" t="n" s="2">
-        <v>45819.0</v>
+        <v>45805.0</v>
       </c>
       <c r="D546" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="547">
@@ -7786,7 +7786,7 @@
         <v>2025.0</v>
       </c>
       <c r="C547" t="n" s="2">
-        <v>45833.0</v>
+        <v>45812.0</v>
       </c>
       <c r="D547" t="n">
         <v>2.0</v>
@@ -7800,10 +7800,10 @@
         <v>2025.0</v>
       </c>
       <c r="C548" t="n" s="2">
-        <v>45847.0</v>
+        <v>45819.0</v>
       </c>
       <c r="D548" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="549">
@@ -7814,10 +7814,10 @@
         <v>2025.0</v>
       </c>
       <c r="C549" t="n" s="2">
-        <v>45854.0</v>
+        <v>45833.0</v>
       </c>
       <c r="D549" t="n">
-        <v>8.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="550">
@@ -7828,10 +7828,10 @@
         <v>2025.0</v>
       </c>
       <c r="C550" t="n" s="2">
-        <v>45861.0</v>
+        <v>45847.0</v>
       </c>
       <c r="D550" t="n">
-        <v>12.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="551">
@@ -7842,10 +7842,10 @@
         <v>2025.0</v>
       </c>
       <c r="C551" t="n" s="2">
-        <v>45868.0</v>
+        <v>45854.0</v>
       </c>
       <c r="D551" t="n">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="552">
@@ -7856,10 +7856,10 @@
         <v>2025.0</v>
       </c>
       <c r="C552" t="n" s="2">
-        <v>45875.0</v>
+        <v>45861.0</v>
       </c>
       <c r="D552" t="n">
-        <v>1.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="553">
@@ -7870,10 +7870,10 @@
         <v>2025.0</v>
       </c>
       <c r="C553" t="n" s="2">
-        <v>45896.0</v>
+        <v>45868.0</v>
       </c>
       <c r="D553" t="n">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="554">
@@ -7884,7 +7884,7 @@
         <v>2025.0</v>
       </c>
       <c r="C554" t="n" s="2">
-        <v>45903.0</v>
+        <v>45875.0</v>
       </c>
       <c r="D554" t="n">
         <v>1.0</v>
@@ -7898,7 +7898,7 @@
         <v>2025.0</v>
       </c>
       <c r="C555" t="n" s="2">
-        <v>45931.0</v>
+        <v>45896.0</v>
       </c>
       <c r="D555" t="n">
         <v>1.0</v>
@@ -7912,10 +7912,10 @@
         <v>2025.0</v>
       </c>
       <c r="C556" t="n" s="2">
-        <v>45938.0</v>
+        <v>45903.0</v>
       </c>
       <c r="D556" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="557">
@@ -7926,10 +7926,10 @@
         <v>2025.0</v>
       </c>
       <c r="C557" t="n" s="2">
-        <v>45945.0</v>
+        <v>45931.0</v>
       </c>
       <c r="D557" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="558">
@@ -7940,10 +7940,10 @@
         <v>2025.0</v>
       </c>
       <c r="C558" t="n" s="2">
-        <v>45966.0</v>
+        <v>45938.0</v>
       </c>
       <c r="D558" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="559">
@@ -7954,10 +7954,10 @@
         <v>2025.0</v>
       </c>
       <c r="C559" t="n" s="2">
-        <v>45973.0</v>
+        <v>45945.0</v>
       </c>
       <c r="D559" t="n">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="560">
@@ -7968,10 +7968,10 @@
         <v>2025.0</v>
       </c>
       <c r="C560" t="n" s="2">
-        <v>45980.0</v>
+        <v>45966.0</v>
       </c>
       <c r="D560" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="561">
@@ -7982,10 +7982,10 @@
         <v>2025.0</v>
       </c>
       <c r="C561" t="n" s="2">
-        <v>45987.0</v>
+        <v>45973.0</v>
       </c>
       <c r="D561" t="n">
-        <v>20.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="562">
@@ -7996,10 +7996,10 @@
         <v>2025.0</v>
       </c>
       <c r="C562" t="n" s="2">
-        <v>45994.0</v>
+        <v>45980.0</v>
       </c>
       <c r="D562" t="n">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="563">
@@ -8010,10 +8010,10 @@
         <v>2025.0</v>
       </c>
       <c r="C563" t="n" s="2">
-        <v>46001.0</v>
+        <v>45987.0</v>
       </c>
       <c r="D563" t="n">
-        <v>8.0</v>
+        <v>20.0</v>
       </c>
     </row>
     <row r="564">
@@ -8024,10 +8024,10 @@
         <v>2025.0</v>
       </c>
       <c r="C564" t="n" s="2">
-        <v>46008.0</v>
+        <v>45994.0</v>
       </c>
       <c r="D564" t="n">
-        <v>24.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="565">
@@ -8038,10 +8038,10 @@
         <v>2025.0</v>
       </c>
       <c r="C565" t="n" s="2">
-        <v>46015.0</v>
+        <v>46001.0</v>
       </c>
       <c r="D565" t="n">
-        <v>13.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="566">
@@ -8052,10 +8052,10 @@
         <v>2025.0</v>
       </c>
       <c r="C566" t="n" s="2">
-        <v>46022.0</v>
+        <v>46008.0</v>
       </c>
       <c r="D566" t="n">
-        <v>8.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="567">
@@ -8066,10 +8066,10 @@
         <v>2025.0</v>
       </c>
       <c r="C567" t="n" s="2">
-        <v>46029.0</v>
+        <v>46015.0</v>
       </c>
       <c r="D567" t="n">
-        <v>3.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="568">
@@ -8077,13 +8077,13 @@
         <v>8</v>
       </c>
       <c r="B568" t="n">
-        <v>2026.0</v>
+        <v>2025.0</v>
       </c>
       <c r="C568" t="n" s="2">
-        <v>46030.0</v>
+        <v>46022.0</v>
       </c>
       <c r="D568" t="n">
-        <v>24.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="569">
@@ -8091,13 +8091,13 @@
         <v>8</v>
       </c>
       <c r="B569" t="n">
-        <v>2026.0</v>
+        <v>2025.0</v>
       </c>
       <c r="C569" t="n" s="2">
-        <v>46037.0</v>
+        <v>46029.0</v>
       </c>
       <c r="D569" t="n">
-        <v>22.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="570">
@@ -8108,10 +8108,10 @@
         <v>2026.0</v>
       </c>
       <c r="C570" t="n" s="2">
-        <v>46044.0</v>
+        <v>46030.0</v>
       </c>
       <c r="D570" t="n">
-        <v>27.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="571">
@@ -8122,10 +8122,10 @@
         <v>2026.0</v>
       </c>
       <c r="C571" t="n" s="2">
-        <v>46051.0</v>
+        <v>46037.0</v>
       </c>
       <c r="D571" t="n">
-        <v>18.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="572">
@@ -8136,10 +8136,10 @@
         <v>2026.0</v>
       </c>
       <c r="C572" t="n" s="2">
-        <v>46058.0</v>
+        <v>46044.0</v>
       </c>
       <c r="D572" t="n">
-        <v>25.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="573">
@@ -8150,10 +8150,10 @@
         <v>2026.0</v>
       </c>
       <c r="C573" t="n" s="2">
-        <v>46065.0</v>
+        <v>46051.0</v>
       </c>
       <c r="D573" t="n">
-        <v>22.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="574">
@@ -8164,10 +8164,10 @@
         <v>2026.0</v>
       </c>
       <c r="C574" t="n" s="2">
-        <v>46072.0</v>
+        <v>46058.0</v>
       </c>
       <c r="D574" t="n">
-        <v>13.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="575">
@@ -8178,10 +8178,10 @@
         <v>2026.0</v>
       </c>
       <c r="C575" t="n" s="2">
-        <v>46079.0</v>
+        <v>46065.0</v>
       </c>
       <c r="D575" t="n">
-        <v>24.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="576">
@@ -8192,10 +8192,10 @@
         <v>2026.0</v>
       </c>
       <c r="C576" t="n" s="2">
-        <v>46086.0</v>
+        <v>46072.0</v>
       </c>
       <c r="D576" t="n">
-        <v>26.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="577">
@@ -8206,10 +8206,10 @@
         <v>2026.0</v>
       </c>
       <c r="C577" t="n" s="2">
-        <v>46093.0</v>
+        <v>46079.0</v>
       </c>
       <c r="D577" t="n">
-        <v>33.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="578">
@@ -8220,10 +8220,10 @@
         <v>2026.0</v>
       </c>
       <c r="C578" t="n" s="2">
-        <v>46100.0</v>
+        <v>46086.0</v>
       </c>
       <c r="D578" t="n">
-        <v>25.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="579">
@@ -8234,10 +8234,10 @@
         <v>2026.0</v>
       </c>
       <c r="C579" t="n" s="2">
-        <v>46107.0</v>
+        <v>46093.0</v>
       </c>
       <c r="D579" t="n">
-        <v>31.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="580">
@@ -8248,10 +8248,10 @@
         <v>2026.0</v>
       </c>
       <c r="C580" t="n" s="2">
-        <v>46114.0</v>
+        <v>46100.0</v>
       </c>
       <c r="D580" t="n">
-        <v>10.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="581">
@@ -8262,10 +8262,10 @@
         <v>2026.0</v>
       </c>
       <c r="C581" t="n" s="2">
-        <v>46121.0</v>
+        <v>46107.0</v>
       </c>
       <c r="D581" t="n">
-        <v>9.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="582">
@@ -8276,10 +8276,10 @@
         <v>2026.0</v>
       </c>
       <c r="C582" t="n" s="2">
-        <v>46128.0</v>
+        <v>46114.0</v>
       </c>
       <c r="D582" t="n">
-        <v>15.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="583">
@@ -8290,10 +8290,10 @@
         <v>2026.0</v>
       </c>
       <c r="C583" t="n" s="2">
-        <v>46135.0</v>
+        <v>46121.0</v>
       </c>
       <c r="D583" t="n">
-        <v>35.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="584">
@@ -8304,10 +8304,10 @@
         <v>2026.0</v>
       </c>
       <c r="C584" t="n" s="2">
-        <v>46142.0</v>
+        <v>46128.0</v>
       </c>
       <c r="D584" t="n">
-        <v>21.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="585">
@@ -8318,10 +8318,10 @@
         <v>2026.0</v>
       </c>
       <c r="C585" t="n" s="2">
-        <v>46149.0</v>
+        <v>46135.0</v>
       </c>
       <c r="D585" t="n">
-        <v>6.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="586">
@@ -8332,10 +8332,10 @@
         <v>2026.0</v>
       </c>
       <c r="C586" t="n" s="2">
-        <v>46156.0</v>
+        <v>46142.0</v>
       </c>
       <c r="D586" t="n">
-        <v>27.0</v>
+        <v>21.0</v>
       </c>
     </row>
     <row r="587">
@@ -8346,10 +8346,52 @@
         <v>2026.0</v>
       </c>
       <c r="C587" t="n" s="2">
+        <v>46149.0</v>
+      </c>
+      <c r="D587" t="n">
+        <v>6.0</v>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="s">
+        <v>8</v>
+      </c>
+      <c r="B588" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C588" t="n" s="2">
+        <v>46156.0</v>
+      </c>
+      <c r="D588" t="n">
+        <v>27.0</v>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="s">
+        <v>8</v>
+      </c>
+      <c r="B589" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C589" t="n" s="2">
         <v>46163.0</v>
       </c>
-      <c r="D587" t="n">
-        <v>12.0</v>
+      <c r="D589" t="n">
+        <v>13.0</v>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="s">
+        <v>8</v>
+      </c>
+      <c r="B590" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C590" t="n" s="2">
+        <v>46170.0</v>
+      </c>
+      <c r="D590" t="n">
+        <v>10.0</v>
       </c>
     </row>
   </sheetData>
@@ -8391,7 +8433,7 @@
         <v>12</v>
       </c>
       <c r="B4" t="n">
-        <v>1295.0</v>
+        <v>1299.0</v>
       </c>
     </row>
     <row r="5">
@@ -8399,7 +8441,7 @@
         <v>13</v>
       </c>
       <c r="B5" t="n">
-        <v>2146.0</v>
+        <v>2157.0</v>
       </c>
     </row>
   </sheetData>
@@ -8431,7 +8473,7 @@
         <v>21</v>
       </c>
       <c r="C2" t="n">
-        <v>208.0</v>
+        <v>211.0</v>
       </c>
     </row>
     <row r="3">
@@ -8442,7 +8484,7 @@
         <v>22</v>
       </c>
       <c r="C3" t="n">
-        <v>186.0</v>
+        <v>187.0</v>
       </c>
     </row>
     <row r="4">
@@ -8453,7 +8495,7 @@
         <v>19</v>
       </c>
       <c r="C4" t="n">
-        <v>146.0</v>
+        <v>147.0</v>
       </c>
     </row>
     <row r="5">
@@ -8475,7 +8517,7 @@
         <v>22</v>
       </c>
       <c r="C6" t="n">
-        <v>307.0</v>
+        <v>308.0</v>
       </c>
     </row>
     <row r="7">
@@ -8497,7 +8539,7 @@
         <v>21</v>
       </c>
       <c r="C8" t="n">
-        <v>353.0</v>
+        <v>354.0</v>
       </c>
     </row>
     <row r="9">
@@ -8508,7 +8550,7 @@
         <v>22</v>
       </c>
       <c r="C9" t="n">
-        <v>330.0</v>
+        <v>332.0</v>
       </c>
     </row>
     <row r="10">
@@ -8541,7 +8583,7 @@
         <v>21</v>
       </c>
       <c r="C12" t="n">
-        <v>77.0</v>
+        <v>80.0</v>
       </c>
     </row>
     <row r="13">
@@ -8552,7 +8594,7 @@
         <v>22</v>
       </c>
       <c r="C13" t="n">
-        <v>42.0</v>
+        <v>43.0</v>
       </c>
     </row>
     <row r="14">
@@ -8574,7 +8616,7 @@
         <v>21</v>
       </c>
       <c r="C15" t="n">
-        <v>370.0</v>
+        <v>372.0</v>
       </c>
     </row>
     <row r="16">

--- a/Download/Focus_Positivi_ZR.xlsx
+++ b/Download/Focus_Positivi_ZR.xlsx
@@ -8391,7 +8391,7 @@
         <v>46170.0</v>
       </c>
       <c r="D590" t="n">
-        <v>10.0</v>
+        <v>16.0</v>
       </c>
     </row>
   </sheetData>
@@ -8417,7 +8417,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="n">
-        <v>49.0</v>
+        <v>55.0</v>
       </c>
     </row>
     <row r="3">
@@ -8572,7 +8572,7 @@
         <v>19</v>
       </c>
       <c r="C11" t="n">
-        <v>35.0</v>
+        <v>41.0</v>
       </c>
     </row>
     <row r="12">

--- a/Download/Focus_Positivi_ZR.xlsx
+++ b/Download/Focus_Positivi_ZR.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="634" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="635" uniqueCount="23">
   <si>
     <t>NOME_REGIONE</t>
   </si>
@@ -8335,7 +8335,7 @@
         <v>46142.0</v>
       </c>
       <c r="D586" t="n">
-        <v>21.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="587">
@@ -8391,7 +8391,21 @@
         <v>46170.0</v>
       </c>
       <c r="D590" t="n">
-        <v>16.0</v>
+        <v>21.0</v>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="s">
+        <v>8</v>
+      </c>
+      <c r="B591" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C591" t="n" s="2">
+        <v>46177.0</v>
+      </c>
+      <c r="D591" t="n">
+        <v>1.0</v>
       </c>
     </row>
   </sheetData>
@@ -8417,7 +8431,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="n">
-        <v>55.0</v>
+        <v>50.0</v>
       </c>
     </row>
     <row r="3">
@@ -8433,7 +8447,7 @@
         <v>12</v>
       </c>
       <c r="B4" t="n">
-        <v>1299.0</v>
+        <v>1309.0</v>
       </c>
     </row>
     <row r="5">
@@ -8441,7 +8455,7 @@
         <v>13</v>
       </c>
       <c r="B5" t="n">
-        <v>2157.0</v>
+        <v>2159.0</v>
       </c>
     </row>
   </sheetData>
@@ -8473,7 +8487,7 @@
         <v>21</v>
       </c>
       <c r="C2" t="n">
-        <v>211.0</v>
+        <v>213.0</v>
       </c>
     </row>
     <row r="3">
@@ -8484,7 +8498,7 @@
         <v>22</v>
       </c>
       <c r="C3" t="n">
-        <v>187.0</v>
+        <v>189.0</v>
       </c>
     </row>
     <row r="4">
@@ -8495,7 +8509,7 @@
         <v>19</v>
       </c>
       <c r="C4" t="n">
-        <v>147.0</v>
+        <v>149.0</v>
       </c>
     </row>
     <row r="5">
@@ -8506,7 +8520,7 @@
         <v>21</v>
       </c>
       <c r="C5" t="n">
-        <v>433.0</v>
+        <v>435.0</v>
       </c>
     </row>
     <row r="6">
@@ -8572,7 +8586,7 @@
         <v>19</v>
       </c>
       <c r="C11" t="n">
-        <v>41.0</v>
+        <v>36.0</v>
       </c>
     </row>
     <row r="12">
@@ -8583,7 +8597,7 @@
         <v>21</v>
       </c>
       <c r="C12" t="n">
-        <v>80.0</v>
+        <v>82.0</v>
       </c>
     </row>
     <row r="13">
@@ -8594,7 +8608,7 @@
         <v>22</v>
       </c>
       <c r="C13" t="n">
-        <v>43.0</v>
+        <v>44.0</v>
       </c>
     </row>
     <row r="14">
@@ -8605,7 +8619,7 @@
         <v>19</v>
       </c>
       <c r="C14" t="n">
-        <v>417.0</v>
+        <v>418.0</v>
       </c>
     </row>
     <row r="15">

--- a/Download/Focus_Positivi_ZR.xlsx
+++ b/Download/Focus_Positivi_ZR.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="635" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="636" uniqueCount="23">
   <si>
     <t>NOME_REGIONE</t>
   </si>
@@ -4364,16 +4364,16 @@
     </row>
     <row r="303">
       <c r="A303" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B303" t="n">
-        <v>2023.0</v>
+        <v>2026.0</v>
       </c>
       <c r="C303" t="n" s="2">
-        <v>45095.0</v>
+        <v>46177.0</v>
       </c>
       <c r="D303" t="n">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="304">
@@ -4384,7 +4384,7 @@
         <v>2023.0</v>
       </c>
       <c r="C304" t="n" s="2">
-        <v>45102.0</v>
+        <v>45095.0</v>
       </c>
       <c r="D304" t="n">
         <v>1.0</v>
@@ -4398,7 +4398,7 @@
         <v>2023.0</v>
       </c>
       <c r="C305" t="n" s="2">
-        <v>45158.0</v>
+        <v>45102.0</v>
       </c>
       <c r="D305" t="n">
         <v>1.0</v>
@@ -4412,10 +4412,10 @@
         <v>2023.0</v>
       </c>
       <c r="C306" t="n" s="2">
-        <v>45207.0</v>
+        <v>45158.0</v>
       </c>
       <c r="D306" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="307">
@@ -4426,7 +4426,7 @@
         <v>2023.0</v>
       </c>
       <c r="C307" t="n" s="2">
-        <v>45214.0</v>
+        <v>45207.0</v>
       </c>
       <c r="D307" t="n">
         <v>3.0</v>
@@ -4440,10 +4440,10 @@
         <v>2023.0</v>
       </c>
       <c r="C308" t="n" s="2">
-        <v>45221.0</v>
+        <v>45214.0</v>
       </c>
       <c r="D308" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="309">
@@ -4454,7 +4454,7 @@
         <v>2023.0</v>
       </c>
       <c r="C309" t="n" s="2">
-        <v>45249.0</v>
+        <v>45221.0</v>
       </c>
       <c r="D309" t="n">
         <v>1.0</v>
@@ -4468,10 +4468,10 @@
         <v>2023.0</v>
       </c>
       <c r="C310" t="n" s="2">
-        <v>45256.0</v>
+        <v>45249.0</v>
       </c>
       <c r="D310" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="311">
@@ -4482,10 +4482,10 @@
         <v>2023.0</v>
       </c>
       <c r="C311" t="n" s="2">
-        <v>45263.0</v>
+        <v>45256.0</v>
       </c>
       <c r="D311" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="312">
@@ -4496,10 +4496,10 @@
         <v>2023.0</v>
       </c>
       <c r="C312" t="n" s="2">
-        <v>45270.0</v>
+        <v>45263.0</v>
       </c>
       <c r="D312" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="313">
@@ -4510,10 +4510,10 @@
         <v>2023.0</v>
       </c>
       <c r="C313" t="n" s="2">
-        <v>45277.0</v>
+        <v>45270.0</v>
       </c>
       <c r="D313" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="314">
@@ -4524,10 +4524,10 @@
         <v>2023.0</v>
       </c>
       <c r="C314" t="n" s="2">
-        <v>45284.0</v>
+        <v>45277.0</v>
       </c>
       <c r="D314" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="315">
@@ -4538,10 +4538,10 @@
         <v>2023.0</v>
       </c>
       <c r="C315" t="n" s="2">
-        <v>45291.0</v>
+        <v>45284.0</v>
       </c>
       <c r="D315" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="316">
@@ -4549,13 +4549,13 @@
         <v>6</v>
       </c>
       <c r="B316" t="n">
-        <v>2024.0</v>
+        <v>2023.0</v>
       </c>
       <c r="C316" t="n" s="2">
-        <v>45306.0</v>
+        <v>45291.0</v>
       </c>
       <c r="D316" t="n">
-        <v>7.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="317">
@@ -4566,10 +4566,10 @@
         <v>2024.0</v>
       </c>
       <c r="C317" t="n" s="2">
-        <v>45313.0</v>
+        <v>45306.0</v>
       </c>
       <c r="D317" t="n">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="318">
@@ -4580,10 +4580,10 @@
         <v>2024.0</v>
       </c>
       <c r="C318" t="n" s="2">
-        <v>45320.0</v>
+        <v>45313.0</v>
       </c>
       <c r="D318" t="n">
-        <v>19.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="319">
@@ -4594,10 +4594,10 @@
         <v>2024.0</v>
       </c>
       <c r="C319" t="n" s="2">
-        <v>45327.0</v>
+        <v>45320.0</v>
       </c>
       <c r="D319" t="n">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="320">
@@ -4608,10 +4608,10 @@
         <v>2024.0</v>
       </c>
       <c r="C320" t="n" s="2">
-        <v>45334.0</v>
+        <v>45327.0</v>
       </c>
       <c r="D320" t="n">
-        <v>9.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="321">
@@ -4622,10 +4622,10 @@
         <v>2024.0</v>
       </c>
       <c r="C321" t="n" s="2">
-        <v>45341.0</v>
+        <v>45334.0</v>
       </c>
       <c r="D321" t="n">
-        <v>12.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="322">
@@ -4636,7 +4636,7 @@
         <v>2024.0</v>
       </c>
       <c r="C322" t="n" s="2">
-        <v>45348.0</v>
+        <v>45341.0</v>
       </c>
       <c r="D322" t="n">
         <v>12.0</v>
@@ -4650,10 +4650,10 @@
         <v>2024.0</v>
       </c>
       <c r="C323" t="n" s="2">
-        <v>45355.0</v>
+        <v>45348.0</v>
       </c>
       <c r="D323" t="n">
-        <v>10.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="324">
@@ -4664,10 +4664,10 @@
         <v>2024.0</v>
       </c>
       <c r="C324" t="n" s="2">
-        <v>45362.0</v>
+        <v>45355.0</v>
       </c>
       <c r="D324" t="n">
-        <v>12.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="325">
@@ -4678,10 +4678,10 @@
         <v>2024.0</v>
       </c>
       <c r="C325" t="n" s="2">
-        <v>45369.0</v>
+        <v>45362.0</v>
       </c>
       <c r="D325" t="n">
-        <v>13.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="326">
@@ -4692,10 +4692,10 @@
         <v>2024.0</v>
       </c>
       <c r="C326" t="n" s="2">
-        <v>45376.0</v>
+        <v>45369.0</v>
       </c>
       <c r="D326" t="n">
-        <v>18.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="327">
@@ -4706,10 +4706,10 @@
         <v>2024.0</v>
       </c>
       <c r="C327" t="n" s="2">
-        <v>45383.0</v>
+        <v>45376.0</v>
       </c>
       <c r="D327" t="n">
-        <v>12.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="328">
@@ -4720,10 +4720,10 @@
         <v>2024.0</v>
       </c>
       <c r="C328" t="n" s="2">
-        <v>45390.0</v>
+        <v>45383.0</v>
       </c>
       <c r="D328" t="n">
-        <v>6.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="329">
@@ -4734,10 +4734,10 @@
         <v>2024.0</v>
       </c>
       <c r="C329" t="n" s="2">
-        <v>45397.0</v>
+        <v>45390.0</v>
       </c>
       <c r="D329" t="n">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="330">
@@ -4748,10 +4748,10 @@
         <v>2024.0</v>
       </c>
       <c r="C330" t="n" s="2">
-        <v>45404.0</v>
+        <v>45397.0</v>
       </c>
       <c r="D330" t="n">
-        <v>3.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="331">
@@ -4762,10 +4762,10 @@
         <v>2024.0</v>
       </c>
       <c r="C331" t="n" s="2">
-        <v>45411.0</v>
+        <v>45404.0</v>
       </c>
       <c r="D331" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="332">
@@ -4776,10 +4776,10 @@
         <v>2024.0</v>
       </c>
       <c r="C332" t="n" s="2">
-        <v>45418.0</v>
+        <v>45411.0</v>
       </c>
       <c r="D332" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="333">
@@ -4790,10 +4790,10 @@
         <v>2024.0</v>
       </c>
       <c r="C333" t="n" s="2">
-        <v>45425.0</v>
+        <v>45418.0</v>
       </c>
       <c r="D333" t="n">
-        <v>9.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="334">
@@ -4804,10 +4804,10 @@
         <v>2024.0</v>
       </c>
       <c r="C334" t="n" s="2">
-        <v>45432.0</v>
+        <v>45425.0</v>
       </c>
       <c r="D334" t="n">
-        <v>6.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="335">
@@ -4818,7 +4818,7 @@
         <v>2024.0</v>
       </c>
       <c r="C335" t="n" s="2">
-        <v>45439.0</v>
+        <v>45432.0</v>
       </c>
       <c r="D335" t="n">
         <v>6.0</v>
@@ -4832,10 +4832,10 @@
         <v>2024.0</v>
       </c>
       <c r="C336" t="n" s="2">
-        <v>45446.0</v>
+        <v>45439.0</v>
       </c>
       <c r="D336" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="337">
@@ -4846,10 +4846,10 @@
         <v>2024.0</v>
       </c>
       <c r="C337" t="n" s="2">
-        <v>45453.0</v>
+        <v>45446.0</v>
       </c>
       <c r="D337" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="338">
@@ -4860,7 +4860,7 @@
         <v>2024.0</v>
       </c>
       <c r="C338" t="n" s="2">
-        <v>45460.0</v>
+        <v>45453.0</v>
       </c>
       <c r="D338" t="n">
         <v>4.0</v>
@@ -4874,7 +4874,7 @@
         <v>2024.0</v>
       </c>
       <c r="C339" t="n" s="2">
-        <v>45467.0</v>
+        <v>45460.0</v>
       </c>
       <c r="D339" t="n">
         <v>4.0</v>
@@ -4888,10 +4888,10 @@
         <v>2024.0</v>
       </c>
       <c r="C340" t="n" s="2">
-        <v>45474.0</v>
+        <v>45467.0</v>
       </c>
       <c r="D340" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="341">
@@ -4902,10 +4902,10 @@
         <v>2024.0</v>
       </c>
       <c r="C341" t="n" s="2">
-        <v>45481.0</v>
+        <v>45474.0</v>
       </c>
       <c r="D341" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="342">
@@ -4916,10 +4916,10 @@
         <v>2024.0</v>
       </c>
       <c r="C342" t="n" s="2">
-        <v>45488.0</v>
+        <v>45481.0</v>
       </c>
       <c r="D342" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="343">
@@ -4930,10 +4930,10 @@
         <v>2024.0</v>
       </c>
       <c r="C343" t="n" s="2">
-        <v>45495.0</v>
+        <v>45488.0</v>
       </c>
       <c r="D343" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="344">
@@ -4944,10 +4944,10 @@
         <v>2024.0</v>
       </c>
       <c r="C344" t="n" s="2">
-        <v>45502.0</v>
+        <v>45495.0</v>
       </c>
       <c r="D344" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="345">
@@ -4958,10 +4958,10 @@
         <v>2024.0</v>
       </c>
       <c r="C345" t="n" s="2">
-        <v>45509.0</v>
+        <v>45502.0</v>
       </c>
       <c r="D345" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="346">
@@ -4972,7 +4972,7 @@
         <v>2024.0</v>
       </c>
       <c r="C346" t="n" s="2">
-        <v>45523.0</v>
+        <v>45509.0</v>
       </c>
       <c r="D346" t="n">
         <v>1.0</v>
@@ -4986,7 +4986,7 @@
         <v>2024.0</v>
       </c>
       <c r="C347" t="n" s="2">
-        <v>45551.0</v>
+        <v>45523.0</v>
       </c>
       <c r="D347" t="n">
         <v>1.0</v>
@@ -5000,7 +5000,7 @@
         <v>2024.0</v>
       </c>
       <c r="C348" t="n" s="2">
-        <v>45558.0</v>
+        <v>45551.0</v>
       </c>
       <c r="D348" t="n">
         <v>1.0</v>
@@ -5014,10 +5014,10 @@
         <v>2024.0</v>
       </c>
       <c r="C349" t="n" s="2">
-        <v>45572.0</v>
+        <v>45558.0</v>
       </c>
       <c r="D349" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="350">
@@ -5028,10 +5028,10 @@
         <v>2024.0</v>
       </c>
       <c r="C350" t="n" s="2">
-        <v>45593.0</v>
+        <v>45572.0</v>
       </c>
       <c r="D350" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="351">
@@ -5042,10 +5042,10 @@
         <v>2024.0</v>
       </c>
       <c r="C351" t="n" s="2">
-        <v>45614.0</v>
+        <v>45593.0</v>
       </c>
       <c r="D351" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="352">
@@ -5056,10 +5056,10 @@
         <v>2024.0</v>
       </c>
       <c r="C352" t="n" s="2">
-        <v>45621.0</v>
+        <v>45614.0</v>
       </c>
       <c r="D352" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="353">
@@ -5070,7 +5070,7 @@
         <v>2024.0</v>
       </c>
       <c r="C353" t="n" s="2">
-        <v>45635.0</v>
+        <v>45621.0</v>
       </c>
       <c r="D353" t="n">
         <v>1.0</v>
@@ -5084,7 +5084,7 @@
         <v>2024.0</v>
       </c>
       <c r="C354" t="n" s="2">
-        <v>45649.0</v>
+        <v>45635.0</v>
       </c>
       <c r="D354" t="n">
         <v>1.0</v>
@@ -5095,13 +5095,13 @@
         <v>6</v>
       </c>
       <c r="B355" t="n">
-        <v>2025.0</v>
+        <v>2024.0</v>
       </c>
       <c r="C355" t="n" s="2">
-        <v>45665.0</v>
+        <v>45649.0</v>
       </c>
       <c r="D355" t="n">
-        <v>9.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="356">
@@ -5112,10 +5112,10 @@
         <v>2025.0</v>
       </c>
       <c r="C356" t="n" s="2">
-        <v>45672.0</v>
+        <v>45665.0</v>
       </c>
       <c r="D356" t="n">
-        <v>3.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="357">
@@ -5126,10 +5126,10 @@
         <v>2025.0</v>
       </c>
       <c r="C357" t="n" s="2">
-        <v>45679.0</v>
+        <v>45672.0</v>
       </c>
       <c r="D357" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="358">
@@ -5140,10 +5140,10 @@
         <v>2025.0</v>
       </c>
       <c r="C358" t="n" s="2">
-        <v>45686.0</v>
+        <v>45679.0</v>
       </c>
       <c r="D358" t="n">
-        <v>8.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="359">
@@ -5154,10 +5154,10 @@
         <v>2025.0</v>
       </c>
       <c r="C359" t="n" s="2">
-        <v>45693.0</v>
+        <v>45686.0</v>
       </c>
       <c r="D359" t="n">
-        <v>3.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="360">
@@ -5168,10 +5168,10 @@
         <v>2025.0</v>
       </c>
       <c r="C360" t="n" s="2">
-        <v>45700.0</v>
+        <v>45693.0</v>
       </c>
       <c r="D360" t="n">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="361">
@@ -5182,10 +5182,10 @@
         <v>2025.0</v>
       </c>
       <c r="C361" t="n" s="2">
-        <v>45707.0</v>
+        <v>45700.0</v>
       </c>
       <c r="D361" t="n">
-        <v>8.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="362">
@@ -5196,10 +5196,10 @@
         <v>2025.0</v>
       </c>
       <c r="C362" t="n" s="2">
-        <v>45714.0</v>
+        <v>45707.0</v>
       </c>
       <c r="D362" t="n">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="363">
@@ -5210,10 +5210,10 @@
         <v>2025.0</v>
       </c>
       <c r="C363" t="n" s="2">
-        <v>45721.0</v>
+        <v>45714.0</v>
       </c>
       <c r="D363" t="n">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="364">
@@ -5224,10 +5224,10 @@
         <v>2025.0</v>
       </c>
       <c r="C364" t="n" s="2">
-        <v>45728.0</v>
+        <v>45721.0</v>
       </c>
       <c r="D364" t="n">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="365">
@@ -5238,10 +5238,10 @@
         <v>2025.0</v>
       </c>
       <c r="C365" t="n" s="2">
-        <v>45735.0</v>
+        <v>45728.0</v>
       </c>
       <c r="D365" t="n">
-        <v>4.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="366">
@@ -5252,10 +5252,10 @@
         <v>2025.0</v>
       </c>
       <c r="C366" t="n" s="2">
-        <v>45742.0</v>
+        <v>45735.0</v>
       </c>
       <c r="D366" t="n">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="367">
@@ -5266,10 +5266,10 @@
         <v>2025.0</v>
       </c>
       <c r="C367" t="n" s="2">
-        <v>45749.0</v>
+        <v>45742.0</v>
       </c>
       <c r="D367" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="368">
@@ -5280,10 +5280,10 @@
         <v>2025.0</v>
       </c>
       <c r="C368" t="n" s="2">
-        <v>45756.0</v>
+        <v>45749.0</v>
       </c>
       <c r="D368" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="369">
@@ -5294,10 +5294,10 @@
         <v>2025.0</v>
       </c>
       <c r="C369" t="n" s="2">
-        <v>45763.0</v>
+        <v>45756.0</v>
       </c>
       <c r="D369" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="370">
@@ -5308,7 +5308,7 @@
         <v>2025.0</v>
       </c>
       <c r="C370" t="n" s="2">
-        <v>45770.0</v>
+        <v>45763.0</v>
       </c>
       <c r="D370" t="n">
         <v>4.0</v>
@@ -5322,10 +5322,10 @@
         <v>2025.0</v>
       </c>
       <c r="C371" t="n" s="2">
-        <v>45777.0</v>
+        <v>45770.0</v>
       </c>
       <c r="D371" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="372">
@@ -5336,7 +5336,7 @@
         <v>2025.0</v>
       </c>
       <c r="C372" t="n" s="2">
-        <v>45784.0</v>
+        <v>45777.0</v>
       </c>
       <c r="D372" t="n">
         <v>1.0</v>
@@ -5350,7 +5350,7 @@
         <v>2025.0</v>
       </c>
       <c r="C373" t="n" s="2">
-        <v>45791.0</v>
+        <v>45784.0</v>
       </c>
       <c r="D373" t="n">
         <v>1.0</v>
@@ -5364,7 +5364,7 @@
         <v>2025.0</v>
       </c>
       <c r="C374" t="n" s="2">
-        <v>45840.0</v>
+        <v>45791.0</v>
       </c>
       <c r="D374" t="n">
         <v>1.0</v>
@@ -5378,7 +5378,7 @@
         <v>2025.0</v>
       </c>
       <c r="C375" t="n" s="2">
-        <v>46001.0</v>
+        <v>45840.0</v>
       </c>
       <c r="D375" t="n">
         <v>1.0</v>
@@ -5389,10 +5389,10 @@
         <v>6</v>
       </c>
       <c r="B376" t="n">
-        <v>2026.0</v>
+        <v>2025.0</v>
       </c>
       <c r="C376" t="n" s="2">
-        <v>46037.0</v>
+        <v>46001.0</v>
       </c>
       <c r="D376" t="n">
         <v>1.0</v>
@@ -5400,13 +5400,13 @@
     </row>
     <row r="377">
       <c r="A377" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B377" t="n">
-        <v>2021.0</v>
+        <v>2026.0</v>
       </c>
       <c r="C377" t="n" s="2">
-        <v>44561.0</v>
+        <v>46037.0</v>
       </c>
       <c r="D377" t="n">
         <v>1.0</v>
@@ -5417,10 +5417,10 @@
         <v>7</v>
       </c>
       <c r="B378" t="n">
-        <v>2022.0</v>
+        <v>2021.0</v>
       </c>
       <c r="C378" t="n" s="2">
-        <v>44569.0</v>
+        <v>44561.0</v>
       </c>
       <c r="D378" t="n">
         <v>1.0</v>
@@ -5434,10 +5434,10 @@
         <v>2022.0</v>
       </c>
       <c r="C379" t="n" s="2">
-        <v>44576.0</v>
+        <v>44569.0</v>
       </c>
       <c r="D379" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="380">
@@ -5448,10 +5448,10 @@
         <v>2022.0</v>
       </c>
       <c r="C380" t="n" s="2">
-        <v>44583.0</v>
+        <v>44576.0</v>
       </c>
       <c r="D380" t="n">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="381">
@@ -5462,10 +5462,10 @@
         <v>2022.0</v>
       </c>
       <c r="C381" t="n" s="2">
-        <v>44590.0</v>
+        <v>44583.0</v>
       </c>
       <c r="D381" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="382">
@@ -5476,10 +5476,10 @@
         <v>2022.0</v>
       </c>
       <c r="C382" t="n" s="2">
-        <v>44604.0</v>
+        <v>44590.0</v>
       </c>
       <c r="D382" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="383">
@@ -5490,7 +5490,7 @@
         <v>2022.0</v>
       </c>
       <c r="C383" t="n" s="2">
-        <v>44611.0</v>
+        <v>44604.0</v>
       </c>
       <c r="D383" t="n">
         <v>3.0</v>
@@ -5504,10 +5504,10 @@
         <v>2022.0</v>
       </c>
       <c r="C384" t="n" s="2">
-        <v>44618.0</v>
+        <v>44611.0</v>
       </c>
       <c r="D384" t="n">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="385">
@@ -5518,7 +5518,7 @@
         <v>2022.0</v>
       </c>
       <c r="C385" t="n" s="2">
-        <v>44625.0</v>
+        <v>44618.0</v>
       </c>
       <c r="D385" t="n">
         <v>5.0</v>
@@ -5532,10 +5532,10 @@
         <v>2022.0</v>
       </c>
       <c r="C386" t="n" s="2">
-        <v>44632.0</v>
+        <v>44625.0</v>
       </c>
       <c r="D386" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="387">
@@ -5546,10 +5546,10 @@
         <v>2022.0</v>
       </c>
       <c r="C387" t="n" s="2">
-        <v>44639.0</v>
+        <v>44632.0</v>
       </c>
       <c r="D387" t="n">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="388">
@@ -5560,10 +5560,10 @@
         <v>2022.0</v>
       </c>
       <c r="C388" t="n" s="2">
-        <v>44646.0</v>
+        <v>44639.0</v>
       </c>
       <c r="D388" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="389">
@@ -5574,10 +5574,10 @@
         <v>2022.0</v>
       </c>
       <c r="C389" t="n" s="2">
-        <v>44653.0</v>
+        <v>44646.0</v>
       </c>
       <c r="D389" t="n">
-        <v>9.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="390">
@@ -5588,10 +5588,10 @@
         <v>2022.0</v>
       </c>
       <c r="C390" t="n" s="2">
-        <v>44660.0</v>
+        <v>44653.0</v>
       </c>
       <c r="D390" t="n">
-        <v>6.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="391">
@@ -5602,10 +5602,10 @@
         <v>2022.0</v>
       </c>
       <c r="C391" t="n" s="2">
-        <v>44667.0</v>
+        <v>44660.0</v>
       </c>
       <c r="D391" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="392">
@@ -5616,10 +5616,10 @@
         <v>2022.0</v>
       </c>
       <c r="C392" t="n" s="2">
-        <v>44674.0</v>
+        <v>44667.0</v>
       </c>
       <c r="D392" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="393">
@@ -5630,10 +5630,10 @@
         <v>2022.0</v>
       </c>
       <c r="C393" t="n" s="2">
-        <v>44681.0</v>
+        <v>44674.0</v>
       </c>
       <c r="D393" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="394">
@@ -5644,10 +5644,10 @@
         <v>2022.0</v>
       </c>
       <c r="C394" t="n" s="2">
-        <v>44688.0</v>
+        <v>44681.0</v>
       </c>
       <c r="D394" t="n">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="395">
@@ -5658,10 +5658,10 @@
         <v>2022.0</v>
       </c>
       <c r="C395" t="n" s="2">
-        <v>44695.0</v>
+        <v>44688.0</v>
       </c>
       <c r="D395" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="396">
@@ -5672,10 +5672,10 @@
         <v>2022.0</v>
       </c>
       <c r="C396" t="n" s="2">
-        <v>44702.0</v>
+        <v>44695.0</v>
       </c>
       <c r="D396" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="397">
@@ -5686,10 +5686,10 @@
         <v>2022.0</v>
       </c>
       <c r="C397" t="n" s="2">
-        <v>44709.0</v>
+        <v>44702.0</v>
       </c>
       <c r="D397" t="n">
-        <v>8.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="398">
@@ -5700,10 +5700,10 @@
         <v>2022.0</v>
       </c>
       <c r="C398" t="n" s="2">
-        <v>44716.0</v>
+        <v>44709.0</v>
       </c>
       <c r="D398" t="n">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="399">
@@ -5714,10 +5714,10 @@
         <v>2022.0</v>
       </c>
       <c r="C399" t="n" s="2">
-        <v>44723.0</v>
+        <v>44716.0</v>
       </c>
       <c r="D399" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="400">
@@ -5728,10 +5728,10 @@
         <v>2022.0</v>
       </c>
       <c r="C400" t="n" s="2">
-        <v>44730.0</v>
+        <v>44723.0</v>
       </c>
       <c r="D400" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="401">
@@ -5742,7 +5742,7 @@
         <v>2022.0</v>
       </c>
       <c r="C401" t="n" s="2">
-        <v>44737.0</v>
+        <v>44730.0</v>
       </c>
       <c r="D401" t="n">
         <v>4.0</v>
@@ -5756,10 +5756,10 @@
         <v>2022.0</v>
       </c>
       <c r="C402" t="n" s="2">
-        <v>44744.0</v>
+        <v>44737.0</v>
       </c>
       <c r="D402" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="403">
@@ -5770,10 +5770,10 @@
         <v>2022.0</v>
       </c>
       <c r="C403" t="n" s="2">
-        <v>44751.0</v>
+        <v>44744.0</v>
       </c>
       <c r="D403" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="404">
@@ -5784,10 +5784,10 @@
         <v>2022.0</v>
       </c>
       <c r="C404" t="n" s="2">
-        <v>44758.0</v>
+        <v>44751.0</v>
       </c>
       <c r="D404" t="n">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="405">
@@ -5798,10 +5798,10 @@
         <v>2022.0</v>
       </c>
       <c r="C405" t="n" s="2">
-        <v>44765.0</v>
+        <v>44758.0</v>
       </c>
       <c r="D405" t="n">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="406">
@@ -5812,10 +5812,10 @@
         <v>2022.0</v>
       </c>
       <c r="C406" t="n" s="2">
-        <v>44779.0</v>
+        <v>44765.0</v>
       </c>
       <c r="D406" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="407">
@@ -5826,10 +5826,10 @@
         <v>2022.0</v>
       </c>
       <c r="C407" t="n" s="2">
-        <v>44786.0</v>
+        <v>44779.0</v>
       </c>
       <c r="D407" t="n">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="408">
@@ -5840,10 +5840,10 @@
         <v>2022.0</v>
       </c>
       <c r="C408" t="n" s="2">
-        <v>44863.0</v>
+        <v>44786.0</v>
       </c>
       <c r="D408" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="409">
@@ -5854,10 +5854,10 @@
         <v>2022.0</v>
       </c>
       <c r="C409" t="n" s="2">
-        <v>44870.0</v>
+        <v>44863.0</v>
       </c>
       <c r="D409" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="410">
@@ -5868,10 +5868,10 @@
         <v>2022.0</v>
       </c>
       <c r="C410" t="n" s="2">
-        <v>44884.0</v>
+        <v>44870.0</v>
       </c>
       <c r="D410" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="411">
@@ -5882,7 +5882,7 @@
         <v>2022.0</v>
       </c>
       <c r="C411" t="n" s="2">
-        <v>44891.0</v>
+        <v>44884.0</v>
       </c>
       <c r="D411" t="n">
         <v>2.0</v>
@@ -5896,10 +5896,10 @@
         <v>2022.0</v>
       </c>
       <c r="C412" t="n" s="2">
-        <v>44898.0</v>
+        <v>44891.0</v>
       </c>
       <c r="D412" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="413">
@@ -5910,10 +5910,10 @@
         <v>2022.0</v>
       </c>
       <c r="C413" t="n" s="2">
-        <v>44912.0</v>
+        <v>44898.0</v>
       </c>
       <c r="D413" t="n">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="414">
@@ -5924,10 +5924,10 @@
         <v>2022.0</v>
       </c>
       <c r="C414" t="n" s="2">
-        <v>44919.0</v>
+        <v>44912.0</v>
       </c>
       <c r="D414" t="n">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="415">
@@ -5938,10 +5938,10 @@
         <v>2022.0</v>
       </c>
       <c r="C415" t="n" s="2">
-        <v>44926.0</v>
+        <v>44919.0</v>
       </c>
       <c r="D415" t="n">
-        <v>12.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="416">
@@ -5949,13 +5949,13 @@
         <v>7</v>
       </c>
       <c r="B416" t="n">
-        <v>2023.0</v>
+        <v>2022.0</v>
       </c>
       <c r="C416" t="n" s="2">
-        <v>44934.0</v>
+        <v>44926.0</v>
       </c>
       <c r="D416" t="n">
-        <v>4.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="417">
@@ -5966,10 +5966,10 @@
         <v>2023.0</v>
       </c>
       <c r="C417" t="n" s="2">
-        <v>44941.0</v>
+        <v>44934.0</v>
       </c>
       <c r="D417" t="n">
-        <v>16.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="418">
@@ -5980,10 +5980,10 @@
         <v>2023.0</v>
       </c>
       <c r="C418" t="n" s="2">
-        <v>44948.0</v>
+        <v>44941.0</v>
       </c>
       <c r="D418" t="n">
-        <v>5.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="419">
@@ -5994,10 +5994,10 @@
         <v>2023.0</v>
       </c>
       <c r="C419" t="n" s="2">
-        <v>44955.0</v>
+        <v>44948.0</v>
       </c>
       <c r="D419" t="n">
-        <v>19.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="420">
@@ -6008,10 +6008,10 @@
         <v>2023.0</v>
       </c>
       <c r="C420" t="n" s="2">
-        <v>44962.0</v>
+        <v>44955.0</v>
       </c>
       <c r="D420" t="n">
-        <v>22.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="421">
@@ -6022,10 +6022,10 @@
         <v>2023.0</v>
       </c>
       <c r="C421" t="n" s="2">
-        <v>44969.0</v>
+        <v>44962.0</v>
       </c>
       <c r="D421" t="n">
-        <v>9.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="422">
@@ -6036,10 +6036,10 @@
         <v>2023.0</v>
       </c>
       <c r="C422" t="n" s="2">
-        <v>44976.0</v>
+        <v>44969.0</v>
       </c>
       <c r="D422" t="n">
-        <v>22.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="423">
@@ -6050,10 +6050,10 @@
         <v>2023.0</v>
       </c>
       <c r="C423" t="n" s="2">
-        <v>44983.0</v>
+        <v>44976.0</v>
       </c>
       <c r="D423" t="n">
-        <v>29.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="424">
@@ -6064,10 +6064,10 @@
         <v>2023.0</v>
       </c>
       <c r="C424" t="n" s="2">
-        <v>44990.0</v>
+        <v>44983.0</v>
       </c>
       <c r="D424" t="n">
-        <v>5.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="425">
@@ -6078,10 +6078,10 @@
         <v>2023.0</v>
       </c>
       <c r="C425" t="n" s="2">
-        <v>44997.0</v>
+        <v>44990.0</v>
       </c>
       <c r="D425" t="n">
-        <v>24.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="426">
@@ -6092,10 +6092,10 @@
         <v>2023.0</v>
       </c>
       <c r="C426" t="n" s="2">
-        <v>45004.0</v>
+        <v>44997.0</v>
       </c>
       <c r="D426" t="n">
-        <v>8.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="427">
@@ -6106,10 +6106,10 @@
         <v>2023.0</v>
       </c>
       <c r="C427" t="n" s="2">
-        <v>45011.0</v>
+        <v>45004.0</v>
       </c>
       <c r="D427" t="n">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="428">
@@ -6120,10 +6120,10 @@
         <v>2023.0</v>
       </c>
       <c r="C428" t="n" s="2">
-        <v>45018.0</v>
+        <v>45011.0</v>
       </c>
       <c r="D428" t="n">
-        <v>18.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="429">
@@ -6134,10 +6134,10 @@
         <v>2023.0</v>
       </c>
       <c r="C429" t="n" s="2">
-        <v>45025.0</v>
+        <v>45018.0</v>
       </c>
       <c r="D429" t="n">
-        <v>13.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="430">
@@ -6148,10 +6148,10 @@
         <v>2023.0</v>
       </c>
       <c r="C430" t="n" s="2">
-        <v>45032.0</v>
+        <v>45025.0</v>
       </c>
       <c r="D430" t="n">
-        <v>18.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="431">
@@ -6162,10 +6162,10 @@
         <v>2023.0</v>
       </c>
       <c r="C431" t="n" s="2">
-        <v>45039.0</v>
+        <v>45032.0</v>
       </c>
       <c r="D431" t="n">
-        <v>15.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="432">
@@ -6176,10 +6176,10 @@
         <v>2023.0</v>
       </c>
       <c r="C432" t="n" s="2">
-        <v>45046.0</v>
+        <v>45039.0</v>
       </c>
       <c r="D432" t="n">
-        <v>12.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="433">
@@ -6190,10 +6190,10 @@
         <v>2023.0</v>
       </c>
       <c r="C433" t="n" s="2">
-        <v>45053.0</v>
+        <v>45046.0</v>
       </c>
       <c r="D433" t="n">
-        <v>6.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="434">
@@ -6204,10 +6204,10 @@
         <v>2023.0</v>
       </c>
       <c r="C434" t="n" s="2">
-        <v>45060.0</v>
+        <v>45053.0</v>
       </c>
       <c r="D434" t="n">
-        <v>11.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="435">
@@ -6218,10 +6218,10 @@
         <v>2023.0</v>
       </c>
       <c r="C435" t="n" s="2">
-        <v>45067.0</v>
+        <v>45060.0</v>
       </c>
       <c r="D435" t="n">
-        <v>8.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="436">
@@ -6232,7 +6232,7 @@
         <v>2023.0</v>
       </c>
       <c r="C436" t="n" s="2">
-        <v>45074.0</v>
+        <v>45067.0</v>
       </c>
       <c r="D436" t="n">
         <v>8.0</v>
@@ -6246,10 +6246,10 @@
         <v>2023.0</v>
       </c>
       <c r="C437" t="n" s="2">
-        <v>45081.0</v>
+        <v>45074.0</v>
       </c>
       <c r="D437" t="n">
-        <v>5.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="438">
@@ -6260,10 +6260,10 @@
         <v>2023.0</v>
       </c>
       <c r="C438" t="n" s="2">
-        <v>45088.0</v>
+        <v>45081.0</v>
       </c>
       <c r="D438" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="439">
@@ -6274,10 +6274,10 @@
         <v>2023.0</v>
       </c>
       <c r="C439" t="n" s="2">
-        <v>45095.0</v>
+        <v>45088.0</v>
       </c>
       <c r="D439" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="440">
@@ -6288,10 +6288,10 @@
         <v>2023.0</v>
       </c>
       <c r="C440" t="n" s="2">
-        <v>45102.0</v>
+        <v>45095.0</v>
       </c>
       <c r="D440" t="n">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="441">
@@ -6302,10 +6302,10 @@
         <v>2023.0</v>
       </c>
       <c r="C441" t="n" s="2">
-        <v>45109.0</v>
+        <v>45102.0</v>
       </c>
       <c r="D441" t="n">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="442">
@@ -6316,10 +6316,10 @@
         <v>2023.0</v>
       </c>
       <c r="C442" t="n" s="2">
-        <v>45116.0</v>
+        <v>45109.0</v>
       </c>
       <c r="D442" t="n">
-        <v>3.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="443">
@@ -6330,10 +6330,10 @@
         <v>2023.0</v>
       </c>
       <c r="C443" t="n" s="2">
-        <v>45123.0</v>
+        <v>45116.0</v>
       </c>
       <c r="D443" t="n">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="444">
@@ -6344,7 +6344,7 @@
         <v>2023.0</v>
       </c>
       <c r="C444" t="n" s="2">
-        <v>45130.0</v>
+        <v>45123.0</v>
       </c>
       <c r="D444" t="n">
         <v>6.0</v>
@@ -6358,10 +6358,10 @@
         <v>2023.0</v>
       </c>
       <c r="C445" t="n" s="2">
-        <v>45137.0</v>
+        <v>45130.0</v>
       </c>
       <c r="D445" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="446">
@@ -6372,7 +6372,7 @@
         <v>2023.0</v>
       </c>
       <c r="C446" t="n" s="2">
-        <v>45144.0</v>
+        <v>45137.0</v>
       </c>
       <c r="D446" t="n">
         <v>2.0</v>
@@ -6386,7 +6386,7 @@
         <v>2023.0</v>
       </c>
       <c r="C447" t="n" s="2">
-        <v>45151.0</v>
+        <v>45144.0</v>
       </c>
       <c r="D447" t="n">
         <v>2.0</v>
@@ -6400,7 +6400,7 @@
         <v>2023.0</v>
       </c>
       <c r="C448" t="n" s="2">
-        <v>45165.0</v>
+        <v>45151.0</v>
       </c>
       <c r="D448" t="n">
         <v>2.0</v>
@@ -6414,7 +6414,7 @@
         <v>2023.0</v>
       </c>
       <c r="C449" t="n" s="2">
-        <v>45172.0</v>
+        <v>45165.0</v>
       </c>
       <c r="D449" t="n">
         <v>2.0</v>
@@ -6428,10 +6428,10 @@
         <v>2023.0</v>
       </c>
       <c r="C450" t="n" s="2">
-        <v>45179.0</v>
+        <v>45172.0</v>
       </c>
       <c r="D450" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="451">
@@ -6442,7 +6442,7 @@
         <v>2023.0</v>
       </c>
       <c r="C451" t="n" s="2">
-        <v>45186.0</v>
+        <v>45179.0</v>
       </c>
       <c r="D451" t="n">
         <v>1.0</v>
@@ -6456,7 +6456,7 @@
         <v>2023.0</v>
       </c>
       <c r="C452" t="n" s="2">
-        <v>45193.0</v>
+        <v>45186.0</v>
       </c>
       <c r="D452" t="n">
         <v>1.0</v>
@@ -6470,7 +6470,7 @@
         <v>2023.0</v>
       </c>
       <c r="C453" t="n" s="2">
-        <v>45200.0</v>
+        <v>45193.0</v>
       </c>
       <c r="D453" t="n">
         <v>1.0</v>
@@ -6484,7 +6484,7 @@
         <v>2023.0</v>
       </c>
       <c r="C454" t="n" s="2">
-        <v>45207.0</v>
+        <v>45200.0</v>
       </c>
       <c r="D454" t="n">
         <v>1.0</v>
@@ -6498,7 +6498,7 @@
         <v>2023.0</v>
       </c>
       <c r="C455" t="n" s="2">
-        <v>45235.0</v>
+        <v>45207.0</v>
       </c>
       <c r="D455" t="n">
         <v>1.0</v>
@@ -6512,10 +6512,10 @@
         <v>2023.0</v>
       </c>
       <c r="C456" t="n" s="2">
-        <v>45242.0</v>
+        <v>45235.0</v>
       </c>
       <c r="D456" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="457">
@@ -6526,10 +6526,10 @@
         <v>2023.0</v>
       </c>
       <c r="C457" t="n" s="2">
-        <v>45249.0</v>
+        <v>45242.0</v>
       </c>
       <c r="D457" t="n">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="458">
@@ -6540,10 +6540,10 @@
         <v>2023.0</v>
       </c>
       <c r="C458" t="n" s="2">
-        <v>45256.0</v>
+        <v>45249.0</v>
       </c>
       <c r="D458" t="n">
-        <v>9.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="459">
@@ -6554,10 +6554,10 @@
         <v>2023.0</v>
       </c>
       <c r="C459" t="n" s="2">
-        <v>45263.0</v>
+        <v>45256.0</v>
       </c>
       <c r="D459" t="n">
-        <v>12.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="460">
@@ -6568,10 +6568,10 @@
         <v>2023.0</v>
       </c>
       <c r="C460" t="n" s="2">
-        <v>45270.0</v>
+        <v>45263.0</v>
       </c>
       <c r="D460" t="n">
-        <v>6.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="461">
@@ -6582,10 +6582,10 @@
         <v>2023.0</v>
       </c>
       <c r="C461" t="n" s="2">
-        <v>45277.0</v>
+        <v>45270.0</v>
       </c>
       <c r="D461" t="n">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="462">
@@ -6596,7 +6596,7 @@
         <v>2023.0</v>
       </c>
       <c r="C462" t="n" s="2">
-        <v>45284.0</v>
+        <v>45277.0</v>
       </c>
       <c r="D462" t="n">
         <v>7.0</v>
@@ -6610,10 +6610,10 @@
         <v>2023.0</v>
       </c>
       <c r="C463" t="n" s="2">
-        <v>45291.0</v>
+        <v>45284.0</v>
       </c>
       <c r="D463" t="n">
-        <v>13.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="464">
@@ -6621,13 +6621,13 @@
         <v>7</v>
       </c>
       <c r="B464" t="n">
-        <v>2024.0</v>
+        <v>2023.0</v>
       </c>
       <c r="C464" t="n" s="2">
-        <v>45299.0</v>
+        <v>45291.0</v>
       </c>
       <c r="D464" t="n">
-        <v>6.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="465">
@@ -6638,10 +6638,10 @@
         <v>2024.0</v>
       </c>
       <c r="C465" t="n" s="2">
-        <v>45306.0</v>
+        <v>45299.0</v>
       </c>
       <c r="D465" t="n">
-        <v>11.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="466">
@@ -6652,10 +6652,10 @@
         <v>2024.0</v>
       </c>
       <c r="C466" t="n" s="2">
-        <v>45313.0</v>
+        <v>45306.0</v>
       </c>
       <c r="D466" t="n">
-        <v>5.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="467">
@@ -6666,10 +6666,10 @@
         <v>2024.0</v>
       </c>
       <c r="C467" t="n" s="2">
-        <v>45320.0</v>
+        <v>45313.0</v>
       </c>
       <c r="D467" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="468">
@@ -6680,10 +6680,10 @@
         <v>2024.0</v>
       </c>
       <c r="C468" t="n" s="2">
-        <v>45327.0</v>
+        <v>45320.0</v>
       </c>
       <c r="D468" t="n">
-        <v>9.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="469">
@@ -6694,10 +6694,10 @@
         <v>2024.0</v>
       </c>
       <c r="C469" t="n" s="2">
-        <v>45334.0</v>
+        <v>45327.0</v>
       </c>
       <c r="D469" t="n">
-        <v>3.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="470">
@@ -6708,10 +6708,10 @@
         <v>2024.0</v>
       </c>
       <c r="C470" t="n" s="2">
-        <v>45341.0</v>
+        <v>45334.0</v>
       </c>
       <c r="D470" t="n">
-        <v>21.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="471">
@@ -6722,10 +6722,10 @@
         <v>2024.0</v>
       </c>
       <c r="C471" t="n" s="2">
-        <v>45348.0</v>
+        <v>45341.0</v>
       </c>
       <c r="D471" t="n">
-        <v>1.0</v>
+        <v>21.0</v>
       </c>
     </row>
     <row r="472">
@@ -6736,10 +6736,10 @@
         <v>2024.0</v>
       </c>
       <c r="C472" t="n" s="2">
-        <v>45355.0</v>
+        <v>45348.0</v>
       </c>
       <c r="D472" t="n">
-        <v>9.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="473">
@@ -6750,10 +6750,10 @@
         <v>2024.0</v>
       </c>
       <c r="C473" t="n" s="2">
-        <v>45362.0</v>
+        <v>45355.0</v>
       </c>
       <c r="D473" t="n">
-        <v>4.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="474">
@@ -6764,10 +6764,10 @@
         <v>2024.0</v>
       </c>
       <c r="C474" t="n" s="2">
-        <v>45369.0</v>
+        <v>45362.0</v>
       </c>
       <c r="D474" t="n">
-        <v>14.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="475">
@@ -6778,10 +6778,10 @@
         <v>2024.0</v>
       </c>
       <c r="C475" t="n" s="2">
-        <v>45376.0</v>
+        <v>45369.0</v>
       </c>
       <c r="D475" t="n">
-        <v>4.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="476">
@@ -6792,10 +6792,10 @@
         <v>2024.0</v>
       </c>
       <c r="C476" t="n" s="2">
-        <v>45383.0</v>
+        <v>45376.0</v>
       </c>
       <c r="D476" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="477">
@@ -6806,10 +6806,10 @@
         <v>2024.0</v>
       </c>
       <c r="C477" t="n" s="2">
-        <v>45390.0</v>
+        <v>45383.0</v>
       </c>
       <c r="D477" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="478">
@@ -6820,7 +6820,7 @@
         <v>2024.0</v>
       </c>
       <c r="C478" t="n" s="2">
-        <v>45397.0</v>
+        <v>45390.0</v>
       </c>
       <c r="D478" t="n">
         <v>1.0</v>
@@ -6834,10 +6834,10 @@
         <v>2024.0</v>
       </c>
       <c r="C479" t="n" s="2">
-        <v>45404.0</v>
+        <v>45397.0</v>
       </c>
       <c r="D479" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="480">
@@ -6848,10 +6848,10 @@
         <v>2024.0</v>
       </c>
       <c r="C480" t="n" s="2">
-        <v>45411.0</v>
+        <v>45404.0</v>
       </c>
       <c r="D480" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="481">
@@ -6862,10 +6862,10 @@
         <v>2024.0</v>
       </c>
       <c r="C481" t="n" s="2">
-        <v>45439.0</v>
+        <v>45411.0</v>
       </c>
       <c r="D481" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="482">
@@ -6876,10 +6876,10 @@
         <v>2024.0</v>
       </c>
       <c r="C482" t="n" s="2">
-        <v>45446.0</v>
+        <v>45439.0</v>
       </c>
       <c r="D482" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="483">
@@ -6890,7 +6890,7 @@
         <v>2024.0</v>
       </c>
       <c r="C483" t="n" s="2">
-        <v>45460.0</v>
+        <v>45446.0</v>
       </c>
       <c r="D483" t="n">
         <v>1.0</v>
@@ -6904,7 +6904,7 @@
         <v>2024.0</v>
       </c>
       <c r="C484" t="n" s="2">
-        <v>45481.0</v>
+        <v>45460.0</v>
       </c>
       <c r="D484" t="n">
         <v>1.0</v>
@@ -6918,7 +6918,7 @@
         <v>2024.0</v>
       </c>
       <c r="C485" t="n" s="2">
-        <v>45516.0</v>
+        <v>45481.0</v>
       </c>
       <c r="D485" t="n">
         <v>1.0</v>
@@ -6932,7 +6932,7 @@
         <v>2024.0</v>
       </c>
       <c r="C486" t="n" s="2">
-        <v>45551.0</v>
+        <v>45516.0</v>
       </c>
       <c r="D486" t="n">
         <v>1.0</v>
@@ -6946,7 +6946,7 @@
         <v>2024.0</v>
       </c>
       <c r="C487" t="n" s="2">
-        <v>45579.0</v>
+        <v>45551.0</v>
       </c>
       <c r="D487" t="n">
         <v>1.0</v>
@@ -6960,7 +6960,7 @@
         <v>2024.0</v>
       </c>
       <c r="C488" t="n" s="2">
-        <v>45614.0</v>
+        <v>45579.0</v>
       </c>
       <c r="D488" t="n">
         <v>1.0</v>
@@ -6974,10 +6974,10 @@
         <v>2024.0</v>
       </c>
       <c r="C489" t="n" s="2">
-        <v>45635.0</v>
+        <v>45614.0</v>
       </c>
       <c r="D489" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="490">
@@ -6988,10 +6988,10 @@
         <v>2024.0</v>
       </c>
       <c r="C490" t="n" s="2">
-        <v>45642.0</v>
+        <v>45635.0</v>
       </c>
       <c r="D490" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="491">
@@ -7002,10 +7002,10 @@
         <v>2024.0</v>
       </c>
       <c r="C491" t="n" s="2">
-        <v>45649.0</v>
+        <v>45642.0</v>
       </c>
       <c r="D491" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="492">
@@ -7016,10 +7016,10 @@
         <v>2024.0</v>
       </c>
       <c r="C492" t="n" s="2">
-        <v>45656.0</v>
+        <v>45649.0</v>
       </c>
       <c r="D492" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="493">
@@ -7027,13 +7027,13 @@
         <v>7</v>
       </c>
       <c r="B493" t="n">
-        <v>2025.0</v>
+        <v>2024.0</v>
       </c>
       <c r="C493" t="n" s="2">
-        <v>45665.0</v>
+        <v>45656.0</v>
       </c>
       <c r="D493" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="494">
@@ -7044,10 +7044,10 @@
         <v>2025.0</v>
       </c>
       <c r="C494" t="n" s="2">
-        <v>45672.0</v>
+        <v>45665.0</v>
       </c>
       <c r="D494" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="495">
@@ -7058,7 +7058,7 @@
         <v>2025.0</v>
       </c>
       <c r="C495" t="n" s="2">
-        <v>45686.0</v>
+        <v>45672.0</v>
       </c>
       <c r="D495" t="n">
         <v>2.0</v>
@@ -7072,10 +7072,10 @@
         <v>2025.0</v>
       </c>
       <c r="C496" t="n" s="2">
-        <v>45693.0</v>
+        <v>45686.0</v>
       </c>
       <c r="D496" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="497">
@@ -7086,10 +7086,10 @@
         <v>2025.0</v>
       </c>
       <c r="C497" t="n" s="2">
-        <v>45700.0</v>
+        <v>45693.0</v>
       </c>
       <c r="D497" t="n">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="498">
@@ -7100,10 +7100,10 @@
         <v>2025.0</v>
       </c>
       <c r="C498" t="n" s="2">
-        <v>45707.0</v>
+        <v>45700.0</v>
       </c>
       <c r="D498" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="499">
@@ -7114,10 +7114,10 @@
         <v>2025.0</v>
       </c>
       <c r="C499" t="n" s="2">
-        <v>45714.0</v>
+        <v>45707.0</v>
       </c>
       <c r="D499" t="n">
-        <v>8.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="500">
@@ -7128,10 +7128,10 @@
         <v>2025.0</v>
       </c>
       <c r="C500" t="n" s="2">
-        <v>45721.0</v>
+        <v>45714.0</v>
       </c>
       <c r="D500" t="n">
-        <v>11.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="501">
@@ -7142,10 +7142,10 @@
         <v>2025.0</v>
       </c>
       <c r="C501" t="n" s="2">
-        <v>45728.0</v>
+        <v>45721.0</v>
       </c>
       <c r="D501" t="n">
-        <v>6.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="502">
@@ -7156,10 +7156,10 @@
         <v>2025.0</v>
       </c>
       <c r="C502" t="n" s="2">
-        <v>45735.0</v>
+        <v>45728.0</v>
       </c>
       <c r="D502" t="n">
-        <v>19.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="503">
@@ -7170,10 +7170,10 @@
         <v>2025.0</v>
       </c>
       <c r="C503" t="n" s="2">
-        <v>45742.0</v>
+        <v>45735.0</v>
       </c>
       <c r="D503" t="n">
-        <v>17.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="504">
@@ -7184,10 +7184,10 @@
         <v>2025.0</v>
       </c>
       <c r="C504" t="n" s="2">
-        <v>45749.0</v>
+        <v>45742.0</v>
       </c>
       <c r="D504" t="n">
-        <v>5.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="505">
@@ -7198,10 +7198,10 @@
         <v>2025.0</v>
       </c>
       <c r="C505" t="n" s="2">
-        <v>45756.0</v>
+        <v>45749.0</v>
       </c>
       <c r="D505" t="n">
-        <v>9.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="506">
@@ -7212,10 +7212,10 @@
         <v>2025.0</v>
       </c>
       <c r="C506" t="n" s="2">
-        <v>45763.0</v>
+        <v>45756.0</v>
       </c>
       <c r="D506" t="n">
-        <v>1.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="507">
@@ -7226,7 +7226,7 @@
         <v>2025.0</v>
       </c>
       <c r="C507" t="n" s="2">
-        <v>45770.0</v>
+        <v>45763.0</v>
       </c>
       <c r="D507" t="n">
         <v>1.0</v>
@@ -7240,10 +7240,10 @@
         <v>2025.0</v>
       </c>
       <c r="C508" t="n" s="2">
-        <v>45784.0</v>
+        <v>45770.0</v>
       </c>
       <c r="D508" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="509">
@@ -7254,10 +7254,10 @@
         <v>2025.0</v>
       </c>
       <c r="C509" t="n" s="2">
-        <v>45791.0</v>
+        <v>45784.0</v>
       </c>
       <c r="D509" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="510">
@@ -7268,10 +7268,10 @@
         <v>2025.0</v>
       </c>
       <c r="C510" t="n" s="2">
-        <v>45805.0</v>
+        <v>45791.0</v>
       </c>
       <c r="D510" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="511">
@@ -7282,10 +7282,10 @@
         <v>2025.0</v>
       </c>
       <c r="C511" t="n" s="2">
-        <v>45826.0</v>
+        <v>45805.0</v>
       </c>
       <c r="D511" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="512">
@@ -7296,7 +7296,7 @@
         <v>2025.0</v>
       </c>
       <c r="C512" t="n" s="2">
-        <v>45861.0</v>
+        <v>45826.0</v>
       </c>
       <c r="D512" t="n">
         <v>2.0</v>
@@ -7310,10 +7310,10 @@
         <v>2025.0</v>
       </c>
       <c r="C513" t="n" s="2">
-        <v>45868.0</v>
+        <v>45861.0</v>
       </c>
       <c r="D513" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="514">
@@ -7324,7 +7324,7 @@
         <v>2025.0</v>
       </c>
       <c r="C514" t="n" s="2">
-        <v>45889.0</v>
+        <v>45868.0</v>
       </c>
       <c r="D514" t="n">
         <v>1.0</v>
@@ -7338,7 +7338,7 @@
         <v>2025.0</v>
       </c>
       <c r="C515" t="n" s="2">
-        <v>45924.0</v>
+        <v>45889.0</v>
       </c>
       <c r="D515" t="n">
         <v>1.0</v>
@@ -7352,7 +7352,7 @@
         <v>2025.0</v>
       </c>
       <c r="C516" t="n" s="2">
-        <v>45945.0</v>
+        <v>45924.0</v>
       </c>
       <c r="D516" t="n">
         <v>1.0</v>
@@ -7366,10 +7366,10 @@
         <v>2025.0</v>
       </c>
       <c r="C517" t="n" s="2">
-        <v>45959.0</v>
+        <v>45945.0</v>
       </c>
       <c r="D517" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="518">
@@ -7380,7 +7380,7 @@
         <v>2025.0</v>
       </c>
       <c r="C518" t="n" s="2">
-        <v>46001.0</v>
+        <v>45959.0</v>
       </c>
       <c r="D518" t="n">
         <v>2.0</v>
@@ -7394,10 +7394,10 @@
         <v>2025.0</v>
       </c>
       <c r="C519" t="n" s="2">
-        <v>46008.0</v>
+        <v>46001.0</v>
       </c>
       <c r="D519" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="520">
@@ -7408,7 +7408,7 @@
         <v>2025.0</v>
       </c>
       <c r="C520" t="n" s="2">
-        <v>46022.0</v>
+        <v>46008.0</v>
       </c>
       <c r="D520" t="n">
         <v>1.0</v>
@@ -7419,10 +7419,10 @@
         <v>7</v>
       </c>
       <c r="B521" t="n">
-        <v>2026.0</v>
+        <v>2025.0</v>
       </c>
       <c r="C521" t="n" s="2">
-        <v>46030.0</v>
+        <v>46022.0</v>
       </c>
       <c r="D521" t="n">
         <v>1.0</v>
@@ -7436,7 +7436,7 @@
         <v>2026.0</v>
       </c>
       <c r="C522" t="n" s="2">
-        <v>46051.0</v>
+        <v>46030.0</v>
       </c>
       <c r="D522" t="n">
         <v>1.0</v>
@@ -7450,7 +7450,7 @@
         <v>2026.0</v>
       </c>
       <c r="C523" t="n" s="2">
-        <v>46058.0</v>
+        <v>46051.0</v>
       </c>
       <c r="D523" t="n">
         <v>1.0</v>
@@ -7464,10 +7464,10 @@
         <v>2026.0</v>
       </c>
       <c r="C524" t="n" s="2">
-        <v>46065.0</v>
+        <v>46058.0</v>
       </c>
       <c r="D524" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="525">
@@ -7478,10 +7478,10 @@
         <v>2026.0</v>
       </c>
       <c r="C525" t="n" s="2">
-        <v>46135.0</v>
+        <v>46065.0</v>
       </c>
       <c r="D525" t="n">
-        <v>8.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="526">
@@ -7492,10 +7492,10 @@
         <v>2026.0</v>
       </c>
       <c r="C526" t="n" s="2">
-        <v>46156.0</v>
+        <v>46135.0</v>
       </c>
       <c r="D526" t="n">
-        <v>1.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="527">
@@ -7506,24 +7506,24 @@
         <v>2026.0</v>
       </c>
       <c r="C527" t="n" s="2">
-        <v>46163.0</v>
+        <v>46156.0</v>
       </c>
       <c r="D527" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B528" t="n">
-        <v>2024.0</v>
+        <v>2026.0</v>
       </c>
       <c r="C528" t="n" s="2">
-        <v>45495.0</v>
+        <v>46163.0</v>
       </c>
       <c r="D528" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="529">
@@ -7534,10 +7534,10 @@
         <v>2024.0</v>
       </c>
       <c r="C529" t="n" s="2">
-        <v>45502.0</v>
+        <v>45495.0</v>
       </c>
       <c r="D529" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="530">
@@ -7545,13 +7545,13 @@
         <v>8</v>
       </c>
       <c r="B530" t="n">
-        <v>2025.0</v>
+        <v>2024.0</v>
       </c>
       <c r="C530" t="n" s="2">
-        <v>45665.0</v>
+        <v>45502.0</v>
       </c>
       <c r="D530" t="n">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="531">
@@ -7562,10 +7562,10 @@
         <v>2025.0</v>
       </c>
       <c r="C531" t="n" s="2">
-        <v>45672.0</v>
+        <v>45665.0</v>
       </c>
       <c r="D531" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="532">
@@ -7576,10 +7576,10 @@
         <v>2025.0</v>
       </c>
       <c r="C532" t="n" s="2">
-        <v>45679.0</v>
+        <v>45672.0</v>
       </c>
       <c r="D532" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="533">
@@ -7590,10 +7590,10 @@
         <v>2025.0</v>
       </c>
       <c r="C533" t="n" s="2">
-        <v>45686.0</v>
+        <v>45679.0</v>
       </c>
       <c r="D533" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="534">
@@ -7604,10 +7604,10 @@
         <v>2025.0</v>
       </c>
       <c r="C534" t="n" s="2">
-        <v>45693.0</v>
+        <v>45686.0</v>
       </c>
       <c r="D534" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="535">
@@ -7618,10 +7618,10 @@
         <v>2025.0</v>
       </c>
       <c r="C535" t="n" s="2">
-        <v>45700.0</v>
+        <v>45693.0</v>
       </c>
       <c r="D535" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="536">
@@ -7632,10 +7632,10 @@
         <v>2025.0</v>
       </c>
       <c r="C536" t="n" s="2">
-        <v>45707.0</v>
+        <v>45700.0</v>
       </c>
       <c r="D536" t="n">
-        <v>7.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="537">
@@ -7646,10 +7646,10 @@
         <v>2025.0</v>
       </c>
       <c r="C537" t="n" s="2">
-        <v>45714.0</v>
+        <v>45707.0</v>
       </c>
       <c r="D537" t="n">
-        <v>3.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="538">
@@ -7660,10 +7660,10 @@
         <v>2025.0</v>
       </c>
       <c r="C538" t="n" s="2">
-        <v>45721.0</v>
+        <v>45714.0</v>
       </c>
       <c r="D538" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="539">
@@ -7674,10 +7674,10 @@
         <v>2025.0</v>
       </c>
       <c r="C539" t="n" s="2">
-        <v>45728.0</v>
+        <v>45721.0</v>
       </c>
       <c r="D539" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="540">
@@ -7688,7 +7688,7 @@
         <v>2025.0</v>
       </c>
       <c r="C540" t="n" s="2">
-        <v>45742.0</v>
+        <v>45728.0</v>
       </c>
       <c r="D540" t="n">
         <v>1.0</v>
@@ -7702,7 +7702,7 @@
         <v>2025.0</v>
       </c>
       <c r="C541" t="n" s="2">
-        <v>45749.0</v>
+        <v>45742.0</v>
       </c>
       <c r="D541" t="n">
         <v>1.0</v>
@@ -7716,7 +7716,7 @@
         <v>2025.0</v>
       </c>
       <c r="C542" t="n" s="2">
-        <v>45763.0</v>
+        <v>45749.0</v>
       </c>
       <c r="D542" t="n">
         <v>1.0</v>
@@ -7730,10 +7730,10 @@
         <v>2025.0</v>
       </c>
       <c r="C543" t="n" s="2">
-        <v>45777.0</v>
+        <v>45763.0</v>
       </c>
       <c r="D543" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="544">
@@ -7744,10 +7744,10 @@
         <v>2025.0</v>
       </c>
       <c r="C544" t="n" s="2">
-        <v>45784.0</v>
+        <v>45777.0</v>
       </c>
       <c r="D544" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="545">
@@ -7758,7 +7758,7 @@
         <v>2025.0</v>
       </c>
       <c r="C545" t="n" s="2">
-        <v>45798.0</v>
+        <v>45784.0</v>
       </c>
       <c r="D545" t="n">
         <v>1.0</v>
@@ -7772,7 +7772,7 @@
         <v>2025.0</v>
       </c>
       <c r="C546" t="n" s="2">
-        <v>45805.0</v>
+        <v>45798.0</v>
       </c>
       <c r="D546" t="n">
         <v>1.0</v>
@@ -7786,10 +7786,10 @@
         <v>2025.0</v>
       </c>
       <c r="C547" t="n" s="2">
-        <v>45812.0</v>
+        <v>45805.0</v>
       </c>
       <c r="D547" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="548">
@@ -7800,7 +7800,7 @@
         <v>2025.0</v>
       </c>
       <c r="C548" t="n" s="2">
-        <v>45819.0</v>
+        <v>45812.0</v>
       </c>
       <c r="D548" t="n">
         <v>2.0</v>
@@ -7814,7 +7814,7 @@
         <v>2025.0</v>
       </c>
       <c r="C549" t="n" s="2">
-        <v>45833.0</v>
+        <v>45819.0</v>
       </c>
       <c r="D549" t="n">
         <v>2.0</v>
@@ -7828,10 +7828,10 @@
         <v>2025.0</v>
       </c>
       <c r="C550" t="n" s="2">
-        <v>45847.0</v>
+        <v>45833.0</v>
       </c>
       <c r="D550" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="551">
@@ -7842,10 +7842,10 @@
         <v>2025.0</v>
       </c>
       <c r="C551" t="n" s="2">
-        <v>45854.0</v>
+        <v>45847.0</v>
       </c>
       <c r="D551" t="n">
-        <v>8.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="552">
@@ -7856,10 +7856,10 @@
         <v>2025.0</v>
       </c>
       <c r="C552" t="n" s="2">
-        <v>45861.0</v>
+        <v>45854.0</v>
       </c>
       <c r="D552" t="n">
-        <v>12.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="553">
@@ -7870,10 +7870,10 @@
         <v>2025.0</v>
       </c>
       <c r="C553" t="n" s="2">
-        <v>45868.0</v>
+        <v>45861.0</v>
       </c>
       <c r="D553" t="n">
-        <v>6.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="554">
@@ -7884,10 +7884,10 @@
         <v>2025.0</v>
       </c>
       <c r="C554" t="n" s="2">
-        <v>45875.0</v>
+        <v>45868.0</v>
       </c>
       <c r="D554" t="n">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="555">
@@ -7898,7 +7898,7 @@
         <v>2025.0</v>
       </c>
       <c r="C555" t="n" s="2">
-        <v>45896.0</v>
+        <v>45875.0</v>
       </c>
       <c r="D555" t="n">
         <v>1.0</v>
@@ -7912,7 +7912,7 @@
         <v>2025.0</v>
       </c>
       <c r="C556" t="n" s="2">
-        <v>45903.0</v>
+        <v>45896.0</v>
       </c>
       <c r="D556" t="n">
         <v>1.0</v>
@@ -7926,7 +7926,7 @@
         <v>2025.0</v>
       </c>
       <c r="C557" t="n" s="2">
-        <v>45931.0</v>
+        <v>45903.0</v>
       </c>
       <c r="D557" t="n">
         <v>1.0</v>
@@ -7940,10 +7940,10 @@
         <v>2025.0</v>
       </c>
       <c r="C558" t="n" s="2">
-        <v>45938.0</v>
+        <v>45931.0</v>
       </c>
       <c r="D558" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="559">
@@ -7954,10 +7954,10 @@
         <v>2025.0</v>
       </c>
       <c r="C559" t="n" s="2">
-        <v>45945.0</v>
+        <v>45938.0</v>
       </c>
       <c r="D559" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="560">
@@ -7968,7 +7968,7 @@
         <v>2025.0</v>
       </c>
       <c r="C560" t="n" s="2">
-        <v>45966.0</v>
+        <v>45945.0</v>
       </c>
       <c r="D560" t="n">
         <v>2.0</v>
@@ -7982,10 +7982,10 @@
         <v>2025.0</v>
       </c>
       <c r="C561" t="n" s="2">
-        <v>45973.0</v>
+        <v>45966.0</v>
       </c>
       <c r="D561" t="n">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="562">
@@ -7996,10 +7996,10 @@
         <v>2025.0</v>
       </c>
       <c r="C562" t="n" s="2">
-        <v>45980.0</v>
+        <v>45973.0</v>
       </c>
       <c r="D562" t="n">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="563">
@@ -8010,10 +8010,10 @@
         <v>2025.0</v>
       </c>
       <c r="C563" t="n" s="2">
-        <v>45987.0</v>
+        <v>45980.0</v>
       </c>
       <c r="D563" t="n">
-        <v>20.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="564">
@@ -8024,10 +8024,10 @@
         <v>2025.0</v>
       </c>
       <c r="C564" t="n" s="2">
-        <v>45994.0</v>
+        <v>45987.0</v>
       </c>
       <c r="D564" t="n">
-        <v>5.0</v>
+        <v>20.0</v>
       </c>
     </row>
     <row r="565">
@@ -8038,10 +8038,10 @@
         <v>2025.0</v>
       </c>
       <c r="C565" t="n" s="2">
-        <v>46001.0</v>
+        <v>45994.0</v>
       </c>
       <c r="D565" t="n">
-        <v>8.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="566">
@@ -8052,10 +8052,10 @@
         <v>2025.0</v>
       </c>
       <c r="C566" t="n" s="2">
-        <v>46008.0</v>
+        <v>46001.0</v>
       </c>
       <c r="D566" t="n">
-        <v>24.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="567">
@@ -8066,10 +8066,10 @@
         <v>2025.0</v>
       </c>
       <c r="C567" t="n" s="2">
-        <v>46015.0</v>
+        <v>46008.0</v>
       </c>
       <c r="D567" t="n">
-        <v>13.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="568">
@@ -8080,10 +8080,10 @@
         <v>2025.0</v>
       </c>
       <c r="C568" t="n" s="2">
-        <v>46022.0</v>
+        <v>46015.0</v>
       </c>
       <c r="D568" t="n">
-        <v>8.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="569">
@@ -8094,10 +8094,10 @@
         <v>2025.0</v>
       </c>
       <c r="C569" t="n" s="2">
-        <v>46029.0</v>
+        <v>46022.0</v>
       </c>
       <c r="D569" t="n">
-        <v>3.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="570">
@@ -8105,13 +8105,13 @@
         <v>8</v>
       </c>
       <c r="B570" t="n">
-        <v>2026.0</v>
+        <v>2025.0</v>
       </c>
       <c r="C570" t="n" s="2">
-        <v>46030.0</v>
+        <v>46029.0</v>
       </c>
       <c r="D570" t="n">
-        <v>24.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="571">
@@ -8122,10 +8122,10 @@
         <v>2026.0</v>
       </c>
       <c r="C571" t="n" s="2">
-        <v>46037.0</v>
+        <v>46030.0</v>
       </c>
       <c r="D571" t="n">
-        <v>22.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="572">
@@ -8136,10 +8136,10 @@
         <v>2026.0</v>
       </c>
       <c r="C572" t="n" s="2">
-        <v>46044.0</v>
+        <v>46037.0</v>
       </c>
       <c r="D572" t="n">
-        <v>27.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="573">
@@ -8150,10 +8150,10 @@
         <v>2026.0</v>
       </c>
       <c r="C573" t="n" s="2">
-        <v>46051.0</v>
+        <v>46044.0</v>
       </c>
       <c r="D573" t="n">
-        <v>18.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="574">
@@ -8164,10 +8164,10 @@
         <v>2026.0</v>
       </c>
       <c r="C574" t="n" s="2">
-        <v>46058.0</v>
+        <v>46051.0</v>
       </c>
       <c r="D574" t="n">
-        <v>25.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="575">
@@ -8178,10 +8178,10 @@
         <v>2026.0</v>
       </c>
       <c r="C575" t="n" s="2">
-        <v>46065.0</v>
+        <v>46058.0</v>
       </c>
       <c r="D575" t="n">
-        <v>22.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="576">
@@ -8192,10 +8192,10 @@
         <v>2026.0</v>
       </c>
       <c r="C576" t="n" s="2">
-        <v>46072.0</v>
+        <v>46065.0</v>
       </c>
       <c r="D576" t="n">
-        <v>13.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="577">
@@ -8206,10 +8206,10 @@
         <v>2026.0</v>
       </c>
       <c r="C577" t="n" s="2">
-        <v>46079.0</v>
+        <v>46072.0</v>
       </c>
       <c r="D577" t="n">
-        <v>24.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="578">
@@ -8220,10 +8220,10 @@
         <v>2026.0</v>
       </c>
       <c r="C578" t="n" s="2">
-        <v>46086.0</v>
+        <v>46079.0</v>
       </c>
       <c r="D578" t="n">
-        <v>26.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="579">
@@ -8234,10 +8234,10 @@
         <v>2026.0</v>
       </c>
       <c r="C579" t="n" s="2">
-        <v>46093.0</v>
+        <v>46086.0</v>
       </c>
       <c r="D579" t="n">
-        <v>33.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="580">
@@ -8248,10 +8248,10 @@
         <v>2026.0</v>
       </c>
       <c r="C580" t="n" s="2">
-        <v>46100.0</v>
+        <v>46093.0</v>
       </c>
       <c r="D580" t="n">
-        <v>25.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="581">
@@ -8262,10 +8262,10 @@
         <v>2026.0</v>
       </c>
       <c r="C581" t="n" s="2">
-        <v>46107.0</v>
+        <v>46100.0</v>
       </c>
       <c r="D581" t="n">
-        <v>31.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="582">
@@ -8276,10 +8276,10 @@
         <v>2026.0</v>
       </c>
       <c r="C582" t="n" s="2">
-        <v>46114.0</v>
+        <v>46107.0</v>
       </c>
       <c r="D582" t="n">
-        <v>10.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="583">
@@ -8290,10 +8290,10 @@
         <v>2026.0</v>
       </c>
       <c r="C583" t="n" s="2">
-        <v>46121.0</v>
+        <v>46114.0</v>
       </c>
       <c r="D583" t="n">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="584">
@@ -8304,10 +8304,10 @@
         <v>2026.0</v>
       </c>
       <c r="C584" t="n" s="2">
-        <v>46128.0</v>
+        <v>46121.0</v>
       </c>
       <c r="D584" t="n">
-        <v>15.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="585">
@@ -8318,10 +8318,10 @@
         <v>2026.0</v>
       </c>
       <c r="C585" t="n" s="2">
-        <v>46135.0</v>
+        <v>46128.0</v>
       </c>
       <c r="D585" t="n">
-        <v>35.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="586">
@@ -8332,10 +8332,10 @@
         <v>2026.0</v>
       </c>
       <c r="C586" t="n" s="2">
-        <v>46142.0</v>
+        <v>46135.0</v>
       </c>
       <c r="D586" t="n">
-        <v>22.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="587">
@@ -8346,10 +8346,10 @@
         <v>2026.0</v>
       </c>
       <c r="C587" t="n" s="2">
-        <v>46149.0</v>
+        <v>46142.0</v>
       </c>
       <c r="D587" t="n">
-        <v>6.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="588">
@@ -8360,10 +8360,10 @@
         <v>2026.0</v>
       </c>
       <c r="C588" t="n" s="2">
-        <v>46156.0</v>
+        <v>46149.0</v>
       </c>
       <c r="D588" t="n">
-        <v>27.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="589">
@@ -8374,10 +8374,10 @@
         <v>2026.0</v>
       </c>
       <c r="C589" t="n" s="2">
-        <v>46163.0</v>
+        <v>46156.0</v>
       </c>
       <c r="D589" t="n">
-        <v>13.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="590">
@@ -8388,10 +8388,10 @@
         <v>2026.0</v>
       </c>
       <c r="C590" t="n" s="2">
-        <v>46170.0</v>
+        <v>46163.0</v>
       </c>
       <c r="D590" t="n">
-        <v>21.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="591">
@@ -8402,9 +8402,23 @@
         <v>2026.0</v>
       </c>
       <c r="C591" t="n" s="2">
+        <v>46170.0</v>
+      </c>
+      <c r="D591" t="n">
+        <v>21.0</v>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="s">
+        <v>8</v>
+      </c>
+      <c r="B592" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C592" t="n" s="2">
         <v>46177.0</v>
       </c>
-      <c r="D591" t="n">
+      <c r="D592" t="n">
         <v>1.0</v>
       </c>
     </row>
@@ -8447,7 +8461,7 @@
         <v>12</v>
       </c>
       <c r="B4" t="n">
-        <v>1309.0</v>
+        <v>1313.0</v>
       </c>
     </row>
     <row r="5">
@@ -8455,7 +8469,7 @@
         <v>13</v>
       </c>
       <c r="B5" t="n">
-        <v>2159.0</v>
+        <v>2160.0</v>
       </c>
     </row>
   </sheetData>
@@ -8498,7 +8512,7 @@
         <v>22</v>
       </c>
       <c r="C3" t="n">
-        <v>189.0</v>
+        <v>190.0</v>
       </c>
     </row>
     <row r="4">
@@ -8531,7 +8545,7 @@
         <v>22</v>
       </c>
       <c r="C6" t="n">
-        <v>308.0</v>
+        <v>309.0</v>
       </c>
     </row>
     <row r="7">
@@ -8553,7 +8567,7 @@
         <v>21</v>
       </c>
       <c r="C8" t="n">
-        <v>354.0</v>
+        <v>355.0</v>
       </c>
     </row>
     <row r="9">
@@ -8575,7 +8589,7 @@
         <v>19</v>
       </c>
       <c r="C10" t="n">
-        <v>146.0</v>
+        <v>148.0</v>
       </c>
     </row>
     <row r="11">

--- a/Download/Focus_Positivi_ZR.xlsx
+++ b/Download/Focus_Positivi_ZR.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="636" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="637" uniqueCount="23">
   <si>
     <t>NOME_REGIONE</t>
   </si>
@@ -1648,16 +1648,16 @@
     </row>
     <row r="109">
       <c r="A109" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B109" t="n">
-        <v>2021.0</v>
+        <v>2026.0</v>
       </c>
       <c r="C109" t="n" s="2">
-        <v>44561.0</v>
+        <v>46177.0</v>
       </c>
       <c r="D109" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="110">
@@ -1665,13 +1665,13 @@
         <v>5</v>
       </c>
       <c r="B110" t="n">
-        <v>2022.0</v>
+        <v>2021.0</v>
       </c>
       <c r="C110" t="n" s="2">
-        <v>44576.0</v>
+        <v>44561.0</v>
       </c>
       <c r="D110" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="111">
@@ -1682,10 +1682,10 @@
         <v>2022.0</v>
       </c>
       <c r="C111" t="n" s="2">
-        <v>44583.0</v>
+        <v>44576.0</v>
       </c>
       <c r="D111" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="112">
@@ -1696,10 +1696,10 @@
         <v>2022.0</v>
       </c>
       <c r="C112" t="n" s="2">
-        <v>44590.0</v>
+        <v>44583.0</v>
       </c>
       <c r="D112" t="n">
-        <v>7.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="113">
@@ -1710,10 +1710,10 @@
         <v>2022.0</v>
       </c>
       <c r="C113" t="n" s="2">
-        <v>44597.0</v>
+        <v>44590.0</v>
       </c>
       <c r="D113" t="n">
-        <v>3.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="114">
@@ -1724,10 +1724,10 @@
         <v>2022.0</v>
       </c>
       <c r="C114" t="n" s="2">
-        <v>44604.0</v>
+        <v>44597.0</v>
       </c>
       <c r="D114" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="115">
@@ -1738,10 +1738,10 @@
         <v>2022.0</v>
       </c>
       <c r="C115" t="n" s="2">
-        <v>44611.0</v>
+        <v>44604.0</v>
       </c>
       <c r="D115" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="116">
@@ -1752,7 +1752,7 @@
         <v>2022.0</v>
       </c>
       <c r="C116" t="n" s="2">
-        <v>44618.0</v>
+        <v>44611.0</v>
       </c>
       <c r="D116" t="n">
         <v>1.0</v>
@@ -1766,10 +1766,10 @@
         <v>2022.0</v>
       </c>
       <c r="C117" t="n" s="2">
-        <v>44625.0</v>
+        <v>44618.0</v>
       </c>
       <c r="D117" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="118">
@@ -1780,10 +1780,10 @@
         <v>2022.0</v>
       </c>
       <c r="C118" t="n" s="2">
-        <v>44632.0</v>
+        <v>44625.0</v>
       </c>
       <c r="D118" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="119">
@@ -1794,10 +1794,10 @@
         <v>2022.0</v>
       </c>
       <c r="C119" t="n" s="2">
-        <v>44639.0</v>
+        <v>44632.0</v>
       </c>
       <c r="D119" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="120">
@@ -1808,7 +1808,7 @@
         <v>2022.0</v>
       </c>
       <c r="C120" t="n" s="2">
-        <v>44646.0</v>
+        <v>44639.0</v>
       </c>
       <c r="D120" t="n">
         <v>2.0</v>
@@ -1822,7 +1822,7 @@
         <v>2022.0</v>
       </c>
       <c r="C121" t="n" s="2">
-        <v>44653.0</v>
+        <v>44646.0</v>
       </c>
       <c r="D121" t="n">
         <v>2.0</v>
@@ -1836,10 +1836,10 @@
         <v>2022.0</v>
       </c>
       <c r="C122" t="n" s="2">
-        <v>44660.0</v>
+        <v>44653.0</v>
       </c>
       <c r="D122" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="123">
@@ -1850,10 +1850,10 @@
         <v>2022.0</v>
       </c>
       <c r="C123" t="n" s="2">
-        <v>44667.0</v>
+        <v>44660.0</v>
       </c>
       <c r="D123" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="124">
@@ -1864,7 +1864,7 @@
         <v>2022.0</v>
       </c>
       <c r="C124" t="n" s="2">
-        <v>44674.0</v>
+        <v>44667.0</v>
       </c>
       <c r="D124" t="n">
         <v>3.0</v>
@@ -1878,10 +1878,10 @@
         <v>2022.0</v>
       </c>
       <c r="C125" t="n" s="2">
-        <v>44681.0</v>
+        <v>44674.0</v>
       </c>
       <c r="D125" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="126">
@@ -1892,10 +1892,10 @@
         <v>2022.0</v>
       </c>
       <c r="C126" t="n" s="2">
-        <v>44688.0</v>
+        <v>44681.0</v>
       </c>
       <c r="D126" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="127">
@@ -1906,7 +1906,7 @@
         <v>2022.0</v>
       </c>
       <c r="C127" t="n" s="2">
-        <v>44695.0</v>
+        <v>44688.0</v>
       </c>
       <c r="D127" t="n">
         <v>3.0</v>
@@ -1920,10 +1920,10 @@
         <v>2022.0</v>
       </c>
       <c r="C128" t="n" s="2">
-        <v>44702.0</v>
+        <v>44695.0</v>
       </c>
       <c r="D128" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="129">
@@ -1934,10 +1934,10 @@
         <v>2022.0</v>
       </c>
       <c r="C129" t="n" s="2">
-        <v>44709.0</v>
+        <v>44702.0</v>
       </c>
       <c r="D129" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="130">
@@ -1948,10 +1948,10 @@
         <v>2022.0</v>
       </c>
       <c r="C130" t="n" s="2">
-        <v>44716.0</v>
+        <v>44709.0</v>
       </c>
       <c r="D130" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="131">
@@ -1962,7 +1962,7 @@
         <v>2022.0</v>
       </c>
       <c r="C131" t="n" s="2">
-        <v>44723.0</v>
+        <v>44716.0</v>
       </c>
       <c r="D131" t="n">
         <v>1.0</v>
@@ -1976,7 +1976,7 @@
         <v>2022.0</v>
       </c>
       <c r="C132" t="n" s="2">
-        <v>44730.0</v>
+        <v>44723.0</v>
       </c>
       <c r="D132" t="n">
         <v>1.0</v>
@@ -1990,7 +1990,7 @@
         <v>2022.0</v>
       </c>
       <c r="C133" t="n" s="2">
-        <v>44737.0</v>
+        <v>44730.0</v>
       </c>
       <c r="D133" t="n">
         <v>1.0</v>
@@ -2004,7 +2004,7 @@
         <v>2022.0</v>
       </c>
       <c r="C134" t="n" s="2">
-        <v>44744.0</v>
+        <v>44737.0</v>
       </c>
       <c r="D134" t="n">
         <v>1.0</v>
@@ -2018,7 +2018,7 @@
         <v>2022.0</v>
       </c>
       <c r="C135" t="n" s="2">
-        <v>44751.0</v>
+        <v>44744.0</v>
       </c>
       <c r="D135" t="n">
         <v>1.0</v>
@@ -2032,7 +2032,7 @@
         <v>2022.0</v>
       </c>
       <c r="C136" t="n" s="2">
-        <v>44758.0</v>
+        <v>44751.0</v>
       </c>
       <c r="D136" t="n">
         <v>1.0</v>
@@ -2046,7 +2046,7 @@
         <v>2022.0</v>
       </c>
       <c r="C137" t="n" s="2">
-        <v>44772.0</v>
+        <v>44758.0</v>
       </c>
       <c r="D137" t="n">
         <v>1.0</v>
@@ -2060,7 +2060,7 @@
         <v>2022.0</v>
       </c>
       <c r="C138" t="n" s="2">
-        <v>44793.0</v>
+        <v>44772.0</v>
       </c>
       <c r="D138" t="n">
         <v>1.0</v>
@@ -2074,7 +2074,7 @@
         <v>2022.0</v>
       </c>
       <c r="C139" t="n" s="2">
-        <v>44800.0</v>
+        <v>44793.0</v>
       </c>
       <c r="D139" t="n">
         <v>1.0</v>
@@ -2088,7 +2088,7 @@
         <v>2022.0</v>
       </c>
       <c r="C140" t="n" s="2">
-        <v>44828.0</v>
+        <v>44800.0</v>
       </c>
       <c r="D140" t="n">
         <v>1.0</v>
@@ -2102,7 +2102,7 @@
         <v>2022.0</v>
       </c>
       <c r="C141" t="n" s="2">
-        <v>44849.0</v>
+        <v>44828.0</v>
       </c>
       <c r="D141" t="n">
         <v>1.0</v>
@@ -2116,7 +2116,7 @@
         <v>2022.0</v>
       </c>
       <c r="C142" t="n" s="2">
-        <v>44856.0</v>
+        <v>44849.0</v>
       </c>
       <c r="D142" t="n">
         <v>1.0</v>
@@ -2130,7 +2130,7 @@
         <v>2022.0</v>
       </c>
       <c r="C143" t="n" s="2">
-        <v>44863.0</v>
+        <v>44856.0</v>
       </c>
       <c r="D143" t="n">
         <v>1.0</v>
@@ -2144,10 +2144,10 @@
         <v>2022.0</v>
       </c>
       <c r="C144" t="n" s="2">
-        <v>44884.0</v>
+        <v>44863.0</v>
       </c>
       <c r="D144" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="145">
@@ -2158,10 +2158,10 @@
         <v>2022.0</v>
       </c>
       <c r="C145" t="n" s="2">
-        <v>44891.0</v>
+        <v>44884.0</v>
       </c>
       <c r="D145" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="146">
@@ -2172,7 +2172,7 @@
         <v>2022.0</v>
       </c>
       <c r="C146" t="n" s="2">
-        <v>44905.0</v>
+        <v>44891.0</v>
       </c>
       <c r="D146" t="n">
         <v>1.0</v>
@@ -2186,7 +2186,7 @@
         <v>2022.0</v>
       </c>
       <c r="C147" t="n" s="2">
-        <v>44912.0</v>
+        <v>44905.0</v>
       </c>
       <c r="D147" t="n">
         <v>1.0</v>
@@ -2200,10 +2200,10 @@
         <v>2022.0</v>
       </c>
       <c r="C148" t="n" s="2">
-        <v>44919.0</v>
+        <v>44912.0</v>
       </c>
       <c r="D148" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="149">
@@ -2211,13 +2211,13 @@
         <v>5</v>
       </c>
       <c r="B149" t="n">
-        <v>2023.0</v>
+        <v>2022.0</v>
       </c>
       <c r="C149" t="n" s="2">
-        <v>44934.0</v>
+        <v>44919.0</v>
       </c>
       <c r="D149" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="150">
@@ -2228,10 +2228,10 @@
         <v>2023.0</v>
       </c>
       <c r="C150" t="n" s="2">
-        <v>44941.0</v>
+        <v>44934.0</v>
       </c>
       <c r="D150" t="n">
-        <v>8.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="151">
@@ -2242,10 +2242,10 @@
         <v>2023.0</v>
       </c>
       <c r="C151" t="n" s="2">
-        <v>44948.0</v>
+        <v>44941.0</v>
       </c>
       <c r="D151" t="n">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="152">
@@ -2256,10 +2256,10 @@
         <v>2023.0</v>
       </c>
       <c r="C152" t="n" s="2">
-        <v>44955.0</v>
+        <v>44948.0</v>
       </c>
       <c r="D152" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="153">
@@ -2270,10 +2270,10 @@
         <v>2023.0</v>
       </c>
       <c r="C153" t="n" s="2">
-        <v>44962.0</v>
+        <v>44955.0</v>
       </c>
       <c r="D153" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="154">
@@ -2284,7 +2284,7 @@
         <v>2023.0</v>
       </c>
       <c r="C154" t="n" s="2">
-        <v>44969.0</v>
+        <v>44962.0</v>
       </c>
       <c r="D154" t="n">
         <v>4.0</v>
@@ -2298,10 +2298,10 @@
         <v>2023.0</v>
       </c>
       <c r="C155" t="n" s="2">
-        <v>44976.0</v>
+        <v>44969.0</v>
       </c>
       <c r="D155" t="n">
-        <v>17.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="156">
@@ -2312,10 +2312,10 @@
         <v>2023.0</v>
       </c>
       <c r="C156" t="n" s="2">
-        <v>44983.0</v>
+        <v>44976.0</v>
       </c>
       <c r="D156" t="n">
-        <v>11.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="157">
@@ -2326,10 +2326,10 @@
         <v>2023.0</v>
       </c>
       <c r="C157" t="n" s="2">
-        <v>44990.0</v>
+        <v>44983.0</v>
       </c>
       <c r="D157" t="n">
-        <v>5.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="158">
@@ -2340,10 +2340,10 @@
         <v>2023.0</v>
       </c>
       <c r="C158" t="n" s="2">
-        <v>44997.0</v>
+        <v>44990.0</v>
       </c>
       <c r="D158" t="n">
-        <v>22.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="159">
@@ -2354,10 +2354,10 @@
         <v>2023.0</v>
       </c>
       <c r="C159" t="n" s="2">
-        <v>45004.0</v>
+        <v>44997.0</v>
       </c>
       <c r="D159" t="n">
-        <v>8.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="160">
@@ -2368,10 +2368,10 @@
         <v>2023.0</v>
       </c>
       <c r="C160" t="n" s="2">
-        <v>45011.0</v>
+        <v>45004.0</v>
       </c>
       <c r="D160" t="n">
-        <v>17.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="161">
@@ -2382,10 +2382,10 @@
         <v>2023.0</v>
       </c>
       <c r="C161" t="n" s="2">
-        <v>45018.0</v>
+        <v>45011.0</v>
       </c>
       <c r="D161" t="n">
-        <v>10.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="162">
@@ -2396,10 +2396,10 @@
         <v>2023.0</v>
       </c>
       <c r="C162" t="n" s="2">
-        <v>45025.0</v>
+        <v>45018.0</v>
       </c>
       <c r="D162" t="n">
-        <v>13.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="163">
@@ -2410,10 +2410,10 @@
         <v>2023.0</v>
       </c>
       <c r="C163" t="n" s="2">
-        <v>45032.0</v>
+        <v>45025.0</v>
       </c>
       <c r="D163" t="n">
-        <v>10.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="164">
@@ -2424,10 +2424,10 @@
         <v>2023.0</v>
       </c>
       <c r="C164" t="n" s="2">
-        <v>45039.0</v>
+        <v>45032.0</v>
       </c>
       <c r="D164" t="n">
-        <v>22.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="165">
@@ -2438,10 +2438,10 @@
         <v>2023.0</v>
       </c>
       <c r="C165" t="n" s="2">
-        <v>45046.0</v>
+        <v>45039.0</v>
       </c>
       <c r="D165" t="n">
-        <v>23.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="166">
@@ -2452,10 +2452,10 @@
         <v>2023.0</v>
       </c>
       <c r="C166" t="n" s="2">
-        <v>45053.0</v>
+        <v>45046.0</v>
       </c>
       <c r="D166" t="n">
-        <v>16.0</v>
+        <v>23.0</v>
       </c>
     </row>
     <row r="167">
@@ -2466,10 +2466,10 @@
         <v>2023.0</v>
       </c>
       <c r="C167" t="n" s="2">
-        <v>45060.0</v>
+        <v>45053.0</v>
       </c>
       <c r="D167" t="n">
-        <v>13.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="168">
@@ -2480,10 +2480,10 @@
         <v>2023.0</v>
       </c>
       <c r="C168" t="n" s="2">
-        <v>45067.0</v>
+        <v>45060.0</v>
       </c>
       <c r="D168" t="n">
-        <v>9.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="169">
@@ -2494,10 +2494,10 @@
         <v>2023.0</v>
       </c>
       <c r="C169" t="n" s="2">
-        <v>45074.0</v>
+        <v>45067.0</v>
       </c>
       <c r="D169" t="n">
-        <v>6.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="170">
@@ -2508,10 +2508,10 @@
         <v>2023.0</v>
       </c>
       <c r="C170" t="n" s="2">
-        <v>45081.0</v>
+        <v>45074.0</v>
       </c>
       <c r="D170" t="n">
-        <v>16.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="171">
@@ -2522,10 +2522,10 @@
         <v>2023.0</v>
       </c>
       <c r="C171" t="n" s="2">
-        <v>45088.0</v>
+        <v>45081.0</v>
       </c>
       <c r="D171" t="n">
-        <v>8.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="172">
@@ -2536,10 +2536,10 @@
         <v>2023.0</v>
       </c>
       <c r="C172" t="n" s="2">
-        <v>45095.0</v>
+        <v>45088.0</v>
       </c>
       <c r="D172" t="n">
-        <v>16.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="173">
@@ -2550,10 +2550,10 @@
         <v>2023.0</v>
       </c>
       <c r="C173" t="n" s="2">
-        <v>45102.0</v>
+        <v>45095.0</v>
       </c>
       <c r="D173" t="n">
-        <v>17.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="174">
@@ -2564,10 +2564,10 @@
         <v>2023.0</v>
       </c>
       <c r="C174" t="n" s="2">
-        <v>45109.0</v>
+        <v>45102.0</v>
       </c>
       <c r="D174" t="n">
-        <v>14.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="175">
@@ -2578,10 +2578,10 @@
         <v>2023.0</v>
       </c>
       <c r="C175" t="n" s="2">
-        <v>45116.0</v>
+        <v>45109.0</v>
       </c>
       <c r="D175" t="n">
-        <v>13.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="176">
@@ -2592,10 +2592,10 @@
         <v>2023.0</v>
       </c>
       <c r="C176" t="n" s="2">
-        <v>45123.0</v>
+        <v>45116.0</v>
       </c>
       <c r="D176" t="n">
-        <v>5.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="177">
@@ -2606,10 +2606,10 @@
         <v>2023.0</v>
       </c>
       <c r="C177" t="n" s="2">
-        <v>45130.0</v>
+        <v>45123.0</v>
       </c>
       <c r="D177" t="n">
-        <v>8.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="178">
@@ -2620,10 +2620,10 @@
         <v>2023.0</v>
       </c>
       <c r="C178" t="n" s="2">
-        <v>45137.0</v>
+        <v>45130.0</v>
       </c>
       <c r="D178" t="n">
-        <v>4.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="179">
@@ -2634,10 +2634,10 @@
         <v>2023.0</v>
       </c>
       <c r="C179" t="n" s="2">
-        <v>45144.0</v>
+        <v>45137.0</v>
       </c>
       <c r="D179" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="180">
@@ -2648,7 +2648,7 @@
         <v>2023.0</v>
       </c>
       <c r="C180" t="n" s="2">
-        <v>45151.0</v>
+        <v>45144.0</v>
       </c>
       <c r="D180" t="n">
         <v>2.0</v>
@@ -2662,10 +2662,10 @@
         <v>2023.0</v>
       </c>
       <c r="C181" t="n" s="2">
-        <v>45158.0</v>
+        <v>45151.0</v>
       </c>
       <c r="D181" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="182">
@@ -2676,7 +2676,7 @@
         <v>2023.0</v>
       </c>
       <c r="C182" t="n" s="2">
-        <v>45165.0</v>
+        <v>45158.0</v>
       </c>
       <c r="D182" t="n">
         <v>5.0</v>
@@ -2690,10 +2690,10 @@
         <v>2023.0</v>
       </c>
       <c r="C183" t="n" s="2">
-        <v>45172.0</v>
+        <v>45165.0</v>
       </c>
       <c r="D183" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="184">
@@ -2704,10 +2704,10 @@
         <v>2023.0</v>
       </c>
       <c r="C184" t="n" s="2">
-        <v>45179.0</v>
+        <v>45172.0</v>
       </c>
       <c r="D184" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="185">
@@ -2718,10 +2718,10 @@
         <v>2023.0</v>
       </c>
       <c r="C185" t="n" s="2">
-        <v>45186.0</v>
+        <v>45179.0</v>
       </c>
       <c r="D185" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="186">
@@ -2732,7 +2732,7 @@
         <v>2023.0</v>
       </c>
       <c r="C186" t="n" s="2">
-        <v>45193.0</v>
+        <v>45186.0</v>
       </c>
       <c r="D186" t="n">
         <v>1.0</v>
@@ -2746,10 +2746,10 @@
         <v>2023.0</v>
       </c>
       <c r="C187" t="n" s="2">
-        <v>45200.0</v>
+        <v>45193.0</v>
       </c>
       <c r="D187" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="188">
@@ -2760,10 +2760,10 @@
         <v>2023.0</v>
       </c>
       <c r="C188" t="n" s="2">
-        <v>45207.0</v>
+        <v>45200.0</v>
       </c>
       <c r="D188" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="189">
@@ -2774,10 +2774,10 @@
         <v>2023.0</v>
       </c>
       <c r="C189" t="n" s="2">
-        <v>45214.0</v>
+        <v>45207.0</v>
       </c>
       <c r="D189" t="n">
-        <v>8.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="190">
@@ -2788,7 +2788,7 @@
         <v>2023.0</v>
       </c>
       <c r="C190" t="n" s="2">
-        <v>45221.0</v>
+        <v>45214.0</v>
       </c>
       <c r="D190" t="n">
         <v>8.0</v>
@@ -2802,10 +2802,10 @@
         <v>2023.0</v>
       </c>
       <c r="C191" t="n" s="2">
-        <v>45228.0</v>
+        <v>45221.0</v>
       </c>
       <c r="D191" t="n">
-        <v>17.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="192">
@@ -2816,10 +2816,10 @@
         <v>2023.0</v>
       </c>
       <c r="C192" t="n" s="2">
-        <v>45235.0</v>
+        <v>45228.0</v>
       </c>
       <c r="D192" t="n">
-        <v>9.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="193">
@@ -2830,7 +2830,7 @@
         <v>2023.0</v>
       </c>
       <c r="C193" t="n" s="2">
-        <v>45242.0</v>
+        <v>45235.0</v>
       </c>
       <c r="D193" t="n">
         <v>9.0</v>
@@ -2844,10 +2844,10 @@
         <v>2023.0</v>
       </c>
       <c r="C194" t="n" s="2">
-        <v>45249.0</v>
+        <v>45242.0</v>
       </c>
       <c r="D194" t="n">
-        <v>14.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="195">
@@ -2858,10 +2858,10 @@
         <v>2023.0</v>
       </c>
       <c r="C195" t="n" s="2">
-        <v>45256.0</v>
+        <v>45249.0</v>
       </c>
       <c r="D195" t="n">
-        <v>17.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="196">
@@ -2872,10 +2872,10 @@
         <v>2023.0</v>
       </c>
       <c r="C196" t="n" s="2">
-        <v>45263.0</v>
+        <v>45256.0</v>
       </c>
       <c r="D196" t="n">
-        <v>14.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="197">
@@ -2886,10 +2886,10 @@
         <v>2023.0</v>
       </c>
       <c r="C197" t="n" s="2">
-        <v>45270.0</v>
+        <v>45263.0</v>
       </c>
       <c r="D197" t="n">
-        <v>26.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="198">
@@ -2900,10 +2900,10 @@
         <v>2023.0</v>
       </c>
       <c r="C198" t="n" s="2">
-        <v>45277.0</v>
+        <v>45270.0</v>
       </c>
       <c r="D198" t="n">
-        <v>19.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="199">
@@ -2914,10 +2914,10 @@
         <v>2023.0</v>
       </c>
       <c r="C199" t="n" s="2">
-        <v>45284.0</v>
+        <v>45277.0</v>
       </c>
       <c r="D199" t="n">
-        <v>21.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="200">
@@ -2928,10 +2928,10 @@
         <v>2023.0</v>
       </c>
       <c r="C200" t="n" s="2">
-        <v>45291.0</v>
+        <v>45284.0</v>
       </c>
       <c r="D200" t="n">
-        <v>9.0</v>
+        <v>21.0</v>
       </c>
     </row>
     <row r="201">
@@ -2939,13 +2939,13 @@
         <v>5</v>
       </c>
       <c r="B201" t="n">
-        <v>2024.0</v>
+        <v>2023.0</v>
       </c>
       <c r="C201" t="n" s="2">
-        <v>45299.0</v>
+        <v>45291.0</v>
       </c>
       <c r="D201" t="n">
-        <v>26.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="202">
@@ -2956,10 +2956,10 @@
         <v>2024.0</v>
       </c>
       <c r="C202" t="n" s="2">
-        <v>45306.0</v>
+        <v>45299.0</v>
       </c>
       <c r="D202" t="n">
-        <v>14.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="203">
@@ -2970,10 +2970,10 @@
         <v>2024.0</v>
       </c>
       <c r="C203" t="n" s="2">
-        <v>45313.0</v>
+        <v>45306.0</v>
       </c>
       <c r="D203" t="n">
-        <v>15.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="204">
@@ -2984,10 +2984,10 @@
         <v>2024.0</v>
       </c>
       <c r="C204" t="n" s="2">
-        <v>45320.0</v>
+        <v>45313.0</v>
       </c>
       <c r="D204" t="n">
-        <v>18.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="205">
@@ -2998,10 +2998,10 @@
         <v>2024.0</v>
       </c>
       <c r="C205" t="n" s="2">
-        <v>45327.0</v>
+        <v>45320.0</v>
       </c>
       <c r="D205" t="n">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="206">
@@ -3012,10 +3012,10 @@
         <v>2024.0</v>
       </c>
       <c r="C206" t="n" s="2">
-        <v>45334.0</v>
+        <v>45327.0</v>
       </c>
       <c r="D206" t="n">
-        <v>13.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="207">
@@ -3026,10 +3026,10 @@
         <v>2024.0</v>
       </c>
       <c r="C207" t="n" s="2">
-        <v>45341.0</v>
+        <v>45334.0</v>
       </c>
       <c r="D207" t="n">
-        <v>11.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="208">
@@ -3040,10 +3040,10 @@
         <v>2024.0</v>
       </c>
       <c r="C208" t="n" s="2">
-        <v>45348.0</v>
+        <v>45341.0</v>
       </c>
       <c r="D208" t="n">
-        <v>8.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="209">
@@ -3054,10 +3054,10 @@
         <v>2024.0</v>
       </c>
       <c r="C209" t="n" s="2">
-        <v>45355.0</v>
+        <v>45348.0</v>
       </c>
       <c r="D209" t="n">
-        <v>1.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="210">
@@ -3068,10 +3068,10 @@
         <v>2024.0</v>
       </c>
       <c r="C210" t="n" s="2">
-        <v>45362.0</v>
+        <v>45355.0</v>
       </c>
       <c r="D210" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="211">
@@ -3082,10 +3082,10 @@
         <v>2024.0</v>
       </c>
       <c r="C211" t="n" s="2">
-        <v>45369.0</v>
+        <v>45362.0</v>
       </c>
       <c r="D211" t="n">
-        <v>8.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="212">
@@ -3096,10 +3096,10 @@
         <v>2024.0</v>
       </c>
       <c r="C212" t="n" s="2">
-        <v>45376.0</v>
+        <v>45369.0</v>
       </c>
       <c r="D212" t="n">
-        <v>9.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="213">
@@ -3110,10 +3110,10 @@
         <v>2024.0</v>
       </c>
       <c r="C213" t="n" s="2">
-        <v>45383.0</v>
+        <v>45376.0</v>
       </c>
       <c r="D213" t="n">
-        <v>5.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="214">
@@ -3124,10 +3124,10 @@
         <v>2024.0</v>
       </c>
       <c r="C214" t="n" s="2">
-        <v>45390.0</v>
+        <v>45383.0</v>
       </c>
       <c r="D214" t="n">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="215">
@@ -3138,10 +3138,10 @@
         <v>2024.0</v>
       </c>
       <c r="C215" t="n" s="2">
-        <v>45397.0</v>
+        <v>45390.0</v>
       </c>
       <c r="D215" t="n">
-        <v>13.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="216">
@@ -3152,10 +3152,10 @@
         <v>2024.0</v>
       </c>
       <c r="C216" t="n" s="2">
-        <v>45404.0</v>
+        <v>45397.0</v>
       </c>
       <c r="D216" t="n">
-        <v>24.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="217">
@@ -3166,10 +3166,10 @@
         <v>2024.0</v>
       </c>
       <c r="C217" t="n" s="2">
-        <v>45411.0</v>
+        <v>45404.0</v>
       </c>
       <c r="D217" t="n">
-        <v>17.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="218">
@@ -3180,10 +3180,10 @@
         <v>2024.0</v>
       </c>
       <c r="C218" t="n" s="2">
-        <v>45418.0</v>
+        <v>45411.0</v>
       </c>
       <c r="D218" t="n">
-        <v>3.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="219">
@@ -3194,10 +3194,10 @@
         <v>2024.0</v>
       </c>
       <c r="C219" t="n" s="2">
-        <v>45425.0</v>
+        <v>45418.0</v>
       </c>
       <c r="D219" t="n">
-        <v>16.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="220">
@@ -3208,10 +3208,10 @@
         <v>2024.0</v>
       </c>
       <c r="C220" t="n" s="2">
-        <v>45432.0</v>
+        <v>45425.0</v>
       </c>
       <c r="D220" t="n">
-        <v>19.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="221">
@@ -3222,10 +3222,10 @@
         <v>2024.0</v>
       </c>
       <c r="C221" t="n" s="2">
-        <v>45439.0</v>
+        <v>45432.0</v>
       </c>
       <c r="D221" t="n">
-        <v>30.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="222">
@@ -3236,10 +3236,10 @@
         <v>2024.0</v>
       </c>
       <c r="C222" t="n" s="2">
-        <v>45446.0</v>
+        <v>45439.0</v>
       </c>
       <c r="D222" t="n">
-        <v>28.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="223">
@@ -3250,10 +3250,10 @@
         <v>2024.0</v>
       </c>
       <c r="C223" t="n" s="2">
-        <v>45453.0</v>
+        <v>45446.0</v>
       </c>
       <c r="D223" t="n">
-        <v>19.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="224">
@@ -3264,10 +3264,10 @@
         <v>2024.0</v>
       </c>
       <c r="C224" t="n" s="2">
-        <v>45460.0</v>
+        <v>45453.0</v>
       </c>
       <c r="D224" t="n">
-        <v>26.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="225">
@@ -3278,10 +3278,10 @@
         <v>2024.0</v>
       </c>
       <c r="C225" t="n" s="2">
-        <v>45467.0</v>
+        <v>45460.0</v>
       </c>
       <c r="D225" t="n">
-        <v>8.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="226">
@@ -3292,10 +3292,10 @@
         <v>2024.0</v>
       </c>
       <c r="C226" t="n" s="2">
-        <v>45474.0</v>
+        <v>45467.0</v>
       </c>
       <c r="D226" t="n">
-        <v>12.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="227">
@@ -3306,7 +3306,7 @@
         <v>2024.0</v>
       </c>
       <c r="C227" t="n" s="2">
-        <v>45481.0</v>
+        <v>45474.0</v>
       </c>
       <c r="D227" t="n">
         <v>12.0</v>
@@ -3320,10 +3320,10 @@
         <v>2024.0</v>
       </c>
       <c r="C228" t="n" s="2">
-        <v>45488.0</v>
+        <v>45481.0</v>
       </c>
       <c r="D228" t="n">
-        <v>4.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="229">
@@ -3334,10 +3334,10 @@
         <v>2024.0</v>
       </c>
       <c r="C229" t="n" s="2">
-        <v>45495.0</v>
+        <v>45488.0</v>
       </c>
       <c r="D229" t="n">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="230">
@@ -3348,10 +3348,10 @@
         <v>2024.0</v>
       </c>
       <c r="C230" t="n" s="2">
-        <v>45502.0</v>
+        <v>45495.0</v>
       </c>
       <c r="D230" t="n">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="231">
@@ -3362,10 +3362,10 @@
         <v>2024.0</v>
       </c>
       <c r="C231" t="n" s="2">
-        <v>45509.0</v>
+        <v>45502.0</v>
       </c>
       <c r="D231" t="n">
-        <v>2.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="232">
@@ -3376,10 +3376,10 @@
         <v>2024.0</v>
       </c>
       <c r="C232" t="n" s="2">
-        <v>45516.0</v>
+        <v>45509.0</v>
       </c>
       <c r="D232" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="233">
@@ -3390,7 +3390,7 @@
         <v>2024.0</v>
       </c>
       <c r="C233" t="n" s="2">
-        <v>45523.0</v>
+        <v>45516.0</v>
       </c>
       <c r="D233" t="n">
         <v>4.0</v>
@@ -3404,7 +3404,7 @@
         <v>2024.0</v>
       </c>
       <c r="C234" t="n" s="2">
-        <v>45530.0</v>
+        <v>45523.0</v>
       </c>
       <c r="D234" t="n">
         <v>4.0</v>
@@ -3418,7 +3418,7 @@
         <v>2024.0</v>
       </c>
       <c r="C235" t="n" s="2">
-        <v>45537.0</v>
+        <v>45530.0</v>
       </c>
       <c r="D235" t="n">
         <v>4.0</v>
@@ -3432,10 +3432,10 @@
         <v>2024.0</v>
       </c>
       <c r="C236" t="n" s="2">
-        <v>45544.0</v>
+        <v>45537.0</v>
       </c>
       <c r="D236" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="237">
@@ -3446,10 +3446,10 @@
         <v>2024.0</v>
       </c>
       <c r="C237" t="n" s="2">
-        <v>45551.0</v>
+        <v>45544.0</v>
       </c>
       <c r="D237" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="238">
@@ -3460,10 +3460,10 @@
         <v>2024.0</v>
       </c>
       <c r="C238" t="n" s="2">
-        <v>45558.0</v>
+        <v>45551.0</v>
       </c>
       <c r="D238" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="239">
@@ -3474,10 +3474,10 @@
         <v>2024.0</v>
       </c>
       <c r="C239" t="n" s="2">
-        <v>45600.0</v>
+        <v>45558.0</v>
       </c>
       <c r="D239" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="240">
@@ -3488,10 +3488,10 @@
         <v>2024.0</v>
       </c>
       <c r="C240" t="n" s="2">
-        <v>45607.0</v>
+        <v>45600.0</v>
       </c>
       <c r="D240" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="241">
@@ -3502,10 +3502,10 @@
         <v>2024.0</v>
       </c>
       <c r="C241" t="n" s="2">
-        <v>45628.0</v>
+        <v>45607.0</v>
       </c>
       <c r="D241" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="242">
@@ -3516,10 +3516,10 @@
         <v>2024.0</v>
       </c>
       <c r="C242" t="n" s="2">
-        <v>45635.0</v>
+        <v>45628.0</v>
       </c>
       <c r="D242" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="243">
@@ -3530,7 +3530,7 @@
         <v>2024.0</v>
       </c>
       <c r="C243" t="n" s="2">
-        <v>45642.0</v>
+        <v>45635.0</v>
       </c>
       <c r="D243" t="n">
         <v>3.0</v>
@@ -3544,10 +3544,10 @@
         <v>2024.0</v>
       </c>
       <c r="C244" t="n" s="2">
-        <v>45649.0</v>
+        <v>45642.0</v>
       </c>
       <c r="D244" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="245">
@@ -3558,7 +3558,7 @@
         <v>2024.0</v>
       </c>
       <c r="C245" t="n" s="2">
-        <v>45656.0</v>
+        <v>45649.0</v>
       </c>
       <c r="D245" t="n">
         <v>1.0</v>
@@ -3569,13 +3569,13 @@
         <v>5</v>
       </c>
       <c r="B246" t="n">
-        <v>2025.0</v>
+        <v>2024.0</v>
       </c>
       <c r="C246" t="n" s="2">
-        <v>45672.0</v>
+        <v>45656.0</v>
       </c>
       <c r="D246" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="247">
@@ -3586,10 +3586,10 @@
         <v>2025.0</v>
       </c>
       <c r="C247" t="n" s="2">
-        <v>45679.0</v>
+        <v>45672.0</v>
       </c>
       <c r="D247" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="248">
@@ -3600,7 +3600,7 @@
         <v>2025.0</v>
       </c>
       <c r="C248" t="n" s="2">
-        <v>45686.0</v>
+        <v>45679.0</v>
       </c>
       <c r="D248" t="n">
         <v>1.0</v>
@@ -3614,10 +3614,10 @@
         <v>2025.0</v>
       </c>
       <c r="C249" t="n" s="2">
-        <v>45721.0</v>
+        <v>45686.0</v>
       </c>
       <c r="D249" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="250">
@@ -3628,10 +3628,10 @@
         <v>2025.0</v>
       </c>
       <c r="C250" t="n" s="2">
-        <v>45728.0</v>
+        <v>45721.0</v>
       </c>
       <c r="D250" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="251">
@@ -3642,10 +3642,10 @@
         <v>2025.0</v>
       </c>
       <c r="C251" t="n" s="2">
-        <v>45742.0</v>
+        <v>45728.0</v>
       </c>
       <c r="D251" t="n">
-        <v>9.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="252">
@@ -3656,10 +3656,10 @@
         <v>2025.0</v>
       </c>
       <c r="C252" t="n" s="2">
-        <v>45749.0</v>
+        <v>45742.0</v>
       </c>
       <c r="D252" t="n">
-        <v>5.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="253">
@@ -3670,10 +3670,10 @@
         <v>2025.0</v>
       </c>
       <c r="C253" t="n" s="2">
-        <v>45756.0</v>
+        <v>45749.0</v>
       </c>
       <c r="D253" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="254">
@@ -3684,10 +3684,10 @@
         <v>2025.0</v>
       </c>
       <c r="C254" t="n" s="2">
-        <v>45763.0</v>
+        <v>45756.0</v>
       </c>
       <c r="D254" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="255">
@@ -3698,10 +3698,10 @@
         <v>2025.0</v>
       </c>
       <c r="C255" t="n" s="2">
-        <v>45770.0</v>
+        <v>45763.0</v>
       </c>
       <c r="D255" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="256">
@@ -3712,10 +3712,10 @@
         <v>2025.0</v>
       </c>
       <c r="C256" t="n" s="2">
-        <v>45777.0</v>
+        <v>45770.0</v>
       </c>
       <c r="D256" t="n">
-        <v>7.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="257">
@@ -3726,10 +3726,10 @@
         <v>2025.0</v>
       </c>
       <c r="C257" t="n" s="2">
-        <v>45784.0</v>
+        <v>45777.0</v>
       </c>
       <c r="D257" t="n">
-        <v>2.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="258">
@@ -3740,10 +3740,10 @@
         <v>2025.0</v>
       </c>
       <c r="C258" t="n" s="2">
-        <v>45791.0</v>
+        <v>45784.0</v>
       </c>
       <c r="D258" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="259">
@@ -3754,10 +3754,10 @@
         <v>2025.0</v>
       </c>
       <c r="C259" t="n" s="2">
-        <v>45798.0</v>
+        <v>45791.0</v>
       </c>
       <c r="D259" t="n">
-        <v>8.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="260">
@@ -3768,10 +3768,10 @@
         <v>2025.0</v>
       </c>
       <c r="C260" t="n" s="2">
-        <v>45805.0</v>
+        <v>45798.0</v>
       </c>
       <c r="D260" t="n">
-        <v>4.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="261">
@@ -3782,10 +3782,10 @@
         <v>2025.0</v>
       </c>
       <c r="C261" t="n" s="2">
-        <v>45812.0</v>
+        <v>45805.0</v>
       </c>
       <c r="D261" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="262">
@@ -3796,10 +3796,10 @@
         <v>2025.0</v>
       </c>
       <c r="C262" t="n" s="2">
-        <v>45819.0</v>
+        <v>45812.0</v>
       </c>
       <c r="D262" t="n">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="263">
@@ -3810,10 +3810,10 @@
         <v>2025.0</v>
       </c>
       <c r="C263" t="n" s="2">
-        <v>45826.0</v>
+        <v>45819.0</v>
       </c>
       <c r="D263" t="n">
-        <v>13.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="264">
@@ -3824,10 +3824,10 @@
         <v>2025.0</v>
       </c>
       <c r="C264" t="n" s="2">
-        <v>45833.0</v>
+        <v>45826.0</v>
       </c>
       <c r="D264" t="n">
-        <v>1.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="265">
@@ -3838,10 +3838,10 @@
         <v>2025.0</v>
       </c>
       <c r="C265" t="n" s="2">
-        <v>45840.0</v>
+        <v>45833.0</v>
       </c>
       <c r="D265" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="266">
@@ -3852,7 +3852,7 @@
         <v>2025.0</v>
       </c>
       <c r="C266" t="n" s="2">
-        <v>45847.0</v>
+        <v>45840.0</v>
       </c>
       <c r="D266" t="n">
         <v>4.0</v>
@@ -3866,10 +3866,10 @@
         <v>2025.0</v>
       </c>
       <c r="C267" t="n" s="2">
-        <v>45854.0</v>
+        <v>45847.0</v>
       </c>
       <c r="D267" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="268">
@@ -3880,10 +3880,10 @@
         <v>2025.0</v>
       </c>
       <c r="C268" t="n" s="2">
-        <v>45861.0</v>
+        <v>45854.0</v>
       </c>
       <c r="D268" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="269">
@@ -3894,10 +3894,10 @@
         <v>2025.0</v>
       </c>
       <c r="C269" t="n" s="2">
-        <v>45868.0</v>
+        <v>45861.0</v>
       </c>
       <c r="D269" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="270">
@@ -3908,10 +3908,10 @@
         <v>2025.0</v>
       </c>
       <c r="C270" t="n" s="2">
-        <v>45882.0</v>
+        <v>45868.0</v>
       </c>
       <c r="D270" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="271">
@@ -3922,7 +3922,7 @@
         <v>2025.0</v>
       </c>
       <c r="C271" t="n" s="2">
-        <v>45889.0</v>
+        <v>45882.0</v>
       </c>
       <c r="D271" t="n">
         <v>1.0</v>
@@ -3936,10 +3936,10 @@
         <v>2025.0</v>
       </c>
       <c r="C272" t="n" s="2">
-        <v>45896.0</v>
+        <v>45889.0</v>
       </c>
       <c r="D272" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="273">
@@ -3950,7 +3950,7 @@
         <v>2025.0</v>
       </c>
       <c r="C273" t="n" s="2">
-        <v>45903.0</v>
+        <v>45896.0</v>
       </c>
       <c r="D273" t="n">
         <v>3.0</v>
@@ -3964,10 +3964,10 @@
         <v>2025.0</v>
       </c>
       <c r="C274" t="n" s="2">
-        <v>45910.0</v>
+        <v>45903.0</v>
       </c>
       <c r="D274" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="275">
@@ -3978,7 +3978,7 @@
         <v>2025.0</v>
       </c>
       <c r="C275" t="n" s="2">
-        <v>45973.0</v>
+        <v>45910.0</v>
       </c>
       <c r="D275" t="n">
         <v>1.0</v>
@@ -3992,10 +3992,10 @@
         <v>2025.0</v>
       </c>
       <c r="C276" t="n" s="2">
-        <v>45987.0</v>
+        <v>45973.0</v>
       </c>
       <c r="D276" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="277">
@@ -4006,10 +4006,10 @@
         <v>2025.0</v>
       </c>
       <c r="C277" t="n" s="2">
-        <v>45994.0</v>
+        <v>45987.0</v>
       </c>
       <c r="D277" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="278">
@@ -4020,10 +4020,10 @@
         <v>2025.0</v>
       </c>
       <c r="C278" t="n" s="2">
-        <v>46001.0</v>
+        <v>45994.0</v>
       </c>
       <c r="D278" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="279">
@@ -4034,10 +4034,10 @@
         <v>2025.0</v>
       </c>
       <c r="C279" t="n" s="2">
-        <v>46008.0</v>
+        <v>46001.0</v>
       </c>
       <c r="D279" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="280">
@@ -4048,10 +4048,10 @@
         <v>2025.0</v>
       </c>
       <c r="C280" t="n" s="2">
-        <v>46022.0</v>
+        <v>46008.0</v>
       </c>
       <c r="D280" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="281">
@@ -4062,10 +4062,10 @@
         <v>2025.0</v>
       </c>
       <c r="C281" t="n" s="2">
-        <v>46029.0</v>
+        <v>46022.0</v>
       </c>
       <c r="D281" t="n">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="282">
@@ -4073,13 +4073,13 @@
         <v>5</v>
       </c>
       <c r="B282" t="n">
-        <v>2026.0</v>
+        <v>2025.0</v>
       </c>
       <c r="C282" t="n" s="2">
-        <v>46030.0</v>
+        <v>46029.0</v>
       </c>
       <c r="D282" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="283">
@@ -4090,10 +4090,10 @@
         <v>2026.0</v>
       </c>
       <c r="C283" t="n" s="2">
-        <v>46037.0</v>
+        <v>46030.0</v>
       </c>
       <c r="D283" t="n">
-        <v>12.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="284">
@@ -4104,10 +4104,10 @@
         <v>2026.0</v>
       </c>
       <c r="C284" t="n" s="2">
-        <v>46044.0</v>
+        <v>46037.0</v>
       </c>
       <c r="D284" t="n">
-        <v>9.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="285">
@@ -4118,10 +4118,10 @@
         <v>2026.0</v>
       </c>
       <c r="C285" t="n" s="2">
-        <v>46051.0</v>
+        <v>46044.0</v>
       </c>
       <c r="D285" t="n">
-        <v>10.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="286">
@@ -4132,10 +4132,10 @@
         <v>2026.0</v>
       </c>
       <c r="C286" t="n" s="2">
-        <v>46058.0</v>
+        <v>46051.0</v>
       </c>
       <c r="D286" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="287">
@@ -4146,10 +4146,10 @@
         <v>2026.0</v>
       </c>
       <c r="C287" t="n" s="2">
-        <v>46065.0</v>
+        <v>46058.0</v>
       </c>
       <c r="D287" t="n">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="288">
@@ -4160,10 +4160,10 @@
         <v>2026.0</v>
       </c>
       <c r="C288" t="n" s="2">
-        <v>46072.0</v>
+        <v>46065.0</v>
       </c>
       <c r="D288" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="289">
@@ -4174,7 +4174,7 @@
         <v>2026.0</v>
       </c>
       <c r="C289" t="n" s="2">
-        <v>46079.0</v>
+        <v>46072.0</v>
       </c>
       <c r="D289" t="n">
         <v>5.0</v>
@@ -4188,10 +4188,10 @@
         <v>2026.0</v>
       </c>
       <c r="C290" t="n" s="2">
-        <v>46086.0</v>
+        <v>46079.0</v>
       </c>
       <c r="D290" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="291">
@@ -4202,7 +4202,7 @@
         <v>2026.0</v>
       </c>
       <c r="C291" t="n" s="2">
-        <v>46093.0</v>
+        <v>46086.0</v>
       </c>
       <c r="D291" t="n">
         <v>2.0</v>
@@ -4216,10 +4216,10 @@
         <v>2026.0</v>
       </c>
       <c r="C292" t="n" s="2">
-        <v>46100.0</v>
+        <v>46093.0</v>
       </c>
       <c r="D292" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="293">
@@ -4230,10 +4230,10 @@
         <v>2026.0</v>
       </c>
       <c r="C293" t="n" s="2">
-        <v>46107.0</v>
+        <v>46100.0</v>
       </c>
       <c r="D293" t="n">
-        <v>9.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="294">
@@ -4244,10 +4244,10 @@
         <v>2026.0</v>
       </c>
       <c r="C294" t="n" s="2">
-        <v>46114.0</v>
+        <v>46107.0</v>
       </c>
       <c r="D294" t="n">
-        <v>5.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="295">
@@ -4258,10 +4258,10 @@
         <v>2026.0</v>
       </c>
       <c r="C295" t="n" s="2">
-        <v>46121.0</v>
+        <v>46114.0</v>
       </c>
       <c r="D295" t="n">
-        <v>13.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="296">
@@ -4272,10 +4272,10 @@
         <v>2026.0</v>
       </c>
       <c r="C296" t="n" s="2">
-        <v>46128.0</v>
+        <v>46121.0</v>
       </c>
       <c r="D296" t="n">
-        <v>4.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="297">
@@ -4286,7 +4286,7 @@
         <v>2026.0</v>
       </c>
       <c r="C297" t="n" s="2">
-        <v>46135.0</v>
+        <v>46128.0</v>
       </c>
       <c r="D297" t="n">
         <v>4.0</v>
@@ -4300,10 +4300,10 @@
         <v>2026.0</v>
       </c>
       <c r="C298" t="n" s="2">
-        <v>46142.0</v>
+        <v>46135.0</v>
       </c>
       <c r="D298" t="n">
-        <v>7.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="299">
@@ -4314,10 +4314,10 @@
         <v>2026.0</v>
       </c>
       <c r="C299" t="n" s="2">
-        <v>46149.0</v>
+        <v>46142.0</v>
       </c>
       <c r="D299" t="n">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="300">
@@ -4328,10 +4328,10 @@
         <v>2026.0</v>
       </c>
       <c r="C300" t="n" s="2">
-        <v>46156.0</v>
+        <v>46149.0</v>
       </c>
       <c r="D300" t="n">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="301">
@@ -4342,10 +4342,10 @@
         <v>2026.0</v>
       </c>
       <c r="C301" t="n" s="2">
-        <v>46163.0</v>
+        <v>46156.0</v>
       </c>
       <c r="D301" t="n">
-        <v>7.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="302">
@@ -4356,10 +4356,10 @@
         <v>2026.0</v>
       </c>
       <c r="C302" t="n" s="2">
-        <v>46170.0</v>
+        <v>46163.0</v>
       </c>
       <c r="D302" t="n">
-        <v>2.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="303">
@@ -4370,24 +4370,24 @@
         <v>2026.0</v>
       </c>
       <c r="C303" t="n" s="2">
-        <v>46177.0</v>
+        <v>46170.0</v>
       </c>
       <c r="D303" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B304" t="n">
-        <v>2023.0</v>
+        <v>2026.0</v>
       </c>
       <c r="C304" t="n" s="2">
-        <v>45095.0</v>
+        <v>46177.0</v>
       </c>
       <c r="D304" t="n">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="305">
@@ -4398,7 +4398,7 @@
         <v>2023.0</v>
       </c>
       <c r="C305" t="n" s="2">
-        <v>45102.0</v>
+        <v>45095.0</v>
       </c>
       <c r="D305" t="n">
         <v>1.0</v>
@@ -4412,7 +4412,7 @@
         <v>2023.0</v>
       </c>
       <c r="C306" t="n" s="2">
-        <v>45158.0</v>
+        <v>45102.0</v>
       </c>
       <c r="D306" t="n">
         <v>1.0</v>
@@ -4426,10 +4426,10 @@
         <v>2023.0</v>
       </c>
       <c r="C307" t="n" s="2">
-        <v>45207.0</v>
+        <v>45158.0</v>
       </c>
       <c r="D307" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="308">
@@ -4440,7 +4440,7 @@
         <v>2023.0</v>
       </c>
       <c r="C308" t="n" s="2">
-        <v>45214.0</v>
+        <v>45207.0</v>
       </c>
       <c r="D308" t="n">
         <v>3.0</v>
@@ -4454,10 +4454,10 @@
         <v>2023.0</v>
       </c>
       <c r="C309" t="n" s="2">
-        <v>45221.0</v>
+        <v>45214.0</v>
       </c>
       <c r="D309" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="310">
@@ -4468,7 +4468,7 @@
         <v>2023.0</v>
       </c>
       <c r="C310" t="n" s="2">
-        <v>45249.0</v>
+        <v>45221.0</v>
       </c>
       <c r="D310" t="n">
         <v>1.0</v>
@@ -4482,10 +4482,10 @@
         <v>2023.0</v>
       </c>
       <c r="C311" t="n" s="2">
-        <v>45256.0</v>
+        <v>45249.0</v>
       </c>
       <c r="D311" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="312">
@@ -4496,10 +4496,10 @@
         <v>2023.0</v>
       </c>
       <c r="C312" t="n" s="2">
-        <v>45263.0</v>
+        <v>45256.0</v>
       </c>
       <c r="D312" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="313">
@@ -4510,10 +4510,10 @@
         <v>2023.0</v>
       </c>
       <c r="C313" t="n" s="2">
-        <v>45270.0</v>
+        <v>45263.0</v>
       </c>
       <c r="D313" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="314">
@@ -4524,10 +4524,10 @@
         <v>2023.0</v>
       </c>
       <c r="C314" t="n" s="2">
-        <v>45277.0</v>
+        <v>45270.0</v>
       </c>
       <c r="D314" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="315">
@@ -4538,10 +4538,10 @@
         <v>2023.0</v>
       </c>
       <c r="C315" t="n" s="2">
-        <v>45284.0</v>
+        <v>45277.0</v>
       </c>
       <c r="D315" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="316">
@@ -4552,10 +4552,10 @@
         <v>2023.0</v>
       </c>
       <c r="C316" t="n" s="2">
-        <v>45291.0</v>
+        <v>45284.0</v>
       </c>
       <c r="D316" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="317">
@@ -4563,13 +4563,13 @@
         <v>6</v>
       </c>
       <c r="B317" t="n">
-        <v>2024.0</v>
+        <v>2023.0</v>
       </c>
       <c r="C317" t="n" s="2">
-        <v>45306.0</v>
+        <v>45291.0</v>
       </c>
       <c r="D317" t="n">
-        <v>7.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="318">
@@ -4580,10 +4580,10 @@
         <v>2024.0</v>
       </c>
       <c r="C318" t="n" s="2">
-        <v>45313.0</v>
+        <v>45306.0</v>
       </c>
       <c r="D318" t="n">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="319">
@@ -4594,10 +4594,10 @@
         <v>2024.0</v>
       </c>
       <c r="C319" t="n" s="2">
-        <v>45320.0</v>
+        <v>45313.0</v>
       </c>
       <c r="D319" t="n">
-        <v>19.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="320">
@@ -4608,10 +4608,10 @@
         <v>2024.0</v>
       </c>
       <c r="C320" t="n" s="2">
-        <v>45327.0</v>
+        <v>45320.0</v>
       </c>
       <c r="D320" t="n">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="321">
@@ -4622,10 +4622,10 @@
         <v>2024.0</v>
       </c>
       <c r="C321" t="n" s="2">
-        <v>45334.0</v>
+        <v>45327.0</v>
       </c>
       <c r="D321" t="n">
-        <v>9.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="322">
@@ -4636,10 +4636,10 @@
         <v>2024.0</v>
       </c>
       <c r="C322" t="n" s="2">
-        <v>45341.0</v>
+        <v>45334.0</v>
       </c>
       <c r="D322" t="n">
-        <v>12.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="323">
@@ -4650,7 +4650,7 @@
         <v>2024.0</v>
       </c>
       <c r="C323" t="n" s="2">
-        <v>45348.0</v>
+        <v>45341.0</v>
       </c>
       <c r="D323" t="n">
         <v>12.0</v>
@@ -4664,10 +4664,10 @@
         <v>2024.0</v>
       </c>
       <c r="C324" t="n" s="2">
-        <v>45355.0</v>
+        <v>45348.0</v>
       </c>
       <c r="D324" t="n">
-        <v>10.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="325">
@@ -4678,10 +4678,10 @@
         <v>2024.0</v>
       </c>
       <c r="C325" t="n" s="2">
-        <v>45362.0</v>
+        <v>45355.0</v>
       </c>
       <c r="D325" t="n">
-        <v>12.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="326">
@@ -4692,10 +4692,10 @@
         <v>2024.0</v>
       </c>
       <c r="C326" t="n" s="2">
-        <v>45369.0</v>
+        <v>45362.0</v>
       </c>
       <c r="D326" t="n">
-        <v>13.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="327">
@@ -4706,10 +4706,10 @@
         <v>2024.0</v>
       </c>
       <c r="C327" t="n" s="2">
-        <v>45376.0</v>
+        <v>45369.0</v>
       </c>
       <c r="D327" t="n">
-        <v>18.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="328">
@@ -4720,10 +4720,10 @@
         <v>2024.0</v>
       </c>
       <c r="C328" t="n" s="2">
-        <v>45383.0</v>
+        <v>45376.0</v>
       </c>
       <c r="D328" t="n">
-        <v>12.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="329">
@@ -4734,10 +4734,10 @@
         <v>2024.0</v>
       </c>
       <c r="C329" t="n" s="2">
-        <v>45390.0</v>
+        <v>45383.0</v>
       </c>
       <c r="D329" t="n">
-        <v>6.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="330">
@@ -4748,10 +4748,10 @@
         <v>2024.0</v>
       </c>
       <c r="C330" t="n" s="2">
-        <v>45397.0</v>
+        <v>45390.0</v>
       </c>
       <c r="D330" t="n">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="331">
@@ -4762,10 +4762,10 @@
         <v>2024.0</v>
       </c>
       <c r="C331" t="n" s="2">
-        <v>45404.0</v>
+        <v>45397.0</v>
       </c>
       <c r="D331" t="n">
-        <v>3.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="332">
@@ -4776,10 +4776,10 @@
         <v>2024.0</v>
       </c>
       <c r="C332" t="n" s="2">
-        <v>45411.0</v>
+        <v>45404.0</v>
       </c>
       <c r="D332" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="333">
@@ -4790,10 +4790,10 @@
         <v>2024.0</v>
       </c>
       <c r="C333" t="n" s="2">
-        <v>45418.0</v>
+        <v>45411.0</v>
       </c>
       <c r="D333" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="334">
@@ -4804,10 +4804,10 @@
         <v>2024.0</v>
       </c>
       <c r="C334" t="n" s="2">
-        <v>45425.0</v>
+        <v>45418.0</v>
       </c>
       <c r="D334" t="n">
-        <v>9.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="335">
@@ -4818,10 +4818,10 @@
         <v>2024.0</v>
       </c>
       <c r="C335" t="n" s="2">
-        <v>45432.0</v>
+        <v>45425.0</v>
       </c>
       <c r="D335" t="n">
-        <v>6.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="336">
@@ -4832,7 +4832,7 @@
         <v>2024.0</v>
       </c>
       <c r="C336" t="n" s="2">
-        <v>45439.0</v>
+        <v>45432.0</v>
       </c>
       <c r="D336" t="n">
         <v>6.0</v>
@@ -4846,10 +4846,10 @@
         <v>2024.0</v>
       </c>
       <c r="C337" t="n" s="2">
-        <v>45446.0</v>
+        <v>45439.0</v>
       </c>
       <c r="D337" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="338">
@@ -4860,10 +4860,10 @@
         <v>2024.0</v>
       </c>
       <c r="C338" t="n" s="2">
-        <v>45453.0</v>
+        <v>45446.0</v>
       </c>
       <c r="D338" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="339">
@@ -4874,7 +4874,7 @@
         <v>2024.0</v>
       </c>
       <c r="C339" t="n" s="2">
-        <v>45460.0</v>
+        <v>45453.0</v>
       </c>
       <c r="D339" t="n">
         <v>4.0</v>
@@ -4888,7 +4888,7 @@
         <v>2024.0</v>
       </c>
       <c r="C340" t="n" s="2">
-        <v>45467.0</v>
+        <v>45460.0</v>
       </c>
       <c r="D340" t="n">
         <v>4.0</v>
@@ -4902,10 +4902,10 @@
         <v>2024.0</v>
       </c>
       <c r="C341" t="n" s="2">
-        <v>45474.0</v>
+        <v>45467.0</v>
       </c>
       <c r="D341" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="342">
@@ -4916,10 +4916,10 @@
         <v>2024.0</v>
       </c>
       <c r="C342" t="n" s="2">
-        <v>45481.0</v>
+        <v>45474.0</v>
       </c>
       <c r="D342" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="343">
@@ -4930,10 +4930,10 @@
         <v>2024.0</v>
       </c>
       <c r="C343" t="n" s="2">
-        <v>45488.0</v>
+        <v>45481.0</v>
       </c>
       <c r="D343" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="344">
@@ -4944,10 +4944,10 @@
         <v>2024.0</v>
       </c>
       <c r="C344" t="n" s="2">
-        <v>45495.0</v>
+        <v>45488.0</v>
       </c>
       <c r="D344" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="345">
@@ -4958,10 +4958,10 @@
         <v>2024.0</v>
       </c>
       <c r="C345" t="n" s="2">
-        <v>45502.0</v>
+        <v>45495.0</v>
       </c>
       <c r="D345" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="346">
@@ -4972,10 +4972,10 @@
         <v>2024.0</v>
       </c>
       <c r="C346" t="n" s="2">
-        <v>45509.0</v>
+        <v>45502.0</v>
       </c>
       <c r="D346" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="347">
@@ -4986,7 +4986,7 @@
         <v>2024.0</v>
       </c>
       <c r="C347" t="n" s="2">
-        <v>45523.0</v>
+        <v>45509.0</v>
       </c>
       <c r="D347" t="n">
         <v>1.0</v>
@@ -5000,7 +5000,7 @@
         <v>2024.0</v>
       </c>
       <c r="C348" t="n" s="2">
-        <v>45551.0</v>
+        <v>45523.0</v>
       </c>
       <c r="D348" t="n">
         <v>1.0</v>
@@ -5014,7 +5014,7 @@
         <v>2024.0</v>
       </c>
       <c r="C349" t="n" s="2">
-        <v>45558.0</v>
+        <v>45551.0</v>
       </c>
       <c r="D349" t="n">
         <v>1.0</v>
@@ -5028,10 +5028,10 @@
         <v>2024.0</v>
       </c>
       <c r="C350" t="n" s="2">
-        <v>45572.0</v>
+        <v>45558.0</v>
       </c>
       <c r="D350" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="351">
@@ -5042,10 +5042,10 @@
         <v>2024.0</v>
       </c>
       <c r="C351" t="n" s="2">
-        <v>45593.0</v>
+        <v>45572.0</v>
       </c>
       <c r="D351" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="352">
@@ -5056,10 +5056,10 @@
         <v>2024.0</v>
       </c>
       <c r="C352" t="n" s="2">
-        <v>45614.0</v>
+        <v>45593.0</v>
       </c>
       <c r="D352" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="353">
@@ -5070,10 +5070,10 @@
         <v>2024.0</v>
       </c>
       <c r="C353" t="n" s="2">
-        <v>45621.0</v>
+        <v>45614.0</v>
       </c>
       <c r="D353" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="354">
@@ -5084,7 +5084,7 @@
         <v>2024.0</v>
       </c>
       <c r="C354" t="n" s="2">
-        <v>45635.0</v>
+        <v>45621.0</v>
       </c>
       <c r="D354" t="n">
         <v>1.0</v>
@@ -5098,7 +5098,7 @@
         <v>2024.0</v>
       </c>
       <c r="C355" t="n" s="2">
-        <v>45649.0</v>
+        <v>45635.0</v>
       </c>
       <c r="D355" t="n">
         <v>1.0</v>
@@ -5109,13 +5109,13 @@
         <v>6</v>
       </c>
       <c r="B356" t="n">
-        <v>2025.0</v>
+        <v>2024.0</v>
       </c>
       <c r="C356" t="n" s="2">
-        <v>45665.0</v>
+        <v>45649.0</v>
       </c>
       <c r="D356" t="n">
-        <v>9.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="357">
@@ -5126,10 +5126,10 @@
         <v>2025.0</v>
       </c>
       <c r="C357" t="n" s="2">
-        <v>45672.0</v>
+        <v>45665.0</v>
       </c>
       <c r="D357" t="n">
-        <v>3.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="358">
@@ -5140,10 +5140,10 @@
         <v>2025.0</v>
       </c>
       <c r="C358" t="n" s="2">
-        <v>45679.0</v>
+        <v>45672.0</v>
       </c>
       <c r="D358" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="359">
@@ -5154,10 +5154,10 @@
         <v>2025.0</v>
       </c>
       <c r="C359" t="n" s="2">
-        <v>45686.0</v>
+        <v>45679.0</v>
       </c>
       <c r="D359" t="n">
-        <v>8.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="360">
@@ -5168,10 +5168,10 @@
         <v>2025.0</v>
       </c>
       <c r="C360" t="n" s="2">
-        <v>45693.0</v>
+        <v>45686.0</v>
       </c>
       <c r="D360" t="n">
-        <v>3.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="361">
@@ -5182,10 +5182,10 @@
         <v>2025.0</v>
       </c>
       <c r="C361" t="n" s="2">
-        <v>45700.0</v>
+        <v>45693.0</v>
       </c>
       <c r="D361" t="n">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="362">
@@ -5196,10 +5196,10 @@
         <v>2025.0</v>
       </c>
       <c r="C362" t="n" s="2">
-        <v>45707.0</v>
+        <v>45700.0</v>
       </c>
       <c r="D362" t="n">
-        <v>8.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="363">
@@ -5210,10 +5210,10 @@
         <v>2025.0</v>
       </c>
       <c r="C363" t="n" s="2">
-        <v>45714.0</v>
+        <v>45707.0</v>
       </c>
       <c r="D363" t="n">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="364">
@@ -5224,10 +5224,10 @@
         <v>2025.0</v>
       </c>
       <c r="C364" t="n" s="2">
-        <v>45721.0</v>
+        <v>45714.0</v>
       </c>
       <c r="D364" t="n">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="365">
@@ -5238,10 +5238,10 @@
         <v>2025.0</v>
       </c>
       <c r="C365" t="n" s="2">
-        <v>45728.0</v>
+        <v>45721.0</v>
       </c>
       <c r="D365" t="n">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="366">
@@ -5252,10 +5252,10 @@
         <v>2025.0</v>
       </c>
       <c r="C366" t="n" s="2">
-        <v>45735.0</v>
+        <v>45728.0</v>
       </c>
       <c r="D366" t="n">
-        <v>4.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="367">
@@ -5266,10 +5266,10 @@
         <v>2025.0</v>
       </c>
       <c r="C367" t="n" s="2">
-        <v>45742.0</v>
+        <v>45735.0</v>
       </c>
       <c r="D367" t="n">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="368">
@@ -5280,10 +5280,10 @@
         <v>2025.0</v>
       </c>
       <c r="C368" t="n" s="2">
-        <v>45749.0</v>
+        <v>45742.0</v>
       </c>
       <c r="D368" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="369">
@@ -5294,10 +5294,10 @@
         <v>2025.0</v>
       </c>
       <c r="C369" t="n" s="2">
-        <v>45756.0</v>
+        <v>45749.0</v>
       </c>
       <c r="D369" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="370">
@@ -5308,10 +5308,10 @@
         <v>2025.0</v>
       </c>
       <c r="C370" t="n" s="2">
-        <v>45763.0</v>
+        <v>45756.0</v>
       </c>
       <c r="D370" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="371">
@@ -5322,7 +5322,7 @@
         <v>2025.0</v>
       </c>
       <c r="C371" t="n" s="2">
-        <v>45770.0</v>
+        <v>45763.0</v>
       </c>
       <c r="D371" t="n">
         <v>4.0</v>
@@ -5336,10 +5336,10 @@
         <v>2025.0</v>
       </c>
       <c r="C372" t="n" s="2">
-        <v>45777.0</v>
+        <v>45770.0</v>
       </c>
       <c r="D372" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="373">
@@ -5350,7 +5350,7 @@
         <v>2025.0</v>
       </c>
       <c r="C373" t="n" s="2">
-        <v>45784.0</v>
+        <v>45777.0</v>
       </c>
       <c r="D373" t="n">
         <v>1.0</v>
@@ -5364,7 +5364,7 @@
         <v>2025.0</v>
       </c>
       <c r="C374" t="n" s="2">
-        <v>45791.0</v>
+        <v>45784.0</v>
       </c>
       <c r="D374" t="n">
         <v>1.0</v>
@@ -5378,7 +5378,7 @@
         <v>2025.0</v>
       </c>
       <c r="C375" t="n" s="2">
-        <v>45840.0</v>
+        <v>45791.0</v>
       </c>
       <c r="D375" t="n">
         <v>1.0</v>
@@ -5392,7 +5392,7 @@
         <v>2025.0</v>
       </c>
       <c r="C376" t="n" s="2">
-        <v>46001.0</v>
+        <v>45840.0</v>
       </c>
       <c r="D376" t="n">
         <v>1.0</v>
@@ -5403,10 +5403,10 @@
         <v>6</v>
       </c>
       <c r="B377" t="n">
-        <v>2026.0</v>
+        <v>2025.0</v>
       </c>
       <c r="C377" t="n" s="2">
-        <v>46037.0</v>
+        <v>46001.0</v>
       </c>
       <c r="D377" t="n">
         <v>1.0</v>
@@ -5414,13 +5414,13 @@
     </row>
     <row r="378">
       <c r="A378" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B378" t="n">
-        <v>2021.0</v>
+        <v>2026.0</v>
       </c>
       <c r="C378" t="n" s="2">
-        <v>44561.0</v>
+        <v>46037.0</v>
       </c>
       <c r="D378" t="n">
         <v>1.0</v>
@@ -5431,10 +5431,10 @@
         <v>7</v>
       </c>
       <c r="B379" t="n">
-        <v>2022.0</v>
+        <v>2021.0</v>
       </c>
       <c r="C379" t="n" s="2">
-        <v>44569.0</v>
+        <v>44561.0</v>
       </c>
       <c r="D379" t="n">
         <v>1.0</v>
@@ -5448,10 +5448,10 @@
         <v>2022.0</v>
       </c>
       <c r="C380" t="n" s="2">
-        <v>44576.0</v>
+        <v>44569.0</v>
       </c>
       <c r="D380" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="381">
@@ -5462,10 +5462,10 @@
         <v>2022.0</v>
       </c>
       <c r="C381" t="n" s="2">
-        <v>44583.0</v>
+        <v>44576.0</v>
       </c>
       <c r="D381" t="n">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="382">
@@ -5476,10 +5476,10 @@
         <v>2022.0</v>
       </c>
       <c r="C382" t="n" s="2">
-        <v>44590.0</v>
+        <v>44583.0</v>
       </c>
       <c r="D382" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="383">
@@ -5490,10 +5490,10 @@
         <v>2022.0</v>
       </c>
       <c r="C383" t="n" s="2">
-        <v>44604.0</v>
+        <v>44590.0</v>
       </c>
       <c r="D383" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="384">
@@ -5504,7 +5504,7 @@
         <v>2022.0</v>
       </c>
       <c r="C384" t="n" s="2">
-        <v>44611.0</v>
+        <v>44604.0</v>
       </c>
       <c r="D384" t="n">
         <v>3.0</v>
@@ -5518,10 +5518,10 @@
         <v>2022.0</v>
       </c>
       <c r="C385" t="n" s="2">
-        <v>44618.0</v>
+        <v>44611.0</v>
       </c>
       <c r="D385" t="n">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="386">
@@ -5532,7 +5532,7 @@
         <v>2022.0</v>
       </c>
       <c r="C386" t="n" s="2">
-        <v>44625.0</v>
+        <v>44618.0</v>
       </c>
       <c r="D386" t="n">
         <v>5.0</v>
@@ -5546,10 +5546,10 @@
         <v>2022.0</v>
       </c>
       <c r="C387" t="n" s="2">
-        <v>44632.0</v>
+        <v>44625.0</v>
       </c>
       <c r="D387" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="388">
@@ -5560,10 +5560,10 @@
         <v>2022.0</v>
       </c>
       <c r="C388" t="n" s="2">
-        <v>44639.0</v>
+        <v>44632.0</v>
       </c>
       <c r="D388" t="n">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="389">
@@ -5574,10 +5574,10 @@
         <v>2022.0</v>
       </c>
       <c r="C389" t="n" s="2">
-        <v>44646.0</v>
+        <v>44639.0</v>
       </c>
       <c r="D389" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="390">
@@ -5588,10 +5588,10 @@
         <v>2022.0</v>
       </c>
       <c r="C390" t="n" s="2">
-        <v>44653.0</v>
+        <v>44646.0</v>
       </c>
       <c r="D390" t="n">
-        <v>9.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="391">
@@ -5602,10 +5602,10 @@
         <v>2022.0</v>
       </c>
       <c r="C391" t="n" s="2">
-        <v>44660.0</v>
+        <v>44653.0</v>
       </c>
       <c r="D391" t="n">
-        <v>6.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="392">
@@ -5616,10 +5616,10 @@
         <v>2022.0</v>
       </c>
       <c r="C392" t="n" s="2">
-        <v>44667.0</v>
+        <v>44660.0</v>
       </c>
       <c r="D392" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="393">
@@ -5630,10 +5630,10 @@
         <v>2022.0</v>
       </c>
       <c r="C393" t="n" s="2">
-        <v>44674.0</v>
+        <v>44667.0</v>
       </c>
       <c r="D393" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="394">
@@ -5644,10 +5644,10 @@
         <v>2022.0</v>
       </c>
       <c r="C394" t="n" s="2">
-        <v>44681.0</v>
+        <v>44674.0</v>
       </c>
       <c r="D394" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="395">
@@ -5658,10 +5658,10 @@
         <v>2022.0</v>
       </c>
       <c r="C395" t="n" s="2">
-        <v>44688.0</v>
+        <v>44681.0</v>
       </c>
       <c r="D395" t="n">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="396">
@@ -5672,10 +5672,10 @@
         <v>2022.0</v>
       </c>
       <c r="C396" t="n" s="2">
-        <v>44695.0</v>
+        <v>44688.0</v>
       </c>
       <c r="D396" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="397">
@@ -5686,10 +5686,10 @@
         <v>2022.0</v>
       </c>
       <c r="C397" t="n" s="2">
-        <v>44702.0</v>
+        <v>44695.0</v>
       </c>
       <c r="D397" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="398">
@@ -5700,10 +5700,10 @@
         <v>2022.0</v>
       </c>
       <c r="C398" t="n" s="2">
-        <v>44709.0</v>
+        <v>44702.0</v>
       </c>
       <c r="D398" t="n">
-        <v>8.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="399">
@@ -5714,10 +5714,10 @@
         <v>2022.0</v>
       </c>
       <c r="C399" t="n" s="2">
-        <v>44716.0</v>
+        <v>44709.0</v>
       </c>
       <c r="D399" t="n">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="400">
@@ -5728,10 +5728,10 @@
         <v>2022.0</v>
       </c>
       <c r="C400" t="n" s="2">
-        <v>44723.0</v>
+        <v>44716.0</v>
       </c>
       <c r="D400" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="401">
@@ -5742,10 +5742,10 @@
         <v>2022.0</v>
       </c>
       <c r="C401" t="n" s="2">
-        <v>44730.0</v>
+        <v>44723.0</v>
       </c>
       <c r="D401" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="402">
@@ -5756,7 +5756,7 @@
         <v>2022.0</v>
       </c>
       <c r="C402" t="n" s="2">
-        <v>44737.0</v>
+        <v>44730.0</v>
       </c>
       <c r="D402" t="n">
         <v>4.0</v>
@@ -5770,10 +5770,10 @@
         <v>2022.0</v>
       </c>
       <c r="C403" t="n" s="2">
-        <v>44744.0</v>
+        <v>44737.0</v>
       </c>
       <c r="D403" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="404">
@@ -5784,10 +5784,10 @@
         <v>2022.0</v>
       </c>
       <c r="C404" t="n" s="2">
-        <v>44751.0</v>
+        <v>44744.0</v>
       </c>
       <c r="D404" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="405">
@@ -5798,10 +5798,10 @@
         <v>2022.0</v>
       </c>
       <c r="C405" t="n" s="2">
-        <v>44758.0</v>
+        <v>44751.0</v>
       </c>
       <c r="D405" t="n">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="406">
@@ -5812,10 +5812,10 @@
         <v>2022.0</v>
       </c>
       <c r="C406" t="n" s="2">
-        <v>44765.0</v>
+        <v>44758.0</v>
       </c>
       <c r="D406" t="n">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="407">
@@ -5826,10 +5826,10 @@
         <v>2022.0</v>
       </c>
       <c r="C407" t="n" s="2">
-        <v>44779.0</v>
+        <v>44765.0</v>
       </c>
       <c r="D407" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="408">
@@ -5840,10 +5840,10 @@
         <v>2022.0</v>
       </c>
       <c r="C408" t="n" s="2">
-        <v>44786.0</v>
+        <v>44779.0</v>
       </c>
       <c r="D408" t="n">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="409">
@@ -5854,10 +5854,10 @@
         <v>2022.0</v>
       </c>
       <c r="C409" t="n" s="2">
-        <v>44863.0</v>
+        <v>44786.0</v>
       </c>
       <c r="D409" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="410">
@@ -5868,10 +5868,10 @@
         <v>2022.0</v>
       </c>
       <c r="C410" t="n" s="2">
-        <v>44870.0</v>
+        <v>44863.0</v>
       </c>
       <c r="D410" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="411">
@@ -5882,10 +5882,10 @@
         <v>2022.0</v>
       </c>
       <c r="C411" t="n" s="2">
-        <v>44884.0</v>
+        <v>44870.0</v>
       </c>
       <c r="D411" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="412">
@@ -5896,7 +5896,7 @@
         <v>2022.0</v>
       </c>
       <c r="C412" t="n" s="2">
-        <v>44891.0</v>
+        <v>44884.0</v>
       </c>
       <c r="D412" t="n">
         <v>2.0</v>
@@ -5910,10 +5910,10 @@
         <v>2022.0</v>
       </c>
       <c r="C413" t="n" s="2">
-        <v>44898.0</v>
+        <v>44891.0</v>
       </c>
       <c r="D413" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="414">
@@ -5924,10 +5924,10 @@
         <v>2022.0</v>
       </c>
       <c r="C414" t="n" s="2">
-        <v>44912.0</v>
+        <v>44898.0</v>
       </c>
       <c r="D414" t="n">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="415">
@@ -5938,10 +5938,10 @@
         <v>2022.0</v>
       </c>
       <c r="C415" t="n" s="2">
-        <v>44919.0</v>
+        <v>44912.0</v>
       </c>
       <c r="D415" t="n">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="416">
@@ -5952,10 +5952,10 @@
         <v>2022.0</v>
       </c>
       <c r="C416" t="n" s="2">
-        <v>44926.0</v>
+        <v>44919.0</v>
       </c>
       <c r="D416" t="n">
-        <v>12.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="417">
@@ -5963,13 +5963,13 @@
         <v>7</v>
       </c>
       <c r="B417" t="n">
-        <v>2023.0</v>
+        <v>2022.0</v>
       </c>
       <c r="C417" t="n" s="2">
-        <v>44934.0</v>
+        <v>44926.0</v>
       </c>
       <c r="D417" t="n">
-        <v>4.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="418">
@@ -5980,10 +5980,10 @@
         <v>2023.0</v>
       </c>
       <c r="C418" t="n" s="2">
-        <v>44941.0</v>
+        <v>44934.0</v>
       </c>
       <c r="D418" t="n">
-        <v>16.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="419">
@@ -5994,10 +5994,10 @@
         <v>2023.0</v>
       </c>
       <c r="C419" t="n" s="2">
-        <v>44948.0</v>
+        <v>44941.0</v>
       </c>
       <c r="D419" t="n">
-        <v>5.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="420">
@@ -6008,10 +6008,10 @@
         <v>2023.0</v>
       </c>
       <c r="C420" t="n" s="2">
-        <v>44955.0</v>
+        <v>44948.0</v>
       </c>
       <c r="D420" t="n">
-        <v>19.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="421">
@@ -6022,10 +6022,10 @@
         <v>2023.0</v>
       </c>
       <c r="C421" t="n" s="2">
-        <v>44962.0</v>
+        <v>44955.0</v>
       </c>
       <c r="D421" t="n">
-        <v>22.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="422">
@@ -6036,10 +6036,10 @@
         <v>2023.0</v>
       </c>
       <c r="C422" t="n" s="2">
-        <v>44969.0</v>
+        <v>44962.0</v>
       </c>
       <c r="D422" t="n">
-        <v>9.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="423">
@@ -6050,10 +6050,10 @@
         <v>2023.0</v>
       </c>
       <c r="C423" t="n" s="2">
-        <v>44976.0</v>
+        <v>44969.0</v>
       </c>
       <c r="D423" t="n">
-        <v>22.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="424">
@@ -6064,10 +6064,10 @@
         <v>2023.0</v>
       </c>
       <c r="C424" t="n" s="2">
-        <v>44983.0</v>
+        <v>44976.0</v>
       </c>
       <c r="D424" t="n">
-        <v>29.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="425">
@@ -6078,10 +6078,10 @@
         <v>2023.0</v>
       </c>
       <c r="C425" t="n" s="2">
-        <v>44990.0</v>
+        <v>44983.0</v>
       </c>
       <c r="D425" t="n">
-        <v>5.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="426">
@@ -6092,10 +6092,10 @@
         <v>2023.0</v>
       </c>
       <c r="C426" t="n" s="2">
-        <v>44997.0</v>
+        <v>44990.0</v>
       </c>
       <c r="D426" t="n">
-        <v>24.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="427">
@@ -6106,10 +6106,10 @@
         <v>2023.0</v>
       </c>
       <c r="C427" t="n" s="2">
-        <v>45004.0</v>
+        <v>44997.0</v>
       </c>
       <c r="D427" t="n">
-        <v>8.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="428">
@@ -6120,10 +6120,10 @@
         <v>2023.0</v>
       </c>
       <c r="C428" t="n" s="2">
-        <v>45011.0</v>
+        <v>45004.0</v>
       </c>
       <c r="D428" t="n">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="429">
@@ -6134,10 +6134,10 @@
         <v>2023.0</v>
       </c>
       <c r="C429" t="n" s="2">
-        <v>45018.0</v>
+        <v>45011.0</v>
       </c>
       <c r="D429" t="n">
-        <v>18.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="430">
@@ -6148,10 +6148,10 @@
         <v>2023.0</v>
       </c>
       <c r="C430" t="n" s="2">
-        <v>45025.0</v>
+        <v>45018.0</v>
       </c>
       <c r="D430" t="n">
-        <v>13.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="431">
@@ -6162,10 +6162,10 @@
         <v>2023.0</v>
       </c>
       <c r="C431" t="n" s="2">
-        <v>45032.0</v>
+        <v>45025.0</v>
       </c>
       <c r="D431" t="n">
-        <v>18.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="432">
@@ -6176,10 +6176,10 @@
         <v>2023.0</v>
       </c>
       <c r="C432" t="n" s="2">
-        <v>45039.0</v>
+        <v>45032.0</v>
       </c>
       <c r="D432" t="n">
-        <v>15.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="433">
@@ -6190,10 +6190,10 @@
         <v>2023.0</v>
       </c>
       <c r="C433" t="n" s="2">
-        <v>45046.0</v>
+        <v>45039.0</v>
       </c>
       <c r="D433" t="n">
-        <v>12.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="434">
@@ -6204,10 +6204,10 @@
         <v>2023.0</v>
       </c>
       <c r="C434" t="n" s="2">
-        <v>45053.0</v>
+        <v>45046.0</v>
       </c>
       <c r="D434" t="n">
-        <v>6.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="435">
@@ -6218,10 +6218,10 @@
         <v>2023.0</v>
       </c>
       <c r="C435" t="n" s="2">
-        <v>45060.0</v>
+        <v>45053.0</v>
       </c>
       <c r="D435" t="n">
-        <v>11.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="436">
@@ -6232,10 +6232,10 @@
         <v>2023.0</v>
       </c>
       <c r="C436" t="n" s="2">
-        <v>45067.0</v>
+        <v>45060.0</v>
       </c>
       <c r="D436" t="n">
-        <v>8.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="437">
@@ -6246,7 +6246,7 @@
         <v>2023.0</v>
       </c>
       <c r="C437" t="n" s="2">
-        <v>45074.0</v>
+        <v>45067.0</v>
       </c>
       <c r="D437" t="n">
         <v>8.0</v>
@@ -6260,10 +6260,10 @@
         <v>2023.0</v>
       </c>
       <c r="C438" t="n" s="2">
-        <v>45081.0</v>
+        <v>45074.0</v>
       </c>
       <c r="D438" t="n">
-        <v>5.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="439">
@@ -6274,10 +6274,10 @@
         <v>2023.0</v>
       </c>
       <c r="C439" t="n" s="2">
-        <v>45088.0</v>
+        <v>45081.0</v>
       </c>
       <c r="D439" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="440">
@@ -6288,10 +6288,10 @@
         <v>2023.0</v>
       </c>
       <c r="C440" t="n" s="2">
-        <v>45095.0</v>
+        <v>45088.0</v>
       </c>
       <c r="D440" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="441">
@@ -6302,10 +6302,10 @@
         <v>2023.0</v>
       </c>
       <c r="C441" t="n" s="2">
-        <v>45102.0</v>
+        <v>45095.0</v>
       </c>
       <c r="D441" t="n">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="442">
@@ -6316,10 +6316,10 @@
         <v>2023.0</v>
       </c>
       <c r="C442" t="n" s="2">
-        <v>45109.0</v>
+        <v>45102.0</v>
       </c>
       <c r="D442" t="n">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="443">
@@ -6330,10 +6330,10 @@
         <v>2023.0</v>
       </c>
       <c r="C443" t="n" s="2">
-        <v>45116.0</v>
+        <v>45109.0</v>
       </c>
       <c r="D443" t="n">
-        <v>3.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="444">
@@ -6344,10 +6344,10 @@
         <v>2023.0</v>
       </c>
       <c r="C444" t="n" s="2">
-        <v>45123.0</v>
+        <v>45116.0</v>
       </c>
       <c r="D444" t="n">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="445">
@@ -6358,7 +6358,7 @@
         <v>2023.0</v>
       </c>
       <c r="C445" t="n" s="2">
-        <v>45130.0</v>
+        <v>45123.0</v>
       </c>
       <c r="D445" t="n">
         <v>6.0</v>
@@ -6372,10 +6372,10 @@
         <v>2023.0</v>
       </c>
       <c r="C446" t="n" s="2">
-        <v>45137.0</v>
+        <v>45130.0</v>
       </c>
       <c r="D446" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="447">
@@ -6386,7 +6386,7 @@
         <v>2023.0</v>
       </c>
       <c r="C447" t="n" s="2">
-        <v>45144.0</v>
+        <v>45137.0</v>
       </c>
       <c r="D447" t="n">
         <v>2.0</v>
@@ -6400,7 +6400,7 @@
         <v>2023.0</v>
       </c>
       <c r="C448" t="n" s="2">
-        <v>45151.0</v>
+        <v>45144.0</v>
       </c>
       <c r="D448" t="n">
         <v>2.0</v>
@@ -6414,7 +6414,7 @@
         <v>2023.0</v>
       </c>
       <c r="C449" t="n" s="2">
-        <v>45165.0</v>
+        <v>45151.0</v>
       </c>
       <c r="D449" t="n">
         <v>2.0</v>
@@ -6428,7 +6428,7 @@
         <v>2023.0</v>
       </c>
       <c r="C450" t="n" s="2">
-        <v>45172.0</v>
+        <v>45165.0</v>
       </c>
       <c r="D450" t="n">
         <v>2.0</v>
@@ -6442,10 +6442,10 @@
         <v>2023.0</v>
       </c>
       <c r="C451" t="n" s="2">
-        <v>45179.0</v>
+        <v>45172.0</v>
       </c>
       <c r="D451" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="452">
@@ -6456,7 +6456,7 @@
         <v>2023.0</v>
       </c>
       <c r="C452" t="n" s="2">
-        <v>45186.0</v>
+        <v>45179.0</v>
       </c>
       <c r="D452" t="n">
         <v>1.0</v>
@@ -6470,7 +6470,7 @@
         <v>2023.0</v>
       </c>
       <c r="C453" t="n" s="2">
-        <v>45193.0</v>
+        <v>45186.0</v>
       </c>
       <c r="D453" t="n">
         <v>1.0</v>
@@ -6484,7 +6484,7 @@
         <v>2023.0</v>
       </c>
       <c r="C454" t="n" s="2">
-        <v>45200.0</v>
+        <v>45193.0</v>
       </c>
       <c r="D454" t="n">
         <v>1.0</v>
@@ -6498,7 +6498,7 @@
         <v>2023.0</v>
       </c>
       <c r="C455" t="n" s="2">
-        <v>45207.0</v>
+        <v>45200.0</v>
       </c>
       <c r="D455" t="n">
         <v>1.0</v>
@@ -6512,7 +6512,7 @@
         <v>2023.0</v>
       </c>
       <c r="C456" t="n" s="2">
-        <v>45235.0</v>
+        <v>45207.0</v>
       </c>
       <c r="D456" t="n">
         <v>1.0</v>
@@ -6526,10 +6526,10 @@
         <v>2023.0</v>
       </c>
       <c r="C457" t="n" s="2">
-        <v>45242.0</v>
+        <v>45235.0</v>
       </c>
       <c r="D457" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="458">
@@ -6540,10 +6540,10 @@
         <v>2023.0</v>
       </c>
       <c r="C458" t="n" s="2">
-        <v>45249.0</v>
+        <v>45242.0</v>
       </c>
       <c r="D458" t="n">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="459">
@@ -6554,10 +6554,10 @@
         <v>2023.0</v>
       </c>
       <c r="C459" t="n" s="2">
-        <v>45256.0</v>
+        <v>45249.0</v>
       </c>
       <c r="D459" t="n">
-        <v>9.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="460">
@@ -6568,10 +6568,10 @@
         <v>2023.0</v>
       </c>
       <c r="C460" t="n" s="2">
-        <v>45263.0</v>
+        <v>45256.0</v>
       </c>
       <c r="D460" t="n">
-        <v>12.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="461">
@@ -6582,10 +6582,10 @@
         <v>2023.0</v>
       </c>
       <c r="C461" t="n" s="2">
-        <v>45270.0</v>
+        <v>45263.0</v>
       </c>
       <c r="D461" t="n">
-        <v>6.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="462">
@@ -6596,10 +6596,10 @@
         <v>2023.0</v>
       </c>
       <c r="C462" t="n" s="2">
-        <v>45277.0</v>
+        <v>45270.0</v>
       </c>
       <c r="D462" t="n">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="463">
@@ -6610,7 +6610,7 @@
         <v>2023.0</v>
       </c>
       <c r="C463" t="n" s="2">
-        <v>45284.0</v>
+        <v>45277.0</v>
       </c>
       <c r="D463" t="n">
         <v>7.0</v>
@@ -6624,10 +6624,10 @@
         <v>2023.0</v>
       </c>
       <c r="C464" t="n" s="2">
-        <v>45291.0</v>
+        <v>45284.0</v>
       </c>
       <c r="D464" t="n">
-        <v>13.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="465">
@@ -6635,13 +6635,13 @@
         <v>7</v>
       </c>
       <c r="B465" t="n">
-        <v>2024.0</v>
+        <v>2023.0</v>
       </c>
       <c r="C465" t="n" s="2">
-        <v>45299.0</v>
+        <v>45291.0</v>
       </c>
       <c r="D465" t="n">
-        <v>6.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="466">
@@ -6652,10 +6652,10 @@
         <v>2024.0</v>
       </c>
       <c r="C466" t="n" s="2">
-        <v>45306.0</v>
+        <v>45299.0</v>
       </c>
       <c r="D466" t="n">
-        <v>11.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="467">
@@ -6666,10 +6666,10 @@
         <v>2024.0</v>
       </c>
       <c r="C467" t="n" s="2">
-        <v>45313.0</v>
+        <v>45306.0</v>
       </c>
       <c r="D467" t="n">
-        <v>5.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="468">
@@ -6680,10 +6680,10 @@
         <v>2024.0</v>
       </c>
       <c r="C468" t="n" s="2">
-        <v>45320.0</v>
+        <v>45313.0</v>
       </c>
       <c r="D468" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="469">
@@ -6694,10 +6694,10 @@
         <v>2024.0</v>
       </c>
       <c r="C469" t="n" s="2">
-        <v>45327.0</v>
+        <v>45320.0</v>
       </c>
       <c r="D469" t="n">
-        <v>9.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="470">
@@ -6708,10 +6708,10 @@
         <v>2024.0</v>
       </c>
       <c r="C470" t="n" s="2">
-        <v>45334.0</v>
+        <v>45327.0</v>
       </c>
       <c r="D470" t="n">
-        <v>3.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="471">
@@ -6722,10 +6722,10 @@
         <v>2024.0</v>
       </c>
       <c r="C471" t="n" s="2">
-        <v>45341.0</v>
+        <v>45334.0</v>
       </c>
       <c r="D471" t="n">
-        <v>21.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="472">
@@ -6736,10 +6736,10 @@
         <v>2024.0</v>
       </c>
       <c r="C472" t="n" s="2">
-        <v>45348.0</v>
+        <v>45341.0</v>
       </c>
       <c r="D472" t="n">
-        <v>1.0</v>
+        <v>21.0</v>
       </c>
     </row>
     <row r="473">
@@ -6750,10 +6750,10 @@
         <v>2024.0</v>
       </c>
       <c r="C473" t="n" s="2">
-        <v>45355.0</v>
+        <v>45348.0</v>
       </c>
       <c r="D473" t="n">
-        <v>9.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="474">
@@ -6764,10 +6764,10 @@
         <v>2024.0</v>
       </c>
       <c r="C474" t="n" s="2">
-        <v>45362.0</v>
+        <v>45355.0</v>
       </c>
       <c r="D474" t="n">
-        <v>4.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="475">
@@ -6778,10 +6778,10 @@
         <v>2024.0</v>
       </c>
       <c r="C475" t="n" s="2">
-        <v>45369.0</v>
+        <v>45362.0</v>
       </c>
       <c r="D475" t="n">
-        <v>14.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="476">
@@ -6792,10 +6792,10 @@
         <v>2024.0</v>
       </c>
       <c r="C476" t="n" s="2">
-        <v>45376.0</v>
+        <v>45369.0</v>
       </c>
       <c r="D476" t="n">
-        <v>4.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="477">
@@ -6806,10 +6806,10 @@
         <v>2024.0</v>
       </c>
       <c r="C477" t="n" s="2">
-        <v>45383.0</v>
+        <v>45376.0</v>
       </c>
       <c r="D477" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="478">
@@ -6820,10 +6820,10 @@
         <v>2024.0</v>
       </c>
       <c r="C478" t="n" s="2">
-        <v>45390.0</v>
+        <v>45383.0</v>
       </c>
       <c r="D478" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="479">
@@ -6834,7 +6834,7 @@
         <v>2024.0</v>
       </c>
       <c r="C479" t="n" s="2">
-        <v>45397.0</v>
+        <v>45390.0</v>
       </c>
       <c r="D479" t="n">
         <v>1.0</v>
@@ -6848,10 +6848,10 @@
         <v>2024.0</v>
       </c>
       <c r="C480" t="n" s="2">
-        <v>45404.0</v>
+        <v>45397.0</v>
       </c>
       <c r="D480" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="481">
@@ -6862,10 +6862,10 @@
         <v>2024.0</v>
       </c>
       <c r="C481" t="n" s="2">
-        <v>45411.0</v>
+        <v>45404.0</v>
       </c>
       <c r="D481" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="482">
@@ -6876,10 +6876,10 @@
         <v>2024.0</v>
       </c>
       <c r="C482" t="n" s="2">
-        <v>45439.0</v>
+        <v>45411.0</v>
       </c>
       <c r="D482" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="483">
@@ -6890,10 +6890,10 @@
         <v>2024.0</v>
       </c>
       <c r="C483" t="n" s="2">
-        <v>45446.0</v>
+        <v>45439.0</v>
       </c>
       <c r="D483" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="484">
@@ -6904,7 +6904,7 @@
         <v>2024.0</v>
       </c>
       <c r="C484" t="n" s="2">
-        <v>45460.0</v>
+        <v>45446.0</v>
       </c>
       <c r="D484" t="n">
         <v>1.0</v>
@@ -6918,7 +6918,7 @@
         <v>2024.0</v>
       </c>
       <c r="C485" t="n" s="2">
-        <v>45481.0</v>
+        <v>45460.0</v>
       </c>
       <c r="D485" t="n">
         <v>1.0</v>
@@ -6932,7 +6932,7 @@
         <v>2024.0</v>
       </c>
       <c r="C486" t="n" s="2">
-        <v>45516.0</v>
+        <v>45481.0</v>
       </c>
       <c r="D486" t="n">
         <v>1.0</v>
@@ -6946,7 +6946,7 @@
         <v>2024.0</v>
       </c>
       <c r="C487" t="n" s="2">
-        <v>45551.0</v>
+        <v>45516.0</v>
       </c>
       <c r="D487" t="n">
         <v>1.0</v>
@@ -6960,7 +6960,7 @@
         <v>2024.0</v>
       </c>
       <c r="C488" t="n" s="2">
-        <v>45579.0</v>
+        <v>45551.0</v>
       </c>
       <c r="D488" t="n">
         <v>1.0</v>
@@ -6974,7 +6974,7 @@
         <v>2024.0</v>
       </c>
       <c r="C489" t="n" s="2">
-        <v>45614.0</v>
+        <v>45579.0</v>
       </c>
       <c r="D489" t="n">
         <v>1.0</v>
@@ -6988,10 +6988,10 @@
         <v>2024.0</v>
       </c>
       <c r="C490" t="n" s="2">
-        <v>45635.0</v>
+        <v>45614.0</v>
       </c>
       <c r="D490" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="491">
@@ -7002,10 +7002,10 @@
         <v>2024.0</v>
       </c>
       <c r="C491" t="n" s="2">
-        <v>45642.0</v>
+        <v>45635.0</v>
       </c>
       <c r="D491" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="492">
@@ -7016,10 +7016,10 @@
         <v>2024.0</v>
       </c>
       <c r="C492" t="n" s="2">
-        <v>45649.0</v>
+        <v>45642.0</v>
       </c>
       <c r="D492" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="493">
@@ -7030,10 +7030,10 @@
         <v>2024.0</v>
       </c>
       <c r="C493" t="n" s="2">
-        <v>45656.0</v>
+        <v>45649.0</v>
       </c>
       <c r="D493" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="494">
@@ -7041,13 +7041,13 @@
         <v>7</v>
       </c>
       <c r="B494" t="n">
-        <v>2025.0</v>
+        <v>2024.0</v>
       </c>
       <c r="C494" t="n" s="2">
-        <v>45665.0</v>
+        <v>45656.0</v>
       </c>
       <c r="D494" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="495">
@@ -7058,10 +7058,10 @@
         <v>2025.0</v>
       </c>
       <c r="C495" t="n" s="2">
-        <v>45672.0</v>
+        <v>45665.0</v>
       </c>
       <c r="D495" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="496">
@@ -7072,7 +7072,7 @@
         <v>2025.0</v>
       </c>
       <c r="C496" t="n" s="2">
-        <v>45686.0</v>
+        <v>45672.0</v>
       </c>
       <c r="D496" t="n">
         <v>2.0</v>
@@ -7086,10 +7086,10 @@
         <v>2025.0</v>
       </c>
       <c r="C497" t="n" s="2">
-        <v>45693.0</v>
+        <v>45686.0</v>
       </c>
       <c r="D497" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="498">
@@ -7100,10 +7100,10 @@
         <v>2025.0</v>
       </c>
       <c r="C498" t="n" s="2">
-        <v>45700.0</v>
+        <v>45693.0</v>
       </c>
       <c r="D498" t="n">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="499">
@@ -7114,10 +7114,10 @@
         <v>2025.0</v>
       </c>
       <c r="C499" t="n" s="2">
-        <v>45707.0</v>
+        <v>45700.0</v>
       </c>
       <c r="D499" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="500">
@@ -7128,10 +7128,10 @@
         <v>2025.0</v>
       </c>
       <c r="C500" t="n" s="2">
-        <v>45714.0</v>
+        <v>45707.0</v>
       </c>
       <c r="D500" t="n">
-        <v>8.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="501">
@@ -7142,10 +7142,10 @@
         <v>2025.0</v>
       </c>
       <c r="C501" t="n" s="2">
-        <v>45721.0</v>
+        <v>45714.0</v>
       </c>
       <c r="D501" t="n">
-        <v>11.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="502">
@@ -7156,10 +7156,10 @@
         <v>2025.0</v>
       </c>
       <c r="C502" t="n" s="2">
-        <v>45728.0</v>
+        <v>45721.0</v>
       </c>
       <c r="D502" t="n">
-        <v>6.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="503">
@@ -7170,10 +7170,10 @@
         <v>2025.0</v>
       </c>
       <c r="C503" t="n" s="2">
-        <v>45735.0</v>
+        <v>45728.0</v>
       </c>
       <c r="D503" t="n">
-        <v>19.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="504">
@@ -7184,10 +7184,10 @@
         <v>2025.0</v>
       </c>
       <c r="C504" t="n" s="2">
-        <v>45742.0</v>
+        <v>45735.0</v>
       </c>
       <c r="D504" t="n">
-        <v>17.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="505">
@@ -7198,10 +7198,10 @@
         <v>2025.0</v>
       </c>
       <c r="C505" t="n" s="2">
-        <v>45749.0</v>
+        <v>45742.0</v>
       </c>
       <c r="D505" t="n">
-        <v>5.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="506">
@@ -7212,10 +7212,10 @@
         <v>2025.0</v>
       </c>
       <c r="C506" t="n" s="2">
-        <v>45756.0</v>
+        <v>45749.0</v>
       </c>
       <c r="D506" t="n">
-        <v>9.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="507">
@@ -7226,10 +7226,10 @@
         <v>2025.0</v>
       </c>
       <c r="C507" t="n" s="2">
-        <v>45763.0</v>
+        <v>45756.0</v>
       </c>
       <c r="D507" t="n">
-        <v>1.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="508">
@@ -7240,7 +7240,7 @@
         <v>2025.0</v>
       </c>
       <c r="C508" t="n" s="2">
-        <v>45770.0</v>
+        <v>45763.0</v>
       </c>
       <c r="D508" t="n">
         <v>1.0</v>
@@ -7254,10 +7254,10 @@
         <v>2025.0</v>
       </c>
       <c r="C509" t="n" s="2">
-        <v>45784.0</v>
+        <v>45770.0</v>
       </c>
       <c r="D509" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="510">
@@ -7268,10 +7268,10 @@
         <v>2025.0</v>
       </c>
       <c r="C510" t="n" s="2">
-        <v>45791.0</v>
+        <v>45784.0</v>
       </c>
       <c r="D510" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="511">
@@ -7282,10 +7282,10 @@
         <v>2025.0</v>
       </c>
       <c r="C511" t="n" s="2">
-        <v>45805.0</v>
+        <v>45791.0</v>
       </c>
       <c r="D511" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="512">
@@ -7296,10 +7296,10 @@
         <v>2025.0</v>
       </c>
       <c r="C512" t="n" s="2">
-        <v>45826.0</v>
+        <v>45805.0</v>
       </c>
       <c r="D512" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="513">
@@ -7310,7 +7310,7 @@
         <v>2025.0</v>
       </c>
       <c r="C513" t="n" s="2">
-        <v>45861.0</v>
+        <v>45826.0</v>
       </c>
       <c r="D513" t="n">
         <v>2.0</v>
@@ -7324,10 +7324,10 @@
         <v>2025.0</v>
       </c>
       <c r="C514" t="n" s="2">
-        <v>45868.0</v>
+        <v>45861.0</v>
       </c>
       <c r="D514" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="515">
@@ -7338,7 +7338,7 @@
         <v>2025.0</v>
       </c>
       <c r="C515" t="n" s="2">
-        <v>45889.0</v>
+        <v>45868.0</v>
       </c>
       <c r="D515" t="n">
         <v>1.0</v>
@@ -7352,7 +7352,7 @@
         <v>2025.0</v>
       </c>
       <c r="C516" t="n" s="2">
-        <v>45924.0</v>
+        <v>45889.0</v>
       </c>
       <c r="D516" t="n">
         <v>1.0</v>
@@ -7366,7 +7366,7 @@
         <v>2025.0</v>
       </c>
       <c r="C517" t="n" s="2">
-        <v>45945.0</v>
+        <v>45924.0</v>
       </c>
       <c r="D517" t="n">
         <v>1.0</v>
@@ -7380,10 +7380,10 @@
         <v>2025.0</v>
       </c>
       <c r="C518" t="n" s="2">
-        <v>45959.0</v>
+        <v>45945.0</v>
       </c>
       <c r="D518" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="519">
@@ -7394,7 +7394,7 @@
         <v>2025.0</v>
       </c>
       <c r="C519" t="n" s="2">
-        <v>46001.0</v>
+        <v>45959.0</v>
       </c>
       <c r="D519" t="n">
         <v>2.0</v>
@@ -7408,10 +7408,10 @@
         <v>2025.0</v>
       </c>
       <c r="C520" t="n" s="2">
-        <v>46008.0</v>
+        <v>46001.0</v>
       </c>
       <c r="D520" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="521">
@@ -7422,7 +7422,7 @@
         <v>2025.0</v>
       </c>
       <c r="C521" t="n" s="2">
-        <v>46022.0</v>
+        <v>46008.0</v>
       </c>
       <c r="D521" t="n">
         <v>1.0</v>
@@ -7433,10 +7433,10 @@
         <v>7</v>
       </c>
       <c r="B522" t="n">
-        <v>2026.0</v>
+        <v>2025.0</v>
       </c>
       <c r="C522" t="n" s="2">
-        <v>46030.0</v>
+        <v>46022.0</v>
       </c>
       <c r="D522" t="n">
         <v>1.0</v>
@@ -7450,7 +7450,7 @@
         <v>2026.0</v>
       </c>
       <c r="C523" t="n" s="2">
-        <v>46051.0</v>
+        <v>46030.0</v>
       </c>
       <c r="D523" t="n">
         <v>1.0</v>
@@ -7464,7 +7464,7 @@
         <v>2026.0</v>
       </c>
       <c r="C524" t="n" s="2">
-        <v>46058.0</v>
+        <v>46051.0</v>
       </c>
       <c r="D524" t="n">
         <v>1.0</v>
@@ -7478,10 +7478,10 @@
         <v>2026.0</v>
       </c>
       <c r="C525" t="n" s="2">
-        <v>46065.0</v>
+        <v>46058.0</v>
       </c>
       <c r="D525" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="526">
@@ -7492,10 +7492,10 @@
         <v>2026.0</v>
       </c>
       <c r="C526" t="n" s="2">
-        <v>46135.0</v>
+        <v>46065.0</v>
       </c>
       <c r="D526" t="n">
-        <v>8.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="527">
@@ -7506,10 +7506,10 @@
         <v>2026.0</v>
       </c>
       <c r="C527" t="n" s="2">
-        <v>46156.0</v>
+        <v>46135.0</v>
       </c>
       <c r="D527" t="n">
-        <v>1.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="528">
@@ -7520,24 +7520,24 @@
         <v>2026.0</v>
       </c>
       <c r="C528" t="n" s="2">
-        <v>46163.0</v>
+        <v>46156.0</v>
       </c>
       <c r="D528" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B529" t="n">
-        <v>2024.0</v>
+        <v>2026.0</v>
       </c>
       <c r="C529" t="n" s="2">
-        <v>45495.0</v>
+        <v>46163.0</v>
       </c>
       <c r="D529" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="530">
@@ -7548,10 +7548,10 @@
         <v>2024.0</v>
       </c>
       <c r="C530" t="n" s="2">
-        <v>45502.0</v>
+        <v>45495.0</v>
       </c>
       <c r="D530" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="531">
@@ -7559,13 +7559,13 @@
         <v>8</v>
       </c>
       <c r="B531" t="n">
-        <v>2025.0</v>
+        <v>2024.0</v>
       </c>
       <c r="C531" t="n" s="2">
-        <v>45665.0</v>
+        <v>45502.0</v>
       </c>
       <c r="D531" t="n">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="532">
@@ -7576,10 +7576,10 @@
         <v>2025.0</v>
       </c>
       <c r="C532" t="n" s="2">
-        <v>45672.0</v>
+        <v>45665.0</v>
       </c>
       <c r="D532" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="533">
@@ -7590,10 +7590,10 @@
         <v>2025.0</v>
       </c>
       <c r="C533" t="n" s="2">
-        <v>45679.0</v>
+        <v>45672.0</v>
       </c>
       <c r="D533" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="534">
@@ -7604,10 +7604,10 @@
         <v>2025.0</v>
       </c>
       <c r="C534" t="n" s="2">
-        <v>45686.0</v>
+        <v>45679.0</v>
       </c>
       <c r="D534" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="535">
@@ -7618,10 +7618,10 @@
         <v>2025.0</v>
       </c>
       <c r="C535" t="n" s="2">
-        <v>45693.0</v>
+        <v>45686.0</v>
       </c>
       <c r="D535" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="536">
@@ -7632,10 +7632,10 @@
         <v>2025.0</v>
       </c>
       <c r="C536" t="n" s="2">
-        <v>45700.0</v>
+        <v>45693.0</v>
       </c>
       <c r="D536" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="537">
@@ -7646,10 +7646,10 @@
         <v>2025.0</v>
       </c>
       <c r="C537" t="n" s="2">
-        <v>45707.0</v>
+        <v>45700.0</v>
       </c>
       <c r="D537" t="n">
-        <v>7.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="538">
@@ -7660,10 +7660,10 @@
         <v>2025.0</v>
       </c>
       <c r="C538" t="n" s="2">
-        <v>45714.0</v>
+        <v>45707.0</v>
       </c>
       <c r="D538" t="n">
-        <v>3.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="539">
@@ -7674,10 +7674,10 @@
         <v>2025.0</v>
       </c>
       <c r="C539" t="n" s="2">
-        <v>45721.0</v>
+        <v>45714.0</v>
       </c>
       <c r="D539" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="540">
@@ -7688,10 +7688,10 @@
         <v>2025.0</v>
       </c>
       <c r="C540" t="n" s="2">
-        <v>45728.0</v>
+        <v>45721.0</v>
       </c>
       <c r="D540" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="541">
@@ -7702,7 +7702,7 @@
         <v>2025.0</v>
       </c>
       <c r="C541" t="n" s="2">
-        <v>45742.0</v>
+        <v>45728.0</v>
       </c>
       <c r="D541" t="n">
         <v>1.0</v>
@@ -7716,7 +7716,7 @@
         <v>2025.0</v>
       </c>
       <c r="C542" t="n" s="2">
-        <v>45749.0</v>
+        <v>45742.0</v>
       </c>
       <c r="D542" t="n">
         <v>1.0</v>
@@ -7730,7 +7730,7 @@
         <v>2025.0</v>
       </c>
       <c r="C543" t="n" s="2">
-        <v>45763.0</v>
+        <v>45749.0</v>
       </c>
       <c r="D543" t="n">
         <v>1.0</v>
@@ -7744,10 +7744,10 @@
         <v>2025.0</v>
       </c>
       <c r="C544" t="n" s="2">
-        <v>45777.0</v>
+        <v>45763.0</v>
       </c>
       <c r="D544" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="545">
@@ -7758,10 +7758,10 @@
         <v>2025.0</v>
       </c>
       <c r="C545" t="n" s="2">
-        <v>45784.0</v>
+        <v>45777.0</v>
       </c>
       <c r="D545" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="546">
@@ -7772,7 +7772,7 @@
         <v>2025.0</v>
       </c>
       <c r="C546" t="n" s="2">
-        <v>45798.0</v>
+        <v>45784.0</v>
       </c>
       <c r="D546" t="n">
         <v>1.0</v>
@@ -7786,7 +7786,7 @@
         <v>2025.0</v>
       </c>
       <c r="C547" t="n" s="2">
-        <v>45805.0</v>
+        <v>45798.0</v>
       </c>
       <c r="D547" t="n">
         <v>1.0</v>
@@ -7800,10 +7800,10 @@
         <v>2025.0</v>
       </c>
       <c r="C548" t="n" s="2">
-        <v>45812.0</v>
+        <v>45805.0</v>
       </c>
       <c r="D548" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="549">
@@ -7814,7 +7814,7 @@
         <v>2025.0</v>
       </c>
       <c r="C549" t="n" s="2">
-        <v>45819.0</v>
+        <v>45812.0</v>
       </c>
       <c r="D549" t="n">
         <v>2.0</v>
@@ -7828,7 +7828,7 @@
         <v>2025.0</v>
       </c>
       <c r="C550" t="n" s="2">
-        <v>45833.0</v>
+        <v>45819.0</v>
       </c>
       <c r="D550" t="n">
         <v>2.0</v>
@@ -7842,10 +7842,10 @@
         <v>2025.0</v>
       </c>
       <c r="C551" t="n" s="2">
-        <v>45847.0</v>
+        <v>45833.0</v>
       </c>
       <c r="D551" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="552">
@@ -7856,10 +7856,10 @@
         <v>2025.0</v>
       </c>
       <c r="C552" t="n" s="2">
-        <v>45854.0</v>
+        <v>45847.0</v>
       </c>
       <c r="D552" t="n">
-        <v>8.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="553">
@@ -7870,10 +7870,10 @@
         <v>2025.0</v>
       </c>
       <c r="C553" t="n" s="2">
-        <v>45861.0</v>
+        <v>45854.0</v>
       </c>
       <c r="D553" t="n">
-        <v>12.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="554">
@@ -7884,10 +7884,10 @@
         <v>2025.0</v>
       </c>
       <c r="C554" t="n" s="2">
-        <v>45868.0</v>
+        <v>45861.0</v>
       </c>
       <c r="D554" t="n">
-        <v>6.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="555">
@@ -7898,10 +7898,10 @@
         <v>2025.0</v>
       </c>
       <c r="C555" t="n" s="2">
-        <v>45875.0</v>
+        <v>45868.0</v>
       </c>
       <c r="D555" t="n">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="556">
@@ -7912,7 +7912,7 @@
         <v>2025.0</v>
       </c>
       <c r="C556" t="n" s="2">
-        <v>45896.0</v>
+        <v>45875.0</v>
       </c>
       <c r="D556" t="n">
         <v>1.0</v>
@@ -7926,7 +7926,7 @@
         <v>2025.0</v>
       </c>
       <c r="C557" t="n" s="2">
-        <v>45903.0</v>
+        <v>45896.0</v>
       </c>
       <c r="D557" t="n">
         <v>1.0</v>
@@ -7940,7 +7940,7 @@
         <v>2025.0</v>
       </c>
       <c r="C558" t="n" s="2">
-        <v>45931.0</v>
+        <v>45903.0</v>
       </c>
       <c r="D558" t="n">
         <v>1.0</v>
@@ -7954,10 +7954,10 @@
         <v>2025.0</v>
       </c>
       <c r="C559" t="n" s="2">
-        <v>45938.0</v>
+        <v>45931.0</v>
       </c>
       <c r="D559" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="560">
@@ -7968,10 +7968,10 @@
         <v>2025.0</v>
       </c>
       <c r="C560" t="n" s="2">
-        <v>45945.0</v>
+        <v>45938.0</v>
       </c>
       <c r="D560" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="561">
@@ -7982,7 +7982,7 @@
         <v>2025.0</v>
       </c>
       <c r="C561" t="n" s="2">
-        <v>45966.0</v>
+        <v>45945.0</v>
       </c>
       <c r="D561" t="n">
         <v>2.0</v>
@@ -7996,10 +7996,10 @@
         <v>2025.0</v>
       </c>
       <c r="C562" t="n" s="2">
-        <v>45973.0</v>
+        <v>45966.0</v>
       </c>
       <c r="D562" t="n">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="563">
@@ -8010,10 +8010,10 @@
         <v>2025.0</v>
       </c>
       <c r="C563" t="n" s="2">
-        <v>45980.0</v>
+        <v>45973.0</v>
       </c>
       <c r="D563" t="n">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="564">
@@ -8024,10 +8024,10 @@
         <v>2025.0</v>
       </c>
       <c r="C564" t="n" s="2">
-        <v>45987.0</v>
+        <v>45980.0</v>
       </c>
       <c r="D564" t="n">
-        <v>20.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="565">
@@ -8038,10 +8038,10 @@
         <v>2025.0</v>
       </c>
       <c r="C565" t="n" s="2">
-        <v>45994.0</v>
+        <v>45987.0</v>
       </c>
       <c r="D565" t="n">
-        <v>5.0</v>
+        <v>20.0</v>
       </c>
     </row>
     <row r="566">
@@ -8052,10 +8052,10 @@
         <v>2025.0</v>
       </c>
       <c r="C566" t="n" s="2">
-        <v>46001.0</v>
+        <v>45994.0</v>
       </c>
       <c r="D566" t="n">
-        <v>8.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="567">
@@ -8066,10 +8066,10 @@
         <v>2025.0</v>
       </c>
       <c r="C567" t="n" s="2">
-        <v>46008.0</v>
+        <v>46001.0</v>
       </c>
       <c r="D567" t="n">
-        <v>24.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="568">
@@ -8080,10 +8080,10 @@
         <v>2025.0</v>
       </c>
       <c r="C568" t="n" s="2">
-        <v>46015.0</v>
+        <v>46008.0</v>
       </c>
       <c r="D568" t="n">
-        <v>13.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="569">
@@ -8094,10 +8094,10 @@
         <v>2025.0</v>
       </c>
       <c r="C569" t="n" s="2">
-        <v>46022.0</v>
+        <v>46015.0</v>
       </c>
       <c r="D569" t="n">
-        <v>8.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="570">
@@ -8108,10 +8108,10 @@
         <v>2025.0</v>
       </c>
       <c r="C570" t="n" s="2">
-        <v>46029.0</v>
+        <v>46022.0</v>
       </c>
       <c r="D570" t="n">
-        <v>3.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="571">
@@ -8119,13 +8119,13 @@
         <v>8</v>
       </c>
       <c r="B571" t="n">
-        <v>2026.0</v>
+        <v>2025.0</v>
       </c>
       <c r="C571" t="n" s="2">
-        <v>46030.0</v>
+        <v>46029.0</v>
       </c>
       <c r="D571" t="n">
-        <v>24.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="572">
@@ -8136,10 +8136,10 @@
         <v>2026.0</v>
       </c>
       <c r="C572" t="n" s="2">
-        <v>46037.0</v>
+        <v>46030.0</v>
       </c>
       <c r="D572" t="n">
-        <v>22.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="573">
@@ -8150,10 +8150,10 @@
         <v>2026.0</v>
       </c>
       <c r="C573" t="n" s="2">
-        <v>46044.0</v>
+        <v>46037.0</v>
       </c>
       <c r="D573" t="n">
-        <v>27.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="574">
@@ -8164,10 +8164,10 @@
         <v>2026.0</v>
       </c>
       <c r="C574" t="n" s="2">
-        <v>46051.0</v>
+        <v>46044.0</v>
       </c>
       <c r="D574" t="n">
-        <v>18.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="575">
@@ -8178,10 +8178,10 @@
         <v>2026.0</v>
       </c>
       <c r="C575" t="n" s="2">
-        <v>46058.0</v>
+        <v>46051.0</v>
       </c>
       <c r="D575" t="n">
-        <v>25.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="576">
@@ -8192,10 +8192,10 @@
         <v>2026.0</v>
       </c>
       <c r="C576" t="n" s="2">
-        <v>46065.0</v>
+        <v>46058.0</v>
       </c>
       <c r="D576" t="n">
-        <v>22.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="577">
@@ -8206,10 +8206,10 @@
         <v>2026.0</v>
       </c>
       <c r="C577" t="n" s="2">
-        <v>46072.0</v>
+        <v>46065.0</v>
       </c>
       <c r="D577" t="n">
-        <v>13.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="578">
@@ -8220,10 +8220,10 @@
         <v>2026.0</v>
       </c>
       <c r="C578" t="n" s="2">
-        <v>46079.0</v>
+        <v>46072.0</v>
       </c>
       <c r="D578" t="n">
-        <v>24.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="579">
@@ -8234,10 +8234,10 @@
         <v>2026.0</v>
       </c>
       <c r="C579" t="n" s="2">
-        <v>46086.0</v>
+        <v>46079.0</v>
       </c>
       <c r="D579" t="n">
-        <v>26.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="580">
@@ -8248,10 +8248,10 @@
         <v>2026.0</v>
       </c>
       <c r="C580" t="n" s="2">
-        <v>46093.0</v>
+        <v>46086.0</v>
       </c>
       <c r="D580" t="n">
-        <v>33.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="581">
@@ -8262,10 +8262,10 @@
         <v>2026.0</v>
       </c>
       <c r="C581" t="n" s="2">
-        <v>46100.0</v>
+        <v>46093.0</v>
       </c>
       <c r="D581" t="n">
-        <v>25.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="582">
@@ -8276,10 +8276,10 @@
         <v>2026.0</v>
       </c>
       <c r="C582" t="n" s="2">
-        <v>46107.0</v>
+        <v>46100.0</v>
       </c>
       <c r="D582" t="n">
-        <v>31.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="583">
@@ -8290,10 +8290,10 @@
         <v>2026.0</v>
       </c>
       <c r="C583" t="n" s="2">
-        <v>46114.0</v>
+        <v>46107.0</v>
       </c>
       <c r="D583" t="n">
-        <v>10.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="584">
@@ -8304,10 +8304,10 @@
         <v>2026.0</v>
       </c>
       <c r="C584" t="n" s="2">
-        <v>46121.0</v>
+        <v>46114.0</v>
       </c>
       <c r="D584" t="n">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="585">
@@ -8318,10 +8318,10 @@
         <v>2026.0</v>
       </c>
       <c r="C585" t="n" s="2">
-        <v>46128.0</v>
+        <v>46121.0</v>
       </c>
       <c r="D585" t="n">
-        <v>15.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="586">
@@ -8332,10 +8332,10 @@
         <v>2026.0</v>
       </c>
       <c r="C586" t="n" s="2">
-        <v>46135.0</v>
+        <v>46128.0</v>
       </c>
       <c r="D586" t="n">
-        <v>35.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="587">
@@ -8346,10 +8346,10 @@
         <v>2026.0</v>
       </c>
       <c r="C587" t="n" s="2">
-        <v>46142.0</v>
+        <v>46135.0</v>
       </c>
       <c r="D587" t="n">
-        <v>22.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="588">
@@ -8360,10 +8360,10 @@
         <v>2026.0</v>
       </c>
       <c r="C588" t="n" s="2">
-        <v>46149.0</v>
+        <v>46142.0</v>
       </c>
       <c r="D588" t="n">
-        <v>6.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="589">
@@ -8374,10 +8374,10 @@
         <v>2026.0</v>
       </c>
       <c r="C589" t="n" s="2">
-        <v>46156.0</v>
+        <v>46149.0</v>
       </c>
       <c r="D589" t="n">
-        <v>27.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="590">
@@ -8388,10 +8388,10 @@
         <v>2026.0</v>
       </c>
       <c r="C590" t="n" s="2">
-        <v>46163.0</v>
+        <v>46156.0</v>
       </c>
       <c r="D590" t="n">
-        <v>13.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="591">
@@ -8402,10 +8402,10 @@
         <v>2026.0</v>
       </c>
       <c r="C591" t="n" s="2">
-        <v>46170.0</v>
+        <v>46163.0</v>
       </c>
       <c r="D591" t="n">
-        <v>21.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="592">
@@ -8416,9 +8416,23 @@
         <v>2026.0</v>
       </c>
       <c r="C592" t="n" s="2">
+        <v>46170.0</v>
+      </c>
+      <c r="D592" t="n">
+        <v>21.0</v>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="s">
+        <v>8</v>
+      </c>
+      <c r="B593" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C593" t="n" s="2">
         <v>46177.0</v>
       </c>
-      <c r="D592" t="n">
+      <c r="D593" t="n">
         <v>1.0</v>
       </c>
     </row>
@@ -8461,7 +8475,7 @@
         <v>12</v>
       </c>
       <c r="B4" t="n">
-        <v>1313.0</v>
+        <v>1315.0</v>
       </c>
     </row>
     <row r="5">
@@ -8523,7 +8537,7 @@
         <v>19</v>
       </c>
       <c r="C4" t="n">
-        <v>149.0</v>
+        <v>150.0</v>
       </c>
     </row>
     <row r="5">
@@ -8633,7 +8647,7 @@
         <v>19</v>
       </c>
       <c r="C14" t="n">
-        <v>418.0</v>
+        <v>419.0</v>
       </c>
     </row>
     <row r="15">

--- a/Download/Focus_Positivi_ZR.xlsx
+++ b/Download/Focus_Positivi_ZR.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="637" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="638" uniqueCount="23">
   <si>
     <t>NOME_REGIONE</t>
   </si>
@@ -7542,13 +7542,13 @@
     </row>
     <row r="530">
       <c r="A530" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B530" t="n">
-        <v>2024.0</v>
+        <v>2026.0</v>
       </c>
       <c r="C530" t="n" s="2">
-        <v>45495.0</v>
+        <v>46177.0</v>
       </c>
       <c r="D530" t="n">
         <v>1.0</v>
@@ -7562,10 +7562,10 @@
         <v>2024.0</v>
       </c>
       <c r="C531" t="n" s="2">
-        <v>45502.0</v>
+        <v>45495.0</v>
       </c>
       <c r="D531" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="532">
@@ -7573,13 +7573,13 @@
         <v>8</v>
       </c>
       <c r="B532" t="n">
-        <v>2025.0</v>
+        <v>2024.0</v>
       </c>
       <c r="C532" t="n" s="2">
-        <v>45665.0</v>
+        <v>45502.0</v>
       </c>
       <c r="D532" t="n">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="533">
@@ -7590,10 +7590,10 @@
         <v>2025.0</v>
       </c>
       <c r="C533" t="n" s="2">
-        <v>45672.0</v>
+        <v>45665.0</v>
       </c>
       <c r="D533" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="534">
@@ -7604,10 +7604,10 @@
         <v>2025.0</v>
       </c>
       <c r="C534" t="n" s="2">
-        <v>45679.0</v>
+        <v>45672.0</v>
       </c>
       <c r="D534" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="535">
@@ -7618,10 +7618,10 @@
         <v>2025.0</v>
       </c>
       <c r="C535" t="n" s="2">
-        <v>45686.0</v>
+        <v>45679.0</v>
       </c>
       <c r="D535" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="536">
@@ -7632,10 +7632,10 @@
         <v>2025.0</v>
       </c>
       <c r="C536" t="n" s="2">
-        <v>45693.0</v>
+        <v>45686.0</v>
       </c>
       <c r="D536" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="537">
@@ -7646,10 +7646,10 @@
         <v>2025.0</v>
       </c>
       <c r="C537" t="n" s="2">
-        <v>45700.0</v>
+        <v>45693.0</v>
       </c>
       <c r="D537" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="538">
@@ -7660,10 +7660,10 @@
         <v>2025.0</v>
       </c>
       <c r="C538" t="n" s="2">
-        <v>45707.0</v>
+        <v>45700.0</v>
       </c>
       <c r="D538" t="n">
-        <v>7.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="539">
@@ -7674,10 +7674,10 @@
         <v>2025.0</v>
       </c>
       <c r="C539" t="n" s="2">
-        <v>45714.0</v>
+        <v>45707.0</v>
       </c>
       <c r="D539" t="n">
-        <v>3.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="540">
@@ -7688,10 +7688,10 @@
         <v>2025.0</v>
       </c>
       <c r="C540" t="n" s="2">
-        <v>45721.0</v>
+        <v>45714.0</v>
       </c>
       <c r="D540" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="541">
@@ -7702,10 +7702,10 @@
         <v>2025.0</v>
       </c>
       <c r="C541" t="n" s="2">
-        <v>45728.0</v>
+        <v>45721.0</v>
       </c>
       <c r="D541" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="542">
@@ -7716,7 +7716,7 @@
         <v>2025.0</v>
       </c>
       <c r="C542" t="n" s="2">
-        <v>45742.0</v>
+        <v>45728.0</v>
       </c>
       <c r="D542" t="n">
         <v>1.0</v>
@@ -7730,7 +7730,7 @@
         <v>2025.0</v>
       </c>
       <c r="C543" t="n" s="2">
-        <v>45749.0</v>
+        <v>45742.0</v>
       </c>
       <c r="D543" t="n">
         <v>1.0</v>
@@ -7744,7 +7744,7 @@
         <v>2025.0</v>
       </c>
       <c r="C544" t="n" s="2">
-        <v>45763.0</v>
+        <v>45749.0</v>
       </c>
       <c r="D544" t="n">
         <v>1.0</v>
@@ -7758,10 +7758,10 @@
         <v>2025.0</v>
       </c>
       <c r="C545" t="n" s="2">
-        <v>45777.0</v>
+        <v>45763.0</v>
       </c>
       <c r="D545" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="546">
@@ -7772,10 +7772,10 @@
         <v>2025.0</v>
       </c>
       <c r="C546" t="n" s="2">
-        <v>45784.0</v>
+        <v>45777.0</v>
       </c>
       <c r="D546" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="547">
@@ -7786,7 +7786,7 @@
         <v>2025.0</v>
       </c>
       <c r="C547" t="n" s="2">
-        <v>45798.0</v>
+        <v>45784.0</v>
       </c>
       <c r="D547" t="n">
         <v>1.0</v>
@@ -7800,7 +7800,7 @@
         <v>2025.0</v>
       </c>
       <c r="C548" t="n" s="2">
-        <v>45805.0</v>
+        <v>45798.0</v>
       </c>
       <c r="D548" t="n">
         <v>1.0</v>
@@ -7814,10 +7814,10 @@
         <v>2025.0</v>
       </c>
       <c r="C549" t="n" s="2">
-        <v>45812.0</v>
+        <v>45805.0</v>
       </c>
       <c r="D549" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="550">
@@ -7828,7 +7828,7 @@
         <v>2025.0</v>
       </c>
       <c r="C550" t="n" s="2">
-        <v>45819.0</v>
+        <v>45812.0</v>
       </c>
       <c r="D550" t="n">
         <v>2.0</v>
@@ -7842,7 +7842,7 @@
         <v>2025.0</v>
       </c>
       <c r="C551" t="n" s="2">
-        <v>45833.0</v>
+        <v>45819.0</v>
       </c>
       <c r="D551" t="n">
         <v>2.0</v>
@@ -7856,10 +7856,10 @@
         <v>2025.0</v>
       </c>
       <c r="C552" t="n" s="2">
-        <v>45847.0</v>
+        <v>45833.0</v>
       </c>
       <c r="D552" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="553">
@@ -7870,10 +7870,10 @@
         <v>2025.0</v>
       </c>
       <c r="C553" t="n" s="2">
-        <v>45854.0</v>
+        <v>45847.0</v>
       </c>
       <c r="D553" t="n">
-        <v>8.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="554">
@@ -7884,10 +7884,10 @@
         <v>2025.0</v>
       </c>
       <c r="C554" t="n" s="2">
-        <v>45861.0</v>
+        <v>45854.0</v>
       </c>
       <c r="D554" t="n">
-        <v>12.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="555">
@@ -7898,10 +7898,10 @@
         <v>2025.0</v>
       </c>
       <c r="C555" t="n" s="2">
-        <v>45868.0</v>
+        <v>45861.0</v>
       </c>
       <c r="D555" t="n">
-        <v>6.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="556">
@@ -7912,10 +7912,10 @@
         <v>2025.0</v>
       </c>
       <c r="C556" t="n" s="2">
-        <v>45875.0</v>
+        <v>45868.0</v>
       </c>
       <c r="D556" t="n">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="557">
@@ -7926,7 +7926,7 @@
         <v>2025.0</v>
       </c>
       <c r="C557" t="n" s="2">
-        <v>45896.0</v>
+        <v>45875.0</v>
       </c>
       <c r="D557" t="n">
         <v>1.0</v>
@@ -7940,7 +7940,7 @@
         <v>2025.0</v>
       </c>
       <c r="C558" t="n" s="2">
-        <v>45903.0</v>
+        <v>45896.0</v>
       </c>
       <c r="D558" t="n">
         <v>1.0</v>
@@ -7954,7 +7954,7 @@
         <v>2025.0</v>
       </c>
       <c r="C559" t="n" s="2">
-        <v>45931.0</v>
+        <v>45903.0</v>
       </c>
       <c r="D559" t="n">
         <v>1.0</v>
@@ -7968,10 +7968,10 @@
         <v>2025.0</v>
       </c>
       <c r="C560" t="n" s="2">
-        <v>45938.0</v>
+        <v>45931.0</v>
       </c>
       <c r="D560" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="561">
@@ -7982,10 +7982,10 @@
         <v>2025.0</v>
       </c>
       <c r="C561" t="n" s="2">
-        <v>45945.0</v>
+        <v>45938.0</v>
       </c>
       <c r="D561" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="562">
@@ -7996,7 +7996,7 @@
         <v>2025.0</v>
       </c>
       <c r="C562" t="n" s="2">
-        <v>45966.0</v>
+        <v>45945.0</v>
       </c>
       <c r="D562" t="n">
         <v>2.0</v>
@@ -8010,10 +8010,10 @@
         <v>2025.0</v>
       </c>
       <c r="C563" t="n" s="2">
-        <v>45973.0</v>
+        <v>45966.0</v>
       </c>
       <c r="D563" t="n">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="564">
@@ -8024,10 +8024,10 @@
         <v>2025.0</v>
       </c>
       <c r="C564" t="n" s="2">
-        <v>45980.0</v>
+        <v>45973.0</v>
       </c>
       <c r="D564" t="n">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="565">
@@ -8038,10 +8038,10 @@
         <v>2025.0</v>
       </c>
       <c r="C565" t="n" s="2">
-        <v>45987.0</v>
+        <v>45980.0</v>
       </c>
       <c r="D565" t="n">
-        <v>20.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="566">
@@ -8052,10 +8052,10 @@
         <v>2025.0</v>
       </c>
       <c r="C566" t="n" s="2">
-        <v>45994.0</v>
+        <v>45987.0</v>
       </c>
       <c r="D566" t="n">
-        <v>5.0</v>
+        <v>20.0</v>
       </c>
     </row>
     <row r="567">
@@ -8066,10 +8066,10 @@
         <v>2025.0</v>
       </c>
       <c r="C567" t="n" s="2">
-        <v>46001.0</v>
+        <v>45994.0</v>
       </c>
       <c r="D567" t="n">
-        <v>8.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="568">
@@ -8080,10 +8080,10 @@
         <v>2025.0</v>
       </c>
       <c r="C568" t="n" s="2">
-        <v>46008.0</v>
+        <v>46001.0</v>
       </c>
       <c r="D568" t="n">
-        <v>24.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="569">
@@ -8094,10 +8094,10 @@
         <v>2025.0</v>
       </c>
       <c r="C569" t="n" s="2">
-        <v>46015.0</v>
+        <v>46008.0</v>
       </c>
       <c r="D569" t="n">
-        <v>13.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="570">
@@ -8108,10 +8108,10 @@
         <v>2025.0</v>
       </c>
       <c r="C570" t="n" s="2">
-        <v>46022.0</v>
+        <v>46015.0</v>
       </c>
       <c r="D570" t="n">
-        <v>8.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="571">
@@ -8122,10 +8122,10 @@
         <v>2025.0</v>
       </c>
       <c r="C571" t="n" s="2">
-        <v>46029.0</v>
+        <v>46022.0</v>
       </c>
       <c r="D571" t="n">
-        <v>3.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="572">
@@ -8133,13 +8133,13 @@
         <v>8</v>
       </c>
       <c r="B572" t="n">
-        <v>2026.0</v>
+        <v>2025.0</v>
       </c>
       <c r="C572" t="n" s="2">
-        <v>46030.0</v>
+        <v>46029.0</v>
       </c>
       <c r="D572" t="n">
-        <v>24.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="573">
@@ -8150,10 +8150,10 @@
         <v>2026.0</v>
       </c>
       <c r="C573" t="n" s="2">
-        <v>46037.0</v>
+        <v>46030.0</v>
       </c>
       <c r="D573" t="n">
-        <v>22.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="574">
@@ -8164,10 +8164,10 @@
         <v>2026.0</v>
       </c>
       <c r="C574" t="n" s="2">
-        <v>46044.0</v>
+        <v>46037.0</v>
       </c>
       <c r="D574" t="n">
-        <v>27.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="575">
@@ -8178,10 +8178,10 @@
         <v>2026.0</v>
       </c>
       <c r="C575" t="n" s="2">
-        <v>46051.0</v>
+        <v>46044.0</v>
       </c>
       <c r="D575" t="n">
-        <v>18.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="576">
@@ -8192,10 +8192,10 @@
         <v>2026.0</v>
       </c>
       <c r="C576" t="n" s="2">
-        <v>46058.0</v>
+        <v>46051.0</v>
       </c>
       <c r="D576" t="n">
-        <v>25.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="577">
@@ -8206,10 +8206,10 @@
         <v>2026.0</v>
       </c>
       <c r="C577" t="n" s="2">
-        <v>46065.0</v>
+        <v>46058.0</v>
       </c>
       <c r="D577" t="n">
-        <v>22.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="578">
@@ -8220,10 +8220,10 @@
         <v>2026.0</v>
       </c>
       <c r="C578" t="n" s="2">
-        <v>46072.0</v>
+        <v>46065.0</v>
       </c>
       <c r="D578" t="n">
-        <v>13.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="579">
@@ -8234,10 +8234,10 @@
         <v>2026.0</v>
       </c>
       <c r="C579" t="n" s="2">
-        <v>46079.0</v>
+        <v>46072.0</v>
       </c>
       <c r="D579" t="n">
-        <v>24.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="580">
@@ -8248,10 +8248,10 @@
         <v>2026.0</v>
       </c>
       <c r="C580" t="n" s="2">
-        <v>46086.0</v>
+        <v>46079.0</v>
       </c>
       <c r="D580" t="n">
-        <v>26.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="581">
@@ -8262,10 +8262,10 @@
         <v>2026.0</v>
       </c>
       <c r="C581" t="n" s="2">
-        <v>46093.0</v>
+        <v>46086.0</v>
       </c>
       <c r="D581" t="n">
-        <v>33.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="582">
@@ -8276,10 +8276,10 @@
         <v>2026.0</v>
       </c>
       <c r="C582" t="n" s="2">
-        <v>46100.0</v>
+        <v>46093.0</v>
       </c>
       <c r="D582" t="n">
-        <v>25.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="583">
@@ -8290,10 +8290,10 @@
         <v>2026.0</v>
       </c>
       <c r="C583" t="n" s="2">
-        <v>46107.0</v>
+        <v>46100.0</v>
       </c>
       <c r="D583" t="n">
-        <v>31.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="584">
@@ -8304,10 +8304,10 @@
         <v>2026.0</v>
       </c>
       <c r="C584" t="n" s="2">
-        <v>46114.0</v>
+        <v>46107.0</v>
       </c>
       <c r="D584" t="n">
-        <v>10.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="585">
@@ -8318,10 +8318,10 @@
         <v>2026.0</v>
       </c>
       <c r="C585" t="n" s="2">
-        <v>46121.0</v>
+        <v>46114.0</v>
       </c>
       <c r="D585" t="n">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="586">
@@ -8332,10 +8332,10 @@
         <v>2026.0</v>
       </c>
       <c r="C586" t="n" s="2">
-        <v>46128.0</v>
+        <v>46121.0</v>
       </c>
       <c r="D586" t="n">
-        <v>15.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="587">
@@ -8346,10 +8346,10 @@
         <v>2026.0</v>
       </c>
       <c r="C587" t="n" s="2">
-        <v>46135.0</v>
+        <v>46128.0</v>
       </c>
       <c r="D587" t="n">
-        <v>35.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="588">
@@ -8360,10 +8360,10 @@
         <v>2026.0</v>
       </c>
       <c r="C588" t="n" s="2">
-        <v>46142.0</v>
+        <v>46135.0</v>
       </c>
       <c r="D588" t="n">
-        <v>22.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="589">
@@ -8374,10 +8374,10 @@
         <v>2026.0</v>
       </c>
       <c r="C589" t="n" s="2">
-        <v>46149.0</v>
+        <v>46142.0</v>
       </c>
       <c r="D589" t="n">
-        <v>6.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="590">
@@ -8388,10 +8388,10 @@
         <v>2026.0</v>
       </c>
       <c r="C590" t="n" s="2">
-        <v>46156.0</v>
+        <v>46149.0</v>
       </c>
       <c r="D590" t="n">
-        <v>27.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="591">
@@ -8402,10 +8402,10 @@
         <v>2026.0</v>
       </c>
       <c r="C591" t="n" s="2">
-        <v>46163.0</v>
+        <v>46156.0</v>
       </c>
       <c r="D591" t="n">
-        <v>13.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="592">
@@ -8416,10 +8416,10 @@
         <v>2026.0</v>
       </c>
       <c r="C592" t="n" s="2">
-        <v>46170.0</v>
+        <v>46163.0</v>
       </c>
       <c r="D592" t="n">
-        <v>21.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="593">
@@ -8430,10 +8430,24 @@
         <v>2026.0</v>
       </c>
       <c r="C593" t="n" s="2">
+        <v>46170.0</v>
+      </c>
+      <c r="D593" t="n">
+        <v>21.0</v>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="s">
+        <v>8</v>
+      </c>
+      <c r="B594" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C594" t="n" s="2">
         <v>46177.0</v>
       </c>
-      <c r="D593" t="n">
-        <v>1.0</v>
+      <c r="D594" t="n">
+        <v>2.0</v>
       </c>
     </row>
   </sheetData>
@@ -8459,7 +8473,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="n">
-        <v>50.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="3">
@@ -8614,7 +8628,7 @@
         <v>19</v>
       </c>
       <c r="C11" t="n">
-        <v>36.0</v>
+        <v>38.0</v>
       </c>
     </row>
     <row r="12">

--- a/Download/Focus_Positivi_ZR.xlsx
+++ b/Download/Focus_Positivi_ZR.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="638" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="639" uniqueCount="23">
   <si>
     <t>NOME_REGIONE</t>
   </si>
@@ -1657,7 +1657,7 @@
         <v>46177.0</v>
       </c>
       <c r="D109" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="110">
@@ -4387,7 +4387,7 @@
         <v>46177.0</v>
       </c>
       <c r="D304" t="n">
-        <v>5.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="305">
@@ -8433,7 +8433,7 @@
         <v>46170.0</v>
       </c>
       <c r="D593" t="n">
-        <v>21.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="594">
@@ -8447,7 +8447,21 @@
         <v>46177.0</v>
       </c>
       <c r="D594" t="n">
-        <v>2.0</v>
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="s">
+        <v>8</v>
+      </c>
+      <c r="B595" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C595" t="n" s="2">
+        <v>46184.0</v>
+      </c>
+      <c r="D595" t="n">
+        <v>1.0</v>
       </c>
     </row>
   </sheetData>
@@ -8473,7 +8487,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="n">
-        <v>52.0</v>
+        <v>61.0</v>
       </c>
     </row>
     <row r="3">
@@ -8489,7 +8503,7 @@
         <v>12</v>
       </c>
       <c r="B4" t="n">
-        <v>1315.0</v>
+        <v>1327.0</v>
       </c>
     </row>
     <row r="5">
@@ -8529,7 +8543,7 @@
         <v>21</v>
       </c>
       <c r="C2" t="n">
-        <v>213.0</v>
+        <v>214.0</v>
       </c>
     </row>
     <row r="3">
@@ -8540,7 +8554,7 @@
         <v>22</v>
       </c>
       <c r="C3" t="n">
-        <v>190.0</v>
+        <v>191.0</v>
       </c>
     </row>
     <row r="4">
@@ -8562,7 +8576,7 @@
         <v>21</v>
       </c>
       <c r="C5" t="n">
-        <v>435.0</v>
+        <v>440.0</v>
       </c>
     </row>
     <row r="6">
@@ -8595,7 +8609,7 @@
         <v>21</v>
       </c>
       <c r="C8" t="n">
-        <v>355.0</v>
+        <v>356.0</v>
       </c>
     </row>
     <row r="9">
@@ -8628,7 +8642,7 @@
         <v>19</v>
       </c>
       <c r="C11" t="n">
-        <v>38.0</v>
+        <v>47.0</v>
       </c>
     </row>
     <row r="12">
@@ -8639,7 +8653,7 @@
         <v>21</v>
       </c>
       <c r="C12" t="n">
-        <v>82.0</v>
+        <v>84.0</v>
       </c>
     </row>
     <row r="13">
@@ -8661,7 +8675,7 @@
         <v>19</v>
       </c>
       <c r="C14" t="n">
-        <v>419.0</v>
+        <v>420.0</v>
       </c>
     </row>
     <row r="15">
@@ -8672,7 +8686,7 @@
         <v>21</v>
       </c>
       <c r="C15" t="n">
-        <v>372.0</v>
+        <v>373.0</v>
       </c>
     </row>
     <row r="16">

--- a/Download/Focus_Positivi_ZR.xlsx
+++ b/Download/Focus_Positivi_ZR.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="639" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="638" uniqueCount="23">
   <si>
     <t>NOME_REGIONE</t>
   </si>
@@ -4373,7 +4373,7 @@
         <v>46170.0</v>
       </c>
       <c r="D303" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="304">
@@ -7551,7 +7551,7 @@
         <v>46177.0</v>
       </c>
       <c r="D530" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="531">
@@ -8447,21 +8447,7 @@
         <v>46177.0</v>
       </c>
       <c r="D594" t="n">
-        <v>12.0</v>
-      </c>
-    </row>
-    <row r="595">
-      <c r="A595" t="s">
-        <v>8</v>
-      </c>
-      <c r="B595" t="n">
-        <v>2026.0</v>
-      </c>
-      <c r="C595" t="n" s="2">
-        <v>46184.0</v>
-      </c>
-      <c r="D595" t="n">
-        <v>1.0</v>
+        <v>13.0</v>
       </c>
     </row>
   </sheetData>
@@ -8487,7 +8473,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="n">
-        <v>61.0</v>
+        <v>50.0</v>
       </c>
     </row>
     <row r="3">
@@ -8495,7 +8481,7 @@
         <v>11</v>
       </c>
       <c r="B3" t="n">
-        <v>199.0</v>
+        <v>201.0</v>
       </c>
     </row>
     <row r="4">
@@ -8503,7 +8489,7 @@
         <v>12</v>
       </c>
       <c r="B4" t="n">
-        <v>1327.0</v>
+        <v>1337.0</v>
       </c>
     </row>
     <row r="5">
@@ -8511,7 +8497,7 @@
         <v>13</v>
       </c>
       <c r="B5" t="n">
-        <v>2160.0</v>
+        <v>2162.0</v>
       </c>
     </row>
   </sheetData>
@@ -8554,7 +8540,7 @@
         <v>22</v>
       </c>
       <c r="C3" t="n">
-        <v>191.0</v>
+        <v>192.0</v>
       </c>
     </row>
     <row r="4">
@@ -8565,7 +8551,7 @@
         <v>19</v>
       </c>
       <c r="C4" t="n">
-        <v>150.0</v>
+        <v>157.0</v>
       </c>
     </row>
     <row r="5">
@@ -8642,7 +8628,7 @@
         <v>19</v>
       </c>
       <c r="C11" t="n">
-        <v>47.0</v>
+        <v>36.0</v>
       </c>
     </row>
     <row r="12">
@@ -8653,7 +8639,7 @@
         <v>21</v>
       </c>
       <c r="C12" t="n">
-        <v>84.0</v>
+        <v>87.0</v>
       </c>
     </row>
     <row r="13">
@@ -8664,7 +8650,7 @@
         <v>22</v>
       </c>
       <c r="C13" t="n">
-        <v>44.0</v>
+        <v>45.0</v>
       </c>
     </row>
     <row r="14">
@@ -8697,7 +8683,7 @@
         <v>22</v>
       </c>
       <c r="C16" t="n">
-        <v>366.0</v>
+        <v>368.0</v>
       </c>
     </row>
     <row r="17">

--- a/Download/Focus_Positivi_ZR.xlsx
+++ b/Download/Focus_Positivi_ZR.xlsx
@@ -1657,7 +1657,7 @@
         <v>46177.0</v>
       </c>
       <c r="D109" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="110">
@@ -8497,7 +8497,7 @@
         <v>13</v>
       </c>
       <c r="B5" t="n">
-        <v>2162.0</v>
+        <v>2163.0</v>
       </c>
     </row>
   </sheetData>
@@ -8562,7 +8562,7 @@
         <v>21</v>
       </c>
       <c r="C5" t="n">
-        <v>440.0</v>
+        <v>441.0</v>
       </c>
     </row>
     <row r="6">

--- a/Download/Focus_Positivi_ZR.xlsx
+++ b/Download/Focus_Positivi_ZR.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="638" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="639" uniqueCount="23">
   <si>
     <t>NOME_REGIONE</t>
   </si>
@@ -8450,6 +8450,20 @@
         <v>13.0</v>
       </c>
     </row>
+    <row r="595">
+      <c r="A595" t="s">
+        <v>8</v>
+      </c>
+      <c r="B595" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C595" t="n" s="2">
+        <v>46184.0</v>
+      </c>
+      <c r="D595" t="n">
+        <v>3.0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
@@ -8473,7 +8487,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="n">
-        <v>50.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="3">
@@ -8628,7 +8642,7 @@
         <v>19</v>
       </c>
       <c r="C11" t="n">
-        <v>36.0</v>
+        <v>39.0</v>
       </c>
     </row>
     <row r="12">

--- a/Download/Focus_Positivi_ZR.xlsx
+++ b/Download/Focus_Positivi_ZR.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="639" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="640" uniqueCount="23">
   <si>
     <t>NOME_REGIONE</t>
   </si>
@@ -1662,16 +1662,16 @@
     </row>
     <row r="110">
       <c r="A110" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B110" t="n">
-        <v>2021.0</v>
+        <v>2026.0</v>
       </c>
       <c r="C110" t="n" s="2">
-        <v>44561.0</v>
+        <v>46184.0</v>
       </c>
       <c r="D110" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="111">
@@ -1679,13 +1679,13 @@
         <v>5</v>
       </c>
       <c r="B111" t="n">
-        <v>2022.0</v>
+        <v>2021.0</v>
       </c>
       <c r="C111" t="n" s="2">
-        <v>44576.0</v>
+        <v>44561.0</v>
       </c>
       <c r="D111" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="112">
@@ -1696,10 +1696,10 @@
         <v>2022.0</v>
       </c>
       <c r="C112" t="n" s="2">
-        <v>44583.0</v>
+        <v>44576.0</v>
       </c>
       <c r="D112" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="113">
@@ -1710,10 +1710,10 @@
         <v>2022.0</v>
       </c>
       <c r="C113" t="n" s="2">
-        <v>44590.0</v>
+        <v>44583.0</v>
       </c>
       <c r="D113" t="n">
-        <v>7.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="114">
@@ -1724,10 +1724,10 @@
         <v>2022.0</v>
       </c>
       <c r="C114" t="n" s="2">
-        <v>44597.0</v>
+        <v>44590.0</v>
       </c>
       <c r="D114" t="n">
-        <v>3.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="115">
@@ -1738,10 +1738,10 @@
         <v>2022.0</v>
       </c>
       <c r="C115" t="n" s="2">
-        <v>44604.0</v>
+        <v>44597.0</v>
       </c>
       <c r="D115" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="116">
@@ -1752,10 +1752,10 @@
         <v>2022.0</v>
       </c>
       <c r="C116" t="n" s="2">
-        <v>44611.0</v>
+        <v>44604.0</v>
       </c>
       <c r="D116" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="117">
@@ -1766,7 +1766,7 @@
         <v>2022.0</v>
       </c>
       <c r="C117" t="n" s="2">
-        <v>44618.0</v>
+        <v>44611.0</v>
       </c>
       <c r="D117" t="n">
         <v>1.0</v>
@@ -1780,10 +1780,10 @@
         <v>2022.0</v>
       </c>
       <c r="C118" t="n" s="2">
-        <v>44625.0</v>
+        <v>44618.0</v>
       </c>
       <c r="D118" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="119">
@@ -1794,10 +1794,10 @@
         <v>2022.0</v>
       </c>
       <c r="C119" t="n" s="2">
-        <v>44632.0</v>
+        <v>44625.0</v>
       </c>
       <c r="D119" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="120">
@@ -1808,10 +1808,10 @@
         <v>2022.0</v>
       </c>
       <c r="C120" t="n" s="2">
-        <v>44639.0</v>
+        <v>44632.0</v>
       </c>
       <c r="D120" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="121">
@@ -1822,7 +1822,7 @@
         <v>2022.0</v>
       </c>
       <c r="C121" t="n" s="2">
-        <v>44646.0</v>
+        <v>44639.0</v>
       </c>
       <c r="D121" t="n">
         <v>2.0</v>
@@ -1836,7 +1836,7 @@
         <v>2022.0</v>
       </c>
       <c r="C122" t="n" s="2">
-        <v>44653.0</v>
+        <v>44646.0</v>
       </c>
       <c r="D122" t="n">
         <v>2.0</v>
@@ -1850,10 +1850,10 @@
         <v>2022.0</v>
       </c>
       <c r="C123" t="n" s="2">
-        <v>44660.0</v>
+        <v>44653.0</v>
       </c>
       <c r="D123" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="124">
@@ -1864,10 +1864,10 @@
         <v>2022.0</v>
       </c>
       <c r="C124" t="n" s="2">
-        <v>44667.0</v>
+        <v>44660.0</v>
       </c>
       <c r="D124" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="125">
@@ -1878,7 +1878,7 @@
         <v>2022.0</v>
       </c>
       <c r="C125" t="n" s="2">
-        <v>44674.0</v>
+        <v>44667.0</v>
       </c>
       <c r="D125" t="n">
         <v>3.0</v>
@@ -1892,10 +1892,10 @@
         <v>2022.0</v>
       </c>
       <c r="C126" t="n" s="2">
-        <v>44681.0</v>
+        <v>44674.0</v>
       </c>
       <c r="D126" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="127">
@@ -1906,10 +1906,10 @@
         <v>2022.0</v>
       </c>
       <c r="C127" t="n" s="2">
-        <v>44688.0</v>
+        <v>44681.0</v>
       </c>
       <c r="D127" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="128">
@@ -1920,7 +1920,7 @@
         <v>2022.0</v>
       </c>
       <c r="C128" t="n" s="2">
-        <v>44695.0</v>
+        <v>44688.0</v>
       </c>
       <c r="D128" t="n">
         <v>3.0</v>
@@ -1934,10 +1934,10 @@
         <v>2022.0</v>
       </c>
       <c r="C129" t="n" s="2">
-        <v>44702.0</v>
+        <v>44695.0</v>
       </c>
       <c r="D129" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="130">
@@ -1948,10 +1948,10 @@
         <v>2022.0</v>
       </c>
       <c r="C130" t="n" s="2">
-        <v>44709.0</v>
+        <v>44702.0</v>
       </c>
       <c r="D130" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="131">
@@ -1962,10 +1962,10 @@
         <v>2022.0</v>
       </c>
       <c r="C131" t="n" s="2">
-        <v>44716.0</v>
+        <v>44709.0</v>
       </c>
       <c r="D131" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="132">
@@ -1976,7 +1976,7 @@
         <v>2022.0</v>
       </c>
       <c r="C132" t="n" s="2">
-        <v>44723.0</v>
+        <v>44716.0</v>
       </c>
       <c r="D132" t="n">
         <v>1.0</v>
@@ -1990,7 +1990,7 @@
         <v>2022.0</v>
       </c>
       <c r="C133" t="n" s="2">
-        <v>44730.0</v>
+        <v>44723.0</v>
       </c>
       <c r="D133" t="n">
         <v>1.0</v>
@@ -2004,7 +2004,7 @@
         <v>2022.0</v>
       </c>
       <c r="C134" t="n" s="2">
-        <v>44737.0</v>
+        <v>44730.0</v>
       </c>
       <c r="D134" t="n">
         <v>1.0</v>
@@ -2018,7 +2018,7 @@
         <v>2022.0</v>
       </c>
       <c r="C135" t="n" s="2">
-        <v>44744.0</v>
+        <v>44737.0</v>
       </c>
       <c r="D135" t="n">
         <v>1.0</v>
@@ -2032,7 +2032,7 @@
         <v>2022.0</v>
       </c>
       <c r="C136" t="n" s="2">
-        <v>44751.0</v>
+        <v>44744.0</v>
       </c>
       <c r="D136" t="n">
         <v>1.0</v>
@@ -2046,7 +2046,7 @@
         <v>2022.0</v>
       </c>
       <c r="C137" t="n" s="2">
-        <v>44758.0</v>
+        <v>44751.0</v>
       </c>
       <c r="D137" t="n">
         <v>1.0</v>
@@ -2060,7 +2060,7 @@
         <v>2022.0</v>
       </c>
       <c r="C138" t="n" s="2">
-        <v>44772.0</v>
+        <v>44758.0</v>
       </c>
       <c r="D138" t="n">
         <v>1.0</v>
@@ -2074,7 +2074,7 @@
         <v>2022.0</v>
       </c>
       <c r="C139" t="n" s="2">
-        <v>44793.0</v>
+        <v>44772.0</v>
       </c>
       <c r="D139" t="n">
         <v>1.0</v>
@@ -2088,7 +2088,7 @@
         <v>2022.0</v>
       </c>
       <c r="C140" t="n" s="2">
-        <v>44800.0</v>
+        <v>44793.0</v>
       </c>
       <c r="D140" t="n">
         <v>1.0</v>
@@ -2102,7 +2102,7 @@
         <v>2022.0</v>
       </c>
       <c r="C141" t="n" s="2">
-        <v>44828.0</v>
+        <v>44800.0</v>
       </c>
       <c r="D141" t="n">
         <v>1.0</v>
@@ -2116,7 +2116,7 @@
         <v>2022.0</v>
       </c>
       <c r="C142" t="n" s="2">
-        <v>44849.0</v>
+        <v>44828.0</v>
       </c>
       <c r="D142" t="n">
         <v>1.0</v>
@@ -2130,7 +2130,7 @@
         <v>2022.0</v>
       </c>
       <c r="C143" t="n" s="2">
-        <v>44856.0</v>
+        <v>44849.0</v>
       </c>
       <c r="D143" t="n">
         <v>1.0</v>
@@ -2144,7 +2144,7 @@
         <v>2022.0</v>
       </c>
       <c r="C144" t="n" s="2">
-        <v>44863.0</v>
+        <v>44856.0</v>
       </c>
       <c r="D144" t="n">
         <v>1.0</v>
@@ -2158,10 +2158,10 @@
         <v>2022.0</v>
       </c>
       <c r="C145" t="n" s="2">
-        <v>44884.0</v>
+        <v>44863.0</v>
       </c>
       <c r="D145" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="146">
@@ -2172,10 +2172,10 @@
         <v>2022.0</v>
       </c>
       <c r="C146" t="n" s="2">
-        <v>44891.0</v>
+        <v>44884.0</v>
       </c>
       <c r="D146" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="147">
@@ -2186,7 +2186,7 @@
         <v>2022.0</v>
       </c>
       <c r="C147" t="n" s="2">
-        <v>44905.0</v>
+        <v>44891.0</v>
       </c>
       <c r="D147" t="n">
         <v>1.0</v>
@@ -2200,7 +2200,7 @@
         <v>2022.0</v>
       </c>
       <c r="C148" t="n" s="2">
-        <v>44912.0</v>
+        <v>44905.0</v>
       </c>
       <c r="D148" t="n">
         <v>1.0</v>
@@ -2214,10 +2214,10 @@
         <v>2022.0</v>
       </c>
       <c r="C149" t="n" s="2">
-        <v>44919.0</v>
+        <v>44912.0</v>
       </c>
       <c r="D149" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="150">
@@ -2225,13 +2225,13 @@
         <v>5</v>
       </c>
       <c r="B150" t="n">
-        <v>2023.0</v>
+        <v>2022.0</v>
       </c>
       <c r="C150" t="n" s="2">
-        <v>44934.0</v>
+        <v>44919.0</v>
       </c>
       <c r="D150" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="151">
@@ -2242,10 +2242,10 @@
         <v>2023.0</v>
       </c>
       <c r="C151" t="n" s="2">
-        <v>44941.0</v>
+        <v>44934.0</v>
       </c>
       <c r="D151" t="n">
-        <v>8.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="152">
@@ -2256,10 +2256,10 @@
         <v>2023.0</v>
       </c>
       <c r="C152" t="n" s="2">
-        <v>44948.0</v>
+        <v>44941.0</v>
       </c>
       <c r="D152" t="n">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="153">
@@ -2270,10 +2270,10 @@
         <v>2023.0</v>
       </c>
       <c r="C153" t="n" s="2">
-        <v>44955.0</v>
+        <v>44948.0</v>
       </c>
       <c r="D153" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="154">
@@ -2284,10 +2284,10 @@
         <v>2023.0</v>
       </c>
       <c r="C154" t="n" s="2">
-        <v>44962.0</v>
+        <v>44955.0</v>
       </c>
       <c r="D154" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="155">
@@ -2298,7 +2298,7 @@
         <v>2023.0</v>
       </c>
       <c r="C155" t="n" s="2">
-        <v>44969.0</v>
+        <v>44962.0</v>
       </c>
       <c r="D155" t="n">
         <v>4.0</v>
@@ -2312,10 +2312,10 @@
         <v>2023.0</v>
       </c>
       <c r="C156" t="n" s="2">
-        <v>44976.0</v>
+        <v>44969.0</v>
       </c>
       <c r="D156" t="n">
-        <v>17.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="157">
@@ -2326,10 +2326,10 @@
         <v>2023.0</v>
       </c>
       <c r="C157" t="n" s="2">
-        <v>44983.0</v>
+        <v>44976.0</v>
       </c>
       <c r="D157" t="n">
-        <v>11.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="158">
@@ -2340,10 +2340,10 @@
         <v>2023.0</v>
       </c>
       <c r="C158" t="n" s="2">
-        <v>44990.0</v>
+        <v>44983.0</v>
       </c>
       <c r="D158" t="n">
-        <v>5.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="159">
@@ -2354,10 +2354,10 @@
         <v>2023.0</v>
       </c>
       <c r="C159" t="n" s="2">
-        <v>44997.0</v>
+        <v>44990.0</v>
       </c>
       <c r="D159" t="n">
-        <v>22.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="160">
@@ -2368,10 +2368,10 @@
         <v>2023.0</v>
       </c>
       <c r="C160" t="n" s="2">
-        <v>45004.0</v>
+        <v>44997.0</v>
       </c>
       <c r="D160" t="n">
-        <v>8.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="161">
@@ -2382,10 +2382,10 @@
         <v>2023.0</v>
       </c>
       <c r="C161" t="n" s="2">
-        <v>45011.0</v>
+        <v>45004.0</v>
       </c>
       <c r="D161" t="n">
-        <v>17.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="162">
@@ -2396,10 +2396,10 @@
         <v>2023.0</v>
       </c>
       <c r="C162" t="n" s="2">
-        <v>45018.0</v>
+        <v>45011.0</v>
       </c>
       <c r="D162" t="n">
-        <v>10.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="163">
@@ -2410,10 +2410,10 @@
         <v>2023.0</v>
       </c>
       <c r="C163" t="n" s="2">
-        <v>45025.0</v>
+        <v>45018.0</v>
       </c>
       <c r="D163" t="n">
-        <v>13.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="164">
@@ -2424,10 +2424,10 @@
         <v>2023.0</v>
       </c>
       <c r="C164" t="n" s="2">
-        <v>45032.0</v>
+        <v>45025.0</v>
       </c>
       <c r="D164" t="n">
-        <v>10.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="165">
@@ -2438,10 +2438,10 @@
         <v>2023.0</v>
       </c>
       <c r="C165" t="n" s="2">
-        <v>45039.0</v>
+        <v>45032.0</v>
       </c>
       <c r="D165" t="n">
-        <v>22.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="166">
@@ -2452,10 +2452,10 @@
         <v>2023.0</v>
       </c>
       <c r="C166" t="n" s="2">
-        <v>45046.0</v>
+        <v>45039.0</v>
       </c>
       <c r="D166" t="n">
-        <v>23.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="167">
@@ -2466,10 +2466,10 @@
         <v>2023.0</v>
       </c>
       <c r="C167" t="n" s="2">
-        <v>45053.0</v>
+        <v>45046.0</v>
       </c>
       <c r="D167" t="n">
-        <v>16.0</v>
+        <v>23.0</v>
       </c>
     </row>
     <row r="168">
@@ -2480,10 +2480,10 @@
         <v>2023.0</v>
       </c>
       <c r="C168" t="n" s="2">
-        <v>45060.0</v>
+        <v>45053.0</v>
       </c>
       <c r="D168" t="n">
-        <v>13.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="169">
@@ -2494,10 +2494,10 @@
         <v>2023.0</v>
       </c>
       <c r="C169" t="n" s="2">
-        <v>45067.0</v>
+        <v>45060.0</v>
       </c>
       <c r="D169" t="n">
-        <v>9.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="170">
@@ -2508,10 +2508,10 @@
         <v>2023.0</v>
       </c>
       <c r="C170" t="n" s="2">
-        <v>45074.0</v>
+        <v>45067.0</v>
       </c>
       <c r="D170" t="n">
-        <v>6.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="171">
@@ -2522,10 +2522,10 @@
         <v>2023.0</v>
       </c>
       <c r="C171" t="n" s="2">
-        <v>45081.0</v>
+        <v>45074.0</v>
       </c>
       <c r="D171" t="n">
-        <v>16.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="172">
@@ -2536,10 +2536,10 @@
         <v>2023.0</v>
       </c>
       <c r="C172" t="n" s="2">
-        <v>45088.0</v>
+        <v>45081.0</v>
       </c>
       <c r="D172" t="n">
-        <v>8.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="173">
@@ -2550,10 +2550,10 @@
         <v>2023.0</v>
       </c>
       <c r="C173" t="n" s="2">
-        <v>45095.0</v>
+        <v>45088.0</v>
       </c>
       <c r="D173" t="n">
-        <v>16.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="174">
@@ -2564,10 +2564,10 @@
         <v>2023.0</v>
       </c>
       <c r="C174" t="n" s="2">
-        <v>45102.0</v>
+        <v>45095.0</v>
       </c>
       <c r="D174" t="n">
-        <v>17.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="175">
@@ -2578,10 +2578,10 @@
         <v>2023.0</v>
       </c>
       <c r="C175" t="n" s="2">
-        <v>45109.0</v>
+        <v>45102.0</v>
       </c>
       <c r="D175" t="n">
-        <v>14.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="176">
@@ -2592,10 +2592,10 @@
         <v>2023.0</v>
       </c>
       <c r="C176" t="n" s="2">
-        <v>45116.0</v>
+        <v>45109.0</v>
       </c>
       <c r="D176" t="n">
-        <v>13.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="177">
@@ -2606,10 +2606,10 @@
         <v>2023.0</v>
       </c>
       <c r="C177" t="n" s="2">
-        <v>45123.0</v>
+        <v>45116.0</v>
       </c>
       <c r="D177" t="n">
-        <v>5.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="178">
@@ -2620,10 +2620,10 @@
         <v>2023.0</v>
       </c>
       <c r="C178" t="n" s="2">
-        <v>45130.0</v>
+        <v>45123.0</v>
       </c>
       <c r="D178" t="n">
-        <v>8.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="179">
@@ -2634,10 +2634,10 @@
         <v>2023.0</v>
       </c>
       <c r="C179" t="n" s="2">
-        <v>45137.0</v>
+        <v>45130.0</v>
       </c>
       <c r="D179" t="n">
-        <v>4.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="180">
@@ -2648,10 +2648,10 @@
         <v>2023.0</v>
       </c>
       <c r="C180" t="n" s="2">
-        <v>45144.0</v>
+        <v>45137.0</v>
       </c>
       <c r="D180" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="181">
@@ -2662,7 +2662,7 @@
         <v>2023.0</v>
       </c>
       <c r="C181" t="n" s="2">
-        <v>45151.0</v>
+        <v>45144.0</v>
       </c>
       <c r="D181" t="n">
         <v>2.0</v>
@@ -2676,10 +2676,10 @@
         <v>2023.0</v>
       </c>
       <c r="C182" t="n" s="2">
-        <v>45158.0</v>
+        <v>45151.0</v>
       </c>
       <c r="D182" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="183">
@@ -2690,7 +2690,7 @@
         <v>2023.0</v>
       </c>
       <c r="C183" t="n" s="2">
-        <v>45165.0</v>
+        <v>45158.0</v>
       </c>
       <c r="D183" t="n">
         <v>5.0</v>
@@ -2704,10 +2704,10 @@
         <v>2023.0</v>
       </c>
       <c r="C184" t="n" s="2">
-        <v>45172.0</v>
+        <v>45165.0</v>
       </c>
       <c r="D184" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="185">
@@ -2718,10 +2718,10 @@
         <v>2023.0</v>
       </c>
       <c r="C185" t="n" s="2">
-        <v>45179.0</v>
+        <v>45172.0</v>
       </c>
       <c r="D185" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="186">
@@ -2732,10 +2732,10 @@
         <v>2023.0</v>
       </c>
       <c r="C186" t="n" s="2">
-        <v>45186.0</v>
+        <v>45179.0</v>
       </c>
       <c r="D186" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="187">
@@ -2746,7 +2746,7 @@
         <v>2023.0</v>
       </c>
       <c r="C187" t="n" s="2">
-        <v>45193.0</v>
+        <v>45186.0</v>
       </c>
       <c r="D187" t="n">
         <v>1.0</v>
@@ -2760,10 +2760,10 @@
         <v>2023.0</v>
       </c>
       <c r="C188" t="n" s="2">
-        <v>45200.0</v>
+        <v>45193.0</v>
       </c>
       <c r="D188" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="189">
@@ -2774,10 +2774,10 @@
         <v>2023.0</v>
       </c>
       <c r="C189" t="n" s="2">
-        <v>45207.0</v>
+        <v>45200.0</v>
       </c>
       <c r="D189" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="190">
@@ -2788,10 +2788,10 @@
         <v>2023.0</v>
       </c>
       <c r="C190" t="n" s="2">
-        <v>45214.0</v>
+        <v>45207.0</v>
       </c>
       <c r="D190" t="n">
-        <v>8.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="191">
@@ -2802,7 +2802,7 @@
         <v>2023.0</v>
       </c>
       <c r="C191" t="n" s="2">
-        <v>45221.0</v>
+        <v>45214.0</v>
       </c>
       <c r="D191" t="n">
         <v>8.0</v>
@@ -2816,10 +2816,10 @@
         <v>2023.0</v>
       </c>
       <c r="C192" t="n" s="2">
-        <v>45228.0</v>
+        <v>45221.0</v>
       </c>
       <c r="D192" t="n">
-        <v>17.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="193">
@@ -2830,10 +2830,10 @@
         <v>2023.0</v>
       </c>
       <c r="C193" t="n" s="2">
-        <v>45235.0</v>
+        <v>45228.0</v>
       </c>
       <c r="D193" t="n">
-        <v>9.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="194">
@@ -2844,7 +2844,7 @@
         <v>2023.0</v>
       </c>
       <c r="C194" t="n" s="2">
-        <v>45242.0</v>
+        <v>45235.0</v>
       </c>
       <c r="D194" t="n">
         <v>9.0</v>
@@ -2858,10 +2858,10 @@
         <v>2023.0</v>
       </c>
       <c r="C195" t="n" s="2">
-        <v>45249.0</v>
+        <v>45242.0</v>
       </c>
       <c r="D195" t="n">
-        <v>14.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="196">
@@ -2872,10 +2872,10 @@
         <v>2023.0</v>
       </c>
       <c r="C196" t="n" s="2">
-        <v>45256.0</v>
+        <v>45249.0</v>
       </c>
       <c r="D196" t="n">
-        <v>17.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="197">
@@ -2886,10 +2886,10 @@
         <v>2023.0</v>
       </c>
       <c r="C197" t="n" s="2">
-        <v>45263.0</v>
+        <v>45256.0</v>
       </c>
       <c r="D197" t="n">
-        <v>14.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="198">
@@ -2900,10 +2900,10 @@
         <v>2023.0</v>
       </c>
       <c r="C198" t="n" s="2">
-        <v>45270.0</v>
+        <v>45263.0</v>
       </c>
       <c r="D198" t="n">
-        <v>26.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="199">
@@ -2914,10 +2914,10 @@
         <v>2023.0</v>
       </c>
       <c r="C199" t="n" s="2">
-        <v>45277.0</v>
+        <v>45270.0</v>
       </c>
       <c r="D199" t="n">
-        <v>19.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="200">
@@ -2928,10 +2928,10 @@
         <v>2023.0</v>
       </c>
       <c r="C200" t="n" s="2">
-        <v>45284.0</v>
+        <v>45277.0</v>
       </c>
       <c r="D200" t="n">
-        <v>21.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="201">
@@ -2942,10 +2942,10 @@
         <v>2023.0</v>
       </c>
       <c r="C201" t="n" s="2">
-        <v>45291.0</v>
+        <v>45284.0</v>
       </c>
       <c r="D201" t="n">
-        <v>9.0</v>
+        <v>21.0</v>
       </c>
     </row>
     <row r="202">
@@ -2953,13 +2953,13 @@
         <v>5</v>
       </c>
       <c r="B202" t="n">
-        <v>2024.0</v>
+        <v>2023.0</v>
       </c>
       <c r="C202" t="n" s="2">
-        <v>45299.0</v>
+        <v>45291.0</v>
       </c>
       <c r="D202" t="n">
-        <v>26.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="203">
@@ -2970,10 +2970,10 @@
         <v>2024.0</v>
       </c>
       <c r="C203" t="n" s="2">
-        <v>45306.0</v>
+        <v>45299.0</v>
       </c>
       <c r="D203" t="n">
-        <v>14.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="204">
@@ -2984,10 +2984,10 @@
         <v>2024.0</v>
       </c>
       <c r="C204" t="n" s="2">
-        <v>45313.0</v>
+        <v>45306.0</v>
       </c>
       <c r="D204" t="n">
-        <v>15.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="205">
@@ -2998,10 +2998,10 @@
         <v>2024.0</v>
       </c>
       <c r="C205" t="n" s="2">
-        <v>45320.0</v>
+        <v>45313.0</v>
       </c>
       <c r="D205" t="n">
-        <v>18.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="206">
@@ -3012,10 +3012,10 @@
         <v>2024.0</v>
       </c>
       <c r="C206" t="n" s="2">
-        <v>45327.0</v>
+        <v>45320.0</v>
       </c>
       <c r="D206" t="n">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="207">
@@ -3026,10 +3026,10 @@
         <v>2024.0</v>
       </c>
       <c r="C207" t="n" s="2">
-        <v>45334.0</v>
+        <v>45327.0</v>
       </c>
       <c r="D207" t="n">
-        <v>13.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="208">
@@ -3040,10 +3040,10 @@
         <v>2024.0</v>
       </c>
       <c r="C208" t="n" s="2">
-        <v>45341.0</v>
+        <v>45334.0</v>
       </c>
       <c r="D208" t="n">
-        <v>11.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="209">
@@ -3054,10 +3054,10 @@
         <v>2024.0</v>
       </c>
       <c r="C209" t="n" s="2">
-        <v>45348.0</v>
+        <v>45341.0</v>
       </c>
       <c r="D209" t="n">
-        <v>8.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="210">
@@ -3068,10 +3068,10 @@
         <v>2024.0</v>
       </c>
       <c r="C210" t="n" s="2">
-        <v>45355.0</v>
+        <v>45348.0</v>
       </c>
       <c r="D210" t="n">
-        <v>1.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="211">
@@ -3082,10 +3082,10 @@
         <v>2024.0</v>
       </c>
       <c r="C211" t="n" s="2">
-        <v>45362.0</v>
+        <v>45355.0</v>
       </c>
       <c r="D211" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="212">
@@ -3096,10 +3096,10 @@
         <v>2024.0</v>
       </c>
       <c r="C212" t="n" s="2">
-        <v>45369.0</v>
+        <v>45362.0</v>
       </c>
       <c r="D212" t="n">
-        <v>8.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="213">
@@ -3110,10 +3110,10 @@
         <v>2024.0</v>
       </c>
       <c r="C213" t="n" s="2">
-        <v>45376.0</v>
+        <v>45369.0</v>
       </c>
       <c r="D213" t="n">
-        <v>9.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="214">
@@ -3124,10 +3124,10 @@
         <v>2024.0</v>
       </c>
       <c r="C214" t="n" s="2">
-        <v>45383.0</v>
+        <v>45376.0</v>
       </c>
       <c r="D214" t="n">
-        <v>5.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="215">
@@ -3138,10 +3138,10 @@
         <v>2024.0</v>
       </c>
       <c r="C215" t="n" s="2">
-        <v>45390.0</v>
+        <v>45383.0</v>
       </c>
       <c r="D215" t="n">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="216">
@@ -3152,10 +3152,10 @@
         <v>2024.0</v>
       </c>
       <c r="C216" t="n" s="2">
-        <v>45397.0</v>
+        <v>45390.0</v>
       </c>
       <c r="D216" t="n">
-        <v>13.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="217">
@@ -3166,10 +3166,10 @@
         <v>2024.0</v>
       </c>
       <c r="C217" t="n" s="2">
-        <v>45404.0</v>
+        <v>45397.0</v>
       </c>
       <c r="D217" t="n">
-        <v>24.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="218">
@@ -3180,10 +3180,10 @@
         <v>2024.0</v>
       </c>
       <c r="C218" t="n" s="2">
-        <v>45411.0</v>
+        <v>45404.0</v>
       </c>
       <c r="D218" t="n">
-        <v>17.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="219">
@@ -3194,10 +3194,10 @@
         <v>2024.0</v>
       </c>
       <c r="C219" t="n" s="2">
-        <v>45418.0</v>
+        <v>45411.0</v>
       </c>
       <c r="D219" t="n">
-        <v>3.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="220">
@@ -3208,10 +3208,10 @@
         <v>2024.0</v>
       </c>
       <c r="C220" t="n" s="2">
-        <v>45425.0</v>
+        <v>45418.0</v>
       </c>
       <c r="D220" t="n">
-        <v>16.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="221">
@@ -3222,10 +3222,10 @@
         <v>2024.0</v>
       </c>
       <c r="C221" t="n" s="2">
-        <v>45432.0</v>
+        <v>45425.0</v>
       </c>
       <c r="D221" t="n">
-        <v>19.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="222">
@@ -3236,10 +3236,10 @@
         <v>2024.0</v>
       </c>
       <c r="C222" t="n" s="2">
-        <v>45439.0</v>
+        <v>45432.0</v>
       </c>
       <c r="D222" t="n">
-        <v>30.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="223">
@@ -3250,10 +3250,10 @@
         <v>2024.0</v>
       </c>
       <c r="C223" t="n" s="2">
-        <v>45446.0</v>
+        <v>45439.0</v>
       </c>
       <c r="D223" t="n">
-        <v>28.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="224">
@@ -3264,10 +3264,10 @@
         <v>2024.0</v>
       </c>
       <c r="C224" t="n" s="2">
-        <v>45453.0</v>
+        <v>45446.0</v>
       </c>
       <c r="D224" t="n">
-        <v>19.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="225">
@@ -3278,10 +3278,10 @@
         <v>2024.0</v>
       </c>
       <c r="C225" t="n" s="2">
-        <v>45460.0</v>
+        <v>45453.0</v>
       </c>
       <c r="D225" t="n">
-        <v>26.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="226">
@@ -3292,10 +3292,10 @@
         <v>2024.0</v>
       </c>
       <c r="C226" t="n" s="2">
-        <v>45467.0</v>
+        <v>45460.0</v>
       </c>
       <c r="D226" t="n">
-        <v>8.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="227">
@@ -3306,10 +3306,10 @@
         <v>2024.0</v>
       </c>
       <c r="C227" t="n" s="2">
-        <v>45474.0</v>
+        <v>45467.0</v>
       </c>
       <c r="D227" t="n">
-        <v>12.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="228">
@@ -3320,7 +3320,7 @@
         <v>2024.0</v>
       </c>
       <c r="C228" t="n" s="2">
-        <v>45481.0</v>
+        <v>45474.0</v>
       </c>
       <c r="D228" t="n">
         <v>12.0</v>
@@ -3334,10 +3334,10 @@
         <v>2024.0</v>
       </c>
       <c r="C229" t="n" s="2">
-        <v>45488.0</v>
+        <v>45481.0</v>
       </c>
       <c r="D229" t="n">
-        <v>4.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="230">
@@ -3348,10 +3348,10 @@
         <v>2024.0</v>
       </c>
       <c r="C230" t="n" s="2">
-        <v>45495.0</v>
+        <v>45488.0</v>
       </c>
       <c r="D230" t="n">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="231">
@@ -3362,10 +3362,10 @@
         <v>2024.0</v>
       </c>
       <c r="C231" t="n" s="2">
-        <v>45502.0</v>
+        <v>45495.0</v>
       </c>
       <c r="D231" t="n">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="232">
@@ -3376,10 +3376,10 @@
         <v>2024.0</v>
       </c>
       <c r="C232" t="n" s="2">
-        <v>45509.0</v>
+        <v>45502.0</v>
       </c>
       <c r="D232" t="n">
-        <v>2.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="233">
@@ -3390,10 +3390,10 @@
         <v>2024.0</v>
       </c>
       <c r="C233" t="n" s="2">
-        <v>45516.0</v>
+        <v>45509.0</v>
       </c>
       <c r="D233" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="234">
@@ -3404,7 +3404,7 @@
         <v>2024.0</v>
       </c>
       <c r="C234" t="n" s="2">
-        <v>45523.0</v>
+        <v>45516.0</v>
       </c>
       <c r="D234" t="n">
         <v>4.0</v>
@@ -3418,7 +3418,7 @@
         <v>2024.0</v>
       </c>
       <c r="C235" t="n" s="2">
-        <v>45530.0</v>
+        <v>45523.0</v>
       </c>
       <c r="D235" t="n">
         <v>4.0</v>
@@ -3432,7 +3432,7 @@
         <v>2024.0</v>
       </c>
       <c r="C236" t="n" s="2">
-        <v>45537.0</v>
+        <v>45530.0</v>
       </c>
       <c r="D236" t="n">
         <v>4.0</v>
@@ -3446,10 +3446,10 @@
         <v>2024.0</v>
       </c>
       <c r="C237" t="n" s="2">
-        <v>45544.0</v>
+        <v>45537.0</v>
       </c>
       <c r="D237" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="238">
@@ -3460,10 +3460,10 @@
         <v>2024.0</v>
       </c>
       <c r="C238" t="n" s="2">
-        <v>45551.0</v>
+        <v>45544.0</v>
       </c>
       <c r="D238" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="239">
@@ -3474,10 +3474,10 @@
         <v>2024.0</v>
       </c>
       <c r="C239" t="n" s="2">
-        <v>45558.0</v>
+        <v>45551.0</v>
       </c>
       <c r="D239" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="240">
@@ -3488,10 +3488,10 @@
         <v>2024.0</v>
       </c>
       <c r="C240" t="n" s="2">
-        <v>45600.0</v>
+        <v>45558.0</v>
       </c>
       <c r="D240" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="241">
@@ -3502,10 +3502,10 @@
         <v>2024.0</v>
       </c>
       <c r="C241" t="n" s="2">
-        <v>45607.0</v>
+        <v>45600.0</v>
       </c>
       <c r="D241" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="242">
@@ -3516,10 +3516,10 @@
         <v>2024.0</v>
       </c>
       <c r="C242" t="n" s="2">
-        <v>45628.0</v>
+        <v>45607.0</v>
       </c>
       <c r="D242" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="243">
@@ -3530,10 +3530,10 @@
         <v>2024.0</v>
       </c>
       <c r="C243" t="n" s="2">
-        <v>45635.0</v>
+        <v>45628.0</v>
       </c>
       <c r="D243" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="244">
@@ -3544,7 +3544,7 @@
         <v>2024.0</v>
       </c>
       <c r="C244" t="n" s="2">
-        <v>45642.0</v>
+        <v>45635.0</v>
       </c>
       <c r="D244" t="n">
         <v>3.0</v>
@@ -3558,10 +3558,10 @@
         <v>2024.0</v>
       </c>
       <c r="C245" t="n" s="2">
-        <v>45649.0</v>
+        <v>45642.0</v>
       </c>
       <c r="D245" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="246">
@@ -3572,7 +3572,7 @@
         <v>2024.0</v>
       </c>
       <c r="C246" t="n" s="2">
-        <v>45656.0</v>
+        <v>45649.0</v>
       </c>
       <c r="D246" t="n">
         <v>1.0</v>
@@ -3583,13 +3583,13 @@
         <v>5</v>
       </c>
       <c r="B247" t="n">
-        <v>2025.0</v>
+        <v>2024.0</v>
       </c>
       <c r="C247" t="n" s="2">
-        <v>45672.0</v>
+        <v>45656.0</v>
       </c>
       <c r="D247" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="248">
@@ -3600,10 +3600,10 @@
         <v>2025.0</v>
       </c>
       <c r="C248" t="n" s="2">
-        <v>45679.0</v>
+        <v>45672.0</v>
       </c>
       <c r="D248" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="249">
@@ -3614,7 +3614,7 @@
         <v>2025.0</v>
       </c>
       <c r="C249" t="n" s="2">
-        <v>45686.0</v>
+        <v>45679.0</v>
       </c>
       <c r="D249" t="n">
         <v>1.0</v>
@@ -3628,10 +3628,10 @@
         <v>2025.0</v>
       </c>
       <c r="C250" t="n" s="2">
-        <v>45721.0</v>
+        <v>45686.0</v>
       </c>
       <c r="D250" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="251">
@@ -3642,10 +3642,10 @@
         <v>2025.0</v>
       </c>
       <c r="C251" t="n" s="2">
-        <v>45728.0</v>
+        <v>45721.0</v>
       </c>
       <c r="D251" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="252">
@@ -3656,10 +3656,10 @@
         <v>2025.0</v>
       </c>
       <c r="C252" t="n" s="2">
-        <v>45742.0</v>
+        <v>45728.0</v>
       </c>
       <c r="D252" t="n">
-        <v>9.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="253">
@@ -3670,10 +3670,10 @@
         <v>2025.0</v>
       </c>
       <c r="C253" t="n" s="2">
-        <v>45749.0</v>
+        <v>45742.0</v>
       </c>
       <c r="D253" t="n">
-        <v>5.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="254">
@@ -3684,10 +3684,10 @@
         <v>2025.0</v>
       </c>
       <c r="C254" t="n" s="2">
-        <v>45756.0</v>
+        <v>45749.0</v>
       </c>
       <c r="D254" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="255">
@@ -3698,10 +3698,10 @@
         <v>2025.0</v>
       </c>
       <c r="C255" t="n" s="2">
-        <v>45763.0</v>
+        <v>45756.0</v>
       </c>
       <c r="D255" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="256">
@@ -3712,10 +3712,10 @@
         <v>2025.0</v>
       </c>
       <c r="C256" t="n" s="2">
-        <v>45770.0</v>
+        <v>45763.0</v>
       </c>
       <c r="D256" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="257">
@@ -3726,10 +3726,10 @@
         <v>2025.0</v>
       </c>
       <c r="C257" t="n" s="2">
-        <v>45777.0</v>
+        <v>45770.0</v>
       </c>
       <c r="D257" t="n">
-        <v>7.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="258">
@@ -3740,10 +3740,10 @@
         <v>2025.0</v>
       </c>
       <c r="C258" t="n" s="2">
-        <v>45784.0</v>
+        <v>45777.0</v>
       </c>
       <c r="D258" t="n">
-        <v>2.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="259">
@@ -3754,10 +3754,10 @@
         <v>2025.0</v>
       </c>
       <c r="C259" t="n" s="2">
-        <v>45791.0</v>
+        <v>45784.0</v>
       </c>
       <c r="D259" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="260">
@@ -3768,10 +3768,10 @@
         <v>2025.0</v>
       </c>
       <c r="C260" t="n" s="2">
-        <v>45798.0</v>
+        <v>45791.0</v>
       </c>
       <c r="D260" t="n">
-        <v>8.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="261">
@@ -3782,10 +3782,10 @@
         <v>2025.0</v>
       </c>
       <c r="C261" t="n" s="2">
-        <v>45805.0</v>
+        <v>45798.0</v>
       </c>
       <c r="D261" t="n">
-        <v>4.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="262">
@@ -3796,10 +3796,10 @@
         <v>2025.0</v>
       </c>
       <c r="C262" t="n" s="2">
-        <v>45812.0</v>
+        <v>45805.0</v>
       </c>
       <c r="D262" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="263">
@@ -3810,10 +3810,10 @@
         <v>2025.0</v>
       </c>
       <c r="C263" t="n" s="2">
-        <v>45819.0</v>
+        <v>45812.0</v>
       </c>
       <c r="D263" t="n">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="264">
@@ -3824,10 +3824,10 @@
         <v>2025.0</v>
       </c>
       <c r="C264" t="n" s="2">
-        <v>45826.0</v>
+        <v>45819.0</v>
       </c>
       <c r="D264" t="n">
-        <v>13.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="265">
@@ -3838,10 +3838,10 @@
         <v>2025.0</v>
       </c>
       <c r="C265" t="n" s="2">
-        <v>45833.0</v>
+        <v>45826.0</v>
       </c>
       <c r="D265" t="n">
-        <v>1.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="266">
@@ -3852,10 +3852,10 @@
         <v>2025.0</v>
       </c>
       <c r="C266" t="n" s="2">
-        <v>45840.0</v>
+        <v>45833.0</v>
       </c>
       <c r="D266" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="267">
@@ -3866,7 +3866,7 @@
         <v>2025.0</v>
       </c>
       <c r="C267" t="n" s="2">
-        <v>45847.0</v>
+        <v>45840.0</v>
       </c>
       <c r="D267" t="n">
         <v>4.0</v>
@@ -3880,10 +3880,10 @@
         <v>2025.0</v>
       </c>
       <c r="C268" t="n" s="2">
-        <v>45854.0</v>
+        <v>45847.0</v>
       </c>
       <c r="D268" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="269">
@@ -3894,10 +3894,10 @@
         <v>2025.0</v>
       </c>
       <c r="C269" t="n" s="2">
-        <v>45861.0</v>
+        <v>45854.0</v>
       </c>
       <c r="D269" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="270">
@@ -3908,10 +3908,10 @@
         <v>2025.0</v>
       </c>
       <c r="C270" t="n" s="2">
-        <v>45868.0</v>
+        <v>45861.0</v>
       </c>
       <c r="D270" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="271">
@@ -3922,10 +3922,10 @@
         <v>2025.0</v>
       </c>
       <c r="C271" t="n" s="2">
-        <v>45882.0</v>
+        <v>45868.0</v>
       </c>
       <c r="D271" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="272">
@@ -3936,7 +3936,7 @@
         <v>2025.0</v>
       </c>
       <c r="C272" t="n" s="2">
-        <v>45889.0</v>
+        <v>45882.0</v>
       </c>
       <c r="D272" t="n">
         <v>1.0</v>
@@ -3950,10 +3950,10 @@
         <v>2025.0</v>
       </c>
       <c r="C273" t="n" s="2">
-        <v>45896.0</v>
+        <v>45889.0</v>
       </c>
       <c r="D273" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="274">
@@ -3964,7 +3964,7 @@
         <v>2025.0</v>
       </c>
       <c r="C274" t="n" s="2">
-        <v>45903.0</v>
+        <v>45896.0</v>
       </c>
       <c r="D274" t="n">
         <v>3.0</v>
@@ -3978,10 +3978,10 @@
         <v>2025.0</v>
       </c>
       <c r="C275" t="n" s="2">
-        <v>45910.0</v>
+        <v>45903.0</v>
       </c>
       <c r="D275" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="276">
@@ -3992,7 +3992,7 @@
         <v>2025.0</v>
       </c>
       <c r="C276" t="n" s="2">
-        <v>45973.0</v>
+        <v>45910.0</v>
       </c>
       <c r="D276" t="n">
         <v>1.0</v>
@@ -4006,10 +4006,10 @@
         <v>2025.0</v>
       </c>
       <c r="C277" t="n" s="2">
-        <v>45987.0</v>
+        <v>45973.0</v>
       </c>
       <c r="D277" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="278">
@@ -4020,10 +4020,10 @@
         <v>2025.0</v>
       </c>
       <c r="C278" t="n" s="2">
-        <v>45994.0</v>
+        <v>45987.0</v>
       </c>
       <c r="D278" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="279">
@@ -4034,10 +4034,10 @@
         <v>2025.0</v>
       </c>
       <c r="C279" t="n" s="2">
-        <v>46001.0</v>
+        <v>45994.0</v>
       </c>
       <c r="D279" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="280">
@@ -4048,10 +4048,10 @@
         <v>2025.0</v>
       </c>
       <c r="C280" t="n" s="2">
-        <v>46008.0</v>
+        <v>46001.0</v>
       </c>
       <c r="D280" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="281">
@@ -4062,10 +4062,10 @@
         <v>2025.0</v>
       </c>
       <c r="C281" t="n" s="2">
-        <v>46022.0</v>
+        <v>46008.0</v>
       </c>
       <c r="D281" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="282">
@@ -4076,10 +4076,10 @@
         <v>2025.0</v>
       </c>
       <c r="C282" t="n" s="2">
-        <v>46029.0</v>
+        <v>46022.0</v>
       </c>
       <c r="D282" t="n">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="283">
@@ -4087,13 +4087,13 @@
         <v>5</v>
       </c>
       <c r="B283" t="n">
-        <v>2026.0</v>
+        <v>2025.0</v>
       </c>
       <c r="C283" t="n" s="2">
-        <v>46030.0</v>
+        <v>46029.0</v>
       </c>
       <c r="D283" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="284">
@@ -4104,10 +4104,10 @@
         <v>2026.0</v>
       </c>
       <c r="C284" t="n" s="2">
-        <v>46037.0</v>
+        <v>46030.0</v>
       </c>
       <c r="D284" t="n">
-        <v>12.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="285">
@@ -4118,10 +4118,10 @@
         <v>2026.0</v>
       </c>
       <c r="C285" t="n" s="2">
-        <v>46044.0</v>
+        <v>46037.0</v>
       </c>
       <c r="D285" t="n">
-        <v>9.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="286">
@@ -4132,10 +4132,10 @@
         <v>2026.0</v>
       </c>
       <c r="C286" t="n" s="2">
-        <v>46051.0</v>
+        <v>46044.0</v>
       </c>
       <c r="D286" t="n">
-        <v>10.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="287">
@@ -4146,10 +4146,10 @@
         <v>2026.0</v>
       </c>
       <c r="C287" t="n" s="2">
-        <v>46058.0</v>
+        <v>46051.0</v>
       </c>
       <c r="D287" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="288">
@@ -4160,10 +4160,10 @@
         <v>2026.0</v>
       </c>
       <c r="C288" t="n" s="2">
-        <v>46065.0</v>
+        <v>46058.0</v>
       </c>
       <c r="D288" t="n">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="289">
@@ -4174,10 +4174,10 @@
         <v>2026.0</v>
       </c>
       <c r="C289" t="n" s="2">
-        <v>46072.0</v>
+        <v>46065.0</v>
       </c>
       <c r="D289" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="290">
@@ -4188,7 +4188,7 @@
         <v>2026.0</v>
       </c>
       <c r="C290" t="n" s="2">
-        <v>46079.0</v>
+        <v>46072.0</v>
       </c>
       <c r="D290" t="n">
         <v>5.0</v>
@@ -4202,10 +4202,10 @@
         <v>2026.0</v>
       </c>
       <c r="C291" t="n" s="2">
-        <v>46086.0</v>
+        <v>46079.0</v>
       </c>
       <c r="D291" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="292">
@@ -4216,7 +4216,7 @@
         <v>2026.0</v>
       </c>
       <c r="C292" t="n" s="2">
-        <v>46093.0</v>
+        <v>46086.0</v>
       </c>
       <c r="D292" t="n">
         <v>2.0</v>
@@ -4230,10 +4230,10 @@
         <v>2026.0</v>
       </c>
       <c r="C293" t="n" s="2">
-        <v>46100.0</v>
+        <v>46093.0</v>
       </c>
       <c r="D293" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="294">
@@ -4244,10 +4244,10 @@
         <v>2026.0</v>
       </c>
       <c r="C294" t="n" s="2">
-        <v>46107.0</v>
+        <v>46100.0</v>
       </c>
       <c r="D294" t="n">
-        <v>9.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="295">
@@ -4258,10 +4258,10 @@
         <v>2026.0</v>
       </c>
       <c r="C295" t="n" s="2">
-        <v>46114.0</v>
+        <v>46107.0</v>
       </c>
       <c r="D295" t="n">
-        <v>5.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="296">
@@ -4272,10 +4272,10 @@
         <v>2026.0</v>
       </c>
       <c r="C296" t="n" s="2">
-        <v>46121.0</v>
+        <v>46114.0</v>
       </c>
       <c r="D296" t="n">
-        <v>13.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="297">
@@ -4286,10 +4286,10 @@
         <v>2026.0</v>
       </c>
       <c r="C297" t="n" s="2">
-        <v>46128.0</v>
+        <v>46121.0</v>
       </c>
       <c r="D297" t="n">
-        <v>4.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="298">
@@ -4300,7 +4300,7 @@
         <v>2026.0</v>
       </c>
       <c r="C298" t="n" s="2">
-        <v>46135.0</v>
+        <v>46128.0</v>
       </c>
       <c r="D298" t="n">
         <v>4.0</v>
@@ -4314,10 +4314,10 @@
         <v>2026.0</v>
       </c>
       <c r="C299" t="n" s="2">
-        <v>46142.0</v>
+        <v>46135.0</v>
       </c>
       <c r="D299" t="n">
-        <v>7.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="300">
@@ -4328,10 +4328,10 @@
         <v>2026.0</v>
       </c>
       <c r="C300" t="n" s="2">
-        <v>46149.0</v>
+        <v>46142.0</v>
       </c>
       <c r="D300" t="n">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="301">
@@ -4342,10 +4342,10 @@
         <v>2026.0</v>
       </c>
       <c r="C301" t="n" s="2">
-        <v>46156.0</v>
+        <v>46149.0</v>
       </c>
       <c r="D301" t="n">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="302">
@@ -4356,10 +4356,10 @@
         <v>2026.0</v>
       </c>
       <c r="C302" t="n" s="2">
-        <v>46163.0</v>
+        <v>46156.0</v>
       </c>
       <c r="D302" t="n">
-        <v>7.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="303">
@@ -4370,10 +4370,10 @@
         <v>2026.0</v>
       </c>
       <c r="C303" t="n" s="2">
-        <v>46170.0</v>
+        <v>46163.0</v>
       </c>
       <c r="D303" t="n">
-        <v>3.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="304">
@@ -4384,24 +4384,24 @@
         <v>2026.0</v>
       </c>
       <c r="C304" t="n" s="2">
-        <v>46177.0</v>
+        <v>46170.0</v>
       </c>
       <c r="D304" t="n">
-        <v>7.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B305" t="n">
-        <v>2023.0</v>
+        <v>2026.0</v>
       </c>
       <c r="C305" t="n" s="2">
-        <v>45095.0</v>
+        <v>46177.0</v>
       </c>
       <c r="D305" t="n">
-        <v>1.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="306">
@@ -4412,7 +4412,7 @@
         <v>2023.0</v>
       </c>
       <c r="C306" t="n" s="2">
-        <v>45102.0</v>
+        <v>45095.0</v>
       </c>
       <c r="D306" t="n">
         <v>1.0</v>
@@ -4426,7 +4426,7 @@
         <v>2023.0</v>
       </c>
       <c r="C307" t="n" s="2">
-        <v>45158.0</v>
+        <v>45102.0</v>
       </c>
       <c r="D307" t="n">
         <v>1.0</v>
@@ -4440,10 +4440,10 @@
         <v>2023.0</v>
       </c>
       <c r="C308" t="n" s="2">
-        <v>45207.0</v>
+        <v>45158.0</v>
       </c>
       <c r="D308" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="309">
@@ -4454,7 +4454,7 @@
         <v>2023.0</v>
       </c>
       <c r="C309" t="n" s="2">
-        <v>45214.0</v>
+        <v>45207.0</v>
       </c>
       <c r="D309" t="n">
         <v>3.0</v>
@@ -4468,10 +4468,10 @@
         <v>2023.0</v>
       </c>
       <c r="C310" t="n" s="2">
-        <v>45221.0</v>
+        <v>45214.0</v>
       </c>
       <c r="D310" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="311">
@@ -4482,7 +4482,7 @@
         <v>2023.0</v>
       </c>
       <c r="C311" t="n" s="2">
-        <v>45249.0</v>
+        <v>45221.0</v>
       </c>
       <c r="D311" t="n">
         <v>1.0</v>
@@ -4496,10 +4496,10 @@
         <v>2023.0</v>
       </c>
       <c r="C312" t="n" s="2">
-        <v>45256.0</v>
+        <v>45249.0</v>
       </c>
       <c r="D312" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="313">
@@ -4510,10 +4510,10 @@
         <v>2023.0</v>
       </c>
       <c r="C313" t="n" s="2">
-        <v>45263.0</v>
+        <v>45256.0</v>
       </c>
       <c r="D313" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="314">
@@ -4524,10 +4524,10 @@
         <v>2023.0</v>
       </c>
       <c r="C314" t="n" s="2">
-        <v>45270.0</v>
+        <v>45263.0</v>
       </c>
       <c r="D314" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="315">
@@ -4538,10 +4538,10 @@
         <v>2023.0</v>
       </c>
       <c r="C315" t="n" s="2">
-        <v>45277.0</v>
+        <v>45270.0</v>
       </c>
       <c r="D315" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="316">
@@ -4552,10 +4552,10 @@
         <v>2023.0</v>
       </c>
       <c r="C316" t="n" s="2">
-        <v>45284.0</v>
+        <v>45277.0</v>
       </c>
       <c r="D316" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="317">
@@ -4566,10 +4566,10 @@
         <v>2023.0</v>
       </c>
       <c r="C317" t="n" s="2">
-        <v>45291.0</v>
+        <v>45284.0</v>
       </c>
       <c r="D317" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="318">
@@ -4577,13 +4577,13 @@
         <v>6</v>
       </c>
       <c r="B318" t="n">
-        <v>2024.0</v>
+        <v>2023.0</v>
       </c>
       <c r="C318" t="n" s="2">
-        <v>45306.0</v>
+        <v>45291.0</v>
       </c>
       <c r="D318" t="n">
-        <v>7.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="319">
@@ -4594,10 +4594,10 @@
         <v>2024.0</v>
       </c>
       <c r="C319" t="n" s="2">
-        <v>45313.0</v>
+        <v>45306.0</v>
       </c>
       <c r="D319" t="n">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="320">
@@ -4608,10 +4608,10 @@
         <v>2024.0</v>
       </c>
       <c r="C320" t="n" s="2">
-        <v>45320.0</v>
+        <v>45313.0</v>
       </c>
       <c r="D320" t="n">
-        <v>19.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="321">
@@ -4622,10 +4622,10 @@
         <v>2024.0</v>
       </c>
       <c r="C321" t="n" s="2">
-        <v>45327.0</v>
+        <v>45320.0</v>
       </c>
       <c r="D321" t="n">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="322">
@@ -4636,10 +4636,10 @@
         <v>2024.0</v>
       </c>
       <c r="C322" t="n" s="2">
-        <v>45334.0</v>
+        <v>45327.0</v>
       </c>
       <c r="D322" t="n">
-        <v>9.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="323">
@@ -4650,10 +4650,10 @@
         <v>2024.0</v>
       </c>
       <c r="C323" t="n" s="2">
-        <v>45341.0</v>
+        <v>45334.0</v>
       </c>
       <c r="D323" t="n">
-        <v>12.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="324">
@@ -4664,7 +4664,7 @@
         <v>2024.0</v>
       </c>
       <c r="C324" t="n" s="2">
-        <v>45348.0</v>
+        <v>45341.0</v>
       </c>
       <c r="D324" t="n">
         <v>12.0</v>
@@ -4678,10 +4678,10 @@
         <v>2024.0</v>
       </c>
       <c r="C325" t="n" s="2">
-        <v>45355.0</v>
+        <v>45348.0</v>
       </c>
       <c r="D325" t="n">
-        <v>10.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="326">
@@ -4692,10 +4692,10 @@
         <v>2024.0</v>
       </c>
       <c r="C326" t="n" s="2">
-        <v>45362.0</v>
+        <v>45355.0</v>
       </c>
       <c r="D326" t="n">
-        <v>12.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="327">
@@ -4706,10 +4706,10 @@
         <v>2024.0</v>
       </c>
       <c r="C327" t="n" s="2">
-        <v>45369.0</v>
+        <v>45362.0</v>
       </c>
       <c r="D327" t="n">
-        <v>13.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="328">
@@ -4720,10 +4720,10 @@
         <v>2024.0</v>
       </c>
       <c r="C328" t="n" s="2">
-        <v>45376.0</v>
+        <v>45369.0</v>
       </c>
       <c r="D328" t="n">
-        <v>18.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="329">
@@ -4734,10 +4734,10 @@
         <v>2024.0</v>
       </c>
       <c r="C329" t="n" s="2">
-        <v>45383.0</v>
+        <v>45376.0</v>
       </c>
       <c r="D329" t="n">
-        <v>12.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="330">
@@ -4748,10 +4748,10 @@
         <v>2024.0</v>
       </c>
       <c r="C330" t="n" s="2">
-        <v>45390.0</v>
+        <v>45383.0</v>
       </c>
       <c r="D330" t="n">
-        <v>6.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="331">
@@ -4762,10 +4762,10 @@
         <v>2024.0</v>
       </c>
       <c r="C331" t="n" s="2">
-        <v>45397.0</v>
+        <v>45390.0</v>
       </c>
       <c r="D331" t="n">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="332">
@@ -4776,10 +4776,10 @@
         <v>2024.0</v>
       </c>
       <c r="C332" t="n" s="2">
-        <v>45404.0</v>
+        <v>45397.0</v>
       </c>
       <c r="D332" t="n">
-        <v>3.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="333">
@@ -4790,10 +4790,10 @@
         <v>2024.0</v>
       </c>
       <c r="C333" t="n" s="2">
-        <v>45411.0</v>
+        <v>45404.0</v>
       </c>
       <c r="D333" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="334">
@@ -4804,10 +4804,10 @@
         <v>2024.0</v>
       </c>
       <c r="C334" t="n" s="2">
-        <v>45418.0</v>
+        <v>45411.0</v>
       </c>
       <c r="D334" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="335">
@@ -4818,10 +4818,10 @@
         <v>2024.0</v>
       </c>
       <c r="C335" t="n" s="2">
-        <v>45425.0</v>
+        <v>45418.0</v>
       </c>
       <c r="D335" t="n">
-        <v>9.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="336">
@@ -4832,10 +4832,10 @@
         <v>2024.0</v>
       </c>
       <c r="C336" t="n" s="2">
-        <v>45432.0</v>
+        <v>45425.0</v>
       </c>
       <c r="D336" t="n">
-        <v>6.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="337">
@@ -4846,7 +4846,7 @@
         <v>2024.0</v>
       </c>
       <c r="C337" t="n" s="2">
-        <v>45439.0</v>
+        <v>45432.0</v>
       </c>
       <c r="D337" t="n">
         <v>6.0</v>
@@ -4860,10 +4860,10 @@
         <v>2024.0</v>
       </c>
       <c r="C338" t="n" s="2">
-        <v>45446.0</v>
+        <v>45439.0</v>
       </c>
       <c r="D338" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="339">
@@ -4874,10 +4874,10 @@
         <v>2024.0</v>
       </c>
       <c r="C339" t="n" s="2">
-        <v>45453.0</v>
+        <v>45446.0</v>
       </c>
       <c r="D339" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="340">
@@ -4888,7 +4888,7 @@
         <v>2024.0</v>
       </c>
       <c r="C340" t="n" s="2">
-        <v>45460.0</v>
+        <v>45453.0</v>
       </c>
       <c r="D340" t="n">
         <v>4.0</v>
@@ -4902,7 +4902,7 @@
         <v>2024.0</v>
       </c>
       <c r="C341" t="n" s="2">
-        <v>45467.0</v>
+        <v>45460.0</v>
       </c>
       <c r="D341" t="n">
         <v>4.0</v>
@@ -4916,10 +4916,10 @@
         <v>2024.0</v>
       </c>
       <c r="C342" t="n" s="2">
-        <v>45474.0</v>
+        <v>45467.0</v>
       </c>
       <c r="D342" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="343">
@@ -4930,10 +4930,10 @@
         <v>2024.0</v>
       </c>
       <c r="C343" t="n" s="2">
-        <v>45481.0</v>
+        <v>45474.0</v>
       </c>
       <c r="D343" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="344">
@@ -4944,10 +4944,10 @@
         <v>2024.0</v>
       </c>
       <c r="C344" t="n" s="2">
-        <v>45488.0</v>
+        <v>45481.0</v>
       </c>
       <c r="D344" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="345">
@@ -4958,10 +4958,10 @@
         <v>2024.0</v>
       </c>
       <c r="C345" t="n" s="2">
-        <v>45495.0</v>
+        <v>45488.0</v>
       </c>
       <c r="D345" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="346">
@@ -4972,10 +4972,10 @@
         <v>2024.0</v>
       </c>
       <c r="C346" t="n" s="2">
-        <v>45502.0</v>
+        <v>45495.0</v>
       </c>
       <c r="D346" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="347">
@@ -4986,10 +4986,10 @@
         <v>2024.0</v>
       </c>
       <c r="C347" t="n" s="2">
-        <v>45509.0</v>
+        <v>45502.0</v>
       </c>
       <c r="D347" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="348">
@@ -5000,7 +5000,7 @@
         <v>2024.0</v>
       </c>
       <c r="C348" t="n" s="2">
-        <v>45523.0</v>
+        <v>45509.0</v>
       </c>
       <c r="D348" t="n">
         <v>1.0</v>
@@ -5014,7 +5014,7 @@
         <v>2024.0</v>
       </c>
       <c r="C349" t="n" s="2">
-        <v>45551.0</v>
+        <v>45523.0</v>
       </c>
       <c r="D349" t="n">
         <v>1.0</v>
@@ -5028,7 +5028,7 @@
         <v>2024.0</v>
       </c>
       <c r="C350" t="n" s="2">
-        <v>45558.0</v>
+        <v>45551.0</v>
       </c>
       <c r="D350" t="n">
         <v>1.0</v>
@@ -5042,10 +5042,10 @@
         <v>2024.0</v>
       </c>
       <c r="C351" t="n" s="2">
-        <v>45572.0</v>
+        <v>45558.0</v>
       </c>
       <c r="D351" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="352">
@@ -5056,10 +5056,10 @@
         <v>2024.0</v>
       </c>
       <c r="C352" t="n" s="2">
-        <v>45593.0</v>
+        <v>45572.0</v>
       </c>
       <c r="D352" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="353">
@@ -5070,10 +5070,10 @@
         <v>2024.0</v>
       </c>
       <c r="C353" t="n" s="2">
-        <v>45614.0</v>
+        <v>45593.0</v>
       </c>
       <c r="D353" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="354">
@@ -5084,10 +5084,10 @@
         <v>2024.0</v>
       </c>
       <c r="C354" t="n" s="2">
-        <v>45621.0</v>
+        <v>45614.0</v>
       </c>
       <c r="D354" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="355">
@@ -5098,7 +5098,7 @@
         <v>2024.0</v>
       </c>
       <c r="C355" t="n" s="2">
-        <v>45635.0</v>
+        <v>45621.0</v>
       </c>
       <c r="D355" t="n">
         <v>1.0</v>
@@ -5112,7 +5112,7 @@
         <v>2024.0</v>
       </c>
       <c r="C356" t="n" s="2">
-        <v>45649.0</v>
+        <v>45635.0</v>
       </c>
       <c r="D356" t="n">
         <v>1.0</v>
@@ -5123,13 +5123,13 @@
         <v>6</v>
       </c>
       <c r="B357" t="n">
-        <v>2025.0</v>
+        